--- a/review/Olink_Bank_Assist_language_review.xlsx
+++ b/review/Olink_Bank_Assist_language_review.xlsx
@@ -16,8 +16,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1. What the assistant says'!$A$1:$H$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2. What it understands'!$A$1:$E$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3. Buttons customers see'!$A$1:$H$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$H$199</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3. Buttons customers see'!$A$1:$H$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$H$207</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -773,7 +773,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>265 strings in 5 languages</t>
+          <t>275 strings in 5 languages</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5049,8 +5049,84 @@
       </c>
       <c r="H48" s="15" t="inlineStr"/>
     </row>
+    <row r="49" ht="44" customHeight="1">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>Button, label or placeholder in the chat window. Keep it short — it has to fit the same space as the English, on a phone.</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>Today</t>
+        </is>
+      </c>
+      <c r="D49" s="13" t="inlineStr">
+        <is>
+          <t>ዛሬ</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>Har'a</t>
+        </is>
+      </c>
+      <c r="F49" s="13" t="inlineStr">
+        <is>
+          <t>ሎሚ</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>Maanta</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="inlineStr"/>
+    </row>
+    <row r="50" ht="44" customHeight="1">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>yesterday</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>Button, label or placeholder in the chat window. Keep it short — it has to fit the same space as the English, on a phone.</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>Yesterday</t>
+        </is>
+      </c>
+      <c r="D50" s="13" t="inlineStr">
+        <is>
+          <t>ትናንት</t>
+        </is>
+      </c>
+      <c r="E50" s="14" t="inlineStr">
+        <is>
+          <t>Kaleessa</t>
+        </is>
+      </c>
+      <c r="F50" s="13" t="inlineStr">
+        <is>
+          <t>ትማሊ</t>
+        </is>
+      </c>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>Shalay</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H48"/>
+  <autoFilter ref="A1:H50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5061,7 +5137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H199"/>
+  <dimension ref="A1:H207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -12640,8 +12716,312 @@
       </c>
       <c r="H199" s="15" t="inlineStr"/>
     </row>
+    <row r="200" ht="44" customHeight="1">
+      <c r="A200" s="12" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="B200" s="12" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C200" s="12" t="inlineStr">
+        <is>
+          <t>Today</t>
+        </is>
+      </c>
+      <c r="D200" s="13" t="inlineStr">
+        <is>
+          <t>ዛሬ</t>
+        </is>
+      </c>
+      <c r="E200" s="14" t="inlineStr">
+        <is>
+          <t>Har'a</t>
+        </is>
+      </c>
+      <c r="F200" s="13" t="inlineStr">
+        <is>
+          <t>ሎሚ</t>
+        </is>
+      </c>
+      <c r="G200" s="14" t="inlineStr">
+        <is>
+          <t>Maanta</t>
+        </is>
+      </c>
+      <c r="H200" s="15" t="inlineStr"/>
+    </row>
+    <row r="201" ht="44" customHeight="1">
+      <c r="A201" s="12" t="inlineStr">
+        <is>
+          <t>yesterday</t>
+        </is>
+      </c>
+      <c r="B201" s="12" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C201" s="12" t="inlineStr">
+        <is>
+          <t>Yesterday</t>
+        </is>
+      </c>
+      <c r="D201" s="13" t="inlineStr">
+        <is>
+          <t>ትናንት</t>
+        </is>
+      </c>
+      <c r="E201" s="14" t="inlineStr">
+        <is>
+          <t>Kaleessa</t>
+        </is>
+      </c>
+      <c r="F201" s="13" t="inlineStr">
+        <is>
+          <t>ትማሊ</t>
+        </is>
+      </c>
+      <c r="G201" s="14" t="inlineStr">
+        <is>
+          <t>Shalay</t>
+        </is>
+      </c>
+      <c r="H201" s="15" t="inlineStr"/>
+    </row>
+    <row r="202" ht="44" customHeight="1">
+      <c r="A202" s="12" t="inlineStr">
+        <is>
+          <t>earlier_in_conversation</t>
+        </is>
+      </c>
+      <c r="B202" s="12" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C202" s="12" t="inlineStr">
+        <is>
+          <t>Earlier in this conversation</t>
+        </is>
+      </c>
+      <c r="D202" s="13" t="inlineStr">
+        <is>
+          <t>ቀደም ብሎ በዚህ ውይይት</t>
+        </is>
+      </c>
+      <c r="E202" s="14" t="inlineStr">
+        <is>
+          <t>Marii kana keessatti duraan</t>
+        </is>
+      </c>
+      <c r="F202" s="13" t="inlineStr">
+        <is>
+          <t>ኣቐዲሙ ኣብዚ ዝርርብ</t>
+        </is>
+      </c>
+      <c r="G202" s="14" t="inlineStr">
+        <is>
+          <t>Horaantii wadahadalkan</t>
+        </is>
+      </c>
+      <c r="H202" s="15" t="inlineStr"/>
+    </row>
+    <row r="203" ht="44" customHeight="1">
+      <c r="A203" s="12" t="inlineStr">
+        <is>
+          <t>call_started</t>
+        </is>
+      </c>
+      <c r="B203" s="12" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C203" s="12" t="inlineStr">
+        <is>
+          <t>The customer asked for a person here</t>
+        </is>
+      </c>
+      <c r="D203" s="13" t="inlineStr">
+        <is>
+          <t>ደንበኛው እዚህ ላይ ሰው ጠየቀ</t>
+        </is>
+      </c>
+      <c r="E203" s="14" t="inlineStr">
+        <is>
+          <t>Maamilaan asitti nama gaafate</t>
+        </is>
+      </c>
+      <c r="F203" s="13" t="inlineStr">
+        <is>
+          <t>እቲ ዓሚል ኣብዚ ሰብ ሓቲቱ</t>
+        </is>
+      </c>
+      <c r="G203" s="14" t="inlineStr">
+        <is>
+          <t>Macmiilku halkan ayuu qof weydiistay</t>
+        </is>
+      </c>
+      <c r="H203" s="15" t="inlineStr"/>
+    </row>
+    <row r="204" ht="44" customHeight="1">
+      <c r="A204" s="12" t="inlineStr">
+        <is>
+          <t>no_messages</t>
+        </is>
+      </c>
+      <c r="B204" s="12" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C204" s="12" t="inlineStr">
+        <is>
+          <t>No messages in this conversation.</t>
+        </is>
+      </c>
+      <c r="D204" s="13" t="inlineStr">
+        <is>
+          <t>በዚህ ውይይት ውስጥ መልእክት የለም።</t>
+        </is>
+      </c>
+      <c r="E204" s="14" t="inlineStr">
+        <is>
+          <t>Marii kana keessa ergaan hin jiru.</t>
+        </is>
+      </c>
+      <c r="F204" s="13" t="inlineStr">
+        <is>
+          <t>ኣብዚ ዝርርብ መልእኽቲ የለን።</t>
+        </is>
+      </c>
+      <c r="G204" s="14" t="inlineStr">
+        <is>
+          <t>Wadahadalkan fariin kuma jirto.</t>
+        </is>
+      </c>
+      <c r="H204" s="15" t="inlineStr"/>
+    </row>
+    <row r="205" ht="44" customHeight="1">
+      <c r="A205" s="12" t="inlineStr">
+        <is>
+          <t>donut_all_in_one</t>
+        </is>
+      </c>
+      <c r="B205" s="12" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C205" s="12" t="inlineStr">
+        <is>
+          <t>The single {unit} was in {label}.</t>
+        </is>
+      </c>
+      <c r="D205" s="13" t="inlineStr">
+        <is>
+          <t>ብቸኛው {unit} በ{label} ነበር።</t>
+        </is>
+      </c>
+      <c r="E205" s="14" t="inlineStr">
+        <is>
+          <t>{unit} tokkichi {label} keessa ture.</t>
+        </is>
+      </c>
+      <c r="F205" s="13" t="inlineStr">
+        <is>
+          <t>እቲ ሓደ {unit} ብ{label} ነይሩ።</t>
+        </is>
+      </c>
+      <c r="G205" s="14" t="inlineStr">
+        <is>
+          <t>{unit} kaliya wuxuu ku jiray {label}.</t>
+        </is>
+      </c>
+      <c r="H205" s="15" t="inlineStr"/>
+    </row>
+    <row r="206" ht="44" customHeight="1">
+      <c r="A206" s="12" t="inlineStr">
+        <is>
+          <t>channel_all_from_one</t>
+        </is>
+      </c>
+      <c r="B206" s="12" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C206" s="12" t="inlineStr">
+        <is>
+          <t>The single conversation came from {label}.</t>
+        </is>
+      </c>
+      <c r="D206" s="13" t="inlineStr">
+        <is>
+          <t>ብቸኛው ውይይት ከ{label} መጥቷል።</t>
+        </is>
+      </c>
+      <c r="E206" s="14" t="inlineStr">
+        <is>
+          <t>Mariin tokkichi {label} irraa dhufe.</t>
+        </is>
+      </c>
+      <c r="F206" s="13" t="inlineStr">
+        <is>
+          <t>እቲ ሓደ ዝርርብ ካብ {label} መጺኡ።</t>
+        </is>
+      </c>
+      <c r="G206" s="14" t="inlineStr">
+        <is>
+          <t>Wadahadalka kaliya wuxuu ka yimid {label}.</t>
+        </is>
+      </c>
+      <c r="H206" s="15" t="inlineStr"/>
+    </row>
+    <row r="207" ht="44" customHeight="1">
+      <c r="A207" s="12" t="inlineStr">
+        <is>
+          <t>unit_conversation</t>
+        </is>
+      </c>
+      <c r="B207" s="12" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C207" s="12" t="inlineStr">
+        <is>
+          <t>conversation</t>
+        </is>
+      </c>
+      <c r="D207" s="13" t="inlineStr">
+        <is>
+          <t>ውይይት</t>
+        </is>
+      </c>
+      <c r="E207" s="14" t="inlineStr">
+        <is>
+          <t>marii</t>
+        </is>
+      </c>
+      <c r="F207" s="13" t="inlineStr">
+        <is>
+          <t>ዝርርብ</t>
+        </is>
+      </c>
+      <c r="G207" s="14" t="inlineStr">
+        <is>
+          <t>wadahadal</t>
+        </is>
+      </c>
+      <c r="H207" s="15" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H199"/>
+  <autoFilter ref="A1:H207"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/review/Olink_Bank_Assist_language_review.xlsx
+++ b/review/Olink_Bank_Assist_language_review.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1. What the assistant says'!$A$1:$H$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2. What it understands'!$A$1:$E$78</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3. Buttons customers see'!$A$1:$H$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$H$207</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$H$250</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -752,7 +752,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>275 strings in 5 languages</t>
+          <t>318 strings in 5 languages</t>
         </is>
       </c>
     </row>
@@ -5415,7 +5415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H207"/>
+  <dimension ref="A1:H250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7373,7 +7373,7 @@
     <row r="52" ht="44" customHeight="1">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>enter</t>
+          <t>account_question_answered</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
@@ -7383,27 +7383,27 @@
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>Enter</t>
+          <t>Answered a question only the account holder could</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>አስገባ</t>
+          <t>የሂሳቡ ባለቤት ብቻ የሚያውቀውን ጥያቄ መልሷል</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>Galchi</t>
+          <t>Gaaffii abbaan herregaa qofti beeku deebiseera</t>
         </is>
       </c>
       <c r="F52" s="12" t="inlineStr">
         <is>
-          <t>ኣእቱ</t>
+          <t>ዋና እቲ ሕሳብ ጥራይ ዝፈልጦ ሕቶ መሊሱ</t>
         </is>
       </c>
       <c r="G52" s="13" t="inlineStr">
         <is>
-          <t>Geli</t>
+          <t>Wuxuu ka jawaabay su'aal uu keliya og yahay milkiilaha xisaabta</t>
         </is>
       </c>
       <c r="H52" s="14" t="inlineStr"/>
@@ -7411,7 +7411,7 @@
     <row r="53" ht="44" customHeight="1">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>id_seen</t>
+          <t>approved_answers</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
@@ -7421,27 +7421,27 @@
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Saw the Fayda ID</t>
+          <t>Approved answers</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ መታወቂያውን አይቻለሁ</t>
+          <t>የጸደቁ መልሶች</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>Waraqaa eenyummaa Fayda argeera</t>
+          <t>Deebiiwwan mirkanaa'an</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>መንነት ፋይዳ ርእየ</t>
+          <t>ዝጸደቑ መልስታት</t>
         </is>
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
-          <t>Waan arkay aqoonsiga Fayda</t>
+          <t>Jawaabaha la ansixiyay</t>
         </is>
       </c>
       <c r="H53" s="14" t="inlineStr"/>
@@ -7449,7 +7449,7 @@
     <row r="54" ht="44" customHeight="1">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>account_question_answered</t>
+          <t>search_approved_answers</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
@@ -7459,27 +7459,27 @@
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>Answered a question only the account holder could</t>
+          <t>Search the bank's approved answers…</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>የሂሳቡ ባለቤት ብቻ የሚያውቀውን ጥያቄ መልሷል</t>
+          <t>የባንኩን የጸደቁ መልሶች ይፈልጉ…</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>Gaaffii abbaan herregaa qofti beeku deebiseera</t>
+          <t>Deebiiwwan baankichi mirkaneesse barbaadi…</t>
         </is>
       </c>
       <c r="F54" s="12" t="inlineStr">
         <is>
-          <t>ዋና እቲ ሕሳብ ጥራይ ዝፈልጦ ሕቶ መሊሱ</t>
+          <t>ዝጸደቑ መልስታት ባንኪ ድለ…</t>
         </is>
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
-          <t>Wuxuu ka jawaabay su'aal uu keliya og yahay milkiilaha xisaabta</t>
+          <t>Raadi jawaabaha uu bangigu ansixiyay…</t>
         </is>
       </c>
       <c r="H54" s="14" t="inlineStr"/>
@@ -7487,7 +7487,7 @@
     <row r="55" ht="44" customHeight="1">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>approved_answers</t>
+          <t>approved_answers_unavailable</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
@@ -7497,27 +7497,27 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Approved answers</t>
+          <t>Approved answers unavailable.</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>የጸደቁ መልሶች</t>
+          <t>የጸደቁ መልሶች አልተገኙም።</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>Deebiiwwan mirkanaa'an</t>
+          <t>Deebiiwwan mirkanaa'an hin argamne.</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
         <is>
-          <t>ዝጸደቑ መልስታት</t>
+          <t>ዝጸደቑ መልስታት ኣይተረኽቡን።</t>
         </is>
       </c>
       <c r="G55" s="13" t="inlineStr">
         <is>
-          <t>Jawaabaha la ansixiyay</t>
+          <t>Jawaabaha la ansixiyay lama helin.</t>
         </is>
       </c>
       <c r="H55" s="14" t="inlineStr"/>
@@ -7525,7 +7525,7 @@
     <row r="56" ht="44" customHeight="1">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>search_approved_answers</t>
+          <t>no_approved_answers</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
@@ -7535,27 +7535,27 @@
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>Search the bank's approved answers…</t>
+          <t>No approved answers yet.</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>የባንኩን የጸደቁ መልሶች ይፈልጉ…</t>
+          <t>እስካሁን የጸደቀ መልስ የለም።</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>Deebiiwwan baankichi mirkaneesse barbaadi…</t>
+          <t>Ammatti deebiin mirkanaa'e hin jiru.</t>
         </is>
       </c>
       <c r="F56" s="12" t="inlineStr">
         <is>
-          <t>ዝጸደቑ መልስታት ባንኪ ድለ…</t>
+          <t>ክሳብ ሕጂ ዝጸደቐ መልሲ የለን።</t>
         </is>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>Raadi jawaabaha uu bangigu ansixiyay…</t>
+          <t>Weli ma jiraan jawaabo la ansixiyay.</t>
         </is>
       </c>
       <c r="H56" s="14" t="inlineStr"/>
@@ -7563,7 +7563,7 @@
     <row r="57" ht="44" customHeight="1">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>approved_answers_unavailable</t>
+          <t>nothing_matches</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
@@ -7573,27 +7573,27 @@
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Approved answers unavailable.</t>
+          <t>Nothing matches</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>የጸደቁ መልሶች አልተገኙም።</t>
+          <t>ምንም አልተገኘም</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>Deebiiwwan mirkanaa'an hin argamne.</t>
+          <t>Wanti walsimu hin jiru</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
-          <t>ዝጸደቑ መልስታት ኣይተረኽቡን።</t>
+          <t>ዝሰማማዕ የለን</t>
         </is>
       </c>
       <c r="G57" s="13" t="inlineStr">
         <is>
-          <t>Jawaabaha la ansixiyay lama helin.</t>
+          <t>Waxba kuma habboona</t>
         </is>
       </c>
       <c r="H57" s="14" t="inlineStr"/>
@@ -7601,7 +7601,7 @@
     <row r="58" ht="44" customHeight="1">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>no_approved_answers</t>
+          <t>assistant_report</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
@@ -7611,27 +7611,27 @@
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>No approved answers yet.</t>
+          <t>{bank} — assistant report</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>እስካሁን የጸደቀ መልስ የለም።</t>
+          <t>{bank} — የረዳት ሪፖርት</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
-          <t>Ammatti deebiin mirkanaa'e hin jiru.</t>
+          <t>{bank} — gabaasa gargaaraa</t>
         </is>
       </c>
       <c r="F58" s="12" t="inlineStr">
         <is>
-          <t>ክሳብ ሕጂ ዝጸደቐ መልሲ የለን።</t>
+          <t>{bank} — ጸብጻብ ሓጋዚ</t>
         </is>
       </c>
       <c r="G58" s="13" t="inlineStr">
         <is>
-          <t>Weli ma jiraan jawaabo la ansixiyay.</t>
+          <t>{bank} — warbixinta kaaliyaha</t>
         </is>
       </c>
       <c r="H58" s="14" t="inlineStr"/>
@@ -7639,7 +7639,7 @@
     <row r="59" ht="44" customHeight="1">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>nothing_matches</t>
+          <t>last_n_days</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
@@ -7649,27 +7649,27 @@
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Nothing matches</t>
+          <t>Last {n} days</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>ምንም አልተገኘም</t>
+          <t>ያለፉት {n} ቀናት</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>Wanti walsimu hin jiru</t>
+          <t>Guyyoota {n} darban</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>ዝሰማማዕ የለን</t>
+          <t>ዝሓለፉ {n} መዓልታት</t>
         </is>
       </c>
       <c r="G59" s="13" t="inlineStr">
         <is>
-          <t>Waxba kuma habboona</t>
+          <t>{n} maalmood ee la soo dhaafay</t>
         </is>
       </c>
       <c r="H59" s="14" t="inlineStr"/>
@@ -7677,7 +7677,7 @@
     <row r="60" ht="44" customHeight="1">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>assistant_report</t>
+          <t>all_time</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
@@ -7687,27 +7687,27 @@
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>{bank} — assistant report</t>
+          <t>All time</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>{bank} — የረዳት ሪፖርት</t>
+          <t>ሁሉም ጊዜ</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>{bank} — gabaasa gargaaraa</t>
+          <t>Yeroo hunda</t>
         </is>
       </c>
       <c r="F60" s="12" t="inlineStr">
         <is>
-          <t>{bank} — ጸብጻብ ሓጋዚ</t>
+          <t>ኩሉ ግዜ</t>
         </is>
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
-          <t>{bank} — warbixinta kaaliyaha</t>
+          <t>Waqti kasta</t>
         </is>
       </c>
       <c r="H60" s="14" t="inlineStr"/>
@@ -7715,7 +7715,7 @@
     <row r="61" ht="44" customHeight="1">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>last_n_days</t>
+          <t>generated_at</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
@@ -7725,27 +7725,27 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Last {n} days</t>
+          <t>generated {when}</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>ያለፉት {n} ቀናት</t>
+          <t>የተፈጠረው {when}</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>Guyyoota {n} darban</t>
+          <t>kan uumame {when}</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>ዝሓለፉ {n} መዓልታት</t>
+          <t>ዝተፈጥረ {when}</t>
         </is>
       </c>
       <c r="G61" s="13" t="inlineStr">
         <is>
-          <t>{n} maalmood ee la soo dhaafay</t>
+          <t>la sameeyay {when}</t>
         </is>
       </c>
       <c r="H61" s="14" t="inlineStr"/>
@@ -7753,7 +7753,7 @@
     <row r="62" ht="44" customHeight="1">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>all_time</t>
+          <t>days_7</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
@@ -7763,27 +7763,27 @@
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>All time</t>
+          <t>7 days</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>ሁሉም ጊዜ</t>
+          <t>7 ቀናት</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>Yeroo hunda</t>
+          <t>Guyyoota 7</t>
         </is>
       </c>
       <c r="F62" s="12" t="inlineStr">
         <is>
-          <t>ኩሉ ግዜ</t>
+          <t>7 መዓልታት</t>
         </is>
       </c>
       <c r="G62" s="13" t="inlineStr">
         <is>
-          <t>Waqti kasta</t>
+          <t>7 maalmood</t>
         </is>
       </c>
       <c r="H62" s="14" t="inlineStr"/>
@@ -7791,7 +7791,7 @@
     <row r="63" ht="44" customHeight="1">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>generated_at</t>
+          <t>days_30</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
@@ -7801,27 +7801,27 @@
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>generated {when}</t>
+          <t>30 days</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>የተፈጠረው {when}</t>
+          <t>30 ቀናት</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>kan uumame {when}</t>
+          <t>Guyyoota 30</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
         <is>
-          <t>ዝተፈጥረ {when}</t>
+          <t>30 መዓልታት</t>
         </is>
       </c>
       <c r="G63" s="13" t="inlineStr">
         <is>
-          <t>la sameeyay {when}</t>
+          <t>30 maalmood</t>
         </is>
       </c>
       <c r="H63" s="14" t="inlineStr"/>
@@ -7829,7 +7829,7 @@
     <row r="64" ht="44" customHeight="1">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>days_7</t>
+          <t>days_90</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
@@ -7839,27 +7839,27 @@
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>7 days</t>
+          <t>90 days</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>7 ቀናት</t>
+          <t>90 ቀናት</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>Guyyoota 7</t>
+          <t>Guyyoota 90</t>
         </is>
       </c>
       <c r="F64" s="12" t="inlineStr">
         <is>
-          <t>7 መዓልታት</t>
+          <t>90 መዓልታት</t>
         </is>
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
-          <t>7 maalmood</t>
+          <t>90 maalmood</t>
         </is>
       </c>
       <c r="H64" s="14" t="inlineStr"/>
@@ -7867,7 +7867,7 @@
     <row r="65" ht="44" customHeight="1">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>days_30</t>
+          <t>days_all</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
@@ -7877,27 +7877,27 @@
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>30 days</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>30 ቀናት</t>
+          <t>ሁሉም</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
-          <t>Guyyoota 30</t>
+          <t>Hunda</t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
-          <t>30 መዓልታት</t>
+          <t>ኩሉ</t>
         </is>
       </c>
       <c r="G65" s="13" t="inlineStr">
         <is>
-          <t>30 maalmood</t>
+          <t>Dhammaan</t>
         </is>
       </c>
       <c r="H65" s="14" t="inlineStr"/>
@@ -7905,7 +7905,7 @@
     <row r="66" ht="44" customHeight="1">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>days_90</t>
+          <t>export_csv</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
@@ -7915,27 +7915,27 @@
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>90 days</t>
+          <t>Export CSV</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>90 ቀናት</t>
+          <t>CSV አውጣ</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>Guyyoota 90</t>
+          <t>CSV baasi</t>
         </is>
       </c>
       <c r="F66" s="12" t="inlineStr">
         <is>
-          <t>90 መዓልታት</t>
+          <t>CSV ኣውጽእ</t>
         </is>
       </c>
       <c r="G66" s="13" t="inlineStr">
         <is>
-          <t>90 maalmood</t>
+          <t>CSV soo saar</t>
         </is>
       </c>
       <c r="H66" s="14" t="inlineStr"/>
@@ -7943,7 +7943,7 @@
     <row r="67" ht="44" customHeight="1">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>days_all</t>
+          <t>print</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
@@ -7953,27 +7953,27 @@
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Print</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>ሁሉም</t>
+          <t>አትም</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>Hunda</t>
+          <t>Maxxansi</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
         <is>
-          <t>ኩሉ</t>
+          <t>ሕተም</t>
         </is>
       </c>
       <c r="G67" s="13" t="inlineStr">
         <is>
-          <t>Dhammaan</t>
+          <t>Daabac</t>
         </is>
       </c>
       <c r="H67" s="14" t="inlineStr"/>
@@ -7981,7 +7981,7 @@
     <row r="68" ht="44" customHeight="1">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>export_csv</t>
+          <t>good_morning</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
@@ -7991,27 +7991,27 @@
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>Export CSV</t>
+          <t>Good morning</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>CSV አውጣ</t>
+          <t>እንደምን አደሩ</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>CSV baasi</t>
+          <t>Akkam bulte</t>
         </is>
       </c>
       <c r="F68" s="12" t="inlineStr">
         <is>
-          <t>CSV ኣውጽእ</t>
+          <t>ከመይ ሓዲርኩም</t>
         </is>
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
-          <t>CSV soo saar</t>
+          <t>Subax wanaagsan</t>
         </is>
       </c>
       <c r="H68" s="14" t="inlineStr"/>
@@ -8019,7 +8019,7 @@
     <row r="69" ht="44" customHeight="1">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>print</t>
+          <t>good_afternoon</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
@@ -8029,27 +8029,27 @@
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Print</t>
+          <t>Good afternoon</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>አትም</t>
+          <t>እንደምን ዋሉ</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
         <is>
-          <t>Maxxansi</t>
+          <t>Akkam oolte</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
         <is>
-          <t>ሕተም</t>
+          <t>ከመይ ወዓልኩም</t>
         </is>
       </c>
       <c r="G69" s="13" t="inlineStr">
         <is>
-          <t>Daabac</t>
+          <t>Galab wanaagsan</t>
         </is>
       </c>
       <c r="H69" s="14" t="inlineStr"/>
@@ -8057,7 +8057,7 @@
     <row r="70" ht="44" customHeight="1">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>good_morning</t>
+          <t>good_evening</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
@@ -8067,27 +8067,27 @@
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>Good morning</t>
+          <t>Good evening</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>እንደምን አደሩ</t>
+          <t>እንደምን አመሹ</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>Akkam bulte</t>
+          <t>Akkam galgalte</t>
         </is>
       </c>
       <c r="F70" s="12" t="inlineStr">
         <is>
-          <t>ከመይ ሓዲርኩም</t>
+          <t>ከመይ ኣምሰኹም</t>
         </is>
       </c>
       <c r="G70" s="13" t="inlineStr">
         <is>
-          <t>Subax wanaagsan</t>
+          <t>Fiid wanaagsan</t>
         </is>
       </c>
       <c r="H70" s="14" t="inlineStr"/>
@@ -8095,7 +8095,7 @@
     <row r="71" ht="44" customHeight="1">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>good_afternoon</t>
+          <t>escalation_waiting</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
@@ -8105,27 +8105,27 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Good afternoon</t>
+          <t>{n} escalation waiting for someone.</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>እንደምን ዋሉ</t>
+          <t>{n} ጉዳይ ሰው እየጠበቀ ነው።</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>Akkam oolte</t>
+          <t>Dhimmi {n} nama eeggachaa jira.</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
         <is>
-          <t>ከመይ ወዓልኩም</t>
+          <t>{n} ጉዳይ ሰብ ይጽበ ኣሎ።</t>
         </is>
       </c>
       <c r="G71" s="13" t="inlineStr">
         <is>
-          <t>Galab wanaagsan</t>
+          <t>{n} arrin ayaa qof sugaya.</t>
         </is>
       </c>
       <c r="H71" s="14" t="inlineStr"/>
@@ -8133,7 +8133,7 @@
     <row r="72" ht="44" customHeight="1">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>good_evening</t>
+          <t>escalations_waiting</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
@@ -8143,27 +8143,27 @@
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>Good evening</t>
+          <t>{n} escalations waiting for someone.</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>እንደምን አመሹ</t>
+          <t>{n} ጉዳዮች ሰው እየጠበቁ ናቸው።</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>Akkam galgalte</t>
+          <t>Dhimmoonni {n} nama eeggachaa jiru.</t>
         </is>
       </c>
       <c r="F72" s="12" t="inlineStr">
         <is>
-          <t>ከመይ ኣምሰኹም</t>
+          <t>{n} ጉዳያት ሰብ ይጽበዩ ኣለዉ።</t>
         </is>
       </c>
       <c r="G72" s="13" t="inlineStr">
         <is>
-          <t>Fiid wanaagsan</t>
+          <t>{n} arrimood ayaa qof sugaya.</t>
         </is>
       </c>
       <c r="H72" s="14" t="inlineStr"/>
@@ -8171,7 +8171,7 @@
     <row r="73" ht="44" customHeight="1">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>escalation_waiting</t>
+          <t>queue_empty</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
@@ -8181,27 +8181,27 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>{n} escalation waiting for someone.</t>
+          <t>Nothing is waiting in the queue.</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>{n} ጉዳይ ሰው እየጠበቀ ነው።</t>
+          <t>በወረፋ ላይ የሚጠብቅ የለም።</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
         <is>
-          <t>Dhimmi {n} nama eeggachaa jira.</t>
+          <t>Sararaa keessa kan eeggatu hin jiru.</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
-          <t>{n} ጉዳይ ሰብ ይጽበ ኣሎ።</t>
+          <t>ኣብ ሪጋ ዝጽበ የለን።</t>
         </is>
       </c>
       <c r="G73" s="13" t="inlineStr">
         <is>
-          <t>{n} arrin ayaa qof sugaya.</t>
+          <t>Waxba safka kuma jiraan.</t>
         </is>
       </c>
       <c r="H73" s="14" t="inlineStr"/>
@@ -8209,7 +8209,7 @@
     <row r="74" ht="44" customHeight="1">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>escalations_waiting</t>
+          <t>last_n_days_lower</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
@@ -8219,27 +8219,27 @@
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>{n} escalations waiting for someone.</t>
+          <t>last {n} days</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>{n} ጉዳዮች ሰው እየጠበቁ ናቸው።</t>
+          <t>ያለፉት {n} ቀናት</t>
         </is>
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>Dhimmoonni {n} nama eeggachaa jiru.</t>
+          <t>guyyoota {n} darban</t>
         </is>
       </c>
       <c r="F74" s="12" t="inlineStr">
         <is>
-          <t>{n} ጉዳያት ሰብ ይጽበዩ ኣለዉ።</t>
+          <t>ዝሓለፉ {n} መዓልታት</t>
         </is>
       </c>
       <c r="G74" s="13" t="inlineStr">
         <is>
-          <t>{n} arrimood ayaa qof sugaya.</t>
+          <t>{n} maalmood ee la soo dhaafay</t>
         </is>
       </c>
       <c r="H74" s="14" t="inlineStr"/>
@@ -8247,7 +8247,7 @@
     <row r="75" ht="44" customHeight="1">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>queue_empty</t>
+          <t>all_time_lower</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
@@ -8257,27 +8257,27 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Nothing is waiting in the queue.</t>
+          <t>all time</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>በወረፋ ላይ የሚጠብቅ የለም።</t>
+          <t>ሁሉም ጊዜ</t>
         </is>
       </c>
       <c r="E75" s="13" t="inlineStr">
         <is>
-          <t>Sararaa keessa kan eeggatu hin jiru.</t>
+          <t>yeroo hunda</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ሪጋ ዝጽበ የለን።</t>
+          <t>ኩሉ ግዜ</t>
         </is>
       </c>
       <c r="G75" s="13" t="inlineStr">
         <is>
-          <t>Waxba safka kuma jiraan.</t>
+          <t>waqti kasta</t>
         </is>
       </c>
       <c r="H75" s="14" t="inlineStr"/>
@@ -8285,7 +8285,7 @@
     <row r="76" ht="44" customHeight="1">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>last_n_days_lower</t>
+          <t>conversations</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
@@ -8295,27 +8295,27 @@
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>last {n} days</t>
+          <t>Conversations</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>ያለፉት {n} ቀናት</t>
+          <t>ውይይቶች</t>
         </is>
       </c>
       <c r="E76" s="13" t="inlineStr">
         <is>
-          <t>guyyoota {n} darban</t>
+          <t>Marii</t>
         </is>
       </c>
       <c r="F76" s="12" t="inlineStr">
         <is>
-          <t>ዝሓለፉ {n} መዓልታት</t>
+          <t>ዝርርባት</t>
         </is>
       </c>
       <c r="G76" s="13" t="inlineStr">
         <is>
-          <t>{n} maalmood ee la soo dhaafay</t>
+          <t>Wadahadallo</t>
         </is>
       </c>
       <c r="H76" s="14" t="inlineStr"/>
@@ -8323,7 +8323,7 @@
     <row r="77" ht="44" customHeight="1">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>all_time_lower</t>
+          <t>questions_asked</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
@@ -8333,27 +8333,27 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>all time</t>
+          <t>Questions asked</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>ሁሉም ጊዜ</t>
+          <t>የተጠየቁ ጥያቄዎች</t>
         </is>
       </c>
       <c r="E77" s="13" t="inlineStr">
         <is>
-          <t>yeroo hunda</t>
+          <t>Gaaffiiwwan gaafataman</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
-          <t>ኩሉ ግዜ</t>
+          <t>ዝተሓተቱ ሕቶታት</t>
         </is>
       </c>
       <c r="G77" s="13" t="inlineStr">
         <is>
-          <t>waqti kasta</t>
+          <t>Su'aalaha la weydiiyay</t>
         </is>
       </c>
       <c r="H77" s="14" t="inlineStr"/>
@@ -8361,7 +8361,7 @@
     <row r="78" ht="44" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>conversations</t>
+          <t>greetings_excluded</t>
         </is>
       </c>
       <c r="B78" s="11" t="inlineStr">
@@ -8371,27 +8371,27 @@
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>Conversations</t>
+          <t>greetings and thanks excluded</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>ውይይቶች</t>
+          <t>ሰላምታና ምስጋና ሳይካተት</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
         <is>
-          <t>Marii</t>
+          <t>nagaa fi galanni hin dabalamne</t>
         </is>
       </c>
       <c r="F78" s="12" t="inlineStr">
         <is>
-          <t>ዝርርባት</t>
+          <t>ሰላምታን ምስጋናን ከይሓወሰ</t>
         </is>
       </c>
       <c r="G78" s="13" t="inlineStr">
         <is>
-          <t>Wadahadallo</t>
+          <t>salaanta iyo mahadnaqa lagama tirinayo</t>
         </is>
       </c>
       <c r="H78" s="14" t="inlineStr"/>
@@ -8399,7 +8399,7 @@
     <row r="79" ht="44" customHeight="1">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>questions_asked</t>
+          <t>resolved_without_person</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
@@ -8409,27 +8409,27 @@
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Questions asked</t>
+          <t>Resolved without a person</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>የተጠየቁ ጥያቄዎች</t>
+          <t>ያለ ሰው የተፈቱ</t>
         </is>
       </c>
       <c r="E79" s="13" t="inlineStr">
         <is>
-          <t>Gaaffiiwwan gaafataman</t>
+          <t>Nama malee kan furaman</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
-          <t>ዝተሓተቱ ሕቶታት</t>
+          <t>ብዘይ ሰብ ዝተፈትሑ</t>
         </is>
       </c>
       <c r="G79" s="13" t="inlineStr">
         <is>
-          <t>Su'aalaha la weydiiyay</t>
+          <t>Qof la'aan la xalliyay</t>
         </is>
       </c>
       <c r="H79" s="14" t="inlineStr"/>
@@ -8437,7 +8437,7 @@
     <row r="80" ht="44" customHeight="1">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>greetings_excluded</t>
+          <t>no_questions_yet</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
@@ -8447,27 +8447,27 @@
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>greetings and thanks excluded</t>
+          <t>no questions yet</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>ሰላምታና ምስጋና ሳይካተት</t>
+          <t>እስካሁን ጥያቄ የለም</t>
         </is>
       </c>
       <c r="E80" s="13" t="inlineStr">
         <is>
-          <t>nagaa fi galanni hin dabalamne</t>
+          <t>hanga ammaatti gaaffiin hin jiru</t>
         </is>
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
-          <t>ሰላምታን ምስጋናን ከይሓወሰ</t>
+          <t>ክሳብ ሕጂ ሕቶ የለን</t>
         </is>
       </c>
       <c r="G80" s="13" t="inlineStr">
         <is>
-          <t>salaanta iyo mahadnaqa lagama tirinayo</t>
+          <t>weli su'aalo ma jiraan</t>
         </is>
       </c>
       <c r="H80" s="14" t="inlineStr"/>
@@ -8475,7 +8475,7 @@
     <row r="81" ht="44" customHeight="1">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>resolved_without_person</t>
+          <t>answered_own_content</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
@@ -8485,27 +8485,27 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Resolved without a person</t>
+          <t>Answered from your own content</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>ያለ ሰው የተፈቱ</t>
+          <t>ከራስዎ ይዘት የተመለሱ</t>
         </is>
       </c>
       <c r="E81" s="13" t="inlineStr">
         <is>
-          <t>Nama malee kan furaman</t>
+          <t>Qabiyyee keessan irraa kan deebi'an</t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
-          <t>ብዘይ ሰብ ዝተፈትሑ</t>
+          <t>ካብ ናትኩም ትሕዝቶ ዝተመለሱ</t>
         </is>
       </c>
       <c r="G81" s="13" t="inlineStr">
         <is>
-          <t>Qof la'aan la xalliyay</t>
+          <t>Laga jawaabay macluumaadkaaga</t>
         </is>
       </c>
       <c r="H81" s="14" t="inlineStr"/>
@@ -8513,7 +8513,7 @@
     <row r="82" ht="44" customHeight="1">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>no_questions_yet</t>
+          <t>n_of_m</t>
         </is>
       </c>
       <c r="B82" s="11" t="inlineStr">
@@ -8523,27 +8523,27 @@
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>no questions yet</t>
+          <t>{n} of {m}</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>እስካሁን ጥያቄ የለም</t>
+          <t>{n} ከ{m}</t>
         </is>
       </c>
       <c r="E82" s="13" t="inlineStr">
         <is>
-          <t>hanga ammaatti gaaffiin hin jiru</t>
+          <t>{n} kan {m} keessaa</t>
         </is>
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
-          <t>ክሳብ ሕጂ ሕቶ የለን</t>
+          <t>{n} ካብ {m}</t>
         </is>
       </c>
       <c r="G82" s="13" t="inlineStr">
         <is>
-          <t>weli su'aalo ma jiraan</t>
+          <t>{n} ka mid ah {m}</t>
         </is>
       </c>
       <c r="H82" s="14" t="inlineStr"/>
@@ -8551,7 +8551,7 @@
     <row r="83" ht="44" customHeight="1">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>answered_own_content</t>
+          <t>conversations_per_day</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
@@ -8561,27 +8561,27 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Answered from your own content</t>
+          <t>Conversations per day</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>ከራስዎ ይዘት የተመለሱ</t>
+          <t>በቀን ውይይቶች</t>
         </is>
       </c>
       <c r="E83" s="13" t="inlineStr">
         <is>
-          <t>Qabiyyee keessan irraa kan deebi'an</t>
+          <t>Marii guyyaatti</t>
         </is>
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
-          <t>ካብ ናትኩም ትሕዝቶ ዝተመለሱ</t>
+          <t>ኣብ መዓልቲ ዝርርባት</t>
         </is>
       </c>
       <c r="G83" s="13" t="inlineStr">
         <is>
-          <t>Laga jawaabay macluumaadkaaga</t>
+          <t>Wadahadallada maalintii</t>
         </is>
       </c>
       <c r="H83" s="14" t="inlineStr"/>
@@ -8589,7 +8589,7 @@
     <row r="84" ht="44" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>n_of_m</t>
+          <t>escalation_queue</t>
         </is>
       </c>
       <c r="B84" s="11" t="inlineStr">
@@ -8599,27 +8599,27 @@
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>{n} of {m}</t>
+          <t>Escalation queue</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>{n} ከ{m}</t>
+          <t>የማሸጋገሪያ ወረፋ</t>
         </is>
       </c>
       <c r="E84" s="13" t="inlineStr">
         <is>
-          <t>{n} kan {m} keessaa</t>
+          <t>Sararaa dabarsaa</t>
         </is>
       </c>
       <c r="F84" s="12" t="inlineStr">
         <is>
-          <t>{n} ካብ {m}</t>
+          <t>ሪጋ ምትሕልላፍ</t>
         </is>
       </c>
       <c r="G84" s="13" t="inlineStr">
         <is>
-          <t>{n} ka mid ah {m}</t>
+          <t>Safka gudbinta</t>
         </is>
       </c>
       <c r="H84" s="14" t="inlineStr"/>
@@ -8627,7 +8627,7 @@
     <row r="85" ht="44" customHeight="1">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>conversations_per_day</t>
+          <t>open_label</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
@@ -8637,27 +8637,27 @@
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Conversations per day</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>በቀን ውይይቶች</t>
+          <t>ክፍት</t>
         </is>
       </c>
       <c r="E85" s="13" t="inlineStr">
         <is>
-          <t>Marii guyyaatti</t>
+          <t>Banaa</t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መዓልቲ ዝርርባት</t>
+          <t>ክፉት</t>
         </is>
       </c>
       <c r="G85" s="13" t="inlineStr">
         <is>
-          <t>Wadahadallada maalintii</t>
+          <t>Furan</t>
         </is>
       </c>
       <c r="H85" s="14" t="inlineStr"/>
@@ -8665,7 +8665,7 @@
     <row r="86" ht="44" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>escalation_queue</t>
+          <t>closed_label</t>
         </is>
       </c>
       <c r="B86" s="11" t="inlineStr">
@@ -8675,27 +8675,27 @@
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>Escalation queue</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ወረፋ</t>
+          <t>የተዘጋ</t>
         </is>
       </c>
       <c r="E86" s="13" t="inlineStr">
         <is>
-          <t>Sararaa dabarsaa</t>
+          <t>Cufaa</t>
         </is>
       </c>
       <c r="F86" s="12" t="inlineStr">
         <is>
-          <t>ሪጋ ምትሕልላፍ</t>
+          <t>ዕጹው</t>
         </is>
       </c>
       <c r="G86" s="13" t="inlineStr">
         <is>
-          <t>Safka gudbinta</t>
+          <t>Xiran</t>
         </is>
       </c>
       <c r="H86" s="14" t="inlineStr"/>
@@ -8703,7 +8703,7 @@
     <row r="87" ht="44" customHeight="1">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>open_label</t>
+          <t>n_reachable</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
@@ -8713,27 +8713,27 @@
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>{n} reachable</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>ክፍት</t>
+          <t>{n} ሊደረስባቸው የሚችሉ</t>
         </is>
       </c>
       <c r="E87" s="13" t="inlineStr">
         <is>
-          <t>Banaa</t>
+          <t>{n} kan bira gahamu</t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
         <is>
-          <t>ክፉት</t>
+          <t>{n} ክብጻሕዎም ዝኽእሉ</t>
         </is>
       </c>
       <c r="G87" s="13" t="inlineStr">
         <is>
-          <t>Furan</t>
+          <t>{n} la gaari karo</t>
         </is>
       </c>
       <c r="H87" s="14" t="inlineStr"/>
@@ -8741,7 +8741,7 @@
     <row r="88" ht="44" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>closed_label</t>
+          <t>n_no_contact</t>
         </is>
       </c>
       <c r="B88" s="11" t="inlineStr">
@@ -8751,27 +8751,27 @@
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>{n} with no contact details</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>የተዘጋ</t>
+          <t>{n} የመገናኛ መረጃ የሌላቸው</t>
         </is>
       </c>
       <c r="E88" s="13" t="inlineStr">
         <is>
-          <t>Cufaa</t>
+          <t>{n} odeeffannoo quunnamtii hin qabne</t>
         </is>
       </c>
       <c r="F88" s="12" t="inlineStr">
         <is>
-          <t>ዕጹው</t>
+          <t>{n} ሓበሬታ መራኸቢ ዘይብሎም</t>
         </is>
       </c>
       <c r="G88" s="13" t="inlineStr">
         <is>
-          <t>Xiran</t>
+          <t>{n} aan lahayn xogta xiriirka</t>
         </is>
       </c>
       <c r="H88" s="14" t="inlineStr"/>
@@ -8779,7 +8779,7 @@
     <row r="89" ht="44" customHeight="1">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>n_reachable</t>
+          <t>what_happened</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
@@ -8789,27 +8789,27 @@
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>{n} reachable</t>
+          <t>What happened to each question</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>{n} ሊደረስባቸው የሚችሉ</t>
+          <t>ለእያንዳንዱ ጥያቄ ምን ተፈጠረ</t>
         </is>
       </c>
       <c r="E89" s="13" t="inlineStr">
         <is>
-          <t>{n} kan bira gahamu</t>
+          <t>Gaaffii tokkoon tokkoon isaanii maaltu isaan mudate</t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
         <is>
-          <t>{n} ክብጻሕዎም ዝኽእሉ</t>
+          <t>ንነፍስ ወከፍ ሕቶ እንታይ ኮነ</t>
         </is>
       </c>
       <c r="G89" s="13" t="inlineStr">
         <is>
-          <t>{n} la gaari karo</t>
+          <t>Maxaa ku dhacay su'aal kasta</t>
         </is>
       </c>
       <c r="H89" s="14" t="inlineStr"/>
@@ -8817,7 +8817,7 @@
     <row r="90" ht="44" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>n_no_contact</t>
+          <t>also_recorded</t>
         </is>
       </c>
       <c r="B90" s="11" t="inlineStr">
@@ -8827,27 +8827,27 @@
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>{n} with no contact details</t>
+          <t>Also recorded: {items}</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>{n} የመገናኛ መረጃ የሌላቸው</t>
+          <t>እንዲሁም ተመዝግቧል፦ {items}</t>
         </is>
       </c>
       <c r="E90" s="13" t="inlineStr">
         <is>
-          <t>{n} odeeffannoo quunnamtii hin qabne</t>
+          <t>Akkasumas galmaa'e: {items}</t>
         </is>
       </c>
       <c r="F90" s="12" t="inlineStr">
         <is>
-          <t>{n} ሓበሬታ መራኸቢ ዘይብሎም</t>
+          <t>ከምኡ'ውን ተመዝጊቡ፦ {items}</t>
         </is>
       </c>
       <c r="G90" s="13" t="inlineStr">
         <is>
-          <t>{n} aan lahayn xogta xiriirka</t>
+          <t>Sidoo kale waa la diiwaangeliyay: {items}</t>
         </is>
       </c>
       <c r="H90" s="14" t="inlineStr"/>
@@ -8855,7 +8855,7 @@
     <row r="91" ht="44" customHeight="1">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>what_happened</t>
+          <t>unclassified_note</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
@@ -8865,27 +8865,27 @@
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>What happened to each question</t>
+          <t>{n} earlier replies carry no outcome and are not counted above.</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>ለእያንዳንዱ ጥያቄ ምን ተፈጠረ</t>
+          <t>{n} ቀደም ያሉ መልሶች ውጤት የላቸውም፤ ከላይ አልተቆጠሩም።</t>
         </is>
       </c>
       <c r="E91" s="13" t="inlineStr">
         <is>
-          <t>Gaaffii tokkoon tokkoon isaanii maaltu isaan mudate</t>
+          <t>Deebiiwwan {n} kanneen duraa bu'aa hin qaban, olitti hin lakkaa'amne.</t>
         </is>
       </c>
       <c r="F91" s="12" t="inlineStr">
         <is>
-          <t>ንነፍስ ወከፍ ሕቶ እንታይ ኮነ</t>
+          <t>{n} ናይ ቅድሚ ሕጂ መልስታት ውጽኢት የብሎምን፣ ኣብ ላዕሊ ኣይተቖጽሩን።</t>
         </is>
       </c>
       <c r="G91" s="13" t="inlineStr">
         <is>
-          <t>Maxaa ku dhacay su'aal kasta</t>
+          <t>{n} jawaabihii hore natiijo ma laha, korna laguma tirin.</t>
         </is>
       </c>
       <c r="H91" s="14" t="inlineStr"/>
@@ -8893,7 +8893,7 @@
     <row r="92" ht="44" customHeight="1">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>also_recorded</t>
+          <t>most_asked</t>
         </is>
       </c>
       <c r="B92" s="11" t="inlineStr">
@@ -8903,27 +8903,27 @@
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>Also recorded: {items}</t>
+          <t>Most asked</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>እንዲሁም ተመዝግቧል፦ {items}</t>
+          <t>በብዛት የተጠየቁ</t>
         </is>
       </c>
       <c r="E92" s="13" t="inlineStr">
         <is>
-          <t>Akkasumas galmaa'e: {items}</t>
+          <t>Kan baay'inaan gaafataman</t>
         </is>
       </c>
       <c r="F92" s="12" t="inlineStr">
         <is>
-          <t>ከምኡ'ውን ተመዝጊቡ፦ {items}</t>
+          <t>ብብዝሒ ዝተሓተቱ</t>
         </is>
       </c>
       <c r="G92" s="13" t="inlineStr">
         <is>
-          <t>Sidoo kale waa la diiwaangeliyay: {items}</t>
+          <t>Kuwa ugu badan ee la weydiiyay</t>
         </is>
       </c>
       <c r="H92" s="14" t="inlineStr"/>
@@ -8931,7 +8931,7 @@
     <row r="93" ht="44" customHeight="1">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>unclassified_note</t>
+          <t>nothing_asked_yet</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
@@ -8941,27 +8941,27 @@
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>{n} earlier replies carry no outcome and are not counted above.</t>
+          <t>Nothing asked yet in this window.</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>{n} ቀደም ያሉ መልሶች ውጤት የላቸውም፤ ከላይ አልተቆጠሩም።</t>
+          <t>በዚህ ጊዜ ውስጥ የተጠየቀ የለም።</t>
         </is>
       </c>
       <c r="E93" s="13" t="inlineStr">
         <is>
-          <t>Deebiiwwan {n} kanneen duraa bu'aa hin qaban, olitti hin lakkaa'amne.</t>
+          <t>Yeroo kana keessatti wanti gaafatame hin jiru.</t>
         </is>
       </c>
       <c r="F93" s="12" t="inlineStr">
         <is>
-          <t>{n} ናይ ቅድሚ ሕጂ መልስታት ውጽኢት የብሎምን፣ ኣብ ላዕሊ ኣይተቖጽሩን።</t>
+          <t>ኣብዚ እዋን'ዚ ዝተሓተተ የለን።</t>
         </is>
       </c>
       <c r="G93" s="13" t="inlineStr">
         <is>
-          <t>{n} jawaabihii hore natiijo ma laha, korna laguma tirin.</t>
+          <t>Waqtigan waxba lama weydiin.</t>
         </is>
       </c>
       <c r="H93" s="14" t="inlineStr"/>
@@ -8969,7 +8969,7 @@
     <row r="94" ht="44" customHeight="1">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>most_asked</t>
+          <t>grouped_by_wording</t>
         </is>
       </c>
       <c r="B94" s="11" t="inlineStr">
@@ -8979,27 +8979,27 @@
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>Most asked</t>
+          <t>Grouped by wording. Phone numbers and names are removed before grouping.</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
-          <t>በብዛት የተጠየቁ</t>
+          <t>በአገላለጽ የተመደበ። ስልክ ቁጥሮችና ስሞች ከመመደቡ በፊት ይወገዳሉ።</t>
         </is>
       </c>
       <c r="E94" s="13" t="inlineStr">
         <is>
-          <t>Kan baay'inaan gaafataman</t>
+          <t>Jechaan kan ramadame. Lakkoofsi bilbilaa fi maqaan osoo hin ramadamin dura ni haqama.</t>
         </is>
       </c>
       <c r="F94" s="12" t="inlineStr">
         <is>
-          <t>ብብዝሒ ዝተሓተቱ</t>
+          <t>ብኣዘራርባ ዝተጠርነፈ። ቁጽሪ ስልክን ስማትን ቅድሚ ምጥርናፍ ይእለዩ።</t>
         </is>
       </c>
       <c r="G94" s="13" t="inlineStr">
         <is>
-          <t>Kuwa ugu badan ee la weydiiyay</t>
+          <t>Waxaa loo kala saaray erayada. Lambarrada taleefanka iyo magacyada waa la saaraa ka hor.</t>
         </is>
       </c>
       <c r="H94" s="14" t="inlineStr"/>
@@ -9007,7 +9007,7 @@
     <row r="95" ht="44" customHeight="1">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>nothing_asked_yet</t>
+          <t>languages</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
@@ -9017,27 +9017,27 @@
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Nothing asked yet in this window.</t>
+          <t>Languages</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>በዚህ ጊዜ ውስጥ የተጠየቀ የለም።</t>
+          <t>ቋንቋዎች</t>
         </is>
       </c>
       <c r="E95" s="13" t="inlineStr">
         <is>
-          <t>Yeroo kana keessatti wanti gaafatame hin jiru.</t>
+          <t>Afaanota</t>
         </is>
       </c>
       <c r="F95" s="12" t="inlineStr">
         <is>
-          <t>ኣብዚ እዋን'ዚ ዝተሓተተ የለን።</t>
+          <t>ቋንቋታት</t>
         </is>
       </c>
       <c r="G95" s="13" t="inlineStr">
         <is>
-          <t>Waqtigan waxba lama weydiin.</t>
+          <t>Luqadaha</t>
         </is>
       </c>
       <c r="H95" s="14" t="inlineStr"/>
@@ -9045,7 +9045,7 @@
     <row r="96" ht="44" customHeight="1">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>grouped_by_wording</t>
+          <t>unit_conversations</t>
         </is>
       </c>
       <c r="B96" s="11" t="inlineStr">
@@ -9055,27 +9055,27 @@
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>Grouped by wording. Phone numbers and names are removed before grouping.</t>
+          <t>conversations</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>በአገላለጽ የተመደበ። ስልክ ቁጥሮችና ስሞች ከመመደቡ በፊት ይወገዳሉ።</t>
+          <t>ውይይቶች</t>
         </is>
       </c>
       <c r="E96" s="13" t="inlineStr">
         <is>
-          <t>Jechaan kan ramadame. Lakkoofsi bilbilaa fi maqaan osoo hin ramadamin dura ni haqama.</t>
+          <t>marii</t>
         </is>
       </c>
       <c r="F96" s="12" t="inlineStr">
         <is>
-          <t>ብኣዘራርባ ዝተጠርነፈ። ቁጽሪ ስልክን ስማትን ቅድሚ ምጥርናፍ ይእለዩ።</t>
+          <t>ዝርርባት</t>
         </is>
       </c>
       <c r="G96" s="13" t="inlineStr">
         <is>
-          <t>Waxaa loo kala saaray erayada. Lambarrada taleefanka iyo magacyada waa la saaraa ka hor.</t>
+          <t>wadahadallo</t>
         </is>
       </c>
       <c r="H96" s="14" t="inlineStr"/>
@@ -9083,7 +9083,7 @@
     <row r="97" ht="44" customHeight="1">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>languages</t>
+          <t>donut_all_in</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
@@ -9093,27 +9093,27 @@
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Languages</t>
+          <t>All {n} {unit} were in {label}.</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>ቋንቋዎች</t>
+          <t>ሁሉም {n} {unit} በ{label} ነበሩ።</t>
         </is>
       </c>
       <c r="E97" s="13" t="inlineStr">
         <is>
-          <t>Afaanota</t>
+          <t>{unit} {n} hundi {label} keessa turan.</t>
         </is>
       </c>
       <c r="F97" s="12" t="inlineStr">
         <is>
-          <t>ቋንቋታት</t>
+          <t>ኩሎም {n} {unit} ብ{label} ነይሮም።</t>
         </is>
       </c>
       <c r="G97" s="13" t="inlineStr">
         <is>
-          <t>Luqadaha</t>
+          <t>Dhammaan {n} {unit} waxay ku jireen {label}.</t>
         </is>
       </c>
       <c r="H97" s="14" t="inlineStr"/>
@@ -9121,7 +9121,7 @@
     <row r="98" ht="44" customHeight="1">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>unit_conversations</t>
+          <t>conversations_by_language</t>
         </is>
       </c>
       <c r="B98" s="11" t="inlineStr">
@@ -9131,27 +9131,27 @@
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>conversations</t>
+          <t>Conversations by language</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>ውይይቶች</t>
+          <t>በቋንቋ የተከፋፈሉ ውይይቶች</t>
         </is>
       </c>
       <c r="E98" s="13" t="inlineStr">
         <is>
-          <t>marii</t>
+          <t>Marii afaaniin</t>
         </is>
       </c>
       <c r="F98" s="12" t="inlineStr">
         <is>
-          <t>ዝርርባት</t>
+          <t>ዝርርባት ብቋንቋ</t>
         </is>
       </c>
       <c r="G98" s="13" t="inlineStr">
         <is>
-          <t>wadahadallo</t>
+          <t>Wadahadallada luqadda</t>
         </is>
       </c>
       <c r="H98" s="14" t="inlineStr"/>
@@ -9159,7 +9159,7 @@
     <row r="99" ht="44" customHeight="1">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>donut_all_in</t>
+          <t>no_conversations_window</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
@@ -9169,27 +9169,27 @@
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>All {n} {unit} were in {label}.</t>
+          <t>No conversations yet in this window.</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>ሁሉም {n} {unit} በ{label} ነበሩ።</t>
+          <t>በዚህ ጊዜ ውስጥ ውይይት የለም።</t>
         </is>
       </c>
       <c r="E99" s="13" t="inlineStr">
         <is>
-          <t>{unit} {n} hundi {label} keessa turan.</t>
+          <t>Yeroo kana keessatti mariin hin jiru.</t>
         </is>
       </c>
       <c r="F99" s="12" t="inlineStr">
         <is>
-          <t>ኩሎም {n} {unit} ብ{label} ነይሮም።</t>
+          <t>ኣብዚ እዋን'ዚ ዝርርብ የለን።</t>
         </is>
       </c>
       <c r="G99" s="13" t="inlineStr">
         <is>
-          <t>Dhammaan {n} {unit} waxay ku jireen {label}.</t>
+          <t>Waqtigan wadahadal ma jiro.</t>
         </is>
       </c>
       <c r="H99" s="14" t="inlineStr"/>
@@ -9197,7 +9197,7 @@
     <row r="100" ht="44" customHeight="1">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>conversations_by_language</t>
+          <t>recent_activity</t>
         </is>
       </c>
       <c r="B100" s="11" t="inlineStr">
@@ -9207,27 +9207,27 @@
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>Conversations by language</t>
+          <t>Recent activity</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>በቋንቋ የተከፋፈሉ ውይይቶች</t>
+          <t>የቅርብ ጊዜ እንቅስቃሴ</t>
         </is>
       </c>
       <c r="E100" s="13" t="inlineStr">
         <is>
-          <t>Marii afaaniin</t>
+          <t>Sochii dhiyoo</t>
         </is>
       </c>
       <c r="F100" s="12" t="inlineStr">
         <is>
-          <t>ዝርርባት ብቋንቋ</t>
+          <t>ናይ ቀረባ እዋን ንጥፈት</t>
         </is>
       </c>
       <c r="G100" s="13" t="inlineStr">
         <is>
-          <t>Wadahadallada luqadda</t>
+          <t>Dhaqdhaqaaqa dhawaan</t>
         </is>
       </c>
       <c r="H100" s="14" t="inlineStr"/>
@@ -9235,7 +9235,7 @@
     <row r="101" ht="44" customHeight="1">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>no_conversations_window</t>
+          <t>live_preview</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
@@ -9245,27 +9245,27 @@
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>No conversations yet in this window.</t>
+          <t>Live preview</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>በዚህ ጊዜ ውስጥ ውይይት የለም።</t>
+          <t>የቀጥታ ዕይታ</t>
         </is>
       </c>
       <c r="E101" s="13" t="inlineStr">
         <is>
-          <t>Yeroo kana keessatti mariin hin jiru.</t>
+          <t>Mul'ata kallattii</t>
         </is>
       </c>
       <c r="F101" s="12" t="inlineStr">
         <is>
-          <t>ኣብዚ እዋን'ዚ ዝርርብ የለን።</t>
+          <t>ቀጥታ ትርኢት</t>
         </is>
       </c>
       <c r="G101" s="13" t="inlineStr">
         <is>
-          <t>Waqtigan wadahadal ma jiro.</t>
+          <t>Muuqaal toos ah</t>
         </is>
       </c>
       <c r="H101" s="14" t="inlineStr"/>
@@ -9273,7 +9273,7 @@
     <row r="102" ht="44" customHeight="1">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>recent_activity</t>
+          <t>assistant_preview</t>
         </is>
       </c>
       <c r="B102" s="11" t="inlineStr">
@@ -9283,27 +9283,27 @@
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>Recent activity</t>
+          <t>Assistant preview</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
         <is>
-          <t>የቅርብ ጊዜ እንቅስቃሴ</t>
+          <t>የረዳት ዕይታ</t>
         </is>
       </c>
       <c r="E102" s="13" t="inlineStr">
         <is>
-          <t>Sochii dhiyoo</t>
+          <t>Mul'ata gargaaraa</t>
         </is>
       </c>
       <c r="F102" s="12" t="inlineStr">
         <is>
-          <t>ናይ ቀረባ እዋን ንጥፈት</t>
+          <t>ትርኢት ሓጋዚ</t>
         </is>
       </c>
       <c r="G102" s="13" t="inlineStr">
         <is>
-          <t>Dhaqdhaqaaqa dhawaan</t>
+          <t>Muuqaalka kaaliyaha</t>
         </is>
       </c>
       <c r="H102" s="14" t="inlineStr"/>
@@ -9311,7 +9311,7 @@
     <row r="103" ht="44" customHeight="1">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>live_preview</t>
+          <t>preview_caption</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
@@ -9321,27 +9321,27 @@
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Live preview</t>
+          <t>Exactly what a customer sees on your website. Messages sent here are real and appear in Conversations.</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>የቀጥታ ዕይታ</t>
+          <t>ደንበኛ በድረ-ገጽዎ ላይ የሚያየው በትክክል ይህ ነው። እዚህ የሚላኩ መልእክቶች እውነተኛ ናቸው እና በውይይቶች ውስጥ ይታያሉ።</t>
         </is>
       </c>
       <c r="E103" s="13" t="inlineStr">
         <is>
-          <t>Mul'ata kallattii</t>
+          <t>Waanuma maamiltoonni marsariitii keessan irratti argan. Ergaan asitti ergamu dhugaadha, Marii keessattis ni mul'ata.</t>
         </is>
       </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታ ትርኢት</t>
+          <t>ልክዕ ከምቲ ዓሚል ኣብ መርበብ ሓበሬታኹም ዝርእዮ። ኣብዚ ዝለኣኹ መልእኽትታት ናይ ሓቂ ኮይኖም ኣብ ዝርርባት ይረኣዩ።</t>
         </is>
       </c>
       <c r="G103" s="13" t="inlineStr">
         <is>
-          <t>Muuqaal toos ah</t>
+          <t>Waa waxa uu macmiilku ku arko degelkaaga. Fariimaha halkan laga diro waa dhab, waxayna ka muuqdaan Wadahadallada.</t>
         </is>
       </c>
       <c r="H103" s="14" t="inlineStr"/>
@@ -9349,7 +9349,7 @@
     <row r="104" ht="44" customHeight="1">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>assistant_preview</t>
+          <t>n_conversations</t>
         </is>
       </c>
       <c r="B104" s="11" t="inlineStr">
@@ -9359,27 +9359,27 @@
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>Assistant preview</t>
+          <t>{n} conversations</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
         <is>
-          <t>የረዳት ዕይታ</t>
+          <t>{n} ውይይቶች</t>
         </is>
       </c>
       <c r="E104" s="13" t="inlineStr">
         <is>
-          <t>Mul'ata gargaaraa</t>
+          <t>Marii {n}</t>
         </is>
       </c>
       <c r="F104" s="12" t="inlineStr">
         <is>
-          <t>ትርኢት ሓጋዚ</t>
+          <t>{n} ዝርርባት</t>
         </is>
       </c>
       <c r="G104" s="13" t="inlineStr">
         <is>
-          <t>Muuqaalka kaaliyaha</t>
+          <t>{n} wadahadal</t>
         </is>
       </c>
       <c r="H104" s="14" t="inlineStr"/>
@@ -9387,7 +9387,7 @@
     <row r="105" ht="44" customHeight="1">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>preview_caption</t>
+          <t>one_conversation</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
@@ -9397,27 +9397,27 @@
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Exactly what a customer sees on your website. Messages sent here are real and appear in Conversations.</t>
+          <t>{n} conversation</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛ በድረ-ገጽዎ ላይ የሚያየው በትክክል ይህ ነው። እዚህ የሚላኩ መልእክቶች እውነተኛ ናቸው እና በውይይቶች ውስጥ ይታያሉ።</t>
+          <t>{n} ውይይት</t>
         </is>
       </c>
       <c r="E105" s="13" t="inlineStr">
         <is>
-          <t>Waanuma maamiltoonni marsariitii keessan irratti argan. Ergaan asitti ergamu dhugaadha, Marii keessattis ni mul'ata.</t>
+          <t>Marii {n}</t>
         </is>
       </c>
       <c r="F105" s="12" t="inlineStr">
         <is>
-          <t>ልክዕ ከምቲ ዓሚል ኣብ መርበብ ሓበሬታኹም ዝርእዮ። ኣብዚ ዝለኣኹ መልእኽትታት ናይ ሓቂ ኮይኖም ኣብ ዝርርባት ይረኣዩ።</t>
+          <t>{n} ዝርርብ</t>
         </is>
       </c>
       <c r="G105" s="13" t="inlineStr">
         <is>
-          <t>Waa waxa uu macmiilku ku arko degelkaaga. Fariimaha halkan laga diro waa dhab, waxayna ka muuqdaan Wadahadallada.</t>
+          <t>{n} wadahadal</t>
         </is>
       </c>
       <c r="H105" s="14" t="inlineStr"/>
@@ -9425,7 +9425,7 @@
     <row r="106" ht="44" customHeight="1">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>n_conversations</t>
+          <t>outcome_answered</t>
         </is>
       </c>
       <c r="B106" s="11" t="inlineStr">
@@ -9435,27 +9435,27 @@
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>{n} conversations</t>
+          <t>Answered from your content</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
         <is>
-          <t>{n} ውይይቶች</t>
+          <t>ከይዘትዎ የተመለሰ</t>
         </is>
       </c>
       <c r="E106" s="13" t="inlineStr">
         <is>
-          <t>Marii {n}</t>
+          <t>Qabiyyee keessan irraa deebi'e</t>
         </is>
       </c>
       <c r="F106" s="12" t="inlineStr">
         <is>
-          <t>{n} ዝርርባት</t>
+          <t>ካብ ትሕዝቶኹም ዝተመለሰ</t>
         </is>
       </c>
       <c r="G106" s="13" t="inlineStr">
         <is>
-          <t>{n} wadahadal</t>
+          <t>Laga jawaabay macluumaadkaaga</t>
         </is>
       </c>
       <c r="H106" s="14" t="inlineStr"/>
@@ -9463,7 +9463,7 @@
     <row r="107" ht="44" customHeight="1">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>one_conversation</t>
+          <t>outcome_general_guidance</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
@@ -9473,27 +9473,27 @@
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>{n} conversation</t>
+          <t>Answered from general banking knowledge</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>{n} ውይይት</t>
+          <t>ከአጠቃላይ የባንክ እውቀት የተመለሰ</t>
         </is>
       </c>
       <c r="E107" s="13" t="inlineStr">
         <is>
-          <t>Marii {n}</t>
+          <t>Beekumsa baankii waliigalaa irraa deebi'e</t>
         </is>
       </c>
       <c r="F107" s="12" t="inlineStr">
         <is>
-          <t>{n} ዝርርብ</t>
+          <t>ካብ ሓፈሻዊ ፍልጠት ባንክ ዝተመለሰ</t>
         </is>
       </c>
       <c r="G107" s="13" t="inlineStr">
         <is>
-          <t>{n} wadahadal</t>
+          <t>Laga jawaabay aqoonta guud ee bangiga</t>
         </is>
       </c>
       <c r="H107" s="14" t="inlineStr"/>
@@ -9501,7 +9501,7 @@
     <row r="108" ht="44" customHeight="1">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>outcome_answered</t>
+          <t>outcome_unanswered</t>
         </is>
       </c>
       <c r="B108" s="11" t="inlineStr">
@@ -9511,27 +9511,27 @@
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>Answered from your content</t>
+          <t>Could not answer</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>ከይዘትዎ የተመለሰ</t>
+          <t>መልስ ማግኘት አልተቻለም</t>
         </is>
       </c>
       <c r="E108" s="13" t="inlineStr">
         <is>
-          <t>Qabiyyee keessan irraa deebi'e</t>
+          <t>Deebisuu hin dandeenye</t>
         </is>
       </c>
       <c r="F108" s="12" t="inlineStr">
         <is>
-          <t>ካብ ትሕዝቶኹም ዝተመለሰ</t>
+          <t>መልሲ ክርከብ ኣይተኻእለን</t>
         </is>
       </c>
       <c r="G108" s="13" t="inlineStr">
         <is>
-          <t>Laga jawaabay macluumaadkaaga</t>
+          <t>Lama jawaabi karin</t>
         </is>
       </c>
       <c r="H108" s="14" t="inlineStr"/>
@@ -9539,7 +9539,7 @@
     <row r="109" ht="44" customHeight="1">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>outcome_general_guidance</t>
+          <t>outcome_complaint</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
@@ -9549,27 +9549,27 @@
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Answered from general banking knowledge</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>ከአጠቃላይ የባንክ እውቀት የተመለሰ</t>
+          <t>ቅሬታ</t>
         </is>
       </c>
       <c r="E109" s="13" t="inlineStr">
         <is>
-          <t>Beekumsa baankii waliigalaa irraa deebi'e</t>
+          <t>Komii</t>
         </is>
       </c>
       <c r="F109" s="12" t="inlineStr">
         <is>
-          <t>ካብ ሓፈሻዊ ፍልጠት ባንክ ዝተመለሰ</t>
+          <t>ጥርዓን</t>
         </is>
       </c>
       <c r="G109" s="13" t="inlineStr">
         <is>
-          <t>Laga jawaabay aqoonta guud ee bangiga</t>
+          <t>Cabasho</t>
         </is>
       </c>
       <c r="H109" s="14" t="inlineStr"/>
@@ -9577,7 +9577,7 @@
     <row r="110" ht="44" customHeight="1">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>outcome_unanswered</t>
+          <t>outcome_account_blocked</t>
         </is>
       </c>
       <c r="B110" s="11" t="inlineStr">
@@ -9587,27 +9587,27 @@
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>Could not answer</t>
+          <t>Account access problem</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>መልስ ማግኘት አልተቻለም</t>
+          <t>የመለያ መግቢያ ችግር</t>
         </is>
       </c>
       <c r="E110" s="13" t="inlineStr">
         <is>
-          <t>Deebisuu hin dandeenye</t>
+          <t>Rakkoo herrega seenuu</t>
         </is>
       </c>
       <c r="F110" s="12" t="inlineStr">
         <is>
-          <t>መልሲ ክርከብ ኣይተኻእለን</t>
+          <t>ጸገም ኣታውነት ሕሳብ</t>
         </is>
       </c>
       <c r="G110" s="13" t="inlineStr">
         <is>
-          <t>Lama jawaabi karin</t>
+          <t>Dhibaato gelitaanka xisaabta</t>
         </is>
       </c>
       <c r="H110" s="14" t="inlineStr"/>
@@ -9615,7 +9615,7 @@
     <row r="111" ht="44" customHeight="1">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>outcome_complaint</t>
+          <t>outcome_comparison</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
@@ -9625,27 +9625,27 @@
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Compared with another bank</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>ቅሬታ</t>
+          <t>ከሌላ ባንክ ጋር ተነጻጽሯል</t>
         </is>
       </c>
       <c r="E111" s="13" t="inlineStr">
         <is>
-          <t>Komii</t>
+          <t>Baankii biraa waliin walbira qabame</t>
         </is>
       </c>
       <c r="F111" s="12" t="inlineStr">
         <is>
-          <t>ጥርዓን</t>
+          <t>ምስ ካልእ ባንክ ተነጻጺሩ</t>
         </is>
       </c>
       <c r="G111" s="13" t="inlineStr">
         <is>
-          <t>Cabasho</t>
+          <t>Lala barbardhigay bangi kale</t>
         </is>
       </c>
       <c r="H111" s="14" t="inlineStr"/>
@@ -9653,7 +9653,7 @@
     <row r="112" ht="44" customHeight="1">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>outcome_account_blocked</t>
+          <t>outcome_greeting</t>
         </is>
       </c>
       <c r="B112" s="11" t="inlineStr">
@@ -9663,27 +9663,27 @@
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>Account access problem</t>
+          <t>Greeting</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr">
         <is>
-          <t>የመለያ መግቢያ ችግር</t>
+          <t>ሰላምታ</t>
         </is>
       </c>
       <c r="E112" s="13" t="inlineStr">
         <is>
-          <t>Rakkoo herrega seenuu</t>
+          <t>Nagaa</t>
         </is>
       </c>
       <c r="F112" s="12" t="inlineStr">
         <is>
-          <t>ጸገም ኣታውነት ሕሳብ</t>
+          <t>ሰላምታ</t>
         </is>
       </c>
       <c r="G112" s="13" t="inlineStr">
         <is>
-          <t>Dhibaato gelitaanka xisaabta</t>
+          <t>Salaan</t>
         </is>
       </c>
       <c r="H112" s="14" t="inlineStr"/>
@@ -9691,7 +9691,7 @@
     <row r="113" ht="44" customHeight="1">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>outcome_comparison</t>
+          <t>outcome_contact_captured</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
@@ -9701,27 +9701,27 @@
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Compared with another bank</t>
+          <t>Contact details captured</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>ከሌላ ባንክ ጋር ተነጻጽሯል</t>
+          <t>የመገናኛ መረጃ ተመዝግቧል</t>
         </is>
       </c>
       <c r="E113" s="13" t="inlineStr">
         <is>
-          <t>Baankii biraa waliin walbira qabame</t>
+          <t>Odeeffannoon quunnamtii galmaa'e</t>
         </is>
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
-          <t>ምስ ካልእ ባንክ ተነጻጺሩ</t>
+          <t>ሓበሬታ መራኸቢ ተመዝጊቡ</t>
         </is>
       </c>
       <c r="G113" s="13" t="inlineStr">
         <is>
-          <t>Lala barbardhigay bangi kale</t>
+          <t>Xogta xiriirka waa la diiwaangeliyay</t>
         </is>
       </c>
       <c r="H113" s="14" t="inlineStr"/>
@@ -9729,7 +9729,7 @@
     <row r="114" ht="44" customHeight="1">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>outcome_greeting</t>
+          <t>outcome_human_request</t>
         </is>
       </c>
       <c r="B114" s="11" t="inlineStr">
@@ -9739,27 +9739,27 @@
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>Greeting</t>
+          <t>Asked for a person</t>
         </is>
       </c>
       <c r="D114" s="12" t="inlineStr">
         <is>
-          <t>ሰላምታ</t>
+          <t>ሰው ተጠይቋል</t>
         </is>
       </c>
       <c r="E114" s="13" t="inlineStr">
         <is>
-          <t>Nagaa</t>
+          <t>Nama gaafate</t>
         </is>
       </c>
       <c r="F114" s="12" t="inlineStr">
         <is>
-          <t>ሰላምታ</t>
+          <t>ሰብ ተሓቲቱ</t>
         </is>
       </c>
       <c r="G114" s="13" t="inlineStr">
         <is>
-          <t>Salaan</t>
+          <t>Qof ayaa la codsaday</t>
         </is>
       </c>
       <c r="H114" s="14" t="inlineStr"/>
@@ -9767,7 +9767,7 @@
     <row r="115" ht="44" customHeight="1">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>outcome_contact_captured</t>
+          <t>reason_complaint</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
@@ -9777,27 +9777,27 @@
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Contact details captured</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>የመገናኛ መረጃ ተመዝግቧል</t>
+          <t>ቅሬታ</t>
         </is>
       </c>
       <c r="E115" s="13" t="inlineStr">
         <is>
-          <t>Odeeffannoon quunnamtii galmaa'e</t>
+          <t>Komii</t>
         </is>
       </c>
       <c r="F115" s="12" t="inlineStr">
         <is>
-          <t>ሓበሬታ መራኸቢ ተመዝጊቡ</t>
+          <t>ጥርዓን</t>
         </is>
       </c>
       <c r="G115" s="13" t="inlineStr">
         <is>
-          <t>Xogta xiriirka waa la diiwaangeliyay</t>
+          <t>Cabasho</t>
         </is>
       </c>
       <c r="H115" s="14" t="inlineStr"/>
@@ -9805,7 +9805,7 @@
     <row r="116" ht="44" customHeight="1">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>outcome_human_request</t>
+          <t>reason_human_requested</t>
         </is>
       </c>
       <c r="B116" s="11" t="inlineStr">
@@ -9843,7 +9843,7 @@
     <row r="117" ht="44" customHeight="1">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>reason_complaint</t>
+          <t>reason_unanswered_question</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
@@ -9853,27 +9853,27 @@
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>No answer in your content</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>ቅሬታ</t>
+          <t>በይዘትዎ ውስጥ መልስ የለም</t>
         </is>
       </c>
       <c r="E117" s="13" t="inlineStr">
         <is>
-          <t>Komii</t>
+          <t>Qabiyyee keessan keessa deebiin hin jiru</t>
         </is>
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
-          <t>ጥርዓን</t>
+          <t>ኣብ ትሕዝቶኹም መልሲ የለን</t>
         </is>
       </c>
       <c r="G117" s="13" t="inlineStr">
         <is>
-          <t>Cabasho</t>
+          <t>Macluumaadkaaga jawaab kuma jirto</t>
         </is>
       </c>
       <c r="H117" s="14" t="inlineStr"/>
@@ -9881,7 +9881,7 @@
     <row r="118" ht="44" customHeight="1">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>reason_human_requested</t>
+          <t>reason_answered_from_general_knowledge</t>
         </is>
       </c>
       <c r="B118" s="11" t="inlineStr">
@@ -9891,27 +9891,27 @@
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>Asked for a person</t>
+          <t>Answered from general knowledge</t>
         </is>
       </c>
       <c r="D118" s="12" t="inlineStr">
         <is>
-          <t>ሰው ተጠይቋል</t>
+          <t>ከአጠቃላይ እውቀት የተመለሰ</t>
         </is>
       </c>
       <c r="E118" s="13" t="inlineStr">
         <is>
-          <t>Nama gaafate</t>
+          <t>Beekumsa waliigalaa irraa deebi'e</t>
         </is>
       </c>
       <c r="F118" s="12" t="inlineStr">
         <is>
-          <t>ሰብ ተሓቲቱ</t>
+          <t>ካብ ሓፈሻዊ ፍልጠት ዝተመለሰ</t>
         </is>
       </c>
       <c r="G118" s="13" t="inlineStr">
         <is>
-          <t>Qof ayaa la codsaday</t>
+          <t>Laga jawaabay aqoon guud</t>
         </is>
       </c>
       <c r="H118" s="14" t="inlineStr"/>
@@ -9919,7 +9919,7 @@
     <row r="119" ht="44" customHeight="1">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>reason_unanswered_question</t>
+          <t>branding</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
@@ -9929,27 +9929,27 @@
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>No answer in your content</t>
+          <t>Branding</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>በይዘትዎ ውስጥ መልስ የለም</t>
+          <t>የምርት ስም</t>
         </is>
       </c>
       <c r="E119" s="13" t="inlineStr">
         <is>
-          <t>Qabiyyee keessan keessa deebiin hin jiru</t>
+          <t>Mallattoo dhaabbataa</t>
         </is>
       </c>
       <c r="F119" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ትሕዝቶኹም መልሲ የለን</t>
+          <t>ንግዲ ምልክት</t>
         </is>
       </c>
       <c r="G119" s="13" t="inlineStr">
         <is>
-          <t>Macluumaadkaaga jawaab kuma jirto</t>
+          <t>Astaanta</t>
         </is>
       </c>
       <c r="H119" s="14" t="inlineStr"/>
@@ -9957,7 +9957,7 @@
     <row r="120" ht="44" customHeight="1">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>reason_answered_from_general_knowledge</t>
+          <t>branding_help</t>
         </is>
       </c>
       <c r="B120" s="11" t="inlineStr">
@@ -9967,27 +9967,27 @@
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>Answered from general knowledge</t>
+          <t>Your colour and logo, used in this panel and in the chat widget on your website. Saved values apply immediately — no deploy.</t>
         </is>
       </c>
       <c r="D120" s="12" t="inlineStr">
         <is>
-          <t>ከአጠቃላይ እውቀት የተመለሰ</t>
+          <t>በዚህ ፓነልና በድረ-ገጽዎ ላይ ባለው የውይይት መስኮት የሚያገለግሉ ቀለምዎና አርማዎ። የተቀመጡ እሴቶች ወዲያውኑ ተግባራዊ ይሆናሉ — ማሰማራት አያስፈልግም።</t>
         </is>
       </c>
       <c r="E120" s="13" t="inlineStr">
         <is>
-          <t>Beekumsa waliigalaa irraa deebi'e</t>
+          <t>Halluu fi mallattoo keessan, panaalii kana keessattii fi widjetii chat marsariitii keessan irratti kan hojiirra oolu. Gatiin olkaa'ame battalumatti hojiirra oola — bobbaasuun hin barbaachisu.</t>
         </is>
       </c>
       <c r="F120" s="12" t="inlineStr">
         <is>
-          <t>ካብ ሓፈሻዊ ፍልጠት ዝተመለሰ</t>
+          <t>ኣብዚ ፓነልን ኣብ መርበብ ሓበሬታኹም ዘሎ መስኮት ዝርርብን ዝጠቅም ሕብርኹምን ኣርማኹምን። ዝተዓቀቡ ዋጋታት ብቕጽበት ይሰርሑ — ምዝርጋሕ ኣየድልን።</t>
         </is>
       </c>
       <c r="G120" s="13" t="inlineStr">
         <is>
-          <t>Laga jawaabay aqoon guud</t>
+          <t>Midabkaaga iyo astaantaada, oo laga isticmaalo daaqadan iyo widget-ka sheekada degelkaaga. Qiyamka la keydiyay isla markiiba way shaqeeyaan — geyn looma baahna.</t>
         </is>
       </c>
       <c r="H120" s="14" t="inlineStr"/>
@@ -9995,7 +9995,7 @@
     <row r="121" ht="44" customHeight="1">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>branding</t>
+          <t>brand_name</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
@@ -10005,7 +10005,7 @@
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Branding</t>
+          <t>Brand name</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
@@ -10015,17 +10015,17 @@
       </c>
       <c r="E121" s="13" t="inlineStr">
         <is>
-          <t>Mallattoo dhaabbataa</t>
+          <t>Maqaa mallattoo</t>
         </is>
       </c>
       <c r="F121" s="12" t="inlineStr">
         <is>
-          <t>ንግዲ ምልክት</t>
+          <t>ስም ንግዲ ምልክት</t>
         </is>
       </c>
       <c r="G121" s="13" t="inlineStr">
         <is>
-          <t>Astaanta</t>
+          <t>Magaca astaanta</t>
         </is>
       </c>
       <c r="H121" s="14" t="inlineStr"/>
@@ -10033,7 +10033,7 @@
     <row r="122" ht="44" customHeight="1">
       <c r="A122" s="11" t="inlineStr">
         <is>
-          <t>branding_help</t>
+          <t>brand_name_help</t>
         </is>
       </c>
       <c r="B122" s="11" t="inlineStr">
@@ -10043,27 +10043,27 @@
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>Your colour and logo, used in this panel and in the chat widget on your website. Saved values apply immediately — no deploy.</t>
+          <t>What people call you — for example "CBE". Shown in the chat header, this panel and greetings to customers. Leave blank to use your registered name, {legal}, which is kept either way for printed reports.</t>
         </is>
       </c>
       <c r="D122" s="12" t="inlineStr">
         <is>
-          <t>በዚህ ፓነልና በድረ-ገጽዎ ላይ ባለው የውይይት መስኮት የሚያገለግሉ ቀለምዎና አርማዎ። የተቀመጡ እሴቶች ወዲያውኑ ተግባራዊ ይሆናሉ — ማሰማራት አያስፈልግም።</t>
+          <t>ሰዎች የሚጠሩዎት ስም — ለምሳሌ "CBE"። በውይይቱ ራስጌ፣ በዚህ ፓነልና ለደንበኞች በሚቀርብ ሰላምታ ላይ ይታያል። ባዶ ከተውት የተመዘገበው ስምዎ {legal} ይሆናል፤ ለሚታተሙ ሪፖርቶች በሁለቱም መንገድ ይቀመጣል።</t>
         </is>
       </c>
       <c r="E122" s="13" t="inlineStr">
         <is>
-          <t>Halluu fi mallattoo keessan, panaalii kana keessattii fi widjetii chat marsariitii keessan irratti kan hojiirra oolu. Gatiin olkaa'ame battalumatti hojiirra oola — bobbaasuun hin barbaachisu.</t>
+          <t>Maqaa namoonni ittiin isin waaman — fakkeenyaaf "CBE". Mataduree chat, panaalii kanaa fi nagaa maamiltootaaf dhiyaatu irratti ni mul'ata. Duwwaa yoo dhiiftan maqaan galmaa'aa keessan {legal} fayyadama; gabaasa maxxanfamuuf karaa lamaanuu ni qabama.</t>
         </is>
       </c>
       <c r="F122" s="12" t="inlineStr">
         <is>
-          <t>ኣብዚ ፓነልን ኣብ መርበብ ሓበሬታኹም ዘሎ መስኮት ዝርርብን ዝጠቅም ሕብርኹምን ኣርማኹምን። ዝተዓቀቡ ዋጋታት ብቕጽበት ይሰርሑ — ምዝርጋሕ ኣየድልን።</t>
+          <t>ሰባት ዝጽውዑኹም ስም — ንኣብነት "CBE"። ኣብ ርእሲ ዝርርብ፣ ኣብዚ ፓነልን ንዓማዊል ኣብ ዝቐርብ ሰላምታን ይረአ። ባዶ እንተ ገዲፍኩምዎ እቲ ዝተመዝገበ ስምኩም {legal} ይኸውን፤ ንዝሕተሙ ጸብጻባት ብኽልቲኡ መገዲ ይዕቀብ።</t>
         </is>
       </c>
       <c r="G122" s="13" t="inlineStr">
         <is>
-          <t>Midabkaaga iyo astaantaada, oo laga isticmaalo daaqadan iyo widget-ka sheekada degelkaaga. Qiyamka la keydiyay isla markiiba way shaqeeyaan — geyn looma baahna.</t>
+          <t>Waxa dadku kugu yeeraan — tusaale "CBE". Waxay ka muuqataa madaxa sheekada, daaqadan iyo salaanta macaamiisha. Haddii aad banaan ka tagto waxaa la isticmaalayaa magacaaga diiwaangashan, {legal}, oo si kastaba lagu hayo warbixinnada la daabaco.</t>
         </is>
       </c>
       <c r="H122" s="14" t="inlineStr"/>
@@ -10071,7 +10071,7 @@
     <row r="123" ht="44" customHeight="1">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>brand_name</t>
+          <t>brand_colour</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
@@ -10081,27 +10081,27 @@
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Brand name</t>
+          <t>Brand colour</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>የምርት ስም</t>
+          <t>የምርት ቀለም</t>
         </is>
       </c>
       <c r="E123" s="13" t="inlineStr">
         <is>
-          <t>Maqaa mallattoo</t>
+          <t>Halluu mallattoo</t>
         </is>
       </c>
       <c r="F123" s="12" t="inlineStr">
         <is>
-          <t>ስም ንግዲ ምልክት</t>
+          <t>ሕብሪ ንግዲ ምልክት</t>
         </is>
       </c>
       <c r="G123" s="13" t="inlineStr">
         <is>
-          <t>Magaca astaanta</t>
+          <t>Midabka astaanta</t>
         </is>
       </c>
       <c r="H123" s="14" t="inlineStr"/>
@@ -10109,7 +10109,7 @@
     <row r="124" ht="44" customHeight="1">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t>brand_name_help</t>
+          <t>logo_url</t>
         </is>
       </c>
       <c r="B124" s="11" t="inlineStr">
@@ -10119,27 +10119,27 @@
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>What people call you — for example "CBE". Shown in the chat header, this panel and greetings to customers. Leave blank to use your registered name, {legal}, which is kept either way for printed reports.</t>
+          <t>Logo URL (https)</t>
         </is>
       </c>
       <c r="D124" s="12" t="inlineStr">
         <is>
-          <t>ሰዎች የሚጠሩዎት ስም — ለምሳሌ "CBE"። በውይይቱ ራስጌ፣ በዚህ ፓነልና ለደንበኞች በሚቀርብ ሰላምታ ላይ ይታያል። ባዶ ከተውት የተመዘገበው ስምዎ {legal} ይሆናል፤ ለሚታተሙ ሪፖርቶች በሁለቱም መንገድ ይቀመጣል።</t>
+          <t>የአርማ አድራሻ (https)</t>
         </is>
       </c>
       <c r="E124" s="13" t="inlineStr">
         <is>
-          <t>Maqaa namoonni ittiin isin waaman — fakkeenyaaf "CBE". Mataduree chat, panaalii kanaa fi nagaa maamiltootaaf dhiyaatu irratti ni mul'ata. Duwwaa yoo dhiiftan maqaan galmaa'aa keessan {legal} fayyadama; gabaasa maxxanfamuuf karaa lamaanuu ni qabama.</t>
+          <t>Teessoo mallattoo (https)</t>
         </is>
       </c>
       <c r="F124" s="12" t="inlineStr">
         <is>
-          <t>ሰባት ዝጽውዑኹም ስም — ንኣብነት "CBE"። ኣብ ርእሲ ዝርርብ፣ ኣብዚ ፓነልን ንዓማዊል ኣብ ዝቐርብ ሰላምታን ይረአ። ባዶ እንተ ገዲፍኩምዎ እቲ ዝተመዝገበ ስምኩም {legal} ይኸውን፤ ንዝሕተሙ ጸብጻባት ብኽልቲኡ መገዲ ይዕቀብ።</t>
+          <t>ኣድራሻ ኣርማ (https)</t>
         </is>
       </c>
       <c r="G124" s="13" t="inlineStr">
         <is>
-          <t>Waxa dadku kugu yeeraan — tusaale "CBE". Waxay ka muuqataa madaxa sheekada, daaqadan iyo salaanta macaamiisha. Haddii aad banaan ka tagto waxaa la isticmaalayaa magacaaga diiwaangashan, {legal}, oo si kastaba lagu hayo warbixinnada la daabaco.</t>
+          <t>Ciwaanka astaanta (https)</t>
         </is>
       </c>
       <c r="H124" s="14" t="inlineStr"/>
@@ -10147,7 +10147,7 @@
     <row r="125" ht="44" customHeight="1">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>brand_colour</t>
+          <t>seeded_colours_help</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
@@ -10157,27 +10157,27 @@
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Brand colour</t>
+          <t>Seeded colours are our reading of your public site, not your brand book. If it is wrong, this is where to fix it.</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>የምርት ቀለም</t>
+          <t>የቀረቡት ቀለሞች ከይፋዊ ድረ-ገጽዎ የተወሰዱ ግምቶች እንጂ ከምርት መመሪያ መጽሐፍዎ አይደሉም። ስህተት ከሆነ የሚታረመው እዚህ ነው።</t>
         </is>
       </c>
       <c r="E125" s="13" t="inlineStr">
         <is>
-          <t>Halluu mallattoo</t>
+          <t>Halluuwwan durfaman marsariitii keessan ifaa irraa kan dubbifame malee kitaaba mallattoo keessanii irraa miti. Yoo dogoggora ta'e, asitti sirreessaa.</t>
         </is>
       </c>
       <c r="F125" s="12" t="inlineStr">
         <is>
-          <t>ሕብሪ ንግዲ ምልክት</t>
+          <t>እቶም ዝቐረቡ ሕብርታት ካብ ወግዓዊ መርበብ ሓበሬታኹም ዝተወስዱ ግምት እምበር ካብ መጽሓፍ ንግዲ ምልክትኩም ኣይኮኑን። ጌጋ እንተኾይኑ ኣብዚ ይእረም።</t>
         </is>
       </c>
       <c r="G125" s="13" t="inlineStr">
         <is>
-          <t>Midabka astaanta</t>
+          <t>Midabbada la soo bandhigay waa akhrinteenna degelkaaga guud, ma aha buuggaaga astaanta. Haddii ay khalad tahay, halkan ayaa lagu saxaa.</t>
         </is>
       </c>
       <c r="H125" s="14" t="inlineStr"/>
@@ -10185,7 +10185,7 @@
     <row r="126" ht="44" customHeight="1">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>logo_url</t>
+          <t>save_branding</t>
         </is>
       </c>
       <c r="B126" s="11" t="inlineStr">
@@ -10195,27 +10195,27 @@
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>Logo URL (https)</t>
+          <t>Save branding</t>
         </is>
       </c>
       <c r="D126" s="12" t="inlineStr">
         <is>
-          <t>የአርማ አድራሻ (https)</t>
+          <t>የምርት ስም አስቀምጥ</t>
         </is>
       </c>
       <c r="E126" s="13" t="inlineStr">
         <is>
-          <t>Teessoo mallattoo (https)</t>
+          <t>Mallattoo olkaa'i</t>
         </is>
       </c>
       <c r="F126" s="12" t="inlineStr">
         <is>
-          <t>ኣድራሻ ኣርማ (https)</t>
+          <t>ንግዲ ምልክት ኣቐምጥ</t>
         </is>
       </c>
       <c r="G126" s="13" t="inlineStr">
         <is>
-          <t>Ciwaanka astaanta (https)</t>
+          <t>Keydi astaanta</t>
         </is>
       </c>
       <c r="H126" s="14" t="inlineStr"/>
@@ -10223,7 +10223,7 @@
     <row r="127" ht="44" customHeight="1">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>seeded_colours_help</t>
+          <t>branding_saved</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
@@ -10233,27 +10233,27 @@
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>Seeded colours are our reading of your public site, not your brand book. If it is wrong, this is where to fix it.</t>
+          <t>Branding saved</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>የቀረቡት ቀለሞች ከይፋዊ ድረ-ገጽዎ የተወሰዱ ግምቶች እንጂ ከምርት መመሪያ መጽሐፍዎ አይደሉም። ስህተት ከሆነ የሚታረመው እዚህ ነው።</t>
+          <t>የምርት ስም ተቀምጧል</t>
         </is>
       </c>
       <c r="E127" s="13" t="inlineStr">
         <is>
-          <t>Halluuwwan durfaman marsariitii keessan ifaa irraa kan dubbifame malee kitaaba mallattoo keessanii irraa miti. Yoo dogoggora ta'e, asitti sirreessaa.</t>
+          <t>Mallattoon olkaa'ame</t>
         </is>
       </c>
       <c r="F127" s="12" t="inlineStr">
         <is>
-          <t>እቶም ዝቐረቡ ሕብርታት ካብ ወግዓዊ መርበብ ሓበሬታኹም ዝተወስዱ ግምት እምበር ካብ መጽሓፍ ንግዲ ምልክትኩም ኣይኮኑን። ጌጋ እንተኾይኑ ኣብዚ ይእረም።</t>
+          <t>ንግዲ ምልክት ተቐሚጡ</t>
         </is>
       </c>
       <c r="G127" s="13" t="inlineStr">
         <is>
-          <t>Midabbada la soo bandhigay waa akhrinteenna degelkaaga guud, ma aha buuggaaga astaanta. Haddii ay khalad tahay, halkan ayaa lagu saxaa.</t>
+          <t>Astaanta waa la keydiyay</t>
         </is>
       </c>
       <c r="H127" s="14" t="inlineStr"/>
@@ -10261,7 +10261,7 @@
     <row r="128" ht="44" customHeight="1">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t>save_branding</t>
+          <t>escalation_webhook</t>
         </is>
       </c>
       <c r="B128" s="11" t="inlineStr">
@@ -10271,27 +10271,27 @@
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>Save branding</t>
+          <t>Escalation webhook</t>
         </is>
       </c>
       <c r="D128" s="12" t="inlineStr">
         <is>
-          <t>የምርት ስም አስቀምጥ</t>
+          <t>የማሸጋገሪያ ዌብሁክ</t>
         </is>
       </c>
       <c r="E128" s="13" t="inlineStr">
         <is>
-          <t>Mallattoo olkaa'i</t>
+          <t>Webhook dabarsaa</t>
         </is>
       </c>
       <c r="F128" s="12" t="inlineStr">
         <is>
-          <t>ንግዲ ምልክት ኣቐምጥ</t>
+          <t>ዌብሁክ ምትሕልላፍ</t>
         </is>
       </c>
       <c r="G128" s="13" t="inlineStr">
         <is>
-          <t>Keydi astaanta</t>
+          <t>Webhook-ga gudbinta</t>
         </is>
       </c>
       <c r="H128" s="14" t="inlineStr"/>
@@ -10299,7 +10299,7 @@
     <row r="129" ht="44" customHeight="1">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>branding_saved</t>
+          <t>webhook_help</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
@@ -10309,27 +10309,27 @@
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>Branding saved</t>
+          <t>Where escalations are delivered in your contact-centre tool. Requests are signed, so the receiving system can verify they came from us. Clear the field to disconnect.</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>የምርት ስም ተቀምጧል</t>
+          <t>ጉዳዮች በእርስዎ የደንበኞች መገልገያ መሣሪያ ውስጥ የሚደርሱበት ቦታ። ጥያቄዎቹ የተፈረሙ ናቸው፤ ስለዚህ ተቀባዩ ሥርዓት ከእኛ መምጣታቸውን ማረጋገጥ ይችላል። ለማቋረጥ መስኩን ባዶ ያድርጉ።</t>
         </is>
       </c>
       <c r="E129" s="13" t="inlineStr">
         <is>
-          <t>Mallattoon olkaa'ame</t>
+          <t>Iddoo dhimmoonni meeshaa wiirtuu quunnamtii keessan keessatti geessifaman. Gaaffiiwwan mallatteeffamaniiru, kanaafuu sirni fudhatu nurraa dhufuu isaanii mirkaneessuu danda'a. Addaan kutuuf dirree duwwaa godhaa.</t>
         </is>
       </c>
       <c r="F129" s="12" t="inlineStr">
         <is>
-          <t>ንግዲ ምልክት ተቐሚጡ</t>
+          <t>ጉዳያት ኣብ መሳርሒ ማእከል ርክብኩም ዝበጽሑሉ ቦታ። እቶም ሕቶታት ዝተፈረሙ ስለዝኾኑ እቲ ተቐባሊ ስርዓት ካባና ምምጻኦም ከረጋግጽ ይኽእል። ንምቁራጽ እቲ ሜዳ ባዶ ግበሩ።</t>
         </is>
       </c>
       <c r="G129" s="13" t="inlineStr">
         <is>
-          <t>Astaanta waa la keydiyay</t>
+          <t>Halka arrimaha lagu gudbiyo qalabkaaga xarunta macaamiisha. Codsiyada waa la saxeexay, sidaas darteed nidaamka qaataa wuu xaqiijin karaa inay naga yimaadeen. Si aad u gooyso, banaani meesha.</t>
         </is>
       </c>
       <c r="H129" s="14" t="inlineStr"/>
@@ -10337,7 +10337,7 @@
     <row r="130" ht="44" customHeight="1">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t>escalation_webhook</t>
+          <t>signing_secret_set</t>
         </is>
       </c>
       <c r="B130" s="11" t="inlineStr">
@@ -10347,27 +10347,27 @@
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>Escalation webhook</t>
+          <t>A signing secret is set. It cannot be shown again — saving a URL here issues a new one and the old one stops working.</t>
         </is>
       </c>
       <c r="D130" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ዌብሁክ</t>
+          <t>የፊርማ ሚስጥር ተዘጋጅቷል። እንደገና ማሳየት አይቻልም — እዚህ አድራሻ ማስቀመጥ አዲስ ያወጣል፤ አሮጌው መስራት ያቆማል።</t>
         </is>
       </c>
       <c r="E130" s="13" t="inlineStr">
         <is>
-          <t>Webhook dabarsaa</t>
+          <t>Iccitiin mallattoo qophaa'eera. Irra deebi'anii agarsiisuun hin danda'amu — asitti URL olkaa'uun haaraa baasa, kan duraa immoo hojii dhaaba.</t>
         </is>
       </c>
       <c r="F130" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ምትሕልላፍ</t>
+          <t>ምስጢር ፌርማ ተቐሚጡ። መሊስካ ክርአ ኣይክእልን — ኣብዚ ኣድራሻ ምቕማጥ ሓድሽ የውጽእ፣ እቲ ናይ ቀደም ይቋረጽ።</t>
         </is>
       </c>
       <c r="G130" s="13" t="inlineStr">
         <is>
-          <t>Webhook-ga gudbinta</t>
+          <t>Sir saxeex ayaa la dejiyay. Mar kale lama tusi karo — URL halkan lagu keydiyo wuxuu soo saarayaa mid cusub, kii hore wuu shaqo joojiyaa.</t>
         </is>
       </c>
       <c r="H130" s="14" t="inlineStr"/>
@@ -10375,7 +10375,7 @@
     <row r="131" ht="44" customHeight="1">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>webhook_help</t>
+          <t>webhook_connected</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
@@ -10385,27 +10385,27 @@
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>Where escalations are delivered in your contact-centre tool. Requests are signed, so the receiving system can verify they came from us. Clear the field to disconnect.</t>
+          <t>Webhook connected</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>ጉዳዮች በእርስዎ የደንበኞች መገልገያ መሣሪያ ውስጥ የሚደርሱበት ቦታ። ጥያቄዎቹ የተፈረሙ ናቸው፤ ስለዚህ ተቀባዩ ሥርዓት ከእኛ መምጣታቸውን ማረጋገጥ ይችላል። ለማቋረጥ መስኩን ባዶ ያድርጉ።</t>
+          <t>ዌብሁክ ተገናኝቷል</t>
         </is>
       </c>
       <c r="E131" s="13" t="inlineStr">
         <is>
-          <t>Iddoo dhimmoonni meeshaa wiirtuu quunnamtii keessan keessatti geessifaman. Gaaffiiwwan mallatteeffamaniiru, kanaafuu sirni fudhatu nurraa dhufuu isaanii mirkaneessuu danda'a. Addaan kutuuf dirree duwwaa godhaa.</t>
+          <t>Webhook walqunnamsiifame</t>
         </is>
       </c>
       <c r="F131" s="12" t="inlineStr">
         <is>
-          <t>ጉዳያት ኣብ መሳርሒ ማእከል ርክብኩም ዝበጽሑሉ ቦታ። እቶም ሕቶታት ዝተፈረሙ ስለዝኾኑ እቲ ተቐባሊ ስርዓት ካባና ምምጻኦም ከረጋግጽ ይኽእል። ንምቁራጽ እቲ ሜዳ ባዶ ግበሩ።</t>
+          <t>ዌብሁክ ተራኺቡ</t>
         </is>
       </c>
       <c r="G131" s="13" t="inlineStr">
         <is>
-          <t>Halka arrimaha lagu gudbiyo qalabkaaga xarunta macaamiisha. Codsiyada waa la saxeexay, sidaas darteed nidaamka qaataa wuu xaqiijin karaa inay naga yimaadeen. Si aad u gooyso, banaani meesha.</t>
+          <t>Webhook waa la xiray</t>
         </is>
       </c>
       <c r="H131" s="14" t="inlineStr"/>
@@ -10413,7 +10413,7 @@
     <row r="132" ht="44" customHeight="1">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t>signing_secret_set</t>
+          <t>webhook_disconnected</t>
         </is>
       </c>
       <c r="B132" s="11" t="inlineStr">
@@ -10423,27 +10423,27 @@
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>A signing secret is set. It cannot be shown again — saving a URL here issues a new one and the old one stops working.</t>
+          <t>Webhook disconnected</t>
         </is>
       </c>
       <c r="D132" s="12" t="inlineStr">
         <is>
-          <t>የፊርማ ሚስጥር ተዘጋጅቷል። እንደገና ማሳየት አይቻልም — እዚህ አድራሻ ማስቀመጥ አዲስ ያወጣል፤ አሮጌው መስራት ያቆማል።</t>
+          <t>ዌብሁክ ተቋርጧል</t>
         </is>
       </c>
       <c r="E132" s="13" t="inlineStr">
         <is>
-          <t>Iccitiin mallattoo qophaa'eera. Irra deebi'anii agarsiisuun hin danda'amu — asitti URL olkaa'uun haaraa baasa, kan duraa immoo hojii dhaaba.</t>
+          <t>Webhook addaan kutame</t>
         </is>
       </c>
       <c r="F132" s="12" t="inlineStr">
         <is>
-          <t>ምስጢር ፌርማ ተቐሚጡ። መሊስካ ክርአ ኣይክእልን — ኣብዚ ኣድራሻ ምቕማጥ ሓድሽ የውጽእ፣ እቲ ናይ ቀደም ይቋረጽ።</t>
+          <t>ዌብሁክ ተቛሪጹ</t>
         </is>
       </c>
       <c r="G132" s="13" t="inlineStr">
         <is>
-          <t>Sir saxeex ayaa la dejiyay. Mar kale lama tusi karo — URL halkan lagu keydiyo wuxuu soo saarayaa mid cusub, kii hore wuu shaqo joojiyaa.</t>
+          <t>Webhook waa la goynay</t>
         </is>
       </c>
       <c r="H132" s="14" t="inlineStr"/>
@@ -10451,7 +10451,7 @@
     <row r="133" ht="44" customHeight="1">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>webhook_connected</t>
+          <t>your_password</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
@@ -10461,27 +10461,27 @@
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>Webhook connected</t>
+          <t>Your password</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ተገናኝቷል</t>
+          <t>የይለፍ ቃልዎ</t>
         </is>
       </c>
       <c r="E133" s="13" t="inlineStr">
         <is>
-          <t>Webhook walqunnamsiifame</t>
+          <t>Jecha darbii keessan</t>
         </is>
       </c>
       <c r="F133" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ተራኺቡ</t>
+          <t>መሕለፊ ቃልኩም</t>
         </is>
       </c>
       <c r="G133" s="13" t="inlineStr">
         <is>
-          <t>Webhook waa la xiray</t>
+          <t>Furahaaga sirta ah</t>
         </is>
       </c>
       <c r="H133" s="14" t="inlineStr"/>
@@ -10489,7 +10489,7 @@
     <row r="134" ht="44" customHeight="1">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>webhook_disconnected</t>
+          <t>current_password</t>
         </is>
       </c>
       <c r="B134" s="11" t="inlineStr">
@@ -10499,27 +10499,27 @@
       </c>
       <c r="C134" s="11" t="inlineStr">
         <is>
-          <t>Webhook disconnected</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="D134" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ተቋርጧል</t>
+          <t>አሁን ያለው</t>
         </is>
       </c>
       <c r="E134" s="13" t="inlineStr">
         <is>
-          <t>Webhook addaan kutame</t>
+          <t>Kan ammaa</t>
         </is>
       </c>
       <c r="F134" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ተቛሪጹ</t>
+          <t>ናይ ሕጂ</t>
         </is>
       </c>
       <c r="G134" s="13" t="inlineStr">
         <is>
-          <t>Webhook waa la goynay</t>
+          <t>Kan hadda</t>
         </is>
       </c>
       <c r="H134" s="14" t="inlineStr"/>
@@ -10527,7 +10527,7 @@
     <row r="135" ht="44" customHeight="1">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>your_password</t>
+          <t>new_password_12</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
@@ -10537,27 +10537,27 @@
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>Your password</t>
+          <t>New (12+ characters)</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>የይለፍ ቃልዎ</t>
+          <t>አዲስ (12+ ቁምፊዎች)</t>
         </is>
       </c>
       <c r="E135" s="13" t="inlineStr">
         <is>
-          <t>Jecha darbii keessan</t>
+          <t>Haaraa (arfiilee 12+)</t>
         </is>
       </c>
       <c r="F135" s="12" t="inlineStr">
         <is>
-          <t>መሕለፊ ቃልኩም</t>
+          <t>ሓድሽ (12+ ፊደላት)</t>
         </is>
       </c>
       <c r="G135" s="13" t="inlineStr">
         <is>
-          <t>Furahaaga sirta ah</t>
+          <t>Cusub (12+ xaraf)</t>
         </is>
       </c>
       <c r="H135" s="14" t="inlineStr"/>
@@ -10565,7 +10565,7 @@
     <row r="136" ht="44" customHeight="1">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t>current_password</t>
+          <t>password_change_help</t>
         </is>
       </c>
       <c r="B136" s="11" t="inlineStr">
@@ -10575,27 +10575,27 @@
       </c>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Changing it signs out every other browser you are signed in on.</t>
         </is>
       </c>
       <c r="D136" s="12" t="inlineStr">
         <is>
-          <t>አሁን ያለው</t>
+          <t>መቀየር በገቡበት በሌላ በእያንዳንዱ አሳሽ ላይ ያስወጣዎታል።</t>
         </is>
       </c>
       <c r="E136" s="13" t="inlineStr">
         <is>
-          <t>Kan ammaa</t>
+          <t>Jijjiiruun biraawzarii biroo isin keessa seentan hunda irraa isin baasa.</t>
         </is>
       </c>
       <c r="F136" s="12" t="inlineStr">
         <is>
-          <t>ናይ ሕጂ</t>
+          <t>ምቕያሩ ኣብ ካልእ ዝኣተኹምሉ ኩሉ መርበብ መንሸራተቲ የውጽኣኩም።</t>
         </is>
       </c>
       <c r="G136" s="13" t="inlineStr">
         <is>
-          <t>Kan hadda</t>
+          <t>Beddelkeedu wuxuu kaa saarayaa dhammaan browser-yada kale ee aad ku jirto.</t>
         </is>
       </c>
       <c r="H136" s="14" t="inlineStr"/>
@@ -10603,7 +10603,7 @@
     <row r="137" ht="44" customHeight="1">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>new_password_12</t>
+          <t>change_password</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
@@ -10613,27 +10613,27 @@
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>New (12+ characters)</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>አዲስ (12+ ቁምፊዎች)</t>
+          <t>የይለፍ ቃል ቀይር</t>
         </is>
       </c>
       <c r="E137" s="13" t="inlineStr">
         <is>
-          <t>Haaraa (arfiilee 12+)</t>
+          <t>Jecha darbii jijjiiri</t>
         </is>
       </c>
       <c r="F137" s="12" t="inlineStr">
         <is>
-          <t>ሓድሽ (12+ ፊደላት)</t>
+          <t>መሕለፊ ቃል ቀይር</t>
         </is>
       </c>
       <c r="G137" s="13" t="inlineStr">
         <is>
-          <t>Cusub (12+ xaraf)</t>
+          <t>Bedel furaha sirta ah</t>
         </is>
       </c>
       <c r="H137" s="14" t="inlineStr"/>
@@ -10641,7 +10641,7 @@
     <row r="138" ht="44" customHeight="1">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t>password_change_help</t>
+          <t>password_changed</t>
         </is>
       </c>
       <c r="B138" s="11" t="inlineStr">
@@ -10651,27 +10651,27 @@
       </c>
       <c r="C138" s="11" t="inlineStr">
         <is>
-          <t>Changing it signs out every other browser you are signed in on.</t>
+          <t>Password changed. Other sessions were signed out.</t>
         </is>
       </c>
       <c r="D138" s="12" t="inlineStr">
         <is>
-          <t>መቀየር በገቡበት በሌላ በእያንዳንዱ አሳሽ ላይ ያስወጣዎታል።</t>
+          <t>የይለፍ ቃል ተቀይሯል። ሌሎች ክፍለ-ጊዜዎች ወጥተዋል።</t>
         </is>
       </c>
       <c r="E138" s="13" t="inlineStr">
         <is>
-          <t>Jijjiiruun biraawzarii biroo isin keessa seentan hunda irraa isin baasa.</t>
+          <t>Jechi darbii jijjiirameera. Sessionoonni biroo ba'aniiru.</t>
         </is>
       </c>
       <c r="F138" s="12" t="inlineStr">
         <is>
-          <t>ምቕያሩ ኣብ ካልእ ዝኣተኹምሉ ኩሉ መርበብ መንሸራተቲ የውጽኣኩም።</t>
+          <t>መሕለፊ ቃል ተቐዪሩ። ካልኦት ክፍለ-ግዜታት ወጺኦም።</t>
         </is>
       </c>
       <c r="G138" s="13" t="inlineStr">
         <is>
-          <t>Beddelkeedu wuxuu kaa saarayaa dhammaan browser-yada kale ee aad ku jirto.</t>
+          <t>Furaha sirta ah waa la beddelay. Kalfadhiyada kale waa laga saaray.</t>
         </is>
       </c>
       <c r="H138" s="14" t="inlineStr"/>
@@ -10679,7 +10679,7 @@
     <row r="139" ht="44" customHeight="1">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>change_password</t>
+          <t>add_person</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
@@ -10689,27 +10689,27 @@
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>Change password</t>
+          <t>Add person</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>የይለፍ ቃል ቀይር</t>
+          <t>ሰው ጨምር</t>
         </is>
       </c>
       <c r="E139" s="13" t="inlineStr">
         <is>
-          <t>Jecha darbii jijjiiri</t>
+          <t>Nama dabali</t>
         </is>
       </c>
       <c r="F139" s="12" t="inlineStr">
         <is>
-          <t>መሕለፊ ቃል ቀይር</t>
+          <t>ሰብ ወስኽ</t>
         </is>
       </c>
       <c r="G139" s="13" t="inlineStr">
         <is>
-          <t>Bedel furaha sirta ah</t>
+          <t>Ku dar qof</t>
         </is>
       </c>
       <c r="H139" s="14" t="inlineStr"/>
@@ -10717,7 +10717,7 @@
     <row r="140" ht="44" customHeight="1">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t>password_changed</t>
+          <t>n_accounts</t>
         </is>
       </c>
       <c r="B140" s="11" t="inlineStr">
@@ -10727,27 +10727,27 @@
       </c>
       <c r="C140" s="11" t="inlineStr">
         <is>
-          <t>Password changed. Other sessions were signed out.</t>
+          <t>{n} accounts</t>
         </is>
       </c>
       <c r="D140" s="12" t="inlineStr">
         <is>
-          <t>የይለፍ ቃል ተቀይሯል። ሌሎች ክፍለ-ጊዜዎች ወጥተዋል።</t>
+          <t>{n} መለያዎች</t>
         </is>
       </c>
       <c r="E140" s="13" t="inlineStr">
         <is>
-          <t>Jechi darbii jijjiirameera. Sessionoonni biroo ba'aniiru.</t>
+          <t>Herregoota {n}</t>
         </is>
       </c>
       <c r="F140" s="12" t="inlineStr">
         <is>
-          <t>መሕለፊ ቃል ተቐዪሩ። ካልኦት ክፍለ-ግዜታት ወጺኦም።</t>
+          <t>{n} ሕሳባት</t>
         </is>
       </c>
       <c r="G140" s="13" t="inlineStr">
         <is>
-          <t>Furaha sirta ah waa la beddelay. Kalfadhiyada kale waa laga saaray.</t>
+          <t>{n} xisaabood</t>
         </is>
       </c>
       <c r="H140" s="14" t="inlineStr"/>
@@ -10755,7 +10755,7 @@
     <row r="141" ht="44" customHeight="1">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>add_person</t>
+          <t>one_account</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
@@ -10765,27 +10765,27 @@
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>Add person</t>
+          <t>{n} account</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>ሰው ጨምር</t>
+          <t>{n} መለያ</t>
         </is>
       </c>
       <c r="E141" s="13" t="inlineStr">
         <is>
-          <t>Nama dabali</t>
+          <t>Herrega {n}</t>
         </is>
       </c>
       <c r="F141" s="12" t="inlineStr">
         <is>
-          <t>ሰብ ወስኽ</t>
+          <t>{n} ሕሳብ</t>
         </is>
       </c>
       <c r="G141" s="13" t="inlineStr">
         <is>
-          <t>Ku dar qof</t>
+          <t>{n} xisaab</t>
         </is>
       </c>
       <c r="H141" s="14" t="inlineStr"/>
@@ -10793,7 +10793,7 @@
     <row r="142" ht="44" customHeight="1">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t>n_accounts</t>
+          <t>person</t>
         </is>
       </c>
       <c r="B142" s="11" t="inlineStr">
@@ -10803,27 +10803,27 @@
       </c>
       <c r="C142" s="11" t="inlineStr">
         <is>
-          <t>{n} accounts</t>
+          <t>Person</t>
         </is>
       </c>
       <c r="D142" s="12" t="inlineStr">
         <is>
-          <t>{n} መለያዎች</t>
+          <t>ሰው</t>
         </is>
       </c>
       <c r="E142" s="13" t="inlineStr">
         <is>
-          <t>Herregoota {n}</t>
+          <t>Nama</t>
         </is>
       </c>
       <c r="F142" s="12" t="inlineStr">
         <is>
-          <t>{n} ሕሳባት</t>
+          <t>ሰብ</t>
         </is>
       </c>
       <c r="G142" s="13" t="inlineStr">
         <is>
-          <t>{n} xisaabood</t>
+          <t>Qof</t>
         </is>
       </c>
       <c r="H142" s="14" t="inlineStr"/>
@@ -10831,7 +10831,7 @@
     <row r="143" ht="44" customHeight="1">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>one_account</t>
+          <t>role</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
@@ -10841,27 +10841,27 @@
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>{n} account</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>{n} መለያ</t>
+          <t>ሚና</t>
         </is>
       </c>
       <c r="E143" s="13" t="inlineStr">
         <is>
-          <t>Herrega {n}</t>
+          <t>Gahee</t>
         </is>
       </c>
       <c r="F143" s="12" t="inlineStr">
         <is>
-          <t>{n} ሕሳብ</t>
+          <t>ግደ</t>
         </is>
       </c>
       <c r="G143" s="13" t="inlineStr">
         <is>
-          <t>{n} xisaab</t>
+          <t>Doorka</t>
         </is>
       </c>
       <c r="H143" s="14" t="inlineStr"/>
@@ -10869,7 +10869,7 @@
     <row r="144" ht="44" customHeight="1">
       <c r="A144" s="11" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>status</t>
         </is>
       </c>
       <c r="B144" s="11" t="inlineStr">
@@ -10879,27 +10879,27 @@
       </c>
       <c r="C144" s="11" t="inlineStr">
         <is>
-          <t>Person</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="D144" s="12" t="inlineStr">
         <is>
-          <t>ሰው</t>
+          <t>ሁኔታ</t>
         </is>
       </c>
       <c r="E144" s="13" t="inlineStr">
         <is>
-          <t>Nama</t>
+          <t>Haala</t>
         </is>
       </c>
       <c r="F144" s="12" t="inlineStr">
         <is>
-          <t>ሰብ</t>
+          <t>ኩነታት</t>
         </is>
       </c>
       <c r="G144" s="13" t="inlineStr">
         <is>
-          <t>Qof</t>
+          <t>Xaalada</t>
         </is>
       </c>
       <c r="H144" s="14" t="inlineStr"/>
@@ -10907,7 +10907,7 @@
     <row r="145" ht="44" customHeight="1">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>last_signed_in</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
@@ -10917,27 +10917,27 @@
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Last signed in</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>ሚና</t>
+          <t>መጨረሻ የገቡበት</t>
         </is>
       </c>
       <c r="E145" s="13" t="inlineStr">
         <is>
-          <t>Gahee</t>
+          <t>Yeroo dhumaa seenan</t>
         </is>
       </c>
       <c r="F145" s="12" t="inlineStr">
         <is>
-          <t>ግደ</t>
+          <t>ናይ መወዳእታ ዝኣተዉሉ</t>
         </is>
       </c>
       <c r="G145" s="13" t="inlineStr">
         <is>
-          <t>Doorka</t>
+          <t>Markii ugu dambeysay ee la galay</t>
         </is>
       </c>
       <c r="H145" s="14" t="inlineStr"/>
@@ -10945,7 +10945,7 @@
     <row r="146" ht="44" customHeight="1">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>actions</t>
         </is>
       </c>
       <c r="B146" s="11" t="inlineStr">
@@ -10955,27 +10955,27 @@
       </c>
       <c r="C146" s="11" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Actions</t>
         </is>
       </c>
       <c r="D146" s="12" t="inlineStr">
         <is>
-          <t>ሁኔታ</t>
+          <t>ድርጊቶች</t>
         </is>
       </c>
       <c r="E146" s="13" t="inlineStr">
         <is>
-          <t>Haala</t>
+          <t>Gochaalee</t>
         </is>
       </c>
       <c r="F146" s="12" t="inlineStr">
         <is>
-          <t>ኩነታት</t>
+          <t>ተግባራት</t>
         </is>
       </c>
       <c r="G146" s="13" t="inlineStr">
         <is>
-          <t>Xaalada</t>
+          <t>Ficillo</t>
         </is>
       </c>
       <c r="H146" s="14" t="inlineStr"/>
@@ -10983,7 +10983,7 @@
     <row r="147" ht="44" customHeight="1">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>last_signed_in</t>
+          <t>thats_you</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
@@ -10993,27 +10993,27 @@
       </c>
       <c r="C147" s="11" t="inlineStr">
         <is>
-          <t>Last signed in</t>
+          <t>that’s you</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>መጨረሻ የገቡበት</t>
+          <t>ይህ እርስዎ ነዎት</t>
         </is>
       </c>
       <c r="E147" s="13" t="inlineStr">
         <is>
-          <t>Yeroo dhumaa seenan</t>
+          <t>kun isinuma</t>
         </is>
       </c>
       <c r="F147" s="12" t="inlineStr">
         <is>
-          <t>ናይ መወዳእታ ዝኣተዉሉ</t>
+          <t>እዚ ንስኹም ኢኹም</t>
         </is>
       </c>
       <c r="G147" s="13" t="inlineStr">
         <is>
-          <t>Markii ugu dambeysay ee la galay</t>
+          <t>kaasi waa adiga</t>
         </is>
       </c>
       <c r="H147" s="14" t="inlineStr"/>
@@ -11021,7 +11021,7 @@
     <row r="148" ht="44" customHeight="1">
       <c r="A148" s="11" t="inlineStr">
         <is>
-          <t>actions</t>
+          <t>active</t>
         </is>
       </c>
       <c r="B148" s="11" t="inlineStr">
@@ -11031,27 +11031,27 @@
       </c>
       <c r="C148" s="11" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="D148" s="12" t="inlineStr">
         <is>
-          <t>ድርጊቶች</t>
+          <t>ንቁ</t>
         </is>
       </c>
       <c r="E148" s="13" t="inlineStr">
         <is>
-          <t>Gochaalee</t>
+          <t>Ka'aa</t>
         </is>
       </c>
       <c r="F148" s="12" t="inlineStr">
         <is>
-          <t>ተግባራት</t>
+          <t>ንጡፍ</t>
         </is>
       </c>
       <c r="G148" s="13" t="inlineStr">
         <is>
-          <t>Ficillo</t>
+          <t>Firfircoon</t>
         </is>
       </c>
       <c r="H148" s="14" t="inlineStr"/>
@@ -11059,7 +11059,7 @@
     <row r="149" ht="44" customHeight="1">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>thats_you</t>
+          <t>disabled</t>
         </is>
       </c>
       <c r="B149" s="11" t="inlineStr">
@@ -11069,27 +11069,27 @@
       </c>
       <c r="C149" s="11" t="inlineStr">
         <is>
-          <t>that’s you</t>
+          <t>Disabled</t>
         </is>
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>ይህ እርስዎ ነዎት</t>
+          <t>የተሰናከለ</t>
         </is>
       </c>
       <c r="E149" s="13" t="inlineStr">
         <is>
-          <t>kun isinuma</t>
+          <t>Kan dhaabame</t>
         </is>
       </c>
       <c r="F149" s="12" t="inlineStr">
         <is>
-          <t>እዚ ንስኹም ኢኹም</t>
+          <t>ዝተዓገተ</t>
         </is>
       </c>
       <c r="G149" s="13" t="inlineStr">
         <is>
-          <t>kaasi waa adiga</t>
+          <t>La demiyay</t>
         </is>
       </c>
       <c r="H149" s="14" t="inlineStr"/>
@@ -11097,7 +11097,7 @@
     <row r="150" ht="44" customHeight="1">
       <c r="A150" s="11" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>never</t>
         </is>
       </c>
       <c r="B150" s="11" t="inlineStr">
@@ -11107,27 +11107,27 @@
       </c>
       <c r="C150" s="11" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>never</t>
         </is>
       </c>
       <c r="D150" s="12" t="inlineStr">
         <is>
-          <t>ንቁ</t>
+          <t>በጭራሽ</t>
         </is>
       </c>
       <c r="E150" s="13" t="inlineStr">
         <is>
-          <t>Ka'aa</t>
+          <t>gonkumaa</t>
         </is>
       </c>
       <c r="F150" s="12" t="inlineStr">
         <is>
-          <t>ንጡፍ</t>
+          <t>ፈጺሙ</t>
         </is>
       </c>
       <c r="G150" s="13" t="inlineStr">
         <is>
-          <t>Firfircoon</t>
+          <t>waligeed</t>
         </is>
       </c>
       <c r="H150" s="14" t="inlineStr"/>
@@ -11135,7 +11135,7 @@
     <row r="151" ht="44" customHeight="1">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>disabled</t>
+          <t>disable</t>
         </is>
       </c>
       <c r="B151" s="11" t="inlineStr">
@@ -11145,27 +11145,27 @@
       </c>
       <c r="C151" s="11" t="inlineStr">
         <is>
-          <t>Disabled</t>
+          <t>Disable</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>የተሰናከለ</t>
+          <t>አሰናክል</t>
         </is>
       </c>
       <c r="E151" s="13" t="inlineStr">
         <is>
-          <t>Kan dhaabame</t>
+          <t>Dhaabi</t>
         </is>
       </c>
       <c r="F151" s="12" t="inlineStr">
         <is>
-          <t>ዝተዓገተ</t>
+          <t>ዓግት</t>
         </is>
       </c>
       <c r="G151" s="13" t="inlineStr">
         <is>
-          <t>La demiyay</t>
+          <t>Demi</t>
         </is>
       </c>
       <c r="H151" s="14" t="inlineStr"/>
@@ -11173,7 +11173,7 @@
     <row r="152" ht="44" customHeight="1">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>restore</t>
         </is>
       </c>
       <c r="B152" s="11" t="inlineStr">
@@ -11183,27 +11183,27 @@
       </c>
       <c r="C152" s="11" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>Restore</t>
         </is>
       </c>
       <c r="D152" s="12" t="inlineStr">
         <is>
-          <t>በጭራሽ</t>
+          <t>መልስ</t>
         </is>
       </c>
       <c r="E152" s="13" t="inlineStr">
         <is>
-          <t>gonkumaa</t>
+          <t>Deebisi</t>
         </is>
       </c>
       <c r="F152" s="12" t="inlineStr">
         <is>
-          <t>ፈጺሙ</t>
+          <t>መልስ</t>
         </is>
       </c>
       <c r="G152" s="13" t="inlineStr">
         <is>
-          <t>waligeed</t>
+          <t>Soo celi</t>
         </is>
       </c>
       <c r="H152" s="14" t="inlineStr"/>
@@ -11211,7 +11211,7 @@
     <row r="153" ht="44" customHeight="1">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>disable</t>
+          <t>what_each_role_can_do</t>
         </is>
       </c>
       <c r="B153" s="11" t="inlineStr">
@@ -11221,27 +11221,27 @@
       </c>
       <c r="C153" s="11" t="inlineStr">
         <is>
-          <t>Disable</t>
+          <t>What each role can do</t>
         </is>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>አሰናክል</t>
+          <t>እያንዳንዱ ሚና ምን ማድረግ ይችላል</t>
         </is>
       </c>
       <c r="E153" s="13" t="inlineStr">
         <is>
-          <t>Dhaabi</t>
+          <t>Gaheen tokkoon tokkoon isaanii maal gochuu danda'a</t>
         </is>
       </c>
       <c r="F153" s="12" t="inlineStr">
         <is>
-          <t>ዓግት</t>
+          <t>ነፍስ ወከፍ ግደ እንታይ ክገብር ይኽእል</t>
         </is>
       </c>
       <c r="G153" s="13" t="inlineStr">
         <is>
-          <t>Demi</t>
+          <t>Waxa doorkiiba uu samayn karo</t>
         </is>
       </c>
       <c r="H153" s="14" t="inlineStr"/>
@@ -11249,7 +11249,7 @@
     <row r="154" ht="44" customHeight="1">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t>restore</t>
+          <t>built_in</t>
         </is>
       </c>
       <c r="B154" s="11" t="inlineStr">
@@ -11259,27 +11259,27 @@
       </c>
       <c r="C154" s="11" t="inlineStr">
         <is>
-          <t>Restore</t>
+          <t>built-in</t>
         </is>
       </c>
       <c r="D154" s="12" t="inlineStr">
         <is>
-          <t>መልስ</t>
+          <t>አብሮ የተሰራ</t>
         </is>
       </c>
       <c r="E154" s="13" t="inlineStr">
         <is>
-          <t>Deebisi</t>
+          <t>kan ijaarame</t>
         </is>
       </c>
       <c r="F154" s="12" t="inlineStr">
         <is>
-          <t>መልስ</t>
+          <t>ውሁድ</t>
         </is>
       </c>
       <c r="G154" s="13" t="inlineStr">
         <is>
-          <t>Soo celi</t>
+          <t>ku dhex jira</t>
         </is>
       </c>
       <c r="H154" s="14" t="inlineStr"/>
@@ -11287,7 +11287,7 @@
     <row r="155" ht="44" customHeight="1">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>what_each_role_can_do</t>
+          <t>add_a_person</t>
         </is>
       </c>
       <c r="B155" s="11" t="inlineStr">
@@ -11297,27 +11297,27 @@
       </c>
       <c r="C155" s="11" t="inlineStr">
         <is>
-          <t>What each role can do</t>
+          <t>Add a person</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>እያንዳንዱ ሚና ምን ማድረግ ይችላል</t>
+          <t>ሰው ጨምር</t>
         </is>
       </c>
       <c r="E155" s="13" t="inlineStr">
         <is>
-          <t>Gaheen tokkoon tokkoon isaanii maal gochuu danda'a</t>
+          <t>Nama dabali</t>
         </is>
       </c>
       <c r="F155" s="12" t="inlineStr">
         <is>
-          <t>ነፍስ ወከፍ ግደ እንታይ ክገብር ይኽእል</t>
+          <t>ሰብ ወስኽ</t>
         </is>
       </c>
       <c r="G155" s="13" t="inlineStr">
         <is>
-          <t>Waxa doorkiiba uu samayn karo</t>
+          <t>Qof ku dar</t>
         </is>
       </c>
       <c r="H155" s="14" t="inlineStr"/>
@@ -11325,7 +11325,7 @@
     <row r="156" ht="44" customHeight="1">
       <c r="A156" s="11" t="inlineStr">
         <is>
-          <t>built_in</t>
+          <t>email</t>
         </is>
       </c>
       <c r="B156" s="11" t="inlineStr">
@@ -11335,27 +11335,27 @@
       </c>
       <c r="C156" s="11" t="inlineStr">
         <is>
-          <t>built-in</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D156" s="12" t="inlineStr">
         <is>
-          <t>አብሮ የተሰራ</t>
+          <t>ኢሜይል</t>
         </is>
       </c>
       <c r="E156" s="13" t="inlineStr">
         <is>
-          <t>kan ijaarame</t>
+          <t>Imeelii</t>
         </is>
       </c>
       <c r="F156" s="12" t="inlineStr">
         <is>
-          <t>ውሁድ</t>
+          <t>ኢመይል</t>
         </is>
       </c>
       <c r="G156" s="13" t="inlineStr">
         <is>
-          <t>ku dhex jira</t>
+          <t>Iimayl</t>
         </is>
       </c>
       <c r="H156" s="14" t="inlineStr"/>
@@ -11363,7 +11363,7 @@
     <row r="157" ht="44" customHeight="1">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>add_a_person</t>
+          <t>name_optional</t>
         </is>
       </c>
       <c r="B157" s="11" t="inlineStr">
@@ -11373,27 +11373,27 @@
       </c>
       <c r="C157" s="11" t="inlineStr">
         <is>
-          <t>Add a person</t>
+          <t>Name (optional)</t>
         </is>
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>ሰው ጨምር</t>
+          <t>ስም (አማራጭ)</t>
         </is>
       </c>
       <c r="E157" s="13" t="inlineStr">
         <is>
-          <t>Nama dabali</t>
+          <t>Maqaa (filannoo)</t>
         </is>
       </c>
       <c r="F157" s="12" t="inlineStr">
         <is>
-          <t>ሰብ ወስኽ</t>
+          <t>ስም (ኣማራጺ)</t>
         </is>
       </c>
       <c r="G157" s="13" t="inlineStr">
         <is>
-          <t>Qof ku dar</t>
+          <t>Magac (ikhtiyaari)</t>
         </is>
       </c>
       <c r="H157" s="14" t="inlineStr"/>
@@ -11401,7 +11401,7 @@
     <row r="158" ht="44" customHeight="1">
       <c r="A158" s="11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>temporary_password</t>
         </is>
       </c>
       <c r="B158" s="11" t="inlineStr">
@@ -11411,27 +11411,27 @@
       </c>
       <c r="C158" s="11" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Temporary password</t>
         </is>
       </c>
       <c r="D158" s="12" t="inlineStr">
         <is>
-          <t>ኢሜይል</t>
+          <t>ጊዜያዊ የይለፍ ቃል</t>
         </is>
       </c>
       <c r="E158" s="13" t="inlineStr">
         <is>
-          <t>Imeelii</t>
+          <t>Jecha darbii yeroo</t>
         </is>
       </c>
       <c r="F158" s="12" t="inlineStr">
         <is>
-          <t>ኢመይል</t>
+          <t>ግዝያዊ መሕለፊ ቃል</t>
         </is>
       </c>
       <c r="G158" s="13" t="inlineStr">
         <is>
-          <t>Iimayl</t>
+          <t>Fure ku meel gaar ah</t>
         </is>
       </c>
       <c r="H158" s="14" t="inlineStr"/>
@@ -11439,7 +11439,7 @@
     <row r="159" ht="44" customHeight="1">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>name_optional</t>
+          <t>temp_password_help</t>
         </is>
       </c>
       <c r="B159" s="11" t="inlineStr">
@@ -11449,27 +11449,27 @@
       </c>
       <c r="C159" s="11" t="inlineStr">
         <is>
-          <t>Name (optional)</t>
+          <t>At least 12 characters. Until invitation emails are set up, this password has to be given to them directly — which is why it is shown here rather than hidden.</t>
         </is>
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>ስም (አማራጭ)</t>
+          <t>ቢያንስ 12 ቁምፊ። የግብዣ ኢሜይሎች እስኪዘጋጁ ድረስ ይህ የይለፍ ቃል በቀጥታ ሊሰጣቸው ይገባል — ስለዚህ ተደብቆ ሳይሆን እዚህ ይታያል።</t>
         </is>
       </c>
       <c r="E159" s="13" t="inlineStr">
         <is>
-          <t>Maqaa (filannoo)</t>
+          <t>Yoo xiqqaate arfiilee 12. Hanga imeeliin afeerraa qophaa'utti, jechi darbii kun kallattiin isaaniif kennamuu qaba — kanaafuu dhokfamuu mannaa asitti ni mul'ata.</t>
         </is>
       </c>
       <c r="F159" s="12" t="inlineStr">
         <is>
-          <t>ስም (ኣማራጺ)</t>
+          <t>ብውሑዱ 12 ፊደላት። መጸዋዕታ ኢመይል ክሳብ ዝዳሎ እዚ መሕለፊ ቃል ብቐጥታ ክወሃቦም ኣለዎ — ስለዚ ተሓቢኡ ዘይኮነ ኣብዚ ይረአ።</t>
         </is>
       </c>
       <c r="G159" s="13" t="inlineStr">
         <is>
-          <t>Magac (ikhtiyaari)</t>
+          <t>Ugu yaraan 12 xaraf. Ilaa iimaylada casumaadda la dejiyo, furahan si toos ah ayaa loo siin doonaa — sidaas darteed halkan ayuu ka muuqdaa halkii la qarin lahaa.</t>
         </is>
       </c>
       <c r="H159" s="14" t="inlineStr"/>
@@ -11477,7 +11477,7 @@
     <row r="160" ht="44" customHeight="1">
       <c r="A160" s="11" t="inlineStr">
         <is>
-          <t>temporary_password</t>
+          <t>create</t>
         </is>
       </c>
       <c r="B160" s="11" t="inlineStr">
@@ -11487,27 +11487,27 @@
       </c>
       <c r="C160" s="11" t="inlineStr">
         <is>
-          <t>Temporary password</t>
+          <t>Create</t>
         </is>
       </c>
       <c r="D160" s="12" t="inlineStr">
         <is>
-          <t>ጊዜያዊ የይለፍ ቃል</t>
+          <t>ፍጠር</t>
         </is>
       </c>
       <c r="E160" s="13" t="inlineStr">
         <is>
-          <t>Jecha darbii yeroo</t>
+          <t>Uumi</t>
         </is>
       </c>
       <c r="F160" s="12" t="inlineStr">
         <is>
-          <t>ግዝያዊ መሕለፊ ቃል</t>
+          <t>ፍጠር</t>
         </is>
       </c>
       <c r="G160" s="13" t="inlineStr">
         <is>
-          <t>Fure ku meel gaar ah</t>
+          <t>Abuur</t>
         </is>
       </c>
       <c r="H160" s="14" t="inlineStr"/>
@@ -11515,7 +11515,7 @@
     <row r="161" ht="44" customHeight="1">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>temp_password_help</t>
+          <t>account_created</t>
         </is>
       </c>
       <c r="B161" s="11" t="inlineStr">
@@ -11525,27 +11525,27 @@
       </c>
       <c r="C161" s="11" t="inlineStr">
         <is>
-          <t>At least 12 characters. Until invitation emails are set up, this password has to be given to them directly — which is why it is shown here rather than hidden.</t>
+          <t>Account created</t>
         </is>
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>ቢያንስ 12 ቁምፊ። የግብዣ ኢሜይሎች እስኪዘጋጁ ድረስ ይህ የይለፍ ቃል በቀጥታ ሊሰጣቸው ይገባል — ስለዚህ ተደብቆ ሳይሆን እዚህ ይታያል።</t>
+          <t>መለያ ተፈጥሯል</t>
         </is>
       </c>
       <c r="E161" s="13" t="inlineStr">
         <is>
-          <t>Yoo xiqqaate arfiilee 12. Hanga imeeliin afeerraa qophaa'utti, jechi darbii kun kallattiin isaaniif kennamuu qaba — kanaafuu dhokfamuu mannaa asitti ni mul'ata.</t>
+          <t>Herregni uumame</t>
         </is>
       </c>
       <c r="F161" s="12" t="inlineStr">
         <is>
-          <t>ብውሑዱ 12 ፊደላት። መጸዋዕታ ኢመይል ክሳብ ዝዳሎ እዚ መሕለፊ ቃል ብቐጥታ ክወሃቦም ኣለዎ — ስለዚ ተሓቢኡ ዘይኮነ ኣብዚ ይረአ።</t>
+          <t>ሕሳብ ተፈጢሩ</t>
         </is>
       </c>
       <c r="G161" s="13" t="inlineStr">
         <is>
-          <t>Ugu yaraan 12 xaraf. Ilaa iimaylada casumaadda la dejiyo, furahan si toos ah ayaa loo siin doonaa — sidaas darteed halkan ayuu ka muuqdaa halkii la qarin lahaa.</t>
+          <t>Xisaab waa la abuuray</t>
         </is>
       </c>
       <c r="H161" s="14" t="inlineStr"/>
@@ -11553,7 +11553,7 @@
     <row r="162" ht="44" customHeight="1">
       <c r="A162" s="11" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>account_restored</t>
         </is>
       </c>
       <c r="B162" s="11" t="inlineStr">
@@ -11563,27 +11563,27 @@
       </c>
       <c r="C162" s="11" t="inlineStr">
         <is>
-          <t>Create</t>
+          <t>Account restored</t>
         </is>
       </c>
       <c r="D162" s="12" t="inlineStr">
         <is>
-          <t>ፍጠር</t>
+          <t>መለያ ተመልሷል</t>
         </is>
       </c>
       <c r="E162" s="13" t="inlineStr">
         <is>
-          <t>Uumi</t>
+          <t>Herregni deebi'e</t>
         </is>
       </c>
       <c r="F162" s="12" t="inlineStr">
         <is>
-          <t>ፍጠር</t>
+          <t>ሕሳብ ተመሊሱ</t>
         </is>
       </c>
       <c r="G162" s="13" t="inlineStr">
         <is>
-          <t>Abuur</t>
+          <t>Xisaabta waa la soo celiyay</t>
         </is>
       </c>
       <c r="H162" s="14" t="inlineStr"/>
@@ -11591,7 +11591,7 @@
     <row r="163" ht="44" customHeight="1">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>account_created</t>
+          <t>account_disabled_n</t>
         </is>
       </c>
       <c r="B163" s="11" t="inlineStr">
@@ -11601,27 +11601,27 @@
       </c>
       <c r="C163" s="11" t="inlineStr">
         <is>
-          <t>Account created</t>
+          <t>Account disabled, {n} session(s) ended</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>መለያ ተፈጥሯል</t>
+          <t>መለያ ተሰናክሏል፤ {n} ክፍለ-ጊዜ ተዘግቷል</t>
         </is>
       </c>
       <c r="E163" s="13" t="inlineStr">
         <is>
-          <t>Herregni uumame</t>
+          <t>Herregni dhaabame, session {n} xumurame</t>
         </is>
       </c>
       <c r="F163" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ ተፈጢሩ</t>
+          <t>ሕሳብ ተዓጊቱ፣ {n} ክፍለ-ግዜ ተዛዚሙ</t>
         </is>
       </c>
       <c r="G163" s="13" t="inlineStr">
         <is>
-          <t>Xisaab waa la abuuray</t>
+          <t>Xisaabta waa la demiyay, {n} kalfadhi ayaa dhammaaday</t>
         </is>
       </c>
       <c r="H163" s="14" t="inlineStr"/>
@@ -11629,7 +11629,7 @@
     <row r="164" ht="44" customHeight="1">
       <c r="A164" s="11" t="inlineStr">
         <is>
-          <t>account_restored</t>
+          <t>confirm_disable_account</t>
         </is>
       </c>
       <c r="B164" s="11" t="inlineStr">
@@ -11639,27 +11639,27 @@
       </c>
       <c r="C164" s="11" t="inlineStr">
         <is>
-          <t>Account restored</t>
+          <t>Disable this account? They will be signed out immediately.</t>
         </is>
       </c>
       <c r="D164" s="12" t="inlineStr">
         <is>
-          <t>መለያ ተመልሷል</t>
+          <t>ይህን መለያ ማሰናከል? ወዲያውኑ ይወጣሉ።</t>
         </is>
       </c>
       <c r="E164" s="13" t="inlineStr">
         <is>
-          <t>Herregni deebi'e</t>
+          <t>Herrega kana dhaabuu? Battalumatti ni baafamu.</t>
         </is>
       </c>
       <c r="F164" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ ተመሊሱ</t>
+          <t>ነዚ ሕሳብ ክዕገት? ብቕጽበት ይወጹ።</t>
         </is>
       </c>
       <c r="G164" s="13" t="inlineStr">
         <is>
-          <t>Xisaabta waa la soo celiyay</t>
+          <t>Xisaabtan ma demineysaa? Isla markiiba waa laga saarayaa.</t>
         </is>
       </c>
       <c r="H164" s="14" t="inlineStr"/>
@@ -11667,7 +11667,7 @@
     <row r="165" ht="44" customHeight="1">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>account_disabled_n</t>
+          <t>action_document_created</t>
         </is>
       </c>
       <c r="B165" s="11" t="inlineStr">
@@ -11677,27 +11677,27 @@
       </c>
       <c r="C165" s="11" t="inlineStr">
         <is>
-          <t>Account disabled, {n} session(s) ended</t>
+          <t>added an article</t>
         </is>
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>መለያ ተሰናክሏል፤ {n} ክፍለ-ጊዜ ተዘግቷል</t>
+          <t>ጽሑፍ ጨምሯል</t>
         </is>
       </c>
       <c r="E165" s="13" t="inlineStr">
         <is>
-          <t>Herregni dhaabame, session {n} xumurame</t>
+          <t>barruu dabale</t>
         </is>
       </c>
       <c r="F165" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ ተዓጊቱ፣ {n} ክፍለ-ግዜ ተዛዚሙ</t>
+          <t>ጽሑፍ ወሲኹ</t>
         </is>
       </c>
       <c r="G165" s="13" t="inlineStr">
         <is>
-          <t>Xisaabta waa la demiyay, {n} kalfadhi ayaa dhammaaday</t>
+          <t>maqaal ku daray</t>
         </is>
       </c>
       <c r="H165" s="14" t="inlineStr"/>
@@ -11705,7 +11705,7 @@
     <row r="166" ht="44" customHeight="1">
       <c r="A166" s="11" t="inlineStr">
         <is>
-          <t>confirm_disable_account</t>
+          <t>action_document_updated</t>
         </is>
       </c>
       <c r="B166" s="11" t="inlineStr">
@@ -11715,27 +11715,27 @@
       </c>
       <c r="C166" s="11" t="inlineStr">
         <is>
-          <t>Disable this account? They will be signed out immediately.</t>
+          <t>edited an article</t>
         </is>
       </c>
       <c r="D166" s="12" t="inlineStr">
         <is>
-          <t>ይህን መለያ ማሰናከል? ወዲያውኑ ይወጣሉ።</t>
+          <t>ጽሑፍ አርሟል</t>
         </is>
       </c>
       <c r="E166" s="13" t="inlineStr">
         <is>
-          <t>Herrega kana dhaabuu? Battalumatti ni baafamu.</t>
+          <t>barruu gulaale</t>
         </is>
       </c>
       <c r="F166" s="12" t="inlineStr">
         <is>
-          <t>ነዚ ሕሳብ ክዕገት? ብቕጽበት ይወጹ።</t>
+          <t>ጽሑፍ ኣርሚዑ</t>
         </is>
       </c>
       <c r="G166" s="13" t="inlineStr">
         <is>
-          <t>Xisaabtan ma demineysaa? Isla markiiba waa laga saarayaa.</t>
+          <t>maqaal wax ka beddelay</t>
         </is>
       </c>
       <c r="H166" s="14" t="inlineStr"/>
@@ -11743,7 +11743,7 @@
     <row r="167" ht="44" customHeight="1">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>action_document_created</t>
+          <t>action_document_deleted</t>
         </is>
       </c>
       <c r="B167" s="11" t="inlineStr">
@@ -11753,27 +11753,27 @@
       </c>
       <c r="C167" s="11" t="inlineStr">
         <is>
-          <t>added an article</t>
+          <t>deleted an article</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ጨምሯል</t>
+          <t>ጽሑፍ ሰርዟል</t>
         </is>
       </c>
       <c r="E167" s="13" t="inlineStr">
         <is>
-          <t>barruu dabale</t>
+          <t>barruu haqe</t>
         </is>
       </c>
       <c r="F167" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ወሲኹ</t>
+          <t>ጽሑፍ ደምሲሱ</t>
         </is>
       </c>
       <c r="G167" s="13" t="inlineStr">
         <is>
-          <t>maqaal ku daray</t>
+          <t>maqaal tirtiray</t>
         </is>
       </c>
       <c r="H167" s="14" t="inlineStr"/>
@@ -11781,7 +11781,7 @@
     <row r="168" ht="44" customHeight="1">
       <c r="A168" s="11" t="inlineStr">
         <is>
-          <t>action_document_updated</t>
+          <t>action_documents_bulk_imported</t>
         </is>
       </c>
       <c r="B168" s="11" t="inlineStr">
@@ -11791,27 +11791,27 @@
       </c>
       <c r="C168" s="11" t="inlineStr">
         <is>
-          <t>edited an article</t>
+          <t>imported articles</t>
         </is>
       </c>
       <c r="D168" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ አርሟል</t>
+          <t>ጽሑፎችን አስገብቷል</t>
         </is>
       </c>
       <c r="E168" s="13" t="inlineStr">
         <is>
-          <t>barruu gulaale</t>
+          <t>barruulee galche</t>
         </is>
       </c>
       <c r="F168" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ኣርሚዑ</t>
+          <t>ጽሑፋት ኣእትዩ</t>
         </is>
       </c>
       <c r="G168" s="13" t="inlineStr">
         <is>
-          <t>maqaal wax ka beddelay</t>
+          <t>maqaallo soo dhoofiyay</t>
         </is>
       </c>
       <c r="H168" s="14" t="inlineStr"/>
@@ -11819,7 +11819,7 @@
     <row r="169" ht="44" customHeight="1">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>action_document_deleted</t>
+          <t>action_handoff_closed</t>
         </is>
       </c>
       <c r="B169" s="11" t="inlineStr">
@@ -11829,27 +11829,27 @@
       </c>
       <c r="C169" s="11" t="inlineStr">
         <is>
-          <t>deleted an article</t>
+          <t>closed an escalation</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ሰርዟል</t>
+          <t>ጉዳይ ዘግቷል</t>
         </is>
       </c>
       <c r="E169" s="13" t="inlineStr">
         <is>
-          <t>barruu haqe</t>
+          <t>dhimma cufe</t>
         </is>
       </c>
       <c r="F169" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ደምሲሱ</t>
+          <t>ጉዳይ ዓጺዩ</t>
         </is>
       </c>
       <c r="G169" s="13" t="inlineStr">
         <is>
-          <t>maqaal tirtiray</t>
+          <t>arrin xiray</t>
         </is>
       </c>
       <c r="H169" s="14" t="inlineStr"/>
@@ -11857,7 +11857,7 @@
     <row r="170" ht="44" customHeight="1">
       <c r="A170" s="11" t="inlineStr">
         <is>
-          <t>action_documents_bulk_imported</t>
+          <t>action_handoff_reopened</t>
         </is>
       </c>
       <c r="B170" s="11" t="inlineStr">
@@ -11867,27 +11867,27 @@
       </c>
       <c r="C170" s="11" t="inlineStr">
         <is>
-          <t>imported articles</t>
+          <t>reopened an escalation</t>
         </is>
       </c>
       <c r="D170" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፎችን አስገብቷል</t>
+          <t>ጉዳይ በድጋሚ ከፍቷል</t>
         </is>
       </c>
       <c r="E170" s="13" t="inlineStr">
         <is>
-          <t>barruulee galche</t>
+          <t>dhimma irra deebi'ee bane</t>
         </is>
       </c>
       <c r="F170" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፋት ኣእትዩ</t>
+          <t>ጉዳይ ደጊሙ ከፊቱ</t>
         </is>
       </c>
       <c r="G170" s="13" t="inlineStr">
         <is>
-          <t>maqaallo soo dhoofiyay</t>
+          <t>arrin dib u furay</t>
         </is>
       </c>
       <c r="H170" s="14" t="inlineStr"/>
@@ -11895,7 +11895,7 @@
     <row r="171" ht="44" customHeight="1">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_closed</t>
+          <t>action_handoff_webhook_connected</t>
         </is>
       </c>
       <c r="B171" s="11" t="inlineStr">
@@ -11905,27 +11905,27 @@
       </c>
       <c r="C171" s="11" t="inlineStr">
         <is>
-          <t>closed an escalation</t>
+          <t>connected the escalation webhook</t>
         </is>
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ ዘግቷል</t>
+          <t>የማሸጋገሪያ ዌብሁክ አገናኝቷል</t>
         </is>
       </c>
       <c r="E171" s="13" t="inlineStr">
         <is>
-          <t>dhimma cufe</t>
+          <t>webhook dabarsaa walqunnamsiise</t>
         </is>
       </c>
       <c r="F171" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ ዓጺዩ</t>
+          <t>ዌብሁክ ምትሕልላፍ ኣራኺቡ</t>
         </is>
       </c>
       <c r="G171" s="13" t="inlineStr">
         <is>
-          <t>arrin xiray</t>
+          <t>ku xiray webhook-ga gudbinta</t>
         </is>
       </c>
       <c r="H171" s="14" t="inlineStr"/>
@@ -11933,7 +11933,7 @@
     <row r="172" ht="44" customHeight="1">
       <c r="A172" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_reopened</t>
+          <t>action_handoff_webhook_disconnected</t>
         </is>
       </c>
       <c r="B172" s="11" t="inlineStr">
@@ -11943,27 +11943,27 @@
       </c>
       <c r="C172" s="11" t="inlineStr">
         <is>
-          <t>reopened an escalation</t>
+          <t>disconnected the escalation webhook</t>
         </is>
       </c>
       <c r="D172" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ በድጋሚ ከፍቷል</t>
+          <t>የማሸጋገሪያ ዌብሁክ አቋርጧል</t>
         </is>
       </c>
       <c r="E172" s="13" t="inlineStr">
         <is>
-          <t>dhimma irra deebi'ee bane</t>
+          <t>webhook dabarsaa addaan kute</t>
         </is>
       </c>
       <c r="F172" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ ደጊሙ ከፊቱ</t>
+          <t>ዌብሁክ ምትሕልላፍ ቆሪጹ</t>
         </is>
       </c>
       <c r="G172" s="13" t="inlineStr">
         <is>
-          <t>arrin dib u furay</t>
+          <t>goynay webhook-ga gudbinta</t>
         </is>
       </c>
       <c r="H172" s="14" t="inlineStr"/>
@@ -11971,7 +11971,7 @@
     <row r="173" ht="44" customHeight="1">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_webhook_connected</t>
+          <t>action_telegram_connected</t>
         </is>
       </c>
       <c r="B173" s="11" t="inlineStr">
@@ -11981,27 +11981,27 @@
       </c>
       <c r="C173" s="11" t="inlineStr">
         <is>
-          <t>connected the escalation webhook</t>
+          <t>connected Telegram</t>
         </is>
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ዌብሁክ አገናኝቷል</t>
+          <t>ቴሌግራም አገናኝቷል</t>
         </is>
       </c>
       <c r="E173" s="13" t="inlineStr">
         <is>
-          <t>webhook dabarsaa walqunnamsiise</t>
+          <t>Telegram walqunnamsiise</t>
         </is>
       </c>
       <c r="F173" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ምትሕልላፍ ኣራኺቡ</t>
+          <t>ቴሌግራም ኣራኺቡ</t>
         </is>
       </c>
       <c r="G173" s="13" t="inlineStr">
         <is>
-          <t>ku xiray webhook-ga gudbinta</t>
+          <t>Telegram ku xiray</t>
         </is>
       </c>
       <c r="H173" s="14" t="inlineStr"/>
@@ -12009,7 +12009,7 @@
     <row r="174" ht="44" customHeight="1">
       <c r="A174" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_webhook_disconnected</t>
+          <t>action_user_created</t>
         </is>
       </c>
       <c r="B174" s="11" t="inlineStr">
@@ -12019,27 +12019,27 @@
       </c>
       <c r="C174" s="11" t="inlineStr">
         <is>
-          <t>disconnected the escalation webhook</t>
+          <t>added a colleague</t>
         </is>
       </c>
       <c r="D174" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ዌብሁክ አቋርጧል</t>
+          <t>ባልደረባ ጨምሯል</t>
         </is>
       </c>
       <c r="E174" s="13" t="inlineStr">
         <is>
-          <t>webhook dabarsaa addaan kute</t>
+          <t>hojjetaa dabale</t>
         </is>
       </c>
       <c r="F174" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ምትሕልላፍ ቆሪጹ</t>
+          <t>መሳርሕቲ ወሲኹ</t>
         </is>
       </c>
       <c r="G174" s="13" t="inlineStr">
         <is>
-          <t>goynay webhook-ga gudbinta</t>
+          <t>shaqaale ku daray</t>
         </is>
       </c>
       <c r="H174" s="14" t="inlineStr"/>
@@ -12047,7 +12047,7 @@
     <row r="175" ht="44" customHeight="1">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>action_telegram_connected</t>
+          <t>action_user_disabled</t>
         </is>
       </c>
       <c r="B175" s="11" t="inlineStr">
@@ -12057,27 +12057,27 @@
       </c>
       <c r="C175" s="11" t="inlineStr">
         <is>
-          <t>connected Telegram</t>
+          <t>disabled an account</t>
         </is>
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>ቴሌግራም አገናኝቷል</t>
+          <t>መለያ አሰናክሏል</t>
         </is>
       </c>
       <c r="E175" s="13" t="inlineStr">
         <is>
-          <t>Telegram walqunnamsiise</t>
+          <t>herrega dhaabe</t>
         </is>
       </c>
       <c r="F175" s="12" t="inlineStr">
         <is>
-          <t>ቴሌግራም ኣራኺቡ</t>
+          <t>ሕሳብ ዓጊቱ</t>
         </is>
       </c>
       <c r="G175" s="13" t="inlineStr">
         <is>
-          <t>Telegram ku xiray</t>
+          <t>xisaab demiyay</t>
         </is>
       </c>
       <c r="H175" s="14" t="inlineStr"/>
@@ -12085,7 +12085,7 @@
     <row r="176" ht="44" customHeight="1">
       <c r="A176" s="11" t="inlineStr">
         <is>
-          <t>action_user_created</t>
+          <t>action_user_enabled</t>
         </is>
       </c>
       <c r="B176" s="11" t="inlineStr">
@@ -12095,27 +12095,27 @@
       </c>
       <c r="C176" s="11" t="inlineStr">
         <is>
-          <t>added a colleague</t>
+          <t>restored an account</t>
         </is>
       </c>
       <c r="D176" s="12" t="inlineStr">
         <is>
-          <t>ባልደረባ ጨምሯል</t>
+          <t>መለያ መልሷል</t>
         </is>
       </c>
       <c r="E176" s="13" t="inlineStr">
         <is>
-          <t>hojjetaa dabale</t>
+          <t>herrega deebise</t>
         </is>
       </c>
       <c r="F176" s="12" t="inlineStr">
         <is>
-          <t>መሳርሕቲ ወሲኹ</t>
+          <t>ሕሳብ መሊሱ</t>
         </is>
       </c>
       <c r="G176" s="13" t="inlineStr">
         <is>
-          <t>shaqaale ku daray</t>
+          <t>xisaab soo celiyay</t>
         </is>
       </c>
       <c r="H176" s="14" t="inlineStr"/>
@@ -12123,7 +12123,7 @@
     <row r="177" ht="44" customHeight="1">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>action_user_disabled</t>
+          <t>action_admin_login</t>
         </is>
       </c>
       <c r="B177" s="11" t="inlineStr">
@@ -12133,27 +12133,27 @@
       </c>
       <c r="C177" s="11" t="inlineStr">
         <is>
-          <t>disabled an account</t>
+          <t>signed in</t>
         </is>
       </c>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>መለያ አሰናክሏል</t>
+          <t>ገብቷል</t>
         </is>
       </c>
       <c r="E177" s="13" t="inlineStr">
         <is>
-          <t>herrega dhaabe</t>
+          <t>seene</t>
         </is>
       </c>
       <c r="F177" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ ዓጊቱ</t>
+          <t>ኣትዩ</t>
         </is>
       </c>
       <c r="G177" s="13" t="inlineStr">
         <is>
-          <t>xisaab demiyay</t>
+          <t>gashay</t>
         </is>
       </c>
       <c r="H177" s="14" t="inlineStr"/>
@@ -12161,7 +12161,7 @@
     <row r="178" ht="44" customHeight="1">
       <c r="A178" s="11" t="inlineStr">
         <is>
-          <t>action_user_enabled</t>
+          <t>action_password_changed</t>
         </is>
       </c>
       <c r="B178" s="11" t="inlineStr">
@@ -12171,27 +12171,27 @@
       </c>
       <c r="C178" s="11" t="inlineStr">
         <is>
-          <t>restored an account</t>
+          <t>changed their password</t>
         </is>
       </c>
       <c r="D178" s="12" t="inlineStr">
         <is>
-          <t>መለያ መልሷል</t>
+          <t>የይለፍ ቃል ቀይሯል</t>
         </is>
       </c>
       <c r="E178" s="13" t="inlineStr">
         <is>
-          <t>herrega deebise</t>
+          <t>jecha darbii jijjiire</t>
         </is>
       </c>
       <c r="F178" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ መሊሱ</t>
+          <t>መሕለፊ ቃል ቀዪሩ</t>
         </is>
       </c>
       <c r="G178" s="13" t="inlineStr">
         <is>
-          <t>xisaab soo celiyay</t>
+          <t>beddelay furihiisa</t>
         </is>
       </c>
       <c r="H178" s="14" t="inlineStr"/>
@@ -12199,7 +12199,7 @@
     <row r="179" ht="44" customHeight="1">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>action_admin_login</t>
+          <t>nothing_yet</t>
         </is>
       </c>
       <c r="B179" s="11" t="inlineStr">
@@ -12209,27 +12209,27 @@
       </c>
       <c r="C179" s="11" t="inlineStr">
         <is>
-          <t>signed in</t>
+          <t>Nothing yet.</t>
         </is>
       </c>
       <c r="D179" s="12" t="inlineStr">
         <is>
-          <t>ገብቷል</t>
+          <t>እስካሁን ምንም የለም።</t>
         </is>
       </c>
       <c r="E179" s="13" t="inlineStr">
         <is>
-          <t>seene</t>
+          <t>Ammaaf homaa hin jiru.</t>
         </is>
       </c>
       <c r="F179" s="12" t="inlineStr">
         <is>
-          <t>ኣትዩ</t>
+          <t>ክሳብ ሕጂ ዋላ ሓደ የለን።</t>
         </is>
       </c>
       <c r="G179" s="13" t="inlineStr">
         <is>
-          <t>gashay</t>
+          <t>Weli waxba ma jiraan.</t>
         </is>
       </c>
       <c r="H179" s="14" t="inlineStr"/>
@@ -12237,7 +12237,7 @@
     <row r="180" ht="44" customHeight="1">
       <c r="A180" s="11" t="inlineStr">
         <is>
-          <t>action_password_changed</t>
+          <t>unavailable</t>
         </is>
       </c>
       <c r="B180" s="11" t="inlineStr">
@@ -12247,27 +12247,27 @@
       </c>
       <c r="C180" s="11" t="inlineStr">
         <is>
-          <t>changed their password</t>
+          <t>Unavailable.</t>
         </is>
       </c>
       <c r="D180" s="12" t="inlineStr">
         <is>
-          <t>የይለፍ ቃል ቀይሯል</t>
+          <t>አይገኝም።</t>
         </is>
       </c>
       <c r="E180" s="13" t="inlineStr">
         <is>
-          <t>jecha darbii jijjiire</t>
+          <t>Hin argamu.</t>
         </is>
       </c>
       <c r="F180" s="12" t="inlineStr">
         <is>
-          <t>መሕለፊ ቃል ቀዪሩ</t>
+          <t>ኣይርከብን።</t>
         </is>
       </c>
       <c r="G180" s="13" t="inlineStr">
         <is>
-          <t>beddelay furihiisa</t>
+          <t>Lama heli karo.</t>
         </is>
       </c>
       <c r="H180" s="14" t="inlineStr"/>
@@ -12275,7 +12275,7 @@
     <row r="181" ht="44" customHeight="1">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t>nothing_yet</t>
+          <t>just_now</t>
         </is>
       </c>
       <c r="B181" s="11" t="inlineStr">
@@ -12285,27 +12285,27 @@
       </c>
       <c r="C181" s="11" t="inlineStr">
         <is>
-          <t>Nothing yet.</t>
+          <t>just now</t>
         </is>
       </c>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>እስካሁን ምንም የለም።</t>
+          <t>አሁን</t>
         </is>
       </c>
       <c r="E181" s="13" t="inlineStr">
         <is>
-          <t>Ammaaf homaa hin jiru.</t>
+          <t>amma</t>
         </is>
       </c>
       <c r="F181" s="12" t="inlineStr">
         <is>
-          <t>ክሳብ ሕጂ ዋላ ሓደ የለን።</t>
+          <t>ሕጂ</t>
         </is>
       </c>
       <c r="G181" s="13" t="inlineStr">
         <is>
-          <t>Weli waxba ma jiraan.</t>
+          <t>hadda</t>
         </is>
       </c>
       <c r="H181" s="14" t="inlineStr"/>
@@ -12313,7 +12313,7 @@
     <row r="182" ht="44" customHeight="1">
       <c r="A182" s="11" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>n_min_ago</t>
         </is>
       </c>
       <c r="B182" s="11" t="inlineStr">
@@ -12323,27 +12323,27 @@
       </c>
       <c r="C182" s="11" t="inlineStr">
         <is>
-          <t>Unavailable.</t>
+          <t>{n} min ago</t>
         </is>
       </c>
       <c r="D182" s="12" t="inlineStr">
         <is>
-          <t>አይገኝም።</t>
+          <t>ከ{n} ደቂቃ በፊት</t>
         </is>
       </c>
       <c r="E182" s="13" t="inlineStr">
         <is>
-          <t>Hin argamu.</t>
+          <t>daqiiqaa {n} dura</t>
         </is>
       </c>
       <c r="F182" s="12" t="inlineStr">
         <is>
-          <t>ኣይርከብን።</t>
+          <t>ቅድሚ {n} ደቒቕ</t>
         </is>
       </c>
       <c r="G182" s="13" t="inlineStr">
         <is>
-          <t>Lama heli karo.</t>
+          <t>{n} daqiiqo ka hor</t>
         </is>
       </c>
       <c r="H182" s="14" t="inlineStr"/>
@@ -12351,7 +12351,7 @@
     <row r="183" ht="44" customHeight="1">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t>just_now</t>
+          <t>n_h_ago</t>
         </is>
       </c>
       <c r="B183" s="11" t="inlineStr">
@@ -12361,27 +12361,27 @@
       </c>
       <c r="C183" s="11" t="inlineStr">
         <is>
-          <t>just now</t>
+          <t>{n} h ago</t>
         </is>
       </c>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>አሁን</t>
+          <t>ከ{n} ሰዓት በፊት</t>
         </is>
       </c>
       <c r="E183" s="13" t="inlineStr">
         <is>
-          <t>amma</t>
+          <t>sa'aatii {n} dura</t>
         </is>
       </c>
       <c r="F183" s="12" t="inlineStr">
         <is>
-          <t>ሕጂ</t>
+          <t>ቅድሚ {n} ሰዓት</t>
         </is>
       </c>
       <c r="G183" s="13" t="inlineStr">
         <is>
-          <t>hadda</t>
+          <t>{n} saac ka hor</t>
         </is>
       </c>
       <c r="H183" s="14" t="inlineStr"/>
@@ -12389,7 +12389,7 @@
     <row r="184" ht="44" customHeight="1">
       <c r="A184" s="11" t="inlineStr">
         <is>
-          <t>n_min_ago</t>
+          <t>n_d_ago</t>
         </is>
       </c>
       <c r="B184" s="11" t="inlineStr">
@@ -12399,27 +12399,27 @@
       </c>
       <c r="C184" s="11" t="inlineStr">
         <is>
-          <t>{n} min ago</t>
+          <t>{n} d ago</t>
         </is>
       </c>
       <c r="D184" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ደቂቃ በፊት</t>
+          <t>ከ{n} ቀን በፊት</t>
         </is>
       </c>
       <c r="E184" s="13" t="inlineStr">
         <is>
-          <t>daqiiqaa {n} dura</t>
+          <t>guyyaa {n} dura</t>
         </is>
       </c>
       <c r="F184" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ደቒቕ</t>
+          <t>ቅድሚ {n} መዓልቲ</t>
         </is>
       </c>
       <c r="G184" s="13" t="inlineStr">
         <is>
-          <t>{n} daqiiqo ka hor</t>
+          <t>{n} maalmood ka hor</t>
         </is>
       </c>
       <c r="H184" s="14" t="inlineStr"/>
@@ -12427,7 +12427,7 @@
     <row r="185" ht="44" customHeight="1">
       <c r="A185" s="11" t="inlineStr">
         <is>
-          <t>n_h_ago</t>
+          <t>channel_all_from</t>
         </is>
       </c>
       <c r="B185" s="11" t="inlineStr">
@@ -12437,27 +12437,27 @@
       </c>
       <c r="C185" s="11" t="inlineStr">
         <is>
-          <t>{n} h ago</t>
+          <t>All {n} conversations came from {label}.</t>
         </is>
       </c>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ሰዓት በፊት</t>
+          <t>ሁሉም {n} ውይይቶች ከ{label} መጥተዋል።</t>
         </is>
       </c>
       <c r="E185" s="13" t="inlineStr">
         <is>
-          <t>sa'aatii {n} dura</t>
+          <t>Mariin {n} hundi {label} irraa dhufe.</t>
         </is>
       </c>
       <c r="F185" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ሰዓት</t>
+          <t>ኩሎም {n} ዝርርባት ካብ {label} መጺኦም።</t>
         </is>
       </c>
       <c r="G185" s="13" t="inlineStr">
         <is>
-          <t>{n} saac ka hor</t>
+          <t>Dhammaan {n} wadahadal waxay ka yimaadeen {label}.</t>
         </is>
       </c>
       <c r="H185" s="14" t="inlineStr"/>
@@ -12465,7 +12465,7 @@
     <row r="186" ht="44" customHeight="1">
       <c r="A186" s="11" t="inlineStr">
         <is>
-          <t>n_d_ago</t>
+          <t>channel_live</t>
         </is>
       </c>
       <c r="B186" s="11" t="inlineStr">
@@ -12475,27 +12475,27 @@
       </c>
       <c r="C186" s="11" t="inlineStr">
         <is>
-          <t>{n} d ago</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="D186" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ቀን በፊት</t>
+          <t>በሥራ ላይ</t>
         </is>
       </c>
       <c r="E186" s="13" t="inlineStr">
         <is>
-          <t>guyyaa {n} dura</t>
+          <t>Hojiirra</t>
         </is>
       </c>
       <c r="F186" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} መዓልቲ</t>
+          <t>ኣብ ስራሕ</t>
         </is>
       </c>
       <c r="G186" s="13" t="inlineStr">
         <is>
-          <t>{n} maalmood ka hor</t>
+          <t>Shaqeynaya</t>
         </is>
       </c>
       <c r="H186" s="14" t="inlineStr"/>
@@ -12503,7 +12503,7 @@
     <row r="187" ht="44" customHeight="1">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t>channel_all_from</t>
+          <t>channel_ready</t>
         </is>
       </c>
       <c r="B187" s="11" t="inlineStr">
@@ -12513,27 +12513,27 @@
       </c>
       <c r="C187" s="11" t="inlineStr">
         <is>
-          <t>All {n} conversations came from {label}.</t>
+          <t>Ready to connect</t>
         </is>
       </c>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>ሁሉም {n} ውይይቶች ከ{label} መጥተዋል።</t>
+          <t>ለመገናኘት ዝግጁ</t>
         </is>
       </c>
       <c r="E187" s="13" t="inlineStr">
         <is>
-          <t>Mariin {n} hundi {label} irraa dhufe.</t>
+          <t>Walqunnamuuf qophaa'aa</t>
         </is>
       </c>
       <c r="F187" s="12" t="inlineStr">
         <is>
-          <t>ኩሎም {n} ዝርርባት ካብ {label} መጺኦም።</t>
+          <t>ንምርኻብ ድሉው</t>
         </is>
       </c>
       <c r="G187" s="13" t="inlineStr">
         <is>
-          <t>Dhammaan {n} wadahadal waxay ka yimaadeen {label}.</t>
+          <t>Diyaar u ah xiriirka</t>
         </is>
       </c>
       <c r="H187" s="14" t="inlineStr"/>
@@ -12541,7 +12541,7 @@
     <row r="188" ht="44" customHeight="1">
       <c r="A188" s="11" t="inlineStr">
         <is>
-          <t>channel_live</t>
+          <t>channel_needs_setup</t>
         </is>
       </c>
       <c r="B188" s="11" t="inlineStr">
@@ -12551,27 +12551,27 @@
       </c>
       <c r="C188" s="11" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Needs setup</t>
         </is>
       </c>
       <c r="D188" s="12" t="inlineStr">
         <is>
-          <t>በሥራ ላይ</t>
+          <t>ማዋቀር ይፈልጋል</t>
         </is>
       </c>
       <c r="E188" s="13" t="inlineStr">
         <is>
-          <t>Hojiirra</t>
+          <t>Qindeessuu barbaada</t>
         </is>
       </c>
       <c r="F188" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ስራሕ</t>
+          <t>ምድላው የድልዮ</t>
         </is>
       </c>
       <c r="G188" s="13" t="inlineStr">
         <is>
-          <t>Shaqeynaya</t>
+          <t>Waxay u baahan tahay dejin</t>
         </is>
       </c>
       <c r="H188" s="14" t="inlineStr"/>
@@ -12579,7 +12579,7 @@
     <row r="189" ht="44" customHeight="1">
       <c r="A189" s="11" t="inlineStr">
         <is>
-          <t>channel_ready</t>
+          <t>share_by_channel</t>
         </is>
       </c>
       <c r="B189" s="11" t="inlineStr">
@@ -12589,27 +12589,27 @@
       </c>
       <c r="C189" s="11" t="inlineStr">
         <is>
-          <t>Ready to connect</t>
+          <t>Share of conversations by channel</t>
         </is>
       </c>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>ለመገናኘት ዝግጁ</t>
+          <t>በመስመር የተከፋፈሉ ውይይቶች ድርሻ</t>
         </is>
       </c>
       <c r="E189" s="13" t="inlineStr">
         <is>
-          <t>Walqunnamuuf qophaa'aa</t>
+          <t>Qooda marii karaa tokkoon tokkoon isaanii</t>
         </is>
       </c>
       <c r="F189" s="12" t="inlineStr">
         <is>
-          <t>ንምርኻብ ድሉው</t>
+          <t>ብመስመር ዝተኸፋፈለ ግደ ዝርርባት</t>
         </is>
       </c>
       <c r="G189" s="13" t="inlineStr">
         <is>
-          <t>Diyaar u ah xiriirka</t>
+          <t>Qaybta wadahadallada kanaalka</t>
         </is>
       </c>
       <c r="H189" s="14" t="inlineStr"/>
@@ -12617,7 +12617,7 @@
     <row r="190" ht="44" customHeight="1">
       <c r="A190" s="11" t="inlineStr">
         <is>
-          <t>channel_needs_setup</t>
+          <t>up_to_date</t>
         </is>
       </c>
       <c r="B190" s="11" t="inlineStr">
@@ -12627,27 +12627,27 @@
       </c>
       <c r="C190" s="11" t="inlineStr">
         <is>
-          <t>Needs setup</t>
+          <t>Up to date</t>
         </is>
       </c>
       <c r="D190" s="12" t="inlineStr">
         <is>
-          <t>ማዋቀር ይፈልጋል</t>
+          <t>የተዘመነ</t>
         </is>
       </c>
       <c r="E190" s="13" t="inlineStr">
         <is>
-          <t>Qindeessuu barbaada</t>
+          <t>Haaraa</t>
         </is>
       </c>
       <c r="F190" s="12" t="inlineStr">
         <is>
-          <t>ምድላው የድልዮ</t>
+          <t>ዝተሓደሰ</t>
         </is>
       </c>
       <c r="G190" s="13" t="inlineStr">
         <is>
-          <t>Waxay u baahan tahay dejin</t>
+          <t>La cusbooneysiiyay</t>
         </is>
       </c>
       <c r="H190" s="14" t="inlineStr"/>
@@ -12655,7 +12655,7 @@
     <row r="191" ht="44" customHeight="1">
       <c r="A191" s="11" t="inlineStr">
         <is>
-          <t>share_by_channel</t>
+          <t>updated_m_ago</t>
         </is>
       </c>
       <c r="B191" s="11" t="inlineStr">
@@ -12665,27 +12665,27 @@
       </c>
       <c r="C191" s="11" t="inlineStr">
         <is>
-          <t>Share of conversations by channel</t>
+          <t>Updated {n}m ago</t>
         </is>
       </c>
       <c r="D191" s="12" t="inlineStr">
         <is>
-          <t>በመስመር የተከፋፈሉ ውይይቶች ድርሻ</t>
+          <t>ከ{n} ደቂቃ በፊት ተዘምኗል</t>
         </is>
       </c>
       <c r="E191" s="13" t="inlineStr">
         <is>
-          <t>Qooda marii karaa tokkoon tokkoon isaanii</t>
+          <t>Daqiiqaa {n} dura haaromfame</t>
         </is>
       </c>
       <c r="F191" s="12" t="inlineStr">
         <is>
-          <t>ብመስመር ዝተኸፋፈለ ግደ ዝርርባት</t>
+          <t>ቅድሚ {n} ደቒቕ ተሓዲሱ</t>
         </is>
       </c>
       <c r="G191" s="13" t="inlineStr">
         <is>
-          <t>Qaybta wadahadallada kanaalka</t>
+          <t>La cusbooneysiiyay {n}daq ka hor</t>
         </is>
       </c>
       <c r="H191" s="14" t="inlineStr"/>
@@ -12693,7 +12693,7 @@
     <row r="192" ht="44" customHeight="1">
       <c r="A192" s="11" t="inlineStr">
         <is>
-          <t>up_to_date</t>
+          <t>updated_h_ago</t>
         </is>
       </c>
       <c r="B192" s="11" t="inlineStr">
@@ -12703,27 +12703,27 @@
       </c>
       <c r="C192" s="11" t="inlineStr">
         <is>
-          <t>Up to date</t>
+          <t>Updated {n}h ago</t>
         </is>
       </c>
       <c r="D192" s="12" t="inlineStr">
         <is>
-          <t>የተዘመነ</t>
+          <t>ከ{n} ሰዓት በፊት ተዘምኗል</t>
         </is>
       </c>
       <c r="E192" s="13" t="inlineStr">
         <is>
-          <t>Haaraa</t>
+          <t>Sa'aatii {n} dura haaromfame</t>
         </is>
       </c>
       <c r="F192" s="12" t="inlineStr">
         <is>
-          <t>ዝተሓደሰ</t>
+          <t>ቅድሚ {n} ሰዓት ተሓዲሱ</t>
         </is>
       </c>
       <c r="G192" s="13" t="inlineStr">
         <is>
-          <t>La cusbooneysiiyay</t>
+          <t>La cusbooneysiiyay {n}saac ka hor</t>
         </is>
       </c>
       <c r="H192" s="14" t="inlineStr"/>
@@ -12731,7 +12731,7 @@
     <row r="193" ht="44" customHeight="1">
       <c r="A193" s="11" t="inlineStr">
         <is>
-          <t>updated_m_ago</t>
+          <t>queue</t>
         </is>
       </c>
       <c r="B193" s="11" t="inlineStr">
@@ -12741,27 +12741,27 @@
       </c>
       <c r="C193" s="11" t="inlineStr">
         <is>
-          <t>Updated {n}m ago</t>
+          <t>Queue</t>
         </is>
       </c>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ደቂቃ በፊት ተዘምኗል</t>
+          <t>ወረፋ</t>
         </is>
       </c>
       <c r="E193" s="13" t="inlineStr">
         <is>
-          <t>Daqiiqaa {n} dura haaromfame</t>
+          <t>Sararaa</t>
         </is>
       </c>
       <c r="F193" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ደቒቕ ተሓዲሱ</t>
+          <t>ሪጋ</t>
         </is>
       </c>
       <c r="G193" s="13" t="inlineStr">
         <is>
-          <t>La cusbooneysiiyay {n}daq ka hor</t>
+          <t>Safka</t>
         </is>
       </c>
       <c r="H193" s="14" t="inlineStr"/>
@@ -12769,7 +12769,7 @@
     <row r="194" ht="44" customHeight="1">
       <c r="A194" s="11" t="inlineStr">
         <is>
-          <t>updated_h_ago</t>
+          <t>collapse</t>
         </is>
       </c>
       <c r="B194" s="11" t="inlineStr">
@@ -12779,27 +12779,27 @@
       </c>
       <c r="C194" s="11" t="inlineStr">
         <is>
-          <t>Updated {n}h ago</t>
+          <t>Collapse</t>
         </is>
       </c>
       <c r="D194" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ሰዓት በፊት ተዘምኗል</t>
+          <t>አጥብብ</t>
         </is>
       </c>
       <c r="E194" s="13" t="inlineStr">
         <is>
-          <t>Sa'aatii {n} dura haaromfame</t>
+          <t>Xiqqeessi</t>
         </is>
       </c>
       <c r="F194" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ሰዓት ተሓዲሱ</t>
+          <t>ኣጽብብ</t>
         </is>
       </c>
       <c r="G194" s="13" t="inlineStr">
         <is>
-          <t>La cusbooneysiiyay {n}saac ka hor</t>
+          <t>Yaree</t>
         </is>
       </c>
       <c r="H194" s="14" t="inlineStr"/>
@@ -12807,7 +12807,7 @@
     <row r="195" ht="44" customHeight="1">
       <c r="A195" s="11" t="inlineStr">
         <is>
-          <t>queue</t>
+          <t>expand</t>
         </is>
       </c>
       <c r="B195" s="11" t="inlineStr">
@@ -12817,27 +12817,27 @@
       </c>
       <c r="C195" s="11" t="inlineStr">
         <is>
-          <t>Queue</t>
+          <t>Expand</t>
         </is>
       </c>
       <c r="D195" s="12" t="inlineStr">
         <is>
-          <t>ወረፋ</t>
+          <t>አስፋ</t>
         </is>
       </c>
       <c r="E195" s="13" t="inlineStr">
         <is>
-          <t>Sararaa</t>
+          <t>Balleessi</t>
         </is>
       </c>
       <c r="F195" s="12" t="inlineStr">
         <is>
-          <t>ሪጋ</t>
+          <t>ኣስፍሕ</t>
         </is>
       </c>
       <c r="G195" s="13" t="inlineStr">
         <is>
-          <t>Safka</t>
+          <t>Balaadhi</t>
         </is>
       </c>
       <c r="H195" s="14" t="inlineStr"/>
@@ -12845,7 +12845,7 @@
     <row r="196" ht="44" customHeight="1">
       <c r="A196" s="11" t="inlineStr">
         <is>
-          <t>collapse</t>
+          <t>collapse_or_expand</t>
         </is>
       </c>
       <c r="B196" s="11" t="inlineStr">
@@ -12855,27 +12855,27 @@
       </c>
       <c r="C196" s="11" t="inlineStr">
         <is>
-          <t>Collapse</t>
+          <t>Collapse or expand the sidebar</t>
         </is>
       </c>
       <c r="D196" s="12" t="inlineStr">
         <is>
-          <t>አጥብብ</t>
+          <t>የጎን አሞሌውን አጥብብ ወይም አስፋ</t>
         </is>
       </c>
       <c r="E196" s="13" t="inlineStr">
         <is>
-          <t>Xiqqeessi</t>
+          <t>Cinaacha xiqqeessi ykn balleessi</t>
         </is>
       </c>
       <c r="F196" s="12" t="inlineStr">
         <is>
-          <t>ኣጽብብ</t>
+          <t>ናይ ጎኒ መስመር ኣጽብብ ወይ ኣስፍሕ</t>
         </is>
       </c>
       <c r="G196" s="13" t="inlineStr">
         <is>
-          <t>Yaree</t>
+          <t>Yaree ama balaadhi dhinaca</t>
         </is>
       </c>
       <c r="H196" s="14" t="inlineStr"/>
@@ -12883,7 +12883,7 @@
     <row r="197" ht="44" customHeight="1">
       <c r="A197" s="11" t="inlineStr">
         <is>
-          <t>expand</t>
+          <t>show_hide_channels</t>
         </is>
       </c>
       <c r="B197" s="11" t="inlineStr">
@@ -12893,27 +12893,27 @@
       </c>
       <c r="C197" s="11" t="inlineStr">
         <is>
-          <t>Expand</t>
+          <t>Show or hide the channel list</t>
         </is>
       </c>
       <c r="D197" s="12" t="inlineStr">
         <is>
-          <t>አስፋ</t>
+          <t>የመስመሮችን ዝርዝር አሳይ ወይም ደብቅ</t>
         </is>
       </c>
       <c r="E197" s="13" t="inlineStr">
         <is>
-          <t>Balleessi</t>
+          <t>Tarreeffama karaalee agarsiisi ykn dhoksi</t>
         </is>
       </c>
       <c r="F197" s="12" t="inlineStr">
         <is>
-          <t>ኣስፍሕ</t>
+          <t>ዝርዝር መስመራት ኣርኢ ወይ ሕባእ</t>
         </is>
       </c>
       <c r="G197" s="13" t="inlineStr">
         <is>
-          <t>Balaadhi</t>
+          <t>Muuji ama qari liiska kanaalada</t>
         </is>
       </c>
       <c r="H197" s="14" t="inlineStr"/>
@@ -12921,7 +12921,7 @@
     <row r="198" ht="44" customHeight="1">
       <c r="A198" s="11" t="inlineStr">
         <is>
-          <t>collapse_or_expand</t>
+          <t>today</t>
         </is>
       </c>
       <c r="B198" s="11" t="inlineStr">
@@ -12931,27 +12931,27 @@
       </c>
       <c r="C198" s="11" t="inlineStr">
         <is>
-          <t>Collapse or expand the sidebar</t>
+          <t>Today</t>
         </is>
       </c>
       <c r="D198" s="12" t="inlineStr">
         <is>
-          <t>የጎን አሞሌውን አጥብብ ወይም አስፋ</t>
+          <t>ዛሬ</t>
         </is>
       </c>
       <c r="E198" s="13" t="inlineStr">
         <is>
-          <t>Cinaacha xiqqeessi ykn balleessi</t>
+          <t>Har'a</t>
         </is>
       </c>
       <c r="F198" s="12" t="inlineStr">
         <is>
-          <t>ናይ ጎኒ መስመር ኣጽብብ ወይ ኣስፍሕ</t>
+          <t>ሎሚ</t>
         </is>
       </c>
       <c r="G198" s="13" t="inlineStr">
         <is>
-          <t>Yaree ama balaadhi dhinaca</t>
+          <t>Maanta</t>
         </is>
       </c>
       <c r="H198" s="14" t="inlineStr"/>
@@ -12959,7 +12959,7 @@
     <row r="199" ht="44" customHeight="1">
       <c r="A199" s="11" t="inlineStr">
         <is>
-          <t>show_hide_channels</t>
+          <t>yesterday</t>
         </is>
       </c>
       <c r="B199" s="11" t="inlineStr">
@@ -12969,27 +12969,27 @@
       </c>
       <c r="C199" s="11" t="inlineStr">
         <is>
-          <t>Show or hide the channel list</t>
+          <t>Yesterday</t>
         </is>
       </c>
       <c r="D199" s="12" t="inlineStr">
         <is>
-          <t>የመስመሮችን ዝርዝር አሳይ ወይም ደብቅ</t>
+          <t>ትናንት</t>
         </is>
       </c>
       <c r="E199" s="13" t="inlineStr">
         <is>
-          <t>Tarreeffama karaalee agarsiisi ykn dhoksi</t>
+          <t>Kaleessa</t>
         </is>
       </c>
       <c r="F199" s="12" t="inlineStr">
         <is>
-          <t>ዝርዝር መስመራት ኣርኢ ወይ ሕባእ</t>
+          <t>ትማሊ</t>
         </is>
       </c>
       <c r="G199" s="13" t="inlineStr">
         <is>
-          <t>Muuji ama qari liiska kanaalada</t>
+          <t>Shalay</t>
         </is>
       </c>
       <c r="H199" s="14" t="inlineStr"/>
@@ -12997,7 +12997,7 @@
     <row r="200" ht="44" customHeight="1">
       <c r="A200" s="11" t="inlineStr">
         <is>
-          <t>today</t>
+          <t>call_started</t>
         </is>
       </c>
       <c r="B200" s="11" t="inlineStr">
@@ -13007,27 +13007,27 @@
       </c>
       <c r="C200" s="11" t="inlineStr">
         <is>
-          <t>Today</t>
+          <t>The customer asked for a person here</t>
         </is>
       </c>
       <c r="D200" s="12" t="inlineStr">
         <is>
-          <t>ዛሬ</t>
+          <t>ደንበኛው እዚህ ላይ ሰው ጠየቀ</t>
         </is>
       </c>
       <c r="E200" s="13" t="inlineStr">
         <is>
-          <t>Har'a</t>
+          <t>Maamilaan asitti nama gaafate</t>
         </is>
       </c>
       <c r="F200" s="12" t="inlineStr">
         <is>
-          <t>ሎሚ</t>
+          <t>እቲ ዓሚል ኣብዚ ሰብ ሓቲቱ</t>
         </is>
       </c>
       <c r="G200" s="13" t="inlineStr">
         <is>
-          <t>Maanta</t>
+          <t>Macmiilku halkan ayuu qof weydiistay</t>
         </is>
       </c>
       <c r="H200" s="14" t="inlineStr"/>
@@ -13035,7 +13035,7 @@
     <row r="201" ht="44" customHeight="1">
       <c r="A201" s="11" t="inlineStr">
         <is>
-          <t>yesterday</t>
+          <t>no_messages</t>
         </is>
       </c>
       <c r="B201" s="11" t="inlineStr">
@@ -13045,27 +13045,27 @@
       </c>
       <c r="C201" s="11" t="inlineStr">
         <is>
-          <t>Yesterday</t>
+          <t>No messages in this conversation.</t>
         </is>
       </c>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>ትናንት</t>
+          <t>በዚህ ውይይት ውስጥ መልእክት የለም።</t>
         </is>
       </c>
       <c r="E201" s="13" t="inlineStr">
         <is>
-          <t>Kaleessa</t>
+          <t>Marii kana keessa ergaan hin jiru.</t>
         </is>
       </c>
       <c r="F201" s="12" t="inlineStr">
         <is>
-          <t>ትማሊ</t>
+          <t>ኣብዚ ዝርርብ መልእኽቲ የለን።</t>
         </is>
       </c>
       <c r="G201" s="13" t="inlineStr">
         <is>
-          <t>Shalay</t>
+          <t>Wadahadalkan fariin kuma jirto.</t>
         </is>
       </c>
       <c r="H201" s="14" t="inlineStr"/>
@@ -13073,7 +13073,7 @@
     <row r="202" ht="44" customHeight="1">
       <c r="A202" s="11" t="inlineStr">
         <is>
-          <t>earlier_in_conversation</t>
+          <t>donut_all_in_one</t>
         </is>
       </c>
       <c r="B202" s="11" t="inlineStr">
@@ -13083,27 +13083,27 @@
       </c>
       <c r="C202" s="11" t="inlineStr">
         <is>
-          <t>Earlier in this conversation</t>
+          <t>The single {unit} was in {label}.</t>
         </is>
       </c>
       <c r="D202" s="12" t="inlineStr">
         <is>
-          <t>ቀደም ብሎ በዚህ ውይይት</t>
+          <t>ብቸኛው {unit} በ{label} ነበር።</t>
         </is>
       </c>
       <c r="E202" s="13" t="inlineStr">
         <is>
-          <t>Marii kana keessatti duraan</t>
+          <t>{unit} tokkichi {label} keessa ture.</t>
         </is>
       </c>
       <c r="F202" s="12" t="inlineStr">
         <is>
-          <t>ኣቐዲሙ ኣብዚ ዝርርብ</t>
+          <t>እቲ ሓደ {unit} ብ{label} ነይሩ።</t>
         </is>
       </c>
       <c r="G202" s="13" t="inlineStr">
         <is>
-          <t>Horaantii wadahadalkan</t>
+          <t>{unit} kaliya wuxuu ku jiray {label}.</t>
         </is>
       </c>
       <c r="H202" s="14" t="inlineStr"/>
@@ -13111,7 +13111,7 @@
     <row r="203" ht="44" customHeight="1">
       <c r="A203" s="11" t="inlineStr">
         <is>
-          <t>call_started</t>
+          <t>channel_all_from_one</t>
         </is>
       </c>
       <c r="B203" s="11" t="inlineStr">
@@ -13121,27 +13121,27 @@
       </c>
       <c r="C203" s="11" t="inlineStr">
         <is>
-          <t>The customer asked for a person here</t>
+          <t>The single conversation came from {label}.</t>
         </is>
       </c>
       <c r="D203" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛው እዚህ ላይ ሰው ጠየቀ</t>
+          <t>ብቸኛው ውይይት ከ{label} መጥቷል።</t>
         </is>
       </c>
       <c r="E203" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan asitti nama gaafate</t>
+          <t>Mariin tokkichi {label} irraa dhufe.</t>
         </is>
       </c>
       <c r="F203" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዓሚል ኣብዚ ሰብ ሓቲቱ</t>
+          <t>እቲ ሓደ ዝርርብ ካብ {label} መጺኡ።</t>
         </is>
       </c>
       <c r="G203" s="13" t="inlineStr">
         <is>
-          <t>Macmiilku halkan ayuu qof weydiistay</t>
+          <t>Wadahadalka kaliya wuxuu ka yimid {label}.</t>
         </is>
       </c>
       <c r="H203" s="14" t="inlineStr"/>
@@ -13149,7 +13149,7 @@
     <row r="204" ht="44" customHeight="1">
       <c r="A204" s="11" t="inlineStr">
         <is>
-          <t>no_messages</t>
+          <t>unit_conversation</t>
         </is>
       </c>
       <c r="B204" s="11" t="inlineStr">
@@ -13159,27 +13159,27 @@
       </c>
       <c r="C204" s="11" t="inlineStr">
         <is>
-          <t>No messages in this conversation.</t>
+          <t>conversation</t>
         </is>
       </c>
       <c r="D204" s="12" t="inlineStr">
         <is>
-          <t>በዚህ ውይይት ውስጥ መልእክት የለም።</t>
+          <t>ውይይት</t>
         </is>
       </c>
       <c r="E204" s="13" t="inlineStr">
         <is>
-          <t>Marii kana keessa ergaan hin jiru.</t>
+          <t>marii</t>
         </is>
       </c>
       <c r="F204" s="12" t="inlineStr">
         <is>
-          <t>ኣብዚ ዝርርብ መልእኽቲ የለን።</t>
+          <t>ዝርርብ</t>
         </is>
       </c>
       <c r="G204" s="13" t="inlineStr">
         <is>
-          <t>Wadahadalkan fariin kuma jirto.</t>
+          <t>wadahadal</t>
         </is>
       </c>
       <c r="H204" s="14" t="inlineStr"/>
@@ -13187,7 +13187,7 @@
     <row r="205" ht="44" customHeight="1">
       <c r="A205" s="11" t="inlineStr">
         <is>
-          <t>donut_all_in_one</t>
+          <t>live_sessions</t>
         </is>
       </c>
       <c r="B205" s="11" t="inlineStr">
@@ -13197,27 +13197,27 @@
       </c>
       <c r="C205" s="11" t="inlineStr">
         <is>
-          <t>The single {unit} was in {label}.</t>
+          <t>Live sessions</t>
         </is>
       </c>
       <c r="D205" s="12" t="inlineStr">
         <is>
-          <t>ብቸኛው {unit} በ{label} ነበር።</t>
+          <t>የቀጥታ ክፍለ-ጊዜዎች</t>
         </is>
       </c>
       <c r="E205" s="13" t="inlineStr">
         <is>
-          <t>{unit} tokkichi {label} keessa ture.</t>
+          <t>Marii kallattii</t>
         </is>
       </c>
       <c r="F205" s="12" t="inlineStr">
         <is>
-          <t>እቲ ሓደ {unit} ብ{label} ነይሩ።</t>
+          <t>ቀጥታ ክፍለ-ግዜታት</t>
         </is>
       </c>
       <c r="G205" s="13" t="inlineStr">
         <is>
-          <t>{unit} kaliya wuxuu ku jiray {label}.</t>
+          <t>Kalfadhiyada tooska ah</t>
         </is>
       </c>
       <c r="H205" s="14" t="inlineStr"/>
@@ -13225,7 +13225,7 @@
     <row r="206" ht="44" customHeight="1">
       <c r="A206" s="11" t="inlineStr">
         <is>
-          <t>channel_all_from_one</t>
+          <t>switched_off_for_bank</t>
         </is>
       </c>
       <c r="B206" s="11" t="inlineStr">
@@ -13235,27 +13235,27 @@
       </c>
       <c r="C206" s="11" t="inlineStr">
         <is>
-          <t>The single conversation came from {label}.</t>
+          <t>Switched off for this bank</t>
         </is>
       </c>
       <c r="D206" s="12" t="inlineStr">
         <is>
-          <t>ብቸኛው ውይይት ከ{label} መጥቷል።</t>
+          <t>ለዚህ ባንክ ጠፍቷል</t>
         </is>
       </c>
       <c r="E206" s="13" t="inlineStr">
         <is>
-          <t>Mariin tokkichi {label} irraa dhufe.</t>
+          <t>Baankii kanaaf dhaamsameera</t>
         </is>
       </c>
       <c r="F206" s="12" t="inlineStr">
         <is>
-          <t>እቲ ሓደ ዝርርብ ካብ {label} መጺኡ።</t>
+          <t>ነዚ ባንኪ ጠፊኡ</t>
         </is>
       </c>
       <c r="G206" s="13" t="inlineStr">
         <is>
-          <t>Wadahadalka kaliya wuxuu ka yimid {label}.</t>
+          <t>Bangigan waa la damiyay</t>
         </is>
       </c>
       <c r="H206" s="14" t="inlineStr"/>
@@ -13263,7 +13263,7 @@
     <row r="207" ht="44" customHeight="1">
       <c r="A207" s="11" t="inlineStr">
         <is>
-          <t>unit_conversation</t>
+          <t>switched_on_nobody_on_duty</t>
         </is>
       </c>
       <c r="B207" s="11" t="inlineStr">
@@ -13273,33 +13273,1667 @@
       </c>
       <c r="C207" s="11" t="inlineStr">
         <is>
-          <t>conversation</t>
+          <t>Switched on — but nobody is on duty</t>
         </is>
       </c>
       <c r="D207" s="12" t="inlineStr">
         <is>
-          <t>ውይይት</t>
+          <t>በርቷል — ግን ማንም በሥራ ላይ የለም</t>
         </is>
       </c>
       <c r="E207" s="13" t="inlineStr">
         <is>
-          <t>marii</t>
+          <t>Banameera — garuu namni hojii irra hin jiru</t>
         </is>
       </c>
       <c r="F207" s="12" t="inlineStr">
         <is>
-          <t>ዝርርብ</t>
+          <t>በሪሁ — ግና ዋላ ሓደ ኣብ ስራሕ የለን</t>
         </is>
       </c>
       <c r="G207" s="13" t="inlineStr">
         <is>
-          <t>wadahadal</t>
+          <t>Waa la shiday — laakiin qofna shaqada ma joogo</t>
         </is>
       </c>
       <c r="H207" s="14" t="inlineStr"/>
     </row>
+    <row r="208" ht="44" customHeight="1">
+      <c r="A208" s="11" t="inlineStr">
+        <is>
+          <t>no_teller_button</t>
+        </is>
+      </c>
+      <c r="B208" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C208" s="11" t="inlineStr">
+        <is>
+          <t>No “Speak to a teller” button appears in your widget.</t>
+        </is>
+      </c>
+      <c r="D208" s="12" t="inlineStr">
+        <is>
+          <t>በመግብርዎ ውስጥ “ከገንዘብ ተቀባይ ጋር ይነጋገሩ” የሚል አዝራር አይታይም።</t>
+        </is>
+      </c>
+      <c r="E208" s="13" t="inlineStr">
+        <is>
+          <t>Widjetii keessan keessatti qabduun “Namaa waliin haasa'aa” hin mul'atu.</t>
+        </is>
+      </c>
+      <c r="F208" s="12" t="inlineStr">
+        <is>
+          <t>ኣብ መግበሪኹም “ምስ ተቐባሊ ገንዘብ ተዛረቡ” ዝብል መጠወቒ ኣይረአን።</t>
+        </is>
+      </c>
+      <c r="G208" s="13" t="inlineStr">
+        <is>
+          <t>Badhanka “La hadal shaqaale” kama muuqan widget-kaaga.</t>
+        </is>
+      </c>
+      <c r="H208" s="14" t="inlineStr"/>
+    </row>
+    <row r="209" ht="44" customHeight="1">
+      <c r="A209" s="11" t="inlineStr">
+        <is>
+          <t>on_duty_explainer</t>
+        </is>
+      </c>
+      <c r="B209" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C209" s="11" t="inlineStr">
+        <is>
+          <t>You are on duty, so waiting customers can be routed to you. Go off duty from the sidebar when you step away — you stay on the air anywhere in the console until you do.</t>
+        </is>
+      </c>
+      <c r="D209" s="12" t="inlineStr">
+        <is>
+          <t>በሥራ ላይ ነዎት፤ ስለዚህ የሚጠብቁ ደንበኞች ወደ እርስዎ ሊመሩ ይችላሉ። ሲርቁ ከጎን አሞሌው ከሥራ ውጡ — እስከዚያ ድረስ በየትኛውም ገጽ ላይ በሥራ ላይ ይቆያሉ።</t>
+        </is>
+      </c>
+      <c r="E209" s="13" t="inlineStr">
+        <is>
+          <t>Hojii irra jirtu, kanaafuu maamiltoonni eegaa jiran gara keessan qajeelfamuu danda'u. Yeroo achii deemtan cinaacha irraa hojii keessaa ba'aa — hanga sanatti fuula kamiyyuu irratti hojii irra turtu.</t>
+        </is>
+      </c>
+      <c r="F209" s="12" t="inlineStr">
+        <is>
+          <t>ኣብ ስራሕ ኢኹም፣ ስለዚ ዝጽበዩ ዓማዊል ናባኹም ክምርሑ ይኽእሉ። ክትርሕቁ ከለኹም ካብ ናይ ጎኒ መስመር ካብ ስራሕ ውጹ — ክሳብ ሽዑ ኣብ ዝኾነ ገጽ ኣብ ስራሕ ትጸንሑ።</t>
+        </is>
+      </c>
+      <c r="G209" s="13" t="inlineStr">
+        <is>
+          <t>Shaqada ayaad joogtaa, sidaas darteed macaamiisha sugaya waa lagu soo dhiibi karaa. Marka aad tagto shaqada ka bax dhinaca — ilaa markaas bog kasta ayaad ku sii shaqeynaysaa.</t>
+        </is>
+      </c>
+      <c r="H209" s="14" t="inlineStr"/>
+    </row>
+    <row r="210" ht="44" customHeight="1">
+      <c r="A210" s="11" t="inlineStr">
+        <is>
+          <t>off_duty_explainer</t>
+        </is>
+      </c>
+      <c r="B210" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C210" s="11" t="inlineStr">
+        <is>
+          <t>Switch On duty in the sidebar to start taking calls. It follows you across every page, so you no longer have to keep this one open.</t>
+        </is>
+      </c>
+      <c r="D210" s="12" t="inlineStr">
+        <is>
+          <t>ጥሪዎችን መቀበል ለመጀመር ከጎን አሞሌው “በሥራ ላይ” ያብሩ። በሁሉም ገጽ ላይ ይከተልዎታል፤ ስለዚህ ይህን ገጽ ክፍት ማድረግ አያስፈልግም።</t>
+        </is>
+      </c>
+      <c r="E210" s="13" t="inlineStr">
+        <is>
+          <t>Bilbila fudhachuu jalqabuuf cinaacha irraa “Hojii irra” banaa. Fuula hunda irratti isin hordofa, kanaafuu fuula kana banaa gochuun hin barbaachisu.</t>
+        </is>
+      </c>
+      <c r="F210" s="12" t="inlineStr">
+        <is>
+          <t>ጻውዒታት ክትቅበሉ ንምጅማር ካብ ናይ ጎኒ መስመር “ኣብ ስራሕ” ኣብርሁ። ኣብ ኩሉ ገጽ ይስዕበኩም፣ ስለዚ ነዚ ገጽ ክፉት ምግባር ኣየድልን።</t>
+        </is>
+      </c>
+      <c r="G210" s="13" t="inlineStr">
+        <is>
+          <t>Si aad u bilowdo qaadista wicitaannada, dhinaca ka shid “Shaqada”. Bog kasta ayuu kula socdaa, sidaas darteed uma baahnid inaad tan furan ka tagto.</t>
+        </is>
+      </c>
+      <c r="H210" s="14" t="inlineStr"/>
+    </row>
+    <row r="211" ht="44" customHeight="1">
+      <c r="A211" s="11" t="inlineStr">
+        <is>
+          <t>colleague_must_be_on_duty</t>
+        </is>
+      </c>
+      <c r="B211" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C211" s="11" t="inlineStr">
+        <is>
+          <t>A colleague with permission to take calls has to be on duty before customers are offered one.</t>
+        </is>
+      </c>
+      <c r="D211" s="12" t="inlineStr">
+        <is>
+          <t>ጥሪ የመቀበል ፈቃድ ያለው ባልደረባ በሥራ ላይ መሆን አለበት፤ ከዚያ በፊት ለደንበኞች አይቀርብም።</t>
+        </is>
+      </c>
+      <c r="E211" s="13" t="inlineStr">
+        <is>
+          <t>Hojjetaan hayyama bilbila fudhachuu qabu hojii irra jiraachuu qaba, sana dura maamiltootaaf hin dhiyaatu.</t>
+        </is>
+      </c>
+      <c r="F211" s="12" t="inlineStr">
+        <is>
+          <t>ጻውዒት ናይ ምቕባል ፍቓድ ዘለዎ መሳርሕቲ ኣብ ስራሕ ክህሉ ኣለዎ፣ ቅድሚኡ ንዓማዊል ኣይቀርብን።</t>
+        </is>
+      </c>
+      <c r="G211" s="13" t="inlineStr">
+        <is>
+          <t>Shaqaale haysta ogolaanshaha qaadista wicitaannada waa inuu shaqada joogaa ka hor inta aan macaamiisha la siin.</t>
+        </is>
+      </c>
+      <c r="H211" s="14" t="inlineStr"/>
+    </row>
+    <row r="212" ht="44" customHeight="1">
+      <c r="A212" s="11" t="inlineStr">
+        <is>
+          <t>i_can_converse_in</t>
+        </is>
+      </c>
+      <c r="B212" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C212" s="11" t="inlineStr">
+        <is>
+          <t>I can hold a conversation in:</t>
+        </is>
+      </c>
+      <c r="D212" s="12" t="inlineStr">
+        <is>
+          <t>በእነዚህ ቋንቋዎች መነጋገር እችላለሁ፦</t>
+        </is>
+      </c>
+      <c r="E212" s="13" t="inlineStr">
+        <is>
+          <t>Afaanota kanneeniin haasa'uu nan danda'a:</t>
+        </is>
+      </c>
+      <c r="F212" s="12" t="inlineStr">
+        <is>
+          <t>በዞም ቋንቋታት ክዛረብ እኽእል፦</t>
+        </is>
+      </c>
+      <c r="G212" s="13" t="inlineStr">
+        <is>
+          <t>Waxaan ku hadli karaa:</t>
+        </is>
+      </c>
+      <c r="H212" s="14" t="inlineStr"/>
+    </row>
+    <row r="213" ht="44" customHeight="1">
+      <c r="A213" s="11" t="inlineStr">
+        <is>
+          <t>languages_picked_note</t>
+        </is>
+      </c>
+      <c r="B213" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C213" s="11" t="inlineStr">
+        <is>
+          <t>Customers writing in these reach you first. Everyone else still reaches you — after a short wait, so nobody is stranded.</t>
+        </is>
+      </c>
+      <c r="D213" s="12" t="inlineStr">
+        <is>
+          <t>በእነዚህ ቋንቋዎች የሚጽፉ ደንበኞች መጀመሪያ ወደ እርስዎ ይደርሳሉ። ሌሎችም ይደርሳሉ — ከአጭር ጥበቃ በኋላ፤ ማንም አይቀርም።</t>
+        </is>
+      </c>
+      <c r="E213" s="13" t="inlineStr">
+        <is>
+          <t>Maamiltoonni afaanota kanaan barreessan jalqaba isin bira ga'u. Kaan hundinuu ammas isin bira ga'u — eegumsa gabaabaa booda, namni hafu hin jiru.</t>
+        </is>
+      </c>
+      <c r="F213" s="12" t="inlineStr">
+        <is>
+          <t>በዞም ቋንቋታት ዝጽሕፉ ዓማዊል ቅድም ናባኹም ይበጽሑ። እቶም ካልኦት እውን ይበጽሑ — ድሕሪ ሓጺር ጽበት፣ ዋላ ሓደ ኣይተርፍን።</t>
+        </is>
+      </c>
+      <c r="G213" s="13" t="inlineStr">
+        <is>
+          <t>Macaamiisha ku qora kuwan ayaa marka hore kugu soo gaara. Qof kastana wuu ku soo gaari doonaa — sug gaaban ka dib, sidaas qofna ma harayo.</t>
+        </is>
+      </c>
+      <c r="H213" s="14" t="inlineStr"/>
+    </row>
+    <row r="214" ht="44" customHeight="1">
+      <c r="A214" s="11" t="inlineStr">
+        <is>
+          <t>languages_none_note</t>
+        </is>
+      </c>
+      <c r="B214" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C214" s="11" t="inlineStr">
+        <is>
+          <t>Nothing selected, so every waiting customer is offered to you in plain oldest-first order.</t>
+        </is>
+      </c>
+      <c r="D214" s="12" t="inlineStr">
+        <is>
+          <t>ምንም አልተመረጠም፤ ስለዚህ እያንዳንዱ የሚጠብቅ ደንበኛ በቀላል ቀዳሚ-መጀመሪያ ቅደም ተከተል ይቀርብልዎታል።</t>
+        </is>
+      </c>
+      <c r="E214" s="13" t="inlineStr">
+        <is>
+          <t>Wanti filatame hin jiru, kanaafuu maamilli eegaa jiru hundi tartiiba dursaa-jalqabaatiin isinii dhiyaata.</t>
+        </is>
+      </c>
+      <c r="F214" s="12" t="inlineStr">
+        <is>
+          <t>ዋላ ሓደ ኣይተመርጸን፣ ስለዚ ነፍስ ወከፍ ዝጽበ ዓሚል ብቐሊል ናይ ቀዳምነት ስርዓት ይቐርበልኩም።</t>
+        </is>
+      </c>
+      <c r="G214" s="13" t="inlineStr">
+        <is>
+          <t>Waxba lama dooran, sidaas darteed macmiil kasta oo sugaya waxaa laguu soo bandhigayaa sida caadiga ah ee ugu horreeya.</t>
+        </is>
+      </c>
+      <c r="H214" s="14" t="inlineStr"/>
+    </row>
+    <row r="215" ht="44" customHeight="1">
+      <c r="A215" s="11" t="inlineStr">
+        <is>
+          <t>languages_updated</t>
+        </is>
+      </c>
+      <c r="B215" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C215" s="11" t="inlineStr">
+        <is>
+          <t>Languages updated</t>
+        </is>
+      </c>
+      <c r="D215" s="12" t="inlineStr">
+        <is>
+          <t>ቋንቋዎች ተዘምነዋል</t>
+        </is>
+      </c>
+      <c r="E215" s="13" t="inlineStr">
+        <is>
+          <t>Afaanonni haaromfaman</t>
+        </is>
+      </c>
+      <c r="F215" s="12" t="inlineStr">
+        <is>
+          <t>ቋንቋታት ተሓዲሶም</t>
+        </is>
+      </c>
+      <c r="G215" s="13" t="inlineStr">
+        <is>
+          <t>Luqadaha waa la cusbooneysiiyay</t>
+        </is>
+      </c>
+      <c r="H215" s="14" t="inlineStr"/>
+    </row>
+    <row r="216" ht="44" customHeight="1">
+      <c r="A216" s="11" t="inlineStr">
+        <is>
+          <t>media_video</t>
+        </is>
+      </c>
+      <c r="B216" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C216" s="11" t="inlineStr">
+        <is>
+          <t>Video</t>
+        </is>
+      </c>
+      <c r="D216" s="12" t="inlineStr">
+        <is>
+          <t>ቪዲዮ</t>
+        </is>
+      </c>
+      <c r="E216" s="13" t="inlineStr">
+        <is>
+          <t>Viidiyoo</t>
+        </is>
+      </c>
+      <c r="F216" s="12" t="inlineStr">
+        <is>
+          <t>ቪድዮ</t>
+        </is>
+      </c>
+      <c r="G216" s="13" t="inlineStr">
+        <is>
+          <t>Fiidyow</t>
+        </is>
+      </c>
+      <c r="H216" s="14" t="inlineStr"/>
+    </row>
+    <row r="217" ht="44" customHeight="1">
+      <c r="A217" s="11" t="inlineStr">
+        <is>
+          <t>media_audio</t>
+        </is>
+      </c>
+      <c r="B217" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C217" s="11" t="inlineStr">
+        <is>
+          <t>Audio</t>
+        </is>
+      </c>
+      <c r="D217" s="12" t="inlineStr">
+        <is>
+          <t>ድምፅ</t>
+        </is>
+      </c>
+      <c r="E217" s="13" t="inlineStr">
+        <is>
+          <t>Sagalee</t>
+        </is>
+      </c>
+      <c r="F217" s="12" t="inlineStr">
+        <is>
+          <t>ድምጺ</t>
+        </is>
+      </c>
+      <c r="G217" s="13" t="inlineStr">
+        <is>
+          <t>Cod</t>
+        </is>
+      </c>
+      <c r="H217" s="14" t="inlineStr"/>
+    </row>
+    <row r="218" ht="44" customHeight="1">
+      <c r="A218" s="11" t="inlineStr">
+        <is>
+          <t>not_your_language</t>
+        </is>
+      </c>
+      <c r="B218" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C218" s="11" t="inlineStr">
+        <is>
+          <t>not your language</t>
+        </is>
+      </c>
+      <c r="D218" s="12" t="inlineStr">
+        <is>
+          <t>የእርስዎ ቋንቋ አይደለም</t>
+        </is>
+      </c>
+      <c r="E218" s="13" t="inlineStr">
+        <is>
+          <t>afaan keessanii miti</t>
+        </is>
+      </c>
+      <c r="F218" s="12" t="inlineStr">
+        <is>
+          <t>ናትኩም ቋንቋ ኣይኮነን</t>
+        </is>
+      </c>
+      <c r="G218" s="13" t="inlineStr">
+        <is>
+          <t>ma aha luqaddaada</t>
+        </is>
+      </c>
+      <c r="H218" s="14" t="inlineStr"/>
+    </row>
+    <row r="219" ht="44" customHeight="1">
+      <c r="A219" s="11" t="inlineStr">
+        <is>
+          <t>languages_first_note</t>
+        </is>
+      </c>
+      <c r="B219" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C219" s="11" t="inlineStr">
+        <is>
+          <t>Your languages first, longest wait within each. Anyone waiting too long moves to the top whatever they speak.</t>
+        </is>
+      </c>
+      <c r="D219" s="12" t="inlineStr">
+        <is>
+          <t>የእርስዎ ቋንቋዎች መጀመሪያ፤ በእያንዳንዱ ውስጥ ረጅም የጠበቀው ይቀድማል። ከልክ በላይ የጠበቀ ማንኛውም ሰው የሚናገረው ምንም ይሁን ወደ ላይ ይወጣል።</t>
+        </is>
+      </c>
+      <c r="E219" s="13" t="inlineStr">
+        <is>
+          <t>Afaanonni keessan jalqaba, tokkoon tokkoon isaanii keessatti kan yeroo dheeraa eege dursa. Namni baay'ee eege afaan kamiyyuu haa dubbatu gara oliitti deema.</t>
+        </is>
+      </c>
+      <c r="F219" s="12" t="inlineStr">
+        <is>
+          <t>ቋንቋታትኩም ቅድም፣ ኣብ ነፍስ ወከፍ እቲ ነዊሕ ዝጸንሐ ይቐድም። ካብ ንቡር ንላዕሊ ዝጸንሐ ዝኾነ ሰብ ዝዛረቦ ብዘየገድስ ናብ ላዕሊ ይመጽእ።</t>
+        </is>
+      </c>
+      <c r="G219" s="13" t="inlineStr">
+        <is>
+          <t>Luqadahaaga marka hore, kii ugu sugay dheeraa mid kasta gudahood. Qof kasta oo aad u sugay ayaa kor u kaca luqad kastoo uu ku hadloba.</t>
+        </is>
+      </c>
+      <c r="H219" s="14" t="inlineStr"/>
+    </row>
+    <row r="220" ht="44" customHeight="1">
+      <c r="A220" s="11" t="inlineStr">
+        <is>
+          <t>in_progress</t>
+        </is>
+      </c>
+      <c r="B220" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C220" s="11" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="D220" s="12" t="inlineStr">
+        <is>
+          <t>በሂደት ላይ</t>
+        </is>
+      </c>
+      <c r="E220" s="13" t="inlineStr">
+        <is>
+          <t>Adeemsa irra</t>
+        </is>
+      </c>
+      <c r="F220" s="12" t="inlineStr">
+        <is>
+          <t>ኣብ መስርሕ</t>
+        </is>
+      </c>
+      <c r="G220" s="13" t="inlineStr">
+        <is>
+          <t>Socda</t>
+        </is>
+      </c>
+      <c r="H220" s="14" t="inlineStr"/>
+    </row>
+    <row r="221" ht="44" customHeight="1">
+      <c r="A221" s="11" t="inlineStr">
+        <is>
+          <t>no_session_in_progress</t>
+        </is>
+      </c>
+      <c r="B221" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C221" s="11" t="inlineStr">
+        <is>
+          <t>No session in progress.</t>
+        </is>
+      </c>
+      <c r="D221" s="12" t="inlineStr">
+        <is>
+          <t>በሂደት ላይ ያለ ክፍለ-ጊዜ የለም።</t>
+        </is>
+      </c>
+      <c r="E221" s="13" t="inlineStr">
+        <is>
+          <t>Sessionii adeemsa irra jiru hin jiru.</t>
+        </is>
+      </c>
+      <c r="F221" s="12" t="inlineStr">
+        <is>
+          <t>ኣብ መስርሕ ዘሎ ክፍለ-ግዜ የለን።</t>
+        </is>
+      </c>
+      <c r="G221" s="13" t="inlineStr">
+        <is>
+          <t>Ma jiro kalfadhi socda.</t>
+        </is>
+      </c>
+      <c r="H221" s="14" t="inlineStr"/>
+    </row>
+    <row r="222" ht="44" customHeight="1">
+      <c r="A222" s="11" t="inlineStr">
+        <is>
+          <t>wait_suffix</t>
+        </is>
+      </c>
+      <c r="B222" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C222" s="11" t="inlineStr">
+        <is>
+          <t>wait</t>
+        </is>
+      </c>
+      <c r="D222" s="12" t="inlineStr">
+        <is>
+          <t>ጥበቃ</t>
+        </is>
+      </c>
+      <c r="E222" s="13" t="inlineStr">
+        <is>
+          <t>eegumsa</t>
+        </is>
+      </c>
+      <c r="F222" s="12" t="inlineStr">
+        <is>
+          <t>ጽበት</t>
+        </is>
+      </c>
+      <c r="G222" s="13" t="inlineStr">
+        <is>
+          <t>sug</t>
+        </is>
+      </c>
+      <c r="H222" s="14" t="inlineStr"/>
+    </row>
+    <row r="223" ht="44" customHeight="1">
+      <c r="A223" s="11" t="inlineStr">
+        <is>
+          <t>what_session_covers</t>
+        </is>
+      </c>
+      <c r="B223" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C223" s="11" t="inlineStr">
+        <is>
+          <t>What a session covers</t>
+        </is>
+      </c>
+      <c r="D223" s="12" t="inlineStr">
+        <is>
+          <t>አንድ ክፍለ-ጊዜ ምን ይሸፍናል</t>
+        </is>
+      </c>
+      <c r="E223" s="13" t="inlineStr">
+        <is>
+          <t>Sessioniin maal haguuga</t>
+        </is>
+      </c>
+      <c r="F223" s="12" t="inlineStr">
+        <is>
+          <t>ሓደ ክፍለ-ግዜ እንታይ ይሽፍን</t>
+        </is>
+      </c>
+      <c r="G223" s="13" t="inlineStr">
+        <is>
+          <t>Waxa kalfadhigu daboolo</t>
+        </is>
+      </c>
+      <c r="H223" s="14" t="inlineStr"/>
+    </row>
+    <row r="224" ht="44" customHeight="1">
+      <c r="A224" s="11" t="inlineStr">
+        <is>
+          <t>session_scope_body</t>
+        </is>
+      </c>
+      <c r="B224" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C224" s="11" t="inlineStr">
+        <is>
+          <t>Before someone is identified: general questions about products, eligibility and how to apply. Once you have checked their Fayda ID against the account and asked something only the account holder could answer: their own application, documents and disputes.</t>
+        </is>
+      </c>
+      <c r="D224" s="12" t="inlineStr">
+        <is>
+          <t>አንድ ሰው ከመለየቱ በፊት፦ ስለ ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል አጠቃላይ ጥያቄዎች። የፋይዳ መታወቂያቸውን ከሂሳቡ ጋር አመሳክረው የሂሳቡ ባለቤት ብቻ ሊመልሰው የሚችለውን ከጠየቁ በኋላ፦ የራሳቸው ማመልከቻ፣ ሰነዶችና ቅሬታዎች።</t>
+        </is>
+      </c>
+      <c r="E224" s="13" t="inlineStr">
+        <is>
+          <t>Namni tokko utuu hin beekamin dura: gaaffii waliigalaa waa'ee oomishaalee, ulaagaa fi akkaataa itti iyyatan. Erga waraqaa eenyummaa Fayda isaanii herrega waliin madaalchiftanii waan abbaan herregaa qofti deebisuu danda'u gaafattanii booda: iyyannoo, sanadoota fi komii isaanii.</t>
+        </is>
+      </c>
+      <c r="F224" s="12" t="inlineStr">
+        <is>
+          <t>ሓደ ሰብ ቅድሚ ምልላዩ፦ ብዛዕባ ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን ሓፈሻዊ ሕቶታት። መንነት ፋይዳኦም ምስ ሕሳብ ኣረጋጊጽኩም እቲ ወናኒ ሕሳብ ጥራይ ክምልሶ ዝኽእል ምስ ሓተትኩም፦ ናቶም ምልክታ፣ ሰነዳትን ጥርዓናትን።</t>
+        </is>
+      </c>
+      <c r="G224" s="13" t="inlineStr">
+        <is>
+          <t>Ka hor inta aan qofka la aqoonsan: su'aalo guud oo ku saabsan alaabta, u-qalmitaanka iyo sida loo codsado. Marka aad hubiso aqoonsigooda Fayda ee xisaabta oo aad weydiiso wax uu kaliya milkiilaha xisaabtu ka jawaabi karo: codsigooda, dukumiintiyada iyo cabashooyinka.</t>
+        </is>
+      </c>
+      <c r="H224" s="14" t="inlineStr"/>
+    </row>
+    <row r="225" ht="44" customHeight="1">
+      <c r="A225" s="11" t="inlineStr">
+        <is>
+          <t>never_money_movement</t>
+        </is>
+      </c>
+      <c r="B225" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C225" s="11" t="inlineStr">
+        <is>
+          <t>Never, at any point and for anyone: deposits, withdrawals or transfers. Those do not happen on a call.</t>
+        </is>
+      </c>
+      <c r="D225" s="12" t="inlineStr">
+        <is>
+          <t>በፍጹም፣ በማንኛውም ጊዜና ለማንም፦ ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም። እነዚያ በጥሪ ላይ አይፈጸሙም።</t>
+        </is>
+      </c>
+      <c r="E225" s="13" t="inlineStr">
+        <is>
+          <t>Gonkumaa, yeroo kamiyyuu fi eenyuufiyyuu: kuusaa, baasii yookiin dabarsa hin jiru. Isaan sun bilbila irratti hin raawwataman.</t>
+        </is>
+      </c>
+      <c r="F225" s="12" t="inlineStr">
+        <is>
+          <t>ፈጺሙ፣ ኣብ ዝኾነ እዋንን ንዝኾነ ሰብን፦ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን። እዚኣቶም ኣብ ጻውዒት ኣይፍጸሙን።</t>
+        </is>
+      </c>
+      <c r="G225" s="13" t="inlineStr">
+        <is>
+          <t>Weligaa, wakhti kasta iyo qof kasta: dhigasho, qaadis ama wareejin ma jirto. Kuwaas wicitaan laguma sameeyo.</t>
+        </is>
+      </c>
+      <c r="H225" s="14" t="inlineStr"/>
+    </row>
+    <row r="226" ht="44" customHeight="1">
+      <c r="A226" s="11" t="inlineStr">
+        <is>
+          <t>open_escalation_queue</t>
+        </is>
+      </c>
+      <c r="B226" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C226" s="11" t="inlineStr">
+        <is>
+          <t>Open the escalation queue</t>
+        </is>
+      </c>
+      <c r="D226" s="12" t="inlineStr">
+        <is>
+          <t>የማሸጋገሪያ ወረፋውን ክፈት</t>
+        </is>
+      </c>
+      <c r="E226" s="13" t="inlineStr">
+        <is>
+          <t>Sararaa dabarsaa banaa</t>
+        </is>
+      </c>
+      <c r="F226" s="12" t="inlineStr">
+        <is>
+          <t>ሪጋ ምትሕልላፍ ክፈት</t>
+        </is>
+      </c>
+      <c r="G226" s="13" t="inlineStr">
+        <is>
+          <t>Fur safka gudbinta</t>
+        </is>
+      </c>
+      <c r="H226" s="14" t="inlineStr"/>
+    </row>
+    <row r="227" ht="44" customHeight="1">
+      <c r="A227" s="11" t="inlineStr">
+        <is>
+          <t>switch_dark_light</t>
+        </is>
+      </c>
+      <c r="B227" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C227" s="11" t="inlineStr">
+        <is>
+          <t>Switch between dark and light</t>
+        </is>
+      </c>
+      <c r="D227" s="12" t="inlineStr">
+        <is>
+          <t>በጨለማና በብርሃን መካከል ቀይር</t>
+        </is>
+      </c>
+      <c r="E227" s="13" t="inlineStr">
+        <is>
+          <t>Dukkanaa fi ifa gidduu jijjiiri</t>
+        </is>
+      </c>
+      <c r="F227" s="12" t="inlineStr">
+        <is>
+          <t>ኣብ መንጎ ጸላምን ብርሃንን ቀይር</t>
+        </is>
+      </c>
+      <c r="G227" s="13" t="inlineStr">
+        <is>
+          <t>U beddel mugdiga iyo iftiinka</t>
+        </is>
+      </c>
+      <c r="H227" s="14" t="inlineStr"/>
+    </row>
+    <row r="228" ht="44" customHeight="1">
+      <c r="A228" s="11" t="inlineStr">
+        <is>
+          <t>live_session</t>
+        </is>
+      </c>
+      <c r="B228" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C228" s="11" t="inlineStr">
+        <is>
+          <t>Live session</t>
+        </is>
+      </c>
+      <c r="D228" s="12" t="inlineStr">
+        <is>
+          <t>የቀጥታ ክፍለ-ጊዜ</t>
+        </is>
+      </c>
+      <c r="E228" s="13" t="inlineStr">
+        <is>
+          <t>Session kallattii</t>
+        </is>
+      </c>
+      <c r="F228" s="12" t="inlineStr">
+        <is>
+          <t>ቀጥታ ክፍለ-ግዜ</t>
+        </is>
+      </c>
+      <c r="G228" s="13" t="inlineStr">
+        <is>
+          <t>Kalfadhi toos ah</t>
+        </is>
+      </c>
+      <c r="H228" s="14" t="inlineStr"/>
+    </row>
+    <row r="229" ht="44" customHeight="1">
+      <c r="A229" s="11" t="inlineStr">
+        <is>
+          <t>customer_left_call</t>
+        </is>
+      </c>
+      <c r="B229" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C229" s="11" t="inlineStr">
+        <is>
+          <t>The customer has left the call.</t>
+        </is>
+      </c>
+      <c r="D229" s="12" t="inlineStr">
+        <is>
+          <t>ደንበኛው ጥሪውን ለቅቋል።</t>
+        </is>
+      </c>
+      <c r="E229" s="13" t="inlineStr">
+        <is>
+          <t>Maamilaan bilbila irraa ba'eera.</t>
+        </is>
+      </c>
+      <c r="F229" s="12" t="inlineStr">
+        <is>
+          <t>እቲ ዓሚል ካብቲ ጻውዒት ወጺኡ።</t>
+        </is>
+      </c>
+      <c r="G229" s="13" t="inlineStr">
+        <is>
+          <t>Macmiilku wicitaanka wuu ka baxay.</t>
+        </is>
+      </c>
+      <c r="H229" s="14" t="inlineStr"/>
+    </row>
+    <row r="230" ht="44" customHeight="1">
+      <c r="A230" s="11" t="inlineStr">
+        <is>
+          <t>waiting_for_customer</t>
+        </is>
+      </c>
+      <c r="B230" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C230" s="11" t="inlineStr">
+        <is>
+          <t>Waiting for the customer…</t>
+        </is>
+      </c>
+      <c r="D230" s="12" t="inlineStr">
+        <is>
+          <t>ደንበኛውን በመጠበቅ ላይ…</t>
+        </is>
+      </c>
+      <c r="E230" s="13" t="inlineStr">
+        <is>
+          <t>Maamilaa eegaa jirra…</t>
+        </is>
+      </c>
+      <c r="F230" s="12" t="inlineStr">
+        <is>
+          <t>ነቲ ዓሚል ንጽበ ኣለና…</t>
+        </is>
+      </c>
+      <c r="G230" s="13" t="inlineStr">
+        <is>
+          <t>Macmiilka la sugayo…</t>
+        </is>
+      </c>
+      <c r="H230" s="14" t="inlineStr"/>
+    </row>
+    <row r="231" ht="44" customHeight="1">
+      <c r="A231" s="11" t="inlineStr">
+        <is>
+          <t>mic_blocked</t>
+        </is>
+      </c>
+      <c r="B231" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C231" s="11" t="inlineStr">
+        <is>
+          <t>Microphone access is blocked. Allow it in your browser and take the session again.</t>
+        </is>
+      </c>
+      <c r="D231" s="12" t="inlineStr">
+        <is>
+          <t>የማይክሮፎን መዳረሻ ታግዷል። በአሳሽዎ ውስጥ ይፍቀዱና ክፍለ-ጊዜውን እንደገና ይውሰዱ።</t>
+        </is>
+      </c>
+      <c r="E231" s="13" t="inlineStr">
+        <is>
+          <t>Maayikiroofoonii dhorkameera. Biraawzarii keessan keessatti hayyamaatii session irra deebi'aa fudhadhaa.</t>
+        </is>
+      </c>
+      <c r="F231" s="12" t="inlineStr">
+        <is>
+          <t>መእተዊ ማይክሮፎን ተዓጊቱ። ኣብ መርበብ መንሸራተቲኹም ፍቐዱ እሞ ነቲ ክፍለ-ግዜ ደጊምኩም ውሰዱ።</t>
+        </is>
+      </c>
+      <c r="G231" s="13" t="inlineStr">
+        <is>
+          <t>Makarafoonka waa la xannibay. Browser-kaaga ka ogolow oo kalfadhiga mar kale qaado.</t>
+        </is>
+      </c>
+      <c r="H231" s="14" t="inlineStr"/>
+    </row>
+    <row r="232" ht="44" customHeight="1">
+      <c r="A232" s="11" t="inlineStr">
+        <is>
+          <t>unknown_error</t>
+        </is>
+      </c>
+      <c r="B232" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C232" s="11" t="inlineStr">
+        <is>
+          <t>unknown error</t>
+        </is>
+      </c>
+      <c r="D232" s="12" t="inlineStr">
+        <is>
+          <t>ያልታወቀ ስህተት</t>
+        </is>
+      </c>
+      <c r="E232" s="13" t="inlineStr">
+        <is>
+          <t>dogoggora hin beekamne</t>
+        </is>
+      </c>
+      <c r="F232" s="12" t="inlineStr">
+        <is>
+          <t>ዘይተፈልጠ ጌጋ</t>
+        </is>
+      </c>
+      <c r="G232" s="13" t="inlineStr">
+        <is>
+          <t>khalad aan la garanayn</t>
+        </is>
+      </c>
+      <c r="H232" s="14" t="inlineStr"/>
+    </row>
+    <row r="233" ht="44" customHeight="1">
+      <c r="A233" s="11" t="inlineStr">
+        <is>
+          <t>no_messages_yet</t>
+        </is>
+      </c>
+      <c r="B233" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C233" s="11" t="inlineStr">
+        <is>
+          <t>No messages yet.</t>
+        </is>
+      </c>
+      <c r="D233" s="12" t="inlineStr">
+        <is>
+          <t>እስካሁን መልእክት የለም።</t>
+        </is>
+      </c>
+      <c r="E233" s="13" t="inlineStr">
+        <is>
+          <t>Ammaaf ergaan hin jiru.</t>
+        </is>
+      </c>
+      <c r="F233" s="12" t="inlineStr">
+        <is>
+          <t>ክሳብ ሕጂ መልእኽቲ የለን።</t>
+        </is>
+      </c>
+      <c r="G233" s="13" t="inlineStr">
+        <is>
+          <t>Weli fariimo ma jiraan.</t>
+        </is>
+      </c>
+      <c r="H233" s="14" t="inlineStr"/>
+    </row>
+    <row r="234" ht="44" customHeight="1">
+      <c r="A234" s="11" t="inlineStr">
+        <is>
+          <t>you_label</t>
+        </is>
+      </c>
+      <c r="B234" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C234" s="11" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="D234" s="12" t="inlineStr">
+        <is>
+          <t>እርስዎ</t>
+        </is>
+      </c>
+      <c r="E234" s="13" t="inlineStr">
+        <is>
+          <t>Isin</t>
+        </is>
+      </c>
+      <c r="F234" s="12" t="inlineStr">
+        <is>
+          <t>ንስኹም</t>
+        </is>
+      </c>
+      <c r="G234" s="13" t="inlineStr">
+        <is>
+          <t>Adiga</t>
+        </is>
+      </c>
+      <c r="H234" s="14" t="inlineStr"/>
+    </row>
+    <row r="235" ht="44" customHeight="1">
+      <c r="A235" s="11" t="inlineStr">
+        <is>
+          <t>assistant_label</t>
+        </is>
+      </c>
+      <c r="B235" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C235" s="11" t="inlineStr">
+        <is>
+          <t>Assistant</t>
+        </is>
+      </c>
+      <c r="D235" s="12" t="inlineStr">
+        <is>
+          <t>ረዳት</t>
+        </is>
+      </c>
+      <c r="E235" s="13" t="inlineStr">
+        <is>
+          <t>Gargaaraa</t>
+        </is>
+      </c>
+      <c r="F235" s="12" t="inlineStr">
+        <is>
+          <t>ሓጋዚ</t>
+        </is>
+      </c>
+      <c r="G235" s="13" t="inlineStr">
+        <is>
+          <t>Kaaliye</t>
+        </is>
+      </c>
+      <c r="H235" s="14" t="inlineStr"/>
+    </row>
+    <row r="236" ht="44" customHeight="1">
+      <c r="A236" s="11" t="inlineStr">
+        <is>
+          <t>conversation_unavailable</t>
+        </is>
+      </c>
+      <c r="B236" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C236" s="11" t="inlineStr">
+        <is>
+          <t>Conversation unavailable.</t>
+        </is>
+      </c>
+      <c r="D236" s="12" t="inlineStr">
+        <is>
+          <t>ውይይቱ አይገኝም።</t>
+        </is>
+      </c>
+      <c r="E236" s="13" t="inlineStr">
+        <is>
+          <t>Mariin hin argamu.</t>
+        </is>
+      </c>
+      <c r="F236" s="12" t="inlineStr">
+        <is>
+          <t>እቲ ዝርርብ ኣይርከብን።</t>
+        </is>
+      </c>
+      <c r="G236" s="13" t="inlineStr">
+        <is>
+          <t>Wadahadalka lama heli karo.</t>
+        </is>
+      </c>
+      <c r="H236" s="14" t="inlineStr"/>
+    </row>
+    <row r="237" ht="44" customHeight="1">
+      <c r="A237" s="11" t="inlineStr">
+        <is>
+          <t>unmute</t>
+        </is>
+      </c>
+      <c r="B237" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C237" s="11" t="inlineStr">
+        <is>
+          <t>Unmute</t>
+        </is>
+      </c>
+      <c r="D237" s="12" t="inlineStr">
+        <is>
+          <t>ድምፅ አብራ</t>
+        </is>
+      </c>
+      <c r="E237" s="13" t="inlineStr">
+        <is>
+          <t>Sagalee banaa</t>
+        </is>
+      </c>
+      <c r="F237" s="12" t="inlineStr">
+        <is>
+          <t>ድምጺ ኣብርህ</t>
+        </is>
+      </c>
+      <c r="G237" s="13" t="inlineStr">
+        <is>
+          <t>Codka fur</t>
+        </is>
+      </c>
+      <c r="H237" s="14" t="inlineStr"/>
+    </row>
+    <row r="238" ht="44" customHeight="1">
+      <c r="A238" s="11" t="inlineStr">
+        <is>
+          <t>session_summary_prompt</t>
+        </is>
+      </c>
+      <c r="B238" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C238" s="11" t="inlineStr">
+        <is>
+          <t>What did this session cover? (optional)</t>
+        </is>
+      </c>
+      <c r="D238" s="12" t="inlineStr">
+        <is>
+          <t>ይህ ክፍለ-ጊዜ ምን ሸፈነ? (አማራጭ)</t>
+        </is>
+      </c>
+      <c r="E238" s="13" t="inlineStr">
+        <is>
+          <t>Sessioniin kun maal haguuge? (filannoo)</t>
+        </is>
+      </c>
+      <c r="F238" s="12" t="inlineStr">
+        <is>
+          <t>እዚ ክፍለ-ግዜ እንታይ ሸፈነ? (ኣማራጺ)</t>
+        </is>
+      </c>
+      <c r="G238" s="13" t="inlineStr">
+        <is>
+          <t>Kalfadhigan muxuu daboolay? (ikhtiyaari)</t>
+        </is>
+      </c>
+      <c r="H238" s="14" t="inlineStr"/>
+    </row>
+    <row r="239" ht="44" customHeight="1">
+      <c r="A239" s="11" t="inlineStr">
+        <is>
+          <t>customer_ended_call</t>
+        </is>
+      </c>
+      <c r="B239" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C239" s="11" t="inlineStr">
+        <is>
+          <t>The customer ended the call</t>
+        </is>
+      </c>
+      <c r="D239" s="12" t="inlineStr">
+        <is>
+          <t>ደንበኛው ጥሪውን አቋረጠ</t>
+        </is>
+      </c>
+      <c r="E239" s="13" t="inlineStr">
+        <is>
+          <t>Maamilaan bilbila xumure</t>
+        </is>
+      </c>
+      <c r="F239" s="12" t="inlineStr">
+        <is>
+          <t>እቲ ዓሚል ነቲ ጻውዒት ወዲኡዎ</t>
+        </is>
+      </c>
+      <c r="G239" s="13" t="inlineStr">
+        <is>
+          <t>Macmiilku wicitaanka wuu joojiyay</t>
+        </is>
+      </c>
+      <c r="H239" s="14" t="inlineStr"/>
+    </row>
+    <row r="240" ht="44" customHeight="1">
+      <c r="A240" s="11" t="inlineStr">
+        <is>
+          <t>verified_scope</t>
+        </is>
+      </c>
+      <c r="B240" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C240" s="11" t="inlineStr">
+        <is>
+          <t>You can now discuss their own records, take documents and file a dispute. Never a deposit, withdrawal or transfer.</t>
+        </is>
+      </c>
+      <c r="D240" s="12" t="inlineStr">
+        <is>
+          <t>አሁን ስለ ራሳቸው መዝገቦች መወያየት፣ ሰነዶች መቀበልና ቅሬታ ማስመዝገብ ይችላሉ። በፍጹም ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም።</t>
+        </is>
+      </c>
+      <c r="E240" s="13" t="inlineStr">
+        <is>
+          <t>Amma waa'ee galmee isaanii mari'achuu, sanadoota fudhachuu fi komii galmeessuu dandeessu. Gonkumaa kuusaa, baasii yookiin dabarsa hin jiru.</t>
+        </is>
+      </c>
+      <c r="F240" s="12" t="inlineStr">
+        <is>
+          <t>ሕጂ ብዛዕባ ናቶም መዝገባት ክትዘራረቡ፣ ሰነዳት ክትቅበሉን ጥርዓን ከተመዝግቡን ትኽእሉ። ፈጺሙ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን።</t>
+        </is>
+      </c>
+      <c r="G240" s="13" t="inlineStr">
+        <is>
+          <t>Hadda waad kala hadli kartaa diiwaankooda, dukumiinti qaadan iyo cabasho diiwaangelin. Weligaa dhigasho, qaadis ama wareejin ma jirto.</t>
+        </is>
+      </c>
+      <c r="H240" s="14" t="inlineStr"/>
+    </row>
+    <row r="241" ht="44" customHeight="1">
+      <c r="A241" s="11" t="inlineStr">
+        <is>
+          <t>establish_who_they_are</t>
+        </is>
+      </c>
+      <c r="B241" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C241" s="11" t="inlineStr">
+        <is>
+          <t>Establish who they are — either one</t>
+        </is>
+      </c>
+      <c r="D241" s="12" t="inlineStr">
+        <is>
+          <t>ማንነታቸውን ያረጋግጡ — አንዱ ይበቃል</t>
+        </is>
+      </c>
+      <c r="E241" s="13" t="inlineStr">
+        <is>
+          <t>Eenyummaa isaanii mirkaneessaa — tokko ni ga'a</t>
+        </is>
+      </c>
+      <c r="F241" s="12" t="inlineStr">
+        <is>
+          <t>መንነቶም ኣረጋግጹ — ሓደ እኹል እዩ</t>
+        </is>
+      </c>
+      <c r="G241" s="13" t="inlineStr">
+        <is>
+          <t>Ogow cidda ay yihiin — mid kasta</t>
+        </is>
+      </c>
+      <c r="H241" s="14" t="inlineStr"/>
+    </row>
+    <row r="242" ht="44" customHeight="1">
+      <c r="A242" s="11" t="inlineStr">
+        <is>
+          <t>chk_id_document</t>
+        </is>
+      </c>
+      <c r="B242" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C242" s="11" t="inlineStr">
+        <is>
+          <t>Fayda ID shown and matches the account name</t>
+        </is>
+      </c>
+      <c r="D242" s="12" t="inlineStr">
+        <is>
+          <t>የፋይዳ መታወቂያ ታይቷል እና ከሂሳቡ ስም ጋር ይዛመዳል</t>
+        </is>
+      </c>
+      <c r="E242" s="13" t="inlineStr">
+        <is>
+          <t>Waraqaan eenyummaa Fayda agarsiifame maqaa herregaa waliin walsimeera</t>
+        </is>
+      </c>
+      <c r="F242" s="12" t="inlineStr">
+        <is>
+          <t>መንነት ፋይዳ ተራእዩን ምስ ስም ሕሳብ ይሰማማዕን</t>
+        </is>
+      </c>
+      <c r="G242" s="13" t="inlineStr">
+        <is>
+          <t>Aqoonsiga Fayda waa la tusay wuxuuna la mid yahay magaca xisaabta</t>
+        </is>
+      </c>
+      <c r="H242" s="14" t="inlineStr"/>
+    </row>
+    <row r="243" ht="44" customHeight="1">
+      <c r="A243" s="11" t="inlineStr">
+        <is>
+          <t>chk_fayda_matched</t>
+        </is>
+      </c>
+      <c r="B243" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C243" s="11" t="inlineStr">
+        <is>
+          <t>Fayda number matches the account record</t>
+        </is>
+      </c>
+      <c r="D243" s="12" t="inlineStr">
+        <is>
+          <t>የፋይዳ ቁጥር ከሂሳቡ መዝገብ ጋር ይዛመዳል</t>
+        </is>
+      </c>
+      <c r="E243" s="13" t="inlineStr">
+        <is>
+          <t>Lakkoofsi Fayda galmee herregaa waliin walsimeera</t>
+        </is>
+      </c>
+      <c r="F243" s="12" t="inlineStr">
+        <is>
+          <t>ቁጽሪ ፋይዳ ምስ መዝገብ ሕሳብ ይሰማማዕ</t>
+        </is>
+      </c>
+      <c r="G243" s="13" t="inlineStr">
+        <is>
+          <t>Lambarka Fayda wuxuu la mid yahay diiwaanka xisaabta</t>
+        </is>
+      </c>
+      <c r="H243" s="14" t="inlineStr"/>
+    </row>
+    <row r="244" ht="44" customHeight="1">
+      <c r="A244" s="11" t="inlineStr">
+        <is>
+          <t>chk_fayda_matched_note</t>
+        </is>
+      </c>
+      <c r="B244" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C244" s="11" t="inlineStr">
+        <is>
+          <t>on your own screen — works on an audio call</t>
+        </is>
+      </c>
+      <c r="D244" s="12" t="inlineStr">
+        <is>
+          <t>በራስዎ ስክሪን ላይ — በድምፅ ጥሪም ይሠራል</t>
+        </is>
+      </c>
+      <c r="E244" s="13" t="inlineStr">
+        <is>
+          <t>iskiriinii keessan irratti — bilbila sagalee irrattis ni hojjeta</t>
+        </is>
+      </c>
+      <c r="F244" s="12" t="inlineStr">
+        <is>
+          <t>ኣብ ናትኩም መርአዪ — ኣብ ናይ ድምጺ ጻውዒት እውን ይሰርሕ</t>
+        </is>
+      </c>
+      <c r="G244" s="13" t="inlineStr">
+        <is>
+          <t>shaashaddaada — wicitaan cod ahna wuu ka shaqeeyaa</t>
+        </is>
+      </c>
+      <c r="H244" s="14" t="inlineStr"/>
+    </row>
+    <row r="245" ht="44" customHeight="1">
+      <c r="A245" s="11" t="inlineStr">
+        <is>
+          <t>chk_id_photo</t>
+        </is>
+      </c>
+      <c r="B245" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C245" s="11" t="inlineStr">
+        <is>
+          <t>Photo on the ID matches the person on the call</t>
+        </is>
+      </c>
+      <c r="D245" s="12" t="inlineStr">
+        <is>
+          <t>በመታወቂያው ላይ ያለው ፎቶ ከጥሪው ላይ ካለው ሰው ጋር ይዛመዳል</t>
+        </is>
+      </c>
+      <c r="E245" s="13" t="inlineStr">
+        <is>
+          <t>Suuraan waraqaa eenyummaa irra jiru nama bilbila irra jiru waliin walsimeera</t>
+        </is>
+      </c>
+      <c r="F245" s="12" t="inlineStr">
+        <is>
+          <t>እቲ ኣብ መንነት ዘሎ ስእሊ ምስቲ ኣብ ጻውዒት ዘሎ ሰብ ይሰማማዕ</t>
+        </is>
+      </c>
+      <c r="G245" s="13" t="inlineStr">
+        <is>
+          <t>Sawirka aqoonsiga wuxuu la mid yahay qofka wicitaanka ku jira</t>
+        </is>
+      </c>
+      <c r="H245" s="14" t="inlineStr"/>
+    </row>
+    <row r="246" ht="44" customHeight="1">
+      <c r="A246" s="11" t="inlineStr">
+        <is>
+          <t>chk_video_only</t>
+        </is>
+      </c>
+      <c r="B246" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C246" s="11" t="inlineStr">
+        <is>
+          <t>video only</t>
+        </is>
+      </c>
+      <c r="D246" s="12" t="inlineStr">
+        <is>
+          <t>ቪዲዮ ብቻ</t>
+        </is>
+      </c>
+      <c r="E246" s="13" t="inlineStr">
+        <is>
+          <t>viidiyoo qofa</t>
+        </is>
+      </c>
+      <c r="F246" s="12" t="inlineStr">
+        <is>
+          <t>ቪድዮ ጥራይ</t>
+        </is>
+      </c>
+      <c r="G246" s="13" t="inlineStr">
+        <is>
+          <t>fiidyow oo kaliya</t>
+        </is>
+      </c>
+      <c r="H246" s="14" t="inlineStr"/>
+    </row>
+    <row r="247" ht="44" customHeight="1">
+      <c r="A247" s="11" t="inlineStr">
+        <is>
+          <t>confirm_account_theirs</t>
+        </is>
+      </c>
+      <c r="B247" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C247" s="11" t="inlineStr">
+        <is>
+          <t>And confirm the account is theirs</t>
+        </is>
+      </c>
+      <c r="D247" s="12" t="inlineStr">
+        <is>
+          <t>እና ሂሳቡ የእነሱ መሆኑን ያረጋግጡ</t>
+        </is>
+      </c>
+      <c r="E247" s="13" t="inlineStr">
+        <is>
+          <t>Akkasumas herregni kan isaanii ta'uu mirkaneessaa</t>
+        </is>
+      </c>
+      <c r="F247" s="12" t="inlineStr">
+        <is>
+          <t>ከምኡ'ውን እቲ ሕሳብ ናቶም ምዃኑ ኣረጋግጹ</t>
+        </is>
+      </c>
+      <c r="G247" s="13" t="inlineStr">
+        <is>
+          <t>Xaqiiji in xisaabtu tahay tooda</t>
+        </is>
+      </c>
+      <c r="H247" s="14" t="inlineStr"/>
+    </row>
+    <row r="248" ht="44" customHeight="1">
+      <c r="A248" s="11" t="inlineStr">
+        <is>
+          <t>confirm_identity</t>
+        </is>
+      </c>
+      <c r="B248" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C248" s="11" t="inlineStr">
+        <is>
+          <t>Confirm identity</t>
+        </is>
+      </c>
+      <c r="D248" s="12" t="inlineStr">
+        <is>
+          <t>ማንነት አረጋግጥ</t>
+        </is>
+      </c>
+      <c r="E248" s="13" t="inlineStr">
+        <is>
+          <t>Eenyummaa mirkaneessi</t>
+        </is>
+      </c>
+      <c r="F248" s="12" t="inlineStr">
+        <is>
+          <t>መንነት ኣረጋግጽ</t>
+        </is>
+      </c>
+      <c r="G248" s="13" t="inlineStr">
+        <is>
+          <t>Xaqiiji aqoonsiga</t>
+        </is>
+      </c>
+      <c r="H248" s="14" t="inlineStr"/>
+    </row>
+    <row r="249" ht="44" customHeight="1">
+      <c r="A249" s="11" t="inlineStr">
+        <is>
+          <t>unverified_scope</t>
+        </is>
+      </c>
+      <c r="B249" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C249" s="11" t="inlineStr">
+        <is>
+          <t>Until this is done you can only give general guidance — products, eligibility and how to apply.</t>
+        </is>
+      </c>
+      <c r="D249" s="12" t="inlineStr">
+        <is>
+          <t>ይህ እስኪከናወን ድረስ አጠቃላይ መመሪያ ብቻ መስጠት ይችላሉ — ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል።</t>
+        </is>
+      </c>
+      <c r="E249" s="13" t="inlineStr">
+        <is>
+          <t>Hanga kun raawwatutti qajeelfama waliigalaa qofa kennuu dandeessu — oomishaalee, ulaagaa fi akkaataa itti iyyatan.</t>
+        </is>
+      </c>
+      <c r="F249" s="12" t="inlineStr">
+        <is>
+          <t>እዚ ክሳብ ዝፍጸም ሓፈሻዊ መምርሒ ጥራይ ክትህቡ ትኽእሉ — ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን።</t>
+        </is>
+      </c>
+      <c r="G249" s="13" t="inlineStr">
+        <is>
+          <t>Ilaa tan la sameeyo waxaad kaliya bixin kartaa hagaajin guud — alaabta, u-qalmitaanka iyo sida loo codsado.</t>
+        </is>
+      </c>
+      <c r="H249" s="14" t="inlineStr"/>
+    </row>
+    <row r="250" ht="44" customHeight="1">
+      <c r="A250" s="11" t="inlineStr">
+        <is>
+          <t>fayda_number_required</t>
+        </is>
+      </c>
+      <c r="B250" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C250" s="11" t="inlineStr">
+        <is>
+          <t>Fayda number (required — it is what the record keeps)</t>
+        </is>
+      </c>
+      <c r="D250" s="12" t="inlineStr">
+        <is>
+          <t>የፋይዳ ቁጥር (ያስፈልጋል — መዝገቡ የሚይዘው ይህ ነው)</t>
+        </is>
+      </c>
+      <c r="E250" s="13" t="inlineStr">
+        <is>
+          <t>Lakkoofsa Fayda (barbaachisaa — kan galmeen qabatu isa kana)</t>
+        </is>
+      </c>
+      <c r="F250" s="12" t="inlineStr">
+        <is>
+          <t>ቁጽሪ ፋይዳ (የድሊ — እቲ መዝገብ ዝሕዞ እዚ እዩ)</t>
+        </is>
+      </c>
+      <c r="G250" s="13" t="inlineStr">
+        <is>
+          <t>Lambarka Fayda (loo baahan yahay — waa waxa diiwaanku hayo)</t>
+        </is>
+      </c>
+      <c r="H250" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H207"/>
+  <autoFilter ref="A1:H250"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/review/Olink_Bank_Assist_language_review.xlsx
+++ b/review/Olink_Bank_Assist_language_review.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1. What the assistant says'!$A$1:$H$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2. What it understands'!$A$1:$E$78</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3. Buttons customers see'!$A$1:$H$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$H$250</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$H$252</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -752,7 +752,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>318 strings in 5 languages</t>
+          <t>320 strings in 5 languages</t>
         </is>
       </c>
     </row>
@@ -5415,7 +5415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H250"/>
+  <dimension ref="A1:H252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -14932,8 +14932,84 @@
       </c>
       <c r="H250" s="14" t="inlineStr"/>
     </row>
+    <row r="251" ht="44" customHeight="1">
+      <c r="A251" s="11" t="inlineStr">
+        <is>
+          <t>download_for_translation</t>
+        </is>
+      </c>
+      <c r="B251" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C251" s="11" t="inlineStr">
+        <is>
+          <t>Download for translation</t>
+        </is>
+      </c>
+      <c r="D251" s="12" t="inlineStr">
+        <is>
+          <t>ለትርጉም አውርድ</t>
+        </is>
+      </c>
+      <c r="E251" s="13" t="inlineStr">
+        <is>
+          <t>Hiikkaaf buufadhu</t>
+        </is>
+      </c>
+      <c r="F251" s="12" t="inlineStr">
+        <is>
+          <t>ንትርጉም ኣውርድ</t>
+        </is>
+      </c>
+      <c r="G251" s="13" t="inlineStr">
+        <is>
+          <t>Soo dejiso turjumaadda</t>
+        </is>
+      </c>
+      <c r="H251" s="14" t="inlineStr"/>
+    </row>
+    <row r="252" ht="44" customHeight="1">
+      <c r="A252" s="11" t="inlineStr">
+        <is>
+          <t>nothing_to_download</t>
+        </is>
+      </c>
+      <c r="B252" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C252" s="11" t="inlineStr">
+        <is>
+          <t>No approved answers to download yet.</t>
+        </is>
+      </c>
+      <c r="D252" s="12" t="inlineStr">
+        <is>
+          <t>እስካሁን የሚወርድ የተፈቀደ መልስ የለም።</t>
+        </is>
+      </c>
+      <c r="E252" s="13" t="inlineStr">
+        <is>
+          <t>Hanga ammaatti deebiin mirkanaa'e buufamu hin jiru.</t>
+        </is>
+      </c>
+      <c r="F252" s="12" t="inlineStr">
+        <is>
+          <t>ክሳብ ሕጂ ዝወርድ ዝጸደቐ መልሲ የለን።</t>
+        </is>
+      </c>
+      <c r="G252" s="13" t="inlineStr">
+        <is>
+          <t>Weli ma jiraan jawaabo la ansixiyay oo la soo dejiyo.</t>
+        </is>
+      </c>
+      <c r="H252" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H250"/>
+  <autoFilter ref="A1:H252"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/review/Olink_Bank_Assist_language_review.xlsx
+++ b/review/Olink_Bank_Assist_language_review.xlsx
@@ -902,27 +902,32 @@
       </c>
       <c r="C2" s="11" t="inlineStr">
         <is>
-          <t>Hello! I am {bank}'s virtual assistant. Ask me anything about our accounts, services, fees, or how to bank with us.</t>
+          <t>Hello! I am {bank}'s virtual assistant. Ask me anything about our accounts, services, fees, or how to bank with us.
+🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali</t>
         </is>
       </c>
       <c r="D2" s="12" t="inlineStr">
         <is>
-          <t>ሰላም! እኔ የ{bank} ዲጂታል ረዳት ነኝ። ስለ ሂሳቦቻችን፣ አገልግሎቶቻችን፣ ክፍያዎች ወይም አጠቃቀም ማንኛውንም ጥያቄ ይጠይቁኝ።</t>
+          <t>ሰላም! እኔ የ{bank} ዲጂታል ረዳት ነኝ። ስለ ሂሳቦቻችን፣ አገልግሎቶቻችን፣ ክፍያዎች ወይም አጠቃቀም ማንኛውንም ጥያቄ ይጠይቁኝ።
+🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali</t>
         </is>
       </c>
       <c r="E2" s="13" t="inlineStr">
         <is>
-          <t>Akkam! Ani gargaaraa dijitaalaa {bank} ti. Waa'ee herregaa, tajaajilaa, kaffaltii fi fayyadama keenyaa gaaffii kamiyyuu na gaafadhaa.</t>
+          <t>Akkam! Ani gargaaraa dijitaalaa {bank} ti. Waa'ee herregaa, tajaajilaa, kaffaltii fi fayyadama keenyaa gaaffii kamiyyuu na gaafadhaa.
+🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali</t>
         </is>
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>ሰላም! ኣነ ናይ {bank} ዲጂታላዊ ሓጋዚ እየ። ብዛዕባ ሕሳባትና፣ ኣገልግሎታትና፣ ክፍሊታት ወይ ኣጠቓቕማ ዝኾነ ሕቶ ሕተቱኒ።</t>
+          <t>ሰላም! ኣነ ናይ {bank} ዲጂታላዊ ሓጋዚ እየ። ብዛዕባ ሕሳባትና፣ ኣገልግሎታትና፣ ክፍሊታት ወይ ኣጠቓቕማ ዝኾነ ሕቶ ሕተቱኒ።
+🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali</t>
         </is>
       </c>
       <c r="G2" s="13" t="inlineStr">
         <is>
-          <t>Salaan! Waxaan ahay kaaliyaha dijitaalka ah ee {bank}. Wax kasta oo ku saabsan xisaabaadka, adeegyada, khidmadaha iyo isticmaalka i weydii.</t>
+          <t>Salaan! Waxaan ahay kaaliyaha dijitaalka ah ee {bank}. Wax kasta oo ku saabsan xisaabaadka, adeegyada, khidmadaha iyo isticmaalka i weydii.
+🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali</t>
         </is>
       </c>
       <c r="H2" s="14" t="inlineStr"/>
@@ -940,27 +945,32 @@
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>Hello {name}! I am {bank}'s virtual assistant. Ask me anything about our accounts, services, fees, or how to bank with us.</t>
+          <t>Hello {name}! I am {bank}'s virtual assistant. Ask me anything about our accounts, services, fees, or how to bank with us.
+🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>ሰላም {name}! እኔ የ{bank} ዲጂታል ረዳት ነኝ። ስለ ሂሳቦቻችን፣ አገልግሎቶቻችን፣ ክፍያዎች ወይም አጠቃቀም ማንኛውንም ጥያቄ ይጠይቁኝ።</t>
+          <t>ሰላም {name}! እኔ የ{bank} ዲጂታል ረዳት ነኝ። ስለ ሂሳቦቻችን፣ አገልግሎቶቻችን፣ ክፍያዎች ወይም አጠቃቀም ማንኛውንም ጥያቄ ይጠይቁኝ።
+🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali</t>
         </is>
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t>Akkam {name}! Ani gargaaraa dijitaalaa {bank} dha. Waa'ee herregaa, tajaajilaa, kaffaltii yookaan itti fayyadama gaafadhaa.</t>
+          <t>Akkam {name}! Ani gargaaraa dijitaalaa {bank} dha. Waa'ee herregaa, tajaajilaa, kaffaltii yookaan itti fayyadama gaafadhaa.
+🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>ሰላም {name}! ኣነ ናይ {bank} ዲጂታላዊ ሓጋዚ እየ። ብዛዕባ ሕሳባትና፣ ኣገልግሎትና፣ ክፍሊት ወይ ኣጠቓቕማ ዝኾነ ሕቶ ሕተቱኒ።</t>
+          <t>ሰላም {name}! ኣነ ናይ {bank} ዲጂታላዊ ሓጋዚ እየ። ብዛዕባ ሕሳባትና፣ ኣገልግሎትና፣ ክፍሊት ወይ ኣጠቓቕማ ዝኾነ ሕቶ ሕተቱኒ።
+🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali</t>
         </is>
       </c>
       <c r="G3" s="13" t="inlineStr">
         <is>
-          <t>Salaan {name}! Waxaan ahay kaaliyaha dijitaalka ah ee {bank}. Wax walba oo ku saabsan xisaabaha, adeegyada, khidmadaha ama isticmaalka i weydii.</t>
+          <t>Salaan {name}! Waxaan ahay kaaliyaha dijitaalka ah ee {bank}. Wax walba oo ku saabsan xisaabaha, adeegyada, khidmadaha ama isticmaalka i weydii.
+🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali</t>
         </is>
       </c>
       <c r="H3" s="14" t="inlineStr"/>
@@ -3706,27 +3716,27 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Selam! I'm {bank}'s AI assistant. Ask me about accounts, transfers, loans or saving — in English or አማርኛ, I'll follow your language automatically.</t>
+          <t>Selam! I'm {bank}'s AI assistant. Ask me about accounts, transfers, loans or saving — I'll follow your language automatically.</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>ሰላም! የ{bank} AI ረዳት ነኝ። ስለ ሂሳብ፣ ገንዘብ ማስተላለፍ፣ ብድር ወይም ቁጠባ ይጠይቁኝ — በአማርኛ ወይም በእንግሊዝኛ፣ ቋንቋዎን በራሱ እከተላለሁ።</t>
+          <t>ሰላም! የ{bank} AI ረዳት ነኝ። ስለ ሂሳብ፣ ገንዘብ ማስተላለፍ፣ ብድር ወይም ቁጠባ ይጠይቁኝ — ቋንቋዎን በራሱ እከተላለሁ።</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Nagaa! Ani gargaaraa AI {bank} ti. Waa'ee herrega, maallaqa dabarsuu, liqii yookaan qusannaa na gaafadhu — Afaan Oromoo yookaan Ingiliffaan, afaan kee ofumaan hordofa.</t>
+          <t>Nagaa! Ani gargaaraa AI {bank} ti. Waa'ee herrega, maallaqa dabarsuu, liqii yookaan qusannaa na gaafadhu — afaan kee ofumaan hordofa.</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>ሰላም! ናይ {bank} AI ሓጋዚ እየ። ብዛዕባ ሕሳብ፣ ገንዘብ ምትሕልላፍ፣ ልቓሕ ወይ ቁጠባ ሕተተኒ — ብትግርኛ ወይ ብእንግሊዝኛ፣ ቋንቋኻ ባዕለይ እኽተል።</t>
+          <t>ሰላም! ናይ {bank} AI ሓጋዚ እየ። ብዛዕባ ሕሳብ፣ ገንዘብ ምትሕልላፍ፣ ልቓሕ ወይ ቁጠባ ሕተተኒ — ቋንቋኻ ባዕለይ እኽተል።</t>
         </is>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>Salaam! Waxaan ahay kaaliyaha AI ee {bank}. Wax iga weydii xisaabaha, wareejinta lacagta, amaahda ama kaydinta — Af-Soomaali ama Ingiriisi, luqaddaada ayaan si toos ah u raacayaa.</t>
+          <t>Salaam! Waxaan ahay kaaliyaha AI ee {bank}. Wax iga weydii xisaabaha, wareejinta lacagta, amaahda ama kaydinta — luqaddaada ayaan si toos ah u raacayaa.</t>
         </is>
       </c>
       <c r="H6" s="14" t="inlineStr"/>

--- a/review/Olink_Bank_Assist_language_review.xlsx
+++ b/review/Olink_Bank_Assist_language_review.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1. What the assistant says'!$A$1:$H$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2. What it understands'!$A$1:$E$78</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3. Buttons customers see'!$A$1:$H$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$H$252</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$H$256</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -752,7 +752,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>320 strings in 5 languages</t>
+          <t>324 strings in 5 languages</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H252"/>
+  <dimension ref="A1:H256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9017,7 +9017,7 @@
     <row r="95" ht="44" customHeight="1">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>languages</t>
+          <t>what_happened_when_asked</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
@@ -9027,27 +9027,27 @@
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Languages</t>
+          <t>What happened when this was asked</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>ቋንቋዎች</t>
+          <t>ይህ ሲጠየቅ ምን ሆነ</t>
         </is>
       </c>
       <c r="E95" s="13" t="inlineStr">
         <is>
-          <t>Afaanota</t>
+          <t>Yeroo kun gaafatametti maaltu ta'e</t>
         </is>
       </c>
       <c r="F95" s="12" t="inlineStr">
         <is>
-          <t>ቋንቋታት</t>
+          <t>እዚ ምስ ተሓተተ እንታይ ኮነ</t>
         </is>
       </c>
       <c r="G95" s="13" t="inlineStr">
         <is>
-          <t>Luqadaha</t>
+          <t>Maxaa dhacay markii tan la weydiiyay</t>
         </is>
       </c>
       <c r="H95" s="14" t="inlineStr"/>
@@ -9055,7 +9055,7 @@
     <row r="96" ht="44" customHeight="1">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>unit_conversations</t>
+          <t>n_other_questions</t>
         </is>
       </c>
       <c r="B96" s="11" t="inlineStr">
@@ -9065,27 +9065,27 @@
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>conversations</t>
+          <t>{n} other questions</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>ውይይቶች</t>
+          <t>{n} ሌሎች ጥያቄዎች</t>
         </is>
       </c>
       <c r="E96" s="13" t="inlineStr">
         <is>
-          <t>marii</t>
+          <t>Gaaffii {n} biroo</t>
         </is>
       </c>
       <c r="F96" s="12" t="inlineStr">
         <is>
-          <t>ዝርርባት</t>
+          <t>{n} ካልኦት ሕቶታት</t>
         </is>
       </c>
       <c r="G96" s="13" t="inlineStr">
         <is>
-          <t>wadahadallo</t>
+          <t>{n} su'aalood oo kale</t>
         </is>
       </c>
       <c r="H96" s="14" t="inlineStr"/>
@@ -9093,7 +9093,7 @@
     <row r="97" ht="44" customHeight="1">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>donut_all_in</t>
+          <t>view_in_content_gaps</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
@@ -9103,27 +9103,27 @@
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>All {n} {unit} were in {label}.</t>
+          <t>View in Content Gaps</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>ሁሉም {n} {unit} በ{label} ነበሩ።</t>
+          <t>በይዘት ክፍተቶች ይመልከቱ</t>
         </is>
       </c>
       <c r="E97" s="13" t="inlineStr">
         <is>
-          <t>{unit} {n} hundi {label} keessa turan.</t>
+          <t>Hanqina Qabiyyee keessatti ilaali</t>
         </is>
       </c>
       <c r="F97" s="12" t="inlineStr">
         <is>
-          <t>ኩሎም {n} {unit} ብ{label} ነይሮም።</t>
+          <t>ኣብ ናይ ትሕዝቶ ክፍተታት ርአ</t>
         </is>
       </c>
       <c r="G97" s="13" t="inlineStr">
         <is>
-          <t>Dhammaan {n} {unit} waxay ku jireen {label}.</t>
+          <t>Ka eeg Farqiyada Nuxurka</t>
         </is>
       </c>
       <c r="H97" s="14" t="inlineStr"/>
@@ -9131,7 +9131,7 @@
     <row r="98" ht="44" customHeight="1">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>conversations_by_language</t>
+          <t>languages</t>
         </is>
       </c>
       <c r="B98" s="11" t="inlineStr">
@@ -9141,27 +9141,27 @@
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>Conversations by language</t>
+          <t>Languages</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>በቋንቋ የተከፋፈሉ ውይይቶች</t>
+          <t>ቋንቋዎች</t>
         </is>
       </c>
       <c r="E98" s="13" t="inlineStr">
         <is>
-          <t>Marii afaaniin</t>
+          <t>Afaanota</t>
         </is>
       </c>
       <c r="F98" s="12" t="inlineStr">
         <is>
-          <t>ዝርርባት ብቋንቋ</t>
+          <t>ቋንቋታት</t>
         </is>
       </c>
       <c r="G98" s="13" t="inlineStr">
         <is>
-          <t>Wadahadallada luqadda</t>
+          <t>Luqadaha</t>
         </is>
       </c>
       <c r="H98" s="14" t="inlineStr"/>
@@ -9169,7 +9169,7 @@
     <row r="99" ht="44" customHeight="1">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>no_conversations_window</t>
+          <t>unit_conversations</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
@@ -9179,27 +9179,27 @@
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>No conversations yet in this window.</t>
+          <t>conversations</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>በዚህ ጊዜ ውስጥ ውይይት የለም።</t>
+          <t>ውይይቶች</t>
         </is>
       </c>
       <c r="E99" s="13" t="inlineStr">
         <is>
-          <t>Yeroo kana keessatti mariin hin jiru.</t>
+          <t>marii</t>
         </is>
       </c>
       <c r="F99" s="12" t="inlineStr">
         <is>
-          <t>ኣብዚ እዋን'ዚ ዝርርብ የለን።</t>
+          <t>ዝርርባት</t>
         </is>
       </c>
       <c r="G99" s="13" t="inlineStr">
         <is>
-          <t>Waqtigan wadahadal ma jiro.</t>
+          <t>wadahadallo</t>
         </is>
       </c>
       <c r="H99" s="14" t="inlineStr"/>
@@ -9207,7 +9207,7 @@
     <row r="100" ht="44" customHeight="1">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>recent_activity</t>
+          <t>unit_questions</t>
         </is>
       </c>
       <c r="B100" s="11" t="inlineStr">
@@ -9217,27 +9217,27 @@
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>Recent activity</t>
+          <t>questions</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>የቅርብ ጊዜ እንቅስቃሴ</t>
+          <t>ጥያቄዎች</t>
         </is>
       </c>
       <c r="E100" s="13" t="inlineStr">
         <is>
-          <t>Sochii dhiyoo</t>
+          <t>gaaffiiwwan</t>
         </is>
       </c>
       <c r="F100" s="12" t="inlineStr">
         <is>
-          <t>ናይ ቀረባ እዋን ንጥፈት</t>
+          <t>ሕቶታት</t>
         </is>
       </c>
       <c r="G100" s="13" t="inlineStr">
         <is>
-          <t>Dhaqdhaqaaqa dhawaan</t>
+          <t>su'aalaha</t>
         </is>
       </c>
       <c r="H100" s="14" t="inlineStr"/>
@@ -9245,7 +9245,7 @@
     <row r="101" ht="44" customHeight="1">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>live_preview</t>
+          <t>donut_all_in</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
@@ -9255,27 +9255,27 @@
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Live preview</t>
+          <t>All {n} {unit} were in {label}.</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>የቀጥታ ዕይታ</t>
+          <t>ሁሉም {n} {unit} በ{label} ነበሩ።</t>
         </is>
       </c>
       <c r="E101" s="13" t="inlineStr">
         <is>
-          <t>Mul'ata kallattii</t>
+          <t>{unit} {n} hundi {label} keessa turan.</t>
         </is>
       </c>
       <c r="F101" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታ ትርኢት</t>
+          <t>ኩሎም {n} {unit} ብ{label} ነይሮም።</t>
         </is>
       </c>
       <c r="G101" s="13" t="inlineStr">
         <is>
-          <t>Muuqaal toos ah</t>
+          <t>Dhammaan {n} {unit} waxay ku jireen {label}.</t>
         </is>
       </c>
       <c r="H101" s="14" t="inlineStr"/>
@@ -9283,7 +9283,7 @@
     <row r="102" ht="44" customHeight="1">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>assistant_preview</t>
+          <t>conversations_by_language</t>
         </is>
       </c>
       <c r="B102" s="11" t="inlineStr">
@@ -9293,27 +9293,27 @@
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>Assistant preview</t>
+          <t>Conversations by language</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
         <is>
-          <t>የረዳት ዕይታ</t>
+          <t>በቋንቋ የተከፋፈሉ ውይይቶች</t>
         </is>
       </c>
       <c r="E102" s="13" t="inlineStr">
         <is>
-          <t>Mul'ata gargaaraa</t>
+          <t>Marii afaaniin</t>
         </is>
       </c>
       <c r="F102" s="12" t="inlineStr">
         <is>
-          <t>ትርኢት ሓጋዚ</t>
+          <t>ዝርርባት ብቋንቋ</t>
         </is>
       </c>
       <c r="G102" s="13" t="inlineStr">
         <is>
-          <t>Muuqaalka kaaliyaha</t>
+          <t>Wadahadallada luqadda</t>
         </is>
       </c>
       <c r="H102" s="14" t="inlineStr"/>
@@ -9321,7 +9321,7 @@
     <row r="103" ht="44" customHeight="1">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>preview_caption</t>
+          <t>no_conversations_window</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
@@ -9331,27 +9331,27 @@
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Exactly what a customer sees on your website. Messages sent here are real and appear in Conversations.</t>
+          <t>No conversations yet in this window.</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛ በድረ-ገጽዎ ላይ የሚያየው በትክክል ይህ ነው። እዚህ የሚላኩ መልእክቶች እውነተኛ ናቸው እና በውይይቶች ውስጥ ይታያሉ።</t>
+          <t>በዚህ ጊዜ ውስጥ ውይይት የለም።</t>
         </is>
       </c>
       <c r="E103" s="13" t="inlineStr">
         <is>
-          <t>Waanuma maamiltoonni marsariitii keessan irratti argan. Ergaan asitti ergamu dhugaadha, Marii keessattis ni mul'ata.</t>
+          <t>Yeroo kana keessatti mariin hin jiru.</t>
         </is>
       </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
-          <t>ልክዕ ከምቲ ዓሚል ኣብ መርበብ ሓበሬታኹም ዝርእዮ። ኣብዚ ዝለኣኹ መልእኽትታት ናይ ሓቂ ኮይኖም ኣብ ዝርርባት ይረኣዩ።</t>
+          <t>ኣብዚ እዋን'ዚ ዝርርብ የለን።</t>
         </is>
       </c>
       <c r="G103" s="13" t="inlineStr">
         <is>
-          <t>Waa waxa uu macmiilku ku arko degelkaaga. Fariimaha halkan laga diro waa dhab, waxayna ka muuqdaan Wadahadallada.</t>
+          <t>Waqtigan wadahadal ma jiro.</t>
         </is>
       </c>
       <c r="H103" s="14" t="inlineStr"/>
@@ -9359,7 +9359,7 @@
     <row r="104" ht="44" customHeight="1">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>n_conversations</t>
+          <t>recent_activity</t>
         </is>
       </c>
       <c r="B104" s="11" t="inlineStr">
@@ -9369,27 +9369,27 @@
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>{n} conversations</t>
+          <t>Recent activity</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
         <is>
-          <t>{n} ውይይቶች</t>
+          <t>የቅርብ ጊዜ እንቅስቃሴ</t>
         </is>
       </c>
       <c r="E104" s="13" t="inlineStr">
         <is>
-          <t>Marii {n}</t>
+          <t>Sochii dhiyoo</t>
         </is>
       </c>
       <c r="F104" s="12" t="inlineStr">
         <is>
-          <t>{n} ዝርርባት</t>
+          <t>ናይ ቀረባ እዋን ንጥፈት</t>
         </is>
       </c>
       <c r="G104" s="13" t="inlineStr">
         <is>
-          <t>{n} wadahadal</t>
+          <t>Dhaqdhaqaaqa dhawaan</t>
         </is>
       </c>
       <c r="H104" s="14" t="inlineStr"/>
@@ -9397,7 +9397,7 @@
     <row r="105" ht="44" customHeight="1">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>one_conversation</t>
+          <t>live_preview</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
@@ -9407,27 +9407,27 @@
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>{n} conversation</t>
+          <t>Live preview</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>{n} ውይይት</t>
+          <t>የቀጥታ ዕይታ</t>
         </is>
       </c>
       <c r="E105" s="13" t="inlineStr">
         <is>
-          <t>Marii {n}</t>
+          <t>Mul'ata kallattii</t>
         </is>
       </c>
       <c r="F105" s="12" t="inlineStr">
         <is>
-          <t>{n} ዝርርብ</t>
+          <t>ቀጥታ ትርኢት</t>
         </is>
       </c>
       <c r="G105" s="13" t="inlineStr">
         <is>
-          <t>{n} wadahadal</t>
+          <t>Muuqaal toos ah</t>
         </is>
       </c>
       <c r="H105" s="14" t="inlineStr"/>
@@ -9435,7 +9435,7 @@
     <row r="106" ht="44" customHeight="1">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>outcome_answered</t>
+          <t>assistant_preview</t>
         </is>
       </c>
       <c r="B106" s="11" t="inlineStr">
@@ -9445,27 +9445,27 @@
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>Answered from your content</t>
+          <t>Assistant preview</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
         <is>
-          <t>ከይዘትዎ የተመለሰ</t>
+          <t>የረዳት ዕይታ</t>
         </is>
       </c>
       <c r="E106" s="13" t="inlineStr">
         <is>
-          <t>Qabiyyee keessan irraa deebi'e</t>
+          <t>Mul'ata gargaaraa</t>
         </is>
       </c>
       <c r="F106" s="12" t="inlineStr">
         <is>
-          <t>ካብ ትሕዝቶኹም ዝተመለሰ</t>
+          <t>ትርኢት ሓጋዚ</t>
         </is>
       </c>
       <c r="G106" s="13" t="inlineStr">
         <is>
-          <t>Laga jawaabay macluumaadkaaga</t>
+          <t>Muuqaalka kaaliyaha</t>
         </is>
       </c>
       <c r="H106" s="14" t="inlineStr"/>
@@ -9473,7 +9473,7 @@
     <row r="107" ht="44" customHeight="1">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>outcome_general_guidance</t>
+          <t>preview_caption</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
@@ -9483,27 +9483,27 @@
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Answered from general banking knowledge</t>
+          <t>Exactly what a customer sees on your website. Messages sent here are real and appear in Conversations.</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>ከአጠቃላይ የባንክ እውቀት የተመለሰ</t>
+          <t>ደንበኛ በድረ-ገጽዎ ላይ የሚያየው በትክክል ይህ ነው። እዚህ የሚላኩ መልእክቶች እውነተኛ ናቸው እና በውይይቶች ውስጥ ይታያሉ።</t>
         </is>
       </c>
       <c r="E107" s="13" t="inlineStr">
         <is>
-          <t>Beekumsa baankii waliigalaa irraa deebi'e</t>
+          <t>Waanuma maamiltoonni marsariitii keessan irratti argan. Ergaan asitti ergamu dhugaadha, Marii keessattis ni mul'ata.</t>
         </is>
       </c>
       <c r="F107" s="12" t="inlineStr">
         <is>
-          <t>ካብ ሓፈሻዊ ፍልጠት ባንክ ዝተመለሰ</t>
+          <t>ልክዕ ከምቲ ዓሚል ኣብ መርበብ ሓበሬታኹም ዝርእዮ። ኣብዚ ዝለኣኹ መልእኽትታት ናይ ሓቂ ኮይኖም ኣብ ዝርርባት ይረኣዩ።</t>
         </is>
       </c>
       <c r="G107" s="13" t="inlineStr">
         <is>
-          <t>Laga jawaabay aqoonta guud ee bangiga</t>
+          <t>Waa waxa uu macmiilku ku arko degelkaaga. Fariimaha halkan laga diro waa dhab, waxayna ka muuqdaan Wadahadallada.</t>
         </is>
       </c>
       <c r="H107" s="14" t="inlineStr"/>
@@ -9511,7 +9511,7 @@
     <row r="108" ht="44" customHeight="1">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>outcome_unanswered</t>
+          <t>n_conversations</t>
         </is>
       </c>
       <c r="B108" s="11" t="inlineStr">
@@ -9521,27 +9521,27 @@
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>Could not answer</t>
+          <t>{n} conversations</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>መልስ ማግኘት አልተቻለም</t>
+          <t>{n} ውይይቶች</t>
         </is>
       </c>
       <c r="E108" s="13" t="inlineStr">
         <is>
-          <t>Deebisuu hin dandeenye</t>
+          <t>Marii {n}</t>
         </is>
       </c>
       <c r="F108" s="12" t="inlineStr">
         <is>
-          <t>መልሲ ክርከብ ኣይተኻእለን</t>
+          <t>{n} ዝርርባት</t>
         </is>
       </c>
       <c r="G108" s="13" t="inlineStr">
         <is>
-          <t>Lama jawaabi karin</t>
+          <t>{n} wadahadal</t>
         </is>
       </c>
       <c r="H108" s="14" t="inlineStr"/>
@@ -9549,7 +9549,7 @@
     <row r="109" ht="44" customHeight="1">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>outcome_complaint</t>
+          <t>one_conversation</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
@@ -9559,27 +9559,27 @@
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>{n} conversation</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>ቅሬታ</t>
+          <t>{n} ውይይት</t>
         </is>
       </c>
       <c r="E109" s="13" t="inlineStr">
         <is>
-          <t>Komii</t>
+          <t>Marii {n}</t>
         </is>
       </c>
       <c r="F109" s="12" t="inlineStr">
         <is>
-          <t>ጥርዓን</t>
+          <t>{n} ዝርርብ</t>
         </is>
       </c>
       <c r="G109" s="13" t="inlineStr">
         <is>
-          <t>Cabasho</t>
+          <t>{n} wadahadal</t>
         </is>
       </c>
       <c r="H109" s="14" t="inlineStr"/>
@@ -9587,7 +9587,7 @@
     <row r="110" ht="44" customHeight="1">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>outcome_account_blocked</t>
+          <t>outcome_answered</t>
         </is>
       </c>
       <c r="B110" s="11" t="inlineStr">
@@ -9597,27 +9597,27 @@
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>Account access problem</t>
+          <t>Answered from your content</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>የመለያ መግቢያ ችግር</t>
+          <t>ከይዘትዎ የተመለሰ</t>
         </is>
       </c>
       <c r="E110" s="13" t="inlineStr">
         <is>
-          <t>Rakkoo herrega seenuu</t>
+          <t>Qabiyyee keessan irraa deebi'e</t>
         </is>
       </c>
       <c r="F110" s="12" t="inlineStr">
         <is>
-          <t>ጸገም ኣታውነት ሕሳብ</t>
+          <t>ካብ ትሕዝቶኹም ዝተመለሰ</t>
         </is>
       </c>
       <c r="G110" s="13" t="inlineStr">
         <is>
-          <t>Dhibaato gelitaanka xisaabta</t>
+          <t>Laga jawaabay macluumaadkaaga</t>
         </is>
       </c>
       <c r="H110" s="14" t="inlineStr"/>
@@ -9625,7 +9625,7 @@
     <row r="111" ht="44" customHeight="1">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>outcome_comparison</t>
+          <t>outcome_general_guidance</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
@@ -9635,27 +9635,27 @@
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Compared with another bank</t>
+          <t>Answered from general banking knowledge</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>ከሌላ ባንክ ጋር ተነጻጽሯል</t>
+          <t>ከአጠቃላይ የባንክ እውቀት የተመለሰ</t>
         </is>
       </c>
       <c r="E111" s="13" t="inlineStr">
         <is>
-          <t>Baankii biraa waliin walbira qabame</t>
+          <t>Beekumsa baankii waliigalaa irraa deebi'e</t>
         </is>
       </c>
       <c r="F111" s="12" t="inlineStr">
         <is>
-          <t>ምስ ካልእ ባንክ ተነጻጺሩ</t>
+          <t>ካብ ሓፈሻዊ ፍልጠት ባንክ ዝተመለሰ</t>
         </is>
       </c>
       <c r="G111" s="13" t="inlineStr">
         <is>
-          <t>Lala barbardhigay bangi kale</t>
+          <t>Laga jawaabay aqoonta guud ee bangiga</t>
         </is>
       </c>
       <c r="H111" s="14" t="inlineStr"/>
@@ -9663,7 +9663,7 @@
     <row r="112" ht="44" customHeight="1">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>outcome_greeting</t>
+          <t>outcome_unanswered</t>
         </is>
       </c>
       <c r="B112" s="11" t="inlineStr">
@@ -9673,27 +9673,27 @@
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>Greeting</t>
+          <t>Could not answer</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr">
         <is>
-          <t>ሰላምታ</t>
+          <t>መልስ ማግኘት አልተቻለም</t>
         </is>
       </c>
       <c r="E112" s="13" t="inlineStr">
         <is>
-          <t>Nagaa</t>
+          <t>Deebisuu hin dandeenye</t>
         </is>
       </c>
       <c r="F112" s="12" t="inlineStr">
         <is>
-          <t>ሰላምታ</t>
+          <t>መልሲ ክርከብ ኣይተኻእለን</t>
         </is>
       </c>
       <c r="G112" s="13" t="inlineStr">
         <is>
-          <t>Salaan</t>
+          <t>Lama jawaabi karin</t>
         </is>
       </c>
       <c r="H112" s="14" t="inlineStr"/>
@@ -9701,7 +9701,7 @@
     <row r="113" ht="44" customHeight="1">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>outcome_contact_captured</t>
+          <t>outcome_complaint</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
@@ -9711,27 +9711,27 @@
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Contact details captured</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>የመገናኛ መረጃ ተመዝግቧል</t>
+          <t>ቅሬታ</t>
         </is>
       </c>
       <c r="E113" s="13" t="inlineStr">
         <is>
-          <t>Odeeffannoon quunnamtii galmaa'e</t>
+          <t>Komii</t>
         </is>
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
-          <t>ሓበሬታ መራኸቢ ተመዝጊቡ</t>
+          <t>ጥርዓን</t>
         </is>
       </c>
       <c r="G113" s="13" t="inlineStr">
         <is>
-          <t>Xogta xiriirka waa la diiwaangeliyay</t>
+          <t>Cabasho</t>
         </is>
       </c>
       <c r="H113" s="14" t="inlineStr"/>
@@ -9739,7 +9739,7 @@
     <row r="114" ht="44" customHeight="1">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>outcome_human_request</t>
+          <t>outcome_account_blocked</t>
         </is>
       </c>
       <c r="B114" s="11" t="inlineStr">
@@ -9749,27 +9749,27 @@
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>Asked for a person</t>
+          <t>Account access problem</t>
         </is>
       </c>
       <c r="D114" s="12" t="inlineStr">
         <is>
-          <t>ሰው ተጠይቋል</t>
+          <t>የመለያ መግቢያ ችግር</t>
         </is>
       </c>
       <c r="E114" s="13" t="inlineStr">
         <is>
-          <t>Nama gaafate</t>
+          <t>Rakkoo herrega seenuu</t>
         </is>
       </c>
       <c r="F114" s="12" t="inlineStr">
         <is>
-          <t>ሰብ ተሓቲቱ</t>
+          <t>ጸገም ኣታውነት ሕሳብ</t>
         </is>
       </c>
       <c r="G114" s="13" t="inlineStr">
         <is>
-          <t>Qof ayaa la codsaday</t>
+          <t>Dhibaato gelitaanka xisaabta</t>
         </is>
       </c>
       <c r="H114" s="14" t="inlineStr"/>
@@ -9777,7 +9777,7 @@
     <row r="115" ht="44" customHeight="1">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>reason_complaint</t>
+          <t>outcome_comparison</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
@@ -9787,27 +9787,27 @@
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Compared with another bank</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>ቅሬታ</t>
+          <t>ከሌላ ባንክ ጋር ተነጻጽሯል</t>
         </is>
       </c>
       <c r="E115" s="13" t="inlineStr">
         <is>
-          <t>Komii</t>
+          <t>Baankii biraa waliin walbira qabame</t>
         </is>
       </c>
       <c r="F115" s="12" t="inlineStr">
         <is>
-          <t>ጥርዓን</t>
+          <t>ምስ ካልእ ባንክ ተነጻጺሩ</t>
         </is>
       </c>
       <c r="G115" s="13" t="inlineStr">
         <is>
-          <t>Cabasho</t>
+          <t>Lala barbardhigay bangi kale</t>
         </is>
       </c>
       <c r="H115" s="14" t="inlineStr"/>
@@ -9815,7 +9815,7 @@
     <row r="116" ht="44" customHeight="1">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>reason_human_requested</t>
+          <t>outcome_greeting</t>
         </is>
       </c>
       <c r="B116" s="11" t="inlineStr">
@@ -9825,27 +9825,27 @@
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>Asked for a person</t>
+          <t>Greeting</t>
         </is>
       </c>
       <c r="D116" s="12" t="inlineStr">
         <is>
-          <t>ሰው ተጠይቋል</t>
+          <t>ሰላምታ</t>
         </is>
       </c>
       <c r="E116" s="13" t="inlineStr">
         <is>
-          <t>Nama gaafate</t>
+          <t>Nagaa</t>
         </is>
       </c>
       <c r="F116" s="12" t="inlineStr">
         <is>
-          <t>ሰብ ተሓቲቱ</t>
+          <t>ሰላምታ</t>
         </is>
       </c>
       <c r="G116" s="13" t="inlineStr">
         <is>
-          <t>Qof ayaa la codsaday</t>
+          <t>Salaan</t>
         </is>
       </c>
       <c r="H116" s="14" t="inlineStr"/>
@@ -9853,7 +9853,7 @@
     <row r="117" ht="44" customHeight="1">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>reason_unanswered_question</t>
+          <t>outcome_contact_captured</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
@@ -9863,27 +9863,27 @@
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>No answer in your content</t>
+          <t>Contact details captured</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>በይዘትዎ ውስጥ መልስ የለም</t>
+          <t>የመገናኛ መረጃ ተመዝግቧል</t>
         </is>
       </c>
       <c r="E117" s="13" t="inlineStr">
         <is>
-          <t>Qabiyyee keessan keessa deebiin hin jiru</t>
+          <t>Odeeffannoon quunnamtii galmaa'e</t>
         </is>
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ትሕዝቶኹም መልሲ የለን</t>
+          <t>ሓበሬታ መራኸቢ ተመዝጊቡ</t>
         </is>
       </c>
       <c r="G117" s="13" t="inlineStr">
         <is>
-          <t>Macluumaadkaaga jawaab kuma jirto</t>
+          <t>Xogta xiriirka waa la diiwaangeliyay</t>
         </is>
       </c>
       <c r="H117" s="14" t="inlineStr"/>
@@ -9891,7 +9891,7 @@
     <row r="118" ht="44" customHeight="1">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>reason_answered_from_general_knowledge</t>
+          <t>outcome_human_request</t>
         </is>
       </c>
       <c r="B118" s="11" t="inlineStr">
@@ -9901,27 +9901,27 @@
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>Answered from general knowledge</t>
+          <t>Asked for a person</t>
         </is>
       </c>
       <c r="D118" s="12" t="inlineStr">
         <is>
-          <t>ከአጠቃላይ እውቀት የተመለሰ</t>
+          <t>ሰው ተጠይቋል</t>
         </is>
       </c>
       <c r="E118" s="13" t="inlineStr">
         <is>
-          <t>Beekumsa waliigalaa irraa deebi'e</t>
+          <t>Nama gaafate</t>
         </is>
       </c>
       <c r="F118" s="12" t="inlineStr">
         <is>
-          <t>ካብ ሓፈሻዊ ፍልጠት ዝተመለሰ</t>
+          <t>ሰብ ተሓቲቱ</t>
         </is>
       </c>
       <c r="G118" s="13" t="inlineStr">
         <is>
-          <t>Laga jawaabay aqoon guud</t>
+          <t>Qof ayaa la codsaday</t>
         </is>
       </c>
       <c r="H118" s="14" t="inlineStr"/>
@@ -9929,7 +9929,7 @@
     <row r="119" ht="44" customHeight="1">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>branding</t>
+          <t>reason_complaint</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
@@ -9939,27 +9939,27 @@
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Branding</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>የምርት ስም</t>
+          <t>ቅሬታ</t>
         </is>
       </c>
       <c r="E119" s="13" t="inlineStr">
         <is>
-          <t>Mallattoo dhaabbataa</t>
+          <t>Komii</t>
         </is>
       </c>
       <c r="F119" s="12" t="inlineStr">
         <is>
-          <t>ንግዲ ምልክት</t>
+          <t>ጥርዓን</t>
         </is>
       </c>
       <c r="G119" s="13" t="inlineStr">
         <is>
-          <t>Astaanta</t>
+          <t>Cabasho</t>
         </is>
       </c>
       <c r="H119" s="14" t="inlineStr"/>
@@ -9967,7 +9967,7 @@
     <row r="120" ht="44" customHeight="1">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>branding_help</t>
+          <t>reason_human_requested</t>
         </is>
       </c>
       <c r="B120" s="11" t="inlineStr">
@@ -9977,27 +9977,27 @@
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>Your colour and logo, used in this panel and in the chat widget on your website. Saved values apply immediately — no deploy.</t>
+          <t>Asked for a person</t>
         </is>
       </c>
       <c r="D120" s="12" t="inlineStr">
         <is>
-          <t>በዚህ ፓነልና በድረ-ገጽዎ ላይ ባለው የውይይት መስኮት የሚያገለግሉ ቀለምዎና አርማዎ። የተቀመጡ እሴቶች ወዲያውኑ ተግባራዊ ይሆናሉ — ማሰማራት አያስፈልግም።</t>
+          <t>ሰው ተጠይቋል</t>
         </is>
       </c>
       <c r="E120" s="13" t="inlineStr">
         <is>
-          <t>Halluu fi mallattoo keessan, panaalii kana keessattii fi widjetii chat marsariitii keessan irratti kan hojiirra oolu. Gatiin olkaa'ame battalumatti hojiirra oola — bobbaasuun hin barbaachisu.</t>
+          <t>Nama gaafate</t>
         </is>
       </c>
       <c r="F120" s="12" t="inlineStr">
         <is>
-          <t>ኣብዚ ፓነልን ኣብ መርበብ ሓበሬታኹም ዘሎ መስኮት ዝርርብን ዝጠቅም ሕብርኹምን ኣርማኹምን። ዝተዓቀቡ ዋጋታት ብቕጽበት ይሰርሑ — ምዝርጋሕ ኣየድልን።</t>
+          <t>ሰብ ተሓቲቱ</t>
         </is>
       </c>
       <c r="G120" s="13" t="inlineStr">
         <is>
-          <t>Midabkaaga iyo astaantaada, oo laga isticmaalo daaqadan iyo widget-ka sheekada degelkaaga. Qiyamka la keydiyay isla markiiba way shaqeeyaan — geyn looma baahna.</t>
+          <t>Qof ayaa la codsaday</t>
         </is>
       </c>
       <c r="H120" s="14" t="inlineStr"/>
@@ -10005,7 +10005,7 @@
     <row r="121" ht="44" customHeight="1">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>brand_name</t>
+          <t>reason_unanswered_question</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
@@ -10015,27 +10015,27 @@
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Brand name</t>
+          <t>No answer in your content</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>የምርት ስም</t>
+          <t>በይዘትዎ ውስጥ መልስ የለም</t>
         </is>
       </c>
       <c r="E121" s="13" t="inlineStr">
         <is>
-          <t>Maqaa mallattoo</t>
+          <t>Qabiyyee keessan keessa deebiin hin jiru</t>
         </is>
       </c>
       <c r="F121" s="12" t="inlineStr">
         <is>
-          <t>ስም ንግዲ ምልክት</t>
+          <t>ኣብ ትሕዝቶኹም መልሲ የለን</t>
         </is>
       </c>
       <c r="G121" s="13" t="inlineStr">
         <is>
-          <t>Magaca astaanta</t>
+          <t>Macluumaadkaaga jawaab kuma jirto</t>
         </is>
       </c>
       <c r="H121" s="14" t="inlineStr"/>
@@ -10043,7 +10043,7 @@
     <row r="122" ht="44" customHeight="1">
       <c r="A122" s="11" t="inlineStr">
         <is>
-          <t>brand_name_help</t>
+          <t>reason_answered_from_general_knowledge</t>
         </is>
       </c>
       <c r="B122" s="11" t="inlineStr">
@@ -10053,27 +10053,27 @@
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>What people call you — for example "CBE". Shown in the chat header, this panel and greetings to customers. Leave blank to use your registered name, {legal}, which is kept either way for printed reports.</t>
+          <t>Answered from general knowledge</t>
         </is>
       </c>
       <c r="D122" s="12" t="inlineStr">
         <is>
-          <t>ሰዎች የሚጠሩዎት ስም — ለምሳሌ "CBE"። በውይይቱ ራስጌ፣ በዚህ ፓነልና ለደንበኞች በሚቀርብ ሰላምታ ላይ ይታያል። ባዶ ከተውት የተመዘገበው ስምዎ {legal} ይሆናል፤ ለሚታተሙ ሪፖርቶች በሁለቱም መንገድ ይቀመጣል።</t>
+          <t>ከአጠቃላይ እውቀት የተመለሰ</t>
         </is>
       </c>
       <c r="E122" s="13" t="inlineStr">
         <is>
-          <t>Maqaa namoonni ittiin isin waaman — fakkeenyaaf "CBE". Mataduree chat, panaalii kanaa fi nagaa maamiltootaaf dhiyaatu irratti ni mul'ata. Duwwaa yoo dhiiftan maqaan galmaa'aa keessan {legal} fayyadama; gabaasa maxxanfamuuf karaa lamaanuu ni qabama.</t>
+          <t>Beekumsa waliigalaa irraa deebi'e</t>
         </is>
       </c>
       <c r="F122" s="12" t="inlineStr">
         <is>
-          <t>ሰባት ዝጽውዑኹም ስም — ንኣብነት "CBE"። ኣብ ርእሲ ዝርርብ፣ ኣብዚ ፓነልን ንዓማዊል ኣብ ዝቐርብ ሰላምታን ይረአ። ባዶ እንተ ገዲፍኩምዎ እቲ ዝተመዝገበ ስምኩም {legal} ይኸውን፤ ንዝሕተሙ ጸብጻባት ብኽልቲኡ መገዲ ይዕቀብ።</t>
+          <t>ካብ ሓፈሻዊ ፍልጠት ዝተመለሰ</t>
         </is>
       </c>
       <c r="G122" s="13" t="inlineStr">
         <is>
-          <t>Waxa dadku kugu yeeraan — tusaale "CBE". Waxay ka muuqataa madaxa sheekada, daaqadan iyo salaanta macaamiisha. Haddii aad banaan ka tagto waxaa la isticmaalayaa magacaaga diiwaangashan, {legal}, oo si kastaba lagu hayo warbixinnada la daabaco.</t>
+          <t>Laga jawaabay aqoon guud</t>
         </is>
       </c>
       <c r="H122" s="14" t="inlineStr"/>
@@ -10081,7 +10081,7 @@
     <row r="123" ht="44" customHeight="1">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>brand_colour</t>
+          <t>branding</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
@@ -10091,27 +10091,27 @@
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Brand colour</t>
+          <t>Branding</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>የምርት ቀለም</t>
+          <t>የምርት ስም</t>
         </is>
       </c>
       <c r="E123" s="13" t="inlineStr">
         <is>
-          <t>Halluu mallattoo</t>
+          <t>Mallattoo dhaabbataa</t>
         </is>
       </c>
       <c r="F123" s="12" t="inlineStr">
         <is>
-          <t>ሕብሪ ንግዲ ምልክት</t>
+          <t>ንግዲ ምልክት</t>
         </is>
       </c>
       <c r="G123" s="13" t="inlineStr">
         <is>
-          <t>Midabka astaanta</t>
+          <t>Astaanta</t>
         </is>
       </c>
       <c r="H123" s="14" t="inlineStr"/>
@@ -10119,7 +10119,7 @@
     <row r="124" ht="44" customHeight="1">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t>logo_url</t>
+          <t>branding_help</t>
         </is>
       </c>
       <c r="B124" s="11" t="inlineStr">
@@ -10129,27 +10129,27 @@
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>Logo URL (https)</t>
+          <t>Your colour and logo, used in this panel and in the chat widget on your website. Saved values apply immediately — no deploy.</t>
         </is>
       </c>
       <c r="D124" s="12" t="inlineStr">
         <is>
-          <t>የአርማ አድራሻ (https)</t>
+          <t>በዚህ ፓነልና በድረ-ገጽዎ ላይ ባለው የውይይት መስኮት የሚያገለግሉ ቀለምዎና አርማዎ። የተቀመጡ እሴቶች ወዲያውኑ ተግባራዊ ይሆናሉ — ማሰማራት አያስፈልግም።</t>
         </is>
       </c>
       <c r="E124" s="13" t="inlineStr">
         <is>
-          <t>Teessoo mallattoo (https)</t>
+          <t>Halluu fi mallattoo keessan, panaalii kana keessattii fi widjetii chat marsariitii keessan irratti kan hojiirra oolu. Gatiin olkaa'ame battalumatti hojiirra oola — bobbaasuun hin barbaachisu.</t>
         </is>
       </c>
       <c r="F124" s="12" t="inlineStr">
         <is>
-          <t>ኣድራሻ ኣርማ (https)</t>
+          <t>ኣብዚ ፓነልን ኣብ መርበብ ሓበሬታኹም ዘሎ መስኮት ዝርርብን ዝጠቅም ሕብርኹምን ኣርማኹምን። ዝተዓቀቡ ዋጋታት ብቕጽበት ይሰርሑ — ምዝርጋሕ ኣየድልን።</t>
         </is>
       </c>
       <c r="G124" s="13" t="inlineStr">
         <is>
-          <t>Ciwaanka astaanta (https)</t>
+          <t>Midabkaaga iyo astaantaada, oo laga isticmaalo daaqadan iyo widget-ka sheekada degelkaaga. Qiyamka la keydiyay isla markiiba way shaqeeyaan — geyn looma baahna.</t>
         </is>
       </c>
       <c r="H124" s="14" t="inlineStr"/>
@@ -10157,7 +10157,7 @@
     <row r="125" ht="44" customHeight="1">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>seeded_colours_help</t>
+          <t>brand_name</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
@@ -10167,27 +10167,27 @@
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Seeded colours are our reading of your public site, not your brand book. If it is wrong, this is where to fix it.</t>
+          <t>Brand name</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>የቀረቡት ቀለሞች ከይፋዊ ድረ-ገጽዎ የተወሰዱ ግምቶች እንጂ ከምርት መመሪያ መጽሐፍዎ አይደሉም። ስህተት ከሆነ የሚታረመው እዚህ ነው።</t>
+          <t>የምርት ስም</t>
         </is>
       </c>
       <c r="E125" s="13" t="inlineStr">
         <is>
-          <t>Halluuwwan durfaman marsariitii keessan ifaa irraa kan dubbifame malee kitaaba mallattoo keessanii irraa miti. Yoo dogoggora ta'e, asitti sirreessaa.</t>
+          <t>Maqaa mallattoo</t>
         </is>
       </c>
       <c r="F125" s="12" t="inlineStr">
         <is>
-          <t>እቶም ዝቐረቡ ሕብርታት ካብ ወግዓዊ መርበብ ሓበሬታኹም ዝተወስዱ ግምት እምበር ካብ መጽሓፍ ንግዲ ምልክትኩም ኣይኮኑን። ጌጋ እንተኾይኑ ኣብዚ ይእረም።</t>
+          <t>ስም ንግዲ ምልክት</t>
         </is>
       </c>
       <c r="G125" s="13" t="inlineStr">
         <is>
-          <t>Midabbada la soo bandhigay waa akhrinteenna degelkaaga guud, ma aha buuggaaga astaanta. Haddii ay khalad tahay, halkan ayaa lagu saxaa.</t>
+          <t>Magaca astaanta</t>
         </is>
       </c>
       <c r="H125" s="14" t="inlineStr"/>
@@ -10195,7 +10195,7 @@
     <row r="126" ht="44" customHeight="1">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>save_branding</t>
+          <t>brand_name_help</t>
         </is>
       </c>
       <c r="B126" s="11" t="inlineStr">
@@ -10205,27 +10205,27 @@
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>Save branding</t>
+          <t>What people call you — for example "CBE". Shown in the chat header, this panel and greetings to customers. Leave blank to use your registered name, {legal}, which is kept either way for printed reports.</t>
         </is>
       </c>
       <c r="D126" s="12" t="inlineStr">
         <is>
-          <t>የምርት ስም አስቀምጥ</t>
+          <t>ሰዎች የሚጠሩዎት ስም — ለምሳሌ "CBE"። በውይይቱ ራስጌ፣ በዚህ ፓነልና ለደንበኞች በሚቀርብ ሰላምታ ላይ ይታያል። ባዶ ከተውት የተመዘገበው ስምዎ {legal} ይሆናል፤ ለሚታተሙ ሪፖርቶች በሁለቱም መንገድ ይቀመጣል።</t>
         </is>
       </c>
       <c r="E126" s="13" t="inlineStr">
         <is>
-          <t>Mallattoo olkaa'i</t>
+          <t>Maqaa namoonni ittiin isin waaman — fakkeenyaaf "CBE". Mataduree chat, panaalii kanaa fi nagaa maamiltootaaf dhiyaatu irratti ni mul'ata. Duwwaa yoo dhiiftan maqaan galmaa'aa keessan {legal} fayyadama; gabaasa maxxanfamuuf karaa lamaanuu ni qabama.</t>
         </is>
       </c>
       <c r="F126" s="12" t="inlineStr">
         <is>
-          <t>ንግዲ ምልክት ኣቐምጥ</t>
+          <t>ሰባት ዝጽውዑኹም ስም — ንኣብነት "CBE"። ኣብ ርእሲ ዝርርብ፣ ኣብዚ ፓነልን ንዓማዊል ኣብ ዝቐርብ ሰላምታን ይረአ። ባዶ እንተ ገዲፍኩምዎ እቲ ዝተመዝገበ ስምኩም {legal} ይኸውን፤ ንዝሕተሙ ጸብጻባት ብኽልቲኡ መገዲ ይዕቀብ።</t>
         </is>
       </c>
       <c r="G126" s="13" t="inlineStr">
         <is>
-          <t>Keydi astaanta</t>
+          <t>Waxa dadku kugu yeeraan — tusaale "CBE". Waxay ka muuqataa madaxa sheekada, daaqadan iyo salaanta macaamiisha. Haddii aad banaan ka tagto waxaa la isticmaalayaa magacaaga diiwaangashan, {legal}, oo si kastaba lagu hayo warbixinnada la daabaco.</t>
         </is>
       </c>
       <c r="H126" s="14" t="inlineStr"/>
@@ -10233,7 +10233,7 @@
     <row r="127" ht="44" customHeight="1">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>branding_saved</t>
+          <t>brand_colour</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
@@ -10243,27 +10243,27 @@
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>Branding saved</t>
+          <t>Brand colour</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>የምርት ስም ተቀምጧል</t>
+          <t>የምርት ቀለም</t>
         </is>
       </c>
       <c r="E127" s="13" t="inlineStr">
         <is>
-          <t>Mallattoon olkaa'ame</t>
+          <t>Halluu mallattoo</t>
         </is>
       </c>
       <c r="F127" s="12" t="inlineStr">
         <is>
-          <t>ንግዲ ምልክት ተቐሚጡ</t>
+          <t>ሕብሪ ንግዲ ምልክት</t>
         </is>
       </c>
       <c r="G127" s="13" t="inlineStr">
         <is>
-          <t>Astaanta waa la keydiyay</t>
+          <t>Midabka astaanta</t>
         </is>
       </c>
       <c r="H127" s="14" t="inlineStr"/>
@@ -10271,7 +10271,7 @@
     <row r="128" ht="44" customHeight="1">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t>escalation_webhook</t>
+          <t>logo_url</t>
         </is>
       </c>
       <c r="B128" s="11" t="inlineStr">
@@ -10281,27 +10281,27 @@
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>Escalation webhook</t>
+          <t>Logo URL (https)</t>
         </is>
       </c>
       <c r="D128" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ዌብሁክ</t>
+          <t>የአርማ አድራሻ (https)</t>
         </is>
       </c>
       <c r="E128" s="13" t="inlineStr">
         <is>
-          <t>Webhook dabarsaa</t>
+          <t>Teessoo mallattoo (https)</t>
         </is>
       </c>
       <c r="F128" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ምትሕልላፍ</t>
+          <t>ኣድራሻ ኣርማ (https)</t>
         </is>
       </c>
       <c r="G128" s="13" t="inlineStr">
         <is>
-          <t>Webhook-ga gudbinta</t>
+          <t>Ciwaanka astaanta (https)</t>
         </is>
       </c>
       <c r="H128" s="14" t="inlineStr"/>
@@ -10309,7 +10309,7 @@
     <row r="129" ht="44" customHeight="1">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>webhook_help</t>
+          <t>seeded_colours_help</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
@@ -10319,27 +10319,27 @@
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>Where escalations are delivered in your contact-centre tool. Requests are signed, so the receiving system can verify they came from us. Clear the field to disconnect.</t>
+          <t>Seeded colours are our reading of your public site, not your brand book. If it is wrong, this is where to fix it.</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>ጉዳዮች በእርስዎ የደንበኞች መገልገያ መሣሪያ ውስጥ የሚደርሱበት ቦታ። ጥያቄዎቹ የተፈረሙ ናቸው፤ ስለዚህ ተቀባዩ ሥርዓት ከእኛ መምጣታቸውን ማረጋገጥ ይችላል። ለማቋረጥ መስኩን ባዶ ያድርጉ።</t>
+          <t>የቀረቡት ቀለሞች ከይፋዊ ድረ-ገጽዎ የተወሰዱ ግምቶች እንጂ ከምርት መመሪያ መጽሐፍዎ አይደሉም። ስህተት ከሆነ የሚታረመው እዚህ ነው።</t>
         </is>
       </c>
       <c r="E129" s="13" t="inlineStr">
         <is>
-          <t>Iddoo dhimmoonni meeshaa wiirtuu quunnamtii keessan keessatti geessifaman. Gaaffiiwwan mallatteeffamaniiru, kanaafuu sirni fudhatu nurraa dhufuu isaanii mirkaneessuu danda'a. Addaan kutuuf dirree duwwaa godhaa.</t>
+          <t>Halluuwwan durfaman marsariitii keessan ifaa irraa kan dubbifame malee kitaaba mallattoo keessanii irraa miti. Yoo dogoggora ta'e, asitti sirreessaa.</t>
         </is>
       </c>
       <c r="F129" s="12" t="inlineStr">
         <is>
-          <t>ጉዳያት ኣብ መሳርሒ ማእከል ርክብኩም ዝበጽሑሉ ቦታ። እቶም ሕቶታት ዝተፈረሙ ስለዝኾኑ እቲ ተቐባሊ ስርዓት ካባና ምምጻኦም ከረጋግጽ ይኽእል። ንምቁራጽ እቲ ሜዳ ባዶ ግበሩ።</t>
+          <t>እቶም ዝቐረቡ ሕብርታት ካብ ወግዓዊ መርበብ ሓበሬታኹም ዝተወስዱ ግምት እምበር ካብ መጽሓፍ ንግዲ ምልክትኩም ኣይኮኑን። ጌጋ እንተኾይኑ ኣብዚ ይእረም።</t>
         </is>
       </c>
       <c r="G129" s="13" t="inlineStr">
         <is>
-          <t>Halka arrimaha lagu gudbiyo qalabkaaga xarunta macaamiisha. Codsiyada waa la saxeexay, sidaas darteed nidaamka qaataa wuu xaqiijin karaa inay naga yimaadeen. Si aad u gooyso, banaani meesha.</t>
+          <t>Midabbada la soo bandhigay waa akhrinteenna degelkaaga guud, ma aha buuggaaga astaanta. Haddii ay khalad tahay, halkan ayaa lagu saxaa.</t>
         </is>
       </c>
       <c r="H129" s="14" t="inlineStr"/>
@@ -10347,7 +10347,7 @@
     <row r="130" ht="44" customHeight="1">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t>signing_secret_set</t>
+          <t>save_branding</t>
         </is>
       </c>
       <c r="B130" s="11" t="inlineStr">
@@ -10357,27 +10357,27 @@
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>A signing secret is set. It cannot be shown again — saving a URL here issues a new one and the old one stops working.</t>
+          <t>Save branding</t>
         </is>
       </c>
       <c r="D130" s="12" t="inlineStr">
         <is>
-          <t>የፊርማ ሚስጥር ተዘጋጅቷል። እንደገና ማሳየት አይቻልም — እዚህ አድራሻ ማስቀመጥ አዲስ ያወጣል፤ አሮጌው መስራት ያቆማል።</t>
+          <t>የምርት ስም አስቀምጥ</t>
         </is>
       </c>
       <c r="E130" s="13" t="inlineStr">
         <is>
-          <t>Iccitiin mallattoo qophaa'eera. Irra deebi'anii agarsiisuun hin danda'amu — asitti URL olkaa'uun haaraa baasa, kan duraa immoo hojii dhaaba.</t>
+          <t>Mallattoo olkaa'i</t>
         </is>
       </c>
       <c r="F130" s="12" t="inlineStr">
         <is>
-          <t>ምስጢር ፌርማ ተቐሚጡ። መሊስካ ክርአ ኣይክእልን — ኣብዚ ኣድራሻ ምቕማጥ ሓድሽ የውጽእ፣ እቲ ናይ ቀደም ይቋረጽ።</t>
+          <t>ንግዲ ምልክት ኣቐምጥ</t>
         </is>
       </c>
       <c r="G130" s="13" t="inlineStr">
         <is>
-          <t>Sir saxeex ayaa la dejiyay. Mar kale lama tusi karo — URL halkan lagu keydiyo wuxuu soo saarayaa mid cusub, kii hore wuu shaqo joojiyaa.</t>
+          <t>Keydi astaanta</t>
         </is>
       </c>
       <c r="H130" s="14" t="inlineStr"/>
@@ -10385,7 +10385,7 @@
     <row r="131" ht="44" customHeight="1">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>webhook_connected</t>
+          <t>branding_saved</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
@@ -10395,27 +10395,27 @@
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>Webhook connected</t>
+          <t>Branding saved</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ተገናኝቷል</t>
+          <t>የምርት ስም ተቀምጧል</t>
         </is>
       </c>
       <c r="E131" s="13" t="inlineStr">
         <is>
-          <t>Webhook walqunnamsiifame</t>
+          <t>Mallattoon olkaa'ame</t>
         </is>
       </c>
       <c r="F131" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ተራኺቡ</t>
+          <t>ንግዲ ምልክት ተቐሚጡ</t>
         </is>
       </c>
       <c r="G131" s="13" t="inlineStr">
         <is>
-          <t>Webhook waa la xiray</t>
+          <t>Astaanta waa la keydiyay</t>
         </is>
       </c>
       <c r="H131" s="14" t="inlineStr"/>
@@ -10423,7 +10423,7 @@
     <row r="132" ht="44" customHeight="1">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t>webhook_disconnected</t>
+          <t>escalation_webhook</t>
         </is>
       </c>
       <c r="B132" s="11" t="inlineStr">
@@ -10433,27 +10433,27 @@
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>Webhook disconnected</t>
+          <t>Escalation webhook</t>
         </is>
       </c>
       <c r="D132" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ተቋርጧል</t>
+          <t>የማሸጋገሪያ ዌብሁክ</t>
         </is>
       </c>
       <c r="E132" s="13" t="inlineStr">
         <is>
-          <t>Webhook addaan kutame</t>
+          <t>Webhook dabarsaa</t>
         </is>
       </c>
       <c r="F132" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ተቛሪጹ</t>
+          <t>ዌብሁክ ምትሕልላፍ</t>
         </is>
       </c>
       <c r="G132" s="13" t="inlineStr">
         <is>
-          <t>Webhook waa la goynay</t>
+          <t>Webhook-ga gudbinta</t>
         </is>
       </c>
       <c r="H132" s="14" t="inlineStr"/>
@@ -10461,7 +10461,7 @@
     <row r="133" ht="44" customHeight="1">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>your_password</t>
+          <t>webhook_help</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
@@ -10471,27 +10471,27 @@
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>Your password</t>
+          <t>Where escalations are delivered in your contact-centre tool. Requests are signed, so the receiving system can verify they came from us. Clear the field to disconnect.</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>የይለፍ ቃልዎ</t>
+          <t>ጉዳዮች በእርስዎ የደንበኞች መገልገያ መሣሪያ ውስጥ የሚደርሱበት ቦታ። ጥያቄዎቹ የተፈረሙ ናቸው፤ ስለዚህ ተቀባዩ ሥርዓት ከእኛ መምጣታቸውን ማረጋገጥ ይችላል። ለማቋረጥ መስኩን ባዶ ያድርጉ።</t>
         </is>
       </c>
       <c r="E133" s="13" t="inlineStr">
         <is>
-          <t>Jecha darbii keessan</t>
+          <t>Iddoo dhimmoonni meeshaa wiirtuu quunnamtii keessan keessatti geessifaman. Gaaffiiwwan mallatteeffamaniiru, kanaafuu sirni fudhatu nurraa dhufuu isaanii mirkaneessuu danda'a. Addaan kutuuf dirree duwwaa godhaa.</t>
         </is>
       </c>
       <c r="F133" s="12" t="inlineStr">
         <is>
-          <t>መሕለፊ ቃልኩም</t>
+          <t>ጉዳያት ኣብ መሳርሒ ማእከል ርክብኩም ዝበጽሑሉ ቦታ። እቶም ሕቶታት ዝተፈረሙ ስለዝኾኑ እቲ ተቐባሊ ስርዓት ካባና ምምጻኦም ከረጋግጽ ይኽእል። ንምቁራጽ እቲ ሜዳ ባዶ ግበሩ።</t>
         </is>
       </c>
       <c r="G133" s="13" t="inlineStr">
         <is>
-          <t>Furahaaga sirta ah</t>
+          <t>Halka arrimaha lagu gudbiyo qalabkaaga xarunta macaamiisha. Codsiyada waa la saxeexay, sidaas darteed nidaamka qaataa wuu xaqiijin karaa inay naga yimaadeen. Si aad u gooyso, banaani meesha.</t>
         </is>
       </c>
       <c r="H133" s="14" t="inlineStr"/>
@@ -10499,7 +10499,7 @@
     <row r="134" ht="44" customHeight="1">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>current_password</t>
+          <t>signing_secret_set</t>
         </is>
       </c>
       <c r="B134" s="11" t="inlineStr">
@@ -10509,27 +10509,27 @@
       </c>
       <c r="C134" s="11" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>A signing secret is set. It cannot be shown again — saving a URL here issues a new one and the old one stops working.</t>
         </is>
       </c>
       <c r="D134" s="12" t="inlineStr">
         <is>
-          <t>አሁን ያለው</t>
+          <t>የፊርማ ሚስጥር ተዘጋጅቷል። እንደገና ማሳየት አይቻልም — እዚህ አድራሻ ማስቀመጥ አዲስ ያወጣል፤ አሮጌው መስራት ያቆማል።</t>
         </is>
       </c>
       <c r="E134" s="13" t="inlineStr">
         <is>
-          <t>Kan ammaa</t>
+          <t>Iccitiin mallattoo qophaa'eera. Irra deebi'anii agarsiisuun hin danda'amu — asitti URL olkaa'uun haaraa baasa, kan duraa immoo hojii dhaaba.</t>
         </is>
       </c>
       <c r="F134" s="12" t="inlineStr">
         <is>
-          <t>ናይ ሕጂ</t>
+          <t>ምስጢር ፌርማ ተቐሚጡ። መሊስካ ክርአ ኣይክእልን — ኣብዚ ኣድራሻ ምቕማጥ ሓድሽ የውጽእ፣ እቲ ናይ ቀደም ይቋረጽ።</t>
         </is>
       </c>
       <c r="G134" s="13" t="inlineStr">
         <is>
-          <t>Kan hadda</t>
+          <t>Sir saxeex ayaa la dejiyay. Mar kale lama tusi karo — URL halkan lagu keydiyo wuxuu soo saarayaa mid cusub, kii hore wuu shaqo joojiyaa.</t>
         </is>
       </c>
       <c r="H134" s="14" t="inlineStr"/>
@@ -10537,7 +10537,7 @@
     <row r="135" ht="44" customHeight="1">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>new_password_12</t>
+          <t>webhook_connected</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
@@ -10547,27 +10547,27 @@
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>New (12+ characters)</t>
+          <t>Webhook connected</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>አዲስ (12+ ቁምፊዎች)</t>
+          <t>ዌብሁክ ተገናኝቷል</t>
         </is>
       </c>
       <c r="E135" s="13" t="inlineStr">
         <is>
-          <t>Haaraa (arfiilee 12+)</t>
+          <t>Webhook walqunnamsiifame</t>
         </is>
       </c>
       <c r="F135" s="12" t="inlineStr">
         <is>
-          <t>ሓድሽ (12+ ፊደላት)</t>
+          <t>ዌብሁክ ተራኺቡ</t>
         </is>
       </c>
       <c r="G135" s="13" t="inlineStr">
         <is>
-          <t>Cusub (12+ xaraf)</t>
+          <t>Webhook waa la xiray</t>
         </is>
       </c>
       <c r="H135" s="14" t="inlineStr"/>
@@ -10575,7 +10575,7 @@
     <row r="136" ht="44" customHeight="1">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t>password_change_help</t>
+          <t>webhook_disconnected</t>
         </is>
       </c>
       <c r="B136" s="11" t="inlineStr">
@@ -10585,27 +10585,27 @@
       </c>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>Changing it signs out every other browser you are signed in on.</t>
+          <t>Webhook disconnected</t>
         </is>
       </c>
       <c r="D136" s="12" t="inlineStr">
         <is>
-          <t>መቀየር በገቡበት በሌላ በእያንዳንዱ አሳሽ ላይ ያስወጣዎታል።</t>
+          <t>ዌብሁክ ተቋርጧል</t>
         </is>
       </c>
       <c r="E136" s="13" t="inlineStr">
         <is>
-          <t>Jijjiiruun biraawzarii biroo isin keessa seentan hunda irraa isin baasa.</t>
+          <t>Webhook addaan kutame</t>
         </is>
       </c>
       <c r="F136" s="12" t="inlineStr">
         <is>
-          <t>ምቕያሩ ኣብ ካልእ ዝኣተኹምሉ ኩሉ መርበብ መንሸራተቲ የውጽኣኩም።</t>
+          <t>ዌብሁክ ተቛሪጹ</t>
         </is>
       </c>
       <c r="G136" s="13" t="inlineStr">
         <is>
-          <t>Beddelkeedu wuxuu kaa saarayaa dhammaan browser-yada kale ee aad ku jirto.</t>
+          <t>Webhook waa la goynay</t>
         </is>
       </c>
       <c r="H136" s="14" t="inlineStr"/>
@@ -10613,7 +10613,7 @@
     <row r="137" ht="44" customHeight="1">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>change_password</t>
+          <t>your_password</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
@@ -10623,27 +10623,27 @@
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>Change password</t>
+          <t>Your password</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>የይለፍ ቃል ቀይር</t>
+          <t>የይለፍ ቃልዎ</t>
         </is>
       </c>
       <c r="E137" s="13" t="inlineStr">
         <is>
-          <t>Jecha darbii jijjiiri</t>
+          <t>Jecha darbii keessan</t>
         </is>
       </c>
       <c r="F137" s="12" t="inlineStr">
         <is>
-          <t>መሕለፊ ቃል ቀይር</t>
+          <t>መሕለፊ ቃልኩም</t>
         </is>
       </c>
       <c r="G137" s="13" t="inlineStr">
         <is>
-          <t>Bedel furaha sirta ah</t>
+          <t>Furahaaga sirta ah</t>
         </is>
       </c>
       <c r="H137" s="14" t="inlineStr"/>
@@ -10651,7 +10651,7 @@
     <row r="138" ht="44" customHeight="1">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t>password_changed</t>
+          <t>current_password</t>
         </is>
       </c>
       <c r="B138" s="11" t="inlineStr">
@@ -10661,27 +10661,27 @@
       </c>
       <c r="C138" s="11" t="inlineStr">
         <is>
-          <t>Password changed. Other sessions were signed out.</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="D138" s="12" t="inlineStr">
         <is>
-          <t>የይለፍ ቃል ተቀይሯል። ሌሎች ክፍለ-ጊዜዎች ወጥተዋል።</t>
+          <t>አሁን ያለው</t>
         </is>
       </c>
       <c r="E138" s="13" t="inlineStr">
         <is>
-          <t>Jechi darbii jijjiirameera. Sessionoonni biroo ba'aniiru.</t>
+          <t>Kan ammaa</t>
         </is>
       </c>
       <c r="F138" s="12" t="inlineStr">
         <is>
-          <t>መሕለፊ ቃል ተቐዪሩ። ካልኦት ክፍለ-ግዜታት ወጺኦም።</t>
+          <t>ናይ ሕጂ</t>
         </is>
       </c>
       <c r="G138" s="13" t="inlineStr">
         <is>
-          <t>Furaha sirta ah waa la beddelay. Kalfadhiyada kale waa laga saaray.</t>
+          <t>Kan hadda</t>
         </is>
       </c>
       <c r="H138" s="14" t="inlineStr"/>
@@ -10689,7 +10689,7 @@
     <row r="139" ht="44" customHeight="1">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>add_person</t>
+          <t>new_password_12</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
@@ -10699,27 +10699,27 @@
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>Add person</t>
+          <t>New (12+ characters)</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>ሰው ጨምር</t>
+          <t>አዲስ (12+ ቁምፊዎች)</t>
         </is>
       </c>
       <c r="E139" s="13" t="inlineStr">
         <is>
-          <t>Nama dabali</t>
+          <t>Haaraa (arfiilee 12+)</t>
         </is>
       </c>
       <c r="F139" s="12" t="inlineStr">
         <is>
-          <t>ሰብ ወስኽ</t>
+          <t>ሓድሽ (12+ ፊደላት)</t>
         </is>
       </c>
       <c r="G139" s="13" t="inlineStr">
         <is>
-          <t>Ku dar qof</t>
+          <t>Cusub (12+ xaraf)</t>
         </is>
       </c>
       <c r="H139" s="14" t="inlineStr"/>
@@ -10727,7 +10727,7 @@
     <row r="140" ht="44" customHeight="1">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t>n_accounts</t>
+          <t>password_change_help</t>
         </is>
       </c>
       <c r="B140" s="11" t="inlineStr">
@@ -10737,27 +10737,27 @@
       </c>
       <c r="C140" s="11" t="inlineStr">
         <is>
-          <t>{n} accounts</t>
+          <t>Changing it signs out every other browser you are signed in on.</t>
         </is>
       </c>
       <c r="D140" s="12" t="inlineStr">
         <is>
-          <t>{n} መለያዎች</t>
+          <t>መቀየር በገቡበት በሌላ በእያንዳንዱ አሳሽ ላይ ያስወጣዎታል።</t>
         </is>
       </c>
       <c r="E140" s="13" t="inlineStr">
         <is>
-          <t>Herregoota {n}</t>
+          <t>Jijjiiruun biraawzarii biroo isin keessa seentan hunda irraa isin baasa.</t>
         </is>
       </c>
       <c r="F140" s="12" t="inlineStr">
         <is>
-          <t>{n} ሕሳባት</t>
+          <t>ምቕያሩ ኣብ ካልእ ዝኣተኹምሉ ኩሉ መርበብ መንሸራተቲ የውጽኣኩም።</t>
         </is>
       </c>
       <c r="G140" s="13" t="inlineStr">
         <is>
-          <t>{n} xisaabood</t>
+          <t>Beddelkeedu wuxuu kaa saarayaa dhammaan browser-yada kale ee aad ku jirto.</t>
         </is>
       </c>
       <c r="H140" s="14" t="inlineStr"/>
@@ -10765,7 +10765,7 @@
     <row r="141" ht="44" customHeight="1">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>one_account</t>
+          <t>change_password</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
@@ -10775,27 +10775,27 @@
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>{n} account</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>{n} መለያ</t>
+          <t>የይለፍ ቃል ቀይር</t>
         </is>
       </c>
       <c r="E141" s="13" t="inlineStr">
         <is>
-          <t>Herrega {n}</t>
+          <t>Jecha darbii jijjiiri</t>
         </is>
       </c>
       <c r="F141" s="12" t="inlineStr">
         <is>
-          <t>{n} ሕሳብ</t>
+          <t>መሕለፊ ቃል ቀይር</t>
         </is>
       </c>
       <c r="G141" s="13" t="inlineStr">
         <is>
-          <t>{n} xisaab</t>
+          <t>Bedel furaha sirta ah</t>
         </is>
       </c>
       <c r="H141" s="14" t="inlineStr"/>
@@ -10803,7 +10803,7 @@
     <row r="142" ht="44" customHeight="1">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>password_changed</t>
         </is>
       </c>
       <c r="B142" s="11" t="inlineStr">
@@ -10813,27 +10813,27 @@
       </c>
       <c r="C142" s="11" t="inlineStr">
         <is>
-          <t>Person</t>
+          <t>Password changed. Other sessions were signed out.</t>
         </is>
       </c>
       <c r="D142" s="12" t="inlineStr">
         <is>
-          <t>ሰው</t>
+          <t>የይለፍ ቃል ተቀይሯል። ሌሎች ክፍለ-ጊዜዎች ወጥተዋል።</t>
         </is>
       </c>
       <c r="E142" s="13" t="inlineStr">
         <is>
-          <t>Nama</t>
+          <t>Jechi darbii jijjiirameera. Sessionoonni biroo ba'aniiru.</t>
         </is>
       </c>
       <c r="F142" s="12" t="inlineStr">
         <is>
-          <t>ሰብ</t>
+          <t>መሕለፊ ቃል ተቐዪሩ። ካልኦት ክፍለ-ግዜታት ወጺኦም።</t>
         </is>
       </c>
       <c r="G142" s="13" t="inlineStr">
         <is>
-          <t>Qof</t>
+          <t>Furaha sirta ah waa la beddelay. Kalfadhiyada kale waa laga saaray.</t>
         </is>
       </c>
       <c r="H142" s="14" t="inlineStr"/>
@@ -10841,7 +10841,7 @@
     <row r="143" ht="44" customHeight="1">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>add_person</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
@@ -10851,27 +10851,27 @@
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Add person</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>ሚና</t>
+          <t>ሰው ጨምር</t>
         </is>
       </c>
       <c r="E143" s="13" t="inlineStr">
         <is>
-          <t>Gahee</t>
+          <t>Nama dabali</t>
         </is>
       </c>
       <c r="F143" s="12" t="inlineStr">
         <is>
-          <t>ግደ</t>
+          <t>ሰብ ወስኽ</t>
         </is>
       </c>
       <c r="G143" s="13" t="inlineStr">
         <is>
-          <t>Doorka</t>
+          <t>Ku dar qof</t>
         </is>
       </c>
       <c r="H143" s="14" t="inlineStr"/>
@@ -10879,7 +10879,7 @@
     <row r="144" ht="44" customHeight="1">
       <c r="A144" s="11" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>n_accounts</t>
         </is>
       </c>
       <c r="B144" s="11" t="inlineStr">
@@ -10889,27 +10889,27 @@
       </c>
       <c r="C144" s="11" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>{n} accounts</t>
         </is>
       </c>
       <c r="D144" s="12" t="inlineStr">
         <is>
-          <t>ሁኔታ</t>
+          <t>{n} መለያዎች</t>
         </is>
       </c>
       <c r="E144" s="13" t="inlineStr">
         <is>
-          <t>Haala</t>
+          <t>Herregoota {n}</t>
         </is>
       </c>
       <c r="F144" s="12" t="inlineStr">
         <is>
-          <t>ኩነታት</t>
+          <t>{n} ሕሳባት</t>
         </is>
       </c>
       <c r="G144" s="13" t="inlineStr">
         <is>
-          <t>Xaalada</t>
+          <t>{n} xisaabood</t>
         </is>
       </c>
       <c r="H144" s="14" t="inlineStr"/>
@@ -10917,7 +10917,7 @@
     <row r="145" ht="44" customHeight="1">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>last_signed_in</t>
+          <t>one_account</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
@@ -10927,27 +10927,27 @@
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>Last signed in</t>
+          <t>{n} account</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>መጨረሻ የገቡበት</t>
+          <t>{n} መለያ</t>
         </is>
       </c>
       <c r="E145" s="13" t="inlineStr">
         <is>
-          <t>Yeroo dhumaa seenan</t>
+          <t>Herrega {n}</t>
         </is>
       </c>
       <c r="F145" s="12" t="inlineStr">
         <is>
-          <t>ናይ መወዳእታ ዝኣተዉሉ</t>
+          <t>{n} ሕሳብ</t>
         </is>
       </c>
       <c r="G145" s="13" t="inlineStr">
         <is>
-          <t>Markii ugu dambeysay ee la galay</t>
+          <t>{n} xisaab</t>
         </is>
       </c>
       <c r="H145" s="14" t="inlineStr"/>
@@ -10955,7 +10955,7 @@
     <row r="146" ht="44" customHeight="1">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t>actions</t>
+          <t>person</t>
         </is>
       </c>
       <c r="B146" s="11" t="inlineStr">
@@ -10965,27 +10965,27 @@
       </c>
       <c r="C146" s="11" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Person</t>
         </is>
       </c>
       <c r="D146" s="12" t="inlineStr">
         <is>
-          <t>ድርጊቶች</t>
+          <t>ሰው</t>
         </is>
       </c>
       <c r="E146" s="13" t="inlineStr">
         <is>
-          <t>Gochaalee</t>
+          <t>Nama</t>
         </is>
       </c>
       <c r="F146" s="12" t="inlineStr">
         <is>
-          <t>ተግባራት</t>
+          <t>ሰብ</t>
         </is>
       </c>
       <c r="G146" s="13" t="inlineStr">
         <is>
-          <t>Ficillo</t>
+          <t>Qof</t>
         </is>
       </c>
       <c r="H146" s="14" t="inlineStr"/>
@@ -10993,7 +10993,7 @@
     <row r="147" ht="44" customHeight="1">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>thats_you</t>
+          <t>role</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
@@ -11003,27 +11003,27 @@
       </c>
       <c r="C147" s="11" t="inlineStr">
         <is>
-          <t>that’s you</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>ይህ እርስዎ ነዎት</t>
+          <t>ሚና</t>
         </is>
       </c>
       <c r="E147" s="13" t="inlineStr">
         <is>
-          <t>kun isinuma</t>
+          <t>Gahee</t>
         </is>
       </c>
       <c r="F147" s="12" t="inlineStr">
         <is>
-          <t>እዚ ንስኹም ኢኹም</t>
+          <t>ግደ</t>
         </is>
       </c>
       <c r="G147" s="13" t="inlineStr">
         <is>
-          <t>kaasi waa adiga</t>
+          <t>Doorka</t>
         </is>
       </c>
       <c r="H147" s="14" t="inlineStr"/>
@@ -11031,7 +11031,7 @@
     <row r="148" ht="44" customHeight="1">
       <c r="A148" s="11" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>status</t>
         </is>
       </c>
       <c r="B148" s="11" t="inlineStr">
@@ -11041,27 +11041,27 @@
       </c>
       <c r="C148" s="11" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="D148" s="12" t="inlineStr">
         <is>
-          <t>ንቁ</t>
+          <t>ሁኔታ</t>
         </is>
       </c>
       <c r="E148" s="13" t="inlineStr">
         <is>
-          <t>Ka'aa</t>
+          <t>Haala</t>
         </is>
       </c>
       <c r="F148" s="12" t="inlineStr">
         <is>
-          <t>ንጡፍ</t>
+          <t>ኩነታት</t>
         </is>
       </c>
       <c r="G148" s="13" t="inlineStr">
         <is>
-          <t>Firfircoon</t>
+          <t>Xaalada</t>
         </is>
       </c>
       <c r="H148" s="14" t="inlineStr"/>
@@ -11069,7 +11069,7 @@
     <row r="149" ht="44" customHeight="1">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>disabled</t>
+          <t>last_signed_in</t>
         </is>
       </c>
       <c r="B149" s="11" t="inlineStr">
@@ -11079,27 +11079,27 @@
       </c>
       <c r="C149" s="11" t="inlineStr">
         <is>
-          <t>Disabled</t>
+          <t>Last signed in</t>
         </is>
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>የተሰናከለ</t>
+          <t>መጨረሻ የገቡበት</t>
         </is>
       </c>
       <c r="E149" s="13" t="inlineStr">
         <is>
-          <t>Kan dhaabame</t>
+          <t>Yeroo dhumaa seenan</t>
         </is>
       </c>
       <c r="F149" s="12" t="inlineStr">
         <is>
-          <t>ዝተዓገተ</t>
+          <t>ናይ መወዳእታ ዝኣተዉሉ</t>
         </is>
       </c>
       <c r="G149" s="13" t="inlineStr">
         <is>
-          <t>La demiyay</t>
+          <t>Markii ugu dambeysay ee la galay</t>
         </is>
       </c>
       <c r="H149" s="14" t="inlineStr"/>
@@ -11107,7 +11107,7 @@
     <row r="150" ht="44" customHeight="1">
       <c r="A150" s="11" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>actions</t>
         </is>
       </c>
       <c r="B150" s="11" t="inlineStr">
@@ -11117,27 +11117,27 @@
       </c>
       <c r="C150" s="11" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>Actions</t>
         </is>
       </c>
       <c r="D150" s="12" t="inlineStr">
         <is>
-          <t>በጭራሽ</t>
+          <t>ድርጊቶች</t>
         </is>
       </c>
       <c r="E150" s="13" t="inlineStr">
         <is>
-          <t>gonkumaa</t>
+          <t>Gochaalee</t>
         </is>
       </c>
       <c r="F150" s="12" t="inlineStr">
         <is>
-          <t>ፈጺሙ</t>
+          <t>ተግባራት</t>
         </is>
       </c>
       <c r="G150" s="13" t="inlineStr">
         <is>
-          <t>waligeed</t>
+          <t>Ficillo</t>
         </is>
       </c>
       <c r="H150" s="14" t="inlineStr"/>
@@ -11145,7 +11145,7 @@
     <row r="151" ht="44" customHeight="1">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>disable</t>
+          <t>thats_you</t>
         </is>
       </c>
       <c r="B151" s="11" t="inlineStr">
@@ -11155,27 +11155,27 @@
       </c>
       <c r="C151" s="11" t="inlineStr">
         <is>
-          <t>Disable</t>
+          <t>that’s you</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>አሰናክል</t>
+          <t>ይህ እርስዎ ነዎት</t>
         </is>
       </c>
       <c r="E151" s="13" t="inlineStr">
         <is>
-          <t>Dhaabi</t>
+          <t>kun isinuma</t>
         </is>
       </c>
       <c r="F151" s="12" t="inlineStr">
         <is>
-          <t>ዓግት</t>
+          <t>እዚ ንስኹም ኢኹም</t>
         </is>
       </c>
       <c r="G151" s="13" t="inlineStr">
         <is>
-          <t>Demi</t>
+          <t>kaasi waa adiga</t>
         </is>
       </c>
       <c r="H151" s="14" t="inlineStr"/>
@@ -11183,7 +11183,7 @@
     <row r="152" ht="44" customHeight="1">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>restore</t>
+          <t>active</t>
         </is>
       </c>
       <c r="B152" s="11" t="inlineStr">
@@ -11193,27 +11193,27 @@
       </c>
       <c r="C152" s="11" t="inlineStr">
         <is>
-          <t>Restore</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="D152" s="12" t="inlineStr">
         <is>
-          <t>መልስ</t>
+          <t>ንቁ</t>
         </is>
       </c>
       <c r="E152" s="13" t="inlineStr">
         <is>
-          <t>Deebisi</t>
+          <t>Ka'aa</t>
         </is>
       </c>
       <c r="F152" s="12" t="inlineStr">
         <is>
-          <t>መልስ</t>
+          <t>ንጡፍ</t>
         </is>
       </c>
       <c r="G152" s="13" t="inlineStr">
         <is>
-          <t>Soo celi</t>
+          <t>Firfircoon</t>
         </is>
       </c>
       <c r="H152" s="14" t="inlineStr"/>
@@ -11221,7 +11221,7 @@
     <row r="153" ht="44" customHeight="1">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>what_each_role_can_do</t>
+          <t>disabled</t>
         </is>
       </c>
       <c r="B153" s="11" t="inlineStr">
@@ -11231,27 +11231,27 @@
       </c>
       <c r="C153" s="11" t="inlineStr">
         <is>
-          <t>What each role can do</t>
+          <t>Disabled</t>
         </is>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>እያንዳንዱ ሚና ምን ማድረግ ይችላል</t>
+          <t>የተሰናከለ</t>
         </is>
       </c>
       <c r="E153" s="13" t="inlineStr">
         <is>
-          <t>Gaheen tokkoon tokkoon isaanii maal gochuu danda'a</t>
+          <t>Kan dhaabame</t>
         </is>
       </c>
       <c r="F153" s="12" t="inlineStr">
         <is>
-          <t>ነፍስ ወከፍ ግደ እንታይ ክገብር ይኽእል</t>
+          <t>ዝተዓገተ</t>
         </is>
       </c>
       <c r="G153" s="13" t="inlineStr">
         <is>
-          <t>Waxa doorkiiba uu samayn karo</t>
+          <t>La demiyay</t>
         </is>
       </c>
       <c r="H153" s="14" t="inlineStr"/>
@@ -11259,7 +11259,7 @@
     <row r="154" ht="44" customHeight="1">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t>built_in</t>
+          <t>never</t>
         </is>
       </c>
       <c r="B154" s="11" t="inlineStr">
@@ -11269,27 +11269,27 @@
       </c>
       <c r="C154" s="11" t="inlineStr">
         <is>
-          <t>built-in</t>
+          <t>never</t>
         </is>
       </c>
       <c r="D154" s="12" t="inlineStr">
         <is>
-          <t>አብሮ የተሰራ</t>
+          <t>በጭራሽ</t>
         </is>
       </c>
       <c r="E154" s="13" t="inlineStr">
         <is>
-          <t>kan ijaarame</t>
+          <t>gonkumaa</t>
         </is>
       </c>
       <c r="F154" s="12" t="inlineStr">
         <is>
-          <t>ውሁድ</t>
+          <t>ፈጺሙ</t>
         </is>
       </c>
       <c r="G154" s="13" t="inlineStr">
         <is>
-          <t>ku dhex jira</t>
+          <t>waligeed</t>
         </is>
       </c>
       <c r="H154" s="14" t="inlineStr"/>
@@ -11297,7 +11297,7 @@
     <row r="155" ht="44" customHeight="1">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>add_a_person</t>
+          <t>disable</t>
         </is>
       </c>
       <c r="B155" s="11" t="inlineStr">
@@ -11307,27 +11307,27 @@
       </c>
       <c r="C155" s="11" t="inlineStr">
         <is>
-          <t>Add a person</t>
+          <t>Disable</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>ሰው ጨምር</t>
+          <t>አሰናክል</t>
         </is>
       </c>
       <c r="E155" s="13" t="inlineStr">
         <is>
-          <t>Nama dabali</t>
+          <t>Dhaabi</t>
         </is>
       </c>
       <c r="F155" s="12" t="inlineStr">
         <is>
-          <t>ሰብ ወስኽ</t>
+          <t>ዓግት</t>
         </is>
       </c>
       <c r="G155" s="13" t="inlineStr">
         <is>
-          <t>Qof ku dar</t>
+          <t>Demi</t>
         </is>
       </c>
       <c r="H155" s="14" t="inlineStr"/>
@@ -11335,7 +11335,7 @@
     <row r="156" ht="44" customHeight="1">
       <c r="A156" s="11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>restore</t>
         </is>
       </c>
       <c r="B156" s="11" t="inlineStr">
@@ -11345,27 +11345,27 @@
       </c>
       <c r="C156" s="11" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Restore</t>
         </is>
       </c>
       <c r="D156" s="12" t="inlineStr">
         <is>
-          <t>ኢሜይል</t>
+          <t>መልስ</t>
         </is>
       </c>
       <c r="E156" s="13" t="inlineStr">
         <is>
-          <t>Imeelii</t>
+          <t>Deebisi</t>
         </is>
       </c>
       <c r="F156" s="12" t="inlineStr">
         <is>
-          <t>ኢመይል</t>
+          <t>መልስ</t>
         </is>
       </c>
       <c r="G156" s="13" t="inlineStr">
         <is>
-          <t>Iimayl</t>
+          <t>Soo celi</t>
         </is>
       </c>
       <c r="H156" s="14" t="inlineStr"/>
@@ -11373,7 +11373,7 @@
     <row r="157" ht="44" customHeight="1">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>name_optional</t>
+          <t>what_each_role_can_do</t>
         </is>
       </c>
       <c r="B157" s="11" t="inlineStr">
@@ -11383,27 +11383,27 @@
       </c>
       <c r="C157" s="11" t="inlineStr">
         <is>
-          <t>Name (optional)</t>
+          <t>What each role can do</t>
         </is>
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>ስም (አማራጭ)</t>
+          <t>እያንዳንዱ ሚና ምን ማድረግ ይችላል</t>
         </is>
       </c>
       <c r="E157" s="13" t="inlineStr">
         <is>
-          <t>Maqaa (filannoo)</t>
+          <t>Gaheen tokkoon tokkoon isaanii maal gochuu danda'a</t>
         </is>
       </c>
       <c r="F157" s="12" t="inlineStr">
         <is>
-          <t>ስም (ኣማራጺ)</t>
+          <t>ነፍስ ወከፍ ግደ እንታይ ክገብር ይኽእል</t>
         </is>
       </c>
       <c r="G157" s="13" t="inlineStr">
         <is>
-          <t>Magac (ikhtiyaari)</t>
+          <t>Waxa doorkiiba uu samayn karo</t>
         </is>
       </c>
       <c r="H157" s="14" t="inlineStr"/>
@@ -11411,7 +11411,7 @@
     <row r="158" ht="44" customHeight="1">
       <c r="A158" s="11" t="inlineStr">
         <is>
-          <t>temporary_password</t>
+          <t>built_in</t>
         </is>
       </c>
       <c r="B158" s="11" t="inlineStr">
@@ -11421,27 +11421,27 @@
       </c>
       <c r="C158" s="11" t="inlineStr">
         <is>
-          <t>Temporary password</t>
+          <t>built-in</t>
         </is>
       </c>
       <c r="D158" s="12" t="inlineStr">
         <is>
-          <t>ጊዜያዊ የይለፍ ቃል</t>
+          <t>አብሮ የተሰራ</t>
         </is>
       </c>
       <c r="E158" s="13" t="inlineStr">
         <is>
-          <t>Jecha darbii yeroo</t>
+          <t>kan ijaarame</t>
         </is>
       </c>
       <c r="F158" s="12" t="inlineStr">
         <is>
-          <t>ግዝያዊ መሕለፊ ቃል</t>
+          <t>ውሁድ</t>
         </is>
       </c>
       <c r="G158" s="13" t="inlineStr">
         <is>
-          <t>Fure ku meel gaar ah</t>
+          <t>ku dhex jira</t>
         </is>
       </c>
       <c r="H158" s="14" t="inlineStr"/>
@@ -11449,7 +11449,7 @@
     <row r="159" ht="44" customHeight="1">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>temp_password_help</t>
+          <t>add_a_person</t>
         </is>
       </c>
       <c r="B159" s="11" t="inlineStr">
@@ -11459,27 +11459,27 @@
       </c>
       <c r="C159" s="11" t="inlineStr">
         <is>
-          <t>At least 12 characters. Until invitation emails are set up, this password has to be given to them directly — which is why it is shown here rather than hidden.</t>
+          <t>Add a person</t>
         </is>
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>ቢያንስ 12 ቁምፊ። የግብዣ ኢሜይሎች እስኪዘጋጁ ድረስ ይህ የይለፍ ቃል በቀጥታ ሊሰጣቸው ይገባል — ስለዚህ ተደብቆ ሳይሆን እዚህ ይታያል።</t>
+          <t>ሰው ጨምር</t>
         </is>
       </c>
       <c r="E159" s="13" t="inlineStr">
         <is>
-          <t>Yoo xiqqaate arfiilee 12. Hanga imeeliin afeerraa qophaa'utti, jechi darbii kun kallattiin isaaniif kennamuu qaba — kanaafuu dhokfamuu mannaa asitti ni mul'ata.</t>
+          <t>Nama dabali</t>
         </is>
       </c>
       <c r="F159" s="12" t="inlineStr">
         <is>
-          <t>ብውሑዱ 12 ፊደላት። መጸዋዕታ ኢመይል ክሳብ ዝዳሎ እዚ መሕለፊ ቃል ብቐጥታ ክወሃቦም ኣለዎ — ስለዚ ተሓቢኡ ዘይኮነ ኣብዚ ይረአ።</t>
+          <t>ሰብ ወስኽ</t>
         </is>
       </c>
       <c r="G159" s="13" t="inlineStr">
         <is>
-          <t>Ugu yaraan 12 xaraf. Ilaa iimaylada casumaadda la dejiyo, furahan si toos ah ayaa loo siin doonaa — sidaas darteed halkan ayuu ka muuqdaa halkii la qarin lahaa.</t>
+          <t>Qof ku dar</t>
         </is>
       </c>
       <c r="H159" s="14" t="inlineStr"/>
@@ -11487,7 +11487,7 @@
     <row r="160" ht="44" customHeight="1">
       <c r="A160" s="11" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>email</t>
         </is>
       </c>
       <c r="B160" s="11" t="inlineStr">
@@ -11497,27 +11497,27 @@
       </c>
       <c r="C160" s="11" t="inlineStr">
         <is>
-          <t>Create</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D160" s="12" t="inlineStr">
         <is>
-          <t>ፍጠር</t>
+          <t>ኢሜይል</t>
         </is>
       </c>
       <c r="E160" s="13" t="inlineStr">
         <is>
-          <t>Uumi</t>
+          <t>Imeelii</t>
         </is>
       </c>
       <c r="F160" s="12" t="inlineStr">
         <is>
-          <t>ፍጠር</t>
+          <t>ኢመይል</t>
         </is>
       </c>
       <c r="G160" s="13" t="inlineStr">
         <is>
-          <t>Abuur</t>
+          <t>Iimayl</t>
         </is>
       </c>
       <c r="H160" s="14" t="inlineStr"/>
@@ -11525,7 +11525,7 @@
     <row r="161" ht="44" customHeight="1">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>account_created</t>
+          <t>name_optional</t>
         </is>
       </c>
       <c r="B161" s="11" t="inlineStr">
@@ -11535,27 +11535,27 @@
       </c>
       <c r="C161" s="11" t="inlineStr">
         <is>
-          <t>Account created</t>
+          <t>Name (optional)</t>
         </is>
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>መለያ ተፈጥሯል</t>
+          <t>ስም (አማራጭ)</t>
         </is>
       </c>
       <c r="E161" s="13" t="inlineStr">
         <is>
-          <t>Herregni uumame</t>
+          <t>Maqaa (filannoo)</t>
         </is>
       </c>
       <c r="F161" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ ተፈጢሩ</t>
+          <t>ስም (ኣማራጺ)</t>
         </is>
       </c>
       <c r="G161" s="13" t="inlineStr">
         <is>
-          <t>Xisaab waa la abuuray</t>
+          <t>Magac (ikhtiyaari)</t>
         </is>
       </c>
       <c r="H161" s="14" t="inlineStr"/>
@@ -11563,7 +11563,7 @@
     <row r="162" ht="44" customHeight="1">
       <c r="A162" s="11" t="inlineStr">
         <is>
-          <t>account_restored</t>
+          <t>temporary_password</t>
         </is>
       </c>
       <c r="B162" s="11" t="inlineStr">
@@ -11573,27 +11573,27 @@
       </c>
       <c r="C162" s="11" t="inlineStr">
         <is>
-          <t>Account restored</t>
+          <t>Temporary password</t>
         </is>
       </c>
       <c r="D162" s="12" t="inlineStr">
         <is>
-          <t>መለያ ተመልሷል</t>
+          <t>ጊዜያዊ የይለፍ ቃል</t>
         </is>
       </c>
       <c r="E162" s="13" t="inlineStr">
         <is>
-          <t>Herregni deebi'e</t>
+          <t>Jecha darbii yeroo</t>
         </is>
       </c>
       <c r="F162" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ ተመሊሱ</t>
+          <t>ግዝያዊ መሕለፊ ቃል</t>
         </is>
       </c>
       <c r="G162" s="13" t="inlineStr">
         <is>
-          <t>Xisaabta waa la soo celiyay</t>
+          <t>Fure ku meel gaar ah</t>
         </is>
       </c>
       <c r="H162" s="14" t="inlineStr"/>
@@ -11601,7 +11601,7 @@
     <row r="163" ht="44" customHeight="1">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>account_disabled_n</t>
+          <t>temp_password_help</t>
         </is>
       </c>
       <c r="B163" s="11" t="inlineStr">
@@ -11611,27 +11611,27 @@
       </c>
       <c r="C163" s="11" t="inlineStr">
         <is>
-          <t>Account disabled, {n} session(s) ended</t>
+          <t>At least 12 characters. Until invitation emails are set up, this password has to be given to them directly — which is why it is shown here rather than hidden.</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>መለያ ተሰናክሏል፤ {n} ክፍለ-ጊዜ ተዘግቷል</t>
+          <t>ቢያንስ 12 ቁምፊ። የግብዣ ኢሜይሎች እስኪዘጋጁ ድረስ ይህ የይለፍ ቃል በቀጥታ ሊሰጣቸው ይገባል — ስለዚህ ተደብቆ ሳይሆን እዚህ ይታያል።</t>
         </is>
       </c>
       <c r="E163" s="13" t="inlineStr">
         <is>
-          <t>Herregni dhaabame, session {n} xumurame</t>
+          <t>Yoo xiqqaate arfiilee 12. Hanga imeeliin afeerraa qophaa'utti, jechi darbii kun kallattiin isaaniif kennamuu qaba — kanaafuu dhokfamuu mannaa asitti ni mul'ata.</t>
         </is>
       </c>
       <c r="F163" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ ተዓጊቱ፣ {n} ክፍለ-ግዜ ተዛዚሙ</t>
+          <t>ብውሑዱ 12 ፊደላት። መጸዋዕታ ኢመይል ክሳብ ዝዳሎ እዚ መሕለፊ ቃል ብቐጥታ ክወሃቦም ኣለዎ — ስለዚ ተሓቢኡ ዘይኮነ ኣብዚ ይረአ።</t>
         </is>
       </c>
       <c r="G163" s="13" t="inlineStr">
         <is>
-          <t>Xisaabta waa la demiyay, {n} kalfadhi ayaa dhammaaday</t>
+          <t>Ugu yaraan 12 xaraf. Ilaa iimaylada casumaadda la dejiyo, furahan si toos ah ayaa loo siin doonaa — sidaas darteed halkan ayuu ka muuqdaa halkii la qarin lahaa.</t>
         </is>
       </c>
       <c r="H163" s="14" t="inlineStr"/>
@@ -11639,7 +11639,7 @@
     <row r="164" ht="44" customHeight="1">
       <c r="A164" s="11" t="inlineStr">
         <is>
-          <t>confirm_disable_account</t>
+          <t>create</t>
         </is>
       </c>
       <c r="B164" s="11" t="inlineStr">
@@ -11649,27 +11649,27 @@
       </c>
       <c r="C164" s="11" t="inlineStr">
         <is>
-          <t>Disable this account? They will be signed out immediately.</t>
+          <t>Create</t>
         </is>
       </c>
       <c r="D164" s="12" t="inlineStr">
         <is>
-          <t>ይህን መለያ ማሰናከል? ወዲያውኑ ይወጣሉ።</t>
+          <t>ፍጠር</t>
         </is>
       </c>
       <c r="E164" s="13" t="inlineStr">
         <is>
-          <t>Herrega kana dhaabuu? Battalumatti ni baafamu.</t>
+          <t>Uumi</t>
         </is>
       </c>
       <c r="F164" s="12" t="inlineStr">
         <is>
-          <t>ነዚ ሕሳብ ክዕገት? ብቕጽበት ይወጹ።</t>
+          <t>ፍጠር</t>
         </is>
       </c>
       <c r="G164" s="13" t="inlineStr">
         <is>
-          <t>Xisaabtan ma demineysaa? Isla markiiba waa laga saarayaa.</t>
+          <t>Abuur</t>
         </is>
       </c>
       <c r="H164" s="14" t="inlineStr"/>
@@ -11677,7 +11677,7 @@
     <row r="165" ht="44" customHeight="1">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>action_document_created</t>
+          <t>account_created</t>
         </is>
       </c>
       <c r="B165" s="11" t="inlineStr">
@@ -11687,27 +11687,27 @@
       </c>
       <c r="C165" s="11" t="inlineStr">
         <is>
-          <t>added an article</t>
+          <t>Account created</t>
         </is>
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ጨምሯል</t>
+          <t>መለያ ተፈጥሯል</t>
         </is>
       </c>
       <c r="E165" s="13" t="inlineStr">
         <is>
-          <t>barruu dabale</t>
+          <t>Herregni uumame</t>
         </is>
       </c>
       <c r="F165" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ወሲኹ</t>
+          <t>ሕሳብ ተፈጢሩ</t>
         </is>
       </c>
       <c r="G165" s="13" t="inlineStr">
         <is>
-          <t>maqaal ku daray</t>
+          <t>Xisaab waa la abuuray</t>
         </is>
       </c>
       <c r="H165" s="14" t="inlineStr"/>
@@ -11715,7 +11715,7 @@
     <row r="166" ht="44" customHeight="1">
       <c r="A166" s="11" t="inlineStr">
         <is>
-          <t>action_document_updated</t>
+          <t>account_restored</t>
         </is>
       </c>
       <c r="B166" s="11" t="inlineStr">
@@ -11725,27 +11725,27 @@
       </c>
       <c r="C166" s="11" t="inlineStr">
         <is>
-          <t>edited an article</t>
+          <t>Account restored</t>
         </is>
       </c>
       <c r="D166" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ አርሟል</t>
+          <t>መለያ ተመልሷል</t>
         </is>
       </c>
       <c r="E166" s="13" t="inlineStr">
         <is>
-          <t>barruu gulaale</t>
+          <t>Herregni deebi'e</t>
         </is>
       </c>
       <c r="F166" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ኣርሚዑ</t>
+          <t>ሕሳብ ተመሊሱ</t>
         </is>
       </c>
       <c r="G166" s="13" t="inlineStr">
         <is>
-          <t>maqaal wax ka beddelay</t>
+          <t>Xisaabta waa la soo celiyay</t>
         </is>
       </c>
       <c r="H166" s="14" t="inlineStr"/>
@@ -11753,7 +11753,7 @@
     <row r="167" ht="44" customHeight="1">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>action_document_deleted</t>
+          <t>account_disabled_n</t>
         </is>
       </c>
       <c r="B167" s="11" t="inlineStr">
@@ -11763,27 +11763,27 @@
       </c>
       <c r="C167" s="11" t="inlineStr">
         <is>
-          <t>deleted an article</t>
+          <t>Account disabled, {n} session(s) ended</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ሰርዟል</t>
+          <t>መለያ ተሰናክሏል፤ {n} ክፍለ-ጊዜ ተዘግቷል</t>
         </is>
       </c>
       <c r="E167" s="13" t="inlineStr">
         <is>
-          <t>barruu haqe</t>
+          <t>Herregni dhaabame, session {n} xumurame</t>
         </is>
       </c>
       <c r="F167" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ደምሲሱ</t>
+          <t>ሕሳብ ተዓጊቱ፣ {n} ክፍለ-ግዜ ተዛዚሙ</t>
         </is>
       </c>
       <c r="G167" s="13" t="inlineStr">
         <is>
-          <t>maqaal tirtiray</t>
+          <t>Xisaabta waa la demiyay, {n} kalfadhi ayaa dhammaaday</t>
         </is>
       </c>
       <c r="H167" s="14" t="inlineStr"/>
@@ -11791,7 +11791,7 @@
     <row r="168" ht="44" customHeight="1">
       <c r="A168" s="11" t="inlineStr">
         <is>
-          <t>action_documents_bulk_imported</t>
+          <t>confirm_disable_account</t>
         </is>
       </c>
       <c r="B168" s="11" t="inlineStr">
@@ -11801,27 +11801,27 @@
       </c>
       <c r="C168" s="11" t="inlineStr">
         <is>
-          <t>imported articles</t>
+          <t>Disable this account? They will be signed out immediately.</t>
         </is>
       </c>
       <c r="D168" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፎችን አስገብቷል</t>
+          <t>ይህን መለያ ማሰናከል? ወዲያውኑ ይወጣሉ።</t>
         </is>
       </c>
       <c r="E168" s="13" t="inlineStr">
         <is>
-          <t>barruulee galche</t>
+          <t>Herrega kana dhaabuu? Battalumatti ni baafamu.</t>
         </is>
       </c>
       <c r="F168" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፋት ኣእትዩ</t>
+          <t>ነዚ ሕሳብ ክዕገት? ብቕጽበት ይወጹ።</t>
         </is>
       </c>
       <c r="G168" s="13" t="inlineStr">
         <is>
-          <t>maqaallo soo dhoofiyay</t>
+          <t>Xisaabtan ma demineysaa? Isla markiiba waa laga saarayaa.</t>
         </is>
       </c>
       <c r="H168" s="14" t="inlineStr"/>
@@ -11829,7 +11829,7 @@
     <row r="169" ht="44" customHeight="1">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_closed</t>
+          <t>action_document_created</t>
         </is>
       </c>
       <c r="B169" s="11" t="inlineStr">
@@ -11839,27 +11839,27 @@
       </c>
       <c r="C169" s="11" t="inlineStr">
         <is>
-          <t>closed an escalation</t>
+          <t>added an article</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ ዘግቷል</t>
+          <t>ጽሑፍ ጨምሯል</t>
         </is>
       </c>
       <c r="E169" s="13" t="inlineStr">
         <is>
-          <t>dhimma cufe</t>
+          <t>barruu dabale</t>
         </is>
       </c>
       <c r="F169" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ ዓጺዩ</t>
+          <t>ጽሑፍ ወሲኹ</t>
         </is>
       </c>
       <c r="G169" s="13" t="inlineStr">
         <is>
-          <t>arrin xiray</t>
+          <t>maqaal ku daray</t>
         </is>
       </c>
       <c r="H169" s="14" t="inlineStr"/>
@@ -11867,7 +11867,7 @@
     <row r="170" ht="44" customHeight="1">
       <c r="A170" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_reopened</t>
+          <t>action_document_updated</t>
         </is>
       </c>
       <c r="B170" s="11" t="inlineStr">
@@ -11877,27 +11877,27 @@
       </c>
       <c r="C170" s="11" t="inlineStr">
         <is>
-          <t>reopened an escalation</t>
+          <t>edited an article</t>
         </is>
       </c>
       <c r="D170" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ በድጋሚ ከፍቷል</t>
+          <t>ጽሑፍ አርሟል</t>
         </is>
       </c>
       <c r="E170" s="13" t="inlineStr">
         <is>
-          <t>dhimma irra deebi'ee bane</t>
+          <t>barruu gulaale</t>
         </is>
       </c>
       <c r="F170" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ ደጊሙ ከፊቱ</t>
+          <t>ጽሑፍ ኣርሚዑ</t>
         </is>
       </c>
       <c r="G170" s="13" t="inlineStr">
         <is>
-          <t>arrin dib u furay</t>
+          <t>maqaal wax ka beddelay</t>
         </is>
       </c>
       <c r="H170" s="14" t="inlineStr"/>
@@ -11905,7 +11905,7 @@
     <row r="171" ht="44" customHeight="1">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_webhook_connected</t>
+          <t>action_document_deleted</t>
         </is>
       </c>
       <c r="B171" s="11" t="inlineStr">
@@ -11915,27 +11915,27 @@
       </c>
       <c r="C171" s="11" t="inlineStr">
         <is>
-          <t>connected the escalation webhook</t>
+          <t>deleted an article</t>
         </is>
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ዌብሁክ አገናኝቷል</t>
+          <t>ጽሑፍ ሰርዟል</t>
         </is>
       </c>
       <c r="E171" s="13" t="inlineStr">
         <is>
-          <t>webhook dabarsaa walqunnamsiise</t>
+          <t>barruu haqe</t>
         </is>
       </c>
       <c r="F171" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ምትሕልላፍ ኣራኺቡ</t>
+          <t>ጽሑፍ ደምሲሱ</t>
         </is>
       </c>
       <c r="G171" s="13" t="inlineStr">
         <is>
-          <t>ku xiray webhook-ga gudbinta</t>
+          <t>maqaal tirtiray</t>
         </is>
       </c>
       <c r="H171" s="14" t="inlineStr"/>
@@ -11943,7 +11943,7 @@
     <row r="172" ht="44" customHeight="1">
       <c r="A172" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_webhook_disconnected</t>
+          <t>action_documents_bulk_imported</t>
         </is>
       </c>
       <c r="B172" s="11" t="inlineStr">
@@ -11953,27 +11953,27 @@
       </c>
       <c r="C172" s="11" t="inlineStr">
         <is>
-          <t>disconnected the escalation webhook</t>
+          <t>imported articles</t>
         </is>
       </c>
       <c r="D172" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ዌብሁክ አቋርጧል</t>
+          <t>ጽሑፎችን አስገብቷል</t>
         </is>
       </c>
       <c r="E172" s="13" t="inlineStr">
         <is>
-          <t>webhook dabarsaa addaan kute</t>
+          <t>barruulee galche</t>
         </is>
       </c>
       <c r="F172" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ምትሕልላፍ ቆሪጹ</t>
+          <t>ጽሑፋት ኣእትዩ</t>
         </is>
       </c>
       <c r="G172" s="13" t="inlineStr">
         <is>
-          <t>goynay webhook-ga gudbinta</t>
+          <t>maqaallo soo dhoofiyay</t>
         </is>
       </c>
       <c r="H172" s="14" t="inlineStr"/>
@@ -11981,7 +11981,7 @@
     <row r="173" ht="44" customHeight="1">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>action_telegram_connected</t>
+          <t>action_handoff_closed</t>
         </is>
       </c>
       <c r="B173" s="11" t="inlineStr">
@@ -11991,27 +11991,27 @@
       </c>
       <c r="C173" s="11" t="inlineStr">
         <is>
-          <t>connected Telegram</t>
+          <t>closed an escalation</t>
         </is>
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>ቴሌግራም አገናኝቷል</t>
+          <t>ጉዳይ ዘግቷል</t>
         </is>
       </c>
       <c r="E173" s="13" t="inlineStr">
         <is>
-          <t>Telegram walqunnamsiise</t>
+          <t>dhimma cufe</t>
         </is>
       </c>
       <c r="F173" s="12" t="inlineStr">
         <is>
-          <t>ቴሌግራም ኣራኺቡ</t>
+          <t>ጉዳይ ዓጺዩ</t>
         </is>
       </c>
       <c r="G173" s="13" t="inlineStr">
         <is>
-          <t>Telegram ku xiray</t>
+          <t>arrin xiray</t>
         </is>
       </c>
       <c r="H173" s="14" t="inlineStr"/>
@@ -12019,7 +12019,7 @@
     <row r="174" ht="44" customHeight="1">
       <c r="A174" s="11" t="inlineStr">
         <is>
-          <t>action_user_created</t>
+          <t>action_handoff_reopened</t>
         </is>
       </c>
       <c r="B174" s="11" t="inlineStr">
@@ -12029,27 +12029,27 @@
       </c>
       <c r="C174" s="11" t="inlineStr">
         <is>
-          <t>added a colleague</t>
+          <t>reopened an escalation</t>
         </is>
       </c>
       <c r="D174" s="12" t="inlineStr">
         <is>
-          <t>ባልደረባ ጨምሯል</t>
+          <t>ጉዳይ በድጋሚ ከፍቷል</t>
         </is>
       </c>
       <c r="E174" s="13" t="inlineStr">
         <is>
-          <t>hojjetaa dabale</t>
+          <t>dhimma irra deebi'ee bane</t>
         </is>
       </c>
       <c r="F174" s="12" t="inlineStr">
         <is>
-          <t>መሳርሕቲ ወሲኹ</t>
+          <t>ጉዳይ ደጊሙ ከፊቱ</t>
         </is>
       </c>
       <c r="G174" s="13" t="inlineStr">
         <is>
-          <t>shaqaale ku daray</t>
+          <t>arrin dib u furay</t>
         </is>
       </c>
       <c r="H174" s="14" t="inlineStr"/>
@@ -12057,7 +12057,7 @@
     <row r="175" ht="44" customHeight="1">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>action_user_disabled</t>
+          <t>action_handoff_webhook_connected</t>
         </is>
       </c>
       <c r="B175" s="11" t="inlineStr">
@@ -12067,27 +12067,27 @@
       </c>
       <c r="C175" s="11" t="inlineStr">
         <is>
-          <t>disabled an account</t>
+          <t>connected the escalation webhook</t>
         </is>
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>መለያ አሰናክሏል</t>
+          <t>የማሸጋገሪያ ዌብሁክ አገናኝቷል</t>
         </is>
       </c>
       <c r="E175" s="13" t="inlineStr">
         <is>
-          <t>herrega dhaabe</t>
+          <t>webhook dabarsaa walqunnamsiise</t>
         </is>
       </c>
       <c r="F175" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ ዓጊቱ</t>
+          <t>ዌብሁክ ምትሕልላፍ ኣራኺቡ</t>
         </is>
       </c>
       <c r="G175" s="13" t="inlineStr">
         <is>
-          <t>xisaab demiyay</t>
+          <t>ku xiray webhook-ga gudbinta</t>
         </is>
       </c>
       <c r="H175" s="14" t="inlineStr"/>
@@ -12095,7 +12095,7 @@
     <row r="176" ht="44" customHeight="1">
       <c r="A176" s="11" t="inlineStr">
         <is>
-          <t>action_user_enabled</t>
+          <t>action_handoff_webhook_disconnected</t>
         </is>
       </c>
       <c r="B176" s="11" t="inlineStr">
@@ -12105,27 +12105,27 @@
       </c>
       <c r="C176" s="11" t="inlineStr">
         <is>
-          <t>restored an account</t>
+          <t>disconnected the escalation webhook</t>
         </is>
       </c>
       <c r="D176" s="12" t="inlineStr">
         <is>
-          <t>መለያ መልሷል</t>
+          <t>የማሸጋገሪያ ዌብሁክ አቋርጧል</t>
         </is>
       </c>
       <c r="E176" s="13" t="inlineStr">
         <is>
-          <t>herrega deebise</t>
+          <t>webhook dabarsaa addaan kute</t>
         </is>
       </c>
       <c r="F176" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ መሊሱ</t>
+          <t>ዌብሁክ ምትሕልላፍ ቆሪጹ</t>
         </is>
       </c>
       <c r="G176" s="13" t="inlineStr">
         <is>
-          <t>xisaab soo celiyay</t>
+          <t>goynay webhook-ga gudbinta</t>
         </is>
       </c>
       <c r="H176" s="14" t="inlineStr"/>
@@ -12133,7 +12133,7 @@
     <row r="177" ht="44" customHeight="1">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>action_admin_login</t>
+          <t>action_telegram_connected</t>
         </is>
       </c>
       <c r="B177" s="11" t="inlineStr">
@@ -12143,27 +12143,27 @@
       </c>
       <c r="C177" s="11" t="inlineStr">
         <is>
-          <t>signed in</t>
+          <t>connected Telegram</t>
         </is>
       </c>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>ገብቷል</t>
+          <t>ቴሌግራም አገናኝቷል</t>
         </is>
       </c>
       <c r="E177" s="13" t="inlineStr">
         <is>
-          <t>seene</t>
+          <t>Telegram walqunnamsiise</t>
         </is>
       </c>
       <c r="F177" s="12" t="inlineStr">
         <is>
-          <t>ኣትዩ</t>
+          <t>ቴሌግራም ኣራኺቡ</t>
         </is>
       </c>
       <c r="G177" s="13" t="inlineStr">
         <is>
-          <t>gashay</t>
+          <t>Telegram ku xiray</t>
         </is>
       </c>
       <c r="H177" s="14" t="inlineStr"/>
@@ -12171,7 +12171,7 @@
     <row r="178" ht="44" customHeight="1">
       <c r="A178" s="11" t="inlineStr">
         <is>
-          <t>action_password_changed</t>
+          <t>action_user_created</t>
         </is>
       </c>
       <c r="B178" s="11" t="inlineStr">
@@ -12181,27 +12181,27 @@
       </c>
       <c r="C178" s="11" t="inlineStr">
         <is>
-          <t>changed their password</t>
+          <t>added a colleague</t>
         </is>
       </c>
       <c r="D178" s="12" t="inlineStr">
         <is>
-          <t>የይለፍ ቃል ቀይሯል</t>
+          <t>ባልደረባ ጨምሯል</t>
         </is>
       </c>
       <c r="E178" s="13" t="inlineStr">
         <is>
-          <t>jecha darbii jijjiire</t>
+          <t>hojjetaa dabale</t>
         </is>
       </c>
       <c r="F178" s="12" t="inlineStr">
         <is>
-          <t>መሕለፊ ቃል ቀዪሩ</t>
+          <t>መሳርሕቲ ወሲኹ</t>
         </is>
       </c>
       <c r="G178" s="13" t="inlineStr">
         <is>
-          <t>beddelay furihiisa</t>
+          <t>shaqaale ku daray</t>
         </is>
       </c>
       <c r="H178" s="14" t="inlineStr"/>
@@ -12209,7 +12209,7 @@
     <row r="179" ht="44" customHeight="1">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>nothing_yet</t>
+          <t>action_user_disabled</t>
         </is>
       </c>
       <c r="B179" s="11" t="inlineStr">
@@ -12219,27 +12219,27 @@
       </c>
       <c r="C179" s="11" t="inlineStr">
         <is>
-          <t>Nothing yet.</t>
+          <t>disabled an account</t>
         </is>
       </c>
       <c r="D179" s="12" t="inlineStr">
         <is>
-          <t>እስካሁን ምንም የለም።</t>
+          <t>መለያ አሰናክሏል</t>
         </is>
       </c>
       <c r="E179" s="13" t="inlineStr">
         <is>
-          <t>Ammaaf homaa hin jiru.</t>
+          <t>herrega dhaabe</t>
         </is>
       </c>
       <c r="F179" s="12" t="inlineStr">
         <is>
-          <t>ክሳብ ሕጂ ዋላ ሓደ የለን።</t>
+          <t>ሕሳብ ዓጊቱ</t>
         </is>
       </c>
       <c r="G179" s="13" t="inlineStr">
         <is>
-          <t>Weli waxba ma jiraan.</t>
+          <t>xisaab demiyay</t>
         </is>
       </c>
       <c r="H179" s="14" t="inlineStr"/>
@@ -12247,7 +12247,7 @@
     <row r="180" ht="44" customHeight="1">
       <c r="A180" s="11" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>action_user_enabled</t>
         </is>
       </c>
       <c r="B180" s="11" t="inlineStr">
@@ -12257,27 +12257,27 @@
       </c>
       <c r="C180" s="11" t="inlineStr">
         <is>
-          <t>Unavailable.</t>
+          <t>restored an account</t>
         </is>
       </c>
       <c r="D180" s="12" t="inlineStr">
         <is>
-          <t>አይገኝም።</t>
+          <t>መለያ መልሷል</t>
         </is>
       </c>
       <c r="E180" s="13" t="inlineStr">
         <is>
-          <t>Hin argamu.</t>
+          <t>herrega deebise</t>
         </is>
       </c>
       <c r="F180" s="12" t="inlineStr">
         <is>
-          <t>ኣይርከብን።</t>
+          <t>ሕሳብ መሊሱ</t>
         </is>
       </c>
       <c r="G180" s="13" t="inlineStr">
         <is>
-          <t>Lama heli karo.</t>
+          <t>xisaab soo celiyay</t>
         </is>
       </c>
       <c r="H180" s="14" t="inlineStr"/>
@@ -12285,7 +12285,7 @@
     <row r="181" ht="44" customHeight="1">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t>just_now</t>
+          <t>action_admin_login</t>
         </is>
       </c>
       <c r="B181" s="11" t="inlineStr">
@@ -12295,27 +12295,27 @@
       </c>
       <c r="C181" s="11" t="inlineStr">
         <is>
-          <t>just now</t>
+          <t>signed in</t>
         </is>
       </c>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>አሁን</t>
+          <t>ገብቷል</t>
         </is>
       </c>
       <c r="E181" s="13" t="inlineStr">
         <is>
-          <t>amma</t>
+          <t>seene</t>
         </is>
       </c>
       <c r="F181" s="12" t="inlineStr">
         <is>
-          <t>ሕጂ</t>
+          <t>ኣትዩ</t>
         </is>
       </c>
       <c r="G181" s="13" t="inlineStr">
         <is>
-          <t>hadda</t>
+          <t>gashay</t>
         </is>
       </c>
       <c r="H181" s="14" t="inlineStr"/>
@@ -12323,7 +12323,7 @@
     <row r="182" ht="44" customHeight="1">
       <c r="A182" s="11" t="inlineStr">
         <is>
-          <t>n_min_ago</t>
+          <t>action_password_changed</t>
         </is>
       </c>
       <c r="B182" s="11" t="inlineStr">
@@ -12333,27 +12333,27 @@
       </c>
       <c r="C182" s="11" t="inlineStr">
         <is>
-          <t>{n} min ago</t>
+          <t>changed their password</t>
         </is>
       </c>
       <c r="D182" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ደቂቃ በፊት</t>
+          <t>የይለፍ ቃል ቀይሯል</t>
         </is>
       </c>
       <c r="E182" s="13" t="inlineStr">
         <is>
-          <t>daqiiqaa {n} dura</t>
+          <t>jecha darbii jijjiire</t>
         </is>
       </c>
       <c r="F182" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ደቒቕ</t>
+          <t>መሕለፊ ቃል ቀዪሩ</t>
         </is>
       </c>
       <c r="G182" s="13" t="inlineStr">
         <is>
-          <t>{n} daqiiqo ka hor</t>
+          <t>beddelay furihiisa</t>
         </is>
       </c>
       <c r="H182" s="14" t="inlineStr"/>
@@ -12361,7 +12361,7 @@
     <row r="183" ht="44" customHeight="1">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t>n_h_ago</t>
+          <t>nothing_yet</t>
         </is>
       </c>
       <c r="B183" s="11" t="inlineStr">
@@ -12371,27 +12371,27 @@
       </c>
       <c r="C183" s="11" t="inlineStr">
         <is>
-          <t>{n} h ago</t>
+          <t>Nothing yet.</t>
         </is>
       </c>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ሰዓት በፊት</t>
+          <t>እስካሁን ምንም የለም።</t>
         </is>
       </c>
       <c r="E183" s="13" t="inlineStr">
         <is>
-          <t>sa'aatii {n} dura</t>
+          <t>Ammaaf homaa hin jiru.</t>
         </is>
       </c>
       <c r="F183" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ሰዓት</t>
+          <t>ክሳብ ሕጂ ዋላ ሓደ የለን።</t>
         </is>
       </c>
       <c r="G183" s="13" t="inlineStr">
         <is>
-          <t>{n} saac ka hor</t>
+          <t>Weli waxba ma jiraan.</t>
         </is>
       </c>
       <c r="H183" s="14" t="inlineStr"/>
@@ -12399,7 +12399,7 @@
     <row r="184" ht="44" customHeight="1">
       <c r="A184" s="11" t="inlineStr">
         <is>
-          <t>n_d_ago</t>
+          <t>unavailable</t>
         </is>
       </c>
       <c r="B184" s="11" t="inlineStr">
@@ -12409,27 +12409,27 @@
       </c>
       <c r="C184" s="11" t="inlineStr">
         <is>
-          <t>{n} d ago</t>
+          <t>Unavailable.</t>
         </is>
       </c>
       <c r="D184" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ቀን በፊት</t>
+          <t>አይገኝም።</t>
         </is>
       </c>
       <c r="E184" s="13" t="inlineStr">
         <is>
-          <t>guyyaa {n} dura</t>
+          <t>Hin argamu.</t>
         </is>
       </c>
       <c r="F184" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} መዓልቲ</t>
+          <t>ኣይርከብን።</t>
         </is>
       </c>
       <c r="G184" s="13" t="inlineStr">
         <is>
-          <t>{n} maalmood ka hor</t>
+          <t>Lama heli karo.</t>
         </is>
       </c>
       <c r="H184" s="14" t="inlineStr"/>
@@ -12437,7 +12437,7 @@
     <row r="185" ht="44" customHeight="1">
       <c r="A185" s="11" t="inlineStr">
         <is>
-          <t>channel_all_from</t>
+          <t>just_now</t>
         </is>
       </c>
       <c r="B185" s="11" t="inlineStr">
@@ -12447,27 +12447,27 @@
       </c>
       <c r="C185" s="11" t="inlineStr">
         <is>
-          <t>All {n} conversations came from {label}.</t>
+          <t>just now</t>
         </is>
       </c>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>ሁሉም {n} ውይይቶች ከ{label} መጥተዋል።</t>
+          <t>አሁን</t>
         </is>
       </c>
       <c r="E185" s="13" t="inlineStr">
         <is>
-          <t>Mariin {n} hundi {label} irraa dhufe.</t>
+          <t>amma</t>
         </is>
       </c>
       <c r="F185" s="12" t="inlineStr">
         <is>
-          <t>ኩሎም {n} ዝርርባት ካብ {label} መጺኦም።</t>
+          <t>ሕጂ</t>
         </is>
       </c>
       <c r="G185" s="13" t="inlineStr">
         <is>
-          <t>Dhammaan {n} wadahadal waxay ka yimaadeen {label}.</t>
+          <t>hadda</t>
         </is>
       </c>
       <c r="H185" s="14" t="inlineStr"/>
@@ -12475,7 +12475,7 @@
     <row r="186" ht="44" customHeight="1">
       <c r="A186" s="11" t="inlineStr">
         <is>
-          <t>channel_live</t>
+          <t>n_min_ago</t>
         </is>
       </c>
       <c r="B186" s="11" t="inlineStr">
@@ -12485,27 +12485,27 @@
       </c>
       <c r="C186" s="11" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>{n} min ago</t>
         </is>
       </c>
       <c r="D186" s="12" t="inlineStr">
         <is>
-          <t>በሥራ ላይ</t>
+          <t>ከ{n} ደቂቃ በፊት</t>
         </is>
       </c>
       <c r="E186" s="13" t="inlineStr">
         <is>
-          <t>Hojiirra</t>
+          <t>daqiiqaa {n} dura</t>
         </is>
       </c>
       <c r="F186" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ስራሕ</t>
+          <t>ቅድሚ {n} ደቒቕ</t>
         </is>
       </c>
       <c r="G186" s="13" t="inlineStr">
         <is>
-          <t>Shaqeynaya</t>
+          <t>{n} daqiiqo ka hor</t>
         </is>
       </c>
       <c r="H186" s="14" t="inlineStr"/>
@@ -12513,7 +12513,7 @@
     <row r="187" ht="44" customHeight="1">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t>channel_ready</t>
+          <t>n_h_ago</t>
         </is>
       </c>
       <c r="B187" s="11" t="inlineStr">
@@ -12523,27 +12523,27 @@
       </c>
       <c r="C187" s="11" t="inlineStr">
         <is>
-          <t>Ready to connect</t>
+          <t>{n} h ago</t>
         </is>
       </c>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>ለመገናኘት ዝግጁ</t>
+          <t>ከ{n} ሰዓት በፊት</t>
         </is>
       </c>
       <c r="E187" s="13" t="inlineStr">
         <is>
-          <t>Walqunnamuuf qophaa'aa</t>
+          <t>sa'aatii {n} dura</t>
         </is>
       </c>
       <c r="F187" s="12" t="inlineStr">
         <is>
-          <t>ንምርኻብ ድሉው</t>
+          <t>ቅድሚ {n} ሰዓት</t>
         </is>
       </c>
       <c r="G187" s="13" t="inlineStr">
         <is>
-          <t>Diyaar u ah xiriirka</t>
+          <t>{n} saac ka hor</t>
         </is>
       </c>
       <c r="H187" s="14" t="inlineStr"/>
@@ -12551,7 +12551,7 @@
     <row r="188" ht="44" customHeight="1">
       <c r="A188" s="11" t="inlineStr">
         <is>
-          <t>channel_needs_setup</t>
+          <t>n_d_ago</t>
         </is>
       </c>
       <c r="B188" s="11" t="inlineStr">
@@ -12561,27 +12561,27 @@
       </c>
       <c r="C188" s="11" t="inlineStr">
         <is>
-          <t>Needs setup</t>
+          <t>{n} d ago</t>
         </is>
       </c>
       <c r="D188" s="12" t="inlineStr">
         <is>
-          <t>ማዋቀር ይፈልጋል</t>
+          <t>ከ{n} ቀን በፊት</t>
         </is>
       </c>
       <c r="E188" s="13" t="inlineStr">
         <is>
-          <t>Qindeessuu barbaada</t>
+          <t>guyyaa {n} dura</t>
         </is>
       </c>
       <c r="F188" s="12" t="inlineStr">
         <is>
-          <t>ምድላው የድልዮ</t>
+          <t>ቅድሚ {n} መዓልቲ</t>
         </is>
       </c>
       <c r="G188" s="13" t="inlineStr">
         <is>
-          <t>Waxay u baahan tahay dejin</t>
+          <t>{n} maalmood ka hor</t>
         </is>
       </c>
       <c r="H188" s="14" t="inlineStr"/>
@@ -12589,7 +12589,7 @@
     <row r="189" ht="44" customHeight="1">
       <c r="A189" s="11" t="inlineStr">
         <is>
-          <t>share_by_channel</t>
+          <t>channel_all_from</t>
         </is>
       </c>
       <c r="B189" s="11" t="inlineStr">
@@ -12599,27 +12599,27 @@
       </c>
       <c r="C189" s="11" t="inlineStr">
         <is>
-          <t>Share of conversations by channel</t>
+          <t>All {n} conversations came from {label}.</t>
         </is>
       </c>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>በመስመር የተከፋፈሉ ውይይቶች ድርሻ</t>
+          <t>ሁሉም {n} ውይይቶች ከ{label} መጥተዋል።</t>
         </is>
       </c>
       <c r="E189" s="13" t="inlineStr">
         <is>
-          <t>Qooda marii karaa tokkoon tokkoon isaanii</t>
+          <t>Mariin {n} hundi {label} irraa dhufe.</t>
         </is>
       </c>
       <c r="F189" s="12" t="inlineStr">
         <is>
-          <t>ብመስመር ዝተኸፋፈለ ግደ ዝርርባት</t>
+          <t>ኩሎም {n} ዝርርባት ካብ {label} መጺኦም።</t>
         </is>
       </c>
       <c r="G189" s="13" t="inlineStr">
         <is>
-          <t>Qaybta wadahadallada kanaalka</t>
+          <t>Dhammaan {n} wadahadal waxay ka yimaadeen {label}.</t>
         </is>
       </c>
       <c r="H189" s="14" t="inlineStr"/>
@@ -12627,7 +12627,7 @@
     <row r="190" ht="44" customHeight="1">
       <c r="A190" s="11" t="inlineStr">
         <is>
-          <t>up_to_date</t>
+          <t>channel_live</t>
         </is>
       </c>
       <c r="B190" s="11" t="inlineStr">
@@ -12637,27 +12637,27 @@
       </c>
       <c r="C190" s="11" t="inlineStr">
         <is>
-          <t>Up to date</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="D190" s="12" t="inlineStr">
         <is>
-          <t>የተዘመነ</t>
+          <t>በሥራ ላይ</t>
         </is>
       </c>
       <c r="E190" s="13" t="inlineStr">
         <is>
-          <t>Haaraa</t>
+          <t>Hojiirra</t>
         </is>
       </c>
       <c r="F190" s="12" t="inlineStr">
         <is>
-          <t>ዝተሓደሰ</t>
+          <t>ኣብ ስራሕ</t>
         </is>
       </c>
       <c r="G190" s="13" t="inlineStr">
         <is>
-          <t>La cusbooneysiiyay</t>
+          <t>Shaqeynaya</t>
         </is>
       </c>
       <c r="H190" s="14" t="inlineStr"/>
@@ -12665,7 +12665,7 @@
     <row r="191" ht="44" customHeight="1">
       <c r="A191" s="11" t="inlineStr">
         <is>
-          <t>updated_m_ago</t>
+          <t>channel_ready</t>
         </is>
       </c>
       <c r="B191" s="11" t="inlineStr">
@@ -12675,27 +12675,27 @@
       </c>
       <c r="C191" s="11" t="inlineStr">
         <is>
-          <t>Updated {n}m ago</t>
+          <t>Ready to connect</t>
         </is>
       </c>
       <c r="D191" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ደቂቃ በፊት ተዘምኗል</t>
+          <t>ለመገናኘት ዝግጁ</t>
         </is>
       </c>
       <c r="E191" s="13" t="inlineStr">
         <is>
-          <t>Daqiiqaa {n} dura haaromfame</t>
+          <t>Walqunnamuuf qophaa'aa</t>
         </is>
       </c>
       <c r="F191" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ደቒቕ ተሓዲሱ</t>
+          <t>ንምርኻብ ድሉው</t>
         </is>
       </c>
       <c r="G191" s="13" t="inlineStr">
         <is>
-          <t>La cusbooneysiiyay {n}daq ka hor</t>
+          <t>Diyaar u ah xiriirka</t>
         </is>
       </c>
       <c r="H191" s="14" t="inlineStr"/>
@@ -12703,7 +12703,7 @@
     <row r="192" ht="44" customHeight="1">
       <c r="A192" s="11" t="inlineStr">
         <is>
-          <t>updated_h_ago</t>
+          <t>channel_needs_setup</t>
         </is>
       </c>
       <c r="B192" s="11" t="inlineStr">
@@ -12713,27 +12713,27 @@
       </c>
       <c r="C192" s="11" t="inlineStr">
         <is>
-          <t>Updated {n}h ago</t>
+          <t>Needs setup</t>
         </is>
       </c>
       <c r="D192" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ሰዓት በፊት ተዘምኗል</t>
+          <t>ማዋቀር ይፈልጋል</t>
         </is>
       </c>
       <c r="E192" s="13" t="inlineStr">
         <is>
-          <t>Sa'aatii {n} dura haaromfame</t>
+          <t>Qindeessuu barbaada</t>
         </is>
       </c>
       <c r="F192" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ሰዓት ተሓዲሱ</t>
+          <t>ምድላው የድልዮ</t>
         </is>
       </c>
       <c r="G192" s="13" t="inlineStr">
         <is>
-          <t>La cusbooneysiiyay {n}saac ka hor</t>
+          <t>Waxay u baahan tahay dejin</t>
         </is>
       </c>
       <c r="H192" s="14" t="inlineStr"/>
@@ -12741,7 +12741,7 @@
     <row r="193" ht="44" customHeight="1">
       <c r="A193" s="11" t="inlineStr">
         <is>
-          <t>queue</t>
+          <t>share_by_channel</t>
         </is>
       </c>
       <c r="B193" s="11" t="inlineStr">
@@ -12751,27 +12751,27 @@
       </c>
       <c r="C193" s="11" t="inlineStr">
         <is>
-          <t>Queue</t>
+          <t>Share of conversations by channel</t>
         </is>
       </c>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>ወረፋ</t>
+          <t>በመስመር የተከፋፈሉ ውይይቶች ድርሻ</t>
         </is>
       </c>
       <c r="E193" s="13" t="inlineStr">
         <is>
-          <t>Sararaa</t>
+          <t>Qooda marii karaa tokkoon tokkoon isaanii</t>
         </is>
       </c>
       <c r="F193" s="12" t="inlineStr">
         <is>
-          <t>ሪጋ</t>
+          <t>ብመስመር ዝተኸፋፈለ ግደ ዝርርባት</t>
         </is>
       </c>
       <c r="G193" s="13" t="inlineStr">
         <is>
-          <t>Safka</t>
+          <t>Qaybta wadahadallada kanaalka</t>
         </is>
       </c>
       <c r="H193" s="14" t="inlineStr"/>
@@ -12779,7 +12779,7 @@
     <row r="194" ht="44" customHeight="1">
       <c r="A194" s="11" t="inlineStr">
         <is>
-          <t>collapse</t>
+          <t>up_to_date</t>
         </is>
       </c>
       <c r="B194" s="11" t="inlineStr">
@@ -12789,27 +12789,27 @@
       </c>
       <c r="C194" s="11" t="inlineStr">
         <is>
-          <t>Collapse</t>
+          <t>Up to date</t>
         </is>
       </c>
       <c r="D194" s="12" t="inlineStr">
         <is>
-          <t>አጥብብ</t>
+          <t>የተዘመነ</t>
         </is>
       </c>
       <c r="E194" s="13" t="inlineStr">
         <is>
-          <t>Xiqqeessi</t>
+          <t>Haaraa</t>
         </is>
       </c>
       <c r="F194" s="12" t="inlineStr">
         <is>
-          <t>ኣጽብብ</t>
+          <t>ዝተሓደሰ</t>
         </is>
       </c>
       <c r="G194" s="13" t="inlineStr">
         <is>
-          <t>Yaree</t>
+          <t>La cusbooneysiiyay</t>
         </is>
       </c>
       <c r="H194" s="14" t="inlineStr"/>
@@ -12817,7 +12817,7 @@
     <row r="195" ht="44" customHeight="1">
       <c r="A195" s="11" t="inlineStr">
         <is>
-          <t>expand</t>
+          <t>updated_m_ago</t>
         </is>
       </c>
       <c r="B195" s="11" t="inlineStr">
@@ -12827,27 +12827,27 @@
       </c>
       <c r="C195" s="11" t="inlineStr">
         <is>
-          <t>Expand</t>
+          <t>Updated {n}m ago</t>
         </is>
       </c>
       <c r="D195" s="12" t="inlineStr">
         <is>
-          <t>አስፋ</t>
+          <t>ከ{n} ደቂቃ በፊት ተዘምኗል</t>
         </is>
       </c>
       <c r="E195" s="13" t="inlineStr">
         <is>
-          <t>Balleessi</t>
+          <t>Daqiiqaa {n} dura haaromfame</t>
         </is>
       </c>
       <c r="F195" s="12" t="inlineStr">
         <is>
-          <t>ኣስፍሕ</t>
+          <t>ቅድሚ {n} ደቒቕ ተሓዲሱ</t>
         </is>
       </c>
       <c r="G195" s="13" t="inlineStr">
         <is>
-          <t>Balaadhi</t>
+          <t>La cusbooneysiiyay {n}daq ka hor</t>
         </is>
       </c>
       <c r="H195" s="14" t="inlineStr"/>
@@ -12855,7 +12855,7 @@
     <row r="196" ht="44" customHeight="1">
       <c r="A196" s="11" t="inlineStr">
         <is>
-          <t>collapse_or_expand</t>
+          <t>updated_h_ago</t>
         </is>
       </c>
       <c r="B196" s="11" t="inlineStr">
@@ -12865,27 +12865,27 @@
       </c>
       <c r="C196" s="11" t="inlineStr">
         <is>
-          <t>Collapse or expand the sidebar</t>
+          <t>Updated {n}h ago</t>
         </is>
       </c>
       <c r="D196" s="12" t="inlineStr">
         <is>
-          <t>የጎን አሞሌውን አጥብብ ወይም አስፋ</t>
+          <t>ከ{n} ሰዓት በፊት ተዘምኗል</t>
         </is>
       </c>
       <c r="E196" s="13" t="inlineStr">
         <is>
-          <t>Cinaacha xiqqeessi ykn balleessi</t>
+          <t>Sa'aatii {n} dura haaromfame</t>
         </is>
       </c>
       <c r="F196" s="12" t="inlineStr">
         <is>
-          <t>ናይ ጎኒ መስመር ኣጽብብ ወይ ኣስፍሕ</t>
+          <t>ቅድሚ {n} ሰዓት ተሓዲሱ</t>
         </is>
       </c>
       <c r="G196" s="13" t="inlineStr">
         <is>
-          <t>Yaree ama balaadhi dhinaca</t>
+          <t>La cusbooneysiiyay {n}saac ka hor</t>
         </is>
       </c>
       <c r="H196" s="14" t="inlineStr"/>
@@ -12893,7 +12893,7 @@
     <row r="197" ht="44" customHeight="1">
       <c r="A197" s="11" t="inlineStr">
         <is>
-          <t>show_hide_channels</t>
+          <t>queue</t>
         </is>
       </c>
       <c r="B197" s="11" t="inlineStr">
@@ -12903,27 +12903,27 @@
       </c>
       <c r="C197" s="11" t="inlineStr">
         <is>
-          <t>Show or hide the channel list</t>
+          <t>Queue</t>
         </is>
       </c>
       <c r="D197" s="12" t="inlineStr">
         <is>
-          <t>የመስመሮችን ዝርዝር አሳይ ወይም ደብቅ</t>
+          <t>ወረፋ</t>
         </is>
       </c>
       <c r="E197" s="13" t="inlineStr">
         <is>
-          <t>Tarreeffama karaalee agarsiisi ykn dhoksi</t>
+          <t>Sararaa</t>
         </is>
       </c>
       <c r="F197" s="12" t="inlineStr">
         <is>
-          <t>ዝርዝር መስመራት ኣርኢ ወይ ሕባእ</t>
+          <t>ሪጋ</t>
         </is>
       </c>
       <c r="G197" s="13" t="inlineStr">
         <is>
-          <t>Muuji ama qari liiska kanaalada</t>
+          <t>Safka</t>
         </is>
       </c>
       <c r="H197" s="14" t="inlineStr"/>
@@ -12931,7 +12931,7 @@
     <row r="198" ht="44" customHeight="1">
       <c r="A198" s="11" t="inlineStr">
         <is>
-          <t>today</t>
+          <t>collapse</t>
         </is>
       </c>
       <c r="B198" s="11" t="inlineStr">
@@ -12941,27 +12941,27 @@
       </c>
       <c r="C198" s="11" t="inlineStr">
         <is>
-          <t>Today</t>
+          <t>Collapse</t>
         </is>
       </c>
       <c r="D198" s="12" t="inlineStr">
         <is>
-          <t>ዛሬ</t>
+          <t>አጥብብ</t>
         </is>
       </c>
       <c r="E198" s="13" t="inlineStr">
         <is>
-          <t>Har'a</t>
+          <t>Xiqqeessi</t>
         </is>
       </c>
       <c r="F198" s="12" t="inlineStr">
         <is>
-          <t>ሎሚ</t>
+          <t>ኣጽብብ</t>
         </is>
       </c>
       <c r="G198" s="13" t="inlineStr">
         <is>
-          <t>Maanta</t>
+          <t>Yaree</t>
         </is>
       </c>
       <c r="H198" s="14" t="inlineStr"/>
@@ -12969,7 +12969,7 @@
     <row r="199" ht="44" customHeight="1">
       <c r="A199" s="11" t="inlineStr">
         <is>
-          <t>yesterday</t>
+          <t>expand</t>
         </is>
       </c>
       <c r="B199" s="11" t="inlineStr">
@@ -12979,27 +12979,27 @@
       </c>
       <c r="C199" s="11" t="inlineStr">
         <is>
-          <t>Yesterday</t>
+          <t>Expand</t>
         </is>
       </c>
       <c r="D199" s="12" t="inlineStr">
         <is>
-          <t>ትናንት</t>
+          <t>አስፋ</t>
         </is>
       </c>
       <c r="E199" s="13" t="inlineStr">
         <is>
-          <t>Kaleessa</t>
+          <t>Balleessi</t>
         </is>
       </c>
       <c r="F199" s="12" t="inlineStr">
         <is>
-          <t>ትማሊ</t>
+          <t>ኣስፍሕ</t>
         </is>
       </c>
       <c r="G199" s="13" t="inlineStr">
         <is>
-          <t>Shalay</t>
+          <t>Balaadhi</t>
         </is>
       </c>
       <c r="H199" s="14" t="inlineStr"/>
@@ -13007,7 +13007,7 @@
     <row r="200" ht="44" customHeight="1">
       <c r="A200" s="11" t="inlineStr">
         <is>
-          <t>call_started</t>
+          <t>collapse_or_expand</t>
         </is>
       </c>
       <c r="B200" s="11" t="inlineStr">
@@ -13017,27 +13017,27 @@
       </c>
       <c r="C200" s="11" t="inlineStr">
         <is>
-          <t>The customer asked for a person here</t>
+          <t>Collapse or expand the sidebar</t>
         </is>
       </c>
       <c r="D200" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛው እዚህ ላይ ሰው ጠየቀ</t>
+          <t>የጎን አሞሌውን አጥብብ ወይም አስፋ</t>
         </is>
       </c>
       <c r="E200" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan asitti nama gaafate</t>
+          <t>Cinaacha xiqqeessi ykn balleessi</t>
         </is>
       </c>
       <c r="F200" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዓሚል ኣብዚ ሰብ ሓቲቱ</t>
+          <t>ናይ ጎኒ መስመር ኣጽብብ ወይ ኣስፍሕ</t>
         </is>
       </c>
       <c r="G200" s="13" t="inlineStr">
         <is>
-          <t>Macmiilku halkan ayuu qof weydiistay</t>
+          <t>Yaree ama balaadhi dhinaca</t>
         </is>
       </c>
       <c r="H200" s="14" t="inlineStr"/>
@@ -13045,7 +13045,7 @@
     <row r="201" ht="44" customHeight="1">
       <c r="A201" s="11" t="inlineStr">
         <is>
-          <t>no_messages</t>
+          <t>show_hide_channels</t>
         </is>
       </c>
       <c r="B201" s="11" t="inlineStr">
@@ -13055,27 +13055,27 @@
       </c>
       <c r="C201" s="11" t="inlineStr">
         <is>
-          <t>No messages in this conversation.</t>
+          <t>Show or hide the channel list</t>
         </is>
       </c>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>በዚህ ውይይት ውስጥ መልእክት የለም።</t>
+          <t>የመስመሮችን ዝርዝር አሳይ ወይም ደብቅ</t>
         </is>
       </c>
       <c r="E201" s="13" t="inlineStr">
         <is>
-          <t>Marii kana keessa ergaan hin jiru.</t>
+          <t>Tarreeffama karaalee agarsiisi ykn dhoksi</t>
         </is>
       </c>
       <c r="F201" s="12" t="inlineStr">
         <is>
-          <t>ኣብዚ ዝርርብ መልእኽቲ የለን።</t>
+          <t>ዝርዝር መስመራት ኣርኢ ወይ ሕባእ</t>
         </is>
       </c>
       <c r="G201" s="13" t="inlineStr">
         <is>
-          <t>Wadahadalkan fariin kuma jirto.</t>
+          <t>Muuji ama qari liiska kanaalada</t>
         </is>
       </c>
       <c r="H201" s="14" t="inlineStr"/>
@@ -13083,7 +13083,7 @@
     <row r="202" ht="44" customHeight="1">
       <c r="A202" s="11" t="inlineStr">
         <is>
-          <t>donut_all_in_one</t>
+          <t>today</t>
         </is>
       </c>
       <c r="B202" s="11" t="inlineStr">
@@ -13093,27 +13093,27 @@
       </c>
       <c r="C202" s="11" t="inlineStr">
         <is>
-          <t>The single {unit} was in {label}.</t>
+          <t>Today</t>
         </is>
       </c>
       <c r="D202" s="12" t="inlineStr">
         <is>
-          <t>ብቸኛው {unit} በ{label} ነበር።</t>
+          <t>ዛሬ</t>
         </is>
       </c>
       <c r="E202" s="13" t="inlineStr">
         <is>
-          <t>{unit} tokkichi {label} keessa ture.</t>
+          <t>Har'a</t>
         </is>
       </c>
       <c r="F202" s="12" t="inlineStr">
         <is>
-          <t>እቲ ሓደ {unit} ብ{label} ነይሩ።</t>
+          <t>ሎሚ</t>
         </is>
       </c>
       <c r="G202" s="13" t="inlineStr">
         <is>
-          <t>{unit} kaliya wuxuu ku jiray {label}.</t>
+          <t>Maanta</t>
         </is>
       </c>
       <c r="H202" s="14" t="inlineStr"/>
@@ -13121,7 +13121,7 @@
     <row r="203" ht="44" customHeight="1">
       <c r="A203" s="11" t="inlineStr">
         <is>
-          <t>channel_all_from_one</t>
+          <t>yesterday</t>
         </is>
       </c>
       <c r="B203" s="11" t="inlineStr">
@@ -13131,27 +13131,27 @@
       </c>
       <c r="C203" s="11" t="inlineStr">
         <is>
-          <t>The single conversation came from {label}.</t>
+          <t>Yesterday</t>
         </is>
       </c>
       <c r="D203" s="12" t="inlineStr">
         <is>
-          <t>ብቸኛው ውይይት ከ{label} መጥቷል።</t>
+          <t>ትናንት</t>
         </is>
       </c>
       <c r="E203" s="13" t="inlineStr">
         <is>
-          <t>Mariin tokkichi {label} irraa dhufe.</t>
+          <t>Kaleessa</t>
         </is>
       </c>
       <c r="F203" s="12" t="inlineStr">
         <is>
-          <t>እቲ ሓደ ዝርርብ ካብ {label} መጺኡ።</t>
+          <t>ትማሊ</t>
         </is>
       </c>
       <c r="G203" s="13" t="inlineStr">
         <is>
-          <t>Wadahadalka kaliya wuxuu ka yimid {label}.</t>
+          <t>Shalay</t>
         </is>
       </c>
       <c r="H203" s="14" t="inlineStr"/>
@@ -13159,7 +13159,7 @@
     <row r="204" ht="44" customHeight="1">
       <c r="A204" s="11" t="inlineStr">
         <is>
-          <t>unit_conversation</t>
+          <t>call_started</t>
         </is>
       </c>
       <c r="B204" s="11" t="inlineStr">
@@ -13169,27 +13169,27 @@
       </c>
       <c r="C204" s="11" t="inlineStr">
         <is>
-          <t>conversation</t>
+          <t>The customer asked for a person here</t>
         </is>
       </c>
       <c r="D204" s="12" t="inlineStr">
         <is>
-          <t>ውይይት</t>
+          <t>ደንበኛው እዚህ ላይ ሰው ጠየቀ</t>
         </is>
       </c>
       <c r="E204" s="13" t="inlineStr">
         <is>
-          <t>marii</t>
+          <t>Maamilaan asitti nama gaafate</t>
         </is>
       </c>
       <c r="F204" s="12" t="inlineStr">
         <is>
-          <t>ዝርርብ</t>
+          <t>እቲ ዓሚል ኣብዚ ሰብ ሓቲቱ</t>
         </is>
       </c>
       <c r="G204" s="13" t="inlineStr">
         <is>
-          <t>wadahadal</t>
+          <t>Macmiilku halkan ayuu qof weydiistay</t>
         </is>
       </c>
       <c r="H204" s="14" t="inlineStr"/>
@@ -13197,7 +13197,7 @@
     <row r="205" ht="44" customHeight="1">
       <c r="A205" s="11" t="inlineStr">
         <is>
-          <t>live_sessions</t>
+          <t>no_messages</t>
         </is>
       </c>
       <c r="B205" s="11" t="inlineStr">
@@ -13207,27 +13207,27 @@
       </c>
       <c r="C205" s="11" t="inlineStr">
         <is>
-          <t>Live sessions</t>
+          <t>No messages in this conversation.</t>
         </is>
       </c>
       <c r="D205" s="12" t="inlineStr">
         <is>
-          <t>የቀጥታ ክፍለ-ጊዜዎች</t>
+          <t>በዚህ ውይይት ውስጥ መልእክት የለም።</t>
         </is>
       </c>
       <c r="E205" s="13" t="inlineStr">
         <is>
-          <t>Marii kallattii</t>
+          <t>Marii kana keessa ergaan hin jiru.</t>
         </is>
       </c>
       <c r="F205" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታ ክፍለ-ግዜታት</t>
+          <t>ኣብዚ ዝርርብ መልእኽቲ የለን።</t>
         </is>
       </c>
       <c r="G205" s="13" t="inlineStr">
         <is>
-          <t>Kalfadhiyada tooska ah</t>
+          <t>Wadahadalkan fariin kuma jirto.</t>
         </is>
       </c>
       <c r="H205" s="14" t="inlineStr"/>
@@ -13235,7 +13235,7 @@
     <row r="206" ht="44" customHeight="1">
       <c r="A206" s="11" t="inlineStr">
         <is>
-          <t>switched_off_for_bank</t>
+          <t>donut_all_in_one</t>
         </is>
       </c>
       <c r="B206" s="11" t="inlineStr">
@@ -13245,27 +13245,27 @@
       </c>
       <c r="C206" s="11" t="inlineStr">
         <is>
-          <t>Switched off for this bank</t>
+          <t>The single {unit} was in {label}.</t>
         </is>
       </c>
       <c r="D206" s="12" t="inlineStr">
         <is>
-          <t>ለዚህ ባንክ ጠፍቷል</t>
+          <t>ብቸኛው {unit} በ{label} ነበር።</t>
         </is>
       </c>
       <c r="E206" s="13" t="inlineStr">
         <is>
-          <t>Baankii kanaaf dhaamsameera</t>
+          <t>{unit} tokkichi {label} keessa ture.</t>
         </is>
       </c>
       <c r="F206" s="12" t="inlineStr">
         <is>
-          <t>ነዚ ባንኪ ጠፊኡ</t>
+          <t>እቲ ሓደ {unit} ብ{label} ነይሩ።</t>
         </is>
       </c>
       <c r="G206" s="13" t="inlineStr">
         <is>
-          <t>Bangigan waa la damiyay</t>
+          <t>{unit} kaliya wuxuu ku jiray {label}.</t>
         </is>
       </c>
       <c r="H206" s="14" t="inlineStr"/>
@@ -13273,7 +13273,7 @@
     <row r="207" ht="44" customHeight="1">
       <c r="A207" s="11" t="inlineStr">
         <is>
-          <t>switched_on_nobody_on_duty</t>
+          <t>channel_all_from_one</t>
         </is>
       </c>
       <c r="B207" s="11" t="inlineStr">
@@ -13283,27 +13283,27 @@
       </c>
       <c r="C207" s="11" t="inlineStr">
         <is>
-          <t>Switched on — but nobody is on duty</t>
+          <t>The single conversation came from {label}.</t>
         </is>
       </c>
       <c r="D207" s="12" t="inlineStr">
         <is>
-          <t>በርቷል — ግን ማንም በሥራ ላይ የለም</t>
+          <t>ብቸኛው ውይይት ከ{label} መጥቷል።</t>
         </is>
       </c>
       <c r="E207" s="13" t="inlineStr">
         <is>
-          <t>Banameera — garuu namni hojii irra hin jiru</t>
+          <t>Mariin tokkichi {label} irraa dhufe.</t>
         </is>
       </c>
       <c r="F207" s="12" t="inlineStr">
         <is>
-          <t>በሪሁ — ግና ዋላ ሓደ ኣብ ስራሕ የለን</t>
+          <t>እቲ ሓደ ዝርርብ ካብ {label} መጺኡ።</t>
         </is>
       </c>
       <c r="G207" s="13" t="inlineStr">
         <is>
-          <t>Waa la shiday — laakiin qofna shaqada ma joogo</t>
+          <t>Wadahadalka kaliya wuxuu ka yimid {label}.</t>
         </is>
       </c>
       <c r="H207" s="14" t="inlineStr"/>
@@ -13311,7 +13311,7 @@
     <row r="208" ht="44" customHeight="1">
       <c r="A208" s="11" t="inlineStr">
         <is>
-          <t>no_teller_button</t>
+          <t>unit_conversation</t>
         </is>
       </c>
       <c r="B208" s="11" t="inlineStr">
@@ -13321,27 +13321,27 @@
       </c>
       <c r="C208" s="11" t="inlineStr">
         <is>
-          <t>No “Speak to a teller” button appears in your widget.</t>
+          <t>conversation</t>
         </is>
       </c>
       <c r="D208" s="12" t="inlineStr">
         <is>
-          <t>በመግብርዎ ውስጥ “ከገንዘብ ተቀባይ ጋር ይነጋገሩ” የሚል አዝራር አይታይም።</t>
+          <t>ውይይት</t>
         </is>
       </c>
       <c r="E208" s="13" t="inlineStr">
         <is>
-          <t>Widjetii keessan keessatti qabduun “Namaa waliin haasa'aa” hin mul'atu.</t>
+          <t>marii</t>
         </is>
       </c>
       <c r="F208" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መግበሪኹም “ምስ ተቐባሊ ገንዘብ ተዛረቡ” ዝብል መጠወቒ ኣይረአን።</t>
+          <t>ዝርርብ</t>
         </is>
       </c>
       <c r="G208" s="13" t="inlineStr">
         <is>
-          <t>Badhanka “La hadal shaqaale” kama muuqan widget-kaaga.</t>
+          <t>wadahadal</t>
         </is>
       </c>
       <c r="H208" s="14" t="inlineStr"/>
@@ -13349,7 +13349,7 @@
     <row r="209" ht="44" customHeight="1">
       <c r="A209" s="11" t="inlineStr">
         <is>
-          <t>on_duty_explainer</t>
+          <t>live_sessions</t>
         </is>
       </c>
       <c r="B209" s="11" t="inlineStr">
@@ -13359,27 +13359,27 @@
       </c>
       <c r="C209" s="11" t="inlineStr">
         <is>
-          <t>You are on duty, so waiting customers can be routed to you. Go off duty from the sidebar when you step away — you stay on the air anywhere in the console until you do.</t>
+          <t>Live sessions</t>
         </is>
       </c>
       <c r="D209" s="12" t="inlineStr">
         <is>
-          <t>በሥራ ላይ ነዎት፤ ስለዚህ የሚጠብቁ ደንበኞች ወደ እርስዎ ሊመሩ ይችላሉ። ሲርቁ ከጎን አሞሌው ከሥራ ውጡ — እስከዚያ ድረስ በየትኛውም ገጽ ላይ በሥራ ላይ ይቆያሉ።</t>
+          <t>የቀጥታ ክፍለ-ጊዜዎች</t>
         </is>
       </c>
       <c r="E209" s="13" t="inlineStr">
         <is>
-          <t>Hojii irra jirtu, kanaafuu maamiltoonni eegaa jiran gara keessan qajeelfamuu danda'u. Yeroo achii deemtan cinaacha irraa hojii keessaa ba'aa — hanga sanatti fuula kamiyyuu irratti hojii irra turtu.</t>
+          <t>Marii kallattii</t>
         </is>
       </c>
       <c r="F209" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ስራሕ ኢኹም፣ ስለዚ ዝጽበዩ ዓማዊል ናባኹም ክምርሑ ይኽእሉ። ክትርሕቁ ከለኹም ካብ ናይ ጎኒ መስመር ካብ ስራሕ ውጹ — ክሳብ ሽዑ ኣብ ዝኾነ ገጽ ኣብ ስራሕ ትጸንሑ።</t>
+          <t>ቀጥታ ክፍለ-ግዜታት</t>
         </is>
       </c>
       <c r="G209" s="13" t="inlineStr">
         <is>
-          <t>Shaqada ayaad joogtaa, sidaas darteed macaamiisha sugaya waa lagu soo dhiibi karaa. Marka aad tagto shaqada ka bax dhinaca — ilaa markaas bog kasta ayaad ku sii shaqeynaysaa.</t>
+          <t>Kalfadhiyada tooska ah</t>
         </is>
       </c>
       <c r="H209" s="14" t="inlineStr"/>
@@ -13387,7 +13387,7 @@
     <row r="210" ht="44" customHeight="1">
       <c r="A210" s="11" t="inlineStr">
         <is>
-          <t>off_duty_explainer</t>
+          <t>switched_off_for_bank</t>
         </is>
       </c>
       <c r="B210" s="11" t="inlineStr">
@@ -13397,27 +13397,27 @@
       </c>
       <c r="C210" s="11" t="inlineStr">
         <is>
-          <t>Switch On duty in the sidebar to start taking calls. It follows you across every page, so you no longer have to keep this one open.</t>
+          <t>Switched off for this bank</t>
         </is>
       </c>
       <c r="D210" s="12" t="inlineStr">
         <is>
-          <t>ጥሪዎችን መቀበል ለመጀመር ከጎን አሞሌው “በሥራ ላይ” ያብሩ። በሁሉም ገጽ ላይ ይከተልዎታል፤ ስለዚህ ይህን ገጽ ክፍት ማድረግ አያስፈልግም።</t>
+          <t>ለዚህ ባንክ ጠፍቷል</t>
         </is>
       </c>
       <c r="E210" s="13" t="inlineStr">
         <is>
-          <t>Bilbila fudhachuu jalqabuuf cinaacha irraa “Hojii irra” banaa. Fuula hunda irratti isin hordofa, kanaafuu fuula kana banaa gochuun hin barbaachisu.</t>
+          <t>Baankii kanaaf dhaamsameera</t>
         </is>
       </c>
       <c r="F210" s="12" t="inlineStr">
         <is>
-          <t>ጻውዒታት ክትቅበሉ ንምጅማር ካብ ናይ ጎኒ መስመር “ኣብ ስራሕ” ኣብርሁ። ኣብ ኩሉ ገጽ ይስዕበኩም፣ ስለዚ ነዚ ገጽ ክፉት ምግባር ኣየድልን።</t>
+          <t>ነዚ ባንኪ ጠፊኡ</t>
         </is>
       </c>
       <c r="G210" s="13" t="inlineStr">
         <is>
-          <t>Si aad u bilowdo qaadista wicitaannada, dhinaca ka shid “Shaqada”. Bog kasta ayuu kula socdaa, sidaas darteed uma baahnid inaad tan furan ka tagto.</t>
+          <t>Bangigan waa la damiyay</t>
         </is>
       </c>
       <c r="H210" s="14" t="inlineStr"/>
@@ -13425,7 +13425,7 @@
     <row r="211" ht="44" customHeight="1">
       <c r="A211" s="11" t="inlineStr">
         <is>
-          <t>colleague_must_be_on_duty</t>
+          <t>switched_on_nobody_on_duty</t>
         </is>
       </c>
       <c r="B211" s="11" t="inlineStr">
@@ -13435,27 +13435,27 @@
       </c>
       <c r="C211" s="11" t="inlineStr">
         <is>
-          <t>A colleague with permission to take calls has to be on duty before customers are offered one.</t>
+          <t>Switched on — but nobody is on duty</t>
         </is>
       </c>
       <c r="D211" s="12" t="inlineStr">
         <is>
-          <t>ጥሪ የመቀበል ፈቃድ ያለው ባልደረባ በሥራ ላይ መሆን አለበት፤ ከዚያ በፊት ለደንበኞች አይቀርብም።</t>
+          <t>በርቷል — ግን ማንም በሥራ ላይ የለም</t>
         </is>
       </c>
       <c r="E211" s="13" t="inlineStr">
         <is>
-          <t>Hojjetaan hayyama bilbila fudhachuu qabu hojii irra jiraachuu qaba, sana dura maamiltootaaf hin dhiyaatu.</t>
+          <t>Banameera — garuu namni hojii irra hin jiru</t>
         </is>
       </c>
       <c r="F211" s="12" t="inlineStr">
         <is>
-          <t>ጻውዒት ናይ ምቕባል ፍቓድ ዘለዎ መሳርሕቲ ኣብ ስራሕ ክህሉ ኣለዎ፣ ቅድሚኡ ንዓማዊል ኣይቀርብን።</t>
+          <t>በሪሁ — ግና ዋላ ሓደ ኣብ ስራሕ የለን</t>
         </is>
       </c>
       <c r="G211" s="13" t="inlineStr">
         <is>
-          <t>Shaqaale haysta ogolaanshaha qaadista wicitaannada waa inuu shaqada joogaa ka hor inta aan macaamiisha la siin.</t>
+          <t>Waa la shiday — laakiin qofna shaqada ma joogo</t>
         </is>
       </c>
       <c r="H211" s="14" t="inlineStr"/>
@@ -13463,7 +13463,7 @@
     <row r="212" ht="44" customHeight="1">
       <c r="A212" s="11" t="inlineStr">
         <is>
-          <t>i_can_converse_in</t>
+          <t>no_teller_button</t>
         </is>
       </c>
       <c r="B212" s="11" t="inlineStr">
@@ -13473,27 +13473,27 @@
       </c>
       <c r="C212" s="11" t="inlineStr">
         <is>
-          <t>I can hold a conversation in:</t>
+          <t>No “Speak to a teller” button appears in your widget.</t>
         </is>
       </c>
       <c r="D212" s="12" t="inlineStr">
         <is>
-          <t>በእነዚህ ቋንቋዎች መነጋገር እችላለሁ፦</t>
+          <t>በመግብርዎ ውስጥ “ከገንዘብ ተቀባይ ጋር ይነጋገሩ” የሚል አዝራር አይታይም።</t>
         </is>
       </c>
       <c r="E212" s="13" t="inlineStr">
         <is>
-          <t>Afaanota kanneeniin haasa'uu nan danda'a:</t>
+          <t>Widjetii keessan keessatti qabduun “Namaa waliin haasa'aa” hin mul'atu.</t>
         </is>
       </c>
       <c r="F212" s="12" t="inlineStr">
         <is>
-          <t>በዞም ቋንቋታት ክዛረብ እኽእል፦</t>
+          <t>ኣብ መግበሪኹም “ምስ ተቐባሊ ገንዘብ ተዛረቡ” ዝብል መጠወቒ ኣይረአን።</t>
         </is>
       </c>
       <c r="G212" s="13" t="inlineStr">
         <is>
-          <t>Waxaan ku hadli karaa:</t>
+          <t>Badhanka “La hadal shaqaale” kama muuqan widget-kaaga.</t>
         </is>
       </c>
       <c r="H212" s="14" t="inlineStr"/>
@@ -13501,7 +13501,7 @@
     <row r="213" ht="44" customHeight="1">
       <c r="A213" s="11" t="inlineStr">
         <is>
-          <t>languages_picked_note</t>
+          <t>on_duty_explainer</t>
         </is>
       </c>
       <c r="B213" s="11" t="inlineStr">
@@ -13511,27 +13511,27 @@
       </c>
       <c r="C213" s="11" t="inlineStr">
         <is>
-          <t>Customers writing in these reach you first. Everyone else still reaches you — after a short wait, so nobody is stranded.</t>
+          <t>You are on duty, so waiting customers can be routed to you. Go off duty from the sidebar when you step away — you stay on the air anywhere in the console until you do.</t>
         </is>
       </c>
       <c r="D213" s="12" t="inlineStr">
         <is>
-          <t>በእነዚህ ቋንቋዎች የሚጽፉ ደንበኞች መጀመሪያ ወደ እርስዎ ይደርሳሉ። ሌሎችም ይደርሳሉ — ከአጭር ጥበቃ በኋላ፤ ማንም አይቀርም።</t>
+          <t>በሥራ ላይ ነዎት፤ ስለዚህ የሚጠብቁ ደንበኞች ወደ እርስዎ ሊመሩ ይችላሉ። ሲርቁ ከጎን አሞሌው ከሥራ ውጡ — እስከዚያ ድረስ በየትኛውም ገጽ ላይ በሥራ ላይ ይቆያሉ።</t>
         </is>
       </c>
       <c r="E213" s="13" t="inlineStr">
         <is>
-          <t>Maamiltoonni afaanota kanaan barreessan jalqaba isin bira ga'u. Kaan hundinuu ammas isin bira ga'u — eegumsa gabaabaa booda, namni hafu hin jiru.</t>
+          <t>Hojii irra jirtu, kanaafuu maamiltoonni eegaa jiran gara keessan qajeelfamuu danda'u. Yeroo achii deemtan cinaacha irraa hojii keessaa ba'aa — hanga sanatti fuula kamiyyuu irratti hojii irra turtu.</t>
         </is>
       </c>
       <c r="F213" s="12" t="inlineStr">
         <is>
-          <t>በዞም ቋንቋታት ዝጽሕፉ ዓማዊል ቅድም ናባኹም ይበጽሑ። እቶም ካልኦት እውን ይበጽሑ — ድሕሪ ሓጺር ጽበት፣ ዋላ ሓደ ኣይተርፍን።</t>
+          <t>ኣብ ስራሕ ኢኹም፣ ስለዚ ዝጽበዩ ዓማዊል ናባኹም ክምርሑ ይኽእሉ። ክትርሕቁ ከለኹም ካብ ናይ ጎኒ መስመር ካብ ስራሕ ውጹ — ክሳብ ሽዑ ኣብ ዝኾነ ገጽ ኣብ ስራሕ ትጸንሑ።</t>
         </is>
       </c>
       <c r="G213" s="13" t="inlineStr">
         <is>
-          <t>Macaamiisha ku qora kuwan ayaa marka hore kugu soo gaara. Qof kastana wuu ku soo gaari doonaa — sug gaaban ka dib, sidaas qofna ma harayo.</t>
+          <t>Shaqada ayaad joogtaa, sidaas darteed macaamiisha sugaya waa lagu soo dhiibi karaa. Marka aad tagto shaqada ka bax dhinaca — ilaa markaas bog kasta ayaad ku sii shaqeynaysaa.</t>
         </is>
       </c>
       <c r="H213" s="14" t="inlineStr"/>
@@ -13539,7 +13539,7 @@
     <row r="214" ht="44" customHeight="1">
       <c r="A214" s="11" t="inlineStr">
         <is>
-          <t>languages_none_note</t>
+          <t>off_duty_explainer</t>
         </is>
       </c>
       <c r="B214" s="11" t="inlineStr">
@@ -13549,27 +13549,27 @@
       </c>
       <c r="C214" s="11" t="inlineStr">
         <is>
-          <t>Nothing selected, so every waiting customer is offered to you in plain oldest-first order.</t>
+          <t>Switch On duty in the sidebar to start taking calls. It follows you across every page, so you no longer have to keep this one open.</t>
         </is>
       </c>
       <c r="D214" s="12" t="inlineStr">
         <is>
-          <t>ምንም አልተመረጠም፤ ስለዚህ እያንዳንዱ የሚጠብቅ ደንበኛ በቀላል ቀዳሚ-መጀመሪያ ቅደም ተከተል ይቀርብልዎታል።</t>
+          <t>ጥሪዎችን መቀበል ለመጀመር ከጎን አሞሌው “በሥራ ላይ” ያብሩ። በሁሉም ገጽ ላይ ይከተልዎታል፤ ስለዚህ ይህን ገጽ ክፍት ማድረግ አያስፈልግም።</t>
         </is>
       </c>
       <c r="E214" s="13" t="inlineStr">
         <is>
-          <t>Wanti filatame hin jiru, kanaafuu maamilli eegaa jiru hundi tartiiba dursaa-jalqabaatiin isinii dhiyaata.</t>
+          <t>Bilbila fudhachuu jalqabuuf cinaacha irraa “Hojii irra” banaa. Fuula hunda irratti isin hordofa, kanaafuu fuula kana banaa gochuun hin barbaachisu.</t>
         </is>
       </c>
       <c r="F214" s="12" t="inlineStr">
         <is>
-          <t>ዋላ ሓደ ኣይተመርጸን፣ ስለዚ ነፍስ ወከፍ ዝጽበ ዓሚል ብቐሊል ናይ ቀዳምነት ስርዓት ይቐርበልኩም።</t>
+          <t>ጻውዒታት ክትቅበሉ ንምጅማር ካብ ናይ ጎኒ መስመር “ኣብ ስራሕ” ኣብርሁ። ኣብ ኩሉ ገጽ ይስዕበኩም፣ ስለዚ ነዚ ገጽ ክፉት ምግባር ኣየድልን።</t>
         </is>
       </c>
       <c r="G214" s="13" t="inlineStr">
         <is>
-          <t>Waxba lama dooran, sidaas darteed macmiil kasta oo sugaya waxaa laguu soo bandhigayaa sida caadiga ah ee ugu horreeya.</t>
+          <t>Si aad u bilowdo qaadista wicitaannada, dhinaca ka shid “Shaqada”. Bog kasta ayuu kula socdaa, sidaas darteed uma baahnid inaad tan furan ka tagto.</t>
         </is>
       </c>
       <c r="H214" s="14" t="inlineStr"/>
@@ -13577,7 +13577,7 @@
     <row r="215" ht="44" customHeight="1">
       <c r="A215" s="11" t="inlineStr">
         <is>
-          <t>languages_updated</t>
+          <t>colleague_must_be_on_duty</t>
         </is>
       </c>
       <c r="B215" s="11" t="inlineStr">
@@ -13587,27 +13587,27 @@
       </c>
       <c r="C215" s="11" t="inlineStr">
         <is>
-          <t>Languages updated</t>
+          <t>A colleague with permission to take calls has to be on duty before customers are offered one.</t>
         </is>
       </c>
       <c r="D215" s="12" t="inlineStr">
         <is>
-          <t>ቋንቋዎች ተዘምነዋል</t>
+          <t>ጥሪ የመቀበል ፈቃድ ያለው ባልደረባ በሥራ ላይ መሆን አለበት፤ ከዚያ በፊት ለደንበኞች አይቀርብም።</t>
         </is>
       </c>
       <c r="E215" s="13" t="inlineStr">
         <is>
-          <t>Afaanonni haaromfaman</t>
+          <t>Hojjetaan hayyama bilbila fudhachuu qabu hojii irra jiraachuu qaba, sana dura maamiltootaaf hin dhiyaatu.</t>
         </is>
       </c>
       <c r="F215" s="12" t="inlineStr">
         <is>
-          <t>ቋንቋታት ተሓዲሶም</t>
+          <t>ጻውዒት ናይ ምቕባል ፍቓድ ዘለዎ መሳርሕቲ ኣብ ስራሕ ክህሉ ኣለዎ፣ ቅድሚኡ ንዓማዊል ኣይቀርብን።</t>
         </is>
       </c>
       <c r="G215" s="13" t="inlineStr">
         <is>
-          <t>Luqadaha waa la cusbooneysiiyay</t>
+          <t>Shaqaale haysta ogolaanshaha qaadista wicitaannada waa inuu shaqada joogaa ka hor inta aan macaamiisha la siin.</t>
         </is>
       </c>
       <c r="H215" s="14" t="inlineStr"/>
@@ -13615,7 +13615,7 @@
     <row r="216" ht="44" customHeight="1">
       <c r="A216" s="11" t="inlineStr">
         <is>
-          <t>media_video</t>
+          <t>i_can_converse_in</t>
         </is>
       </c>
       <c r="B216" s="11" t="inlineStr">
@@ -13625,27 +13625,27 @@
       </c>
       <c r="C216" s="11" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>I can hold a conversation in:</t>
         </is>
       </c>
       <c r="D216" s="12" t="inlineStr">
         <is>
-          <t>ቪዲዮ</t>
+          <t>በእነዚህ ቋንቋዎች መነጋገር እችላለሁ፦</t>
         </is>
       </c>
       <c r="E216" s="13" t="inlineStr">
         <is>
-          <t>Viidiyoo</t>
+          <t>Afaanota kanneeniin haasa'uu nan danda'a:</t>
         </is>
       </c>
       <c r="F216" s="12" t="inlineStr">
         <is>
-          <t>ቪድዮ</t>
+          <t>በዞም ቋንቋታት ክዛረብ እኽእል፦</t>
         </is>
       </c>
       <c r="G216" s="13" t="inlineStr">
         <is>
-          <t>Fiidyow</t>
+          <t>Waxaan ku hadli karaa:</t>
         </is>
       </c>
       <c r="H216" s="14" t="inlineStr"/>
@@ -13653,7 +13653,7 @@
     <row r="217" ht="44" customHeight="1">
       <c r="A217" s="11" t="inlineStr">
         <is>
-          <t>media_audio</t>
+          <t>languages_picked_note</t>
         </is>
       </c>
       <c r="B217" s="11" t="inlineStr">
@@ -13663,27 +13663,27 @@
       </c>
       <c r="C217" s="11" t="inlineStr">
         <is>
-          <t>Audio</t>
+          <t>Customers writing in these reach you first. Everyone else still reaches you — after a short wait, so nobody is stranded.</t>
         </is>
       </c>
       <c r="D217" s="12" t="inlineStr">
         <is>
-          <t>ድምፅ</t>
+          <t>በእነዚህ ቋንቋዎች የሚጽፉ ደንበኞች መጀመሪያ ወደ እርስዎ ይደርሳሉ። ሌሎችም ይደርሳሉ — ከአጭር ጥበቃ በኋላ፤ ማንም አይቀርም።</t>
         </is>
       </c>
       <c r="E217" s="13" t="inlineStr">
         <is>
-          <t>Sagalee</t>
+          <t>Maamiltoonni afaanota kanaan barreessan jalqaba isin bira ga'u. Kaan hundinuu ammas isin bira ga'u — eegumsa gabaabaa booda, namni hafu hin jiru.</t>
         </is>
       </c>
       <c r="F217" s="12" t="inlineStr">
         <is>
-          <t>ድምጺ</t>
+          <t>በዞም ቋንቋታት ዝጽሕፉ ዓማዊል ቅድም ናባኹም ይበጽሑ። እቶም ካልኦት እውን ይበጽሑ — ድሕሪ ሓጺር ጽበት፣ ዋላ ሓደ ኣይተርፍን።</t>
         </is>
       </c>
       <c r="G217" s="13" t="inlineStr">
         <is>
-          <t>Cod</t>
+          <t>Macaamiisha ku qora kuwan ayaa marka hore kugu soo gaara. Qof kastana wuu ku soo gaari doonaa — sug gaaban ka dib, sidaas qofna ma harayo.</t>
         </is>
       </c>
       <c r="H217" s="14" t="inlineStr"/>
@@ -13691,7 +13691,7 @@
     <row r="218" ht="44" customHeight="1">
       <c r="A218" s="11" t="inlineStr">
         <is>
-          <t>not_your_language</t>
+          <t>languages_none_note</t>
         </is>
       </c>
       <c r="B218" s="11" t="inlineStr">
@@ -13701,27 +13701,27 @@
       </c>
       <c r="C218" s="11" t="inlineStr">
         <is>
-          <t>not your language</t>
+          <t>Nothing selected, so every waiting customer is offered to you in plain oldest-first order.</t>
         </is>
       </c>
       <c r="D218" s="12" t="inlineStr">
         <is>
-          <t>የእርስዎ ቋንቋ አይደለም</t>
+          <t>ምንም አልተመረጠም፤ ስለዚህ እያንዳንዱ የሚጠብቅ ደንበኛ በቀላል ቀዳሚ-መጀመሪያ ቅደም ተከተል ይቀርብልዎታል።</t>
         </is>
       </c>
       <c r="E218" s="13" t="inlineStr">
         <is>
-          <t>afaan keessanii miti</t>
+          <t>Wanti filatame hin jiru, kanaafuu maamilli eegaa jiru hundi tartiiba dursaa-jalqabaatiin isinii dhiyaata.</t>
         </is>
       </c>
       <c r="F218" s="12" t="inlineStr">
         <is>
-          <t>ናትኩም ቋንቋ ኣይኮነን</t>
+          <t>ዋላ ሓደ ኣይተመርጸን፣ ስለዚ ነፍስ ወከፍ ዝጽበ ዓሚል ብቐሊል ናይ ቀዳምነት ስርዓት ይቐርበልኩም።</t>
         </is>
       </c>
       <c r="G218" s="13" t="inlineStr">
         <is>
-          <t>ma aha luqaddaada</t>
+          <t>Waxba lama dooran, sidaas darteed macmiil kasta oo sugaya waxaa laguu soo bandhigayaa sida caadiga ah ee ugu horreeya.</t>
         </is>
       </c>
       <c r="H218" s="14" t="inlineStr"/>
@@ -13729,7 +13729,7 @@
     <row r="219" ht="44" customHeight="1">
       <c r="A219" s="11" t="inlineStr">
         <is>
-          <t>languages_first_note</t>
+          <t>languages_updated</t>
         </is>
       </c>
       <c r="B219" s="11" t="inlineStr">
@@ -13739,27 +13739,27 @@
       </c>
       <c r="C219" s="11" t="inlineStr">
         <is>
-          <t>Your languages first, longest wait within each. Anyone waiting too long moves to the top whatever they speak.</t>
+          <t>Languages updated</t>
         </is>
       </c>
       <c r="D219" s="12" t="inlineStr">
         <is>
-          <t>የእርስዎ ቋንቋዎች መጀመሪያ፤ በእያንዳንዱ ውስጥ ረጅም የጠበቀው ይቀድማል። ከልክ በላይ የጠበቀ ማንኛውም ሰው የሚናገረው ምንም ይሁን ወደ ላይ ይወጣል።</t>
+          <t>ቋንቋዎች ተዘምነዋል</t>
         </is>
       </c>
       <c r="E219" s="13" t="inlineStr">
         <is>
-          <t>Afaanonni keessan jalqaba, tokkoon tokkoon isaanii keessatti kan yeroo dheeraa eege dursa. Namni baay'ee eege afaan kamiyyuu haa dubbatu gara oliitti deema.</t>
+          <t>Afaanonni haaromfaman</t>
         </is>
       </c>
       <c r="F219" s="12" t="inlineStr">
         <is>
-          <t>ቋንቋታትኩም ቅድም፣ ኣብ ነፍስ ወከፍ እቲ ነዊሕ ዝጸንሐ ይቐድም። ካብ ንቡር ንላዕሊ ዝጸንሐ ዝኾነ ሰብ ዝዛረቦ ብዘየገድስ ናብ ላዕሊ ይመጽእ።</t>
+          <t>ቋንቋታት ተሓዲሶም</t>
         </is>
       </c>
       <c r="G219" s="13" t="inlineStr">
         <is>
-          <t>Luqadahaaga marka hore, kii ugu sugay dheeraa mid kasta gudahood. Qof kasta oo aad u sugay ayaa kor u kaca luqad kastoo uu ku hadloba.</t>
+          <t>Luqadaha waa la cusbooneysiiyay</t>
         </is>
       </c>
       <c r="H219" s="14" t="inlineStr"/>
@@ -13767,7 +13767,7 @@
     <row r="220" ht="44" customHeight="1">
       <c r="A220" s="11" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>media_video</t>
         </is>
       </c>
       <c r="B220" s="11" t="inlineStr">
@@ -13777,27 +13777,27 @@
       </c>
       <c r="C220" s="11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="D220" s="12" t="inlineStr">
         <is>
-          <t>በሂደት ላይ</t>
+          <t>ቪዲዮ</t>
         </is>
       </c>
       <c r="E220" s="13" t="inlineStr">
         <is>
-          <t>Adeemsa irra</t>
+          <t>Viidiyoo</t>
         </is>
       </c>
       <c r="F220" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መስርሕ</t>
+          <t>ቪድዮ</t>
         </is>
       </c>
       <c r="G220" s="13" t="inlineStr">
         <is>
-          <t>Socda</t>
+          <t>Fiidyow</t>
         </is>
       </c>
       <c r="H220" s="14" t="inlineStr"/>
@@ -13805,7 +13805,7 @@
     <row r="221" ht="44" customHeight="1">
       <c r="A221" s="11" t="inlineStr">
         <is>
-          <t>no_session_in_progress</t>
+          <t>media_audio</t>
         </is>
       </c>
       <c r="B221" s="11" t="inlineStr">
@@ -13815,27 +13815,27 @@
       </c>
       <c r="C221" s="11" t="inlineStr">
         <is>
-          <t>No session in progress.</t>
+          <t>Audio</t>
         </is>
       </c>
       <c r="D221" s="12" t="inlineStr">
         <is>
-          <t>በሂደት ላይ ያለ ክፍለ-ጊዜ የለም።</t>
+          <t>ድምፅ</t>
         </is>
       </c>
       <c r="E221" s="13" t="inlineStr">
         <is>
-          <t>Sessionii adeemsa irra jiru hin jiru.</t>
+          <t>Sagalee</t>
         </is>
       </c>
       <c r="F221" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መስርሕ ዘሎ ክፍለ-ግዜ የለን።</t>
+          <t>ድምጺ</t>
         </is>
       </c>
       <c r="G221" s="13" t="inlineStr">
         <is>
-          <t>Ma jiro kalfadhi socda.</t>
+          <t>Cod</t>
         </is>
       </c>
       <c r="H221" s="14" t="inlineStr"/>
@@ -13843,7 +13843,7 @@
     <row r="222" ht="44" customHeight="1">
       <c r="A222" s="11" t="inlineStr">
         <is>
-          <t>wait_suffix</t>
+          <t>not_your_language</t>
         </is>
       </c>
       <c r="B222" s="11" t="inlineStr">
@@ -13853,27 +13853,27 @@
       </c>
       <c r="C222" s="11" t="inlineStr">
         <is>
-          <t>wait</t>
+          <t>not your language</t>
         </is>
       </c>
       <c r="D222" s="12" t="inlineStr">
         <is>
-          <t>ጥበቃ</t>
+          <t>የእርስዎ ቋንቋ አይደለም</t>
         </is>
       </c>
       <c r="E222" s="13" t="inlineStr">
         <is>
-          <t>eegumsa</t>
+          <t>afaan keessanii miti</t>
         </is>
       </c>
       <c r="F222" s="12" t="inlineStr">
         <is>
-          <t>ጽበት</t>
+          <t>ናትኩም ቋንቋ ኣይኮነን</t>
         </is>
       </c>
       <c r="G222" s="13" t="inlineStr">
         <is>
-          <t>sug</t>
+          <t>ma aha luqaddaada</t>
         </is>
       </c>
       <c r="H222" s="14" t="inlineStr"/>
@@ -13881,7 +13881,7 @@
     <row r="223" ht="44" customHeight="1">
       <c r="A223" s="11" t="inlineStr">
         <is>
-          <t>what_session_covers</t>
+          <t>languages_first_note</t>
         </is>
       </c>
       <c r="B223" s="11" t="inlineStr">
@@ -13891,27 +13891,27 @@
       </c>
       <c r="C223" s="11" t="inlineStr">
         <is>
-          <t>What a session covers</t>
+          <t>Your languages first, longest wait within each. Anyone waiting too long moves to the top whatever they speak.</t>
         </is>
       </c>
       <c r="D223" s="12" t="inlineStr">
         <is>
-          <t>አንድ ክፍለ-ጊዜ ምን ይሸፍናል</t>
+          <t>የእርስዎ ቋንቋዎች መጀመሪያ፤ በእያንዳንዱ ውስጥ ረጅም የጠበቀው ይቀድማል። ከልክ በላይ የጠበቀ ማንኛውም ሰው የሚናገረው ምንም ይሁን ወደ ላይ ይወጣል።</t>
         </is>
       </c>
       <c r="E223" s="13" t="inlineStr">
         <is>
-          <t>Sessioniin maal haguuga</t>
+          <t>Afaanonni keessan jalqaba, tokkoon tokkoon isaanii keessatti kan yeroo dheeraa eege dursa. Namni baay'ee eege afaan kamiyyuu haa dubbatu gara oliitti deema.</t>
         </is>
       </c>
       <c r="F223" s="12" t="inlineStr">
         <is>
-          <t>ሓደ ክፍለ-ግዜ እንታይ ይሽፍን</t>
+          <t>ቋንቋታትኩም ቅድም፣ ኣብ ነፍስ ወከፍ እቲ ነዊሕ ዝጸንሐ ይቐድም። ካብ ንቡር ንላዕሊ ዝጸንሐ ዝኾነ ሰብ ዝዛረቦ ብዘየገድስ ናብ ላዕሊ ይመጽእ።</t>
         </is>
       </c>
       <c r="G223" s="13" t="inlineStr">
         <is>
-          <t>Waxa kalfadhigu daboolo</t>
+          <t>Luqadahaaga marka hore, kii ugu sugay dheeraa mid kasta gudahood. Qof kasta oo aad u sugay ayaa kor u kaca luqad kastoo uu ku hadloba.</t>
         </is>
       </c>
       <c r="H223" s="14" t="inlineStr"/>
@@ -13919,7 +13919,7 @@
     <row r="224" ht="44" customHeight="1">
       <c r="A224" s="11" t="inlineStr">
         <is>
-          <t>session_scope_body</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="B224" s="11" t="inlineStr">
@@ -13929,27 +13929,27 @@
       </c>
       <c r="C224" s="11" t="inlineStr">
         <is>
-          <t>Before someone is identified: general questions about products, eligibility and how to apply. Once you have checked their Fayda ID against the account and asked something only the account holder could answer: their own application, documents and disputes.</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="D224" s="12" t="inlineStr">
         <is>
-          <t>አንድ ሰው ከመለየቱ በፊት፦ ስለ ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል አጠቃላይ ጥያቄዎች። የፋይዳ መታወቂያቸውን ከሂሳቡ ጋር አመሳክረው የሂሳቡ ባለቤት ብቻ ሊመልሰው የሚችለውን ከጠየቁ በኋላ፦ የራሳቸው ማመልከቻ፣ ሰነዶችና ቅሬታዎች።</t>
+          <t>በሂደት ላይ</t>
         </is>
       </c>
       <c r="E224" s="13" t="inlineStr">
         <is>
-          <t>Namni tokko utuu hin beekamin dura: gaaffii waliigalaa waa'ee oomishaalee, ulaagaa fi akkaataa itti iyyatan. Erga waraqaa eenyummaa Fayda isaanii herrega waliin madaalchiftanii waan abbaan herregaa qofti deebisuu danda'u gaafattanii booda: iyyannoo, sanadoota fi komii isaanii.</t>
+          <t>Adeemsa irra</t>
         </is>
       </c>
       <c r="F224" s="12" t="inlineStr">
         <is>
-          <t>ሓደ ሰብ ቅድሚ ምልላዩ፦ ብዛዕባ ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን ሓፈሻዊ ሕቶታት። መንነት ፋይዳኦም ምስ ሕሳብ ኣረጋጊጽኩም እቲ ወናኒ ሕሳብ ጥራይ ክምልሶ ዝኽእል ምስ ሓተትኩም፦ ናቶም ምልክታ፣ ሰነዳትን ጥርዓናትን።</t>
+          <t>ኣብ መስርሕ</t>
         </is>
       </c>
       <c r="G224" s="13" t="inlineStr">
         <is>
-          <t>Ka hor inta aan qofka la aqoonsan: su'aalo guud oo ku saabsan alaabta, u-qalmitaanka iyo sida loo codsado. Marka aad hubiso aqoonsigooda Fayda ee xisaabta oo aad weydiiso wax uu kaliya milkiilaha xisaabtu ka jawaabi karo: codsigooda, dukumiintiyada iyo cabashooyinka.</t>
+          <t>Socda</t>
         </is>
       </c>
       <c r="H224" s="14" t="inlineStr"/>
@@ -13957,7 +13957,7 @@
     <row r="225" ht="44" customHeight="1">
       <c r="A225" s="11" t="inlineStr">
         <is>
-          <t>never_money_movement</t>
+          <t>no_session_in_progress</t>
         </is>
       </c>
       <c r="B225" s="11" t="inlineStr">
@@ -13967,27 +13967,27 @@
       </c>
       <c r="C225" s="11" t="inlineStr">
         <is>
-          <t>Never, at any point and for anyone: deposits, withdrawals or transfers. Those do not happen on a call.</t>
+          <t>No session in progress.</t>
         </is>
       </c>
       <c r="D225" s="12" t="inlineStr">
         <is>
-          <t>በፍጹም፣ በማንኛውም ጊዜና ለማንም፦ ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም። እነዚያ በጥሪ ላይ አይፈጸሙም።</t>
+          <t>በሂደት ላይ ያለ ክፍለ-ጊዜ የለም።</t>
         </is>
       </c>
       <c r="E225" s="13" t="inlineStr">
         <is>
-          <t>Gonkumaa, yeroo kamiyyuu fi eenyuufiyyuu: kuusaa, baasii yookiin dabarsa hin jiru. Isaan sun bilbila irratti hin raawwataman.</t>
+          <t>Sessionii adeemsa irra jiru hin jiru.</t>
         </is>
       </c>
       <c r="F225" s="12" t="inlineStr">
         <is>
-          <t>ፈጺሙ፣ ኣብ ዝኾነ እዋንን ንዝኾነ ሰብን፦ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን። እዚኣቶም ኣብ ጻውዒት ኣይፍጸሙን።</t>
+          <t>ኣብ መስርሕ ዘሎ ክፍለ-ግዜ የለን።</t>
         </is>
       </c>
       <c r="G225" s="13" t="inlineStr">
         <is>
-          <t>Weligaa, wakhti kasta iyo qof kasta: dhigasho, qaadis ama wareejin ma jirto. Kuwaas wicitaan laguma sameeyo.</t>
+          <t>Ma jiro kalfadhi socda.</t>
         </is>
       </c>
       <c r="H225" s="14" t="inlineStr"/>
@@ -13995,7 +13995,7 @@
     <row r="226" ht="44" customHeight="1">
       <c r="A226" s="11" t="inlineStr">
         <is>
-          <t>open_escalation_queue</t>
+          <t>wait_suffix</t>
         </is>
       </c>
       <c r="B226" s="11" t="inlineStr">
@@ -14005,27 +14005,27 @@
       </c>
       <c r="C226" s="11" t="inlineStr">
         <is>
-          <t>Open the escalation queue</t>
+          <t>wait</t>
         </is>
       </c>
       <c r="D226" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ወረፋውን ክፈት</t>
+          <t>ጥበቃ</t>
         </is>
       </c>
       <c r="E226" s="13" t="inlineStr">
         <is>
-          <t>Sararaa dabarsaa banaa</t>
+          <t>eegumsa</t>
         </is>
       </c>
       <c r="F226" s="12" t="inlineStr">
         <is>
-          <t>ሪጋ ምትሕልላፍ ክፈት</t>
+          <t>ጽበት</t>
         </is>
       </c>
       <c r="G226" s="13" t="inlineStr">
         <is>
-          <t>Fur safka gudbinta</t>
+          <t>sug</t>
         </is>
       </c>
       <c r="H226" s="14" t="inlineStr"/>
@@ -14033,7 +14033,7 @@
     <row r="227" ht="44" customHeight="1">
       <c r="A227" s="11" t="inlineStr">
         <is>
-          <t>switch_dark_light</t>
+          <t>what_session_covers</t>
         </is>
       </c>
       <c r="B227" s="11" t="inlineStr">
@@ -14043,27 +14043,27 @@
       </c>
       <c r="C227" s="11" t="inlineStr">
         <is>
-          <t>Switch between dark and light</t>
+          <t>What a session covers</t>
         </is>
       </c>
       <c r="D227" s="12" t="inlineStr">
         <is>
-          <t>በጨለማና በብርሃን መካከል ቀይር</t>
+          <t>አንድ ክፍለ-ጊዜ ምን ይሸፍናል</t>
         </is>
       </c>
       <c r="E227" s="13" t="inlineStr">
         <is>
-          <t>Dukkanaa fi ifa gidduu jijjiiri</t>
+          <t>Sessioniin maal haguuga</t>
         </is>
       </c>
       <c r="F227" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መንጎ ጸላምን ብርሃንን ቀይር</t>
+          <t>ሓደ ክፍለ-ግዜ እንታይ ይሽፍን</t>
         </is>
       </c>
       <c r="G227" s="13" t="inlineStr">
         <is>
-          <t>U beddel mugdiga iyo iftiinka</t>
+          <t>Waxa kalfadhigu daboolo</t>
         </is>
       </c>
       <c r="H227" s="14" t="inlineStr"/>
@@ -14071,7 +14071,7 @@
     <row r="228" ht="44" customHeight="1">
       <c r="A228" s="11" t="inlineStr">
         <is>
-          <t>live_session</t>
+          <t>session_scope_body</t>
         </is>
       </c>
       <c r="B228" s="11" t="inlineStr">
@@ -14081,27 +14081,27 @@
       </c>
       <c r="C228" s="11" t="inlineStr">
         <is>
-          <t>Live session</t>
+          <t>Before someone is identified: general questions about products, eligibility and how to apply. Once you have checked their Fayda ID against the account and asked something only the account holder could answer: their own application, documents and disputes.</t>
         </is>
       </c>
       <c r="D228" s="12" t="inlineStr">
         <is>
-          <t>የቀጥታ ክፍለ-ጊዜ</t>
+          <t>አንድ ሰው ከመለየቱ በፊት፦ ስለ ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል አጠቃላይ ጥያቄዎች። የፋይዳ መታወቂያቸውን ከሂሳቡ ጋር አመሳክረው የሂሳቡ ባለቤት ብቻ ሊመልሰው የሚችለውን ከጠየቁ በኋላ፦ የራሳቸው ማመልከቻ፣ ሰነዶችና ቅሬታዎች።</t>
         </is>
       </c>
       <c r="E228" s="13" t="inlineStr">
         <is>
-          <t>Session kallattii</t>
+          <t>Namni tokko utuu hin beekamin dura: gaaffii waliigalaa waa'ee oomishaalee, ulaagaa fi akkaataa itti iyyatan. Erga waraqaa eenyummaa Fayda isaanii herrega waliin madaalchiftanii waan abbaan herregaa qofti deebisuu danda'u gaafattanii booda: iyyannoo, sanadoota fi komii isaanii.</t>
         </is>
       </c>
       <c r="F228" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታ ክፍለ-ግዜ</t>
+          <t>ሓደ ሰብ ቅድሚ ምልላዩ፦ ብዛዕባ ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን ሓፈሻዊ ሕቶታት። መንነት ፋይዳኦም ምስ ሕሳብ ኣረጋጊጽኩም እቲ ወናኒ ሕሳብ ጥራይ ክምልሶ ዝኽእል ምስ ሓተትኩም፦ ናቶም ምልክታ፣ ሰነዳትን ጥርዓናትን።</t>
         </is>
       </c>
       <c r="G228" s="13" t="inlineStr">
         <is>
-          <t>Kalfadhi toos ah</t>
+          <t>Ka hor inta aan qofka la aqoonsan: su'aalo guud oo ku saabsan alaabta, u-qalmitaanka iyo sida loo codsado. Marka aad hubiso aqoonsigooda Fayda ee xisaabta oo aad weydiiso wax uu kaliya milkiilaha xisaabtu ka jawaabi karo: codsigooda, dukumiintiyada iyo cabashooyinka.</t>
         </is>
       </c>
       <c r="H228" s="14" t="inlineStr"/>
@@ -14109,7 +14109,7 @@
     <row r="229" ht="44" customHeight="1">
       <c r="A229" s="11" t="inlineStr">
         <is>
-          <t>customer_left_call</t>
+          <t>never_money_movement</t>
         </is>
       </c>
       <c r="B229" s="11" t="inlineStr">
@@ -14119,27 +14119,27 @@
       </c>
       <c r="C229" s="11" t="inlineStr">
         <is>
-          <t>The customer has left the call.</t>
+          <t>Never, at any point and for anyone: deposits, withdrawals or transfers. Those do not happen on a call.</t>
         </is>
       </c>
       <c r="D229" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛው ጥሪውን ለቅቋል።</t>
+          <t>በፍጹም፣ በማንኛውም ጊዜና ለማንም፦ ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም። እነዚያ በጥሪ ላይ አይፈጸሙም።</t>
         </is>
       </c>
       <c r="E229" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan bilbila irraa ba'eera.</t>
+          <t>Gonkumaa, yeroo kamiyyuu fi eenyuufiyyuu: kuusaa, baasii yookiin dabarsa hin jiru. Isaan sun bilbila irratti hin raawwataman.</t>
         </is>
       </c>
       <c r="F229" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዓሚል ካብቲ ጻውዒት ወጺኡ።</t>
+          <t>ፈጺሙ፣ ኣብ ዝኾነ እዋንን ንዝኾነ ሰብን፦ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን። እዚኣቶም ኣብ ጻውዒት ኣይፍጸሙን።</t>
         </is>
       </c>
       <c r="G229" s="13" t="inlineStr">
         <is>
-          <t>Macmiilku wicitaanka wuu ka baxay.</t>
+          <t>Weligaa, wakhti kasta iyo qof kasta: dhigasho, qaadis ama wareejin ma jirto. Kuwaas wicitaan laguma sameeyo.</t>
         </is>
       </c>
       <c r="H229" s="14" t="inlineStr"/>
@@ -14147,7 +14147,7 @@
     <row r="230" ht="44" customHeight="1">
       <c r="A230" s="11" t="inlineStr">
         <is>
-          <t>waiting_for_customer</t>
+          <t>open_escalation_queue</t>
         </is>
       </c>
       <c r="B230" s="11" t="inlineStr">
@@ -14157,27 +14157,27 @@
       </c>
       <c r="C230" s="11" t="inlineStr">
         <is>
-          <t>Waiting for the customer…</t>
+          <t>Open the escalation queue</t>
         </is>
       </c>
       <c r="D230" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛውን በመጠበቅ ላይ…</t>
+          <t>የማሸጋገሪያ ወረፋውን ክፈት</t>
         </is>
       </c>
       <c r="E230" s="13" t="inlineStr">
         <is>
-          <t>Maamilaa eegaa jirra…</t>
+          <t>Sararaa dabarsaa banaa</t>
         </is>
       </c>
       <c r="F230" s="12" t="inlineStr">
         <is>
-          <t>ነቲ ዓሚል ንጽበ ኣለና…</t>
+          <t>ሪጋ ምትሕልላፍ ክፈት</t>
         </is>
       </c>
       <c r="G230" s="13" t="inlineStr">
         <is>
-          <t>Macmiilka la sugayo…</t>
+          <t>Fur safka gudbinta</t>
         </is>
       </c>
       <c r="H230" s="14" t="inlineStr"/>
@@ -14185,7 +14185,7 @@
     <row r="231" ht="44" customHeight="1">
       <c r="A231" s="11" t="inlineStr">
         <is>
-          <t>mic_blocked</t>
+          <t>switch_dark_light</t>
         </is>
       </c>
       <c r="B231" s="11" t="inlineStr">
@@ -14195,27 +14195,27 @@
       </c>
       <c r="C231" s="11" t="inlineStr">
         <is>
-          <t>Microphone access is blocked. Allow it in your browser and take the session again.</t>
+          <t>Switch between dark and light</t>
         </is>
       </c>
       <c r="D231" s="12" t="inlineStr">
         <is>
-          <t>የማይክሮፎን መዳረሻ ታግዷል። በአሳሽዎ ውስጥ ይፍቀዱና ክፍለ-ጊዜውን እንደገና ይውሰዱ።</t>
+          <t>በጨለማና በብርሃን መካከል ቀይር</t>
         </is>
       </c>
       <c r="E231" s="13" t="inlineStr">
         <is>
-          <t>Maayikiroofoonii dhorkameera. Biraawzarii keessan keessatti hayyamaatii session irra deebi'aa fudhadhaa.</t>
+          <t>Dukkanaa fi ifa gidduu jijjiiri</t>
         </is>
       </c>
       <c r="F231" s="12" t="inlineStr">
         <is>
-          <t>መእተዊ ማይክሮፎን ተዓጊቱ። ኣብ መርበብ መንሸራተቲኹም ፍቐዱ እሞ ነቲ ክፍለ-ግዜ ደጊምኩም ውሰዱ።</t>
+          <t>ኣብ መንጎ ጸላምን ብርሃንን ቀይር</t>
         </is>
       </c>
       <c r="G231" s="13" t="inlineStr">
         <is>
-          <t>Makarafoonka waa la xannibay. Browser-kaaga ka ogolow oo kalfadhiga mar kale qaado.</t>
+          <t>U beddel mugdiga iyo iftiinka</t>
         </is>
       </c>
       <c r="H231" s="14" t="inlineStr"/>
@@ -14223,7 +14223,7 @@
     <row r="232" ht="44" customHeight="1">
       <c r="A232" s="11" t="inlineStr">
         <is>
-          <t>unknown_error</t>
+          <t>live_session</t>
         </is>
       </c>
       <c r="B232" s="11" t="inlineStr">
@@ -14233,27 +14233,27 @@
       </c>
       <c r="C232" s="11" t="inlineStr">
         <is>
-          <t>unknown error</t>
+          <t>Live session</t>
         </is>
       </c>
       <c r="D232" s="12" t="inlineStr">
         <is>
-          <t>ያልታወቀ ስህተት</t>
+          <t>የቀጥታ ክፍለ-ጊዜ</t>
         </is>
       </c>
       <c r="E232" s="13" t="inlineStr">
         <is>
-          <t>dogoggora hin beekamne</t>
+          <t>Session kallattii</t>
         </is>
       </c>
       <c r="F232" s="12" t="inlineStr">
         <is>
-          <t>ዘይተፈልጠ ጌጋ</t>
+          <t>ቀጥታ ክፍለ-ግዜ</t>
         </is>
       </c>
       <c r="G232" s="13" t="inlineStr">
         <is>
-          <t>khalad aan la garanayn</t>
+          <t>Kalfadhi toos ah</t>
         </is>
       </c>
       <c r="H232" s="14" t="inlineStr"/>
@@ -14261,7 +14261,7 @@
     <row r="233" ht="44" customHeight="1">
       <c r="A233" s="11" t="inlineStr">
         <is>
-          <t>no_messages_yet</t>
+          <t>customer_left_call</t>
         </is>
       </c>
       <c r="B233" s="11" t="inlineStr">
@@ -14271,27 +14271,27 @@
       </c>
       <c r="C233" s="11" t="inlineStr">
         <is>
-          <t>No messages yet.</t>
+          <t>The customer has left the call.</t>
         </is>
       </c>
       <c r="D233" s="12" t="inlineStr">
         <is>
-          <t>እስካሁን መልእክት የለም።</t>
+          <t>ደንበኛው ጥሪውን ለቅቋል።</t>
         </is>
       </c>
       <c r="E233" s="13" t="inlineStr">
         <is>
-          <t>Ammaaf ergaan hin jiru.</t>
+          <t>Maamilaan bilbila irraa ba'eera.</t>
         </is>
       </c>
       <c r="F233" s="12" t="inlineStr">
         <is>
-          <t>ክሳብ ሕጂ መልእኽቲ የለን።</t>
+          <t>እቲ ዓሚል ካብቲ ጻውዒት ወጺኡ።</t>
         </is>
       </c>
       <c r="G233" s="13" t="inlineStr">
         <is>
-          <t>Weli fariimo ma jiraan.</t>
+          <t>Macmiilku wicitaanka wuu ka baxay.</t>
         </is>
       </c>
       <c r="H233" s="14" t="inlineStr"/>
@@ -14299,7 +14299,7 @@
     <row r="234" ht="44" customHeight="1">
       <c r="A234" s="11" t="inlineStr">
         <is>
-          <t>you_label</t>
+          <t>waiting_for_customer</t>
         </is>
       </c>
       <c r="B234" s="11" t="inlineStr">
@@ -14309,27 +14309,27 @@
       </c>
       <c r="C234" s="11" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Waiting for the customer…</t>
         </is>
       </c>
       <c r="D234" s="12" t="inlineStr">
         <is>
-          <t>እርስዎ</t>
+          <t>ደንበኛውን በመጠበቅ ላይ…</t>
         </is>
       </c>
       <c r="E234" s="13" t="inlineStr">
         <is>
-          <t>Isin</t>
+          <t>Maamilaa eegaa jirra…</t>
         </is>
       </c>
       <c r="F234" s="12" t="inlineStr">
         <is>
-          <t>ንስኹም</t>
+          <t>ነቲ ዓሚል ንጽበ ኣለና…</t>
         </is>
       </c>
       <c r="G234" s="13" t="inlineStr">
         <is>
-          <t>Adiga</t>
+          <t>Macmiilka la sugayo…</t>
         </is>
       </c>
       <c r="H234" s="14" t="inlineStr"/>
@@ -14337,7 +14337,7 @@
     <row r="235" ht="44" customHeight="1">
       <c r="A235" s="11" t="inlineStr">
         <is>
-          <t>assistant_label</t>
+          <t>mic_blocked</t>
         </is>
       </c>
       <c r="B235" s="11" t="inlineStr">
@@ -14347,27 +14347,27 @@
       </c>
       <c r="C235" s="11" t="inlineStr">
         <is>
-          <t>Assistant</t>
+          <t>Microphone access is blocked. Allow it in your browser and take the session again.</t>
         </is>
       </c>
       <c r="D235" s="12" t="inlineStr">
         <is>
-          <t>ረዳት</t>
+          <t>የማይክሮፎን መዳረሻ ታግዷል። በአሳሽዎ ውስጥ ይፍቀዱና ክፍለ-ጊዜውን እንደገና ይውሰዱ።</t>
         </is>
       </c>
       <c r="E235" s="13" t="inlineStr">
         <is>
-          <t>Gargaaraa</t>
+          <t>Maayikiroofoonii dhorkameera. Biraawzarii keessan keessatti hayyamaatii session irra deebi'aa fudhadhaa.</t>
         </is>
       </c>
       <c r="F235" s="12" t="inlineStr">
         <is>
-          <t>ሓጋዚ</t>
+          <t>መእተዊ ማይክሮፎን ተዓጊቱ። ኣብ መርበብ መንሸራተቲኹም ፍቐዱ እሞ ነቲ ክፍለ-ግዜ ደጊምኩም ውሰዱ።</t>
         </is>
       </c>
       <c r="G235" s="13" t="inlineStr">
         <is>
-          <t>Kaaliye</t>
+          <t>Makarafoonka waa la xannibay. Browser-kaaga ka ogolow oo kalfadhiga mar kale qaado.</t>
         </is>
       </c>
       <c r="H235" s="14" t="inlineStr"/>
@@ -14375,7 +14375,7 @@
     <row r="236" ht="44" customHeight="1">
       <c r="A236" s="11" t="inlineStr">
         <is>
-          <t>conversation_unavailable</t>
+          <t>unknown_error</t>
         </is>
       </c>
       <c r="B236" s="11" t="inlineStr">
@@ -14385,27 +14385,27 @@
       </c>
       <c r="C236" s="11" t="inlineStr">
         <is>
-          <t>Conversation unavailable.</t>
+          <t>unknown error</t>
         </is>
       </c>
       <c r="D236" s="12" t="inlineStr">
         <is>
-          <t>ውይይቱ አይገኝም።</t>
+          <t>ያልታወቀ ስህተት</t>
         </is>
       </c>
       <c r="E236" s="13" t="inlineStr">
         <is>
-          <t>Mariin hin argamu.</t>
+          <t>dogoggora hin beekamne</t>
         </is>
       </c>
       <c r="F236" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዝርርብ ኣይርከብን።</t>
+          <t>ዘይተፈልጠ ጌጋ</t>
         </is>
       </c>
       <c r="G236" s="13" t="inlineStr">
         <is>
-          <t>Wadahadalka lama heli karo.</t>
+          <t>khalad aan la garanayn</t>
         </is>
       </c>
       <c r="H236" s="14" t="inlineStr"/>
@@ -14413,7 +14413,7 @@
     <row r="237" ht="44" customHeight="1">
       <c r="A237" s="11" t="inlineStr">
         <is>
-          <t>unmute</t>
+          <t>no_messages_yet</t>
         </is>
       </c>
       <c r="B237" s="11" t="inlineStr">
@@ -14423,27 +14423,27 @@
       </c>
       <c r="C237" s="11" t="inlineStr">
         <is>
-          <t>Unmute</t>
+          <t>No messages yet.</t>
         </is>
       </c>
       <c r="D237" s="12" t="inlineStr">
         <is>
-          <t>ድምፅ አብራ</t>
+          <t>እስካሁን መልእክት የለም።</t>
         </is>
       </c>
       <c r="E237" s="13" t="inlineStr">
         <is>
-          <t>Sagalee banaa</t>
+          <t>Ammaaf ergaan hin jiru.</t>
         </is>
       </c>
       <c r="F237" s="12" t="inlineStr">
         <is>
-          <t>ድምጺ ኣብርህ</t>
+          <t>ክሳብ ሕጂ መልእኽቲ የለን።</t>
         </is>
       </c>
       <c r="G237" s="13" t="inlineStr">
         <is>
-          <t>Codka fur</t>
+          <t>Weli fariimo ma jiraan.</t>
         </is>
       </c>
       <c r="H237" s="14" t="inlineStr"/>
@@ -14451,7 +14451,7 @@
     <row r="238" ht="44" customHeight="1">
       <c r="A238" s="11" t="inlineStr">
         <is>
-          <t>session_summary_prompt</t>
+          <t>you_label</t>
         </is>
       </c>
       <c r="B238" s="11" t="inlineStr">
@@ -14461,27 +14461,27 @@
       </c>
       <c r="C238" s="11" t="inlineStr">
         <is>
-          <t>What did this session cover? (optional)</t>
+          <t>You</t>
         </is>
       </c>
       <c r="D238" s="12" t="inlineStr">
         <is>
-          <t>ይህ ክፍለ-ጊዜ ምን ሸፈነ? (አማራጭ)</t>
+          <t>እርስዎ</t>
         </is>
       </c>
       <c r="E238" s="13" t="inlineStr">
         <is>
-          <t>Sessioniin kun maal haguuge? (filannoo)</t>
+          <t>Isin</t>
         </is>
       </c>
       <c r="F238" s="12" t="inlineStr">
         <is>
-          <t>እዚ ክፍለ-ግዜ እንታይ ሸፈነ? (ኣማራጺ)</t>
+          <t>ንስኹም</t>
         </is>
       </c>
       <c r="G238" s="13" t="inlineStr">
         <is>
-          <t>Kalfadhigan muxuu daboolay? (ikhtiyaari)</t>
+          <t>Adiga</t>
         </is>
       </c>
       <c r="H238" s="14" t="inlineStr"/>
@@ -14489,7 +14489,7 @@
     <row r="239" ht="44" customHeight="1">
       <c r="A239" s="11" t="inlineStr">
         <is>
-          <t>customer_ended_call</t>
+          <t>assistant_label</t>
         </is>
       </c>
       <c r="B239" s="11" t="inlineStr">
@@ -14499,27 +14499,27 @@
       </c>
       <c r="C239" s="11" t="inlineStr">
         <is>
-          <t>The customer ended the call</t>
+          <t>Assistant</t>
         </is>
       </c>
       <c r="D239" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛው ጥሪውን አቋረጠ</t>
+          <t>ረዳት</t>
         </is>
       </c>
       <c r="E239" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan bilbila xumure</t>
+          <t>Gargaaraa</t>
         </is>
       </c>
       <c r="F239" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዓሚል ነቲ ጻውዒት ወዲኡዎ</t>
+          <t>ሓጋዚ</t>
         </is>
       </c>
       <c r="G239" s="13" t="inlineStr">
         <is>
-          <t>Macmiilku wicitaanka wuu joojiyay</t>
+          <t>Kaaliye</t>
         </is>
       </c>
       <c r="H239" s="14" t="inlineStr"/>
@@ -14527,7 +14527,7 @@
     <row r="240" ht="44" customHeight="1">
       <c r="A240" s="11" t="inlineStr">
         <is>
-          <t>verified_scope</t>
+          <t>conversation_unavailable</t>
         </is>
       </c>
       <c r="B240" s="11" t="inlineStr">
@@ -14537,27 +14537,27 @@
       </c>
       <c r="C240" s="11" t="inlineStr">
         <is>
-          <t>You can now discuss their own records, take documents and file a dispute. Never a deposit, withdrawal or transfer.</t>
+          <t>Conversation unavailable.</t>
         </is>
       </c>
       <c r="D240" s="12" t="inlineStr">
         <is>
-          <t>አሁን ስለ ራሳቸው መዝገቦች መወያየት፣ ሰነዶች መቀበልና ቅሬታ ማስመዝገብ ይችላሉ። በፍጹም ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም።</t>
+          <t>ውይይቱ አይገኝም።</t>
         </is>
       </c>
       <c r="E240" s="13" t="inlineStr">
         <is>
-          <t>Amma waa'ee galmee isaanii mari'achuu, sanadoota fudhachuu fi komii galmeessuu dandeessu. Gonkumaa kuusaa, baasii yookiin dabarsa hin jiru.</t>
+          <t>Mariin hin argamu.</t>
         </is>
       </c>
       <c r="F240" s="12" t="inlineStr">
         <is>
-          <t>ሕጂ ብዛዕባ ናቶም መዝገባት ክትዘራረቡ፣ ሰነዳት ክትቅበሉን ጥርዓን ከተመዝግቡን ትኽእሉ። ፈጺሙ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን።</t>
+          <t>እቲ ዝርርብ ኣይርከብን።</t>
         </is>
       </c>
       <c r="G240" s="13" t="inlineStr">
         <is>
-          <t>Hadda waad kala hadli kartaa diiwaankooda, dukumiinti qaadan iyo cabasho diiwaangelin. Weligaa dhigasho, qaadis ama wareejin ma jirto.</t>
+          <t>Wadahadalka lama heli karo.</t>
         </is>
       </c>
       <c r="H240" s="14" t="inlineStr"/>
@@ -14565,7 +14565,7 @@
     <row r="241" ht="44" customHeight="1">
       <c r="A241" s="11" t="inlineStr">
         <is>
-          <t>establish_who_they_are</t>
+          <t>unmute</t>
         </is>
       </c>
       <c r="B241" s="11" t="inlineStr">
@@ -14575,27 +14575,27 @@
       </c>
       <c r="C241" s="11" t="inlineStr">
         <is>
-          <t>Establish who they are — either one</t>
+          <t>Unmute</t>
         </is>
       </c>
       <c r="D241" s="12" t="inlineStr">
         <is>
-          <t>ማንነታቸውን ያረጋግጡ — አንዱ ይበቃል</t>
+          <t>ድምፅ አብራ</t>
         </is>
       </c>
       <c r="E241" s="13" t="inlineStr">
         <is>
-          <t>Eenyummaa isaanii mirkaneessaa — tokko ni ga'a</t>
+          <t>Sagalee banaa</t>
         </is>
       </c>
       <c r="F241" s="12" t="inlineStr">
         <is>
-          <t>መንነቶም ኣረጋግጹ — ሓደ እኹል እዩ</t>
+          <t>ድምጺ ኣብርህ</t>
         </is>
       </c>
       <c r="G241" s="13" t="inlineStr">
         <is>
-          <t>Ogow cidda ay yihiin — mid kasta</t>
+          <t>Codka fur</t>
         </is>
       </c>
       <c r="H241" s="14" t="inlineStr"/>
@@ -14603,7 +14603,7 @@
     <row r="242" ht="44" customHeight="1">
       <c r="A242" s="11" t="inlineStr">
         <is>
-          <t>chk_id_document</t>
+          <t>session_summary_prompt</t>
         </is>
       </c>
       <c r="B242" s="11" t="inlineStr">
@@ -14613,27 +14613,27 @@
       </c>
       <c r="C242" s="11" t="inlineStr">
         <is>
-          <t>Fayda ID shown and matches the account name</t>
+          <t>What did this session cover? (optional)</t>
         </is>
       </c>
       <c r="D242" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ መታወቂያ ታይቷል እና ከሂሳቡ ስም ጋር ይዛመዳል</t>
+          <t>ይህ ክፍለ-ጊዜ ምን ሸፈነ? (አማራጭ)</t>
         </is>
       </c>
       <c r="E242" s="13" t="inlineStr">
         <is>
-          <t>Waraqaan eenyummaa Fayda agarsiifame maqaa herregaa waliin walsimeera</t>
+          <t>Sessioniin kun maal haguuge? (filannoo)</t>
         </is>
       </c>
       <c r="F242" s="12" t="inlineStr">
         <is>
-          <t>መንነት ፋይዳ ተራእዩን ምስ ስም ሕሳብ ይሰማማዕን</t>
+          <t>እዚ ክፍለ-ግዜ እንታይ ሸፈነ? (ኣማራጺ)</t>
         </is>
       </c>
       <c r="G242" s="13" t="inlineStr">
         <is>
-          <t>Aqoonsiga Fayda waa la tusay wuxuuna la mid yahay magaca xisaabta</t>
+          <t>Kalfadhigan muxuu daboolay? (ikhtiyaari)</t>
         </is>
       </c>
       <c r="H242" s="14" t="inlineStr"/>
@@ -14641,7 +14641,7 @@
     <row r="243" ht="44" customHeight="1">
       <c r="A243" s="11" t="inlineStr">
         <is>
-          <t>chk_fayda_matched</t>
+          <t>customer_ended_call</t>
         </is>
       </c>
       <c r="B243" s="11" t="inlineStr">
@@ -14651,27 +14651,27 @@
       </c>
       <c r="C243" s="11" t="inlineStr">
         <is>
-          <t>Fayda number matches the account record</t>
+          <t>The customer ended the call</t>
         </is>
       </c>
       <c r="D243" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ ቁጥር ከሂሳቡ መዝገብ ጋር ይዛመዳል</t>
+          <t>ደንበኛው ጥሪውን አቋረጠ</t>
         </is>
       </c>
       <c r="E243" s="13" t="inlineStr">
         <is>
-          <t>Lakkoofsi Fayda galmee herregaa waliin walsimeera</t>
+          <t>Maamilaan bilbila xumure</t>
         </is>
       </c>
       <c r="F243" s="12" t="inlineStr">
         <is>
-          <t>ቁጽሪ ፋይዳ ምስ መዝገብ ሕሳብ ይሰማማዕ</t>
+          <t>እቲ ዓሚል ነቲ ጻውዒት ወዲኡዎ</t>
         </is>
       </c>
       <c r="G243" s="13" t="inlineStr">
         <is>
-          <t>Lambarka Fayda wuxuu la mid yahay diiwaanka xisaabta</t>
+          <t>Macmiilku wicitaanka wuu joojiyay</t>
         </is>
       </c>
       <c r="H243" s="14" t="inlineStr"/>
@@ -14679,7 +14679,7 @@
     <row r="244" ht="44" customHeight="1">
       <c r="A244" s="11" t="inlineStr">
         <is>
-          <t>chk_fayda_matched_note</t>
+          <t>verified_scope</t>
         </is>
       </c>
       <c r="B244" s="11" t="inlineStr">
@@ -14689,27 +14689,27 @@
       </c>
       <c r="C244" s="11" t="inlineStr">
         <is>
-          <t>on your own screen — works on an audio call</t>
+          <t>You can now discuss their own records, take documents and file a dispute. Never a deposit, withdrawal or transfer.</t>
         </is>
       </c>
       <c r="D244" s="12" t="inlineStr">
         <is>
-          <t>በራስዎ ስክሪን ላይ — በድምፅ ጥሪም ይሠራል</t>
+          <t>አሁን ስለ ራሳቸው መዝገቦች መወያየት፣ ሰነዶች መቀበልና ቅሬታ ማስመዝገብ ይችላሉ። በፍጹም ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም።</t>
         </is>
       </c>
       <c r="E244" s="13" t="inlineStr">
         <is>
-          <t>iskiriinii keessan irratti — bilbila sagalee irrattis ni hojjeta</t>
+          <t>Amma waa'ee galmee isaanii mari'achuu, sanadoota fudhachuu fi komii galmeessuu dandeessu. Gonkumaa kuusaa, baasii yookiin dabarsa hin jiru.</t>
         </is>
       </c>
       <c r="F244" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ናትኩም መርአዪ — ኣብ ናይ ድምጺ ጻውዒት እውን ይሰርሕ</t>
+          <t>ሕጂ ብዛዕባ ናቶም መዝገባት ክትዘራረቡ፣ ሰነዳት ክትቅበሉን ጥርዓን ከተመዝግቡን ትኽእሉ። ፈጺሙ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን።</t>
         </is>
       </c>
       <c r="G244" s="13" t="inlineStr">
         <is>
-          <t>shaashaddaada — wicitaan cod ahna wuu ka shaqeeyaa</t>
+          <t>Hadda waad kala hadli kartaa diiwaankooda, dukumiinti qaadan iyo cabasho diiwaangelin. Weligaa dhigasho, qaadis ama wareejin ma jirto.</t>
         </is>
       </c>
       <c r="H244" s="14" t="inlineStr"/>
@@ -14717,7 +14717,7 @@
     <row r="245" ht="44" customHeight="1">
       <c r="A245" s="11" t="inlineStr">
         <is>
-          <t>chk_id_photo</t>
+          <t>establish_who_they_are</t>
         </is>
       </c>
       <c r="B245" s="11" t="inlineStr">
@@ -14727,27 +14727,27 @@
       </c>
       <c r="C245" s="11" t="inlineStr">
         <is>
-          <t>Photo on the ID matches the person on the call</t>
+          <t>Establish who they are — either one</t>
         </is>
       </c>
       <c r="D245" s="12" t="inlineStr">
         <is>
-          <t>በመታወቂያው ላይ ያለው ፎቶ ከጥሪው ላይ ካለው ሰው ጋር ይዛመዳል</t>
+          <t>ማንነታቸውን ያረጋግጡ — አንዱ ይበቃል</t>
         </is>
       </c>
       <c r="E245" s="13" t="inlineStr">
         <is>
-          <t>Suuraan waraqaa eenyummaa irra jiru nama bilbila irra jiru waliin walsimeera</t>
+          <t>Eenyummaa isaanii mirkaneessaa — tokko ni ga'a</t>
         </is>
       </c>
       <c r="F245" s="12" t="inlineStr">
         <is>
-          <t>እቲ ኣብ መንነት ዘሎ ስእሊ ምስቲ ኣብ ጻውዒት ዘሎ ሰብ ይሰማማዕ</t>
+          <t>መንነቶም ኣረጋግጹ — ሓደ እኹል እዩ</t>
         </is>
       </c>
       <c r="G245" s="13" t="inlineStr">
         <is>
-          <t>Sawirka aqoonsiga wuxuu la mid yahay qofka wicitaanka ku jira</t>
+          <t>Ogow cidda ay yihiin — mid kasta</t>
         </is>
       </c>
       <c r="H245" s="14" t="inlineStr"/>
@@ -14755,7 +14755,7 @@
     <row r="246" ht="44" customHeight="1">
       <c r="A246" s="11" t="inlineStr">
         <is>
-          <t>chk_video_only</t>
+          <t>chk_id_document</t>
         </is>
       </c>
       <c r="B246" s="11" t="inlineStr">
@@ -14765,27 +14765,27 @@
       </c>
       <c r="C246" s="11" t="inlineStr">
         <is>
-          <t>video only</t>
+          <t>Fayda ID shown and matches the account name</t>
         </is>
       </c>
       <c r="D246" s="12" t="inlineStr">
         <is>
-          <t>ቪዲዮ ብቻ</t>
+          <t>የፋይዳ መታወቂያ ታይቷል እና ከሂሳቡ ስም ጋር ይዛመዳል</t>
         </is>
       </c>
       <c r="E246" s="13" t="inlineStr">
         <is>
-          <t>viidiyoo qofa</t>
+          <t>Waraqaan eenyummaa Fayda agarsiifame maqaa herregaa waliin walsimeera</t>
         </is>
       </c>
       <c r="F246" s="12" t="inlineStr">
         <is>
-          <t>ቪድዮ ጥራይ</t>
+          <t>መንነት ፋይዳ ተራእዩን ምስ ስም ሕሳብ ይሰማማዕን</t>
         </is>
       </c>
       <c r="G246" s="13" t="inlineStr">
         <is>
-          <t>fiidyow oo kaliya</t>
+          <t>Aqoonsiga Fayda waa la tusay wuxuuna la mid yahay magaca xisaabta</t>
         </is>
       </c>
       <c r="H246" s="14" t="inlineStr"/>
@@ -14793,7 +14793,7 @@
     <row r="247" ht="44" customHeight="1">
       <c r="A247" s="11" t="inlineStr">
         <is>
-          <t>confirm_account_theirs</t>
+          <t>chk_fayda_matched</t>
         </is>
       </c>
       <c r="B247" s="11" t="inlineStr">
@@ -14803,27 +14803,27 @@
       </c>
       <c r="C247" s="11" t="inlineStr">
         <is>
-          <t>And confirm the account is theirs</t>
+          <t>Fayda number matches the account record</t>
         </is>
       </c>
       <c r="D247" s="12" t="inlineStr">
         <is>
-          <t>እና ሂሳቡ የእነሱ መሆኑን ያረጋግጡ</t>
+          <t>የፋይዳ ቁጥር ከሂሳቡ መዝገብ ጋር ይዛመዳል</t>
         </is>
       </c>
       <c r="E247" s="13" t="inlineStr">
         <is>
-          <t>Akkasumas herregni kan isaanii ta'uu mirkaneessaa</t>
+          <t>Lakkoofsi Fayda galmee herregaa waliin walsimeera</t>
         </is>
       </c>
       <c r="F247" s="12" t="inlineStr">
         <is>
-          <t>ከምኡ'ውን እቲ ሕሳብ ናቶም ምዃኑ ኣረጋግጹ</t>
+          <t>ቁጽሪ ፋይዳ ምስ መዝገብ ሕሳብ ይሰማማዕ</t>
         </is>
       </c>
       <c r="G247" s="13" t="inlineStr">
         <is>
-          <t>Xaqiiji in xisaabtu tahay tooda</t>
+          <t>Lambarka Fayda wuxuu la mid yahay diiwaanka xisaabta</t>
         </is>
       </c>
       <c r="H247" s="14" t="inlineStr"/>
@@ -14831,7 +14831,7 @@
     <row r="248" ht="44" customHeight="1">
       <c r="A248" s="11" t="inlineStr">
         <is>
-          <t>confirm_identity</t>
+          <t>chk_fayda_matched_note</t>
         </is>
       </c>
       <c r="B248" s="11" t="inlineStr">
@@ -14841,27 +14841,27 @@
       </c>
       <c r="C248" s="11" t="inlineStr">
         <is>
-          <t>Confirm identity</t>
+          <t>on your own screen — works on an audio call</t>
         </is>
       </c>
       <c r="D248" s="12" t="inlineStr">
         <is>
-          <t>ማንነት አረጋግጥ</t>
+          <t>በራስዎ ስክሪን ላይ — በድምፅ ጥሪም ይሠራል</t>
         </is>
       </c>
       <c r="E248" s="13" t="inlineStr">
         <is>
-          <t>Eenyummaa mirkaneessi</t>
+          <t>iskiriinii keessan irratti — bilbila sagalee irrattis ni hojjeta</t>
         </is>
       </c>
       <c r="F248" s="12" t="inlineStr">
         <is>
-          <t>መንነት ኣረጋግጽ</t>
+          <t>ኣብ ናትኩም መርአዪ — ኣብ ናይ ድምጺ ጻውዒት እውን ይሰርሕ</t>
         </is>
       </c>
       <c r="G248" s="13" t="inlineStr">
         <is>
-          <t>Xaqiiji aqoonsiga</t>
+          <t>shaashaddaada — wicitaan cod ahna wuu ka shaqeeyaa</t>
         </is>
       </c>
       <c r="H248" s="14" t="inlineStr"/>
@@ -14869,7 +14869,7 @@
     <row r="249" ht="44" customHeight="1">
       <c r="A249" s="11" t="inlineStr">
         <is>
-          <t>unverified_scope</t>
+          <t>chk_id_photo</t>
         </is>
       </c>
       <c r="B249" s="11" t="inlineStr">
@@ -14879,27 +14879,27 @@
       </c>
       <c r="C249" s="11" t="inlineStr">
         <is>
-          <t>Until this is done you can only give general guidance — products, eligibility and how to apply.</t>
+          <t>Photo on the ID matches the person on the call</t>
         </is>
       </c>
       <c r="D249" s="12" t="inlineStr">
         <is>
-          <t>ይህ እስኪከናወን ድረስ አጠቃላይ መመሪያ ብቻ መስጠት ይችላሉ — ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል።</t>
+          <t>በመታወቂያው ላይ ያለው ፎቶ ከጥሪው ላይ ካለው ሰው ጋር ይዛመዳል</t>
         </is>
       </c>
       <c r="E249" s="13" t="inlineStr">
         <is>
-          <t>Hanga kun raawwatutti qajeelfama waliigalaa qofa kennuu dandeessu — oomishaalee, ulaagaa fi akkaataa itti iyyatan.</t>
+          <t>Suuraan waraqaa eenyummaa irra jiru nama bilbila irra jiru waliin walsimeera</t>
         </is>
       </c>
       <c r="F249" s="12" t="inlineStr">
         <is>
-          <t>እዚ ክሳብ ዝፍጸም ሓፈሻዊ መምርሒ ጥራይ ክትህቡ ትኽእሉ — ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን።</t>
+          <t>እቲ ኣብ መንነት ዘሎ ስእሊ ምስቲ ኣብ ጻውዒት ዘሎ ሰብ ይሰማማዕ</t>
         </is>
       </c>
       <c r="G249" s="13" t="inlineStr">
         <is>
-          <t>Ilaa tan la sameeyo waxaad kaliya bixin kartaa hagaajin guud — alaabta, u-qalmitaanka iyo sida loo codsado.</t>
+          <t>Sawirka aqoonsiga wuxuu la mid yahay qofka wicitaanka ku jira</t>
         </is>
       </c>
       <c r="H249" s="14" t="inlineStr"/>
@@ -14907,7 +14907,7 @@
     <row r="250" ht="44" customHeight="1">
       <c r="A250" s="11" t="inlineStr">
         <is>
-          <t>fayda_number_required</t>
+          <t>chk_video_only</t>
         </is>
       </c>
       <c r="B250" s="11" t="inlineStr">
@@ -14917,27 +14917,27 @@
       </c>
       <c r="C250" s="11" t="inlineStr">
         <is>
-          <t>Fayda number (required — it is what the record keeps)</t>
+          <t>video only</t>
         </is>
       </c>
       <c r="D250" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ ቁጥር (ያስፈልጋል — መዝገቡ የሚይዘው ይህ ነው)</t>
+          <t>ቪዲዮ ብቻ</t>
         </is>
       </c>
       <c r="E250" s="13" t="inlineStr">
         <is>
-          <t>Lakkoofsa Fayda (barbaachisaa — kan galmeen qabatu isa kana)</t>
+          <t>viidiyoo qofa</t>
         </is>
       </c>
       <c r="F250" s="12" t="inlineStr">
         <is>
-          <t>ቁጽሪ ፋይዳ (የድሊ — እቲ መዝገብ ዝሕዞ እዚ እዩ)</t>
+          <t>ቪድዮ ጥራይ</t>
         </is>
       </c>
       <c r="G250" s="13" t="inlineStr">
         <is>
-          <t>Lambarka Fayda (loo baahan yahay — waa waxa diiwaanku hayo)</t>
+          <t>fiidyow oo kaliya</t>
         </is>
       </c>
       <c r="H250" s="14" t="inlineStr"/>
@@ -14945,7 +14945,7 @@
     <row r="251" ht="44" customHeight="1">
       <c r="A251" s="11" t="inlineStr">
         <is>
-          <t>download_for_translation</t>
+          <t>confirm_account_theirs</t>
         </is>
       </c>
       <c r="B251" s="11" t="inlineStr">
@@ -14955,27 +14955,27 @@
       </c>
       <c r="C251" s="11" t="inlineStr">
         <is>
-          <t>Download for translation</t>
+          <t>And confirm the account is theirs</t>
         </is>
       </c>
       <c r="D251" s="12" t="inlineStr">
         <is>
-          <t>ለትርጉም አውርድ</t>
+          <t>እና ሂሳቡ የእነሱ መሆኑን ያረጋግጡ</t>
         </is>
       </c>
       <c r="E251" s="13" t="inlineStr">
         <is>
-          <t>Hiikkaaf buufadhu</t>
+          <t>Akkasumas herregni kan isaanii ta'uu mirkaneessaa</t>
         </is>
       </c>
       <c r="F251" s="12" t="inlineStr">
         <is>
-          <t>ንትርጉም ኣውርድ</t>
+          <t>ከምኡ'ውን እቲ ሕሳብ ናቶም ምዃኑ ኣረጋግጹ</t>
         </is>
       </c>
       <c r="G251" s="13" t="inlineStr">
         <is>
-          <t>Soo dejiso turjumaadda</t>
+          <t>Xaqiiji in xisaabtu tahay tooda</t>
         </is>
       </c>
       <c r="H251" s="14" t="inlineStr"/>
@@ -14983,43 +14983,195 @@
     <row r="252" ht="44" customHeight="1">
       <c r="A252" s="11" t="inlineStr">
         <is>
+          <t>confirm_identity</t>
+        </is>
+      </c>
+      <c r="B252" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C252" s="11" t="inlineStr">
+        <is>
+          <t>Confirm identity</t>
+        </is>
+      </c>
+      <c r="D252" s="12" t="inlineStr">
+        <is>
+          <t>ማንነት አረጋግጥ</t>
+        </is>
+      </c>
+      <c r="E252" s="13" t="inlineStr">
+        <is>
+          <t>Eenyummaa mirkaneessi</t>
+        </is>
+      </c>
+      <c r="F252" s="12" t="inlineStr">
+        <is>
+          <t>መንነት ኣረጋግጽ</t>
+        </is>
+      </c>
+      <c r="G252" s="13" t="inlineStr">
+        <is>
+          <t>Xaqiiji aqoonsiga</t>
+        </is>
+      </c>
+      <c r="H252" s="14" t="inlineStr"/>
+    </row>
+    <row r="253" ht="44" customHeight="1">
+      <c r="A253" s="11" t="inlineStr">
+        <is>
+          <t>unverified_scope</t>
+        </is>
+      </c>
+      <c r="B253" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C253" s="11" t="inlineStr">
+        <is>
+          <t>Until this is done you can only give general guidance — products, eligibility and how to apply.</t>
+        </is>
+      </c>
+      <c r="D253" s="12" t="inlineStr">
+        <is>
+          <t>ይህ እስኪከናወን ድረስ አጠቃላይ መመሪያ ብቻ መስጠት ይችላሉ — ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል።</t>
+        </is>
+      </c>
+      <c r="E253" s="13" t="inlineStr">
+        <is>
+          <t>Hanga kun raawwatutti qajeelfama waliigalaa qofa kennuu dandeessu — oomishaalee, ulaagaa fi akkaataa itti iyyatan.</t>
+        </is>
+      </c>
+      <c r="F253" s="12" t="inlineStr">
+        <is>
+          <t>እዚ ክሳብ ዝፍጸም ሓፈሻዊ መምርሒ ጥራይ ክትህቡ ትኽእሉ — ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን።</t>
+        </is>
+      </c>
+      <c r="G253" s="13" t="inlineStr">
+        <is>
+          <t>Ilaa tan la sameeyo waxaad kaliya bixin kartaa hagaajin guud — alaabta, u-qalmitaanka iyo sida loo codsado.</t>
+        </is>
+      </c>
+      <c r="H253" s="14" t="inlineStr"/>
+    </row>
+    <row r="254" ht="44" customHeight="1">
+      <c r="A254" s="11" t="inlineStr">
+        <is>
+          <t>fayda_number_required</t>
+        </is>
+      </c>
+      <c r="B254" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C254" s="11" t="inlineStr">
+        <is>
+          <t>Fayda number (required — it is what the record keeps)</t>
+        </is>
+      </c>
+      <c r="D254" s="12" t="inlineStr">
+        <is>
+          <t>የፋይዳ ቁጥር (ያስፈልጋል — መዝገቡ የሚይዘው ይህ ነው)</t>
+        </is>
+      </c>
+      <c r="E254" s="13" t="inlineStr">
+        <is>
+          <t>Lakkoofsa Fayda (barbaachisaa — kan galmeen qabatu isa kana)</t>
+        </is>
+      </c>
+      <c r="F254" s="12" t="inlineStr">
+        <is>
+          <t>ቁጽሪ ፋይዳ (የድሊ — እቲ መዝገብ ዝሕዞ እዚ እዩ)</t>
+        </is>
+      </c>
+      <c r="G254" s="13" t="inlineStr">
+        <is>
+          <t>Lambarka Fayda (loo baahan yahay — waa waxa diiwaanku hayo)</t>
+        </is>
+      </c>
+      <c r="H254" s="14" t="inlineStr"/>
+    </row>
+    <row r="255" ht="44" customHeight="1">
+      <c r="A255" s="11" t="inlineStr">
+        <is>
+          <t>download_for_translation</t>
+        </is>
+      </c>
+      <c r="B255" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C255" s="11" t="inlineStr">
+        <is>
+          <t>Download for translation</t>
+        </is>
+      </c>
+      <c r="D255" s="12" t="inlineStr">
+        <is>
+          <t>ለትርጉም አውርድ</t>
+        </is>
+      </c>
+      <c r="E255" s="13" t="inlineStr">
+        <is>
+          <t>Hiikkaaf buufadhu</t>
+        </is>
+      </c>
+      <c r="F255" s="12" t="inlineStr">
+        <is>
+          <t>ንትርጉም ኣውርድ</t>
+        </is>
+      </c>
+      <c r="G255" s="13" t="inlineStr">
+        <is>
+          <t>Soo dejiso turjumaadda</t>
+        </is>
+      </c>
+      <c r="H255" s="14" t="inlineStr"/>
+    </row>
+    <row r="256" ht="44" customHeight="1">
+      <c r="A256" s="11" t="inlineStr">
+        <is>
           <t>nothing_to_download</t>
         </is>
       </c>
-      <c r="B252" s="11" t="inlineStr">
-        <is>
-          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
-        </is>
-      </c>
-      <c r="C252" s="11" t="inlineStr">
+      <c r="B256" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C256" s="11" t="inlineStr">
         <is>
           <t>No approved answers to download yet.</t>
         </is>
       </c>
-      <c r="D252" s="12" t="inlineStr">
+      <c r="D256" s="12" t="inlineStr">
         <is>
           <t>እስካሁን የሚወርድ የተፈቀደ መልስ የለም።</t>
         </is>
       </c>
-      <c r="E252" s="13" t="inlineStr">
+      <c r="E256" s="13" t="inlineStr">
         <is>
           <t>Hanga ammaatti deebiin mirkanaa'e buufamu hin jiru.</t>
         </is>
       </c>
-      <c r="F252" s="12" t="inlineStr">
+      <c r="F256" s="12" t="inlineStr">
         <is>
           <t>ክሳብ ሕጂ ዝወርድ ዝጸደቐ መልሲ የለን።</t>
         </is>
       </c>
-      <c r="G252" s="13" t="inlineStr">
+      <c r="G256" s="13" t="inlineStr">
         <is>
           <t>Weli ma jiraan jawaabo la ansixiyay oo la soo dejiyo.</t>
         </is>
       </c>
-      <c r="H252" s="14" t="inlineStr"/>
+      <c r="H256" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H252"/>
+  <autoFilter ref="A1:H256"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/review/Olink_Bank_Assist_language_review.xlsx
+++ b/review/Olink_Bank_Assist_language_review.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1. What the assistant says'!$A$1:$H$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2. What it understands'!$A$1:$E$78</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3. Buttons customers see'!$A$1:$H$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$H$256</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$H$257</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -752,7 +752,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>324 strings in 5 languages</t>
+          <t>325 strings in 5 languages</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H256"/>
+  <dimension ref="A1:H257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9131,7 +9131,7 @@
     <row r="98" ht="44" customHeight="1">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>languages</t>
+          <t>view_conversations</t>
         </is>
       </c>
       <c r="B98" s="11" t="inlineStr">
@@ -9141,27 +9141,27 @@
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>Languages</t>
+          <t>View Conversations</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>ቋንቋዎች</t>
+          <t>ውይይቶችን ይመልከቱ</t>
         </is>
       </c>
       <c r="E98" s="13" t="inlineStr">
         <is>
-          <t>Afaanota</t>
+          <t>Haasawaa Ilaali</t>
         </is>
       </c>
       <c r="F98" s="12" t="inlineStr">
         <is>
-          <t>ቋንቋታት</t>
+          <t>ዝርርባት ርአ</t>
         </is>
       </c>
       <c r="G98" s="13" t="inlineStr">
         <is>
-          <t>Luqadaha</t>
+          <t>Fiiri Wadahadalada</t>
         </is>
       </c>
       <c r="H98" s="14" t="inlineStr"/>
@@ -9169,7 +9169,7 @@
     <row r="99" ht="44" customHeight="1">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>unit_conversations</t>
+          <t>languages</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
@@ -9179,27 +9179,27 @@
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>conversations</t>
+          <t>Languages</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>ውይይቶች</t>
+          <t>ቋንቋዎች</t>
         </is>
       </c>
       <c r="E99" s="13" t="inlineStr">
         <is>
-          <t>marii</t>
+          <t>Afaanota</t>
         </is>
       </c>
       <c r="F99" s="12" t="inlineStr">
         <is>
-          <t>ዝርርባት</t>
+          <t>ቋንቋታት</t>
         </is>
       </c>
       <c r="G99" s="13" t="inlineStr">
         <is>
-          <t>wadahadallo</t>
+          <t>Luqadaha</t>
         </is>
       </c>
       <c r="H99" s="14" t="inlineStr"/>
@@ -9207,7 +9207,7 @@
     <row r="100" ht="44" customHeight="1">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>unit_questions</t>
+          <t>unit_conversations</t>
         </is>
       </c>
       <c r="B100" s="11" t="inlineStr">
@@ -9217,27 +9217,27 @@
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>conversations</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>ጥያቄዎች</t>
+          <t>ውይይቶች</t>
         </is>
       </c>
       <c r="E100" s="13" t="inlineStr">
         <is>
-          <t>gaaffiiwwan</t>
+          <t>marii</t>
         </is>
       </c>
       <c r="F100" s="12" t="inlineStr">
         <is>
-          <t>ሕቶታት</t>
+          <t>ዝርርባት</t>
         </is>
       </c>
       <c r="G100" s="13" t="inlineStr">
         <is>
-          <t>su'aalaha</t>
+          <t>wadahadallo</t>
         </is>
       </c>
       <c r="H100" s="14" t="inlineStr"/>
@@ -9245,7 +9245,7 @@
     <row r="101" ht="44" customHeight="1">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>donut_all_in</t>
+          <t>unit_questions</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
@@ -9255,27 +9255,27 @@
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>All {n} {unit} were in {label}.</t>
+          <t>questions</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>ሁሉም {n} {unit} በ{label} ነበሩ።</t>
+          <t>ጥያቄዎች</t>
         </is>
       </c>
       <c r="E101" s="13" t="inlineStr">
         <is>
-          <t>{unit} {n} hundi {label} keessa turan.</t>
+          <t>gaaffiiwwan</t>
         </is>
       </c>
       <c r="F101" s="12" t="inlineStr">
         <is>
-          <t>ኩሎም {n} {unit} ብ{label} ነይሮም።</t>
+          <t>ሕቶታት</t>
         </is>
       </c>
       <c r="G101" s="13" t="inlineStr">
         <is>
-          <t>Dhammaan {n} {unit} waxay ku jireen {label}.</t>
+          <t>su'aalaha</t>
         </is>
       </c>
       <c r="H101" s="14" t="inlineStr"/>
@@ -9283,7 +9283,7 @@
     <row r="102" ht="44" customHeight="1">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>conversations_by_language</t>
+          <t>donut_all_in</t>
         </is>
       </c>
       <c r="B102" s="11" t="inlineStr">
@@ -9293,27 +9293,27 @@
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>Conversations by language</t>
+          <t>All {n} {unit} were in {label}.</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
         <is>
-          <t>በቋንቋ የተከፋፈሉ ውይይቶች</t>
+          <t>ሁሉም {n} {unit} በ{label} ነበሩ።</t>
         </is>
       </c>
       <c r="E102" s="13" t="inlineStr">
         <is>
-          <t>Marii afaaniin</t>
+          <t>{unit} {n} hundi {label} keessa turan.</t>
         </is>
       </c>
       <c r="F102" s="12" t="inlineStr">
         <is>
-          <t>ዝርርባት ብቋንቋ</t>
+          <t>ኩሎም {n} {unit} ብ{label} ነይሮም።</t>
         </is>
       </c>
       <c r="G102" s="13" t="inlineStr">
         <is>
-          <t>Wadahadallada luqadda</t>
+          <t>Dhammaan {n} {unit} waxay ku jireen {label}.</t>
         </is>
       </c>
       <c r="H102" s="14" t="inlineStr"/>
@@ -9321,7 +9321,7 @@
     <row r="103" ht="44" customHeight="1">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>no_conversations_window</t>
+          <t>conversations_by_language</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
@@ -9331,27 +9331,27 @@
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>No conversations yet in this window.</t>
+          <t>Conversations by language</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>በዚህ ጊዜ ውስጥ ውይይት የለም።</t>
+          <t>በቋንቋ የተከፋፈሉ ውይይቶች</t>
         </is>
       </c>
       <c r="E103" s="13" t="inlineStr">
         <is>
-          <t>Yeroo kana keessatti mariin hin jiru.</t>
+          <t>Marii afaaniin</t>
         </is>
       </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
-          <t>ኣብዚ እዋን'ዚ ዝርርብ የለን።</t>
+          <t>ዝርርባት ብቋንቋ</t>
         </is>
       </c>
       <c r="G103" s="13" t="inlineStr">
         <is>
-          <t>Waqtigan wadahadal ma jiro.</t>
+          <t>Wadahadallada luqadda</t>
         </is>
       </c>
       <c r="H103" s="14" t="inlineStr"/>
@@ -9359,7 +9359,7 @@
     <row r="104" ht="44" customHeight="1">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>recent_activity</t>
+          <t>no_conversations_window</t>
         </is>
       </c>
       <c r="B104" s="11" t="inlineStr">
@@ -9369,27 +9369,27 @@
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>Recent activity</t>
+          <t>No conversations yet in this window.</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
         <is>
-          <t>የቅርብ ጊዜ እንቅስቃሴ</t>
+          <t>በዚህ ጊዜ ውስጥ ውይይት የለም።</t>
         </is>
       </c>
       <c r="E104" s="13" t="inlineStr">
         <is>
-          <t>Sochii dhiyoo</t>
+          <t>Yeroo kana keessatti mariin hin jiru.</t>
         </is>
       </c>
       <c r="F104" s="12" t="inlineStr">
         <is>
-          <t>ናይ ቀረባ እዋን ንጥፈት</t>
+          <t>ኣብዚ እዋን'ዚ ዝርርብ የለን።</t>
         </is>
       </c>
       <c r="G104" s="13" t="inlineStr">
         <is>
-          <t>Dhaqdhaqaaqa dhawaan</t>
+          <t>Waqtigan wadahadal ma jiro.</t>
         </is>
       </c>
       <c r="H104" s="14" t="inlineStr"/>
@@ -9397,7 +9397,7 @@
     <row r="105" ht="44" customHeight="1">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>live_preview</t>
+          <t>recent_activity</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
@@ -9407,27 +9407,27 @@
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Live preview</t>
+          <t>Recent activity</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>የቀጥታ ዕይታ</t>
+          <t>የቅርብ ጊዜ እንቅስቃሴ</t>
         </is>
       </c>
       <c r="E105" s="13" t="inlineStr">
         <is>
-          <t>Mul'ata kallattii</t>
+          <t>Sochii dhiyoo</t>
         </is>
       </c>
       <c r="F105" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታ ትርኢት</t>
+          <t>ናይ ቀረባ እዋን ንጥፈት</t>
         </is>
       </c>
       <c r="G105" s="13" t="inlineStr">
         <is>
-          <t>Muuqaal toos ah</t>
+          <t>Dhaqdhaqaaqa dhawaan</t>
         </is>
       </c>
       <c r="H105" s="14" t="inlineStr"/>
@@ -9435,7 +9435,7 @@
     <row r="106" ht="44" customHeight="1">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>assistant_preview</t>
+          <t>live_preview</t>
         </is>
       </c>
       <c r="B106" s="11" t="inlineStr">
@@ -9445,27 +9445,27 @@
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>Assistant preview</t>
+          <t>Live preview</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
         <is>
-          <t>የረዳት ዕይታ</t>
+          <t>የቀጥታ ዕይታ</t>
         </is>
       </c>
       <c r="E106" s="13" t="inlineStr">
         <is>
-          <t>Mul'ata gargaaraa</t>
+          <t>Mul'ata kallattii</t>
         </is>
       </c>
       <c r="F106" s="12" t="inlineStr">
         <is>
-          <t>ትርኢት ሓጋዚ</t>
+          <t>ቀጥታ ትርኢት</t>
         </is>
       </c>
       <c r="G106" s="13" t="inlineStr">
         <is>
-          <t>Muuqaalka kaaliyaha</t>
+          <t>Muuqaal toos ah</t>
         </is>
       </c>
       <c r="H106" s="14" t="inlineStr"/>
@@ -9473,7 +9473,7 @@
     <row r="107" ht="44" customHeight="1">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>preview_caption</t>
+          <t>assistant_preview</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
@@ -9483,27 +9483,27 @@
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Exactly what a customer sees on your website. Messages sent here are real and appear in Conversations.</t>
+          <t>Assistant preview</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛ በድረ-ገጽዎ ላይ የሚያየው በትክክል ይህ ነው። እዚህ የሚላኩ መልእክቶች እውነተኛ ናቸው እና በውይይቶች ውስጥ ይታያሉ።</t>
+          <t>የረዳት ዕይታ</t>
         </is>
       </c>
       <c r="E107" s="13" t="inlineStr">
         <is>
-          <t>Waanuma maamiltoonni marsariitii keessan irratti argan. Ergaan asitti ergamu dhugaadha, Marii keessattis ni mul'ata.</t>
+          <t>Mul'ata gargaaraa</t>
         </is>
       </c>
       <c r="F107" s="12" t="inlineStr">
         <is>
-          <t>ልክዕ ከምቲ ዓሚል ኣብ መርበብ ሓበሬታኹም ዝርእዮ። ኣብዚ ዝለኣኹ መልእኽትታት ናይ ሓቂ ኮይኖም ኣብ ዝርርባት ይረኣዩ።</t>
+          <t>ትርኢት ሓጋዚ</t>
         </is>
       </c>
       <c r="G107" s="13" t="inlineStr">
         <is>
-          <t>Waa waxa uu macmiilku ku arko degelkaaga. Fariimaha halkan laga diro waa dhab, waxayna ka muuqdaan Wadahadallada.</t>
+          <t>Muuqaalka kaaliyaha</t>
         </is>
       </c>
       <c r="H107" s="14" t="inlineStr"/>
@@ -9511,7 +9511,7 @@
     <row r="108" ht="44" customHeight="1">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>n_conversations</t>
+          <t>preview_caption</t>
         </is>
       </c>
       <c r="B108" s="11" t="inlineStr">
@@ -9521,27 +9521,27 @@
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>{n} conversations</t>
+          <t>Exactly what a customer sees on your website. Messages sent here are real and appear in Conversations.</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>{n} ውይይቶች</t>
+          <t>ደንበኛ በድረ-ገጽዎ ላይ የሚያየው በትክክል ይህ ነው። እዚህ የሚላኩ መልእክቶች እውነተኛ ናቸው እና በውይይቶች ውስጥ ይታያሉ።</t>
         </is>
       </c>
       <c r="E108" s="13" t="inlineStr">
         <is>
-          <t>Marii {n}</t>
+          <t>Waanuma maamiltoonni marsariitii keessan irratti argan. Ergaan asitti ergamu dhugaadha, Marii keessattis ni mul'ata.</t>
         </is>
       </c>
       <c r="F108" s="12" t="inlineStr">
         <is>
-          <t>{n} ዝርርባት</t>
+          <t>ልክዕ ከምቲ ዓሚል ኣብ መርበብ ሓበሬታኹም ዝርእዮ። ኣብዚ ዝለኣኹ መልእኽትታት ናይ ሓቂ ኮይኖም ኣብ ዝርርባት ይረኣዩ።</t>
         </is>
       </c>
       <c r="G108" s="13" t="inlineStr">
         <is>
-          <t>{n} wadahadal</t>
+          <t>Waa waxa uu macmiilku ku arko degelkaaga. Fariimaha halkan laga diro waa dhab, waxayna ka muuqdaan Wadahadallada.</t>
         </is>
       </c>
       <c r="H108" s="14" t="inlineStr"/>
@@ -9549,7 +9549,7 @@
     <row r="109" ht="44" customHeight="1">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>one_conversation</t>
+          <t>n_conversations</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>{n} conversation</t>
+          <t>{n} conversations</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>{n} ውይይት</t>
+          <t>{n} ውይይቶች</t>
         </is>
       </c>
       <c r="E109" s="13" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="F109" s="12" t="inlineStr">
         <is>
-          <t>{n} ዝርርብ</t>
+          <t>{n} ዝርርባት</t>
         </is>
       </c>
       <c r="G109" s="13" t="inlineStr">
@@ -9587,7 +9587,7 @@
     <row r="110" ht="44" customHeight="1">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>outcome_answered</t>
+          <t>one_conversation</t>
         </is>
       </c>
       <c r="B110" s="11" t="inlineStr">
@@ -9597,27 +9597,27 @@
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>Answered from your content</t>
+          <t>{n} conversation</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>ከይዘትዎ የተመለሰ</t>
+          <t>{n} ውይይት</t>
         </is>
       </c>
       <c r="E110" s="13" t="inlineStr">
         <is>
-          <t>Qabiyyee keessan irraa deebi'e</t>
+          <t>Marii {n}</t>
         </is>
       </c>
       <c r="F110" s="12" t="inlineStr">
         <is>
-          <t>ካብ ትሕዝቶኹም ዝተመለሰ</t>
+          <t>{n} ዝርርብ</t>
         </is>
       </c>
       <c r="G110" s="13" t="inlineStr">
         <is>
-          <t>Laga jawaabay macluumaadkaaga</t>
+          <t>{n} wadahadal</t>
         </is>
       </c>
       <c r="H110" s="14" t="inlineStr"/>
@@ -9625,7 +9625,7 @@
     <row r="111" ht="44" customHeight="1">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>outcome_general_guidance</t>
+          <t>outcome_answered</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
@@ -9635,27 +9635,27 @@
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Answered from general banking knowledge</t>
+          <t>Answered from your content</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>ከአጠቃላይ የባንክ እውቀት የተመለሰ</t>
+          <t>ከይዘትዎ የተመለሰ</t>
         </is>
       </c>
       <c r="E111" s="13" t="inlineStr">
         <is>
-          <t>Beekumsa baankii waliigalaa irraa deebi'e</t>
+          <t>Qabiyyee keessan irraa deebi'e</t>
         </is>
       </c>
       <c r="F111" s="12" t="inlineStr">
         <is>
-          <t>ካብ ሓፈሻዊ ፍልጠት ባንክ ዝተመለሰ</t>
+          <t>ካብ ትሕዝቶኹም ዝተመለሰ</t>
         </is>
       </c>
       <c r="G111" s="13" t="inlineStr">
         <is>
-          <t>Laga jawaabay aqoonta guud ee bangiga</t>
+          <t>Laga jawaabay macluumaadkaaga</t>
         </is>
       </c>
       <c r="H111" s="14" t="inlineStr"/>
@@ -9663,7 +9663,7 @@
     <row r="112" ht="44" customHeight="1">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>outcome_unanswered</t>
+          <t>outcome_general_guidance</t>
         </is>
       </c>
       <c r="B112" s="11" t="inlineStr">
@@ -9673,27 +9673,27 @@
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>Could not answer</t>
+          <t>Answered from general banking knowledge</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr">
         <is>
-          <t>መልስ ማግኘት አልተቻለም</t>
+          <t>ከአጠቃላይ የባንክ እውቀት የተመለሰ</t>
         </is>
       </c>
       <c r="E112" s="13" t="inlineStr">
         <is>
-          <t>Deebisuu hin dandeenye</t>
+          <t>Beekumsa baankii waliigalaa irraa deebi'e</t>
         </is>
       </c>
       <c r="F112" s="12" t="inlineStr">
         <is>
-          <t>መልሲ ክርከብ ኣይተኻእለን</t>
+          <t>ካብ ሓፈሻዊ ፍልጠት ባንክ ዝተመለሰ</t>
         </is>
       </c>
       <c r="G112" s="13" t="inlineStr">
         <is>
-          <t>Lama jawaabi karin</t>
+          <t>Laga jawaabay aqoonta guud ee bangiga</t>
         </is>
       </c>
       <c r="H112" s="14" t="inlineStr"/>
@@ -9701,7 +9701,7 @@
     <row r="113" ht="44" customHeight="1">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>outcome_complaint</t>
+          <t>outcome_unanswered</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
@@ -9711,27 +9711,27 @@
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Could not answer</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>ቅሬታ</t>
+          <t>መልስ ማግኘት አልተቻለም</t>
         </is>
       </c>
       <c r="E113" s="13" t="inlineStr">
         <is>
-          <t>Komii</t>
+          <t>Deebisuu hin dandeenye</t>
         </is>
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
-          <t>ጥርዓን</t>
+          <t>መልሲ ክርከብ ኣይተኻእለን</t>
         </is>
       </c>
       <c r="G113" s="13" t="inlineStr">
         <is>
-          <t>Cabasho</t>
+          <t>Lama jawaabi karin</t>
         </is>
       </c>
       <c r="H113" s="14" t="inlineStr"/>
@@ -9739,7 +9739,7 @@
     <row r="114" ht="44" customHeight="1">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>outcome_account_blocked</t>
+          <t>outcome_complaint</t>
         </is>
       </c>
       <c r="B114" s="11" t="inlineStr">
@@ -9749,27 +9749,27 @@
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>Account access problem</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="D114" s="12" t="inlineStr">
         <is>
-          <t>የመለያ መግቢያ ችግር</t>
+          <t>ቅሬታ</t>
         </is>
       </c>
       <c r="E114" s="13" t="inlineStr">
         <is>
-          <t>Rakkoo herrega seenuu</t>
+          <t>Komii</t>
         </is>
       </c>
       <c r="F114" s="12" t="inlineStr">
         <is>
-          <t>ጸገም ኣታውነት ሕሳብ</t>
+          <t>ጥርዓን</t>
         </is>
       </c>
       <c r="G114" s="13" t="inlineStr">
         <is>
-          <t>Dhibaato gelitaanka xisaabta</t>
+          <t>Cabasho</t>
         </is>
       </c>
       <c r="H114" s="14" t="inlineStr"/>
@@ -9777,7 +9777,7 @@
     <row r="115" ht="44" customHeight="1">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>outcome_comparison</t>
+          <t>outcome_account_blocked</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
@@ -9787,27 +9787,27 @@
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Compared with another bank</t>
+          <t>Account access problem</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>ከሌላ ባንክ ጋር ተነጻጽሯል</t>
+          <t>የመለያ መግቢያ ችግር</t>
         </is>
       </c>
       <c r="E115" s="13" t="inlineStr">
         <is>
-          <t>Baankii biraa waliin walbira qabame</t>
+          <t>Rakkoo herrega seenuu</t>
         </is>
       </c>
       <c r="F115" s="12" t="inlineStr">
         <is>
-          <t>ምስ ካልእ ባንክ ተነጻጺሩ</t>
+          <t>ጸገም ኣታውነት ሕሳብ</t>
         </is>
       </c>
       <c r="G115" s="13" t="inlineStr">
         <is>
-          <t>Lala barbardhigay bangi kale</t>
+          <t>Dhibaato gelitaanka xisaabta</t>
         </is>
       </c>
       <c r="H115" s="14" t="inlineStr"/>
@@ -9815,7 +9815,7 @@
     <row r="116" ht="44" customHeight="1">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>outcome_greeting</t>
+          <t>outcome_comparison</t>
         </is>
       </c>
       <c r="B116" s="11" t="inlineStr">
@@ -9825,27 +9825,27 @@
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>Greeting</t>
+          <t>Compared with another bank</t>
         </is>
       </c>
       <c r="D116" s="12" t="inlineStr">
         <is>
-          <t>ሰላምታ</t>
+          <t>ከሌላ ባንክ ጋር ተነጻጽሯል</t>
         </is>
       </c>
       <c r="E116" s="13" t="inlineStr">
         <is>
-          <t>Nagaa</t>
+          <t>Baankii biraa waliin walbira qabame</t>
         </is>
       </c>
       <c r="F116" s="12" t="inlineStr">
         <is>
-          <t>ሰላምታ</t>
+          <t>ምስ ካልእ ባንክ ተነጻጺሩ</t>
         </is>
       </c>
       <c r="G116" s="13" t="inlineStr">
         <is>
-          <t>Salaan</t>
+          <t>Lala barbardhigay bangi kale</t>
         </is>
       </c>
       <c r="H116" s="14" t="inlineStr"/>
@@ -9853,7 +9853,7 @@
     <row r="117" ht="44" customHeight="1">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>outcome_contact_captured</t>
+          <t>outcome_greeting</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
@@ -9863,27 +9863,27 @@
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Contact details captured</t>
+          <t>Greeting</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>የመገናኛ መረጃ ተመዝግቧል</t>
+          <t>ሰላምታ</t>
         </is>
       </c>
       <c r="E117" s="13" t="inlineStr">
         <is>
-          <t>Odeeffannoon quunnamtii galmaa'e</t>
+          <t>Nagaa</t>
         </is>
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
-          <t>ሓበሬታ መራኸቢ ተመዝጊቡ</t>
+          <t>ሰላምታ</t>
         </is>
       </c>
       <c r="G117" s="13" t="inlineStr">
         <is>
-          <t>Xogta xiriirka waa la diiwaangeliyay</t>
+          <t>Salaan</t>
         </is>
       </c>
       <c r="H117" s="14" t="inlineStr"/>
@@ -9891,7 +9891,7 @@
     <row r="118" ht="44" customHeight="1">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>outcome_human_request</t>
+          <t>outcome_contact_captured</t>
         </is>
       </c>
       <c r="B118" s="11" t="inlineStr">
@@ -9901,27 +9901,27 @@
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>Asked for a person</t>
+          <t>Contact details captured</t>
         </is>
       </c>
       <c r="D118" s="12" t="inlineStr">
         <is>
-          <t>ሰው ተጠይቋል</t>
+          <t>የመገናኛ መረጃ ተመዝግቧል</t>
         </is>
       </c>
       <c r="E118" s="13" t="inlineStr">
         <is>
-          <t>Nama gaafate</t>
+          <t>Odeeffannoon quunnamtii galmaa'e</t>
         </is>
       </c>
       <c r="F118" s="12" t="inlineStr">
         <is>
-          <t>ሰብ ተሓቲቱ</t>
+          <t>ሓበሬታ መራኸቢ ተመዝጊቡ</t>
         </is>
       </c>
       <c r="G118" s="13" t="inlineStr">
         <is>
-          <t>Qof ayaa la codsaday</t>
+          <t>Xogta xiriirka waa la diiwaangeliyay</t>
         </is>
       </c>
       <c r="H118" s="14" t="inlineStr"/>
@@ -9929,7 +9929,7 @@
     <row r="119" ht="44" customHeight="1">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>reason_complaint</t>
+          <t>outcome_human_request</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
@@ -9939,27 +9939,27 @@
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Asked for a person</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>ቅሬታ</t>
+          <t>ሰው ተጠይቋል</t>
         </is>
       </c>
       <c r="E119" s="13" t="inlineStr">
         <is>
-          <t>Komii</t>
+          <t>Nama gaafate</t>
         </is>
       </c>
       <c r="F119" s="12" t="inlineStr">
         <is>
-          <t>ጥርዓን</t>
+          <t>ሰብ ተሓቲቱ</t>
         </is>
       </c>
       <c r="G119" s="13" t="inlineStr">
         <is>
-          <t>Cabasho</t>
+          <t>Qof ayaa la codsaday</t>
         </is>
       </c>
       <c r="H119" s="14" t="inlineStr"/>
@@ -9967,7 +9967,7 @@
     <row r="120" ht="44" customHeight="1">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>reason_human_requested</t>
+          <t>reason_complaint</t>
         </is>
       </c>
       <c r="B120" s="11" t="inlineStr">
@@ -9977,27 +9977,27 @@
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>Asked for a person</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="D120" s="12" t="inlineStr">
         <is>
-          <t>ሰው ተጠይቋል</t>
+          <t>ቅሬታ</t>
         </is>
       </c>
       <c r="E120" s="13" t="inlineStr">
         <is>
-          <t>Nama gaafate</t>
+          <t>Komii</t>
         </is>
       </c>
       <c r="F120" s="12" t="inlineStr">
         <is>
-          <t>ሰብ ተሓቲቱ</t>
+          <t>ጥርዓን</t>
         </is>
       </c>
       <c r="G120" s="13" t="inlineStr">
         <is>
-          <t>Qof ayaa la codsaday</t>
+          <t>Cabasho</t>
         </is>
       </c>
       <c r="H120" s="14" t="inlineStr"/>
@@ -10005,7 +10005,7 @@
     <row r="121" ht="44" customHeight="1">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>reason_unanswered_question</t>
+          <t>reason_human_requested</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
@@ -10015,27 +10015,27 @@
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>No answer in your content</t>
+          <t>Asked for a person</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>በይዘትዎ ውስጥ መልስ የለም</t>
+          <t>ሰው ተጠይቋል</t>
         </is>
       </c>
       <c r="E121" s="13" t="inlineStr">
         <is>
-          <t>Qabiyyee keessan keessa deebiin hin jiru</t>
+          <t>Nama gaafate</t>
         </is>
       </c>
       <c r="F121" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ትሕዝቶኹም መልሲ የለን</t>
+          <t>ሰብ ተሓቲቱ</t>
         </is>
       </c>
       <c r="G121" s="13" t="inlineStr">
         <is>
-          <t>Macluumaadkaaga jawaab kuma jirto</t>
+          <t>Qof ayaa la codsaday</t>
         </is>
       </c>
       <c r="H121" s="14" t="inlineStr"/>
@@ -10043,7 +10043,7 @@
     <row r="122" ht="44" customHeight="1">
       <c r="A122" s="11" t="inlineStr">
         <is>
-          <t>reason_answered_from_general_knowledge</t>
+          <t>reason_unanswered_question</t>
         </is>
       </c>
       <c r="B122" s="11" t="inlineStr">
@@ -10053,27 +10053,27 @@
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>Answered from general knowledge</t>
+          <t>No answer in your content</t>
         </is>
       </c>
       <c r="D122" s="12" t="inlineStr">
         <is>
-          <t>ከአጠቃላይ እውቀት የተመለሰ</t>
+          <t>በይዘትዎ ውስጥ መልስ የለም</t>
         </is>
       </c>
       <c r="E122" s="13" t="inlineStr">
         <is>
-          <t>Beekumsa waliigalaa irraa deebi'e</t>
+          <t>Qabiyyee keessan keessa deebiin hin jiru</t>
         </is>
       </c>
       <c r="F122" s="12" t="inlineStr">
         <is>
-          <t>ካብ ሓፈሻዊ ፍልጠት ዝተመለሰ</t>
+          <t>ኣብ ትሕዝቶኹም መልሲ የለን</t>
         </is>
       </c>
       <c r="G122" s="13" t="inlineStr">
         <is>
-          <t>Laga jawaabay aqoon guud</t>
+          <t>Macluumaadkaaga jawaab kuma jirto</t>
         </is>
       </c>
       <c r="H122" s="14" t="inlineStr"/>
@@ -10081,7 +10081,7 @@
     <row r="123" ht="44" customHeight="1">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>branding</t>
+          <t>reason_answered_from_general_knowledge</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
@@ -10091,27 +10091,27 @@
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Branding</t>
+          <t>Answered from general knowledge</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>የምርት ስም</t>
+          <t>ከአጠቃላይ እውቀት የተመለሰ</t>
         </is>
       </c>
       <c r="E123" s="13" t="inlineStr">
         <is>
-          <t>Mallattoo dhaabbataa</t>
+          <t>Beekumsa waliigalaa irraa deebi'e</t>
         </is>
       </c>
       <c r="F123" s="12" t="inlineStr">
         <is>
-          <t>ንግዲ ምልክት</t>
+          <t>ካብ ሓፈሻዊ ፍልጠት ዝተመለሰ</t>
         </is>
       </c>
       <c r="G123" s="13" t="inlineStr">
         <is>
-          <t>Astaanta</t>
+          <t>Laga jawaabay aqoon guud</t>
         </is>
       </c>
       <c r="H123" s="14" t="inlineStr"/>
@@ -10119,7 +10119,7 @@
     <row r="124" ht="44" customHeight="1">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t>branding_help</t>
+          <t>branding</t>
         </is>
       </c>
       <c r="B124" s="11" t="inlineStr">
@@ -10129,27 +10129,27 @@
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>Your colour and logo, used in this panel and in the chat widget on your website. Saved values apply immediately — no deploy.</t>
+          <t>Branding</t>
         </is>
       </c>
       <c r="D124" s="12" t="inlineStr">
         <is>
-          <t>በዚህ ፓነልና በድረ-ገጽዎ ላይ ባለው የውይይት መስኮት የሚያገለግሉ ቀለምዎና አርማዎ። የተቀመጡ እሴቶች ወዲያውኑ ተግባራዊ ይሆናሉ — ማሰማራት አያስፈልግም።</t>
+          <t>የምርት ስም</t>
         </is>
       </c>
       <c r="E124" s="13" t="inlineStr">
         <is>
-          <t>Halluu fi mallattoo keessan, panaalii kana keessattii fi widjetii chat marsariitii keessan irratti kan hojiirra oolu. Gatiin olkaa'ame battalumatti hojiirra oola — bobbaasuun hin barbaachisu.</t>
+          <t>Mallattoo dhaabbataa</t>
         </is>
       </c>
       <c r="F124" s="12" t="inlineStr">
         <is>
-          <t>ኣብዚ ፓነልን ኣብ መርበብ ሓበሬታኹም ዘሎ መስኮት ዝርርብን ዝጠቅም ሕብርኹምን ኣርማኹምን። ዝተዓቀቡ ዋጋታት ብቕጽበት ይሰርሑ — ምዝርጋሕ ኣየድልን።</t>
+          <t>ንግዲ ምልክት</t>
         </is>
       </c>
       <c r="G124" s="13" t="inlineStr">
         <is>
-          <t>Midabkaaga iyo astaantaada, oo laga isticmaalo daaqadan iyo widget-ka sheekada degelkaaga. Qiyamka la keydiyay isla markiiba way shaqeeyaan — geyn looma baahna.</t>
+          <t>Astaanta</t>
         </is>
       </c>
       <c r="H124" s="14" t="inlineStr"/>
@@ -10157,7 +10157,7 @@
     <row r="125" ht="44" customHeight="1">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>brand_name</t>
+          <t>branding_help</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
@@ -10167,27 +10167,27 @@
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Brand name</t>
+          <t>Your colour and logo, used in this panel and in the chat widget on your website. Saved values apply immediately — no deploy.</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>የምርት ስም</t>
+          <t>በዚህ ፓነልና በድረ-ገጽዎ ላይ ባለው የውይይት መስኮት የሚያገለግሉ ቀለምዎና አርማዎ። የተቀመጡ እሴቶች ወዲያውኑ ተግባራዊ ይሆናሉ — ማሰማራት አያስፈልግም።</t>
         </is>
       </c>
       <c r="E125" s="13" t="inlineStr">
         <is>
-          <t>Maqaa mallattoo</t>
+          <t>Halluu fi mallattoo keessan, panaalii kana keessattii fi widjetii chat marsariitii keessan irratti kan hojiirra oolu. Gatiin olkaa'ame battalumatti hojiirra oola — bobbaasuun hin barbaachisu.</t>
         </is>
       </c>
       <c r="F125" s="12" t="inlineStr">
         <is>
-          <t>ስም ንግዲ ምልክት</t>
+          <t>ኣብዚ ፓነልን ኣብ መርበብ ሓበሬታኹም ዘሎ መስኮት ዝርርብን ዝጠቅም ሕብርኹምን ኣርማኹምን። ዝተዓቀቡ ዋጋታት ብቕጽበት ይሰርሑ — ምዝርጋሕ ኣየድልን።</t>
         </is>
       </c>
       <c r="G125" s="13" t="inlineStr">
         <is>
-          <t>Magaca astaanta</t>
+          <t>Midabkaaga iyo astaantaada, oo laga isticmaalo daaqadan iyo widget-ka sheekada degelkaaga. Qiyamka la keydiyay isla markiiba way shaqeeyaan — geyn looma baahna.</t>
         </is>
       </c>
       <c r="H125" s="14" t="inlineStr"/>
@@ -10195,7 +10195,7 @@
     <row r="126" ht="44" customHeight="1">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>brand_name_help</t>
+          <t>brand_name</t>
         </is>
       </c>
       <c r="B126" s="11" t="inlineStr">
@@ -10205,27 +10205,27 @@
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>What people call you — for example "CBE". Shown in the chat header, this panel and greetings to customers. Leave blank to use your registered name, {legal}, which is kept either way for printed reports.</t>
+          <t>Brand name</t>
         </is>
       </c>
       <c r="D126" s="12" t="inlineStr">
         <is>
-          <t>ሰዎች የሚጠሩዎት ስም — ለምሳሌ "CBE"። በውይይቱ ራስጌ፣ በዚህ ፓነልና ለደንበኞች በሚቀርብ ሰላምታ ላይ ይታያል። ባዶ ከተውት የተመዘገበው ስምዎ {legal} ይሆናል፤ ለሚታተሙ ሪፖርቶች በሁለቱም መንገድ ይቀመጣል።</t>
+          <t>የምርት ስም</t>
         </is>
       </c>
       <c r="E126" s="13" t="inlineStr">
         <is>
-          <t>Maqaa namoonni ittiin isin waaman — fakkeenyaaf "CBE". Mataduree chat, panaalii kanaa fi nagaa maamiltootaaf dhiyaatu irratti ni mul'ata. Duwwaa yoo dhiiftan maqaan galmaa'aa keessan {legal} fayyadama; gabaasa maxxanfamuuf karaa lamaanuu ni qabama.</t>
+          <t>Maqaa mallattoo</t>
         </is>
       </c>
       <c r="F126" s="12" t="inlineStr">
         <is>
-          <t>ሰባት ዝጽውዑኹም ስም — ንኣብነት "CBE"። ኣብ ርእሲ ዝርርብ፣ ኣብዚ ፓነልን ንዓማዊል ኣብ ዝቐርብ ሰላምታን ይረአ። ባዶ እንተ ገዲፍኩምዎ እቲ ዝተመዝገበ ስምኩም {legal} ይኸውን፤ ንዝሕተሙ ጸብጻባት ብኽልቲኡ መገዲ ይዕቀብ።</t>
+          <t>ስም ንግዲ ምልክት</t>
         </is>
       </c>
       <c r="G126" s="13" t="inlineStr">
         <is>
-          <t>Waxa dadku kugu yeeraan — tusaale "CBE". Waxay ka muuqataa madaxa sheekada, daaqadan iyo salaanta macaamiisha. Haddii aad banaan ka tagto waxaa la isticmaalayaa magacaaga diiwaangashan, {legal}, oo si kastaba lagu hayo warbixinnada la daabaco.</t>
+          <t>Magaca astaanta</t>
         </is>
       </c>
       <c r="H126" s="14" t="inlineStr"/>
@@ -10233,7 +10233,7 @@
     <row r="127" ht="44" customHeight="1">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>brand_colour</t>
+          <t>brand_name_help</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
@@ -10243,27 +10243,27 @@
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>Brand colour</t>
+          <t>What people call you — for example "CBE". Shown in the chat header, this panel and greetings to customers. Leave blank to use your registered name, {legal}, which is kept either way for printed reports.</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>የምርት ቀለም</t>
+          <t>ሰዎች የሚጠሩዎት ስም — ለምሳሌ "CBE"። በውይይቱ ራስጌ፣ በዚህ ፓነልና ለደንበኞች በሚቀርብ ሰላምታ ላይ ይታያል። ባዶ ከተውት የተመዘገበው ስምዎ {legal} ይሆናል፤ ለሚታተሙ ሪፖርቶች በሁለቱም መንገድ ይቀመጣል።</t>
         </is>
       </c>
       <c r="E127" s="13" t="inlineStr">
         <is>
-          <t>Halluu mallattoo</t>
+          <t>Maqaa namoonni ittiin isin waaman — fakkeenyaaf "CBE". Mataduree chat, panaalii kanaa fi nagaa maamiltootaaf dhiyaatu irratti ni mul'ata. Duwwaa yoo dhiiftan maqaan galmaa'aa keessan {legal} fayyadama; gabaasa maxxanfamuuf karaa lamaanuu ni qabama.</t>
         </is>
       </c>
       <c r="F127" s="12" t="inlineStr">
         <is>
-          <t>ሕብሪ ንግዲ ምልክት</t>
+          <t>ሰባት ዝጽውዑኹም ስም — ንኣብነት "CBE"። ኣብ ርእሲ ዝርርብ፣ ኣብዚ ፓነልን ንዓማዊል ኣብ ዝቐርብ ሰላምታን ይረአ። ባዶ እንተ ገዲፍኩምዎ እቲ ዝተመዝገበ ስምኩም {legal} ይኸውን፤ ንዝሕተሙ ጸብጻባት ብኽልቲኡ መገዲ ይዕቀብ።</t>
         </is>
       </c>
       <c r="G127" s="13" t="inlineStr">
         <is>
-          <t>Midabka astaanta</t>
+          <t>Waxa dadku kugu yeeraan — tusaale "CBE". Waxay ka muuqataa madaxa sheekada, daaqadan iyo salaanta macaamiisha. Haddii aad banaan ka tagto waxaa la isticmaalayaa magacaaga diiwaangashan, {legal}, oo si kastaba lagu hayo warbixinnada la daabaco.</t>
         </is>
       </c>
       <c r="H127" s="14" t="inlineStr"/>
@@ -10271,7 +10271,7 @@
     <row r="128" ht="44" customHeight="1">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t>logo_url</t>
+          <t>brand_colour</t>
         </is>
       </c>
       <c r="B128" s="11" t="inlineStr">
@@ -10281,27 +10281,27 @@
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>Logo URL (https)</t>
+          <t>Brand colour</t>
         </is>
       </c>
       <c r="D128" s="12" t="inlineStr">
         <is>
-          <t>የአርማ አድራሻ (https)</t>
+          <t>የምርት ቀለም</t>
         </is>
       </c>
       <c r="E128" s="13" t="inlineStr">
         <is>
-          <t>Teessoo mallattoo (https)</t>
+          <t>Halluu mallattoo</t>
         </is>
       </c>
       <c r="F128" s="12" t="inlineStr">
         <is>
-          <t>ኣድራሻ ኣርማ (https)</t>
+          <t>ሕብሪ ንግዲ ምልክት</t>
         </is>
       </c>
       <c r="G128" s="13" t="inlineStr">
         <is>
-          <t>Ciwaanka astaanta (https)</t>
+          <t>Midabka astaanta</t>
         </is>
       </c>
       <c r="H128" s="14" t="inlineStr"/>
@@ -10309,7 +10309,7 @@
     <row r="129" ht="44" customHeight="1">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>seeded_colours_help</t>
+          <t>logo_url</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
@@ -10319,27 +10319,27 @@
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>Seeded colours are our reading of your public site, not your brand book. If it is wrong, this is where to fix it.</t>
+          <t>Logo URL (https)</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>የቀረቡት ቀለሞች ከይፋዊ ድረ-ገጽዎ የተወሰዱ ግምቶች እንጂ ከምርት መመሪያ መጽሐፍዎ አይደሉም። ስህተት ከሆነ የሚታረመው እዚህ ነው።</t>
+          <t>የአርማ አድራሻ (https)</t>
         </is>
       </c>
       <c r="E129" s="13" t="inlineStr">
         <is>
-          <t>Halluuwwan durfaman marsariitii keessan ifaa irraa kan dubbifame malee kitaaba mallattoo keessanii irraa miti. Yoo dogoggora ta'e, asitti sirreessaa.</t>
+          <t>Teessoo mallattoo (https)</t>
         </is>
       </c>
       <c r="F129" s="12" t="inlineStr">
         <is>
-          <t>እቶም ዝቐረቡ ሕብርታት ካብ ወግዓዊ መርበብ ሓበሬታኹም ዝተወስዱ ግምት እምበር ካብ መጽሓፍ ንግዲ ምልክትኩም ኣይኮኑን። ጌጋ እንተኾይኑ ኣብዚ ይእረም።</t>
+          <t>ኣድራሻ ኣርማ (https)</t>
         </is>
       </c>
       <c r="G129" s="13" t="inlineStr">
         <is>
-          <t>Midabbada la soo bandhigay waa akhrinteenna degelkaaga guud, ma aha buuggaaga astaanta. Haddii ay khalad tahay, halkan ayaa lagu saxaa.</t>
+          <t>Ciwaanka astaanta (https)</t>
         </is>
       </c>
       <c r="H129" s="14" t="inlineStr"/>
@@ -10347,7 +10347,7 @@
     <row r="130" ht="44" customHeight="1">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t>save_branding</t>
+          <t>seeded_colours_help</t>
         </is>
       </c>
       <c r="B130" s="11" t="inlineStr">
@@ -10357,27 +10357,27 @@
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>Save branding</t>
+          <t>Seeded colours are our reading of your public site, not your brand book. If it is wrong, this is where to fix it.</t>
         </is>
       </c>
       <c r="D130" s="12" t="inlineStr">
         <is>
-          <t>የምርት ስም አስቀምጥ</t>
+          <t>የቀረቡት ቀለሞች ከይፋዊ ድረ-ገጽዎ የተወሰዱ ግምቶች እንጂ ከምርት መመሪያ መጽሐፍዎ አይደሉም። ስህተት ከሆነ የሚታረመው እዚህ ነው።</t>
         </is>
       </c>
       <c r="E130" s="13" t="inlineStr">
         <is>
-          <t>Mallattoo olkaa'i</t>
+          <t>Halluuwwan durfaman marsariitii keessan ifaa irraa kan dubbifame malee kitaaba mallattoo keessanii irraa miti. Yoo dogoggora ta'e, asitti sirreessaa.</t>
         </is>
       </c>
       <c r="F130" s="12" t="inlineStr">
         <is>
-          <t>ንግዲ ምልክት ኣቐምጥ</t>
+          <t>እቶም ዝቐረቡ ሕብርታት ካብ ወግዓዊ መርበብ ሓበሬታኹም ዝተወስዱ ግምት እምበር ካብ መጽሓፍ ንግዲ ምልክትኩም ኣይኮኑን። ጌጋ እንተኾይኑ ኣብዚ ይእረም።</t>
         </is>
       </c>
       <c r="G130" s="13" t="inlineStr">
         <is>
-          <t>Keydi astaanta</t>
+          <t>Midabbada la soo bandhigay waa akhrinteenna degelkaaga guud, ma aha buuggaaga astaanta. Haddii ay khalad tahay, halkan ayaa lagu saxaa.</t>
         </is>
       </c>
       <c r="H130" s="14" t="inlineStr"/>
@@ -10385,7 +10385,7 @@
     <row r="131" ht="44" customHeight="1">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>branding_saved</t>
+          <t>save_branding</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
@@ -10395,27 +10395,27 @@
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>Branding saved</t>
+          <t>Save branding</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>የምርት ስም ተቀምጧል</t>
+          <t>የምርት ስም አስቀምጥ</t>
         </is>
       </c>
       <c r="E131" s="13" t="inlineStr">
         <is>
-          <t>Mallattoon olkaa'ame</t>
+          <t>Mallattoo olkaa'i</t>
         </is>
       </c>
       <c r="F131" s="12" t="inlineStr">
         <is>
-          <t>ንግዲ ምልክት ተቐሚጡ</t>
+          <t>ንግዲ ምልክት ኣቐምጥ</t>
         </is>
       </c>
       <c r="G131" s="13" t="inlineStr">
         <is>
-          <t>Astaanta waa la keydiyay</t>
+          <t>Keydi astaanta</t>
         </is>
       </c>
       <c r="H131" s="14" t="inlineStr"/>
@@ -10423,7 +10423,7 @@
     <row r="132" ht="44" customHeight="1">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t>escalation_webhook</t>
+          <t>branding_saved</t>
         </is>
       </c>
       <c r="B132" s="11" t="inlineStr">
@@ -10433,27 +10433,27 @@
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>Escalation webhook</t>
+          <t>Branding saved</t>
         </is>
       </c>
       <c r="D132" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ዌብሁክ</t>
+          <t>የምርት ስም ተቀምጧል</t>
         </is>
       </c>
       <c r="E132" s="13" t="inlineStr">
         <is>
-          <t>Webhook dabarsaa</t>
+          <t>Mallattoon olkaa'ame</t>
         </is>
       </c>
       <c r="F132" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ምትሕልላፍ</t>
+          <t>ንግዲ ምልክት ተቐሚጡ</t>
         </is>
       </c>
       <c r="G132" s="13" t="inlineStr">
         <is>
-          <t>Webhook-ga gudbinta</t>
+          <t>Astaanta waa la keydiyay</t>
         </is>
       </c>
       <c r="H132" s="14" t="inlineStr"/>
@@ -10461,7 +10461,7 @@
     <row r="133" ht="44" customHeight="1">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>webhook_help</t>
+          <t>escalation_webhook</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
@@ -10471,27 +10471,27 @@
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>Where escalations are delivered in your contact-centre tool. Requests are signed, so the receiving system can verify they came from us. Clear the field to disconnect.</t>
+          <t>Escalation webhook</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>ጉዳዮች በእርስዎ የደንበኞች መገልገያ መሣሪያ ውስጥ የሚደርሱበት ቦታ። ጥያቄዎቹ የተፈረሙ ናቸው፤ ስለዚህ ተቀባዩ ሥርዓት ከእኛ መምጣታቸውን ማረጋገጥ ይችላል። ለማቋረጥ መስኩን ባዶ ያድርጉ።</t>
+          <t>የማሸጋገሪያ ዌብሁክ</t>
         </is>
       </c>
       <c r="E133" s="13" t="inlineStr">
         <is>
-          <t>Iddoo dhimmoonni meeshaa wiirtuu quunnamtii keessan keessatti geessifaman. Gaaffiiwwan mallatteeffamaniiru, kanaafuu sirni fudhatu nurraa dhufuu isaanii mirkaneessuu danda'a. Addaan kutuuf dirree duwwaa godhaa.</t>
+          <t>Webhook dabarsaa</t>
         </is>
       </c>
       <c r="F133" s="12" t="inlineStr">
         <is>
-          <t>ጉዳያት ኣብ መሳርሒ ማእከል ርክብኩም ዝበጽሑሉ ቦታ። እቶም ሕቶታት ዝተፈረሙ ስለዝኾኑ እቲ ተቐባሊ ስርዓት ካባና ምምጻኦም ከረጋግጽ ይኽእል። ንምቁራጽ እቲ ሜዳ ባዶ ግበሩ።</t>
+          <t>ዌብሁክ ምትሕልላፍ</t>
         </is>
       </c>
       <c r="G133" s="13" t="inlineStr">
         <is>
-          <t>Halka arrimaha lagu gudbiyo qalabkaaga xarunta macaamiisha. Codsiyada waa la saxeexay, sidaas darteed nidaamka qaataa wuu xaqiijin karaa inay naga yimaadeen. Si aad u gooyso, banaani meesha.</t>
+          <t>Webhook-ga gudbinta</t>
         </is>
       </c>
       <c r="H133" s="14" t="inlineStr"/>
@@ -10499,7 +10499,7 @@
     <row r="134" ht="44" customHeight="1">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>signing_secret_set</t>
+          <t>webhook_help</t>
         </is>
       </c>
       <c r="B134" s="11" t="inlineStr">
@@ -10509,27 +10509,27 @@
       </c>
       <c r="C134" s="11" t="inlineStr">
         <is>
-          <t>A signing secret is set. It cannot be shown again — saving a URL here issues a new one and the old one stops working.</t>
+          <t>Where escalations are delivered in your contact-centre tool. Requests are signed, so the receiving system can verify they came from us. Clear the field to disconnect.</t>
         </is>
       </c>
       <c r="D134" s="12" t="inlineStr">
         <is>
-          <t>የፊርማ ሚስጥር ተዘጋጅቷል። እንደገና ማሳየት አይቻልም — እዚህ አድራሻ ማስቀመጥ አዲስ ያወጣል፤ አሮጌው መስራት ያቆማል።</t>
+          <t>ጉዳዮች በእርስዎ የደንበኞች መገልገያ መሣሪያ ውስጥ የሚደርሱበት ቦታ። ጥያቄዎቹ የተፈረሙ ናቸው፤ ስለዚህ ተቀባዩ ሥርዓት ከእኛ መምጣታቸውን ማረጋገጥ ይችላል። ለማቋረጥ መስኩን ባዶ ያድርጉ።</t>
         </is>
       </c>
       <c r="E134" s="13" t="inlineStr">
         <is>
-          <t>Iccitiin mallattoo qophaa'eera. Irra deebi'anii agarsiisuun hin danda'amu — asitti URL olkaa'uun haaraa baasa, kan duraa immoo hojii dhaaba.</t>
+          <t>Iddoo dhimmoonni meeshaa wiirtuu quunnamtii keessan keessatti geessifaman. Gaaffiiwwan mallatteeffamaniiru, kanaafuu sirni fudhatu nurraa dhufuu isaanii mirkaneessuu danda'a. Addaan kutuuf dirree duwwaa godhaa.</t>
         </is>
       </c>
       <c r="F134" s="12" t="inlineStr">
         <is>
-          <t>ምስጢር ፌርማ ተቐሚጡ። መሊስካ ክርአ ኣይክእልን — ኣብዚ ኣድራሻ ምቕማጥ ሓድሽ የውጽእ፣ እቲ ናይ ቀደም ይቋረጽ።</t>
+          <t>ጉዳያት ኣብ መሳርሒ ማእከል ርክብኩም ዝበጽሑሉ ቦታ። እቶም ሕቶታት ዝተፈረሙ ስለዝኾኑ እቲ ተቐባሊ ስርዓት ካባና ምምጻኦም ከረጋግጽ ይኽእል። ንምቁራጽ እቲ ሜዳ ባዶ ግበሩ።</t>
         </is>
       </c>
       <c r="G134" s="13" t="inlineStr">
         <is>
-          <t>Sir saxeex ayaa la dejiyay. Mar kale lama tusi karo — URL halkan lagu keydiyo wuxuu soo saarayaa mid cusub, kii hore wuu shaqo joojiyaa.</t>
+          <t>Halka arrimaha lagu gudbiyo qalabkaaga xarunta macaamiisha. Codsiyada waa la saxeexay, sidaas darteed nidaamka qaataa wuu xaqiijin karaa inay naga yimaadeen. Si aad u gooyso, banaani meesha.</t>
         </is>
       </c>
       <c r="H134" s="14" t="inlineStr"/>
@@ -10537,7 +10537,7 @@
     <row r="135" ht="44" customHeight="1">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>webhook_connected</t>
+          <t>signing_secret_set</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
@@ -10547,27 +10547,27 @@
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>Webhook connected</t>
+          <t>A signing secret is set. It cannot be shown again — saving a URL here issues a new one and the old one stops working.</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ተገናኝቷል</t>
+          <t>የፊርማ ሚስጥር ተዘጋጅቷል። እንደገና ማሳየት አይቻልም — እዚህ አድራሻ ማስቀመጥ አዲስ ያወጣል፤ አሮጌው መስራት ያቆማል።</t>
         </is>
       </c>
       <c r="E135" s="13" t="inlineStr">
         <is>
-          <t>Webhook walqunnamsiifame</t>
+          <t>Iccitiin mallattoo qophaa'eera. Irra deebi'anii agarsiisuun hin danda'amu — asitti URL olkaa'uun haaraa baasa, kan duraa immoo hojii dhaaba.</t>
         </is>
       </c>
       <c r="F135" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ተራኺቡ</t>
+          <t>ምስጢር ፌርማ ተቐሚጡ። መሊስካ ክርአ ኣይክእልን — ኣብዚ ኣድራሻ ምቕማጥ ሓድሽ የውጽእ፣ እቲ ናይ ቀደም ይቋረጽ።</t>
         </is>
       </c>
       <c r="G135" s="13" t="inlineStr">
         <is>
-          <t>Webhook waa la xiray</t>
+          <t>Sir saxeex ayaa la dejiyay. Mar kale lama tusi karo — URL halkan lagu keydiyo wuxuu soo saarayaa mid cusub, kii hore wuu shaqo joojiyaa.</t>
         </is>
       </c>
       <c r="H135" s="14" t="inlineStr"/>
@@ -10575,7 +10575,7 @@
     <row r="136" ht="44" customHeight="1">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t>webhook_disconnected</t>
+          <t>webhook_connected</t>
         </is>
       </c>
       <c r="B136" s="11" t="inlineStr">
@@ -10585,27 +10585,27 @@
       </c>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>Webhook disconnected</t>
+          <t>Webhook connected</t>
         </is>
       </c>
       <c r="D136" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ተቋርጧል</t>
+          <t>ዌብሁክ ተገናኝቷል</t>
         </is>
       </c>
       <c r="E136" s="13" t="inlineStr">
         <is>
-          <t>Webhook addaan kutame</t>
+          <t>Webhook walqunnamsiifame</t>
         </is>
       </c>
       <c r="F136" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ተቛሪጹ</t>
+          <t>ዌብሁክ ተራኺቡ</t>
         </is>
       </c>
       <c r="G136" s="13" t="inlineStr">
         <is>
-          <t>Webhook waa la goynay</t>
+          <t>Webhook waa la xiray</t>
         </is>
       </c>
       <c r="H136" s="14" t="inlineStr"/>
@@ -10613,7 +10613,7 @@
     <row r="137" ht="44" customHeight="1">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>your_password</t>
+          <t>webhook_disconnected</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
@@ -10623,27 +10623,27 @@
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>Your password</t>
+          <t>Webhook disconnected</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>የይለፍ ቃልዎ</t>
+          <t>ዌብሁክ ተቋርጧል</t>
         </is>
       </c>
       <c r="E137" s="13" t="inlineStr">
         <is>
-          <t>Jecha darbii keessan</t>
+          <t>Webhook addaan kutame</t>
         </is>
       </c>
       <c r="F137" s="12" t="inlineStr">
         <is>
-          <t>መሕለፊ ቃልኩም</t>
+          <t>ዌብሁክ ተቛሪጹ</t>
         </is>
       </c>
       <c r="G137" s="13" t="inlineStr">
         <is>
-          <t>Furahaaga sirta ah</t>
+          <t>Webhook waa la goynay</t>
         </is>
       </c>
       <c r="H137" s="14" t="inlineStr"/>
@@ -10651,7 +10651,7 @@
     <row r="138" ht="44" customHeight="1">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t>current_password</t>
+          <t>your_password</t>
         </is>
       </c>
       <c r="B138" s="11" t="inlineStr">
@@ -10661,27 +10661,27 @@
       </c>
       <c r="C138" s="11" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Your password</t>
         </is>
       </c>
       <c r="D138" s="12" t="inlineStr">
         <is>
-          <t>አሁን ያለው</t>
+          <t>የይለፍ ቃልዎ</t>
         </is>
       </c>
       <c r="E138" s="13" t="inlineStr">
         <is>
-          <t>Kan ammaa</t>
+          <t>Jecha darbii keessan</t>
         </is>
       </c>
       <c r="F138" s="12" t="inlineStr">
         <is>
-          <t>ናይ ሕጂ</t>
+          <t>መሕለፊ ቃልኩም</t>
         </is>
       </c>
       <c r="G138" s="13" t="inlineStr">
         <is>
-          <t>Kan hadda</t>
+          <t>Furahaaga sirta ah</t>
         </is>
       </c>
       <c r="H138" s="14" t="inlineStr"/>
@@ -10689,7 +10689,7 @@
     <row r="139" ht="44" customHeight="1">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>new_password_12</t>
+          <t>current_password</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
@@ -10699,27 +10699,27 @@
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>New (12+ characters)</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>አዲስ (12+ ቁምፊዎች)</t>
+          <t>አሁን ያለው</t>
         </is>
       </c>
       <c r="E139" s="13" t="inlineStr">
         <is>
-          <t>Haaraa (arfiilee 12+)</t>
+          <t>Kan ammaa</t>
         </is>
       </c>
       <c r="F139" s="12" t="inlineStr">
         <is>
-          <t>ሓድሽ (12+ ፊደላት)</t>
+          <t>ናይ ሕጂ</t>
         </is>
       </c>
       <c r="G139" s="13" t="inlineStr">
         <is>
-          <t>Cusub (12+ xaraf)</t>
+          <t>Kan hadda</t>
         </is>
       </c>
       <c r="H139" s="14" t="inlineStr"/>
@@ -10727,7 +10727,7 @@
     <row r="140" ht="44" customHeight="1">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t>password_change_help</t>
+          <t>new_password_12</t>
         </is>
       </c>
       <c r="B140" s="11" t="inlineStr">
@@ -10737,27 +10737,27 @@
       </c>
       <c r="C140" s="11" t="inlineStr">
         <is>
-          <t>Changing it signs out every other browser you are signed in on.</t>
+          <t>New (12+ characters)</t>
         </is>
       </c>
       <c r="D140" s="12" t="inlineStr">
         <is>
-          <t>መቀየር በገቡበት በሌላ በእያንዳንዱ አሳሽ ላይ ያስወጣዎታል።</t>
+          <t>አዲስ (12+ ቁምፊዎች)</t>
         </is>
       </c>
       <c r="E140" s="13" t="inlineStr">
         <is>
-          <t>Jijjiiruun biraawzarii biroo isin keessa seentan hunda irraa isin baasa.</t>
+          <t>Haaraa (arfiilee 12+)</t>
         </is>
       </c>
       <c r="F140" s="12" t="inlineStr">
         <is>
-          <t>ምቕያሩ ኣብ ካልእ ዝኣተኹምሉ ኩሉ መርበብ መንሸራተቲ የውጽኣኩም።</t>
+          <t>ሓድሽ (12+ ፊደላት)</t>
         </is>
       </c>
       <c r="G140" s="13" t="inlineStr">
         <is>
-          <t>Beddelkeedu wuxuu kaa saarayaa dhammaan browser-yada kale ee aad ku jirto.</t>
+          <t>Cusub (12+ xaraf)</t>
         </is>
       </c>
       <c r="H140" s="14" t="inlineStr"/>
@@ -10765,7 +10765,7 @@
     <row r="141" ht="44" customHeight="1">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>change_password</t>
+          <t>password_change_help</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
@@ -10775,27 +10775,27 @@
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>Change password</t>
+          <t>Changing it signs out every other browser you are signed in on.</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>የይለፍ ቃል ቀይር</t>
+          <t>መቀየር በገቡበት በሌላ በእያንዳንዱ አሳሽ ላይ ያስወጣዎታል።</t>
         </is>
       </c>
       <c r="E141" s="13" t="inlineStr">
         <is>
-          <t>Jecha darbii jijjiiri</t>
+          <t>Jijjiiruun biraawzarii biroo isin keessa seentan hunda irraa isin baasa.</t>
         </is>
       </c>
       <c r="F141" s="12" t="inlineStr">
         <is>
-          <t>መሕለፊ ቃል ቀይር</t>
+          <t>ምቕያሩ ኣብ ካልእ ዝኣተኹምሉ ኩሉ መርበብ መንሸራተቲ የውጽኣኩም።</t>
         </is>
       </c>
       <c r="G141" s="13" t="inlineStr">
         <is>
-          <t>Bedel furaha sirta ah</t>
+          <t>Beddelkeedu wuxuu kaa saarayaa dhammaan browser-yada kale ee aad ku jirto.</t>
         </is>
       </c>
       <c r="H141" s="14" t="inlineStr"/>
@@ -10803,7 +10803,7 @@
     <row r="142" ht="44" customHeight="1">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t>password_changed</t>
+          <t>change_password</t>
         </is>
       </c>
       <c r="B142" s="11" t="inlineStr">
@@ -10813,27 +10813,27 @@
       </c>
       <c r="C142" s="11" t="inlineStr">
         <is>
-          <t>Password changed. Other sessions were signed out.</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="D142" s="12" t="inlineStr">
         <is>
-          <t>የይለፍ ቃል ተቀይሯል። ሌሎች ክፍለ-ጊዜዎች ወጥተዋል።</t>
+          <t>የይለፍ ቃል ቀይር</t>
         </is>
       </c>
       <c r="E142" s="13" t="inlineStr">
         <is>
-          <t>Jechi darbii jijjiirameera. Sessionoonni biroo ba'aniiru.</t>
+          <t>Jecha darbii jijjiiri</t>
         </is>
       </c>
       <c r="F142" s="12" t="inlineStr">
         <is>
-          <t>መሕለፊ ቃል ተቐዪሩ። ካልኦት ክፍለ-ግዜታት ወጺኦም።</t>
+          <t>መሕለፊ ቃል ቀይር</t>
         </is>
       </c>
       <c r="G142" s="13" t="inlineStr">
         <is>
-          <t>Furaha sirta ah waa la beddelay. Kalfadhiyada kale waa laga saaray.</t>
+          <t>Bedel furaha sirta ah</t>
         </is>
       </c>
       <c r="H142" s="14" t="inlineStr"/>
@@ -10841,7 +10841,7 @@
     <row r="143" ht="44" customHeight="1">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>add_person</t>
+          <t>password_changed</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
@@ -10851,27 +10851,27 @@
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>Add person</t>
+          <t>Password changed. Other sessions were signed out.</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>ሰው ጨምር</t>
+          <t>የይለፍ ቃል ተቀይሯል። ሌሎች ክፍለ-ጊዜዎች ወጥተዋል።</t>
         </is>
       </c>
       <c r="E143" s="13" t="inlineStr">
         <is>
-          <t>Nama dabali</t>
+          <t>Jechi darbii jijjiirameera. Sessionoonni biroo ba'aniiru.</t>
         </is>
       </c>
       <c r="F143" s="12" t="inlineStr">
         <is>
-          <t>ሰብ ወስኽ</t>
+          <t>መሕለፊ ቃል ተቐዪሩ። ካልኦት ክፍለ-ግዜታት ወጺኦም።</t>
         </is>
       </c>
       <c r="G143" s="13" t="inlineStr">
         <is>
-          <t>Ku dar qof</t>
+          <t>Furaha sirta ah waa la beddelay. Kalfadhiyada kale waa laga saaray.</t>
         </is>
       </c>
       <c r="H143" s="14" t="inlineStr"/>
@@ -10879,7 +10879,7 @@
     <row r="144" ht="44" customHeight="1">
       <c r="A144" s="11" t="inlineStr">
         <is>
-          <t>n_accounts</t>
+          <t>add_person</t>
         </is>
       </c>
       <c r="B144" s="11" t="inlineStr">
@@ -10889,27 +10889,27 @@
       </c>
       <c r="C144" s="11" t="inlineStr">
         <is>
-          <t>{n} accounts</t>
+          <t>Add person</t>
         </is>
       </c>
       <c r="D144" s="12" t="inlineStr">
         <is>
-          <t>{n} መለያዎች</t>
+          <t>ሰው ጨምር</t>
         </is>
       </c>
       <c r="E144" s="13" t="inlineStr">
         <is>
-          <t>Herregoota {n}</t>
+          <t>Nama dabali</t>
         </is>
       </c>
       <c r="F144" s="12" t="inlineStr">
         <is>
-          <t>{n} ሕሳባት</t>
+          <t>ሰብ ወስኽ</t>
         </is>
       </c>
       <c r="G144" s="13" t="inlineStr">
         <is>
-          <t>{n} xisaabood</t>
+          <t>Ku dar qof</t>
         </is>
       </c>
       <c r="H144" s="14" t="inlineStr"/>
@@ -10917,7 +10917,7 @@
     <row r="145" ht="44" customHeight="1">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>one_account</t>
+          <t>n_accounts</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
@@ -10927,27 +10927,27 @@
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>{n} account</t>
+          <t>{n} accounts</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>{n} መለያ</t>
+          <t>{n} መለያዎች</t>
         </is>
       </c>
       <c r="E145" s="13" t="inlineStr">
         <is>
-          <t>Herrega {n}</t>
+          <t>Herregoota {n}</t>
         </is>
       </c>
       <c r="F145" s="12" t="inlineStr">
         <is>
-          <t>{n} ሕሳብ</t>
+          <t>{n} ሕሳባት</t>
         </is>
       </c>
       <c r="G145" s="13" t="inlineStr">
         <is>
-          <t>{n} xisaab</t>
+          <t>{n} xisaabood</t>
         </is>
       </c>
       <c r="H145" s="14" t="inlineStr"/>
@@ -10955,7 +10955,7 @@
     <row r="146" ht="44" customHeight="1">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>one_account</t>
         </is>
       </c>
       <c r="B146" s="11" t="inlineStr">
@@ -10965,27 +10965,27 @@
       </c>
       <c r="C146" s="11" t="inlineStr">
         <is>
-          <t>Person</t>
+          <t>{n} account</t>
         </is>
       </c>
       <c r="D146" s="12" t="inlineStr">
         <is>
-          <t>ሰው</t>
+          <t>{n} መለያ</t>
         </is>
       </c>
       <c r="E146" s="13" t="inlineStr">
         <is>
-          <t>Nama</t>
+          <t>Herrega {n}</t>
         </is>
       </c>
       <c r="F146" s="12" t="inlineStr">
         <is>
-          <t>ሰብ</t>
+          <t>{n} ሕሳብ</t>
         </is>
       </c>
       <c r="G146" s="13" t="inlineStr">
         <is>
-          <t>Qof</t>
+          <t>{n} xisaab</t>
         </is>
       </c>
       <c r="H146" s="14" t="inlineStr"/>
@@ -10993,7 +10993,7 @@
     <row r="147" ht="44" customHeight="1">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>person</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
@@ -11003,27 +11003,27 @@
       </c>
       <c r="C147" s="11" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Person</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>ሚና</t>
+          <t>ሰው</t>
         </is>
       </c>
       <c r="E147" s="13" t="inlineStr">
         <is>
-          <t>Gahee</t>
+          <t>Nama</t>
         </is>
       </c>
       <c r="F147" s="12" t="inlineStr">
         <is>
-          <t>ግደ</t>
+          <t>ሰብ</t>
         </is>
       </c>
       <c r="G147" s="13" t="inlineStr">
         <is>
-          <t>Doorka</t>
+          <t>Qof</t>
         </is>
       </c>
       <c r="H147" s="14" t="inlineStr"/>
@@ -11031,7 +11031,7 @@
     <row r="148" ht="44" customHeight="1">
       <c r="A148" s="11" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>role</t>
         </is>
       </c>
       <c r="B148" s="11" t="inlineStr">
@@ -11041,27 +11041,27 @@
       </c>
       <c r="C148" s="11" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="D148" s="12" t="inlineStr">
         <is>
-          <t>ሁኔታ</t>
+          <t>ሚና</t>
         </is>
       </c>
       <c r="E148" s="13" t="inlineStr">
         <is>
-          <t>Haala</t>
+          <t>Gahee</t>
         </is>
       </c>
       <c r="F148" s="12" t="inlineStr">
         <is>
-          <t>ኩነታት</t>
+          <t>ግደ</t>
         </is>
       </c>
       <c r="G148" s="13" t="inlineStr">
         <is>
-          <t>Xaalada</t>
+          <t>Doorka</t>
         </is>
       </c>
       <c r="H148" s="14" t="inlineStr"/>
@@ -11069,7 +11069,7 @@
     <row r="149" ht="44" customHeight="1">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>last_signed_in</t>
+          <t>status</t>
         </is>
       </c>
       <c r="B149" s="11" t="inlineStr">
@@ -11079,27 +11079,27 @@
       </c>
       <c r="C149" s="11" t="inlineStr">
         <is>
-          <t>Last signed in</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>መጨረሻ የገቡበት</t>
+          <t>ሁኔታ</t>
         </is>
       </c>
       <c r="E149" s="13" t="inlineStr">
         <is>
-          <t>Yeroo dhumaa seenan</t>
+          <t>Haala</t>
         </is>
       </c>
       <c r="F149" s="12" t="inlineStr">
         <is>
-          <t>ናይ መወዳእታ ዝኣተዉሉ</t>
+          <t>ኩነታት</t>
         </is>
       </c>
       <c r="G149" s="13" t="inlineStr">
         <is>
-          <t>Markii ugu dambeysay ee la galay</t>
+          <t>Xaalada</t>
         </is>
       </c>
       <c r="H149" s="14" t="inlineStr"/>
@@ -11107,7 +11107,7 @@
     <row r="150" ht="44" customHeight="1">
       <c r="A150" s="11" t="inlineStr">
         <is>
-          <t>actions</t>
+          <t>last_signed_in</t>
         </is>
       </c>
       <c r="B150" s="11" t="inlineStr">
@@ -11117,27 +11117,27 @@
       </c>
       <c r="C150" s="11" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Last signed in</t>
         </is>
       </c>
       <c r="D150" s="12" t="inlineStr">
         <is>
-          <t>ድርጊቶች</t>
+          <t>መጨረሻ የገቡበት</t>
         </is>
       </c>
       <c r="E150" s="13" t="inlineStr">
         <is>
-          <t>Gochaalee</t>
+          <t>Yeroo dhumaa seenan</t>
         </is>
       </c>
       <c r="F150" s="12" t="inlineStr">
         <is>
-          <t>ተግባራት</t>
+          <t>ናይ መወዳእታ ዝኣተዉሉ</t>
         </is>
       </c>
       <c r="G150" s="13" t="inlineStr">
         <is>
-          <t>Ficillo</t>
+          <t>Markii ugu dambeysay ee la galay</t>
         </is>
       </c>
       <c r="H150" s="14" t="inlineStr"/>
@@ -11145,7 +11145,7 @@
     <row r="151" ht="44" customHeight="1">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>thats_you</t>
+          <t>actions</t>
         </is>
       </c>
       <c r="B151" s="11" t="inlineStr">
@@ -11155,27 +11155,27 @@
       </c>
       <c r="C151" s="11" t="inlineStr">
         <is>
-          <t>that’s you</t>
+          <t>Actions</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>ይህ እርስዎ ነዎት</t>
+          <t>ድርጊቶች</t>
         </is>
       </c>
       <c r="E151" s="13" t="inlineStr">
         <is>
-          <t>kun isinuma</t>
+          <t>Gochaalee</t>
         </is>
       </c>
       <c r="F151" s="12" t="inlineStr">
         <is>
-          <t>እዚ ንስኹም ኢኹም</t>
+          <t>ተግባራት</t>
         </is>
       </c>
       <c r="G151" s="13" t="inlineStr">
         <is>
-          <t>kaasi waa adiga</t>
+          <t>Ficillo</t>
         </is>
       </c>
       <c r="H151" s="14" t="inlineStr"/>
@@ -11183,7 +11183,7 @@
     <row r="152" ht="44" customHeight="1">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>thats_you</t>
         </is>
       </c>
       <c r="B152" s="11" t="inlineStr">
@@ -11193,27 +11193,27 @@
       </c>
       <c r="C152" s="11" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>that’s you</t>
         </is>
       </c>
       <c r="D152" s="12" t="inlineStr">
         <is>
-          <t>ንቁ</t>
+          <t>ይህ እርስዎ ነዎት</t>
         </is>
       </c>
       <c r="E152" s="13" t="inlineStr">
         <is>
-          <t>Ka'aa</t>
+          <t>kun isinuma</t>
         </is>
       </c>
       <c r="F152" s="12" t="inlineStr">
         <is>
-          <t>ንጡፍ</t>
+          <t>እዚ ንስኹም ኢኹም</t>
         </is>
       </c>
       <c r="G152" s="13" t="inlineStr">
         <is>
-          <t>Firfircoon</t>
+          <t>kaasi waa adiga</t>
         </is>
       </c>
       <c r="H152" s="14" t="inlineStr"/>
@@ -11221,7 +11221,7 @@
     <row r="153" ht="44" customHeight="1">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>disabled</t>
+          <t>active</t>
         </is>
       </c>
       <c r="B153" s="11" t="inlineStr">
@@ -11231,27 +11231,27 @@
       </c>
       <c r="C153" s="11" t="inlineStr">
         <is>
-          <t>Disabled</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>የተሰናከለ</t>
+          <t>ንቁ</t>
         </is>
       </c>
       <c r="E153" s="13" t="inlineStr">
         <is>
-          <t>Kan dhaabame</t>
+          <t>Ka'aa</t>
         </is>
       </c>
       <c r="F153" s="12" t="inlineStr">
         <is>
-          <t>ዝተዓገተ</t>
+          <t>ንጡፍ</t>
         </is>
       </c>
       <c r="G153" s="13" t="inlineStr">
         <is>
-          <t>La demiyay</t>
+          <t>Firfircoon</t>
         </is>
       </c>
       <c r="H153" s="14" t="inlineStr"/>
@@ -11259,7 +11259,7 @@
     <row r="154" ht="44" customHeight="1">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>disabled</t>
         </is>
       </c>
       <c r="B154" s="11" t="inlineStr">
@@ -11269,27 +11269,27 @@
       </c>
       <c r="C154" s="11" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>Disabled</t>
         </is>
       </c>
       <c r="D154" s="12" t="inlineStr">
         <is>
-          <t>በጭራሽ</t>
+          <t>የተሰናከለ</t>
         </is>
       </c>
       <c r="E154" s="13" t="inlineStr">
         <is>
-          <t>gonkumaa</t>
+          <t>Kan dhaabame</t>
         </is>
       </c>
       <c r="F154" s="12" t="inlineStr">
         <is>
-          <t>ፈጺሙ</t>
+          <t>ዝተዓገተ</t>
         </is>
       </c>
       <c r="G154" s="13" t="inlineStr">
         <is>
-          <t>waligeed</t>
+          <t>La demiyay</t>
         </is>
       </c>
       <c r="H154" s="14" t="inlineStr"/>
@@ -11297,7 +11297,7 @@
     <row r="155" ht="44" customHeight="1">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>disable</t>
+          <t>never</t>
         </is>
       </c>
       <c r="B155" s="11" t="inlineStr">
@@ -11307,27 +11307,27 @@
       </c>
       <c r="C155" s="11" t="inlineStr">
         <is>
-          <t>Disable</t>
+          <t>never</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>አሰናክል</t>
+          <t>በጭራሽ</t>
         </is>
       </c>
       <c r="E155" s="13" t="inlineStr">
         <is>
-          <t>Dhaabi</t>
+          <t>gonkumaa</t>
         </is>
       </c>
       <c r="F155" s="12" t="inlineStr">
         <is>
-          <t>ዓግት</t>
+          <t>ፈጺሙ</t>
         </is>
       </c>
       <c r="G155" s="13" t="inlineStr">
         <is>
-          <t>Demi</t>
+          <t>waligeed</t>
         </is>
       </c>
       <c r="H155" s="14" t="inlineStr"/>
@@ -11335,7 +11335,7 @@
     <row r="156" ht="44" customHeight="1">
       <c r="A156" s="11" t="inlineStr">
         <is>
-          <t>restore</t>
+          <t>disable</t>
         </is>
       </c>
       <c r="B156" s="11" t="inlineStr">
@@ -11345,27 +11345,27 @@
       </c>
       <c r="C156" s="11" t="inlineStr">
         <is>
-          <t>Restore</t>
+          <t>Disable</t>
         </is>
       </c>
       <c r="D156" s="12" t="inlineStr">
         <is>
-          <t>መልስ</t>
+          <t>አሰናክል</t>
         </is>
       </c>
       <c r="E156" s="13" t="inlineStr">
         <is>
-          <t>Deebisi</t>
+          <t>Dhaabi</t>
         </is>
       </c>
       <c r="F156" s="12" t="inlineStr">
         <is>
-          <t>መልስ</t>
+          <t>ዓግት</t>
         </is>
       </c>
       <c r="G156" s="13" t="inlineStr">
         <is>
-          <t>Soo celi</t>
+          <t>Demi</t>
         </is>
       </c>
       <c r="H156" s="14" t="inlineStr"/>
@@ -11373,7 +11373,7 @@
     <row r="157" ht="44" customHeight="1">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>what_each_role_can_do</t>
+          <t>restore</t>
         </is>
       </c>
       <c r="B157" s="11" t="inlineStr">
@@ -11383,27 +11383,27 @@
       </c>
       <c r="C157" s="11" t="inlineStr">
         <is>
-          <t>What each role can do</t>
+          <t>Restore</t>
         </is>
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>እያንዳንዱ ሚና ምን ማድረግ ይችላል</t>
+          <t>መልስ</t>
         </is>
       </c>
       <c r="E157" s="13" t="inlineStr">
         <is>
-          <t>Gaheen tokkoon tokkoon isaanii maal gochuu danda'a</t>
+          <t>Deebisi</t>
         </is>
       </c>
       <c r="F157" s="12" t="inlineStr">
         <is>
-          <t>ነፍስ ወከፍ ግደ እንታይ ክገብር ይኽእል</t>
+          <t>መልስ</t>
         </is>
       </c>
       <c r="G157" s="13" t="inlineStr">
         <is>
-          <t>Waxa doorkiiba uu samayn karo</t>
+          <t>Soo celi</t>
         </is>
       </c>
       <c r="H157" s="14" t="inlineStr"/>
@@ -11411,7 +11411,7 @@
     <row r="158" ht="44" customHeight="1">
       <c r="A158" s="11" t="inlineStr">
         <is>
-          <t>built_in</t>
+          <t>what_each_role_can_do</t>
         </is>
       </c>
       <c r="B158" s="11" t="inlineStr">
@@ -11421,27 +11421,27 @@
       </c>
       <c r="C158" s="11" t="inlineStr">
         <is>
-          <t>built-in</t>
+          <t>What each role can do</t>
         </is>
       </c>
       <c r="D158" s="12" t="inlineStr">
         <is>
-          <t>አብሮ የተሰራ</t>
+          <t>እያንዳንዱ ሚና ምን ማድረግ ይችላል</t>
         </is>
       </c>
       <c r="E158" s="13" t="inlineStr">
         <is>
-          <t>kan ijaarame</t>
+          <t>Gaheen tokkoon tokkoon isaanii maal gochuu danda'a</t>
         </is>
       </c>
       <c r="F158" s="12" t="inlineStr">
         <is>
-          <t>ውሁድ</t>
+          <t>ነፍስ ወከፍ ግደ እንታይ ክገብር ይኽእል</t>
         </is>
       </c>
       <c r="G158" s="13" t="inlineStr">
         <is>
-          <t>ku dhex jira</t>
+          <t>Waxa doorkiiba uu samayn karo</t>
         </is>
       </c>
       <c r="H158" s="14" t="inlineStr"/>
@@ -11449,7 +11449,7 @@
     <row r="159" ht="44" customHeight="1">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>add_a_person</t>
+          <t>built_in</t>
         </is>
       </c>
       <c r="B159" s="11" t="inlineStr">
@@ -11459,27 +11459,27 @@
       </c>
       <c r="C159" s="11" t="inlineStr">
         <is>
-          <t>Add a person</t>
+          <t>built-in</t>
         </is>
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>ሰው ጨምር</t>
+          <t>አብሮ የተሰራ</t>
         </is>
       </c>
       <c r="E159" s="13" t="inlineStr">
         <is>
-          <t>Nama dabali</t>
+          <t>kan ijaarame</t>
         </is>
       </c>
       <c r="F159" s="12" t="inlineStr">
         <is>
-          <t>ሰብ ወስኽ</t>
+          <t>ውሁድ</t>
         </is>
       </c>
       <c r="G159" s="13" t="inlineStr">
         <is>
-          <t>Qof ku dar</t>
+          <t>ku dhex jira</t>
         </is>
       </c>
       <c r="H159" s="14" t="inlineStr"/>
@@ -11487,7 +11487,7 @@
     <row r="160" ht="44" customHeight="1">
       <c r="A160" s="11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>add_a_person</t>
         </is>
       </c>
       <c r="B160" s="11" t="inlineStr">
@@ -11497,27 +11497,27 @@
       </c>
       <c r="C160" s="11" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Add a person</t>
         </is>
       </c>
       <c r="D160" s="12" t="inlineStr">
         <is>
-          <t>ኢሜይል</t>
+          <t>ሰው ጨምር</t>
         </is>
       </c>
       <c r="E160" s="13" t="inlineStr">
         <is>
-          <t>Imeelii</t>
+          <t>Nama dabali</t>
         </is>
       </c>
       <c r="F160" s="12" t="inlineStr">
         <is>
-          <t>ኢመይል</t>
+          <t>ሰብ ወስኽ</t>
         </is>
       </c>
       <c r="G160" s="13" t="inlineStr">
         <is>
-          <t>Iimayl</t>
+          <t>Qof ku dar</t>
         </is>
       </c>
       <c r="H160" s="14" t="inlineStr"/>
@@ -11525,7 +11525,7 @@
     <row r="161" ht="44" customHeight="1">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>name_optional</t>
+          <t>email</t>
         </is>
       </c>
       <c r="B161" s="11" t="inlineStr">
@@ -11535,27 +11535,27 @@
       </c>
       <c r="C161" s="11" t="inlineStr">
         <is>
-          <t>Name (optional)</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>ስም (አማራጭ)</t>
+          <t>ኢሜይል</t>
         </is>
       </c>
       <c r="E161" s="13" t="inlineStr">
         <is>
-          <t>Maqaa (filannoo)</t>
+          <t>Imeelii</t>
         </is>
       </c>
       <c r="F161" s="12" t="inlineStr">
         <is>
-          <t>ስም (ኣማራጺ)</t>
+          <t>ኢመይል</t>
         </is>
       </c>
       <c r="G161" s="13" t="inlineStr">
         <is>
-          <t>Magac (ikhtiyaari)</t>
+          <t>Iimayl</t>
         </is>
       </c>
       <c r="H161" s="14" t="inlineStr"/>
@@ -11563,7 +11563,7 @@
     <row r="162" ht="44" customHeight="1">
       <c r="A162" s="11" t="inlineStr">
         <is>
-          <t>temporary_password</t>
+          <t>name_optional</t>
         </is>
       </c>
       <c r="B162" s="11" t="inlineStr">
@@ -11573,27 +11573,27 @@
       </c>
       <c r="C162" s="11" t="inlineStr">
         <is>
-          <t>Temporary password</t>
+          <t>Name (optional)</t>
         </is>
       </c>
       <c r="D162" s="12" t="inlineStr">
         <is>
-          <t>ጊዜያዊ የይለፍ ቃል</t>
+          <t>ስም (አማራጭ)</t>
         </is>
       </c>
       <c r="E162" s="13" t="inlineStr">
         <is>
-          <t>Jecha darbii yeroo</t>
+          <t>Maqaa (filannoo)</t>
         </is>
       </c>
       <c r="F162" s="12" t="inlineStr">
         <is>
-          <t>ግዝያዊ መሕለፊ ቃል</t>
+          <t>ስም (ኣማራጺ)</t>
         </is>
       </c>
       <c r="G162" s="13" t="inlineStr">
         <is>
-          <t>Fure ku meel gaar ah</t>
+          <t>Magac (ikhtiyaari)</t>
         </is>
       </c>
       <c r="H162" s="14" t="inlineStr"/>
@@ -11601,7 +11601,7 @@
     <row r="163" ht="44" customHeight="1">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>temp_password_help</t>
+          <t>temporary_password</t>
         </is>
       </c>
       <c r="B163" s="11" t="inlineStr">
@@ -11611,27 +11611,27 @@
       </c>
       <c r="C163" s="11" t="inlineStr">
         <is>
-          <t>At least 12 characters. Until invitation emails are set up, this password has to be given to them directly — which is why it is shown here rather than hidden.</t>
+          <t>Temporary password</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>ቢያንስ 12 ቁምፊ። የግብዣ ኢሜይሎች እስኪዘጋጁ ድረስ ይህ የይለፍ ቃል በቀጥታ ሊሰጣቸው ይገባል — ስለዚህ ተደብቆ ሳይሆን እዚህ ይታያል።</t>
+          <t>ጊዜያዊ የይለፍ ቃል</t>
         </is>
       </c>
       <c r="E163" s="13" t="inlineStr">
         <is>
-          <t>Yoo xiqqaate arfiilee 12. Hanga imeeliin afeerraa qophaa'utti, jechi darbii kun kallattiin isaaniif kennamuu qaba — kanaafuu dhokfamuu mannaa asitti ni mul'ata.</t>
+          <t>Jecha darbii yeroo</t>
         </is>
       </c>
       <c r="F163" s="12" t="inlineStr">
         <is>
-          <t>ብውሑዱ 12 ፊደላት። መጸዋዕታ ኢመይል ክሳብ ዝዳሎ እዚ መሕለፊ ቃል ብቐጥታ ክወሃቦም ኣለዎ — ስለዚ ተሓቢኡ ዘይኮነ ኣብዚ ይረአ።</t>
+          <t>ግዝያዊ መሕለፊ ቃል</t>
         </is>
       </c>
       <c r="G163" s="13" t="inlineStr">
         <is>
-          <t>Ugu yaraan 12 xaraf. Ilaa iimaylada casumaadda la dejiyo, furahan si toos ah ayaa loo siin doonaa — sidaas darteed halkan ayuu ka muuqdaa halkii la qarin lahaa.</t>
+          <t>Fure ku meel gaar ah</t>
         </is>
       </c>
       <c r="H163" s="14" t="inlineStr"/>
@@ -11639,7 +11639,7 @@
     <row r="164" ht="44" customHeight="1">
       <c r="A164" s="11" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>temp_password_help</t>
         </is>
       </c>
       <c r="B164" s="11" t="inlineStr">
@@ -11649,27 +11649,27 @@
       </c>
       <c r="C164" s="11" t="inlineStr">
         <is>
-          <t>Create</t>
+          <t>At least 12 characters. Until invitation emails are set up, this password has to be given to them directly — which is why it is shown here rather than hidden.</t>
         </is>
       </c>
       <c r="D164" s="12" t="inlineStr">
         <is>
-          <t>ፍጠር</t>
+          <t>ቢያንስ 12 ቁምፊ። የግብዣ ኢሜይሎች እስኪዘጋጁ ድረስ ይህ የይለፍ ቃል በቀጥታ ሊሰጣቸው ይገባል — ስለዚህ ተደብቆ ሳይሆን እዚህ ይታያል።</t>
         </is>
       </c>
       <c r="E164" s="13" t="inlineStr">
         <is>
-          <t>Uumi</t>
+          <t>Yoo xiqqaate arfiilee 12. Hanga imeeliin afeerraa qophaa'utti, jechi darbii kun kallattiin isaaniif kennamuu qaba — kanaafuu dhokfamuu mannaa asitti ni mul'ata.</t>
         </is>
       </c>
       <c r="F164" s="12" t="inlineStr">
         <is>
-          <t>ፍጠር</t>
+          <t>ብውሑዱ 12 ፊደላት። መጸዋዕታ ኢመይል ክሳብ ዝዳሎ እዚ መሕለፊ ቃል ብቐጥታ ክወሃቦም ኣለዎ — ስለዚ ተሓቢኡ ዘይኮነ ኣብዚ ይረአ።</t>
         </is>
       </c>
       <c r="G164" s="13" t="inlineStr">
         <is>
-          <t>Abuur</t>
+          <t>Ugu yaraan 12 xaraf. Ilaa iimaylada casumaadda la dejiyo, furahan si toos ah ayaa loo siin doonaa — sidaas darteed halkan ayuu ka muuqdaa halkii la qarin lahaa.</t>
         </is>
       </c>
       <c r="H164" s="14" t="inlineStr"/>
@@ -11677,7 +11677,7 @@
     <row r="165" ht="44" customHeight="1">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>account_created</t>
+          <t>create</t>
         </is>
       </c>
       <c r="B165" s="11" t="inlineStr">
@@ -11687,27 +11687,27 @@
       </c>
       <c r="C165" s="11" t="inlineStr">
         <is>
-          <t>Account created</t>
+          <t>Create</t>
         </is>
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>መለያ ተፈጥሯል</t>
+          <t>ፍጠር</t>
         </is>
       </c>
       <c r="E165" s="13" t="inlineStr">
         <is>
-          <t>Herregni uumame</t>
+          <t>Uumi</t>
         </is>
       </c>
       <c r="F165" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ ተፈጢሩ</t>
+          <t>ፍጠር</t>
         </is>
       </c>
       <c r="G165" s="13" t="inlineStr">
         <is>
-          <t>Xisaab waa la abuuray</t>
+          <t>Abuur</t>
         </is>
       </c>
       <c r="H165" s="14" t="inlineStr"/>
@@ -11715,7 +11715,7 @@
     <row r="166" ht="44" customHeight="1">
       <c r="A166" s="11" t="inlineStr">
         <is>
-          <t>account_restored</t>
+          <t>account_created</t>
         </is>
       </c>
       <c r="B166" s="11" t="inlineStr">
@@ -11725,27 +11725,27 @@
       </c>
       <c r="C166" s="11" t="inlineStr">
         <is>
-          <t>Account restored</t>
+          <t>Account created</t>
         </is>
       </c>
       <c r="D166" s="12" t="inlineStr">
         <is>
-          <t>መለያ ተመልሷል</t>
+          <t>መለያ ተፈጥሯል</t>
         </is>
       </c>
       <c r="E166" s="13" t="inlineStr">
         <is>
-          <t>Herregni deebi'e</t>
+          <t>Herregni uumame</t>
         </is>
       </c>
       <c r="F166" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ ተመሊሱ</t>
+          <t>ሕሳብ ተፈጢሩ</t>
         </is>
       </c>
       <c r="G166" s="13" t="inlineStr">
         <is>
-          <t>Xisaabta waa la soo celiyay</t>
+          <t>Xisaab waa la abuuray</t>
         </is>
       </c>
       <c r="H166" s="14" t="inlineStr"/>
@@ -11753,7 +11753,7 @@
     <row r="167" ht="44" customHeight="1">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>account_disabled_n</t>
+          <t>account_restored</t>
         </is>
       </c>
       <c r="B167" s="11" t="inlineStr">
@@ -11763,27 +11763,27 @@
       </c>
       <c r="C167" s="11" t="inlineStr">
         <is>
-          <t>Account disabled, {n} session(s) ended</t>
+          <t>Account restored</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>መለያ ተሰናክሏል፤ {n} ክፍለ-ጊዜ ተዘግቷል</t>
+          <t>መለያ ተመልሷል</t>
         </is>
       </c>
       <c r="E167" s="13" t="inlineStr">
         <is>
-          <t>Herregni dhaabame, session {n} xumurame</t>
+          <t>Herregni deebi'e</t>
         </is>
       </c>
       <c r="F167" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ ተዓጊቱ፣ {n} ክፍለ-ግዜ ተዛዚሙ</t>
+          <t>ሕሳብ ተመሊሱ</t>
         </is>
       </c>
       <c r="G167" s="13" t="inlineStr">
         <is>
-          <t>Xisaabta waa la demiyay, {n} kalfadhi ayaa dhammaaday</t>
+          <t>Xisaabta waa la soo celiyay</t>
         </is>
       </c>
       <c r="H167" s="14" t="inlineStr"/>
@@ -11791,7 +11791,7 @@
     <row r="168" ht="44" customHeight="1">
       <c r="A168" s="11" t="inlineStr">
         <is>
-          <t>confirm_disable_account</t>
+          <t>account_disabled_n</t>
         </is>
       </c>
       <c r="B168" s="11" t="inlineStr">
@@ -11801,27 +11801,27 @@
       </c>
       <c r="C168" s="11" t="inlineStr">
         <is>
-          <t>Disable this account? They will be signed out immediately.</t>
+          <t>Account disabled, {n} session(s) ended</t>
         </is>
       </c>
       <c r="D168" s="12" t="inlineStr">
         <is>
-          <t>ይህን መለያ ማሰናከል? ወዲያውኑ ይወጣሉ።</t>
+          <t>መለያ ተሰናክሏል፤ {n} ክፍለ-ጊዜ ተዘግቷል</t>
         </is>
       </c>
       <c r="E168" s="13" t="inlineStr">
         <is>
-          <t>Herrega kana dhaabuu? Battalumatti ni baafamu.</t>
+          <t>Herregni dhaabame, session {n} xumurame</t>
         </is>
       </c>
       <c r="F168" s="12" t="inlineStr">
         <is>
-          <t>ነዚ ሕሳብ ክዕገት? ብቕጽበት ይወጹ።</t>
+          <t>ሕሳብ ተዓጊቱ፣ {n} ክፍለ-ግዜ ተዛዚሙ</t>
         </is>
       </c>
       <c r="G168" s="13" t="inlineStr">
         <is>
-          <t>Xisaabtan ma demineysaa? Isla markiiba waa laga saarayaa.</t>
+          <t>Xisaabta waa la demiyay, {n} kalfadhi ayaa dhammaaday</t>
         </is>
       </c>
       <c r="H168" s="14" t="inlineStr"/>
@@ -11829,7 +11829,7 @@
     <row r="169" ht="44" customHeight="1">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>action_document_created</t>
+          <t>confirm_disable_account</t>
         </is>
       </c>
       <c r="B169" s="11" t="inlineStr">
@@ -11839,27 +11839,27 @@
       </c>
       <c r="C169" s="11" t="inlineStr">
         <is>
-          <t>added an article</t>
+          <t>Disable this account? They will be signed out immediately.</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ጨምሯል</t>
+          <t>ይህን መለያ ማሰናከል? ወዲያውኑ ይወጣሉ።</t>
         </is>
       </c>
       <c r="E169" s="13" t="inlineStr">
         <is>
-          <t>barruu dabale</t>
+          <t>Herrega kana dhaabuu? Battalumatti ni baafamu.</t>
         </is>
       </c>
       <c r="F169" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ወሲኹ</t>
+          <t>ነዚ ሕሳብ ክዕገት? ብቕጽበት ይወጹ።</t>
         </is>
       </c>
       <c r="G169" s="13" t="inlineStr">
         <is>
-          <t>maqaal ku daray</t>
+          <t>Xisaabtan ma demineysaa? Isla markiiba waa laga saarayaa.</t>
         </is>
       </c>
       <c r="H169" s="14" t="inlineStr"/>
@@ -11867,7 +11867,7 @@
     <row r="170" ht="44" customHeight="1">
       <c r="A170" s="11" t="inlineStr">
         <is>
-          <t>action_document_updated</t>
+          <t>action_document_created</t>
         </is>
       </c>
       <c r="B170" s="11" t="inlineStr">
@@ -11877,27 +11877,27 @@
       </c>
       <c r="C170" s="11" t="inlineStr">
         <is>
-          <t>edited an article</t>
+          <t>added an article</t>
         </is>
       </c>
       <c r="D170" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ አርሟል</t>
+          <t>ጽሑፍ ጨምሯል</t>
         </is>
       </c>
       <c r="E170" s="13" t="inlineStr">
         <is>
-          <t>barruu gulaale</t>
+          <t>barruu dabale</t>
         </is>
       </c>
       <c r="F170" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ኣርሚዑ</t>
+          <t>ጽሑፍ ወሲኹ</t>
         </is>
       </c>
       <c r="G170" s="13" t="inlineStr">
         <is>
-          <t>maqaal wax ka beddelay</t>
+          <t>maqaal ku daray</t>
         </is>
       </c>
       <c r="H170" s="14" t="inlineStr"/>
@@ -11905,7 +11905,7 @@
     <row r="171" ht="44" customHeight="1">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>action_document_deleted</t>
+          <t>action_document_updated</t>
         </is>
       </c>
       <c r="B171" s="11" t="inlineStr">
@@ -11915,27 +11915,27 @@
       </c>
       <c r="C171" s="11" t="inlineStr">
         <is>
-          <t>deleted an article</t>
+          <t>edited an article</t>
         </is>
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ሰርዟል</t>
+          <t>ጽሑፍ አርሟል</t>
         </is>
       </c>
       <c r="E171" s="13" t="inlineStr">
         <is>
-          <t>barruu haqe</t>
+          <t>barruu gulaale</t>
         </is>
       </c>
       <c r="F171" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ደምሲሱ</t>
+          <t>ጽሑፍ ኣርሚዑ</t>
         </is>
       </c>
       <c r="G171" s="13" t="inlineStr">
         <is>
-          <t>maqaal tirtiray</t>
+          <t>maqaal wax ka beddelay</t>
         </is>
       </c>
       <c r="H171" s="14" t="inlineStr"/>
@@ -11943,7 +11943,7 @@
     <row r="172" ht="44" customHeight="1">
       <c r="A172" s="11" t="inlineStr">
         <is>
-          <t>action_documents_bulk_imported</t>
+          <t>action_document_deleted</t>
         </is>
       </c>
       <c r="B172" s="11" t="inlineStr">
@@ -11953,27 +11953,27 @@
       </c>
       <c r="C172" s="11" t="inlineStr">
         <is>
-          <t>imported articles</t>
+          <t>deleted an article</t>
         </is>
       </c>
       <c r="D172" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፎችን አስገብቷል</t>
+          <t>ጽሑፍ ሰርዟል</t>
         </is>
       </c>
       <c r="E172" s="13" t="inlineStr">
         <is>
-          <t>barruulee galche</t>
+          <t>barruu haqe</t>
         </is>
       </c>
       <c r="F172" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፋት ኣእትዩ</t>
+          <t>ጽሑፍ ደምሲሱ</t>
         </is>
       </c>
       <c r="G172" s="13" t="inlineStr">
         <is>
-          <t>maqaallo soo dhoofiyay</t>
+          <t>maqaal tirtiray</t>
         </is>
       </c>
       <c r="H172" s="14" t="inlineStr"/>
@@ -11981,7 +11981,7 @@
     <row r="173" ht="44" customHeight="1">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_closed</t>
+          <t>action_documents_bulk_imported</t>
         </is>
       </c>
       <c r="B173" s="11" t="inlineStr">
@@ -11991,27 +11991,27 @@
       </c>
       <c r="C173" s="11" t="inlineStr">
         <is>
-          <t>closed an escalation</t>
+          <t>imported articles</t>
         </is>
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ ዘግቷል</t>
+          <t>ጽሑፎችን አስገብቷል</t>
         </is>
       </c>
       <c r="E173" s="13" t="inlineStr">
         <is>
-          <t>dhimma cufe</t>
+          <t>barruulee galche</t>
         </is>
       </c>
       <c r="F173" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ ዓጺዩ</t>
+          <t>ጽሑፋት ኣእትዩ</t>
         </is>
       </c>
       <c r="G173" s="13" t="inlineStr">
         <is>
-          <t>arrin xiray</t>
+          <t>maqaallo soo dhoofiyay</t>
         </is>
       </c>
       <c r="H173" s="14" t="inlineStr"/>
@@ -12019,7 +12019,7 @@
     <row r="174" ht="44" customHeight="1">
       <c r="A174" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_reopened</t>
+          <t>action_handoff_closed</t>
         </is>
       </c>
       <c r="B174" s="11" t="inlineStr">
@@ -12029,27 +12029,27 @@
       </c>
       <c r="C174" s="11" t="inlineStr">
         <is>
-          <t>reopened an escalation</t>
+          <t>closed an escalation</t>
         </is>
       </c>
       <c r="D174" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ በድጋሚ ከፍቷል</t>
+          <t>ጉዳይ ዘግቷል</t>
         </is>
       </c>
       <c r="E174" s="13" t="inlineStr">
         <is>
-          <t>dhimma irra deebi'ee bane</t>
+          <t>dhimma cufe</t>
         </is>
       </c>
       <c r="F174" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ ደጊሙ ከፊቱ</t>
+          <t>ጉዳይ ዓጺዩ</t>
         </is>
       </c>
       <c r="G174" s="13" t="inlineStr">
         <is>
-          <t>arrin dib u furay</t>
+          <t>arrin xiray</t>
         </is>
       </c>
       <c r="H174" s="14" t="inlineStr"/>
@@ -12057,7 +12057,7 @@
     <row r="175" ht="44" customHeight="1">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_webhook_connected</t>
+          <t>action_handoff_reopened</t>
         </is>
       </c>
       <c r="B175" s="11" t="inlineStr">
@@ -12067,27 +12067,27 @@
       </c>
       <c r="C175" s="11" t="inlineStr">
         <is>
-          <t>connected the escalation webhook</t>
+          <t>reopened an escalation</t>
         </is>
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ዌብሁክ አገናኝቷል</t>
+          <t>ጉዳይ በድጋሚ ከፍቷል</t>
         </is>
       </c>
       <c r="E175" s="13" t="inlineStr">
         <is>
-          <t>webhook dabarsaa walqunnamsiise</t>
+          <t>dhimma irra deebi'ee bane</t>
         </is>
       </c>
       <c r="F175" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ምትሕልላፍ ኣራኺቡ</t>
+          <t>ጉዳይ ደጊሙ ከፊቱ</t>
         </is>
       </c>
       <c r="G175" s="13" t="inlineStr">
         <is>
-          <t>ku xiray webhook-ga gudbinta</t>
+          <t>arrin dib u furay</t>
         </is>
       </c>
       <c r="H175" s="14" t="inlineStr"/>
@@ -12095,7 +12095,7 @@
     <row r="176" ht="44" customHeight="1">
       <c r="A176" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_webhook_disconnected</t>
+          <t>action_handoff_webhook_connected</t>
         </is>
       </c>
       <c r="B176" s="11" t="inlineStr">
@@ -12105,27 +12105,27 @@
       </c>
       <c r="C176" s="11" t="inlineStr">
         <is>
-          <t>disconnected the escalation webhook</t>
+          <t>connected the escalation webhook</t>
         </is>
       </c>
       <c r="D176" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ዌብሁክ አቋርጧል</t>
+          <t>የማሸጋገሪያ ዌብሁክ አገናኝቷል</t>
         </is>
       </c>
       <c r="E176" s="13" t="inlineStr">
         <is>
-          <t>webhook dabarsaa addaan kute</t>
+          <t>webhook dabarsaa walqunnamsiise</t>
         </is>
       </c>
       <c r="F176" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ምትሕልላፍ ቆሪጹ</t>
+          <t>ዌብሁክ ምትሕልላፍ ኣራኺቡ</t>
         </is>
       </c>
       <c r="G176" s="13" t="inlineStr">
         <is>
-          <t>goynay webhook-ga gudbinta</t>
+          <t>ku xiray webhook-ga gudbinta</t>
         </is>
       </c>
       <c r="H176" s="14" t="inlineStr"/>
@@ -12133,7 +12133,7 @@
     <row r="177" ht="44" customHeight="1">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>action_telegram_connected</t>
+          <t>action_handoff_webhook_disconnected</t>
         </is>
       </c>
       <c r="B177" s="11" t="inlineStr">
@@ -12143,27 +12143,27 @@
       </c>
       <c r="C177" s="11" t="inlineStr">
         <is>
-          <t>connected Telegram</t>
+          <t>disconnected the escalation webhook</t>
         </is>
       </c>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>ቴሌግራም አገናኝቷል</t>
+          <t>የማሸጋገሪያ ዌብሁክ አቋርጧል</t>
         </is>
       </c>
       <c r="E177" s="13" t="inlineStr">
         <is>
-          <t>Telegram walqunnamsiise</t>
+          <t>webhook dabarsaa addaan kute</t>
         </is>
       </c>
       <c r="F177" s="12" t="inlineStr">
         <is>
-          <t>ቴሌግራም ኣራኺቡ</t>
+          <t>ዌብሁክ ምትሕልላፍ ቆሪጹ</t>
         </is>
       </c>
       <c r="G177" s="13" t="inlineStr">
         <is>
-          <t>Telegram ku xiray</t>
+          <t>goynay webhook-ga gudbinta</t>
         </is>
       </c>
       <c r="H177" s="14" t="inlineStr"/>
@@ -12171,7 +12171,7 @@
     <row r="178" ht="44" customHeight="1">
       <c r="A178" s="11" t="inlineStr">
         <is>
-          <t>action_user_created</t>
+          <t>action_telegram_connected</t>
         </is>
       </c>
       <c r="B178" s="11" t="inlineStr">
@@ -12181,27 +12181,27 @@
       </c>
       <c r="C178" s="11" t="inlineStr">
         <is>
-          <t>added a colleague</t>
+          <t>connected Telegram</t>
         </is>
       </c>
       <c r="D178" s="12" t="inlineStr">
         <is>
-          <t>ባልደረባ ጨምሯል</t>
+          <t>ቴሌግራም አገናኝቷል</t>
         </is>
       </c>
       <c r="E178" s="13" t="inlineStr">
         <is>
-          <t>hojjetaa dabale</t>
+          <t>Telegram walqunnamsiise</t>
         </is>
       </c>
       <c r="F178" s="12" t="inlineStr">
         <is>
-          <t>መሳርሕቲ ወሲኹ</t>
+          <t>ቴሌግራም ኣራኺቡ</t>
         </is>
       </c>
       <c r="G178" s="13" t="inlineStr">
         <is>
-          <t>shaqaale ku daray</t>
+          <t>Telegram ku xiray</t>
         </is>
       </c>
       <c r="H178" s="14" t="inlineStr"/>
@@ -12209,7 +12209,7 @@
     <row r="179" ht="44" customHeight="1">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>action_user_disabled</t>
+          <t>action_user_created</t>
         </is>
       </c>
       <c r="B179" s="11" t="inlineStr">
@@ -12219,27 +12219,27 @@
       </c>
       <c r="C179" s="11" t="inlineStr">
         <is>
-          <t>disabled an account</t>
+          <t>added a colleague</t>
         </is>
       </c>
       <c r="D179" s="12" t="inlineStr">
         <is>
-          <t>መለያ አሰናክሏል</t>
+          <t>ባልደረባ ጨምሯል</t>
         </is>
       </c>
       <c r="E179" s="13" t="inlineStr">
         <is>
-          <t>herrega dhaabe</t>
+          <t>hojjetaa dabale</t>
         </is>
       </c>
       <c r="F179" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ ዓጊቱ</t>
+          <t>መሳርሕቲ ወሲኹ</t>
         </is>
       </c>
       <c r="G179" s="13" t="inlineStr">
         <is>
-          <t>xisaab demiyay</t>
+          <t>shaqaale ku daray</t>
         </is>
       </c>
       <c r="H179" s="14" t="inlineStr"/>
@@ -12247,7 +12247,7 @@
     <row r="180" ht="44" customHeight="1">
       <c r="A180" s="11" t="inlineStr">
         <is>
-          <t>action_user_enabled</t>
+          <t>action_user_disabled</t>
         </is>
       </c>
       <c r="B180" s="11" t="inlineStr">
@@ -12257,27 +12257,27 @@
       </c>
       <c r="C180" s="11" t="inlineStr">
         <is>
-          <t>restored an account</t>
+          <t>disabled an account</t>
         </is>
       </c>
       <c r="D180" s="12" t="inlineStr">
         <is>
-          <t>መለያ መልሷል</t>
+          <t>መለያ አሰናክሏል</t>
         </is>
       </c>
       <c r="E180" s="13" t="inlineStr">
         <is>
-          <t>herrega deebise</t>
+          <t>herrega dhaabe</t>
         </is>
       </c>
       <c r="F180" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ መሊሱ</t>
+          <t>ሕሳብ ዓጊቱ</t>
         </is>
       </c>
       <c r="G180" s="13" t="inlineStr">
         <is>
-          <t>xisaab soo celiyay</t>
+          <t>xisaab demiyay</t>
         </is>
       </c>
       <c r="H180" s="14" t="inlineStr"/>
@@ -12285,7 +12285,7 @@
     <row r="181" ht="44" customHeight="1">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t>action_admin_login</t>
+          <t>action_user_enabled</t>
         </is>
       </c>
       <c r="B181" s="11" t="inlineStr">
@@ -12295,27 +12295,27 @@
       </c>
       <c r="C181" s="11" t="inlineStr">
         <is>
-          <t>signed in</t>
+          <t>restored an account</t>
         </is>
       </c>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>ገብቷል</t>
+          <t>መለያ መልሷል</t>
         </is>
       </c>
       <c r="E181" s="13" t="inlineStr">
         <is>
-          <t>seene</t>
+          <t>herrega deebise</t>
         </is>
       </c>
       <c r="F181" s="12" t="inlineStr">
         <is>
-          <t>ኣትዩ</t>
+          <t>ሕሳብ መሊሱ</t>
         </is>
       </c>
       <c r="G181" s="13" t="inlineStr">
         <is>
-          <t>gashay</t>
+          <t>xisaab soo celiyay</t>
         </is>
       </c>
       <c r="H181" s="14" t="inlineStr"/>
@@ -12323,7 +12323,7 @@
     <row r="182" ht="44" customHeight="1">
       <c r="A182" s="11" t="inlineStr">
         <is>
-          <t>action_password_changed</t>
+          <t>action_admin_login</t>
         </is>
       </c>
       <c r="B182" s="11" t="inlineStr">
@@ -12333,27 +12333,27 @@
       </c>
       <c r="C182" s="11" t="inlineStr">
         <is>
-          <t>changed their password</t>
+          <t>signed in</t>
         </is>
       </c>
       <c r="D182" s="12" t="inlineStr">
         <is>
-          <t>የይለፍ ቃል ቀይሯል</t>
+          <t>ገብቷል</t>
         </is>
       </c>
       <c r="E182" s="13" t="inlineStr">
         <is>
-          <t>jecha darbii jijjiire</t>
+          <t>seene</t>
         </is>
       </c>
       <c r="F182" s="12" t="inlineStr">
         <is>
-          <t>መሕለፊ ቃል ቀዪሩ</t>
+          <t>ኣትዩ</t>
         </is>
       </c>
       <c r="G182" s="13" t="inlineStr">
         <is>
-          <t>beddelay furihiisa</t>
+          <t>gashay</t>
         </is>
       </c>
       <c r="H182" s="14" t="inlineStr"/>
@@ -12361,7 +12361,7 @@
     <row r="183" ht="44" customHeight="1">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t>nothing_yet</t>
+          <t>action_password_changed</t>
         </is>
       </c>
       <c r="B183" s="11" t="inlineStr">
@@ -12371,27 +12371,27 @@
       </c>
       <c r="C183" s="11" t="inlineStr">
         <is>
-          <t>Nothing yet.</t>
+          <t>changed their password</t>
         </is>
       </c>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>እስካሁን ምንም የለም።</t>
+          <t>የይለፍ ቃል ቀይሯል</t>
         </is>
       </c>
       <c r="E183" s="13" t="inlineStr">
         <is>
-          <t>Ammaaf homaa hin jiru.</t>
+          <t>jecha darbii jijjiire</t>
         </is>
       </c>
       <c r="F183" s="12" t="inlineStr">
         <is>
-          <t>ክሳብ ሕጂ ዋላ ሓደ የለን።</t>
+          <t>መሕለፊ ቃል ቀዪሩ</t>
         </is>
       </c>
       <c r="G183" s="13" t="inlineStr">
         <is>
-          <t>Weli waxba ma jiraan.</t>
+          <t>beddelay furihiisa</t>
         </is>
       </c>
       <c r="H183" s="14" t="inlineStr"/>
@@ -12399,7 +12399,7 @@
     <row r="184" ht="44" customHeight="1">
       <c r="A184" s="11" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>nothing_yet</t>
         </is>
       </c>
       <c r="B184" s="11" t="inlineStr">
@@ -12409,27 +12409,27 @@
       </c>
       <c r="C184" s="11" t="inlineStr">
         <is>
-          <t>Unavailable.</t>
+          <t>Nothing yet.</t>
         </is>
       </c>
       <c r="D184" s="12" t="inlineStr">
         <is>
-          <t>አይገኝም።</t>
+          <t>እስካሁን ምንም የለም።</t>
         </is>
       </c>
       <c r="E184" s="13" t="inlineStr">
         <is>
-          <t>Hin argamu.</t>
+          <t>Ammaaf homaa hin jiru.</t>
         </is>
       </c>
       <c r="F184" s="12" t="inlineStr">
         <is>
-          <t>ኣይርከብን።</t>
+          <t>ክሳብ ሕጂ ዋላ ሓደ የለን።</t>
         </is>
       </c>
       <c r="G184" s="13" t="inlineStr">
         <is>
-          <t>Lama heli karo.</t>
+          <t>Weli waxba ma jiraan.</t>
         </is>
       </c>
       <c r="H184" s="14" t="inlineStr"/>
@@ -12437,7 +12437,7 @@
     <row r="185" ht="44" customHeight="1">
       <c r="A185" s="11" t="inlineStr">
         <is>
-          <t>just_now</t>
+          <t>unavailable</t>
         </is>
       </c>
       <c r="B185" s="11" t="inlineStr">
@@ -12447,27 +12447,27 @@
       </c>
       <c r="C185" s="11" t="inlineStr">
         <is>
-          <t>just now</t>
+          <t>Unavailable.</t>
         </is>
       </c>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>አሁን</t>
+          <t>አይገኝም።</t>
         </is>
       </c>
       <c r="E185" s="13" t="inlineStr">
         <is>
-          <t>amma</t>
+          <t>Hin argamu.</t>
         </is>
       </c>
       <c r="F185" s="12" t="inlineStr">
         <is>
-          <t>ሕጂ</t>
+          <t>ኣይርከብን።</t>
         </is>
       </c>
       <c r="G185" s="13" t="inlineStr">
         <is>
-          <t>hadda</t>
+          <t>Lama heli karo.</t>
         </is>
       </c>
       <c r="H185" s="14" t="inlineStr"/>
@@ -12475,7 +12475,7 @@
     <row r="186" ht="44" customHeight="1">
       <c r="A186" s="11" t="inlineStr">
         <is>
-          <t>n_min_ago</t>
+          <t>just_now</t>
         </is>
       </c>
       <c r="B186" s="11" t="inlineStr">
@@ -12485,27 +12485,27 @@
       </c>
       <c r="C186" s="11" t="inlineStr">
         <is>
-          <t>{n} min ago</t>
+          <t>just now</t>
         </is>
       </c>
       <c r="D186" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ደቂቃ በፊት</t>
+          <t>አሁን</t>
         </is>
       </c>
       <c r="E186" s="13" t="inlineStr">
         <is>
-          <t>daqiiqaa {n} dura</t>
+          <t>amma</t>
         </is>
       </c>
       <c r="F186" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ደቒቕ</t>
+          <t>ሕጂ</t>
         </is>
       </c>
       <c r="G186" s="13" t="inlineStr">
         <is>
-          <t>{n} daqiiqo ka hor</t>
+          <t>hadda</t>
         </is>
       </c>
       <c r="H186" s="14" t="inlineStr"/>
@@ -12513,7 +12513,7 @@
     <row r="187" ht="44" customHeight="1">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t>n_h_ago</t>
+          <t>n_min_ago</t>
         </is>
       </c>
       <c r="B187" s="11" t="inlineStr">
@@ -12523,27 +12523,27 @@
       </c>
       <c r="C187" s="11" t="inlineStr">
         <is>
-          <t>{n} h ago</t>
+          <t>{n} min ago</t>
         </is>
       </c>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ሰዓት በፊት</t>
+          <t>ከ{n} ደቂቃ በፊት</t>
         </is>
       </c>
       <c r="E187" s="13" t="inlineStr">
         <is>
-          <t>sa'aatii {n} dura</t>
+          <t>daqiiqaa {n} dura</t>
         </is>
       </c>
       <c r="F187" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ሰዓት</t>
+          <t>ቅድሚ {n} ደቒቕ</t>
         </is>
       </c>
       <c r="G187" s="13" t="inlineStr">
         <is>
-          <t>{n} saac ka hor</t>
+          <t>{n} daqiiqo ka hor</t>
         </is>
       </c>
       <c r="H187" s="14" t="inlineStr"/>
@@ -12551,7 +12551,7 @@
     <row r="188" ht="44" customHeight="1">
       <c r="A188" s="11" t="inlineStr">
         <is>
-          <t>n_d_ago</t>
+          <t>n_h_ago</t>
         </is>
       </c>
       <c r="B188" s="11" t="inlineStr">
@@ -12561,27 +12561,27 @@
       </c>
       <c r="C188" s="11" t="inlineStr">
         <is>
-          <t>{n} d ago</t>
+          <t>{n} h ago</t>
         </is>
       </c>
       <c r="D188" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ቀን በፊት</t>
+          <t>ከ{n} ሰዓት በፊት</t>
         </is>
       </c>
       <c r="E188" s="13" t="inlineStr">
         <is>
-          <t>guyyaa {n} dura</t>
+          <t>sa'aatii {n} dura</t>
         </is>
       </c>
       <c r="F188" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} መዓልቲ</t>
+          <t>ቅድሚ {n} ሰዓት</t>
         </is>
       </c>
       <c r="G188" s="13" t="inlineStr">
         <is>
-          <t>{n} maalmood ka hor</t>
+          <t>{n} saac ka hor</t>
         </is>
       </c>
       <c r="H188" s="14" t="inlineStr"/>
@@ -12589,7 +12589,7 @@
     <row r="189" ht="44" customHeight="1">
       <c r="A189" s="11" t="inlineStr">
         <is>
-          <t>channel_all_from</t>
+          <t>n_d_ago</t>
         </is>
       </c>
       <c r="B189" s="11" t="inlineStr">
@@ -12599,27 +12599,27 @@
       </c>
       <c r="C189" s="11" t="inlineStr">
         <is>
-          <t>All {n} conversations came from {label}.</t>
+          <t>{n} d ago</t>
         </is>
       </c>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>ሁሉም {n} ውይይቶች ከ{label} መጥተዋል።</t>
+          <t>ከ{n} ቀን በፊት</t>
         </is>
       </c>
       <c r="E189" s="13" t="inlineStr">
         <is>
-          <t>Mariin {n} hundi {label} irraa dhufe.</t>
+          <t>guyyaa {n} dura</t>
         </is>
       </c>
       <c r="F189" s="12" t="inlineStr">
         <is>
-          <t>ኩሎም {n} ዝርርባት ካብ {label} መጺኦም።</t>
+          <t>ቅድሚ {n} መዓልቲ</t>
         </is>
       </c>
       <c r="G189" s="13" t="inlineStr">
         <is>
-          <t>Dhammaan {n} wadahadal waxay ka yimaadeen {label}.</t>
+          <t>{n} maalmood ka hor</t>
         </is>
       </c>
       <c r="H189" s="14" t="inlineStr"/>
@@ -12627,7 +12627,7 @@
     <row r="190" ht="44" customHeight="1">
       <c r="A190" s="11" t="inlineStr">
         <is>
-          <t>channel_live</t>
+          <t>channel_all_from</t>
         </is>
       </c>
       <c r="B190" s="11" t="inlineStr">
@@ -12637,27 +12637,27 @@
       </c>
       <c r="C190" s="11" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>All {n} conversations came from {label}.</t>
         </is>
       </c>
       <c r="D190" s="12" t="inlineStr">
         <is>
-          <t>በሥራ ላይ</t>
+          <t>ሁሉም {n} ውይይቶች ከ{label} መጥተዋል።</t>
         </is>
       </c>
       <c r="E190" s="13" t="inlineStr">
         <is>
-          <t>Hojiirra</t>
+          <t>Mariin {n} hundi {label} irraa dhufe.</t>
         </is>
       </c>
       <c r="F190" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ስራሕ</t>
+          <t>ኩሎም {n} ዝርርባት ካብ {label} መጺኦም።</t>
         </is>
       </c>
       <c r="G190" s="13" t="inlineStr">
         <is>
-          <t>Shaqeynaya</t>
+          <t>Dhammaan {n} wadahadal waxay ka yimaadeen {label}.</t>
         </is>
       </c>
       <c r="H190" s="14" t="inlineStr"/>
@@ -12665,7 +12665,7 @@
     <row r="191" ht="44" customHeight="1">
       <c r="A191" s="11" t="inlineStr">
         <is>
-          <t>channel_ready</t>
+          <t>channel_live</t>
         </is>
       </c>
       <c r="B191" s="11" t="inlineStr">
@@ -12675,27 +12675,27 @@
       </c>
       <c r="C191" s="11" t="inlineStr">
         <is>
-          <t>Ready to connect</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="D191" s="12" t="inlineStr">
         <is>
-          <t>ለመገናኘት ዝግጁ</t>
+          <t>በሥራ ላይ</t>
         </is>
       </c>
       <c r="E191" s="13" t="inlineStr">
         <is>
-          <t>Walqunnamuuf qophaa'aa</t>
+          <t>Hojiirra</t>
         </is>
       </c>
       <c r="F191" s="12" t="inlineStr">
         <is>
-          <t>ንምርኻብ ድሉው</t>
+          <t>ኣብ ስራሕ</t>
         </is>
       </c>
       <c r="G191" s="13" t="inlineStr">
         <is>
-          <t>Diyaar u ah xiriirka</t>
+          <t>Shaqeynaya</t>
         </is>
       </c>
       <c r="H191" s="14" t="inlineStr"/>
@@ -12703,7 +12703,7 @@
     <row r="192" ht="44" customHeight="1">
       <c r="A192" s="11" t="inlineStr">
         <is>
-          <t>channel_needs_setup</t>
+          <t>channel_ready</t>
         </is>
       </c>
       <c r="B192" s="11" t="inlineStr">
@@ -12713,27 +12713,27 @@
       </c>
       <c r="C192" s="11" t="inlineStr">
         <is>
-          <t>Needs setup</t>
+          <t>Ready to connect</t>
         </is>
       </c>
       <c r="D192" s="12" t="inlineStr">
         <is>
-          <t>ማዋቀር ይፈልጋል</t>
+          <t>ለመገናኘት ዝግጁ</t>
         </is>
       </c>
       <c r="E192" s="13" t="inlineStr">
         <is>
-          <t>Qindeessuu barbaada</t>
+          <t>Walqunnamuuf qophaa'aa</t>
         </is>
       </c>
       <c r="F192" s="12" t="inlineStr">
         <is>
-          <t>ምድላው የድልዮ</t>
+          <t>ንምርኻብ ድሉው</t>
         </is>
       </c>
       <c r="G192" s="13" t="inlineStr">
         <is>
-          <t>Waxay u baahan tahay dejin</t>
+          <t>Diyaar u ah xiriirka</t>
         </is>
       </c>
       <c r="H192" s="14" t="inlineStr"/>
@@ -12741,7 +12741,7 @@
     <row r="193" ht="44" customHeight="1">
       <c r="A193" s="11" t="inlineStr">
         <is>
-          <t>share_by_channel</t>
+          <t>channel_needs_setup</t>
         </is>
       </c>
       <c r="B193" s="11" t="inlineStr">
@@ -12751,27 +12751,27 @@
       </c>
       <c r="C193" s="11" t="inlineStr">
         <is>
-          <t>Share of conversations by channel</t>
+          <t>Needs setup</t>
         </is>
       </c>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>በመስመር የተከፋፈሉ ውይይቶች ድርሻ</t>
+          <t>ማዋቀር ይፈልጋል</t>
         </is>
       </c>
       <c r="E193" s="13" t="inlineStr">
         <is>
-          <t>Qooda marii karaa tokkoon tokkoon isaanii</t>
+          <t>Qindeessuu barbaada</t>
         </is>
       </c>
       <c r="F193" s="12" t="inlineStr">
         <is>
-          <t>ብመስመር ዝተኸፋፈለ ግደ ዝርርባት</t>
+          <t>ምድላው የድልዮ</t>
         </is>
       </c>
       <c r="G193" s="13" t="inlineStr">
         <is>
-          <t>Qaybta wadahadallada kanaalka</t>
+          <t>Waxay u baahan tahay dejin</t>
         </is>
       </c>
       <c r="H193" s="14" t="inlineStr"/>
@@ -12779,7 +12779,7 @@
     <row r="194" ht="44" customHeight="1">
       <c r="A194" s="11" t="inlineStr">
         <is>
-          <t>up_to_date</t>
+          <t>share_by_channel</t>
         </is>
       </c>
       <c r="B194" s="11" t="inlineStr">
@@ -12789,27 +12789,27 @@
       </c>
       <c r="C194" s="11" t="inlineStr">
         <is>
-          <t>Up to date</t>
+          <t>Share of conversations by channel</t>
         </is>
       </c>
       <c r="D194" s="12" t="inlineStr">
         <is>
-          <t>የተዘመነ</t>
+          <t>በመስመር የተከፋፈሉ ውይይቶች ድርሻ</t>
         </is>
       </c>
       <c r="E194" s="13" t="inlineStr">
         <is>
-          <t>Haaraa</t>
+          <t>Qooda marii karaa tokkoon tokkoon isaanii</t>
         </is>
       </c>
       <c r="F194" s="12" t="inlineStr">
         <is>
-          <t>ዝተሓደሰ</t>
+          <t>ብመስመር ዝተኸፋፈለ ግደ ዝርርባት</t>
         </is>
       </c>
       <c r="G194" s="13" t="inlineStr">
         <is>
-          <t>La cusbooneysiiyay</t>
+          <t>Qaybta wadahadallada kanaalka</t>
         </is>
       </c>
       <c r="H194" s="14" t="inlineStr"/>
@@ -12817,7 +12817,7 @@
     <row r="195" ht="44" customHeight="1">
       <c r="A195" s="11" t="inlineStr">
         <is>
-          <t>updated_m_ago</t>
+          <t>up_to_date</t>
         </is>
       </c>
       <c r="B195" s="11" t="inlineStr">
@@ -12827,27 +12827,27 @@
       </c>
       <c r="C195" s="11" t="inlineStr">
         <is>
-          <t>Updated {n}m ago</t>
+          <t>Up to date</t>
         </is>
       </c>
       <c r="D195" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ደቂቃ በፊት ተዘምኗል</t>
+          <t>የተዘመነ</t>
         </is>
       </c>
       <c r="E195" s="13" t="inlineStr">
         <is>
-          <t>Daqiiqaa {n} dura haaromfame</t>
+          <t>Haaraa</t>
         </is>
       </c>
       <c r="F195" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ደቒቕ ተሓዲሱ</t>
+          <t>ዝተሓደሰ</t>
         </is>
       </c>
       <c r="G195" s="13" t="inlineStr">
         <is>
-          <t>La cusbooneysiiyay {n}daq ka hor</t>
+          <t>La cusbooneysiiyay</t>
         </is>
       </c>
       <c r="H195" s="14" t="inlineStr"/>
@@ -12855,7 +12855,7 @@
     <row r="196" ht="44" customHeight="1">
       <c r="A196" s="11" t="inlineStr">
         <is>
-          <t>updated_h_ago</t>
+          <t>updated_m_ago</t>
         </is>
       </c>
       <c r="B196" s="11" t="inlineStr">
@@ -12865,27 +12865,27 @@
       </c>
       <c r="C196" s="11" t="inlineStr">
         <is>
-          <t>Updated {n}h ago</t>
+          <t>Updated {n}m ago</t>
         </is>
       </c>
       <c r="D196" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ሰዓት በፊት ተዘምኗል</t>
+          <t>ከ{n} ደቂቃ በፊት ተዘምኗል</t>
         </is>
       </c>
       <c r="E196" s="13" t="inlineStr">
         <is>
-          <t>Sa'aatii {n} dura haaromfame</t>
+          <t>Daqiiqaa {n} dura haaromfame</t>
         </is>
       </c>
       <c r="F196" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ሰዓት ተሓዲሱ</t>
+          <t>ቅድሚ {n} ደቒቕ ተሓዲሱ</t>
         </is>
       </c>
       <c r="G196" s="13" t="inlineStr">
         <is>
-          <t>La cusbooneysiiyay {n}saac ka hor</t>
+          <t>La cusbooneysiiyay {n}daq ka hor</t>
         </is>
       </c>
       <c r="H196" s="14" t="inlineStr"/>
@@ -12893,7 +12893,7 @@
     <row r="197" ht="44" customHeight="1">
       <c r="A197" s="11" t="inlineStr">
         <is>
-          <t>queue</t>
+          <t>updated_h_ago</t>
         </is>
       </c>
       <c r="B197" s="11" t="inlineStr">
@@ -12903,27 +12903,27 @@
       </c>
       <c r="C197" s="11" t="inlineStr">
         <is>
-          <t>Queue</t>
+          <t>Updated {n}h ago</t>
         </is>
       </c>
       <c r="D197" s="12" t="inlineStr">
         <is>
-          <t>ወረፋ</t>
+          <t>ከ{n} ሰዓት በፊት ተዘምኗል</t>
         </is>
       </c>
       <c r="E197" s="13" t="inlineStr">
         <is>
-          <t>Sararaa</t>
+          <t>Sa'aatii {n} dura haaromfame</t>
         </is>
       </c>
       <c r="F197" s="12" t="inlineStr">
         <is>
-          <t>ሪጋ</t>
+          <t>ቅድሚ {n} ሰዓት ተሓዲሱ</t>
         </is>
       </c>
       <c r="G197" s="13" t="inlineStr">
         <is>
-          <t>Safka</t>
+          <t>La cusbooneysiiyay {n}saac ka hor</t>
         </is>
       </c>
       <c r="H197" s="14" t="inlineStr"/>
@@ -12931,7 +12931,7 @@
     <row r="198" ht="44" customHeight="1">
       <c r="A198" s="11" t="inlineStr">
         <is>
-          <t>collapse</t>
+          <t>queue</t>
         </is>
       </c>
       <c r="B198" s="11" t="inlineStr">
@@ -12941,27 +12941,27 @@
       </c>
       <c r="C198" s="11" t="inlineStr">
         <is>
-          <t>Collapse</t>
+          <t>Queue</t>
         </is>
       </c>
       <c r="D198" s="12" t="inlineStr">
         <is>
-          <t>አጥብብ</t>
+          <t>ወረፋ</t>
         </is>
       </c>
       <c r="E198" s="13" t="inlineStr">
         <is>
-          <t>Xiqqeessi</t>
+          <t>Sararaa</t>
         </is>
       </c>
       <c r="F198" s="12" t="inlineStr">
         <is>
-          <t>ኣጽብብ</t>
+          <t>ሪጋ</t>
         </is>
       </c>
       <c r="G198" s="13" t="inlineStr">
         <is>
-          <t>Yaree</t>
+          <t>Safka</t>
         </is>
       </c>
       <c r="H198" s="14" t="inlineStr"/>
@@ -12969,7 +12969,7 @@
     <row r="199" ht="44" customHeight="1">
       <c r="A199" s="11" t="inlineStr">
         <is>
-          <t>expand</t>
+          <t>collapse</t>
         </is>
       </c>
       <c r="B199" s="11" t="inlineStr">
@@ -12979,27 +12979,27 @@
       </c>
       <c r="C199" s="11" t="inlineStr">
         <is>
-          <t>Expand</t>
+          <t>Collapse</t>
         </is>
       </c>
       <c r="D199" s="12" t="inlineStr">
         <is>
-          <t>አስፋ</t>
+          <t>አጥብብ</t>
         </is>
       </c>
       <c r="E199" s="13" t="inlineStr">
         <is>
-          <t>Balleessi</t>
+          <t>Xiqqeessi</t>
         </is>
       </c>
       <c r="F199" s="12" t="inlineStr">
         <is>
-          <t>ኣስፍሕ</t>
+          <t>ኣጽብብ</t>
         </is>
       </c>
       <c r="G199" s="13" t="inlineStr">
         <is>
-          <t>Balaadhi</t>
+          <t>Yaree</t>
         </is>
       </c>
       <c r="H199" s="14" t="inlineStr"/>
@@ -13007,7 +13007,7 @@
     <row r="200" ht="44" customHeight="1">
       <c r="A200" s="11" t="inlineStr">
         <is>
-          <t>collapse_or_expand</t>
+          <t>expand</t>
         </is>
       </c>
       <c r="B200" s="11" t="inlineStr">
@@ -13017,27 +13017,27 @@
       </c>
       <c r="C200" s="11" t="inlineStr">
         <is>
-          <t>Collapse or expand the sidebar</t>
+          <t>Expand</t>
         </is>
       </c>
       <c r="D200" s="12" t="inlineStr">
         <is>
-          <t>የጎን አሞሌውን አጥብብ ወይም አስፋ</t>
+          <t>አስፋ</t>
         </is>
       </c>
       <c r="E200" s="13" t="inlineStr">
         <is>
-          <t>Cinaacha xiqqeessi ykn balleessi</t>
+          <t>Balleessi</t>
         </is>
       </c>
       <c r="F200" s="12" t="inlineStr">
         <is>
-          <t>ናይ ጎኒ መስመር ኣጽብብ ወይ ኣስፍሕ</t>
+          <t>ኣስፍሕ</t>
         </is>
       </c>
       <c r="G200" s="13" t="inlineStr">
         <is>
-          <t>Yaree ama balaadhi dhinaca</t>
+          <t>Balaadhi</t>
         </is>
       </c>
       <c r="H200" s="14" t="inlineStr"/>
@@ -13045,7 +13045,7 @@
     <row r="201" ht="44" customHeight="1">
       <c r="A201" s="11" t="inlineStr">
         <is>
-          <t>show_hide_channels</t>
+          <t>collapse_or_expand</t>
         </is>
       </c>
       <c r="B201" s="11" t="inlineStr">
@@ -13055,27 +13055,27 @@
       </c>
       <c r="C201" s="11" t="inlineStr">
         <is>
-          <t>Show or hide the channel list</t>
+          <t>Collapse or expand the sidebar</t>
         </is>
       </c>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>የመስመሮችን ዝርዝር አሳይ ወይም ደብቅ</t>
+          <t>የጎን አሞሌውን አጥብብ ወይም አስፋ</t>
         </is>
       </c>
       <c r="E201" s="13" t="inlineStr">
         <is>
-          <t>Tarreeffama karaalee agarsiisi ykn dhoksi</t>
+          <t>Cinaacha xiqqeessi ykn balleessi</t>
         </is>
       </c>
       <c r="F201" s="12" t="inlineStr">
         <is>
-          <t>ዝርዝር መስመራት ኣርኢ ወይ ሕባእ</t>
+          <t>ናይ ጎኒ መስመር ኣጽብብ ወይ ኣስፍሕ</t>
         </is>
       </c>
       <c r="G201" s="13" t="inlineStr">
         <is>
-          <t>Muuji ama qari liiska kanaalada</t>
+          <t>Yaree ama balaadhi dhinaca</t>
         </is>
       </c>
       <c r="H201" s="14" t="inlineStr"/>
@@ -13083,7 +13083,7 @@
     <row r="202" ht="44" customHeight="1">
       <c r="A202" s="11" t="inlineStr">
         <is>
-          <t>today</t>
+          <t>show_hide_channels</t>
         </is>
       </c>
       <c r="B202" s="11" t="inlineStr">
@@ -13093,27 +13093,27 @@
       </c>
       <c r="C202" s="11" t="inlineStr">
         <is>
-          <t>Today</t>
+          <t>Show or hide the channel list</t>
         </is>
       </c>
       <c r="D202" s="12" t="inlineStr">
         <is>
-          <t>ዛሬ</t>
+          <t>የመስመሮችን ዝርዝር አሳይ ወይም ደብቅ</t>
         </is>
       </c>
       <c r="E202" s="13" t="inlineStr">
         <is>
-          <t>Har'a</t>
+          <t>Tarreeffama karaalee agarsiisi ykn dhoksi</t>
         </is>
       </c>
       <c r="F202" s="12" t="inlineStr">
         <is>
-          <t>ሎሚ</t>
+          <t>ዝርዝር መስመራት ኣርኢ ወይ ሕባእ</t>
         </is>
       </c>
       <c r="G202" s="13" t="inlineStr">
         <is>
-          <t>Maanta</t>
+          <t>Muuji ama qari liiska kanaalada</t>
         </is>
       </c>
       <c r="H202" s="14" t="inlineStr"/>
@@ -13121,7 +13121,7 @@
     <row r="203" ht="44" customHeight="1">
       <c r="A203" s="11" t="inlineStr">
         <is>
-          <t>yesterday</t>
+          <t>today</t>
         </is>
       </c>
       <c r="B203" s="11" t="inlineStr">
@@ -13131,27 +13131,27 @@
       </c>
       <c r="C203" s="11" t="inlineStr">
         <is>
-          <t>Yesterday</t>
+          <t>Today</t>
         </is>
       </c>
       <c r="D203" s="12" t="inlineStr">
         <is>
-          <t>ትናንት</t>
+          <t>ዛሬ</t>
         </is>
       </c>
       <c r="E203" s="13" t="inlineStr">
         <is>
-          <t>Kaleessa</t>
+          <t>Har'a</t>
         </is>
       </c>
       <c r="F203" s="12" t="inlineStr">
         <is>
-          <t>ትማሊ</t>
+          <t>ሎሚ</t>
         </is>
       </c>
       <c r="G203" s="13" t="inlineStr">
         <is>
-          <t>Shalay</t>
+          <t>Maanta</t>
         </is>
       </c>
       <c r="H203" s="14" t="inlineStr"/>
@@ -13159,7 +13159,7 @@
     <row r="204" ht="44" customHeight="1">
       <c r="A204" s="11" t="inlineStr">
         <is>
-          <t>call_started</t>
+          <t>yesterday</t>
         </is>
       </c>
       <c r="B204" s="11" t="inlineStr">
@@ -13169,27 +13169,27 @@
       </c>
       <c r="C204" s="11" t="inlineStr">
         <is>
-          <t>The customer asked for a person here</t>
+          <t>Yesterday</t>
         </is>
       </c>
       <c r="D204" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛው እዚህ ላይ ሰው ጠየቀ</t>
+          <t>ትናንት</t>
         </is>
       </c>
       <c r="E204" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan asitti nama gaafate</t>
+          <t>Kaleessa</t>
         </is>
       </c>
       <c r="F204" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዓሚል ኣብዚ ሰብ ሓቲቱ</t>
+          <t>ትማሊ</t>
         </is>
       </c>
       <c r="G204" s="13" t="inlineStr">
         <is>
-          <t>Macmiilku halkan ayuu qof weydiistay</t>
+          <t>Shalay</t>
         </is>
       </c>
       <c r="H204" s="14" t="inlineStr"/>
@@ -13197,7 +13197,7 @@
     <row r="205" ht="44" customHeight="1">
       <c r="A205" s="11" t="inlineStr">
         <is>
-          <t>no_messages</t>
+          <t>call_started</t>
         </is>
       </c>
       <c r="B205" s="11" t="inlineStr">
@@ -13207,27 +13207,27 @@
       </c>
       <c r="C205" s="11" t="inlineStr">
         <is>
-          <t>No messages in this conversation.</t>
+          <t>The customer asked for a person here</t>
         </is>
       </c>
       <c r="D205" s="12" t="inlineStr">
         <is>
-          <t>በዚህ ውይይት ውስጥ መልእክት የለም።</t>
+          <t>ደንበኛው እዚህ ላይ ሰው ጠየቀ</t>
         </is>
       </c>
       <c r="E205" s="13" t="inlineStr">
         <is>
-          <t>Marii kana keessa ergaan hin jiru.</t>
+          <t>Maamilaan asitti nama gaafate</t>
         </is>
       </c>
       <c r="F205" s="12" t="inlineStr">
         <is>
-          <t>ኣብዚ ዝርርብ መልእኽቲ የለን።</t>
+          <t>እቲ ዓሚል ኣብዚ ሰብ ሓቲቱ</t>
         </is>
       </c>
       <c r="G205" s="13" t="inlineStr">
         <is>
-          <t>Wadahadalkan fariin kuma jirto.</t>
+          <t>Macmiilku halkan ayuu qof weydiistay</t>
         </is>
       </c>
       <c r="H205" s="14" t="inlineStr"/>
@@ -13235,7 +13235,7 @@
     <row r="206" ht="44" customHeight="1">
       <c r="A206" s="11" t="inlineStr">
         <is>
-          <t>donut_all_in_one</t>
+          <t>no_messages</t>
         </is>
       </c>
       <c r="B206" s="11" t="inlineStr">
@@ -13245,27 +13245,27 @@
       </c>
       <c r="C206" s="11" t="inlineStr">
         <is>
-          <t>The single {unit} was in {label}.</t>
+          <t>No messages in this conversation.</t>
         </is>
       </c>
       <c r="D206" s="12" t="inlineStr">
         <is>
-          <t>ብቸኛው {unit} በ{label} ነበር።</t>
+          <t>በዚህ ውይይት ውስጥ መልእክት የለም።</t>
         </is>
       </c>
       <c r="E206" s="13" t="inlineStr">
         <is>
-          <t>{unit} tokkichi {label} keessa ture.</t>
+          <t>Marii kana keessa ergaan hin jiru.</t>
         </is>
       </c>
       <c r="F206" s="12" t="inlineStr">
         <is>
-          <t>እቲ ሓደ {unit} ብ{label} ነይሩ።</t>
+          <t>ኣብዚ ዝርርብ መልእኽቲ የለን።</t>
         </is>
       </c>
       <c r="G206" s="13" t="inlineStr">
         <is>
-          <t>{unit} kaliya wuxuu ku jiray {label}.</t>
+          <t>Wadahadalkan fariin kuma jirto.</t>
         </is>
       </c>
       <c r="H206" s="14" t="inlineStr"/>
@@ -13273,7 +13273,7 @@
     <row r="207" ht="44" customHeight="1">
       <c r="A207" s="11" t="inlineStr">
         <is>
-          <t>channel_all_from_one</t>
+          <t>donut_all_in_one</t>
         </is>
       </c>
       <c r="B207" s="11" t="inlineStr">
@@ -13283,27 +13283,27 @@
       </c>
       <c r="C207" s="11" t="inlineStr">
         <is>
-          <t>The single conversation came from {label}.</t>
+          <t>The single {unit} was in {label}.</t>
         </is>
       </c>
       <c r="D207" s="12" t="inlineStr">
         <is>
-          <t>ብቸኛው ውይይት ከ{label} መጥቷል።</t>
+          <t>ብቸኛው {unit} በ{label} ነበር።</t>
         </is>
       </c>
       <c r="E207" s="13" t="inlineStr">
         <is>
-          <t>Mariin tokkichi {label} irraa dhufe.</t>
+          <t>{unit} tokkichi {label} keessa ture.</t>
         </is>
       </c>
       <c r="F207" s="12" t="inlineStr">
         <is>
-          <t>እቲ ሓደ ዝርርብ ካብ {label} መጺኡ።</t>
+          <t>እቲ ሓደ {unit} ብ{label} ነይሩ።</t>
         </is>
       </c>
       <c r="G207" s="13" t="inlineStr">
         <is>
-          <t>Wadahadalka kaliya wuxuu ka yimid {label}.</t>
+          <t>{unit} kaliya wuxuu ku jiray {label}.</t>
         </is>
       </c>
       <c r="H207" s="14" t="inlineStr"/>
@@ -13311,7 +13311,7 @@
     <row r="208" ht="44" customHeight="1">
       <c r="A208" s="11" t="inlineStr">
         <is>
-          <t>unit_conversation</t>
+          <t>channel_all_from_one</t>
         </is>
       </c>
       <c r="B208" s="11" t="inlineStr">
@@ -13321,27 +13321,27 @@
       </c>
       <c r="C208" s="11" t="inlineStr">
         <is>
-          <t>conversation</t>
+          <t>The single conversation came from {label}.</t>
         </is>
       </c>
       <c r="D208" s="12" t="inlineStr">
         <is>
-          <t>ውይይት</t>
+          <t>ብቸኛው ውይይት ከ{label} መጥቷል።</t>
         </is>
       </c>
       <c r="E208" s="13" t="inlineStr">
         <is>
-          <t>marii</t>
+          <t>Mariin tokkichi {label} irraa dhufe.</t>
         </is>
       </c>
       <c r="F208" s="12" t="inlineStr">
         <is>
-          <t>ዝርርብ</t>
+          <t>እቲ ሓደ ዝርርብ ካብ {label} መጺኡ።</t>
         </is>
       </c>
       <c r="G208" s="13" t="inlineStr">
         <is>
-          <t>wadahadal</t>
+          <t>Wadahadalka kaliya wuxuu ka yimid {label}.</t>
         </is>
       </c>
       <c r="H208" s="14" t="inlineStr"/>
@@ -13349,7 +13349,7 @@
     <row r="209" ht="44" customHeight="1">
       <c r="A209" s="11" t="inlineStr">
         <is>
-          <t>live_sessions</t>
+          <t>unit_conversation</t>
         </is>
       </c>
       <c r="B209" s="11" t="inlineStr">
@@ -13359,27 +13359,27 @@
       </c>
       <c r="C209" s="11" t="inlineStr">
         <is>
-          <t>Live sessions</t>
+          <t>conversation</t>
         </is>
       </c>
       <c r="D209" s="12" t="inlineStr">
         <is>
-          <t>የቀጥታ ክፍለ-ጊዜዎች</t>
+          <t>ውይይት</t>
         </is>
       </c>
       <c r="E209" s="13" t="inlineStr">
         <is>
-          <t>Marii kallattii</t>
+          <t>marii</t>
         </is>
       </c>
       <c r="F209" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታ ክፍለ-ግዜታት</t>
+          <t>ዝርርብ</t>
         </is>
       </c>
       <c r="G209" s="13" t="inlineStr">
         <is>
-          <t>Kalfadhiyada tooska ah</t>
+          <t>wadahadal</t>
         </is>
       </c>
       <c r="H209" s="14" t="inlineStr"/>
@@ -13387,7 +13387,7 @@
     <row r="210" ht="44" customHeight="1">
       <c r="A210" s="11" t="inlineStr">
         <is>
-          <t>switched_off_for_bank</t>
+          <t>live_sessions</t>
         </is>
       </c>
       <c r="B210" s="11" t="inlineStr">
@@ -13397,27 +13397,27 @@
       </c>
       <c r="C210" s="11" t="inlineStr">
         <is>
-          <t>Switched off for this bank</t>
+          <t>Live sessions</t>
         </is>
       </c>
       <c r="D210" s="12" t="inlineStr">
         <is>
-          <t>ለዚህ ባንክ ጠፍቷል</t>
+          <t>የቀጥታ ክፍለ-ጊዜዎች</t>
         </is>
       </c>
       <c r="E210" s="13" t="inlineStr">
         <is>
-          <t>Baankii kanaaf dhaamsameera</t>
+          <t>Marii kallattii</t>
         </is>
       </c>
       <c r="F210" s="12" t="inlineStr">
         <is>
-          <t>ነዚ ባንኪ ጠፊኡ</t>
+          <t>ቀጥታ ክፍለ-ግዜታት</t>
         </is>
       </c>
       <c r="G210" s="13" t="inlineStr">
         <is>
-          <t>Bangigan waa la damiyay</t>
+          <t>Kalfadhiyada tooska ah</t>
         </is>
       </c>
       <c r="H210" s="14" t="inlineStr"/>
@@ -13425,7 +13425,7 @@
     <row r="211" ht="44" customHeight="1">
       <c r="A211" s="11" t="inlineStr">
         <is>
-          <t>switched_on_nobody_on_duty</t>
+          <t>switched_off_for_bank</t>
         </is>
       </c>
       <c r="B211" s="11" t="inlineStr">
@@ -13435,27 +13435,27 @@
       </c>
       <c r="C211" s="11" t="inlineStr">
         <is>
-          <t>Switched on — but nobody is on duty</t>
+          <t>Switched off for this bank</t>
         </is>
       </c>
       <c r="D211" s="12" t="inlineStr">
         <is>
-          <t>በርቷል — ግን ማንም በሥራ ላይ የለም</t>
+          <t>ለዚህ ባንክ ጠፍቷል</t>
         </is>
       </c>
       <c r="E211" s="13" t="inlineStr">
         <is>
-          <t>Banameera — garuu namni hojii irra hin jiru</t>
+          <t>Baankii kanaaf dhaamsameera</t>
         </is>
       </c>
       <c r="F211" s="12" t="inlineStr">
         <is>
-          <t>በሪሁ — ግና ዋላ ሓደ ኣብ ስራሕ የለን</t>
+          <t>ነዚ ባንኪ ጠፊኡ</t>
         </is>
       </c>
       <c r="G211" s="13" t="inlineStr">
         <is>
-          <t>Waa la shiday — laakiin qofna shaqada ma joogo</t>
+          <t>Bangigan waa la damiyay</t>
         </is>
       </c>
       <c r="H211" s="14" t="inlineStr"/>
@@ -13463,7 +13463,7 @@
     <row r="212" ht="44" customHeight="1">
       <c r="A212" s="11" t="inlineStr">
         <is>
-          <t>no_teller_button</t>
+          <t>switched_on_nobody_on_duty</t>
         </is>
       </c>
       <c r="B212" s="11" t="inlineStr">
@@ -13473,27 +13473,27 @@
       </c>
       <c r="C212" s="11" t="inlineStr">
         <is>
-          <t>No “Speak to a teller” button appears in your widget.</t>
+          <t>Switched on — but nobody is on duty</t>
         </is>
       </c>
       <c r="D212" s="12" t="inlineStr">
         <is>
-          <t>በመግብርዎ ውስጥ “ከገንዘብ ተቀባይ ጋር ይነጋገሩ” የሚል አዝራር አይታይም።</t>
+          <t>በርቷል — ግን ማንም በሥራ ላይ የለም</t>
         </is>
       </c>
       <c r="E212" s="13" t="inlineStr">
         <is>
-          <t>Widjetii keessan keessatti qabduun “Namaa waliin haasa'aa” hin mul'atu.</t>
+          <t>Banameera — garuu namni hojii irra hin jiru</t>
         </is>
       </c>
       <c r="F212" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መግበሪኹም “ምስ ተቐባሊ ገንዘብ ተዛረቡ” ዝብል መጠወቒ ኣይረአን።</t>
+          <t>በሪሁ — ግና ዋላ ሓደ ኣብ ስራሕ የለን</t>
         </is>
       </c>
       <c r="G212" s="13" t="inlineStr">
         <is>
-          <t>Badhanka “La hadal shaqaale” kama muuqan widget-kaaga.</t>
+          <t>Waa la shiday — laakiin qofna shaqada ma joogo</t>
         </is>
       </c>
       <c r="H212" s="14" t="inlineStr"/>
@@ -13501,7 +13501,7 @@
     <row r="213" ht="44" customHeight="1">
       <c r="A213" s="11" t="inlineStr">
         <is>
-          <t>on_duty_explainer</t>
+          <t>no_teller_button</t>
         </is>
       </c>
       <c r="B213" s="11" t="inlineStr">
@@ -13511,27 +13511,27 @@
       </c>
       <c r="C213" s="11" t="inlineStr">
         <is>
-          <t>You are on duty, so waiting customers can be routed to you. Go off duty from the sidebar when you step away — you stay on the air anywhere in the console until you do.</t>
+          <t>No “Speak to a teller” button appears in your widget.</t>
         </is>
       </c>
       <c r="D213" s="12" t="inlineStr">
         <is>
-          <t>በሥራ ላይ ነዎት፤ ስለዚህ የሚጠብቁ ደንበኞች ወደ እርስዎ ሊመሩ ይችላሉ። ሲርቁ ከጎን አሞሌው ከሥራ ውጡ — እስከዚያ ድረስ በየትኛውም ገጽ ላይ በሥራ ላይ ይቆያሉ።</t>
+          <t>በመግብርዎ ውስጥ “ከገንዘብ ተቀባይ ጋር ይነጋገሩ” የሚል አዝራር አይታይም።</t>
         </is>
       </c>
       <c r="E213" s="13" t="inlineStr">
         <is>
-          <t>Hojii irra jirtu, kanaafuu maamiltoonni eegaa jiran gara keessan qajeelfamuu danda'u. Yeroo achii deemtan cinaacha irraa hojii keessaa ba'aa — hanga sanatti fuula kamiyyuu irratti hojii irra turtu.</t>
+          <t>Widjetii keessan keessatti qabduun “Namaa waliin haasa'aa” hin mul'atu.</t>
         </is>
       </c>
       <c r="F213" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ስራሕ ኢኹም፣ ስለዚ ዝጽበዩ ዓማዊል ናባኹም ክምርሑ ይኽእሉ። ክትርሕቁ ከለኹም ካብ ናይ ጎኒ መስመር ካብ ስራሕ ውጹ — ክሳብ ሽዑ ኣብ ዝኾነ ገጽ ኣብ ስራሕ ትጸንሑ።</t>
+          <t>ኣብ መግበሪኹም “ምስ ተቐባሊ ገንዘብ ተዛረቡ” ዝብል መጠወቒ ኣይረአን።</t>
         </is>
       </c>
       <c r="G213" s="13" t="inlineStr">
         <is>
-          <t>Shaqada ayaad joogtaa, sidaas darteed macaamiisha sugaya waa lagu soo dhiibi karaa. Marka aad tagto shaqada ka bax dhinaca — ilaa markaas bog kasta ayaad ku sii shaqeynaysaa.</t>
+          <t>Badhanka “La hadal shaqaale” kama muuqan widget-kaaga.</t>
         </is>
       </c>
       <c r="H213" s="14" t="inlineStr"/>
@@ -13539,7 +13539,7 @@
     <row r="214" ht="44" customHeight="1">
       <c r="A214" s="11" t="inlineStr">
         <is>
-          <t>off_duty_explainer</t>
+          <t>on_duty_explainer</t>
         </is>
       </c>
       <c r="B214" s="11" t="inlineStr">
@@ -13549,27 +13549,27 @@
       </c>
       <c r="C214" s="11" t="inlineStr">
         <is>
-          <t>Switch On duty in the sidebar to start taking calls. It follows you across every page, so you no longer have to keep this one open.</t>
+          <t>You are on duty, so waiting customers can be routed to you. Go off duty from the sidebar when you step away — you stay on the air anywhere in the console until you do.</t>
         </is>
       </c>
       <c r="D214" s="12" t="inlineStr">
         <is>
-          <t>ጥሪዎችን መቀበል ለመጀመር ከጎን አሞሌው “በሥራ ላይ” ያብሩ። በሁሉም ገጽ ላይ ይከተልዎታል፤ ስለዚህ ይህን ገጽ ክፍት ማድረግ አያስፈልግም።</t>
+          <t>በሥራ ላይ ነዎት፤ ስለዚህ የሚጠብቁ ደንበኞች ወደ እርስዎ ሊመሩ ይችላሉ። ሲርቁ ከጎን አሞሌው ከሥራ ውጡ — እስከዚያ ድረስ በየትኛውም ገጽ ላይ በሥራ ላይ ይቆያሉ።</t>
         </is>
       </c>
       <c r="E214" s="13" t="inlineStr">
         <is>
-          <t>Bilbila fudhachuu jalqabuuf cinaacha irraa “Hojii irra” banaa. Fuula hunda irratti isin hordofa, kanaafuu fuula kana banaa gochuun hin barbaachisu.</t>
+          <t>Hojii irra jirtu, kanaafuu maamiltoonni eegaa jiran gara keessan qajeelfamuu danda'u. Yeroo achii deemtan cinaacha irraa hojii keessaa ba'aa — hanga sanatti fuula kamiyyuu irratti hojii irra turtu.</t>
         </is>
       </c>
       <c r="F214" s="12" t="inlineStr">
         <is>
-          <t>ጻውዒታት ክትቅበሉ ንምጅማር ካብ ናይ ጎኒ መስመር “ኣብ ስራሕ” ኣብርሁ። ኣብ ኩሉ ገጽ ይስዕበኩም፣ ስለዚ ነዚ ገጽ ክፉት ምግባር ኣየድልን።</t>
+          <t>ኣብ ስራሕ ኢኹም፣ ስለዚ ዝጽበዩ ዓማዊል ናባኹም ክምርሑ ይኽእሉ። ክትርሕቁ ከለኹም ካብ ናይ ጎኒ መስመር ካብ ስራሕ ውጹ — ክሳብ ሽዑ ኣብ ዝኾነ ገጽ ኣብ ስራሕ ትጸንሑ።</t>
         </is>
       </c>
       <c r="G214" s="13" t="inlineStr">
         <is>
-          <t>Si aad u bilowdo qaadista wicitaannada, dhinaca ka shid “Shaqada”. Bog kasta ayuu kula socdaa, sidaas darteed uma baahnid inaad tan furan ka tagto.</t>
+          <t>Shaqada ayaad joogtaa, sidaas darteed macaamiisha sugaya waa lagu soo dhiibi karaa. Marka aad tagto shaqada ka bax dhinaca — ilaa markaas bog kasta ayaad ku sii shaqeynaysaa.</t>
         </is>
       </c>
       <c r="H214" s="14" t="inlineStr"/>
@@ -13577,7 +13577,7 @@
     <row r="215" ht="44" customHeight="1">
       <c r="A215" s="11" t="inlineStr">
         <is>
-          <t>colleague_must_be_on_duty</t>
+          <t>off_duty_explainer</t>
         </is>
       </c>
       <c r="B215" s="11" t="inlineStr">
@@ -13587,27 +13587,27 @@
       </c>
       <c r="C215" s="11" t="inlineStr">
         <is>
-          <t>A colleague with permission to take calls has to be on duty before customers are offered one.</t>
+          <t>Switch On duty in the sidebar to start taking calls. It follows you across every page, so you no longer have to keep this one open.</t>
         </is>
       </c>
       <c r="D215" s="12" t="inlineStr">
         <is>
-          <t>ጥሪ የመቀበል ፈቃድ ያለው ባልደረባ በሥራ ላይ መሆን አለበት፤ ከዚያ በፊት ለደንበኞች አይቀርብም።</t>
+          <t>ጥሪዎችን መቀበል ለመጀመር ከጎን አሞሌው “በሥራ ላይ” ያብሩ። በሁሉም ገጽ ላይ ይከተልዎታል፤ ስለዚህ ይህን ገጽ ክፍት ማድረግ አያስፈልግም።</t>
         </is>
       </c>
       <c r="E215" s="13" t="inlineStr">
         <is>
-          <t>Hojjetaan hayyama bilbila fudhachuu qabu hojii irra jiraachuu qaba, sana dura maamiltootaaf hin dhiyaatu.</t>
+          <t>Bilbila fudhachuu jalqabuuf cinaacha irraa “Hojii irra” banaa. Fuula hunda irratti isin hordofa, kanaafuu fuula kana banaa gochuun hin barbaachisu.</t>
         </is>
       </c>
       <c r="F215" s="12" t="inlineStr">
         <is>
-          <t>ጻውዒት ናይ ምቕባል ፍቓድ ዘለዎ መሳርሕቲ ኣብ ስራሕ ክህሉ ኣለዎ፣ ቅድሚኡ ንዓማዊል ኣይቀርብን።</t>
+          <t>ጻውዒታት ክትቅበሉ ንምጅማር ካብ ናይ ጎኒ መስመር “ኣብ ስራሕ” ኣብርሁ። ኣብ ኩሉ ገጽ ይስዕበኩም፣ ስለዚ ነዚ ገጽ ክፉት ምግባር ኣየድልን።</t>
         </is>
       </c>
       <c r="G215" s="13" t="inlineStr">
         <is>
-          <t>Shaqaale haysta ogolaanshaha qaadista wicitaannada waa inuu shaqada joogaa ka hor inta aan macaamiisha la siin.</t>
+          <t>Si aad u bilowdo qaadista wicitaannada, dhinaca ka shid “Shaqada”. Bog kasta ayuu kula socdaa, sidaas darteed uma baahnid inaad tan furan ka tagto.</t>
         </is>
       </c>
       <c r="H215" s="14" t="inlineStr"/>
@@ -13615,7 +13615,7 @@
     <row r="216" ht="44" customHeight="1">
       <c r="A216" s="11" t="inlineStr">
         <is>
-          <t>i_can_converse_in</t>
+          <t>colleague_must_be_on_duty</t>
         </is>
       </c>
       <c r="B216" s="11" t="inlineStr">
@@ -13625,27 +13625,27 @@
       </c>
       <c r="C216" s="11" t="inlineStr">
         <is>
-          <t>I can hold a conversation in:</t>
+          <t>A colleague with permission to take calls has to be on duty before customers are offered one.</t>
         </is>
       </c>
       <c r="D216" s="12" t="inlineStr">
         <is>
-          <t>በእነዚህ ቋንቋዎች መነጋገር እችላለሁ፦</t>
+          <t>ጥሪ የመቀበል ፈቃድ ያለው ባልደረባ በሥራ ላይ መሆን አለበት፤ ከዚያ በፊት ለደንበኞች አይቀርብም።</t>
         </is>
       </c>
       <c r="E216" s="13" t="inlineStr">
         <is>
-          <t>Afaanota kanneeniin haasa'uu nan danda'a:</t>
+          <t>Hojjetaan hayyama bilbila fudhachuu qabu hojii irra jiraachuu qaba, sana dura maamiltootaaf hin dhiyaatu.</t>
         </is>
       </c>
       <c r="F216" s="12" t="inlineStr">
         <is>
-          <t>በዞም ቋንቋታት ክዛረብ እኽእል፦</t>
+          <t>ጻውዒት ናይ ምቕባል ፍቓድ ዘለዎ መሳርሕቲ ኣብ ስራሕ ክህሉ ኣለዎ፣ ቅድሚኡ ንዓማዊል ኣይቀርብን።</t>
         </is>
       </c>
       <c r="G216" s="13" t="inlineStr">
         <is>
-          <t>Waxaan ku hadli karaa:</t>
+          <t>Shaqaale haysta ogolaanshaha qaadista wicitaannada waa inuu shaqada joogaa ka hor inta aan macaamiisha la siin.</t>
         </is>
       </c>
       <c r="H216" s="14" t="inlineStr"/>
@@ -13653,7 +13653,7 @@
     <row r="217" ht="44" customHeight="1">
       <c r="A217" s="11" t="inlineStr">
         <is>
-          <t>languages_picked_note</t>
+          <t>i_can_converse_in</t>
         </is>
       </c>
       <c r="B217" s="11" t="inlineStr">
@@ -13663,27 +13663,27 @@
       </c>
       <c r="C217" s="11" t="inlineStr">
         <is>
-          <t>Customers writing in these reach you first. Everyone else still reaches you — after a short wait, so nobody is stranded.</t>
+          <t>I can hold a conversation in:</t>
         </is>
       </c>
       <c r="D217" s="12" t="inlineStr">
         <is>
-          <t>በእነዚህ ቋንቋዎች የሚጽፉ ደንበኞች መጀመሪያ ወደ እርስዎ ይደርሳሉ። ሌሎችም ይደርሳሉ — ከአጭር ጥበቃ በኋላ፤ ማንም አይቀርም።</t>
+          <t>በእነዚህ ቋንቋዎች መነጋገር እችላለሁ፦</t>
         </is>
       </c>
       <c r="E217" s="13" t="inlineStr">
         <is>
-          <t>Maamiltoonni afaanota kanaan barreessan jalqaba isin bira ga'u. Kaan hundinuu ammas isin bira ga'u — eegumsa gabaabaa booda, namni hafu hin jiru.</t>
+          <t>Afaanota kanneeniin haasa'uu nan danda'a:</t>
         </is>
       </c>
       <c r="F217" s="12" t="inlineStr">
         <is>
-          <t>በዞም ቋንቋታት ዝጽሕፉ ዓማዊል ቅድም ናባኹም ይበጽሑ። እቶም ካልኦት እውን ይበጽሑ — ድሕሪ ሓጺር ጽበት፣ ዋላ ሓደ ኣይተርፍን።</t>
+          <t>በዞም ቋንቋታት ክዛረብ እኽእል፦</t>
         </is>
       </c>
       <c r="G217" s="13" t="inlineStr">
         <is>
-          <t>Macaamiisha ku qora kuwan ayaa marka hore kugu soo gaara. Qof kastana wuu ku soo gaari doonaa — sug gaaban ka dib, sidaas qofna ma harayo.</t>
+          <t>Waxaan ku hadli karaa:</t>
         </is>
       </c>
       <c r="H217" s="14" t="inlineStr"/>
@@ -13691,7 +13691,7 @@
     <row r="218" ht="44" customHeight="1">
       <c r="A218" s="11" t="inlineStr">
         <is>
-          <t>languages_none_note</t>
+          <t>languages_picked_note</t>
         </is>
       </c>
       <c r="B218" s="11" t="inlineStr">
@@ -13701,27 +13701,27 @@
       </c>
       <c r="C218" s="11" t="inlineStr">
         <is>
-          <t>Nothing selected, so every waiting customer is offered to you in plain oldest-first order.</t>
+          <t>Customers writing in these reach you first. Everyone else still reaches you — after a short wait, so nobody is stranded.</t>
         </is>
       </c>
       <c r="D218" s="12" t="inlineStr">
         <is>
-          <t>ምንም አልተመረጠም፤ ስለዚህ እያንዳንዱ የሚጠብቅ ደንበኛ በቀላል ቀዳሚ-መጀመሪያ ቅደም ተከተል ይቀርብልዎታል።</t>
+          <t>በእነዚህ ቋንቋዎች የሚጽፉ ደንበኞች መጀመሪያ ወደ እርስዎ ይደርሳሉ። ሌሎችም ይደርሳሉ — ከአጭር ጥበቃ በኋላ፤ ማንም አይቀርም።</t>
         </is>
       </c>
       <c r="E218" s="13" t="inlineStr">
         <is>
-          <t>Wanti filatame hin jiru, kanaafuu maamilli eegaa jiru hundi tartiiba dursaa-jalqabaatiin isinii dhiyaata.</t>
+          <t>Maamiltoonni afaanota kanaan barreessan jalqaba isin bira ga'u. Kaan hundinuu ammas isin bira ga'u — eegumsa gabaabaa booda, namni hafu hin jiru.</t>
         </is>
       </c>
       <c r="F218" s="12" t="inlineStr">
         <is>
-          <t>ዋላ ሓደ ኣይተመርጸን፣ ስለዚ ነፍስ ወከፍ ዝጽበ ዓሚል ብቐሊል ናይ ቀዳምነት ስርዓት ይቐርበልኩም።</t>
+          <t>በዞም ቋንቋታት ዝጽሕፉ ዓማዊል ቅድም ናባኹም ይበጽሑ። እቶም ካልኦት እውን ይበጽሑ — ድሕሪ ሓጺር ጽበት፣ ዋላ ሓደ ኣይተርፍን።</t>
         </is>
       </c>
       <c r="G218" s="13" t="inlineStr">
         <is>
-          <t>Waxba lama dooran, sidaas darteed macmiil kasta oo sugaya waxaa laguu soo bandhigayaa sida caadiga ah ee ugu horreeya.</t>
+          <t>Macaamiisha ku qora kuwan ayaa marka hore kugu soo gaara. Qof kastana wuu ku soo gaari doonaa — sug gaaban ka dib, sidaas qofna ma harayo.</t>
         </is>
       </c>
       <c r="H218" s="14" t="inlineStr"/>
@@ -13729,7 +13729,7 @@
     <row r="219" ht="44" customHeight="1">
       <c r="A219" s="11" t="inlineStr">
         <is>
-          <t>languages_updated</t>
+          <t>languages_none_note</t>
         </is>
       </c>
       <c r="B219" s="11" t="inlineStr">
@@ -13739,27 +13739,27 @@
       </c>
       <c r="C219" s="11" t="inlineStr">
         <is>
-          <t>Languages updated</t>
+          <t>Nothing selected, so every waiting customer is offered to you in plain oldest-first order.</t>
         </is>
       </c>
       <c r="D219" s="12" t="inlineStr">
         <is>
-          <t>ቋንቋዎች ተዘምነዋል</t>
+          <t>ምንም አልተመረጠም፤ ስለዚህ እያንዳንዱ የሚጠብቅ ደንበኛ በቀላል ቀዳሚ-መጀመሪያ ቅደም ተከተል ይቀርብልዎታል።</t>
         </is>
       </c>
       <c r="E219" s="13" t="inlineStr">
         <is>
-          <t>Afaanonni haaromfaman</t>
+          <t>Wanti filatame hin jiru, kanaafuu maamilli eegaa jiru hundi tartiiba dursaa-jalqabaatiin isinii dhiyaata.</t>
         </is>
       </c>
       <c r="F219" s="12" t="inlineStr">
         <is>
-          <t>ቋንቋታት ተሓዲሶም</t>
+          <t>ዋላ ሓደ ኣይተመርጸን፣ ስለዚ ነፍስ ወከፍ ዝጽበ ዓሚል ብቐሊል ናይ ቀዳምነት ስርዓት ይቐርበልኩም።</t>
         </is>
       </c>
       <c r="G219" s="13" t="inlineStr">
         <is>
-          <t>Luqadaha waa la cusbooneysiiyay</t>
+          <t>Waxba lama dooran, sidaas darteed macmiil kasta oo sugaya waxaa laguu soo bandhigayaa sida caadiga ah ee ugu horreeya.</t>
         </is>
       </c>
       <c r="H219" s="14" t="inlineStr"/>
@@ -13767,7 +13767,7 @@
     <row r="220" ht="44" customHeight="1">
       <c r="A220" s="11" t="inlineStr">
         <is>
-          <t>media_video</t>
+          <t>languages_updated</t>
         </is>
       </c>
       <c r="B220" s="11" t="inlineStr">
@@ -13777,27 +13777,27 @@
       </c>
       <c r="C220" s="11" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Languages updated</t>
         </is>
       </c>
       <c r="D220" s="12" t="inlineStr">
         <is>
-          <t>ቪዲዮ</t>
+          <t>ቋንቋዎች ተዘምነዋል</t>
         </is>
       </c>
       <c r="E220" s="13" t="inlineStr">
         <is>
-          <t>Viidiyoo</t>
+          <t>Afaanonni haaromfaman</t>
         </is>
       </c>
       <c r="F220" s="12" t="inlineStr">
         <is>
-          <t>ቪድዮ</t>
+          <t>ቋንቋታት ተሓዲሶም</t>
         </is>
       </c>
       <c r="G220" s="13" t="inlineStr">
         <is>
-          <t>Fiidyow</t>
+          <t>Luqadaha waa la cusbooneysiiyay</t>
         </is>
       </c>
       <c r="H220" s="14" t="inlineStr"/>
@@ -13805,7 +13805,7 @@
     <row r="221" ht="44" customHeight="1">
       <c r="A221" s="11" t="inlineStr">
         <is>
-          <t>media_audio</t>
+          <t>media_video</t>
         </is>
       </c>
       <c r="B221" s="11" t="inlineStr">
@@ -13815,27 +13815,27 @@
       </c>
       <c r="C221" s="11" t="inlineStr">
         <is>
-          <t>Audio</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="D221" s="12" t="inlineStr">
         <is>
-          <t>ድምፅ</t>
+          <t>ቪዲዮ</t>
         </is>
       </c>
       <c r="E221" s="13" t="inlineStr">
         <is>
-          <t>Sagalee</t>
+          <t>Viidiyoo</t>
         </is>
       </c>
       <c r="F221" s="12" t="inlineStr">
         <is>
-          <t>ድምጺ</t>
+          <t>ቪድዮ</t>
         </is>
       </c>
       <c r="G221" s="13" t="inlineStr">
         <is>
-          <t>Cod</t>
+          <t>Fiidyow</t>
         </is>
       </c>
       <c r="H221" s="14" t="inlineStr"/>
@@ -13843,7 +13843,7 @@
     <row r="222" ht="44" customHeight="1">
       <c r="A222" s="11" t="inlineStr">
         <is>
-          <t>not_your_language</t>
+          <t>media_audio</t>
         </is>
       </c>
       <c r="B222" s="11" t="inlineStr">
@@ -13853,27 +13853,27 @@
       </c>
       <c r="C222" s="11" t="inlineStr">
         <is>
-          <t>not your language</t>
+          <t>Audio</t>
         </is>
       </c>
       <c r="D222" s="12" t="inlineStr">
         <is>
-          <t>የእርስዎ ቋንቋ አይደለም</t>
+          <t>ድምፅ</t>
         </is>
       </c>
       <c r="E222" s="13" t="inlineStr">
         <is>
-          <t>afaan keessanii miti</t>
+          <t>Sagalee</t>
         </is>
       </c>
       <c r="F222" s="12" t="inlineStr">
         <is>
-          <t>ናትኩም ቋንቋ ኣይኮነን</t>
+          <t>ድምጺ</t>
         </is>
       </c>
       <c r="G222" s="13" t="inlineStr">
         <is>
-          <t>ma aha luqaddaada</t>
+          <t>Cod</t>
         </is>
       </c>
       <c r="H222" s="14" t="inlineStr"/>
@@ -13881,7 +13881,7 @@
     <row r="223" ht="44" customHeight="1">
       <c r="A223" s="11" t="inlineStr">
         <is>
-          <t>languages_first_note</t>
+          <t>not_your_language</t>
         </is>
       </c>
       <c r="B223" s="11" t="inlineStr">
@@ -13891,27 +13891,27 @@
       </c>
       <c r="C223" s="11" t="inlineStr">
         <is>
-          <t>Your languages first, longest wait within each. Anyone waiting too long moves to the top whatever they speak.</t>
+          <t>not your language</t>
         </is>
       </c>
       <c r="D223" s="12" t="inlineStr">
         <is>
-          <t>የእርስዎ ቋንቋዎች መጀመሪያ፤ በእያንዳንዱ ውስጥ ረጅም የጠበቀው ይቀድማል። ከልክ በላይ የጠበቀ ማንኛውም ሰው የሚናገረው ምንም ይሁን ወደ ላይ ይወጣል።</t>
+          <t>የእርስዎ ቋንቋ አይደለም</t>
         </is>
       </c>
       <c r="E223" s="13" t="inlineStr">
         <is>
-          <t>Afaanonni keessan jalqaba, tokkoon tokkoon isaanii keessatti kan yeroo dheeraa eege dursa. Namni baay'ee eege afaan kamiyyuu haa dubbatu gara oliitti deema.</t>
+          <t>afaan keessanii miti</t>
         </is>
       </c>
       <c r="F223" s="12" t="inlineStr">
         <is>
-          <t>ቋንቋታትኩም ቅድም፣ ኣብ ነፍስ ወከፍ እቲ ነዊሕ ዝጸንሐ ይቐድም። ካብ ንቡር ንላዕሊ ዝጸንሐ ዝኾነ ሰብ ዝዛረቦ ብዘየገድስ ናብ ላዕሊ ይመጽእ።</t>
+          <t>ናትኩም ቋንቋ ኣይኮነን</t>
         </is>
       </c>
       <c r="G223" s="13" t="inlineStr">
         <is>
-          <t>Luqadahaaga marka hore, kii ugu sugay dheeraa mid kasta gudahood. Qof kasta oo aad u sugay ayaa kor u kaca luqad kastoo uu ku hadloba.</t>
+          <t>ma aha luqaddaada</t>
         </is>
       </c>
       <c r="H223" s="14" t="inlineStr"/>
@@ -13919,7 +13919,7 @@
     <row r="224" ht="44" customHeight="1">
       <c r="A224" s="11" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>languages_first_note</t>
         </is>
       </c>
       <c r="B224" s="11" t="inlineStr">
@@ -13929,27 +13929,27 @@
       </c>
       <c r="C224" s="11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Your languages first, longest wait within each. Anyone waiting too long moves to the top whatever they speak.</t>
         </is>
       </c>
       <c r="D224" s="12" t="inlineStr">
         <is>
-          <t>በሂደት ላይ</t>
+          <t>የእርስዎ ቋንቋዎች መጀመሪያ፤ በእያንዳንዱ ውስጥ ረጅም የጠበቀው ይቀድማል። ከልክ በላይ የጠበቀ ማንኛውም ሰው የሚናገረው ምንም ይሁን ወደ ላይ ይወጣል።</t>
         </is>
       </c>
       <c r="E224" s="13" t="inlineStr">
         <is>
-          <t>Adeemsa irra</t>
+          <t>Afaanonni keessan jalqaba, tokkoon tokkoon isaanii keessatti kan yeroo dheeraa eege dursa. Namni baay'ee eege afaan kamiyyuu haa dubbatu gara oliitti deema.</t>
         </is>
       </c>
       <c r="F224" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መስርሕ</t>
+          <t>ቋንቋታትኩም ቅድም፣ ኣብ ነፍስ ወከፍ እቲ ነዊሕ ዝጸንሐ ይቐድም። ካብ ንቡር ንላዕሊ ዝጸንሐ ዝኾነ ሰብ ዝዛረቦ ብዘየገድስ ናብ ላዕሊ ይመጽእ።</t>
         </is>
       </c>
       <c r="G224" s="13" t="inlineStr">
         <is>
-          <t>Socda</t>
+          <t>Luqadahaaga marka hore, kii ugu sugay dheeraa mid kasta gudahood. Qof kasta oo aad u sugay ayaa kor u kaca luqad kastoo uu ku hadloba.</t>
         </is>
       </c>
       <c r="H224" s="14" t="inlineStr"/>
@@ -13957,7 +13957,7 @@
     <row r="225" ht="44" customHeight="1">
       <c r="A225" s="11" t="inlineStr">
         <is>
-          <t>no_session_in_progress</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="B225" s="11" t="inlineStr">
@@ -13967,27 +13967,27 @@
       </c>
       <c r="C225" s="11" t="inlineStr">
         <is>
-          <t>No session in progress.</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="D225" s="12" t="inlineStr">
         <is>
-          <t>በሂደት ላይ ያለ ክፍለ-ጊዜ የለም።</t>
+          <t>በሂደት ላይ</t>
         </is>
       </c>
       <c r="E225" s="13" t="inlineStr">
         <is>
-          <t>Sessionii adeemsa irra jiru hin jiru.</t>
+          <t>Adeemsa irra</t>
         </is>
       </c>
       <c r="F225" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መስርሕ ዘሎ ክፍለ-ግዜ የለን።</t>
+          <t>ኣብ መስርሕ</t>
         </is>
       </c>
       <c r="G225" s="13" t="inlineStr">
         <is>
-          <t>Ma jiro kalfadhi socda.</t>
+          <t>Socda</t>
         </is>
       </c>
       <c r="H225" s="14" t="inlineStr"/>
@@ -13995,7 +13995,7 @@
     <row r="226" ht="44" customHeight="1">
       <c r="A226" s="11" t="inlineStr">
         <is>
-          <t>wait_suffix</t>
+          <t>no_session_in_progress</t>
         </is>
       </c>
       <c r="B226" s="11" t="inlineStr">
@@ -14005,27 +14005,27 @@
       </c>
       <c r="C226" s="11" t="inlineStr">
         <is>
-          <t>wait</t>
+          <t>No session in progress.</t>
         </is>
       </c>
       <c r="D226" s="12" t="inlineStr">
         <is>
-          <t>ጥበቃ</t>
+          <t>በሂደት ላይ ያለ ክፍለ-ጊዜ የለም።</t>
         </is>
       </c>
       <c r="E226" s="13" t="inlineStr">
         <is>
-          <t>eegumsa</t>
+          <t>Sessionii adeemsa irra jiru hin jiru.</t>
         </is>
       </c>
       <c r="F226" s="12" t="inlineStr">
         <is>
-          <t>ጽበት</t>
+          <t>ኣብ መስርሕ ዘሎ ክፍለ-ግዜ የለን።</t>
         </is>
       </c>
       <c r="G226" s="13" t="inlineStr">
         <is>
-          <t>sug</t>
+          <t>Ma jiro kalfadhi socda.</t>
         </is>
       </c>
       <c r="H226" s="14" t="inlineStr"/>
@@ -14033,7 +14033,7 @@
     <row r="227" ht="44" customHeight="1">
       <c r="A227" s="11" t="inlineStr">
         <is>
-          <t>what_session_covers</t>
+          <t>wait_suffix</t>
         </is>
       </c>
       <c r="B227" s="11" t="inlineStr">
@@ -14043,27 +14043,27 @@
       </c>
       <c r="C227" s="11" t="inlineStr">
         <is>
-          <t>What a session covers</t>
+          <t>wait</t>
         </is>
       </c>
       <c r="D227" s="12" t="inlineStr">
         <is>
-          <t>አንድ ክፍለ-ጊዜ ምን ይሸፍናል</t>
+          <t>ጥበቃ</t>
         </is>
       </c>
       <c r="E227" s="13" t="inlineStr">
         <is>
-          <t>Sessioniin maal haguuga</t>
+          <t>eegumsa</t>
         </is>
       </c>
       <c r="F227" s="12" t="inlineStr">
         <is>
-          <t>ሓደ ክፍለ-ግዜ እንታይ ይሽፍን</t>
+          <t>ጽበት</t>
         </is>
       </c>
       <c r="G227" s="13" t="inlineStr">
         <is>
-          <t>Waxa kalfadhigu daboolo</t>
+          <t>sug</t>
         </is>
       </c>
       <c r="H227" s="14" t="inlineStr"/>
@@ -14071,7 +14071,7 @@
     <row r="228" ht="44" customHeight="1">
       <c r="A228" s="11" t="inlineStr">
         <is>
-          <t>session_scope_body</t>
+          <t>what_session_covers</t>
         </is>
       </c>
       <c r="B228" s="11" t="inlineStr">
@@ -14081,27 +14081,27 @@
       </c>
       <c r="C228" s="11" t="inlineStr">
         <is>
-          <t>Before someone is identified: general questions about products, eligibility and how to apply. Once you have checked their Fayda ID against the account and asked something only the account holder could answer: their own application, documents and disputes.</t>
+          <t>What a session covers</t>
         </is>
       </c>
       <c r="D228" s="12" t="inlineStr">
         <is>
-          <t>አንድ ሰው ከመለየቱ በፊት፦ ስለ ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል አጠቃላይ ጥያቄዎች። የፋይዳ መታወቂያቸውን ከሂሳቡ ጋር አመሳክረው የሂሳቡ ባለቤት ብቻ ሊመልሰው የሚችለውን ከጠየቁ በኋላ፦ የራሳቸው ማመልከቻ፣ ሰነዶችና ቅሬታዎች።</t>
+          <t>አንድ ክፍለ-ጊዜ ምን ይሸፍናል</t>
         </is>
       </c>
       <c r="E228" s="13" t="inlineStr">
         <is>
-          <t>Namni tokko utuu hin beekamin dura: gaaffii waliigalaa waa'ee oomishaalee, ulaagaa fi akkaataa itti iyyatan. Erga waraqaa eenyummaa Fayda isaanii herrega waliin madaalchiftanii waan abbaan herregaa qofti deebisuu danda'u gaafattanii booda: iyyannoo, sanadoota fi komii isaanii.</t>
+          <t>Sessioniin maal haguuga</t>
         </is>
       </c>
       <c r="F228" s="12" t="inlineStr">
         <is>
-          <t>ሓደ ሰብ ቅድሚ ምልላዩ፦ ብዛዕባ ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን ሓፈሻዊ ሕቶታት። መንነት ፋይዳኦም ምስ ሕሳብ ኣረጋጊጽኩም እቲ ወናኒ ሕሳብ ጥራይ ክምልሶ ዝኽእል ምስ ሓተትኩም፦ ናቶም ምልክታ፣ ሰነዳትን ጥርዓናትን።</t>
+          <t>ሓደ ክፍለ-ግዜ እንታይ ይሽፍን</t>
         </is>
       </c>
       <c r="G228" s="13" t="inlineStr">
         <is>
-          <t>Ka hor inta aan qofka la aqoonsan: su'aalo guud oo ku saabsan alaabta, u-qalmitaanka iyo sida loo codsado. Marka aad hubiso aqoonsigooda Fayda ee xisaabta oo aad weydiiso wax uu kaliya milkiilaha xisaabtu ka jawaabi karo: codsigooda, dukumiintiyada iyo cabashooyinka.</t>
+          <t>Waxa kalfadhigu daboolo</t>
         </is>
       </c>
       <c r="H228" s="14" t="inlineStr"/>
@@ -14109,7 +14109,7 @@
     <row r="229" ht="44" customHeight="1">
       <c r="A229" s="11" t="inlineStr">
         <is>
-          <t>never_money_movement</t>
+          <t>session_scope_body</t>
         </is>
       </c>
       <c r="B229" s="11" t="inlineStr">
@@ -14119,27 +14119,27 @@
       </c>
       <c r="C229" s="11" t="inlineStr">
         <is>
-          <t>Never, at any point and for anyone: deposits, withdrawals or transfers. Those do not happen on a call.</t>
+          <t>Before someone is identified: general questions about products, eligibility and how to apply. Once you have checked their Fayda ID against the account and asked something only the account holder could answer: their own application, documents and disputes.</t>
         </is>
       </c>
       <c r="D229" s="12" t="inlineStr">
         <is>
-          <t>በፍጹም፣ በማንኛውም ጊዜና ለማንም፦ ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም። እነዚያ በጥሪ ላይ አይፈጸሙም።</t>
+          <t>አንድ ሰው ከመለየቱ በፊት፦ ስለ ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል አጠቃላይ ጥያቄዎች። የፋይዳ መታወቂያቸውን ከሂሳቡ ጋር አመሳክረው የሂሳቡ ባለቤት ብቻ ሊመልሰው የሚችለውን ከጠየቁ በኋላ፦ የራሳቸው ማመልከቻ፣ ሰነዶችና ቅሬታዎች።</t>
         </is>
       </c>
       <c r="E229" s="13" t="inlineStr">
         <is>
-          <t>Gonkumaa, yeroo kamiyyuu fi eenyuufiyyuu: kuusaa, baasii yookiin dabarsa hin jiru. Isaan sun bilbila irratti hin raawwataman.</t>
+          <t>Namni tokko utuu hin beekamin dura: gaaffii waliigalaa waa'ee oomishaalee, ulaagaa fi akkaataa itti iyyatan. Erga waraqaa eenyummaa Fayda isaanii herrega waliin madaalchiftanii waan abbaan herregaa qofti deebisuu danda'u gaafattanii booda: iyyannoo, sanadoota fi komii isaanii.</t>
         </is>
       </c>
       <c r="F229" s="12" t="inlineStr">
         <is>
-          <t>ፈጺሙ፣ ኣብ ዝኾነ እዋንን ንዝኾነ ሰብን፦ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን። እዚኣቶም ኣብ ጻውዒት ኣይፍጸሙን።</t>
+          <t>ሓደ ሰብ ቅድሚ ምልላዩ፦ ብዛዕባ ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን ሓፈሻዊ ሕቶታት። መንነት ፋይዳኦም ምስ ሕሳብ ኣረጋጊጽኩም እቲ ወናኒ ሕሳብ ጥራይ ክምልሶ ዝኽእል ምስ ሓተትኩም፦ ናቶም ምልክታ፣ ሰነዳትን ጥርዓናትን።</t>
         </is>
       </c>
       <c r="G229" s="13" t="inlineStr">
         <is>
-          <t>Weligaa, wakhti kasta iyo qof kasta: dhigasho, qaadis ama wareejin ma jirto. Kuwaas wicitaan laguma sameeyo.</t>
+          <t>Ka hor inta aan qofka la aqoonsan: su'aalo guud oo ku saabsan alaabta, u-qalmitaanka iyo sida loo codsado. Marka aad hubiso aqoonsigooda Fayda ee xisaabta oo aad weydiiso wax uu kaliya milkiilaha xisaabtu ka jawaabi karo: codsigooda, dukumiintiyada iyo cabashooyinka.</t>
         </is>
       </c>
       <c r="H229" s="14" t="inlineStr"/>
@@ -14147,7 +14147,7 @@
     <row r="230" ht="44" customHeight="1">
       <c r="A230" s="11" t="inlineStr">
         <is>
-          <t>open_escalation_queue</t>
+          <t>never_money_movement</t>
         </is>
       </c>
       <c r="B230" s="11" t="inlineStr">
@@ -14157,27 +14157,27 @@
       </c>
       <c r="C230" s="11" t="inlineStr">
         <is>
-          <t>Open the escalation queue</t>
+          <t>Never, at any point and for anyone: deposits, withdrawals or transfers. Those do not happen on a call.</t>
         </is>
       </c>
       <c r="D230" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ወረፋውን ክፈት</t>
+          <t>በፍጹም፣ በማንኛውም ጊዜና ለማንም፦ ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም። እነዚያ በጥሪ ላይ አይፈጸሙም።</t>
         </is>
       </c>
       <c r="E230" s="13" t="inlineStr">
         <is>
-          <t>Sararaa dabarsaa banaa</t>
+          <t>Gonkumaa, yeroo kamiyyuu fi eenyuufiyyuu: kuusaa, baasii yookiin dabarsa hin jiru. Isaan sun bilbila irratti hin raawwataman.</t>
         </is>
       </c>
       <c r="F230" s="12" t="inlineStr">
         <is>
-          <t>ሪጋ ምትሕልላፍ ክፈት</t>
+          <t>ፈጺሙ፣ ኣብ ዝኾነ እዋንን ንዝኾነ ሰብን፦ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን። እዚኣቶም ኣብ ጻውዒት ኣይፍጸሙን።</t>
         </is>
       </c>
       <c r="G230" s="13" t="inlineStr">
         <is>
-          <t>Fur safka gudbinta</t>
+          <t>Weligaa, wakhti kasta iyo qof kasta: dhigasho, qaadis ama wareejin ma jirto. Kuwaas wicitaan laguma sameeyo.</t>
         </is>
       </c>
       <c r="H230" s="14" t="inlineStr"/>
@@ -14185,7 +14185,7 @@
     <row r="231" ht="44" customHeight="1">
       <c r="A231" s="11" t="inlineStr">
         <is>
-          <t>switch_dark_light</t>
+          <t>open_escalation_queue</t>
         </is>
       </c>
       <c r="B231" s="11" t="inlineStr">
@@ -14195,27 +14195,27 @@
       </c>
       <c r="C231" s="11" t="inlineStr">
         <is>
-          <t>Switch between dark and light</t>
+          <t>Open the escalation queue</t>
         </is>
       </c>
       <c r="D231" s="12" t="inlineStr">
         <is>
-          <t>በጨለማና በብርሃን መካከል ቀይር</t>
+          <t>የማሸጋገሪያ ወረፋውን ክፈት</t>
         </is>
       </c>
       <c r="E231" s="13" t="inlineStr">
         <is>
-          <t>Dukkanaa fi ifa gidduu jijjiiri</t>
+          <t>Sararaa dabarsaa banaa</t>
         </is>
       </c>
       <c r="F231" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መንጎ ጸላምን ብርሃንን ቀይር</t>
+          <t>ሪጋ ምትሕልላፍ ክፈት</t>
         </is>
       </c>
       <c r="G231" s="13" t="inlineStr">
         <is>
-          <t>U beddel mugdiga iyo iftiinka</t>
+          <t>Fur safka gudbinta</t>
         </is>
       </c>
       <c r="H231" s="14" t="inlineStr"/>
@@ -14223,7 +14223,7 @@
     <row r="232" ht="44" customHeight="1">
       <c r="A232" s="11" t="inlineStr">
         <is>
-          <t>live_session</t>
+          <t>switch_dark_light</t>
         </is>
       </c>
       <c r="B232" s="11" t="inlineStr">
@@ -14233,27 +14233,27 @@
       </c>
       <c r="C232" s="11" t="inlineStr">
         <is>
-          <t>Live session</t>
+          <t>Switch between dark and light</t>
         </is>
       </c>
       <c r="D232" s="12" t="inlineStr">
         <is>
-          <t>የቀጥታ ክፍለ-ጊዜ</t>
+          <t>በጨለማና በብርሃን መካከል ቀይር</t>
         </is>
       </c>
       <c r="E232" s="13" t="inlineStr">
         <is>
-          <t>Session kallattii</t>
+          <t>Dukkanaa fi ifa gidduu jijjiiri</t>
         </is>
       </c>
       <c r="F232" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታ ክፍለ-ግዜ</t>
+          <t>ኣብ መንጎ ጸላምን ብርሃንን ቀይር</t>
         </is>
       </c>
       <c r="G232" s="13" t="inlineStr">
         <is>
-          <t>Kalfadhi toos ah</t>
+          <t>U beddel mugdiga iyo iftiinka</t>
         </is>
       </c>
       <c r="H232" s="14" t="inlineStr"/>
@@ -14261,7 +14261,7 @@
     <row r="233" ht="44" customHeight="1">
       <c r="A233" s="11" t="inlineStr">
         <is>
-          <t>customer_left_call</t>
+          <t>live_session</t>
         </is>
       </c>
       <c r="B233" s="11" t="inlineStr">
@@ -14271,27 +14271,27 @@
       </c>
       <c r="C233" s="11" t="inlineStr">
         <is>
-          <t>The customer has left the call.</t>
+          <t>Live session</t>
         </is>
       </c>
       <c r="D233" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛው ጥሪውን ለቅቋል።</t>
+          <t>የቀጥታ ክፍለ-ጊዜ</t>
         </is>
       </c>
       <c r="E233" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan bilbila irraa ba'eera.</t>
+          <t>Session kallattii</t>
         </is>
       </c>
       <c r="F233" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዓሚል ካብቲ ጻውዒት ወጺኡ።</t>
+          <t>ቀጥታ ክፍለ-ግዜ</t>
         </is>
       </c>
       <c r="G233" s="13" t="inlineStr">
         <is>
-          <t>Macmiilku wicitaanka wuu ka baxay.</t>
+          <t>Kalfadhi toos ah</t>
         </is>
       </c>
       <c r="H233" s="14" t="inlineStr"/>
@@ -14299,7 +14299,7 @@
     <row r="234" ht="44" customHeight="1">
       <c r="A234" s="11" t="inlineStr">
         <is>
-          <t>waiting_for_customer</t>
+          <t>customer_left_call</t>
         </is>
       </c>
       <c r="B234" s="11" t="inlineStr">
@@ -14309,27 +14309,27 @@
       </c>
       <c r="C234" s="11" t="inlineStr">
         <is>
-          <t>Waiting for the customer…</t>
+          <t>The customer has left the call.</t>
         </is>
       </c>
       <c r="D234" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛውን በመጠበቅ ላይ…</t>
+          <t>ደንበኛው ጥሪውን ለቅቋል።</t>
         </is>
       </c>
       <c r="E234" s="13" t="inlineStr">
         <is>
-          <t>Maamilaa eegaa jirra…</t>
+          <t>Maamilaan bilbila irraa ba'eera.</t>
         </is>
       </c>
       <c r="F234" s="12" t="inlineStr">
         <is>
-          <t>ነቲ ዓሚል ንጽበ ኣለና…</t>
+          <t>እቲ ዓሚል ካብቲ ጻውዒት ወጺኡ።</t>
         </is>
       </c>
       <c r="G234" s="13" t="inlineStr">
         <is>
-          <t>Macmiilka la sugayo…</t>
+          <t>Macmiilku wicitaanka wuu ka baxay.</t>
         </is>
       </c>
       <c r="H234" s="14" t="inlineStr"/>
@@ -14337,7 +14337,7 @@
     <row r="235" ht="44" customHeight="1">
       <c r="A235" s="11" t="inlineStr">
         <is>
-          <t>mic_blocked</t>
+          <t>waiting_for_customer</t>
         </is>
       </c>
       <c r="B235" s="11" t="inlineStr">
@@ -14347,27 +14347,27 @@
       </c>
       <c r="C235" s="11" t="inlineStr">
         <is>
-          <t>Microphone access is blocked. Allow it in your browser and take the session again.</t>
+          <t>Waiting for the customer…</t>
         </is>
       </c>
       <c r="D235" s="12" t="inlineStr">
         <is>
-          <t>የማይክሮፎን መዳረሻ ታግዷል። በአሳሽዎ ውስጥ ይፍቀዱና ክፍለ-ጊዜውን እንደገና ይውሰዱ።</t>
+          <t>ደንበኛውን በመጠበቅ ላይ…</t>
         </is>
       </c>
       <c r="E235" s="13" t="inlineStr">
         <is>
-          <t>Maayikiroofoonii dhorkameera. Biraawzarii keessan keessatti hayyamaatii session irra deebi'aa fudhadhaa.</t>
+          <t>Maamilaa eegaa jirra…</t>
         </is>
       </c>
       <c r="F235" s="12" t="inlineStr">
         <is>
-          <t>መእተዊ ማይክሮፎን ተዓጊቱ። ኣብ መርበብ መንሸራተቲኹም ፍቐዱ እሞ ነቲ ክፍለ-ግዜ ደጊምኩም ውሰዱ።</t>
+          <t>ነቲ ዓሚል ንጽበ ኣለና…</t>
         </is>
       </c>
       <c r="G235" s="13" t="inlineStr">
         <is>
-          <t>Makarafoonka waa la xannibay. Browser-kaaga ka ogolow oo kalfadhiga mar kale qaado.</t>
+          <t>Macmiilka la sugayo…</t>
         </is>
       </c>
       <c r="H235" s="14" t="inlineStr"/>
@@ -14375,7 +14375,7 @@
     <row r="236" ht="44" customHeight="1">
       <c r="A236" s="11" t="inlineStr">
         <is>
-          <t>unknown_error</t>
+          <t>mic_blocked</t>
         </is>
       </c>
       <c r="B236" s="11" t="inlineStr">
@@ -14385,27 +14385,27 @@
       </c>
       <c r="C236" s="11" t="inlineStr">
         <is>
-          <t>unknown error</t>
+          <t>Microphone access is blocked. Allow it in your browser and take the session again.</t>
         </is>
       </c>
       <c r="D236" s="12" t="inlineStr">
         <is>
-          <t>ያልታወቀ ስህተት</t>
+          <t>የማይክሮፎን መዳረሻ ታግዷል። በአሳሽዎ ውስጥ ይፍቀዱና ክፍለ-ጊዜውን እንደገና ይውሰዱ።</t>
         </is>
       </c>
       <c r="E236" s="13" t="inlineStr">
         <is>
-          <t>dogoggora hin beekamne</t>
+          <t>Maayikiroofoonii dhorkameera. Biraawzarii keessan keessatti hayyamaatii session irra deebi'aa fudhadhaa.</t>
         </is>
       </c>
       <c r="F236" s="12" t="inlineStr">
         <is>
-          <t>ዘይተፈልጠ ጌጋ</t>
+          <t>መእተዊ ማይክሮፎን ተዓጊቱ። ኣብ መርበብ መንሸራተቲኹም ፍቐዱ እሞ ነቲ ክፍለ-ግዜ ደጊምኩም ውሰዱ።</t>
         </is>
       </c>
       <c r="G236" s="13" t="inlineStr">
         <is>
-          <t>khalad aan la garanayn</t>
+          <t>Makarafoonka waa la xannibay. Browser-kaaga ka ogolow oo kalfadhiga mar kale qaado.</t>
         </is>
       </c>
       <c r="H236" s="14" t="inlineStr"/>
@@ -14413,7 +14413,7 @@
     <row r="237" ht="44" customHeight="1">
       <c r="A237" s="11" t="inlineStr">
         <is>
-          <t>no_messages_yet</t>
+          <t>unknown_error</t>
         </is>
       </c>
       <c r="B237" s="11" t="inlineStr">
@@ -14423,27 +14423,27 @@
       </c>
       <c r="C237" s="11" t="inlineStr">
         <is>
-          <t>No messages yet.</t>
+          <t>unknown error</t>
         </is>
       </c>
       <c r="D237" s="12" t="inlineStr">
         <is>
-          <t>እስካሁን መልእክት የለም።</t>
+          <t>ያልታወቀ ስህተት</t>
         </is>
       </c>
       <c r="E237" s="13" t="inlineStr">
         <is>
-          <t>Ammaaf ergaan hin jiru.</t>
+          <t>dogoggora hin beekamne</t>
         </is>
       </c>
       <c r="F237" s="12" t="inlineStr">
         <is>
-          <t>ክሳብ ሕጂ መልእኽቲ የለን።</t>
+          <t>ዘይተፈልጠ ጌጋ</t>
         </is>
       </c>
       <c r="G237" s="13" t="inlineStr">
         <is>
-          <t>Weli fariimo ma jiraan.</t>
+          <t>khalad aan la garanayn</t>
         </is>
       </c>
       <c r="H237" s="14" t="inlineStr"/>
@@ -14451,7 +14451,7 @@
     <row r="238" ht="44" customHeight="1">
       <c r="A238" s="11" t="inlineStr">
         <is>
-          <t>you_label</t>
+          <t>no_messages_yet</t>
         </is>
       </c>
       <c r="B238" s="11" t="inlineStr">
@@ -14461,27 +14461,27 @@
       </c>
       <c r="C238" s="11" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>No messages yet.</t>
         </is>
       </c>
       <c r="D238" s="12" t="inlineStr">
         <is>
-          <t>እርስዎ</t>
+          <t>እስካሁን መልእክት የለም።</t>
         </is>
       </c>
       <c r="E238" s="13" t="inlineStr">
         <is>
-          <t>Isin</t>
+          <t>Ammaaf ergaan hin jiru.</t>
         </is>
       </c>
       <c r="F238" s="12" t="inlineStr">
         <is>
-          <t>ንስኹም</t>
+          <t>ክሳብ ሕጂ መልእኽቲ የለን።</t>
         </is>
       </c>
       <c r="G238" s="13" t="inlineStr">
         <is>
-          <t>Adiga</t>
+          <t>Weli fariimo ma jiraan.</t>
         </is>
       </c>
       <c r="H238" s="14" t="inlineStr"/>
@@ -14489,7 +14489,7 @@
     <row r="239" ht="44" customHeight="1">
       <c r="A239" s="11" t="inlineStr">
         <is>
-          <t>assistant_label</t>
+          <t>you_label</t>
         </is>
       </c>
       <c r="B239" s="11" t="inlineStr">
@@ -14499,27 +14499,27 @@
       </c>
       <c r="C239" s="11" t="inlineStr">
         <is>
-          <t>Assistant</t>
+          <t>You</t>
         </is>
       </c>
       <c r="D239" s="12" t="inlineStr">
         <is>
-          <t>ረዳት</t>
+          <t>እርስዎ</t>
         </is>
       </c>
       <c r="E239" s="13" t="inlineStr">
         <is>
-          <t>Gargaaraa</t>
+          <t>Isin</t>
         </is>
       </c>
       <c r="F239" s="12" t="inlineStr">
         <is>
-          <t>ሓጋዚ</t>
+          <t>ንስኹም</t>
         </is>
       </c>
       <c r="G239" s="13" t="inlineStr">
         <is>
-          <t>Kaaliye</t>
+          <t>Adiga</t>
         </is>
       </c>
       <c r="H239" s="14" t="inlineStr"/>
@@ -14527,7 +14527,7 @@
     <row r="240" ht="44" customHeight="1">
       <c r="A240" s="11" t="inlineStr">
         <is>
-          <t>conversation_unavailable</t>
+          <t>assistant_label</t>
         </is>
       </c>
       <c r="B240" s="11" t="inlineStr">
@@ -14537,27 +14537,27 @@
       </c>
       <c r="C240" s="11" t="inlineStr">
         <is>
-          <t>Conversation unavailable.</t>
+          <t>Assistant</t>
         </is>
       </c>
       <c r="D240" s="12" t="inlineStr">
         <is>
-          <t>ውይይቱ አይገኝም።</t>
+          <t>ረዳት</t>
         </is>
       </c>
       <c r="E240" s="13" t="inlineStr">
         <is>
-          <t>Mariin hin argamu.</t>
+          <t>Gargaaraa</t>
         </is>
       </c>
       <c r="F240" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዝርርብ ኣይርከብን።</t>
+          <t>ሓጋዚ</t>
         </is>
       </c>
       <c r="G240" s="13" t="inlineStr">
         <is>
-          <t>Wadahadalka lama heli karo.</t>
+          <t>Kaaliye</t>
         </is>
       </c>
       <c r="H240" s="14" t="inlineStr"/>
@@ -14565,7 +14565,7 @@
     <row r="241" ht="44" customHeight="1">
       <c r="A241" s="11" t="inlineStr">
         <is>
-          <t>unmute</t>
+          <t>conversation_unavailable</t>
         </is>
       </c>
       <c r="B241" s="11" t="inlineStr">
@@ -14575,27 +14575,27 @@
       </c>
       <c r="C241" s="11" t="inlineStr">
         <is>
-          <t>Unmute</t>
+          <t>Conversation unavailable.</t>
         </is>
       </c>
       <c r="D241" s="12" t="inlineStr">
         <is>
-          <t>ድምፅ አብራ</t>
+          <t>ውይይቱ አይገኝም።</t>
         </is>
       </c>
       <c r="E241" s="13" t="inlineStr">
         <is>
-          <t>Sagalee banaa</t>
+          <t>Mariin hin argamu.</t>
         </is>
       </c>
       <c r="F241" s="12" t="inlineStr">
         <is>
-          <t>ድምጺ ኣብርህ</t>
+          <t>እቲ ዝርርብ ኣይርከብን።</t>
         </is>
       </c>
       <c r="G241" s="13" t="inlineStr">
         <is>
-          <t>Codka fur</t>
+          <t>Wadahadalka lama heli karo.</t>
         </is>
       </c>
       <c r="H241" s="14" t="inlineStr"/>
@@ -14603,7 +14603,7 @@
     <row r="242" ht="44" customHeight="1">
       <c r="A242" s="11" t="inlineStr">
         <is>
-          <t>session_summary_prompt</t>
+          <t>unmute</t>
         </is>
       </c>
       <c r="B242" s="11" t="inlineStr">
@@ -14613,27 +14613,27 @@
       </c>
       <c r="C242" s="11" t="inlineStr">
         <is>
-          <t>What did this session cover? (optional)</t>
+          <t>Unmute</t>
         </is>
       </c>
       <c r="D242" s="12" t="inlineStr">
         <is>
-          <t>ይህ ክፍለ-ጊዜ ምን ሸፈነ? (አማራጭ)</t>
+          <t>ድምፅ አብራ</t>
         </is>
       </c>
       <c r="E242" s="13" t="inlineStr">
         <is>
-          <t>Sessioniin kun maal haguuge? (filannoo)</t>
+          <t>Sagalee banaa</t>
         </is>
       </c>
       <c r="F242" s="12" t="inlineStr">
         <is>
-          <t>እዚ ክፍለ-ግዜ እንታይ ሸፈነ? (ኣማራጺ)</t>
+          <t>ድምጺ ኣብርህ</t>
         </is>
       </c>
       <c r="G242" s="13" t="inlineStr">
         <is>
-          <t>Kalfadhigan muxuu daboolay? (ikhtiyaari)</t>
+          <t>Codka fur</t>
         </is>
       </c>
       <c r="H242" s="14" t="inlineStr"/>
@@ -14641,7 +14641,7 @@
     <row r="243" ht="44" customHeight="1">
       <c r="A243" s="11" t="inlineStr">
         <is>
-          <t>customer_ended_call</t>
+          <t>session_summary_prompt</t>
         </is>
       </c>
       <c r="B243" s="11" t="inlineStr">
@@ -14651,27 +14651,27 @@
       </c>
       <c r="C243" s="11" t="inlineStr">
         <is>
-          <t>The customer ended the call</t>
+          <t>What did this session cover? (optional)</t>
         </is>
       </c>
       <c r="D243" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛው ጥሪውን አቋረጠ</t>
+          <t>ይህ ክፍለ-ጊዜ ምን ሸፈነ? (አማራጭ)</t>
         </is>
       </c>
       <c r="E243" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan bilbila xumure</t>
+          <t>Sessioniin kun maal haguuge? (filannoo)</t>
         </is>
       </c>
       <c r="F243" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዓሚል ነቲ ጻውዒት ወዲኡዎ</t>
+          <t>እዚ ክፍለ-ግዜ እንታይ ሸፈነ? (ኣማራጺ)</t>
         </is>
       </c>
       <c r="G243" s="13" t="inlineStr">
         <is>
-          <t>Macmiilku wicitaanka wuu joojiyay</t>
+          <t>Kalfadhigan muxuu daboolay? (ikhtiyaari)</t>
         </is>
       </c>
       <c r="H243" s="14" t="inlineStr"/>
@@ -14679,7 +14679,7 @@
     <row r="244" ht="44" customHeight="1">
       <c r="A244" s="11" t="inlineStr">
         <is>
-          <t>verified_scope</t>
+          <t>customer_ended_call</t>
         </is>
       </c>
       <c r="B244" s="11" t="inlineStr">
@@ -14689,27 +14689,27 @@
       </c>
       <c r="C244" s="11" t="inlineStr">
         <is>
-          <t>You can now discuss their own records, take documents and file a dispute. Never a deposit, withdrawal or transfer.</t>
+          <t>The customer ended the call</t>
         </is>
       </c>
       <c r="D244" s="12" t="inlineStr">
         <is>
-          <t>አሁን ስለ ራሳቸው መዝገቦች መወያየት፣ ሰነዶች መቀበልና ቅሬታ ማስመዝገብ ይችላሉ። በፍጹም ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም።</t>
+          <t>ደንበኛው ጥሪውን አቋረጠ</t>
         </is>
       </c>
       <c r="E244" s="13" t="inlineStr">
         <is>
-          <t>Amma waa'ee galmee isaanii mari'achuu, sanadoota fudhachuu fi komii galmeessuu dandeessu. Gonkumaa kuusaa, baasii yookiin dabarsa hin jiru.</t>
+          <t>Maamilaan bilbila xumure</t>
         </is>
       </c>
       <c r="F244" s="12" t="inlineStr">
         <is>
-          <t>ሕጂ ብዛዕባ ናቶም መዝገባት ክትዘራረቡ፣ ሰነዳት ክትቅበሉን ጥርዓን ከተመዝግቡን ትኽእሉ። ፈጺሙ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን።</t>
+          <t>እቲ ዓሚል ነቲ ጻውዒት ወዲኡዎ</t>
         </is>
       </c>
       <c r="G244" s="13" t="inlineStr">
         <is>
-          <t>Hadda waad kala hadli kartaa diiwaankooda, dukumiinti qaadan iyo cabasho diiwaangelin. Weligaa dhigasho, qaadis ama wareejin ma jirto.</t>
+          <t>Macmiilku wicitaanka wuu joojiyay</t>
         </is>
       </c>
       <c r="H244" s="14" t="inlineStr"/>
@@ -14717,7 +14717,7 @@
     <row r="245" ht="44" customHeight="1">
       <c r="A245" s="11" t="inlineStr">
         <is>
-          <t>establish_who_they_are</t>
+          <t>verified_scope</t>
         </is>
       </c>
       <c r="B245" s="11" t="inlineStr">
@@ -14727,27 +14727,27 @@
       </c>
       <c r="C245" s="11" t="inlineStr">
         <is>
-          <t>Establish who they are — either one</t>
+          <t>You can now discuss their own records, take documents and file a dispute. Never a deposit, withdrawal or transfer.</t>
         </is>
       </c>
       <c r="D245" s="12" t="inlineStr">
         <is>
-          <t>ማንነታቸውን ያረጋግጡ — አንዱ ይበቃል</t>
+          <t>አሁን ስለ ራሳቸው መዝገቦች መወያየት፣ ሰነዶች መቀበልና ቅሬታ ማስመዝገብ ይችላሉ። በፍጹም ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም።</t>
         </is>
       </c>
       <c r="E245" s="13" t="inlineStr">
         <is>
-          <t>Eenyummaa isaanii mirkaneessaa — tokko ni ga'a</t>
+          <t>Amma waa'ee galmee isaanii mari'achuu, sanadoota fudhachuu fi komii galmeessuu dandeessu. Gonkumaa kuusaa, baasii yookiin dabarsa hin jiru.</t>
         </is>
       </c>
       <c r="F245" s="12" t="inlineStr">
         <is>
-          <t>መንነቶም ኣረጋግጹ — ሓደ እኹል እዩ</t>
+          <t>ሕጂ ብዛዕባ ናቶም መዝገባት ክትዘራረቡ፣ ሰነዳት ክትቅበሉን ጥርዓን ከተመዝግቡን ትኽእሉ። ፈጺሙ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን።</t>
         </is>
       </c>
       <c r="G245" s="13" t="inlineStr">
         <is>
-          <t>Ogow cidda ay yihiin — mid kasta</t>
+          <t>Hadda waad kala hadli kartaa diiwaankooda, dukumiinti qaadan iyo cabasho diiwaangelin. Weligaa dhigasho, qaadis ama wareejin ma jirto.</t>
         </is>
       </c>
       <c r="H245" s="14" t="inlineStr"/>
@@ -14755,7 +14755,7 @@
     <row r="246" ht="44" customHeight="1">
       <c r="A246" s="11" t="inlineStr">
         <is>
-          <t>chk_id_document</t>
+          <t>establish_who_they_are</t>
         </is>
       </c>
       <c r="B246" s="11" t="inlineStr">
@@ -14765,27 +14765,27 @@
       </c>
       <c r="C246" s="11" t="inlineStr">
         <is>
-          <t>Fayda ID shown and matches the account name</t>
+          <t>Establish who they are — either one</t>
         </is>
       </c>
       <c r="D246" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ መታወቂያ ታይቷል እና ከሂሳቡ ስም ጋር ይዛመዳል</t>
+          <t>ማንነታቸውን ያረጋግጡ — አንዱ ይበቃል</t>
         </is>
       </c>
       <c r="E246" s="13" t="inlineStr">
         <is>
-          <t>Waraqaan eenyummaa Fayda agarsiifame maqaa herregaa waliin walsimeera</t>
+          <t>Eenyummaa isaanii mirkaneessaa — tokko ni ga'a</t>
         </is>
       </c>
       <c r="F246" s="12" t="inlineStr">
         <is>
-          <t>መንነት ፋይዳ ተራእዩን ምስ ስም ሕሳብ ይሰማማዕን</t>
+          <t>መንነቶም ኣረጋግጹ — ሓደ እኹል እዩ</t>
         </is>
       </c>
       <c r="G246" s="13" t="inlineStr">
         <is>
-          <t>Aqoonsiga Fayda waa la tusay wuxuuna la mid yahay magaca xisaabta</t>
+          <t>Ogow cidda ay yihiin — mid kasta</t>
         </is>
       </c>
       <c r="H246" s="14" t="inlineStr"/>
@@ -14793,7 +14793,7 @@
     <row r="247" ht="44" customHeight="1">
       <c r="A247" s="11" t="inlineStr">
         <is>
-          <t>chk_fayda_matched</t>
+          <t>chk_id_document</t>
         </is>
       </c>
       <c r="B247" s="11" t="inlineStr">
@@ -14803,27 +14803,27 @@
       </c>
       <c r="C247" s="11" t="inlineStr">
         <is>
-          <t>Fayda number matches the account record</t>
+          <t>Fayda ID shown and matches the account name</t>
         </is>
       </c>
       <c r="D247" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ ቁጥር ከሂሳቡ መዝገብ ጋር ይዛመዳል</t>
+          <t>የፋይዳ መታወቂያ ታይቷል እና ከሂሳቡ ስም ጋር ይዛመዳል</t>
         </is>
       </c>
       <c r="E247" s="13" t="inlineStr">
         <is>
-          <t>Lakkoofsi Fayda galmee herregaa waliin walsimeera</t>
+          <t>Waraqaan eenyummaa Fayda agarsiifame maqaa herregaa waliin walsimeera</t>
         </is>
       </c>
       <c r="F247" s="12" t="inlineStr">
         <is>
-          <t>ቁጽሪ ፋይዳ ምስ መዝገብ ሕሳብ ይሰማማዕ</t>
+          <t>መንነት ፋይዳ ተራእዩን ምስ ስም ሕሳብ ይሰማማዕን</t>
         </is>
       </c>
       <c r="G247" s="13" t="inlineStr">
         <is>
-          <t>Lambarka Fayda wuxuu la mid yahay diiwaanka xisaabta</t>
+          <t>Aqoonsiga Fayda waa la tusay wuxuuna la mid yahay magaca xisaabta</t>
         </is>
       </c>
       <c r="H247" s="14" t="inlineStr"/>
@@ -14831,7 +14831,7 @@
     <row r="248" ht="44" customHeight="1">
       <c r="A248" s="11" t="inlineStr">
         <is>
-          <t>chk_fayda_matched_note</t>
+          <t>chk_fayda_matched</t>
         </is>
       </c>
       <c r="B248" s="11" t="inlineStr">
@@ -14841,27 +14841,27 @@
       </c>
       <c r="C248" s="11" t="inlineStr">
         <is>
-          <t>on your own screen — works on an audio call</t>
+          <t>Fayda number matches the account record</t>
         </is>
       </c>
       <c r="D248" s="12" t="inlineStr">
         <is>
-          <t>በራስዎ ስክሪን ላይ — በድምፅ ጥሪም ይሠራል</t>
+          <t>የፋይዳ ቁጥር ከሂሳቡ መዝገብ ጋር ይዛመዳል</t>
         </is>
       </c>
       <c r="E248" s="13" t="inlineStr">
         <is>
-          <t>iskiriinii keessan irratti — bilbila sagalee irrattis ni hojjeta</t>
+          <t>Lakkoofsi Fayda galmee herregaa waliin walsimeera</t>
         </is>
       </c>
       <c r="F248" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ናትኩም መርአዪ — ኣብ ናይ ድምጺ ጻውዒት እውን ይሰርሕ</t>
+          <t>ቁጽሪ ፋይዳ ምስ መዝገብ ሕሳብ ይሰማማዕ</t>
         </is>
       </c>
       <c r="G248" s="13" t="inlineStr">
         <is>
-          <t>shaashaddaada — wicitaan cod ahna wuu ka shaqeeyaa</t>
+          <t>Lambarka Fayda wuxuu la mid yahay diiwaanka xisaabta</t>
         </is>
       </c>
       <c r="H248" s="14" t="inlineStr"/>
@@ -14869,7 +14869,7 @@
     <row r="249" ht="44" customHeight="1">
       <c r="A249" s="11" t="inlineStr">
         <is>
-          <t>chk_id_photo</t>
+          <t>chk_fayda_matched_note</t>
         </is>
       </c>
       <c r="B249" s="11" t="inlineStr">
@@ -14879,27 +14879,27 @@
       </c>
       <c r="C249" s="11" t="inlineStr">
         <is>
-          <t>Photo on the ID matches the person on the call</t>
+          <t>on your own screen — works on an audio call</t>
         </is>
       </c>
       <c r="D249" s="12" t="inlineStr">
         <is>
-          <t>በመታወቂያው ላይ ያለው ፎቶ ከጥሪው ላይ ካለው ሰው ጋር ይዛመዳል</t>
+          <t>በራስዎ ስክሪን ላይ — በድምፅ ጥሪም ይሠራል</t>
         </is>
       </c>
       <c r="E249" s="13" t="inlineStr">
         <is>
-          <t>Suuraan waraqaa eenyummaa irra jiru nama bilbila irra jiru waliin walsimeera</t>
+          <t>iskiriinii keessan irratti — bilbila sagalee irrattis ni hojjeta</t>
         </is>
       </c>
       <c r="F249" s="12" t="inlineStr">
         <is>
-          <t>እቲ ኣብ መንነት ዘሎ ስእሊ ምስቲ ኣብ ጻውዒት ዘሎ ሰብ ይሰማማዕ</t>
+          <t>ኣብ ናትኩም መርአዪ — ኣብ ናይ ድምጺ ጻውዒት እውን ይሰርሕ</t>
         </is>
       </c>
       <c r="G249" s="13" t="inlineStr">
         <is>
-          <t>Sawirka aqoonsiga wuxuu la mid yahay qofka wicitaanka ku jira</t>
+          <t>shaashaddaada — wicitaan cod ahna wuu ka shaqeeyaa</t>
         </is>
       </c>
       <c r="H249" s="14" t="inlineStr"/>
@@ -14907,7 +14907,7 @@
     <row r="250" ht="44" customHeight="1">
       <c r="A250" s="11" t="inlineStr">
         <is>
-          <t>chk_video_only</t>
+          <t>chk_id_photo</t>
         </is>
       </c>
       <c r="B250" s="11" t="inlineStr">
@@ -14917,27 +14917,27 @@
       </c>
       <c r="C250" s="11" t="inlineStr">
         <is>
-          <t>video only</t>
+          <t>Photo on the ID matches the person on the call</t>
         </is>
       </c>
       <c r="D250" s="12" t="inlineStr">
         <is>
-          <t>ቪዲዮ ብቻ</t>
+          <t>በመታወቂያው ላይ ያለው ፎቶ ከጥሪው ላይ ካለው ሰው ጋር ይዛመዳል</t>
         </is>
       </c>
       <c r="E250" s="13" t="inlineStr">
         <is>
-          <t>viidiyoo qofa</t>
+          <t>Suuraan waraqaa eenyummaa irra jiru nama bilbila irra jiru waliin walsimeera</t>
         </is>
       </c>
       <c r="F250" s="12" t="inlineStr">
         <is>
-          <t>ቪድዮ ጥራይ</t>
+          <t>እቲ ኣብ መንነት ዘሎ ስእሊ ምስቲ ኣብ ጻውዒት ዘሎ ሰብ ይሰማማዕ</t>
         </is>
       </c>
       <c r="G250" s="13" t="inlineStr">
         <is>
-          <t>fiidyow oo kaliya</t>
+          <t>Sawirka aqoonsiga wuxuu la mid yahay qofka wicitaanka ku jira</t>
         </is>
       </c>
       <c r="H250" s="14" t="inlineStr"/>
@@ -14945,7 +14945,7 @@
     <row r="251" ht="44" customHeight="1">
       <c r="A251" s="11" t="inlineStr">
         <is>
-          <t>confirm_account_theirs</t>
+          <t>chk_video_only</t>
         </is>
       </c>
       <c r="B251" s="11" t="inlineStr">
@@ -14955,27 +14955,27 @@
       </c>
       <c r="C251" s="11" t="inlineStr">
         <is>
-          <t>And confirm the account is theirs</t>
+          <t>video only</t>
         </is>
       </c>
       <c r="D251" s="12" t="inlineStr">
         <is>
-          <t>እና ሂሳቡ የእነሱ መሆኑን ያረጋግጡ</t>
+          <t>ቪዲዮ ብቻ</t>
         </is>
       </c>
       <c r="E251" s="13" t="inlineStr">
         <is>
-          <t>Akkasumas herregni kan isaanii ta'uu mirkaneessaa</t>
+          <t>viidiyoo qofa</t>
         </is>
       </c>
       <c r="F251" s="12" t="inlineStr">
         <is>
-          <t>ከምኡ'ውን እቲ ሕሳብ ናቶም ምዃኑ ኣረጋግጹ</t>
+          <t>ቪድዮ ጥራይ</t>
         </is>
       </c>
       <c r="G251" s="13" t="inlineStr">
         <is>
-          <t>Xaqiiji in xisaabtu tahay tooda</t>
+          <t>fiidyow oo kaliya</t>
         </is>
       </c>
       <c r="H251" s="14" t="inlineStr"/>
@@ -14983,7 +14983,7 @@
     <row r="252" ht="44" customHeight="1">
       <c r="A252" s="11" t="inlineStr">
         <is>
-          <t>confirm_identity</t>
+          <t>confirm_account_theirs</t>
         </is>
       </c>
       <c r="B252" s="11" t="inlineStr">
@@ -14993,27 +14993,27 @@
       </c>
       <c r="C252" s="11" t="inlineStr">
         <is>
-          <t>Confirm identity</t>
+          <t>And confirm the account is theirs</t>
         </is>
       </c>
       <c r="D252" s="12" t="inlineStr">
         <is>
-          <t>ማንነት አረጋግጥ</t>
+          <t>እና ሂሳቡ የእነሱ መሆኑን ያረጋግጡ</t>
         </is>
       </c>
       <c r="E252" s="13" t="inlineStr">
         <is>
-          <t>Eenyummaa mirkaneessi</t>
+          <t>Akkasumas herregni kan isaanii ta'uu mirkaneessaa</t>
         </is>
       </c>
       <c r="F252" s="12" t="inlineStr">
         <is>
-          <t>መንነት ኣረጋግጽ</t>
+          <t>ከምኡ'ውን እቲ ሕሳብ ናቶም ምዃኑ ኣረጋግጹ</t>
         </is>
       </c>
       <c r="G252" s="13" t="inlineStr">
         <is>
-          <t>Xaqiiji aqoonsiga</t>
+          <t>Xaqiiji in xisaabtu tahay tooda</t>
         </is>
       </c>
       <c r="H252" s="14" t="inlineStr"/>
@@ -15021,7 +15021,7 @@
     <row r="253" ht="44" customHeight="1">
       <c r="A253" s="11" t="inlineStr">
         <is>
-          <t>unverified_scope</t>
+          <t>confirm_identity</t>
         </is>
       </c>
       <c r="B253" s="11" t="inlineStr">
@@ -15031,27 +15031,27 @@
       </c>
       <c r="C253" s="11" t="inlineStr">
         <is>
-          <t>Until this is done you can only give general guidance — products, eligibility and how to apply.</t>
+          <t>Confirm identity</t>
         </is>
       </c>
       <c r="D253" s="12" t="inlineStr">
         <is>
-          <t>ይህ እስኪከናወን ድረስ አጠቃላይ መመሪያ ብቻ መስጠት ይችላሉ — ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል።</t>
+          <t>ማንነት አረጋግጥ</t>
         </is>
       </c>
       <c r="E253" s="13" t="inlineStr">
         <is>
-          <t>Hanga kun raawwatutti qajeelfama waliigalaa qofa kennuu dandeessu — oomishaalee, ulaagaa fi akkaataa itti iyyatan.</t>
+          <t>Eenyummaa mirkaneessi</t>
         </is>
       </c>
       <c r="F253" s="12" t="inlineStr">
         <is>
-          <t>እዚ ክሳብ ዝፍጸም ሓፈሻዊ መምርሒ ጥራይ ክትህቡ ትኽእሉ — ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን።</t>
+          <t>መንነት ኣረጋግጽ</t>
         </is>
       </c>
       <c r="G253" s="13" t="inlineStr">
         <is>
-          <t>Ilaa tan la sameeyo waxaad kaliya bixin kartaa hagaajin guud — alaabta, u-qalmitaanka iyo sida loo codsado.</t>
+          <t>Xaqiiji aqoonsiga</t>
         </is>
       </c>
       <c r="H253" s="14" t="inlineStr"/>
@@ -15059,7 +15059,7 @@
     <row r="254" ht="44" customHeight="1">
       <c r="A254" s="11" t="inlineStr">
         <is>
-          <t>fayda_number_required</t>
+          <t>unverified_scope</t>
         </is>
       </c>
       <c r="B254" s="11" t="inlineStr">
@@ -15069,27 +15069,27 @@
       </c>
       <c r="C254" s="11" t="inlineStr">
         <is>
-          <t>Fayda number (required — it is what the record keeps)</t>
+          <t>Until this is done you can only give general guidance — products, eligibility and how to apply.</t>
         </is>
       </c>
       <c r="D254" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ ቁጥር (ያስፈልጋል — መዝገቡ የሚይዘው ይህ ነው)</t>
+          <t>ይህ እስኪከናወን ድረስ አጠቃላይ መመሪያ ብቻ መስጠት ይችላሉ — ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል።</t>
         </is>
       </c>
       <c r="E254" s="13" t="inlineStr">
         <is>
-          <t>Lakkoofsa Fayda (barbaachisaa — kan galmeen qabatu isa kana)</t>
+          <t>Hanga kun raawwatutti qajeelfama waliigalaa qofa kennuu dandeessu — oomishaalee, ulaagaa fi akkaataa itti iyyatan.</t>
         </is>
       </c>
       <c r="F254" s="12" t="inlineStr">
         <is>
-          <t>ቁጽሪ ፋይዳ (የድሊ — እቲ መዝገብ ዝሕዞ እዚ እዩ)</t>
+          <t>እዚ ክሳብ ዝፍጸም ሓፈሻዊ መምርሒ ጥራይ ክትህቡ ትኽእሉ — ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን።</t>
         </is>
       </c>
       <c r="G254" s="13" t="inlineStr">
         <is>
-          <t>Lambarka Fayda (loo baahan yahay — waa waxa diiwaanku hayo)</t>
+          <t>Ilaa tan la sameeyo waxaad kaliya bixin kartaa hagaajin guud — alaabta, u-qalmitaanka iyo sida loo codsado.</t>
         </is>
       </c>
       <c r="H254" s="14" t="inlineStr"/>
@@ -15097,7 +15097,7 @@
     <row r="255" ht="44" customHeight="1">
       <c r="A255" s="11" t="inlineStr">
         <is>
-          <t>download_for_translation</t>
+          <t>fayda_number_required</t>
         </is>
       </c>
       <c r="B255" s="11" t="inlineStr">
@@ -15107,27 +15107,27 @@
       </c>
       <c r="C255" s="11" t="inlineStr">
         <is>
-          <t>Download for translation</t>
+          <t>Fayda number (required — it is what the record keeps)</t>
         </is>
       </c>
       <c r="D255" s="12" t="inlineStr">
         <is>
-          <t>ለትርጉም አውርድ</t>
+          <t>የፋይዳ ቁጥር (ያስፈልጋል — መዝገቡ የሚይዘው ይህ ነው)</t>
         </is>
       </c>
       <c r="E255" s="13" t="inlineStr">
         <is>
-          <t>Hiikkaaf buufadhu</t>
+          <t>Lakkoofsa Fayda (barbaachisaa — kan galmeen qabatu isa kana)</t>
         </is>
       </c>
       <c r="F255" s="12" t="inlineStr">
         <is>
-          <t>ንትርጉም ኣውርድ</t>
+          <t>ቁጽሪ ፋይዳ (የድሊ — እቲ መዝገብ ዝሕዞ እዚ እዩ)</t>
         </is>
       </c>
       <c r="G255" s="13" t="inlineStr">
         <is>
-          <t>Soo dejiso turjumaadda</t>
+          <t>Lambarka Fayda (loo baahan yahay — waa waxa diiwaanku hayo)</t>
         </is>
       </c>
       <c r="H255" s="14" t="inlineStr"/>
@@ -15135,43 +15135,81 @@
     <row r="256" ht="44" customHeight="1">
       <c r="A256" s="11" t="inlineStr">
         <is>
+          <t>download_for_translation</t>
+        </is>
+      </c>
+      <c r="B256" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C256" s="11" t="inlineStr">
+        <is>
+          <t>Download for translation</t>
+        </is>
+      </c>
+      <c r="D256" s="12" t="inlineStr">
+        <is>
+          <t>ለትርጉም አውርድ</t>
+        </is>
+      </c>
+      <c r="E256" s="13" t="inlineStr">
+        <is>
+          <t>Hiikkaaf buufadhu</t>
+        </is>
+      </c>
+      <c r="F256" s="12" t="inlineStr">
+        <is>
+          <t>ንትርጉም ኣውርድ</t>
+        </is>
+      </c>
+      <c r="G256" s="13" t="inlineStr">
+        <is>
+          <t>Soo dejiso turjumaadda</t>
+        </is>
+      </c>
+      <c r="H256" s="14" t="inlineStr"/>
+    </row>
+    <row r="257" ht="44" customHeight="1">
+      <c r="A257" s="11" t="inlineStr">
+        <is>
           <t>nothing_to_download</t>
         </is>
       </c>
-      <c r="B256" s="11" t="inlineStr">
-        <is>
-          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
-        </is>
-      </c>
-      <c r="C256" s="11" t="inlineStr">
+      <c r="B257" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C257" s="11" t="inlineStr">
         <is>
           <t>No approved answers to download yet.</t>
         </is>
       </c>
-      <c r="D256" s="12" t="inlineStr">
+      <c r="D257" s="12" t="inlineStr">
         <is>
           <t>እስካሁን የሚወርድ የተፈቀደ መልስ የለም።</t>
         </is>
       </c>
-      <c r="E256" s="13" t="inlineStr">
+      <c r="E257" s="13" t="inlineStr">
         <is>
           <t>Hanga ammaatti deebiin mirkanaa'e buufamu hin jiru.</t>
         </is>
       </c>
-      <c r="F256" s="12" t="inlineStr">
+      <c r="F257" s="12" t="inlineStr">
         <is>
           <t>ክሳብ ሕጂ ዝወርድ ዝጸደቐ መልሲ የለን።</t>
         </is>
       </c>
-      <c r="G256" s="13" t="inlineStr">
+      <c r="G257" s="13" t="inlineStr">
         <is>
           <t>Weli ma jiraan jawaabo la ansixiyay oo la soo dejiyo.</t>
         </is>
       </c>
-      <c r="H256" s="14" t="inlineStr"/>
+      <c r="H257" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H256"/>
+  <autoFilter ref="A1:H257"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/review/Olink_Bank_Assist_language_review.xlsx
+++ b/review/Olink_Bank_Assist_language_review.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1. What the assistant says'!$A$1:$H$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2. What it understands'!$A$1:$E$78</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3. Buttons customers see'!$A$1:$H$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$H$257</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$H$266</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -752,7 +752,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>325 strings in 5 languages</t>
+          <t>334 strings in 5 languages</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H257"/>
+  <dimension ref="A1:H266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -11449,7 +11449,7 @@
     <row r="159" ht="44" customHeight="1">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>built_in</t>
+          <t>calls_per_teller</t>
         </is>
       </c>
       <c r="B159" s="11" t="inlineStr">
@@ -11459,27 +11459,27 @@
       </c>
       <c r="C159" s="11" t="inlineStr">
         <is>
-          <t>built-in</t>
+          <t>Calls per teller</t>
         </is>
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>አብሮ የተሰራ</t>
+          <t>በተጠሪ የተያዙ ጥሪዎች</t>
         </is>
       </c>
       <c r="E159" s="13" t="inlineStr">
         <is>
-          <t>kan ijaarame</t>
+          <t>Bilbilawwan teellaraan</t>
         </is>
       </c>
       <c r="F159" s="12" t="inlineStr">
         <is>
-          <t>ውሁድ</t>
+          <t>ጻውዒታት ብተለር</t>
         </is>
       </c>
       <c r="G159" s="13" t="inlineStr">
         <is>
-          <t>ku dhex jira</t>
+          <t>Wicitaanka teller kasta</t>
         </is>
       </c>
       <c r="H159" s="14" t="inlineStr"/>
@@ -11487,7 +11487,7 @@
     <row r="160" ht="44" customHeight="1">
       <c r="A160" s="11" t="inlineStr">
         <is>
-          <t>add_a_person</t>
+          <t>unit_calls</t>
         </is>
       </c>
       <c r="B160" s="11" t="inlineStr">
@@ -11497,27 +11497,27 @@
       </c>
       <c r="C160" s="11" t="inlineStr">
         <is>
-          <t>Add a person</t>
+          <t>calls</t>
         </is>
       </c>
       <c r="D160" s="12" t="inlineStr">
         <is>
-          <t>ሰው ጨምር</t>
+          <t>ጥሪዎች</t>
         </is>
       </c>
       <c r="E160" s="13" t="inlineStr">
         <is>
-          <t>Nama dabali</t>
+          <t>bilbilawwan</t>
         </is>
       </c>
       <c r="F160" s="12" t="inlineStr">
         <is>
-          <t>ሰብ ወስኽ</t>
+          <t>ጻውዒታት</t>
         </is>
       </c>
       <c r="G160" s="13" t="inlineStr">
         <is>
-          <t>Qof ku dar</t>
+          <t>wicitaanno</t>
         </is>
       </c>
       <c r="H160" s="14" t="inlineStr"/>
@@ -11525,7 +11525,7 @@
     <row r="161" ht="44" customHeight="1">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>no_calls_taken_yet</t>
         </is>
       </c>
       <c r="B161" s="11" t="inlineStr">
@@ -11535,27 +11535,27 @@
       </c>
       <c r="C161" s="11" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Nobody has taken a call yet in this window.</t>
         </is>
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>ኢሜይል</t>
+          <t>በዚህ ጊዜ ውስጥ ማንም ጥሪ አልያዘም።</t>
         </is>
       </c>
       <c r="E161" s="13" t="inlineStr">
         <is>
-          <t>Imeelii</t>
+          <t>Yeroo kana keessatti namni bilbila fudhate hin jiru.</t>
         </is>
       </c>
       <c r="F161" s="12" t="inlineStr">
         <is>
-          <t>ኢመይል</t>
+          <t>ኣብዚ እዋን'ዚ ዝሓዘ ጻውዒት የለን።</t>
         </is>
       </c>
       <c r="G161" s="13" t="inlineStr">
         <is>
-          <t>Iimayl</t>
+          <t>Cidina ma qaadan wicitaan waqtigan.</t>
         </is>
       </c>
       <c r="H161" s="14" t="inlineStr"/>
@@ -11563,7 +11563,7 @@
     <row r="162" ht="44" customHeight="1">
       <c r="A162" s="11" t="inlineStr">
         <is>
-          <t>name_optional</t>
+          <t>call_resolved</t>
         </is>
       </c>
       <c r="B162" s="11" t="inlineStr">
@@ -11573,27 +11573,27 @@
       </c>
       <c r="C162" s="11" t="inlineStr">
         <is>
-          <t>Name (optional)</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="D162" s="12" t="inlineStr">
         <is>
-          <t>ስም (አማራጭ)</t>
+          <t>ተፈትቷል</t>
         </is>
       </c>
       <c r="E162" s="13" t="inlineStr">
         <is>
-          <t>Maqaa (filannoo)</t>
+          <t>Furameera</t>
         </is>
       </c>
       <c r="F162" s="12" t="inlineStr">
         <is>
-          <t>ስም (ኣማራጺ)</t>
+          <t>ተፈቲሑ</t>
         </is>
       </c>
       <c r="G162" s="13" t="inlineStr">
         <is>
-          <t>Magac (ikhtiyaari)</t>
+          <t>La xaliyay</t>
         </is>
       </c>
       <c r="H162" s="14" t="inlineStr"/>
@@ -11601,7 +11601,7 @@
     <row r="163" ht="44" customHeight="1">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>temporary_password</t>
+          <t>call_dropped</t>
         </is>
       </c>
       <c r="B163" s="11" t="inlineStr">
@@ -11611,27 +11611,27 @@
       </c>
       <c r="C163" s="11" t="inlineStr">
         <is>
-          <t>Temporary password</t>
+          <t>Dropped (technical issue)</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>ጊዜያዊ የይለፍ ቃል</t>
+          <t>ተቋርጧል (ቴክኒካዊ ችግር)</t>
         </is>
       </c>
       <c r="E163" s="13" t="inlineStr">
         <is>
-          <t>Jecha darbii yeroo</t>
+          <t>Cite (rakkoo teekniikaa)</t>
         </is>
       </c>
       <c r="F163" s="12" t="inlineStr">
         <is>
-          <t>ግዝያዊ መሕለፊ ቃል</t>
+          <t>ተቋሪጹ (ቴክኒካዊ ጸገም)</t>
         </is>
       </c>
       <c r="G163" s="13" t="inlineStr">
         <is>
-          <t>Fure ku meel gaar ah</t>
+          <t>Wuu jabay (dhibaato farsamo)</t>
         </is>
       </c>
       <c r="H163" s="14" t="inlineStr"/>
@@ -11639,7 +11639,7 @@
     <row r="164" ht="44" customHeight="1">
       <c r="A164" s="11" t="inlineStr">
         <is>
-          <t>temp_password_help</t>
+          <t>avg_wait_before_answering</t>
         </is>
       </c>
       <c r="B164" s="11" t="inlineStr">
@@ -11649,27 +11649,27 @@
       </c>
       <c r="C164" s="11" t="inlineStr">
         <is>
-          <t>At least 12 characters. Until invitation emails are set up, this password has to be given to them directly — which is why it is shown here rather than hidden.</t>
+          <t>Avg. wait before answering:</t>
         </is>
       </c>
       <c r="D164" s="12" t="inlineStr">
         <is>
-          <t>ቢያንስ 12 ቁምፊ። የግብዣ ኢሜይሎች እስኪዘጋጁ ድረስ ይህ የይለፍ ቃል በቀጥታ ሊሰጣቸው ይገባል — ስለዚህ ተደብቆ ሳይሆን እዚህ ይታያል።</t>
+          <t>ከመመለስ በፊት አማካይ የመጠበቅ ጊዜ፦</t>
         </is>
       </c>
       <c r="E164" s="13" t="inlineStr">
         <is>
-          <t>Yoo xiqqaate arfiilee 12. Hanga imeeliin afeerraa qophaa'utti, jechi darbii kun kallattiin isaaniif kennamuu qaba — kanaafuu dhokfamuu mannaa asitti ni mul'ata.</t>
+          <t>Giddu-galeessa yeroo eegumsaa deebii dura:</t>
         </is>
       </c>
       <c r="F164" s="12" t="inlineStr">
         <is>
-          <t>ብውሑዱ 12 ፊደላት። መጸዋዕታ ኢመይል ክሳብ ዝዳሎ እዚ መሕለፊ ቃል ብቐጥታ ክወሃቦም ኣለዎ — ስለዚ ተሓቢኡ ዘይኮነ ኣብዚ ይረአ።</t>
+          <t>ማእከላይ ግዜ ምጽባይ ቅድሚ ምምላስ፦</t>
         </is>
       </c>
       <c r="G164" s="13" t="inlineStr">
         <is>
-          <t>Ugu yaraan 12 xaraf. Ilaa iimaylada casumaadda la dejiyo, furahan si toos ah ayaa loo siin doonaa — sidaas darteed halkan ayuu ka muuqdaa halkii la qarin lahaa.</t>
+          <t>Celceliska sugitaanka ka hor jawaabta:</t>
         </is>
       </c>
       <c r="H164" s="14" t="inlineStr"/>
@@ -11677,7 +11677,7 @@
     <row r="165" ht="44" customHeight="1">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>no_calls_yet_window</t>
         </is>
       </c>
       <c r="B165" s="11" t="inlineStr">
@@ -11687,27 +11687,27 @@
       </c>
       <c r="C165" s="11" t="inlineStr">
         <is>
-          <t>Create</t>
+          <t>No calls yet in this window.</t>
         </is>
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>ፍጠር</t>
+          <t>በዚህ ጊዜ ውስጥ ጥሪ የለም።</t>
         </is>
       </c>
       <c r="E165" s="13" t="inlineStr">
         <is>
-          <t>Uumi</t>
+          <t>Yeroo kana keessatti bilbilli hin jiru.</t>
         </is>
       </c>
       <c r="F165" s="12" t="inlineStr">
         <is>
-          <t>ፍጠር</t>
+          <t>ኣብዚ እዋን'ዚ ጻውዒት የለን።</t>
         </is>
       </c>
       <c r="G165" s="13" t="inlineStr">
         <is>
-          <t>Abuur</t>
+          <t>Wicitaan lama helin waqtigan.</t>
         </is>
       </c>
       <c r="H165" s="14" t="inlineStr"/>
@@ -11715,7 +11715,7 @@
     <row r="166" ht="44" customHeight="1">
       <c r="A166" s="11" t="inlineStr">
         <is>
-          <t>account_created</t>
+          <t>your_performance</t>
         </is>
       </c>
       <c r="B166" s="11" t="inlineStr">
@@ -11725,27 +11725,27 @@
       </c>
       <c r="C166" s="11" t="inlineStr">
         <is>
-          <t>Account created</t>
+          <t>Your performance</t>
         </is>
       </c>
       <c r="D166" s="12" t="inlineStr">
         <is>
-          <t>መለያ ተፈጥሯል</t>
+          <t>የእርስዎ አፈጻጸም</t>
         </is>
       </c>
       <c r="E166" s="13" t="inlineStr">
         <is>
-          <t>Herregni uumame</t>
+          <t>Hojii kee</t>
         </is>
       </c>
       <c r="F166" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ ተፈጢሩ</t>
+          <t>ኣፈጻጽማኻ</t>
         </is>
       </c>
       <c r="G166" s="13" t="inlineStr">
         <is>
-          <t>Xisaab waa la abuuray</t>
+          <t>Waxqabadkaaga</t>
         </is>
       </c>
       <c r="H166" s="14" t="inlineStr"/>
@@ -11753,7 +11753,7 @@
     <row r="167" ht="44" customHeight="1">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>account_restored</t>
+          <t>n_other_tellers</t>
         </is>
       </c>
       <c r="B167" s="11" t="inlineStr">
@@ -11763,27 +11763,27 @@
       </c>
       <c r="C167" s="11" t="inlineStr">
         <is>
-          <t>Account restored</t>
+          <t>{n} other tellers</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>መለያ ተመልሷል</t>
+          <t>{n} ሌሎች ተጠሪዎች</t>
         </is>
       </c>
       <c r="E167" s="13" t="inlineStr">
         <is>
-          <t>Herregni deebi'e</t>
+          <t>{n} teellaroota biroo</t>
         </is>
       </c>
       <c r="F167" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ ተመሊሱ</t>
+          <t>{n} ካልኦት ተለራት</t>
         </is>
       </c>
       <c r="G167" s="13" t="inlineStr">
         <is>
-          <t>Xisaabta waa la soo celiyay</t>
+          <t>{n} teller oo kale</t>
         </is>
       </c>
       <c r="H167" s="14" t="inlineStr"/>
@@ -11791,7 +11791,7 @@
     <row r="168" ht="44" customHeight="1">
       <c r="A168" s="11" t="inlineStr">
         <is>
-          <t>account_disabled_n</t>
+          <t>built_in</t>
         </is>
       </c>
       <c r="B168" s="11" t="inlineStr">
@@ -11801,27 +11801,27 @@
       </c>
       <c r="C168" s="11" t="inlineStr">
         <is>
-          <t>Account disabled, {n} session(s) ended</t>
+          <t>built-in</t>
         </is>
       </c>
       <c r="D168" s="12" t="inlineStr">
         <is>
-          <t>መለያ ተሰናክሏል፤ {n} ክፍለ-ጊዜ ተዘግቷል</t>
+          <t>አብሮ የተሰራ</t>
         </is>
       </c>
       <c r="E168" s="13" t="inlineStr">
         <is>
-          <t>Herregni dhaabame, session {n} xumurame</t>
+          <t>kan ijaarame</t>
         </is>
       </c>
       <c r="F168" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ ተዓጊቱ፣ {n} ክፍለ-ግዜ ተዛዚሙ</t>
+          <t>ውሁድ</t>
         </is>
       </c>
       <c r="G168" s="13" t="inlineStr">
         <is>
-          <t>Xisaabta waa la demiyay, {n} kalfadhi ayaa dhammaaday</t>
+          <t>ku dhex jira</t>
         </is>
       </c>
       <c r="H168" s="14" t="inlineStr"/>
@@ -11829,7 +11829,7 @@
     <row r="169" ht="44" customHeight="1">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>confirm_disable_account</t>
+          <t>add_a_person</t>
         </is>
       </c>
       <c r="B169" s="11" t="inlineStr">
@@ -11839,27 +11839,27 @@
       </c>
       <c r="C169" s="11" t="inlineStr">
         <is>
-          <t>Disable this account? They will be signed out immediately.</t>
+          <t>Add a person</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>ይህን መለያ ማሰናከል? ወዲያውኑ ይወጣሉ።</t>
+          <t>ሰው ጨምር</t>
         </is>
       </c>
       <c r="E169" s="13" t="inlineStr">
         <is>
-          <t>Herrega kana dhaabuu? Battalumatti ni baafamu.</t>
+          <t>Nama dabali</t>
         </is>
       </c>
       <c r="F169" s="12" t="inlineStr">
         <is>
-          <t>ነዚ ሕሳብ ክዕገት? ብቕጽበት ይወጹ።</t>
+          <t>ሰብ ወስኽ</t>
         </is>
       </c>
       <c r="G169" s="13" t="inlineStr">
         <is>
-          <t>Xisaabtan ma demineysaa? Isla markiiba waa laga saarayaa.</t>
+          <t>Qof ku dar</t>
         </is>
       </c>
       <c r="H169" s="14" t="inlineStr"/>
@@ -11867,7 +11867,7 @@
     <row r="170" ht="44" customHeight="1">
       <c r="A170" s="11" t="inlineStr">
         <is>
-          <t>action_document_created</t>
+          <t>email</t>
         </is>
       </c>
       <c r="B170" s="11" t="inlineStr">
@@ -11877,27 +11877,27 @@
       </c>
       <c r="C170" s="11" t="inlineStr">
         <is>
-          <t>added an article</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D170" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ጨምሯል</t>
+          <t>ኢሜይል</t>
         </is>
       </c>
       <c r="E170" s="13" t="inlineStr">
         <is>
-          <t>barruu dabale</t>
+          <t>Imeelii</t>
         </is>
       </c>
       <c r="F170" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ወሲኹ</t>
+          <t>ኢመይል</t>
         </is>
       </c>
       <c r="G170" s="13" t="inlineStr">
         <is>
-          <t>maqaal ku daray</t>
+          <t>Iimayl</t>
         </is>
       </c>
       <c r="H170" s="14" t="inlineStr"/>
@@ -11905,7 +11905,7 @@
     <row r="171" ht="44" customHeight="1">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>action_document_updated</t>
+          <t>name_optional</t>
         </is>
       </c>
       <c r="B171" s="11" t="inlineStr">
@@ -11915,27 +11915,27 @@
       </c>
       <c r="C171" s="11" t="inlineStr">
         <is>
-          <t>edited an article</t>
+          <t>Name (optional)</t>
         </is>
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ አርሟል</t>
+          <t>ስም (አማራጭ)</t>
         </is>
       </c>
       <c r="E171" s="13" t="inlineStr">
         <is>
-          <t>barruu gulaale</t>
+          <t>Maqaa (filannoo)</t>
         </is>
       </c>
       <c r="F171" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ኣርሚዑ</t>
+          <t>ስም (ኣማራጺ)</t>
         </is>
       </c>
       <c r="G171" s="13" t="inlineStr">
         <is>
-          <t>maqaal wax ka beddelay</t>
+          <t>Magac (ikhtiyaari)</t>
         </is>
       </c>
       <c r="H171" s="14" t="inlineStr"/>
@@ -11943,7 +11943,7 @@
     <row r="172" ht="44" customHeight="1">
       <c r="A172" s="11" t="inlineStr">
         <is>
-          <t>action_document_deleted</t>
+          <t>temporary_password</t>
         </is>
       </c>
       <c r="B172" s="11" t="inlineStr">
@@ -11953,27 +11953,27 @@
       </c>
       <c r="C172" s="11" t="inlineStr">
         <is>
-          <t>deleted an article</t>
+          <t>Temporary password</t>
         </is>
       </c>
       <c r="D172" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ሰርዟል</t>
+          <t>ጊዜያዊ የይለፍ ቃል</t>
         </is>
       </c>
       <c r="E172" s="13" t="inlineStr">
         <is>
-          <t>barruu haqe</t>
+          <t>Jecha darbii yeroo</t>
         </is>
       </c>
       <c r="F172" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ደምሲሱ</t>
+          <t>ግዝያዊ መሕለፊ ቃል</t>
         </is>
       </c>
       <c r="G172" s="13" t="inlineStr">
         <is>
-          <t>maqaal tirtiray</t>
+          <t>Fure ku meel gaar ah</t>
         </is>
       </c>
       <c r="H172" s="14" t="inlineStr"/>
@@ -11981,7 +11981,7 @@
     <row r="173" ht="44" customHeight="1">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>action_documents_bulk_imported</t>
+          <t>temp_password_help</t>
         </is>
       </c>
       <c r="B173" s="11" t="inlineStr">
@@ -11991,27 +11991,27 @@
       </c>
       <c r="C173" s="11" t="inlineStr">
         <is>
-          <t>imported articles</t>
+          <t>At least 12 characters. Until invitation emails are set up, this password has to be given to them directly — which is why it is shown here rather than hidden.</t>
         </is>
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፎችን አስገብቷል</t>
+          <t>ቢያንስ 12 ቁምፊ። የግብዣ ኢሜይሎች እስኪዘጋጁ ድረስ ይህ የይለፍ ቃል በቀጥታ ሊሰጣቸው ይገባል — ስለዚህ ተደብቆ ሳይሆን እዚህ ይታያል።</t>
         </is>
       </c>
       <c r="E173" s="13" t="inlineStr">
         <is>
-          <t>barruulee galche</t>
+          <t>Yoo xiqqaate arfiilee 12. Hanga imeeliin afeerraa qophaa'utti, jechi darbii kun kallattiin isaaniif kennamuu qaba — kanaafuu dhokfamuu mannaa asitti ni mul'ata.</t>
         </is>
       </c>
       <c r="F173" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፋት ኣእትዩ</t>
+          <t>ብውሑዱ 12 ፊደላት። መጸዋዕታ ኢመይል ክሳብ ዝዳሎ እዚ መሕለፊ ቃል ብቐጥታ ክወሃቦም ኣለዎ — ስለዚ ተሓቢኡ ዘይኮነ ኣብዚ ይረአ።</t>
         </is>
       </c>
       <c r="G173" s="13" t="inlineStr">
         <is>
-          <t>maqaallo soo dhoofiyay</t>
+          <t>Ugu yaraan 12 xaraf. Ilaa iimaylada casumaadda la dejiyo, furahan si toos ah ayaa loo siin doonaa — sidaas darteed halkan ayuu ka muuqdaa halkii la qarin lahaa.</t>
         </is>
       </c>
       <c r="H173" s="14" t="inlineStr"/>
@@ -12019,7 +12019,7 @@
     <row r="174" ht="44" customHeight="1">
       <c r="A174" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_closed</t>
+          <t>create</t>
         </is>
       </c>
       <c r="B174" s="11" t="inlineStr">
@@ -12029,27 +12029,27 @@
       </c>
       <c r="C174" s="11" t="inlineStr">
         <is>
-          <t>closed an escalation</t>
+          <t>Create</t>
         </is>
       </c>
       <c r="D174" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ ዘግቷል</t>
+          <t>ፍጠር</t>
         </is>
       </c>
       <c r="E174" s="13" t="inlineStr">
         <is>
-          <t>dhimma cufe</t>
+          <t>Uumi</t>
         </is>
       </c>
       <c r="F174" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ ዓጺዩ</t>
+          <t>ፍጠር</t>
         </is>
       </c>
       <c r="G174" s="13" t="inlineStr">
         <is>
-          <t>arrin xiray</t>
+          <t>Abuur</t>
         </is>
       </c>
       <c r="H174" s="14" t="inlineStr"/>
@@ -12057,7 +12057,7 @@
     <row r="175" ht="44" customHeight="1">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_reopened</t>
+          <t>account_created</t>
         </is>
       </c>
       <c r="B175" s="11" t="inlineStr">
@@ -12067,27 +12067,27 @@
       </c>
       <c r="C175" s="11" t="inlineStr">
         <is>
-          <t>reopened an escalation</t>
+          <t>Account created</t>
         </is>
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ በድጋሚ ከፍቷል</t>
+          <t>መለያ ተፈጥሯል</t>
         </is>
       </c>
       <c r="E175" s="13" t="inlineStr">
         <is>
-          <t>dhimma irra deebi'ee bane</t>
+          <t>Herregni uumame</t>
         </is>
       </c>
       <c r="F175" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ ደጊሙ ከፊቱ</t>
+          <t>ሕሳብ ተፈጢሩ</t>
         </is>
       </c>
       <c r="G175" s="13" t="inlineStr">
         <is>
-          <t>arrin dib u furay</t>
+          <t>Xisaab waa la abuuray</t>
         </is>
       </c>
       <c r="H175" s="14" t="inlineStr"/>
@@ -12095,7 +12095,7 @@
     <row r="176" ht="44" customHeight="1">
       <c r="A176" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_webhook_connected</t>
+          <t>account_restored</t>
         </is>
       </c>
       <c r="B176" s="11" t="inlineStr">
@@ -12105,27 +12105,27 @@
       </c>
       <c r="C176" s="11" t="inlineStr">
         <is>
-          <t>connected the escalation webhook</t>
+          <t>Account restored</t>
         </is>
       </c>
       <c r="D176" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ዌብሁክ አገናኝቷል</t>
+          <t>መለያ ተመልሷል</t>
         </is>
       </c>
       <c r="E176" s="13" t="inlineStr">
         <is>
-          <t>webhook dabarsaa walqunnamsiise</t>
+          <t>Herregni deebi'e</t>
         </is>
       </c>
       <c r="F176" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ምትሕልላፍ ኣራኺቡ</t>
+          <t>ሕሳብ ተመሊሱ</t>
         </is>
       </c>
       <c r="G176" s="13" t="inlineStr">
         <is>
-          <t>ku xiray webhook-ga gudbinta</t>
+          <t>Xisaabta waa la soo celiyay</t>
         </is>
       </c>
       <c r="H176" s="14" t="inlineStr"/>
@@ -12133,7 +12133,7 @@
     <row r="177" ht="44" customHeight="1">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_webhook_disconnected</t>
+          <t>account_disabled_n</t>
         </is>
       </c>
       <c r="B177" s="11" t="inlineStr">
@@ -12143,27 +12143,27 @@
       </c>
       <c r="C177" s="11" t="inlineStr">
         <is>
-          <t>disconnected the escalation webhook</t>
+          <t>Account disabled, {n} session(s) ended</t>
         </is>
       </c>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ዌብሁክ አቋርጧል</t>
+          <t>መለያ ተሰናክሏል፤ {n} ክፍለ-ጊዜ ተዘግቷል</t>
         </is>
       </c>
       <c r="E177" s="13" t="inlineStr">
         <is>
-          <t>webhook dabarsaa addaan kute</t>
+          <t>Herregni dhaabame, session {n} xumurame</t>
         </is>
       </c>
       <c r="F177" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ምትሕልላፍ ቆሪጹ</t>
+          <t>ሕሳብ ተዓጊቱ፣ {n} ክፍለ-ግዜ ተዛዚሙ</t>
         </is>
       </c>
       <c r="G177" s="13" t="inlineStr">
         <is>
-          <t>goynay webhook-ga gudbinta</t>
+          <t>Xisaabta waa la demiyay, {n} kalfadhi ayaa dhammaaday</t>
         </is>
       </c>
       <c r="H177" s="14" t="inlineStr"/>
@@ -12171,7 +12171,7 @@
     <row r="178" ht="44" customHeight="1">
       <c r="A178" s="11" t="inlineStr">
         <is>
-          <t>action_telegram_connected</t>
+          <t>confirm_disable_account</t>
         </is>
       </c>
       <c r="B178" s="11" t="inlineStr">
@@ -12181,27 +12181,27 @@
       </c>
       <c r="C178" s="11" t="inlineStr">
         <is>
-          <t>connected Telegram</t>
+          <t>Disable this account? They will be signed out immediately.</t>
         </is>
       </c>
       <c r="D178" s="12" t="inlineStr">
         <is>
-          <t>ቴሌግራም አገናኝቷል</t>
+          <t>ይህን መለያ ማሰናከል? ወዲያውኑ ይወጣሉ።</t>
         </is>
       </c>
       <c r="E178" s="13" t="inlineStr">
         <is>
-          <t>Telegram walqunnamsiise</t>
+          <t>Herrega kana dhaabuu? Battalumatti ni baafamu.</t>
         </is>
       </c>
       <c r="F178" s="12" t="inlineStr">
         <is>
-          <t>ቴሌግራም ኣራኺቡ</t>
+          <t>ነዚ ሕሳብ ክዕገት? ብቕጽበት ይወጹ።</t>
         </is>
       </c>
       <c r="G178" s="13" t="inlineStr">
         <is>
-          <t>Telegram ku xiray</t>
+          <t>Xisaabtan ma demineysaa? Isla markiiba waa laga saarayaa.</t>
         </is>
       </c>
       <c r="H178" s="14" t="inlineStr"/>
@@ -12209,7 +12209,7 @@
     <row r="179" ht="44" customHeight="1">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>action_user_created</t>
+          <t>action_document_created</t>
         </is>
       </c>
       <c r="B179" s="11" t="inlineStr">
@@ -12219,27 +12219,27 @@
       </c>
       <c r="C179" s="11" t="inlineStr">
         <is>
-          <t>added a colleague</t>
+          <t>added an article</t>
         </is>
       </c>
       <c r="D179" s="12" t="inlineStr">
         <is>
-          <t>ባልደረባ ጨምሯል</t>
+          <t>ጽሑፍ ጨምሯል</t>
         </is>
       </c>
       <c r="E179" s="13" t="inlineStr">
         <is>
-          <t>hojjetaa dabale</t>
+          <t>barruu dabale</t>
         </is>
       </c>
       <c r="F179" s="12" t="inlineStr">
         <is>
-          <t>መሳርሕቲ ወሲኹ</t>
+          <t>ጽሑፍ ወሲኹ</t>
         </is>
       </c>
       <c r="G179" s="13" t="inlineStr">
         <is>
-          <t>shaqaale ku daray</t>
+          <t>maqaal ku daray</t>
         </is>
       </c>
       <c r="H179" s="14" t="inlineStr"/>
@@ -12247,7 +12247,7 @@
     <row r="180" ht="44" customHeight="1">
       <c r="A180" s="11" t="inlineStr">
         <is>
-          <t>action_user_disabled</t>
+          <t>action_document_updated</t>
         </is>
       </c>
       <c r="B180" s="11" t="inlineStr">
@@ -12257,27 +12257,27 @@
       </c>
       <c r="C180" s="11" t="inlineStr">
         <is>
-          <t>disabled an account</t>
+          <t>edited an article</t>
         </is>
       </c>
       <c r="D180" s="12" t="inlineStr">
         <is>
-          <t>መለያ አሰናክሏል</t>
+          <t>ጽሑፍ አርሟል</t>
         </is>
       </c>
       <c r="E180" s="13" t="inlineStr">
         <is>
-          <t>herrega dhaabe</t>
+          <t>barruu gulaale</t>
         </is>
       </c>
       <c r="F180" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ ዓጊቱ</t>
+          <t>ጽሑፍ ኣርሚዑ</t>
         </is>
       </c>
       <c r="G180" s="13" t="inlineStr">
         <is>
-          <t>xisaab demiyay</t>
+          <t>maqaal wax ka beddelay</t>
         </is>
       </c>
       <c r="H180" s="14" t="inlineStr"/>
@@ -12285,7 +12285,7 @@
     <row r="181" ht="44" customHeight="1">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t>action_user_enabled</t>
+          <t>action_document_deleted</t>
         </is>
       </c>
       <c r="B181" s="11" t="inlineStr">
@@ -12295,27 +12295,27 @@
       </c>
       <c r="C181" s="11" t="inlineStr">
         <is>
-          <t>restored an account</t>
+          <t>deleted an article</t>
         </is>
       </c>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>መለያ መልሷል</t>
+          <t>ጽሑፍ ሰርዟል</t>
         </is>
       </c>
       <c r="E181" s="13" t="inlineStr">
         <is>
-          <t>herrega deebise</t>
+          <t>barruu haqe</t>
         </is>
       </c>
       <c r="F181" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ መሊሱ</t>
+          <t>ጽሑፍ ደምሲሱ</t>
         </is>
       </c>
       <c r="G181" s="13" t="inlineStr">
         <is>
-          <t>xisaab soo celiyay</t>
+          <t>maqaal tirtiray</t>
         </is>
       </c>
       <c r="H181" s="14" t="inlineStr"/>
@@ -12323,7 +12323,7 @@
     <row r="182" ht="44" customHeight="1">
       <c r="A182" s="11" t="inlineStr">
         <is>
-          <t>action_admin_login</t>
+          <t>action_documents_bulk_imported</t>
         </is>
       </c>
       <c r="B182" s="11" t="inlineStr">
@@ -12333,27 +12333,27 @@
       </c>
       <c r="C182" s="11" t="inlineStr">
         <is>
-          <t>signed in</t>
+          <t>imported articles</t>
         </is>
       </c>
       <c r="D182" s="12" t="inlineStr">
         <is>
-          <t>ገብቷል</t>
+          <t>ጽሑፎችን አስገብቷል</t>
         </is>
       </c>
       <c r="E182" s="13" t="inlineStr">
         <is>
-          <t>seene</t>
+          <t>barruulee galche</t>
         </is>
       </c>
       <c r="F182" s="12" t="inlineStr">
         <is>
-          <t>ኣትዩ</t>
+          <t>ጽሑፋት ኣእትዩ</t>
         </is>
       </c>
       <c r="G182" s="13" t="inlineStr">
         <is>
-          <t>gashay</t>
+          <t>maqaallo soo dhoofiyay</t>
         </is>
       </c>
       <c r="H182" s="14" t="inlineStr"/>
@@ -12361,7 +12361,7 @@
     <row r="183" ht="44" customHeight="1">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t>action_password_changed</t>
+          <t>action_handoff_closed</t>
         </is>
       </c>
       <c r="B183" s="11" t="inlineStr">
@@ -12371,27 +12371,27 @@
       </c>
       <c r="C183" s="11" t="inlineStr">
         <is>
-          <t>changed their password</t>
+          <t>closed an escalation</t>
         </is>
       </c>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>የይለፍ ቃል ቀይሯል</t>
+          <t>ጉዳይ ዘግቷል</t>
         </is>
       </c>
       <c r="E183" s="13" t="inlineStr">
         <is>
-          <t>jecha darbii jijjiire</t>
+          <t>dhimma cufe</t>
         </is>
       </c>
       <c r="F183" s="12" t="inlineStr">
         <is>
-          <t>መሕለፊ ቃል ቀዪሩ</t>
+          <t>ጉዳይ ዓጺዩ</t>
         </is>
       </c>
       <c r="G183" s="13" t="inlineStr">
         <is>
-          <t>beddelay furihiisa</t>
+          <t>arrin xiray</t>
         </is>
       </c>
       <c r="H183" s="14" t="inlineStr"/>
@@ -12399,7 +12399,7 @@
     <row r="184" ht="44" customHeight="1">
       <c r="A184" s="11" t="inlineStr">
         <is>
-          <t>nothing_yet</t>
+          <t>action_handoff_reopened</t>
         </is>
       </c>
       <c r="B184" s="11" t="inlineStr">
@@ -12409,27 +12409,27 @@
       </c>
       <c r="C184" s="11" t="inlineStr">
         <is>
-          <t>Nothing yet.</t>
+          <t>reopened an escalation</t>
         </is>
       </c>
       <c r="D184" s="12" t="inlineStr">
         <is>
-          <t>እስካሁን ምንም የለም።</t>
+          <t>ጉዳይ በድጋሚ ከፍቷል</t>
         </is>
       </c>
       <c r="E184" s="13" t="inlineStr">
         <is>
-          <t>Ammaaf homaa hin jiru.</t>
+          <t>dhimma irra deebi'ee bane</t>
         </is>
       </c>
       <c r="F184" s="12" t="inlineStr">
         <is>
-          <t>ክሳብ ሕጂ ዋላ ሓደ የለን።</t>
+          <t>ጉዳይ ደጊሙ ከፊቱ</t>
         </is>
       </c>
       <c r="G184" s="13" t="inlineStr">
         <is>
-          <t>Weli waxba ma jiraan.</t>
+          <t>arrin dib u furay</t>
         </is>
       </c>
       <c r="H184" s="14" t="inlineStr"/>
@@ -12437,7 +12437,7 @@
     <row r="185" ht="44" customHeight="1">
       <c r="A185" s="11" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>action_handoff_webhook_connected</t>
         </is>
       </c>
       <c r="B185" s="11" t="inlineStr">
@@ -12447,27 +12447,27 @@
       </c>
       <c r="C185" s="11" t="inlineStr">
         <is>
-          <t>Unavailable.</t>
+          <t>connected the escalation webhook</t>
         </is>
       </c>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>አይገኝም።</t>
+          <t>የማሸጋገሪያ ዌብሁክ አገናኝቷል</t>
         </is>
       </c>
       <c r="E185" s="13" t="inlineStr">
         <is>
-          <t>Hin argamu.</t>
+          <t>webhook dabarsaa walqunnamsiise</t>
         </is>
       </c>
       <c r="F185" s="12" t="inlineStr">
         <is>
-          <t>ኣይርከብን።</t>
+          <t>ዌብሁክ ምትሕልላፍ ኣራኺቡ</t>
         </is>
       </c>
       <c r="G185" s="13" t="inlineStr">
         <is>
-          <t>Lama heli karo.</t>
+          <t>ku xiray webhook-ga gudbinta</t>
         </is>
       </c>
       <c r="H185" s="14" t="inlineStr"/>
@@ -12475,7 +12475,7 @@
     <row r="186" ht="44" customHeight="1">
       <c r="A186" s="11" t="inlineStr">
         <is>
-          <t>just_now</t>
+          <t>action_handoff_webhook_disconnected</t>
         </is>
       </c>
       <c r="B186" s="11" t="inlineStr">
@@ -12485,27 +12485,27 @@
       </c>
       <c r="C186" s="11" t="inlineStr">
         <is>
-          <t>just now</t>
+          <t>disconnected the escalation webhook</t>
         </is>
       </c>
       <c r="D186" s="12" t="inlineStr">
         <is>
-          <t>አሁን</t>
+          <t>የማሸጋገሪያ ዌብሁክ አቋርጧል</t>
         </is>
       </c>
       <c r="E186" s="13" t="inlineStr">
         <is>
-          <t>amma</t>
+          <t>webhook dabarsaa addaan kute</t>
         </is>
       </c>
       <c r="F186" s="12" t="inlineStr">
         <is>
-          <t>ሕጂ</t>
+          <t>ዌብሁክ ምትሕልላፍ ቆሪጹ</t>
         </is>
       </c>
       <c r="G186" s="13" t="inlineStr">
         <is>
-          <t>hadda</t>
+          <t>goynay webhook-ga gudbinta</t>
         </is>
       </c>
       <c r="H186" s="14" t="inlineStr"/>
@@ -12513,7 +12513,7 @@
     <row r="187" ht="44" customHeight="1">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t>n_min_ago</t>
+          <t>action_telegram_connected</t>
         </is>
       </c>
       <c r="B187" s="11" t="inlineStr">
@@ -12523,27 +12523,27 @@
       </c>
       <c r="C187" s="11" t="inlineStr">
         <is>
-          <t>{n} min ago</t>
+          <t>connected Telegram</t>
         </is>
       </c>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ደቂቃ በፊት</t>
+          <t>ቴሌግራም አገናኝቷል</t>
         </is>
       </c>
       <c r="E187" s="13" t="inlineStr">
         <is>
-          <t>daqiiqaa {n} dura</t>
+          <t>Telegram walqunnamsiise</t>
         </is>
       </c>
       <c r="F187" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ደቒቕ</t>
+          <t>ቴሌግራም ኣራኺቡ</t>
         </is>
       </c>
       <c r="G187" s="13" t="inlineStr">
         <is>
-          <t>{n} daqiiqo ka hor</t>
+          <t>Telegram ku xiray</t>
         </is>
       </c>
       <c r="H187" s="14" t="inlineStr"/>
@@ -12551,7 +12551,7 @@
     <row r="188" ht="44" customHeight="1">
       <c r="A188" s="11" t="inlineStr">
         <is>
-          <t>n_h_ago</t>
+          <t>action_user_created</t>
         </is>
       </c>
       <c r="B188" s="11" t="inlineStr">
@@ -12561,27 +12561,27 @@
       </c>
       <c r="C188" s="11" t="inlineStr">
         <is>
-          <t>{n} h ago</t>
+          <t>added a colleague</t>
         </is>
       </c>
       <c r="D188" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ሰዓት በፊት</t>
+          <t>ባልደረባ ጨምሯል</t>
         </is>
       </c>
       <c r="E188" s="13" t="inlineStr">
         <is>
-          <t>sa'aatii {n} dura</t>
+          <t>hojjetaa dabale</t>
         </is>
       </c>
       <c r="F188" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ሰዓት</t>
+          <t>መሳርሕቲ ወሲኹ</t>
         </is>
       </c>
       <c r="G188" s="13" t="inlineStr">
         <is>
-          <t>{n} saac ka hor</t>
+          <t>shaqaale ku daray</t>
         </is>
       </c>
       <c r="H188" s="14" t="inlineStr"/>
@@ -12589,7 +12589,7 @@
     <row r="189" ht="44" customHeight="1">
       <c r="A189" s="11" t="inlineStr">
         <is>
-          <t>n_d_ago</t>
+          <t>action_user_disabled</t>
         </is>
       </c>
       <c r="B189" s="11" t="inlineStr">
@@ -12599,27 +12599,27 @@
       </c>
       <c r="C189" s="11" t="inlineStr">
         <is>
-          <t>{n} d ago</t>
+          <t>disabled an account</t>
         </is>
       </c>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ቀን በፊት</t>
+          <t>መለያ አሰናክሏል</t>
         </is>
       </c>
       <c r="E189" s="13" t="inlineStr">
         <is>
-          <t>guyyaa {n} dura</t>
+          <t>herrega dhaabe</t>
         </is>
       </c>
       <c r="F189" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} መዓልቲ</t>
+          <t>ሕሳብ ዓጊቱ</t>
         </is>
       </c>
       <c r="G189" s="13" t="inlineStr">
         <is>
-          <t>{n} maalmood ka hor</t>
+          <t>xisaab demiyay</t>
         </is>
       </c>
       <c r="H189" s="14" t="inlineStr"/>
@@ -12627,7 +12627,7 @@
     <row r="190" ht="44" customHeight="1">
       <c r="A190" s="11" t="inlineStr">
         <is>
-          <t>channel_all_from</t>
+          <t>action_user_enabled</t>
         </is>
       </c>
       <c r="B190" s="11" t="inlineStr">
@@ -12637,27 +12637,27 @@
       </c>
       <c r="C190" s="11" t="inlineStr">
         <is>
-          <t>All {n} conversations came from {label}.</t>
+          <t>restored an account</t>
         </is>
       </c>
       <c r="D190" s="12" t="inlineStr">
         <is>
-          <t>ሁሉም {n} ውይይቶች ከ{label} መጥተዋል።</t>
+          <t>መለያ መልሷል</t>
         </is>
       </c>
       <c r="E190" s="13" t="inlineStr">
         <is>
-          <t>Mariin {n} hundi {label} irraa dhufe.</t>
+          <t>herrega deebise</t>
         </is>
       </c>
       <c r="F190" s="12" t="inlineStr">
         <is>
-          <t>ኩሎም {n} ዝርርባት ካብ {label} መጺኦም።</t>
+          <t>ሕሳብ መሊሱ</t>
         </is>
       </c>
       <c r="G190" s="13" t="inlineStr">
         <is>
-          <t>Dhammaan {n} wadahadal waxay ka yimaadeen {label}.</t>
+          <t>xisaab soo celiyay</t>
         </is>
       </c>
       <c r="H190" s="14" t="inlineStr"/>
@@ -12665,7 +12665,7 @@
     <row r="191" ht="44" customHeight="1">
       <c r="A191" s="11" t="inlineStr">
         <is>
-          <t>channel_live</t>
+          <t>action_admin_login</t>
         </is>
       </c>
       <c r="B191" s="11" t="inlineStr">
@@ -12675,27 +12675,27 @@
       </c>
       <c r="C191" s="11" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>signed in</t>
         </is>
       </c>
       <c r="D191" s="12" t="inlineStr">
         <is>
-          <t>በሥራ ላይ</t>
+          <t>ገብቷል</t>
         </is>
       </c>
       <c r="E191" s="13" t="inlineStr">
         <is>
-          <t>Hojiirra</t>
+          <t>seene</t>
         </is>
       </c>
       <c r="F191" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ስራሕ</t>
+          <t>ኣትዩ</t>
         </is>
       </c>
       <c r="G191" s="13" t="inlineStr">
         <is>
-          <t>Shaqeynaya</t>
+          <t>gashay</t>
         </is>
       </c>
       <c r="H191" s="14" t="inlineStr"/>
@@ -12703,7 +12703,7 @@
     <row r="192" ht="44" customHeight="1">
       <c r="A192" s="11" t="inlineStr">
         <is>
-          <t>channel_ready</t>
+          <t>action_password_changed</t>
         </is>
       </c>
       <c r="B192" s="11" t="inlineStr">
@@ -12713,27 +12713,27 @@
       </c>
       <c r="C192" s="11" t="inlineStr">
         <is>
-          <t>Ready to connect</t>
+          <t>changed their password</t>
         </is>
       </c>
       <c r="D192" s="12" t="inlineStr">
         <is>
-          <t>ለመገናኘት ዝግጁ</t>
+          <t>የይለፍ ቃል ቀይሯል</t>
         </is>
       </c>
       <c r="E192" s="13" t="inlineStr">
         <is>
-          <t>Walqunnamuuf qophaa'aa</t>
+          <t>jecha darbii jijjiire</t>
         </is>
       </c>
       <c r="F192" s="12" t="inlineStr">
         <is>
-          <t>ንምርኻብ ድሉው</t>
+          <t>መሕለፊ ቃል ቀዪሩ</t>
         </is>
       </c>
       <c r="G192" s="13" t="inlineStr">
         <is>
-          <t>Diyaar u ah xiriirka</t>
+          <t>beddelay furihiisa</t>
         </is>
       </c>
       <c r="H192" s="14" t="inlineStr"/>
@@ -12741,7 +12741,7 @@
     <row r="193" ht="44" customHeight="1">
       <c r="A193" s="11" t="inlineStr">
         <is>
-          <t>channel_needs_setup</t>
+          <t>nothing_yet</t>
         </is>
       </c>
       <c r="B193" s="11" t="inlineStr">
@@ -12751,27 +12751,27 @@
       </c>
       <c r="C193" s="11" t="inlineStr">
         <is>
-          <t>Needs setup</t>
+          <t>Nothing yet.</t>
         </is>
       </c>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>ማዋቀር ይፈልጋል</t>
+          <t>እስካሁን ምንም የለም።</t>
         </is>
       </c>
       <c r="E193" s="13" t="inlineStr">
         <is>
-          <t>Qindeessuu barbaada</t>
+          <t>Ammaaf homaa hin jiru.</t>
         </is>
       </c>
       <c r="F193" s="12" t="inlineStr">
         <is>
-          <t>ምድላው የድልዮ</t>
+          <t>ክሳብ ሕጂ ዋላ ሓደ የለን።</t>
         </is>
       </c>
       <c r="G193" s="13" t="inlineStr">
         <is>
-          <t>Waxay u baahan tahay dejin</t>
+          <t>Weli waxba ma jiraan.</t>
         </is>
       </c>
       <c r="H193" s="14" t="inlineStr"/>
@@ -12779,7 +12779,7 @@
     <row r="194" ht="44" customHeight="1">
       <c r="A194" s="11" t="inlineStr">
         <is>
-          <t>share_by_channel</t>
+          <t>unavailable</t>
         </is>
       </c>
       <c r="B194" s="11" t="inlineStr">
@@ -12789,27 +12789,27 @@
       </c>
       <c r="C194" s="11" t="inlineStr">
         <is>
-          <t>Share of conversations by channel</t>
+          <t>Unavailable.</t>
         </is>
       </c>
       <c r="D194" s="12" t="inlineStr">
         <is>
-          <t>በመስመር የተከፋፈሉ ውይይቶች ድርሻ</t>
+          <t>አይገኝም።</t>
         </is>
       </c>
       <c r="E194" s="13" t="inlineStr">
         <is>
-          <t>Qooda marii karaa tokkoon tokkoon isaanii</t>
+          <t>Hin argamu.</t>
         </is>
       </c>
       <c r="F194" s="12" t="inlineStr">
         <is>
-          <t>ብመስመር ዝተኸፋፈለ ግደ ዝርርባት</t>
+          <t>ኣይርከብን።</t>
         </is>
       </c>
       <c r="G194" s="13" t="inlineStr">
         <is>
-          <t>Qaybta wadahadallada kanaalka</t>
+          <t>Lama heli karo.</t>
         </is>
       </c>
       <c r="H194" s="14" t="inlineStr"/>
@@ -12817,7 +12817,7 @@
     <row r="195" ht="44" customHeight="1">
       <c r="A195" s="11" t="inlineStr">
         <is>
-          <t>up_to_date</t>
+          <t>just_now</t>
         </is>
       </c>
       <c r="B195" s="11" t="inlineStr">
@@ -12827,27 +12827,27 @@
       </c>
       <c r="C195" s="11" t="inlineStr">
         <is>
-          <t>Up to date</t>
+          <t>just now</t>
         </is>
       </c>
       <c r="D195" s="12" t="inlineStr">
         <is>
-          <t>የተዘመነ</t>
+          <t>አሁን</t>
         </is>
       </c>
       <c r="E195" s="13" t="inlineStr">
         <is>
-          <t>Haaraa</t>
+          <t>amma</t>
         </is>
       </c>
       <c r="F195" s="12" t="inlineStr">
         <is>
-          <t>ዝተሓደሰ</t>
+          <t>ሕጂ</t>
         </is>
       </c>
       <c r="G195" s="13" t="inlineStr">
         <is>
-          <t>La cusbooneysiiyay</t>
+          <t>hadda</t>
         </is>
       </c>
       <c r="H195" s="14" t="inlineStr"/>
@@ -12855,7 +12855,7 @@
     <row r="196" ht="44" customHeight="1">
       <c r="A196" s="11" t="inlineStr">
         <is>
-          <t>updated_m_ago</t>
+          <t>n_min_ago</t>
         </is>
       </c>
       <c r="B196" s="11" t="inlineStr">
@@ -12865,27 +12865,27 @@
       </c>
       <c r="C196" s="11" t="inlineStr">
         <is>
-          <t>Updated {n}m ago</t>
+          <t>{n} min ago</t>
         </is>
       </c>
       <c r="D196" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ደቂቃ በፊት ተዘምኗል</t>
+          <t>ከ{n} ደቂቃ በፊት</t>
         </is>
       </c>
       <c r="E196" s="13" t="inlineStr">
         <is>
-          <t>Daqiiqaa {n} dura haaromfame</t>
+          <t>daqiiqaa {n} dura</t>
         </is>
       </c>
       <c r="F196" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ደቒቕ ተሓዲሱ</t>
+          <t>ቅድሚ {n} ደቒቕ</t>
         </is>
       </c>
       <c r="G196" s="13" t="inlineStr">
         <is>
-          <t>La cusbooneysiiyay {n}daq ka hor</t>
+          <t>{n} daqiiqo ka hor</t>
         </is>
       </c>
       <c r="H196" s="14" t="inlineStr"/>
@@ -12893,7 +12893,7 @@
     <row r="197" ht="44" customHeight="1">
       <c r="A197" s="11" t="inlineStr">
         <is>
-          <t>updated_h_ago</t>
+          <t>n_h_ago</t>
         </is>
       </c>
       <c r="B197" s="11" t="inlineStr">
@@ -12903,27 +12903,27 @@
       </c>
       <c r="C197" s="11" t="inlineStr">
         <is>
-          <t>Updated {n}h ago</t>
+          <t>{n} h ago</t>
         </is>
       </c>
       <c r="D197" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ሰዓት በፊት ተዘምኗል</t>
+          <t>ከ{n} ሰዓት በፊት</t>
         </is>
       </c>
       <c r="E197" s="13" t="inlineStr">
         <is>
-          <t>Sa'aatii {n} dura haaromfame</t>
+          <t>sa'aatii {n} dura</t>
         </is>
       </c>
       <c r="F197" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ሰዓት ተሓዲሱ</t>
+          <t>ቅድሚ {n} ሰዓት</t>
         </is>
       </c>
       <c r="G197" s="13" t="inlineStr">
         <is>
-          <t>La cusbooneysiiyay {n}saac ka hor</t>
+          <t>{n} saac ka hor</t>
         </is>
       </c>
       <c r="H197" s="14" t="inlineStr"/>
@@ -12931,7 +12931,7 @@
     <row r="198" ht="44" customHeight="1">
       <c r="A198" s="11" t="inlineStr">
         <is>
-          <t>queue</t>
+          <t>n_d_ago</t>
         </is>
       </c>
       <c r="B198" s="11" t="inlineStr">
@@ -12941,27 +12941,27 @@
       </c>
       <c r="C198" s="11" t="inlineStr">
         <is>
-          <t>Queue</t>
+          <t>{n} d ago</t>
         </is>
       </c>
       <c r="D198" s="12" t="inlineStr">
         <is>
-          <t>ወረፋ</t>
+          <t>ከ{n} ቀን በፊት</t>
         </is>
       </c>
       <c r="E198" s="13" t="inlineStr">
         <is>
-          <t>Sararaa</t>
+          <t>guyyaa {n} dura</t>
         </is>
       </c>
       <c r="F198" s="12" t="inlineStr">
         <is>
-          <t>ሪጋ</t>
+          <t>ቅድሚ {n} መዓልቲ</t>
         </is>
       </c>
       <c r="G198" s="13" t="inlineStr">
         <is>
-          <t>Safka</t>
+          <t>{n} maalmood ka hor</t>
         </is>
       </c>
       <c r="H198" s="14" t="inlineStr"/>
@@ -12969,7 +12969,7 @@
     <row r="199" ht="44" customHeight="1">
       <c r="A199" s="11" t="inlineStr">
         <is>
-          <t>collapse</t>
+          <t>channel_all_from</t>
         </is>
       </c>
       <c r="B199" s="11" t="inlineStr">
@@ -12979,27 +12979,27 @@
       </c>
       <c r="C199" s="11" t="inlineStr">
         <is>
-          <t>Collapse</t>
+          <t>All {n} conversations came from {label}.</t>
         </is>
       </c>
       <c r="D199" s="12" t="inlineStr">
         <is>
-          <t>አጥብብ</t>
+          <t>ሁሉም {n} ውይይቶች ከ{label} መጥተዋል።</t>
         </is>
       </c>
       <c r="E199" s="13" t="inlineStr">
         <is>
-          <t>Xiqqeessi</t>
+          <t>Mariin {n} hundi {label} irraa dhufe.</t>
         </is>
       </c>
       <c r="F199" s="12" t="inlineStr">
         <is>
-          <t>ኣጽብብ</t>
+          <t>ኩሎም {n} ዝርርባት ካብ {label} መጺኦም።</t>
         </is>
       </c>
       <c r="G199" s="13" t="inlineStr">
         <is>
-          <t>Yaree</t>
+          <t>Dhammaan {n} wadahadal waxay ka yimaadeen {label}.</t>
         </is>
       </c>
       <c r="H199" s="14" t="inlineStr"/>
@@ -13007,7 +13007,7 @@
     <row r="200" ht="44" customHeight="1">
       <c r="A200" s="11" t="inlineStr">
         <is>
-          <t>expand</t>
+          <t>channel_live</t>
         </is>
       </c>
       <c r="B200" s="11" t="inlineStr">
@@ -13017,27 +13017,27 @@
       </c>
       <c r="C200" s="11" t="inlineStr">
         <is>
-          <t>Expand</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="D200" s="12" t="inlineStr">
         <is>
-          <t>አስፋ</t>
+          <t>በሥራ ላይ</t>
         </is>
       </c>
       <c r="E200" s="13" t="inlineStr">
         <is>
-          <t>Balleessi</t>
+          <t>Hojiirra</t>
         </is>
       </c>
       <c r="F200" s="12" t="inlineStr">
         <is>
-          <t>ኣስፍሕ</t>
+          <t>ኣብ ስራሕ</t>
         </is>
       </c>
       <c r="G200" s="13" t="inlineStr">
         <is>
-          <t>Balaadhi</t>
+          <t>Shaqeynaya</t>
         </is>
       </c>
       <c r="H200" s="14" t="inlineStr"/>
@@ -13045,7 +13045,7 @@
     <row r="201" ht="44" customHeight="1">
       <c r="A201" s="11" t="inlineStr">
         <is>
-          <t>collapse_or_expand</t>
+          <t>channel_ready</t>
         </is>
       </c>
       <c r="B201" s="11" t="inlineStr">
@@ -13055,27 +13055,27 @@
       </c>
       <c r="C201" s="11" t="inlineStr">
         <is>
-          <t>Collapse or expand the sidebar</t>
+          <t>Ready to connect</t>
         </is>
       </c>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>የጎን አሞሌውን አጥብብ ወይም አስፋ</t>
+          <t>ለመገናኘት ዝግጁ</t>
         </is>
       </c>
       <c r="E201" s="13" t="inlineStr">
         <is>
-          <t>Cinaacha xiqqeessi ykn balleessi</t>
+          <t>Walqunnamuuf qophaa'aa</t>
         </is>
       </c>
       <c r="F201" s="12" t="inlineStr">
         <is>
-          <t>ናይ ጎኒ መስመር ኣጽብብ ወይ ኣስፍሕ</t>
+          <t>ንምርኻብ ድሉው</t>
         </is>
       </c>
       <c r="G201" s="13" t="inlineStr">
         <is>
-          <t>Yaree ama balaadhi dhinaca</t>
+          <t>Diyaar u ah xiriirka</t>
         </is>
       </c>
       <c r="H201" s="14" t="inlineStr"/>
@@ -13083,7 +13083,7 @@
     <row r="202" ht="44" customHeight="1">
       <c r="A202" s="11" t="inlineStr">
         <is>
-          <t>show_hide_channels</t>
+          <t>channel_needs_setup</t>
         </is>
       </c>
       <c r="B202" s="11" t="inlineStr">
@@ -13093,27 +13093,27 @@
       </c>
       <c r="C202" s="11" t="inlineStr">
         <is>
-          <t>Show or hide the channel list</t>
+          <t>Needs setup</t>
         </is>
       </c>
       <c r="D202" s="12" t="inlineStr">
         <is>
-          <t>የመስመሮችን ዝርዝር አሳይ ወይም ደብቅ</t>
+          <t>ማዋቀር ይፈልጋል</t>
         </is>
       </c>
       <c r="E202" s="13" t="inlineStr">
         <is>
-          <t>Tarreeffama karaalee agarsiisi ykn dhoksi</t>
+          <t>Qindeessuu barbaada</t>
         </is>
       </c>
       <c r="F202" s="12" t="inlineStr">
         <is>
-          <t>ዝርዝር መስመራት ኣርኢ ወይ ሕባእ</t>
+          <t>ምድላው የድልዮ</t>
         </is>
       </c>
       <c r="G202" s="13" t="inlineStr">
         <is>
-          <t>Muuji ama qari liiska kanaalada</t>
+          <t>Waxay u baahan tahay dejin</t>
         </is>
       </c>
       <c r="H202" s="14" t="inlineStr"/>
@@ -13121,7 +13121,7 @@
     <row r="203" ht="44" customHeight="1">
       <c r="A203" s="11" t="inlineStr">
         <is>
-          <t>today</t>
+          <t>share_by_channel</t>
         </is>
       </c>
       <c r="B203" s="11" t="inlineStr">
@@ -13131,27 +13131,27 @@
       </c>
       <c r="C203" s="11" t="inlineStr">
         <is>
-          <t>Today</t>
+          <t>Share of conversations by channel</t>
         </is>
       </c>
       <c r="D203" s="12" t="inlineStr">
         <is>
-          <t>ዛሬ</t>
+          <t>በመስመር የተከፋፈሉ ውይይቶች ድርሻ</t>
         </is>
       </c>
       <c r="E203" s="13" t="inlineStr">
         <is>
-          <t>Har'a</t>
+          <t>Qooda marii karaa tokkoon tokkoon isaanii</t>
         </is>
       </c>
       <c r="F203" s="12" t="inlineStr">
         <is>
-          <t>ሎሚ</t>
+          <t>ብመስመር ዝተኸፋፈለ ግደ ዝርርባት</t>
         </is>
       </c>
       <c r="G203" s="13" t="inlineStr">
         <is>
-          <t>Maanta</t>
+          <t>Qaybta wadahadallada kanaalka</t>
         </is>
       </c>
       <c r="H203" s="14" t="inlineStr"/>
@@ -13159,7 +13159,7 @@
     <row r="204" ht="44" customHeight="1">
       <c r="A204" s="11" t="inlineStr">
         <is>
-          <t>yesterday</t>
+          <t>up_to_date</t>
         </is>
       </c>
       <c r="B204" s="11" t="inlineStr">
@@ -13169,27 +13169,27 @@
       </c>
       <c r="C204" s="11" t="inlineStr">
         <is>
-          <t>Yesterday</t>
+          <t>Up to date</t>
         </is>
       </c>
       <c r="D204" s="12" t="inlineStr">
         <is>
-          <t>ትናንት</t>
+          <t>የተዘመነ</t>
         </is>
       </c>
       <c r="E204" s="13" t="inlineStr">
         <is>
-          <t>Kaleessa</t>
+          <t>Haaraa</t>
         </is>
       </c>
       <c r="F204" s="12" t="inlineStr">
         <is>
-          <t>ትማሊ</t>
+          <t>ዝተሓደሰ</t>
         </is>
       </c>
       <c r="G204" s="13" t="inlineStr">
         <is>
-          <t>Shalay</t>
+          <t>La cusbooneysiiyay</t>
         </is>
       </c>
       <c r="H204" s="14" t="inlineStr"/>
@@ -13197,7 +13197,7 @@
     <row r="205" ht="44" customHeight="1">
       <c r="A205" s="11" t="inlineStr">
         <is>
-          <t>call_started</t>
+          <t>updated_m_ago</t>
         </is>
       </c>
       <c r="B205" s="11" t="inlineStr">
@@ -13207,27 +13207,27 @@
       </c>
       <c r="C205" s="11" t="inlineStr">
         <is>
-          <t>The customer asked for a person here</t>
+          <t>Updated {n}m ago</t>
         </is>
       </c>
       <c r="D205" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛው እዚህ ላይ ሰው ጠየቀ</t>
+          <t>ከ{n} ደቂቃ በፊት ተዘምኗል</t>
         </is>
       </c>
       <c r="E205" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan asitti nama gaafate</t>
+          <t>Daqiiqaa {n} dura haaromfame</t>
         </is>
       </c>
       <c r="F205" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዓሚል ኣብዚ ሰብ ሓቲቱ</t>
+          <t>ቅድሚ {n} ደቒቕ ተሓዲሱ</t>
         </is>
       </c>
       <c r="G205" s="13" t="inlineStr">
         <is>
-          <t>Macmiilku halkan ayuu qof weydiistay</t>
+          <t>La cusbooneysiiyay {n}daq ka hor</t>
         </is>
       </c>
       <c r="H205" s="14" t="inlineStr"/>
@@ -13235,7 +13235,7 @@
     <row r="206" ht="44" customHeight="1">
       <c r="A206" s="11" t="inlineStr">
         <is>
-          <t>no_messages</t>
+          <t>updated_h_ago</t>
         </is>
       </c>
       <c r="B206" s="11" t="inlineStr">
@@ -13245,27 +13245,27 @@
       </c>
       <c r="C206" s="11" t="inlineStr">
         <is>
-          <t>No messages in this conversation.</t>
+          <t>Updated {n}h ago</t>
         </is>
       </c>
       <c r="D206" s="12" t="inlineStr">
         <is>
-          <t>በዚህ ውይይት ውስጥ መልእክት የለም።</t>
+          <t>ከ{n} ሰዓት በፊት ተዘምኗል</t>
         </is>
       </c>
       <c r="E206" s="13" t="inlineStr">
         <is>
-          <t>Marii kana keessa ergaan hin jiru.</t>
+          <t>Sa'aatii {n} dura haaromfame</t>
         </is>
       </c>
       <c r="F206" s="12" t="inlineStr">
         <is>
-          <t>ኣብዚ ዝርርብ መልእኽቲ የለን።</t>
+          <t>ቅድሚ {n} ሰዓት ተሓዲሱ</t>
         </is>
       </c>
       <c r="G206" s="13" t="inlineStr">
         <is>
-          <t>Wadahadalkan fariin kuma jirto.</t>
+          <t>La cusbooneysiiyay {n}saac ka hor</t>
         </is>
       </c>
       <c r="H206" s="14" t="inlineStr"/>
@@ -13273,7 +13273,7 @@
     <row r="207" ht="44" customHeight="1">
       <c r="A207" s="11" t="inlineStr">
         <is>
-          <t>donut_all_in_one</t>
+          <t>queue</t>
         </is>
       </c>
       <c r="B207" s="11" t="inlineStr">
@@ -13283,27 +13283,27 @@
       </c>
       <c r="C207" s="11" t="inlineStr">
         <is>
-          <t>The single {unit} was in {label}.</t>
+          <t>Queue</t>
         </is>
       </c>
       <c r="D207" s="12" t="inlineStr">
         <is>
-          <t>ብቸኛው {unit} በ{label} ነበር።</t>
+          <t>ወረፋ</t>
         </is>
       </c>
       <c r="E207" s="13" t="inlineStr">
         <is>
-          <t>{unit} tokkichi {label} keessa ture.</t>
+          <t>Sararaa</t>
         </is>
       </c>
       <c r="F207" s="12" t="inlineStr">
         <is>
-          <t>እቲ ሓደ {unit} ብ{label} ነይሩ።</t>
+          <t>ሪጋ</t>
         </is>
       </c>
       <c r="G207" s="13" t="inlineStr">
         <is>
-          <t>{unit} kaliya wuxuu ku jiray {label}.</t>
+          <t>Safka</t>
         </is>
       </c>
       <c r="H207" s="14" t="inlineStr"/>
@@ -13311,7 +13311,7 @@
     <row r="208" ht="44" customHeight="1">
       <c r="A208" s="11" t="inlineStr">
         <is>
-          <t>channel_all_from_one</t>
+          <t>collapse</t>
         </is>
       </c>
       <c r="B208" s="11" t="inlineStr">
@@ -13321,27 +13321,27 @@
       </c>
       <c r="C208" s="11" t="inlineStr">
         <is>
-          <t>The single conversation came from {label}.</t>
+          <t>Collapse</t>
         </is>
       </c>
       <c r="D208" s="12" t="inlineStr">
         <is>
-          <t>ብቸኛው ውይይት ከ{label} መጥቷል።</t>
+          <t>አጥብብ</t>
         </is>
       </c>
       <c r="E208" s="13" t="inlineStr">
         <is>
-          <t>Mariin tokkichi {label} irraa dhufe.</t>
+          <t>Xiqqeessi</t>
         </is>
       </c>
       <c r="F208" s="12" t="inlineStr">
         <is>
-          <t>እቲ ሓደ ዝርርብ ካብ {label} መጺኡ።</t>
+          <t>ኣጽብብ</t>
         </is>
       </c>
       <c r="G208" s="13" t="inlineStr">
         <is>
-          <t>Wadahadalka kaliya wuxuu ka yimid {label}.</t>
+          <t>Yaree</t>
         </is>
       </c>
       <c r="H208" s="14" t="inlineStr"/>
@@ -13349,7 +13349,7 @@
     <row r="209" ht="44" customHeight="1">
       <c r="A209" s="11" t="inlineStr">
         <is>
-          <t>unit_conversation</t>
+          <t>expand</t>
         </is>
       </c>
       <c r="B209" s="11" t="inlineStr">
@@ -13359,27 +13359,27 @@
       </c>
       <c r="C209" s="11" t="inlineStr">
         <is>
-          <t>conversation</t>
+          <t>Expand</t>
         </is>
       </c>
       <c r="D209" s="12" t="inlineStr">
         <is>
-          <t>ውይይት</t>
+          <t>አስፋ</t>
         </is>
       </c>
       <c r="E209" s="13" t="inlineStr">
         <is>
-          <t>marii</t>
+          <t>Balleessi</t>
         </is>
       </c>
       <c r="F209" s="12" t="inlineStr">
         <is>
-          <t>ዝርርብ</t>
+          <t>ኣስፍሕ</t>
         </is>
       </c>
       <c r="G209" s="13" t="inlineStr">
         <is>
-          <t>wadahadal</t>
+          <t>Balaadhi</t>
         </is>
       </c>
       <c r="H209" s="14" t="inlineStr"/>
@@ -13387,7 +13387,7 @@
     <row r="210" ht="44" customHeight="1">
       <c r="A210" s="11" t="inlineStr">
         <is>
-          <t>live_sessions</t>
+          <t>collapse_or_expand</t>
         </is>
       </c>
       <c r="B210" s="11" t="inlineStr">
@@ -13397,27 +13397,27 @@
       </c>
       <c r="C210" s="11" t="inlineStr">
         <is>
-          <t>Live sessions</t>
+          <t>Collapse or expand the sidebar</t>
         </is>
       </c>
       <c r="D210" s="12" t="inlineStr">
         <is>
-          <t>የቀጥታ ክፍለ-ጊዜዎች</t>
+          <t>የጎን አሞሌውን አጥብብ ወይም አስፋ</t>
         </is>
       </c>
       <c r="E210" s="13" t="inlineStr">
         <is>
-          <t>Marii kallattii</t>
+          <t>Cinaacha xiqqeessi ykn balleessi</t>
         </is>
       </c>
       <c r="F210" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታ ክፍለ-ግዜታት</t>
+          <t>ናይ ጎኒ መስመር ኣጽብብ ወይ ኣስፍሕ</t>
         </is>
       </c>
       <c r="G210" s="13" t="inlineStr">
         <is>
-          <t>Kalfadhiyada tooska ah</t>
+          <t>Yaree ama balaadhi dhinaca</t>
         </is>
       </c>
       <c r="H210" s="14" t="inlineStr"/>
@@ -13425,7 +13425,7 @@
     <row r="211" ht="44" customHeight="1">
       <c r="A211" s="11" t="inlineStr">
         <is>
-          <t>switched_off_for_bank</t>
+          <t>show_hide_channels</t>
         </is>
       </c>
       <c r="B211" s="11" t="inlineStr">
@@ -13435,27 +13435,27 @@
       </c>
       <c r="C211" s="11" t="inlineStr">
         <is>
-          <t>Switched off for this bank</t>
+          <t>Show or hide the channel list</t>
         </is>
       </c>
       <c r="D211" s="12" t="inlineStr">
         <is>
-          <t>ለዚህ ባንክ ጠፍቷል</t>
+          <t>የመስመሮችን ዝርዝር አሳይ ወይም ደብቅ</t>
         </is>
       </c>
       <c r="E211" s="13" t="inlineStr">
         <is>
-          <t>Baankii kanaaf dhaamsameera</t>
+          <t>Tarreeffama karaalee agarsiisi ykn dhoksi</t>
         </is>
       </c>
       <c r="F211" s="12" t="inlineStr">
         <is>
-          <t>ነዚ ባንኪ ጠፊኡ</t>
+          <t>ዝርዝር መስመራት ኣርኢ ወይ ሕባእ</t>
         </is>
       </c>
       <c r="G211" s="13" t="inlineStr">
         <is>
-          <t>Bangigan waa la damiyay</t>
+          <t>Muuji ama qari liiska kanaalada</t>
         </is>
       </c>
       <c r="H211" s="14" t="inlineStr"/>
@@ -13463,7 +13463,7 @@
     <row r="212" ht="44" customHeight="1">
       <c r="A212" s="11" t="inlineStr">
         <is>
-          <t>switched_on_nobody_on_duty</t>
+          <t>today</t>
         </is>
       </c>
       <c r="B212" s="11" t="inlineStr">
@@ -13473,27 +13473,27 @@
       </c>
       <c r="C212" s="11" t="inlineStr">
         <is>
-          <t>Switched on — but nobody is on duty</t>
+          <t>Today</t>
         </is>
       </c>
       <c r="D212" s="12" t="inlineStr">
         <is>
-          <t>በርቷል — ግን ማንም በሥራ ላይ የለም</t>
+          <t>ዛሬ</t>
         </is>
       </c>
       <c r="E212" s="13" t="inlineStr">
         <is>
-          <t>Banameera — garuu namni hojii irra hin jiru</t>
+          <t>Har'a</t>
         </is>
       </c>
       <c r="F212" s="12" t="inlineStr">
         <is>
-          <t>በሪሁ — ግና ዋላ ሓደ ኣብ ስራሕ የለን</t>
+          <t>ሎሚ</t>
         </is>
       </c>
       <c r="G212" s="13" t="inlineStr">
         <is>
-          <t>Waa la shiday — laakiin qofna shaqada ma joogo</t>
+          <t>Maanta</t>
         </is>
       </c>
       <c r="H212" s="14" t="inlineStr"/>
@@ -13501,7 +13501,7 @@
     <row r="213" ht="44" customHeight="1">
       <c r="A213" s="11" t="inlineStr">
         <is>
-          <t>no_teller_button</t>
+          <t>yesterday</t>
         </is>
       </c>
       <c r="B213" s="11" t="inlineStr">
@@ -13511,27 +13511,27 @@
       </c>
       <c r="C213" s="11" t="inlineStr">
         <is>
-          <t>No “Speak to a teller” button appears in your widget.</t>
+          <t>Yesterday</t>
         </is>
       </c>
       <c r="D213" s="12" t="inlineStr">
         <is>
-          <t>በመግብርዎ ውስጥ “ከገንዘብ ተቀባይ ጋር ይነጋገሩ” የሚል አዝራር አይታይም።</t>
+          <t>ትናንት</t>
         </is>
       </c>
       <c r="E213" s="13" t="inlineStr">
         <is>
-          <t>Widjetii keessan keessatti qabduun “Namaa waliin haasa'aa” hin mul'atu.</t>
+          <t>Kaleessa</t>
         </is>
       </c>
       <c r="F213" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መግበሪኹም “ምስ ተቐባሊ ገንዘብ ተዛረቡ” ዝብል መጠወቒ ኣይረአን።</t>
+          <t>ትማሊ</t>
         </is>
       </c>
       <c r="G213" s="13" t="inlineStr">
         <is>
-          <t>Badhanka “La hadal shaqaale” kama muuqan widget-kaaga.</t>
+          <t>Shalay</t>
         </is>
       </c>
       <c r="H213" s="14" t="inlineStr"/>
@@ -13539,7 +13539,7 @@
     <row r="214" ht="44" customHeight="1">
       <c r="A214" s="11" t="inlineStr">
         <is>
-          <t>on_duty_explainer</t>
+          <t>call_started</t>
         </is>
       </c>
       <c r="B214" s="11" t="inlineStr">
@@ -13549,27 +13549,27 @@
       </c>
       <c r="C214" s="11" t="inlineStr">
         <is>
-          <t>You are on duty, so waiting customers can be routed to you. Go off duty from the sidebar when you step away — you stay on the air anywhere in the console until you do.</t>
+          <t>The customer asked for a person here</t>
         </is>
       </c>
       <c r="D214" s="12" t="inlineStr">
         <is>
-          <t>በሥራ ላይ ነዎት፤ ስለዚህ የሚጠብቁ ደንበኞች ወደ እርስዎ ሊመሩ ይችላሉ። ሲርቁ ከጎን አሞሌው ከሥራ ውጡ — እስከዚያ ድረስ በየትኛውም ገጽ ላይ በሥራ ላይ ይቆያሉ።</t>
+          <t>ደንበኛው እዚህ ላይ ሰው ጠየቀ</t>
         </is>
       </c>
       <c r="E214" s="13" t="inlineStr">
         <is>
-          <t>Hojii irra jirtu, kanaafuu maamiltoonni eegaa jiran gara keessan qajeelfamuu danda'u. Yeroo achii deemtan cinaacha irraa hojii keessaa ba'aa — hanga sanatti fuula kamiyyuu irratti hojii irra turtu.</t>
+          <t>Maamilaan asitti nama gaafate</t>
         </is>
       </c>
       <c r="F214" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ስራሕ ኢኹም፣ ስለዚ ዝጽበዩ ዓማዊል ናባኹም ክምርሑ ይኽእሉ። ክትርሕቁ ከለኹም ካብ ናይ ጎኒ መስመር ካብ ስራሕ ውጹ — ክሳብ ሽዑ ኣብ ዝኾነ ገጽ ኣብ ስራሕ ትጸንሑ።</t>
+          <t>እቲ ዓሚል ኣብዚ ሰብ ሓቲቱ</t>
         </is>
       </c>
       <c r="G214" s="13" t="inlineStr">
         <is>
-          <t>Shaqada ayaad joogtaa, sidaas darteed macaamiisha sugaya waa lagu soo dhiibi karaa. Marka aad tagto shaqada ka bax dhinaca — ilaa markaas bog kasta ayaad ku sii shaqeynaysaa.</t>
+          <t>Macmiilku halkan ayuu qof weydiistay</t>
         </is>
       </c>
       <c r="H214" s="14" t="inlineStr"/>
@@ -13577,7 +13577,7 @@
     <row r="215" ht="44" customHeight="1">
       <c r="A215" s="11" t="inlineStr">
         <is>
-          <t>off_duty_explainer</t>
+          <t>no_messages</t>
         </is>
       </c>
       <c r="B215" s="11" t="inlineStr">
@@ -13587,27 +13587,27 @@
       </c>
       <c r="C215" s="11" t="inlineStr">
         <is>
-          <t>Switch On duty in the sidebar to start taking calls. It follows you across every page, so you no longer have to keep this one open.</t>
+          <t>No messages in this conversation.</t>
         </is>
       </c>
       <c r="D215" s="12" t="inlineStr">
         <is>
-          <t>ጥሪዎችን መቀበል ለመጀመር ከጎን አሞሌው “በሥራ ላይ” ያብሩ። በሁሉም ገጽ ላይ ይከተልዎታል፤ ስለዚህ ይህን ገጽ ክፍት ማድረግ አያስፈልግም።</t>
+          <t>በዚህ ውይይት ውስጥ መልእክት የለም።</t>
         </is>
       </c>
       <c r="E215" s="13" t="inlineStr">
         <is>
-          <t>Bilbila fudhachuu jalqabuuf cinaacha irraa “Hojii irra” banaa. Fuula hunda irratti isin hordofa, kanaafuu fuula kana banaa gochuun hin barbaachisu.</t>
+          <t>Marii kana keessa ergaan hin jiru.</t>
         </is>
       </c>
       <c r="F215" s="12" t="inlineStr">
         <is>
-          <t>ጻውዒታት ክትቅበሉ ንምጅማር ካብ ናይ ጎኒ መስመር “ኣብ ስራሕ” ኣብርሁ። ኣብ ኩሉ ገጽ ይስዕበኩም፣ ስለዚ ነዚ ገጽ ክፉት ምግባር ኣየድልን።</t>
+          <t>ኣብዚ ዝርርብ መልእኽቲ የለን።</t>
         </is>
       </c>
       <c r="G215" s="13" t="inlineStr">
         <is>
-          <t>Si aad u bilowdo qaadista wicitaannada, dhinaca ka shid “Shaqada”. Bog kasta ayuu kula socdaa, sidaas darteed uma baahnid inaad tan furan ka tagto.</t>
+          <t>Wadahadalkan fariin kuma jirto.</t>
         </is>
       </c>
       <c r="H215" s="14" t="inlineStr"/>
@@ -13615,7 +13615,7 @@
     <row r="216" ht="44" customHeight="1">
       <c r="A216" s="11" t="inlineStr">
         <is>
-          <t>colleague_must_be_on_duty</t>
+          <t>donut_all_in_one</t>
         </is>
       </c>
       <c r="B216" s="11" t="inlineStr">
@@ -13625,27 +13625,27 @@
       </c>
       <c r="C216" s="11" t="inlineStr">
         <is>
-          <t>A colleague with permission to take calls has to be on duty before customers are offered one.</t>
+          <t>The single {unit} was in {label}.</t>
         </is>
       </c>
       <c r="D216" s="12" t="inlineStr">
         <is>
-          <t>ጥሪ የመቀበል ፈቃድ ያለው ባልደረባ በሥራ ላይ መሆን አለበት፤ ከዚያ በፊት ለደንበኞች አይቀርብም።</t>
+          <t>ብቸኛው {unit} በ{label} ነበር።</t>
         </is>
       </c>
       <c r="E216" s="13" t="inlineStr">
         <is>
-          <t>Hojjetaan hayyama bilbila fudhachuu qabu hojii irra jiraachuu qaba, sana dura maamiltootaaf hin dhiyaatu.</t>
+          <t>{unit} tokkichi {label} keessa ture.</t>
         </is>
       </c>
       <c r="F216" s="12" t="inlineStr">
         <is>
-          <t>ጻውዒት ናይ ምቕባል ፍቓድ ዘለዎ መሳርሕቲ ኣብ ስራሕ ክህሉ ኣለዎ፣ ቅድሚኡ ንዓማዊል ኣይቀርብን።</t>
+          <t>እቲ ሓደ {unit} ብ{label} ነይሩ።</t>
         </is>
       </c>
       <c r="G216" s="13" t="inlineStr">
         <is>
-          <t>Shaqaale haysta ogolaanshaha qaadista wicitaannada waa inuu shaqada joogaa ka hor inta aan macaamiisha la siin.</t>
+          <t>{unit} kaliya wuxuu ku jiray {label}.</t>
         </is>
       </c>
       <c r="H216" s="14" t="inlineStr"/>
@@ -13653,7 +13653,7 @@
     <row r="217" ht="44" customHeight="1">
       <c r="A217" s="11" t="inlineStr">
         <is>
-          <t>i_can_converse_in</t>
+          <t>channel_all_from_one</t>
         </is>
       </c>
       <c r="B217" s="11" t="inlineStr">
@@ -13663,27 +13663,27 @@
       </c>
       <c r="C217" s="11" t="inlineStr">
         <is>
-          <t>I can hold a conversation in:</t>
+          <t>The single conversation came from {label}.</t>
         </is>
       </c>
       <c r="D217" s="12" t="inlineStr">
         <is>
-          <t>በእነዚህ ቋንቋዎች መነጋገር እችላለሁ፦</t>
+          <t>ብቸኛው ውይይት ከ{label} መጥቷል።</t>
         </is>
       </c>
       <c r="E217" s="13" t="inlineStr">
         <is>
-          <t>Afaanota kanneeniin haasa'uu nan danda'a:</t>
+          <t>Mariin tokkichi {label} irraa dhufe.</t>
         </is>
       </c>
       <c r="F217" s="12" t="inlineStr">
         <is>
-          <t>በዞም ቋንቋታት ክዛረብ እኽእል፦</t>
+          <t>እቲ ሓደ ዝርርብ ካብ {label} መጺኡ።</t>
         </is>
       </c>
       <c r="G217" s="13" t="inlineStr">
         <is>
-          <t>Waxaan ku hadli karaa:</t>
+          <t>Wadahadalka kaliya wuxuu ka yimid {label}.</t>
         </is>
       </c>
       <c r="H217" s="14" t="inlineStr"/>
@@ -13691,7 +13691,7 @@
     <row r="218" ht="44" customHeight="1">
       <c r="A218" s="11" t="inlineStr">
         <is>
-          <t>languages_picked_note</t>
+          <t>unit_conversation</t>
         </is>
       </c>
       <c r="B218" s="11" t="inlineStr">
@@ -13701,27 +13701,27 @@
       </c>
       <c r="C218" s="11" t="inlineStr">
         <is>
-          <t>Customers writing in these reach you first. Everyone else still reaches you — after a short wait, so nobody is stranded.</t>
+          <t>conversation</t>
         </is>
       </c>
       <c r="D218" s="12" t="inlineStr">
         <is>
-          <t>በእነዚህ ቋንቋዎች የሚጽፉ ደንበኞች መጀመሪያ ወደ እርስዎ ይደርሳሉ። ሌሎችም ይደርሳሉ — ከአጭር ጥበቃ በኋላ፤ ማንም አይቀርም።</t>
+          <t>ውይይት</t>
         </is>
       </c>
       <c r="E218" s="13" t="inlineStr">
         <is>
-          <t>Maamiltoonni afaanota kanaan barreessan jalqaba isin bira ga'u. Kaan hundinuu ammas isin bira ga'u — eegumsa gabaabaa booda, namni hafu hin jiru.</t>
+          <t>marii</t>
         </is>
       </c>
       <c r="F218" s="12" t="inlineStr">
         <is>
-          <t>በዞም ቋንቋታት ዝጽሕፉ ዓማዊል ቅድም ናባኹም ይበጽሑ። እቶም ካልኦት እውን ይበጽሑ — ድሕሪ ሓጺር ጽበት፣ ዋላ ሓደ ኣይተርፍን።</t>
+          <t>ዝርርብ</t>
         </is>
       </c>
       <c r="G218" s="13" t="inlineStr">
         <is>
-          <t>Macaamiisha ku qora kuwan ayaa marka hore kugu soo gaara. Qof kastana wuu ku soo gaari doonaa — sug gaaban ka dib, sidaas qofna ma harayo.</t>
+          <t>wadahadal</t>
         </is>
       </c>
       <c r="H218" s="14" t="inlineStr"/>
@@ -13729,7 +13729,7 @@
     <row r="219" ht="44" customHeight="1">
       <c r="A219" s="11" t="inlineStr">
         <is>
-          <t>languages_none_note</t>
+          <t>live_sessions</t>
         </is>
       </c>
       <c r="B219" s="11" t="inlineStr">
@@ -13739,27 +13739,27 @@
       </c>
       <c r="C219" s="11" t="inlineStr">
         <is>
-          <t>Nothing selected, so every waiting customer is offered to you in plain oldest-first order.</t>
+          <t>Live sessions</t>
         </is>
       </c>
       <c r="D219" s="12" t="inlineStr">
         <is>
-          <t>ምንም አልተመረጠም፤ ስለዚህ እያንዳንዱ የሚጠብቅ ደንበኛ በቀላል ቀዳሚ-መጀመሪያ ቅደም ተከተል ይቀርብልዎታል።</t>
+          <t>የቀጥታ ክፍለ-ጊዜዎች</t>
         </is>
       </c>
       <c r="E219" s="13" t="inlineStr">
         <is>
-          <t>Wanti filatame hin jiru, kanaafuu maamilli eegaa jiru hundi tartiiba dursaa-jalqabaatiin isinii dhiyaata.</t>
+          <t>Marii kallattii</t>
         </is>
       </c>
       <c r="F219" s="12" t="inlineStr">
         <is>
-          <t>ዋላ ሓደ ኣይተመርጸን፣ ስለዚ ነፍስ ወከፍ ዝጽበ ዓሚል ብቐሊል ናይ ቀዳምነት ስርዓት ይቐርበልኩም።</t>
+          <t>ቀጥታ ክፍለ-ግዜታት</t>
         </is>
       </c>
       <c r="G219" s="13" t="inlineStr">
         <is>
-          <t>Waxba lama dooran, sidaas darteed macmiil kasta oo sugaya waxaa laguu soo bandhigayaa sida caadiga ah ee ugu horreeya.</t>
+          <t>Kalfadhiyada tooska ah</t>
         </is>
       </c>
       <c r="H219" s="14" t="inlineStr"/>
@@ -13767,7 +13767,7 @@
     <row r="220" ht="44" customHeight="1">
       <c r="A220" s="11" t="inlineStr">
         <is>
-          <t>languages_updated</t>
+          <t>switched_off_for_bank</t>
         </is>
       </c>
       <c r="B220" s="11" t="inlineStr">
@@ -13777,27 +13777,27 @@
       </c>
       <c r="C220" s="11" t="inlineStr">
         <is>
-          <t>Languages updated</t>
+          <t>Switched off for this bank</t>
         </is>
       </c>
       <c r="D220" s="12" t="inlineStr">
         <is>
-          <t>ቋንቋዎች ተዘምነዋል</t>
+          <t>ለዚህ ባንክ ጠፍቷል</t>
         </is>
       </c>
       <c r="E220" s="13" t="inlineStr">
         <is>
-          <t>Afaanonni haaromfaman</t>
+          <t>Baankii kanaaf dhaamsameera</t>
         </is>
       </c>
       <c r="F220" s="12" t="inlineStr">
         <is>
-          <t>ቋንቋታት ተሓዲሶም</t>
+          <t>ነዚ ባንኪ ጠፊኡ</t>
         </is>
       </c>
       <c r="G220" s="13" t="inlineStr">
         <is>
-          <t>Luqadaha waa la cusbooneysiiyay</t>
+          <t>Bangigan waa la damiyay</t>
         </is>
       </c>
       <c r="H220" s="14" t="inlineStr"/>
@@ -13805,7 +13805,7 @@
     <row r="221" ht="44" customHeight="1">
       <c r="A221" s="11" t="inlineStr">
         <is>
-          <t>media_video</t>
+          <t>switched_on_nobody_on_duty</t>
         </is>
       </c>
       <c r="B221" s="11" t="inlineStr">
@@ -13815,27 +13815,27 @@
       </c>
       <c r="C221" s="11" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Switched on — but nobody is on duty</t>
         </is>
       </c>
       <c r="D221" s="12" t="inlineStr">
         <is>
-          <t>ቪዲዮ</t>
+          <t>በርቷል — ግን ማንም በሥራ ላይ የለም</t>
         </is>
       </c>
       <c r="E221" s="13" t="inlineStr">
         <is>
-          <t>Viidiyoo</t>
+          <t>Banameera — garuu namni hojii irra hin jiru</t>
         </is>
       </c>
       <c r="F221" s="12" t="inlineStr">
         <is>
-          <t>ቪድዮ</t>
+          <t>በሪሁ — ግና ዋላ ሓደ ኣብ ስራሕ የለን</t>
         </is>
       </c>
       <c r="G221" s="13" t="inlineStr">
         <is>
-          <t>Fiidyow</t>
+          <t>Waa la shiday — laakiin qofna shaqada ma joogo</t>
         </is>
       </c>
       <c r="H221" s="14" t="inlineStr"/>
@@ -13843,7 +13843,7 @@
     <row r="222" ht="44" customHeight="1">
       <c r="A222" s="11" t="inlineStr">
         <is>
-          <t>media_audio</t>
+          <t>no_teller_button</t>
         </is>
       </c>
       <c r="B222" s="11" t="inlineStr">
@@ -13853,27 +13853,27 @@
       </c>
       <c r="C222" s="11" t="inlineStr">
         <is>
-          <t>Audio</t>
+          <t>No “Speak to a teller” button appears in your widget.</t>
         </is>
       </c>
       <c r="D222" s="12" t="inlineStr">
         <is>
-          <t>ድምፅ</t>
+          <t>በመግብርዎ ውስጥ “ከገንዘብ ተቀባይ ጋር ይነጋገሩ” የሚል አዝራር አይታይም።</t>
         </is>
       </c>
       <c r="E222" s="13" t="inlineStr">
         <is>
-          <t>Sagalee</t>
+          <t>Widjetii keessan keessatti qabduun “Namaa waliin haasa'aa” hin mul'atu.</t>
         </is>
       </c>
       <c r="F222" s="12" t="inlineStr">
         <is>
-          <t>ድምጺ</t>
+          <t>ኣብ መግበሪኹም “ምስ ተቐባሊ ገንዘብ ተዛረቡ” ዝብል መጠወቒ ኣይረአን።</t>
         </is>
       </c>
       <c r="G222" s="13" t="inlineStr">
         <is>
-          <t>Cod</t>
+          <t>Badhanka “La hadal shaqaale” kama muuqan widget-kaaga.</t>
         </is>
       </c>
       <c r="H222" s="14" t="inlineStr"/>
@@ -13881,7 +13881,7 @@
     <row r="223" ht="44" customHeight="1">
       <c r="A223" s="11" t="inlineStr">
         <is>
-          <t>not_your_language</t>
+          <t>on_duty_explainer</t>
         </is>
       </c>
       <c r="B223" s="11" t="inlineStr">
@@ -13891,27 +13891,27 @@
       </c>
       <c r="C223" s="11" t="inlineStr">
         <is>
-          <t>not your language</t>
+          <t>You are on duty, so waiting customers can be routed to you. Go off duty from the sidebar when you step away — you stay on the air anywhere in the console until you do.</t>
         </is>
       </c>
       <c r="D223" s="12" t="inlineStr">
         <is>
-          <t>የእርስዎ ቋንቋ አይደለም</t>
+          <t>በሥራ ላይ ነዎት፤ ስለዚህ የሚጠብቁ ደንበኞች ወደ እርስዎ ሊመሩ ይችላሉ። ሲርቁ ከጎን አሞሌው ከሥራ ውጡ — እስከዚያ ድረስ በየትኛውም ገጽ ላይ በሥራ ላይ ይቆያሉ።</t>
         </is>
       </c>
       <c r="E223" s="13" t="inlineStr">
         <is>
-          <t>afaan keessanii miti</t>
+          <t>Hojii irra jirtu, kanaafuu maamiltoonni eegaa jiran gara keessan qajeelfamuu danda'u. Yeroo achii deemtan cinaacha irraa hojii keessaa ba'aa — hanga sanatti fuula kamiyyuu irratti hojii irra turtu.</t>
         </is>
       </c>
       <c r="F223" s="12" t="inlineStr">
         <is>
-          <t>ናትኩም ቋንቋ ኣይኮነን</t>
+          <t>ኣብ ስራሕ ኢኹም፣ ስለዚ ዝጽበዩ ዓማዊል ናባኹም ክምርሑ ይኽእሉ። ክትርሕቁ ከለኹም ካብ ናይ ጎኒ መስመር ካብ ስራሕ ውጹ — ክሳብ ሽዑ ኣብ ዝኾነ ገጽ ኣብ ስራሕ ትጸንሑ።</t>
         </is>
       </c>
       <c r="G223" s="13" t="inlineStr">
         <is>
-          <t>ma aha luqaddaada</t>
+          <t>Shaqada ayaad joogtaa, sidaas darteed macaamiisha sugaya waa lagu soo dhiibi karaa. Marka aad tagto shaqada ka bax dhinaca — ilaa markaas bog kasta ayaad ku sii shaqeynaysaa.</t>
         </is>
       </c>
       <c r="H223" s="14" t="inlineStr"/>
@@ -13919,7 +13919,7 @@
     <row r="224" ht="44" customHeight="1">
       <c r="A224" s="11" t="inlineStr">
         <is>
-          <t>languages_first_note</t>
+          <t>off_duty_explainer</t>
         </is>
       </c>
       <c r="B224" s="11" t="inlineStr">
@@ -13929,27 +13929,27 @@
       </c>
       <c r="C224" s="11" t="inlineStr">
         <is>
-          <t>Your languages first, longest wait within each. Anyone waiting too long moves to the top whatever they speak.</t>
+          <t>Switch On duty in the sidebar to start taking calls. It follows you across every page, so you no longer have to keep this one open.</t>
         </is>
       </c>
       <c r="D224" s="12" t="inlineStr">
         <is>
-          <t>የእርስዎ ቋንቋዎች መጀመሪያ፤ በእያንዳንዱ ውስጥ ረጅም የጠበቀው ይቀድማል። ከልክ በላይ የጠበቀ ማንኛውም ሰው የሚናገረው ምንም ይሁን ወደ ላይ ይወጣል።</t>
+          <t>ጥሪዎችን መቀበል ለመጀመር ከጎን አሞሌው “በሥራ ላይ” ያብሩ። በሁሉም ገጽ ላይ ይከተልዎታል፤ ስለዚህ ይህን ገጽ ክፍት ማድረግ አያስፈልግም።</t>
         </is>
       </c>
       <c r="E224" s="13" t="inlineStr">
         <is>
-          <t>Afaanonni keessan jalqaba, tokkoon tokkoon isaanii keessatti kan yeroo dheeraa eege dursa. Namni baay'ee eege afaan kamiyyuu haa dubbatu gara oliitti deema.</t>
+          <t>Bilbila fudhachuu jalqabuuf cinaacha irraa “Hojii irra” banaa. Fuula hunda irratti isin hordofa, kanaafuu fuula kana banaa gochuun hin barbaachisu.</t>
         </is>
       </c>
       <c r="F224" s="12" t="inlineStr">
         <is>
-          <t>ቋንቋታትኩም ቅድም፣ ኣብ ነፍስ ወከፍ እቲ ነዊሕ ዝጸንሐ ይቐድም። ካብ ንቡር ንላዕሊ ዝጸንሐ ዝኾነ ሰብ ዝዛረቦ ብዘየገድስ ናብ ላዕሊ ይመጽእ።</t>
+          <t>ጻውዒታት ክትቅበሉ ንምጅማር ካብ ናይ ጎኒ መስመር “ኣብ ስራሕ” ኣብርሁ። ኣብ ኩሉ ገጽ ይስዕበኩም፣ ስለዚ ነዚ ገጽ ክፉት ምግባር ኣየድልን።</t>
         </is>
       </c>
       <c r="G224" s="13" t="inlineStr">
         <is>
-          <t>Luqadahaaga marka hore, kii ugu sugay dheeraa mid kasta gudahood. Qof kasta oo aad u sugay ayaa kor u kaca luqad kastoo uu ku hadloba.</t>
+          <t>Si aad u bilowdo qaadista wicitaannada, dhinaca ka shid “Shaqada”. Bog kasta ayuu kula socdaa, sidaas darteed uma baahnid inaad tan furan ka tagto.</t>
         </is>
       </c>
       <c r="H224" s="14" t="inlineStr"/>
@@ -13957,7 +13957,7 @@
     <row r="225" ht="44" customHeight="1">
       <c r="A225" s="11" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>colleague_must_be_on_duty</t>
         </is>
       </c>
       <c r="B225" s="11" t="inlineStr">
@@ -13967,27 +13967,27 @@
       </c>
       <c r="C225" s="11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>A colleague with permission to take calls has to be on duty before customers are offered one.</t>
         </is>
       </c>
       <c r="D225" s="12" t="inlineStr">
         <is>
-          <t>በሂደት ላይ</t>
+          <t>ጥሪ የመቀበል ፈቃድ ያለው ባልደረባ በሥራ ላይ መሆን አለበት፤ ከዚያ በፊት ለደንበኞች አይቀርብም።</t>
         </is>
       </c>
       <c r="E225" s="13" t="inlineStr">
         <is>
-          <t>Adeemsa irra</t>
+          <t>Hojjetaan hayyama bilbila fudhachuu qabu hojii irra jiraachuu qaba, sana dura maamiltootaaf hin dhiyaatu.</t>
         </is>
       </c>
       <c r="F225" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መስርሕ</t>
+          <t>ጻውዒት ናይ ምቕባል ፍቓድ ዘለዎ መሳርሕቲ ኣብ ስራሕ ክህሉ ኣለዎ፣ ቅድሚኡ ንዓማዊል ኣይቀርብን።</t>
         </is>
       </c>
       <c r="G225" s="13" t="inlineStr">
         <is>
-          <t>Socda</t>
+          <t>Shaqaale haysta ogolaanshaha qaadista wicitaannada waa inuu shaqada joogaa ka hor inta aan macaamiisha la siin.</t>
         </is>
       </c>
       <c r="H225" s="14" t="inlineStr"/>
@@ -13995,7 +13995,7 @@
     <row r="226" ht="44" customHeight="1">
       <c r="A226" s="11" t="inlineStr">
         <is>
-          <t>no_session_in_progress</t>
+          <t>i_can_converse_in</t>
         </is>
       </c>
       <c r="B226" s="11" t="inlineStr">
@@ -14005,27 +14005,27 @@
       </c>
       <c r="C226" s="11" t="inlineStr">
         <is>
-          <t>No session in progress.</t>
+          <t>I can hold a conversation in:</t>
         </is>
       </c>
       <c r="D226" s="12" t="inlineStr">
         <is>
-          <t>በሂደት ላይ ያለ ክፍለ-ጊዜ የለም።</t>
+          <t>በእነዚህ ቋንቋዎች መነጋገር እችላለሁ፦</t>
         </is>
       </c>
       <c r="E226" s="13" t="inlineStr">
         <is>
-          <t>Sessionii adeemsa irra jiru hin jiru.</t>
+          <t>Afaanota kanneeniin haasa'uu nan danda'a:</t>
         </is>
       </c>
       <c r="F226" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መስርሕ ዘሎ ክፍለ-ግዜ የለን።</t>
+          <t>በዞም ቋንቋታት ክዛረብ እኽእል፦</t>
         </is>
       </c>
       <c r="G226" s="13" t="inlineStr">
         <is>
-          <t>Ma jiro kalfadhi socda.</t>
+          <t>Waxaan ku hadli karaa:</t>
         </is>
       </c>
       <c r="H226" s="14" t="inlineStr"/>
@@ -14033,7 +14033,7 @@
     <row r="227" ht="44" customHeight="1">
       <c r="A227" s="11" t="inlineStr">
         <is>
-          <t>wait_suffix</t>
+          <t>languages_picked_note</t>
         </is>
       </c>
       <c r="B227" s="11" t="inlineStr">
@@ -14043,27 +14043,27 @@
       </c>
       <c r="C227" s="11" t="inlineStr">
         <is>
-          <t>wait</t>
+          <t>Customers writing in these reach you first. Everyone else still reaches you — after a short wait, so nobody is stranded.</t>
         </is>
       </c>
       <c r="D227" s="12" t="inlineStr">
         <is>
-          <t>ጥበቃ</t>
+          <t>በእነዚህ ቋንቋዎች የሚጽፉ ደንበኞች መጀመሪያ ወደ እርስዎ ይደርሳሉ። ሌሎችም ይደርሳሉ — ከአጭር ጥበቃ በኋላ፤ ማንም አይቀርም።</t>
         </is>
       </c>
       <c r="E227" s="13" t="inlineStr">
         <is>
-          <t>eegumsa</t>
+          <t>Maamiltoonni afaanota kanaan barreessan jalqaba isin bira ga'u. Kaan hundinuu ammas isin bira ga'u — eegumsa gabaabaa booda, namni hafu hin jiru.</t>
         </is>
       </c>
       <c r="F227" s="12" t="inlineStr">
         <is>
-          <t>ጽበት</t>
+          <t>በዞም ቋንቋታት ዝጽሕፉ ዓማዊል ቅድም ናባኹም ይበጽሑ። እቶም ካልኦት እውን ይበጽሑ — ድሕሪ ሓጺር ጽበት፣ ዋላ ሓደ ኣይተርፍን።</t>
         </is>
       </c>
       <c r="G227" s="13" t="inlineStr">
         <is>
-          <t>sug</t>
+          <t>Macaamiisha ku qora kuwan ayaa marka hore kugu soo gaara. Qof kastana wuu ku soo gaari doonaa — sug gaaban ka dib, sidaas qofna ma harayo.</t>
         </is>
       </c>
       <c r="H227" s="14" t="inlineStr"/>
@@ -14071,7 +14071,7 @@
     <row r="228" ht="44" customHeight="1">
       <c r="A228" s="11" t="inlineStr">
         <is>
-          <t>what_session_covers</t>
+          <t>languages_none_note</t>
         </is>
       </c>
       <c r="B228" s="11" t="inlineStr">
@@ -14081,27 +14081,27 @@
       </c>
       <c r="C228" s="11" t="inlineStr">
         <is>
-          <t>What a session covers</t>
+          <t>Nothing selected, so every waiting customer is offered to you in plain oldest-first order.</t>
         </is>
       </c>
       <c r="D228" s="12" t="inlineStr">
         <is>
-          <t>አንድ ክፍለ-ጊዜ ምን ይሸፍናል</t>
+          <t>ምንም አልተመረጠም፤ ስለዚህ እያንዳንዱ የሚጠብቅ ደንበኛ በቀላል ቀዳሚ-መጀመሪያ ቅደም ተከተል ይቀርብልዎታል።</t>
         </is>
       </c>
       <c r="E228" s="13" t="inlineStr">
         <is>
-          <t>Sessioniin maal haguuga</t>
+          <t>Wanti filatame hin jiru, kanaafuu maamilli eegaa jiru hundi tartiiba dursaa-jalqabaatiin isinii dhiyaata.</t>
         </is>
       </c>
       <c r="F228" s="12" t="inlineStr">
         <is>
-          <t>ሓደ ክፍለ-ግዜ እንታይ ይሽፍን</t>
+          <t>ዋላ ሓደ ኣይተመርጸን፣ ስለዚ ነፍስ ወከፍ ዝጽበ ዓሚል ብቐሊል ናይ ቀዳምነት ስርዓት ይቐርበልኩም።</t>
         </is>
       </c>
       <c r="G228" s="13" t="inlineStr">
         <is>
-          <t>Waxa kalfadhigu daboolo</t>
+          <t>Waxba lama dooran, sidaas darteed macmiil kasta oo sugaya waxaa laguu soo bandhigayaa sida caadiga ah ee ugu horreeya.</t>
         </is>
       </c>
       <c r="H228" s="14" t="inlineStr"/>
@@ -14109,7 +14109,7 @@
     <row r="229" ht="44" customHeight="1">
       <c r="A229" s="11" t="inlineStr">
         <is>
-          <t>session_scope_body</t>
+          <t>languages_updated</t>
         </is>
       </c>
       <c r="B229" s="11" t="inlineStr">
@@ -14119,27 +14119,27 @@
       </c>
       <c r="C229" s="11" t="inlineStr">
         <is>
-          <t>Before someone is identified: general questions about products, eligibility and how to apply. Once you have checked their Fayda ID against the account and asked something only the account holder could answer: their own application, documents and disputes.</t>
+          <t>Languages updated</t>
         </is>
       </c>
       <c r="D229" s="12" t="inlineStr">
         <is>
-          <t>አንድ ሰው ከመለየቱ በፊት፦ ስለ ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል አጠቃላይ ጥያቄዎች። የፋይዳ መታወቂያቸውን ከሂሳቡ ጋር አመሳክረው የሂሳቡ ባለቤት ብቻ ሊመልሰው የሚችለውን ከጠየቁ በኋላ፦ የራሳቸው ማመልከቻ፣ ሰነዶችና ቅሬታዎች።</t>
+          <t>ቋንቋዎች ተዘምነዋል</t>
         </is>
       </c>
       <c r="E229" s="13" t="inlineStr">
         <is>
-          <t>Namni tokko utuu hin beekamin dura: gaaffii waliigalaa waa'ee oomishaalee, ulaagaa fi akkaataa itti iyyatan. Erga waraqaa eenyummaa Fayda isaanii herrega waliin madaalchiftanii waan abbaan herregaa qofti deebisuu danda'u gaafattanii booda: iyyannoo, sanadoota fi komii isaanii.</t>
+          <t>Afaanonni haaromfaman</t>
         </is>
       </c>
       <c r="F229" s="12" t="inlineStr">
         <is>
-          <t>ሓደ ሰብ ቅድሚ ምልላዩ፦ ብዛዕባ ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን ሓፈሻዊ ሕቶታት። መንነት ፋይዳኦም ምስ ሕሳብ ኣረጋጊጽኩም እቲ ወናኒ ሕሳብ ጥራይ ክምልሶ ዝኽእል ምስ ሓተትኩም፦ ናቶም ምልክታ፣ ሰነዳትን ጥርዓናትን።</t>
+          <t>ቋንቋታት ተሓዲሶም</t>
         </is>
       </c>
       <c r="G229" s="13" t="inlineStr">
         <is>
-          <t>Ka hor inta aan qofka la aqoonsan: su'aalo guud oo ku saabsan alaabta, u-qalmitaanka iyo sida loo codsado. Marka aad hubiso aqoonsigooda Fayda ee xisaabta oo aad weydiiso wax uu kaliya milkiilaha xisaabtu ka jawaabi karo: codsigooda, dukumiintiyada iyo cabashooyinka.</t>
+          <t>Luqadaha waa la cusbooneysiiyay</t>
         </is>
       </c>
       <c r="H229" s="14" t="inlineStr"/>
@@ -14147,7 +14147,7 @@
     <row r="230" ht="44" customHeight="1">
       <c r="A230" s="11" t="inlineStr">
         <is>
-          <t>never_money_movement</t>
+          <t>media_video</t>
         </is>
       </c>
       <c r="B230" s="11" t="inlineStr">
@@ -14157,27 +14157,27 @@
       </c>
       <c r="C230" s="11" t="inlineStr">
         <is>
-          <t>Never, at any point and for anyone: deposits, withdrawals or transfers. Those do not happen on a call.</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="D230" s="12" t="inlineStr">
         <is>
-          <t>በፍጹም፣ በማንኛውም ጊዜና ለማንም፦ ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም። እነዚያ በጥሪ ላይ አይፈጸሙም።</t>
+          <t>ቪዲዮ</t>
         </is>
       </c>
       <c r="E230" s="13" t="inlineStr">
         <is>
-          <t>Gonkumaa, yeroo kamiyyuu fi eenyuufiyyuu: kuusaa, baasii yookiin dabarsa hin jiru. Isaan sun bilbila irratti hin raawwataman.</t>
+          <t>Viidiyoo</t>
         </is>
       </c>
       <c r="F230" s="12" t="inlineStr">
         <is>
-          <t>ፈጺሙ፣ ኣብ ዝኾነ እዋንን ንዝኾነ ሰብን፦ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን። እዚኣቶም ኣብ ጻውዒት ኣይፍጸሙን።</t>
+          <t>ቪድዮ</t>
         </is>
       </c>
       <c r="G230" s="13" t="inlineStr">
         <is>
-          <t>Weligaa, wakhti kasta iyo qof kasta: dhigasho, qaadis ama wareejin ma jirto. Kuwaas wicitaan laguma sameeyo.</t>
+          <t>Fiidyow</t>
         </is>
       </c>
       <c r="H230" s="14" t="inlineStr"/>
@@ -14185,7 +14185,7 @@
     <row r="231" ht="44" customHeight="1">
       <c r="A231" s="11" t="inlineStr">
         <is>
-          <t>open_escalation_queue</t>
+          <t>media_audio</t>
         </is>
       </c>
       <c r="B231" s="11" t="inlineStr">
@@ -14195,27 +14195,27 @@
       </c>
       <c r="C231" s="11" t="inlineStr">
         <is>
-          <t>Open the escalation queue</t>
+          <t>Audio</t>
         </is>
       </c>
       <c r="D231" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ወረፋውን ክፈት</t>
+          <t>ድምፅ</t>
         </is>
       </c>
       <c r="E231" s="13" t="inlineStr">
         <is>
-          <t>Sararaa dabarsaa banaa</t>
+          <t>Sagalee</t>
         </is>
       </c>
       <c r="F231" s="12" t="inlineStr">
         <is>
-          <t>ሪጋ ምትሕልላፍ ክፈት</t>
+          <t>ድምጺ</t>
         </is>
       </c>
       <c r="G231" s="13" t="inlineStr">
         <is>
-          <t>Fur safka gudbinta</t>
+          <t>Cod</t>
         </is>
       </c>
       <c r="H231" s="14" t="inlineStr"/>
@@ -14223,7 +14223,7 @@
     <row r="232" ht="44" customHeight="1">
       <c r="A232" s="11" t="inlineStr">
         <is>
-          <t>switch_dark_light</t>
+          <t>not_your_language</t>
         </is>
       </c>
       <c r="B232" s="11" t="inlineStr">
@@ -14233,27 +14233,27 @@
       </c>
       <c r="C232" s="11" t="inlineStr">
         <is>
-          <t>Switch between dark and light</t>
+          <t>not your language</t>
         </is>
       </c>
       <c r="D232" s="12" t="inlineStr">
         <is>
-          <t>በጨለማና በብርሃን መካከል ቀይር</t>
+          <t>የእርስዎ ቋንቋ አይደለም</t>
         </is>
       </c>
       <c r="E232" s="13" t="inlineStr">
         <is>
-          <t>Dukkanaa fi ifa gidduu jijjiiri</t>
+          <t>afaan keessanii miti</t>
         </is>
       </c>
       <c r="F232" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መንጎ ጸላምን ብርሃንን ቀይር</t>
+          <t>ናትኩም ቋንቋ ኣይኮነን</t>
         </is>
       </c>
       <c r="G232" s="13" t="inlineStr">
         <is>
-          <t>U beddel mugdiga iyo iftiinka</t>
+          <t>ma aha luqaddaada</t>
         </is>
       </c>
       <c r="H232" s="14" t="inlineStr"/>
@@ -14261,7 +14261,7 @@
     <row r="233" ht="44" customHeight="1">
       <c r="A233" s="11" t="inlineStr">
         <is>
-          <t>live_session</t>
+          <t>languages_first_note</t>
         </is>
       </c>
       <c r="B233" s="11" t="inlineStr">
@@ -14271,27 +14271,27 @@
       </c>
       <c r="C233" s="11" t="inlineStr">
         <is>
-          <t>Live session</t>
+          <t>Your languages first, longest wait within each. Anyone waiting too long moves to the top whatever they speak.</t>
         </is>
       </c>
       <c r="D233" s="12" t="inlineStr">
         <is>
-          <t>የቀጥታ ክፍለ-ጊዜ</t>
+          <t>የእርስዎ ቋንቋዎች መጀመሪያ፤ በእያንዳንዱ ውስጥ ረጅም የጠበቀው ይቀድማል። ከልክ በላይ የጠበቀ ማንኛውም ሰው የሚናገረው ምንም ይሁን ወደ ላይ ይወጣል።</t>
         </is>
       </c>
       <c r="E233" s="13" t="inlineStr">
         <is>
-          <t>Session kallattii</t>
+          <t>Afaanonni keessan jalqaba, tokkoon tokkoon isaanii keessatti kan yeroo dheeraa eege dursa. Namni baay'ee eege afaan kamiyyuu haa dubbatu gara oliitti deema.</t>
         </is>
       </c>
       <c r="F233" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታ ክፍለ-ግዜ</t>
+          <t>ቋንቋታትኩም ቅድም፣ ኣብ ነፍስ ወከፍ እቲ ነዊሕ ዝጸንሐ ይቐድም። ካብ ንቡር ንላዕሊ ዝጸንሐ ዝኾነ ሰብ ዝዛረቦ ብዘየገድስ ናብ ላዕሊ ይመጽእ።</t>
         </is>
       </c>
       <c r="G233" s="13" t="inlineStr">
         <is>
-          <t>Kalfadhi toos ah</t>
+          <t>Luqadahaaga marka hore, kii ugu sugay dheeraa mid kasta gudahood. Qof kasta oo aad u sugay ayaa kor u kaca luqad kastoo uu ku hadloba.</t>
         </is>
       </c>
       <c r="H233" s="14" t="inlineStr"/>
@@ -14299,7 +14299,7 @@
     <row r="234" ht="44" customHeight="1">
       <c r="A234" s="11" t="inlineStr">
         <is>
-          <t>customer_left_call</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="B234" s="11" t="inlineStr">
@@ -14309,27 +14309,27 @@
       </c>
       <c r="C234" s="11" t="inlineStr">
         <is>
-          <t>The customer has left the call.</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="D234" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛው ጥሪውን ለቅቋል።</t>
+          <t>በሂደት ላይ</t>
         </is>
       </c>
       <c r="E234" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan bilbila irraa ba'eera.</t>
+          <t>Adeemsa irra</t>
         </is>
       </c>
       <c r="F234" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዓሚል ካብቲ ጻውዒት ወጺኡ።</t>
+          <t>ኣብ መስርሕ</t>
         </is>
       </c>
       <c r="G234" s="13" t="inlineStr">
         <is>
-          <t>Macmiilku wicitaanka wuu ka baxay.</t>
+          <t>Socda</t>
         </is>
       </c>
       <c r="H234" s="14" t="inlineStr"/>
@@ -14337,7 +14337,7 @@
     <row r="235" ht="44" customHeight="1">
       <c r="A235" s="11" t="inlineStr">
         <is>
-          <t>waiting_for_customer</t>
+          <t>no_session_in_progress</t>
         </is>
       </c>
       <c r="B235" s="11" t="inlineStr">
@@ -14347,27 +14347,27 @@
       </c>
       <c r="C235" s="11" t="inlineStr">
         <is>
-          <t>Waiting for the customer…</t>
+          <t>No session in progress.</t>
         </is>
       </c>
       <c r="D235" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛውን በመጠበቅ ላይ…</t>
+          <t>በሂደት ላይ ያለ ክፍለ-ጊዜ የለም።</t>
         </is>
       </c>
       <c r="E235" s="13" t="inlineStr">
         <is>
-          <t>Maamilaa eegaa jirra…</t>
+          <t>Sessionii adeemsa irra jiru hin jiru.</t>
         </is>
       </c>
       <c r="F235" s="12" t="inlineStr">
         <is>
-          <t>ነቲ ዓሚል ንጽበ ኣለና…</t>
+          <t>ኣብ መስርሕ ዘሎ ክፍለ-ግዜ የለን።</t>
         </is>
       </c>
       <c r="G235" s="13" t="inlineStr">
         <is>
-          <t>Macmiilka la sugayo…</t>
+          <t>Ma jiro kalfadhi socda.</t>
         </is>
       </c>
       <c r="H235" s="14" t="inlineStr"/>
@@ -14375,7 +14375,7 @@
     <row r="236" ht="44" customHeight="1">
       <c r="A236" s="11" t="inlineStr">
         <is>
-          <t>mic_blocked</t>
+          <t>wait_suffix</t>
         </is>
       </c>
       <c r="B236" s="11" t="inlineStr">
@@ -14385,27 +14385,27 @@
       </c>
       <c r="C236" s="11" t="inlineStr">
         <is>
-          <t>Microphone access is blocked. Allow it in your browser and take the session again.</t>
+          <t>wait</t>
         </is>
       </c>
       <c r="D236" s="12" t="inlineStr">
         <is>
-          <t>የማይክሮፎን መዳረሻ ታግዷል። በአሳሽዎ ውስጥ ይፍቀዱና ክፍለ-ጊዜውን እንደገና ይውሰዱ።</t>
+          <t>ጥበቃ</t>
         </is>
       </c>
       <c r="E236" s="13" t="inlineStr">
         <is>
-          <t>Maayikiroofoonii dhorkameera. Biraawzarii keessan keessatti hayyamaatii session irra deebi'aa fudhadhaa.</t>
+          <t>eegumsa</t>
         </is>
       </c>
       <c r="F236" s="12" t="inlineStr">
         <is>
-          <t>መእተዊ ማይክሮፎን ተዓጊቱ። ኣብ መርበብ መንሸራተቲኹም ፍቐዱ እሞ ነቲ ክፍለ-ግዜ ደጊምኩም ውሰዱ።</t>
+          <t>ጽበት</t>
         </is>
       </c>
       <c r="G236" s="13" t="inlineStr">
         <is>
-          <t>Makarafoonka waa la xannibay. Browser-kaaga ka ogolow oo kalfadhiga mar kale qaado.</t>
+          <t>sug</t>
         </is>
       </c>
       <c r="H236" s="14" t="inlineStr"/>
@@ -14413,7 +14413,7 @@
     <row r="237" ht="44" customHeight="1">
       <c r="A237" s="11" t="inlineStr">
         <is>
-          <t>unknown_error</t>
+          <t>what_session_covers</t>
         </is>
       </c>
       <c r="B237" s="11" t="inlineStr">
@@ -14423,27 +14423,27 @@
       </c>
       <c r="C237" s="11" t="inlineStr">
         <is>
-          <t>unknown error</t>
+          <t>What a session covers</t>
         </is>
       </c>
       <c r="D237" s="12" t="inlineStr">
         <is>
-          <t>ያልታወቀ ስህተት</t>
+          <t>አንድ ክፍለ-ጊዜ ምን ይሸፍናል</t>
         </is>
       </c>
       <c r="E237" s="13" t="inlineStr">
         <is>
-          <t>dogoggora hin beekamne</t>
+          <t>Sessioniin maal haguuga</t>
         </is>
       </c>
       <c r="F237" s="12" t="inlineStr">
         <is>
-          <t>ዘይተፈልጠ ጌጋ</t>
+          <t>ሓደ ክፍለ-ግዜ እንታይ ይሽፍን</t>
         </is>
       </c>
       <c r="G237" s="13" t="inlineStr">
         <is>
-          <t>khalad aan la garanayn</t>
+          <t>Waxa kalfadhigu daboolo</t>
         </is>
       </c>
       <c r="H237" s="14" t="inlineStr"/>
@@ -14451,7 +14451,7 @@
     <row r="238" ht="44" customHeight="1">
       <c r="A238" s="11" t="inlineStr">
         <is>
-          <t>no_messages_yet</t>
+          <t>session_scope_body</t>
         </is>
       </c>
       <c r="B238" s="11" t="inlineStr">
@@ -14461,27 +14461,27 @@
       </c>
       <c r="C238" s="11" t="inlineStr">
         <is>
-          <t>No messages yet.</t>
+          <t>Before someone is identified: general questions about products, eligibility and how to apply. Once you have checked their Fayda ID against the account and asked something only the account holder could answer: their own application, documents and disputes.</t>
         </is>
       </c>
       <c r="D238" s="12" t="inlineStr">
         <is>
-          <t>እስካሁን መልእክት የለም።</t>
+          <t>አንድ ሰው ከመለየቱ በፊት፦ ስለ ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል አጠቃላይ ጥያቄዎች። የፋይዳ መታወቂያቸውን ከሂሳቡ ጋር አመሳክረው የሂሳቡ ባለቤት ብቻ ሊመልሰው የሚችለውን ከጠየቁ በኋላ፦ የራሳቸው ማመልከቻ፣ ሰነዶችና ቅሬታዎች።</t>
         </is>
       </c>
       <c r="E238" s="13" t="inlineStr">
         <is>
-          <t>Ammaaf ergaan hin jiru.</t>
+          <t>Namni tokko utuu hin beekamin dura: gaaffii waliigalaa waa'ee oomishaalee, ulaagaa fi akkaataa itti iyyatan. Erga waraqaa eenyummaa Fayda isaanii herrega waliin madaalchiftanii waan abbaan herregaa qofti deebisuu danda'u gaafattanii booda: iyyannoo, sanadoota fi komii isaanii.</t>
         </is>
       </c>
       <c r="F238" s="12" t="inlineStr">
         <is>
-          <t>ክሳብ ሕጂ መልእኽቲ የለን።</t>
+          <t>ሓደ ሰብ ቅድሚ ምልላዩ፦ ብዛዕባ ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን ሓፈሻዊ ሕቶታት። መንነት ፋይዳኦም ምስ ሕሳብ ኣረጋጊጽኩም እቲ ወናኒ ሕሳብ ጥራይ ክምልሶ ዝኽእል ምስ ሓተትኩም፦ ናቶም ምልክታ፣ ሰነዳትን ጥርዓናትን።</t>
         </is>
       </c>
       <c r="G238" s="13" t="inlineStr">
         <is>
-          <t>Weli fariimo ma jiraan.</t>
+          <t>Ka hor inta aan qofka la aqoonsan: su'aalo guud oo ku saabsan alaabta, u-qalmitaanka iyo sida loo codsado. Marka aad hubiso aqoonsigooda Fayda ee xisaabta oo aad weydiiso wax uu kaliya milkiilaha xisaabtu ka jawaabi karo: codsigooda, dukumiintiyada iyo cabashooyinka.</t>
         </is>
       </c>
       <c r="H238" s="14" t="inlineStr"/>
@@ -14489,7 +14489,7 @@
     <row r="239" ht="44" customHeight="1">
       <c r="A239" s="11" t="inlineStr">
         <is>
-          <t>you_label</t>
+          <t>never_money_movement</t>
         </is>
       </c>
       <c r="B239" s="11" t="inlineStr">
@@ -14499,27 +14499,27 @@
       </c>
       <c r="C239" s="11" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Never, at any point and for anyone: deposits, withdrawals or transfers. Those do not happen on a call.</t>
         </is>
       </c>
       <c r="D239" s="12" t="inlineStr">
         <is>
-          <t>እርስዎ</t>
+          <t>በፍጹም፣ በማንኛውም ጊዜና ለማንም፦ ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም። እነዚያ በጥሪ ላይ አይፈጸሙም።</t>
         </is>
       </c>
       <c r="E239" s="13" t="inlineStr">
         <is>
-          <t>Isin</t>
+          <t>Gonkumaa, yeroo kamiyyuu fi eenyuufiyyuu: kuusaa, baasii yookiin dabarsa hin jiru. Isaan sun bilbila irratti hin raawwataman.</t>
         </is>
       </c>
       <c r="F239" s="12" t="inlineStr">
         <is>
-          <t>ንስኹም</t>
+          <t>ፈጺሙ፣ ኣብ ዝኾነ እዋንን ንዝኾነ ሰብን፦ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን። እዚኣቶም ኣብ ጻውዒት ኣይፍጸሙን።</t>
         </is>
       </c>
       <c r="G239" s="13" t="inlineStr">
         <is>
-          <t>Adiga</t>
+          <t>Weligaa, wakhti kasta iyo qof kasta: dhigasho, qaadis ama wareejin ma jirto. Kuwaas wicitaan laguma sameeyo.</t>
         </is>
       </c>
       <c r="H239" s="14" t="inlineStr"/>
@@ -14527,7 +14527,7 @@
     <row r="240" ht="44" customHeight="1">
       <c r="A240" s="11" t="inlineStr">
         <is>
-          <t>assistant_label</t>
+          <t>open_escalation_queue</t>
         </is>
       </c>
       <c r="B240" s="11" t="inlineStr">
@@ -14537,27 +14537,27 @@
       </c>
       <c r="C240" s="11" t="inlineStr">
         <is>
-          <t>Assistant</t>
+          <t>Open the escalation queue</t>
         </is>
       </c>
       <c r="D240" s="12" t="inlineStr">
         <is>
-          <t>ረዳት</t>
+          <t>የማሸጋገሪያ ወረፋውን ክፈት</t>
         </is>
       </c>
       <c r="E240" s="13" t="inlineStr">
         <is>
-          <t>Gargaaraa</t>
+          <t>Sararaa dabarsaa banaa</t>
         </is>
       </c>
       <c r="F240" s="12" t="inlineStr">
         <is>
-          <t>ሓጋዚ</t>
+          <t>ሪጋ ምትሕልላፍ ክፈት</t>
         </is>
       </c>
       <c r="G240" s="13" t="inlineStr">
         <is>
-          <t>Kaaliye</t>
+          <t>Fur safka gudbinta</t>
         </is>
       </c>
       <c r="H240" s="14" t="inlineStr"/>
@@ -14565,7 +14565,7 @@
     <row r="241" ht="44" customHeight="1">
       <c r="A241" s="11" t="inlineStr">
         <is>
-          <t>conversation_unavailable</t>
+          <t>switch_dark_light</t>
         </is>
       </c>
       <c r="B241" s="11" t="inlineStr">
@@ -14575,27 +14575,27 @@
       </c>
       <c r="C241" s="11" t="inlineStr">
         <is>
-          <t>Conversation unavailable.</t>
+          <t>Switch between dark and light</t>
         </is>
       </c>
       <c r="D241" s="12" t="inlineStr">
         <is>
-          <t>ውይይቱ አይገኝም።</t>
+          <t>በጨለማና በብርሃን መካከል ቀይር</t>
         </is>
       </c>
       <c r="E241" s="13" t="inlineStr">
         <is>
-          <t>Mariin hin argamu.</t>
+          <t>Dukkanaa fi ifa gidduu jijjiiri</t>
         </is>
       </c>
       <c r="F241" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዝርርብ ኣይርከብን።</t>
+          <t>ኣብ መንጎ ጸላምን ብርሃንን ቀይር</t>
         </is>
       </c>
       <c r="G241" s="13" t="inlineStr">
         <is>
-          <t>Wadahadalka lama heli karo.</t>
+          <t>U beddel mugdiga iyo iftiinka</t>
         </is>
       </c>
       <c r="H241" s="14" t="inlineStr"/>
@@ -14603,7 +14603,7 @@
     <row r="242" ht="44" customHeight="1">
       <c r="A242" s="11" t="inlineStr">
         <is>
-          <t>unmute</t>
+          <t>live_session</t>
         </is>
       </c>
       <c r="B242" s="11" t="inlineStr">
@@ -14613,27 +14613,27 @@
       </c>
       <c r="C242" s="11" t="inlineStr">
         <is>
-          <t>Unmute</t>
+          <t>Live session</t>
         </is>
       </c>
       <c r="D242" s="12" t="inlineStr">
         <is>
-          <t>ድምፅ አብራ</t>
+          <t>የቀጥታ ክፍለ-ጊዜ</t>
         </is>
       </c>
       <c r="E242" s="13" t="inlineStr">
         <is>
-          <t>Sagalee banaa</t>
+          <t>Session kallattii</t>
         </is>
       </c>
       <c r="F242" s="12" t="inlineStr">
         <is>
-          <t>ድምጺ ኣብርህ</t>
+          <t>ቀጥታ ክፍለ-ግዜ</t>
         </is>
       </c>
       <c r="G242" s="13" t="inlineStr">
         <is>
-          <t>Codka fur</t>
+          <t>Kalfadhi toos ah</t>
         </is>
       </c>
       <c r="H242" s="14" t="inlineStr"/>
@@ -14641,7 +14641,7 @@
     <row r="243" ht="44" customHeight="1">
       <c r="A243" s="11" t="inlineStr">
         <is>
-          <t>session_summary_prompt</t>
+          <t>customer_left_call</t>
         </is>
       </c>
       <c r="B243" s="11" t="inlineStr">
@@ -14651,27 +14651,27 @@
       </c>
       <c r="C243" s="11" t="inlineStr">
         <is>
-          <t>What did this session cover? (optional)</t>
+          <t>The customer has left the call.</t>
         </is>
       </c>
       <c r="D243" s="12" t="inlineStr">
         <is>
-          <t>ይህ ክፍለ-ጊዜ ምን ሸፈነ? (አማራጭ)</t>
+          <t>ደንበኛው ጥሪውን ለቅቋል።</t>
         </is>
       </c>
       <c r="E243" s="13" t="inlineStr">
         <is>
-          <t>Sessioniin kun maal haguuge? (filannoo)</t>
+          <t>Maamilaan bilbila irraa ba'eera.</t>
         </is>
       </c>
       <c r="F243" s="12" t="inlineStr">
         <is>
-          <t>እዚ ክፍለ-ግዜ እንታይ ሸፈነ? (ኣማራጺ)</t>
+          <t>እቲ ዓሚል ካብቲ ጻውዒት ወጺኡ።</t>
         </is>
       </c>
       <c r="G243" s="13" t="inlineStr">
         <is>
-          <t>Kalfadhigan muxuu daboolay? (ikhtiyaari)</t>
+          <t>Macmiilku wicitaanka wuu ka baxay.</t>
         </is>
       </c>
       <c r="H243" s="14" t="inlineStr"/>
@@ -14679,7 +14679,7 @@
     <row r="244" ht="44" customHeight="1">
       <c r="A244" s="11" t="inlineStr">
         <is>
-          <t>customer_ended_call</t>
+          <t>waiting_for_customer</t>
         </is>
       </c>
       <c r="B244" s="11" t="inlineStr">
@@ -14689,27 +14689,27 @@
       </c>
       <c r="C244" s="11" t="inlineStr">
         <is>
-          <t>The customer ended the call</t>
+          <t>Waiting for the customer…</t>
         </is>
       </c>
       <c r="D244" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛው ጥሪውን አቋረጠ</t>
+          <t>ደንበኛውን በመጠበቅ ላይ…</t>
         </is>
       </c>
       <c r="E244" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan bilbila xumure</t>
+          <t>Maamilaa eegaa jirra…</t>
         </is>
       </c>
       <c r="F244" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዓሚል ነቲ ጻውዒት ወዲኡዎ</t>
+          <t>ነቲ ዓሚል ንጽበ ኣለና…</t>
         </is>
       </c>
       <c r="G244" s="13" t="inlineStr">
         <is>
-          <t>Macmiilku wicitaanka wuu joojiyay</t>
+          <t>Macmiilka la sugayo…</t>
         </is>
       </c>
       <c r="H244" s="14" t="inlineStr"/>
@@ -14717,7 +14717,7 @@
     <row r="245" ht="44" customHeight="1">
       <c r="A245" s="11" t="inlineStr">
         <is>
-          <t>verified_scope</t>
+          <t>mic_blocked</t>
         </is>
       </c>
       <c r="B245" s="11" t="inlineStr">
@@ -14727,27 +14727,27 @@
       </c>
       <c r="C245" s="11" t="inlineStr">
         <is>
-          <t>You can now discuss their own records, take documents and file a dispute. Never a deposit, withdrawal or transfer.</t>
+          <t>Microphone access is blocked. Allow it in your browser and take the session again.</t>
         </is>
       </c>
       <c r="D245" s="12" t="inlineStr">
         <is>
-          <t>አሁን ስለ ራሳቸው መዝገቦች መወያየት፣ ሰነዶች መቀበልና ቅሬታ ማስመዝገብ ይችላሉ። በፍጹም ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም።</t>
+          <t>የማይክሮፎን መዳረሻ ታግዷል። በአሳሽዎ ውስጥ ይፍቀዱና ክፍለ-ጊዜውን እንደገና ይውሰዱ።</t>
         </is>
       </c>
       <c r="E245" s="13" t="inlineStr">
         <is>
-          <t>Amma waa'ee galmee isaanii mari'achuu, sanadoota fudhachuu fi komii galmeessuu dandeessu. Gonkumaa kuusaa, baasii yookiin dabarsa hin jiru.</t>
+          <t>Maayikiroofoonii dhorkameera. Biraawzarii keessan keessatti hayyamaatii session irra deebi'aa fudhadhaa.</t>
         </is>
       </c>
       <c r="F245" s="12" t="inlineStr">
         <is>
-          <t>ሕጂ ብዛዕባ ናቶም መዝገባት ክትዘራረቡ፣ ሰነዳት ክትቅበሉን ጥርዓን ከተመዝግቡን ትኽእሉ። ፈጺሙ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን።</t>
+          <t>መእተዊ ማይክሮፎን ተዓጊቱ። ኣብ መርበብ መንሸራተቲኹም ፍቐዱ እሞ ነቲ ክፍለ-ግዜ ደጊምኩም ውሰዱ።</t>
         </is>
       </c>
       <c r="G245" s="13" t="inlineStr">
         <is>
-          <t>Hadda waad kala hadli kartaa diiwaankooda, dukumiinti qaadan iyo cabasho diiwaangelin. Weligaa dhigasho, qaadis ama wareejin ma jirto.</t>
+          <t>Makarafoonka waa la xannibay. Browser-kaaga ka ogolow oo kalfadhiga mar kale qaado.</t>
         </is>
       </c>
       <c r="H245" s="14" t="inlineStr"/>
@@ -14755,7 +14755,7 @@
     <row r="246" ht="44" customHeight="1">
       <c r="A246" s="11" t="inlineStr">
         <is>
-          <t>establish_who_they_are</t>
+          <t>unknown_error</t>
         </is>
       </c>
       <c r="B246" s="11" t="inlineStr">
@@ -14765,27 +14765,27 @@
       </c>
       <c r="C246" s="11" t="inlineStr">
         <is>
-          <t>Establish who they are — either one</t>
+          <t>unknown error</t>
         </is>
       </c>
       <c r="D246" s="12" t="inlineStr">
         <is>
-          <t>ማንነታቸውን ያረጋግጡ — አንዱ ይበቃል</t>
+          <t>ያልታወቀ ስህተት</t>
         </is>
       </c>
       <c r="E246" s="13" t="inlineStr">
         <is>
-          <t>Eenyummaa isaanii mirkaneessaa — tokko ni ga'a</t>
+          <t>dogoggora hin beekamne</t>
         </is>
       </c>
       <c r="F246" s="12" t="inlineStr">
         <is>
-          <t>መንነቶም ኣረጋግጹ — ሓደ እኹል እዩ</t>
+          <t>ዘይተፈልጠ ጌጋ</t>
         </is>
       </c>
       <c r="G246" s="13" t="inlineStr">
         <is>
-          <t>Ogow cidda ay yihiin — mid kasta</t>
+          <t>khalad aan la garanayn</t>
         </is>
       </c>
       <c r="H246" s="14" t="inlineStr"/>
@@ -14793,7 +14793,7 @@
     <row r="247" ht="44" customHeight="1">
       <c r="A247" s="11" t="inlineStr">
         <is>
-          <t>chk_id_document</t>
+          <t>no_messages_yet</t>
         </is>
       </c>
       <c r="B247" s="11" t="inlineStr">
@@ -14803,27 +14803,27 @@
       </c>
       <c r="C247" s="11" t="inlineStr">
         <is>
-          <t>Fayda ID shown and matches the account name</t>
+          <t>No messages yet.</t>
         </is>
       </c>
       <c r="D247" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ መታወቂያ ታይቷል እና ከሂሳቡ ስም ጋር ይዛመዳል</t>
+          <t>እስካሁን መልእክት የለም።</t>
         </is>
       </c>
       <c r="E247" s="13" t="inlineStr">
         <is>
-          <t>Waraqaan eenyummaa Fayda agarsiifame maqaa herregaa waliin walsimeera</t>
+          <t>Ammaaf ergaan hin jiru.</t>
         </is>
       </c>
       <c r="F247" s="12" t="inlineStr">
         <is>
-          <t>መንነት ፋይዳ ተራእዩን ምስ ስም ሕሳብ ይሰማማዕን</t>
+          <t>ክሳብ ሕጂ መልእኽቲ የለን።</t>
         </is>
       </c>
       <c r="G247" s="13" t="inlineStr">
         <is>
-          <t>Aqoonsiga Fayda waa la tusay wuxuuna la mid yahay magaca xisaabta</t>
+          <t>Weli fariimo ma jiraan.</t>
         </is>
       </c>
       <c r="H247" s="14" t="inlineStr"/>
@@ -14831,7 +14831,7 @@
     <row r="248" ht="44" customHeight="1">
       <c r="A248" s="11" t="inlineStr">
         <is>
-          <t>chk_fayda_matched</t>
+          <t>you_label</t>
         </is>
       </c>
       <c r="B248" s="11" t="inlineStr">
@@ -14841,27 +14841,27 @@
       </c>
       <c r="C248" s="11" t="inlineStr">
         <is>
-          <t>Fayda number matches the account record</t>
+          <t>You</t>
         </is>
       </c>
       <c r="D248" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ ቁጥር ከሂሳቡ መዝገብ ጋር ይዛመዳል</t>
+          <t>እርስዎ</t>
         </is>
       </c>
       <c r="E248" s="13" t="inlineStr">
         <is>
-          <t>Lakkoofsi Fayda galmee herregaa waliin walsimeera</t>
+          <t>Isin</t>
         </is>
       </c>
       <c r="F248" s="12" t="inlineStr">
         <is>
-          <t>ቁጽሪ ፋይዳ ምስ መዝገብ ሕሳብ ይሰማማዕ</t>
+          <t>ንስኹም</t>
         </is>
       </c>
       <c r="G248" s="13" t="inlineStr">
         <is>
-          <t>Lambarka Fayda wuxuu la mid yahay diiwaanka xisaabta</t>
+          <t>Adiga</t>
         </is>
       </c>
       <c r="H248" s="14" t="inlineStr"/>
@@ -14869,7 +14869,7 @@
     <row r="249" ht="44" customHeight="1">
       <c r="A249" s="11" t="inlineStr">
         <is>
-          <t>chk_fayda_matched_note</t>
+          <t>assistant_label</t>
         </is>
       </c>
       <c r="B249" s="11" t="inlineStr">
@@ -14879,27 +14879,27 @@
       </c>
       <c r="C249" s="11" t="inlineStr">
         <is>
-          <t>on your own screen — works on an audio call</t>
+          <t>Assistant</t>
         </is>
       </c>
       <c r="D249" s="12" t="inlineStr">
         <is>
-          <t>በራስዎ ስክሪን ላይ — በድምፅ ጥሪም ይሠራል</t>
+          <t>ረዳት</t>
         </is>
       </c>
       <c r="E249" s="13" t="inlineStr">
         <is>
-          <t>iskiriinii keessan irratti — bilbila sagalee irrattis ni hojjeta</t>
+          <t>Gargaaraa</t>
         </is>
       </c>
       <c r="F249" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ናትኩም መርአዪ — ኣብ ናይ ድምጺ ጻውዒት እውን ይሰርሕ</t>
+          <t>ሓጋዚ</t>
         </is>
       </c>
       <c r="G249" s="13" t="inlineStr">
         <is>
-          <t>shaashaddaada — wicitaan cod ahna wuu ka shaqeeyaa</t>
+          <t>Kaaliye</t>
         </is>
       </c>
       <c r="H249" s="14" t="inlineStr"/>
@@ -14907,7 +14907,7 @@
     <row r="250" ht="44" customHeight="1">
       <c r="A250" s="11" t="inlineStr">
         <is>
-          <t>chk_id_photo</t>
+          <t>conversation_unavailable</t>
         </is>
       </c>
       <c r="B250" s="11" t="inlineStr">
@@ -14917,27 +14917,27 @@
       </c>
       <c r="C250" s="11" t="inlineStr">
         <is>
-          <t>Photo on the ID matches the person on the call</t>
+          <t>Conversation unavailable.</t>
         </is>
       </c>
       <c r="D250" s="12" t="inlineStr">
         <is>
-          <t>በመታወቂያው ላይ ያለው ፎቶ ከጥሪው ላይ ካለው ሰው ጋር ይዛመዳል</t>
+          <t>ውይይቱ አይገኝም።</t>
         </is>
       </c>
       <c r="E250" s="13" t="inlineStr">
         <is>
-          <t>Suuraan waraqaa eenyummaa irra jiru nama bilbila irra jiru waliin walsimeera</t>
+          <t>Mariin hin argamu.</t>
         </is>
       </c>
       <c r="F250" s="12" t="inlineStr">
         <is>
-          <t>እቲ ኣብ መንነት ዘሎ ስእሊ ምስቲ ኣብ ጻውዒት ዘሎ ሰብ ይሰማማዕ</t>
+          <t>እቲ ዝርርብ ኣይርከብን።</t>
         </is>
       </c>
       <c r="G250" s="13" t="inlineStr">
         <is>
-          <t>Sawirka aqoonsiga wuxuu la mid yahay qofka wicitaanka ku jira</t>
+          <t>Wadahadalka lama heli karo.</t>
         </is>
       </c>
       <c r="H250" s="14" t="inlineStr"/>
@@ -14945,7 +14945,7 @@
     <row r="251" ht="44" customHeight="1">
       <c r="A251" s="11" t="inlineStr">
         <is>
-          <t>chk_video_only</t>
+          <t>unmute</t>
         </is>
       </c>
       <c r="B251" s="11" t="inlineStr">
@@ -14955,27 +14955,27 @@
       </c>
       <c r="C251" s="11" t="inlineStr">
         <is>
-          <t>video only</t>
+          <t>Unmute</t>
         </is>
       </c>
       <c r="D251" s="12" t="inlineStr">
         <is>
-          <t>ቪዲዮ ብቻ</t>
+          <t>ድምፅ አብራ</t>
         </is>
       </c>
       <c r="E251" s="13" t="inlineStr">
         <is>
-          <t>viidiyoo qofa</t>
+          <t>Sagalee banaa</t>
         </is>
       </c>
       <c r="F251" s="12" t="inlineStr">
         <is>
-          <t>ቪድዮ ጥራይ</t>
+          <t>ድምጺ ኣብርህ</t>
         </is>
       </c>
       <c r="G251" s="13" t="inlineStr">
         <is>
-          <t>fiidyow oo kaliya</t>
+          <t>Codka fur</t>
         </is>
       </c>
       <c r="H251" s="14" t="inlineStr"/>
@@ -14983,7 +14983,7 @@
     <row r="252" ht="44" customHeight="1">
       <c r="A252" s="11" t="inlineStr">
         <is>
-          <t>confirm_account_theirs</t>
+          <t>session_summary_prompt</t>
         </is>
       </c>
       <c r="B252" s="11" t="inlineStr">
@@ -14993,27 +14993,27 @@
       </c>
       <c r="C252" s="11" t="inlineStr">
         <is>
-          <t>And confirm the account is theirs</t>
+          <t>What did this session cover? (optional)</t>
         </is>
       </c>
       <c r="D252" s="12" t="inlineStr">
         <is>
-          <t>እና ሂሳቡ የእነሱ መሆኑን ያረጋግጡ</t>
+          <t>ይህ ክፍለ-ጊዜ ምን ሸፈነ? (አማራጭ)</t>
         </is>
       </c>
       <c r="E252" s="13" t="inlineStr">
         <is>
-          <t>Akkasumas herregni kan isaanii ta'uu mirkaneessaa</t>
+          <t>Sessioniin kun maal haguuge? (filannoo)</t>
         </is>
       </c>
       <c r="F252" s="12" t="inlineStr">
         <is>
-          <t>ከምኡ'ውን እቲ ሕሳብ ናቶም ምዃኑ ኣረጋግጹ</t>
+          <t>እዚ ክፍለ-ግዜ እንታይ ሸፈነ? (ኣማራጺ)</t>
         </is>
       </c>
       <c r="G252" s="13" t="inlineStr">
         <is>
-          <t>Xaqiiji in xisaabtu tahay tooda</t>
+          <t>Kalfadhigan muxuu daboolay? (ikhtiyaari)</t>
         </is>
       </c>
       <c r="H252" s="14" t="inlineStr"/>
@@ -15021,7 +15021,7 @@
     <row r="253" ht="44" customHeight="1">
       <c r="A253" s="11" t="inlineStr">
         <is>
-          <t>confirm_identity</t>
+          <t>customer_ended_call</t>
         </is>
       </c>
       <c r="B253" s="11" t="inlineStr">
@@ -15031,27 +15031,27 @@
       </c>
       <c r="C253" s="11" t="inlineStr">
         <is>
-          <t>Confirm identity</t>
+          <t>The customer ended the call</t>
         </is>
       </c>
       <c r="D253" s="12" t="inlineStr">
         <is>
-          <t>ማንነት አረጋግጥ</t>
+          <t>ደንበኛው ጥሪውን አቋረጠ</t>
         </is>
       </c>
       <c r="E253" s="13" t="inlineStr">
         <is>
-          <t>Eenyummaa mirkaneessi</t>
+          <t>Maamilaan bilbila xumure</t>
         </is>
       </c>
       <c r="F253" s="12" t="inlineStr">
         <is>
-          <t>መንነት ኣረጋግጽ</t>
+          <t>እቲ ዓሚል ነቲ ጻውዒት ወዲኡዎ</t>
         </is>
       </c>
       <c r="G253" s="13" t="inlineStr">
         <is>
-          <t>Xaqiiji aqoonsiga</t>
+          <t>Macmiilku wicitaanka wuu joojiyay</t>
         </is>
       </c>
       <c r="H253" s="14" t="inlineStr"/>
@@ -15059,7 +15059,7 @@
     <row r="254" ht="44" customHeight="1">
       <c r="A254" s="11" t="inlineStr">
         <is>
-          <t>unverified_scope</t>
+          <t>verified_scope</t>
         </is>
       </c>
       <c r="B254" s="11" t="inlineStr">
@@ -15069,27 +15069,27 @@
       </c>
       <c r="C254" s="11" t="inlineStr">
         <is>
-          <t>Until this is done you can only give general guidance — products, eligibility and how to apply.</t>
+          <t>You can now discuss their own records, take documents and file a dispute. Never a deposit, withdrawal or transfer.</t>
         </is>
       </c>
       <c r="D254" s="12" t="inlineStr">
         <is>
-          <t>ይህ እስኪከናወን ድረስ አጠቃላይ መመሪያ ብቻ መስጠት ይችላሉ — ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል።</t>
+          <t>አሁን ስለ ራሳቸው መዝገቦች መወያየት፣ ሰነዶች መቀበልና ቅሬታ ማስመዝገብ ይችላሉ። በፍጹም ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም።</t>
         </is>
       </c>
       <c r="E254" s="13" t="inlineStr">
         <is>
-          <t>Hanga kun raawwatutti qajeelfama waliigalaa qofa kennuu dandeessu — oomishaalee, ulaagaa fi akkaataa itti iyyatan.</t>
+          <t>Amma waa'ee galmee isaanii mari'achuu, sanadoota fudhachuu fi komii galmeessuu dandeessu. Gonkumaa kuusaa, baasii yookiin dabarsa hin jiru.</t>
         </is>
       </c>
       <c r="F254" s="12" t="inlineStr">
         <is>
-          <t>እዚ ክሳብ ዝፍጸም ሓፈሻዊ መምርሒ ጥራይ ክትህቡ ትኽእሉ — ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን።</t>
+          <t>ሕጂ ብዛዕባ ናቶም መዝገባት ክትዘራረቡ፣ ሰነዳት ክትቅበሉን ጥርዓን ከተመዝግቡን ትኽእሉ። ፈጺሙ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን።</t>
         </is>
       </c>
       <c r="G254" s="13" t="inlineStr">
         <is>
-          <t>Ilaa tan la sameeyo waxaad kaliya bixin kartaa hagaajin guud — alaabta, u-qalmitaanka iyo sida loo codsado.</t>
+          <t>Hadda waad kala hadli kartaa diiwaankooda, dukumiinti qaadan iyo cabasho diiwaangelin. Weligaa dhigasho, qaadis ama wareejin ma jirto.</t>
         </is>
       </c>
       <c r="H254" s="14" t="inlineStr"/>
@@ -15097,7 +15097,7 @@
     <row r="255" ht="44" customHeight="1">
       <c r="A255" s="11" t="inlineStr">
         <is>
-          <t>fayda_number_required</t>
+          <t>establish_who_they_are</t>
         </is>
       </c>
       <c r="B255" s="11" t="inlineStr">
@@ -15107,27 +15107,27 @@
       </c>
       <c r="C255" s="11" t="inlineStr">
         <is>
-          <t>Fayda number (required — it is what the record keeps)</t>
+          <t>Establish who they are — either one</t>
         </is>
       </c>
       <c r="D255" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ ቁጥር (ያስፈልጋል — መዝገቡ የሚይዘው ይህ ነው)</t>
+          <t>ማንነታቸውን ያረጋግጡ — አንዱ ይበቃል</t>
         </is>
       </c>
       <c r="E255" s="13" t="inlineStr">
         <is>
-          <t>Lakkoofsa Fayda (barbaachisaa — kan galmeen qabatu isa kana)</t>
+          <t>Eenyummaa isaanii mirkaneessaa — tokko ni ga'a</t>
         </is>
       </c>
       <c r="F255" s="12" t="inlineStr">
         <is>
-          <t>ቁጽሪ ፋይዳ (የድሊ — እቲ መዝገብ ዝሕዞ እዚ እዩ)</t>
+          <t>መንነቶም ኣረጋግጹ — ሓደ እኹል እዩ</t>
         </is>
       </c>
       <c r="G255" s="13" t="inlineStr">
         <is>
-          <t>Lambarka Fayda (loo baahan yahay — waa waxa diiwaanku hayo)</t>
+          <t>Ogow cidda ay yihiin — mid kasta</t>
         </is>
       </c>
       <c r="H255" s="14" t="inlineStr"/>
@@ -15135,7 +15135,7 @@
     <row r="256" ht="44" customHeight="1">
       <c r="A256" s="11" t="inlineStr">
         <is>
-          <t>download_for_translation</t>
+          <t>chk_id_document</t>
         </is>
       </c>
       <c r="B256" s="11" t="inlineStr">
@@ -15145,27 +15145,27 @@
       </c>
       <c r="C256" s="11" t="inlineStr">
         <is>
-          <t>Download for translation</t>
+          <t>Fayda ID shown and matches the account name</t>
         </is>
       </c>
       <c r="D256" s="12" t="inlineStr">
         <is>
-          <t>ለትርጉም አውርድ</t>
+          <t>የፋይዳ መታወቂያ ታይቷል እና ከሂሳቡ ስም ጋር ይዛመዳል</t>
         </is>
       </c>
       <c r="E256" s="13" t="inlineStr">
         <is>
-          <t>Hiikkaaf buufadhu</t>
+          <t>Waraqaan eenyummaa Fayda agarsiifame maqaa herregaa waliin walsimeera</t>
         </is>
       </c>
       <c r="F256" s="12" t="inlineStr">
         <is>
-          <t>ንትርጉም ኣውርድ</t>
+          <t>መንነት ፋይዳ ተራእዩን ምስ ስም ሕሳብ ይሰማማዕን</t>
         </is>
       </c>
       <c r="G256" s="13" t="inlineStr">
         <is>
-          <t>Soo dejiso turjumaadda</t>
+          <t>Aqoonsiga Fayda waa la tusay wuxuuna la mid yahay magaca xisaabta</t>
         </is>
       </c>
       <c r="H256" s="14" t="inlineStr"/>
@@ -15173,43 +15173,385 @@
     <row r="257" ht="44" customHeight="1">
       <c r="A257" s="11" t="inlineStr">
         <is>
+          <t>chk_fayda_matched</t>
+        </is>
+      </c>
+      <c r="B257" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C257" s="11" t="inlineStr">
+        <is>
+          <t>Fayda number matches the account record</t>
+        </is>
+      </c>
+      <c r="D257" s="12" t="inlineStr">
+        <is>
+          <t>የፋይዳ ቁጥር ከሂሳቡ መዝገብ ጋር ይዛመዳል</t>
+        </is>
+      </c>
+      <c r="E257" s="13" t="inlineStr">
+        <is>
+          <t>Lakkoofsi Fayda galmee herregaa waliin walsimeera</t>
+        </is>
+      </c>
+      <c r="F257" s="12" t="inlineStr">
+        <is>
+          <t>ቁጽሪ ፋይዳ ምስ መዝገብ ሕሳብ ይሰማማዕ</t>
+        </is>
+      </c>
+      <c r="G257" s="13" t="inlineStr">
+        <is>
+          <t>Lambarka Fayda wuxuu la mid yahay diiwaanka xisaabta</t>
+        </is>
+      </c>
+      <c r="H257" s="14" t="inlineStr"/>
+    </row>
+    <row r="258" ht="44" customHeight="1">
+      <c r="A258" s="11" t="inlineStr">
+        <is>
+          <t>chk_fayda_matched_note</t>
+        </is>
+      </c>
+      <c r="B258" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C258" s="11" t="inlineStr">
+        <is>
+          <t>on your own screen — works on an audio call</t>
+        </is>
+      </c>
+      <c r="D258" s="12" t="inlineStr">
+        <is>
+          <t>በራስዎ ስክሪን ላይ — በድምፅ ጥሪም ይሠራል</t>
+        </is>
+      </c>
+      <c r="E258" s="13" t="inlineStr">
+        <is>
+          <t>iskiriinii keessan irratti — bilbila sagalee irrattis ni hojjeta</t>
+        </is>
+      </c>
+      <c r="F258" s="12" t="inlineStr">
+        <is>
+          <t>ኣብ ናትኩም መርአዪ — ኣብ ናይ ድምጺ ጻውዒት እውን ይሰርሕ</t>
+        </is>
+      </c>
+      <c r="G258" s="13" t="inlineStr">
+        <is>
+          <t>shaashaddaada — wicitaan cod ahna wuu ka shaqeeyaa</t>
+        </is>
+      </c>
+      <c r="H258" s="14" t="inlineStr"/>
+    </row>
+    <row r="259" ht="44" customHeight="1">
+      <c r="A259" s="11" t="inlineStr">
+        <is>
+          <t>chk_id_photo</t>
+        </is>
+      </c>
+      <c r="B259" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C259" s="11" t="inlineStr">
+        <is>
+          <t>Photo on the ID matches the person on the call</t>
+        </is>
+      </c>
+      <c r="D259" s="12" t="inlineStr">
+        <is>
+          <t>በመታወቂያው ላይ ያለው ፎቶ ከጥሪው ላይ ካለው ሰው ጋር ይዛመዳል</t>
+        </is>
+      </c>
+      <c r="E259" s="13" t="inlineStr">
+        <is>
+          <t>Suuraan waraqaa eenyummaa irra jiru nama bilbila irra jiru waliin walsimeera</t>
+        </is>
+      </c>
+      <c r="F259" s="12" t="inlineStr">
+        <is>
+          <t>እቲ ኣብ መንነት ዘሎ ስእሊ ምስቲ ኣብ ጻውዒት ዘሎ ሰብ ይሰማማዕ</t>
+        </is>
+      </c>
+      <c r="G259" s="13" t="inlineStr">
+        <is>
+          <t>Sawirka aqoonsiga wuxuu la mid yahay qofka wicitaanka ku jira</t>
+        </is>
+      </c>
+      <c r="H259" s="14" t="inlineStr"/>
+    </row>
+    <row r="260" ht="44" customHeight="1">
+      <c r="A260" s="11" t="inlineStr">
+        <is>
+          <t>chk_video_only</t>
+        </is>
+      </c>
+      <c r="B260" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C260" s="11" t="inlineStr">
+        <is>
+          <t>video only</t>
+        </is>
+      </c>
+      <c r="D260" s="12" t="inlineStr">
+        <is>
+          <t>ቪዲዮ ብቻ</t>
+        </is>
+      </c>
+      <c r="E260" s="13" t="inlineStr">
+        <is>
+          <t>viidiyoo qofa</t>
+        </is>
+      </c>
+      <c r="F260" s="12" t="inlineStr">
+        <is>
+          <t>ቪድዮ ጥራይ</t>
+        </is>
+      </c>
+      <c r="G260" s="13" t="inlineStr">
+        <is>
+          <t>fiidyow oo kaliya</t>
+        </is>
+      </c>
+      <c r="H260" s="14" t="inlineStr"/>
+    </row>
+    <row r="261" ht="44" customHeight="1">
+      <c r="A261" s="11" t="inlineStr">
+        <is>
+          <t>confirm_account_theirs</t>
+        </is>
+      </c>
+      <c r="B261" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C261" s="11" t="inlineStr">
+        <is>
+          <t>And confirm the account is theirs</t>
+        </is>
+      </c>
+      <c r="D261" s="12" t="inlineStr">
+        <is>
+          <t>እና ሂሳቡ የእነሱ መሆኑን ያረጋግጡ</t>
+        </is>
+      </c>
+      <c r="E261" s="13" t="inlineStr">
+        <is>
+          <t>Akkasumas herregni kan isaanii ta'uu mirkaneessaa</t>
+        </is>
+      </c>
+      <c r="F261" s="12" t="inlineStr">
+        <is>
+          <t>ከምኡ'ውን እቲ ሕሳብ ናቶም ምዃኑ ኣረጋግጹ</t>
+        </is>
+      </c>
+      <c r="G261" s="13" t="inlineStr">
+        <is>
+          <t>Xaqiiji in xisaabtu tahay tooda</t>
+        </is>
+      </c>
+      <c r="H261" s="14" t="inlineStr"/>
+    </row>
+    <row r="262" ht="44" customHeight="1">
+      <c r="A262" s="11" t="inlineStr">
+        <is>
+          <t>confirm_identity</t>
+        </is>
+      </c>
+      <c r="B262" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C262" s="11" t="inlineStr">
+        <is>
+          <t>Confirm identity</t>
+        </is>
+      </c>
+      <c r="D262" s="12" t="inlineStr">
+        <is>
+          <t>ማንነት አረጋግጥ</t>
+        </is>
+      </c>
+      <c r="E262" s="13" t="inlineStr">
+        <is>
+          <t>Eenyummaa mirkaneessi</t>
+        </is>
+      </c>
+      <c r="F262" s="12" t="inlineStr">
+        <is>
+          <t>መንነት ኣረጋግጽ</t>
+        </is>
+      </c>
+      <c r="G262" s="13" t="inlineStr">
+        <is>
+          <t>Xaqiiji aqoonsiga</t>
+        </is>
+      </c>
+      <c r="H262" s="14" t="inlineStr"/>
+    </row>
+    <row r="263" ht="44" customHeight="1">
+      <c r="A263" s="11" t="inlineStr">
+        <is>
+          <t>unverified_scope</t>
+        </is>
+      </c>
+      <c r="B263" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C263" s="11" t="inlineStr">
+        <is>
+          <t>Until this is done you can only give general guidance — products, eligibility and how to apply.</t>
+        </is>
+      </c>
+      <c r="D263" s="12" t="inlineStr">
+        <is>
+          <t>ይህ እስኪከናወን ድረስ አጠቃላይ መመሪያ ብቻ መስጠት ይችላሉ — ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል።</t>
+        </is>
+      </c>
+      <c r="E263" s="13" t="inlineStr">
+        <is>
+          <t>Hanga kun raawwatutti qajeelfama waliigalaa qofa kennuu dandeessu — oomishaalee, ulaagaa fi akkaataa itti iyyatan.</t>
+        </is>
+      </c>
+      <c r="F263" s="12" t="inlineStr">
+        <is>
+          <t>እዚ ክሳብ ዝፍጸም ሓፈሻዊ መምርሒ ጥራይ ክትህቡ ትኽእሉ — ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን።</t>
+        </is>
+      </c>
+      <c r="G263" s="13" t="inlineStr">
+        <is>
+          <t>Ilaa tan la sameeyo waxaad kaliya bixin kartaa hagaajin guud — alaabta, u-qalmitaanka iyo sida loo codsado.</t>
+        </is>
+      </c>
+      <c r="H263" s="14" t="inlineStr"/>
+    </row>
+    <row r="264" ht="44" customHeight="1">
+      <c r="A264" s="11" t="inlineStr">
+        <is>
+          <t>fayda_number_required</t>
+        </is>
+      </c>
+      <c r="B264" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C264" s="11" t="inlineStr">
+        <is>
+          <t>Fayda number (required — it is what the record keeps)</t>
+        </is>
+      </c>
+      <c r="D264" s="12" t="inlineStr">
+        <is>
+          <t>የፋይዳ ቁጥር (ያስፈልጋል — መዝገቡ የሚይዘው ይህ ነው)</t>
+        </is>
+      </c>
+      <c r="E264" s="13" t="inlineStr">
+        <is>
+          <t>Lakkoofsa Fayda (barbaachisaa — kan galmeen qabatu isa kana)</t>
+        </is>
+      </c>
+      <c r="F264" s="12" t="inlineStr">
+        <is>
+          <t>ቁጽሪ ፋይዳ (የድሊ — እቲ መዝገብ ዝሕዞ እዚ እዩ)</t>
+        </is>
+      </c>
+      <c r="G264" s="13" t="inlineStr">
+        <is>
+          <t>Lambarka Fayda (loo baahan yahay — waa waxa diiwaanku hayo)</t>
+        </is>
+      </c>
+      <c r="H264" s="14" t="inlineStr"/>
+    </row>
+    <row r="265" ht="44" customHeight="1">
+      <c r="A265" s="11" t="inlineStr">
+        <is>
+          <t>download_for_translation</t>
+        </is>
+      </c>
+      <c r="B265" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C265" s="11" t="inlineStr">
+        <is>
+          <t>Download for translation</t>
+        </is>
+      </c>
+      <c r="D265" s="12" t="inlineStr">
+        <is>
+          <t>ለትርጉም አውርድ</t>
+        </is>
+      </c>
+      <c r="E265" s="13" t="inlineStr">
+        <is>
+          <t>Hiikkaaf buufadhu</t>
+        </is>
+      </c>
+      <c r="F265" s="12" t="inlineStr">
+        <is>
+          <t>ንትርጉም ኣውርድ</t>
+        </is>
+      </c>
+      <c r="G265" s="13" t="inlineStr">
+        <is>
+          <t>Soo dejiso turjumaadda</t>
+        </is>
+      </c>
+      <c r="H265" s="14" t="inlineStr"/>
+    </row>
+    <row r="266" ht="44" customHeight="1">
+      <c r="A266" s="11" t="inlineStr">
+        <is>
           <t>nothing_to_download</t>
         </is>
       </c>
-      <c r="B257" s="11" t="inlineStr">
-        <is>
-          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
-        </is>
-      </c>
-      <c r="C257" s="11" t="inlineStr">
+      <c r="B266" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C266" s="11" t="inlineStr">
         <is>
           <t>No approved answers to download yet.</t>
         </is>
       </c>
-      <c r="D257" s="12" t="inlineStr">
+      <c r="D266" s="12" t="inlineStr">
         <is>
           <t>እስካሁን የሚወርድ የተፈቀደ መልስ የለም።</t>
         </is>
       </c>
-      <c r="E257" s="13" t="inlineStr">
+      <c r="E266" s="13" t="inlineStr">
         <is>
           <t>Hanga ammaatti deebiin mirkanaa'e buufamu hin jiru.</t>
         </is>
       </c>
-      <c r="F257" s="12" t="inlineStr">
+      <c r="F266" s="12" t="inlineStr">
         <is>
           <t>ክሳብ ሕጂ ዝወርድ ዝጸደቐ መልሲ የለን።</t>
         </is>
       </c>
-      <c r="G257" s="13" t="inlineStr">
+      <c r="G266" s="13" t="inlineStr">
         <is>
           <t>Weli ma jiraan jawaabo la ansixiyay oo la soo dejiyo.</t>
         </is>
       </c>
-      <c r="H257" s="14" t="inlineStr"/>
+      <c r="H266" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H257"/>
+  <autoFilter ref="A1:H266"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/review/Olink_Bank_Assist_language_review.xlsx
+++ b/review/Olink_Bank_Assist_language_review.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1. What the assistant says'!$A$1:$H$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2. What it understands'!$A$1:$E$78</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3. Buttons customers see'!$A$1:$H$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$H$266</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$H$267</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -752,7 +752,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>334 strings in 5 languages</t>
+          <t>335 strings in 5 languages</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H266"/>
+  <dimension ref="A1:H267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -11525,7 +11525,7 @@
     <row r="161" ht="44" customHeight="1">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>no_calls_taken_yet</t>
+          <t>unit_call</t>
         </is>
       </c>
       <c r="B161" s="11" t="inlineStr">
@@ -11535,27 +11535,27 @@
       </c>
       <c r="C161" s="11" t="inlineStr">
         <is>
-          <t>Nobody has taken a call yet in this window.</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>በዚህ ጊዜ ውስጥ ማንም ጥሪ አልያዘም።</t>
+          <t>ጥሪ</t>
         </is>
       </c>
       <c r="E161" s="13" t="inlineStr">
         <is>
-          <t>Yeroo kana keessatti namni bilbila fudhate hin jiru.</t>
+          <t>bilbila</t>
         </is>
       </c>
       <c r="F161" s="12" t="inlineStr">
         <is>
-          <t>ኣብዚ እዋን'ዚ ዝሓዘ ጻውዒት የለን።</t>
+          <t>ጻውዒት</t>
         </is>
       </c>
       <c r="G161" s="13" t="inlineStr">
         <is>
-          <t>Cidina ma qaadan wicitaan waqtigan.</t>
+          <t>wicitaan</t>
         </is>
       </c>
       <c r="H161" s="14" t="inlineStr"/>
@@ -11563,7 +11563,7 @@
     <row r="162" ht="44" customHeight="1">
       <c r="A162" s="11" t="inlineStr">
         <is>
-          <t>call_resolved</t>
+          <t>no_calls_taken_yet</t>
         </is>
       </c>
       <c r="B162" s="11" t="inlineStr">
@@ -11573,27 +11573,27 @@
       </c>
       <c r="C162" s="11" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Nobody has taken a call yet in this window.</t>
         </is>
       </c>
       <c r="D162" s="12" t="inlineStr">
         <is>
-          <t>ተፈትቷል</t>
+          <t>በዚህ ጊዜ ውስጥ ማንም ጥሪ አልያዘም።</t>
         </is>
       </c>
       <c r="E162" s="13" t="inlineStr">
         <is>
-          <t>Furameera</t>
+          <t>Yeroo kana keessatti namni bilbila fudhate hin jiru.</t>
         </is>
       </c>
       <c r="F162" s="12" t="inlineStr">
         <is>
-          <t>ተፈቲሑ</t>
+          <t>ኣብዚ እዋን'ዚ ዝሓዘ ጻውዒት የለን።</t>
         </is>
       </c>
       <c r="G162" s="13" t="inlineStr">
         <is>
-          <t>La xaliyay</t>
+          <t>Cidina ma qaadan wicitaan waqtigan.</t>
         </is>
       </c>
       <c r="H162" s="14" t="inlineStr"/>
@@ -11601,7 +11601,7 @@
     <row r="163" ht="44" customHeight="1">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>call_dropped</t>
+          <t>call_resolved</t>
         </is>
       </c>
       <c r="B163" s="11" t="inlineStr">
@@ -11611,27 +11611,27 @@
       </c>
       <c r="C163" s="11" t="inlineStr">
         <is>
-          <t>Dropped (technical issue)</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>ተቋርጧል (ቴክኒካዊ ችግር)</t>
+          <t>ተፈትቷል</t>
         </is>
       </c>
       <c r="E163" s="13" t="inlineStr">
         <is>
-          <t>Cite (rakkoo teekniikaa)</t>
+          <t>Furameera</t>
         </is>
       </c>
       <c r="F163" s="12" t="inlineStr">
         <is>
-          <t>ተቋሪጹ (ቴክኒካዊ ጸገም)</t>
+          <t>ተፈቲሑ</t>
         </is>
       </c>
       <c r="G163" s="13" t="inlineStr">
         <is>
-          <t>Wuu jabay (dhibaato farsamo)</t>
+          <t>La xaliyay</t>
         </is>
       </c>
       <c r="H163" s="14" t="inlineStr"/>
@@ -11639,7 +11639,7 @@
     <row r="164" ht="44" customHeight="1">
       <c r="A164" s="11" t="inlineStr">
         <is>
-          <t>avg_wait_before_answering</t>
+          <t>call_dropped</t>
         </is>
       </c>
       <c r="B164" s="11" t="inlineStr">
@@ -11649,27 +11649,27 @@
       </c>
       <c r="C164" s="11" t="inlineStr">
         <is>
-          <t>Avg. wait before answering:</t>
+          <t>Dropped (technical issue)</t>
         </is>
       </c>
       <c r="D164" s="12" t="inlineStr">
         <is>
-          <t>ከመመለስ በፊት አማካይ የመጠበቅ ጊዜ፦</t>
+          <t>ተቋርጧል (ቴክኒካዊ ችግር)</t>
         </is>
       </c>
       <c r="E164" s="13" t="inlineStr">
         <is>
-          <t>Giddu-galeessa yeroo eegumsaa deebii dura:</t>
+          <t>Cite (rakkoo teekniikaa)</t>
         </is>
       </c>
       <c r="F164" s="12" t="inlineStr">
         <is>
-          <t>ማእከላይ ግዜ ምጽባይ ቅድሚ ምምላስ፦</t>
+          <t>ተቋሪጹ (ቴክኒካዊ ጸገም)</t>
         </is>
       </c>
       <c r="G164" s="13" t="inlineStr">
         <is>
-          <t>Celceliska sugitaanka ka hor jawaabta:</t>
+          <t>Wuu jabay (dhibaato farsamo)</t>
         </is>
       </c>
       <c r="H164" s="14" t="inlineStr"/>
@@ -11677,7 +11677,7 @@
     <row r="165" ht="44" customHeight="1">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>no_calls_yet_window</t>
+          <t>avg_wait_before_answering</t>
         </is>
       </c>
       <c r="B165" s="11" t="inlineStr">
@@ -11687,27 +11687,27 @@
       </c>
       <c r="C165" s="11" t="inlineStr">
         <is>
-          <t>No calls yet in this window.</t>
+          <t>Avg. wait before answering:</t>
         </is>
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>በዚህ ጊዜ ውስጥ ጥሪ የለም።</t>
+          <t>ከመመለስ በፊት አማካይ የመጠበቅ ጊዜ፦</t>
         </is>
       </c>
       <c r="E165" s="13" t="inlineStr">
         <is>
-          <t>Yeroo kana keessatti bilbilli hin jiru.</t>
+          <t>Giddu-galeessa yeroo eegumsaa deebii dura:</t>
         </is>
       </c>
       <c r="F165" s="12" t="inlineStr">
         <is>
-          <t>ኣብዚ እዋን'ዚ ጻውዒት የለን።</t>
+          <t>ማእከላይ ግዜ ምጽባይ ቅድሚ ምምላስ፦</t>
         </is>
       </c>
       <c r="G165" s="13" t="inlineStr">
         <is>
-          <t>Wicitaan lama helin waqtigan.</t>
+          <t>Celceliska sugitaanka ka hor jawaabta:</t>
         </is>
       </c>
       <c r="H165" s="14" t="inlineStr"/>
@@ -11715,7 +11715,7 @@
     <row r="166" ht="44" customHeight="1">
       <c r="A166" s="11" t="inlineStr">
         <is>
-          <t>your_performance</t>
+          <t>no_calls_yet_window</t>
         </is>
       </c>
       <c r="B166" s="11" t="inlineStr">
@@ -11725,27 +11725,27 @@
       </c>
       <c r="C166" s="11" t="inlineStr">
         <is>
-          <t>Your performance</t>
+          <t>No calls yet in this window.</t>
         </is>
       </c>
       <c r="D166" s="12" t="inlineStr">
         <is>
-          <t>የእርስዎ አፈጻጸም</t>
+          <t>በዚህ ጊዜ ውስጥ ጥሪ የለም።</t>
         </is>
       </c>
       <c r="E166" s="13" t="inlineStr">
         <is>
-          <t>Hojii kee</t>
+          <t>Yeroo kana keessatti bilbilli hin jiru.</t>
         </is>
       </c>
       <c r="F166" s="12" t="inlineStr">
         <is>
-          <t>ኣፈጻጽማኻ</t>
+          <t>ኣብዚ እዋን'ዚ ጻውዒት የለን።</t>
         </is>
       </c>
       <c r="G166" s="13" t="inlineStr">
         <is>
-          <t>Waxqabadkaaga</t>
+          <t>Wicitaan lama helin waqtigan.</t>
         </is>
       </c>
       <c r="H166" s="14" t="inlineStr"/>
@@ -11753,7 +11753,7 @@
     <row r="167" ht="44" customHeight="1">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>n_other_tellers</t>
+          <t>your_performance</t>
         </is>
       </c>
       <c r="B167" s="11" t="inlineStr">
@@ -11763,27 +11763,27 @@
       </c>
       <c r="C167" s="11" t="inlineStr">
         <is>
-          <t>{n} other tellers</t>
+          <t>Your performance</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>{n} ሌሎች ተጠሪዎች</t>
+          <t>የእርስዎ አፈጻጸም</t>
         </is>
       </c>
       <c r="E167" s="13" t="inlineStr">
         <is>
-          <t>{n} teellaroota biroo</t>
+          <t>Hojii kee</t>
         </is>
       </c>
       <c r="F167" s="12" t="inlineStr">
         <is>
-          <t>{n} ካልኦት ተለራት</t>
+          <t>ኣፈጻጽማኻ</t>
         </is>
       </c>
       <c r="G167" s="13" t="inlineStr">
         <is>
-          <t>{n} teller oo kale</t>
+          <t>Waxqabadkaaga</t>
         </is>
       </c>
       <c r="H167" s="14" t="inlineStr"/>
@@ -11791,7 +11791,7 @@
     <row r="168" ht="44" customHeight="1">
       <c r="A168" s="11" t="inlineStr">
         <is>
-          <t>built_in</t>
+          <t>n_other_tellers</t>
         </is>
       </c>
       <c r="B168" s="11" t="inlineStr">
@@ -11801,27 +11801,27 @@
       </c>
       <c r="C168" s="11" t="inlineStr">
         <is>
-          <t>built-in</t>
+          <t>{n} other tellers</t>
         </is>
       </c>
       <c r="D168" s="12" t="inlineStr">
         <is>
-          <t>አብሮ የተሰራ</t>
+          <t>{n} ሌሎች ተጠሪዎች</t>
         </is>
       </c>
       <c r="E168" s="13" t="inlineStr">
         <is>
-          <t>kan ijaarame</t>
+          <t>{n} teellaroota biroo</t>
         </is>
       </c>
       <c r="F168" s="12" t="inlineStr">
         <is>
-          <t>ውሁድ</t>
+          <t>{n} ካልኦት ተለራት</t>
         </is>
       </c>
       <c r="G168" s="13" t="inlineStr">
         <is>
-          <t>ku dhex jira</t>
+          <t>{n} teller oo kale</t>
         </is>
       </c>
       <c r="H168" s="14" t="inlineStr"/>
@@ -11829,7 +11829,7 @@
     <row r="169" ht="44" customHeight="1">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>add_a_person</t>
+          <t>built_in</t>
         </is>
       </c>
       <c r="B169" s="11" t="inlineStr">
@@ -11839,27 +11839,27 @@
       </c>
       <c r="C169" s="11" t="inlineStr">
         <is>
-          <t>Add a person</t>
+          <t>built-in</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>ሰው ጨምር</t>
+          <t>አብሮ የተሰራ</t>
         </is>
       </c>
       <c r="E169" s="13" t="inlineStr">
         <is>
-          <t>Nama dabali</t>
+          <t>kan ijaarame</t>
         </is>
       </c>
       <c r="F169" s="12" t="inlineStr">
         <is>
-          <t>ሰብ ወስኽ</t>
+          <t>ውሁድ</t>
         </is>
       </c>
       <c r="G169" s="13" t="inlineStr">
         <is>
-          <t>Qof ku dar</t>
+          <t>ku dhex jira</t>
         </is>
       </c>
       <c r="H169" s="14" t="inlineStr"/>
@@ -11867,7 +11867,7 @@
     <row r="170" ht="44" customHeight="1">
       <c r="A170" s="11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>add_a_person</t>
         </is>
       </c>
       <c r="B170" s="11" t="inlineStr">
@@ -11877,27 +11877,27 @@
       </c>
       <c r="C170" s="11" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Add a person</t>
         </is>
       </c>
       <c r="D170" s="12" t="inlineStr">
         <is>
-          <t>ኢሜይል</t>
+          <t>ሰው ጨምር</t>
         </is>
       </c>
       <c r="E170" s="13" t="inlineStr">
         <is>
-          <t>Imeelii</t>
+          <t>Nama dabali</t>
         </is>
       </c>
       <c r="F170" s="12" t="inlineStr">
         <is>
-          <t>ኢመይል</t>
+          <t>ሰብ ወስኽ</t>
         </is>
       </c>
       <c r="G170" s="13" t="inlineStr">
         <is>
-          <t>Iimayl</t>
+          <t>Qof ku dar</t>
         </is>
       </c>
       <c r="H170" s="14" t="inlineStr"/>
@@ -11905,7 +11905,7 @@
     <row r="171" ht="44" customHeight="1">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>name_optional</t>
+          <t>email</t>
         </is>
       </c>
       <c r="B171" s="11" t="inlineStr">
@@ -11915,27 +11915,27 @@
       </c>
       <c r="C171" s="11" t="inlineStr">
         <is>
-          <t>Name (optional)</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>ስም (አማራጭ)</t>
+          <t>ኢሜይል</t>
         </is>
       </c>
       <c r="E171" s="13" t="inlineStr">
         <is>
-          <t>Maqaa (filannoo)</t>
+          <t>Imeelii</t>
         </is>
       </c>
       <c r="F171" s="12" t="inlineStr">
         <is>
-          <t>ስም (ኣማራጺ)</t>
+          <t>ኢመይል</t>
         </is>
       </c>
       <c r="G171" s="13" t="inlineStr">
         <is>
-          <t>Magac (ikhtiyaari)</t>
+          <t>Iimayl</t>
         </is>
       </c>
       <c r="H171" s="14" t="inlineStr"/>
@@ -11943,7 +11943,7 @@
     <row r="172" ht="44" customHeight="1">
       <c r="A172" s="11" t="inlineStr">
         <is>
-          <t>temporary_password</t>
+          <t>name_optional</t>
         </is>
       </c>
       <c r="B172" s="11" t="inlineStr">
@@ -11953,27 +11953,27 @@
       </c>
       <c r="C172" s="11" t="inlineStr">
         <is>
-          <t>Temporary password</t>
+          <t>Name (optional)</t>
         </is>
       </c>
       <c r="D172" s="12" t="inlineStr">
         <is>
-          <t>ጊዜያዊ የይለፍ ቃል</t>
+          <t>ስም (አማራጭ)</t>
         </is>
       </c>
       <c r="E172" s="13" t="inlineStr">
         <is>
-          <t>Jecha darbii yeroo</t>
+          <t>Maqaa (filannoo)</t>
         </is>
       </c>
       <c r="F172" s="12" t="inlineStr">
         <is>
-          <t>ግዝያዊ መሕለፊ ቃል</t>
+          <t>ስም (ኣማራጺ)</t>
         </is>
       </c>
       <c r="G172" s="13" t="inlineStr">
         <is>
-          <t>Fure ku meel gaar ah</t>
+          <t>Magac (ikhtiyaari)</t>
         </is>
       </c>
       <c r="H172" s="14" t="inlineStr"/>
@@ -11981,7 +11981,7 @@
     <row r="173" ht="44" customHeight="1">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>temp_password_help</t>
+          <t>temporary_password</t>
         </is>
       </c>
       <c r="B173" s="11" t="inlineStr">
@@ -11991,27 +11991,27 @@
       </c>
       <c r="C173" s="11" t="inlineStr">
         <is>
-          <t>At least 12 characters. Until invitation emails are set up, this password has to be given to them directly — which is why it is shown here rather than hidden.</t>
+          <t>Temporary password</t>
         </is>
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>ቢያንስ 12 ቁምፊ። የግብዣ ኢሜይሎች እስኪዘጋጁ ድረስ ይህ የይለፍ ቃል በቀጥታ ሊሰጣቸው ይገባል — ስለዚህ ተደብቆ ሳይሆን እዚህ ይታያል።</t>
+          <t>ጊዜያዊ የይለፍ ቃል</t>
         </is>
       </c>
       <c r="E173" s="13" t="inlineStr">
         <is>
-          <t>Yoo xiqqaate arfiilee 12. Hanga imeeliin afeerraa qophaa'utti, jechi darbii kun kallattiin isaaniif kennamuu qaba — kanaafuu dhokfamuu mannaa asitti ni mul'ata.</t>
+          <t>Jecha darbii yeroo</t>
         </is>
       </c>
       <c r="F173" s="12" t="inlineStr">
         <is>
-          <t>ብውሑዱ 12 ፊደላት። መጸዋዕታ ኢመይል ክሳብ ዝዳሎ እዚ መሕለፊ ቃል ብቐጥታ ክወሃቦም ኣለዎ — ስለዚ ተሓቢኡ ዘይኮነ ኣብዚ ይረአ።</t>
+          <t>ግዝያዊ መሕለፊ ቃል</t>
         </is>
       </c>
       <c r="G173" s="13" t="inlineStr">
         <is>
-          <t>Ugu yaraan 12 xaraf. Ilaa iimaylada casumaadda la dejiyo, furahan si toos ah ayaa loo siin doonaa — sidaas darteed halkan ayuu ka muuqdaa halkii la qarin lahaa.</t>
+          <t>Fure ku meel gaar ah</t>
         </is>
       </c>
       <c r="H173" s="14" t="inlineStr"/>
@@ -12019,7 +12019,7 @@
     <row r="174" ht="44" customHeight="1">
       <c r="A174" s="11" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>temp_password_help</t>
         </is>
       </c>
       <c r="B174" s="11" t="inlineStr">
@@ -12029,27 +12029,27 @@
       </c>
       <c r="C174" s="11" t="inlineStr">
         <is>
-          <t>Create</t>
+          <t>At least 12 characters. Until invitation emails are set up, this password has to be given to them directly — which is why it is shown here rather than hidden.</t>
         </is>
       </c>
       <c r="D174" s="12" t="inlineStr">
         <is>
-          <t>ፍጠር</t>
+          <t>ቢያንስ 12 ቁምፊ። የግብዣ ኢሜይሎች እስኪዘጋጁ ድረስ ይህ የይለፍ ቃል በቀጥታ ሊሰጣቸው ይገባል — ስለዚህ ተደብቆ ሳይሆን እዚህ ይታያል።</t>
         </is>
       </c>
       <c r="E174" s="13" t="inlineStr">
         <is>
-          <t>Uumi</t>
+          <t>Yoo xiqqaate arfiilee 12. Hanga imeeliin afeerraa qophaa'utti, jechi darbii kun kallattiin isaaniif kennamuu qaba — kanaafuu dhokfamuu mannaa asitti ni mul'ata.</t>
         </is>
       </c>
       <c r="F174" s="12" t="inlineStr">
         <is>
-          <t>ፍጠር</t>
+          <t>ብውሑዱ 12 ፊደላት። መጸዋዕታ ኢመይል ክሳብ ዝዳሎ እዚ መሕለፊ ቃል ብቐጥታ ክወሃቦም ኣለዎ — ስለዚ ተሓቢኡ ዘይኮነ ኣብዚ ይረአ።</t>
         </is>
       </c>
       <c r="G174" s="13" t="inlineStr">
         <is>
-          <t>Abuur</t>
+          <t>Ugu yaraan 12 xaraf. Ilaa iimaylada casumaadda la dejiyo, furahan si toos ah ayaa loo siin doonaa — sidaas darteed halkan ayuu ka muuqdaa halkii la qarin lahaa.</t>
         </is>
       </c>
       <c r="H174" s="14" t="inlineStr"/>
@@ -12057,7 +12057,7 @@
     <row r="175" ht="44" customHeight="1">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>account_created</t>
+          <t>create</t>
         </is>
       </c>
       <c r="B175" s="11" t="inlineStr">
@@ -12067,27 +12067,27 @@
       </c>
       <c r="C175" s="11" t="inlineStr">
         <is>
-          <t>Account created</t>
+          <t>Create</t>
         </is>
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>መለያ ተፈጥሯል</t>
+          <t>ፍጠር</t>
         </is>
       </c>
       <c r="E175" s="13" t="inlineStr">
         <is>
-          <t>Herregni uumame</t>
+          <t>Uumi</t>
         </is>
       </c>
       <c r="F175" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ ተፈጢሩ</t>
+          <t>ፍጠር</t>
         </is>
       </c>
       <c r="G175" s="13" t="inlineStr">
         <is>
-          <t>Xisaab waa la abuuray</t>
+          <t>Abuur</t>
         </is>
       </c>
       <c r="H175" s="14" t="inlineStr"/>
@@ -12095,7 +12095,7 @@
     <row r="176" ht="44" customHeight="1">
       <c r="A176" s="11" t="inlineStr">
         <is>
-          <t>account_restored</t>
+          <t>account_created</t>
         </is>
       </c>
       <c r="B176" s="11" t="inlineStr">
@@ -12105,27 +12105,27 @@
       </c>
       <c r="C176" s="11" t="inlineStr">
         <is>
-          <t>Account restored</t>
+          <t>Account created</t>
         </is>
       </c>
       <c r="D176" s="12" t="inlineStr">
         <is>
-          <t>መለያ ተመልሷል</t>
+          <t>መለያ ተፈጥሯል</t>
         </is>
       </c>
       <c r="E176" s="13" t="inlineStr">
         <is>
-          <t>Herregni deebi'e</t>
+          <t>Herregni uumame</t>
         </is>
       </c>
       <c r="F176" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ ተመሊሱ</t>
+          <t>ሕሳብ ተፈጢሩ</t>
         </is>
       </c>
       <c r="G176" s="13" t="inlineStr">
         <is>
-          <t>Xisaabta waa la soo celiyay</t>
+          <t>Xisaab waa la abuuray</t>
         </is>
       </c>
       <c r="H176" s="14" t="inlineStr"/>
@@ -12133,7 +12133,7 @@
     <row r="177" ht="44" customHeight="1">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>account_disabled_n</t>
+          <t>account_restored</t>
         </is>
       </c>
       <c r="B177" s="11" t="inlineStr">
@@ -12143,27 +12143,27 @@
       </c>
       <c r="C177" s="11" t="inlineStr">
         <is>
-          <t>Account disabled, {n} session(s) ended</t>
+          <t>Account restored</t>
         </is>
       </c>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>መለያ ተሰናክሏል፤ {n} ክፍለ-ጊዜ ተዘግቷል</t>
+          <t>መለያ ተመልሷል</t>
         </is>
       </c>
       <c r="E177" s="13" t="inlineStr">
         <is>
-          <t>Herregni dhaabame, session {n} xumurame</t>
+          <t>Herregni deebi'e</t>
         </is>
       </c>
       <c r="F177" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ ተዓጊቱ፣ {n} ክፍለ-ግዜ ተዛዚሙ</t>
+          <t>ሕሳብ ተመሊሱ</t>
         </is>
       </c>
       <c r="G177" s="13" t="inlineStr">
         <is>
-          <t>Xisaabta waa la demiyay, {n} kalfadhi ayaa dhammaaday</t>
+          <t>Xisaabta waa la soo celiyay</t>
         </is>
       </c>
       <c r="H177" s="14" t="inlineStr"/>
@@ -12171,7 +12171,7 @@
     <row r="178" ht="44" customHeight="1">
       <c r="A178" s="11" t="inlineStr">
         <is>
-          <t>confirm_disable_account</t>
+          <t>account_disabled_n</t>
         </is>
       </c>
       <c r="B178" s="11" t="inlineStr">
@@ -12181,27 +12181,27 @@
       </c>
       <c r="C178" s="11" t="inlineStr">
         <is>
-          <t>Disable this account? They will be signed out immediately.</t>
+          <t>Account disabled, {n} session(s) ended</t>
         </is>
       </c>
       <c r="D178" s="12" t="inlineStr">
         <is>
-          <t>ይህን መለያ ማሰናከል? ወዲያውኑ ይወጣሉ።</t>
+          <t>መለያ ተሰናክሏል፤ {n} ክፍለ-ጊዜ ተዘግቷል</t>
         </is>
       </c>
       <c r="E178" s="13" t="inlineStr">
         <is>
-          <t>Herrega kana dhaabuu? Battalumatti ni baafamu.</t>
+          <t>Herregni dhaabame, session {n} xumurame</t>
         </is>
       </c>
       <c r="F178" s="12" t="inlineStr">
         <is>
-          <t>ነዚ ሕሳብ ክዕገት? ብቕጽበት ይወጹ።</t>
+          <t>ሕሳብ ተዓጊቱ፣ {n} ክፍለ-ግዜ ተዛዚሙ</t>
         </is>
       </c>
       <c r="G178" s="13" t="inlineStr">
         <is>
-          <t>Xisaabtan ma demineysaa? Isla markiiba waa laga saarayaa.</t>
+          <t>Xisaabta waa la demiyay, {n} kalfadhi ayaa dhammaaday</t>
         </is>
       </c>
       <c r="H178" s="14" t="inlineStr"/>
@@ -12209,7 +12209,7 @@
     <row r="179" ht="44" customHeight="1">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>action_document_created</t>
+          <t>confirm_disable_account</t>
         </is>
       </c>
       <c r="B179" s="11" t="inlineStr">
@@ -12219,27 +12219,27 @@
       </c>
       <c r="C179" s="11" t="inlineStr">
         <is>
-          <t>added an article</t>
+          <t>Disable this account? They will be signed out immediately.</t>
         </is>
       </c>
       <c r="D179" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ጨምሯል</t>
+          <t>ይህን መለያ ማሰናከል? ወዲያውኑ ይወጣሉ።</t>
         </is>
       </c>
       <c r="E179" s="13" t="inlineStr">
         <is>
-          <t>barruu dabale</t>
+          <t>Herrega kana dhaabuu? Battalumatti ni baafamu.</t>
         </is>
       </c>
       <c r="F179" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ወሲኹ</t>
+          <t>ነዚ ሕሳብ ክዕገት? ብቕጽበት ይወጹ።</t>
         </is>
       </c>
       <c r="G179" s="13" t="inlineStr">
         <is>
-          <t>maqaal ku daray</t>
+          <t>Xisaabtan ma demineysaa? Isla markiiba waa laga saarayaa.</t>
         </is>
       </c>
       <c r="H179" s="14" t="inlineStr"/>
@@ -12247,7 +12247,7 @@
     <row r="180" ht="44" customHeight="1">
       <c r="A180" s="11" t="inlineStr">
         <is>
-          <t>action_document_updated</t>
+          <t>action_document_created</t>
         </is>
       </c>
       <c r="B180" s="11" t="inlineStr">
@@ -12257,27 +12257,27 @@
       </c>
       <c r="C180" s="11" t="inlineStr">
         <is>
-          <t>edited an article</t>
+          <t>added an article</t>
         </is>
       </c>
       <c r="D180" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ አርሟል</t>
+          <t>ጽሑፍ ጨምሯል</t>
         </is>
       </c>
       <c r="E180" s="13" t="inlineStr">
         <is>
-          <t>barruu gulaale</t>
+          <t>barruu dabale</t>
         </is>
       </c>
       <c r="F180" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ኣርሚዑ</t>
+          <t>ጽሑፍ ወሲኹ</t>
         </is>
       </c>
       <c r="G180" s="13" t="inlineStr">
         <is>
-          <t>maqaal wax ka beddelay</t>
+          <t>maqaal ku daray</t>
         </is>
       </c>
       <c r="H180" s="14" t="inlineStr"/>
@@ -12285,7 +12285,7 @@
     <row r="181" ht="44" customHeight="1">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t>action_document_deleted</t>
+          <t>action_document_updated</t>
         </is>
       </c>
       <c r="B181" s="11" t="inlineStr">
@@ -12295,27 +12295,27 @@
       </c>
       <c r="C181" s="11" t="inlineStr">
         <is>
-          <t>deleted an article</t>
+          <t>edited an article</t>
         </is>
       </c>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ሰርዟል</t>
+          <t>ጽሑፍ አርሟል</t>
         </is>
       </c>
       <c r="E181" s="13" t="inlineStr">
         <is>
-          <t>barruu haqe</t>
+          <t>barruu gulaale</t>
         </is>
       </c>
       <c r="F181" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ደምሲሱ</t>
+          <t>ጽሑፍ ኣርሚዑ</t>
         </is>
       </c>
       <c r="G181" s="13" t="inlineStr">
         <is>
-          <t>maqaal tirtiray</t>
+          <t>maqaal wax ka beddelay</t>
         </is>
       </c>
       <c r="H181" s="14" t="inlineStr"/>
@@ -12323,7 +12323,7 @@
     <row r="182" ht="44" customHeight="1">
       <c r="A182" s="11" t="inlineStr">
         <is>
-          <t>action_documents_bulk_imported</t>
+          <t>action_document_deleted</t>
         </is>
       </c>
       <c r="B182" s="11" t="inlineStr">
@@ -12333,27 +12333,27 @@
       </c>
       <c r="C182" s="11" t="inlineStr">
         <is>
-          <t>imported articles</t>
+          <t>deleted an article</t>
         </is>
       </c>
       <c r="D182" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፎችን አስገብቷል</t>
+          <t>ጽሑፍ ሰርዟል</t>
         </is>
       </c>
       <c r="E182" s="13" t="inlineStr">
         <is>
-          <t>barruulee galche</t>
+          <t>barruu haqe</t>
         </is>
       </c>
       <c r="F182" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፋት ኣእትዩ</t>
+          <t>ጽሑፍ ደምሲሱ</t>
         </is>
       </c>
       <c r="G182" s="13" t="inlineStr">
         <is>
-          <t>maqaallo soo dhoofiyay</t>
+          <t>maqaal tirtiray</t>
         </is>
       </c>
       <c r="H182" s="14" t="inlineStr"/>
@@ -12361,7 +12361,7 @@
     <row r="183" ht="44" customHeight="1">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_closed</t>
+          <t>action_documents_bulk_imported</t>
         </is>
       </c>
       <c r="B183" s="11" t="inlineStr">
@@ -12371,27 +12371,27 @@
       </c>
       <c r="C183" s="11" t="inlineStr">
         <is>
-          <t>closed an escalation</t>
+          <t>imported articles</t>
         </is>
       </c>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ ዘግቷል</t>
+          <t>ጽሑፎችን አስገብቷል</t>
         </is>
       </c>
       <c r="E183" s="13" t="inlineStr">
         <is>
-          <t>dhimma cufe</t>
+          <t>barruulee galche</t>
         </is>
       </c>
       <c r="F183" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ ዓጺዩ</t>
+          <t>ጽሑፋት ኣእትዩ</t>
         </is>
       </c>
       <c r="G183" s="13" t="inlineStr">
         <is>
-          <t>arrin xiray</t>
+          <t>maqaallo soo dhoofiyay</t>
         </is>
       </c>
       <c r="H183" s="14" t="inlineStr"/>
@@ -12399,7 +12399,7 @@
     <row r="184" ht="44" customHeight="1">
       <c r="A184" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_reopened</t>
+          <t>action_handoff_closed</t>
         </is>
       </c>
       <c r="B184" s="11" t="inlineStr">
@@ -12409,27 +12409,27 @@
       </c>
       <c r="C184" s="11" t="inlineStr">
         <is>
-          <t>reopened an escalation</t>
+          <t>closed an escalation</t>
         </is>
       </c>
       <c r="D184" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ በድጋሚ ከፍቷል</t>
+          <t>ጉዳይ ዘግቷል</t>
         </is>
       </c>
       <c r="E184" s="13" t="inlineStr">
         <is>
-          <t>dhimma irra deebi'ee bane</t>
+          <t>dhimma cufe</t>
         </is>
       </c>
       <c r="F184" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ ደጊሙ ከፊቱ</t>
+          <t>ጉዳይ ዓጺዩ</t>
         </is>
       </c>
       <c r="G184" s="13" t="inlineStr">
         <is>
-          <t>arrin dib u furay</t>
+          <t>arrin xiray</t>
         </is>
       </c>
       <c r="H184" s="14" t="inlineStr"/>
@@ -12437,7 +12437,7 @@
     <row r="185" ht="44" customHeight="1">
       <c r="A185" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_webhook_connected</t>
+          <t>action_handoff_reopened</t>
         </is>
       </c>
       <c r="B185" s="11" t="inlineStr">
@@ -12447,27 +12447,27 @@
       </c>
       <c r="C185" s="11" t="inlineStr">
         <is>
-          <t>connected the escalation webhook</t>
+          <t>reopened an escalation</t>
         </is>
       </c>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ዌብሁክ አገናኝቷል</t>
+          <t>ጉዳይ በድጋሚ ከፍቷል</t>
         </is>
       </c>
       <c r="E185" s="13" t="inlineStr">
         <is>
-          <t>webhook dabarsaa walqunnamsiise</t>
+          <t>dhimma irra deebi'ee bane</t>
         </is>
       </c>
       <c r="F185" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ምትሕልላፍ ኣራኺቡ</t>
+          <t>ጉዳይ ደጊሙ ከፊቱ</t>
         </is>
       </c>
       <c r="G185" s="13" t="inlineStr">
         <is>
-          <t>ku xiray webhook-ga gudbinta</t>
+          <t>arrin dib u furay</t>
         </is>
       </c>
       <c r="H185" s="14" t="inlineStr"/>
@@ -12475,7 +12475,7 @@
     <row r="186" ht="44" customHeight="1">
       <c r="A186" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_webhook_disconnected</t>
+          <t>action_handoff_webhook_connected</t>
         </is>
       </c>
       <c r="B186" s="11" t="inlineStr">
@@ -12485,27 +12485,27 @@
       </c>
       <c r="C186" s="11" t="inlineStr">
         <is>
-          <t>disconnected the escalation webhook</t>
+          <t>connected the escalation webhook</t>
         </is>
       </c>
       <c r="D186" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ዌብሁክ አቋርጧል</t>
+          <t>የማሸጋገሪያ ዌብሁክ አገናኝቷል</t>
         </is>
       </c>
       <c r="E186" s="13" t="inlineStr">
         <is>
-          <t>webhook dabarsaa addaan kute</t>
+          <t>webhook dabarsaa walqunnamsiise</t>
         </is>
       </c>
       <c r="F186" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ምትሕልላፍ ቆሪጹ</t>
+          <t>ዌብሁክ ምትሕልላፍ ኣራኺቡ</t>
         </is>
       </c>
       <c r="G186" s="13" t="inlineStr">
         <is>
-          <t>goynay webhook-ga gudbinta</t>
+          <t>ku xiray webhook-ga gudbinta</t>
         </is>
       </c>
       <c r="H186" s="14" t="inlineStr"/>
@@ -12513,7 +12513,7 @@
     <row r="187" ht="44" customHeight="1">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t>action_telegram_connected</t>
+          <t>action_handoff_webhook_disconnected</t>
         </is>
       </c>
       <c r="B187" s="11" t="inlineStr">
@@ -12523,27 +12523,27 @@
       </c>
       <c r="C187" s="11" t="inlineStr">
         <is>
-          <t>connected Telegram</t>
+          <t>disconnected the escalation webhook</t>
         </is>
       </c>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>ቴሌግራም አገናኝቷል</t>
+          <t>የማሸጋገሪያ ዌብሁክ አቋርጧል</t>
         </is>
       </c>
       <c r="E187" s="13" t="inlineStr">
         <is>
-          <t>Telegram walqunnamsiise</t>
+          <t>webhook dabarsaa addaan kute</t>
         </is>
       </c>
       <c r="F187" s="12" t="inlineStr">
         <is>
-          <t>ቴሌግራም ኣራኺቡ</t>
+          <t>ዌብሁክ ምትሕልላፍ ቆሪጹ</t>
         </is>
       </c>
       <c r="G187" s="13" t="inlineStr">
         <is>
-          <t>Telegram ku xiray</t>
+          <t>goynay webhook-ga gudbinta</t>
         </is>
       </c>
       <c r="H187" s="14" t="inlineStr"/>
@@ -12551,7 +12551,7 @@
     <row r="188" ht="44" customHeight="1">
       <c r="A188" s="11" t="inlineStr">
         <is>
-          <t>action_user_created</t>
+          <t>action_telegram_connected</t>
         </is>
       </c>
       <c r="B188" s="11" t="inlineStr">
@@ -12561,27 +12561,27 @@
       </c>
       <c r="C188" s="11" t="inlineStr">
         <is>
-          <t>added a colleague</t>
+          <t>connected Telegram</t>
         </is>
       </c>
       <c r="D188" s="12" t="inlineStr">
         <is>
-          <t>ባልደረባ ጨምሯል</t>
+          <t>ቴሌግራም አገናኝቷል</t>
         </is>
       </c>
       <c r="E188" s="13" t="inlineStr">
         <is>
-          <t>hojjetaa dabale</t>
+          <t>Telegram walqunnamsiise</t>
         </is>
       </c>
       <c r="F188" s="12" t="inlineStr">
         <is>
-          <t>መሳርሕቲ ወሲኹ</t>
+          <t>ቴሌግራም ኣራኺቡ</t>
         </is>
       </c>
       <c r="G188" s="13" t="inlineStr">
         <is>
-          <t>shaqaale ku daray</t>
+          <t>Telegram ku xiray</t>
         </is>
       </c>
       <c r="H188" s="14" t="inlineStr"/>
@@ -12589,7 +12589,7 @@
     <row r="189" ht="44" customHeight="1">
       <c r="A189" s="11" t="inlineStr">
         <is>
-          <t>action_user_disabled</t>
+          <t>action_user_created</t>
         </is>
       </c>
       <c r="B189" s="11" t="inlineStr">
@@ -12599,27 +12599,27 @@
       </c>
       <c r="C189" s="11" t="inlineStr">
         <is>
-          <t>disabled an account</t>
+          <t>added a colleague</t>
         </is>
       </c>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>መለያ አሰናክሏል</t>
+          <t>ባልደረባ ጨምሯል</t>
         </is>
       </c>
       <c r="E189" s="13" t="inlineStr">
         <is>
-          <t>herrega dhaabe</t>
+          <t>hojjetaa dabale</t>
         </is>
       </c>
       <c r="F189" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ ዓጊቱ</t>
+          <t>መሳርሕቲ ወሲኹ</t>
         </is>
       </c>
       <c r="G189" s="13" t="inlineStr">
         <is>
-          <t>xisaab demiyay</t>
+          <t>shaqaale ku daray</t>
         </is>
       </c>
       <c r="H189" s="14" t="inlineStr"/>
@@ -12627,7 +12627,7 @@
     <row r="190" ht="44" customHeight="1">
       <c r="A190" s="11" t="inlineStr">
         <is>
-          <t>action_user_enabled</t>
+          <t>action_user_disabled</t>
         </is>
       </c>
       <c r="B190" s="11" t="inlineStr">
@@ -12637,27 +12637,27 @@
       </c>
       <c r="C190" s="11" t="inlineStr">
         <is>
-          <t>restored an account</t>
+          <t>disabled an account</t>
         </is>
       </c>
       <c r="D190" s="12" t="inlineStr">
         <is>
-          <t>መለያ መልሷል</t>
+          <t>መለያ አሰናክሏል</t>
         </is>
       </c>
       <c r="E190" s="13" t="inlineStr">
         <is>
-          <t>herrega deebise</t>
+          <t>herrega dhaabe</t>
         </is>
       </c>
       <c r="F190" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ መሊሱ</t>
+          <t>ሕሳብ ዓጊቱ</t>
         </is>
       </c>
       <c r="G190" s="13" t="inlineStr">
         <is>
-          <t>xisaab soo celiyay</t>
+          <t>xisaab demiyay</t>
         </is>
       </c>
       <c r="H190" s="14" t="inlineStr"/>
@@ -12665,7 +12665,7 @@
     <row r="191" ht="44" customHeight="1">
       <c r="A191" s="11" t="inlineStr">
         <is>
-          <t>action_admin_login</t>
+          <t>action_user_enabled</t>
         </is>
       </c>
       <c r="B191" s="11" t="inlineStr">
@@ -12675,27 +12675,27 @@
       </c>
       <c r="C191" s="11" t="inlineStr">
         <is>
-          <t>signed in</t>
+          <t>restored an account</t>
         </is>
       </c>
       <c r="D191" s="12" t="inlineStr">
         <is>
-          <t>ገብቷል</t>
+          <t>መለያ መልሷል</t>
         </is>
       </c>
       <c r="E191" s="13" t="inlineStr">
         <is>
-          <t>seene</t>
+          <t>herrega deebise</t>
         </is>
       </c>
       <c r="F191" s="12" t="inlineStr">
         <is>
-          <t>ኣትዩ</t>
+          <t>ሕሳብ መሊሱ</t>
         </is>
       </c>
       <c r="G191" s="13" t="inlineStr">
         <is>
-          <t>gashay</t>
+          <t>xisaab soo celiyay</t>
         </is>
       </c>
       <c r="H191" s="14" t="inlineStr"/>
@@ -12703,7 +12703,7 @@
     <row r="192" ht="44" customHeight="1">
       <c r="A192" s="11" t="inlineStr">
         <is>
-          <t>action_password_changed</t>
+          <t>action_admin_login</t>
         </is>
       </c>
       <c r="B192" s="11" t="inlineStr">
@@ -12713,27 +12713,27 @@
       </c>
       <c r="C192" s="11" t="inlineStr">
         <is>
-          <t>changed their password</t>
+          <t>signed in</t>
         </is>
       </c>
       <c r="D192" s="12" t="inlineStr">
         <is>
-          <t>የይለፍ ቃል ቀይሯል</t>
+          <t>ገብቷል</t>
         </is>
       </c>
       <c r="E192" s="13" t="inlineStr">
         <is>
-          <t>jecha darbii jijjiire</t>
+          <t>seene</t>
         </is>
       </c>
       <c r="F192" s="12" t="inlineStr">
         <is>
-          <t>መሕለፊ ቃል ቀዪሩ</t>
+          <t>ኣትዩ</t>
         </is>
       </c>
       <c r="G192" s="13" t="inlineStr">
         <is>
-          <t>beddelay furihiisa</t>
+          <t>gashay</t>
         </is>
       </c>
       <c r="H192" s="14" t="inlineStr"/>
@@ -12741,7 +12741,7 @@
     <row r="193" ht="44" customHeight="1">
       <c r="A193" s="11" t="inlineStr">
         <is>
-          <t>nothing_yet</t>
+          <t>action_password_changed</t>
         </is>
       </c>
       <c r="B193" s="11" t="inlineStr">
@@ -12751,27 +12751,27 @@
       </c>
       <c r="C193" s="11" t="inlineStr">
         <is>
-          <t>Nothing yet.</t>
+          <t>changed their password</t>
         </is>
       </c>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>እስካሁን ምንም የለም።</t>
+          <t>የይለፍ ቃል ቀይሯል</t>
         </is>
       </c>
       <c r="E193" s="13" t="inlineStr">
         <is>
-          <t>Ammaaf homaa hin jiru.</t>
+          <t>jecha darbii jijjiire</t>
         </is>
       </c>
       <c r="F193" s="12" t="inlineStr">
         <is>
-          <t>ክሳብ ሕጂ ዋላ ሓደ የለን።</t>
+          <t>መሕለፊ ቃል ቀዪሩ</t>
         </is>
       </c>
       <c r="G193" s="13" t="inlineStr">
         <is>
-          <t>Weli waxba ma jiraan.</t>
+          <t>beddelay furihiisa</t>
         </is>
       </c>
       <c r="H193" s="14" t="inlineStr"/>
@@ -12779,7 +12779,7 @@
     <row r="194" ht="44" customHeight="1">
       <c r="A194" s="11" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>nothing_yet</t>
         </is>
       </c>
       <c r="B194" s="11" t="inlineStr">
@@ -12789,27 +12789,27 @@
       </c>
       <c r="C194" s="11" t="inlineStr">
         <is>
-          <t>Unavailable.</t>
+          <t>Nothing yet.</t>
         </is>
       </c>
       <c r="D194" s="12" t="inlineStr">
         <is>
-          <t>አይገኝም።</t>
+          <t>እስካሁን ምንም የለም።</t>
         </is>
       </c>
       <c r="E194" s="13" t="inlineStr">
         <is>
-          <t>Hin argamu.</t>
+          <t>Ammaaf homaa hin jiru.</t>
         </is>
       </c>
       <c r="F194" s="12" t="inlineStr">
         <is>
-          <t>ኣይርከብን።</t>
+          <t>ክሳብ ሕጂ ዋላ ሓደ የለን።</t>
         </is>
       </c>
       <c r="G194" s="13" t="inlineStr">
         <is>
-          <t>Lama heli karo.</t>
+          <t>Weli waxba ma jiraan.</t>
         </is>
       </c>
       <c r="H194" s="14" t="inlineStr"/>
@@ -12817,7 +12817,7 @@
     <row r="195" ht="44" customHeight="1">
       <c r="A195" s="11" t="inlineStr">
         <is>
-          <t>just_now</t>
+          <t>unavailable</t>
         </is>
       </c>
       <c r="B195" s="11" t="inlineStr">
@@ -12827,27 +12827,27 @@
       </c>
       <c r="C195" s="11" t="inlineStr">
         <is>
-          <t>just now</t>
+          <t>Unavailable.</t>
         </is>
       </c>
       <c r="D195" s="12" t="inlineStr">
         <is>
-          <t>አሁን</t>
+          <t>አይገኝም።</t>
         </is>
       </c>
       <c r="E195" s="13" t="inlineStr">
         <is>
-          <t>amma</t>
+          <t>Hin argamu.</t>
         </is>
       </c>
       <c r="F195" s="12" t="inlineStr">
         <is>
-          <t>ሕጂ</t>
+          <t>ኣይርከብን።</t>
         </is>
       </c>
       <c r="G195" s="13" t="inlineStr">
         <is>
-          <t>hadda</t>
+          <t>Lama heli karo.</t>
         </is>
       </c>
       <c r="H195" s="14" t="inlineStr"/>
@@ -12855,7 +12855,7 @@
     <row r="196" ht="44" customHeight="1">
       <c r="A196" s="11" t="inlineStr">
         <is>
-          <t>n_min_ago</t>
+          <t>just_now</t>
         </is>
       </c>
       <c r="B196" s="11" t="inlineStr">
@@ -12865,27 +12865,27 @@
       </c>
       <c r="C196" s="11" t="inlineStr">
         <is>
-          <t>{n} min ago</t>
+          <t>just now</t>
         </is>
       </c>
       <c r="D196" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ደቂቃ በፊት</t>
+          <t>አሁን</t>
         </is>
       </c>
       <c r="E196" s="13" t="inlineStr">
         <is>
-          <t>daqiiqaa {n} dura</t>
+          <t>amma</t>
         </is>
       </c>
       <c r="F196" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ደቒቕ</t>
+          <t>ሕጂ</t>
         </is>
       </c>
       <c r="G196" s="13" t="inlineStr">
         <is>
-          <t>{n} daqiiqo ka hor</t>
+          <t>hadda</t>
         </is>
       </c>
       <c r="H196" s="14" t="inlineStr"/>
@@ -12893,7 +12893,7 @@
     <row r="197" ht="44" customHeight="1">
       <c r="A197" s="11" t="inlineStr">
         <is>
-          <t>n_h_ago</t>
+          <t>n_min_ago</t>
         </is>
       </c>
       <c r="B197" s="11" t="inlineStr">
@@ -12903,27 +12903,27 @@
       </c>
       <c r="C197" s="11" t="inlineStr">
         <is>
-          <t>{n} h ago</t>
+          <t>{n} min ago</t>
         </is>
       </c>
       <c r="D197" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ሰዓት በፊት</t>
+          <t>ከ{n} ደቂቃ በፊት</t>
         </is>
       </c>
       <c r="E197" s="13" t="inlineStr">
         <is>
-          <t>sa'aatii {n} dura</t>
+          <t>daqiiqaa {n} dura</t>
         </is>
       </c>
       <c r="F197" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ሰዓት</t>
+          <t>ቅድሚ {n} ደቒቕ</t>
         </is>
       </c>
       <c r="G197" s="13" t="inlineStr">
         <is>
-          <t>{n} saac ka hor</t>
+          <t>{n} daqiiqo ka hor</t>
         </is>
       </c>
       <c r="H197" s="14" t="inlineStr"/>
@@ -12931,7 +12931,7 @@
     <row r="198" ht="44" customHeight="1">
       <c r="A198" s="11" t="inlineStr">
         <is>
-          <t>n_d_ago</t>
+          <t>n_h_ago</t>
         </is>
       </c>
       <c r="B198" s="11" t="inlineStr">
@@ -12941,27 +12941,27 @@
       </c>
       <c r="C198" s="11" t="inlineStr">
         <is>
-          <t>{n} d ago</t>
+          <t>{n} h ago</t>
         </is>
       </c>
       <c r="D198" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ቀን በፊት</t>
+          <t>ከ{n} ሰዓት በፊት</t>
         </is>
       </c>
       <c r="E198" s="13" t="inlineStr">
         <is>
-          <t>guyyaa {n} dura</t>
+          <t>sa'aatii {n} dura</t>
         </is>
       </c>
       <c r="F198" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} መዓልቲ</t>
+          <t>ቅድሚ {n} ሰዓት</t>
         </is>
       </c>
       <c r="G198" s="13" t="inlineStr">
         <is>
-          <t>{n} maalmood ka hor</t>
+          <t>{n} saac ka hor</t>
         </is>
       </c>
       <c r="H198" s="14" t="inlineStr"/>
@@ -12969,7 +12969,7 @@
     <row r="199" ht="44" customHeight="1">
       <c r="A199" s="11" t="inlineStr">
         <is>
-          <t>channel_all_from</t>
+          <t>n_d_ago</t>
         </is>
       </c>
       <c r="B199" s="11" t="inlineStr">
@@ -12979,27 +12979,27 @@
       </c>
       <c r="C199" s="11" t="inlineStr">
         <is>
-          <t>All {n} conversations came from {label}.</t>
+          <t>{n} d ago</t>
         </is>
       </c>
       <c r="D199" s="12" t="inlineStr">
         <is>
-          <t>ሁሉም {n} ውይይቶች ከ{label} መጥተዋል።</t>
+          <t>ከ{n} ቀን በፊት</t>
         </is>
       </c>
       <c r="E199" s="13" t="inlineStr">
         <is>
-          <t>Mariin {n} hundi {label} irraa dhufe.</t>
+          <t>guyyaa {n} dura</t>
         </is>
       </c>
       <c r="F199" s="12" t="inlineStr">
         <is>
-          <t>ኩሎም {n} ዝርርባት ካብ {label} መጺኦም።</t>
+          <t>ቅድሚ {n} መዓልቲ</t>
         </is>
       </c>
       <c r="G199" s="13" t="inlineStr">
         <is>
-          <t>Dhammaan {n} wadahadal waxay ka yimaadeen {label}.</t>
+          <t>{n} maalmood ka hor</t>
         </is>
       </c>
       <c r="H199" s="14" t="inlineStr"/>
@@ -13007,7 +13007,7 @@
     <row r="200" ht="44" customHeight="1">
       <c r="A200" s="11" t="inlineStr">
         <is>
-          <t>channel_live</t>
+          <t>channel_all_from</t>
         </is>
       </c>
       <c r="B200" s="11" t="inlineStr">
@@ -13017,27 +13017,27 @@
       </c>
       <c r="C200" s="11" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>All {n} conversations came from {label}.</t>
         </is>
       </c>
       <c r="D200" s="12" t="inlineStr">
         <is>
-          <t>በሥራ ላይ</t>
+          <t>ሁሉም {n} ውይይቶች ከ{label} መጥተዋል።</t>
         </is>
       </c>
       <c r="E200" s="13" t="inlineStr">
         <is>
-          <t>Hojiirra</t>
+          <t>Mariin {n} hundi {label} irraa dhufe.</t>
         </is>
       </c>
       <c r="F200" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ስራሕ</t>
+          <t>ኩሎም {n} ዝርርባት ካብ {label} መጺኦም።</t>
         </is>
       </c>
       <c r="G200" s="13" t="inlineStr">
         <is>
-          <t>Shaqeynaya</t>
+          <t>Dhammaan {n} wadahadal waxay ka yimaadeen {label}.</t>
         </is>
       </c>
       <c r="H200" s="14" t="inlineStr"/>
@@ -13045,7 +13045,7 @@
     <row r="201" ht="44" customHeight="1">
       <c r="A201" s="11" t="inlineStr">
         <is>
-          <t>channel_ready</t>
+          <t>channel_live</t>
         </is>
       </c>
       <c r="B201" s="11" t="inlineStr">
@@ -13055,27 +13055,27 @@
       </c>
       <c r="C201" s="11" t="inlineStr">
         <is>
-          <t>Ready to connect</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>ለመገናኘት ዝግጁ</t>
+          <t>በሥራ ላይ</t>
         </is>
       </c>
       <c r="E201" s="13" t="inlineStr">
         <is>
-          <t>Walqunnamuuf qophaa'aa</t>
+          <t>Hojiirra</t>
         </is>
       </c>
       <c r="F201" s="12" t="inlineStr">
         <is>
-          <t>ንምርኻብ ድሉው</t>
+          <t>ኣብ ስራሕ</t>
         </is>
       </c>
       <c r="G201" s="13" t="inlineStr">
         <is>
-          <t>Diyaar u ah xiriirka</t>
+          <t>Shaqeynaya</t>
         </is>
       </c>
       <c r="H201" s="14" t="inlineStr"/>
@@ -13083,7 +13083,7 @@
     <row r="202" ht="44" customHeight="1">
       <c r="A202" s="11" t="inlineStr">
         <is>
-          <t>channel_needs_setup</t>
+          <t>channel_ready</t>
         </is>
       </c>
       <c r="B202" s="11" t="inlineStr">
@@ -13093,27 +13093,27 @@
       </c>
       <c r="C202" s="11" t="inlineStr">
         <is>
-          <t>Needs setup</t>
+          <t>Ready to connect</t>
         </is>
       </c>
       <c r="D202" s="12" t="inlineStr">
         <is>
-          <t>ማዋቀር ይፈልጋል</t>
+          <t>ለመገናኘት ዝግጁ</t>
         </is>
       </c>
       <c r="E202" s="13" t="inlineStr">
         <is>
-          <t>Qindeessuu barbaada</t>
+          <t>Walqunnamuuf qophaa'aa</t>
         </is>
       </c>
       <c r="F202" s="12" t="inlineStr">
         <is>
-          <t>ምድላው የድልዮ</t>
+          <t>ንምርኻብ ድሉው</t>
         </is>
       </c>
       <c r="G202" s="13" t="inlineStr">
         <is>
-          <t>Waxay u baahan tahay dejin</t>
+          <t>Diyaar u ah xiriirka</t>
         </is>
       </c>
       <c r="H202" s="14" t="inlineStr"/>
@@ -13121,7 +13121,7 @@
     <row r="203" ht="44" customHeight="1">
       <c r="A203" s="11" t="inlineStr">
         <is>
-          <t>share_by_channel</t>
+          <t>channel_needs_setup</t>
         </is>
       </c>
       <c r="B203" s="11" t="inlineStr">
@@ -13131,27 +13131,27 @@
       </c>
       <c r="C203" s="11" t="inlineStr">
         <is>
-          <t>Share of conversations by channel</t>
+          <t>Needs setup</t>
         </is>
       </c>
       <c r="D203" s="12" t="inlineStr">
         <is>
-          <t>በመስመር የተከፋፈሉ ውይይቶች ድርሻ</t>
+          <t>ማዋቀር ይፈልጋል</t>
         </is>
       </c>
       <c r="E203" s="13" t="inlineStr">
         <is>
-          <t>Qooda marii karaa tokkoon tokkoon isaanii</t>
+          <t>Qindeessuu barbaada</t>
         </is>
       </c>
       <c r="F203" s="12" t="inlineStr">
         <is>
-          <t>ብመስመር ዝተኸፋፈለ ግደ ዝርርባት</t>
+          <t>ምድላው የድልዮ</t>
         </is>
       </c>
       <c r="G203" s="13" t="inlineStr">
         <is>
-          <t>Qaybta wadahadallada kanaalka</t>
+          <t>Waxay u baahan tahay dejin</t>
         </is>
       </c>
       <c r="H203" s="14" t="inlineStr"/>
@@ -13159,7 +13159,7 @@
     <row r="204" ht="44" customHeight="1">
       <c r="A204" s="11" t="inlineStr">
         <is>
-          <t>up_to_date</t>
+          <t>share_by_channel</t>
         </is>
       </c>
       <c r="B204" s="11" t="inlineStr">
@@ -13169,27 +13169,27 @@
       </c>
       <c r="C204" s="11" t="inlineStr">
         <is>
-          <t>Up to date</t>
+          <t>Share of conversations by channel</t>
         </is>
       </c>
       <c r="D204" s="12" t="inlineStr">
         <is>
-          <t>የተዘመነ</t>
+          <t>በመስመር የተከፋፈሉ ውይይቶች ድርሻ</t>
         </is>
       </c>
       <c r="E204" s="13" t="inlineStr">
         <is>
-          <t>Haaraa</t>
+          <t>Qooda marii karaa tokkoon tokkoon isaanii</t>
         </is>
       </c>
       <c r="F204" s="12" t="inlineStr">
         <is>
-          <t>ዝተሓደሰ</t>
+          <t>ብመስመር ዝተኸፋፈለ ግደ ዝርርባት</t>
         </is>
       </c>
       <c r="G204" s="13" t="inlineStr">
         <is>
-          <t>La cusbooneysiiyay</t>
+          <t>Qaybta wadahadallada kanaalka</t>
         </is>
       </c>
       <c r="H204" s="14" t="inlineStr"/>
@@ -13197,7 +13197,7 @@
     <row r="205" ht="44" customHeight="1">
       <c r="A205" s="11" t="inlineStr">
         <is>
-          <t>updated_m_ago</t>
+          <t>up_to_date</t>
         </is>
       </c>
       <c r="B205" s="11" t="inlineStr">
@@ -13207,27 +13207,27 @@
       </c>
       <c r="C205" s="11" t="inlineStr">
         <is>
-          <t>Updated {n}m ago</t>
+          <t>Up to date</t>
         </is>
       </c>
       <c r="D205" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ደቂቃ በፊት ተዘምኗል</t>
+          <t>የተዘመነ</t>
         </is>
       </c>
       <c r="E205" s="13" t="inlineStr">
         <is>
-          <t>Daqiiqaa {n} dura haaromfame</t>
+          <t>Haaraa</t>
         </is>
       </c>
       <c r="F205" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ደቒቕ ተሓዲሱ</t>
+          <t>ዝተሓደሰ</t>
         </is>
       </c>
       <c r="G205" s="13" t="inlineStr">
         <is>
-          <t>La cusbooneysiiyay {n}daq ka hor</t>
+          <t>La cusbooneysiiyay</t>
         </is>
       </c>
       <c r="H205" s="14" t="inlineStr"/>
@@ -13235,7 +13235,7 @@
     <row r="206" ht="44" customHeight="1">
       <c r="A206" s="11" t="inlineStr">
         <is>
-          <t>updated_h_ago</t>
+          <t>updated_m_ago</t>
         </is>
       </c>
       <c r="B206" s="11" t="inlineStr">
@@ -13245,27 +13245,27 @@
       </c>
       <c r="C206" s="11" t="inlineStr">
         <is>
-          <t>Updated {n}h ago</t>
+          <t>Updated {n}m ago</t>
         </is>
       </c>
       <c r="D206" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ሰዓት በፊት ተዘምኗል</t>
+          <t>ከ{n} ደቂቃ በፊት ተዘምኗል</t>
         </is>
       </c>
       <c r="E206" s="13" t="inlineStr">
         <is>
-          <t>Sa'aatii {n} dura haaromfame</t>
+          <t>Daqiiqaa {n} dura haaromfame</t>
         </is>
       </c>
       <c r="F206" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ሰዓት ተሓዲሱ</t>
+          <t>ቅድሚ {n} ደቒቕ ተሓዲሱ</t>
         </is>
       </c>
       <c r="G206" s="13" t="inlineStr">
         <is>
-          <t>La cusbooneysiiyay {n}saac ka hor</t>
+          <t>La cusbooneysiiyay {n}daq ka hor</t>
         </is>
       </c>
       <c r="H206" s="14" t="inlineStr"/>
@@ -13273,7 +13273,7 @@
     <row r="207" ht="44" customHeight="1">
       <c r="A207" s="11" t="inlineStr">
         <is>
-          <t>queue</t>
+          <t>updated_h_ago</t>
         </is>
       </c>
       <c r="B207" s="11" t="inlineStr">
@@ -13283,27 +13283,27 @@
       </c>
       <c r="C207" s="11" t="inlineStr">
         <is>
-          <t>Queue</t>
+          <t>Updated {n}h ago</t>
         </is>
       </c>
       <c r="D207" s="12" t="inlineStr">
         <is>
-          <t>ወረፋ</t>
+          <t>ከ{n} ሰዓት በፊት ተዘምኗል</t>
         </is>
       </c>
       <c r="E207" s="13" t="inlineStr">
         <is>
-          <t>Sararaa</t>
+          <t>Sa'aatii {n} dura haaromfame</t>
         </is>
       </c>
       <c r="F207" s="12" t="inlineStr">
         <is>
-          <t>ሪጋ</t>
+          <t>ቅድሚ {n} ሰዓት ተሓዲሱ</t>
         </is>
       </c>
       <c r="G207" s="13" t="inlineStr">
         <is>
-          <t>Safka</t>
+          <t>La cusbooneysiiyay {n}saac ka hor</t>
         </is>
       </c>
       <c r="H207" s="14" t="inlineStr"/>
@@ -13311,7 +13311,7 @@
     <row r="208" ht="44" customHeight="1">
       <c r="A208" s="11" t="inlineStr">
         <is>
-          <t>collapse</t>
+          <t>queue</t>
         </is>
       </c>
       <c r="B208" s="11" t="inlineStr">
@@ -13321,27 +13321,27 @@
       </c>
       <c r="C208" s="11" t="inlineStr">
         <is>
-          <t>Collapse</t>
+          <t>Queue</t>
         </is>
       </c>
       <c r="D208" s="12" t="inlineStr">
         <is>
-          <t>አጥብብ</t>
+          <t>ወረፋ</t>
         </is>
       </c>
       <c r="E208" s="13" t="inlineStr">
         <is>
-          <t>Xiqqeessi</t>
+          <t>Sararaa</t>
         </is>
       </c>
       <c r="F208" s="12" t="inlineStr">
         <is>
-          <t>ኣጽብብ</t>
+          <t>ሪጋ</t>
         </is>
       </c>
       <c r="G208" s="13" t="inlineStr">
         <is>
-          <t>Yaree</t>
+          <t>Safka</t>
         </is>
       </c>
       <c r="H208" s="14" t="inlineStr"/>
@@ -13349,7 +13349,7 @@
     <row r="209" ht="44" customHeight="1">
       <c r="A209" s="11" t="inlineStr">
         <is>
-          <t>expand</t>
+          <t>collapse</t>
         </is>
       </c>
       <c r="B209" s="11" t="inlineStr">
@@ -13359,27 +13359,27 @@
       </c>
       <c r="C209" s="11" t="inlineStr">
         <is>
-          <t>Expand</t>
+          <t>Collapse</t>
         </is>
       </c>
       <c r="D209" s="12" t="inlineStr">
         <is>
-          <t>አስፋ</t>
+          <t>አጥብብ</t>
         </is>
       </c>
       <c r="E209" s="13" t="inlineStr">
         <is>
-          <t>Balleessi</t>
+          <t>Xiqqeessi</t>
         </is>
       </c>
       <c r="F209" s="12" t="inlineStr">
         <is>
-          <t>ኣስፍሕ</t>
+          <t>ኣጽብብ</t>
         </is>
       </c>
       <c r="G209" s="13" t="inlineStr">
         <is>
-          <t>Balaadhi</t>
+          <t>Yaree</t>
         </is>
       </c>
       <c r="H209" s="14" t="inlineStr"/>
@@ -13387,7 +13387,7 @@
     <row r="210" ht="44" customHeight="1">
       <c r="A210" s="11" t="inlineStr">
         <is>
-          <t>collapse_or_expand</t>
+          <t>expand</t>
         </is>
       </c>
       <c r="B210" s="11" t="inlineStr">
@@ -13397,27 +13397,27 @@
       </c>
       <c r="C210" s="11" t="inlineStr">
         <is>
-          <t>Collapse or expand the sidebar</t>
+          <t>Expand</t>
         </is>
       </c>
       <c r="D210" s="12" t="inlineStr">
         <is>
-          <t>የጎን አሞሌውን አጥብብ ወይም አስፋ</t>
+          <t>አስፋ</t>
         </is>
       </c>
       <c r="E210" s="13" t="inlineStr">
         <is>
-          <t>Cinaacha xiqqeessi ykn balleessi</t>
+          <t>Balleessi</t>
         </is>
       </c>
       <c r="F210" s="12" t="inlineStr">
         <is>
-          <t>ናይ ጎኒ መስመር ኣጽብብ ወይ ኣስፍሕ</t>
+          <t>ኣስፍሕ</t>
         </is>
       </c>
       <c r="G210" s="13" t="inlineStr">
         <is>
-          <t>Yaree ama balaadhi dhinaca</t>
+          <t>Balaadhi</t>
         </is>
       </c>
       <c r="H210" s="14" t="inlineStr"/>
@@ -13425,7 +13425,7 @@
     <row r="211" ht="44" customHeight="1">
       <c r="A211" s="11" t="inlineStr">
         <is>
-          <t>show_hide_channels</t>
+          <t>collapse_or_expand</t>
         </is>
       </c>
       <c r="B211" s="11" t="inlineStr">
@@ -13435,27 +13435,27 @@
       </c>
       <c r="C211" s="11" t="inlineStr">
         <is>
-          <t>Show or hide the channel list</t>
+          <t>Collapse or expand the sidebar</t>
         </is>
       </c>
       <c r="D211" s="12" t="inlineStr">
         <is>
-          <t>የመስመሮችን ዝርዝር አሳይ ወይም ደብቅ</t>
+          <t>የጎን አሞሌውን አጥብብ ወይም አስፋ</t>
         </is>
       </c>
       <c r="E211" s="13" t="inlineStr">
         <is>
-          <t>Tarreeffama karaalee agarsiisi ykn dhoksi</t>
+          <t>Cinaacha xiqqeessi ykn balleessi</t>
         </is>
       </c>
       <c r="F211" s="12" t="inlineStr">
         <is>
-          <t>ዝርዝር መስመራት ኣርኢ ወይ ሕባእ</t>
+          <t>ናይ ጎኒ መስመር ኣጽብብ ወይ ኣስፍሕ</t>
         </is>
       </c>
       <c r="G211" s="13" t="inlineStr">
         <is>
-          <t>Muuji ama qari liiska kanaalada</t>
+          <t>Yaree ama balaadhi dhinaca</t>
         </is>
       </c>
       <c r="H211" s="14" t="inlineStr"/>
@@ -13463,7 +13463,7 @@
     <row r="212" ht="44" customHeight="1">
       <c r="A212" s="11" t="inlineStr">
         <is>
-          <t>today</t>
+          <t>show_hide_channels</t>
         </is>
       </c>
       <c r="B212" s="11" t="inlineStr">
@@ -13473,27 +13473,27 @@
       </c>
       <c r="C212" s="11" t="inlineStr">
         <is>
-          <t>Today</t>
+          <t>Show or hide the channel list</t>
         </is>
       </c>
       <c r="D212" s="12" t="inlineStr">
         <is>
-          <t>ዛሬ</t>
+          <t>የመስመሮችን ዝርዝር አሳይ ወይም ደብቅ</t>
         </is>
       </c>
       <c r="E212" s="13" t="inlineStr">
         <is>
-          <t>Har'a</t>
+          <t>Tarreeffama karaalee agarsiisi ykn dhoksi</t>
         </is>
       </c>
       <c r="F212" s="12" t="inlineStr">
         <is>
-          <t>ሎሚ</t>
+          <t>ዝርዝር መስመራት ኣርኢ ወይ ሕባእ</t>
         </is>
       </c>
       <c r="G212" s="13" t="inlineStr">
         <is>
-          <t>Maanta</t>
+          <t>Muuji ama qari liiska kanaalada</t>
         </is>
       </c>
       <c r="H212" s="14" t="inlineStr"/>
@@ -13501,7 +13501,7 @@
     <row r="213" ht="44" customHeight="1">
       <c r="A213" s="11" t="inlineStr">
         <is>
-          <t>yesterday</t>
+          <t>today</t>
         </is>
       </c>
       <c r="B213" s="11" t="inlineStr">
@@ -13511,27 +13511,27 @@
       </c>
       <c r="C213" s="11" t="inlineStr">
         <is>
-          <t>Yesterday</t>
+          <t>Today</t>
         </is>
       </c>
       <c r="D213" s="12" t="inlineStr">
         <is>
-          <t>ትናንት</t>
+          <t>ዛሬ</t>
         </is>
       </c>
       <c r="E213" s="13" t="inlineStr">
         <is>
-          <t>Kaleessa</t>
+          <t>Har'a</t>
         </is>
       </c>
       <c r="F213" s="12" t="inlineStr">
         <is>
-          <t>ትማሊ</t>
+          <t>ሎሚ</t>
         </is>
       </c>
       <c r="G213" s="13" t="inlineStr">
         <is>
-          <t>Shalay</t>
+          <t>Maanta</t>
         </is>
       </c>
       <c r="H213" s="14" t="inlineStr"/>
@@ -13539,7 +13539,7 @@
     <row r="214" ht="44" customHeight="1">
       <c r="A214" s="11" t="inlineStr">
         <is>
-          <t>call_started</t>
+          <t>yesterday</t>
         </is>
       </c>
       <c r="B214" s="11" t="inlineStr">
@@ -13549,27 +13549,27 @@
       </c>
       <c r="C214" s="11" t="inlineStr">
         <is>
-          <t>The customer asked for a person here</t>
+          <t>Yesterday</t>
         </is>
       </c>
       <c r="D214" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛው እዚህ ላይ ሰው ጠየቀ</t>
+          <t>ትናንት</t>
         </is>
       </c>
       <c r="E214" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan asitti nama gaafate</t>
+          <t>Kaleessa</t>
         </is>
       </c>
       <c r="F214" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዓሚል ኣብዚ ሰብ ሓቲቱ</t>
+          <t>ትማሊ</t>
         </is>
       </c>
       <c r="G214" s="13" t="inlineStr">
         <is>
-          <t>Macmiilku halkan ayuu qof weydiistay</t>
+          <t>Shalay</t>
         </is>
       </c>
       <c r="H214" s="14" t="inlineStr"/>
@@ -13577,7 +13577,7 @@
     <row r="215" ht="44" customHeight="1">
       <c r="A215" s="11" t="inlineStr">
         <is>
-          <t>no_messages</t>
+          <t>call_started</t>
         </is>
       </c>
       <c r="B215" s="11" t="inlineStr">
@@ -13587,27 +13587,27 @@
       </c>
       <c r="C215" s="11" t="inlineStr">
         <is>
-          <t>No messages in this conversation.</t>
+          <t>The customer asked for a person here</t>
         </is>
       </c>
       <c r="D215" s="12" t="inlineStr">
         <is>
-          <t>በዚህ ውይይት ውስጥ መልእክት የለም።</t>
+          <t>ደንበኛው እዚህ ላይ ሰው ጠየቀ</t>
         </is>
       </c>
       <c r="E215" s="13" t="inlineStr">
         <is>
-          <t>Marii kana keessa ergaan hin jiru.</t>
+          <t>Maamilaan asitti nama gaafate</t>
         </is>
       </c>
       <c r="F215" s="12" t="inlineStr">
         <is>
-          <t>ኣብዚ ዝርርብ መልእኽቲ የለን።</t>
+          <t>እቲ ዓሚል ኣብዚ ሰብ ሓቲቱ</t>
         </is>
       </c>
       <c r="G215" s="13" t="inlineStr">
         <is>
-          <t>Wadahadalkan fariin kuma jirto.</t>
+          <t>Macmiilku halkan ayuu qof weydiistay</t>
         </is>
       </c>
       <c r="H215" s="14" t="inlineStr"/>
@@ -13615,7 +13615,7 @@
     <row r="216" ht="44" customHeight="1">
       <c r="A216" s="11" t="inlineStr">
         <is>
-          <t>donut_all_in_one</t>
+          <t>no_messages</t>
         </is>
       </c>
       <c r="B216" s="11" t="inlineStr">
@@ -13625,27 +13625,27 @@
       </c>
       <c r="C216" s="11" t="inlineStr">
         <is>
-          <t>The single {unit} was in {label}.</t>
+          <t>No messages in this conversation.</t>
         </is>
       </c>
       <c r="D216" s="12" t="inlineStr">
         <is>
-          <t>ብቸኛው {unit} በ{label} ነበር።</t>
+          <t>በዚህ ውይይት ውስጥ መልእክት የለም።</t>
         </is>
       </c>
       <c r="E216" s="13" t="inlineStr">
         <is>
-          <t>{unit} tokkichi {label} keessa ture.</t>
+          <t>Marii kana keessa ergaan hin jiru.</t>
         </is>
       </c>
       <c r="F216" s="12" t="inlineStr">
         <is>
-          <t>እቲ ሓደ {unit} ብ{label} ነይሩ።</t>
+          <t>ኣብዚ ዝርርብ መልእኽቲ የለን።</t>
         </is>
       </c>
       <c r="G216" s="13" t="inlineStr">
         <is>
-          <t>{unit} kaliya wuxuu ku jiray {label}.</t>
+          <t>Wadahadalkan fariin kuma jirto.</t>
         </is>
       </c>
       <c r="H216" s="14" t="inlineStr"/>
@@ -13653,7 +13653,7 @@
     <row r="217" ht="44" customHeight="1">
       <c r="A217" s="11" t="inlineStr">
         <is>
-          <t>channel_all_from_one</t>
+          <t>donut_all_in_one</t>
         </is>
       </c>
       <c r="B217" s="11" t="inlineStr">
@@ -13663,27 +13663,27 @@
       </c>
       <c r="C217" s="11" t="inlineStr">
         <is>
-          <t>The single conversation came from {label}.</t>
+          <t>The single {unit} was in {label}.</t>
         </is>
       </c>
       <c r="D217" s="12" t="inlineStr">
         <is>
-          <t>ብቸኛው ውይይት ከ{label} መጥቷል።</t>
+          <t>ብቸኛው {unit} በ{label} ነበር።</t>
         </is>
       </c>
       <c r="E217" s="13" t="inlineStr">
         <is>
-          <t>Mariin tokkichi {label} irraa dhufe.</t>
+          <t>{unit} tokkichi {label} keessa ture.</t>
         </is>
       </c>
       <c r="F217" s="12" t="inlineStr">
         <is>
-          <t>እቲ ሓደ ዝርርብ ካብ {label} መጺኡ።</t>
+          <t>እቲ ሓደ {unit} ብ{label} ነይሩ።</t>
         </is>
       </c>
       <c r="G217" s="13" t="inlineStr">
         <is>
-          <t>Wadahadalka kaliya wuxuu ka yimid {label}.</t>
+          <t>{unit} kaliya wuxuu ku jiray {label}.</t>
         </is>
       </c>
       <c r="H217" s="14" t="inlineStr"/>
@@ -13691,7 +13691,7 @@
     <row r="218" ht="44" customHeight="1">
       <c r="A218" s="11" t="inlineStr">
         <is>
-          <t>unit_conversation</t>
+          <t>channel_all_from_one</t>
         </is>
       </c>
       <c r="B218" s="11" t="inlineStr">
@@ -13701,27 +13701,27 @@
       </c>
       <c r="C218" s="11" t="inlineStr">
         <is>
-          <t>conversation</t>
+          <t>The single conversation came from {label}.</t>
         </is>
       </c>
       <c r="D218" s="12" t="inlineStr">
         <is>
-          <t>ውይይት</t>
+          <t>ብቸኛው ውይይት ከ{label} መጥቷል።</t>
         </is>
       </c>
       <c r="E218" s="13" t="inlineStr">
         <is>
-          <t>marii</t>
+          <t>Mariin tokkichi {label} irraa dhufe.</t>
         </is>
       </c>
       <c r="F218" s="12" t="inlineStr">
         <is>
-          <t>ዝርርብ</t>
+          <t>እቲ ሓደ ዝርርብ ካብ {label} መጺኡ።</t>
         </is>
       </c>
       <c r="G218" s="13" t="inlineStr">
         <is>
-          <t>wadahadal</t>
+          <t>Wadahadalka kaliya wuxuu ka yimid {label}.</t>
         </is>
       </c>
       <c r="H218" s="14" t="inlineStr"/>
@@ -13729,7 +13729,7 @@
     <row r="219" ht="44" customHeight="1">
       <c r="A219" s="11" t="inlineStr">
         <is>
-          <t>live_sessions</t>
+          <t>unit_conversation</t>
         </is>
       </c>
       <c r="B219" s="11" t="inlineStr">
@@ -13739,27 +13739,27 @@
       </c>
       <c r="C219" s="11" t="inlineStr">
         <is>
-          <t>Live sessions</t>
+          <t>conversation</t>
         </is>
       </c>
       <c r="D219" s="12" t="inlineStr">
         <is>
-          <t>የቀጥታ ክፍለ-ጊዜዎች</t>
+          <t>ውይይት</t>
         </is>
       </c>
       <c r="E219" s="13" t="inlineStr">
         <is>
-          <t>Marii kallattii</t>
+          <t>marii</t>
         </is>
       </c>
       <c r="F219" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታ ክፍለ-ግዜታት</t>
+          <t>ዝርርብ</t>
         </is>
       </c>
       <c r="G219" s="13" t="inlineStr">
         <is>
-          <t>Kalfadhiyada tooska ah</t>
+          <t>wadahadal</t>
         </is>
       </c>
       <c r="H219" s="14" t="inlineStr"/>
@@ -13767,7 +13767,7 @@
     <row r="220" ht="44" customHeight="1">
       <c r="A220" s="11" t="inlineStr">
         <is>
-          <t>switched_off_for_bank</t>
+          <t>live_sessions</t>
         </is>
       </c>
       <c r="B220" s="11" t="inlineStr">
@@ -13777,27 +13777,27 @@
       </c>
       <c r="C220" s="11" t="inlineStr">
         <is>
-          <t>Switched off for this bank</t>
+          <t>Live sessions</t>
         </is>
       </c>
       <c r="D220" s="12" t="inlineStr">
         <is>
-          <t>ለዚህ ባንክ ጠፍቷል</t>
+          <t>የቀጥታ ክፍለ-ጊዜዎች</t>
         </is>
       </c>
       <c r="E220" s="13" t="inlineStr">
         <is>
-          <t>Baankii kanaaf dhaamsameera</t>
+          <t>Marii kallattii</t>
         </is>
       </c>
       <c r="F220" s="12" t="inlineStr">
         <is>
-          <t>ነዚ ባንኪ ጠፊኡ</t>
+          <t>ቀጥታ ክፍለ-ግዜታት</t>
         </is>
       </c>
       <c r="G220" s="13" t="inlineStr">
         <is>
-          <t>Bangigan waa la damiyay</t>
+          <t>Kalfadhiyada tooska ah</t>
         </is>
       </c>
       <c r="H220" s="14" t="inlineStr"/>
@@ -13805,7 +13805,7 @@
     <row r="221" ht="44" customHeight="1">
       <c r="A221" s="11" t="inlineStr">
         <is>
-          <t>switched_on_nobody_on_duty</t>
+          <t>switched_off_for_bank</t>
         </is>
       </c>
       <c r="B221" s="11" t="inlineStr">
@@ -13815,27 +13815,27 @@
       </c>
       <c r="C221" s="11" t="inlineStr">
         <is>
-          <t>Switched on — but nobody is on duty</t>
+          <t>Switched off for this bank</t>
         </is>
       </c>
       <c r="D221" s="12" t="inlineStr">
         <is>
-          <t>በርቷል — ግን ማንም በሥራ ላይ የለም</t>
+          <t>ለዚህ ባንክ ጠፍቷል</t>
         </is>
       </c>
       <c r="E221" s="13" t="inlineStr">
         <is>
-          <t>Banameera — garuu namni hojii irra hin jiru</t>
+          <t>Baankii kanaaf dhaamsameera</t>
         </is>
       </c>
       <c r="F221" s="12" t="inlineStr">
         <is>
-          <t>በሪሁ — ግና ዋላ ሓደ ኣብ ስራሕ የለን</t>
+          <t>ነዚ ባንኪ ጠፊኡ</t>
         </is>
       </c>
       <c r="G221" s="13" t="inlineStr">
         <is>
-          <t>Waa la shiday — laakiin qofna shaqada ma joogo</t>
+          <t>Bangigan waa la damiyay</t>
         </is>
       </c>
       <c r="H221" s="14" t="inlineStr"/>
@@ -13843,7 +13843,7 @@
     <row r="222" ht="44" customHeight="1">
       <c r="A222" s="11" t="inlineStr">
         <is>
-          <t>no_teller_button</t>
+          <t>switched_on_nobody_on_duty</t>
         </is>
       </c>
       <c r="B222" s="11" t="inlineStr">
@@ -13853,27 +13853,27 @@
       </c>
       <c r="C222" s="11" t="inlineStr">
         <is>
-          <t>No “Speak to a teller” button appears in your widget.</t>
+          <t>Switched on — but nobody is on duty</t>
         </is>
       </c>
       <c r="D222" s="12" t="inlineStr">
         <is>
-          <t>በመግብርዎ ውስጥ “ከገንዘብ ተቀባይ ጋር ይነጋገሩ” የሚል አዝራር አይታይም።</t>
+          <t>በርቷል — ግን ማንም በሥራ ላይ የለም</t>
         </is>
       </c>
       <c r="E222" s="13" t="inlineStr">
         <is>
-          <t>Widjetii keessan keessatti qabduun “Namaa waliin haasa'aa” hin mul'atu.</t>
+          <t>Banameera — garuu namni hojii irra hin jiru</t>
         </is>
       </c>
       <c r="F222" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መግበሪኹም “ምስ ተቐባሊ ገንዘብ ተዛረቡ” ዝብል መጠወቒ ኣይረአን።</t>
+          <t>በሪሁ — ግና ዋላ ሓደ ኣብ ስራሕ የለን</t>
         </is>
       </c>
       <c r="G222" s="13" t="inlineStr">
         <is>
-          <t>Badhanka “La hadal shaqaale” kama muuqan widget-kaaga.</t>
+          <t>Waa la shiday — laakiin qofna shaqada ma joogo</t>
         </is>
       </c>
       <c r="H222" s="14" t="inlineStr"/>
@@ -13881,7 +13881,7 @@
     <row r="223" ht="44" customHeight="1">
       <c r="A223" s="11" t="inlineStr">
         <is>
-          <t>on_duty_explainer</t>
+          <t>no_teller_button</t>
         </is>
       </c>
       <c r="B223" s="11" t="inlineStr">
@@ -13891,27 +13891,27 @@
       </c>
       <c r="C223" s="11" t="inlineStr">
         <is>
-          <t>You are on duty, so waiting customers can be routed to you. Go off duty from the sidebar when you step away — you stay on the air anywhere in the console until you do.</t>
+          <t>No “Speak to a teller” button appears in your widget.</t>
         </is>
       </c>
       <c r="D223" s="12" t="inlineStr">
         <is>
-          <t>በሥራ ላይ ነዎት፤ ስለዚህ የሚጠብቁ ደንበኞች ወደ እርስዎ ሊመሩ ይችላሉ። ሲርቁ ከጎን አሞሌው ከሥራ ውጡ — እስከዚያ ድረስ በየትኛውም ገጽ ላይ በሥራ ላይ ይቆያሉ።</t>
+          <t>በመግብርዎ ውስጥ “ከገንዘብ ተቀባይ ጋር ይነጋገሩ” የሚል አዝራር አይታይም።</t>
         </is>
       </c>
       <c r="E223" s="13" t="inlineStr">
         <is>
-          <t>Hojii irra jirtu, kanaafuu maamiltoonni eegaa jiran gara keessan qajeelfamuu danda'u. Yeroo achii deemtan cinaacha irraa hojii keessaa ba'aa — hanga sanatti fuula kamiyyuu irratti hojii irra turtu.</t>
+          <t>Widjetii keessan keessatti qabduun “Namaa waliin haasa'aa” hin mul'atu.</t>
         </is>
       </c>
       <c r="F223" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ስራሕ ኢኹም፣ ስለዚ ዝጽበዩ ዓማዊል ናባኹም ክምርሑ ይኽእሉ። ክትርሕቁ ከለኹም ካብ ናይ ጎኒ መስመር ካብ ስራሕ ውጹ — ክሳብ ሽዑ ኣብ ዝኾነ ገጽ ኣብ ስራሕ ትጸንሑ።</t>
+          <t>ኣብ መግበሪኹም “ምስ ተቐባሊ ገንዘብ ተዛረቡ” ዝብል መጠወቒ ኣይረአን።</t>
         </is>
       </c>
       <c r="G223" s="13" t="inlineStr">
         <is>
-          <t>Shaqada ayaad joogtaa, sidaas darteed macaamiisha sugaya waa lagu soo dhiibi karaa. Marka aad tagto shaqada ka bax dhinaca — ilaa markaas bog kasta ayaad ku sii shaqeynaysaa.</t>
+          <t>Badhanka “La hadal shaqaale” kama muuqan widget-kaaga.</t>
         </is>
       </c>
       <c r="H223" s="14" t="inlineStr"/>
@@ -13919,7 +13919,7 @@
     <row r="224" ht="44" customHeight="1">
       <c r="A224" s="11" t="inlineStr">
         <is>
-          <t>off_duty_explainer</t>
+          <t>on_duty_explainer</t>
         </is>
       </c>
       <c r="B224" s="11" t="inlineStr">
@@ -13929,27 +13929,27 @@
       </c>
       <c r="C224" s="11" t="inlineStr">
         <is>
-          <t>Switch On duty in the sidebar to start taking calls. It follows you across every page, so you no longer have to keep this one open.</t>
+          <t>You are on duty, so waiting customers can be routed to you. Go off duty from the sidebar when you step away — you stay on the air anywhere in the console until you do.</t>
         </is>
       </c>
       <c r="D224" s="12" t="inlineStr">
         <is>
-          <t>ጥሪዎችን መቀበል ለመጀመር ከጎን አሞሌው “በሥራ ላይ” ያብሩ። በሁሉም ገጽ ላይ ይከተልዎታል፤ ስለዚህ ይህን ገጽ ክፍት ማድረግ አያስፈልግም።</t>
+          <t>በሥራ ላይ ነዎት፤ ስለዚህ የሚጠብቁ ደንበኞች ወደ እርስዎ ሊመሩ ይችላሉ። ሲርቁ ከጎን አሞሌው ከሥራ ውጡ — እስከዚያ ድረስ በየትኛውም ገጽ ላይ በሥራ ላይ ይቆያሉ።</t>
         </is>
       </c>
       <c r="E224" s="13" t="inlineStr">
         <is>
-          <t>Bilbila fudhachuu jalqabuuf cinaacha irraa “Hojii irra” banaa. Fuula hunda irratti isin hordofa, kanaafuu fuula kana banaa gochuun hin barbaachisu.</t>
+          <t>Hojii irra jirtu, kanaafuu maamiltoonni eegaa jiran gara keessan qajeelfamuu danda'u. Yeroo achii deemtan cinaacha irraa hojii keessaa ba'aa — hanga sanatti fuula kamiyyuu irratti hojii irra turtu.</t>
         </is>
       </c>
       <c r="F224" s="12" t="inlineStr">
         <is>
-          <t>ጻውዒታት ክትቅበሉ ንምጅማር ካብ ናይ ጎኒ መስመር “ኣብ ስራሕ” ኣብርሁ። ኣብ ኩሉ ገጽ ይስዕበኩም፣ ስለዚ ነዚ ገጽ ክፉት ምግባር ኣየድልን።</t>
+          <t>ኣብ ስራሕ ኢኹም፣ ስለዚ ዝጽበዩ ዓማዊል ናባኹም ክምርሑ ይኽእሉ። ክትርሕቁ ከለኹም ካብ ናይ ጎኒ መስመር ካብ ስራሕ ውጹ — ክሳብ ሽዑ ኣብ ዝኾነ ገጽ ኣብ ስራሕ ትጸንሑ።</t>
         </is>
       </c>
       <c r="G224" s="13" t="inlineStr">
         <is>
-          <t>Si aad u bilowdo qaadista wicitaannada, dhinaca ka shid “Shaqada”. Bog kasta ayuu kula socdaa, sidaas darteed uma baahnid inaad tan furan ka tagto.</t>
+          <t>Shaqada ayaad joogtaa, sidaas darteed macaamiisha sugaya waa lagu soo dhiibi karaa. Marka aad tagto shaqada ka bax dhinaca — ilaa markaas bog kasta ayaad ku sii shaqeynaysaa.</t>
         </is>
       </c>
       <c r="H224" s="14" t="inlineStr"/>
@@ -13957,7 +13957,7 @@
     <row r="225" ht="44" customHeight="1">
       <c r="A225" s="11" t="inlineStr">
         <is>
-          <t>colleague_must_be_on_duty</t>
+          <t>off_duty_explainer</t>
         </is>
       </c>
       <c r="B225" s="11" t="inlineStr">
@@ -13967,27 +13967,27 @@
       </c>
       <c r="C225" s="11" t="inlineStr">
         <is>
-          <t>A colleague with permission to take calls has to be on duty before customers are offered one.</t>
+          <t>Switch On duty in the sidebar to start taking calls. It follows you across every page, so you no longer have to keep this one open.</t>
         </is>
       </c>
       <c r="D225" s="12" t="inlineStr">
         <is>
-          <t>ጥሪ የመቀበል ፈቃድ ያለው ባልደረባ በሥራ ላይ መሆን አለበት፤ ከዚያ በፊት ለደንበኞች አይቀርብም።</t>
+          <t>ጥሪዎችን መቀበል ለመጀመር ከጎን አሞሌው “በሥራ ላይ” ያብሩ። በሁሉም ገጽ ላይ ይከተልዎታል፤ ስለዚህ ይህን ገጽ ክፍት ማድረግ አያስፈልግም።</t>
         </is>
       </c>
       <c r="E225" s="13" t="inlineStr">
         <is>
-          <t>Hojjetaan hayyama bilbila fudhachuu qabu hojii irra jiraachuu qaba, sana dura maamiltootaaf hin dhiyaatu.</t>
+          <t>Bilbila fudhachuu jalqabuuf cinaacha irraa “Hojii irra” banaa. Fuula hunda irratti isin hordofa, kanaafuu fuula kana banaa gochuun hin barbaachisu.</t>
         </is>
       </c>
       <c r="F225" s="12" t="inlineStr">
         <is>
-          <t>ጻውዒት ናይ ምቕባል ፍቓድ ዘለዎ መሳርሕቲ ኣብ ስራሕ ክህሉ ኣለዎ፣ ቅድሚኡ ንዓማዊል ኣይቀርብን።</t>
+          <t>ጻውዒታት ክትቅበሉ ንምጅማር ካብ ናይ ጎኒ መስመር “ኣብ ስራሕ” ኣብርሁ። ኣብ ኩሉ ገጽ ይስዕበኩም፣ ስለዚ ነዚ ገጽ ክፉት ምግባር ኣየድልን።</t>
         </is>
       </c>
       <c r="G225" s="13" t="inlineStr">
         <is>
-          <t>Shaqaale haysta ogolaanshaha qaadista wicitaannada waa inuu shaqada joogaa ka hor inta aan macaamiisha la siin.</t>
+          <t>Si aad u bilowdo qaadista wicitaannada, dhinaca ka shid “Shaqada”. Bog kasta ayuu kula socdaa, sidaas darteed uma baahnid inaad tan furan ka tagto.</t>
         </is>
       </c>
       <c r="H225" s="14" t="inlineStr"/>
@@ -13995,7 +13995,7 @@
     <row r="226" ht="44" customHeight="1">
       <c r="A226" s="11" t="inlineStr">
         <is>
-          <t>i_can_converse_in</t>
+          <t>colleague_must_be_on_duty</t>
         </is>
       </c>
       <c r="B226" s="11" t="inlineStr">
@@ -14005,27 +14005,27 @@
       </c>
       <c r="C226" s="11" t="inlineStr">
         <is>
-          <t>I can hold a conversation in:</t>
+          <t>A colleague with permission to take calls has to be on duty before customers are offered one.</t>
         </is>
       </c>
       <c r="D226" s="12" t="inlineStr">
         <is>
-          <t>በእነዚህ ቋንቋዎች መነጋገር እችላለሁ፦</t>
+          <t>ጥሪ የመቀበል ፈቃድ ያለው ባልደረባ በሥራ ላይ መሆን አለበት፤ ከዚያ በፊት ለደንበኞች አይቀርብም።</t>
         </is>
       </c>
       <c r="E226" s="13" t="inlineStr">
         <is>
-          <t>Afaanota kanneeniin haasa'uu nan danda'a:</t>
+          <t>Hojjetaan hayyama bilbila fudhachuu qabu hojii irra jiraachuu qaba, sana dura maamiltootaaf hin dhiyaatu.</t>
         </is>
       </c>
       <c r="F226" s="12" t="inlineStr">
         <is>
-          <t>በዞም ቋንቋታት ክዛረብ እኽእል፦</t>
+          <t>ጻውዒት ናይ ምቕባል ፍቓድ ዘለዎ መሳርሕቲ ኣብ ስራሕ ክህሉ ኣለዎ፣ ቅድሚኡ ንዓማዊል ኣይቀርብን።</t>
         </is>
       </c>
       <c r="G226" s="13" t="inlineStr">
         <is>
-          <t>Waxaan ku hadli karaa:</t>
+          <t>Shaqaale haysta ogolaanshaha qaadista wicitaannada waa inuu shaqada joogaa ka hor inta aan macaamiisha la siin.</t>
         </is>
       </c>
       <c r="H226" s="14" t="inlineStr"/>
@@ -14033,7 +14033,7 @@
     <row r="227" ht="44" customHeight="1">
       <c r="A227" s="11" t="inlineStr">
         <is>
-          <t>languages_picked_note</t>
+          <t>i_can_converse_in</t>
         </is>
       </c>
       <c r="B227" s="11" t="inlineStr">
@@ -14043,27 +14043,27 @@
       </c>
       <c r="C227" s="11" t="inlineStr">
         <is>
-          <t>Customers writing in these reach you first. Everyone else still reaches you — after a short wait, so nobody is stranded.</t>
+          <t>I can hold a conversation in:</t>
         </is>
       </c>
       <c r="D227" s="12" t="inlineStr">
         <is>
-          <t>በእነዚህ ቋንቋዎች የሚጽፉ ደንበኞች መጀመሪያ ወደ እርስዎ ይደርሳሉ። ሌሎችም ይደርሳሉ — ከአጭር ጥበቃ በኋላ፤ ማንም አይቀርም።</t>
+          <t>በእነዚህ ቋንቋዎች መነጋገር እችላለሁ፦</t>
         </is>
       </c>
       <c r="E227" s="13" t="inlineStr">
         <is>
-          <t>Maamiltoonni afaanota kanaan barreessan jalqaba isin bira ga'u. Kaan hundinuu ammas isin bira ga'u — eegumsa gabaabaa booda, namni hafu hin jiru.</t>
+          <t>Afaanota kanneeniin haasa'uu nan danda'a:</t>
         </is>
       </c>
       <c r="F227" s="12" t="inlineStr">
         <is>
-          <t>በዞም ቋንቋታት ዝጽሕፉ ዓማዊል ቅድም ናባኹም ይበጽሑ። እቶም ካልኦት እውን ይበጽሑ — ድሕሪ ሓጺር ጽበት፣ ዋላ ሓደ ኣይተርፍን።</t>
+          <t>በዞም ቋንቋታት ክዛረብ እኽእል፦</t>
         </is>
       </c>
       <c r="G227" s="13" t="inlineStr">
         <is>
-          <t>Macaamiisha ku qora kuwan ayaa marka hore kugu soo gaara. Qof kastana wuu ku soo gaari doonaa — sug gaaban ka dib, sidaas qofna ma harayo.</t>
+          <t>Waxaan ku hadli karaa:</t>
         </is>
       </c>
       <c r="H227" s="14" t="inlineStr"/>
@@ -14071,7 +14071,7 @@
     <row r="228" ht="44" customHeight="1">
       <c r="A228" s="11" t="inlineStr">
         <is>
-          <t>languages_none_note</t>
+          <t>languages_picked_note</t>
         </is>
       </c>
       <c r="B228" s="11" t="inlineStr">
@@ -14081,27 +14081,27 @@
       </c>
       <c r="C228" s="11" t="inlineStr">
         <is>
-          <t>Nothing selected, so every waiting customer is offered to you in plain oldest-first order.</t>
+          <t>Customers writing in these reach you first. Everyone else still reaches you — after a short wait, so nobody is stranded.</t>
         </is>
       </c>
       <c r="D228" s="12" t="inlineStr">
         <is>
-          <t>ምንም አልተመረጠም፤ ስለዚህ እያንዳንዱ የሚጠብቅ ደንበኛ በቀላል ቀዳሚ-መጀመሪያ ቅደም ተከተል ይቀርብልዎታል።</t>
+          <t>በእነዚህ ቋንቋዎች የሚጽፉ ደንበኞች መጀመሪያ ወደ እርስዎ ይደርሳሉ። ሌሎችም ይደርሳሉ — ከአጭር ጥበቃ በኋላ፤ ማንም አይቀርም።</t>
         </is>
       </c>
       <c r="E228" s="13" t="inlineStr">
         <is>
-          <t>Wanti filatame hin jiru, kanaafuu maamilli eegaa jiru hundi tartiiba dursaa-jalqabaatiin isinii dhiyaata.</t>
+          <t>Maamiltoonni afaanota kanaan barreessan jalqaba isin bira ga'u. Kaan hundinuu ammas isin bira ga'u — eegumsa gabaabaa booda, namni hafu hin jiru.</t>
         </is>
       </c>
       <c r="F228" s="12" t="inlineStr">
         <is>
-          <t>ዋላ ሓደ ኣይተመርጸን፣ ስለዚ ነፍስ ወከፍ ዝጽበ ዓሚል ብቐሊል ናይ ቀዳምነት ስርዓት ይቐርበልኩም።</t>
+          <t>በዞም ቋንቋታት ዝጽሕፉ ዓማዊል ቅድም ናባኹም ይበጽሑ። እቶም ካልኦት እውን ይበጽሑ — ድሕሪ ሓጺር ጽበት፣ ዋላ ሓደ ኣይተርፍን።</t>
         </is>
       </c>
       <c r="G228" s="13" t="inlineStr">
         <is>
-          <t>Waxba lama dooran, sidaas darteed macmiil kasta oo sugaya waxaa laguu soo bandhigayaa sida caadiga ah ee ugu horreeya.</t>
+          <t>Macaamiisha ku qora kuwan ayaa marka hore kugu soo gaara. Qof kastana wuu ku soo gaari doonaa — sug gaaban ka dib, sidaas qofna ma harayo.</t>
         </is>
       </c>
       <c r="H228" s="14" t="inlineStr"/>
@@ -14109,7 +14109,7 @@
     <row r="229" ht="44" customHeight="1">
       <c r="A229" s="11" t="inlineStr">
         <is>
-          <t>languages_updated</t>
+          <t>languages_none_note</t>
         </is>
       </c>
       <c r="B229" s="11" t="inlineStr">
@@ -14119,27 +14119,27 @@
       </c>
       <c r="C229" s="11" t="inlineStr">
         <is>
-          <t>Languages updated</t>
+          <t>Nothing selected, so every waiting customer is offered to you in plain oldest-first order.</t>
         </is>
       </c>
       <c r="D229" s="12" t="inlineStr">
         <is>
-          <t>ቋንቋዎች ተዘምነዋል</t>
+          <t>ምንም አልተመረጠም፤ ስለዚህ እያንዳንዱ የሚጠብቅ ደንበኛ በቀላል ቀዳሚ-መጀመሪያ ቅደም ተከተል ይቀርብልዎታል።</t>
         </is>
       </c>
       <c r="E229" s="13" t="inlineStr">
         <is>
-          <t>Afaanonni haaromfaman</t>
+          <t>Wanti filatame hin jiru, kanaafuu maamilli eegaa jiru hundi tartiiba dursaa-jalqabaatiin isinii dhiyaata.</t>
         </is>
       </c>
       <c r="F229" s="12" t="inlineStr">
         <is>
-          <t>ቋንቋታት ተሓዲሶም</t>
+          <t>ዋላ ሓደ ኣይተመርጸን፣ ስለዚ ነፍስ ወከፍ ዝጽበ ዓሚል ብቐሊል ናይ ቀዳምነት ስርዓት ይቐርበልኩም።</t>
         </is>
       </c>
       <c r="G229" s="13" t="inlineStr">
         <is>
-          <t>Luqadaha waa la cusbooneysiiyay</t>
+          <t>Waxba lama dooran, sidaas darteed macmiil kasta oo sugaya waxaa laguu soo bandhigayaa sida caadiga ah ee ugu horreeya.</t>
         </is>
       </c>
       <c r="H229" s="14" t="inlineStr"/>
@@ -14147,7 +14147,7 @@
     <row r="230" ht="44" customHeight="1">
       <c r="A230" s="11" t="inlineStr">
         <is>
-          <t>media_video</t>
+          <t>languages_updated</t>
         </is>
       </c>
       <c r="B230" s="11" t="inlineStr">
@@ -14157,27 +14157,27 @@
       </c>
       <c r="C230" s="11" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Languages updated</t>
         </is>
       </c>
       <c r="D230" s="12" t="inlineStr">
         <is>
-          <t>ቪዲዮ</t>
+          <t>ቋንቋዎች ተዘምነዋል</t>
         </is>
       </c>
       <c r="E230" s="13" t="inlineStr">
         <is>
-          <t>Viidiyoo</t>
+          <t>Afaanonni haaromfaman</t>
         </is>
       </c>
       <c r="F230" s="12" t="inlineStr">
         <is>
-          <t>ቪድዮ</t>
+          <t>ቋንቋታት ተሓዲሶም</t>
         </is>
       </c>
       <c r="G230" s="13" t="inlineStr">
         <is>
-          <t>Fiidyow</t>
+          <t>Luqadaha waa la cusbooneysiiyay</t>
         </is>
       </c>
       <c r="H230" s="14" t="inlineStr"/>
@@ -14185,7 +14185,7 @@
     <row r="231" ht="44" customHeight="1">
       <c r="A231" s="11" t="inlineStr">
         <is>
-          <t>media_audio</t>
+          <t>media_video</t>
         </is>
       </c>
       <c r="B231" s="11" t="inlineStr">
@@ -14195,27 +14195,27 @@
       </c>
       <c r="C231" s="11" t="inlineStr">
         <is>
-          <t>Audio</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="D231" s="12" t="inlineStr">
         <is>
-          <t>ድምፅ</t>
+          <t>ቪዲዮ</t>
         </is>
       </c>
       <c r="E231" s="13" t="inlineStr">
         <is>
-          <t>Sagalee</t>
+          <t>Viidiyoo</t>
         </is>
       </c>
       <c r="F231" s="12" t="inlineStr">
         <is>
-          <t>ድምጺ</t>
+          <t>ቪድዮ</t>
         </is>
       </c>
       <c r="G231" s="13" t="inlineStr">
         <is>
-          <t>Cod</t>
+          <t>Fiidyow</t>
         </is>
       </c>
       <c r="H231" s="14" t="inlineStr"/>
@@ -14223,7 +14223,7 @@
     <row r="232" ht="44" customHeight="1">
       <c r="A232" s="11" t="inlineStr">
         <is>
-          <t>not_your_language</t>
+          <t>media_audio</t>
         </is>
       </c>
       <c r="B232" s="11" t="inlineStr">
@@ -14233,27 +14233,27 @@
       </c>
       <c r="C232" s="11" t="inlineStr">
         <is>
-          <t>not your language</t>
+          <t>Audio</t>
         </is>
       </c>
       <c r="D232" s="12" t="inlineStr">
         <is>
-          <t>የእርስዎ ቋንቋ አይደለም</t>
+          <t>ድምፅ</t>
         </is>
       </c>
       <c r="E232" s="13" t="inlineStr">
         <is>
-          <t>afaan keessanii miti</t>
+          <t>Sagalee</t>
         </is>
       </c>
       <c r="F232" s="12" t="inlineStr">
         <is>
-          <t>ናትኩም ቋንቋ ኣይኮነን</t>
+          <t>ድምጺ</t>
         </is>
       </c>
       <c r="G232" s="13" t="inlineStr">
         <is>
-          <t>ma aha luqaddaada</t>
+          <t>Cod</t>
         </is>
       </c>
       <c r="H232" s="14" t="inlineStr"/>
@@ -14261,7 +14261,7 @@
     <row r="233" ht="44" customHeight="1">
       <c r="A233" s="11" t="inlineStr">
         <is>
-          <t>languages_first_note</t>
+          <t>not_your_language</t>
         </is>
       </c>
       <c r="B233" s="11" t="inlineStr">
@@ -14271,27 +14271,27 @@
       </c>
       <c r="C233" s="11" t="inlineStr">
         <is>
-          <t>Your languages first, longest wait within each. Anyone waiting too long moves to the top whatever they speak.</t>
+          <t>not your language</t>
         </is>
       </c>
       <c r="D233" s="12" t="inlineStr">
         <is>
-          <t>የእርስዎ ቋንቋዎች መጀመሪያ፤ በእያንዳንዱ ውስጥ ረጅም የጠበቀው ይቀድማል። ከልክ በላይ የጠበቀ ማንኛውም ሰው የሚናገረው ምንም ይሁን ወደ ላይ ይወጣል።</t>
+          <t>የእርስዎ ቋንቋ አይደለም</t>
         </is>
       </c>
       <c r="E233" s="13" t="inlineStr">
         <is>
-          <t>Afaanonni keessan jalqaba, tokkoon tokkoon isaanii keessatti kan yeroo dheeraa eege dursa. Namni baay'ee eege afaan kamiyyuu haa dubbatu gara oliitti deema.</t>
+          <t>afaan keessanii miti</t>
         </is>
       </c>
       <c r="F233" s="12" t="inlineStr">
         <is>
-          <t>ቋንቋታትኩም ቅድም፣ ኣብ ነፍስ ወከፍ እቲ ነዊሕ ዝጸንሐ ይቐድም። ካብ ንቡር ንላዕሊ ዝጸንሐ ዝኾነ ሰብ ዝዛረቦ ብዘየገድስ ናብ ላዕሊ ይመጽእ።</t>
+          <t>ናትኩም ቋንቋ ኣይኮነን</t>
         </is>
       </c>
       <c r="G233" s="13" t="inlineStr">
         <is>
-          <t>Luqadahaaga marka hore, kii ugu sugay dheeraa mid kasta gudahood. Qof kasta oo aad u sugay ayaa kor u kaca luqad kastoo uu ku hadloba.</t>
+          <t>ma aha luqaddaada</t>
         </is>
       </c>
       <c r="H233" s="14" t="inlineStr"/>
@@ -14299,7 +14299,7 @@
     <row r="234" ht="44" customHeight="1">
       <c r="A234" s="11" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>languages_first_note</t>
         </is>
       </c>
       <c r="B234" s="11" t="inlineStr">
@@ -14309,27 +14309,27 @@
       </c>
       <c r="C234" s="11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Your languages first, longest wait within each. Anyone waiting too long moves to the top whatever they speak.</t>
         </is>
       </c>
       <c r="D234" s="12" t="inlineStr">
         <is>
-          <t>በሂደት ላይ</t>
+          <t>የእርስዎ ቋንቋዎች መጀመሪያ፤ በእያንዳንዱ ውስጥ ረጅም የጠበቀው ይቀድማል። ከልክ በላይ የጠበቀ ማንኛውም ሰው የሚናገረው ምንም ይሁን ወደ ላይ ይወጣል።</t>
         </is>
       </c>
       <c r="E234" s="13" t="inlineStr">
         <is>
-          <t>Adeemsa irra</t>
+          <t>Afaanonni keessan jalqaba, tokkoon tokkoon isaanii keessatti kan yeroo dheeraa eege dursa. Namni baay'ee eege afaan kamiyyuu haa dubbatu gara oliitti deema.</t>
         </is>
       </c>
       <c r="F234" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መስርሕ</t>
+          <t>ቋንቋታትኩም ቅድም፣ ኣብ ነፍስ ወከፍ እቲ ነዊሕ ዝጸንሐ ይቐድም። ካብ ንቡር ንላዕሊ ዝጸንሐ ዝኾነ ሰብ ዝዛረቦ ብዘየገድስ ናብ ላዕሊ ይመጽእ።</t>
         </is>
       </c>
       <c r="G234" s="13" t="inlineStr">
         <is>
-          <t>Socda</t>
+          <t>Luqadahaaga marka hore, kii ugu sugay dheeraa mid kasta gudahood. Qof kasta oo aad u sugay ayaa kor u kaca luqad kastoo uu ku hadloba.</t>
         </is>
       </c>
       <c r="H234" s="14" t="inlineStr"/>
@@ -14337,7 +14337,7 @@
     <row r="235" ht="44" customHeight="1">
       <c r="A235" s="11" t="inlineStr">
         <is>
-          <t>no_session_in_progress</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="B235" s="11" t="inlineStr">
@@ -14347,27 +14347,27 @@
       </c>
       <c r="C235" s="11" t="inlineStr">
         <is>
-          <t>No session in progress.</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="D235" s="12" t="inlineStr">
         <is>
-          <t>በሂደት ላይ ያለ ክፍለ-ጊዜ የለም።</t>
+          <t>በሂደት ላይ</t>
         </is>
       </c>
       <c r="E235" s="13" t="inlineStr">
         <is>
-          <t>Sessionii adeemsa irra jiru hin jiru.</t>
+          <t>Adeemsa irra</t>
         </is>
       </c>
       <c r="F235" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መስርሕ ዘሎ ክፍለ-ግዜ የለን።</t>
+          <t>ኣብ መስርሕ</t>
         </is>
       </c>
       <c r="G235" s="13" t="inlineStr">
         <is>
-          <t>Ma jiro kalfadhi socda.</t>
+          <t>Socda</t>
         </is>
       </c>
       <c r="H235" s="14" t="inlineStr"/>
@@ -14375,7 +14375,7 @@
     <row r="236" ht="44" customHeight="1">
       <c r="A236" s="11" t="inlineStr">
         <is>
-          <t>wait_suffix</t>
+          <t>no_session_in_progress</t>
         </is>
       </c>
       <c r="B236" s="11" t="inlineStr">
@@ -14385,27 +14385,27 @@
       </c>
       <c r="C236" s="11" t="inlineStr">
         <is>
-          <t>wait</t>
+          <t>No session in progress.</t>
         </is>
       </c>
       <c r="D236" s="12" t="inlineStr">
         <is>
-          <t>ጥበቃ</t>
+          <t>በሂደት ላይ ያለ ክፍለ-ጊዜ የለም።</t>
         </is>
       </c>
       <c r="E236" s="13" t="inlineStr">
         <is>
-          <t>eegumsa</t>
+          <t>Sessionii adeemsa irra jiru hin jiru.</t>
         </is>
       </c>
       <c r="F236" s="12" t="inlineStr">
         <is>
-          <t>ጽበት</t>
+          <t>ኣብ መስርሕ ዘሎ ክፍለ-ግዜ የለን።</t>
         </is>
       </c>
       <c r="G236" s="13" t="inlineStr">
         <is>
-          <t>sug</t>
+          <t>Ma jiro kalfadhi socda.</t>
         </is>
       </c>
       <c r="H236" s="14" t="inlineStr"/>
@@ -14413,7 +14413,7 @@
     <row r="237" ht="44" customHeight="1">
       <c r="A237" s="11" t="inlineStr">
         <is>
-          <t>what_session_covers</t>
+          <t>wait_suffix</t>
         </is>
       </c>
       <c r="B237" s="11" t="inlineStr">
@@ -14423,27 +14423,27 @@
       </c>
       <c r="C237" s="11" t="inlineStr">
         <is>
-          <t>What a session covers</t>
+          <t>wait</t>
         </is>
       </c>
       <c r="D237" s="12" t="inlineStr">
         <is>
-          <t>አንድ ክፍለ-ጊዜ ምን ይሸፍናል</t>
+          <t>ጥበቃ</t>
         </is>
       </c>
       <c r="E237" s="13" t="inlineStr">
         <is>
-          <t>Sessioniin maal haguuga</t>
+          <t>eegumsa</t>
         </is>
       </c>
       <c r="F237" s="12" t="inlineStr">
         <is>
-          <t>ሓደ ክፍለ-ግዜ እንታይ ይሽፍን</t>
+          <t>ጽበት</t>
         </is>
       </c>
       <c r="G237" s="13" t="inlineStr">
         <is>
-          <t>Waxa kalfadhigu daboolo</t>
+          <t>sug</t>
         </is>
       </c>
       <c r="H237" s="14" t="inlineStr"/>
@@ -14451,7 +14451,7 @@
     <row r="238" ht="44" customHeight="1">
       <c r="A238" s="11" t="inlineStr">
         <is>
-          <t>session_scope_body</t>
+          <t>what_session_covers</t>
         </is>
       </c>
       <c r="B238" s="11" t="inlineStr">
@@ -14461,27 +14461,27 @@
       </c>
       <c r="C238" s="11" t="inlineStr">
         <is>
-          <t>Before someone is identified: general questions about products, eligibility and how to apply. Once you have checked their Fayda ID against the account and asked something only the account holder could answer: their own application, documents and disputes.</t>
+          <t>What a session covers</t>
         </is>
       </c>
       <c r="D238" s="12" t="inlineStr">
         <is>
-          <t>አንድ ሰው ከመለየቱ በፊት፦ ስለ ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል አጠቃላይ ጥያቄዎች። የፋይዳ መታወቂያቸውን ከሂሳቡ ጋር አመሳክረው የሂሳቡ ባለቤት ብቻ ሊመልሰው የሚችለውን ከጠየቁ በኋላ፦ የራሳቸው ማመልከቻ፣ ሰነዶችና ቅሬታዎች።</t>
+          <t>አንድ ክፍለ-ጊዜ ምን ይሸፍናል</t>
         </is>
       </c>
       <c r="E238" s="13" t="inlineStr">
         <is>
-          <t>Namni tokko utuu hin beekamin dura: gaaffii waliigalaa waa'ee oomishaalee, ulaagaa fi akkaataa itti iyyatan. Erga waraqaa eenyummaa Fayda isaanii herrega waliin madaalchiftanii waan abbaan herregaa qofti deebisuu danda'u gaafattanii booda: iyyannoo, sanadoota fi komii isaanii.</t>
+          <t>Sessioniin maal haguuga</t>
         </is>
       </c>
       <c r="F238" s="12" t="inlineStr">
         <is>
-          <t>ሓደ ሰብ ቅድሚ ምልላዩ፦ ብዛዕባ ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን ሓፈሻዊ ሕቶታት። መንነት ፋይዳኦም ምስ ሕሳብ ኣረጋጊጽኩም እቲ ወናኒ ሕሳብ ጥራይ ክምልሶ ዝኽእል ምስ ሓተትኩም፦ ናቶም ምልክታ፣ ሰነዳትን ጥርዓናትን።</t>
+          <t>ሓደ ክፍለ-ግዜ እንታይ ይሽፍን</t>
         </is>
       </c>
       <c r="G238" s="13" t="inlineStr">
         <is>
-          <t>Ka hor inta aan qofka la aqoonsan: su'aalo guud oo ku saabsan alaabta, u-qalmitaanka iyo sida loo codsado. Marka aad hubiso aqoonsigooda Fayda ee xisaabta oo aad weydiiso wax uu kaliya milkiilaha xisaabtu ka jawaabi karo: codsigooda, dukumiintiyada iyo cabashooyinka.</t>
+          <t>Waxa kalfadhigu daboolo</t>
         </is>
       </c>
       <c r="H238" s="14" t="inlineStr"/>
@@ -14489,7 +14489,7 @@
     <row r="239" ht="44" customHeight="1">
       <c r="A239" s="11" t="inlineStr">
         <is>
-          <t>never_money_movement</t>
+          <t>session_scope_body</t>
         </is>
       </c>
       <c r="B239" s="11" t="inlineStr">
@@ -14499,27 +14499,27 @@
       </c>
       <c r="C239" s="11" t="inlineStr">
         <is>
-          <t>Never, at any point and for anyone: deposits, withdrawals or transfers. Those do not happen on a call.</t>
+          <t>Before someone is identified: general questions about products, eligibility and how to apply. Once you have checked their Fayda ID against the account and asked something only the account holder could answer: their own application, documents and disputes.</t>
         </is>
       </c>
       <c r="D239" s="12" t="inlineStr">
         <is>
-          <t>በፍጹም፣ በማንኛውም ጊዜና ለማንም፦ ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም። እነዚያ በጥሪ ላይ አይፈጸሙም።</t>
+          <t>አንድ ሰው ከመለየቱ በፊት፦ ስለ ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል አጠቃላይ ጥያቄዎች። የፋይዳ መታወቂያቸውን ከሂሳቡ ጋር አመሳክረው የሂሳቡ ባለቤት ብቻ ሊመልሰው የሚችለውን ከጠየቁ በኋላ፦ የራሳቸው ማመልከቻ፣ ሰነዶችና ቅሬታዎች።</t>
         </is>
       </c>
       <c r="E239" s="13" t="inlineStr">
         <is>
-          <t>Gonkumaa, yeroo kamiyyuu fi eenyuufiyyuu: kuusaa, baasii yookiin dabarsa hin jiru. Isaan sun bilbila irratti hin raawwataman.</t>
+          <t>Namni tokko utuu hin beekamin dura: gaaffii waliigalaa waa'ee oomishaalee, ulaagaa fi akkaataa itti iyyatan. Erga waraqaa eenyummaa Fayda isaanii herrega waliin madaalchiftanii waan abbaan herregaa qofti deebisuu danda'u gaafattanii booda: iyyannoo, sanadoota fi komii isaanii.</t>
         </is>
       </c>
       <c r="F239" s="12" t="inlineStr">
         <is>
-          <t>ፈጺሙ፣ ኣብ ዝኾነ እዋንን ንዝኾነ ሰብን፦ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን። እዚኣቶም ኣብ ጻውዒት ኣይፍጸሙን።</t>
+          <t>ሓደ ሰብ ቅድሚ ምልላዩ፦ ብዛዕባ ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን ሓፈሻዊ ሕቶታት። መንነት ፋይዳኦም ምስ ሕሳብ ኣረጋጊጽኩም እቲ ወናኒ ሕሳብ ጥራይ ክምልሶ ዝኽእል ምስ ሓተትኩም፦ ናቶም ምልክታ፣ ሰነዳትን ጥርዓናትን።</t>
         </is>
       </c>
       <c r="G239" s="13" t="inlineStr">
         <is>
-          <t>Weligaa, wakhti kasta iyo qof kasta: dhigasho, qaadis ama wareejin ma jirto. Kuwaas wicitaan laguma sameeyo.</t>
+          <t>Ka hor inta aan qofka la aqoonsan: su'aalo guud oo ku saabsan alaabta, u-qalmitaanka iyo sida loo codsado. Marka aad hubiso aqoonsigooda Fayda ee xisaabta oo aad weydiiso wax uu kaliya milkiilaha xisaabtu ka jawaabi karo: codsigooda, dukumiintiyada iyo cabashooyinka.</t>
         </is>
       </c>
       <c r="H239" s="14" t="inlineStr"/>
@@ -14527,7 +14527,7 @@
     <row r="240" ht="44" customHeight="1">
       <c r="A240" s="11" t="inlineStr">
         <is>
-          <t>open_escalation_queue</t>
+          <t>never_money_movement</t>
         </is>
       </c>
       <c r="B240" s="11" t="inlineStr">
@@ -14537,27 +14537,27 @@
       </c>
       <c r="C240" s="11" t="inlineStr">
         <is>
-          <t>Open the escalation queue</t>
+          <t>Never, at any point and for anyone: deposits, withdrawals or transfers. Those do not happen on a call.</t>
         </is>
       </c>
       <c r="D240" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ወረፋውን ክፈት</t>
+          <t>በፍጹም፣ በማንኛውም ጊዜና ለማንም፦ ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም። እነዚያ በጥሪ ላይ አይፈጸሙም።</t>
         </is>
       </c>
       <c r="E240" s="13" t="inlineStr">
         <is>
-          <t>Sararaa dabarsaa banaa</t>
+          <t>Gonkumaa, yeroo kamiyyuu fi eenyuufiyyuu: kuusaa, baasii yookiin dabarsa hin jiru. Isaan sun bilbila irratti hin raawwataman.</t>
         </is>
       </c>
       <c r="F240" s="12" t="inlineStr">
         <is>
-          <t>ሪጋ ምትሕልላፍ ክፈት</t>
+          <t>ፈጺሙ፣ ኣብ ዝኾነ እዋንን ንዝኾነ ሰብን፦ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን። እዚኣቶም ኣብ ጻውዒት ኣይፍጸሙን።</t>
         </is>
       </c>
       <c r="G240" s="13" t="inlineStr">
         <is>
-          <t>Fur safka gudbinta</t>
+          <t>Weligaa, wakhti kasta iyo qof kasta: dhigasho, qaadis ama wareejin ma jirto. Kuwaas wicitaan laguma sameeyo.</t>
         </is>
       </c>
       <c r="H240" s="14" t="inlineStr"/>
@@ -14565,7 +14565,7 @@
     <row r="241" ht="44" customHeight="1">
       <c r="A241" s="11" t="inlineStr">
         <is>
-          <t>switch_dark_light</t>
+          <t>open_escalation_queue</t>
         </is>
       </c>
       <c r="B241" s="11" t="inlineStr">
@@ -14575,27 +14575,27 @@
       </c>
       <c r="C241" s="11" t="inlineStr">
         <is>
-          <t>Switch between dark and light</t>
+          <t>Open the escalation queue</t>
         </is>
       </c>
       <c r="D241" s="12" t="inlineStr">
         <is>
-          <t>በጨለማና በብርሃን መካከል ቀይር</t>
+          <t>የማሸጋገሪያ ወረፋውን ክፈት</t>
         </is>
       </c>
       <c r="E241" s="13" t="inlineStr">
         <is>
-          <t>Dukkanaa fi ifa gidduu jijjiiri</t>
+          <t>Sararaa dabarsaa banaa</t>
         </is>
       </c>
       <c r="F241" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መንጎ ጸላምን ብርሃንን ቀይር</t>
+          <t>ሪጋ ምትሕልላፍ ክፈት</t>
         </is>
       </c>
       <c r="G241" s="13" t="inlineStr">
         <is>
-          <t>U beddel mugdiga iyo iftiinka</t>
+          <t>Fur safka gudbinta</t>
         </is>
       </c>
       <c r="H241" s="14" t="inlineStr"/>
@@ -14603,7 +14603,7 @@
     <row r="242" ht="44" customHeight="1">
       <c r="A242" s="11" t="inlineStr">
         <is>
-          <t>live_session</t>
+          <t>switch_dark_light</t>
         </is>
       </c>
       <c r="B242" s="11" t="inlineStr">
@@ -14613,27 +14613,27 @@
       </c>
       <c r="C242" s="11" t="inlineStr">
         <is>
-          <t>Live session</t>
+          <t>Switch between dark and light</t>
         </is>
       </c>
       <c r="D242" s="12" t="inlineStr">
         <is>
-          <t>የቀጥታ ክፍለ-ጊዜ</t>
+          <t>በጨለማና በብርሃን መካከል ቀይር</t>
         </is>
       </c>
       <c r="E242" s="13" t="inlineStr">
         <is>
-          <t>Session kallattii</t>
+          <t>Dukkanaa fi ifa gidduu jijjiiri</t>
         </is>
       </c>
       <c r="F242" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታ ክፍለ-ግዜ</t>
+          <t>ኣብ መንጎ ጸላምን ብርሃንን ቀይር</t>
         </is>
       </c>
       <c r="G242" s="13" t="inlineStr">
         <is>
-          <t>Kalfadhi toos ah</t>
+          <t>U beddel mugdiga iyo iftiinka</t>
         </is>
       </c>
       <c r="H242" s="14" t="inlineStr"/>
@@ -14641,7 +14641,7 @@
     <row r="243" ht="44" customHeight="1">
       <c r="A243" s="11" t="inlineStr">
         <is>
-          <t>customer_left_call</t>
+          <t>live_session</t>
         </is>
       </c>
       <c r="B243" s="11" t="inlineStr">
@@ -14651,27 +14651,27 @@
       </c>
       <c r="C243" s="11" t="inlineStr">
         <is>
-          <t>The customer has left the call.</t>
+          <t>Live session</t>
         </is>
       </c>
       <c r="D243" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛው ጥሪውን ለቅቋል።</t>
+          <t>የቀጥታ ክፍለ-ጊዜ</t>
         </is>
       </c>
       <c r="E243" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan bilbila irraa ba'eera.</t>
+          <t>Session kallattii</t>
         </is>
       </c>
       <c r="F243" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዓሚል ካብቲ ጻውዒት ወጺኡ።</t>
+          <t>ቀጥታ ክፍለ-ግዜ</t>
         </is>
       </c>
       <c r="G243" s="13" t="inlineStr">
         <is>
-          <t>Macmiilku wicitaanka wuu ka baxay.</t>
+          <t>Kalfadhi toos ah</t>
         </is>
       </c>
       <c r="H243" s="14" t="inlineStr"/>
@@ -14679,7 +14679,7 @@
     <row r="244" ht="44" customHeight="1">
       <c r="A244" s="11" t="inlineStr">
         <is>
-          <t>waiting_for_customer</t>
+          <t>customer_left_call</t>
         </is>
       </c>
       <c r="B244" s="11" t="inlineStr">
@@ -14689,27 +14689,27 @@
       </c>
       <c r="C244" s="11" t="inlineStr">
         <is>
-          <t>Waiting for the customer…</t>
+          <t>The customer has left the call.</t>
         </is>
       </c>
       <c r="D244" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛውን በመጠበቅ ላይ…</t>
+          <t>ደንበኛው ጥሪውን ለቅቋል።</t>
         </is>
       </c>
       <c r="E244" s="13" t="inlineStr">
         <is>
-          <t>Maamilaa eegaa jirra…</t>
+          <t>Maamilaan bilbila irraa ba'eera.</t>
         </is>
       </c>
       <c r="F244" s="12" t="inlineStr">
         <is>
-          <t>ነቲ ዓሚል ንጽበ ኣለና…</t>
+          <t>እቲ ዓሚል ካብቲ ጻውዒት ወጺኡ።</t>
         </is>
       </c>
       <c r="G244" s="13" t="inlineStr">
         <is>
-          <t>Macmiilka la sugayo…</t>
+          <t>Macmiilku wicitaanka wuu ka baxay.</t>
         </is>
       </c>
       <c r="H244" s="14" t="inlineStr"/>
@@ -14717,7 +14717,7 @@
     <row r="245" ht="44" customHeight="1">
       <c r="A245" s="11" t="inlineStr">
         <is>
-          <t>mic_blocked</t>
+          <t>waiting_for_customer</t>
         </is>
       </c>
       <c r="B245" s="11" t="inlineStr">
@@ -14727,27 +14727,27 @@
       </c>
       <c r="C245" s="11" t="inlineStr">
         <is>
-          <t>Microphone access is blocked. Allow it in your browser and take the session again.</t>
+          <t>Waiting for the customer…</t>
         </is>
       </c>
       <c r="D245" s="12" t="inlineStr">
         <is>
-          <t>የማይክሮፎን መዳረሻ ታግዷል። በአሳሽዎ ውስጥ ይፍቀዱና ክፍለ-ጊዜውን እንደገና ይውሰዱ።</t>
+          <t>ደንበኛውን በመጠበቅ ላይ…</t>
         </is>
       </c>
       <c r="E245" s="13" t="inlineStr">
         <is>
-          <t>Maayikiroofoonii dhorkameera. Biraawzarii keessan keessatti hayyamaatii session irra deebi'aa fudhadhaa.</t>
+          <t>Maamilaa eegaa jirra…</t>
         </is>
       </c>
       <c r="F245" s="12" t="inlineStr">
         <is>
-          <t>መእተዊ ማይክሮፎን ተዓጊቱ። ኣብ መርበብ መንሸራተቲኹም ፍቐዱ እሞ ነቲ ክፍለ-ግዜ ደጊምኩም ውሰዱ።</t>
+          <t>ነቲ ዓሚል ንጽበ ኣለና…</t>
         </is>
       </c>
       <c r="G245" s="13" t="inlineStr">
         <is>
-          <t>Makarafoonka waa la xannibay. Browser-kaaga ka ogolow oo kalfadhiga mar kale qaado.</t>
+          <t>Macmiilka la sugayo…</t>
         </is>
       </c>
       <c r="H245" s="14" t="inlineStr"/>
@@ -14755,7 +14755,7 @@
     <row r="246" ht="44" customHeight="1">
       <c r="A246" s="11" t="inlineStr">
         <is>
-          <t>unknown_error</t>
+          <t>mic_blocked</t>
         </is>
       </c>
       <c r="B246" s="11" t="inlineStr">
@@ -14765,27 +14765,27 @@
       </c>
       <c r="C246" s="11" t="inlineStr">
         <is>
-          <t>unknown error</t>
+          <t>Microphone access is blocked. Allow it in your browser and take the session again.</t>
         </is>
       </c>
       <c r="D246" s="12" t="inlineStr">
         <is>
-          <t>ያልታወቀ ስህተት</t>
+          <t>የማይክሮፎን መዳረሻ ታግዷል። በአሳሽዎ ውስጥ ይፍቀዱና ክፍለ-ጊዜውን እንደገና ይውሰዱ።</t>
         </is>
       </c>
       <c r="E246" s="13" t="inlineStr">
         <is>
-          <t>dogoggora hin beekamne</t>
+          <t>Maayikiroofoonii dhorkameera. Biraawzarii keessan keessatti hayyamaatii session irra deebi'aa fudhadhaa.</t>
         </is>
       </c>
       <c r="F246" s="12" t="inlineStr">
         <is>
-          <t>ዘይተፈልጠ ጌጋ</t>
+          <t>መእተዊ ማይክሮፎን ተዓጊቱ። ኣብ መርበብ መንሸራተቲኹም ፍቐዱ እሞ ነቲ ክፍለ-ግዜ ደጊምኩም ውሰዱ።</t>
         </is>
       </c>
       <c r="G246" s="13" t="inlineStr">
         <is>
-          <t>khalad aan la garanayn</t>
+          <t>Makarafoonka waa la xannibay. Browser-kaaga ka ogolow oo kalfadhiga mar kale qaado.</t>
         </is>
       </c>
       <c r="H246" s="14" t="inlineStr"/>
@@ -14793,7 +14793,7 @@
     <row r="247" ht="44" customHeight="1">
       <c r="A247" s="11" t="inlineStr">
         <is>
-          <t>no_messages_yet</t>
+          <t>unknown_error</t>
         </is>
       </c>
       <c r="B247" s="11" t="inlineStr">
@@ -14803,27 +14803,27 @@
       </c>
       <c r="C247" s="11" t="inlineStr">
         <is>
-          <t>No messages yet.</t>
+          <t>unknown error</t>
         </is>
       </c>
       <c r="D247" s="12" t="inlineStr">
         <is>
-          <t>እስካሁን መልእክት የለም።</t>
+          <t>ያልታወቀ ስህተት</t>
         </is>
       </c>
       <c r="E247" s="13" t="inlineStr">
         <is>
-          <t>Ammaaf ergaan hin jiru.</t>
+          <t>dogoggora hin beekamne</t>
         </is>
       </c>
       <c r="F247" s="12" t="inlineStr">
         <is>
-          <t>ክሳብ ሕጂ መልእኽቲ የለን።</t>
+          <t>ዘይተፈልጠ ጌጋ</t>
         </is>
       </c>
       <c r="G247" s="13" t="inlineStr">
         <is>
-          <t>Weli fariimo ma jiraan.</t>
+          <t>khalad aan la garanayn</t>
         </is>
       </c>
       <c r="H247" s="14" t="inlineStr"/>
@@ -14831,7 +14831,7 @@
     <row r="248" ht="44" customHeight="1">
       <c r="A248" s="11" t="inlineStr">
         <is>
-          <t>you_label</t>
+          <t>no_messages_yet</t>
         </is>
       </c>
       <c r="B248" s="11" t="inlineStr">
@@ -14841,27 +14841,27 @@
       </c>
       <c r="C248" s="11" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>No messages yet.</t>
         </is>
       </c>
       <c r="D248" s="12" t="inlineStr">
         <is>
-          <t>እርስዎ</t>
+          <t>እስካሁን መልእክት የለም።</t>
         </is>
       </c>
       <c r="E248" s="13" t="inlineStr">
         <is>
-          <t>Isin</t>
+          <t>Ammaaf ergaan hin jiru.</t>
         </is>
       </c>
       <c r="F248" s="12" t="inlineStr">
         <is>
-          <t>ንስኹም</t>
+          <t>ክሳብ ሕጂ መልእኽቲ የለን።</t>
         </is>
       </c>
       <c r="G248" s="13" t="inlineStr">
         <is>
-          <t>Adiga</t>
+          <t>Weli fariimo ma jiraan.</t>
         </is>
       </c>
       <c r="H248" s="14" t="inlineStr"/>
@@ -14869,7 +14869,7 @@
     <row r="249" ht="44" customHeight="1">
       <c r="A249" s="11" t="inlineStr">
         <is>
-          <t>assistant_label</t>
+          <t>you_label</t>
         </is>
       </c>
       <c r="B249" s="11" t="inlineStr">
@@ -14879,27 +14879,27 @@
       </c>
       <c r="C249" s="11" t="inlineStr">
         <is>
-          <t>Assistant</t>
+          <t>You</t>
         </is>
       </c>
       <c r="D249" s="12" t="inlineStr">
         <is>
-          <t>ረዳት</t>
+          <t>እርስዎ</t>
         </is>
       </c>
       <c r="E249" s="13" t="inlineStr">
         <is>
-          <t>Gargaaraa</t>
+          <t>Isin</t>
         </is>
       </c>
       <c r="F249" s="12" t="inlineStr">
         <is>
-          <t>ሓጋዚ</t>
+          <t>ንስኹም</t>
         </is>
       </c>
       <c r="G249" s="13" t="inlineStr">
         <is>
-          <t>Kaaliye</t>
+          <t>Adiga</t>
         </is>
       </c>
       <c r="H249" s="14" t="inlineStr"/>
@@ -14907,7 +14907,7 @@
     <row r="250" ht="44" customHeight="1">
       <c r="A250" s="11" t="inlineStr">
         <is>
-          <t>conversation_unavailable</t>
+          <t>assistant_label</t>
         </is>
       </c>
       <c r="B250" s="11" t="inlineStr">
@@ -14917,27 +14917,27 @@
       </c>
       <c r="C250" s="11" t="inlineStr">
         <is>
-          <t>Conversation unavailable.</t>
+          <t>Assistant</t>
         </is>
       </c>
       <c r="D250" s="12" t="inlineStr">
         <is>
-          <t>ውይይቱ አይገኝም።</t>
+          <t>ረዳት</t>
         </is>
       </c>
       <c r="E250" s="13" t="inlineStr">
         <is>
-          <t>Mariin hin argamu.</t>
+          <t>Gargaaraa</t>
         </is>
       </c>
       <c r="F250" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዝርርብ ኣይርከብን።</t>
+          <t>ሓጋዚ</t>
         </is>
       </c>
       <c r="G250" s="13" t="inlineStr">
         <is>
-          <t>Wadahadalka lama heli karo.</t>
+          <t>Kaaliye</t>
         </is>
       </c>
       <c r="H250" s="14" t="inlineStr"/>
@@ -14945,7 +14945,7 @@
     <row r="251" ht="44" customHeight="1">
       <c r="A251" s="11" t="inlineStr">
         <is>
-          <t>unmute</t>
+          <t>conversation_unavailable</t>
         </is>
       </c>
       <c r="B251" s="11" t="inlineStr">
@@ -14955,27 +14955,27 @@
       </c>
       <c r="C251" s="11" t="inlineStr">
         <is>
-          <t>Unmute</t>
+          <t>Conversation unavailable.</t>
         </is>
       </c>
       <c r="D251" s="12" t="inlineStr">
         <is>
-          <t>ድምፅ አብራ</t>
+          <t>ውይይቱ አይገኝም።</t>
         </is>
       </c>
       <c r="E251" s="13" t="inlineStr">
         <is>
-          <t>Sagalee banaa</t>
+          <t>Mariin hin argamu.</t>
         </is>
       </c>
       <c r="F251" s="12" t="inlineStr">
         <is>
-          <t>ድምጺ ኣብርህ</t>
+          <t>እቲ ዝርርብ ኣይርከብን።</t>
         </is>
       </c>
       <c r="G251" s="13" t="inlineStr">
         <is>
-          <t>Codka fur</t>
+          <t>Wadahadalka lama heli karo.</t>
         </is>
       </c>
       <c r="H251" s="14" t="inlineStr"/>
@@ -14983,7 +14983,7 @@
     <row r="252" ht="44" customHeight="1">
       <c r="A252" s="11" t="inlineStr">
         <is>
-          <t>session_summary_prompt</t>
+          <t>unmute</t>
         </is>
       </c>
       <c r="B252" s="11" t="inlineStr">
@@ -14993,27 +14993,27 @@
       </c>
       <c r="C252" s="11" t="inlineStr">
         <is>
-          <t>What did this session cover? (optional)</t>
+          <t>Unmute</t>
         </is>
       </c>
       <c r="D252" s="12" t="inlineStr">
         <is>
-          <t>ይህ ክፍለ-ጊዜ ምን ሸፈነ? (አማራጭ)</t>
+          <t>ድምፅ አብራ</t>
         </is>
       </c>
       <c r="E252" s="13" t="inlineStr">
         <is>
-          <t>Sessioniin kun maal haguuge? (filannoo)</t>
+          <t>Sagalee banaa</t>
         </is>
       </c>
       <c r="F252" s="12" t="inlineStr">
         <is>
-          <t>እዚ ክፍለ-ግዜ እንታይ ሸፈነ? (ኣማራጺ)</t>
+          <t>ድምጺ ኣብርህ</t>
         </is>
       </c>
       <c r="G252" s="13" t="inlineStr">
         <is>
-          <t>Kalfadhigan muxuu daboolay? (ikhtiyaari)</t>
+          <t>Codka fur</t>
         </is>
       </c>
       <c r="H252" s="14" t="inlineStr"/>
@@ -15021,7 +15021,7 @@
     <row r="253" ht="44" customHeight="1">
       <c r="A253" s="11" t="inlineStr">
         <is>
-          <t>customer_ended_call</t>
+          <t>session_summary_prompt</t>
         </is>
       </c>
       <c r="B253" s="11" t="inlineStr">
@@ -15031,27 +15031,27 @@
       </c>
       <c r="C253" s="11" t="inlineStr">
         <is>
-          <t>The customer ended the call</t>
+          <t>What did this session cover? (optional)</t>
         </is>
       </c>
       <c r="D253" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛው ጥሪውን አቋረጠ</t>
+          <t>ይህ ክፍለ-ጊዜ ምን ሸፈነ? (አማራጭ)</t>
         </is>
       </c>
       <c r="E253" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan bilbila xumure</t>
+          <t>Sessioniin kun maal haguuge? (filannoo)</t>
         </is>
       </c>
       <c r="F253" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዓሚል ነቲ ጻውዒት ወዲኡዎ</t>
+          <t>እዚ ክፍለ-ግዜ እንታይ ሸፈነ? (ኣማራጺ)</t>
         </is>
       </c>
       <c r="G253" s="13" t="inlineStr">
         <is>
-          <t>Macmiilku wicitaanka wuu joojiyay</t>
+          <t>Kalfadhigan muxuu daboolay? (ikhtiyaari)</t>
         </is>
       </c>
       <c r="H253" s="14" t="inlineStr"/>
@@ -15059,7 +15059,7 @@
     <row r="254" ht="44" customHeight="1">
       <c r="A254" s="11" t="inlineStr">
         <is>
-          <t>verified_scope</t>
+          <t>customer_ended_call</t>
         </is>
       </c>
       <c r="B254" s="11" t="inlineStr">
@@ -15069,27 +15069,27 @@
       </c>
       <c r="C254" s="11" t="inlineStr">
         <is>
-          <t>You can now discuss their own records, take documents and file a dispute. Never a deposit, withdrawal or transfer.</t>
+          <t>The customer ended the call</t>
         </is>
       </c>
       <c r="D254" s="12" t="inlineStr">
         <is>
-          <t>አሁን ስለ ራሳቸው መዝገቦች መወያየት፣ ሰነዶች መቀበልና ቅሬታ ማስመዝገብ ይችላሉ። በፍጹም ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም።</t>
+          <t>ደንበኛው ጥሪውን አቋረጠ</t>
         </is>
       </c>
       <c r="E254" s="13" t="inlineStr">
         <is>
-          <t>Amma waa'ee galmee isaanii mari'achuu, sanadoota fudhachuu fi komii galmeessuu dandeessu. Gonkumaa kuusaa, baasii yookiin dabarsa hin jiru.</t>
+          <t>Maamilaan bilbila xumure</t>
         </is>
       </c>
       <c r="F254" s="12" t="inlineStr">
         <is>
-          <t>ሕጂ ብዛዕባ ናቶም መዝገባት ክትዘራረቡ፣ ሰነዳት ክትቅበሉን ጥርዓን ከተመዝግቡን ትኽእሉ። ፈጺሙ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን።</t>
+          <t>እቲ ዓሚል ነቲ ጻውዒት ወዲኡዎ</t>
         </is>
       </c>
       <c r="G254" s="13" t="inlineStr">
         <is>
-          <t>Hadda waad kala hadli kartaa diiwaankooda, dukumiinti qaadan iyo cabasho diiwaangelin. Weligaa dhigasho, qaadis ama wareejin ma jirto.</t>
+          <t>Macmiilku wicitaanka wuu joojiyay</t>
         </is>
       </c>
       <c r="H254" s="14" t="inlineStr"/>
@@ -15097,7 +15097,7 @@
     <row r="255" ht="44" customHeight="1">
       <c r="A255" s="11" t="inlineStr">
         <is>
-          <t>establish_who_they_are</t>
+          <t>verified_scope</t>
         </is>
       </c>
       <c r="B255" s="11" t="inlineStr">
@@ -15107,27 +15107,27 @@
       </c>
       <c r="C255" s="11" t="inlineStr">
         <is>
-          <t>Establish who they are — either one</t>
+          <t>You can now discuss their own records, take documents and file a dispute. Never a deposit, withdrawal or transfer.</t>
         </is>
       </c>
       <c r="D255" s="12" t="inlineStr">
         <is>
-          <t>ማንነታቸውን ያረጋግጡ — አንዱ ይበቃል</t>
+          <t>አሁን ስለ ራሳቸው መዝገቦች መወያየት፣ ሰነዶች መቀበልና ቅሬታ ማስመዝገብ ይችላሉ። በፍጹም ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም።</t>
         </is>
       </c>
       <c r="E255" s="13" t="inlineStr">
         <is>
-          <t>Eenyummaa isaanii mirkaneessaa — tokko ni ga'a</t>
+          <t>Amma waa'ee galmee isaanii mari'achuu, sanadoota fudhachuu fi komii galmeessuu dandeessu. Gonkumaa kuusaa, baasii yookiin dabarsa hin jiru.</t>
         </is>
       </c>
       <c r="F255" s="12" t="inlineStr">
         <is>
-          <t>መንነቶም ኣረጋግጹ — ሓደ እኹል እዩ</t>
+          <t>ሕጂ ብዛዕባ ናቶም መዝገባት ክትዘራረቡ፣ ሰነዳት ክትቅበሉን ጥርዓን ከተመዝግቡን ትኽእሉ። ፈጺሙ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን።</t>
         </is>
       </c>
       <c r="G255" s="13" t="inlineStr">
         <is>
-          <t>Ogow cidda ay yihiin — mid kasta</t>
+          <t>Hadda waad kala hadli kartaa diiwaankooda, dukumiinti qaadan iyo cabasho diiwaangelin. Weligaa dhigasho, qaadis ama wareejin ma jirto.</t>
         </is>
       </c>
       <c r="H255" s="14" t="inlineStr"/>
@@ -15135,7 +15135,7 @@
     <row r="256" ht="44" customHeight="1">
       <c r="A256" s="11" t="inlineStr">
         <is>
-          <t>chk_id_document</t>
+          <t>establish_who_they_are</t>
         </is>
       </c>
       <c r="B256" s="11" t="inlineStr">
@@ -15145,27 +15145,27 @@
       </c>
       <c r="C256" s="11" t="inlineStr">
         <is>
-          <t>Fayda ID shown and matches the account name</t>
+          <t>Establish who they are — either one</t>
         </is>
       </c>
       <c r="D256" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ መታወቂያ ታይቷል እና ከሂሳቡ ስም ጋር ይዛመዳል</t>
+          <t>ማንነታቸውን ያረጋግጡ — አንዱ ይበቃል</t>
         </is>
       </c>
       <c r="E256" s="13" t="inlineStr">
         <is>
-          <t>Waraqaan eenyummaa Fayda agarsiifame maqaa herregaa waliin walsimeera</t>
+          <t>Eenyummaa isaanii mirkaneessaa — tokko ni ga'a</t>
         </is>
       </c>
       <c r="F256" s="12" t="inlineStr">
         <is>
-          <t>መንነት ፋይዳ ተራእዩን ምስ ስም ሕሳብ ይሰማማዕን</t>
+          <t>መንነቶም ኣረጋግጹ — ሓደ እኹል እዩ</t>
         </is>
       </c>
       <c r="G256" s="13" t="inlineStr">
         <is>
-          <t>Aqoonsiga Fayda waa la tusay wuxuuna la mid yahay magaca xisaabta</t>
+          <t>Ogow cidda ay yihiin — mid kasta</t>
         </is>
       </c>
       <c r="H256" s="14" t="inlineStr"/>
@@ -15173,7 +15173,7 @@
     <row r="257" ht="44" customHeight="1">
       <c r="A257" s="11" t="inlineStr">
         <is>
-          <t>chk_fayda_matched</t>
+          <t>chk_id_document</t>
         </is>
       </c>
       <c r="B257" s="11" t="inlineStr">
@@ -15183,27 +15183,27 @@
       </c>
       <c r="C257" s="11" t="inlineStr">
         <is>
-          <t>Fayda number matches the account record</t>
+          <t>Fayda ID shown and matches the account name</t>
         </is>
       </c>
       <c r="D257" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ ቁጥር ከሂሳቡ መዝገብ ጋር ይዛመዳል</t>
+          <t>የፋይዳ መታወቂያ ታይቷል እና ከሂሳቡ ስም ጋር ይዛመዳል</t>
         </is>
       </c>
       <c r="E257" s="13" t="inlineStr">
         <is>
-          <t>Lakkoofsi Fayda galmee herregaa waliin walsimeera</t>
+          <t>Waraqaan eenyummaa Fayda agarsiifame maqaa herregaa waliin walsimeera</t>
         </is>
       </c>
       <c r="F257" s="12" t="inlineStr">
         <is>
-          <t>ቁጽሪ ፋይዳ ምስ መዝገብ ሕሳብ ይሰማማዕ</t>
+          <t>መንነት ፋይዳ ተራእዩን ምስ ስም ሕሳብ ይሰማማዕን</t>
         </is>
       </c>
       <c r="G257" s="13" t="inlineStr">
         <is>
-          <t>Lambarka Fayda wuxuu la mid yahay diiwaanka xisaabta</t>
+          <t>Aqoonsiga Fayda waa la tusay wuxuuna la mid yahay magaca xisaabta</t>
         </is>
       </c>
       <c r="H257" s="14" t="inlineStr"/>
@@ -15211,7 +15211,7 @@
     <row r="258" ht="44" customHeight="1">
       <c r="A258" s="11" t="inlineStr">
         <is>
-          <t>chk_fayda_matched_note</t>
+          <t>chk_fayda_matched</t>
         </is>
       </c>
       <c r="B258" s="11" t="inlineStr">
@@ -15221,27 +15221,27 @@
       </c>
       <c r="C258" s="11" t="inlineStr">
         <is>
-          <t>on your own screen — works on an audio call</t>
+          <t>Fayda number matches the account record</t>
         </is>
       </c>
       <c r="D258" s="12" t="inlineStr">
         <is>
-          <t>በራስዎ ስክሪን ላይ — በድምፅ ጥሪም ይሠራል</t>
+          <t>የፋይዳ ቁጥር ከሂሳቡ መዝገብ ጋር ይዛመዳል</t>
         </is>
       </c>
       <c r="E258" s="13" t="inlineStr">
         <is>
-          <t>iskiriinii keessan irratti — bilbila sagalee irrattis ni hojjeta</t>
+          <t>Lakkoofsi Fayda galmee herregaa waliin walsimeera</t>
         </is>
       </c>
       <c r="F258" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ናትኩም መርአዪ — ኣብ ናይ ድምጺ ጻውዒት እውን ይሰርሕ</t>
+          <t>ቁጽሪ ፋይዳ ምስ መዝገብ ሕሳብ ይሰማማዕ</t>
         </is>
       </c>
       <c r="G258" s="13" t="inlineStr">
         <is>
-          <t>shaashaddaada — wicitaan cod ahna wuu ka shaqeeyaa</t>
+          <t>Lambarka Fayda wuxuu la mid yahay diiwaanka xisaabta</t>
         </is>
       </c>
       <c r="H258" s="14" t="inlineStr"/>
@@ -15249,7 +15249,7 @@
     <row r="259" ht="44" customHeight="1">
       <c r="A259" s="11" t="inlineStr">
         <is>
-          <t>chk_id_photo</t>
+          <t>chk_fayda_matched_note</t>
         </is>
       </c>
       <c r="B259" s="11" t="inlineStr">
@@ -15259,27 +15259,27 @@
       </c>
       <c r="C259" s="11" t="inlineStr">
         <is>
-          <t>Photo on the ID matches the person on the call</t>
+          <t>on your own screen — works on an audio call</t>
         </is>
       </c>
       <c r="D259" s="12" t="inlineStr">
         <is>
-          <t>በመታወቂያው ላይ ያለው ፎቶ ከጥሪው ላይ ካለው ሰው ጋር ይዛመዳል</t>
+          <t>በራስዎ ስክሪን ላይ — በድምፅ ጥሪም ይሠራል</t>
         </is>
       </c>
       <c r="E259" s="13" t="inlineStr">
         <is>
-          <t>Suuraan waraqaa eenyummaa irra jiru nama bilbila irra jiru waliin walsimeera</t>
+          <t>iskiriinii keessan irratti — bilbila sagalee irrattis ni hojjeta</t>
         </is>
       </c>
       <c r="F259" s="12" t="inlineStr">
         <is>
-          <t>እቲ ኣብ መንነት ዘሎ ስእሊ ምስቲ ኣብ ጻውዒት ዘሎ ሰብ ይሰማማዕ</t>
+          <t>ኣብ ናትኩም መርአዪ — ኣብ ናይ ድምጺ ጻውዒት እውን ይሰርሕ</t>
         </is>
       </c>
       <c r="G259" s="13" t="inlineStr">
         <is>
-          <t>Sawirka aqoonsiga wuxuu la mid yahay qofka wicitaanka ku jira</t>
+          <t>shaashaddaada — wicitaan cod ahna wuu ka shaqeeyaa</t>
         </is>
       </c>
       <c r="H259" s="14" t="inlineStr"/>
@@ -15287,7 +15287,7 @@
     <row r="260" ht="44" customHeight="1">
       <c r="A260" s="11" t="inlineStr">
         <is>
-          <t>chk_video_only</t>
+          <t>chk_id_photo</t>
         </is>
       </c>
       <c r="B260" s="11" t="inlineStr">
@@ -15297,27 +15297,27 @@
       </c>
       <c r="C260" s="11" t="inlineStr">
         <is>
-          <t>video only</t>
+          <t>Photo on the ID matches the person on the call</t>
         </is>
       </c>
       <c r="D260" s="12" t="inlineStr">
         <is>
-          <t>ቪዲዮ ብቻ</t>
+          <t>በመታወቂያው ላይ ያለው ፎቶ ከጥሪው ላይ ካለው ሰው ጋር ይዛመዳል</t>
         </is>
       </c>
       <c r="E260" s="13" t="inlineStr">
         <is>
-          <t>viidiyoo qofa</t>
+          <t>Suuraan waraqaa eenyummaa irra jiru nama bilbila irra jiru waliin walsimeera</t>
         </is>
       </c>
       <c r="F260" s="12" t="inlineStr">
         <is>
-          <t>ቪድዮ ጥራይ</t>
+          <t>እቲ ኣብ መንነት ዘሎ ስእሊ ምስቲ ኣብ ጻውዒት ዘሎ ሰብ ይሰማማዕ</t>
         </is>
       </c>
       <c r="G260" s="13" t="inlineStr">
         <is>
-          <t>fiidyow oo kaliya</t>
+          <t>Sawirka aqoonsiga wuxuu la mid yahay qofka wicitaanka ku jira</t>
         </is>
       </c>
       <c r="H260" s="14" t="inlineStr"/>
@@ -15325,7 +15325,7 @@
     <row r="261" ht="44" customHeight="1">
       <c r="A261" s="11" t="inlineStr">
         <is>
-          <t>confirm_account_theirs</t>
+          <t>chk_video_only</t>
         </is>
       </c>
       <c r="B261" s="11" t="inlineStr">
@@ -15335,27 +15335,27 @@
       </c>
       <c r="C261" s="11" t="inlineStr">
         <is>
-          <t>And confirm the account is theirs</t>
+          <t>video only</t>
         </is>
       </c>
       <c r="D261" s="12" t="inlineStr">
         <is>
-          <t>እና ሂሳቡ የእነሱ መሆኑን ያረጋግጡ</t>
+          <t>ቪዲዮ ብቻ</t>
         </is>
       </c>
       <c r="E261" s="13" t="inlineStr">
         <is>
-          <t>Akkasumas herregni kan isaanii ta'uu mirkaneessaa</t>
+          <t>viidiyoo qofa</t>
         </is>
       </c>
       <c r="F261" s="12" t="inlineStr">
         <is>
-          <t>ከምኡ'ውን እቲ ሕሳብ ናቶም ምዃኑ ኣረጋግጹ</t>
+          <t>ቪድዮ ጥራይ</t>
         </is>
       </c>
       <c r="G261" s="13" t="inlineStr">
         <is>
-          <t>Xaqiiji in xisaabtu tahay tooda</t>
+          <t>fiidyow oo kaliya</t>
         </is>
       </c>
       <c r="H261" s="14" t="inlineStr"/>
@@ -15363,7 +15363,7 @@
     <row r="262" ht="44" customHeight="1">
       <c r="A262" s="11" t="inlineStr">
         <is>
-          <t>confirm_identity</t>
+          <t>confirm_account_theirs</t>
         </is>
       </c>
       <c r="B262" s="11" t="inlineStr">
@@ -15373,27 +15373,27 @@
       </c>
       <c r="C262" s="11" t="inlineStr">
         <is>
-          <t>Confirm identity</t>
+          <t>And confirm the account is theirs</t>
         </is>
       </c>
       <c r="D262" s="12" t="inlineStr">
         <is>
-          <t>ማንነት አረጋግጥ</t>
+          <t>እና ሂሳቡ የእነሱ መሆኑን ያረጋግጡ</t>
         </is>
       </c>
       <c r="E262" s="13" t="inlineStr">
         <is>
-          <t>Eenyummaa mirkaneessi</t>
+          <t>Akkasumas herregni kan isaanii ta'uu mirkaneessaa</t>
         </is>
       </c>
       <c r="F262" s="12" t="inlineStr">
         <is>
-          <t>መንነት ኣረጋግጽ</t>
+          <t>ከምኡ'ውን እቲ ሕሳብ ናቶም ምዃኑ ኣረጋግጹ</t>
         </is>
       </c>
       <c r="G262" s="13" t="inlineStr">
         <is>
-          <t>Xaqiiji aqoonsiga</t>
+          <t>Xaqiiji in xisaabtu tahay tooda</t>
         </is>
       </c>
       <c r="H262" s="14" t="inlineStr"/>
@@ -15401,7 +15401,7 @@
     <row r="263" ht="44" customHeight="1">
       <c r="A263" s="11" t="inlineStr">
         <is>
-          <t>unverified_scope</t>
+          <t>confirm_identity</t>
         </is>
       </c>
       <c r="B263" s="11" t="inlineStr">
@@ -15411,27 +15411,27 @@
       </c>
       <c r="C263" s="11" t="inlineStr">
         <is>
-          <t>Until this is done you can only give general guidance — products, eligibility and how to apply.</t>
+          <t>Confirm identity</t>
         </is>
       </c>
       <c r="D263" s="12" t="inlineStr">
         <is>
-          <t>ይህ እስኪከናወን ድረስ አጠቃላይ መመሪያ ብቻ መስጠት ይችላሉ — ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል።</t>
+          <t>ማንነት አረጋግጥ</t>
         </is>
       </c>
       <c r="E263" s="13" t="inlineStr">
         <is>
-          <t>Hanga kun raawwatutti qajeelfama waliigalaa qofa kennuu dandeessu — oomishaalee, ulaagaa fi akkaataa itti iyyatan.</t>
+          <t>Eenyummaa mirkaneessi</t>
         </is>
       </c>
       <c r="F263" s="12" t="inlineStr">
         <is>
-          <t>እዚ ክሳብ ዝፍጸም ሓፈሻዊ መምርሒ ጥራይ ክትህቡ ትኽእሉ — ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን።</t>
+          <t>መንነት ኣረጋግጽ</t>
         </is>
       </c>
       <c r="G263" s="13" t="inlineStr">
         <is>
-          <t>Ilaa tan la sameeyo waxaad kaliya bixin kartaa hagaajin guud — alaabta, u-qalmitaanka iyo sida loo codsado.</t>
+          <t>Xaqiiji aqoonsiga</t>
         </is>
       </c>
       <c r="H263" s="14" t="inlineStr"/>
@@ -15439,7 +15439,7 @@
     <row r="264" ht="44" customHeight="1">
       <c r="A264" s="11" t="inlineStr">
         <is>
-          <t>fayda_number_required</t>
+          <t>unverified_scope</t>
         </is>
       </c>
       <c r="B264" s="11" t="inlineStr">
@@ -15449,27 +15449,27 @@
       </c>
       <c r="C264" s="11" t="inlineStr">
         <is>
-          <t>Fayda number (required — it is what the record keeps)</t>
+          <t>Until this is done you can only give general guidance — products, eligibility and how to apply.</t>
         </is>
       </c>
       <c r="D264" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ ቁጥር (ያስፈልጋል — መዝገቡ የሚይዘው ይህ ነው)</t>
+          <t>ይህ እስኪከናወን ድረስ አጠቃላይ መመሪያ ብቻ መስጠት ይችላሉ — ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል።</t>
         </is>
       </c>
       <c r="E264" s="13" t="inlineStr">
         <is>
-          <t>Lakkoofsa Fayda (barbaachisaa — kan galmeen qabatu isa kana)</t>
+          <t>Hanga kun raawwatutti qajeelfama waliigalaa qofa kennuu dandeessu — oomishaalee, ulaagaa fi akkaataa itti iyyatan.</t>
         </is>
       </c>
       <c r="F264" s="12" t="inlineStr">
         <is>
-          <t>ቁጽሪ ፋይዳ (የድሊ — እቲ መዝገብ ዝሕዞ እዚ እዩ)</t>
+          <t>እዚ ክሳብ ዝፍጸም ሓፈሻዊ መምርሒ ጥራይ ክትህቡ ትኽእሉ — ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን።</t>
         </is>
       </c>
       <c r="G264" s="13" t="inlineStr">
         <is>
-          <t>Lambarka Fayda (loo baahan yahay — waa waxa diiwaanku hayo)</t>
+          <t>Ilaa tan la sameeyo waxaad kaliya bixin kartaa hagaajin guud — alaabta, u-qalmitaanka iyo sida loo codsado.</t>
         </is>
       </c>
       <c r="H264" s="14" t="inlineStr"/>
@@ -15477,7 +15477,7 @@
     <row r="265" ht="44" customHeight="1">
       <c r="A265" s="11" t="inlineStr">
         <is>
-          <t>download_for_translation</t>
+          <t>fayda_number_required</t>
         </is>
       </c>
       <c r="B265" s="11" t="inlineStr">
@@ -15487,27 +15487,27 @@
       </c>
       <c r="C265" s="11" t="inlineStr">
         <is>
-          <t>Download for translation</t>
+          <t>Fayda number (required — it is what the record keeps)</t>
         </is>
       </c>
       <c r="D265" s="12" t="inlineStr">
         <is>
-          <t>ለትርጉም አውርድ</t>
+          <t>የፋይዳ ቁጥር (ያስፈልጋል — መዝገቡ የሚይዘው ይህ ነው)</t>
         </is>
       </c>
       <c r="E265" s="13" t="inlineStr">
         <is>
-          <t>Hiikkaaf buufadhu</t>
+          <t>Lakkoofsa Fayda (barbaachisaa — kan galmeen qabatu isa kana)</t>
         </is>
       </c>
       <c r="F265" s="12" t="inlineStr">
         <is>
-          <t>ንትርጉም ኣውርድ</t>
+          <t>ቁጽሪ ፋይዳ (የድሊ — እቲ መዝገብ ዝሕዞ እዚ እዩ)</t>
         </is>
       </c>
       <c r="G265" s="13" t="inlineStr">
         <is>
-          <t>Soo dejiso turjumaadda</t>
+          <t>Lambarka Fayda (loo baahan yahay — waa waxa diiwaanku hayo)</t>
         </is>
       </c>
       <c r="H265" s="14" t="inlineStr"/>
@@ -15515,43 +15515,81 @@
     <row r="266" ht="44" customHeight="1">
       <c r="A266" s="11" t="inlineStr">
         <is>
+          <t>download_for_translation</t>
+        </is>
+      </c>
+      <c r="B266" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C266" s="11" t="inlineStr">
+        <is>
+          <t>Download for translation</t>
+        </is>
+      </c>
+      <c r="D266" s="12" t="inlineStr">
+        <is>
+          <t>ለትርጉም አውርድ</t>
+        </is>
+      </c>
+      <c r="E266" s="13" t="inlineStr">
+        <is>
+          <t>Hiikkaaf buufadhu</t>
+        </is>
+      </c>
+      <c r="F266" s="12" t="inlineStr">
+        <is>
+          <t>ንትርጉም ኣውርድ</t>
+        </is>
+      </c>
+      <c r="G266" s="13" t="inlineStr">
+        <is>
+          <t>Soo dejiso turjumaadda</t>
+        </is>
+      </c>
+      <c r="H266" s="14" t="inlineStr"/>
+    </row>
+    <row r="267" ht="44" customHeight="1">
+      <c r="A267" s="11" t="inlineStr">
+        <is>
           <t>nothing_to_download</t>
         </is>
       </c>
-      <c r="B266" s="11" t="inlineStr">
-        <is>
-          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
-        </is>
-      </c>
-      <c r="C266" s="11" t="inlineStr">
+      <c r="B267" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C267" s="11" t="inlineStr">
         <is>
           <t>No approved answers to download yet.</t>
         </is>
       </c>
-      <c r="D266" s="12" t="inlineStr">
+      <c r="D267" s="12" t="inlineStr">
         <is>
           <t>እስካሁን የሚወርድ የተፈቀደ መልስ የለም።</t>
         </is>
       </c>
-      <c r="E266" s="13" t="inlineStr">
+      <c r="E267" s="13" t="inlineStr">
         <is>
           <t>Hanga ammaatti deebiin mirkanaa'e buufamu hin jiru.</t>
         </is>
       </c>
-      <c r="F266" s="12" t="inlineStr">
+      <c r="F267" s="12" t="inlineStr">
         <is>
           <t>ክሳብ ሕጂ ዝወርድ ዝጸደቐ መልሲ የለን።</t>
         </is>
       </c>
-      <c r="G266" s="13" t="inlineStr">
+      <c r="G267" s="13" t="inlineStr">
         <is>
           <t>Weli ma jiraan jawaabo la ansixiyay oo la soo dejiyo.</t>
         </is>
       </c>
-      <c r="H266" s="14" t="inlineStr"/>
+      <c r="H267" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H266"/>
+  <autoFilter ref="A1:H267"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/review/Olink_Bank_Assist_language_review.xlsx
+++ b/review/Olink_Bank_Assist_language_review.xlsx
@@ -14,10 +14,10 @@
     <sheet name="4. The staff panel" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1. What the assistant says'!$A$1:$H$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2. What it understands'!$A$1:$E$78</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3. Buttons customers see'!$A$1:$H$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$H$270</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1. What the assistant says'!$A$1:$I$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2. What it understands'!$A$1:$E$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3. Buttons customers see'!$A$1:$I$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$I$270</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -589,7 +589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:C33"/>
+  <dimension ref="B1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -617,7 +617,7 @@
     <row r="4" ht="44" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Correct the five language columns. Leave the key, the context and the English columns alone — the code looks strings up by key, and edits to the English are dropped on import.</t>
+          <t>Correct the six language columns. Leave the key, the context and the English columns alone — the code looks strings up by key, and edits to the English are dropped on import.</t>
         </is>
       </c>
     </row>
@@ -816,8 +816,20 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="9" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Kiswahili (sw)</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>sheet 2: 13 rows supplied</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>For the live figure at any time, run:  python scripts/check_phrasebook.py</t>
         </is>
@@ -834,7 +846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -844,7 +856,8 @@
     <col width="44" customWidth="1" min="5" max="5"/>
     <col width="44" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -885,6 +898,11 @@
       </c>
       <c r="H1" s="10" t="inlineStr">
         <is>
+          <t>sw — Kiswahili</t>
+        </is>
+      </c>
+      <c r="I1" s="10" t="inlineStr">
+        <is>
           <t>reviewer notes</t>
         </is>
       </c>
@@ -903,34 +921,40 @@
       <c r="C2" s="11" t="inlineStr">
         <is>
           <t>Hello! I am {bank}'s virtual assistant. Ask me anything about our accounts, services, fees, or how to bank with us.
-🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali</t>
+🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali · Kiswahili</t>
         </is>
       </c>
       <c r="D2" s="12" t="inlineStr">
         <is>
           <t>ሰላም! እኔ የ{bank} ዲጂታል ረዳት ነኝ። ስለ ሂሳቦቻችን፣ አገልግሎቶቻችን፣ ክፍያዎች ወይም አጠቃቀም ማንኛውንም ጥያቄ ይጠይቁኝ።
-🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali</t>
+🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali · Kiswahili</t>
         </is>
       </c>
       <c r="E2" s="13" t="inlineStr">
         <is>
           <t>Akkam! Ani gargaaraa dijitaalaa {bank} ti. Waa'ee herregaa, tajaajilaa, kaffaltii fi fayyadama keenyaa gaaffii kamiyyuu na gaafadhaa.
-🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali</t>
+🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali · Kiswahili</t>
         </is>
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
           <t>ሰላም! ኣነ ናይ {bank} ዲጂታላዊ ሓጋዚ እየ። ብዛዕባ ሕሳባትና፣ ኣገልግሎታትና፣ ክፍሊታት ወይ ኣጠቓቕማ ዝኾነ ሕቶ ሕተቱኒ።
-🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali</t>
+🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali · Kiswahili</t>
         </is>
       </c>
       <c r="G2" s="13" t="inlineStr">
         <is>
           <t>Salaan! Waxaan ahay kaaliyaha dijitaalka ah ee {bank}. Wax kasta oo ku saabsan xisaabaadka, adeegyada, khidmadaha iyo isticmaalka i weydii.
-🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali</t>
-        </is>
-      </c>
-      <c r="H2" s="14" t="inlineStr"/>
+🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali · Kiswahili</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Habari! Mimi ni msaidizi wa kidijitali wa {bank}. Niulize chochote kuhusu akaunti, huduma, ada zetu, au jinsi ya kufanya benki nasi.
+🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali · Kiswahili</t>
+        </is>
+      </c>
+      <c r="I2" s="14" t="inlineStr"/>
     </row>
     <row r="3" ht="74" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
@@ -946,34 +970,40 @@
       <c r="C3" s="11" t="inlineStr">
         <is>
           <t>Hello {name}! I am {bank}'s virtual assistant. Ask me anything about our accounts, services, fees, or how to bank with us.
-🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali</t>
+🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali · Kiswahili</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
           <t>ሰላም {name}! እኔ የ{bank} ዲጂታል ረዳት ነኝ። ስለ ሂሳቦቻችን፣ አገልግሎቶቻችን፣ ክፍያዎች ወይም አጠቃቀም ማንኛውንም ጥያቄ ይጠይቁኝ።
-🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali</t>
+🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali · Kiswahili</t>
         </is>
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Akkam {name}! Ani gargaaraa dijitaalaa {bank} dha. Waa'ee herregaa, tajaajilaa, kaffaltii yookaan itti fayyadama gaafadhaa.
-🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali</t>
+🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali · Kiswahili</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
           <t>ሰላም {name}! ኣነ ናይ {bank} ዲጂታላዊ ሓጋዚ እየ። ብዛዕባ ሕሳባትና፣ ኣገልግሎትና፣ ክፍሊት ወይ ኣጠቓቕማ ዝኾነ ሕቶ ሕተቱኒ።
-🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali</t>
+🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali · Kiswahili</t>
         </is>
       </c>
       <c r="G3" s="13" t="inlineStr">
         <is>
           <t>Salaan {name}! Waxaan ahay kaaliyaha dijitaalka ah ee {bank}. Wax walba oo ku saabsan xisaabaha, adeegyada, khidmadaha ama isticmaalka i weydii.
-🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali</t>
-        </is>
-      </c>
-      <c r="H3" s="14" t="inlineStr"/>
+🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali · Kiswahili</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Habari {name}! Mimi ni msaidizi wa kidijitali wa {bank}. Niulize chochote kuhusu akaunti, huduma, ada zetu, au jinsi ya kufanya benki nasi.
+🌐 English · አማርኛ · Afaan Oromoo · ትግርኛ · Soomaali · Kiswahili</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr"/>
     </row>
     <row r="4" ht="74" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
@@ -1011,7 +1041,12 @@
           <t>Mahadsanid {name} —</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr"/>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>Asante {name} —</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr"/>
     </row>
     <row r="5" ht="74" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
@@ -1049,7 +1084,12 @@
           <t>Arrintan macluumaad la xaqiijiyey kama hayo, mana doonayo inaan qiyaaso. Su'aashaada waxaan u gudbiyey kooxda adeegga macaamiisha — dhawaan way kula soo xiriiri doonaan.</t>
         </is>
       </c>
-      <c r="H5" s="14" t="inlineStr"/>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>Sina taarifa iliyothibitishwa kuhusu hilo bado, kwa hivyo sitakisia. Nimeandika swali lako kwa ajili ya timu yetu ya huduma kwa wateja — wanaweza kuwasiliana nawe.</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr"/>
     </row>
     <row r="6" ht="74" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
@@ -1087,7 +1127,12 @@
           <t>Hagaajin guud — kani waa hab-dhaqanka caadiga ah ee bangiyada, ma aha macluumaadka rasmiga ah ee {bank}. Wax kasta oo la xiriira xisaabtaada la xaqiiji {bank}.</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr"/>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>Mwongozo wa jumla — huu ni utaratibu wa kawaida wa kibenki, si taarifa rasmi ya {bank}. Tafadhali wasiliana na {bank} kwa lolote maalum kuhusu akaunti yako.</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr"/>
     </row>
     <row r="7" ht="74" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
@@ -1125,7 +1170,12 @@
           <t>Inta u dhaxaysa, mawduucyada la xiriira ee hoos ku qoran ayaa laga yaabaa inay ku caawiyaan:</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr"/>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>Wakati huohuo, mada hizi zinazohusiana zinaweza kukusaidia:</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="inlineStr"/>
     </row>
     <row r="8" ht="74" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
@@ -1163,7 +1213,12 @@
           <t>Si qof ka mid ah kooxdayadu ay kuula soo xiriiraan, ma i siin kartaa magacaaga iyo lambarka telefoonka ee lagugu heli karo?</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr"/>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>Ili mtu kutoka timu yetu aweze kuwasiliana nawe, naomba jina lako na namba ya simu nzuri zaidi ya kukufikia?</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr"/>
     </row>
     <row r="9" ht="74" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
@@ -1201,7 +1256,12 @@
           <t>Waxay kugu soo xiriiri doonaan {contact}.</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr"/>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>Watakufikia kupitia {contact}.</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="inlineStr"/>
     </row>
     <row r="10" ht="74" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
@@ -1239,7 +1299,12 @@
           <t>Mahadsanid — macluumaadkaaga waxaan u gudbiyay kooxda adeegga macaamiisha. Waxay kugula soo xiriiri doonaan {contact}.</t>
         </is>
       </c>
-      <c r="H10" s="14" t="inlineStr"/>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>Asante — nimewasilisha taarifa zako kwa timu yetu ya huduma kwa wateja. Watawasiliana nawe kupitia {contact}.</t>
+        </is>
+      </c>
+      <c r="I10" s="14" t="inlineStr"/>
     </row>
     <row r="11" ht="74" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
@@ -1277,7 +1342,12 @@
           <t>Mahadsanid {name} — macluumaadkaaga waxaan u gudbiyay kooxda adeegga macaamiisha. Waxay kugula soo xiriiri doonaan {contact}.</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr"/>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>Asante {name} — nimewasilisha taarifa zako kwa timu yetu ya huduma kwa wateja. Watawasiliana nawe kupitia {contact}.</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="inlineStr"/>
     </row>
     <row r="12" ht="74" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
@@ -1315,7 +1385,12 @@
           <t>Amnigaaga awgiis, wadahadalkan kuma eegi karo macluumaadka xisaabta gaarka ah. Fadlan isticmaal abka bangiga mobilada, booqo laan ama la xiriir adeegga macaamiisha.</t>
         </is>
       </c>
-      <c r="H12" s="14" t="inlineStr"/>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>Kwa usalama wako, siwezi kufikia taarifa za akaunti binafsi katika mazungumzo haya. Tafadhali tumia programu ya benki ya simu, tembelea tawi, au wasiliana na huduma kwa wateja. Kuna kitu chochote cha jumla ninaweza kukusaidia?</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="inlineStr"/>
     </row>
     <row r="13" ht="74" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
@@ -1353,7 +1428,12 @@
           <t>Waan ka xunnahay dhibaatada kaa soo gaartay. Fariintaada waxaan u gudbiyey kooxda adeegga macaamiisha — qof ayaa dhawaan kula soo xiriiri doona.</t>
         </is>
       </c>
-      <c r="H13" s="14" t="inlineStr"/>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>Pole kwa usumbufu uliopata. Nimeweka alama kwenye ujumbe wako kwa ajili ya timu yetu ya huduma kwa wateja ili mtu aweze kuwasiliana nawe.</t>
+        </is>
+      </c>
+      <c r="I13" s="14" t="inlineStr"/>
     </row>
     <row r="14" ht="74" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
@@ -1391,7 +1471,12 @@
           <t>Waa hagaag. Hadda ma jiro qof kooxdayada ka mid ah oo toos kuula hadli kara, sidaas darteed codsigaaga waxaan u gudbiyey adeegga macaamiisha, qofna wuu kula soo xiriiri doonaa.</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr"/>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>Bila shaka. Hakuna mtu kutoka timu yetu aliye huru kuzungumza sasa hivi, kwa hivyo nimewasilisha ombi lako kwa huduma kwa wateja na mtu atawasiliana nawe.</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr"/>
     </row>
     <row r="15" ht="74" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
@@ -1429,7 +1514,12 @@
           <t>Waa hagaag — hadda waxaa diyaar ah bangi-shaqaale. Isticmaal badhanka «Connect» ee hoosta ku yaal si aad kulan ammaan ah ula bilowdo.</t>
         </is>
       </c>
-      <c r="H15" s="14" t="inlineStr"/>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>Bila shaka — kuna afisa wa benki anapatikana sasa hivi. Tumia kitufe cha «Connect» hapa chini kuanza kikao salama nao.</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="inlineStr"/>
     </row>
     <row r="16" ht="74" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
@@ -1467,7 +1557,12 @@
           <t>Ogeysiis: tani waa waxbarasho maaliyadeed oo guud, ma aha talo maalgashi oo shakhsi ah. Ka hor inta aadan go'aan gaarin, la tasho lataliye shati leh.</t>
         </is>
       </c>
-      <c r="H16" s="14" t="inlineStr"/>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>Kumbuka: hii ni elimu ya jumla ya kifedha, si ushauri wa kibinafsi wa uwekezaji. Tafadhali zungumza na mshauri aliyeidhinishwa kabla ya kufanya maamuzi ya uwekezaji.</t>
+        </is>
+      </c>
+      <c r="I16" s="14" t="inlineStr"/>
     </row>
     <row r="17" ht="74" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
@@ -1505,7 +1600,12 @@
           <t>Waa kan waxa aan ka helay macluumaadka rasmiga ah ee {bank}:</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr"/>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>Hii ndiyo niliyoipata katika taarifa rasmi za {bank}:</t>
+        </is>
+      </c>
+      <c r="I17" s="14" t="inlineStr"/>
     </row>
     <row r="18" ht="74" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
@@ -1543,7 +1643,12 @@
           <t>Ilaha</t>
         </is>
       </c>
-      <c r="H18" s="14" t="inlineStr"/>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>Vyanzo</t>
+        </is>
+      </c>
+      <c r="I18" s="14" t="inlineStr"/>
     </row>
     <row r="19" ht="74" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
@@ -1581,7 +1686,12 @@
           <t>Ma bixin karo faallo ku saabsan bangiyada kale, laakiin waa kan {bank} xoog ka dhigaya:</t>
         </is>
       </c>
-      <c r="H19" s="14" t="inlineStr"/>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>Siwezi kutoa madai kuhusu benki nyingine, lakini hivi ndivyo vinavyofanya {bank} kuwa imara:</t>
+        </is>
+      </c>
+      <c r="I19" s="14" t="inlineStr"/>
     </row>
     <row r="20" ht="74" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
@@ -1619,7 +1729,12 @@
           <t>Ma barbardhigi karo bangiyo gaar ah, laakiin waan kuu sheegi lahaa xisaabaadka, adeegyada, iyo astaamaha {bank} — maxaad rabtaa inaad ogaato?</t>
         </is>
       </c>
-      <c r="H20" s="14" t="inlineStr"/>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>Siwezi kulinganisha benki mahususi, lakini ningependa kukueleza kuhusu akaunti, huduma, na vipengele vya {bank} — ungependa kujua nini?</t>
+        </is>
+      </c>
+      <c r="I20" s="14" t="inlineStr"/>
     </row>
     <row r="21" ht="74" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
@@ -1657,10 +1772,15 @@
           <t>Ma hayo macluumaad xiriir oo kuu gaar ah, sidaas darteed ma ballan qaadi karo in laguu soo wacayo.</t>
         </is>
       </c>
-      <c r="H21" s="14" t="inlineStr"/>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>Sina taarifa zako za mawasiliano, kwa hivyo siwezi kuahidi kupiga simu tena.</t>
+        </is>
+      </c>
+      <c r="I21" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H21"/>
+  <autoFilter ref="A1:I21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1671,7 +1791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E78"/>
+  <dimension ref="A1:E91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3479,10 +3599,309 @@
       </c>
       <c r="E78" s="24" t="inlineStr"/>
     </row>
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="20" t="inlineStr">
+        <is>
+          <t>sw</t>
+        </is>
+      </c>
+      <c r="B79" s="21" t="inlineStr">
+        <is>
+          <t>Ninahitaji kuzungumza na meneja</t>
+        </is>
+      </c>
+      <c r="C79" s="22" t="inlineStr">
+        <is>
+          <t>human_request</t>
+        </is>
+      </c>
+      <c r="D79" s="23" t="inlineStr">
+        <is>
+          <t>asking for a person</t>
+        </is>
+      </c>
+      <c r="E79" s="24" t="inlineStr"/>
+    </row>
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="20" t="inlineStr">
+        <is>
+          <t>sw</t>
+        </is>
+      </c>
+      <c r="B80" s="21" t="inlineStr">
+        <is>
+          <t>Naomba niongee na mtu</t>
+        </is>
+      </c>
+      <c r="C80" s="22" t="inlineStr">
+        <is>
+          <t>human_request</t>
+        </is>
+      </c>
+      <c r="D80" s="23" t="inlineStr">
+        <is>
+          <t>a second phrasing of the same request</t>
+        </is>
+      </c>
+      <c r="E80" s="24" t="inlineStr"/>
+    </row>
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="20" t="inlineStr">
+        <is>
+          <t>sw</t>
+        </is>
+      </c>
+      <c r="B81" s="21" t="inlineStr">
+        <is>
+          <t>Nipe namba ya akaunti yake</t>
+        </is>
+      </c>
+      <c r="C81" s="22" t="inlineStr">
+        <is>
+          <t>account_specific</t>
+        </is>
+      </c>
+      <c r="D81" s="23" t="inlineStr">
+        <is>
+          <t>someone else's account</t>
+        </is>
+      </c>
+      <c r="E81" s="24" t="inlineStr"/>
+    </row>
+    <row r="82" ht="30" customHeight="1">
+      <c r="A82" s="20" t="inlineStr">
+        <is>
+          <t>sw</t>
+        </is>
+      </c>
+      <c r="B82" s="21" t="inlineStr">
+        <is>
+          <t>Niambie salio la mke wangu</t>
+        </is>
+      </c>
+      <c r="C82" s="22" t="inlineStr">
+        <is>
+          <t>account_specific</t>
+        </is>
+      </c>
+      <c r="D82" s="23" t="inlineStr">
+        <is>
+          <t>possessive noun between verb and account word</t>
+        </is>
+      </c>
+      <c r="E82" s="24" t="inlineStr"/>
+    </row>
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" s="20" t="inlineStr">
+        <is>
+          <t>sw</t>
+        </is>
+      </c>
+      <c r="B83" s="21" t="inlineStr">
+        <is>
+          <t>Nitumie salio la kaka yangu</t>
+        </is>
+      </c>
+      <c r="C83" s="22" t="inlineStr">
+        <is>
+          <t>account_specific</t>
+        </is>
+      </c>
+      <c r="D83" s="23" t="inlineStr">
+        <is>
+          <t>a sibling is another person too</t>
+        </is>
+      </c>
+      <c r="E83" s="24" t="inlineStr"/>
+    </row>
+    <row r="84" ht="30" customHeight="1">
+      <c r="A84" s="20" t="inlineStr">
+        <is>
+          <t>sw</t>
+        </is>
+      </c>
+      <c r="B84" s="21" t="inlineStr">
+        <is>
+          <t>Amesahau PIN yake, ni nini?</t>
+        </is>
+      </c>
+      <c r="C84" s="22" t="inlineStr">
+        <is>
+          <t>account_specific</t>
+        </is>
+      </c>
+      <c r="D84" s="23" t="inlineStr">
+        <is>
+          <t>a PIN request wearing a helpful face</t>
+        </is>
+      </c>
+      <c r="E84" s="24" t="inlineStr"/>
+    </row>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="20" t="inlineStr">
+        <is>
+          <t>sw</t>
+        </is>
+      </c>
+      <c r="B85" s="21" t="inlineStr">
+        <is>
+          <t>Ninawezaje kufungua akaunti ya akiba?</t>
+        </is>
+      </c>
+      <c r="C85" s="22" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="D85" s="23" t="inlineStr">
+        <is>
+          <t>an ordinary question</t>
+        </is>
+      </c>
+      <c r="E85" s="24" t="inlineStr"/>
+    </row>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="20" t="inlineStr">
+        <is>
+          <t>sw</t>
+        </is>
+      </c>
+      <c r="B86" s="21" t="inlineStr">
+        <is>
+          <t>Kama nikisahau PIN yangu, nifanye nini?</t>
+        </is>
+      </c>
+      <c r="C86" s="22" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="D86" s="23" t="inlineStr">
+        <is>
+          <t>MUST NOT refuse — MY OWN forgotten PIN, conditional</t>
+        </is>
+      </c>
+      <c r="E86" s="24" t="inlineStr"/>
+    </row>
+    <row r="87" ht="30" customHeight="1">
+      <c r="A87" s="20" t="inlineStr">
+        <is>
+          <t>sw</t>
+        </is>
+      </c>
+      <c r="B87" s="21" t="inlineStr">
+        <is>
+          <t>Riba ya mkopo ni ngapi?</t>
+        </is>
+      </c>
+      <c r="C87" s="22" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="D87" s="23" t="inlineStr">
+        <is>
+          <t>an ordinary rate question</t>
+        </is>
+      </c>
+      <c r="E87" s="24" t="inlineStr"/>
+    </row>
+    <row r="88" ht="30" customHeight="1">
+      <c r="A88" s="20" t="inlineStr">
+        <is>
+          <t>sw</t>
+        </is>
+      </c>
+      <c r="B88" s="21" t="inlineStr">
+        <is>
+          <t>Ada ya kutuma pesa ni kiasi gani?</t>
+        </is>
+      </c>
+      <c r="C88" s="22" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="D88" s="23" t="inlineStr">
+        <is>
+          <t>MUST NOT refuse — a published fee, not a value ask</t>
+        </is>
+      </c>
+      <c r="E88" s="24" t="inlineStr"/>
+    </row>
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="20" t="inlineStr">
+        <is>
+          <t>sw</t>
+        </is>
+      </c>
+      <c r="B89" s="21" t="inlineStr">
+        <is>
+          <t>Nataka kutuma pesa kwa mke wangu</t>
+        </is>
+      </c>
+      <c r="C89" s="22" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="D89" s="23" t="inlineStr">
+        <is>
+          <t>MUST NOT refuse — sending money, not asking for details</t>
+        </is>
+      </c>
+      <c r="E89" s="24" t="inlineStr"/>
+    </row>
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="20" t="inlineStr">
+        <is>
+          <t>sw</t>
+        </is>
+      </c>
+      <c r="B90" s="21" t="inlineStr">
+        <is>
+          <t>Pesa zangu zimeibiwa kutoka akaunti yangu</t>
+        </is>
+      </c>
+      <c r="C90" s="22" t="inlineStr">
+        <is>
+          <t>complaint</t>
+        </is>
+      </c>
+      <c r="D90" s="23" t="inlineStr">
+        <is>
+          <t>reporting harm</t>
+        </is>
+      </c>
+      <c r="E90" s="24" t="inlineStr"/>
+    </row>
+    <row r="91" ht="30" customHeight="1">
+      <c r="A91" s="20" t="inlineStr">
+        <is>
+          <t>sw</t>
+        </is>
+      </c>
+      <c r="B91" s="21" t="inlineStr">
+        <is>
+          <t>Habari</t>
+        </is>
+      </c>
+      <c r="C91" s="22" t="inlineStr">
+        <is>
+          <t>greeting</t>
+        </is>
+      </c>
+      <c r="D91" s="23" t="inlineStr">
+        <is>
+          <t>hello, not a question</t>
+        </is>
+      </c>
+      <c r="E91" s="24" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E78"/>
+  <autoFilter ref="A1:E91"/>
   <dataValidations count="1">
-    <dataValidation sqref="C2:C278" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Not a valid outcome" error="Pick one of: human_request, account_specific, complaint, question, greeting" type="list">
+    <dataValidation sqref="C2:C291" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Not a valid outcome" error="Pick one of: human_request, account_specific, complaint, question, greeting" type="list">
       <formula1>"human_request,account_specific,complaint,question,greeting"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3496,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3506,7 +3925,8 @@
     <col width="44" customWidth="1" min="5" max="5"/>
     <col width="44" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -3547,6 +3967,11 @@
       </c>
       <c r="H1" s="10" t="inlineStr">
         <is>
+          <t>sw — Kiswahili</t>
+        </is>
+      </c>
+      <c r="I1" s="10" t="inlineStr">
+        <is>
           <t>reviewer notes</t>
         </is>
       </c>
@@ -3587,7 +4012,12 @@
           <t>Luqadda</t>
         </is>
       </c>
-      <c r="H2" s="14" t="inlineStr"/>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Lugha</t>
+        </is>
+      </c>
+      <c r="I2" s="14" t="inlineStr"/>
     </row>
     <row r="3" ht="44" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
@@ -3625,7 +4055,12 @@
           <t>Wax ka weydii xisaabaha, wareejinta lacagta, amaahda…</t>
         </is>
       </c>
-      <c r="H3" s="14" t="inlineStr"/>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Uliza kuhusu akaunti, uhamishaji, mikopo…</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr"/>
     </row>
     <row r="4" ht="44" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
@@ -3663,7 +4098,12 @@
           <t>Magacaaga iyo lambarka taleefankaaga…</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr"/>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>Jina lako na namba ya simu…</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr"/>
     </row>
     <row r="5" ht="44" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
@@ -3701,7 +4141,12 @@
           <t>Dir</t>
         </is>
       </c>
-      <c r="H5" s="14" t="inlineStr"/>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>Tuma</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr"/>
     </row>
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
@@ -3739,7 +4184,12 @@
           <t>Salaam! Waxaan ahay kaaliyaha AI ee {bank}. Wax iga weydii xisaabaha, wareejinta lacagta, amaahda ama kaydinta — luqaddaada ayaan si toos ah u raacayaa.</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr"/>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>Habari! Mimi ni msaidizi wa AI wa {bank}. Niulize kuhusu akaunti, uhamishaji, mikopo au akiba — nitafuata lugha yako kiotomatiki.</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr"/>
     </row>
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
@@ -3777,7 +4227,12 @@
           <t>Sidee baan xisaab u furaa?</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr"/>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>Ninawezaje kufungua akaunti?</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="inlineStr"/>
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
@@ -3815,7 +4270,12 @@
           <t>Maxaa amaah iiga baahan?</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr"/>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>Ninahitaji nini kwa mkopo?</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr"/>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
@@ -3853,7 +4313,12 @@
           <t>Macluumaadka rasmiga ah ee {bank}</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr"/>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>Taarifa rasmi za {bank}</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="inlineStr"/>
     </row>
     <row r="10" ht="44" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
@@ -3891,7 +4356,12 @@
           <t>Waa la raadinayaa macluumaadka rasmiga ah…</t>
         </is>
       </c>
-      <c r="H10" s="14" t="inlineStr"/>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>Inatafuta taarifa rasmi…</t>
+        </is>
+      </c>
+      <c r="I10" s="14" t="inlineStr"/>
     </row>
     <row r="11" ht="44" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
@@ -3929,7 +4399,12 @@
           <t>Sharaxidda alaabta, khidmadaha iyo u-qalmitaanka</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr"/>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>Kueleza bidhaa, ada na sifa za kustahiki</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="inlineStr"/>
     </row>
     <row r="12" ht="44" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
@@ -3967,7 +4442,12 @@
           <t>Eegista codsigaaga ama diiwaanka xisaabtaada</t>
         </is>
       </c>
-      <c r="H12" s="14" t="inlineStr"/>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>Kuangalia maombi au rekodi za akaunti yako</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="inlineStr"/>
     </row>
     <row r="13" ht="44" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
@@ -4005,7 +4485,12 @@
           <t>Qaadashada nuqul aqoonsigaaga ama foom la buuxiyay</t>
         </is>
       </c>
-      <c r="H13" s="14" t="inlineStr"/>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>Kuchukua nakala ya kitambulisho chako au fomu iliyojazwa</t>
+        </is>
+      </c>
+      <c r="I13" s="14" t="inlineStr"/>
     </row>
     <row r="14" ht="44" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
@@ -4043,7 +4528,12 @@
           <t>Gudbinta cabasho ama muran adiga oo matalaya</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr"/>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>Kuwasilisha malalamiko au mgogoro kwa niaba yako</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr"/>
     </row>
     <row r="15" ht="44" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
@@ -4081,7 +4571,12 @@
           <t>Dhaqaajinta lacagta — dhigasho, qaadasho ama wareejin</t>
         </is>
       </c>
-      <c r="H15" s="14" t="inlineStr"/>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>Kuhamisha pesa — amana, uondoaji au uhamishaji</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="inlineStr"/>
     </row>
     <row r="16" ht="44" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
@@ -4119,7 +4614,12 @@
           <t>Beddelidda PIN-kaaga, furahaaga sirta ah ama macluumaadka amniga</t>
         </is>
       </c>
-      <c r="H16" s="14" t="inlineStr"/>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>Kubadilisha PIN, nenosiri au taarifa za usalama</t>
+        </is>
+      </c>
+      <c r="I16" s="14" t="inlineStr"/>
     </row>
     <row r="17" ht="44" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
@@ -4157,7 +4657,12 @@
           <t>La hadal shaqaale xisaabeed oo {bank}</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr"/>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>Zungumza na afisa wa {bank}</t>
+        </is>
+      </c>
+      <c r="I17" s="14" t="inlineStr"/>
     </row>
     <row r="18" ht="44" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
@@ -4195,7 +4700,12 @@
           <t>Hadda wuu diyaar yahay — cod ama fiidiyow</t>
         </is>
       </c>
-      <c r="H18" s="14" t="inlineStr"/>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>Inapatikana sasa — sauti au video</t>
+        </is>
+      </c>
+      <c r="I18" s="14" t="inlineStr"/>
     </row>
     <row r="19" ht="44" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
@@ -4233,7 +4743,12 @@
           <t>Ku xidh</t>
         </is>
       </c>
-      <c r="H19" s="14" t="inlineStr"/>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>Unganisha</t>
+        </is>
+      </c>
+      <c r="I19" s="14" t="inlineStr"/>
     </row>
     <row r="20" ht="44" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
@@ -4271,7 +4786,12 @@
           <t>La hadal shaqaale xisaabeed</t>
         </is>
       </c>
-      <c r="H20" s="14" t="inlineStr"/>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>Zungumza na afisa</t>
+        </is>
+      </c>
+      <c r="I20" s="14" t="inlineStr"/>
     </row>
     <row r="21" ht="44" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
@@ -4309,7 +4829,12 @@
           <t>Isla markiiba</t>
         </is>
       </c>
-      <c r="H21" s="14" t="inlineStr"/>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>Mara moja</t>
+        </is>
+      </c>
+      <c r="I21" s="14" t="inlineStr"/>
     </row>
     <row r="22" ht="44" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
@@ -4347,7 +4872,12 @@
           <t>Marka ay aqoonsigaaga hubiyaan</t>
         </is>
       </c>
-      <c r="H22" s="14" t="inlineStr"/>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>Baada ya kukagua kitambulisho chako</t>
+        </is>
+      </c>
+      <c r="I22" s="14" t="inlineStr"/>
     </row>
     <row r="23" ht="44" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
@@ -4385,7 +4915,12 @@
           <t>Wicitaankan, waligeed maya</t>
         </is>
       </c>
-      <c r="H23" s="14" t="inlineStr"/>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>Sio kwenye simu hii, kamwe</t>
+        </is>
+      </c>
+      <c r="I23" s="14" t="inlineStr"/>
     </row>
     <row r="24" ht="44" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
@@ -4423,7 +4958,12 @@
           <t>Cod</t>
         </is>
       </c>
-      <c r="H24" s="14" t="inlineStr"/>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>Sauti</t>
+        </is>
+      </c>
+      <c r="I24" s="14" t="inlineStr"/>
     </row>
     <row r="25" ht="44" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
@@ -4461,7 +5001,12 @@
           <t>Fiidiyow</t>
         </is>
       </c>
-      <c r="H25" s="14" t="inlineStr"/>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>Vidio</t>
+        </is>
+      </c>
+      <c r="I25" s="14" t="inlineStr"/>
     </row>
     <row r="26" ht="44" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
@@ -4499,7 +5044,12 @@
           <t>Hadda maya</t>
         </is>
       </c>
-      <c r="H26" s="14" t="inlineStr"/>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>Sio sasa</t>
+        </is>
+      </c>
+      <c r="I26" s="14" t="inlineStr"/>
     </row>
     <row r="27" ht="44" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
@@ -4537,7 +5087,12 @@
           <t>Safka gal</t>
         </is>
       </c>
-      <c r="H27" s="14" t="inlineStr"/>
+      <c r="H27" s="13" t="inlineStr">
+        <is>
+          <t>Jiunge na foleni</t>
+        </is>
+      </c>
+      <c r="I27" s="14" t="inlineStr"/>
     </row>
     <row r="28" ht="44" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
@@ -4575,7 +5130,12 @@
           <t>Waxaa la sugayaa shaqaale xisaabeed</t>
         </is>
       </c>
-      <c r="H28" s="14" t="inlineStr"/>
+      <c r="H28" s="13" t="inlineStr">
+        <is>
+          <t>Inasubiri afisa</t>
+        </is>
+      </c>
+      <c r="I28" s="14" t="inlineStr"/>
     </row>
     <row r="29" ht="44" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
@@ -4613,7 +5173,12 @@
           <t>Safka ka bax</t>
         </is>
       </c>
-      <c r="H29" s="14" t="inlineStr"/>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>Ondoka kwenye foleni</t>
+        </is>
+      </c>
+      <c r="I29" s="14" t="inlineStr"/>
     </row>
     <row r="30" ht="44" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
@@ -4651,7 +5216,12 @@
           <t>Safkii waad ka baxday. Haddii wax kale aan kaa caawiyo jiraan, halkan ayaan joogaa.</t>
         </is>
       </c>
-      <c r="H30" s="14" t="inlineStr"/>
+      <c r="H30" s="13" t="inlineStr">
+        <is>
+          <t>Umeondoka kwenye foleni. Nipo hapa kama kuna kingine ninaweza kukusaidia.</t>
+        </is>
+      </c>
+      <c r="I30" s="14" t="inlineStr"/>
     </row>
     <row r="31" ht="44" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
@@ -4689,7 +5259,12 @@
           <t>Wicitaan shaqaale xisaabeed</t>
         </is>
       </c>
-      <c r="H31" s="14" t="inlineStr"/>
+      <c r="H31" s="13" t="inlineStr">
+        <is>
+          <t>Piga simu na afisa</t>
+        </is>
+      </c>
+      <c r="I31" s="14" t="inlineStr"/>
     </row>
     <row r="32" ht="44" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
@@ -4727,7 +5302,12 @@
           <t>Waa la xidhiidhinayaa…</t>
         </is>
       </c>
-      <c r="H32" s="14" t="inlineStr"/>
+      <c r="H32" s="13" t="inlineStr">
+        <is>
+          <t>Inaunganisha…</t>
+        </is>
+      </c>
+      <c r="I32" s="14" t="inlineStr"/>
     </row>
     <row r="33" ht="44" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
@@ -4765,7 +5345,12 @@
           <t>Dib ayaa loo xidhiidhinayaa…</t>
         </is>
       </c>
-      <c r="H33" s="14" t="inlineStr"/>
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>Inaunganisha upya…</t>
+        </is>
+      </c>
+      <c r="I33" s="14" t="inlineStr"/>
     </row>
     <row r="34" ht="44" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
@@ -4803,7 +5388,12 @@
           <t>Fariimaha</t>
         </is>
       </c>
-      <c r="H34" s="14" t="inlineStr"/>
+      <c r="H34" s="13" t="inlineStr">
+        <is>
+          <t>Ujumbe</t>
+        </is>
+      </c>
+      <c r="I34" s="14" t="inlineStr"/>
     </row>
     <row r="35" ht="44" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
@@ -4841,7 +5431,12 @@
           <t>Xidh fariimaha</t>
         </is>
       </c>
-      <c r="H35" s="14" t="inlineStr"/>
+      <c r="H35" s="13" t="inlineStr">
+        <is>
+          <t>Funga ujumbe</t>
+        </is>
+      </c>
+      <c r="I35" s="14" t="inlineStr"/>
     </row>
     <row r="36" ht="44" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
@@ -4879,7 +5474,12 @@
           <t>Qor fariin…</t>
         </is>
       </c>
-      <c r="H36" s="14" t="inlineStr"/>
+      <c r="H36" s="13" t="inlineStr">
+        <is>
+          <t>Andika ujumbe…</t>
+        </is>
+      </c>
+      <c r="I36" s="14" t="inlineStr"/>
     </row>
     <row r="37" ht="44" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
@@ -4917,7 +5517,12 @@
           <t>Kamarad</t>
         </is>
       </c>
-      <c r="H37" s="14" t="inlineStr"/>
+      <c r="H37" s="13" t="inlineStr">
+        <is>
+          <t>Kamera</t>
+        </is>
+      </c>
+      <c r="I37" s="14" t="inlineStr"/>
     </row>
     <row r="38" ht="44" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
@@ -4955,7 +5560,12 @@
           <t>Tus aqoonsigayga</t>
         </is>
       </c>
-      <c r="H38" s="14" t="inlineStr"/>
+      <c r="H38" s="13" t="inlineStr">
+        <is>
+          <t>Onyesha kitambulisho changu</t>
+        </is>
+      </c>
+      <c r="I38" s="14" t="inlineStr"/>
     </row>
     <row r="39" ht="44" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
@@ -4993,7 +5603,12 @@
           <t>Jooji wicitaanka</t>
         </is>
       </c>
-      <c r="H39" s="14" t="inlineStr"/>
+      <c r="H39" s="13" t="inlineStr">
+        <is>
+          <t>Maliza simu</t>
+        </is>
+      </c>
+      <c r="I39" s="14" t="inlineStr"/>
     </row>
     <row r="40" ht="44" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
@@ -5031,7 +5646,12 @@
           <t>Aqoonsigaaga Fayda kamaradda u muuji</t>
         </is>
       </c>
-      <c r="H40" s="14" t="inlineStr"/>
+      <c r="H40" s="13" t="inlineStr">
+        <is>
+          <t>Shikilia kitambulisho chako cha Fayda mbele ya kamera</t>
+        </is>
+      </c>
+      <c r="I40" s="14" t="inlineStr"/>
     </row>
     <row r="41" ht="44" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
@@ -5069,7 +5689,12 @@
           <t>Hagitaan alaab</t>
         </is>
       </c>
-      <c r="H41" s="14" t="inlineStr"/>
+      <c r="H41" s="13" t="inlineStr">
+        <is>
+          <t>Mwongozo wa bidhaa</t>
+        </is>
+      </c>
+      <c r="I41" s="14" t="inlineStr"/>
     </row>
     <row r="42" ht="44" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
@@ -5107,7 +5732,12 @@
           <t>Su'aal tartan</t>
         </is>
       </c>
-      <c r="H42" s="14" t="inlineStr"/>
+      <c r="H42" s="13" t="inlineStr">
+        <is>
+          <t>Swali la ushindani</t>
+        </is>
+      </c>
+      <c r="I42" s="14" t="inlineStr"/>
     </row>
     <row r="43" ht="44" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
@@ -5145,7 +5775,12 @@
           <t>Ilaalinta talada</t>
         </is>
       </c>
-      <c r="H43" s="14" t="inlineStr"/>
+      <c r="H43" s="13" t="inlineStr">
+        <is>
+          <t>Ulinzi wa ushauri</t>
+        </is>
+      </c>
+      <c r="I43" s="14" t="inlineStr"/>
     </row>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
@@ -5183,7 +5818,12 @@
           <t>Ilaalinta macluumaadka xisaabta</t>
         </is>
       </c>
-      <c r="H44" s="14" t="inlineStr"/>
+      <c r="H44" s="13" t="inlineStr">
+        <is>
+          <t>Ulinzi wa taarifa za akaunti</t>
+        </is>
+      </c>
+      <c r="I44" s="14" t="inlineStr"/>
     </row>
     <row r="45" ht="44" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
@@ -5221,7 +5861,12 @@
           <t>Cabasho</t>
         </is>
       </c>
-      <c r="H45" s="14" t="inlineStr"/>
+      <c r="H45" s="13" t="inlineStr">
+        <is>
+          <t>Malalamiko</t>
+        </is>
+      </c>
+      <c r="I45" s="14" t="inlineStr"/>
     </row>
     <row r="46" ht="44" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
@@ -5259,7 +5904,12 @@
           <t>Xiriirka waa la keydiyay</t>
         </is>
       </c>
-      <c r="H46" s="14" t="inlineStr"/>
+      <c r="H46" s="13" t="inlineStr">
+        <is>
+          <t>Mawasiliano yamehifadhiwa</t>
+        </is>
+      </c>
+      <c r="I46" s="14" t="inlineStr"/>
     </row>
     <row r="47" ht="44" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
@@ -5297,7 +5947,12 @@
           <t>Farqiga macluumaadka</t>
         </is>
       </c>
-      <c r="H47" s="14" t="inlineStr"/>
+      <c r="H47" s="13" t="inlineStr">
+        <is>
+          <t>Pengo la maarifa</t>
+        </is>
+      </c>
+      <c r="I47" s="14" t="inlineStr"/>
     </row>
     <row r="48" ht="44" customHeight="1">
       <c r="A48" s="11" t="inlineStr">
@@ -5335,7 +5990,12 @@
           <t>Hagitaan guud</t>
         </is>
       </c>
-      <c r="H48" s="14" t="inlineStr"/>
+      <c r="H48" s="13" t="inlineStr">
+        <is>
+          <t>Mwongozo wa jumla</t>
+        </is>
+      </c>
+      <c r="I48" s="14" t="inlineStr"/>
     </row>
     <row r="49" ht="44" customHeight="1">
       <c r="A49" s="11" t="inlineStr">
@@ -5373,7 +6033,12 @@
           <t>Maanta</t>
         </is>
       </c>
-      <c r="H49" s="14" t="inlineStr"/>
+      <c r="H49" s="13" t="inlineStr">
+        <is>
+          <t>Leo</t>
+        </is>
+      </c>
+      <c r="I49" s="14" t="inlineStr"/>
     </row>
     <row r="50" ht="44" customHeight="1">
       <c r="A50" s="11" t="inlineStr">
@@ -5411,10 +6076,15 @@
           <t>Shalay</t>
         </is>
       </c>
-      <c r="H50" s="14" t="inlineStr"/>
+      <c r="H50" s="13" t="inlineStr">
+        <is>
+          <t>Jana</t>
+        </is>
+      </c>
+      <c r="I50" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H50"/>
+  <autoFilter ref="A1:I50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5425,7 +6095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H270"/>
+  <dimension ref="A1:I270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5435,7 +6105,8 @@
     <col width="44" customWidth="1" min="5" max="5"/>
     <col width="44" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -5476,6 +6147,11 @@
       </c>
       <c r="H1" s="10" t="inlineStr">
         <is>
+          <t>sw — Kiswahili</t>
+        </is>
+      </c>
+      <c r="I1" s="10" t="inlineStr">
+        <is>
           <t>reviewer notes</t>
         </is>
       </c>
@@ -5516,7 +6192,12 @@
           <t>Dashboard-ka</t>
         </is>
       </c>
-      <c r="H2" s="14" t="inlineStr"/>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Dashibodi</t>
+        </is>
+      </c>
+      <c r="I2" s="14" t="inlineStr"/>
     </row>
     <row r="3" ht="44" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
@@ -5554,7 +6235,12 @@
           <t>Su'aalaha kor loo gudbiyay</t>
         </is>
       </c>
-      <c r="H3" s="14" t="inlineStr"/>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Masuala Yaliyoelekezwa</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr"/>
     </row>
     <row r="4" ht="44" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
@@ -5592,7 +6278,12 @@
           <t>Safka tooska ah</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr"/>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>Foleni ya Moja kwa Moja</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr"/>
     </row>
     <row r="5" ht="44" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
@@ -5630,7 +6321,12 @@
           <t>Wadahadallada</t>
         </is>
       </c>
-      <c r="H5" s="14" t="inlineStr"/>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>Mazungumzo</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr"/>
     </row>
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
@@ -5668,7 +6364,12 @@
           <t>Kaydka macluumaadka</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr"/>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>Hazina ya Maarifa</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr"/>
     </row>
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
@@ -5706,7 +6407,12 @@
           <t>Jawaabaha la ansixiyay</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr"/>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>Majibu Yaliyoidhinishwa</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="inlineStr"/>
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
@@ -5744,7 +6450,12 @@
           <t>Farqiga macluumaadka</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr"/>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>Mapungufu ya Maudhui</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr"/>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
@@ -5782,7 +6493,12 @@
           <t>Kanaallada</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr"/>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>Njia za Mawasiliano</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="inlineStr"/>
     </row>
     <row r="10" ht="44" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
@@ -5820,7 +6536,12 @@
           <t>Diiwaanka hubinta</t>
         </is>
       </c>
-      <c r="H10" s="14" t="inlineStr"/>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>Kumbukumbu za Ukaguzi</t>
+        </is>
+      </c>
+      <c r="I10" s="14" t="inlineStr"/>
     </row>
     <row r="11" ht="44" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
@@ -5858,7 +6579,12 @@
           <t>Dejinta</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr"/>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>Mipangilio</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="inlineStr"/>
     </row>
     <row r="12" ht="44" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
@@ -5896,7 +6622,12 @@
           <t>Kooxda</t>
         </is>
       </c>
-      <c r="H12" s="14" t="inlineStr"/>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>Timu</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="inlineStr"/>
     </row>
     <row r="13" ht="44" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
@@ -5934,7 +6665,12 @@
           <t>Ka bax</t>
         </is>
       </c>
-      <c r="H13" s="14" t="inlineStr"/>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>Toka</t>
+        </is>
+      </c>
+      <c r="I13" s="14" t="inlineStr"/>
     </row>
     <row r="14" ht="44" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
@@ -5972,7 +6708,12 @@
           <t>Kaydi</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr"/>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>Hifadhi</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr"/>
     </row>
     <row r="15" ht="44" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
@@ -6010,7 +6751,12 @@
           <t>Jooji</t>
         </is>
       </c>
-      <c r="H15" s="14" t="inlineStr"/>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>Ghairi</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="inlineStr"/>
     </row>
     <row r="16" ht="44" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
@@ -6048,7 +6794,12 @@
           <t>Xidh</t>
         </is>
       </c>
-      <c r="H16" s="14" t="inlineStr"/>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>Funga</t>
+        </is>
+      </c>
+      <c r="I16" s="14" t="inlineStr"/>
     </row>
     <row r="17" ht="44" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
@@ -6086,7 +6837,12 @@
           <t>Raadi</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr"/>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>Tafuta</t>
+        </is>
+      </c>
+      <c r="I17" s="14" t="inlineStr"/>
     </row>
     <row r="18" ht="44" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
@@ -6124,7 +6880,12 @@
           <t>Raadi wax kasta…</t>
         </is>
       </c>
-      <c r="H18" s="14" t="inlineStr"/>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>Tafuta kila kitu…</t>
+        </is>
+      </c>
+      <c r="I18" s="14" t="inlineStr"/>
     </row>
     <row r="19" ht="44" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
@@ -6162,7 +6923,12 @@
           <t>Natiijo lama helin.</t>
         </is>
       </c>
-      <c r="H19" s="14" t="inlineStr"/>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>Hakuna kinacholingana.</t>
+        </is>
+      </c>
+      <c r="I19" s="14" t="inlineStr"/>
     </row>
     <row r="20" ht="44" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
@@ -6200,7 +6966,12 @@
           <t>Raadi wadahadallada, su'aalaha kor loo gudbiyay, kaydka macluumaadka iyo jawaabaha la ansixiyay</t>
         </is>
       </c>
-      <c r="H20" s="14" t="inlineStr"/>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>Tafuta mazungumzo, masuala yaliyoelekezwa, hazina ya maarifa na majibu yaliyoidhinishwa</t>
+        </is>
+      </c>
+      <c r="I20" s="14" t="inlineStr"/>
     </row>
     <row r="21" ht="44" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
@@ -6238,7 +7009,12 @@
           <t>Waa la soo dejinayaa…</t>
         </is>
       </c>
-      <c r="H21" s="14" t="inlineStr"/>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>Inapakia…</t>
+        </is>
+      </c>
+      <c r="I21" s="14" t="inlineStr"/>
     </row>
     <row r="22" ht="44" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
@@ -6276,7 +7052,12 @@
           <t>Shaqada joog</t>
         </is>
       </c>
-      <c r="H22" s="14" t="inlineStr"/>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>Kazini</t>
+        </is>
+      </c>
+      <c r="I22" s="14" t="inlineStr"/>
     </row>
     <row r="23" ht="44" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
@@ -6314,7 +7095,12 @@
           <t>Shaqada ka maqan</t>
         </is>
       </c>
-      <c r="H23" s="14" t="inlineStr"/>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>Nje ya Kazi</t>
+        </is>
+      </c>
+      <c r="I23" s="14" t="inlineStr"/>
     </row>
     <row r="24" ht="44" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
@@ -6352,7 +7138,12 @@
           <t>Kalfadhiyada tooska ah waa furan yihiin</t>
         </is>
       </c>
-      <c r="H24" s="14" t="inlineStr"/>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>Vikao vya moja kwa moja vimewashwa</t>
+        </is>
+      </c>
+      <c r="I24" s="14" t="inlineStr"/>
     </row>
     <row r="25" ht="44" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
@@ -6390,7 +7181,12 @@
           <t>Kalfadhiyada tooska ah waa xidhan yihiin</t>
         </is>
       </c>
-      <c r="H25" s="14" t="inlineStr"/>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>Vikao vya moja kwa moja vimezimwa</t>
+        </is>
+      </c>
+      <c r="I25" s="14" t="inlineStr"/>
     </row>
     <row r="26" ht="44" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
@@ -6428,7 +7224,12 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="H26" s="14" t="inlineStr"/>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>Washa</t>
+        </is>
+      </c>
+      <c r="I26" s="14" t="inlineStr"/>
     </row>
     <row r="27" ht="44" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
@@ -6466,7 +7267,12 @@
           <t>Xidh</t>
         </is>
       </c>
-      <c r="H27" s="14" t="inlineStr"/>
+      <c r="H27" s="13" t="inlineStr">
+        <is>
+          <t>Zima</t>
+        </is>
+      </c>
+      <c r="I27" s="14" t="inlineStr"/>
     </row>
     <row r="28" ht="44" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
@@ -6504,7 +7310,12 @@
           <t>Macaamiisha hadda way heli karaan shaqaale xisaabeed</t>
         </is>
       </c>
-      <c r="H28" s="14" t="inlineStr"/>
+      <c r="H28" s="13" t="inlineStr">
+        <is>
+          <t>Wateja wanaweza kumfikia afisa sasa</t>
+        </is>
+      </c>
+      <c r="I28" s="14" t="inlineStr"/>
     </row>
     <row r="29" ht="44" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
@@ -6542,7 +7353,12 @@
           <t>Macaamiisha waxay heli doonaan asxaabtaada — adigu shaqada kama joogtid</t>
         </is>
       </c>
-      <c r="H29" s="14" t="inlineStr"/>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>Wateja wanaweza kumfikia mwenzako — wewe upo nje ya kazi</t>
+        </is>
+      </c>
+      <c r="I29" s="14" t="inlineStr"/>
     </row>
     <row r="30" ht="44" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
@@ -6580,7 +7396,12 @@
           <t>Kii ugu horreeyay marka hore. Kii ugu dheeraaday sugitaanka ayaa la qaadaa.</t>
         </is>
       </c>
-      <c r="H30" s="14" t="inlineStr"/>
+      <c r="H30" s="13" t="inlineStr">
+        <is>
+          <t>Wa zamani zaidi kwanza. Aliyesubiri kwa muda mrefu zaidi ndiye wa kuhudumiwa.</t>
+        </is>
+      </c>
+      <c r="I30" s="14" t="inlineStr"/>
     </row>
     <row r="31" ht="44" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
@@ -6618,7 +7439,12 @@
           <t>Sugaya</t>
         </is>
       </c>
-      <c r="H31" s="14" t="inlineStr"/>
+      <c r="H31" s="13" t="inlineStr">
+        <is>
+          <t>Anasubiri</t>
+        </is>
+      </c>
+      <c r="I31" s="14" t="inlineStr"/>
     </row>
     <row r="32" ht="44" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
@@ -6656,7 +7482,12 @@
           <t>Qaado</t>
         </is>
       </c>
-      <c r="H32" s="14" t="inlineStr"/>
+      <c r="H32" s="13" t="inlineStr">
+        <is>
+          <t>Chukua</t>
+        </is>
+      </c>
+      <c r="I32" s="14" t="inlineStr"/>
     </row>
     <row r="33" ht="44" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
@@ -6694,7 +7525,12 @@
           <t>Kalfadhiga waa la qaatay</t>
         </is>
       </c>
-      <c r="H33" s="14" t="inlineStr"/>
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>Kikao kimechukuliwa</t>
+        </is>
+      </c>
+      <c r="I33" s="14" t="inlineStr"/>
     </row>
     <row r="34" ht="44" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
@@ -6732,7 +7568,12 @@
           <t>Kalfadhiga waa la dhammeeyay</t>
         </is>
       </c>
-      <c r="H34" s="14" t="inlineStr"/>
+      <c r="H34" s="13" t="inlineStr">
+        <is>
+          <t>Kikao kimekwisha</t>
+        </is>
+      </c>
+      <c r="I34" s="14" t="inlineStr"/>
     </row>
     <row r="35" ht="44" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
@@ -6770,7 +7611,12 @@
           <t>Ku noqo tooska</t>
         </is>
       </c>
-      <c r="H35" s="14" t="inlineStr"/>
+      <c r="H35" s="13" t="inlineStr">
+        <is>
+          <t>Rudi kwenye moja kwa moja</t>
+        </is>
+      </c>
+      <c r="I35" s="14" t="inlineStr"/>
     </row>
     <row r="36" ht="44" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
@@ -6808,7 +7654,12 @@
           <t>Cidna ma sugayso.</t>
         </is>
       </c>
-      <c r="H36" s="14" t="inlineStr"/>
+      <c r="H36" s="13" t="inlineStr">
+        <is>
+          <t>Hakuna anayesubiri.</t>
+        </is>
+      </c>
+      <c r="I36" s="14" t="inlineStr"/>
     </row>
     <row r="37" ht="44" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
@@ -6846,7 +7697,12 @@
           <t>Wadahadal</t>
         </is>
       </c>
-      <c r="H37" s="14" t="inlineStr"/>
+      <c r="H37" s="13" t="inlineStr">
+        <is>
+          <t>Mazungumzo</t>
+        </is>
+      </c>
+      <c r="I37" s="14" t="inlineStr"/>
     </row>
     <row r="38" ht="44" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
@@ -6884,7 +7740,12 @@
           <t>Dir</t>
         </is>
       </c>
-      <c r="H38" s="14" t="inlineStr"/>
+      <c r="H38" s="13" t="inlineStr">
+        <is>
+          <t>Tuma</t>
+        </is>
+      </c>
+      <c r="I38" s="14" t="inlineStr"/>
     </row>
     <row r="39" ht="44" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
@@ -6922,7 +7783,12 @@
           <t>Fariin u qor macmiilka…</t>
         </is>
       </c>
-      <c r="H39" s="14" t="inlineStr"/>
+      <c r="H39" s="13" t="inlineStr">
+        <is>
+          <t>Mtumie mteja ujumbe…</t>
+        </is>
+      </c>
+      <c r="I39" s="14" t="inlineStr"/>
     </row>
     <row r="40" ht="44" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
@@ -6960,7 +7826,12 @@
           <t>Waa la xidhiidhinayaa…</t>
         </is>
       </c>
-      <c r="H40" s="14" t="inlineStr"/>
+      <c r="H40" s="13" t="inlineStr">
+        <is>
+          <t>Inaunganisha…</t>
+        </is>
+      </c>
+      <c r="I40" s="14" t="inlineStr"/>
     </row>
     <row r="41" ht="44" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
@@ -6998,7 +7869,12 @@
           <t>Waa la xidhiidhiyay</t>
         </is>
       </c>
-      <c r="H41" s="14" t="inlineStr"/>
+      <c r="H41" s="13" t="inlineStr">
+        <is>
+          <t>Imeunganishwa</t>
+        </is>
+      </c>
+      <c r="I41" s="14" t="inlineStr"/>
     </row>
     <row r="42" ht="44" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
@@ -7036,7 +7912,12 @@
           <t>Waa la xidhiidhiyay — cod kaliya</t>
         </is>
       </c>
-      <c r="H42" s="14" t="inlineStr"/>
+      <c r="H42" s="13" t="inlineStr">
+        <is>
+          <t>Imeunganishwa — sauti pekee</t>
+        </is>
+      </c>
+      <c r="I42" s="14" t="inlineStr"/>
     </row>
     <row r="43" ht="44" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
@@ -7074,7 +7955,12 @@
           <t>Lama xidhiidhin</t>
         </is>
       </c>
-      <c r="H43" s="14" t="inlineStr"/>
+      <c r="H43" s="13" t="inlineStr">
+        <is>
+          <t>Haijaunganishwa</t>
+        </is>
+      </c>
+      <c r="I43" s="14" t="inlineStr"/>
     </row>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
@@ -7112,7 +7998,12 @@
           <t xml:space="preserve">Lama xidhiidhin karin: </t>
         </is>
       </c>
-      <c r="H44" s="14" t="inlineStr"/>
+      <c r="H44" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Imeshindwa kuunganisha: </t>
+        </is>
+      </c>
+      <c r="I44" s="14" t="inlineStr"/>
     </row>
     <row r="45" ht="44" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
@@ -7150,7 +8041,12 @@
           <t>Cod xidh</t>
         </is>
       </c>
-      <c r="H45" s="14" t="inlineStr"/>
+      <c r="H45" s="13" t="inlineStr">
+        <is>
+          <t>Zima Sauti</t>
+        </is>
+      </c>
+      <c r="I45" s="14" t="inlineStr"/>
     </row>
     <row r="46" ht="44" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
@@ -7188,7 +8084,12 @@
           <t>Kamarad</t>
         </is>
       </c>
-      <c r="H46" s="14" t="inlineStr"/>
+      <c r="H46" s="13" t="inlineStr">
+        <is>
+          <t>Kamera</t>
+        </is>
+      </c>
+      <c r="I46" s="14" t="inlineStr"/>
     </row>
     <row r="47" ht="44" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
@@ -7226,7 +8127,12 @@
           <t>Kalfadhiga jooji</t>
         </is>
       </c>
-      <c r="H47" s="14" t="inlineStr"/>
+      <c r="H47" s="13" t="inlineStr">
+        <is>
+          <t>Maliza Kikao</t>
+        </is>
+      </c>
+      <c r="I47" s="14" t="inlineStr"/>
     </row>
     <row r="48" ht="44" customHeight="1">
       <c r="A48" s="11" t="inlineStr">
@@ -7264,7 +8170,12 @@
           <t>Sawirka jooji</t>
         </is>
       </c>
-      <c r="H48" s="14" t="inlineStr"/>
+      <c r="H48" s="13" t="inlineStr">
+        <is>
+          <t>Simamisha Picha</t>
+        </is>
+      </c>
+      <c r="I48" s="14" t="inlineStr"/>
     </row>
     <row r="49" ht="44" customHeight="1">
       <c r="A49" s="11" t="inlineStr">
@@ -7302,7 +8213,12 @@
           <t>Luqadda lama garanayo</t>
         </is>
       </c>
-      <c r="H49" s="14" t="inlineStr"/>
+      <c r="H49" s="13" t="inlineStr">
+        <is>
+          <t>Lugha Haijulikani</t>
+        </is>
+      </c>
+      <c r="I49" s="14" t="inlineStr"/>
     </row>
     <row r="50" ht="44" customHeight="1">
       <c r="A50" s="11" t="inlineStr">
@@ -7340,7 +8256,12 @@
           <t>Aqoonsiga waa la xaqiijiyay</t>
         </is>
       </c>
-      <c r="H50" s="14" t="inlineStr"/>
+      <c r="H50" s="13" t="inlineStr">
+        <is>
+          <t>Utambulisho Umethibitishwa</t>
+        </is>
+      </c>
+      <c r="I50" s="14" t="inlineStr"/>
     </row>
     <row r="51" ht="44" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
@@ -7378,7 +8299,12 @@
           <t>Waa la aqoonsaday</t>
         </is>
       </c>
-      <c r="H51" s="14" t="inlineStr"/>
+      <c r="H51" s="13" t="inlineStr">
+        <is>
+          <t>Ametambuliwa</t>
+        </is>
+      </c>
+      <c r="I51" s="14" t="inlineStr"/>
     </row>
     <row r="52" ht="44" customHeight="1">
       <c r="A52" s="11" t="inlineStr">
@@ -7416,7 +8342,12 @@
           <t>Weli lama aqoonsan</t>
         </is>
       </c>
-      <c r="H52" s="14" t="inlineStr"/>
+      <c r="H52" s="13" t="inlineStr">
+        <is>
+          <t>Bado Hajatambuliwa</t>
+        </is>
+      </c>
+      <c r="I52" s="14" t="inlineStr"/>
     </row>
     <row r="53" ht="44" customHeight="1">
       <c r="A53" s="11" t="inlineStr">
@@ -7454,7 +8385,12 @@
           <t>Lambarka Fayda</t>
         </is>
       </c>
-      <c r="H53" s="14" t="inlineStr"/>
+      <c r="H53" s="13" t="inlineStr">
+        <is>
+          <t>Namba ya Fayda</t>
+        </is>
+      </c>
+      <c r="I53" s="14" t="inlineStr"/>
     </row>
     <row r="54" ht="44" customHeight="1">
       <c r="A54" s="11" t="inlineStr">
@@ -7492,7 +8428,12 @@
           <t>Lambarka Fayda (ikhtiyaari)</t>
         </is>
       </c>
-      <c r="H54" s="14" t="inlineStr"/>
+      <c r="H54" s="13" t="inlineStr">
+        <is>
+          <t>Namba ya Fayda (si lazima)</t>
+        </is>
+      </c>
+      <c r="I54" s="14" t="inlineStr"/>
     </row>
     <row r="55" ht="44" customHeight="1">
       <c r="A55" s="11" t="inlineStr">
@@ -7530,7 +8471,12 @@
           <t>Wuxuu ka jawaabay su'aal uu keliya og yahay milkiilaha xisaabta</t>
         </is>
       </c>
-      <c r="H55" s="14" t="inlineStr"/>
+      <c r="H55" s="13" t="inlineStr">
+        <is>
+          <t>Amejibu swali ambalo mmiliki wa akaunti pekee angeweza</t>
+        </is>
+      </c>
+      <c r="I55" s="14" t="inlineStr"/>
     </row>
     <row r="56" ht="44" customHeight="1">
       <c r="A56" s="11" t="inlineStr">
@@ -7568,7 +8514,12 @@
           <t>Jawaabaha la ansixiyay</t>
         </is>
       </c>
-      <c r="H56" s="14" t="inlineStr"/>
+      <c r="H56" s="13" t="inlineStr">
+        <is>
+          <t>Majibu Yaliyoidhinishwa</t>
+        </is>
+      </c>
+      <c r="I56" s="14" t="inlineStr"/>
     </row>
     <row r="57" ht="44" customHeight="1">
       <c r="A57" s="11" t="inlineStr">
@@ -7606,7 +8557,12 @@
           <t>Raadi jawaabaha uu bangigu ansixiyay…</t>
         </is>
       </c>
-      <c r="H57" s="14" t="inlineStr"/>
+      <c r="H57" s="13" t="inlineStr">
+        <is>
+          <t>Tafuta majibu yaliyoidhinishwa ya benki…</t>
+        </is>
+      </c>
+      <c r="I57" s="14" t="inlineStr"/>
     </row>
     <row r="58" ht="44" customHeight="1">
       <c r="A58" s="11" t="inlineStr">
@@ -7644,7 +8600,12 @@
           <t>Jawaabaha la ansixiyay lama helin.</t>
         </is>
       </c>
-      <c r="H58" s="14" t="inlineStr"/>
+      <c r="H58" s="13" t="inlineStr">
+        <is>
+          <t>Majibu yaliyoidhinishwa hayapatikani.</t>
+        </is>
+      </c>
+      <c r="I58" s="14" t="inlineStr"/>
     </row>
     <row r="59" ht="44" customHeight="1">
       <c r="A59" s="11" t="inlineStr">
@@ -7682,7 +8643,12 @@
           <t>Weli ma jiraan jawaabo la ansixiyay.</t>
         </is>
       </c>
-      <c r="H59" s="14" t="inlineStr"/>
+      <c r="H59" s="13" t="inlineStr">
+        <is>
+          <t>Hakuna majibu yaliyoidhinishwa bado.</t>
+        </is>
+      </c>
+      <c r="I59" s="14" t="inlineStr"/>
     </row>
     <row r="60" ht="44" customHeight="1">
       <c r="A60" s="11" t="inlineStr">
@@ -7720,7 +8686,12 @@
           <t>Waxba kuma habboona</t>
         </is>
       </c>
-      <c r="H60" s="14" t="inlineStr"/>
+      <c r="H60" s="13" t="inlineStr">
+        <is>
+          <t>Hakuna kinacholingana</t>
+        </is>
+      </c>
+      <c r="I60" s="14" t="inlineStr"/>
     </row>
     <row r="61" ht="44" customHeight="1">
       <c r="A61" s="11" t="inlineStr">
@@ -7758,7 +8729,12 @@
           <t>{bank} — warbixinta kaaliyaha</t>
         </is>
       </c>
-      <c r="H61" s="14" t="inlineStr"/>
+      <c r="H61" s="13" t="inlineStr">
+        <is>
+          <t>{bank} — ripoti ya msaidizi</t>
+        </is>
+      </c>
+      <c r="I61" s="14" t="inlineStr"/>
     </row>
     <row r="62" ht="44" customHeight="1">
       <c r="A62" s="11" t="inlineStr">
@@ -7796,7 +8772,12 @@
           <t>{n} maalmood ee la soo dhaafay</t>
         </is>
       </c>
-      <c r="H62" s="14" t="inlineStr"/>
+      <c r="H62" s="13" t="inlineStr">
+        <is>
+          <t>Siku {n} zilizopita</t>
+        </is>
+      </c>
+      <c r="I62" s="14" t="inlineStr"/>
     </row>
     <row r="63" ht="44" customHeight="1">
       <c r="A63" s="11" t="inlineStr">
@@ -7834,7 +8815,12 @@
           <t>Waqti kasta</t>
         </is>
       </c>
-      <c r="H63" s="14" t="inlineStr"/>
+      <c r="H63" s="13" t="inlineStr">
+        <is>
+          <t>Wakati Wote</t>
+        </is>
+      </c>
+      <c r="I63" s="14" t="inlineStr"/>
     </row>
     <row r="64" ht="44" customHeight="1">
       <c r="A64" s="11" t="inlineStr">
@@ -7872,7 +8858,12 @@
           <t>la sameeyay {when}</t>
         </is>
       </c>
-      <c r="H64" s="14" t="inlineStr"/>
+      <c r="H64" s="13" t="inlineStr">
+        <is>
+          <t>imetengenezwa {when}</t>
+        </is>
+      </c>
+      <c r="I64" s="14" t="inlineStr"/>
     </row>
     <row r="65" ht="44" customHeight="1">
       <c r="A65" s="11" t="inlineStr">
@@ -7910,7 +8901,12 @@
           <t>7 maalmood</t>
         </is>
       </c>
-      <c r="H65" s="14" t="inlineStr"/>
+      <c r="H65" s="13" t="inlineStr">
+        <is>
+          <t>Siku 7</t>
+        </is>
+      </c>
+      <c r="I65" s="14" t="inlineStr"/>
     </row>
     <row r="66" ht="44" customHeight="1">
       <c r="A66" s="11" t="inlineStr">
@@ -7948,7 +8944,12 @@
           <t>30 maalmood</t>
         </is>
       </c>
-      <c r="H66" s="14" t="inlineStr"/>
+      <c r="H66" s="13" t="inlineStr">
+        <is>
+          <t>Siku 30</t>
+        </is>
+      </c>
+      <c r="I66" s="14" t="inlineStr"/>
     </row>
     <row r="67" ht="44" customHeight="1">
       <c r="A67" s="11" t="inlineStr">
@@ -7986,7 +8987,12 @@
           <t>90 maalmood</t>
         </is>
       </c>
-      <c r="H67" s="14" t="inlineStr"/>
+      <c r="H67" s="13" t="inlineStr">
+        <is>
+          <t>Siku 90</t>
+        </is>
+      </c>
+      <c r="I67" s="14" t="inlineStr"/>
     </row>
     <row r="68" ht="44" customHeight="1">
       <c r="A68" s="11" t="inlineStr">
@@ -8024,7 +9030,12 @@
           <t>Dhammaan</t>
         </is>
       </c>
-      <c r="H68" s="14" t="inlineStr"/>
+      <c r="H68" s="13" t="inlineStr">
+        <is>
+          <t>Zote</t>
+        </is>
+      </c>
+      <c r="I68" s="14" t="inlineStr"/>
     </row>
     <row r="69" ht="44" customHeight="1">
       <c r="A69" s="11" t="inlineStr">
@@ -8062,7 +9073,12 @@
           <t>CSV soo saar</t>
         </is>
       </c>
-      <c r="H69" s="14" t="inlineStr"/>
+      <c r="H69" s="13" t="inlineStr">
+        <is>
+          <t>Hamisha CSV</t>
+        </is>
+      </c>
+      <c r="I69" s="14" t="inlineStr"/>
     </row>
     <row r="70" ht="44" customHeight="1">
       <c r="A70" s="11" t="inlineStr">
@@ -8100,7 +9116,12 @@
           <t>Daabac</t>
         </is>
       </c>
-      <c r="H70" s="14" t="inlineStr"/>
+      <c r="H70" s="13" t="inlineStr">
+        <is>
+          <t>Chapisha</t>
+        </is>
+      </c>
+      <c r="I70" s="14" t="inlineStr"/>
     </row>
     <row r="71" ht="44" customHeight="1">
       <c r="A71" s="11" t="inlineStr">
@@ -8138,7 +9159,12 @@
           <t>Subax wanaagsan</t>
         </is>
       </c>
-      <c r="H71" s="14" t="inlineStr"/>
+      <c r="H71" s="13" t="inlineStr">
+        <is>
+          <t>Habari za Asubuhi</t>
+        </is>
+      </c>
+      <c r="I71" s="14" t="inlineStr"/>
     </row>
     <row r="72" ht="44" customHeight="1">
       <c r="A72" s="11" t="inlineStr">
@@ -8176,7 +9202,12 @@
           <t>Galab wanaagsan</t>
         </is>
       </c>
-      <c r="H72" s="14" t="inlineStr"/>
+      <c r="H72" s="13" t="inlineStr">
+        <is>
+          <t>Habari za Mchana</t>
+        </is>
+      </c>
+      <c r="I72" s="14" t="inlineStr"/>
     </row>
     <row r="73" ht="44" customHeight="1">
       <c r="A73" s="11" t="inlineStr">
@@ -8214,7 +9245,12 @@
           <t>Fiid wanaagsan</t>
         </is>
       </c>
-      <c r="H73" s="14" t="inlineStr"/>
+      <c r="H73" s="13" t="inlineStr">
+        <is>
+          <t>Habari za Jioni</t>
+        </is>
+      </c>
+      <c r="I73" s="14" t="inlineStr"/>
     </row>
     <row r="74" ht="44" customHeight="1">
       <c r="A74" s="11" t="inlineStr">
@@ -8252,7 +9288,12 @@
           <t>{n} arrin ayaa qof sugaya.</t>
         </is>
       </c>
-      <c r="H74" s="14" t="inlineStr"/>
+      <c r="H74" s="13" t="inlineStr">
+        <is>
+          <t>Suala {n} linasubiri mtu.</t>
+        </is>
+      </c>
+      <c r="I74" s="14" t="inlineStr"/>
     </row>
     <row r="75" ht="44" customHeight="1">
       <c r="A75" s="11" t="inlineStr">
@@ -8290,7 +9331,12 @@
           <t>{n} arrimood ayaa qof sugaya.</t>
         </is>
       </c>
-      <c r="H75" s="14" t="inlineStr"/>
+      <c r="H75" s="13" t="inlineStr">
+        <is>
+          <t>Masuala {n} yanasubiri mtu.</t>
+        </is>
+      </c>
+      <c r="I75" s="14" t="inlineStr"/>
     </row>
     <row r="76" ht="44" customHeight="1">
       <c r="A76" s="11" t="inlineStr">
@@ -8328,7 +9374,12 @@
           <t>Waxba safka kuma jiraan.</t>
         </is>
       </c>
-      <c r="H76" s="14" t="inlineStr"/>
+      <c r="H76" s="13" t="inlineStr">
+        <is>
+          <t>Hakuna kinachosubiri kwenye foleni.</t>
+        </is>
+      </c>
+      <c r="I76" s="14" t="inlineStr"/>
     </row>
     <row r="77" ht="44" customHeight="1">
       <c r="A77" s="11" t="inlineStr">
@@ -8366,7 +9417,12 @@
           <t>{n} maalmood ee la soo dhaafay</t>
         </is>
       </c>
-      <c r="H77" s="14" t="inlineStr"/>
+      <c r="H77" s="13" t="inlineStr">
+        <is>
+          <t>siku {n} zilizopita</t>
+        </is>
+      </c>
+      <c r="I77" s="14" t="inlineStr"/>
     </row>
     <row r="78" ht="44" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
@@ -8404,7 +9460,12 @@
           <t>waqti kasta</t>
         </is>
       </c>
-      <c r="H78" s="14" t="inlineStr"/>
+      <c r="H78" s="13" t="inlineStr">
+        <is>
+          <t>wakati wote</t>
+        </is>
+      </c>
+      <c r="I78" s="14" t="inlineStr"/>
     </row>
     <row r="79" ht="44" customHeight="1">
       <c r="A79" s="11" t="inlineStr">
@@ -8442,7 +9503,12 @@
           <t>Wadahadallo</t>
         </is>
       </c>
-      <c r="H79" s="14" t="inlineStr"/>
+      <c r="H79" s="13" t="inlineStr">
+        <is>
+          <t>Mazungumzo</t>
+        </is>
+      </c>
+      <c r="I79" s="14" t="inlineStr"/>
     </row>
     <row r="80" ht="44" customHeight="1">
       <c r="A80" s="11" t="inlineStr">
@@ -8480,7 +9546,12 @@
           <t>Su'aalaha la weydiiyay</t>
         </is>
       </c>
-      <c r="H80" s="14" t="inlineStr"/>
+      <c r="H80" s="13" t="inlineStr">
+        <is>
+          <t>Maswali Yaliyoulizwa</t>
+        </is>
+      </c>
+      <c r="I80" s="14" t="inlineStr"/>
     </row>
     <row r="81" ht="44" customHeight="1">
       <c r="A81" s="11" t="inlineStr">
@@ -8518,7 +9589,12 @@
           <t>salaanta iyo mahadnaqa lagama tirinayo</t>
         </is>
       </c>
-      <c r="H81" s="14" t="inlineStr"/>
+      <c r="H81" s="13" t="inlineStr">
+        <is>
+          <t>salamu na shukrani hazijumuishwi</t>
+        </is>
+      </c>
+      <c r="I81" s="14" t="inlineStr"/>
     </row>
     <row r="82" ht="44" customHeight="1">
       <c r="A82" s="11" t="inlineStr">
@@ -8556,7 +9632,12 @@
           <t>Qof la'aan la xalliyay</t>
         </is>
       </c>
-      <c r="H82" s="14" t="inlineStr"/>
+      <c r="H82" s="13" t="inlineStr">
+        <is>
+          <t>Yalitatuliwa Bila Mtu</t>
+        </is>
+      </c>
+      <c r="I82" s="14" t="inlineStr"/>
     </row>
     <row r="83" ht="44" customHeight="1">
       <c r="A83" s="11" t="inlineStr">
@@ -8594,7 +9675,12 @@
           <t>weli su'aalo ma jiraan</t>
         </is>
       </c>
-      <c r="H83" s="14" t="inlineStr"/>
+      <c r="H83" s="13" t="inlineStr">
+        <is>
+          <t>hakuna swali bado</t>
+        </is>
+      </c>
+      <c r="I83" s="14" t="inlineStr"/>
     </row>
     <row r="84" ht="44" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
@@ -8632,7 +9718,12 @@
           <t>Laga jawaabay macluumaadkaaga</t>
         </is>
       </c>
-      <c r="H84" s="14" t="inlineStr"/>
+      <c r="H84" s="13" t="inlineStr">
+        <is>
+          <t>Imejibiwa Kutoka kwa Maudhui Yako</t>
+        </is>
+      </c>
+      <c r="I84" s="14" t="inlineStr"/>
     </row>
     <row r="85" ht="44" customHeight="1">
       <c r="A85" s="11" t="inlineStr">
@@ -8670,7 +9761,12 @@
           <t>{n} ka mid ah {m}</t>
         </is>
       </c>
-      <c r="H85" s="14" t="inlineStr"/>
+      <c r="H85" s="13" t="inlineStr">
+        <is>
+          <t>{n} ya {m}</t>
+        </is>
+      </c>
+      <c r="I85" s="14" t="inlineStr"/>
     </row>
     <row r="86" ht="44" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
@@ -8708,7 +9804,12 @@
           <t>Wadahadallada maalintii</t>
         </is>
       </c>
-      <c r="H86" s="14" t="inlineStr"/>
+      <c r="H86" s="13" t="inlineStr">
+        <is>
+          <t>Mazungumzo kwa Siku</t>
+        </is>
+      </c>
+      <c r="I86" s="14" t="inlineStr"/>
     </row>
     <row r="87" ht="44" customHeight="1">
       <c r="A87" s="11" t="inlineStr">
@@ -8746,7 +9847,12 @@
           <t>Safka gudbinta</t>
         </is>
       </c>
-      <c r="H87" s="14" t="inlineStr"/>
+      <c r="H87" s="13" t="inlineStr">
+        <is>
+          <t>Foleni ya Masuala Yaliyoelekezwa</t>
+        </is>
+      </c>
+      <c r="I87" s="14" t="inlineStr"/>
     </row>
     <row r="88" ht="44" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
@@ -8784,7 +9890,12 @@
           <t>Furan</t>
         </is>
       </c>
-      <c r="H88" s="14" t="inlineStr"/>
+      <c r="H88" s="13" t="inlineStr">
+        <is>
+          <t>Wazi</t>
+        </is>
+      </c>
+      <c r="I88" s="14" t="inlineStr"/>
     </row>
     <row r="89" ht="44" customHeight="1">
       <c r="A89" s="11" t="inlineStr">
@@ -8822,7 +9933,12 @@
           <t>Xiran</t>
         </is>
       </c>
-      <c r="H89" s="14" t="inlineStr"/>
+      <c r="H89" s="13" t="inlineStr">
+        <is>
+          <t>Imefungwa</t>
+        </is>
+      </c>
+      <c r="I89" s="14" t="inlineStr"/>
     </row>
     <row r="90" ht="44" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
@@ -8860,7 +9976,12 @@
           <t>{n} la gaari karo</t>
         </is>
       </c>
-      <c r="H90" s="14" t="inlineStr"/>
+      <c r="H90" s="13" t="inlineStr">
+        <is>
+          <t>{n} wanapatikana</t>
+        </is>
+      </c>
+      <c r="I90" s="14" t="inlineStr"/>
     </row>
     <row r="91" ht="44" customHeight="1">
       <c r="A91" s="11" t="inlineStr">
@@ -8898,7 +10019,12 @@
           <t>{n} aan lahayn xogta xiriirka</t>
         </is>
       </c>
-      <c r="H91" s="14" t="inlineStr"/>
+      <c r="H91" s="13" t="inlineStr">
+        <is>
+          <t>{n} hawana taarifa za mawasiliano</t>
+        </is>
+      </c>
+      <c r="I91" s="14" t="inlineStr"/>
     </row>
     <row r="92" ht="44" customHeight="1">
       <c r="A92" s="11" t="inlineStr">
@@ -8936,7 +10062,12 @@
           <t>Maxaa ku dhacay su'aal kasta</t>
         </is>
       </c>
-      <c r="H92" s="14" t="inlineStr"/>
+      <c r="H92" s="13" t="inlineStr">
+        <is>
+          <t>Kilichotokea kwa kila swali</t>
+        </is>
+      </c>
+      <c r="I92" s="14" t="inlineStr"/>
     </row>
     <row r="93" ht="44" customHeight="1">
       <c r="A93" s="11" t="inlineStr">
@@ -8974,7 +10105,12 @@
           <t>Sidoo kale waa la diiwaangeliyay: {items}</t>
         </is>
       </c>
-      <c r="H93" s="14" t="inlineStr"/>
+      <c r="H93" s="13" t="inlineStr">
+        <is>
+          <t>Pia imerekodiwa: {items}</t>
+        </is>
+      </c>
+      <c r="I93" s="14" t="inlineStr"/>
     </row>
     <row r="94" ht="44" customHeight="1">
       <c r="A94" s="11" t="inlineStr">
@@ -9012,7 +10148,12 @@
           <t>{n} jawaabihii hore natiijo ma laha, korna laguma tirin.</t>
         </is>
       </c>
-      <c r="H94" s="14" t="inlineStr"/>
+      <c r="H94" s="13" t="inlineStr">
+        <is>
+          <t>Majibu {n} ya awali hayana matokeo yaliyoainishwa na hayajahesabiwa hapo juu.</t>
+        </is>
+      </c>
+      <c r="I94" s="14" t="inlineStr"/>
     </row>
     <row r="95" ht="44" customHeight="1">
       <c r="A95" s="11" t="inlineStr">
@@ -9050,7 +10191,12 @@
           <t>Kuwa ugu badan ee la weydiiyay</t>
         </is>
       </c>
-      <c r="H95" s="14" t="inlineStr"/>
+      <c r="H95" s="13" t="inlineStr">
+        <is>
+          <t>Yanayoulizwa Zaidi</t>
+        </is>
+      </c>
+      <c r="I95" s="14" t="inlineStr"/>
     </row>
     <row r="96" ht="44" customHeight="1">
       <c r="A96" s="11" t="inlineStr">
@@ -9088,7 +10234,12 @@
           <t>Waqtigan waxba lama weydiin.</t>
         </is>
       </c>
-      <c r="H96" s="14" t="inlineStr"/>
+      <c r="H96" s="13" t="inlineStr">
+        <is>
+          <t>Hakuna kilichoulizwa katika muda huu.</t>
+        </is>
+      </c>
+      <c r="I96" s="14" t="inlineStr"/>
     </row>
     <row r="97" ht="44" customHeight="1">
       <c r="A97" s="11" t="inlineStr">
@@ -9126,7 +10277,12 @@
           <t>Waxaa loo kala saaray erayada. Lambarrada taleefanka iyo magacyada waa la saaraa ka hor.</t>
         </is>
       </c>
-      <c r="H97" s="14" t="inlineStr"/>
+      <c r="H97" s="13" t="inlineStr">
+        <is>
+          <t>Yamepangwa kwa maneno. Namba za simu na majina yameondolewa kabla ya kupanga.</t>
+        </is>
+      </c>
+      <c r="I97" s="14" t="inlineStr"/>
     </row>
     <row r="98" ht="44" customHeight="1">
       <c r="A98" s="11" t="inlineStr">
@@ -9164,7 +10320,12 @@
           <t>Maxaa dhacay markii tan la weydiiyay</t>
         </is>
       </c>
-      <c r="H98" s="14" t="inlineStr"/>
+      <c r="H98" s="13" t="inlineStr">
+        <is>
+          <t>Kilichotokea liliposwali hili</t>
+        </is>
+      </c>
+      <c r="I98" s="14" t="inlineStr"/>
     </row>
     <row r="99" ht="44" customHeight="1">
       <c r="A99" s="11" t="inlineStr">
@@ -9202,7 +10363,12 @@
           <t>{n} su'aalood oo kale</t>
         </is>
       </c>
-      <c r="H99" s="14" t="inlineStr"/>
+      <c r="H99" s="13" t="inlineStr">
+        <is>
+          <t>Maswali mengine {n}</t>
+        </is>
+      </c>
+      <c r="I99" s="14" t="inlineStr"/>
     </row>
     <row r="100" ht="44" customHeight="1">
       <c r="A100" s="11" t="inlineStr">
@@ -9240,7 +10406,12 @@
           <t>Ka eeg Farqiyada Nuxurka</t>
         </is>
       </c>
-      <c r="H100" s="14" t="inlineStr"/>
+      <c r="H100" s="13" t="inlineStr">
+        <is>
+          <t>Angalia katika Mapungufu ya Maudhui</t>
+        </is>
+      </c>
+      <c r="I100" s="14" t="inlineStr"/>
     </row>
     <row r="101" ht="44" customHeight="1">
       <c r="A101" s="11" t="inlineStr">
@@ -9278,7 +10449,12 @@
           <t>Fiiri Wadahadalada</t>
         </is>
       </c>
-      <c r="H101" s="14" t="inlineStr"/>
+      <c r="H101" s="13" t="inlineStr">
+        <is>
+          <t>Angalia Mazungumzo</t>
+        </is>
+      </c>
+      <c r="I101" s="14" t="inlineStr"/>
     </row>
     <row r="102" ht="44" customHeight="1">
       <c r="A102" s="11" t="inlineStr">
@@ -9316,7 +10492,12 @@
           <t>Luqadaha</t>
         </is>
       </c>
-      <c r="H102" s="14" t="inlineStr"/>
+      <c r="H102" s="13" t="inlineStr">
+        <is>
+          <t>Lugha</t>
+        </is>
+      </c>
+      <c r="I102" s="14" t="inlineStr"/>
     </row>
     <row r="103" ht="44" customHeight="1">
       <c r="A103" s="11" t="inlineStr">
@@ -9354,7 +10535,12 @@
           <t>wadahadallo</t>
         </is>
       </c>
-      <c r="H103" s="14" t="inlineStr"/>
+      <c r="H103" s="13" t="inlineStr">
+        <is>
+          <t>mazungumzo</t>
+        </is>
+      </c>
+      <c r="I103" s="14" t="inlineStr"/>
     </row>
     <row r="104" ht="44" customHeight="1">
       <c r="A104" s="11" t="inlineStr">
@@ -9392,7 +10578,12 @@
           <t>su'aalaha</t>
         </is>
       </c>
-      <c r="H104" s="14" t="inlineStr"/>
+      <c r="H104" s="13" t="inlineStr">
+        <is>
+          <t>maswali</t>
+        </is>
+      </c>
+      <c r="I104" s="14" t="inlineStr"/>
     </row>
     <row r="105" ht="44" customHeight="1">
       <c r="A105" s="11" t="inlineStr">
@@ -9430,7 +10621,12 @@
           <t>Dhammaan {n} {unit} waxay ku jireen {label}.</t>
         </is>
       </c>
-      <c r="H105" s="14" t="inlineStr"/>
+      <c r="H105" s="13" t="inlineStr">
+        <is>
+          <t>{unit} zote {n} zilikuwa katika {label}.</t>
+        </is>
+      </c>
+      <c r="I105" s="14" t="inlineStr"/>
     </row>
     <row r="106" ht="44" customHeight="1">
       <c r="A106" s="11" t="inlineStr">
@@ -9468,7 +10664,12 @@
           <t>Wadahadallada luqadda</t>
         </is>
       </c>
-      <c r="H106" s="14" t="inlineStr"/>
+      <c r="H106" s="13" t="inlineStr">
+        <is>
+          <t>Mazungumzo kwa Lugha</t>
+        </is>
+      </c>
+      <c r="I106" s="14" t="inlineStr"/>
     </row>
     <row r="107" ht="44" customHeight="1">
       <c r="A107" s="11" t="inlineStr">
@@ -9506,7 +10707,12 @@
           <t>Waqtigan wadahadal ma jiro.</t>
         </is>
       </c>
-      <c r="H107" s="14" t="inlineStr"/>
+      <c r="H107" s="13" t="inlineStr">
+        <is>
+          <t>Hakuna mazungumzo bado katika muda huu.</t>
+        </is>
+      </c>
+      <c r="I107" s="14" t="inlineStr"/>
     </row>
     <row r="108" ht="44" customHeight="1">
       <c r="A108" s="11" t="inlineStr">
@@ -9544,7 +10750,12 @@
           <t>Dhaqdhaqaaqa dhawaan</t>
         </is>
       </c>
-      <c r="H108" s="14" t="inlineStr"/>
+      <c r="H108" s="13" t="inlineStr">
+        <is>
+          <t>Shughuli za Hivi Karibuni</t>
+        </is>
+      </c>
+      <c r="I108" s="14" t="inlineStr"/>
     </row>
     <row r="109" ht="44" customHeight="1">
       <c r="A109" s="11" t="inlineStr">
@@ -9582,7 +10793,12 @@
           <t>Muuqaal toos ah</t>
         </is>
       </c>
-      <c r="H109" s="14" t="inlineStr"/>
+      <c r="H109" s="13" t="inlineStr">
+        <is>
+          <t>Muhtasari wa Moja kwa Moja</t>
+        </is>
+      </c>
+      <c r="I109" s="14" t="inlineStr"/>
     </row>
     <row r="110" ht="44" customHeight="1">
       <c r="A110" s="11" t="inlineStr">
@@ -9620,7 +10836,12 @@
           <t>Muuqaalka kaaliyaha</t>
         </is>
       </c>
-      <c r="H110" s="14" t="inlineStr"/>
+      <c r="H110" s="13" t="inlineStr">
+        <is>
+          <t>Muhtasari wa Msaidizi</t>
+        </is>
+      </c>
+      <c r="I110" s="14" t="inlineStr"/>
     </row>
     <row r="111" ht="44" customHeight="1">
       <c r="A111" s="11" t="inlineStr">
@@ -9658,7 +10879,12 @@
           <t>Waa waxa uu macmiilku ku arko degelkaaga. Fariimaha halkan laga diro waa dhab, waxayna ka muuqdaan Wadahadallada.</t>
         </is>
       </c>
-      <c r="H111" s="14" t="inlineStr"/>
+      <c r="H111" s="13" t="inlineStr">
+        <is>
+          <t>Hasa kile mteja anachokiona kwenye tovuti yako. Ujumbe uliotumwa hapa ni halisi na unaonekana katika Mazungumzo.</t>
+        </is>
+      </c>
+      <c r="I111" s="14" t="inlineStr"/>
     </row>
     <row r="112" ht="44" customHeight="1">
       <c r="A112" s="11" t="inlineStr">
@@ -9696,7 +10922,12 @@
           <t>{n} wadahadal</t>
         </is>
       </c>
-      <c r="H112" s="14" t="inlineStr"/>
+      <c r="H112" s="13" t="inlineStr">
+        <is>
+          <t>Mazungumzo {n}</t>
+        </is>
+      </c>
+      <c r="I112" s="14" t="inlineStr"/>
     </row>
     <row r="113" ht="44" customHeight="1">
       <c r="A113" s="11" t="inlineStr">
@@ -9734,7 +10965,12 @@
           <t>{n} wadahadal</t>
         </is>
       </c>
-      <c r="H113" s="14" t="inlineStr"/>
+      <c r="H113" s="13" t="inlineStr">
+        <is>
+          <t>Mazungumzo {n}</t>
+        </is>
+      </c>
+      <c r="I113" s="14" t="inlineStr"/>
     </row>
     <row r="114" ht="44" customHeight="1">
       <c r="A114" s="11" t="inlineStr">
@@ -9772,7 +11008,12 @@
           <t>Laga jawaabay macluumaadkaaga</t>
         </is>
       </c>
-      <c r="H114" s="14" t="inlineStr"/>
+      <c r="H114" s="13" t="inlineStr">
+        <is>
+          <t>Imejibiwa Kutoka kwa Maudhui Yako</t>
+        </is>
+      </c>
+      <c r="I114" s="14" t="inlineStr"/>
     </row>
     <row r="115" ht="44" customHeight="1">
       <c r="A115" s="11" t="inlineStr">
@@ -9810,7 +11051,12 @@
           <t>Laga jawaabay aqoonta guud ee bangiga</t>
         </is>
       </c>
-      <c r="H115" s="14" t="inlineStr"/>
+      <c r="H115" s="13" t="inlineStr">
+        <is>
+          <t>Imejibiwa Kutoka kwa Maarifa ya Jumla ya Kibenki</t>
+        </is>
+      </c>
+      <c r="I115" s="14" t="inlineStr"/>
     </row>
     <row r="116" ht="44" customHeight="1">
       <c r="A116" s="11" t="inlineStr">
@@ -9848,7 +11094,12 @@
           <t>Lama jawaabi karin</t>
         </is>
       </c>
-      <c r="H116" s="14" t="inlineStr"/>
+      <c r="H116" s="13" t="inlineStr">
+        <is>
+          <t>Haikuweza Kujibiwa</t>
+        </is>
+      </c>
+      <c r="I116" s="14" t="inlineStr"/>
     </row>
     <row r="117" ht="44" customHeight="1">
       <c r="A117" s="11" t="inlineStr">
@@ -9886,7 +11137,12 @@
           <t>Cabasho</t>
         </is>
       </c>
-      <c r="H117" s="14" t="inlineStr"/>
+      <c r="H117" s="13" t="inlineStr">
+        <is>
+          <t>Malalamiko</t>
+        </is>
+      </c>
+      <c r="I117" s="14" t="inlineStr"/>
     </row>
     <row r="118" ht="44" customHeight="1">
       <c r="A118" s="11" t="inlineStr">
@@ -9924,7 +11180,12 @@
           <t>Dhibaato gelitaanka xisaabta</t>
         </is>
       </c>
-      <c r="H118" s="14" t="inlineStr"/>
+      <c r="H118" s="13" t="inlineStr">
+        <is>
+          <t>Tatizo la Ufikiaji wa Akaunti</t>
+        </is>
+      </c>
+      <c r="I118" s="14" t="inlineStr"/>
     </row>
     <row r="119" ht="44" customHeight="1">
       <c r="A119" s="11" t="inlineStr">
@@ -9962,7 +11223,12 @@
           <t>Lala barbardhigay bangi kale</t>
         </is>
       </c>
-      <c r="H119" s="14" t="inlineStr"/>
+      <c r="H119" s="13" t="inlineStr">
+        <is>
+          <t>Ililinganishwa na Benki Nyingine</t>
+        </is>
+      </c>
+      <c r="I119" s="14" t="inlineStr"/>
     </row>
     <row r="120" ht="44" customHeight="1">
       <c r="A120" s="11" t="inlineStr">
@@ -10000,7 +11266,12 @@
           <t>Salaan</t>
         </is>
       </c>
-      <c r="H120" s="14" t="inlineStr"/>
+      <c r="H120" s="13" t="inlineStr">
+        <is>
+          <t>Salamu</t>
+        </is>
+      </c>
+      <c r="I120" s="14" t="inlineStr"/>
     </row>
     <row r="121" ht="44" customHeight="1">
       <c r="A121" s="11" t="inlineStr">
@@ -10038,7 +11309,12 @@
           <t>Xogta xiriirka waa la diiwaangeliyay</t>
         </is>
       </c>
-      <c r="H121" s="14" t="inlineStr"/>
+      <c r="H121" s="13" t="inlineStr">
+        <is>
+          <t>Taarifa za Mawasiliano Zimehifadhiwa</t>
+        </is>
+      </c>
+      <c r="I121" s="14" t="inlineStr"/>
     </row>
     <row r="122" ht="44" customHeight="1">
       <c r="A122" s="11" t="inlineStr">
@@ -10076,7 +11352,12 @@
           <t>Qof ayaa la codsaday</t>
         </is>
       </c>
-      <c r="H122" s="14" t="inlineStr"/>
+      <c r="H122" s="13" t="inlineStr">
+        <is>
+          <t>Aliomba Mtu</t>
+        </is>
+      </c>
+      <c r="I122" s="14" t="inlineStr"/>
     </row>
     <row r="123" ht="44" customHeight="1">
       <c r="A123" s="11" t="inlineStr">
@@ -10114,7 +11395,12 @@
           <t>Cabasho</t>
         </is>
       </c>
-      <c r="H123" s="14" t="inlineStr"/>
+      <c r="H123" s="13" t="inlineStr">
+        <is>
+          <t>Malalamiko</t>
+        </is>
+      </c>
+      <c r="I123" s="14" t="inlineStr"/>
     </row>
     <row r="124" ht="44" customHeight="1">
       <c r="A124" s="11" t="inlineStr">
@@ -10152,7 +11438,12 @@
           <t>Qof ayaa la codsaday</t>
         </is>
       </c>
-      <c r="H124" s="14" t="inlineStr"/>
+      <c r="H124" s="13" t="inlineStr">
+        <is>
+          <t>Aliomba Mtu</t>
+        </is>
+      </c>
+      <c r="I124" s="14" t="inlineStr"/>
     </row>
     <row r="125" ht="44" customHeight="1">
       <c r="A125" s="11" t="inlineStr">
@@ -10190,7 +11481,12 @@
           <t>Macluumaadkaaga jawaab kuma jirto</t>
         </is>
       </c>
-      <c r="H125" s="14" t="inlineStr"/>
+      <c r="H125" s="13" t="inlineStr">
+        <is>
+          <t>Hakuna Jibu Katika Maudhui Yako</t>
+        </is>
+      </c>
+      <c r="I125" s="14" t="inlineStr"/>
     </row>
     <row r="126" ht="44" customHeight="1">
       <c r="A126" s="11" t="inlineStr">
@@ -10228,7 +11524,12 @@
           <t>Laga jawaabay aqoon guud</t>
         </is>
       </c>
-      <c r="H126" s="14" t="inlineStr"/>
+      <c r="H126" s="13" t="inlineStr">
+        <is>
+          <t>Imejibiwa Kutoka kwa Maarifa ya Jumla</t>
+        </is>
+      </c>
+      <c r="I126" s="14" t="inlineStr"/>
     </row>
     <row r="127" ht="44" customHeight="1">
       <c r="A127" s="11" t="inlineStr">
@@ -10266,7 +11567,12 @@
           <t>Astaanta</t>
         </is>
       </c>
-      <c r="H127" s="14" t="inlineStr"/>
+      <c r="H127" s="13" t="inlineStr">
+        <is>
+          <t>Alama ya Biashara</t>
+        </is>
+      </c>
+      <c r="I127" s="14" t="inlineStr"/>
     </row>
     <row r="128" ht="44" customHeight="1">
       <c r="A128" s="11" t="inlineStr">
@@ -10304,7 +11610,12 @@
           <t>Midabkaaga iyo astaantaada, oo laga isticmaalo daaqadan iyo widget-ka sheekada degelkaaga. Qiyamka la keydiyay isla markiiba way shaqeeyaan — geyn looma baahna.</t>
         </is>
       </c>
-      <c r="H128" s="14" t="inlineStr"/>
+      <c r="H128" s="13" t="inlineStr">
+        <is>
+          <t>Rangi na nembo yako, inayotumika kwenye paneli hii na kwenye kidirisha cha mazungumzo kwenye tovuti yako. Thamani zilizohifadhiwa zinatumika mara moja — bila kupeleka toleo jipya.</t>
+        </is>
+      </c>
+      <c r="I128" s="14" t="inlineStr"/>
     </row>
     <row r="129" ht="44" customHeight="1">
       <c r="A129" s="11" t="inlineStr">
@@ -10342,7 +11653,12 @@
           <t>Magaca astaanta</t>
         </is>
       </c>
-      <c r="H129" s="14" t="inlineStr"/>
+      <c r="H129" s="13" t="inlineStr">
+        <is>
+          <t>Jina la Alama</t>
+        </is>
+      </c>
+      <c r="I129" s="14" t="inlineStr"/>
     </row>
     <row r="130" ht="44" customHeight="1">
       <c r="A130" s="11" t="inlineStr">
@@ -10380,7 +11696,12 @@
           <t>Waxa dadku kugu yeeraan — tusaale "CBE". Waxay ka muuqataa madaxa sheekada, daaqadan iyo salaanta macaamiisha. Haddii aad banaan ka tagto waxaa la isticmaalayaa magacaaga diiwaangashan, {legal}, oo si kastaba lagu hayo warbixinnada la daabaco.</t>
         </is>
       </c>
-      <c r="H130" s="14" t="inlineStr"/>
+      <c r="H130" s="13" t="inlineStr">
+        <is>
+          <t>Jina ambalo watu wanakuita — kwa mfano "CBE". Linaonyeshwa kwenye kichwa cha mazungumzo, paneli hii na salamu kwa wateja. Acha wazi ili kutumia jina lako lililosajiliwa, {legal}, ambalo linabaki kutumika kwa ripoti zilizochapishwa.</t>
+        </is>
+      </c>
+      <c r="I130" s="14" t="inlineStr"/>
     </row>
     <row r="131" ht="44" customHeight="1">
       <c r="A131" s="11" t="inlineStr">
@@ -10418,7 +11739,12 @@
           <t>Midabka astaanta</t>
         </is>
       </c>
-      <c r="H131" s="14" t="inlineStr"/>
+      <c r="H131" s="13" t="inlineStr">
+        <is>
+          <t>Rangi ya Alama</t>
+        </is>
+      </c>
+      <c r="I131" s="14" t="inlineStr"/>
     </row>
     <row r="132" ht="44" customHeight="1">
       <c r="A132" s="11" t="inlineStr">
@@ -10456,7 +11782,12 @@
           <t>Ciwaanka astaanta (https)</t>
         </is>
       </c>
-      <c r="H132" s="14" t="inlineStr"/>
+      <c r="H132" s="13" t="inlineStr">
+        <is>
+          <t>Kiungo cha Nembo (https)</t>
+        </is>
+      </c>
+      <c r="I132" s="14" t="inlineStr"/>
     </row>
     <row r="133" ht="44" customHeight="1">
       <c r="A133" s="11" t="inlineStr">
@@ -10494,7 +11825,12 @@
           <t>Midabbada la soo bandhigay waa akhrinteenna degelkaaga guud, ma aha buuggaaga astaanta. Haddii ay khalad tahay, halkan ayaa lagu saxaa.</t>
         </is>
       </c>
-      <c r="H133" s="14" t="inlineStr"/>
+      <c r="H133" s="13" t="inlineStr">
+        <is>
+          <t>Rangi zilizowekwa awali ni uelewa wetu wa tovuti yako ya umma, si kitabu chako cha alama ya biashara. Ikiwa si sahihi, hapa ndipo pa kurekebisha.</t>
+        </is>
+      </c>
+      <c r="I133" s="14" t="inlineStr"/>
     </row>
     <row r="134" ht="44" customHeight="1">
       <c r="A134" s="11" t="inlineStr">
@@ -10532,7 +11868,12 @@
           <t>Keydi astaanta</t>
         </is>
       </c>
-      <c r="H134" s="14" t="inlineStr"/>
+      <c r="H134" s="13" t="inlineStr">
+        <is>
+          <t>Hifadhi Alama</t>
+        </is>
+      </c>
+      <c r="I134" s="14" t="inlineStr"/>
     </row>
     <row r="135" ht="44" customHeight="1">
       <c r="A135" s="11" t="inlineStr">
@@ -10570,7 +11911,12 @@
           <t>Astaanta waa la keydiyay</t>
         </is>
       </c>
-      <c r="H135" s="14" t="inlineStr"/>
+      <c r="H135" s="13" t="inlineStr">
+        <is>
+          <t>Alama Imehifadhiwa</t>
+        </is>
+      </c>
+      <c r="I135" s="14" t="inlineStr"/>
     </row>
     <row r="136" ht="44" customHeight="1">
       <c r="A136" s="11" t="inlineStr">
@@ -10608,7 +11954,12 @@
           <t>Webhook-ga gudbinta</t>
         </is>
       </c>
-      <c r="H136" s="14" t="inlineStr"/>
+      <c r="H136" s="13" t="inlineStr">
+        <is>
+          <t>Wavuti ya Masuala Yaliyoelekezwa</t>
+        </is>
+      </c>
+      <c r="I136" s="14" t="inlineStr"/>
     </row>
     <row r="137" ht="44" customHeight="1">
       <c r="A137" s="11" t="inlineStr">
@@ -10646,7 +11997,12 @@
           <t>Halka arrimaha lagu gudbiyo qalabkaaga xarunta macaamiisha. Codsiyada waa la saxeexay, sidaas darteed nidaamka qaataa wuu xaqiijin karaa inay naga yimaadeen. Si aad u gooyso, banaani meesha.</t>
         </is>
       </c>
-      <c r="H137" s="14" t="inlineStr"/>
+      <c r="H137" s="13" t="inlineStr">
+        <is>
+          <t>Mahali masuala yanapopelekwa kwenye zana yako ya kituo cha huduma kwa wateja. Maombi yamesainiwa, ili mfumo unaopokea uweze kuthibitisha yametoka kwetu. Futa sehemu hii ili kukatisha muunganisho.</t>
+        </is>
+      </c>
+      <c r="I137" s="14" t="inlineStr"/>
     </row>
     <row r="138" ht="44" customHeight="1">
       <c r="A138" s="11" t="inlineStr">
@@ -10684,7 +12040,12 @@
           <t>Sir saxeex ayaa la dejiyay. Mar kale lama tusi karo — URL halkan lagu keydiyo wuxuu soo saarayaa mid cusub, kii hore wuu shaqo joojiyaa.</t>
         </is>
       </c>
-      <c r="H138" s="14" t="inlineStr"/>
+      <c r="H138" s="13" t="inlineStr">
+        <is>
+          <t>Siri ya kusaini imewekwa. Haiwezi kuonyeshwa tena — kuhifadhi kiungo hapa kunatoa siri mpya na ile ya zamani inaacha kufanya kazi.</t>
+        </is>
+      </c>
+      <c r="I138" s="14" t="inlineStr"/>
     </row>
     <row r="139" ht="44" customHeight="1">
       <c r="A139" s="11" t="inlineStr">
@@ -10722,7 +12083,12 @@
           <t>Webhook waa la xiray</t>
         </is>
       </c>
-      <c r="H139" s="14" t="inlineStr"/>
+      <c r="H139" s="13" t="inlineStr">
+        <is>
+          <t>Wavuti Imeunganishwa</t>
+        </is>
+      </c>
+      <c r="I139" s="14" t="inlineStr"/>
     </row>
     <row r="140" ht="44" customHeight="1">
       <c r="A140" s="11" t="inlineStr">
@@ -10760,7 +12126,12 @@
           <t>Webhook waa la goynay</t>
         </is>
       </c>
-      <c r="H140" s="14" t="inlineStr"/>
+      <c r="H140" s="13" t="inlineStr">
+        <is>
+          <t>Wavuti Imekatishwa</t>
+        </is>
+      </c>
+      <c r="I140" s="14" t="inlineStr"/>
     </row>
     <row r="141" ht="44" customHeight="1">
       <c r="A141" s="11" t="inlineStr">
@@ -10798,7 +12169,12 @@
           <t>Furahaaga sirta ah</t>
         </is>
       </c>
-      <c r="H141" s="14" t="inlineStr"/>
+      <c r="H141" s="13" t="inlineStr">
+        <is>
+          <t>Nenosiri Lako</t>
+        </is>
+      </c>
+      <c r="I141" s="14" t="inlineStr"/>
     </row>
     <row r="142" ht="44" customHeight="1">
       <c r="A142" s="11" t="inlineStr">
@@ -10836,7 +12212,12 @@
           <t>Kan hadda</t>
         </is>
       </c>
-      <c r="H142" s="14" t="inlineStr"/>
+      <c r="H142" s="13" t="inlineStr">
+        <is>
+          <t>La Sasa</t>
+        </is>
+      </c>
+      <c r="I142" s="14" t="inlineStr"/>
     </row>
     <row r="143" ht="44" customHeight="1">
       <c r="A143" s="11" t="inlineStr">
@@ -10874,7 +12255,12 @@
           <t>Cusub (12+ xaraf)</t>
         </is>
       </c>
-      <c r="H143" s="14" t="inlineStr"/>
+      <c r="H143" s="13" t="inlineStr">
+        <is>
+          <t>Jipya (herufi 12+)</t>
+        </is>
+      </c>
+      <c r="I143" s="14" t="inlineStr"/>
     </row>
     <row r="144" ht="44" customHeight="1">
       <c r="A144" s="11" t="inlineStr">
@@ -10912,7 +12298,12 @@
           <t>Beddelkeedu wuxuu kaa saarayaa dhammaan browser-yada kale ee aad ku jirto.</t>
         </is>
       </c>
-      <c r="H144" s="14" t="inlineStr"/>
+      <c r="H144" s="13" t="inlineStr">
+        <is>
+          <t>Kulibadilisha kunamtoa kila kivinjari kingine ulichoingia.</t>
+        </is>
+      </c>
+      <c r="I144" s="14" t="inlineStr"/>
     </row>
     <row r="145" ht="44" customHeight="1">
       <c r="A145" s="11" t="inlineStr">
@@ -10950,7 +12341,12 @@
           <t>Bedel furaha sirta ah</t>
         </is>
       </c>
-      <c r="H145" s="14" t="inlineStr"/>
+      <c r="H145" s="13" t="inlineStr">
+        <is>
+          <t>Badilisha Nenosiri</t>
+        </is>
+      </c>
+      <c r="I145" s="14" t="inlineStr"/>
     </row>
     <row r="146" ht="44" customHeight="1">
       <c r="A146" s="11" t="inlineStr">
@@ -10988,7 +12384,12 @@
           <t>Furaha sirta ah waa la beddelay. Kalfadhiyada kale waa laga saaray.</t>
         </is>
       </c>
-      <c r="H146" s="14" t="inlineStr"/>
+      <c r="H146" s="13" t="inlineStr">
+        <is>
+          <t>Nenosiri Limebadilishwa. Vikao vingine vimetolewa.</t>
+        </is>
+      </c>
+      <c r="I146" s="14" t="inlineStr"/>
     </row>
     <row r="147" ht="44" customHeight="1">
       <c r="A147" s="11" t="inlineStr">
@@ -11026,7 +12427,12 @@
           <t>Ku dar qof</t>
         </is>
       </c>
-      <c r="H147" s="14" t="inlineStr"/>
+      <c r="H147" s="13" t="inlineStr">
+        <is>
+          <t>Ongeza Mtu</t>
+        </is>
+      </c>
+      <c r="I147" s="14" t="inlineStr"/>
     </row>
     <row r="148" ht="44" customHeight="1">
       <c r="A148" s="11" t="inlineStr">
@@ -11064,7 +12470,12 @@
           <t>{n} xisaabood</t>
         </is>
       </c>
-      <c r="H148" s="14" t="inlineStr"/>
+      <c r="H148" s="13" t="inlineStr">
+        <is>
+          <t>Akaunti {n}</t>
+        </is>
+      </c>
+      <c r="I148" s="14" t="inlineStr"/>
     </row>
     <row r="149" ht="44" customHeight="1">
       <c r="A149" s="11" t="inlineStr">
@@ -11102,7 +12513,12 @@
           <t>{n} xisaab</t>
         </is>
       </c>
-      <c r="H149" s="14" t="inlineStr"/>
+      <c r="H149" s="13" t="inlineStr">
+        <is>
+          <t>Akaunti {n}</t>
+        </is>
+      </c>
+      <c r="I149" s="14" t="inlineStr"/>
     </row>
     <row r="150" ht="44" customHeight="1">
       <c r="A150" s="11" t="inlineStr">
@@ -11140,7 +12556,12 @@
           <t>Qof</t>
         </is>
       </c>
-      <c r="H150" s="14" t="inlineStr"/>
+      <c r="H150" s="13" t="inlineStr">
+        <is>
+          <t>Mtu</t>
+        </is>
+      </c>
+      <c r="I150" s="14" t="inlineStr"/>
     </row>
     <row r="151" ht="44" customHeight="1">
       <c r="A151" s="11" t="inlineStr">
@@ -11178,7 +12599,12 @@
           <t>Doorka</t>
         </is>
       </c>
-      <c r="H151" s="14" t="inlineStr"/>
+      <c r="H151" s="13" t="inlineStr">
+        <is>
+          <t>Wadhifa</t>
+        </is>
+      </c>
+      <c r="I151" s="14" t="inlineStr"/>
     </row>
     <row r="152" ht="44" customHeight="1">
       <c r="A152" s="11" t="inlineStr">
@@ -11216,7 +12642,12 @@
           <t>Xaalada</t>
         </is>
       </c>
-      <c r="H152" s="14" t="inlineStr"/>
+      <c r="H152" s="13" t="inlineStr">
+        <is>
+          <t>Hali</t>
+        </is>
+      </c>
+      <c r="I152" s="14" t="inlineStr"/>
     </row>
     <row r="153" ht="44" customHeight="1">
       <c r="A153" s="11" t="inlineStr">
@@ -11254,7 +12685,12 @@
           <t>Markii ugu dambeysay ee la galay</t>
         </is>
       </c>
-      <c r="H153" s="14" t="inlineStr"/>
+      <c r="H153" s="13" t="inlineStr">
+        <is>
+          <t>Aliingia Mwisho</t>
+        </is>
+      </c>
+      <c r="I153" s="14" t="inlineStr"/>
     </row>
     <row r="154" ht="44" customHeight="1">
       <c r="A154" s="11" t="inlineStr">
@@ -11292,7 +12728,12 @@
           <t>Ficillo</t>
         </is>
       </c>
-      <c r="H154" s="14" t="inlineStr"/>
+      <c r="H154" s="13" t="inlineStr">
+        <is>
+          <t>Vitendo</t>
+        </is>
+      </c>
+      <c r="I154" s="14" t="inlineStr"/>
     </row>
     <row r="155" ht="44" customHeight="1">
       <c r="A155" s="11" t="inlineStr">
@@ -11330,7 +12771,12 @@
           <t>kaasi waa adiga</t>
         </is>
       </c>
-      <c r="H155" s="14" t="inlineStr"/>
+      <c r="H155" s="13" t="inlineStr">
+        <is>
+          <t>huyo ni wewe</t>
+        </is>
+      </c>
+      <c r="I155" s="14" t="inlineStr"/>
     </row>
     <row r="156" ht="44" customHeight="1">
       <c r="A156" s="11" t="inlineStr">
@@ -11368,7 +12814,12 @@
           <t>Firfircoon</t>
         </is>
       </c>
-      <c r="H156" s="14" t="inlineStr"/>
+      <c r="H156" s="13" t="inlineStr">
+        <is>
+          <t>Hai</t>
+        </is>
+      </c>
+      <c r="I156" s="14" t="inlineStr"/>
     </row>
     <row r="157" ht="44" customHeight="1">
       <c r="A157" s="11" t="inlineStr">
@@ -11406,7 +12857,12 @@
           <t>La demiyay</t>
         </is>
       </c>
-      <c r="H157" s="14" t="inlineStr"/>
+      <c r="H157" s="13" t="inlineStr">
+        <is>
+          <t>Imezimwa</t>
+        </is>
+      </c>
+      <c r="I157" s="14" t="inlineStr"/>
     </row>
     <row r="158" ht="44" customHeight="1">
       <c r="A158" s="11" t="inlineStr">
@@ -11444,7 +12900,12 @@
           <t>waligeed</t>
         </is>
       </c>
-      <c r="H158" s="14" t="inlineStr"/>
+      <c r="H158" s="13" t="inlineStr">
+        <is>
+          <t>kamwe</t>
+        </is>
+      </c>
+      <c r="I158" s="14" t="inlineStr"/>
     </row>
     <row r="159" ht="44" customHeight="1">
       <c r="A159" s="11" t="inlineStr">
@@ -11482,7 +12943,12 @@
           <t>Demi</t>
         </is>
       </c>
-      <c r="H159" s="14" t="inlineStr"/>
+      <c r="H159" s="13" t="inlineStr">
+        <is>
+          <t>Zima</t>
+        </is>
+      </c>
+      <c r="I159" s="14" t="inlineStr"/>
     </row>
     <row r="160" ht="44" customHeight="1">
       <c r="A160" s="11" t="inlineStr">
@@ -11520,7 +12986,12 @@
           <t>Soo celi</t>
         </is>
       </c>
-      <c r="H160" s="14" t="inlineStr"/>
+      <c r="H160" s="13" t="inlineStr">
+        <is>
+          <t>Rejesha</t>
+        </is>
+      </c>
+      <c r="I160" s="14" t="inlineStr"/>
     </row>
     <row r="161" ht="44" customHeight="1">
       <c r="A161" s="11" t="inlineStr">
@@ -11558,7 +13029,12 @@
           <t>Waxa doorkiiba uu samayn karo</t>
         </is>
       </c>
-      <c r="H161" s="14" t="inlineStr"/>
+      <c r="H161" s="13" t="inlineStr">
+        <is>
+          <t>Kila Wadhifa Unaweza Kufanya Nini</t>
+        </is>
+      </c>
+      <c r="I161" s="14" t="inlineStr"/>
     </row>
     <row r="162" ht="44" customHeight="1">
       <c r="A162" s="11" t="inlineStr">
@@ -11596,7 +13072,12 @@
           <t>Wicitaanka teller kasta</t>
         </is>
       </c>
-      <c r="H162" s="14" t="inlineStr"/>
+      <c r="H162" s="13" t="inlineStr">
+        <is>
+          <t>Simu kwa Kila Afisa</t>
+        </is>
+      </c>
+      <c r="I162" s="14" t="inlineStr"/>
     </row>
     <row r="163" ht="44" customHeight="1">
       <c r="A163" s="11" t="inlineStr">
@@ -11634,7 +13115,12 @@
           <t>wicitaanno</t>
         </is>
       </c>
-      <c r="H163" s="14" t="inlineStr"/>
+      <c r="H163" s="13" t="inlineStr">
+        <is>
+          <t>simu</t>
+        </is>
+      </c>
+      <c r="I163" s="14" t="inlineStr"/>
     </row>
     <row r="164" ht="44" customHeight="1">
       <c r="A164" s="11" t="inlineStr">
@@ -11672,7 +13158,12 @@
           <t>wicitaan</t>
         </is>
       </c>
-      <c r="H164" s="14" t="inlineStr"/>
+      <c r="H164" s="13" t="inlineStr">
+        <is>
+          <t>simu</t>
+        </is>
+      </c>
+      <c r="I164" s="14" t="inlineStr"/>
     </row>
     <row r="165" ht="44" customHeight="1">
       <c r="A165" s="11" t="inlineStr">
@@ -11710,7 +13201,12 @@
           <t>Cidina ma qaadan wicitaan waqtigan.</t>
         </is>
       </c>
-      <c r="H165" s="14" t="inlineStr"/>
+      <c r="H165" s="13" t="inlineStr">
+        <is>
+          <t>Hakuna aliyepokea simu bado katika muda huu.</t>
+        </is>
+      </c>
+      <c r="I165" s="14" t="inlineStr"/>
     </row>
     <row r="166" ht="44" customHeight="1">
       <c r="A166" s="11" t="inlineStr">
@@ -11748,7 +13244,12 @@
           <t>La xaliyay</t>
         </is>
       </c>
-      <c r="H166" s="14" t="inlineStr"/>
+      <c r="H166" s="13" t="inlineStr">
+        <is>
+          <t>Imetatuliwa</t>
+        </is>
+      </c>
+      <c r="I166" s="14" t="inlineStr"/>
     </row>
     <row r="167" ht="44" customHeight="1">
       <c r="A167" s="11" t="inlineStr">
@@ -11786,7 +13287,12 @@
           <t>Wuu jabay (dhibaato farsamo)</t>
         </is>
       </c>
-      <c r="H167" s="14" t="inlineStr"/>
+      <c r="H167" s="13" t="inlineStr">
+        <is>
+          <t>Imekatika (tatizo la kiufundi)</t>
+        </is>
+      </c>
+      <c r="I167" s="14" t="inlineStr"/>
     </row>
     <row r="168" ht="44" customHeight="1">
       <c r="A168" s="11" t="inlineStr">
@@ -11824,7 +13330,12 @@
           <t>Celceliska sugitaanka ka hor jawaabta:</t>
         </is>
       </c>
-      <c r="H168" s="14" t="inlineStr"/>
+      <c r="H168" s="13" t="inlineStr">
+        <is>
+          <t>Wastani wa kusubiri kabla ya kujibu:</t>
+        </is>
+      </c>
+      <c r="I168" s="14" t="inlineStr"/>
     </row>
     <row r="169" ht="44" customHeight="1">
       <c r="A169" s="11" t="inlineStr">
@@ -11862,7 +13373,12 @@
           <t>Wicitaan lama helin waqtigan.</t>
         </is>
       </c>
-      <c r="H169" s="14" t="inlineStr"/>
+      <c r="H169" s="13" t="inlineStr">
+        <is>
+          <t>Hakuna simu bado katika muda huu.</t>
+        </is>
+      </c>
+      <c r="I169" s="14" t="inlineStr"/>
     </row>
     <row r="170" ht="44" customHeight="1">
       <c r="A170" s="11" t="inlineStr">
@@ -11900,7 +13416,12 @@
           <t>Waxqabadkaaga</t>
         </is>
       </c>
-      <c r="H170" s="14" t="inlineStr"/>
+      <c r="H170" s="13" t="inlineStr">
+        <is>
+          <t>Utendaji Wako</t>
+        </is>
+      </c>
+      <c r="I170" s="14" t="inlineStr"/>
     </row>
     <row r="171" ht="44" customHeight="1">
       <c r="A171" s="11" t="inlineStr">
@@ -11938,7 +13459,12 @@
           <t>{n} teller oo kale</t>
         </is>
       </c>
-      <c r="H171" s="14" t="inlineStr"/>
+      <c r="H171" s="13" t="inlineStr">
+        <is>
+          <t>Maafisa wengine {n}</t>
+        </is>
+      </c>
+      <c r="I171" s="14" t="inlineStr"/>
     </row>
     <row r="172" ht="44" customHeight="1">
       <c r="A172" s="11" t="inlineStr">
@@ -11976,7 +13502,12 @@
           <t>ku dhex jira</t>
         </is>
       </c>
-      <c r="H172" s="14" t="inlineStr"/>
+      <c r="H172" s="13" t="inlineStr">
+        <is>
+          <t>iliyojengwa ndani</t>
+        </is>
+      </c>
+      <c r="I172" s="14" t="inlineStr"/>
     </row>
     <row r="173" ht="44" customHeight="1">
       <c r="A173" s="11" t="inlineStr">
@@ -12014,7 +13545,12 @@
           <t>Qof ku dar</t>
         </is>
       </c>
-      <c r="H173" s="14" t="inlineStr"/>
+      <c r="H173" s="13" t="inlineStr">
+        <is>
+          <t>Ongeza Mtu</t>
+        </is>
+      </c>
+      <c r="I173" s="14" t="inlineStr"/>
     </row>
     <row r="174" ht="44" customHeight="1">
       <c r="A174" s="11" t="inlineStr">
@@ -12052,7 +13588,12 @@
           <t>Iimayl</t>
         </is>
       </c>
-      <c r="H174" s="14" t="inlineStr"/>
+      <c r="H174" s="13" t="inlineStr">
+        <is>
+          <t>Barua Pepe</t>
+        </is>
+      </c>
+      <c r="I174" s="14" t="inlineStr"/>
     </row>
     <row r="175" ht="44" customHeight="1">
       <c r="A175" s="11" t="inlineStr">
@@ -12090,7 +13631,12 @@
           <t>Magac (ikhtiyaari)</t>
         </is>
       </c>
-      <c r="H175" s="14" t="inlineStr"/>
+      <c r="H175" s="13" t="inlineStr">
+        <is>
+          <t>Jina (si lazima)</t>
+        </is>
+      </c>
+      <c r="I175" s="14" t="inlineStr"/>
     </row>
     <row r="176" ht="44" customHeight="1">
       <c r="A176" s="11" t="inlineStr">
@@ -12128,7 +13674,12 @@
           <t>Fure ku meel gaar ah</t>
         </is>
       </c>
-      <c r="H176" s="14" t="inlineStr"/>
+      <c r="H176" s="13" t="inlineStr">
+        <is>
+          <t>Nenosiri la Muda</t>
+        </is>
+      </c>
+      <c r="I176" s="14" t="inlineStr"/>
     </row>
     <row r="177" ht="44" customHeight="1">
       <c r="A177" s="11" t="inlineStr">
@@ -12166,7 +13717,12 @@
           <t>Ugu yaraan 12 xaraf. Ilaa iimaylada casumaadda la dejiyo, furahan si toos ah ayaa loo siin doonaa — sidaas darteed halkan ayuu ka muuqdaa halkii la qarin lahaa.</t>
         </is>
       </c>
-      <c r="H177" s="14" t="inlineStr"/>
+      <c r="H177" s="13" t="inlineStr">
+        <is>
+          <t>Angalau herufi 12. Hadi barua pepe za mialiko zitakapowekwa, nenosiri hili linapaswa kupewa moja kwa moja — ndiyo maana linaonyeshwa hapa badala ya kufichwa.</t>
+        </is>
+      </c>
+      <c r="I177" s="14" t="inlineStr"/>
     </row>
     <row r="178" ht="44" customHeight="1">
       <c r="A178" s="11" t="inlineStr">
@@ -12204,7 +13760,12 @@
           <t>Abuur</t>
         </is>
       </c>
-      <c r="H178" s="14" t="inlineStr"/>
+      <c r="H178" s="13" t="inlineStr">
+        <is>
+          <t>Unda</t>
+        </is>
+      </c>
+      <c r="I178" s="14" t="inlineStr"/>
     </row>
     <row r="179" ht="44" customHeight="1">
       <c r="A179" s="11" t="inlineStr">
@@ -12242,7 +13803,12 @@
           <t>Xisaab waa la abuuray</t>
         </is>
       </c>
-      <c r="H179" s="14" t="inlineStr"/>
+      <c r="H179" s="13" t="inlineStr">
+        <is>
+          <t>Akaunti Imeundwa</t>
+        </is>
+      </c>
+      <c r="I179" s="14" t="inlineStr"/>
     </row>
     <row r="180" ht="44" customHeight="1">
       <c r="A180" s="11" t="inlineStr">
@@ -12280,7 +13846,12 @@
           <t>Xisaabta waa la soo celiyay</t>
         </is>
       </c>
-      <c r="H180" s="14" t="inlineStr"/>
+      <c r="H180" s="13" t="inlineStr">
+        <is>
+          <t>Akaunti Imerejeshwa</t>
+        </is>
+      </c>
+      <c r="I180" s="14" t="inlineStr"/>
     </row>
     <row r="181" ht="44" customHeight="1">
       <c r="A181" s="11" t="inlineStr">
@@ -12318,7 +13889,12 @@
           <t>Xisaabta waa la demiyay, {n} kalfadhi ayaa dhammaaday</t>
         </is>
       </c>
-      <c r="H181" s="14" t="inlineStr"/>
+      <c r="H181" s="13" t="inlineStr">
+        <is>
+          <t>Akaunti imezimwa, vikao {n} vimemalizika</t>
+        </is>
+      </c>
+      <c r="I181" s="14" t="inlineStr"/>
     </row>
     <row r="182" ht="44" customHeight="1">
       <c r="A182" s="11" t="inlineStr">
@@ -12356,7 +13932,12 @@
           <t>Xisaabtan ma demineysaa? Isla markiiba waa laga saarayaa.</t>
         </is>
       </c>
-      <c r="H182" s="14" t="inlineStr"/>
+      <c r="H182" s="13" t="inlineStr">
+        <is>
+          <t>Zima akaunti hii? Watatolewa mara moja.</t>
+        </is>
+      </c>
+      <c r="I182" s="14" t="inlineStr"/>
     </row>
     <row r="183" ht="44" customHeight="1">
       <c r="A183" s="11" t="inlineStr">
@@ -12394,7 +13975,12 @@
           <t>maqaal ku daray</t>
         </is>
       </c>
-      <c r="H183" s="14" t="inlineStr"/>
+      <c r="H183" s="13" t="inlineStr">
+        <is>
+          <t>aliongeza makala</t>
+        </is>
+      </c>
+      <c r="I183" s="14" t="inlineStr"/>
     </row>
     <row r="184" ht="44" customHeight="1">
       <c r="A184" s="11" t="inlineStr">
@@ -12432,7 +14018,12 @@
           <t>maqaal wax ka beddelay</t>
         </is>
       </c>
-      <c r="H184" s="14" t="inlineStr"/>
+      <c r="H184" s="13" t="inlineStr">
+        <is>
+          <t>alihariri makala</t>
+        </is>
+      </c>
+      <c r="I184" s="14" t="inlineStr"/>
     </row>
     <row r="185" ht="44" customHeight="1">
       <c r="A185" s="11" t="inlineStr">
@@ -12470,7 +14061,12 @@
           <t>maqaal tirtiray</t>
         </is>
       </c>
-      <c r="H185" s="14" t="inlineStr"/>
+      <c r="H185" s="13" t="inlineStr">
+        <is>
+          <t>alifuta makala</t>
+        </is>
+      </c>
+      <c r="I185" s="14" t="inlineStr"/>
     </row>
     <row r="186" ht="44" customHeight="1">
       <c r="A186" s="11" t="inlineStr">
@@ -12508,7 +14104,12 @@
           <t>maqaallo soo dhoofiyay</t>
         </is>
       </c>
-      <c r="H186" s="14" t="inlineStr"/>
+      <c r="H186" s="13" t="inlineStr">
+        <is>
+          <t>aliagiza makala</t>
+        </is>
+      </c>
+      <c r="I186" s="14" t="inlineStr"/>
     </row>
     <row r="187" ht="44" customHeight="1">
       <c r="A187" s="11" t="inlineStr">
@@ -12546,7 +14147,12 @@
           <t>arrin xiray</t>
         </is>
       </c>
-      <c r="H187" s="14" t="inlineStr"/>
+      <c r="H187" s="13" t="inlineStr">
+        <is>
+          <t>alifunga suala</t>
+        </is>
+      </c>
+      <c r="I187" s="14" t="inlineStr"/>
     </row>
     <row r="188" ht="44" customHeight="1">
       <c r="A188" s="11" t="inlineStr">
@@ -12584,7 +14190,12 @@
           <t>arrin dib u furay</t>
         </is>
       </c>
-      <c r="H188" s="14" t="inlineStr"/>
+      <c r="H188" s="13" t="inlineStr">
+        <is>
+          <t>alifungua tena suala</t>
+        </is>
+      </c>
+      <c r="I188" s="14" t="inlineStr"/>
     </row>
     <row r="189" ht="44" customHeight="1">
       <c r="A189" s="11" t="inlineStr">
@@ -12622,7 +14233,12 @@
           <t>ku xiray webhook-ga gudbinta</t>
         </is>
       </c>
-      <c r="H189" s="14" t="inlineStr"/>
+      <c r="H189" s="13" t="inlineStr">
+        <is>
+          <t>aliunganisha wavuti ya masuala</t>
+        </is>
+      </c>
+      <c r="I189" s="14" t="inlineStr"/>
     </row>
     <row r="190" ht="44" customHeight="1">
       <c r="A190" s="11" t="inlineStr">
@@ -12660,7 +14276,12 @@
           <t>goynay webhook-ga gudbinta</t>
         </is>
       </c>
-      <c r="H190" s="14" t="inlineStr"/>
+      <c r="H190" s="13" t="inlineStr">
+        <is>
+          <t>alikatisha wavuti ya masuala</t>
+        </is>
+      </c>
+      <c r="I190" s="14" t="inlineStr"/>
     </row>
     <row r="191" ht="44" customHeight="1">
       <c r="A191" s="11" t="inlineStr">
@@ -12698,7 +14319,12 @@
           <t>Telegram ku xiray</t>
         </is>
       </c>
-      <c r="H191" s="14" t="inlineStr"/>
+      <c r="H191" s="13" t="inlineStr">
+        <is>
+          <t>aliunganisha Telegram</t>
+        </is>
+      </c>
+      <c r="I191" s="14" t="inlineStr"/>
     </row>
     <row r="192" ht="44" customHeight="1">
       <c r="A192" s="11" t="inlineStr">
@@ -12736,7 +14362,12 @@
           <t>shaqaale ku daray</t>
         </is>
       </c>
-      <c r="H192" s="14" t="inlineStr"/>
+      <c r="H192" s="13" t="inlineStr">
+        <is>
+          <t>aliongeza mwenzake</t>
+        </is>
+      </c>
+      <c r="I192" s="14" t="inlineStr"/>
     </row>
     <row r="193" ht="44" customHeight="1">
       <c r="A193" s="11" t="inlineStr">
@@ -12774,7 +14405,12 @@
           <t>xisaab demiyay</t>
         </is>
       </c>
-      <c r="H193" s="14" t="inlineStr"/>
+      <c r="H193" s="13" t="inlineStr">
+        <is>
+          <t>alizima akaunti</t>
+        </is>
+      </c>
+      <c r="I193" s="14" t="inlineStr"/>
     </row>
     <row r="194" ht="44" customHeight="1">
       <c r="A194" s="11" t="inlineStr">
@@ -12812,7 +14448,12 @@
           <t>xisaab soo celiyay</t>
         </is>
       </c>
-      <c r="H194" s="14" t="inlineStr"/>
+      <c r="H194" s="13" t="inlineStr">
+        <is>
+          <t>alirejesha akaunti</t>
+        </is>
+      </c>
+      <c r="I194" s="14" t="inlineStr"/>
     </row>
     <row r="195" ht="44" customHeight="1">
       <c r="A195" s="11" t="inlineStr">
@@ -12850,7 +14491,12 @@
           <t>gashay</t>
         </is>
       </c>
-      <c r="H195" s="14" t="inlineStr"/>
+      <c r="H195" s="13" t="inlineStr">
+        <is>
+          <t>aliingia</t>
+        </is>
+      </c>
+      <c r="I195" s="14" t="inlineStr"/>
     </row>
     <row r="196" ht="44" customHeight="1">
       <c r="A196" s="11" t="inlineStr">
@@ -12888,7 +14534,12 @@
           <t>beddelay furihiisa</t>
         </is>
       </c>
-      <c r="H196" s="14" t="inlineStr"/>
+      <c r="H196" s="13" t="inlineStr">
+        <is>
+          <t>alibadilisha nenosiri lake</t>
+        </is>
+      </c>
+      <c r="I196" s="14" t="inlineStr"/>
     </row>
     <row r="197" ht="44" customHeight="1">
       <c r="A197" s="11" t="inlineStr">
@@ -12926,7 +14577,12 @@
           <t>Weli waxba ma jiraan.</t>
         </is>
       </c>
-      <c r="H197" s="14" t="inlineStr"/>
+      <c r="H197" s="13" t="inlineStr">
+        <is>
+          <t>Bado hakuna.</t>
+        </is>
+      </c>
+      <c r="I197" s="14" t="inlineStr"/>
     </row>
     <row r="198" ht="44" customHeight="1">
       <c r="A198" s="11" t="inlineStr">
@@ -12964,7 +14620,12 @@
           <t>Lama heli karo.</t>
         </is>
       </c>
-      <c r="H198" s="14" t="inlineStr"/>
+      <c r="H198" s="13" t="inlineStr">
+        <is>
+          <t>Haipatikani.</t>
+        </is>
+      </c>
+      <c r="I198" s="14" t="inlineStr"/>
     </row>
     <row r="199" ht="44" customHeight="1">
       <c r="A199" s="11" t="inlineStr">
@@ -13002,7 +14663,12 @@
           <t>hadda</t>
         </is>
       </c>
-      <c r="H199" s="14" t="inlineStr"/>
+      <c r="H199" s="13" t="inlineStr">
+        <is>
+          <t>sasa hivi</t>
+        </is>
+      </c>
+      <c r="I199" s="14" t="inlineStr"/>
     </row>
     <row r="200" ht="44" customHeight="1">
       <c r="A200" s="11" t="inlineStr">
@@ -13040,7 +14706,12 @@
           <t>{n} daqiiqo ka hor</t>
         </is>
       </c>
-      <c r="H200" s="14" t="inlineStr"/>
+      <c r="H200" s="13" t="inlineStr">
+        <is>
+          <t>dakika {n} zilizopita</t>
+        </is>
+      </c>
+      <c r="I200" s="14" t="inlineStr"/>
     </row>
     <row r="201" ht="44" customHeight="1">
       <c r="A201" s="11" t="inlineStr">
@@ -13078,7 +14749,12 @@
           <t>{n} saac ka hor</t>
         </is>
       </c>
-      <c r="H201" s="14" t="inlineStr"/>
+      <c r="H201" s="13" t="inlineStr">
+        <is>
+          <t>saa {n} zilizopita</t>
+        </is>
+      </c>
+      <c r="I201" s="14" t="inlineStr"/>
     </row>
     <row r="202" ht="44" customHeight="1">
       <c r="A202" s="11" t="inlineStr">
@@ -13116,7 +14792,12 @@
           <t>{n} maalmood ka hor</t>
         </is>
       </c>
-      <c r="H202" s="14" t="inlineStr"/>
+      <c r="H202" s="13" t="inlineStr">
+        <is>
+          <t>siku {n} zilizopita</t>
+        </is>
+      </c>
+      <c r="I202" s="14" t="inlineStr"/>
     </row>
     <row r="203" ht="44" customHeight="1">
       <c r="A203" s="11" t="inlineStr">
@@ -13154,7 +14835,12 @@
           <t>Dhammaan {n} wadahadal waxay ka yimaadeen {label}.</t>
         </is>
       </c>
-      <c r="H203" s="14" t="inlineStr"/>
+      <c r="H203" s="13" t="inlineStr">
+        <is>
+          <t>Mazungumzo yote {n} yalitoka {label}.</t>
+        </is>
+      </c>
+      <c r="I203" s="14" t="inlineStr"/>
     </row>
     <row r="204" ht="44" customHeight="1">
       <c r="A204" s="11" t="inlineStr">
@@ -13192,7 +14878,12 @@
           <t>Shaqeynaya</t>
         </is>
       </c>
-      <c r="H204" s="14" t="inlineStr"/>
+      <c r="H204" s="13" t="inlineStr">
+        <is>
+          <t>Moja kwa Moja</t>
+        </is>
+      </c>
+      <c r="I204" s="14" t="inlineStr"/>
     </row>
     <row r="205" ht="44" customHeight="1">
       <c r="A205" s="11" t="inlineStr">
@@ -13230,7 +14921,12 @@
           <t>Diyaar u ah xiriirka</t>
         </is>
       </c>
-      <c r="H205" s="14" t="inlineStr"/>
+      <c r="H205" s="13" t="inlineStr">
+        <is>
+          <t>Tayari Kuunganishwa</t>
+        </is>
+      </c>
+      <c r="I205" s="14" t="inlineStr"/>
     </row>
     <row r="206" ht="44" customHeight="1">
       <c r="A206" s="11" t="inlineStr">
@@ -13268,7 +14964,12 @@
           <t>Waxay u baahan tahay dejin</t>
         </is>
       </c>
-      <c r="H206" s="14" t="inlineStr"/>
+      <c r="H206" s="13" t="inlineStr">
+        <is>
+          <t>Inahitaji Kusanidiwa</t>
+        </is>
+      </c>
+      <c r="I206" s="14" t="inlineStr"/>
     </row>
     <row r="207" ht="44" customHeight="1">
       <c r="A207" s="11" t="inlineStr">
@@ -13306,7 +15007,12 @@
           <t>Qaybta wadahadallada kanaalka</t>
         </is>
       </c>
-      <c r="H207" s="14" t="inlineStr"/>
+      <c r="H207" s="13" t="inlineStr">
+        <is>
+          <t>Mgawanyo wa Mazungumzo kwa Njia</t>
+        </is>
+      </c>
+      <c r="I207" s="14" t="inlineStr"/>
     </row>
     <row r="208" ht="44" customHeight="1">
       <c r="A208" s="11" t="inlineStr">
@@ -13344,7 +15050,12 @@
           <t>La cusbooneysiiyay</t>
         </is>
       </c>
-      <c r="H208" s="14" t="inlineStr"/>
+      <c r="H208" s="13" t="inlineStr">
+        <is>
+          <t>Ni ya Hivi Karibuni</t>
+        </is>
+      </c>
+      <c r="I208" s="14" t="inlineStr"/>
     </row>
     <row r="209" ht="44" customHeight="1">
       <c r="A209" s="11" t="inlineStr">
@@ -13382,7 +15093,12 @@
           <t>La cusbooneysiiyay {n}daq ka hor</t>
         </is>
       </c>
-      <c r="H209" s="14" t="inlineStr"/>
+      <c r="H209" s="13" t="inlineStr">
+        <is>
+          <t>Imesasishwa dakika {n} zilizopita</t>
+        </is>
+      </c>
+      <c r="I209" s="14" t="inlineStr"/>
     </row>
     <row r="210" ht="44" customHeight="1">
       <c r="A210" s="11" t="inlineStr">
@@ -13420,7 +15136,12 @@
           <t>La cusbooneysiiyay {n}saac ka hor</t>
         </is>
       </c>
-      <c r="H210" s="14" t="inlineStr"/>
+      <c r="H210" s="13" t="inlineStr">
+        <is>
+          <t>Imesasishwa saa {n} zilizopita</t>
+        </is>
+      </c>
+      <c r="I210" s="14" t="inlineStr"/>
     </row>
     <row r="211" ht="44" customHeight="1">
       <c r="A211" s="11" t="inlineStr">
@@ -13458,7 +15179,12 @@
           <t>Safka</t>
         </is>
       </c>
-      <c r="H211" s="14" t="inlineStr"/>
+      <c r="H211" s="13" t="inlineStr">
+        <is>
+          <t>Foleni</t>
+        </is>
+      </c>
+      <c r="I211" s="14" t="inlineStr"/>
     </row>
     <row r="212" ht="44" customHeight="1">
       <c r="A212" s="11" t="inlineStr">
@@ -13496,7 +15222,12 @@
           <t>Yaree</t>
         </is>
       </c>
-      <c r="H212" s="14" t="inlineStr"/>
+      <c r="H212" s="13" t="inlineStr">
+        <is>
+          <t>Kunja</t>
+        </is>
+      </c>
+      <c r="I212" s="14" t="inlineStr"/>
     </row>
     <row r="213" ht="44" customHeight="1">
       <c r="A213" s="11" t="inlineStr">
@@ -13534,7 +15265,12 @@
           <t>Balaadhi</t>
         </is>
       </c>
-      <c r="H213" s="14" t="inlineStr"/>
+      <c r="H213" s="13" t="inlineStr">
+        <is>
+          <t>Panua</t>
+        </is>
+      </c>
+      <c r="I213" s="14" t="inlineStr"/>
     </row>
     <row r="214" ht="44" customHeight="1">
       <c r="A214" s="11" t="inlineStr">
@@ -13572,7 +15308,12 @@
           <t>Yaree ama balaadhi dhinaca</t>
         </is>
       </c>
-      <c r="H214" s="14" t="inlineStr"/>
+      <c r="H214" s="13" t="inlineStr">
+        <is>
+          <t>Kunja au panua upande wa kando</t>
+        </is>
+      </c>
+      <c r="I214" s="14" t="inlineStr"/>
     </row>
     <row r="215" ht="44" customHeight="1">
       <c r="A215" s="11" t="inlineStr">
@@ -13610,7 +15351,12 @@
           <t>Muuji ama qari liiska kanaalada</t>
         </is>
       </c>
-      <c r="H215" s="14" t="inlineStr"/>
+      <c r="H215" s="13" t="inlineStr">
+        <is>
+          <t>Onyesha au ficha orodha ya njia</t>
+        </is>
+      </c>
+      <c r="I215" s="14" t="inlineStr"/>
     </row>
     <row r="216" ht="44" customHeight="1">
       <c r="A216" s="11" t="inlineStr">
@@ -13648,7 +15394,12 @@
           <t>Maanta</t>
         </is>
       </c>
-      <c r="H216" s="14" t="inlineStr"/>
+      <c r="H216" s="13" t="inlineStr">
+        <is>
+          <t>Leo</t>
+        </is>
+      </c>
+      <c r="I216" s="14" t="inlineStr"/>
     </row>
     <row r="217" ht="44" customHeight="1">
       <c r="A217" s="11" t="inlineStr">
@@ -13686,7 +15437,12 @@
           <t>Shalay</t>
         </is>
       </c>
-      <c r="H217" s="14" t="inlineStr"/>
+      <c r="H217" s="13" t="inlineStr">
+        <is>
+          <t>Jana</t>
+        </is>
+      </c>
+      <c r="I217" s="14" t="inlineStr"/>
     </row>
     <row r="218" ht="44" customHeight="1">
       <c r="A218" s="11" t="inlineStr">
@@ -13724,7 +15480,12 @@
           <t>Macmiilku halkan ayuu qof weydiistay</t>
         </is>
       </c>
-      <c r="H218" s="14" t="inlineStr"/>
+      <c r="H218" s="13" t="inlineStr">
+        <is>
+          <t>Mteja aliomba mtu hapa</t>
+        </is>
+      </c>
+      <c r="I218" s="14" t="inlineStr"/>
     </row>
     <row r="219" ht="44" customHeight="1">
       <c r="A219" s="11" t="inlineStr">
@@ -13762,7 +15523,12 @@
           <t>Wadahadalkan fariin kuma jirto.</t>
         </is>
       </c>
-      <c r="H219" s="14" t="inlineStr"/>
+      <c r="H219" s="13" t="inlineStr">
+        <is>
+          <t>Hakuna ujumbe katika mazungumzo haya.</t>
+        </is>
+      </c>
+      <c r="I219" s="14" t="inlineStr"/>
     </row>
     <row r="220" ht="44" customHeight="1">
       <c r="A220" s="11" t="inlineStr">
@@ -13800,7 +15566,12 @@
           <t>{unit} kaliya wuxuu ku jiray {label}.</t>
         </is>
       </c>
-      <c r="H220" s="14" t="inlineStr"/>
+      <c r="H220" s="13" t="inlineStr">
+        <is>
+          <t>{unit} pekee ilikuwa katika {label}.</t>
+        </is>
+      </c>
+      <c r="I220" s="14" t="inlineStr"/>
     </row>
     <row r="221" ht="44" customHeight="1">
       <c r="A221" s="11" t="inlineStr">
@@ -13838,7 +15609,12 @@
           <t>Wadahadalka kaliya wuxuu ka yimid {label}.</t>
         </is>
       </c>
-      <c r="H221" s="14" t="inlineStr"/>
+      <c r="H221" s="13" t="inlineStr">
+        <is>
+          <t>Mazungumzo pekee yalitoka {label}.</t>
+        </is>
+      </c>
+      <c r="I221" s="14" t="inlineStr"/>
     </row>
     <row r="222" ht="44" customHeight="1">
       <c r="A222" s="11" t="inlineStr">
@@ -13876,7 +15652,12 @@
           <t>wadahadal</t>
         </is>
       </c>
-      <c r="H222" s="14" t="inlineStr"/>
+      <c r="H222" s="13" t="inlineStr">
+        <is>
+          <t>mazungumzo</t>
+        </is>
+      </c>
+      <c r="I222" s="14" t="inlineStr"/>
     </row>
     <row r="223" ht="44" customHeight="1">
       <c r="A223" s="11" t="inlineStr">
@@ -13914,7 +15695,12 @@
           <t>Kalfadhiyada tooska ah</t>
         </is>
       </c>
-      <c r="H223" s="14" t="inlineStr"/>
+      <c r="H223" s="13" t="inlineStr">
+        <is>
+          <t>Vikao vya Moja kwa Moja</t>
+        </is>
+      </c>
+      <c r="I223" s="14" t="inlineStr"/>
     </row>
     <row r="224" ht="44" customHeight="1">
       <c r="A224" s="11" t="inlineStr">
@@ -13952,7 +15738,12 @@
           <t>Bangigan waa la damiyay</t>
         </is>
       </c>
-      <c r="H224" s="14" t="inlineStr"/>
+      <c r="H224" s="13" t="inlineStr">
+        <is>
+          <t>Vimezimwa kwa Benki Hii</t>
+        </is>
+      </c>
+      <c r="I224" s="14" t="inlineStr"/>
     </row>
     <row r="225" ht="44" customHeight="1">
       <c r="A225" s="11" t="inlineStr">
@@ -13990,7 +15781,12 @@
           <t>Waa la shiday — laakiin qofna shaqada ma joogo</t>
         </is>
       </c>
-      <c r="H225" s="14" t="inlineStr"/>
+      <c r="H225" s="13" t="inlineStr">
+        <is>
+          <t>Vimewashwa — lakini hakuna aliye kazini</t>
+        </is>
+      </c>
+      <c r="I225" s="14" t="inlineStr"/>
     </row>
     <row r="226" ht="44" customHeight="1">
       <c r="A226" s="11" t="inlineStr">
@@ -14028,7 +15824,12 @@
           <t>Badhanka “La hadal shaqaale” kama muuqan widget-kaaga.</t>
         </is>
       </c>
-      <c r="H226" s="14" t="inlineStr"/>
+      <c r="H226" s="13" t="inlineStr">
+        <is>
+          <t>Hakuna kitufe cha "Zungumza na Afisa" kinachoonekana kwenye kidirisha chako.</t>
+        </is>
+      </c>
+      <c r="I226" s="14" t="inlineStr"/>
     </row>
     <row r="227" ht="44" customHeight="1">
       <c r="A227" s="11" t="inlineStr">
@@ -14066,7 +15867,12 @@
           <t>Shaqada ayaad joogtaa, sidaas darteed macaamiisha sugaya waa lagu soo dhiibi karaa. Marka aad tagto shaqada ka bax dhinaca — ilaa markaas bog kasta ayaad ku sii shaqeynaysaa.</t>
         </is>
       </c>
-      <c r="H227" s="14" t="inlineStr"/>
+      <c r="H227" s="13" t="inlineStr">
+        <is>
+          <t>Upo kazini, kwa hivyo wateja wanaosubiri wanaweza kuelekezwa kwako. Toka kazini kutoka upande wa kando unapoondoka — unabaki kwenye mtandao popote kwenye paneli mpaka utakapofanya hivyo.</t>
+        </is>
+      </c>
+      <c r="I227" s="14" t="inlineStr"/>
     </row>
     <row r="228" ht="44" customHeight="1">
       <c r="A228" s="11" t="inlineStr">
@@ -14104,7 +15910,12 @@
           <t>Si aad u bilowdo qaadista wicitaannada, dhinaca ka shid “Shaqada”. Bog kasta ayuu kula socdaa, sidaas darteed uma baahnid inaad tan furan ka tagto.</t>
         </is>
       </c>
-      <c r="H228" s="14" t="inlineStr"/>
+      <c r="H228" s="13" t="inlineStr">
+        <is>
+          <t>Washa Kazini kwenye upande wa kando ili kuanza kupokea simu. Inakufuata kwenye kila ukurasa, hivyo huhitaji tena kuweka huu wazi.</t>
+        </is>
+      </c>
+      <c r="I228" s="14" t="inlineStr"/>
     </row>
     <row r="229" ht="44" customHeight="1">
       <c r="A229" s="11" t="inlineStr">
@@ -14142,7 +15953,12 @@
           <t>Shaqaale haysta ogolaanshaha qaadista wicitaannada waa inuu shaqada joogaa ka hor inta aan macaamiisha la siin.</t>
         </is>
       </c>
-      <c r="H229" s="14" t="inlineStr"/>
+      <c r="H229" s="13" t="inlineStr">
+        <is>
+          <t>Mwenzako mwenye ruhusa ya kupokea simu lazima awe kazini kabla wateja hawajapewa fursa hiyo.</t>
+        </is>
+      </c>
+      <c r="I229" s="14" t="inlineStr"/>
     </row>
     <row r="230" ht="44" customHeight="1">
       <c r="A230" s="11" t="inlineStr">
@@ -14180,7 +15996,12 @@
           <t>Waxaan ku hadli karaa:</t>
         </is>
       </c>
-      <c r="H230" s="14" t="inlineStr"/>
+      <c r="H230" s="13" t="inlineStr">
+        <is>
+          <t>Ninaweza kufanya mazungumzo kwa:</t>
+        </is>
+      </c>
+      <c r="I230" s="14" t="inlineStr"/>
     </row>
     <row r="231" ht="44" customHeight="1">
       <c r="A231" s="11" t="inlineStr">
@@ -14218,7 +16039,12 @@
           <t>Macaamiisha ku qora kuwan ayaa marka hore kugu soo gaara. Qof kastana wuu ku soo gaari doonaa — sug gaaban ka dib, sidaas qofna ma harayo.</t>
         </is>
       </c>
-      <c r="H231" s="14" t="inlineStr"/>
+      <c r="H231" s="13" t="inlineStr">
+        <is>
+          <t>Wateja wanaoandika kwa lugha hizi wanakufikia kwanza. Kila mtu mwingine bado anakufikia — baada ya kusubiri kidogo, ili asibaki bila msaada.</t>
+        </is>
+      </c>
+      <c r="I231" s="14" t="inlineStr"/>
     </row>
     <row r="232" ht="44" customHeight="1">
       <c r="A232" s="11" t="inlineStr">
@@ -14256,7 +16082,12 @@
           <t>Waxba lama dooran, sidaas darteed macmiil kasta oo sugaya waxaa laguu soo bandhigayaa sida caadiga ah ee ugu horreeya.</t>
         </is>
       </c>
-      <c r="H232" s="14" t="inlineStr"/>
+      <c r="H232" s="13" t="inlineStr">
+        <is>
+          <t>Hakuna kilichochaguliwa, kwa hivyo kila mteja anayesubiri anapewa kwako kwa mpangilio wa zamani zaidi kwanza.</t>
+        </is>
+      </c>
+      <c r="I232" s="14" t="inlineStr"/>
     </row>
     <row r="233" ht="44" customHeight="1">
       <c r="A233" s="11" t="inlineStr">
@@ -14294,7 +16125,12 @@
           <t>Luqadaha waa la cusbooneysiiyay</t>
         </is>
       </c>
-      <c r="H233" s="14" t="inlineStr"/>
+      <c r="H233" s="13" t="inlineStr">
+        <is>
+          <t>Lugha Zimesasishwa</t>
+        </is>
+      </c>
+      <c r="I233" s="14" t="inlineStr"/>
     </row>
     <row r="234" ht="44" customHeight="1">
       <c r="A234" s="11" t="inlineStr">
@@ -14332,7 +16168,12 @@
           <t>Fiidyow</t>
         </is>
       </c>
-      <c r="H234" s="14" t="inlineStr"/>
+      <c r="H234" s="13" t="inlineStr">
+        <is>
+          <t>Vidio</t>
+        </is>
+      </c>
+      <c r="I234" s="14" t="inlineStr"/>
     </row>
     <row r="235" ht="44" customHeight="1">
       <c r="A235" s="11" t="inlineStr">
@@ -14370,7 +16211,12 @@
           <t>Cod</t>
         </is>
       </c>
-      <c r="H235" s="14" t="inlineStr"/>
+      <c r="H235" s="13" t="inlineStr">
+        <is>
+          <t>Sauti</t>
+        </is>
+      </c>
+      <c r="I235" s="14" t="inlineStr"/>
     </row>
     <row r="236" ht="44" customHeight="1">
       <c r="A236" s="11" t="inlineStr">
@@ -14408,7 +16254,12 @@
           <t>ma aha luqaddaada</t>
         </is>
       </c>
-      <c r="H236" s="14" t="inlineStr"/>
+      <c r="H236" s="13" t="inlineStr">
+        <is>
+          <t>si lugha yako</t>
+        </is>
+      </c>
+      <c r="I236" s="14" t="inlineStr"/>
     </row>
     <row r="237" ht="44" customHeight="1">
       <c r="A237" s="11" t="inlineStr">
@@ -14446,7 +16297,12 @@
           <t>Luqadahaaga marka hore, kii ugu sugay dheeraa mid kasta gudahood. Qof kasta oo aad u sugay ayaa kor u kaca luqad kastoo uu ku hadloba.</t>
         </is>
       </c>
-      <c r="H237" s="14" t="inlineStr"/>
+      <c r="H237" s="13" t="inlineStr">
+        <is>
+          <t>Lugha zako kwanza, aliyesubiri kwa muda mrefu zaidi ndani ya kila moja. Yeyote anayesubiri kwa muda mrefu sana anapanda juu bila kujali anazungumza lugha gani.</t>
+        </is>
+      </c>
+      <c r="I237" s="14" t="inlineStr"/>
     </row>
     <row r="238" ht="44" customHeight="1">
       <c r="A238" s="11" t="inlineStr">
@@ -14484,7 +16340,12 @@
           <t>Socda</t>
         </is>
       </c>
-      <c r="H238" s="14" t="inlineStr"/>
+      <c r="H238" s="13" t="inlineStr">
+        <is>
+          <t>Inaendelea</t>
+        </is>
+      </c>
+      <c r="I238" s="14" t="inlineStr"/>
     </row>
     <row r="239" ht="44" customHeight="1">
       <c r="A239" s="11" t="inlineStr">
@@ -14522,7 +16383,12 @@
           <t>Ma jiro kalfadhi socda.</t>
         </is>
       </c>
-      <c r="H239" s="14" t="inlineStr"/>
+      <c r="H239" s="13" t="inlineStr">
+        <is>
+          <t>Hakuna kikao kinachoendelea.</t>
+        </is>
+      </c>
+      <c r="I239" s="14" t="inlineStr"/>
     </row>
     <row r="240" ht="44" customHeight="1">
       <c r="A240" s="11" t="inlineStr">
@@ -14560,7 +16426,12 @@
           <t>sug</t>
         </is>
       </c>
-      <c r="H240" s="14" t="inlineStr"/>
+      <c r="H240" s="13" t="inlineStr">
+        <is>
+          <t>kusubiri</t>
+        </is>
+      </c>
+      <c r="I240" s="14" t="inlineStr"/>
     </row>
     <row r="241" ht="44" customHeight="1">
       <c r="A241" s="11" t="inlineStr">
@@ -14598,7 +16469,12 @@
           <t>Waxa kalfadhigu daboolo</t>
         </is>
       </c>
-      <c r="H241" s="14" t="inlineStr"/>
+      <c r="H241" s="13" t="inlineStr">
+        <is>
+          <t>Kikao Kinajumuisha Nini</t>
+        </is>
+      </c>
+      <c r="I241" s="14" t="inlineStr"/>
     </row>
     <row r="242" ht="44" customHeight="1">
       <c r="A242" s="11" t="inlineStr">
@@ -14636,7 +16512,12 @@
           <t>Ka hor inta aan qofka la aqoonsan: su'aalo guud oo ku saabsan alaabta, u-qalmitaanka iyo sida loo codsado. Marka aad hubiso aqoonsigooda Fayda ee xisaabta oo aad weydiiso wax uu kaliya milkiilaha xisaabtu ka jawaabi karo: codsigooda, dukumiintiyada iyo cabashooyinka.</t>
         </is>
       </c>
-      <c r="H242" s="14" t="inlineStr"/>
+      <c r="H242" s="13" t="inlineStr">
+        <is>
+          <t>Kabla mtu hajatambuliwa: maswali ya jumla kuhusu bidhaa, sifa za kustahiki na jinsi ya kuomba. Baada ya kukagua Kitambulisho chao cha Fayda dhidi ya akaunti na kuuliza kitu ambacho mmiliki wa akaunti pekee angeweza kujibu: maombi yao wenyewe, nyaraka na migogoro.</t>
+        </is>
+      </c>
+      <c r="I242" s="14" t="inlineStr"/>
     </row>
     <row r="243" ht="44" customHeight="1">
       <c r="A243" s="11" t="inlineStr">
@@ -14674,7 +16555,12 @@
           <t>Weligaa, wakhti kasta iyo qof kasta: dhigasho, qaadis ama wareejin ma jirto. Kuwaas wicitaan laguma sameeyo.</t>
         </is>
       </c>
-      <c r="H243" s="14" t="inlineStr"/>
+      <c r="H243" s="13" t="inlineStr">
+        <is>
+          <t>Kamwe, wakati wowote na kwa yeyote: amana, uondoaji au uhamishaji. Hizo hazifanyiki kwenye simu.</t>
+        </is>
+      </c>
+      <c r="I243" s="14" t="inlineStr"/>
     </row>
     <row r="244" ht="44" customHeight="1">
       <c r="A244" s="11" t="inlineStr">
@@ -14712,7 +16598,12 @@
           <t>Fur safka gudbinta</t>
         </is>
       </c>
-      <c r="H244" s="14" t="inlineStr"/>
+      <c r="H244" s="13" t="inlineStr">
+        <is>
+          <t>Fungua Foleni ya Masuala Yaliyoelekezwa</t>
+        </is>
+      </c>
+      <c r="I244" s="14" t="inlineStr"/>
     </row>
     <row r="245" ht="44" customHeight="1">
       <c r="A245" s="11" t="inlineStr">
@@ -14750,7 +16641,12 @@
           <t>U beddel mugdiga iyo iftiinka</t>
         </is>
       </c>
-      <c r="H245" s="14" t="inlineStr"/>
+      <c r="H245" s="13" t="inlineStr">
+        <is>
+          <t>Badilisha Kati ya Giza na Mwanga</t>
+        </is>
+      </c>
+      <c r="I245" s="14" t="inlineStr"/>
     </row>
     <row r="246" ht="44" customHeight="1">
       <c r="A246" s="11" t="inlineStr">
@@ -14788,7 +16684,12 @@
           <t>Kalfadhi toos ah</t>
         </is>
       </c>
-      <c r="H246" s="14" t="inlineStr"/>
+      <c r="H246" s="13" t="inlineStr">
+        <is>
+          <t>Kikao cha Moja kwa Moja</t>
+        </is>
+      </c>
+      <c r="I246" s="14" t="inlineStr"/>
     </row>
     <row r="247" ht="44" customHeight="1">
       <c r="A247" s="11" t="inlineStr">
@@ -14826,7 +16727,12 @@
           <t>Macmiilku wicitaanka wuu ka baxay.</t>
         </is>
       </c>
-      <c r="H247" s="14" t="inlineStr"/>
+      <c r="H247" s="13" t="inlineStr">
+        <is>
+          <t>Mteja ameondoka kwenye simu.</t>
+        </is>
+      </c>
+      <c r="I247" s="14" t="inlineStr"/>
     </row>
     <row r="248" ht="44" customHeight="1">
       <c r="A248" s="11" t="inlineStr">
@@ -14864,7 +16770,12 @@
           <t>Macmiilka la sugayo…</t>
         </is>
       </c>
-      <c r="H248" s="14" t="inlineStr"/>
+      <c r="H248" s="13" t="inlineStr">
+        <is>
+          <t>Inasubiri Mteja…</t>
+        </is>
+      </c>
+      <c r="I248" s="14" t="inlineStr"/>
     </row>
     <row r="249" ht="44" customHeight="1">
       <c r="A249" s="11" t="inlineStr">
@@ -14902,7 +16813,12 @@
           <t>Makarafoonka waa la xannibay. Browser-kaaga ka ogolow oo kalfadhiga mar kale qaado.</t>
         </is>
       </c>
-      <c r="H249" s="14" t="inlineStr"/>
+      <c r="H249" s="13" t="inlineStr">
+        <is>
+          <t>Ufikiaji wa maikrofoni umezuiwa. Ruhusu kwenye kivinjari chako na uanze kikao tena.</t>
+        </is>
+      </c>
+      <c r="I249" s="14" t="inlineStr"/>
     </row>
     <row r="250" ht="44" customHeight="1">
       <c r="A250" s="11" t="inlineStr">
@@ -14940,7 +16856,12 @@
           <t>khalad aan la garanayn</t>
         </is>
       </c>
-      <c r="H250" s="14" t="inlineStr"/>
+      <c r="H250" s="13" t="inlineStr">
+        <is>
+          <t>hitilafu isiyojulikana</t>
+        </is>
+      </c>
+      <c r="I250" s="14" t="inlineStr"/>
     </row>
     <row r="251" ht="44" customHeight="1">
       <c r="A251" s="11" t="inlineStr">
@@ -14978,7 +16899,12 @@
           <t>Weli fariimo ma jiraan.</t>
         </is>
       </c>
-      <c r="H251" s="14" t="inlineStr"/>
+      <c r="H251" s="13" t="inlineStr">
+        <is>
+          <t>Hakuna ujumbe bado.</t>
+        </is>
+      </c>
+      <c r="I251" s="14" t="inlineStr"/>
     </row>
     <row r="252" ht="44" customHeight="1">
       <c r="A252" s="11" t="inlineStr">
@@ -15016,7 +16942,12 @@
           <t>Adiga</t>
         </is>
       </c>
-      <c r="H252" s="14" t="inlineStr"/>
+      <c r="H252" s="13" t="inlineStr">
+        <is>
+          <t>Wewe</t>
+        </is>
+      </c>
+      <c r="I252" s="14" t="inlineStr"/>
     </row>
     <row r="253" ht="44" customHeight="1">
       <c r="A253" s="11" t="inlineStr">
@@ -15054,7 +16985,12 @@
           <t>Kaaliye</t>
         </is>
       </c>
-      <c r="H253" s="14" t="inlineStr"/>
+      <c r="H253" s="13" t="inlineStr">
+        <is>
+          <t>Msaidizi</t>
+        </is>
+      </c>
+      <c r="I253" s="14" t="inlineStr"/>
     </row>
     <row r="254" ht="44" customHeight="1">
       <c r="A254" s="11" t="inlineStr">
@@ -15092,7 +17028,12 @@
           <t>Wadahadalka lama heli karo.</t>
         </is>
       </c>
-      <c r="H254" s="14" t="inlineStr"/>
+      <c r="H254" s="13" t="inlineStr">
+        <is>
+          <t>Mazungumzo hayapatikani.</t>
+        </is>
+      </c>
+      <c r="I254" s="14" t="inlineStr"/>
     </row>
     <row r="255" ht="44" customHeight="1">
       <c r="A255" s="11" t="inlineStr">
@@ -15130,7 +17071,12 @@
           <t>Codka fur</t>
         </is>
       </c>
-      <c r="H255" s="14" t="inlineStr"/>
+      <c r="H255" s="13" t="inlineStr">
+        <is>
+          <t>Rudisha Sauti</t>
+        </is>
+      </c>
+      <c r="I255" s="14" t="inlineStr"/>
     </row>
     <row r="256" ht="44" customHeight="1">
       <c r="A256" s="11" t="inlineStr">
@@ -15168,7 +17114,12 @@
           <t>Kalfadhigan muxuu daboolay? (ikhtiyaari)</t>
         </is>
       </c>
-      <c r="H256" s="14" t="inlineStr"/>
+      <c r="H256" s="13" t="inlineStr">
+        <is>
+          <t>Kikao hiki kilihusu nini? (si lazima)</t>
+        </is>
+      </c>
+      <c r="I256" s="14" t="inlineStr"/>
     </row>
     <row r="257" ht="44" customHeight="1">
       <c r="A257" s="11" t="inlineStr">
@@ -15206,7 +17157,12 @@
           <t>Macmiilku wicitaanka wuu joojiyay</t>
         </is>
       </c>
-      <c r="H257" s="14" t="inlineStr"/>
+      <c r="H257" s="13" t="inlineStr">
+        <is>
+          <t>Mteja alimaliza simu</t>
+        </is>
+      </c>
+      <c r="I257" s="14" t="inlineStr"/>
     </row>
     <row r="258" ht="44" customHeight="1">
       <c r="A258" s="11" t="inlineStr">
@@ -15244,7 +17200,12 @@
           <t>Hadda waad kala hadli kartaa diiwaankooda, dukumiinti qaadan iyo cabasho diiwaangelin. Weligaa dhigasho, qaadis ama wareejin ma jirto.</t>
         </is>
       </c>
-      <c r="H258" s="14" t="inlineStr"/>
+      <c r="H258" s="13" t="inlineStr">
+        <is>
+          <t>Sasa unaweza kuzungumzia rekodi zao wenyewe, kuchukua nyaraka na kuwasilisha mgogoro. Kamwe amana, uondoaji au uhamishaji.</t>
+        </is>
+      </c>
+      <c r="I258" s="14" t="inlineStr"/>
     </row>
     <row r="259" ht="44" customHeight="1">
       <c r="A259" s="11" t="inlineStr">
@@ -15282,7 +17243,12 @@
           <t>Ogow cidda ay yihiin — mid kasta</t>
         </is>
       </c>
-      <c r="H259" s="14" t="inlineStr"/>
+      <c r="H259" s="13" t="inlineStr">
+        <is>
+          <t>Thibitisha ni nani — mojawapo</t>
+        </is>
+      </c>
+      <c r="I259" s="14" t="inlineStr"/>
     </row>
     <row r="260" ht="44" customHeight="1">
       <c r="A260" s="11" t="inlineStr">
@@ -15320,7 +17286,12 @@
           <t>Aqoonsiga Fayda waa la tusay wuxuuna la mid yahay magaca xisaabta</t>
         </is>
       </c>
-      <c r="H260" s="14" t="inlineStr"/>
+      <c r="H260" s="13" t="inlineStr">
+        <is>
+          <t>Kitambulisho cha Fayda kimeonyeshwa na kinalingana na jina la akaunti</t>
+        </is>
+      </c>
+      <c r="I260" s="14" t="inlineStr"/>
     </row>
     <row r="261" ht="44" customHeight="1">
       <c r="A261" s="11" t="inlineStr">
@@ -15358,7 +17329,12 @@
           <t>Lambarka Fayda wuxuu la mid yahay diiwaanka xisaabta</t>
         </is>
       </c>
-      <c r="H261" s="14" t="inlineStr"/>
+      <c r="H261" s="13" t="inlineStr">
+        <is>
+          <t>Namba ya Fayda inalingana na rekodi ya akaunti</t>
+        </is>
+      </c>
+      <c r="I261" s="14" t="inlineStr"/>
     </row>
     <row r="262" ht="44" customHeight="1">
       <c r="A262" s="11" t="inlineStr">
@@ -15396,7 +17372,12 @@
           <t>shaashaddaada — wicitaan cod ahna wuu ka shaqeeyaa</t>
         </is>
       </c>
-      <c r="H262" s="14" t="inlineStr"/>
+      <c r="H262" s="13" t="inlineStr">
+        <is>
+          <t>kwenye skrini yako mwenyewe — inafanya kazi kwenye simu ya sauti</t>
+        </is>
+      </c>
+      <c r="I262" s="14" t="inlineStr"/>
     </row>
     <row r="263" ht="44" customHeight="1">
       <c r="A263" s="11" t="inlineStr">
@@ -15434,7 +17415,12 @@
           <t>Sawirka aqoonsiga wuxuu la mid yahay qofka wicitaanka ku jira</t>
         </is>
       </c>
-      <c r="H263" s="14" t="inlineStr"/>
+      <c r="H263" s="13" t="inlineStr">
+        <is>
+          <t>Picha kwenye kitambulisho inalingana na mtu aliye kwenye simu</t>
+        </is>
+      </c>
+      <c r="I263" s="14" t="inlineStr"/>
     </row>
     <row r="264" ht="44" customHeight="1">
       <c r="A264" s="11" t="inlineStr">
@@ -15472,7 +17458,12 @@
           <t>fiidyow oo kaliya</t>
         </is>
       </c>
-      <c r="H264" s="14" t="inlineStr"/>
+      <c r="H264" s="13" t="inlineStr">
+        <is>
+          <t>video pekee</t>
+        </is>
+      </c>
+      <c r="I264" s="14" t="inlineStr"/>
     </row>
     <row r="265" ht="44" customHeight="1">
       <c r="A265" s="11" t="inlineStr">
@@ -15510,7 +17501,12 @@
           <t>Xaqiiji in xisaabtu tahay tooda</t>
         </is>
       </c>
-      <c r="H265" s="14" t="inlineStr"/>
+      <c r="H265" s="13" t="inlineStr">
+        <is>
+          <t>Na thibitisha akaunti ni yao</t>
+        </is>
+      </c>
+      <c r="I265" s="14" t="inlineStr"/>
     </row>
     <row r="266" ht="44" customHeight="1">
       <c r="A266" s="11" t="inlineStr">
@@ -15548,7 +17544,12 @@
           <t>Xaqiiji aqoonsiga</t>
         </is>
       </c>
-      <c r="H266" s="14" t="inlineStr"/>
+      <c r="H266" s="13" t="inlineStr">
+        <is>
+          <t>Thibitisha Utambulisho</t>
+        </is>
+      </c>
+      <c r="I266" s="14" t="inlineStr"/>
     </row>
     <row r="267" ht="44" customHeight="1">
       <c r="A267" s="11" t="inlineStr">
@@ -15586,7 +17587,12 @@
           <t>Ilaa tan la sameeyo waxaad kaliya bixin kartaa hagaajin guud — alaabta, u-qalmitaanka iyo sida loo codsado.</t>
         </is>
       </c>
-      <c r="H267" s="14" t="inlineStr"/>
+      <c r="H267" s="13" t="inlineStr">
+        <is>
+          <t>Hadi hili litakapofanyika unaweza tu kutoa mwongozo wa jumla — bidhaa, sifa za kustahiki na jinsi ya kuomba.</t>
+        </is>
+      </c>
+      <c r="I267" s="14" t="inlineStr"/>
     </row>
     <row r="268" ht="44" customHeight="1">
       <c r="A268" s="11" t="inlineStr">
@@ -15624,7 +17630,12 @@
           <t>Lambarka Fayda (loo baahan yahay — waa waxa diiwaanku hayo)</t>
         </is>
       </c>
-      <c r="H268" s="14" t="inlineStr"/>
+      <c r="H268" s="13" t="inlineStr">
+        <is>
+          <t>Namba ya Fayda (inahitajika — ndiyo inayowekwa kwenye rekodi)</t>
+        </is>
+      </c>
+      <c r="I268" s="14" t="inlineStr"/>
     </row>
     <row r="269" ht="44" customHeight="1">
       <c r="A269" s="11" t="inlineStr">
@@ -15662,7 +17673,12 @@
           <t>Soo dejiso turjumaadda</t>
         </is>
       </c>
-      <c r="H269" s="14" t="inlineStr"/>
+      <c r="H269" s="13" t="inlineStr">
+        <is>
+          <t>Pakua kwa Tafsiri</t>
+        </is>
+      </c>
+      <c r="I269" s="14" t="inlineStr"/>
     </row>
     <row r="270" ht="44" customHeight="1">
       <c r="A270" s="11" t="inlineStr">
@@ -15700,10 +17716,15 @@
           <t>Weli ma jiraan jawaabo la ansixiyay oo la soo dejiyo.</t>
         </is>
       </c>
-      <c r="H270" s="14" t="inlineStr"/>
+      <c r="H270" s="13" t="inlineStr">
+        <is>
+          <t>Hakuna majibu yaliyoidhinishwa ya kupakua bado.</t>
+        </is>
+      </c>
+      <c r="I270" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H270"/>
+  <autoFilter ref="A1:I270"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/review/Olink_Bank_Assist_language_review.xlsx
+++ b/review/Olink_Bank_Assist_language_review.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1. What the assistant says'!$A$1:$I$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2. What it understands'!$A$1:$E$91</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3. Buttons customers see'!$A$1:$I$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3. Buttons customers see'!$A$1:$I$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$I$270</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -752,7 +752,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>338 strings in 5 languages</t>
+          <t>341 strings in 5 languages</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6000,7 +6000,7 @@
     <row r="49" ht="44" customHeight="1">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>today</t>
+          <t>label_routed_to_person</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
@@ -6010,32 +6010,32 @@
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Today</t>
+          <t>Routed to a person</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>ዛሬ</t>
+          <t>ወደ ሰው ተላልፏል</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>Har'a</t>
+          <t>Gara namaatti dabarfameera</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>ሎሚ</t>
+          <t>ናብ ሰብ ተመሓላሊፉ</t>
         </is>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
-          <t>Maanta</t>
+          <t>Loo gudbiyay qof</t>
         </is>
       </c>
       <c r="H49" s="13" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Imeelekezwa kwa mtu</t>
         </is>
       </c>
       <c r="I49" s="14" t="inlineStr"/>
@@ -6043,48 +6043,177 @@
     <row r="50" ht="44" customHeight="1">
       <c r="A50" s="11" t="inlineStr">
         <is>
+          <t>n_sources</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>Button, label or placeholder in the chat window. Keep it short — it has to fit the same space as the English, on a phone.</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>{n} sources</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>{n} ምንጮች</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>Maddoota {n}</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="inlineStr">
+        <is>
+          <t>{n} ምንጭታት</t>
+        </is>
+      </c>
+      <c r="G50" s="13" t="inlineStr">
+        <is>
+          <t>{n} ilo</t>
+        </is>
+      </c>
+      <c r="H50" s="13" t="inlineStr">
+        <is>
+          <t>Vyanzo {n}</t>
+        </is>
+      </c>
+      <c r="I50" s="14" t="inlineStr"/>
+    </row>
+    <row r="51" ht="44" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>one_source</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>Button, label or placeholder in the chat window. Keep it short — it has to fit the same space as the English, on a phone.</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>{n} source</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>{n} ምንጭ</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>Madda {n}</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="inlineStr">
+        <is>
+          <t>{n} ምንጪ</t>
+        </is>
+      </c>
+      <c r="G51" s="13" t="inlineStr">
+        <is>
+          <t>{n} il</t>
+        </is>
+      </c>
+      <c r="H51" s="13" t="inlineStr">
+        <is>
+          <t>Chanzo {n}</t>
+        </is>
+      </c>
+      <c r="I51" s="14" t="inlineStr"/>
+    </row>
+    <row r="52" ht="44" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>Button, label or placeholder in the chat window. Keep it short — it has to fit the same space as the English, on a phone.</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>Today</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>ዛሬ</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>Har'a</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>ሎሚ</t>
+        </is>
+      </c>
+      <c r="G52" s="13" t="inlineStr">
+        <is>
+          <t>Maanta</t>
+        </is>
+      </c>
+      <c r="H52" s="13" t="inlineStr">
+        <is>
+          <t>Leo</t>
+        </is>
+      </c>
+      <c r="I52" s="14" t="inlineStr"/>
+    </row>
+    <row r="53" ht="44" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
           <t>yesterday</t>
         </is>
       </c>
-      <c r="B50" s="11" t="inlineStr">
+      <c r="B53" s="11" t="inlineStr">
         <is>
           <t>Button, label or placeholder in the chat window. Keep it short — it has to fit the same space as the English, on a phone.</t>
         </is>
       </c>
-      <c r="C50" s="11" t="inlineStr">
+      <c r="C53" s="11" t="inlineStr">
         <is>
           <t>Yesterday</t>
         </is>
       </c>
-      <c r="D50" s="12" t="inlineStr">
+      <c r="D53" s="12" t="inlineStr">
         <is>
           <t>ትናንት</t>
         </is>
       </c>
-      <c r="E50" s="13" t="inlineStr">
+      <c r="E53" s="13" t="inlineStr">
         <is>
           <t>Kaleessa</t>
         </is>
       </c>
-      <c r="F50" s="12" t="inlineStr">
+      <c r="F53" s="12" t="inlineStr">
         <is>
           <t>ትማሊ</t>
         </is>
       </c>
-      <c r="G50" s="13" t="inlineStr">
+      <c r="G53" s="13" t="inlineStr">
         <is>
           <t>Shalay</t>
         </is>
       </c>
-      <c r="H50" s="13" t="inlineStr">
+      <c r="H53" s="13" t="inlineStr">
         <is>
           <t>Jana</t>
         </is>
       </c>
-      <c r="I50" s="14" t="inlineStr"/>
+      <c r="I53" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I50"/>
+  <autoFilter ref="A1:I53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/review/Olink_Bank_Assist_language_review.xlsx
+++ b/review/Olink_Bank_Assist_language_review.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1. What the assistant says'!$A$1:$I$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2. What it understands'!$A$1:$E$91</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3. Buttons customers see'!$A$1:$I$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$I$270</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$I$273</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -752,7 +752,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>341 strings in 5 languages</t>
+          <t>344 strings in 5 languages</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I270"/>
+  <dimension ref="A1:I273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -16737,7 +16737,7 @@
     <row r="245" ht="44" customHeight="1">
       <c r="A245" s="11" t="inlineStr">
         <is>
-          <t>switch_dark_light</t>
+          <t>open_live_queue</t>
         </is>
       </c>
       <c r="B245" s="11" t="inlineStr">
@@ -16747,32 +16747,32 @@
       </c>
       <c r="C245" s="11" t="inlineStr">
         <is>
-          <t>Switch between dark and light</t>
+          <t>Open the live call queue</t>
         </is>
       </c>
       <c r="D245" s="12" t="inlineStr">
         <is>
-          <t>በጨለማና በብርሃን መካከል ቀይር</t>
+          <t>ቀጥታ የጥሪ ወረፋውን ክፈት</t>
         </is>
       </c>
       <c r="E245" s="13" t="inlineStr">
         <is>
-          <t>Dukkanaa fi ifa gidduu jijjiiri</t>
+          <t>Sarara bilbilaa kallattii banaa</t>
         </is>
       </c>
       <c r="F245" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መንጎ ጸላምን ብርሃንን ቀይር</t>
+          <t>ቀጥታዊ ናይ ጻውዒት ሰልፊ ክፈት</t>
         </is>
       </c>
       <c r="G245" s="13" t="inlineStr">
         <is>
-          <t>U beddel mugdiga iyo iftiinka</t>
+          <t>Fur safka wicitaanka tooska ah</t>
         </is>
       </c>
       <c r="H245" s="13" t="inlineStr">
         <is>
-          <t>Badilisha Kati ya Giza na Mwanga</t>
+          <t>Fungua foleni ya simu za moja kwa moja</t>
         </is>
       </c>
       <c r="I245" s="14" t="inlineStr"/>
@@ -16780,7 +16780,7 @@
     <row r="246" ht="44" customHeight="1">
       <c r="A246" s="11" t="inlineStr">
         <is>
-          <t>live_session</t>
+          <t>live_waiting_one</t>
         </is>
       </c>
       <c r="B246" s="11" t="inlineStr">
@@ -16790,32 +16790,32 @@
       </c>
       <c r="C246" s="11" t="inlineStr">
         <is>
-          <t>Live session</t>
+          <t>{n} customer waiting for a live call</t>
         </is>
       </c>
       <c r="D246" s="12" t="inlineStr">
         <is>
-          <t>የቀጥታ ክፍለ-ጊዜ</t>
+          <t>{n} ደንበኛ ቀጥታ ጥሪ በመጠበቅ ላይ ነው</t>
         </is>
       </c>
       <c r="E246" s="13" t="inlineStr">
         <is>
-          <t>Session kallattii</t>
+          <t>Maamilaan {n} bilbila kallattii eegaa jira</t>
         </is>
       </c>
       <c r="F246" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታ ክፍለ-ግዜ</t>
+          <t>{n} ዓሚል ቀጥታዊ ጻውዒት ይጽበ ኣሎ</t>
         </is>
       </c>
       <c r="G246" s="13" t="inlineStr">
         <is>
-          <t>Kalfadhi toos ah</t>
+          <t>{n} macmiil ayaa sugaya wicitaan toos ah</t>
         </is>
       </c>
       <c r="H246" s="13" t="inlineStr">
         <is>
-          <t>Kikao cha Moja kwa Moja</t>
+          <t>Mteja {n} anasubiri simu ya moja kwa moja</t>
         </is>
       </c>
       <c r="I246" s="14" t="inlineStr"/>
@@ -16823,7 +16823,7 @@
     <row r="247" ht="44" customHeight="1">
       <c r="A247" s="11" t="inlineStr">
         <is>
-          <t>customer_left_call</t>
+          <t>live_waiting_many</t>
         </is>
       </c>
       <c r="B247" s="11" t="inlineStr">
@@ -16833,32 +16833,32 @@
       </c>
       <c r="C247" s="11" t="inlineStr">
         <is>
-          <t>The customer has left the call.</t>
+          <t>{n} customers waiting for a live call</t>
         </is>
       </c>
       <c r="D247" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛው ጥሪውን ለቅቋል።</t>
+          <t>{n} ደንበኞች ቀጥታ ጥሪ በመጠበቅ ላይ ናቸው</t>
         </is>
       </c>
       <c r="E247" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan bilbila irraa ba'eera.</t>
+          <t>Maamiltoonni {n} bilbila kallattii eegaa jiru</t>
         </is>
       </c>
       <c r="F247" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዓሚል ካብቲ ጻውዒት ወጺኡ።</t>
+          <t>{n} ዓማዊል ቀጥታዊ ጻውዒት ይጽበዩ ኣለዉ</t>
         </is>
       </c>
       <c r="G247" s="13" t="inlineStr">
         <is>
-          <t>Macmiilku wicitaanka wuu ka baxay.</t>
+          <t>{n} macaamiil ayaa sugaya wicitaan toos ah</t>
         </is>
       </c>
       <c r="H247" s="13" t="inlineStr">
         <is>
-          <t>Mteja ameondoka kwenye simu.</t>
+          <t>Wateja {n} wanasubiri simu ya moja kwa moja</t>
         </is>
       </c>
       <c r="I247" s="14" t="inlineStr"/>
@@ -16866,7 +16866,7 @@
     <row r="248" ht="44" customHeight="1">
       <c r="A248" s="11" t="inlineStr">
         <is>
-          <t>waiting_for_customer</t>
+          <t>switch_dark_light</t>
         </is>
       </c>
       <c r="B248" s="11" t="inlineStr">
@@ -16876,32 +16876,32 @@
       </c>
       <c r="C248" s="11" t="inlineStr">
         <is>
-          <t>Waiting for the customer…</t>
+          <t>Switch between dark and light</t>
         </is>
       </c>
       <c r="D248" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛውን በመጠበቅ ላይ…</t>
+          <t>በጨለማና በብርሃን መካከል ቀይር</t>
         </is>
       </c>
       <c r="E248" s="13" t="inlineStr">
         <is>
-          <t>Maamilaa eegaa jirra…</t>
+          <t>Dukkanaa fi ifa gidduu jijjiiri</t>
         </is>
       </c>
       <c r="F248" s="12" t="inlineStr">
         <is>
-          <t>ነቲ ዓሚል ንጽበ ኣለና…</t>
+          <t>ኣብ መንጎ ጸላምን ብርሃንን ቀይር</t>
         </is>
       </c>
       <c r="G248" s="13" t="inlineStr">
         <is>
-          <t>Macmiilka la sugayo…</t>
+          <t>U beddel mugdiga iyo iftiinka</t>
         </is>
       </c>
       <c r="H248" s="13" t="inlineStr">
         <is>
-          <t>Inasubiri Mteja…</t>
+          <t>Badilisha Kati ya Giza na Mwanga</t>
         </is>
       </c>
       <c r="I248" s="14" t="inlineStr"/>
@@ -16909,7 +16909,7 @@
     <row r="249" ht="44" customHeight="1">
       <c r="A249" s="11" t="inlineStr">
         <is>
-          <t>mic_blocked</t>
+          <t>live_session</t>
         </is>
       </c>
       <c r="B249" s="11" t="inlineStr">
@@ -16919,32 +16919,32 @@
       </c>
       <c r="C249" s="11" t="inlineStr">
         <is>
-          <t>Microphone access is blocked. Allow it in your browser and take the session again.</t>
+          <t>Live session</t>
         </is>
       </c>
       <c r="D249" s="12" t="inlineStr">
         <is>
-          <t>የማይክሮፎን መዳረሻ ታግዷል። በአሳሽዎ ውስጥ ይፍቀዱና ክፍለ-ጊዜውን እንደገና ይውሰዱ።</t>
+          <t>የቀጥታ ክፍለ-ጊዜ</t>
         </is>
       </c>
       <c r="E249" s="13" t="inlineStr">
         <is>
-          <t>Maayikiroofoonii dhorkameera. Biraawzarii keessan keessatti hayyamaatii session irra deebi'aa fudhadhaa.</t>
+          <t>Session kallattii</t>
         </is>
       </c>
       <c r="F249" s="12" t="inlineStr">
         <is>
-          <t>መእተዊ ማይክሮፎን ተዓጊቱ። ኣብ መርበብ መንሸራተቲኹም ፍቐዱ እሞ ነቲ ክፍለ-ግዜ ደጊምኩም ውሰዱ።</t>
+          <t>ቀጥታ ክፍለ-ግዜ</t>
         </is>
       </c>
       <c r="G249" s="13" t="inlineStr">
         <is>
-          <t>Makarafoonka waa la xannibay. Browser-kaaga ka ogolow oo kalfadhiga mar kale qaado.</t>
+          <t>Kalfadhi toos ah</t>
         </is>
       </c>
       <c r="H249" s="13" t="inlineStr">
         <is>
-          <t>Ufikiaji wa maikrofoni umezuiwa. Ruhusu kwenye kivinjari chako na uanze kikao tena.</t>
+          <t>Kikao cha Moja kwa Moja</t>
         </is>
       </c>
       <c r="I249" s="14" t="inlineStr"/>
@@ -16952,7 +16952,7 @@
     <row r="250" ht="44" customHeight="1">
       <c r="A250" s="11" t="inlineStr">
         <is>
-          <t>unknown_error</t>
+          <t>customer_left_call</t>
         </is>
       </c>
       <c r="B250" s="11" t="inlineStr">
@@ -16962,32 +16962,32 @@
       </c>
       <c r="C250" s="11" t="inlineStr">
         <is>
-          <t>unknown error</t>
+          <t>The customer has left the call.</t>
         </is>
       </c>
       <c r="D250" s="12" t="inlineStr">
         <is>
-          <t>ያልታወቀ ስህተት</t>
+          <t>ደንበኛው ጥሪውን ለቅቋል።</t>
         </is>
       </c>
       <c r="E250" s="13" t="inlineStr">
         <is>
-          <t>dogoggora hin beekamne</t>
+          <t>Maamilaan bilbila irraa ba'eera.</t>
         </is>
       </c>
       <c r="F250" s="12" t="inlineStr">
         <is>
-          <t>ዘይተፈልጠ ጌጋ</t>
+          <t>እቲ ዓሚል ካብቲ ጻውዒት ወጺኡ።</t>
         </is>
       </c>
       <c r="G250" s="13" t="inlineStr">
         <is>
-          <t>khalad aan la garanayn</t>
+          <t>Macmiilku wicitaanka wuu ka baxay.</t>
         </is>
       </c>
       <c r="H250" s="13" t="inlineStr">
         <is>
-          <t>hitilafu isiyojulikana</t>
+          <t>Mteja ameondoka kwenye simu.</t>
         </is>
       </c>
       <c r="I250" s="14" t="inlineStr"/>
@@ -16995,7 +16995,7 @@
     <row r="251" ht="44" customHeight="1">
       <c r="A251" s="11" t="inlineStr">
         <is>
-          <t>no_messages_yet</t>
+          <t>waiting_for_customer</t>
         </is>
       </c>
       <c r="B251" s="11" t="inlineStr">
@@ -17005,32 +17005,32 @@
       </c>
       <c r="C251" s="11" t="inlineStr">
         <is>
-          <t>No messages yet.</t>
+          <t>Waiting for the customer…</t>
         </is>
       </c>
       <c r="D251" s="12" t="inlineStr">
         <is>
-          <t>እስካሁን መልእክት የለም።</t>
+          <t>ደንበኛውን በመጠበቅ ላይ…</t>
         </is>
       </c>
       <c r="E251" s="13" t="inlineStr">
         <is>
-          <t>Ammaaf ergaan hin jiru.</t>
+          <t>Maamilaa eegaa jirra…</t>
         </is>
       </c>
       <c r="F251" s="12" t="inlineStr">
         <is>
-          <t>ክሳብ ሕጂ መልእኽቲ የለን።</t>
+          <t>ነቲ ዓሚል ንጽበ ኣለና…</t>
         </is>
       </c>
       <c r="G251" s="13" t="inlineStr">
         <is>
-          <t>Weli fariimo ma jiraan.</t>
+          <t>Macmiilka la sugayo…</t>
         </is>
       </c>
       <c r="H251" s="13" t="inlineStr">
         <is>
-          <t>Hakuna ujumbe bado.</t>
+          <t>Inasubiri Mteja…</t>
         </is>
       </c>
       <c r="I251" s="14" t="inlineStr"/>
@@ -17038,7 +17038,7 @@
     <row r="252" ht="44" customHeight="1">
       <c r="A252" s="11" t="inlineStr">
         <is>
-          <t>you_label</t>
+          <t>mic_blocked</t>
         </is>
       </c>
       <c r="B252" s="11" t="inlineStr">
@@ -17048,32 +17048,32 @@
       </c>
       <c r="C252" s="11" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Microphone access is blocked. Allow it in your browser and take the session again.</t>
         </is>
       </c>
       <c r="D252" s="12" t="inlineStr">
         <is>
-          <t>እርስዎ</t>
+          <t>የማይክሮፎን መዳረሻ ታግዷል። በአሳሽዎ ውስጥ ይፍቀዱና ክፍለ-ጊዜውን እንደገና ይውሰዱ።</t>
         </is>
       </c>
       <c r="E252" s="13" t="inlineStr">
         <is>
-          <t>Isin</t>
+          <t>Maayikiroofoonii dhorkameera. Biraawzarii keessan keessatti hayyamaatii session irra deebi'aa fudhadhaa.</t>
         </is>
       </c>
       <c r="F252" s="12" t="inlineStr">
         <is>
-          <t>ንስኹም</t>
+          <t>መእተዊ ማይክሮፎን ተዓጊቱ። ኣብ መርበብ መንሸራተቲኹም ፍቐዱ እሞ ነቲ ክፍለ-ግዜ ደጊምኩም ውሰዱ።</t>
         </is>
       </c>
       <c r="G252" s="13" t="inlineStr">
         <is>
-          <t>Adiga</t>
+          <t>Makarafoonka waa la xannibay. Browser-kaaga ka ogolow oo kalfadhiga mar kale qaado.</t>
         </is>
       </c>
       <c r="H252" s="13" t="inlineStr">
         <is>
-          <t>Wewe</t>
+          <t>Ufikiaji wa maikrofoni umezuiwa. Ruhusu kwenye kivinjari chako na uanze kikao tena.</t>
         </is>
       </c>
       <c r="I252" s="14" t="inlineStr"/>
@@ -17081,7 +17081,7 @@
     <row r="253" ht="44" customHeight="1">
       <c r="A253" s="11" t="inlineStr">
         <is>
-          <t>assistant_label</t>
+          <t>unknown_error</t>
         </is>
       </c>
       <c r="B253" s="11" t="inlineStr">
@@ -17091,32 +17091,32 @@
       </c>
       <c r="C253" s="11" t="inlineStr">
         <is>
-          <t>Assistant</t>
+          <t>unknown error</t>
         </is>
       </c>
       <c r="D253" s="12" t="inlineStr">
         <is>
-          <t>ረዳት</t>
+          <t>ያልታወቀ ስህተት</t>
         </is>
       </c>
       <c r="E253" s="13" t="inlineStr">
         <is>
-          <t>Gargaaraa</t>
+          <t>dogoggora hin beekamne</t>
         </is>
       </c>
       <c r="F253" s="12" t="inlineStr">
         <is>
-          <t>ሓጋዚ</t>
+          <t>ዘይተፈልጠ ጌጋ</t>
         </is>
       </c>
       <c r="G253" s="13" t="inlineStr">
         <is>
-          <t>Kaaliye</t>
+          <t>khalad aan la garanayn</t>
         </is>
       </c>
       <c r="H253" s="13" t="inlineStr">
         <is>
-          <t>Msaidizi</t>
+          <t>hitilafu isiyojulikana</t>
         </is>
       </c>
       <c r="I253" s="14" t="inlineStr"/>
@@ -17124,7 +17124,7 @@
     <row r="254" ht="44" customHeight="1">
       <c r="A254" s="11" t="inlineStr">
         <is>
-          <t>conversation_unavailable</t>
+          <t>no_messages_yet</t>
         </is>
       </c>
       <c r="B254" s="11" t="inlineStr">
@@ -17134,32 +17134,32 @@
       </c>
       <c r="C254" s="11" t="inlineStr">
         <is>
-          <t>Conversation unavailable.</t>
+          <t>No messages yet.</t>
         </is>
       </c>
       <c r="D254" s="12" t="inlineStr">
         <is>
-          <t>ውይይቱ አይገኝም።</t>
+          <t>እስካሁን መልእክት የለም።</t>
         </is>
       </c>
       <c r="E254" s="13" t="inlineStr">
         <is>
-          <t>Mariin hin argamu.</t>
+          <t>Ammaaf ergaan hin jiru.</t>
         </is>
       </c>
       <c r="F254" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዝርርብ ኣይርከብን።</t>
+          <t>ክሳብ ሕጂ መልእኽቲ የለን።</t>
         </is>
       </c>
       <c r="G254" s="13" t="inlineStr">
         <is>
-          <t>Wadahadalka lama heli karo.</t>
+          <t>Weli fariimo ma jiraan.</t>
         </is>
       </c>
       <c r="H254" s="13" t="inlineStr">
         <is>
-          <t>Mazungumzo hayapatikani.</t>
+          <t>Hakuna ujumbe bado.</t>
         </is>
       </c>
       <c r="I254" s="14" t="inlineStr"/>
@@ -17167,7 +17167,7 @@
     <row r="255" ht="44" customHeight="1">
       <c r="A255" s="11" t="inlineStr">
         <is>
-          <t>unmute</t>
+          <t>you_label</t>
         </is>
       </c>
       <c r="B255" s="11" t="inlineStr">
@@ -17177,32 +17177,32 @@
       </c>
       <c r="C255" s="11" t="inlineStr">
         <is>
-          <t>Unmute</t>
+          <t>You</t>
         </is>
       </c>
       <c r="D255" s="12" t="inlineStr">
         <is>
-          <t>ድምፅ አብራ</t>
+          <t>እርስዎ</t>
         </is>
       </c>
       <c r="E255" s="13" t="inlineStr">
         <is>
-          <t>Sagalee banaa</t>
+          <t>Isin</t>
         </is>
       </c>
       <c r="F255" s="12" t="inlineStr">
         <is>
-          <t>ድምጺ ኣብርህ</t>
+          <t>ንስኹም</t>
         </is>
       </c>
       <c r="G255" s="13" t="inlineStr">
         <is>
-          <t>Codka fur</t>
+          <t>Adiga</t>
         </is>
       </c>
       <c r="H255" s="13" t="inlineStr">
         <is>
-          <t>Rudisha Sauti</t>
+          <t>Wewe</t>
         </is>
       </c>
       <c r="I255" s="14" t="inlineStr"/>
@@ -17210,7 +17210,7 @@
     <row r="256" ht="44" customHeight="1">
       <c r="A256" s="11" t="inlineStr">
         <is>
-          <t>session_summary_prompt</t>
+          <t>assistant_label</t>
         </is>
       </c>
       <c r="B256" s="11" t="inlineStr">
@@ -17220,32 +17220,32 @@
       </c>
       <c r="C256" s="11" t="inlineStr">
         <is>
-          <t>What did this session cover? (optional)</t>
+          <t>Assistant</t>
         </is>
       </c>
       <c r="D256" s="12" t="inlineStr">
         <is>
-          <t>ይህ ክፍለ-ጊዜ ምን ሸፈነ? (አማራጭ)</t>
+          <t>ረዳት</t>
         </is>
       </c>
       <c r="E256" s="13" t="inlineStr">
         <is>
-          <t>Sessioniin kun maal haguuge? (filannoo)</t>
+          <t>Gargaaraa</t>
         </is>
       </c>
       <c r="F256" s="12" t="inlineStr">
         <is>
-          <t>እዚ ክፍለ-ግዜ እንታይ ሸፈነ? (ኣማራጺ)</t>
+          <t>ሓጋዚ</t>
         </is>
       </c>
       <c r="G256" s="13" t="inlineStr">
         <is>
-          <t>Kalfadhigan muxuu daboolay? (ikhtiyaari)</t>
+          <t>Kaaliye</t>
         </is>
       </c>
       <c r="H256" s="13" t="inlineStr">
         <is>
-          <t>Kikao hiki kilihusu nini? (si lazima)</t>
+          <t>Msaidizi</t>
         </is>
       </c>
       <c r="I256" s="14" t="inlineStr"/>
@@ -17253,7 +17253,7 @@
     <row r="257" ht="44" customHeight="1">
       <c r="A257" s="11" t="inlineStr">
         <is>
-          <t>customer_ended_call</t>
+          <t>conversation_unavailable</t>
         </is>
       </c>
       <c r="B257" s="11" t="inlineStr">
@@ -17263,32 +17263,32 @@
       </c>
       <c r="C257" s="11" t="inlineStr">
         <is>
-          <t>The customer ended the call</t>
+          <t>Conversation unavailable.</t>
         </is>
       </c>
       <c r="D257" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛው ጥሪውን አቋረጠ</t>
+          <t>ውይይቱ አይገኝም።</t>
         </is>
       </c>
       <c r="E257" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan bilbila xumure</t>
+          <t>Mariin hin argamu.</t>
         </is>
       </c>
       <c r="F257" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዓሚል ነቲ ጻውዒት ወዲኡዎ</t>
+          <t>እቲ ዝርርብ ኣይርከብን።</t>
         </is>
       </c>
       <c r="G257" s="13" t="inlineStr">
         <is>
-          <t>Macmiilku wicitaanka wuu joojiyay</t>
+          <t>Wadahadalka lama heli karo.</t>
         </is>
       </c>
       <c r="H257" s="13" t="inlineStr">
         <is>
-          <t>Mteja alimaliza simu</t>
+          <t>Mazungumzo hayapatikani.</t>
         </is>
       </c>
       <c r="I257" s="14" t="inlineStr"/>
@@ -17296,7 +17296,7 @@
     <row r="258" ht="44" customHeight="1">
       <c r="A258" s="11" t="inlineStr">
         <is>
-          <t>verified_scope</t>
+          <t>unmute</t>
         </is>
       </c>
       <c r="B258" s="11" t="inlineStr">
@@ -17306,32 +17306,32 @@
       </c>
       <c r="C258" s="11" t="inlineStr">
         <is>
-          <t>You can now discuss their own records, take documents and file a dispute. Never a deposit, withdrawal or transfer.</t>
+          <t>Unmute</t>
         </is>
       </c>
       <c r="D258" s="12" t="inlineStr">
         <is>
-          <t>አሁን ስለ ራሳቸው መዝገቦች መወያየት፣ ሰነዶች መቀበልና ቅሬታ ማስመዝገብ ይችላሉ። በፍጹም ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም።</t>
+          <t>ድምፅ አብራ</t>
         </is>
       </c>
       <c r="E258" s="13" t="inlineStr">
         <is>
-          <t>Amma waa'ee galmee isaanii mari'achuu, sanadoota fudhachuu fi komii galmeessuu dandeessu. Gonkumaa kuusaa, baasii yookiin dabarsa hin jiru.</t>
+          <t>Sagalee banaa</t>
         </is>
       </c>
       <c r="F258" s="12" t="inlineStr">
         <is>
-          <t>ሕጂ ብዛዕባ ናቶም መዝገባት ክትዘራረቡ፣ ሰነዳት ክትቅበሉን ጥርዓን ከተመዝግቡን ትኽእሉ። ፈጺሙ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን።</t>
+          <t>ድምጺ ኣብርህ</t>
         </is>
       </c>
       <c r="G258" s="13" t="inlineStr">
         <is>
-          <t>Hadda waad kala hadli kartaa diiwaankooda, dukumiinti qaadan iyo cabasho diiwaangelin. Weligaa dhigasho, qaadis ama wareejin ma jirto.</t>
+          <t>Codka fur</t>
         </is>
       </c>
       <c r="H258" s="13" t="inlineStr">
         <is>
-          <t>Sasa unaweza kuzungumzia rekodi zao wenyewe, kuchukua nyaraka na kuwasilisha mgogoro. Kamwe amana, uondoaji au uhamishaji.</t>
+          <t>Rudisha Sauti</t>
         </is>
       </c>
       <c r="I258" s="14" t="inlineStr"/>
@@ -17339,7 +17339,7 @@
     <row r="259" ht="44" customHeight="1">
       <c r="A259" s="11" t="inlineStr">
         <is>
-          <t>establish_who_they_are</t>
+          <t>session_summary_prompt</t>
         </is>
       </c>
       <c r="B259" s="11" t="inlineStr">
@@ -17349,32 +17349,32 @@
       </c>
       <c r="C259" s="11" t="inlineStr">
         <is>
-          <t>Establish who they are — either one</t>
+          <t>What did this session cover? (optional)</t>
         </is>
       </c>
       <c r="D259" s="12" t="inlineStr">
         <is>
-          <t>ማንነታቸውን ያረጋግጡ — አንዱ ይበቃል</t>
+          <t>ይህ ክፍለ-ጊዜ ምን ሸፈነ? (አማራጭ)</t>
         </is>
       </c>
       <c r="E259" s="13" t="inlineStr">
         <is>
-          <t>Eenyummaa isaanii mirkaneessaa — tokko ni ga'a</t>
+          <t>Sessioniin kun maal haguuge? (filannoo)</t>
         </is>
       </c>
       <c r="F259" s="12" t="inlineStr">
         <is>
-          <t>መንነቶም ኣረጋግጹ — ሓደ እኹል እዩ</t>
+          <t>እዚ ክፍለ-ግዜ እንታይ ሸፈነ? (ኣማራጺ)</t>
         </is>
       </c>
       <c r="G259" s="13" t="inlineStr">
         <is>
-          <t>Ogow cidda ay yihiin — mid kasta</t>
+          <t>Kalfadhigan muxuu daboolay? (ikhtiyaari)</t>
         </is>
       </c>
       <c r="H259" s="13" t="inlineStr">
         <is>
-          <t>Thibitisha ni nani — mojawapo</t>
+          <t>Kikao hiki kilihusu nini? (si lazima)</t>
         </is>
       </c>
       <c r="I259" s="14" t="inlineStr"/>
@@ -17382,7 +17382,7 @@
     <row r="260" ht="44" customHeight="1">
       <c r="A260" s="11" t="inlineStr">
         <is>
-          <t>chk_id_document</t>
+          <t>customer_ended_call</t>
         </is>
       </c>
       <c r="B260" s="11" t="inlineStr">
@@ -17392,32 +17392,32 @@
       </c>
       <c r="C260" s="11" t="inlineStr">
         <is>
-          <t>Fayda ID shown and matches the account name</t>
+          <t>The customer ended the call</t>
         </is>
       </c>
       <c r="D260" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ መታወቂያ ታይቷል እና ከሂሳቡ ስም ጋር ይዛመዳል</t>
+          <t>ደንበኛው ጥሪውን አቋረጠ</t>
         </is>
       </c>
       <c r="E260" s="13" t="inlineStr">
         <is>
-          <t>Waraqaan eenyummaa Fayda agarsiifame maqaa herregaa waliin walsimeera</t>
+          <t>Maamilaan bilbila xumure</t>
         </is>
       </c>
       <c r="F260" s="12" t="inlineStr">
         <is>
-          <t>መንነት ፋይዳ ተራእዩን ምስ ስም ሕሳብ ይሰማማዕን</t>
+          <t>እቲ ዓሚል ነቲ ጻውዒት ወዲኡዎ</t>
         </is>
       </c>
       <c r="G260" s="13" t="inlineStr">
         <is>
-          <t>Aqoonsiga Fayda waa la tusay wuxuuna la mid yahay magaca xisaabta</t>
+          <t>Macmiilku wicitaanka wuu joojiyay</t>
         </is>
       </c>
       <c r="H260" s="13" t="inlineStr">
         <is>
-          <t>Kitambulisho cha Fayda kimeonyeshwa na kinalingana na jina la akaunti</t>
+          <t>Mteja alimaliza simu</t>
         </is>
       </c>
       <c r="I260" s="14" t="inlineStr"/>
@@ -17425,7 +17425,7 @@
     <row r="261" ht="44" customHeight="1">
       <c r="A261" s="11" t="inlineStr">
         <is>
-          <t>chk_fayda_matched</t>
+          <t>verified_scope</t>
         </is>
       </c>
       <c r="B261" s="11" t="inlineStr">
@@ -17435,32 +17435,32 @@
       </c>
       <c r="C261" s="11" t="inlineStr">
         <is>
-          <t>Fayda number matches the account record</t>
+          <t>You can now discuss their own records, take documents and file a dispute. Never a deposit, withdrawal or transfer.</t>
         </is>
       </c>
       <c r="D261" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ ቁጥር ከሂሳቡ መዝገብ ጋር ይዛመዳል</t>
+          <t>አሁን ስለ ራሳቸው መዝገቦች መወያየት፣ ሰነዶች መቀበልና ቅሬታ ማስመዝገብ ይችላሉ። በፍጹም ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም።</t>
         </is>
       </c>
       <c r="E261" s="13" t="inlineStr">
         <is>
-          <t>Lakkoofsi Fayda galmee herregaa waliin walsimeera</t>
+          <t>Amma waa'ee galmee isaanii mari'achuu, sanadoota fudhachuu fi komii galmeessuu dandeessu. Gonkumaa kuusaa, baasii yookiin dabarsa hin jiru.</t>
         </is>
       </c>
       <c r="F261" s="12" t="inlineStr">
         <is>
-          <t>ቁጽሪ ፋይዳ ምስ መዝገብ ሕሳብ ይሰማማዕ</t>
+          <t>ሕጂ ብዛዕባ ናቶም መዝገባት ክትዘራረቡ፣ ሰነዳት ክትቅበሉን ጥርዓን ከተመዝግቡን ትኽእሉ። ፈጺሙ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን።</t>
         </is>
       </c>
       <c r="G261" s="13" t="inlineStr">
         <is>
-          <t>Lambarka Fayda wuxuu la mid yahay diiwaanka xisaabta</t>
+          <t>Hadda waad kala hadli kartaa diiwaankooda, dukumiinti qaadan iyo cabasho diiwaangelin. Weligaa dhigasho, qaadis ama wareejin ma jirto.</t>
         </is>
       </c>
       <c r="H261" s="13" t="inlineStr">
         <is>
-          <t>Namba ya Fayda inalingana na rekodi ya akaunti</t>
+          <t>Sasa unaweza kuzungumzia rekodi zao wenyewe, kuchukua nyaraka na kuwasilisha mgogoro. Kamwe amana, uondoaji au uhamishaji.</t>
         </is>
       </c>
       <c r="I261" s="14" t="inlineStr"/>
@@ -17468,7 +17468,7 @@
     <row r="262" ht="44" customHeight="1">
       <c r="A262" s="11" t="inlineStr">
         <is>
-          <t>chk_fayda_matched_note</t>
+          <t>establish_who_they_are</t>
         </is>
       </c>
       <c r="B262" s="11" t="inlineStr">
@@ -17478,32 +17478,32 @@
       </c>
       <c r="C262" s="11" t="inlineStr">
         <is>
-          <t>on your own screen — works on an audio call</t>
+          <t>Establish who they are — either one</t>
         </is>
       </c>
       <c r="D262" s="12" t="inlineStr">
         <is>
-          <t>በራስዎ ስክሪን ላይ — በድምፅ ጥሪም ይሠራል</t>
+          <t>ማንነታቸውን ያረጋግጡ — አንዱ ይበቃል</t>
         </is>
       </c>
       <c r="E262" s="13" t="inlineStr">
         <is>
-          <t>iskiriinii keessan irratti — bilbila sagalee irrattis ni hojjeta</t>
+          <t>Eenyummaa isaanii mirkaneessaa — tokko ni ga'a</t>
         </is>
       </c>
       <c r="F262" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ናትኩም መርአዪ — ኣብ ናይ ድምጺ ጻውዒት እውን ይሰርሕ</t>
+          <t>መንነቶም ኣረጋግጹ — ሓደ እኹል እዩ</t>
         </is>
       </c>
       <c r="G262" s="13" t="inlineStr">
         <is>
-          <t>shaashaddaada — wicitaan cod ahna wuu ka shaqeeyaa</t>
+          <t>Ogow cidda ay yihiin — mid kasta</t>
         </is>
       </c>
       <c r="H262" s="13" t="inlineStr">
         <is>
-          <t>kwenye skrini yako mwenyewe — inafanya kazi kwenye simu ya sauti</t>
+          <t>Thibitisha ni nani — mojawapo</t>
         </is>
       </c>
       <c r="I262" s="14" t="inlineStr"/>
@@ -17511,7 +17511,7 @@
     <row r="263" ht="44" customHeight="1">
       <c r="A263" s="11" t="inlineStr">
         <is>
-          <t>chk_id_photo</t>
+          <t>chk_id_document</t>
         </is>
       </c>
       <c r="B263" s="11" t="inlineStr">
@@ -17521,32 +17521,32 @@
       </c>
       <c r="C263" s="11" t="inlineStr">
         <is>
-          <t>Photo on the ID matches the person on the call</t>
+          <t>Fayda ID shown and matches the account name</t>
         </is>
       </c>
       <c r="D263" s="12" t="inlineStr">
         <is>
-          <t>በመታወቂያው ላይ ያለው ፎቶ ከጥሪው ላይ ካለው ሰው ጋር ይዛመዳል</t>
+          <t>የፋይዳ መታወቂያ ታይቷል እና ከሂሳቡ ስም ጋር ይዛመዳል</t>
         </is>
       </c>
       <c r="E263" s="13" t="inlineStr">
         <is>
-          <t>Suuraan waraqaa eenyummaa irra jiru nama bilbila irra jiru waliin walsimeera</t>
+          <t>Waraqaan eenyummaa Fayda agarsiifame maqaa herregaa waliin walsimeera</t>
         </is>
       </c>
       <c r="F263" s="12" t="inlineStr">
         <is>
-          <t>እቲ ኣብ መንነት ዘሎ ስእሊ ምስቲ ኣብ ጻውዒት ዘሎ ሰብ ይሰማማዕ</t>
+          <t>መንነት ፋይዳ ተራእዩን ምስ ስም ሕሳብ ይሰማማዕን</t>
         </is>
       </c>
       <c r="G263" s="13" t="inlineStr">
         <is>
-          <t>Sawirka aqoonsiga wuxuu la mid yahay qofka wicitaanka ku jira</t>
+          <t>Aqoonsiga Fayda waa la tusay wuxuuna la mid yahay magaca xisaabta</t>
         </is>
       </c>
       <c r="H263" s="13" t="inlineStr">
         <is>
-          <t>Picha kwenye kitambulisho inalingana na mtu aliye kwenye simu</t>
+          <t>Kitambulisho cha Fayda kimeonyeshwa na kinalingana na jina la akaunti</t>
         </is>
       </c>
       <c r="I263" s="14" t="inlineStr"/>
@@ -17554,7 +17554,7 @@
     <row r="264" ht="44" customHeight="1">
       <c r="A264" s="11" t="inlineStr">
         <is>
-          <t>chk_video_only</t>
+          <t>chk_fayda_matched</t>
         </is>
       </c>
       <c r="B264" s="11" t="inlineStr">
@@ -17564,32 +17564,32 @@
       </c>
       <c r="C264" s="11" t="inlineStr">
         <is>
-          <t>video only</t>
+          <t>Fayda number matches the account record</t>
         </is>
       </c>
       <c r="D264" s="12" t="inlineStr">
         <is>
-          <t>ቪዲዮ ብቻ</t>
+          <t>የፋይዳ ቁጥር ከሂሳቡ መዝገብ ጋር ይዛመዳል</t>
         </is>
       </c>
       <c r="E264" s="13" t="inlineStr">
         <is>
-          <t>viidiyoo qofa</t>
+          <t>Lakkoofsi Fayda galmee herregaa waliin walsimeera</t>
         </is>
       </c>
       <c r="F264" s="12" t="inlineStr">
         <is>
-          <t>ቪድዮ ጥራይ</t>
+          <t>ቁጽሪ ፋይዳ ምስ መዝገብ ሕሳብ ይሰማማዕ</t>
         </is>
       </c>
       <c r="G264" s="13" t="inlineStr">
         <is>
-          <t>fiidyow oo kaliya</t>
+          <t>Lambarka Fayda wuxuu la mid yahay diiwaanka xisaabta</t>
         </is>
       </c>
       <c r="H264" s="13" t="inlineStr">
         <is>
-          <t>video pekee</t>
+          <t>Namba ya Fayda inalingana na rekodi ya akaunti</t>
         </is>
       </c>
       <c r="I264" s="14" t="inlineStr"/>
@@ -17597,7 +17597,7 @@
     <row r="265" ht="44" customHeight="1">
       <c r="A265" s="11" t="inlineStr">
         <is>
-          <t>confirm_account_theirs</t>
+          <t>chk_fayda_matched_note</t>
         </is>
       </c>
       <c r="B265" s="11" t="inlineStr">
@@ -17607,32 +17607,32 @@
       </c>
       <c r="C265" s="11" t="inlineStr">
         <is>
-          <t>And confirm the account is theirs</t>
+          <t>on your own screen — works on an audio call</t>
         </is>
       </c>
       <c r="D265" s="12" t="inlineStr">
         <is>
-          <t>እና ሂሳቡ የእነሱ መሆኑን ያረጋግጡ</t>
+          <t>በራስዎ ስክሪን ላይ — በድምፅ ጥሪም ይሠራል</t>
         </is>
       </c>
       <c r="E265" s="13" t="inlineStr">
         <is>
-          <t>Akkasumas herregni kan isaanii ta'uu mirkaneessaa</t>
+          <t>iskiriinii keessan irratti — bilbila sagalee irrattis ni hojjeta</t>
         </is>
       </c>
       <c r="F265" s="12" t="inlineStr">
         <is>
-          <t>ከምኡ'ውን እቲ ሕሳብ ናቶም ምዃኑ ኣረጋግጹ</t>
+          <t>ኣብ ናትኩም መርአዪ — ኣብ ናይ ድምጺ ጻውዒት እውን ይሰርሕ</t>
         </is>
       </c>
       <c r="G265" s="13" t="inlineStr">
         <is>
-          <t>Xaqiiji in xisaabtu tahay tooda</t>
+          <t>shaashaddaada — wicitaan cod ahna wuu ka shaqeeyaa</t>
         </is>
       </c>
       <c r="H265" s="13" t="inlineStr">
         <is>
-          <t>Na thibitisha akaunti ni yao</t>
+          <t>kwenye skrini yako mwenyewe — inafanya kazi kwenye simu ya sauti</t>
         </is>
       </c>
       <c r="I265" s="14" t="inlineStr"/>
@@ -17640,7 +17640,7 @@
     <row r="266" ht="44" customHeight="1">
       <c r="A266" s="11" t="inlineStr">
         <is>
-          <t>confirm_identity</t>
+          <t>chk_id_photo</t>
         </is>
       </c>
       <c r="B266" s="11" t="inlineStr">
@@ -17650,32 +17650,32 @@
       </c>
       <c r="C266" s="11" t="inlineStr">
         <is>
-          <t>Confirm identity</t>
+          <t>Photo on the ID matches the person on the call</t>
         </is>
       </c>
       <c r="D266" s="12" t="inlineStr">
         <is>
-          <t>ማንነት አረጋግጥ</t>
+          <t>በመታወቂያው ላይ ያለው ፎቶ ከጥሪው ላይ ካለው ሰው ጋር ይዛመዳል</t>
         </is>
       </c>
       <c r="E266" s="13" t="inlineStr">
         <is>
-          <t>Eenyummaa mirkaneessi</t>
+          <t>Suuraan waraqaa eenyummaa irra jiru nama bilbila irra jiru waliin walsimeera</t>
         </is>
       </c>
       <c r="F266" s="12" t="inlineStr">
         <is>
-          <t>መንነት ኣረጋግጽ</t>
+          <t>እቲ ኣብ መንነት ዘሎ ስእሊ ምስቲ ኣብ ጻውዒት ዘሎ ሰብ ይሰማማዕ</t>
         </is>
       </c>
       <c r="G266" s="13" t="inlineStr">
         <is>
-          <t>Xaqiiji aqoonsiga</t>
+          <t>Sawirka aqoonsiga wuxuu la mid yahay qofka wicitaanka ku jira</t>
         </is>
       </c>
       <c r="H266" s="13" t="inlineStr">
         <is>
-          <t>Thibitisha Utambulisho</t>
+          <t>Picha kwenye kitambulisho inalingana na mtu aliye kwenye simu</t>
         </is>
       </c>
       <c r="I266" s="14" t="inlineStr"/>
@@ -17683,7 +17683,7 @@
     <row r="267" ht="44" customHeight="1">
       <c r="A267" s="11" t="inlineStr">
         <is>
-          <t>unverified_scope</t>
+          <t>chk_video_only</t>
         </is>
       </c>
       <c r="B267" s="11" t="inlineStr">
@@ -17693,32 +17693,32 @@
       </c>
       <c r="C267" s="11" t="inlineStr">
         <is>
-          <t>Until this is done you can only give general guidance — products, eligibility and how to apply.</t>
+          <t>video only</t>
         </is>
       </c>
       <c r="D267" s="12" t="inlineStr">
         <is>
-          <t>ይህ እስኪከናወን ድረስ አጠቃላይ መመሪያ ብቻ መስጠት ይችላሉ — ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል።</t>
+          <t>ቪዲዮ ብቻ</t>
         </is>
       </c>
       <c r="E267" s="13" t="inlineStr">
         <is>
-          <t>Hanga kun raawwatutti qajeelfama waliigalaa qofa kennuu dandeessu — oomishaalee, ulaagaa fi akkaataa itti iyyatan.</t>
+          <t>viidiyoo qofa</t>
         </is>
       </c>
       <c r="F267" s="12" t="inlineStr">
         <is>
-          <t>እዚ ክሳብ ዝፍጸም ሓፈሻዊ መምርሒ ጥራይ ክትህቡ ትኽእሉ — ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን።</t>
+          <t>ቪድዮ ጥራይ</t>
         </is>
       </c>
       <c r="G267" s="13" t="inlineStr">
         <is>
-          <t>Ilaa tan la sameeyo waxaad kaliya bixin kartaa hagaajin guud — alaabta, u-qalmitaanka iyo sida loo codsado.</t>
+          <t>fiidyow oo kaliya</t>
         </is>
       </c>
       <c r="H267" s="13" t="inlineStr">
         <is>
-          <t>Hadi hili litakapofanyika unaweza tu kutoa mwongozo wa jumla — bidhaa, sifa za kustahiki na jinsi ya kuomba.</t>
+          <t>video pekee</t>
         </is>
       </c>
       <c r="I267" s="14" t="inlineStr"/>
@@ -17726,7 +17726,7 @@
     <row r="268" ht="44" customHeight="1">
       <c r="A268" s="11" t="inlineStr">
         <is>
-          <t>fayda_number_required</t>
+          <t>confirm_account_theirs</t>
         </is>
       </c>
       <c r="B268" s="11" t="inlineStr">
@@ -17736,32 +17736,32 @@
       </c>
       <c r="C268" s="11" t="inlineStr">
         <is>
-          <t>Fayda number (required — it is what the record keeps)</t>
+          <t>And confirm the account is theirs</t>
         </is>
       </c>
       <c r="D268" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ ቁጥር (ያስፈልጋል — መዝገቡ የሚይዘው ይህ ነው)</t>
+          <t>እና ሂሳቡ የእነሱ መሆኑን ያረጋግጡ</t>
         </is>
       </c>
       <c r="E268" s="13" t="inlineStr">
         <is>
-          <t>Lakkoofsa Fayda (barbaachisaa — kan galmeen qabatu isa kana)</t>
+          <t>Akkasumas herregni kan isaanii ta'uu mirkaneessaa</t>
         </is>
       </c>
       <c r="F268" s="12" t="inlineStr">
         <is>
-          <t>ቁጽሪ ፋይዳ (የድሊ — እቲ መዝገብ ዝሕዞ እዚ እዩ)</t>
+          <t>ከምኡ'ውን እቲ ሕሳብ ናቶም ምዃኑ ኣረጋግጹ</t>
         </is>
       </c>
       <c r="G268" s="13" t="inlineStr">
         <is>
-          <t>Lambarka Fayda (loo baahan yahay — waa waxa diiwaanku hayo)</t>
+          <t>Xaqiiji in xisaabtu tahay tooda</t>
         </is>
       </c>
       <c r="H268" s="13" t="inlineStr">
         <is>
-          <t>Namba ya Fayda (inahitajika — ndiyo inayowekwa kwenye rekodi)</t>
+          <t>Na thibitisha akaunti ni yao</t>
         </is>
       </c>
       <c r="I268" s="14" t="inlineStr"/>
@@ -17769,7 +17769,7 @@
     <row r="269" ht="44" customHeight="1">
       <c r="A269" s="11" t="inlineStr">
         <is>
-          <t>download_for_translation</t>
+          <t>confirm_identity</t>
         </is>
       </c>
       <c r="B269" s="11" t="inlineStr">
@@ -17779,32 +17779,32 @@
       </c>
       <c r="C269" s="11" t="inlineStr">
         <is>
-          <t>Download for translation</t>
+          <t>Confirm identity</t>
         </is>
       </c>
       <c r="D269" s="12" t="inlineStr">
         <is>
-          <t>ለትርጉም አውርድ</t>
+          <t>ማንነት አረጋግጥ</t>
         </is>
       </c>
       <c r="E269" s="13" t="inlineStr">
         <is>
-          <t>Hiikkaaf buufadhu</t>
+          <t>Eenyummaa mirkaneessi</t>
         </is>
       </c>
       <c r="F269" s="12" t="inlineStr">
         <is>
-          <t>ንትርጉም ኣውርድ</t>
+          <t>መንነት ኣረጋግጽ</t>
         </is>
       </c>
       <c r="G269" s="13" t="inlineStr">
         <is>
-          <t>Soo dejiso turjumaadda</t>
+          <t>Xaqiiji aqoonsiga</t>
         </is>
       </c>
       <c r="H269" s="13" t="inlineStr">
         <is>
-          <t>Pakua kwa Tafsiri</t>
+          <t>Thibitisha Utambulisho</t>
         </is>
       </c>
       <c r="I269" s="14" t="inlineStr"/>
@@ -17812,48 +17812,177 @@
     <row r="270" ht="44" customHeight="1">
       <c r="A270" s="11" t="inlineStr">
         <is>
+          <t>unverified_scope</t>
+        </is>
+      </c>
+      <c r="B270" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C270" s="11" t="inlineStr">
+        <is>
+          <t>Until this is done you can only give general guidance — products, eligibility and how to apply.</t>
+        </is>
+      </c>
+      <c r="D270" s="12" t="inlineStr">
+        <is>
+          <t>ይህ እስኪከናወን ድረስ አጠቃላይ መመሪያ ብቻ መስጠት ይችላሉ — ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል።</t>
+        </is>
+      </c>
+      <c r="E270" s="13" t="inlineStr">
+        <is>
+          <t>Hanga kun raawwatutti qajeelfama waliigalaa qofa kennuu dandeessu — oomishaalee, ulaagaa fi akkaataa itti iyyatan.</t>
+        </is>
+      </c>
+      <c r="F270" s="12" t="inlineStr">
+        <is>
+          <t>እዚ ክሳብ ዝፍጸም ሓፈሻዊ መምርሒ ጥራይ ክትህቡ ትኽእሉ — ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን።</t>
+        </is>
+      </c>
+      <c r="G270" s="13" t="inlineStr">
+        <is>
+          <t>Ilaa tan la sameeyo waxaad kaliya bixin kartaa hagaajin guud — alaabta, u-qalmitaanka iyo sida loo codsado.</t>
+        </is>
+      </c>
+      <c r="H270" s="13" t="inlineStr">
+        <is>
+          <t>Hadi hili litakapofanyika unaweza tu kutoa mwongozo wa jumla — bidhaa, sifa za kustahiki na jinsi ya kuomba.</t>
+        </is>
+      </c>
+      <c r="I270" s="14" t="inlineStr"/>
+    </row>
+    <row r="271" ht="44" customHeight="1">
+      <c r="A271" s="11" t="inlineStr">
+        <is>
+          <t>fayda_number_required</t>
+        </is>
+      </c>
+      <c r="B271" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C271" s="11" t="inlineStr">
+        <is>
+          <t>Fayda number (required — it is what the record keeps)</t>
+        </is>
+      </c>
+      <c r="D271" s="12" t="inlineStr">
+        <is>
+          <t>የፋይዳ ቁጥር (ያስፈልጋል — መዝገቡ የሚይዘው ይህ ነው)</t>
+        </is>
+      </c>
+      <c r="E271" s="13" t="inlineStr">
+        <is>
+          <t>Lakkoofsa Fayda (barbaachisaa — kan galmeen qabatu isa kana)</t>
+        </is>
+      </c>
+      <c r="F271" s="12" t="inlineStr">
+        <is>
+          <t>ቁጽሪ ፋይዳ (የድሊ — እቲ መዝገብ ዝሕዞ እዚ እዩ)</t>
+        </is>
+      </c>
+      <c r="G271" s="13" t="inlineStr">
+        <is>
+          <t>Lambarka Fayda (loo baahan yahay — waa waxa diiwaanku hayo)</t>
+        </is>
+      </c>
+      <c r="H271" s="13" t="inlineStr">
+        <is>
+          <t>Namba ya Fayda (inahitajika — ndiyo inayowekwa kwenye rekodi)</t>
+        </is>
+      </c>
+      <c r="I271" s="14" t="inlineStr"/>
+    </row>
+    <row r="272" ht="44" customHeight="1">
+      <c r="A272" s="11" t="inlineStr">
+        <is>
+          <t>download_for_translation</t>
+        </is>
+      </c>
+      <c r="B272" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C272" s="11" t="inlineStr">
+        <is>
+          <t>Download for translation</t>
+        </is>
+      </c>
+      <c r="D272" s="12" t="inlineStr">
+        <is>
+          <t>ለትርጉም አውርድ</t>
+        </is>
+      </c>
+      <c r="E272" s="13" t="inlineStr">
+        <is>
+          <t>Hiikkaaf buufadhu</t>
+        </is>
+      </c>
+      <c r="F272" s="12" t="inlineStr">
+        <is>
+          <t>ንትርጉም ኣውርድ</t>
+        </is>
+      </c>
+      <c r="G272" s="13" t="inlineStr">
+        <is>
+          <t>Soo dejiso turjumaadda</t>
+        </is>
+      </c>
+      <c r="H272" s="13" t="inlineStr">
+        <is>
+          <t>Pakua kwa Tafsiri</t>
+        </is>
+      </c>
+      <c r="I272" s="14" t="inlineStr"/>
+    </row>
+    <row r="273" ht="44" customHeight="1">
+      <c r="A273" s="11" t="inlineStr">
+        <is>
           <t>nothing_to_download</t>
         </is>
       </c>
-      <c r="B270" s="11" t="inlineStr">
-        <is>
-          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
-        </is>
-      </c>
-      <c r="C270" s="11" t="inlineStr">
+      <c r="B273" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C273" s="11" t="inlineStr">
         <is>
           <t>No approved answers to download yet.</t>
         </is>
       </c>
-      <c r="D270" s="12" t="inlineStr">
+      <c r="D273" s="12" t="inlineStr">
         <is>
           <t>እስካሁን የሚወርድ የተፈቀደ መልስ የለም።</t>
         </is>
       </c>
-      <c r="E270" s="13" t="inlineStr">
+      <c r="E273" s="13" t="inlineStr">
         <is>
           <t>Hanga ammaatti deebiin mirkanaa'e buufamu hin jiru.</t>
         </is>
       </c>
-      <c r="F270" s="12" t="inlineStr">
+      <c r="F273" s="12" t="inlineStr">
         <is>
           <t>ክሳብ ሕጂ ዝወርድ ዝጸደቐ መልሲ የለን።</t>
         </is>
       </c>
-      <c r="G270" s="13" t="inlineStr">
+      <c r="G273" s="13" t="inlineStr">
         <is>
           <t>Weli ma jiraan jawaabo la ansixiyay oo la soo dejiyo.</t>
         </is>
       </c>
-      <c r="H270" s="13" t="inlineStr">
+      <c r="H273" s="13" t="inlineStr">
         <is>
           <t>Hakuna majibu yaliyoidhinishwa ya kupakua bado.</t>
         </is>
       </c>
-      <c r="I270" s="14" t="inlineStr"/>
+      <c r="I273" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I270"/>
+  <autoFilter ref="A1:I273"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/review/Olink_Bank_Assist_language_review.xlsx
+++ b/review/Olink_Bank_Assist_language_review.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1. What the assistant says'!$A$1:$I$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2. What it understands'!$A$1:$E$91</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3. Buttons customers see'!$A$1:$I$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$I$273</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$I$282</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -752,7 +752,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>344 strings in 5 languages</t>
+          <t>353 strings in 5 languages</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I273"/>
+  <dimension ref="A1:I282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -16436,7 +16436,7 @@
     <row r="238" ht="44" customHeight="1">
       <c r="A238" s="11" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>my_desks</t>
         </is>
       </c>
       <c r="B238" s="11" t="inlineStr">
@@ -16446,32 +16446,32 @@
       </c>
       <c r="C238" s="11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>I can handle these desks:</t>
         </is>
       </c>
       <c r="D238" s="12" t="inlineStr">
         <is>
-          <t>በሂደት ላይ</t>
+          <t>እነዚህን ዴስኮች ማስተናገድ እችላለሁ፦</t>
         </is>
       </c>
       <c r="E238" s="13" t="inlineStr">
         <is>
-          <t>Adeemsa irra</t>
+          <t>Deeskiiwwan kanneen keessummeessuu nan danda'a:</t>
         </is>
       </c>
       <c r="F238" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መስርሕ</t>
+          <t>ነዞም ዴስክታት ከተኣናግድ እኽእል፦</t>
         </is>
       </c>
       <c r="G238" s="13" t="inlineStr">
         <is>
-          <t>Socda</t>
+          <t>Waxaan qaban karaa miisaskan:</t>
         </is>
       </c>
       <c r="H238" s="13" t="inlineStr">
         <is>
-          <t>Inaendelea</t>
+          <t>Ninaweza kushughulikia madawati haya:</t>
         </is>
       </c>
       <c r="I238" s="14" t="inlineStr"/>
@@ -16479,7 +16479,7 @@
     <row r="239" ht="44" customHeight="1">
       <c r="A239" s="11" t="inlineStr">
         <is>
-          <t>no_session_in_progress</t>
+          <t>desks_picked_note</t>
         </is>
       </c>
       <c r="B239" s="11" t="inlineStr">
@@ -16489,32 +16489,32 @@
       </c>
       <c r="C239" s="11" t="inlineStr">
         <is>
-          <t>No session in progress.</t>
+          <t>Questions about these desks reach you first. Everything else still reaches you — after a short wait, so nobody is stranded.</t>
         </is>
       </c>
       <c r="D239" s="12" t="inlineStr">
         <is>
-          <t>በሂደት ላይ ያለ ክፍለ-ጊዜ የለም።</t>
+          <t>ስለ እነዚህ ዴስኮች የሚነሱ ጥያቄዎች መጀመሪያ ወደ እርስዎ ይደርሳሉ። ሌላው ሁሉ አሁንም ይደርሳል — ከአጭር ጥበቃ በኋላ፤ ማንም አይቀርም።</t>
         </is>
       </c>
       <c r="E239" s="13" t="inlineStr">
         <is>
-          <t>Sessionii adeemsa irra jiru hin jiru.</t>
+          <t>Gaaffiiwwan waa'ee deeskiiwwan kanaa jalqaba isin bira ga'u. Kaan hundinuu ammas isin bira ga'a — eegumsa gabaabaa booda, namni hafu hin jiru.</t>
         </is>
       </c>
       <c r="F239" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መስርሕ ዘሎ ክፍለ-ግዜ የለን።</t>
+          <t>ብዛዕባ እዞም ዴስክታት ዝለዓሉ ሕቶታት ቅድም ናባኹም ይበጽሑ። ካልእ ኩሉ እውን ይበጽሕ — ድሕሪ ሓጺር ጽበት፣ ዋላ ሓደ ኣይተርፍን።</t>
         </is>
       </c>
       <c r="G239" s="13" t="inlineStr">
         <is>
-          <t>Ma jiro kalfadhi socda.</t>
+          <t>Su'aalaha ku saabsan miisaskan ayaa marka hore kugu soo gaara. Wax kastoo kalena wuu ku soo gaaraa — sug gaaban ka dib, sidaas qofna ma harayo.</t>
         </is>
       </c>
       <c r="H239" s="13" t="inlineStr">
         <is>
-          <t>Hakuna kikao kinachoendelea.</t>
+          <t>Maswali kuhusu madawati haya yanakufikia kwanza. Mengine yote bado yanakufikia — baada ya kusubiri kidogo, ili asibaki mtu bila msaada.</t>
         </is>
       </c>
       <c r="I239" s="14" t="inlineStr"/>
@@ -16522,7 +16522,7 @@
     <row r="240" ht="44" customHeight="1">
       <c r="A240" s="11" t="inlineStr">
         <is>
-          <t>wait_suffix</t>
+          <t>desks_none_note</t>
         </is>
       </c>
       <c r="B240" s="11" t="inlineStr">
@@ -16532,32 +16532,32 @@
       </c>
       <c r="C240" s="11" t="inlineStr">
         <is>
-          <t>wait</t>
+          <t>Nothing selected, so desk topics do not change your queue order.</t>
         </is>
       </c>
       <c r="D240" s="12" t="inlineStr">
         <is>
-          <t>ጥበቃ</t>
+          <t>ምንም አልተመረጠም፤ ስለዚህ የዴስክ ርዕሶች የወረፋዎን ቅደም ተከተል አይለውጡም።</t>
         </is>
       </c>
       <c r="E240" s="13" t="inlineStr">
         <is>
-          <t>eegumsa</t>
+          <t>Wanti filatame hin jiru, kanaafuu mata-dureewwan deeskii tartiiba sarara keessanii hin jijjiiran.</t>
         </is>
       </c>
       <c r="F240" s="12" t="inlineStr">
         <is>
-          <t>ጽበት</t>
+          <t>ዋላ ሓደ ኣይተመርጸን፣ ስለዚ ኣርእስታት ዴስክ ስርዓት ሰልፍኹም ኣይልውጡን።</t>
         </is>
       </c>
       <c r="G240" s="13" t="inlineStr">
         <is>
-          <t>sug</t>
+          <t>Waxba lama dooran, sidaas darteed mowduucyada miisasku ma beddelaan kala horreynta safkaaga.</t>
         </is>
       </c>
       <c r="H240" s="13" t="inlineStr">
         <is>
-          <t>kusubiri</t>
+          <t>Hakuna kilichochaguliwa, kwa hivyo mada za madawati hazibadilishi mpangilio wa foleni yako.</t>
         </is>
       </c>
       <c r="I240" s="14" t="inlineStr"/>
@@ -16565,7 +16565,7 @@
     <row r="241" ht="44" customHeight="1">
       <c r="A241" s="11" t="inlineStr">
         <is>
-          <t>what_session_covers</t>
+          <t>desks_first_note</t>
         </is>
       </c>
       <c r="B241" s="11" t="inlineStr">
@@ -16575,32 +16575,32 @@
       </c>
       <c r="C241" s="11" t="inlineStr">
         <is>
-          <t>What a session covers</t>
+          <t>Your desks first, longest wait within each. Anyone waiting too long moves to the top whatever they ask about.</t>
         </is>
       </c>
       <c r="D241" s="12" t="inlineStr">
         <is>
-          <t>አንድ ክፍለ-ጊዜ ምን ይሸፍናል</t>
+          <t>የእርስዎ ዴስኮች መጀመሪያ፤ በእያንዳንዱ ውስጥ ረጅም የጠበቀው ይቀድማል። ከልክ በላይ የጠበቀ ማንኛውም ሰው ስለ ምንም ይጠይቅ ወደ ላይ ይወጣል።</t>
         </is>
       </c>
       <c r="E241" s="13" t="inlineStr">
         <is>
-          <t>Sessioniin maal haguuga</t>
+          <t>Deeskiiwwan keessan jalqaba, tokkoon tokkoon isaanii keessatti kan yeroo dheeraa eege dursa. Namni baay'ee eege waan kamiyyuu haa gaafatu gara oliitti deema.</t>
         </is>
       </c>
       <c r="F241" s="12" t="inlineStr">
         <is>
-          <t>ሓደ ክፍለ-ግዜ እንታይ ይሽፍን</t>
+          <t>ዴስክታትኩም ቅድም፣ ኣብ ነፍስ ወከፍ እቲ ነዊሕ ዝጸንሐ ይቐድም። ካብ ንቡር ንላዕሊ ዝጸንሐ ዝኾነ ሰብ ብዛዕባ እንታይ ይሓትት ብዘየገድስ ናብ ላዕሊ ይመጽእ።</t>
         </is>
       </c>
       <c r="G241" s="13" t="inlineStr">
         <is>
-          <t>Waxa kalfadhigu daboolo</t>
+          <t>Miisaskaaga marka hore, kii ugu sugay dheeraa mid kasta gudahood. Qof kasta oo aad u sugay ayaa kor u kaca wax kastoo uu weydiinayoba.</t>
         </is>
       </c>
       <c r="H241" s="13" t="inlineStr">
         <is>
-          <t>Kikao Kinajumuisha Nini</t>
+          <t>Madawati yako kwanza, aliyesubiri kwa muda mrefu zaidi ndani ya kila moja. Yeyote anayesubiri kwa muda mrefu sana anapanda juu bila kujali anauliza nini.</t>
         </is>
       </c>
       <c r="I241" s="14" t="inlineStr"/>
@@ -16608,7 +16608,7 @@
     <row r="242" ht="44" customHeight="1">
       <c r="A242" s="11" t="inlineStr">
         <is>
-          <t>session_scope_body</t>
+          <t>routing_first_note</t>
         </is>
       </c>
       <c r="B242" s="11" t="inlineStr">
@@ -16618,32 +16618,32 @@
       </c>
       <c r="C242" s="11" t="inlineStr">
         <is>
-          <t>Before someone is identified: general questions about products, eligibility and how to apply. Once you have checked their Fayda ID against the account and asked something only the account holder could answer: their own application, documents and disputes.</t>
+          <t>Your languages first, your desks within them, longest wait within each. Anyone waiting too long moves to the top.</t>
         </is>
       </c>
       <c r="D242" s="12" t="inlineStr">
         <is>
-          <t>አንድ ሰው ከመለየቱ በፊት፦ ስለ ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል አጠቃላይ ጥያቄዎች። የፋይዳ መታወቂያቸውን ከሂሳቡ ጋር አመሳክረው የሂሳቡ ባለቤት ብቻ ሊመልሰው የሚችለውን ከጠየቁ በኋላ፦ የራሳቸው ማመልከቻ፣ ሰነዶችና ቅሬታዎች።</t>
+          <t>የእርስዎ ቋንቋዎች መጀመሪያ፣ በውስጣቸው የእርስዎ ዴስኮች፣ በእያንዳንዱ ውስጥ ረጅም የጠበቀው ይቀድማል። ከልክ በላይ የጠበቀ ወደ ላይ ይወጣል።</t>
         </is>
       </c>
       <c r="E242" s="13" t="inlineStr">
         <is>
-          <t>Namni tokko utuu hin beekamin dura: gaaffii waliigalaa waa'ee oomishaalee, ulaagaa fi akkaataa itti iyyatan. Erga waraqaa eenyummaa Fayda isaanii herrega waliin madaalchiftanii waan abbaan herregaa qofti deebisuu danda'u gaafattanii booda: iyyannoo, sanadoota fi komii isaanii.</t>
+          <t>Afaanonni keessan jalqaba, isaan keessatti deeskiiwwan keessan, tokkoon tokkoon keessatti kan yeroo dheeraa eege dursa. Namni baay'ee eege gara oliitti deema.</t>
         </is>
       </c>
       <c r="F242" s="12" t="inlineStr">
         <is>
-          <t>ሓደ ሰብ ቅድሚ ምልላዩ፦ ብዛዕባ ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን ሓፈሻዊ ሕቶታት። መንነት ፋይዳኦም ምስ ሕሳብ ኣረጋጊጽኩም እቲ ወናኒ ሕሳብ ጥራይ ክምልሶ ዝኽእል ምስ ሓተትኩም፦ ናቶም ምልክታ፣ ሰነዳትን ጥርዓናትን።</t>
+          <t>ቋንቋታትኩም ቅድም፣ ኣብ ውሽጦም ዴስክታትኩም፣ ኣብ ነፍስ ወከፍ እቲ ነዊሕ ዝጸንሐ ይቐድም። ካብ ንቡር ንላዕሊ ዝጸንሐ ናብ ላዕሊ ይመጽእ።</t>
         </is>
       </c>
       <c r="G242" s="13" t="inlineStr">
         <is>
-          <t>Ka hor inta aan qofka la aqoonsan: su'aalo guud oo ku saabsan alaabta, u-qalmitaanka iyo sida loo codsado. Marka aad hubiso aqoonsigooda Fayda ee xisaabta oo aad weydiiso wax uu kaliya milkiilaha xisaabtu ka jawaabi karo: codsigooda, dukumiintiyada iyo cabashooyinka.</t>
+          <t>Luqadahaaga marka hore, miisaskaaga gudahood, kii ugu sugay dheeraa mid kasta gudahood. Qof aad u sugay ayaa kor u kaca.</t>
         </is>
       </c>
       <c r="H242" s="13" t="inlineStr">
         <is>
-          <t>Kabla mtu hajatambuliwa: maswali ya jumla kuhusu bidhaa, sifa za kustahiki na jinsi ya kuomba. Baada ya kukagua Kitambulisho chao cha Fayda dhidi ya akaunti na kuuliza kitu ambacho mmiliki wa akaunti pekee angeweza kujibu: maombi yao wenyewe, nyaraka na migogoro.</t>
+          <t>Lugha zako kwanza, madawati yako ndani yake, aliyesubiri kwa muda mrefu zaidi ndani ya kila moja. Anayesubiri kwa muda mrefu sana anapanda juu.</t>
         </is>
       </c>
       <c r="I242" s="14" t="inlineStr"/>
@@ -16651,7 +16651,7 @@
     <row r="243" ht="44" customHeight="1">
       <c r="A243" s="11" t="inlineStr">
         <is>
-          <t>never_money_movement</t>
+          <t>not_your_desk</t>
         </is>
       </c>
       <c r="B243" s="11" t="inlineStr">
@@ -16661,32 +16661,32 @@
       </c>
       <c r="C243" s="11" t="inlineStr">
         <is>
-          <t>Never, at any point and for anyone: deposits, withdrawals or transfers. Those do not happen on a call.</t>
+          <t>outside your desks</t>
         </is>
       </c>
       <c r="D243" s="12" t="inlineStr">
         <is>
-          <t>በፍጹም፣ በማንኛውም ጊዜና ለማንም፦ ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም። እነዚያ በጥሪ ላይ አይፈጸሙም።</t>
+          <t>ከእርስዎ ዴስኮች ውጭ</t>
         </is>
       </c>
       <c r="E243" s="13" t="inlineStr">
         <is>
-          <t>Gonkumaa, yeroo kamiyyuu fi eenyuufiyyuu: kuusaa, baasii yookiin dabarsa hin jiru. Isaan sun bilbila irratti hin raawwataman.</t>
+          <t>deeskiiwwan keessanii ala</t>
         </is>
       </c>
       <c r="F243" s="12" t="inlineStr">
         <is>
-          <t>ፈጺሙ፣ ኣብ ዝኾነ እዋንን ንዝኾነ ሰብን፦ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን። እዚኣቶም ኣብ ጻውዒት ኣይፍጸሙን።</t>
+          <t>ካብ ዴስክታትኩም ወጻኢ</t>
         </is>
       </c>
       <c r="G243" s="13" t="inlineStr">
         <is>
-          <t>Weligaa, wakhti kasta iyo qof kasta: dhigasho, qaadis ama wareejin ma jirto. Kuwaas wicitaan laguma sameeyo.</t>
+          <t>ka baxsan miisaskaaga</t>
         </is>
       </c>
       <c r="H243" s="13" t="inlineStr">
         <is>
-          <t>Kamwe, wakati wowote na kwa yeyote: amana, uondoaji au uhamishaji. Hizo hazifanyiki kwenye simu.</t>
+          <t>nje ya madawati yako</t>
         </is>
       </c>
       <c r="I243" s="14" t="inlineStr"/>
@@ -16694,7 +16694,7 @@
     <row r="244" ht="44" customHeight="1">
       <c r="A244" s="11" t="inlineStr">
         <is>
-          <t>open_escalation_queue</t>
+          <t>desks_updated</t>
         </is>
       </c>
       <c r="B244" s="11" t="inlineStr">
@@ -16704,32 +16704,32 @@
       </c>
       <c r="C244" s="11" t="inlineStr">
         <is>
-          <t>Open the escalation queue</t>
+          <t>Desks updated</t>
         </is>
       </c>
       <c r="D244" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ወረፋውን ክፈት</t>
+          <t>ዴስኮች ተዘምነዋል</t>
         </is>
       </c>
       <c r="E244" s="13" t="inlineStr">
         <is>
-          <t>Sararaa dabarsaa banaa</t>
+          <t>Deeskiiwwan haaromfaman</t>
         </is>
       </c>
       <c r="F244" s="12" t="inlineStr">
         <is>
-          <t>ሪጋ ምትሕልላፍ ክፈት</t>
+          <t>ዴስክታት ተሓዲሶም</t>
         </is>
       </c>
       <c r="G244" s="13" t="inlineStr">
         <is>
-          <t>Fur safka gudbinta</t>
+          <t>Miisaska waa la cusbooneysiiyay</t>
         </is>
       </c>
       <c r="H244" s="13" t="inlineStr">
         <is>
-          <t>Fungua Foleni ya Masuala Yaliyoelekezwa</t>
+          <t>Madawati yamesasishwa</t>
         </is>
       </c>
       <c r="I244" s="14" t="inlineStr"/>
@@ -16737,7 +16737,7 @@
     <row r="245" ht="44" customHeight="1">
       <c r="A245" s="11" t="inlineStr">
         <is>
-          <t>open_live_queue</t>
+          <t>coverage</t>
         </is>
       </c>
       <c r="B245" s="11" t="inlineStr">
@@ -16747,32 +16747,32 @@
       </c>
       <c r="C245" s="11" t="inlineStr">
         <is>
-          <t>Open the live call queue</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="D245" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታ የጥሪ ወረፋውን ክፈት</t>
+          <t>ሽፋን</t>
         </is>
       </c>
       <c r="E245" s="13" t="inlineStr">
         <is>
-          <t>Sarara bilbilaa kallattii banaa</t>
+          <t>Haguuggii</t>
         </is>
       </c>
       <c r="F245" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታዊ ናይ ጻውዒት ሰልፊ ክፈት</t>
+          <t>ሽፋን</t>
         </is>
       </c>
       <c r="G245" s="13" t="inlineStr">
         <is>
-          <t>Fur safka wicitaanka tooska ah</t>
+          <t>Daboolid</t>
         </is>
       </c>
       <c r="H245" s="13" t="inlineStr">
         <is>
-          <t>Fungua foleni ya simu za moja kwa moja</t>
+          <t>Uwezo</t>
         </is>
       </c>
       <c r="I245" s="14" t="inlineStr"/>
@@ -16780,7 +16780,7 @@
     <row r="246" ht="44" customHeight="1">
       <c r="A246" s="11" t="inlineStr">
         <is>
-          <t>live_waiting_one</t>
+          <t>coverage_everything</t>
         </is>
       </c>
       <c r="B246" s="11" t="inlineStr">
@@ -16790,32 +16790,32 @@
       </c>
       <c r="C246" s="11" t="inlineStr">
         <is>
-          <t>{n} customer waiting for a live call</t>
+          <t>everything — nothing declared</t>
         </is>
       </c>
       <c r="D246" s="12" t="inlineStr">
         <is>
-          <t>{n} ደንበኛ ቀጥታ ጥሪ በመጠበቅ ላይ ነው</t>
+          <t>ሁሉም — ምንም አልተገለጸም</t>
         </is>
       </c>
       <c r="E246" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan {n} bilbila kallattii eegaa jira</t>
+          <t>hunda — wanti labsame hin jiru</t>
         </is>
       </c>
       <c r="F246" s="12" t="inlineStr">
         <is>
-          <t>{n} ዓሚል ቀጥታዊ ጻውዒት ይጽበ ኣሎ</t>
+          <t>ኩሉ — ዋላ ሓደ ኣይተገልጸን</t>
         </is>
       </c>
       <c r="G246" s="13" t="inlineStr">
         <is>
-          <t>{n} macmiil ayaa sugaya wicitaan toos ah</t>
+          <t>wax walba — waxba lama sheegin</t>
         </is>
       </c>
       <c r="H246" s="13" t="inlineStr">
         <is>
-          <t>Mteja {n} anasubiri simu ya moja kwa moja</t>
+          <t>yote — hakuna kilichotangazwa</t>
         </is>
       </c>
       <c r="I246" s="14" t="inlineStr"/>
@@ -16823,7 +16823,7 @@
     <row r="247" ht="44" customHeight="1">
       <c r="A247" s="11" t="inlineStr">
         <is>
-          <t>live_waiting_many</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="B247" s="11" t="inlineStr">
@@ -16833,32 +16833,32 @@
       </c>
       <c r="C247" s="11" t="inlineStr">
         <is>
-          <t>{n} customers waiting for a live call</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="D247" s="12" t="inlineStr">
         <is>
-          <t>{n} ደንበኞች ቀጥታ ጥሪ በመጠበቅ ላይ ናቸው</t>
+          <t>በሂደት ላይ</t>
         </is>
       </c>
       <c r="E247" s="13" t="inlineStr">
         <is>
-          <t>Maamiltoonni {n} bilbila kallattii eegaa jiru</t>
+          <t>Adeemsa irra</t>
         </is>
       </c>
       <c r="F247" s="12" t="inlineStr">
         <is>
-          <t>{n} ዓማዊል ቀጥታዊ ጻውዒት ይጽበዩ ኣለዉ</t>
+          <t>ኣብ መስርሕ</t>
         </is>
       </c>
       <c r="G247" s="13" t="inlineStr">
         <is>
-          <t>{n} macaamiil ayaa sugaya wicitaan toos ah</t>
+          <t>Socda</t>
         </is>
       </c>
       <c r="H247" s="13" t="inlineStr">
         <is>
-          <t>Wateja {n} wanasubiri simu ya moja kwa moja</t>
+          <t>Inaendelea</t>
         </is>
       </c>
       <c r="I247" s="14" t="inlineStr"/>
@@ -16866,7 +16866,7 @@
     <row r="248" ht="44" customHeight="1">
       <c r="A248" s="11" t="inlineStr">
         <is>
-          <t>switch_dark_light</t>
+          <t>no_session_in_progress</t>
         </is>
       </c>
       <c r="B248" s="11" t="inlineStr">
@@ -16876,32 +16876,32 @@
       </c>
       <c r="C248" s="11" t="inlineStr">
         <is>
-          <t>Switch between dark and light</t>
+          <t>No session in progress.</t>
         </is>
       </c>
       <c r="D248" s="12" t="inlineStr">
         <is>
-          <t>በጨለማና በብርሃን መካከል ቀይር</t>
+          <t>በሂደት ላይ ያለ ክፍለ-ጊዜ የለም።</t>
         </is>
       </c>
       <c r="E248" s="13" t="inlineStr">
         <is>
-          <t>Dukkanaa fi ifa gidduu jijjiiri</t>
+          <t>Sessionii adeemsa irra jiru hin jiru.</t>
         </is>
       </c>
       <c r="F248" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መንጎ ጸላምን ብርሃንን ቀይር</t>
+          <t>ኣብ መስርሕ ዘሎ ክፍለ-ግዜ የለን።</t>
         </is>
       </c>
       <c r="G248" s="13" t="inlineStr">
         <is>
-          <t>U beddel mugdiga iyo iftiinka</t>
+          <t>Ma jiro kalfadhi socda.</t>
         </is>
       </c>
       <c r="H248" s="13" t="inlineStr">
         <is>
-          <t>Badilisha Kati ya Giza na Mwanga</t>
+          <t>Hakuna kikao kinachoendelea.</t>
         </is>
       </c>
       <c r="I248" s="14" t="inlineStr"/>
@@ -16909,7 +16909,7 @@
     <row r="249" ht="44" customHeight="1">
       <c r="A249" s="11" t="inlineStr">
         <is>
-          <t>live_session</t>
+          <t>wait_suffix</t>
         </is>
       </c>
       <c r="B249" s="11" t="inlineStr">
@@ -16919,32 +16919,32 @@
       </c>
       <c r="C249" s="11" t="inlineStr">
         <is>
-          <t>Live session</t>
+          <t>wait</t>
         </is>
       </c>
       <c r="D249" s="12" t="inlineStr">
         <is>
-          <t>የቀጥታ ክፍለ-ጊዜ</t>
+          <t>ጥበቃ</t>
         </is>
       </c>
       <c r="E249" s="13" t="inlineStr">
         <is>
-          <t>Session kallattii</t>
+          <t>eegumsa</t>
         </is>
       </c>
       <c r="F249" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታ ክፍለ-ግዜ</t>
+          <t>ጽበት</t>
         </is>
       </c>
       <c r="G249" s="13" t="inlineStr">
         <is>
-          <t>Kalfadhi toos ah</t>
+          <t>sug</t>
         </is>
       </c>
       <c r="H249" s="13" t="inlineStr">
         <is>
-          <t>Kikao cha Moja kwa Moja</t>
+          <t>kusubiri</t>
         </is>
       </c>
       <c r="I249" s="14" t="inlineStr"/>
@@ -16952,7 +16952,7 @@
     <row r="250" ht="44" customHeight="1">
       <c r="A250" s="11" t="inlineStr">
         <is>
-          <t>customer_left_call</t>
+          <t>what_session_covers</t>
         </is>
       </c>
       <c r="B250" s="11" t="inlineStr">
@@ -16962,32 +16962,32 @@
       </c>
       <c r="C250" s="11" t="inlineStr">
         <is>
-          <t>The customer has left the call.</t>
+          <t>What a session covers</t>
         </is>
       </c>
       <c r="D250" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛው ጥሪውን ለቅቋል።</t>
+          <t>አንድ ክፍለ-ጊዜ ምን ይሸፍናል</t>
         </is>
       </c>
       <c r="E250" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan bilbila irraa ba'eera.</t>
+          <t>Sessioniin maal haguuga</t>
         </is>
       </c>
       <c r="F250" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዓሚል ካብቲ ጻውዒት ወጺኡ።</t>
+          <t>ሓደ ክፍለ-ግዜ እንታይ ይሽፍን</t>
         </is>
       </c>
       <c r="G250" s="13" t="inlineStr">
         <is>
-          <t>Macmiilku wicitaanka wuu ka baxay.</t>
+          <t>Waxa kalfadhigu daboolo</t>
         </is>
       </c>
       <c r="H250" s="13" t="inlineStr">
         <is>
-          <t>Mteja ameondoka kwenye simu.</t>
+          <t>Kikao Kinajumuisha Nini</t>
         </is>
       </c>
       <c r="I250" s="14" t="inlineStr"/>
@@ -16995,7 +16995,7 @@
     <row r="251" ht="44" customHeight="1">
       <c r="A251" s="11" t="inlineStr">
         <is>
-          <t>waiting_for_customer</t>
+          <t>session_scope_body</t>
         </is>
       </c>
       <c r="B251" s="11" t="inlineStr">
@@ -17005,32 +17005,32 @@
       </c>
       <c r="C251" s="11" t="inlineStr">
         <is>
-          <t>Waiting for the customer…</t>
+          <t>Before someone is identified: general questions about products, eligibility and how to apply. Once you have checked their Fayda ID against the account and asked something only the account holder could answer: their own application, documents and disputes.</t>
         </is>
       </c>
       <c r="D251" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛውን በመጠበቅ ላይ…</t>
+          <t>አንድ ሰው ከመለየቱ በፊት፦ ስለ ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል አጠቃላይ ጥያቄዎች። የፋይዳ መታወቂያቸውን ከሂሳቡ ጋር አመሳክረው የሂሳቡ ባለቤት ብቻ ሊመልሰው የሚችለውን ከጠየቁ በኋላ፦ የራሳቸው ማመልከቻ፣ ሰነዶችና ቅሬታዎች።</t>
         </is>
       </c>
       <c r="E251" s="13" t="inlineStr">
         <is>
-          <t>Maamilaa eegaa jirra…</t>
+          <t>Namni tokko utuu hin beekamin dura: gaaffii waliigalaa waa'ee oomishaalee, ulaagaa fi akkaataa itti iyyatan. Erga waraqaa eenyummaa Fayda isaanii herrega waliin madaalchiftanii waan abbaan herregaa qofti deebisuu danda'u gaafattanii booda: iyyannoo, sanadoota fi komii isaanii.</t>
         </is>
       </c>
       <c r="F251" s="12" t="inlineStr">
         <is>
-          <t>ነቲ ዓሚል ንጽበ ኣለና…</t>
+          <t>ሓደ ሰብ ቅድሚ ምልላዩ፦ ብዛዕባ ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን ሓፈሻዊ ሕቶታት። መንነት ፋይዳኦም ምስ ሕሳብ ኣረጋጊጽኩም እቲ ወናኒ ሕሳብ ጥራይ ክምልሶ ዝኽእል ምስ ሓተትኩም፦ ናቶም ምልክታ፣ ሰነዳትን ጥርዓናትን።</t>
         </is>
       </c>
       <c r="G251" s="13" t="inlineStr">
         <is>
-          <t>Macmiilka la sugayo…</t>
+          <t>Ka hor inta aan qofka la aqoonsan: su'aalo guud oo ku saabsan alaabta, u-qalmitaanka iyo sida loo codsado. Marka aad hubiso aqoonsigooda Fayda ee xisaabta oo aad weydiiso wax uu kaliya milkiilaha xisaabtu ka jawaabi karo: codsigooda, dukumiintiyada iyo cabashooyinka.</t>
         </is>
       </c>
       <c r="H251" s="13" t="inlineStr">
         <is>
-          <t>Inasubiri Mteja…</t>
+          <t>Kabla mtu hajatambuliwa: maswali ya jumla kuhusu bidhaa, sifa za kustahiki na jinsi ya kuomba. Baada ya kukagua Kitambulisho chao cha Fayda dhidi ya akaunti na kuuliza kitu ambacho mmiliki wa akaunti pekee angeweza kujibu: maombi yao wenyewe, nyaraka na migogoro.</t>
         </is>
       </c>
       <c r="I251" s="14" t="inlineStr"/>
@@ -17038,7 +17038,7 @@
     <row r="252" ht="44" customHeight="1">
       <c r="A252" s="11" t="inlineStr">
         <is>
-          <t>mic_blocked</t>
+          <t>never_money_movement</t>
         </is>
       </c>
       <c r="B252" s="11" t="inlineStr">
@@ -17048,32 +17048,32 @@
       </c>
       <c r="C252" s="11" t="inlineStr">
         <is>
-          <t>Microphone access is blocked. Allow it in your browser and take the session again.</t>
+          <t>Never, at any point and for anyone: deposits, withdrawals or transfers. Those do not happen on a call.</t>
         </is>
       </c>
       <c r="D252" s="12" t="inlineStr">
         <is>
-          <t>የማይክሮፎን መዳረሻ ታግዷል። በአሳሽዎ ውስጥ ይፍቀዱና ክፍለ-ጊዜውን እንደገና ይውሰዱ።</t>
+          <t>በፍጹም፣ በማንኛውም ጊዜና ለማንም፦ ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም። እነዚያ በጥሪ ላይ አይፈጸሙም።</t>
         </is>
       </c>
       <c r="E252" s="13" t="inlineStr">
         <is>
-          <t>Maayikiroofoonii dhorkameera. Biraawzarii keessan keessatti hayyamaatii session irra deebi'aa fudhadhaa.</t>
+          <t>Gonkumaa, yeroo kamiyyuu fi eenyuufiyyuu: kuusaa, baasii yookiin dabarsa hin jiru. Isaan sun bilbila irratti hin raawwataman.</t>
         </is>
       </c>
       <c r="F252" s="12" t="inlineStr">
         <is>
-          <t>መእተዊ ማይክሮፎን ተዓጊቱ። ኣብ መርበብ መንሸራተቲኹም ፍቐዱ እሞ ነቲ ክፍለ-ግዜ ደጊምኩም ውሰዱ።</t>
+          <t>ፈጺሙ፣ ኣብ ዝኾነ እዋንን ንዝኾነ ሰብን፦ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን። እዚኣቶም ኣብ ጻውዒት ኣይፍጸሙን።</t>
         </is>
       </c>
       <c r="G252" s="13" t="inlineStr">
         <is>
-          <t>Makarafoonka waa la xannibay. Browser-kaaga ka ogolow oo kalfadhiga mar kale qaado.</t>
+          <t>Weligaa, wakhti kasta iyo qof kasta: dhigasho, qaadis ama wareejin ma jirto. Kuwaas wicitaan laguma sameeyo.</t>
         </is>
       </c>
       <c r="H252" s="13" t="inlineStr">
         <is>
-          <t>Ufikiaji wa maikrofoni umezuiwa. Ruhusu kwenye kivinjari chako na uanze kikao tena.</t>
+          <t>Kamwe, wakati wowote na kwa yeyote: amana, uondoaji au uhamishaji. Hizo hazifanyiki kwenye simu.</t>
         </is>
       </c>
       <c r="I252" s="14" t="inlineStr"/>
@@ -17081,7 +17081,7 @@
     <row r="253" ht="44" customHeight="1">
       <c r="A253" s="11" t="inlineStr">
         <is>
-          <t>unknown_error</t>
+          <t>open_escalation_queue</t>
         </is>
       </c>
       <c r="B253" s="11" t="inlineStr">
@@ -17091,32 +17091,32 @@
       </c>
       <c r="C253" s="11" t="inlineStr">
         <is>
-          <t>unknown error</t>
+          <t>Open the escalation queue</t>
         </is>
       </c>
       <c r="D253" s="12" t="inlineStr">
         <is>
-          <t>ያልታወቀ ስህተት</t>
+          <t>የማሸጋገሪያ ወረፋውን ክፈት</t>
         </is>
       </c>
       <c r="E253" s="13" t="inlineStr">
         <is>
-          <t>dogoggora hin beekamne</t>
+          <t>Sararaa dabarsaa banaa</t>
         </is>
       </c>
       <c r="F253" s="12" t="inlineStr">
         <is>
-          <t>ዘይተፈልጠ ጌጋ</t>
+          <t>ሪጋ ምትሕልላፍ ክፈት</t>
         </is>
       </c>
       <c r="G253" s="13" t="inlineStr">
         <is>
-          <t>khalad aan la garanayn</t>
+          <t>Fur safka gudbinta</t>
         </is>
       </c>
       <c r="H253" s="13" t="inlineStr">
         <is>
-          <t>hitilafu isiyojulikana</t>
+          <t>Fungua Foleni ya Masuala Yaliyoelekezwa</t>
         </is>
       </c>
       <c r="I253" s="14" t="inlineStr"/>
@@ -17124,7 +17124,7 @@
     <row r="254" ht="44" customHeight="1">
       <c r="A254" s="11" t="inlineStr">
         <is>
-          <t>no_messages_yet</t>
+          <t>open_live_queue</t>
         </is>
       </c>
       <c r="B254" s="11" t="inlineStr">
@@ -17134,32 +17134,32 @@
       </c>
       <c r="C254" s="11" t="inlineStr">
         <is>
-          <t>No messages yet.</t>
+          <t>Open the live call queue</t>
         </is>
       </c>
       <c r="D254" s="12" t="inlineStr">
         <is>
-          <t>እስካሁን መልእክት የለም።</t>
+          <t>ቀጥታ የጥሪ ወረፋውን ክፈት</t>
         </is>
       </c>
       <c r="E254" s="13" t="inlineStr">
         <is>
-          <t>Ammaaf ergaan hin jiru.</t>
+          <t>Sarara bilbilaa kallattii banaa</t>
         </is>
       </c>
       <c r="F254" s="12" t="inlineStr">
         <is>
-          <t>ክሳብ ሕጂ መልእኽቲ የለን።</t>
+          <t>ቀጥታዊ ናይ ጻውዒት ሰልፊ ክፈት</t>
         </is>
       </c>
       <c r="G254" s="13" t="inlineStr">
         <is>
-          <t>Weli fariimo ma jiraan.</t>
+          <t>Fur safka wicitaanka tooska ah</t>
         </is>
       </c>
       <c r="H254" s="13" t="inlineStr">
         <is>
-          <t>Hakuna ujumbe bado.</t>
+          <t>Fungua foleni ya simu za moja kwa moja</t>
         </is>
       </c>
       <c r="I254" s="14" t="inlineStr"/>
@@ -17167,7 +17167,7 @@
     <row r="255" ht="44" customHeight="1">
       <c r="A255" s="11" t="inlineStr">
         <is>
-          <t>you_label</t>
+          <t>live_waiting_one</t>
         </is>
       </c>
       <c r="B255" s="11" t="inlineStr">
@@ -17177,32 +17177,32 @@
       </c>
       <c r="C255" s="11" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>{n} customer waiting for a live call</t>
         </is>
       </c>
       <c r="D255" s="12" t="inlineStr">
         <is>
-          <t>እርስዎ</t>
+          <t>{n} ደንበኛ ቀጥታ ጥሪ በመጠበቅ ላይ ነው</t>
         </is>
       </c>
       <c r="E255" s="13" t="inlineStr">
         <is>
-          <t>Isin</t>
+          <t>Maamilaan {n} bilbila kallattii eegaa jira</t>
         </is>
       </c>
       <c r="F255" s="12" t="inlineStr">
         <is>
-          <t>ንስኹም</t>
+          <t>{n} ዓሚል ቀጥታዊ ጻውዒት ይጽበ ኣሎ</t>
         </is>
       </c>
       <c r="G255" s="13" t="inlineStr">
         <is>
-          <t>Adiga</t>
+          <t>{n} macmiil ayaa sugaya wicitaan toos ah</t>
         </is>
       </c>
       <c r="H255" s="13" t="inlineStr">
         <is>
-          <t>Wewe</t>
+          <t>Mteja {n} anasubiri simu ya moja kwa moja</t>
         </is>
       </c>
       <c r="I255" s="14" t="inlineStr"/>
@@ -17210,7 +17210,7 @@
     <row r="256" ht="44" customHeight="1">
       <c r="A256" s="11" t="inlineStr">
         <is>
-          <t>assistant_label</t>
+          <t>live_waiting_many</t>
         </is>
       </c>
       <c r="B256" s="11" t="inlineStr">
@@ -17220,32 +17220,32 @@
       </c>
       <c r="C256" s="11" t="inlineStr">
         <is>
-          <t>Assistant</t>
+          <t>{n} customers waiting for a live call</t>
         </is>
       </c>
       <c r="D256" s="12" t="inlineStr">
         <is>
-          <t>ረዳት</t>
+          <t>{n} ደንበኞች ቀጥታ ጥሪ በመጠበቅ ላይ ናቸው</t>
         </is>
       </c>
       <c r="E256" s="13" t="inlineStr">
         <is>
-          <t>Gargaaraa</t>
+          <t>Maamiltoonni {n} bilbila kallattii eegaa jiru</t>
         </is>
       </c>
       <c r="F256" s="12" t="inlineStr">
         <is>
-          <t>ሓጋዚ</t>
+          <t>{n} ዓማዊል ቀጥታዊ ጻውዒት ይጽበዩ ኣለዉ</t>
         </is>
       </c>
       <c r="G256" s="13" t="inlineStr">
         <is>
-          <t>Kaaliye</t>
+          <t>{n} macaamiil ayaa sugaya wicitaan toos ah</t>
         </is>
       </c>
       <c r="H256" s="13" t="inlineStr">
         <is>
-          <t>Msaidizi</t>
+          <t>Wateja {n} wanasubiri simu ya moja kwa moja</t>
         </is>
       </c>
       <c r="I256" s="14" t="inlineStr"/>
@@ -17253,7 +17253,7 @@
     <row r="257" ht="44" customHeight="1">
       <c r="A257" s="11" t="inlineStr">
         <is>
-          <t>conversation_unavailable</t>
+          <t>switch_dark_light</t>
         </is>
       </c>
       <c r="B257" s="11" t="inlineStr">
@@ -17263,32 +17263,32 @@
       </c>
       <c r="C257" s="11" t="inlineStr">
         <is>
-          <t>Conversation unavailable.</t>
+          <t>Switch between dark and light</t>
         </is>
       </c>
       <c r="D257" s="12" t="inlineStr">
         <is>
-          <t>ውይይቱ አይገኝም።</t>
+          <t>በጨለማና በብርሃን መካከል ቀይር</t>
         </is>
       </c>
       <c r="E257" s="13" t="inlineStr">
         <is>
-          <t>Mariin hin argamu.</t>
+          <t>Dukkanaa fi ifa gidduu jijjiiri</t>
         </is>
       </c>
       <c r="F257" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዝርርብ ኣይርከብን።</t>
+          <t>ኣብ መንጎ ጸላምን ብርሃንን ቀይር</t>
         </is>
       </c>
       <c r="G257" s="13" t="inlineStr">
         <is>
-          <t>Wadahadalka lama heli karo.</t>
+          <t>U beddel mugdiga iyo iftiinka</t>
         </is>
       </c>
       <c r="H257" s="13" t="inlineStr">
         <is>
-          <t>Mazungumzo hayapatikani.</t>
+          <t>Badilisha Kati ya Giza na Mwanga</t>
         </is>
       </c>
       <c r="I257" s="14" t="inlineStr"/>
@@ -17296,7 +17296,7 @@
     <row r="258" ht="44" customHeight="1">
       <c r="A258" s="11" t="inlineStr">
         <is>
-          <t>unmute</t>
+          <t>live_session</t>
         </is>
       </c>
       <c r="B258" s="11" t="inlineStr">
@@ -17306,32 +17306,32 @@
       </c>
       <c r="C258" s="11" t="inlineStr">
         <is>
-          <t>Unmute</t>
+          <t>Live session</t>
         </is>
       </c>
       <c r="D258" s="12" t="inlineStr">
         <is>
-          <t>ድምፅ አብራ</t>
+          <t>የቀጥታ ክፍለ-ጊዜ</t>
         </is>
       </c>
       <c r="E258" s="13" t="inlineStr">
         <is>
-          <t>Sagalee banaa</t>
+          <t>Session kallattii</t>
         </is>
       </c>
       <c r="F258" s="12" t="inlineStr">
         <is>
-          <t>ድምጺ ኣብርህ</t>
+          <t>ቀጥታ ክፍለ-ግዜ</t>
         </is>
       </c>
       <c r="G258" s="13" t="inlineStr">
         <is>
-          <t>Codka fur</t>
+          <t>Kalfadhi toos ah</t>
         </is>
       </c>
       <c r="H258" s="13" t="inlineStr">
         <is>
-          <t>Rudisha Sauti</t>
+          <t>Kikao cha Moja kwa Moja</t>
         </is>
       </c>
       <c r="I258" s="14" t="inlineStr"/>
@@ -17339,7 +17339,7 @@
     <row r="259" ht="44" customHeight="1">
       <c r="A259" s="11" t="inlineStr">
         <is>
-          <t>session_summary_prompt</t>
+          <t>customer_left_call</t>
         </is>
       </c>
       <c r="B259" s="11" t="inlineStr">
@@ -17349,32 +17349,32 @@
       </c>
       <c r="C259" s="11" t="inlineStr">
         <is>
-          <t>What did this session cover? (optional)</t>
+          <t>The customer has left the call.</t>
         </is>
       </c>
       <c r="D259" s="12" t="inlineStr">
         <is>
-          <t>ይህ ክፍለ-ጊዜ ምን ሸፈነ? (አማራጭ)</t>
+          <t>ደንበኛው ጥሪውን ለቅቋል።</t>
         </is>
       </c>
       <c r="E259" s="13" t="inlineStr">
         <is>
-          <t>Sessioniin kun maal haguuge? (filannoo)</t>
+          <t>Maamilaan bilbila irraa ba'eera.</t>
         </is>
       </c>
       <c r="F259" s="12" t="inlineStr">
         <is>
-          <t>እዚ ክፍለ-ግዜ እንታይ ሸፈነ? (ኣማራጺ)</t>
+          <t>እቲ ዓሚል ካብቲ ጻውዒት ወጺኡ።</t>
         </is>
       </c>
       <c r="G259" s="13" t="inlineStr">
         <is>
-          <t>Kalfadhigan muxuu daboolay? (ikhtiyaari)</t>
+          <t>Macmiilku wicitaanka wuu ka baxay.</t>
         </is>
       </c>
       <c r="H259" s="13" t="inlineStr">
         <is>
-          <t>Kikao hiki kilihusu nini? (si lazima)</t>
+          <t>Mteja ameondoka kwenye simu.</t>
         </is>
       </c>
       <c r="I259" s="14" t="inlineStr"/>
@@ -17382,7 +17382,7 @@
     <row r="260" ht="44" customHeight="1">
       <c r="A260" s="11" t="inlineStr">
         <is>
-          <t>customer_ended_call</t>
+          <t>waiting_for_customer</t>
         </is>
       </c>
       <c r="B260" s="11" t="inlineStr">
@@ -17392,32 +17392,32 @@
       </c>
       <c r="C260" s="11" t="inlineStr">
         <is>
-          <t>The customer ended the call</t>
+          <t>Waiting for the customer…</t>
         </is>
       </c>
       <c r="D260" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛው ጥሪውን አቋረጠ</t>
+          <t>ደንበኛውን በመጠበቅ ላይ…</t>
         </is>
       </c>
       <c r="E260" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan bilbila xumure</t>
+          <t>Maamilaa eegaa jirra…</t>
         </is>
       </c>
       <c r="F260" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዓሚል ነቲ ጻውዒት ወዲኡዎ</t>
+          <t>ነቲ ዓሚል ንጽበ ኣለና…</t>
         </is>
       </c>
       <c r="G260" s="13" t="inlineStr">
         <is>
-          <t>Macmiilku wicitaanka wuu joojiyay</t>
+          <t>Macmiilka la sugayo…</t>
         </is>
       </c>
       <c r="H260" s="13" t="inlineStr">
         <is>
-          <t>Mteja alimaliza simu</t>
+          <t>Inasubiri Mteja…</t>
         </is>
       </c>
       <c r="I260" s="14" t="inlineStr"/>
@@ -17425,7 +17425,7 @@
     <row r="261" ht="44" customHeight="1">
       <c r="A261" s="11" t="inlineStr">
         <is>
-          <t>verified_scope</t>
+          <t>mic_blocked</t>
         </is>
       </c>
       <c r="B261" s="11" t="inlineStr">
@@ -17435,32 +17435,32 @@
       </c>
       <c r="C261" s="11" t="inlineStr">
         <is>
-          <t>You can now discuss their own records, take documents and file a dispute. Never a deposit, withdrawal or transfer.</t>
+          <t>Microphone access is blocked. Allow it in your browser and take the session again.</t>
         </is>
       </c>
       <c r="D261" s="12" t="inlineStr">
         <is>
-          <t>አሁን ስለ ራሳቸው መዝገቦች መወያየት፣ ሰነዶች መቀበልና ቅሬታ ማስመዝገብ ይችላሉ። በፍጹም ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም።</t>
+          <t>የማይክሮፎን መዳረሻ ታግዷል። በአሳሽዎ ውስጥ ይፍቀዱና ክፍለ-ጊዜውን እንደገና ይውሰዱ።</t>
         </is>
       </c>
       <c r="E261" s="13" t="inlineStr">
         <is>
-          <t>Amma waa'ee galmee isaanii mari'achuu, sanadoota fudhachuu fi komii galmeessuu dandeessu. Gonkumaa kuusaa, baasii yookiin dabarsa hin jiru.</t>
+          <t>Maayikiroofoonii dhorkameera. Biraawzarii keessan keessatti hayyamaatii session irra deebi'aa fudhadhaa.</t>
         </is>
       </c>
       <c r="F261" s="12" t="inlineStr">
         <is>
-          <t>ሕጂ ብዛዕባ ናቶም መዝገባት ክትዘራረቡ፣ ሰነዳት ክትቅበሉን ጥርዓን ከተመዝግቡን ትኽእሉ። ፈጺሙ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን።</t>
+          <t>መእተዊ ማይክሮፎን ተዓጊቱ። ኣብ መርበብ መንሸራተቲኹም ፍቐዱ እሞ ነቲ ክፍለ-ግዜ ደጊምኩም ውሰዱ።</t>
         </is>
       </c>
       <c r="G261" s="13" t="inlineStr">
         <is>
-          <t>Hadda waad kala hadli kartaa diiwaankooda, dukumiinti qaadan iyo cabasho diiwaangelin. Weligaa dhigasho, qaadis ama wareejin ma jirto.</t>
+          <t>Makarafoonka waa la xannibay. Browser-kaaga ka ogolow oo kalfadhiga mar kale qaado.</t>
         </is>
       </c>
       <c r="H261" s="13" t="inlineStr">
         <is>
-          <t>Sasa unaweza kuzungumzia rekodi zao wenyewe, kuchukua nyaraka na kuwasilisha mgogoro. Kamwe amana, uondoaji au uhamishaji.</t>
+          <t>Ufikiaji wa maikrofoni umezuiwa. Ruhusu kwenye kivinjari chako na uanze kikao tena.</t>
         </is>
       </c>
       <c r="I261" s="14" t="inlineStr"/>
@@ -17468,7 +17468,7 @@
     <row r="262" ht="44" customHeight="1">
       <c r="A262" s="11" t="inlineStr">
         <is>
-          <t>establish_who_they_are</t>
+          <t>unknown_error</t>
         </is>
       </c>
       <c r="B262" s="11" t="inlineStr">
@@ -17478,32 +17478,32 @@
       </c>
       <c r="C262" s="11" t="inlineStr">
         <is>
-          <t>Establish who they are — either one</t>
+          <t>unknown error</t>
         </is>
       </c>
       <c r="D262" s="12" t="inlineStr">
         <is>
-          <t>ማንነታቸውን ያረጋግጡ — አንዱ ይበቃል</t>
+          <t>ያልታወቀ ስህተት</t>
         </is>
       </c>
       <c r="E262" s="13" t="inlineStr">
         <is>
-          <t>Eenyummaa isaanii mirkaneessaa — tokko ni ga'a</t>
+          <t>dogoggora hin beekamne</t>
         </is>
       </c>
       <c r="F262" s="12" t="inlineStr">
         <is>
-          <t>መንነቶም ኣረጋግጹ — ሓደ እኹል እዩ</t>
+          <t>ዘይተፈልጠ ጌጋ</t>
         </is>
       </c>
       <c r="G262" s="13" t="inlineStr">
         <is>
-          <t>Ogow cidda ay yihiin — mid kasta</t>
+          <t>khalad aan la garanayn</t>
         </is>
       </c>
       <c r="H262" s="13" t="inlineStr">
         <is>
-          <t>Thibitisha ni nani — mojawapo</t>
+          <t>hitilafu isiyojulikana</t>
         </is>
       </c>
       <c r="I262" s="14" t="inlineStr"/>
@@ -17511,7 +17511,7 @@
     <row r="263" ht="44" customHeight="1">
       <c r="A263" s="11" t="inlineStr">
         <is>
-          <t>chk_id_document</t>
+          <t>no_messages_yet</t>
         </is>
       </c>
       <c r="B263" s="11" t="inlineStr">
@@ -17521,32 +17521,32 @@
       </c>
       <c r="C263" s="11" t="inlineStr">
         <is>
-          <t>Fayda ID shown and matches the account name</t>
+          <t>No messages yet.</t>
         </is>
       </c>
       <c r="D263" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ መታወቂያ ታይቷል እና ከሂሳቡ ስም ጋር ይዛመዳል</t>
+          <t>እስካሁን መልእክት የለም።</t>
         </is>
       </c>
       <c r="E263" s="13" t="inlineStr">
         <is>
-          <t>Waraqaan eenyummaa Fayda agarsiifame maqaa herregaa waliin walsimeera</t>
+          <t>Ammaaf ergaan hin jiru.</t>
         </is>
       </c>
       <c r="F263" s="12" t="inlineStr">
         <is>
-          <t>መንነት ፋይዳ ተራእዩን ምስ ስም ሕሳብ ይሰማማዕን</t>
+          <t>ክሳብ ሕጂ መልእኽቲ የለን።</t>
         </is>
       </c>
       <c r="G263" s="13" t="inlineStr">
         <is>
-          <t>Aqoonsiga Fayda waa la tusay wuxuuna la mid yahay magaca xisaabta</t>
+          <t>Weli fariimo ma jiraan.</t>
         </is>
       </c>
       <c r="H263" s="13" t="inlineStr">
         <is>
-          <t>Kitambulisho cha Fayda kimeonyeshwa na kinalingana na jina la akaunti</t>
+          <t>Hakuna ujumbe bado.</t>
         </is>
       </c>
       <c r="I263" s="14" t="inlineStr"/>
@@ -17554,7 +17554,7 @@
     <row r="264" ht="44" customHeight="1">
       <c r="A264" s="11" t="inlineStr">
         <is>
-          <t>chk_fayda_matched</t>
+          <t>you_label</t>
         </is>
       </c>
       <c r="B264" s="11" t="inlineStr">
@@ -17564,32 +17564,32 @@
       </c>
       <c r="C264" s="11" t="inlineStr">
         <is>
-          <t>Fayda number matches the account record</t>
+          <t>You</t>
         </is>
       </c>
       <c r="D264" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ ቁጥር ከሂሳቡ መዝገብ ጋር ይዛመዳል</t>
+          <t>እርስዎ</t>
         </is>
       </c>
       <c r="E264" s="13" t="inlineStr">
         <is>
-          <t>Lakkoofsi Fayda galmee herregaa waliin walsimeera</t>
+          <t>Isin</t>
         </is>
       </c>
       <c r="F264" s="12" t="inlineStr">
         <is>
-          <t>ቁጽሪ ፋይዳ ምስ መዝገብ ሕሳብ ይሰማማዕ</t>
+          <t>ንስኹም</t>
         </is>
       </c>
       <c r="G264" s="13" t="inlineStr">
         <is>
-          <t>Lambarka Fayda wuxuu la mid yahay diiwaanka xisaabta</t>
+          <t>Adiga</t>
         </is>
       </c>
       <c r="H264" s="13" t="inlineStr">
         <is>
-          <t>Namba ya Fayda inalingana na rekodi ya akaunti</t>
+          <t>Wewe</t>
         </is>
       </c>
       <c r="I264" s="14" t="inlineStr"/>
@@ -17597,7 +17597,7 @@
     <row r="265" ht="44" customHeight="1">
       <c r="A265" s="11" t="inlineStr">
         <is>
-          <t>chk_fayda_matched_note</t>
+          <t>assistant_label</t>
         </is>
       </c>
       <c r="B265" s="11" t="inlineStr">
@@ -17607,32 +17607,32 @@
       </c>
       <c r="C265" s="11" t="inlineStr">
         <is>
-          <t>on your own screen — works on an audio call</t>
+          <t>Assistant</t>
         </is>
       </c>
       <c r="D265" s="12" t="inlineStr">
         <is>
-          <t>በራስዎ ስክሪን ላይ — በድምፅ ጥሪም ይሠራል</t>
+          <t>ረዳት</t>
         </is>
       </c>
       <c r="E265" s="13" t="inlineStr">
         <is>
-          <t>iskiriinii keessan irratti — bilbila sagalee irrattis ni hojjeta</t>
+          <t>Gargaaraa</t>
         </is>
       </c>
       <c r="F265" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ናትኩም መርአዪ — ኣብ ናይ ድምጺ ጻውዒት እውን ይሰርሕ</t>
+          <t>ሓጋዚ</t>
         </is>
       </c>
       <c r="G265" s="13" t="inlineStr">
         <is>
-          <t>shaashaddaada — wicitaan cod ahna wuu ka shaqeeyaa</t>
+          <t>Kaaliye</t>
         </is>
       </c>
       <c r="H265" s="13" t="inlineStr">
         <is>
-          <t>kwenye skrini yako mwenyewe — inafanya kazi kwenye simu ya sauti</t>
+          <t>Msaidizi</t>
         </is>
       </c>
       <c r="I265" s="14" t="inlineStr"/>
@@ -17640,7 +17640,7 @@
     <row r="266" ht="44" customHeight="1">
       <c r="A266" s="11" t="inlineStr">
         <is>
-          <t>chk_id_photo</t>
+          <t>conversation_unavailable</t>
         </is>
       </c>
       <c r="B266" s="11" t="inlineStr">
@@ -17650,32 +17650,32 @@
       </c>
       <c r="C266" s="11" t="inlineStr">
         <is>
-          <t>Photo on the ID matches the person on the call</t>
+          <t>Conversation unavailable.</t>
         </is>
       </c>
       <c r="D266" s="12" t="inlineStr">
         <is>
-          <t>በመታወቂያው ላይ ያለው ፎቶ ከጥሪው ላይ ካለው ሰው ጋር ይዛመዳል</t>
+          <t>ውይይቱ አይገኝም።</t>
         </is>
       </c>
       <c r="E266" s="13" t="inlineStr">
         <is>
-          <t>Suuraan waraqaa eenyummaa irra jiru nama bilbila irra jiru waliin walsimeera</t>
+          <t>Mariin hin argamu.</t>
         </is>
       </c>
       <c r="F266" s="12" t="inlineStr">
         <is>
-          <t>እቲ ኣብ መንነት ዘሎ ስእሊ ምስቲ ኣብ ጻውዒት ዘሎ ሰብ ይሰማማዕ</t>
+          <t>እቲ ዝርርብ ኣይርከብን።</t>
         </is>
       </c>
       <c r="G266" s="13" t="inlineStr">
         <is>
-          <t>Sawirka aqoonsiga wuxuu la mid yahay qofka wicitaanka ku jira</t>
+          <t>Wadahadalka lama heli karo.</t>
         </is>
       </c>
       <c r="H266" s="13" t="inlineStr">
         <is>
-          <t>Picha kwenye kitambulisho inalingana na mtu aliye kwenye simu</t>
+          <t>Mazungumzo hayapatikani.</t>
         </is>
       </c>
       <c r="I266" s="14" t="inlineStr"/>
@@ -17683,7 +17683,7 @@
     <row r="267" ht="44" customHeight="1">
       <c r="A267" s="11" t="inlineStr">
         <is>
-          <t>chk_video_only</t>
+          <t>unmute</t>
         </is>
       </c>
       <c r="B267" s="11" t="inlineStr">
@@ -17693,32 +17693,32 @@
       </c>
       <c r="C267" s="11" t="inlineStr">
         <is>
-          <t>video only</t>
+          <t>Unmute</t>
         </is>
       </c>
       <c r="D267" s="12" t="inlineStr">
         <is>
-          <t>ቪዲዮ ብቻ</t>
+          <t>ድምፅ አብራ</t>
         </is>
       </c>
       <c r="E267" s="13" t="inlineStr">
         <is>
-          <t>viidiyoo qofa</t>
+          <t>Sagalee banaa</t>
         </is>
       </c>
       <c r="F267" s="12" t="inlineStr">
         <is>
-          <t>ቪድዮ ጥራይ</t>
+          <t>ድምጺ ኣብርህ</t>
         </is>
       </c>
       <c r="G267" s="13" t="inlineStr">
         <is>
-          <t>fiidyow oo kaliya</t>
+          <t>Codka fur</t>
         </is>
       </c>
       <c r="H267" s="13" t="inlineStr">
         <is>
-          <t>video pekee</t>
+          <t>Rudisha Sauti</t>
         </is>
       </c>
       <c r="I267" s="14" t="inlineStr"/>
@@ -17726,7 +17726,7 @@
     <row r="268" ht="44" customHeight="1">
       <c r="A268" s="11" t="inlineStr">
         <is>
-          <t>confirm_account_theirs</t>
+          <t>session_summary_prompt</t>
         </is>
       </c>
       <c r="B268" s="11" t="inlineStr">
@@ -17736,32 +17736,32 @@
       </c>
       <c r="C268" s="11" t="inlineStr">
         <is>
-          <t>And confirm the account is theirs</t>
+          <t>What did this session cover? (optional)</t>
         </is>
       </c>
       <c r="D268" s="12" t="inlineStr">
         <is>
-          <t>እና ሂሳቡ የእነሱ መሆኑን ያረጋግጡ</t>
+          <t>ይህ ክፍለ-ጊዜ ምን ሸፈነ? (አማራጭ)</t>
         </is>
       </c>
       <c r="E268" s="13" t="inlineStr">
         <is>
-          <t>Akkasumas herregni kan isaanii ta'uu mirkaneessaa</t>
+          <t>Sessioniin kun maal haguuge? (filannoo)</t>
         </is>
       </c>
       <c r="F268" s="12" t="inlineStr">
         <is>
-          <t>ከምኡ'ውን እቲ ሕሳብ ናቶም ምዃኑ ኣረጋግጹ</t>
+          <t>እዚ ክፍለ-ግዜ እንታይ ሸፈነ? (ኣማራጺ)</t>
         </is>
       </c>
       <c r="G268" s="13" t="inlineStr">
         <is>
-          <t>Xaqiiji in xisaabtu tahay tooda</t>
+          <t>Kalfadhigan muxuu daboolay? (ikhtiyaari)</t>
         </is>
       </c>
       <c r="H268" s="13" t="inlineStr">
         <is>
-          <t>Na thibitisha akaunti ni yao</t>
+          <t>Kikao hiki kilihusu nini? (si lazima)</t>
         </is>
       </c>
       <c r="I268" s="14" t="inlineStr"/>
@@ -17769,7 +17769,7 @@
     <row r="269" ht="44" customHeight="1">
       <c r="A269" s="11" t="inlineStr">
         <is>
-          <t>confirm_identity</t>
+          <t>customer_ended_call</t>
         </is>
       </c>
       <c r="B269" s="11" t="inlineStr">
@@ -17779,32 +17779,32 @@
       </c>
       <c r="C269" s="11" t="inlineStr">
         <is>
-          <t>Confirm identity</t>
+          <t>The customer ended the call</t>
         </is>
       </c>
       <c r="D269" s="12" t="inlineStr">
         <is>
-          <t>ማንነት አረጋግጥ</t>
+          <t>ደንበኛው ጥሪውን አቋረጠ</t>
         </is>
       </c>
       <c r="E269" s="13" t="inlineStr">
         <is>
-          <t>Eenyummaa mirkaneessi</t>
+          <t>Maamilaan bilbila xumure</t>
         </is>
       </c>
       <c r="F269" s="12" t="inlineStr">
         <is>
-          <t>መንነት ኣረጋግጽ</t>
+          <t>እቲ ዓሚል ነቲ ጻውዒት ወዲኡዎ</t>
         </is>
       </c>
       <c r="G269" s="13" t="inlineStr">
         <is>
-          <t>Xaqiiji aqoonsiga</t>
+          <t>Macmiilku wicitaanka wuu joojiyay</t>
         </is>
       </c>
       <c r="H269" s="13" t="inlineStr">
         <is>
-          <t>Thibitisha Utambulisho</t>
+          <t>Mteja alimaliza simu</t>
         </is>
       </c>
       <c r="I269" s="14" t="inlineStr"/>
@@ -17812,7 +17812,7 @@
     <row r="270" ht="44" customHeight="1">
       <c r="A270" s="11" t="inlineStr">
         <is>
-          <t>unverified_scope</t>
+          <t>verified_scope</t>
         </is>
       </c>
       <c r="B270" s="11" t="inlineStr">
@@ -17822,32 +17822,32 @@
       </c>
       <c r="C270" s="11" t="inlineStr">
         <is>
-          <t>Until this is done you can only give general guidance — products, eligibility and how to apply.</t>
+          <t>You can now discuss their own records, take documents and file a dispute. Never a deposit, withdrawal or transfer.</t>
         </is>
       </c>
       <c r="D270" s="12" t="inlineStr">
         <is>
-          <t>ይህ እስኪከናወን ድረስ አጠቃላይ መመሪያ ብቻ መስጠት ይችላሉ — ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል።</t>
+          <t>አሁን ስለ ራሳቸው መዝገቦች መወያየት፣ ሰነዶች መቀበልና ቅሬታ ማስመዝገብ ይችላሉ። በፍጹም ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም።</t>
         </is>
       </c>
       <c r="E270" s="13" t="inlineStr">
         <is>
-          <t>Hanga kun raawwatutti qajeelfama waliigalaa qofa kennuu dandeessu — oomishaalee, ulaagaa fi akkaataa itti iyyatan.</t>
+          <t>Amma waa'ee galmee isaanii mari'achuu, sanadoota fudhachuu fi komii galmeessuu dandeessu. Gonkumaa kuusaa, baasii yookiin dabarsa hin jiru.</t>
         </is>
       </c>
       <c r="F270" s="12" t="inlineStr">
         <is>
-          <t>እዚ ክሳብ ዝፍጸም ሓፈሻዊ መምርሒ ጥራይ ክትህቡ ትኽእሉ — ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን።</t>
+          <t>ሕጂ ብዛዕባ ናቶም መዝገባት ክትዘራረቡ፣ ሰነዳት ክትቅበሉን ጥርዓን ከተመዝግቡን ትኽእሉ። ፈጺሙ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን።</t>
         </is>
       </c>
       <c r="G270" s="13" t="inlineStr">
         <is>
-          <t>Ilaa tan la sameeyo waxaad kaliya bixin kartaa hagaajin guud — alaabta, u-qalmitaanka iyo sida loo codsado.</t>
+          <t>Hadda waad kala hadli kartaa diiwaankooda, dukumiinti qaadan iyo cabasho diiwaangelin. Weligaa dhigasho, qaadis ama wareejin ma jirto.</t>
         </is>
       </c>
       <c r="H270" s="13" t="inlineStr">
         <is>
-          <t>Hadi hili litakapofanyika unaweza tu kutoa mwongozo wa jumla — bidhaa, sifa za kustahiki na jinsi ya kuomba.</t>
+          <t>Sasa unaweza kuzungumzia rekodi zao wenyewe, kuchukua nyaraka na kuwasilisha mgogoro. Kamwe amana, uondoaji au uhamishaji.</t>
         </is>
       </c>
       <c r="I270" s="14" t="inlineStr"/>
@@ -17855,7 +17855,7 @@
     <row r="271" ht="44" customHeight="1">
       <c r="A271" s="11" t="inlineStr">
         <is>
-          <t>fayda_number_required</t>
+          <t>establish_who_they_are</t>
         </is>
       </c>
       <c r="B271" s="11" t="inlineStr">
@@ -17865,32 +17865,32 @@
       </c>
       <c r="C271" s="11" t="inlineStr">
         <is>
-          <t>Fayda number (required — it is what the record keeps)</t>
+          <t>Establish who they are — either one</t>
         </is>
       </c>
       <c r="D271" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ ቁጥር (ያስፈልጋል — መዝገቡ የሚይዘው ይህ ነው)</t>
+          <t>ማንነታቸውን ያረጋግጡ — አንዱ ይበቃል</t>
         </is>
       </c>
       <c r="E271" s="13" t="inlineStr">
         <is>
-          <t>Lakkoofsa Fayda (barbaachisaa — kan galmeen qabatu isa kana)</t>
+          <t>Eenyummaa isaanii mirkaneessaa — tokko ni ga'a</t>
         </is>
       </c>
       <c r="F271" s="12" t="inlineStr">
         <is>
-          <t>ቁጽሪ ፋይዳ (የድሊ — እቲ መዝገብ ዝሕዞ እዚ እዩ)</t>
+          <t>መንነቶም ኣረጋግጹ — ሓደ እኹል እዩ</t>
         </is>
       </c>
       <c r="G271" s="13" t="inlineStr">
         <is>
-          <t>Lambarka Fayda (loo baahan yahay — waa waxa diiwaanku hayo)</t>
+          <t>Ogow cidda ay yihiin — mid kasta</t>
         </is>
       </c>
       <c r="H271" s="13" t="inlineStr">
         <is>
-          <t>Namba ya Fayda (inahitajika — ndiyo inayowekwa kwenye rekodi)</t>
+          <t>Thibitisha ni nani — mojawapo</t>
         </is>
       </c>
       <c r="I271" s="14" t="inlineStr"/>
@@ -17898,7 +17898,7 @@
     <row r="272" ht="44" customHeight="1">
       <c r="A272" s="11" t="inlineStr">
         <is>
-          <t>download_for_translation</t>
+          <t>chk_id_document</t>
         </is>
       </c>
       <c r="B272" s="11" t="inlineStr">
@@ -17908,32 +17908,32 @@
       </c>
       <c r="C272" s="11" t="inlineStr">
         <is>
-          <t>Download for translation</t>
+          <t>Fayda ID shown and matches the account name</t>
         </is>
       </c>
       <c r="D272" s="12" t="inlineStr">
         <is>
-          <t>ለትርጉም አውርድ</t>
+          <t>የፋይዳ መታወቂያ ታይቷል እና ከሂሳቡ ስም ጋር ይዛመዳል</t>
         </is>
       </c>
       <c r="E272" s="13" t="inlineStr">
         <is>
-          <t>Hiikkaaf buufadhu</t>
+          <t>Waraqaan eenyummaa Fayda agarsiifame maqaa herregaa waliin walsimeera</t>
         </is>
       </c>
       <c r="F272" s="12" t="inlineStr">
         <is>
-          <t>ንትርጉም ኣውርድ</t>
+          <t>መንነት ፋይዳ ተራእዩን ምስ ስም ሕሳብ ይሰማማዕን</t>
         </is>
       </c>
       <c r="G272" s="13" t="inlineStr">
         <is>
-          <t>Soo dejiso turjumaadda</t>
+          <t>Aqoonsiga Fayda waa la tusay wuxuuna la mid yahay magaca xisaabta</t>
         </is>
       </c>
       <c r="H272" s="13" t="inlineStr">
         <is>
-          <t>Pakua kwa Tafsiri</t>
+          <t>Kitambulisho cha Fayda kimeonyeshwa na kinalingana na jina la akaunti</t>
         </is>
       </c>
       <c r="I272" s="14" t="inlineStr"/>
@@ -17941,48 +17941,435 @@
     <row r="273" ht="44" customHeight="1">
       <c r="A273" s="11" t="inlineStr">
         <is>
+          <t>chk_fayda_matched</t>
+        </is>
+      </c>
+      <c r="B273" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C273" s="11" t="inlineStr">
+        <is>
+          <t>Fayda number matches the account record</t>
+        </is>
+      </c>
+      <c r="D273" s="12" t="inlineStr">
+        <is>
+          <t>የፋይዳ ቁጥር ከሂሳቡ መዝገብ ጋር ይዛመዳል</t>
+        </is>
+      </c>
+      <c r="E273" s="13" t="inlineStr">
+        <is>
+          <t>Lakkoofsi Fayda galmee herregaa waliin walsimeera</t>
+        </is>
+      </c>
+      <c r="F273" s="12" t="inlineStr">
+        <is>
+          <t>ቁጽሪ ፋይዳ ምስ መዝገብ ሕሳብ ይሰማማዕ</t>
+        </is>
+      </c>
+      <c r="G273" s="13" t="inlineStr">
+        <is>
+          <t>Lambarka Fayda wuxuu la mid yahay diiwaanka xisaabta</t>
+        </is>
+      </c>
+      <c r="H273" s="13" t="inlineStr">
+        <is>
+          <t>Namba ya Fayda inalingana na rekodi ya akaunti</t>
+        </is>
+      </c>
+      <c r="I273" s="14" t="inlineStr"/>
+    </row>
+    <row r="274" ht="44" customHeight="1">
+      <c r="A274" s="11" t="inlineStr">
+        <is>
+          <t>chk_fayda_matched_note</t>
+        </is>
+      </c>
+      <c r="B274" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C274" s="11" t="inlineStr">
+        <is>
+          <t>on your own screen — works on an audio call</t>
+        </is>
+      </c>
+      <c r="D274" s="12" t="inlineStr">
+        <is>
+          <t>በራስዎ ስክሪን ላይ — በድምፅ ጥሪም ይሠራል</t>
+        </is>
+      </c>
+      <c r="E274" s="13" t="inlineStr">
+        <is>
+          <t>iskiriinii keessan irratti — bilbila sagalee irrattis ni hojjeta</t>
+        </is>
+      </c>
+      <c r="F274" s="12" t="inlineStr">
+        <is>
+          <t>ኣብ ናትኩም መርአዪ — ኣብ ናይ ድምጺ ጻውዒት እውን ይሰርሕ</t>
+        </is>
+      </c>
+      <c r="G274" s="13" t="inlineStr">
+        <is>
+          <t>shaashaddaada — wicitaan cod ahna wuu ka shaqeeyaa</t>
+        </is>
+      </c>
+      <c r="H274" s="13" t="inlineStr">
+        <is>
+          <t>kwenye skrini yako mwenyewe — inafanya kazi kwenye simu ya sauti</t>
+        </is>
+      </c>
+      <c r="I274" s="14" t="inlineStr"/>
+    </row>
+    <row r="275" ht="44" customHeight="1">
+      <c r="A275" s="11" t="inlineStr">
+        <is>
+          <t>chk_id_photo</t>
+        </is>
+      </c>
+      <c r="B275" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C275" s="11" t="inlineStr">
+        <is>
+          <t>Photo on the ID matches the person on the call</t>
+        </is>
+      </c>
+      <c r="D275" s="12" t="inlineStr">
+        <is>
+          <t>በመታወቂያው ላይ ያለው ፎቶ ከጥሪው ላይ ካለው ሰው ጋር ይዛመዳል</t>
+        </is>
+      </c>
+      <c r="E275" s="13" t="inlineStr">
+        <is>
+          <t>Suuraan waraqaa eenyummaa irra jiru nama bilbila irra jiru waliin walsimeera</t>
+        </is>
+      </c>
+      <c r="F275" s="12" t="inlineStr">
+        <is>
+          <t>እቲ ኣብ መንነት ዘሎ ስእሊ ምስቲ ኣብ ጻውዒት ዘሎ ሰብ ይሰማማዕ</t>
+        </is>
+      </c>
+      <c r="G275" s="13" t="inlineStr">
+        <is>
+          <t>Sawirka aqoonsiga wuxuu la mid yahay qofka wicitaanka ku jira</t>
+        </is>
+      </c>
+      <c r="H275" s="13" t="inlineStr">
+        <is>
+          <t>Picha kwenye kitambulisho inalingana na mtu aliye kwenye simu</t>
+        </is>
+      </c>
+      <c r="I275" s="14" t="inlineStr"/>
+    </row>
+    <row r="276" ht="44" customHeight="1">
+      <c r="A276" s="11" t="inlineStr">
+        <is>
+          <t>chk_video_only</t>
+        </is>
+      </c>
+      <c r="B276" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C276" s="11" t="inlineStr">
+        <is>
+          <t>video only</t>
+        </is>
+      </c>
+      <c r="D276" s="12" t="inlineStr">
+        <is>
+          <t>ቪዲዮ ብቻ</t>
+        </is>
+      </c>
+      <c r="E276" s="13" t="inlineStr">
+        <is>
+          <t>viidiyoo qofa</t>
+        </is>
+      </c>
+      <c r="F276" s="12" t="inlineStr">
+        <is>
+          <t>ቪድዮ ጥራይ</t>
+        </is>
+      </c>
+      <c r="G276" s="13" t="inlineStr">
+        <is>
+          <t>fiidyow oo kaliya</t>
+        </is>
+      </c>
+      <c r="H276" s="13" t="inlineStr">
+        <is>
+          <t>video pekee</t>
+        </is>
+      </c>
+      <c r="I276" s="14" t="inlineStr"/>
+    </row>
+    <row r="277" ht="44" customHeight="1">
+      <c r="A277" s="11" t="inlineStr">
+        <is>
+          <t>confirm_account_theirs</t>
+        </is>
+      </c>
+      <c r="B277" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C277" s="11" t="inlineStr">
+        <is>
+          <t>And confirm the account is theirs</t>
+        </is>
+      </c>
+      <c r="D277" s="12" t="inlineStr">
+        <is>
+          <t>እና ሂሳቡ የእነሱ መሆኑን ያረጋግጡ</t>
+        </is>
+      </c>
+      <c r="E277" s="13" t="inlineStr">
+        <is>
+          <t>Akkasumas herregni kan isaanii ta'uu mirkaneessaa</t>
+        </is>
+      </c>
+      <c r="F277" s="12" t="inlineStr">
+        <is>
+          <t>ከምኡ'ውን እቲ ሕሳብ ናቶም ምዃኑ ኣረጋግጹ</t>
+        </is>
+      </c>
+      <c r="G277" s="13" t="inlineStr">
+        <is>
+          <t>Xaqiiji in xisaabtu tahay tooda</t>
+        </is>
+      </c>
+      <c r="H277" s="13" t="inlineStr">
+        <is>
+          <t>Na thibitisha akaunti ni yao</t>
+        </is>
+      </c>
+      <c r="I277" s="14" t="inlineStr"/>
+    </row>
+    <row r="278" ht="44" customHeight="1">
+      <c r="A278" s="11" t="inlineStr">
+        <is>
+          <t>confirm_identity</t>
+        </is>
+      </c>
+      <c r="B278" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C278" s="11" t="inlineStr">
+        <is>
+          <t>Confirm identity</t>
+        </is>
+      </c>
+      <c r="D278" s="12" t="inlineStr">
+        <is>
+          <t>ማንነት አረጋግጥ</t>
+        </is>
+      </c>
+      <c r="E278" s="13" t="inlineStr">
+        <is>
+          <t>Eenyummaa mirkaneessi</t>
+        </is>
+      </c>
+      <c r="F278" s="12" t="inlineStr">
+        <is>
+          <t>መንነት ኣረጋግጽ</t>
+        </is>
+      </c>
+      <c r="G278" s="13" t="inlineStr">
+        <is>
+          <t>Xaqiiji aqoonsiga</t>
+        </is>
+      </c>
+      <c r="H278" s="13" t="inlineStr">
+        <is>
+          <t>Thibitisha Utambulisho</t>
+        </is>
+      </c>
+      <c r="I278" s="14" t="inlineStr"/>
+    </row>
+    <row r="279" ht="44" customHeight="1">
+      <c r="A279" s="11" t="inlineStr">
+        <is>
+          <t>unverified_scope</t>
+        </is>
+      </c>
+      <c r="B279" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C279" s="11" t="inlineStr">
+        <is>
+          <t>Until this is done you can only give general guidance — products, eligibility and how to apply.</t>
+        </is>
+      </c>
+      <c r="D279" s="12" t="inlineStr">
+        <is>
+          <t>ይህ እስኪከናወን ድረስ አጠቃላይ መመሪያ ብቻ መስጠት ይችላሉ — ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል።</t>
+        </is>
+      </c>
+      <c r="E279" s="13" t="inlineStr">
+        <is>
+          <t>Hanga kun raawwatutti qajeelfama waliigalaa qofa kennuu dandeessu — oomishaalee, ulaagaa fi akkaataa itti iyyatan.</t>
+        </is>
+      </c>
+      <c r="F279" s="12" t="inlineStr">
+        <is>
+          <t>እዚ ክሳብ ዝፍጸም ሓፈሻዊ መምርሒ ጥራይ ክትህቡ ትኽእሉ — ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን።</t>
+        </is>
+      </c>
+      <c r="G279" s="13" t="inlineStr">
+        <is>
+          <t>Ilaa tan la sameeyo waxaad kaliya bixin kartaa hagaajin guud — alaabta, u-qalmitaanka iyo sida loo codsado.</t>
+        </is>
+      </c>
+      <c r="H279" s="13" t="inlineStr">
+        <is>
+          <t>Hadi hili litakapofanyika unaweza tu kutoa mwongozo wa jumla — bidhaa, sifa za kustahiki na jinsi ya kuomba.</t>
+        </is>
+      </c>
+      <c r="I279" s="14" t="inlineStr"/>
+    </row>
+    <row r="280" ht="44" customHeight="1">
+      <c r="A280" s="11" t="inlineStr">
+        <is>
+          <t>fayda_number_required</t>
+        </is>
+      </c>
+      <c r="B280" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C280" s="11" t="inlineStr">
+        <is>
+          <t>Fayda number (required — it is what the record keeps)</t>
+        </is>
+      </c>
+      <c r="D280" s="12" t="inlineStr">
+        <is>
+          <t>የፋይዳ ቁጥር (ያስፈልጋል — መዝገቡ የሚይዘው ይህ ነው)</t>
+        </is>
+      </c>
+      <c r="E280" s="13" t="inlineStr">
+        <is>
+          <t>Lakkoofsa Fayda (barbaachisaa — kan galmeen qabatu isa kana)</t>
+        </is>
+      </c>
+      <c r="F280" s="12" t="inlineStr">
+        <is>
+          <t>ቁጽሪ ፋይዳ (የድሊ — እቲ መዝገብ ዝሕዞ እዚ እዩ)</t>
+        </is>
+      </c>
+      <c r="G280" s="13" t="inlineStr">
+        <is>
+          <t>Lambarka Fayda (loo baahan yahay — waa waxa diiwaanku hayo)</t>
+        </is>
+      </c>
+      <c r="H280" s="13" t="inlineStr">
+        <is>
+          <t>Namba ya Fayda (inahitajika — ndiyo inayowekwa kwenye rekodi)</t>
+        </is>
+      </c>
+      <c r="I280" s="14" t="inlineStr"/>
+    </row>
+    <row r="281" ht="44" customHeight="1">
+      <c r="A281" s="11" t="inlineStr">
+        <is>
+          <t>download_for_translation</t>
+        </is>
+      </c>
+      <c r="B281" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C281" s="11" t="inlineStr">
+        <is>
+          <t>Download for translation</t>
+        </is>
+      </c>
+      <c r="D281" s="12" t="inlineStr">
+        <is>
+          <t>ለትርጉም አውርድ</t>
+        </is>
+      </c>
+      <c r="E281" s="13" t="inlineStr">
+        <is>
+          <t>Hiikkaaf buufadhu</t>
+        </is>
+      </c>
+      <c r="F281" s="12" t="inlineStr">
+        <is>
+          <t>ንትርጉም ኣውርድ</t>
+        </is>
+      </c>
+      <c r="G281" s="13" t="inlineStr">
+        <is>
+          <t>Soo dejiso turjumaadda</t>
+        </is>
+      </c>
+      <c r="H281" s="13" t="inlineStr">
+        <is>
+          <t>Pakua kwa Tafsiri</t>
+        </is>
+      </c>
+      <c r="I281" s="14" t="inlineStr"/>
+    </row>
+    <row r="282" ht="44" customHeight="1">
+      <c r="A282" s="11" t="inlineStr">
+        <is>
           <t>nothing_to_download</t>
         </is>
       </c>
-      <c r="B273" s="11" t="inlineStr">
-        <is>
-          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
-        </is>
-      </c>
-      <c r="C273" s="11" t="inlineStr">
+      <c r="B282" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C282" s="11" t="inlineStr">
         <is>
           <t>No approved answers to download yet.</t>
         </is>
       </c>
-      <c r="D273" s="12" t="inlineStr">
+      <c r="D282" s="12" t="inlineStr">
         <is>
           <t>እስካሁን የሚወርድ የተፈቀደ መልስ የለም።</t>
         </is>
       </c>
-      <c r="E273" s="13" t="inlineStr">
+      <c r="E282" s="13" t="inlineStr">
         <is>
           <t>Hanga ammaatti deebiin mirkanaa'e buufamu hin jiru.</t>
         </is>
       </c>
-      <c r="F273" s="12" t="inlineStr">
+      <c r="F282" s="12" t="inlineStr">
         <is>
           <t>ክሳብ ሕጂ ዝወርድ ዝጸደቐ መልሲ የለን።</t>
         </is>
       </c>
-      <c r="G273" s="13" t="inlineStr">
+      <c r="G282" s="13" t="inlineStr">
         <is>
           <t>Weli ma jiraan jawaabo la ansixiyay oo la soo dejiyo.</t>
         </is>
       </c>
-      <c r="H273" s="13" t="inlineStr">
+      <c r="H282" s="13" t="inlineStr">
         <is>
           <t>Hakuna majibu yaliyoidhinishwa ya kupakua bado.</t>
         </is>
       </c>
-      <c r="I273" s="14" t="inlineStr"/>
+      <c r="I282" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I273"/>
+  <autoFilter ref="A1:I282"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/review/Olink_Bank_Assist_language_review.xlsx
+++ b/review/Olink_Bank_Assist_language_review.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1. What the assistant says'!$A$1:$I$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2. What it understands'!$A$1:$E$91</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3. Buttons customers see'!$A$1:$I$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$I$297</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$I$298</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -752,7 +752,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>368 strings in 5 languages</t>
+          <t>369 strings in 5 languages</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I297"/>
+  <dimension ref="A1:I298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -10975,7 +10975,7 @@
     <row r="111" ht="44" customHeight="1">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>escalation_queue</t>
+          <t>no_days_yet</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
@@ -10985,32 +10985,32 @@
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Escalation queue</t>
+          <t>Nothing in this window yet.</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ወረፋ</t>
+          <t>በዚህ ጊዜ ውስጥ እስካሁን ምንም የለም።</t>
         </is>
       </c>
       <c r="E111" s="13" t="inlineStr">
         <is>
-          <t>Sararaa dabarsaa</t>
+          <t>Yeroo kana keessa hanga ammaatti wanti jiru hin jiru.</t>
         </is>
       </c>
       <c r="F111" s="12" t="inlineStr">
         <is>
-          <t>ሪጋ ምትሕልላፍ</t>
+          <t>ኣብዚ ግዜ ክሳብ ሕጂ ዋላ ሓደ የለን።</t>
         </is>
       </c>
       <c r="G111" s="13" t="inlineStr">
         <is>
-          <t>Safka gudbinta</t>
+          <t>Muddadan weli waxba ma jiraan.</t>
         </is>
       </c>
       <c r="H111" s="13" t="inlineStr">
         <is>
-          <t>Foleni ya Masuala Yaliyoelekezwa</t>
+          <t>Hakuna kitu katika kipindi hiki bado.</t>
         </is>
       </c>
       <c r="I111" s="14" t="inlineStr"/>
@@ -11018,7 +11018,7 @@
     <row r="112" ht="44" customHeight="1">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>open_label</t>
+          <t>escalation_queue</t>
         </is>
       </c>
       <c r="B112" s="11" t="inlineStr">
@@ -11028,32 +11028,32 @@
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Escalation queue</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr">
         <is>
-          <t>ክፍት</t>
+          <t>የማሸጋገሪያ ወረፋ</t>
         </is>
       </c>
       <c r="E112" s="13" t="inlineStr">
         <is>
-          <t>Banaa</t>
+          <t>Sararaa dabarsaa</t>
         </is>
       </c>
       <c r="F112" s="12" t="inlineStr">
         <is>
-          <t>ክፉት</t>
+          <t>ሪጋ ምትሕልላፍ</t>
         </is>
       </c>
       <c r="G112" s="13" t="inlineStr">
         <is>
-          <t>Furan</t>
+          <t>Safka gudbinta</t>
         </is>
       </c>
       <c r="H112" s="13" t="inlineStr">
         <is>
-          <t>Wazi</t>
+          <t>Foleni ya Masuala Yaliyoelekezwa</t>
         </is>
       </c>
       <c r="I112" s="14" t="inlineStr"/>
@@ -11061,7 +11061,7 @@
     <row r="113" ht="44" customHeight="1">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>closed_label</t>
+          <t>open_label</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
@@ -11071,32 +11071,32 @@
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>የተዘጋ</t>
+          <t>ክፍት</t>
         </is>
       </c>
       <c r="E113" s="13" t="inlineStr">
         <is>
-          <t>Cufaa</t>
+          <t>Banaa</t>
         </is>
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
-          <t>ዕጹው</t>
+          <t>ክፉት</t>
         </is>
       </c>
       <c r="G113" s="13" t="inlineStr">
         <is>
-          <t>Xiran</t>
+          <t>Furan</t>
         </is>
       </c>
       <c r="H113" s="13" t="inlineStr">
         <is>
-          <t>Imefungwa</t>
+          <t>Wazi</t>
         </is>
       </c>
       <c r="I113" s="14" t="inlineStr"/>
@@ -11104,7 +11104,7 @@
     <row r="114" ht="44" customHeight="1">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>n_reachable</t>
+          <t>closed_label</t>
         </is>
       </c>
       <c r="B114" s="11" t="inlineStr">
@@ -11114,32 +11114,32 @@
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>{n} reachable</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="D114" s="12" t="inlineStr">
         <is>
-          <t>{n} ሊደረስባቸው የሚችሉ</t>
+          <t>የተዘጋ</t>
         </is>
       </c>
       <c r="E114" s="13" t="inlineStr">
         <is>
-          <t>{n} kan bira gahamu</t>
+          <t>Cufaa</t>
         </is>
       </c>
       <c r="F114" s="12" t="inlineStr">
         <is>
-          <t>{n} ክብጻሕዎም ዝኽእሉ</t>
+          <t>ዕጹው</t>
         </is>
       </c>
       <c r="G114" s="13" t="inlineStr">
         <is>
-          <t>{n} la gaari karo</t>
+          <t>Xiran</t>
         </is>
       </c>
       <c r="H114" s="13" t="inlineStr">
         <is>
-          <t>{n} wanapatikana</t>
+          <t>Imefungwa</t>
         </is>
       </c>
       <c r="I114" s="14" t="inlineStr"/>
@@ -11147,7 +11147,7 @@
     <row r="115" ht="44" customHeight="1">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>n_no_contact</t>
+          <t>n_reachable</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
@@ -11157,32 +11157,32 @@
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>{n} with no contact details</t>
+          <t>{n} reachable</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>{n} የመገናኛ መረጃ የሌላቸው</t>
+          <t>{n} ሊደረስባቸው የሚችሉ</t>
         </is>
       </c>
       <c r="E115" s="13" t="inlineStr">
         <is>
-          <t>{n} odeeffannoo quunnamtii hin qabne</t>
+          <t>{n} kan bira gahamu</t>
         </is>
       </c>
       <c r="F115" s="12" t="inlineStr">
         <is>
-          <t>{n} ሓበሬታ መራኸቢ ዘይብሎም</t>
+          <t>{n} ክብጻሕዎም ዝኽእሉ</t>
         </is>
       </c>
       <c r="G115" s="13" t="inlineStr">
         <is>
-          <t>{n} aan lahayn xogta xiriirka</t>
+          <t>{n} la gaari karo</t>
         </is>
       </c>
       <c r="H115" s="13" t="inlineStr">
         <is>
-          <t>{n} hawana taarifa za mawasiliano</t>
+          <t>{n} wanapatikana</t>
         </is>
       </c>
       <c r="I115" s="14" t="inlineStr"/>
@@ -11190,7 +11190,7 @@
     <row r="116" ht="44" customHeight="1">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>what_happened</t>
+          <t>n_no_contact</t>
         </is>
       </c>
       <c r="B116" s="11" t="inlineStr">
@@ -11200,32 +11200,32 @@
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>What happened to each question</t>
+          <t>{n} with no contact details</t>
         </is>
       </c>
       <c r="D116" s="12" t="inlineStr">
         <is>
-          <t>ለእያንዳንዱ ጥያቄ ምን ተፈጠረ</t>
+          <t>{n} የመገናኛ መረጃ የሌላቸው</t>
         </is>
       </c>
       <c r="E116" s="13" t="inlineStr">
         <is>
-          <t>Gaaffii tokkoon tokkoon isaanii maaltu isaan mudate</t>
+          <t>{n} odeeffannoo quunnamtii hin qabne</t>
         </is>
       </c>
       <c r="F116" s="12" t="inlineStr">
         <is>
-          <t>ንነፍስ ወከፍ ሕቶ እንታይ ኮነ</t>
+          <t>{n} ሓበሬታ መራኸቢ ዘይብሎም</t>
         </is>
       </c>
       <c r="G116" s="13" t="inlineStr">
         <is>
-          <t>Maxaa ku dhacay su'aal kasta</t>
+          <t>{n} aan lahayn xogta xiriirka</t>
         </is>
       </c>
       <c r="H116" s="13" t="inlineStr">
         <is>
-          <t>Kilichotokea kwa kila swali</t>
+          <t>{n} hawana taarifa za mawasiliano</t>
         </is>
       </c>
       <c r="I116" s="14" t="inlineStr"/>
@@ -11233,7 +11233,7 @@
     <row r="117" ht="44" customHeight="1">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>also_recorded</t>
+          <t>what_happened</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
@@ -11243,32 +11243,32 @@
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Also recorded: {items}</t>
+          <t>What happened to each question</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>እንዲሁም ተመዝግቧል፦ {items}</t>
+          <t>ለእያንዳንዱ ጥያቄ ምን ተፈጠረ</t>
         </is>
       </c>
       <c r="E117" s="13" t="inlineStr">
         <is>
-          <t>Akkasumas galmaa'e: {items}</t>
+          <t>Gaaffii tokkoon tokkoon isaanii maaltu isaan mudate</t>
         </is>
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
-          <t>ከምኡ'ውን ተመዝጊቡ፦ {items}</t>
+          <t>ንነፍስ ወከፍ ሕቶ እንታይ ኮነ</t>
         </is>
       </c>
       <c r="G117" s="13" t="inlineStr">
         <is>
-          <t>Sidoo kale waa la diiwaangeliyay: {items}</t>
+          <t>Maxaa ku dhacay su'aal kasta</t>
         </is>
       </c>
       <c r="H117" s="13" t="inlineStr">
         <is>
-          <t>Pia imerekodiwa: {items}</t>
+          <t>Kilichotokea kwa kila swali</t>
         </is>
       </c>
       <c r="I117" s="14" t="inlineStr"/>
@@ -11276,7 +11276,7 @@
     <row r="118" ht="44" customHeight="1">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>unclassified_note</t>
+          <t>also_recorded</t>
         </is>
       </c>
       <c r="B118" s="11" t="inlineStr">
@@ -11286,32 +11286,32 @@
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>{n} earlier replies carry no outcome and are not counted above.</t>
+          <t>Also recorded: {items}</t>
         </is>
       </c>
       <c r="D118" s="12" t="inlineStr">
         <is>
-          <t>{n} ቀደም ያሉ መልሶች ውጤት የላቸውም፤ ከላይ አልተቆጠሩም።</t>
+          <t>እንዲሁም ተመዝግቧል፦ {items}</t>
         </is>
       </c>
       <c r="E118" s="13" t="inlineStr">
         <is>
-          <t>Deebiiwwan {n} kanneen duraa bu'aa hin qaban, olitti hin lakkaa'amne.</t>
+          <t>Akkasumas galmaa'e: {items}</t>
         </is>
       </c>
       <c r="F118" s="12" t="inlineStr">
         <is>
-          <t>{n} ናይ ቅድሚ ሕጂ መልስታት ውጽኢት የብሎምን፣ ኣብ ላዕሊ ኣይተቖጽሩን።</t>
+          <t>ከምኡ'ውን ተመዝጊቡ፦ {items}</t>
         </is>
       </c>
       <c r="G118" s="13" t="inlineStr">
         <is>
-          <t>{n} jawaabihii hore natiijo ma laha, korna laguma tirin.</t>
+          <t>Sidoo kale waa la diiwaangeliyay: {items}</t>
         </is>
       </c>
       <c r="H118" s="13" t="inlineStr">
         <is>
-          <t>Majibu {n} ya awali hayana matokeo yaliyoainishwa na hayajahesabiwa hapo juu.</t>
+          <t>Pia imerekodiwa: {items}</t>
         </is>
       </c>
       <c r="I118" s="14" t="inlineStr"/>
@@ -11319,7 +11319,7 @@
     <row r="119" ht="44" customHeight="1">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>most_asked</t>
+          <t>unclassified_note</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
@@ -11329,32 +11329,32 @@
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Most asked</t>
+          <t>{n} earlier replies carry no outcome and are not counted above.</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>በብዛት የተጠየቁ</t>
+          <t>{n} ቀደም ያሉ መልሶች ውጤት የላቸውም፤ ከላይ አልተቆጠሩም።</t>
         </is>
       </c>
       <c r="E119" s="13" t="inlineStr">
         <is>
-          <t>Kan baay'inaan gaafataman</t>
+          <t>Deebiiwwan {n} kanneen duraa bu'aa hin qaban, olitti hin lakkaa'amne.</t>
         </is>
       </c>
       <c r="F119" s="12" t="inlineStr">
         <is>
-          <t>ብብዝሒ ዝተሓተቱ</t>
+          <t>{n} ናይ ቅድሚ ሕጂ መልስታት ውጽኢት የብሎምን፣ ኣብ ላዕሊ ኣይተቖጽሩን።</t>
         </is>
       </c>
       <c r="G119" s="13" t="inlineStr">
         <is>
-          <t>Kuwa ugu badan ee la weydiiyay</t>
+          <t>{n} jawaabihii hore natiijo ma laha, korna laguma tirin.</t>
         </is>
       </c>
       <c r="H119" s="13" t="inlineStr">
         <is>
-          <t>Yanayoulizwa Zaidi</t>
+          <t>Majibu {n} ya awali hayana matokeo yaliyoainishwa na hayajahesabiwa hapo juu.</t>
         </is>
       </c>
       <c r="I119" s="14" t="inlineStr"/>
@@ -11362,7 +11362,7 @@
     <row r="120" ht="44" customHeight="1">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>nothing_asked_yet</t>
+          <t>most_asked</t>
         </is>
       </c>
       <c r="B120" s="11" t="inlineStr">
@@ -11372,32 +11372,32 @@
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>Nothing asked yet in this window.</t>
+          <t>Most asked</t>
         </is>
       </c>
       <c r="D120" s="12" t="inlineStr">
         <is>
-          <t>በዚህ ጊዜ ውስጥ የተጠየቀ የለም።</t>
+          <t>በብዛት የተጠየቁ</t>
         </is>
       </c>
       <c r="E120" s="13" t="inlineStr">
         <is>
-          <t>Yeroo kana keessatti wanti gaafatame hin jiru.</t>
+          <t>Kan baay'inaan gaafataman</t>
         </is>
       </c>
       <c r="F120" s="12" t="inlineStr">
         <is>
-          <t>ኣብዚ እዋን'ዚ ዝተሓተተ የለን።</t>
+          <t>ብብዝሒ ዝተሓተቱ</t>
         </is>
       </c>
       <c r="G120" s="13" t="inlineStr">
         <is>
-          <t>Waqtigan waxba lama weydiin.</t>
+          <t>Kuwa ugu badan ee la weydiiyay</t>
         </is>
       </c>
       <c r="H120" s="13" t="inlineStr">
         <is>
-          <t>Hakuna kilichoulizwa katika muda huu.</t>
+          <t>Yanayoulizwa Zaidi</t>
         </is>
       </c>
       <c r="I120" s="14" t="inlineStr"/>
@@ -11405,7 +11405,7 @@
     <row r="121" ht="44" customHeight="1">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>grouped_by_wording</t>
+          <t>nothing_asked_yet</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Grouped by wording. Phone numbers and names are removed before grouping.</t>
+          <t>Nothing asked yet in this window.</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>በአገላለጽ የተመደበ። ስልክ ቁጥሮችና ስሞች ከመመደቡ በፊት ይወገዳሉ።</t>
+          <t>በዚህ ጊዜ ውስጥ የተጠየቀ የለም።</t>
         </is>
       </c>
       <c r="E121" s="13" t="inlineStr">
         <is>
-          <t>Jechaan kan ramadame. Lakkoofsi bilbilaa fi maqaan osoo hin ramadamin dura ni haqama.</t>
+          <t>Yeroo kana keessatti wanti gaafatame hin jiru.</t>
         </is>
       </c>
       <c r="F121" s="12" t="inlineStr">
         <is>
-          <t>ብኣዘራርባ ዝተጠርነፈ። ቁጽሪ ስልክን ስማትን ቅድሚ ምጥርናፍ ይእለዩ።</t>
+          <t>ኣብዚ እዋን'ዚ ዝተሓተተ የለን።</t>
         </is>
       </c>
       <c r="G121" s="13" t="inlineStr">
         <is>
-          <t>Waxaa loo kala saaray erayada. Lambarrada taleefanka iyo magacyada waa la saaraa ka hor.</t>
+          <t>Waqtigan waxba lama weydiin.</t>
         </is>
       </c>
       <c r="H121" s="13" t="inlineStr">
         <is>
-          <t>Yamepangwa kwa maneno. Namba za simu na majina yameondolewa kabla ya kupanga.</t>
+          <t>Hakuna kilichoulizwa katika muda huu.</t>
         </is>
       </c>
       <c r="I121" s="14" t="inlineStr"/>
@@ -11448,7 +11448,7 @@
     <row r="122" ht="44" customHeight="1">
       <c r="A122" s="11" t="inlineStr">
         <is>
-          <t>what_happened_when_asked</t>
+          <t>grouped_by_wording</t>
         </is>
       </c>
       <c r="B122" s="11" t="inlineStr">
@@ -11458,32 +11458,32 @@
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>What happened when this was asked</t>
+          <t>Grouped by wording. Phone numbers and names are removed before grouping.</t>
         </is>
       </c>
       <c r="D122" s="12" t="inlineStr">
         <is>
-          <t>ይህ ሲጠየቅ ምን ሆነ</t>
+          <t>በአገላለጽ የተመደበ። ስልክ ቁጥሮችና ስሞች ከመመደቡ በፊት ይወገዳሉ።</t>
         </is>
       </c>
       <c r="E122" s="13" t="inlineStr">
         <is>
-          <t>Yeroo kun gaafatametti maaltu ta'e</t>
+          <t>Jechaan kan ramadame. Lakkoofsi bilbilaa fi maqaan osoo hin ramadamin dura ni haqama.</t>
         </is>
       </c>
       <c r="F122" s="12" t="inlineStr">
         <is>
-          <t>እዚ ምስ ተሓተተ እንታይ ኮነ</t>
+          <t>ብኣዘራርባ ዝተጠርነፈ። ቁጽሪ ስልክን ስማትን ቅድሚ ምጥርናፍ ይእለዩ።</t>
         </is>
       </c>
       <c r="G122" s="13" t="inlineStr">
         <is>
-          <t>Maxaa dhacay markii tan la weydiiyay</t>
+          <t>Waxaa loo kala saaray erayada. Lambarrada taleefanka iyo magacyada waa la saaraa ka hor.</t>
         </is>
       </c>
       <c r="H122" s="13" t="inlineStr">
         <is>
-          <t>Kilichotokea liliposwali hili</t>
+          <t>Yamepangwa kwa maneno. Namba za simu na majina yameondolewa kabla ya kupanga.</t>
         </is>
       </c>
       <c r="I122" s="14" t="inlineStr"/>
@@ -11491,7 +11491,7 @@
     <row r="123" ht="44" customHeight="1">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>n_other_questions</t>
+          <t>what_happened_when_asked</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
@@ -11501,32 +11501,32 @@
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>{n} other questions</t>
+          <t>What happened when this was asked</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>{n} ሌሎች ጥያቄዎች</t>
+          <t>ይህ ሲጠየቅ ምን ሆነ</t>
         </is>
       </c>
       <c r="E123" s="13" t="inlineStr">
         <is>
-          <t>Gaaffii {n} biroo</t>
+          <t>Yeroo kun gaafatametti maaltu ta'e</t>
         </is>
       </c>
       <c r="F123" s="12" t="inlineStr">
         <is>
-          <t>{n} ካልኦት ሕቶታት</t>
+          <t>እዚ ምስ ተሓተተ እንታይ ኮነ</t>
         </is>
       </c>
       <c r="G123" s="13" t="inlineStr">
         <is>
-          <t>{n} su'aalood oo kale</t>
+          <t>Maxaa dhacay markii tan la weydiiyay</t>
         </is>
       </c>
       <c r="H123" s="13" t="inlineStr">
         <is>
-          <t>Maswali mengine {n}</t>
+          <t>Kilichotokea liliposwali hili</t>
         </is>
       </c>
       <c r="I123" s="14" t="inlineStr"/>
@@ -11534,7 +11534,7 @@
     <row r="124" ht="44" customHeight="1">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t>view_in_content_gaps</t>
+          <t>n_other_questions</t>
         </is>
       </c>
       <c r="B124" s="11" t="inlineStr">
@@ -11544,32 +11544,32 @@
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>View in Content Gaps</t>
+          <t>{n} other questions</t>
         </is>
       </c>
       <c r="D124" s="12" t="inlineStr">
         <is>
-          <t>በይዘት ክፍተቶች ይመልከቱ</t>
+          <t>{n} ሌሎች ጥያቄዎች</t>
         </is>
       </c>
       <c r="E124" s="13" t="inlineStr">
         <is>
-          <t>Hanqina Qabiyyee keessatti ilaali</t>
+          <t>Gaaffii {n} biroo</t>
         </is>
       </c>
       <c r="F124" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ናይ ትሕዝቶ ክፍተታት ርአ</t>
+          <t>{n} ካልኦት ሕቶታት</t>
         </is>
       </c>
       <c r="G124" s="13" t="inlineStr">
         <is>
-          <t>Ka eeg Farqiyada Nuxurka</t>
+          <t>{n} su'aalood oo kale</t>
         </is>
       </c>
       <c r="H124" s="13" t="inlineStr">
         <is>
-          <t>Angalia katika Mapungufu ya Maudhui</t>
+          <t>Maswali mengine {n}</t>
         </is>
       </c>
       <c r="I124" s="14" t="inlineStr"/>
@@ -11577,7 +11577,7 @@
     <row r="125" ht="44" customHeight="1">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>view_conversations</t>
+          <t>view_in_content_gaps</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
@@ -11587,32 +11587,32 @@
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>View Conversations</t>
+          <t>View in Content Gaps</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>ውይይቶችን ይመልከቱ</t>
+          <t>በይዘት ክፍተቶች ይመልከቱ</t>
         </is>
       </c>
       <c r="E125" s="13" t="inlineStr">
         <is>
-          <t>Haasawaa Ilaali</t>
+          <t>Hanqina Qabiyyee keessatti ilaali</t>
         </is>
       </c>
       <c r="F125" s="12" t="inlineStr">
         <is>
-          <t>ዝርርባት ርአ</t>
+          <t>ኣብ ናይ ትሕዝቶ ክፍተታት ርአ</t>
         </is>
       </c>
       <c r="G125" s="13" t="inlineStr">
         <is>
-          <t>Fiiri Wadahadalada</t>
+          <t>Ka eeg Farqiyada Nuxurka</t>
         </is>
       </c>
       <c r="H125" s="13" t="inlineStr">
         <is>
-          <t>Angalia Mazungumzo</t>
+          <t>Angalia katika Mapungufu ya Maudhui</t>
         </is>
       </c>
       <c r="I125" s="14" t="inlineStr"/>
@@ -11620,7 +11620,7 @@
     <row r="126" ht="44" customHeight="1">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>languages</t>
+          <t>view_conversations</t>
         </is>
       </c>
       <c r="B126" s="11" t="inlineStr">
@@ -11630,32 +11630,32 @@
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>Languages</t>
+          <t>View Conversations</t>
         </is>
       </c>
       <c r="D126" s="12" t="inlineStr">
         <is>
-          <t>ቋንቋዎች</t>
+          <t>ውይይቶችን ይመልከቱ</t>
         </is>
       </c>
       <c r="E126" s="13" t="inlineStr">
         <is>
-          <t>Afaanota</t>
+          <t>Haasawaa Ilaali</t>
         </is>
       </c>
       <c r="F126" s="12" t="inlineStr">
         <is>
-          <t>ቋንቋታት</t>
+          <t>ዝርርባት ርአ</t>
         </is>
       </c>
       <c r="G126" s="13" t="inlineStr">
         <is>
-          <t>Luqadaha</t>
+          <t>Fiiri Wadahadalada</t>
         </is>
       </c>
       <c r="H126" s="13" t="inlineStr">
         <is>
-          <t>Lugha</t>
+          <t>Angalia Mazungumzo</t>
         </is>
       </c>
       <c r="I126" s="14" t="inlineStr"/>
@@ -11663,7 +11663,7 @@
     <row r="127" ht="44" customHeight="1">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>unit_conversations</t>
+          <t>languages</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
@@ -11673,32 +11673,32 @@
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>conversations</t>
+          <t>Languages</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>ውይይቶች</t>
+          <t>ቋንቋዎች</t>
         </is>
       </c>
       <c r="E127" s="13" t="inlineStr">
         <is>
-          <t>marii</t>
+          <t>Afaanota</t>
         </is>
       </c>
       <c r="F127" s="12" t="inlineStr">
         <is>
-          <t>ዝርርባት</t>
+          <t>ቋንቋታት</t>
         </is>
       </c>
       <c r="G127" s="13" t="inlineStr">
         <is>
-          <t>wadahadallo</t>
+          <t>Luqadaha</t>
         </is>
       </c>
       <c r="H127" s="13" t="inlineStr">
         <is>
-          <t>mazungumzo</t>
+          <t>Lugha</t>
         </is>
       </c>
       <c r="I127" s="14" t="inlineStr"/>
@@ -11706,7 +11706,7 @@
     <row r="128" ht="44" customHeight="1">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t>unit_questions</t>
+          <t>unit_conversations</t>
         </is>
       </c>
       <c r="B128" s="11" t="inlineStr">
@@ -11716,32 +11716,32 @@
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>conversations</t>
         </is>
       </c>
       <c r="D128" s="12" t="inlineStr">
         <is>
-          <t>ጥያቄዎች</t>
+          <t>ውይይቶች</t>
         </is>
       </c>
       <c r="E128" s="13" t="inlineStr">
         <is>
-          <t>gaaffiiwwan</t>
+          <t>marii</t>
         </is>
       </c>
       <c r="F128" s="12" t="inlineStr">
         <is>
-          <t>ሕቶታት</t>
+          <t>ዝርርባት</t>
         </is>
       </c>
       <c r="G128" s="13" t="inlineStr">
         <is>
-          <t>su'aalaha</t>
+          <t>wadahadallo</t>
         </is>
       </c>
       <c r="H128" s="13" t="inlineStr">
         <is>
-          <t>maswali</t>
+          <t>mazungumzo</t>
         </is>
       </c>
       <c r="I128" s="14" t="inlineStr"/>
@@ -11749,7 +11749,7 @@
     <row r="129" ht="44" customHeight="1">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>donut_all_in</t>
+          <t>unit_questions</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
@@ -11759,32 +11759,32 @@
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>All {n} {unit} were in {label}.</t>
+          <t>questions</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>ሁሉም {n} {unit} በ{label} ነበሩ።</t>
+          <t>ጥያቄዎች</t>
         </is>
       </c>
       <c r="E129" s="13" t="inlineStr">
         <is>
-          <t>{unit} {n} hundi {label} keessa turan.</t>
+          <t>gaaffiiwwan</t>
         </is>
       </c>
       <c r="F129" s="12" t="inlineStr">
         <is>
-          <t>ኩሎም {n} {unit} ብ{label} ነይሮም።</t>
+          <t>ሕቶታት</t>
         </is>
       </c>
       <c r="G129" s="13" t="inlineStr">
         <is>
-          <t>Dhammaan {n} {unit} waxay ku jireen {label}.</t>
+          <t>su'aalaha</t>
         </is>
       </c>
       <c r="H129" s="13" t="inlineStr">
         <is>
-          <t>{unit} zote {n} zilikuwa katika {label}.</t>
+          <t>maswali</t>
         </is>
       </c>
       <c r="I129" s="14" t="inlineStr"/>
@@ -11792,7 +11792,7 @@
     <row r="130" ht="44" customHeight="1">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t>conversations_by_language</t>
+          <t>donut_all_in</t>
         </is>
       </c>
       <c r="B130" s="11" t="inlineStr">
@@ -11802,32 +11802,32 @@
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>Conversations by language</t>
+          <t>All {n} {unit} were in {label}.</t>
         </is>
       </c>
       <c r="D130" s="12" t="inlineStr">
         <is>
-          <t>በቋንቋ የተከፋፈሉ ውይይቶች</t>
+          <t>ሁሉም {n} {unit} በ{label} ነበሩ።</t>
         </is>
       </c>
       <c r="E130" s="13" t="inlineStr">
         <is>
-          <t>Marii afaaniin</t>
+          <t>{unit} {n} hundi {label} keessa turan.</t>
         </is>
       </c>
       <c r="F130" s="12" t="inlineStr">
         <is>
-          <t>ዝርርባት ብቋንቋ</t>
+          <t>ኩሎም {n} {unit} ብ{label} ነይሮም።</t>
         </is>
       </c>
       <c r="G130" s="13" t="inlineStr">
         <is>
-          <t>Wadahadallada luqadda</t>
+          <t>Dhammaan {n} {unit} waxay ku jireen {label}.</t>
         </is>
       </c>
       <c r="H130" s="13" t="inlineStr">
         <is>
-          <t>Mazungumzo kwa Lugha</t>
+          <t>{unit} zote {n} zilikuwa katika {label}.</t>
         </is>
       </c>
       <c r="I130" s="14" t="inlineStr"/>
@@ -11835,7 +11835,7 @@
     <row r="131" ht="44" customHeight="1">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>no_conversations_window</t>
+          <t>conversations_by_language</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
@@ -11845,32 +11845,32 @@
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>No conversations yet in this window.</t>
+          <t>Conversations by language</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>በዚህ ጊዜ ውስጥ ውይይት የለም።</t>
+          <t>በቋንቋ የተከፋፈሉ ውይይቶች</t>
         </is>
       </c>
       <c r="E131" s="13" t="inlineStr">
         <is>
-          <t>Yeroo kana keessatti mariin hin jiru.</t>
+          <t>Marii afaaniin</t>
         </is>
       </c>
       <c r="F131" s="12" t="inlineStr">
         <is>
-          <t>ኣብዚ እዋን'ዚ ዝርርብ የለን።</t>
+          <t>ዝርርባት ብቋንቋ</t>
         </is>
       </c>
       <c r="G131" s="13" t="inlineStr">
         <is>
-          <t>Waqtigan wadahadal ma jiro.</t>
+          <t>Wadahadallada luqadda</t>
         </is>
       </c>
       <c r="H131" s="13" t="inlineStr">
         <is>
-          <t>Hakuna mazungumzo bado katika muda huu.</t>
+          <t>Mazungumzo kwa Lugha</t>
         </is>
       </c>
       <c r="I131" s="14" t="inlineStr"/>
@@ -11878,7 +11878,7 @@
     <row r="132" ht="44" customHeight="1">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t>recent_activity</t>
+          <t>no_conversations_window</t>
         </is>
       </c>
       <c r="B132" s="11" t="inlineStr">
@@ -11888,32 +11888,32 @@
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>Recent activity</t>
+          <t>No conversations yet in this window.</t>
         </is>
       </c>
       <c r="D132" s="12" t="inlineStr">
         <is>
-          <t>የቅርብ ጊዜ እንቅስቃሴ</t>
+          <t>በዚህ ጊዜ ውስጥ ውይይት የለም።</t>
         </is>
       </c>
       <c r="E132" s="13" t="inlineStr">
         <is>
-          <t>Sochii dhiyoo</t>
+          <t>Yeroo kana keessatti mariin hin jiru.</t>
         </is>
       </c>
       <c r="F132" s="12" t="inlineStr">
         <is>
-          <t>ናይ ቀረባ እዋን ንጥፈት</t>
+          <t>ኣብዚ እዋን'ዚ ዝርርብ የለን።</t>
         </is>
       </c>
       <c r="G132" s="13" t="inlineStr">
         <is>
-          <t>Dhaqdhaqaaqa dhawaan</t>
+          <t>Waqtigan wadahadal ma jiro.</t>
         </is>
       </c>
       <c r="H132" s="13" t="inlineStr">
         <is>
-          <t>Shughuli za Hivi Karibuni</t>
+          <t>Hakuna mazungumzo bado katika muda huu.</t>
         </is>
       </c>
       <c r="I132" s="14" t="inlineStr"/>
@@ -11921,7 +11921,7 @@
     <row r="133" ht="44" customHeight="1">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>live_preview</t>
+          <t>recent_activity</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
@@ -11931,32 +11931,32 @@
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>Live preview</t>
+          <t>Recent activity</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>የቀጥታ ዕይታ</t>
+          <t>የቅርብ ጊዜ እንቅስቃሴ</t>
         </is>
       </c>
       <c r="E133" s="13" t="inlineStr">
         <is>
-          <t>Mul'ata kallattii</t>
+          <t>Sochii dhiyoo</t>
         </is>
       </c>
       <c r="F133" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታ ትርኢት</t>
+          <t>ናይ ቀረባ እዋን ንጥፈት</t>
         </is>
       </c>
       <c r="G133" s="13" t="inlineStr">
         <is>
-          <t>Muuqaal toos ah</t>
+          <t>Dhaqdhaqaaqa dhawaan</t>
         </is>
       </c>
       <c r="H133" s="13" t="inlineStr">
         <is>
-          <t>Muhtasari wa Moja kwa Moja</t>
+          <t>Shughuli za Hivi Karibuni</t>
         </is>
       </c>
       <c r="I133" s="14" t="inlineStr"/>
@@ -11964,7 +11964,7 @@
     <row r="134" ht="44" customHeight="1">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>assistant_preview</t>
+          <t>live_preview</t>
         </is>
       </c>
       <c r="B134" s="11" t="inlineStr">
@@ -11974,32 +11974,32 @@
       </c>
       <c r="C134" s="11" t="inlineStr">
         <is>
-          <t>Assistant preview</t>
+          <t>Live preview</t>
         </is>
       </c>
       <c r="D134" s="12" t="inlineStr">
         <is>
-          <t>የረዳት ዕይታ</t>
+          <t>የቀጥታ ዕይታ</t>
         </is>
       </c>
       <c r="E134" s="13" t="inlineStr">
         <is>
-          <t>Mul'ata gargaaraa</t>
+          <t>Mul'ata kallattii</t>
         </is>
       </c>
       <c r="F134" s="12" t="inlineStr">
         <is>
-          <t>ትርኢት ሓጋዚ</t>
+          <t>ቀጥታ ትርኢት</t>
         </is>
       </c>
       <c r="G134" s="13" t="inlineStr">
         <is>
-          <t>Muuqaalka kaaliyaha</t>
+          <t>Muuqaal toos ah</t>
         </is>
       </c>
       <c r="H134" s="13" t="inlineStr">
         <is>
-          <t>Muhtasari wa Msaidizi</t>
+          <t>Muhtasari wa Moja kwa Moja</t>
         </is>
       </c>
       <c r="I134" s="14" t="inlineStr"/>
@@ -12007,7 +12007,7 @@
     <row r="135" ht="44" customHeight="1">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>preview_caption</t>
+          <t>assistant_preview</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
@@ -12017,32 +12017,32 @@
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>Exactly what a customer sees on your website. Messages sent here are real and appear in Conversations.</t>
+          <t>Assistant preview</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛ በድረ-ገጽዎ ላይ የሚያየው በትክክል ይህ ነው። እዚህ የሚላኩ መልእክቶች እውነተኛ ናቸው እና በውይይቶች ውስጥ ይታያሉ።</t>
+          <t>የረዳት ዕይታ</t>
         </is>
       </c>
       <c r="E135" s="13" t="inlineStr">
         <is>
-          <t>Waanuma maamiltoonni marsariitii keessan irratti argan. Ergaan asitti ergamu dhugaadha, Marii keessattis ni mul'ata.</t>
+          <t>Mul'ata gargaaraa</t>
         </is>
       </c>
       <c r="F135" s="12" t="inlineStr">
         <is>
-          <t>ልክዕ ከምቲ ዓሚል ኣብ መርበብ ሓበሬታኹም ዝርእዮ። ኣብዚ ዝለኣኹ መልእኽትታት ናይ ሓቂ ኮይኖም ኣብ ዝርርባት ይረኣዩ።</t>
+          <t>ትርኢት ሓጋዚ</t>
         </is>
       </c>
       <c r="G135" s="13" t="inlineStr">
         <is>
-          <t>Waa waxa uu macmiilku ku arko degelkaaga. Fariimaha halkan laga diro waa dhab, waxayna ka muuqdaan Wadahadallada.</t>
+          <t>Muuqaalka kaaliyaha</t>
         </is>
       </c>
       <c r="H135" s="13" t="inlineStr">
         <is>
-          <t>Hasa kile mteja anachokiona kwenye tovuti yako. Ujumbe uliotumwa hapa ni halisi na unaonekana katika Mazungumzo.</t>
+          <t>Muhtasari wa Msaidizi</t>
         </is>
       </c>
       <c r="I135" s="14" t="inlineStr"/>
@@ -12050,7 +12050,7 @@
     <row r="136" ht="44" customHeight="1">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t>n_conversations</t>
+          <t>preview_caption</t>
         </is>
       </c>
       <c r="B136" s="11" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>{n} conversations</t>
+          <t>Exactly what a customer sees on your website. Messages sent here are real and appear in Conversations.</t>
         </is>
       </c>
       <c r="D136" s="12" t="inlineStr">
         <is>
-          <t>{n} ውይይቶች</t>
+          <t>ደንበኛ በድረ-ገጽዎ ላይ የሚያየው በትክክል ይህ ነው። እዚህ የሚላኩ መልእክቶች እውነተኛ ናቸው እና በውይይቶች ውስጥ ይታያሉ።</t>
         </is>
       </c>
       <c r="E136" s="13" t="inlineStr">
         <is>
-          <t>Marii {n}</t>
+          <t>Waanuma maamiltoonni marsariitii keessan irratti argan. Ergaan asitti ergamu dhugaadha, Marii keessattis ni mul'ata.</t>
         </is>
       </c>
       <c r="F136" s="12" t="inlineStr">
         <is>
-          <t>{n} ዝርርባት</t>
+          <t>ልክዕ ከምቲ ዓሚል ኣብ መርበብ ሓበሬታኹም ዝርእዮ። ኣብዚ ዝለኣኹ መልእኽትታት ናይ ሓቂ ኮይኖም ኣብ ዝርርባት ይረኣዩ።</t>
         </is>
       </c>
       <c r="G136" s="13" t="inlineStr">
         <is>
-          <t>{n} wadahadal</t>
+          <t>Waa waxa uu macmiilku ku arko degelkaaga. Fariimaha halkan laga diro waa dhab, waxayna ka muuqdaan Wadahadallada.</t>
         </is>
       </c>
       <c r="H136" s="13" t="inlineStr">
         <is>
-          <t>Mazungumzo {n}</t>
+          <t>Hasa kile mteja anachokiona kwenye tovuti yako. Ujumbe uliotumwa hapa ni halisi na unaonekana katika Mazungumzo.</t>
         </is>
       </c>
       <c r="I136" s="14" t="inlineStr"/>
@@ -12093,7 +12093,7 @@
     <row r="137" ht="44" customHeight="1">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>one_conversation</t>
+          <t>n_conversations</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
@@ -12103,12 +12103,12 @@
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>{n} conversation</t>
+          <t>{n} conversations</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>{n} ውይይት</t>
+          <t>{n} ውይይቶች</t>
         </is>
       </c>
       <c r="E137" s="13" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="F137" s="12" t="inlineStr">
         <is>
-          <t>{n} ዝርርብ</t>
+          <t>{n} ዝርርባት</t>
         </is>
       </c>
       <c r="G137" s="13" t="inlineStr">
@@ -12136,7 +12136,7 @@
     <row r="138" ht="44" customHeight="1">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t>outcome_answered</t>
+          <t>one_conversation</t>
         </is>
       </c>
       <c r="B138" s="11" t="inlineStr">
@@ -12146,32 +12146,32 @@
       </c>
       <c r="C138" s="11" t="inlineStr">
         <is>
-          <t>Answered from your content</t>
+          <t>{n} conversation</t>
         </is>
       </c>
       <c r="D138" s="12" t="inlineStr">
         <is>
-          <t>ከይዘትዎ የተመለሰ</t>
+          <t>{n} ውይይት</t>
         </is>
       </c>
       <c r="E138" s="13" t="inlineStr">
         <is>
-          <t>Qabiyyee keessan irraa deebi'e</t>
+          <t>Marii {n}</t>
         </is>
       </c>
       <c r="F138" s="12" t="inlineStr">
         <is>
-          <t>ካብ ትሕዝቶኹም ዝተመለሰ</t>
+          <t>{n} ዝርርብ</t>
         </is>
       </c>
       <c r="G138" s="13" t="inlineStr">
         <is>
-          <t>Laga jawaabay macluumaadkaaga</t>
+          <t>{n} wadahadal</t>
         </is>
       </c>
       <c r="H138" s="13" t="inlineStr">
         <is>
-          <t>Imejibiwa Kutoka kwa Maudhui Yako</t>
+          <t>Mazungumzo {n}</t>
         </is>
       </c>
       <c r="I138" s="14" t="inlineStr"/>
@@ -12179,7 +12179,7 @@
     <row r="139" ht="44" customHeight="1">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>outcome_general_guidance</t>
+          <t>outcome_answered</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
@@ -12189,32 +12189,32 @@
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>Answered from general banking knowledge</t>
+          <t>Answered from your content</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>ከአጠቃላይ የባንክ እውቀት የተመለሰ</t>
+          <t>ከይዘትዎ የተመለሰ</t>
         </is>
       </c>
       <c r="E139" s="13" t="inlineStr">
         <is>
-          <t>Beekumsa baankii waliigalaa irraa deebi'e</t>
+          <t>Qabiyyee keessan irraa deebi'e</t>
         </is>
       </c>
       <c r="F139" s="12" t="inlineStr">
         <is>
-          <t>ካብ ሓፈሻዊ ፍልጠት ባንክ ዝተመለሰ</t>
+          <t>ካብ ትሕዝቶኹም ዝተመለሰ</t>
         </is>
       </c>
       <c r="G139" s="13" t="inlineStr">
         <is>
-          <t>Laga jawaabay aqoonta guud ee bangiga</t>
+          <t>Laga jawaabay macluumaadkaaga</t>
         </is>
       </c>
       <c r="H139" s="13" t="inlineStr">
         <is>
-          <t>Imejibiwa Kutoka kwa Maarifa ya Jumla ya Kibenki</t>
+          <t>Imejibiwa Kutoka kwa Maudhui Yako</t>
         </is>
       </c>
       <c r="I139" s="14" t="inlineStr"/>
@@ -12222,7 +12222,7 @@
     <row r="140" ht="44" customHeight="1">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t>outcome_unanswered</t>
+          <t>outcome_general_guidance</t>
         </is>
       </c>
       <c r="B140" s="11" t="inlineStr">
@@ -12232,32 +12232,32 @@
       </c>
       <c r="C140" s="11" t="inlineStr">
         <is>
-          <t>Could not answer</t>
+          <t>Answered from general banking knowledge</t>
         </is>
       </c>
       <c r="D140" s="12" t="inlineStr">
         <is>
-          <t>መልስ ማግኘት አልተቻለም</t>
+          <t>ከአጠቃላይ የባንክ እውቀት የተመለሰ</t>
         </is>
       </c>
       <c r="E140" s="13" t="inlineStr">
         <is>
-          <t>Deebisuu hin dandeenye</t>
+          <t>Beekumsa baankii waliigalaa irraa deebi'e</t>
         </is>
       </c>
       <c r="F140" s="12" t="inlineStr">
         <is>
-          <t>መልሲ ክርከብ ኣይተኻእለን</t>
+          <t>ካብ ሓፈሻዊ ፍልጠት ባንክ ዝተመለሰ</t>
         </is>
       </c>
       <c r="G140" s="13" t="inlineStr">
         <is>
-          <t>Lama jawaabi karin</t>
+          <t>Laga jawaabay aqoonta guud ee bangiga</t>
         </is>
       </c>
       <c r="H140" s="13" t="inlineStr">
         <is>
-          <t>Haikuweza Kujibiwa</t>
+          <t>Imejibiwa Kutoka kwa Maarifa ya Jumla ya Kibenki</t>
         </is>
       </c>
       <c r="I140" s="14" t="inlineStr"/>
@@ -12265,7 +12265,7 @@
     <row r="141" ht="44" customHeight="1">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>outcome_complaint</t>
+          <t>outcome_unanswered</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
@@ -12275,32 +12275,32 @@
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Could not answer</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>ቅሬታ</t>
+          <t>መልስ ማግኘት አልተቻለም</t>
         </is>
       </c>
       <c r="E141" s="13" t="inlineStr">
         <is>
-          <t>Komii</t>
+          <t>Deebisuu hin dandeenye</t>
         </is>
       </c>
       <c r="F141" s="12" t="inlineStr">
         <is>
-          <t>ጥርዓን</t>
+          <t>መልሲ ክርከብ ኣይተኻእለን</t>
         </is>
       </c>
       <c r="G141" s="13" t="inlineStr">
         <is>
-          <t>Cabasho</t>
+          <t>Lama jawaabi karin</t>
         </is>
       </c>
       <c r="H141" s="13" t="inlineStr">
         <is>
-          <t>Malalamiko</t>
+          <t>Haikuweza Kujibiwa</t>
         </is>
       </c>
       <c r="I141" s="14" t="inlineStr"/>
@@ -12308,7 +12308,7 @@
     <row r="142" ht="44" customHeight="1">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t>outcome_account_blocked</t>
+          <t>outcome_complaint</t>
         </is>
       </c>
       <c r="B142" s="11" t="inlineStr">
@@ -12318,32 +12318,32 @@
       </c>
       <c r="C142" s="11" t="inlineStr">
         <is>
-          <t>Account access problem</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="D142" s="12" t="inlineStr">
         <is>
-          <t>የመለያ መግቢያ ችግር</t>
+          <t>ቅሬታ</t>
         </is>
       </c>
       <c r="E142" s="13" t="inlineStr">
         <is>
-          <t>Rakkoo herrega seenuu</t>
+          <t>Komii</t>
         </is>
       </c>
       <c r="F142" s="12" t="inlineStr">
         <is>
-          <t>ጸገም ኣታውነት ሕሳብ</t>
+          <t>ጥርዓን</t>
         </is>
       </c>
       <c r="G142" s="13" t="inlineStr">
         <is>
-          <t>Dhibaato gelitaanka xisaabta</t>
+          <t>Cabasho</t>
         </is>
       </c>
       <c r="H142" s="13" t="inlineStr">
         <is>
-          <t>Tatizo la Ufikiaji wa Akaunti</t>
+          <t>Malalamiko</t>
         </is>
       </c>
       <c r="I142" s="14" t="inlineStr"/>
@@ -12351,7 +12351,7 @@
     <row r="143" ht="44" customHeight="1">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>outcome_comparison</t>
+          <t>outcome_account_blocked</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
@@ -12361,32 +12361,32 @@
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>Compared with another bank</t>
+          <t>Account access problem</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>ከሌላ ባንክ ጋር ተነጻጽሯል</t>
+          <t>የመለያ መግቢያ ችግር</t>
         </is>
       </c>
       <c r="E143" s="13" t="inlineStr">
         <is>
-          <t>Baankii biraa waliin walbira qabame</t>
+          <t>Rakkoo herrega seenuu</t>
         </is>
       </c>
       <c r="F143" s="12" t="inlineStr">
         <is>
-          <t>ምስ ካልእ ባንክ ተነጻጺሩ</t>
+          <t>ጸገም ኣታውነት ሕሳብ</t>
         </is>
       </c>
       <c r="G143" s="13" t="inlineStr">
         <is>
-          <t>Lala barbardhigay bangi kale</t>
+          <t>Dhibaato gelitaanka xisaabta</t>
         </is>
       </c>
       <c r="H143" s="13" t="inlineStr">
         <is>
-          <t>Ililinganishwa na Benki Nyingine</t>
+          <t>Tatizo la Ufikiaji wa Akaunti</t>
         </is>
       </c>
       <c r="I143" s="14" t="inlineStr"/>
@@ -12394,7 +12394,7 @@
     <row r="144" ht="44" customHeight="1">
       <c r="A144" s="11" t="inlineStr">
         <is>
-          <t>outcome_greeting</t>
+          <t>outcome_comparison</t>
         </is>
       </c>
       <c r="B144" s="11" t="inlineStr">
@@ -12404,32 +12404,32 @@
       </c>
       <c r="C144" s="11" t="inlineStr">
         <is>
-          <t>Greeting</t>
+          <t>Compared with another bank</t>
         </is>
       </c>
       <c r="D144" s="12" t="inlineStr">
         <is>
-          <t>ሰላምታ</t>
+          <t>ከሌላ ባንክ ጋር ተነጻጽሯል</t>
         </is>
       </c>
       <c r="E144" s="13" t="inlineStr">
         <is>
-          <t>Nagaa</t>
+          <t>Baankii biraa waliin walbira qabame</t>
         </is>
       </c>
       <c r="F144" s="12" t="inlineStr">
         <is>
-          <t>ሰላምታ</t>
+          <t>ምስ ካልእ ባንክ ተነጻጺሩ</t>
         </is>
       </c>
       <c r="G144" s="13" t="inlineStr">
         <is>
-          <t>Salaan</t>
+          <t>Lala barbardhigay bangi kale</t>
         </is>
       </c>
       <c r="H144" s="13" t="inlineStr">
         <is>
-          <t>Salamu</t>
+          <t>Ililinganishwa na Benki Nyingine</t>
         </is>
       </c>
       <c r="I144" s="14" t="inlineStr"/>
@@ -12437,7 +12437,7 @@
     <row r="145" ht="44" customHeight="1">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>outcome_contact_captured</t>
+          <t>outcome_greeting</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>Contact details captured</t>
+          <t>Greeting</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>የመገናኛ መረጃ ተመዝግቧል</t>
+          <t>ሰላምታ</t>
         </is>
       </c>
       <c r="E145" s="13" t="inlineStr">
         <is>
-          <t>Odeeffannoon quunnamtii galmaa'e</t>
+          <t>Nagaa</t>
         </is>
       </c>
       <c r="F145" s="12" t="inlineStr">
         <is>
-          <t>ሓበሬታ መራኸቢ ተመዝጊቡ</t>
+          <t>ሰላምታ</t>
         </is>
       </c>
       <c r="G145" s="13" t="inlineStr">
         <is>
-          <t>Xogta xiriirka waa la diiwaangeliyay</t>
+          <t>Salaan</t>
         </is>
       </c>
       <c r="H145" s="13" t="inlineStr">
         <is>
-          <t>Taarifa za Mawasiliano Zimehifadhiwa</t>
+          <t>Salamu</t>
         </is>
       </c>
       <c r="I145" s="14" t="inlineStr"/>
@@ -12480,7 +12480,7 @@
     <row r="146" ht="44" customHeight="1">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t>outcome_human_request</t>
+          <t>outcome_contact_captured</t>
         </is>
       </c>
       <c r="B146" s="11" t="inlineStr">
@@ -12490,32 +12490,32 @@
       </c>
       <c r="C146" s="11" t="inlineStr">
         <is>
-          <t>Asked for a person</t>
+          <t>Contact details captured</t>
         </is>
       </c>
       <c r="D146" s="12" t="inlineStr">
         <is>
-          <t>ሰው ተጠይቋል</t>
+          <t>የመገናኛ መረጃ ተመዝግቧል</t>
         </is>
       </c>
       <c r="E146" s="13" t="inlineStr">
         <is>
-          <t>Nama gaafate</t>
+          <t>Odeeffannoon quunnamtii galmaa'e</t>
         </is>
       </c>
       <c r="F146" s="12" t="inlineStr">
         <is>
-          <t>ሰብ ተሓቲቱ</t>
+          <t>ሓበሬታ መራኸቢ ተመዝጊቡ</t>
         </is>
       </c>
       <c r="G146" s="13" t="inlineStr">
         <is>
-          <t>Qof ayaa la codsaday</t>
+          <t>Xogta xiriirka waa la diiwaangeliyay</t>
         </is>
       </c>
       <c r="H146" s="13" t="inlineStr">
         <is>
-          <t>Aliomba Mtu</t>
+          <t>Taarifa za Mawasiliano Zimehifadhiwa</t>
         </is>
       </c>
       <c r="I146" s="14" t="inlineStr"/>
@@ -12523,7 +12523,7 @@
     <row r="147" ht="44" customHeight="1">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>reason_complaint</t>
+          <t>outcome_human_request</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
@@ -12533,32 +12533,32 @@
       </c>
       <c r="C147" s="11" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Asked for a person</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>ቅሬታ</t>
+          <t>ሰው ተጠይቋል</t>
         </is>
       </c>
       <c r="E147" s="13" t="inlineStr">
         <is>
-          <t>Komii</t>
+          <t>Nama gaafate</t>
         </is>
       </c>
       <c r="F147" s="12" t="inlineStr">
         <is>
-          <t>ጥርዓን</t>
+          <t>ሰብ ተሓቲቱ</t>
         </is>
       </c>
       <c r="G147" s="13" t="inlineStr">
         <is>
-          <t>Cabasho</t>
+          <t>Qof ayaa la codsaday</t>
         </is>
       </c>
       <c r="H147" s="13" t="inlineStr">
         <is>
-          <t>Malalamiko</t>
+          <t>Aliomba Mtu</t>
         </is>
       </c>
       <c r="I147" s="14" t="inlineStr"/>
@@ -12566,7 +12566,7 @@
     <row r="148" ht="44" customHeight="1">
       <c r="A148" s="11" t="inlineStr">
         <is>
-          <t>reason_human_requested</t>
+          <t>reason_complaint</t>
         </is>
       </c>
       <c r="B148" s="11" t="inlineStr">
@@ -12576,32 +12576,32 @@
       </c>
       <c r="C148" s="11" t="inlineStr">
         <is>
-          <t>Asked for a person</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="D148" s="12" t="inlineStr">
         <is>
-          <t>ሰው ተጠይቋል</t>
+          <t>ቅሬታ</t>
         </is>
       </c>
       <c r="E148" s="13" t="inlineStr">
         <is>
-          <t>Nama gaafate</t>
+          <t>Komii</t>
         </is>
       </c>
       <c r="F148" s="12" t="inlineStr">
         <is>
-          <t>ሰብ ተሓቲቱ</t>
+          <t>ጥርዓን</t>
         </is>
       </c>
       <c r="G148" s="13" t="inlineStr">
         <is>
-          <t>Qof ayaa la codsaday</t>
+          <t>Cabasho</t>
         </is>
       </c>
       <c r="H148" s="13" t="inlineStr">
         <is>
-          <t>Aliomba Mtu</t>
+          <t>Malalamiko</t>
         </is>
       </c>
       <c r="I148" s="14" t="inlineStr"/>
@@ -12609,7 +12609,7 @@
     <row r="149" ht="44" customHeight="1">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>reason_unanswered_question</t>
+          <t>reason_human_requested</t>
         </is>
       </c>
       <c r="B149" s="11" t="inlineStr">
@@ -12619,32 +12619,32 @@
       </c>
       <c r="C149" s="11" t="inlineStr">
         <is>
-          <t>No answer in your content</t>
+          <t>Asked for a person</t>
         </is>
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>በይዘትዎ ውስጥ መልስ የለም</t>
+          <t>ሰው ተጠይቋል</t>
         </is>
       </c>
       <c r="E149" s="13" t="inlineStr">
         <is>
-          <t>Qabiyyee keessan keessa deebiin hin jiru</t>
+          <t>Nama gaafate</t>
         </is>
       </c>
       <c r="F149" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ትሕዝቶኹም መልሲ የለን</t>
+          <t>ሰብ ተሓቲቱ</t>
         </is>
       </c>
       <c r="G149" s="13" t="inlineStr">
         <is>
-          <t>Macluumaadkaaga jawaab kuma jirto</t>
+          <t>Qof ayaa la codsaday</t>
         </is>
       </c>
       <c r="H149" s="13" t="inlineStr">
         <is>
-          <t>Hakuna Jibu Katika Maudhui Yako</t>
+          <t>Aliomba Mtu</t>
         </is>
       </c>
       <c r="I149" s="14" t="inlineStr"/>
@@ -12652,7 +12652,7 @@
     <row r="150" ht="44" customHeight="1">
       <c r="A150" s="11" t="inlineStr">
         <is>
-          <t>reason_answered_from_general_knowledge</t>
+          <t>reason_unanswered_question</t>
         </is>
       </c>
       <c r="B150" s="11" t="inlineStr">
@@ -12662,32 +12662,32 @@
       </c>
       <c r="C150" s="11" t="inlineStr">
         <is>
-          <t>Answered from general knowledge</t>
+          <t>No answer in your content</t>
         </is>
       </c>
       <c r="D150" s="12" t="inlineStr">
         <is>
-          <t>ከአጠቃላይ እውቀት የተመለሰ</t>
+          <t>በይዘትዎ ውስጥ መልስ የለም</t>
         </is>
       </c>
       <c r="E150" s="13" t="inlineStr">
         <is>
-          <t>Beekumsa waliigalaa irraa deebi'e</t>
+          <t>Qabiyyee keessan keessa deebiin hin jiru</t>
         </is>
       </c>
       <c r="F150" s="12" t="inlineStr">
         <is>
-          <t>ካብ ሓፈሻዊ ፍልጠት ዝተመለሰ</t>
+          <t>ኣብ ትሕዝቶኹም መልሲ የለን</t>
         </is>
       </c>
       <c r="G150" s="13" t="inlineStr">
         <is>
-          <t>Laga jawaabay aqoon guud</t>
+          <t>Macluumaadkaaga jawaab kuma jirto</t>
         </is>
       </c>
       <c r="H150" s="13" t="inlineStr">
         <is>
-          <t>Imejibiwa Kutoka kwa Maarifa ya Jumla</t>
+          <t>Hakuna Jibu Katika Maudhui Yako</t>
         </is>
       </c>
       <c r="I150" s="14" t="inlineStr"/>
@@ -12695,7 +12695,7 @@
     <row r="151" ht="44" customHeight="1">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>branding</t>
+          <t>reason_answered_from_general_knowledge</t>
         </is>
       </c>
       <c r="B151" s="11" t="inlineStr">
@@ -12705,32 +12705,32 @@
       </c>
       <c r="C151" s="11" t="inlineStr">
         <is>
-          <t>Branding</t>
+          <t>Answered from general knowledge</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>የምርት ስም</t>
+          <t>ከአጠቃላይ እውቀት የተመለሰ</t>
         </is>
       </c>
       <c r="E151" s="13" t="inlineStr">
         <is>
-          <t>Mallattoo dhaabbataa</t>
+          <t>Beekumsa waliigalaa irraa deebi'e</t>
         </is>
       </c>
       <c r="F151" s="12" t="inlineStr">
         <is>
-          <t>ንግዲ ምልክት</t>
+          <t>ካብ ሓፈሻዊ ፍልጠት ዝተመለሰ</t>
         </is>
       </c>
       <c r="G151" s="13" t="inlineStr">
         <is>
-          <t>Astaanta</t>
+          <t>Laga jawaabay aqoon guud</t>
         </is>
       </c>
       <c r="H151" s="13" t="inlineStr">
         <is>
-          <t>Alama ya Biashara</t>
+          <t>Imejibiwa Kutoka kwa Maarifa ya Jumla</t>
         </is>
       </c>
       <c r="I151" s="14" t="inlineStr"/>
@@ -12738,7 +12738,7 @@
     <row r="152" ht="44" customHeight="1">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>branding_help</t>
+          <t>branding</t>
         </is>
       </c>
       <c r="B152" s="11" t="inlineStr">
@@ -12748,32 +12748,32 @@
       </c>
       <c r="C152" s="11" t="inlineStr">
         <is>
-          <t>Your colour and logo, used in this panel and in the chat widget on your website. Saved values apply immediately — no deploy.</t>
+          <t>Branding</t>
         </is>
       </c>
       <c r="D152" s="12" t="inlineStr">
         <is>
-          <t>በዚህ ፓነልና በድረ-ገጽዎ ላይ ባለው የውይይት መስኮት የሚያገለግሉ ቀለምዎና አርማዎ። የተቀመጡ እሴቶች ወዲያውኑ ተግባራዊ ይሆናሉ — ማሰማራት አያስፈልግም።</t>
+          <t>የምርት ስም</t>
         </is>
       </c>
       <c r="E152" s="13" t="inlineStr">
         <is>
-          <t>Halluu fi mallattoo keessan, panaalii kana keessattii fi widjetii chat marsariitii keessan irratti kan hojiirra oolu. Gatiin olkaa'ame battalumatti hojiirra oola — bobbaasuun hin barbaachisu.</t>
+          <t>Mallattoo dhaabbataa</t>
         </is>
       </c>
       <c r="F152" s="12" t="inlineStr">
         <is>
-          <t>ኣብዚ ፓነልን ኣብ መርበብ ሓበሬታኹም ዘሎ መስኮት ዝርርብን ዝጠቅም ሕብርኹምን ኣርማኹምን። ዝተዓቀቡ ዋጋታት ብቕጽበት ይሰርሑ — ምዝርጋሕ ኣየድልን።</t>
+          <t>ንግዲ ምልክት</t>
         </is>
       </c>
       <c r="G152" s="13" t="inlineStr">
         <is>
-          <t>Midabkaaga iyo astaantaada, oo laga isticmaalo daaqadan iyo widget-ka sheekada degelkaaga. Qiyamka la keydiyay isla markiiba way shaqeeyaan — geyn looma baahna.</t>
+          <t>Astaanta</t>
         </is>
       </c>
       <c r="H152" s="13" t="inlineStr">
         <is>
-          <t>Rangi na nembo yako, inayotumika kwenye paneli hii na kwenye kidirisha cha mazungumzo kwenye tovuti yako. Thamani zilizohifadhiwa zinatumika mara moja — bila kupeleka toleo jipya.</t>
+          <t>Alama ya Biashara</t>
         </is>
       </c>
       <c r="I152" s="14" t="inlineStr"/>
@@ -12781,7 +12781,7 @@
     <row r="153" ht="44" customHeight="1">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>brand_name</t>
+          <t>branding_help</t>
         </is>
       </c>
       <c r="B153" s="11" t="inlineStr">
@@ -12791,32 +12791,32 @@
       </c>
       <c r="C153" s="11" t="inlineStr">
         <is>
-          <t>Brand name</t>
+          <t>Your colour and logo, used in this panel and in the chat widget on your website. Saved values apply immediately — no deploy.</t>
         </is>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>የምርት ስም</t>
+          <t>በዚህ ፓነልና በድረ-ገጽዎ ላይ ባለው የውይይት መስኮት የሚያገለግሉ ቀለምዎና አርማዎ። የተቀመጡ እሴቶች ወዲያውኑ ተግባራዊ ይሆናሉ — ማሰማራት አያስፈልግም።</t>
         </is>
       </c>
       <c r="E153" s="13" t="inlineStr">
         <is>
-          <t>Maqaa mallattoo</t>
+          <t>Halluu fi mallattoo keessan, panaalii kana keessattii fi widjetii chat marsariitii keessan irratti kan hojiirra oolu. Gatiin olkaa'ame battalumatti hojiirra oola — bobbaasuun hin barbaachisu.</t>
         </is>
       </c>
       <c r="F153" s="12" t="inlineStr">
         <is>
-          <t>ስም ንግዲ ምልክት</t>
+          <t>ኣብዚ ፓነልን ኣብ መርበብ ሓበሬታኹም ዘሎ መስኮት ዝርርብን ዝጠቅም ሕብርኹምን ኣርማኹምን። ዝተዓቀቡ ዋጋታት ብቕጽበት ይሰርሑ — ምዝርጋሕ ኣየድልን።</t>
         </is>
       </c>
       <c r="G153" s="13" t="inlineStr">
         <is>
-          <t>Magaca astaanta</t>
+          <t>Midabkaaga iyo astaantaada, oo laga isticmaalo daaqadan iyo widget-ka sheekada degelkaaga. Qiyamka la keydiyay isla markiiba way shaqeeyaan — geyn looma baahna.</t>
         </is>
       </c>
       <c r="H153" s="13" t="inlineStr">
         <is>
-          <t>Jina la Alama</t>
+          <t>Rangi na nembo yako, inayotumika kwenye paneli hii na kwenye kidirisha cha mazungumzo kwenye tovuti yako. Thamani zilizohifadhiwa zinatumika mara moja — bila kupeleka toleo jipya.</t>
         </is>
       </c>
       <c r="I153" s="14" t="inlineStr"/>
@@ -12824,7 +12824,7 @@
     <row r="154" ht="44" customHeight="1">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t>brand_name_help</t>
+          <t>brand_name</t>
         </is>
       </c>
       <c r="B154" s="11" t="inlineStr">
@@ -12834,32 +12834,32 @@
       </c>
       <c r="C154" s="11" t="inlineStr">
         <is>
-          <t>What people call you — for example "CBE". Shown in the chat header, this panel and greetings to customers. Leave blank to use your registered name, {legal}, which is kept either way for printed reports.</t>
+          <t>Brand name</t>
         </is>
       </c>
       <c r="D154" s="12" t="inlineStr">
         <is>
-          <t>ሰዎች የሚጠሩዎት ስም — ለምሳሌ "CBE"። በውይይቱ ራስጌ፣ በዚህ ፓነልና ለደንበኞች በሚቀርብ ሰላምታ ላይ ይታያል። ባዶ ከተውት የተመዘገበው ስምዎ {legal} ይሆናል፤ ለሚታተሙ ሪፖርቶች በሁለቱም መንገድ ይቀመጣል።</t>
+          <t>የምርት ስም</t>
         </is>
       </c>
       <c r="E154" s="13" t="inlineStr">
         <is>
-          <t>Maqaa namoonni ittiin isin waaman — fakkeenyaaf "CBE". Mataduree chat, panaalii kanaa fi nagaa maamiltootaaf dhiyaatu irratti ni mul'ata. Duwwaa yoo dhiiftan maqaan galmaa'aa keessan {legal} fayyadama; gabaasa maxxanfamuuf karaa lamaanuu ni qabama.</t>
+          <t>Maqaa mallattoo</t>
         </is>
       </c>
       <c r="F154" s="12" t="inlineStr">
         <is>
-          <t>ሰባት ዝጽውዑኹም ስም — ንኣብነት "CBE"። ኣብ ርእሲ ዝርርብ፣ ኣብዚ ፓነልን ንዓማዊል ኣብ ዝቐርብ ሰላምታን ይረአ። ባዶ እንተ ገዲፍኩምዎ እቲ ዝተመዝገበ ስምኩም {legal} ይኸውን፤ ንዝሕተሙ ጸብጻባት ብኽልቲኡ መገዲ ይዕቀብ።</t>
+          <t>ስም ንግዲ ምልክት</t>
         </is>
       </c>
       <c r="G154" s="13" t="inlineStr">
         <is>
-          <t>Waxa dadku kugu yeeraan — tusaale "CBE". Waxay ka muuqataa madaxa sheekada, daaqadan iyo salaanta macaamiisha. Haddii aad banaan ka tagto waxaa la isticmaalayaa magacaaga diiwaangashan, {legal}, oo si kastaba lagu hayo warbixinnada la daabaco.</t>
+          <t>Magaca astaanta</t>
         </is>
       </c>
       <c r="H154" s="13" t="inlineStr">
         <is>
-          <t>Jina ambalo watu wanakuita — kwa mfano "CBE". Linaonyeshwa kwenye kichwa cha mazungumzo, paneli hii na salamu kwa wateja. Acha wazi ili kutumia jina lako lililosajiliwa, {legal}, ambalo linabaki kutumika kwa ripoti zilizochapishwa.</t>
+          <t>Jina la Alama</t>
         </is>
       </c>
       <c r="I154" s="14" t="inlineStr"/>
@@ -12867,7 +12867,7 @@
     <row r="155" ht="44" customHeight="1">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>brand_colour</t>
+          <t>brand_name_help</t>
         </is>
       </c>
       <c r="B155" s="11" t="inlineStr">
@@ -12877,32 +12877,32 @@
       </c>
       <c r="C155" s="11" t="inlineStr">
         <is>
-          <t>Brand colour</t>
+          <t>What people call you — for example "CBE". Shown in the chat header, this panel and greetings to customers. Leave blank to use your registered name, {legal}, which is kept either way for printed reports.</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>የምርት ቀለም</t>
+          <t>ሰዎች የሚጠሩዎት ስም — ለምሳሌ "CBE"። በውይይቱ ራስጌ፣ በዚህ ፓነልና ለደንበኞች በሚቀርብ ሰላምታ ላይ ይታያል። ባዶ ከተውት የተመዘገበው ስምዎ {legal} ይሆናል፤ ለሚታተሙ ሪፖርቶች በሁለቱም መንገድ ይቀመጣል።</t>
         </is>
       </c>
       <c r="E155" s="13" t="inlineStr">
         <is>
-          <t>Halluu mallattoo</t>
+          <t>Maqaa namoonni ittiin isin waaman — fakkeenyaaf "CBE". Mataduree chat, panaalii kanaa fi nagaa maamiltootaaf dhiyaatu irratti ni mul'ata. Duwwaa yoo dhiiftan maqaan galmaa'aa keessan {legal} fayyadama; gabaasa maxxanfamuuf karaa lamaanuu ni qabama.</t>
         </is>
       </c>
       <c r="F155" s="12" t="inlineStr">
         <is>
-          <t>ሕብሪ ንግዲ ምልክት</t>
+          <t>ሰባት ዝጽውዑኹም ስም — ንኣብነት "CBE"። ኣብ ርእሲ ዝርርብ፣ ኣብዚ ፓነልን ንዓማዊል ኣብ ዝቐርብ ሰላምታን ይረአ። ባዶ እንተ ገዲፍኩምዎ እቲ ዝተመዝገበ ስምኩም {legal} ይኸውን፤ ንዝሕተሙ ጸብጻባት ብኽልቲኡ መገዲ ይዕቀብ።</t>
         </is>
       </c>
       <c r="G155" s="13" t="inlineStr">
         <is>
-          <t>Midabka astaanta</t>
+          <t>Waxa dadku kugu yeeraan — tusaale "CBE". Waxay ka muuqataa madaxa sheekada, daaqadan iyo salaanta macaamiisha. Haddii aad banaan ka tagto waxaa la isticmaalayaa magacaaga diiwaangashan, {legal}, oo si kastaba lagu hayo warbixinnada la daabaco.</t>
         </is>
       </c>
       <c r="H155" s="13" t="inlineStr">
         <is>
-          <t>Rangi ya Alama</t>
+          <t>Jina ambalo watu wanakuita — kwa mfano "CBE". Linaonyeshwa kwenye kichwa cha mazungumzo, paneli hii na salamu kwa wateja. Acha wazi ili kutumia jina lako lililosajiliwa, {legal}, ambalo linabaki kutumika kwa ripoti zilizochapishwa.</t>
         </is>
       </c>
       <c r="I155" s="14" t="inlineStr"/>
@@ -12910,7 +12910,7 @@
     <row r="156" ht="44" customHeight="1">
       <c r="A156" s="11" t="inlineStr">
         <is>
-          <t>logo_url</t>
+          <t>brand_colour</t>
         </is>
       </c>
       <c r="B156" s="11" t="inlineStr">
@@ -12920,32 +12920,32 @@
       </c>
       <c r="C156" s="11" t="inlineStr">
         <is>
-          <t>Logo URL (https)</t>
+          <t>Brand colour</t>
         </is>
       </c>
       <c r="D156" s="12" t="inlineStr">
         <is>
-          <t>የአርማ አድራሻ (https)</t>
+          <t>የምርት ቀለም</t>
         </is>
       </c>
       <c r="E156" s="13" t="inlineStr">
         <is>
-          <t>Teessoo mallattoo (https)</t>
+          <t>Halluu mallattoo</t>
         </is>
       </c>
       <c r="F156" s="12" t="inlineStr">
         <is>
-          <t>ኣድራሻ ኣርማ (https)</t>
+          <t>ሕብሪ ንግዲ ምልክት</t>
         </is>
       </c>
       <c r="G156" s="13" t="inlineStr">
         <is>
-          <t>Ciwaanka astaanta (https)</t>
+          <t>Midabka astaanta</t>
         </is>
       </c>
       <c r="H156" s="13" t="inlineStr">
         <is>
-          <t>Kiungo cha Nembo (https)</t>
+          <t>Rangi ya Alama</t>
         </is>
       </c>
       <c r="I156" s="14" t="inlineStr"/>
@@ -12953,7 +12953,7 @@
     <row r="157" ht="44" customHeight="1">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>seeded_colours_help</t>
+          <t>logo_url</t>
         </is>
       </c>
       <c r="B157" s="11" t="inlineStr">
@@ -12963,32 +12963,32 @@
       </c>
       <c r="C157" s="11" t="inlineStr">
         <is>
-          <t>Seeded colours are our reading of your public site, not your brand book. If it is wrong, this is where to fix it.</t>
+          <t>Logo URL (https)</t>
         </is>
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>የቀረቡት ቀለሞች ከይፋዊ ድረ-ገጽዎ የተወሰዱ ግምቶች እንጂ ከምርት መመሪያ መጽሐፍዎ አይደሉም። ስህተት ከሆነ የሚታረመው እዚህ ነው።</t>
+          <t>የአርማ አድራሻ (https)</t>
         </is>
       </c>
       <c r="E157" s="13" t="inlineStr">
         <is>
-          <t>Halluuwwan durfaman marsariitii keessan ifaa irraa kan dubbifame malee kitaaba mallattoo keessanii irraa miti. Yoo dogoggora ta'e, asitti sirreessaa.</t>
+          <t>Teessoo mallattoo (https)</t>
         </is>
       </c>
       <c r="F157" s="12" t="inlineStr">
         <is>
-          <t>እቶም ዝቐረቡ ሕብርታት ካብ ወግዓዊ መርበብ ሓበሬታኹም ዝተወስዱ ግምት እምበር ካብ መጽሓፍ ንግዲ ምልክትኩም ኣይኮኑን። ጌጋ እንተኾይኑ ኣብዚ ይእረም።</t>
+          <t>ኣድራሻ ኣርማ (https)</t>
         </is>
       </c>
       <c r="G157" s="13" t="inlineStr">
         <is>
-          <t>Midabbada la soo bandhigay waa akhrinteenna degelkaaga guud, ma aha buuggaaga astaanta. Haddii ay khalad tahay, halkan ayaa lagu saxaa.</t>
+          <t>Ciwaanka astaanta (https)</t>
         </is>
       </c>
       <c r="H157" s="13" t="inlineStr">
         <is>
-          <t>Rangi zilizowekwa awali ni uelewa wetu wa tovuti yako ya umma, si kitabu chako cha alama ya biashara. Ikiwa si sahihi, hapa ndipo pa kurekebisha.</t>
+          <t>Kiungo cha Nembo (https)</t>
         </is>
       </c>
       <c r="I157" s="14" t="inlineStr"/>
@@ -12996,7 +12996,7 @@
     <row r="158" ht="44" customHeight="1">
       <c r="A158" s="11" t="inlineStr">
         <is>
-          <t>save_branding</t>
+          <t>seeded_colours_help</t>
         </is>
       </c>
       <c r="B158" s="11" t="inlineStr">
@@ -13006,32 +13006,32 @@
       </c>
       <c r="C158" s="11" t="inlineStr">
         <is>
-          <t>Save branding</t>
+          <t>Seeded colours are our reading of your public site, not your brand book. If it is wrong, this is where to fix it.</t>
         </is>
       </c>
       <c r="D158" s="12" t="inlineStr">
         <is>
-          <t>የምርት ስም አስቀምጥ</t>
+          <t>የቀረቡት ቀለሞች ከይፋዊ ድረ-ገጽዎ የተወሰዱ ግምቶች እንጂ ከምርት መመሪያ መጽሐፍዎ አይደሉም። ስህተት ከሆነ የሚታረመው እዚህ ነው።</t>
         </is>
       </c>
       <c r="E158" s="13" t="inlineStr">
         <is>
-          <t>Mallattoo olkaa'i</t>
+          <t>Halluuwwan durfaman marsariitii keessan ifaa irraa kan dubbifame malee kitaaba mallattoo keessanii irraa miti. Yoo dogoggora ta'e, asitti sirreessaa.</t>
         </is>
       </c>
       <c r="F158" s="12" t="inlineStr">
         <is>
-          <t>ንግዲ ምልክት ኣቐምጥ</t>
+          <t>እቶም ዝቐረቡ ሕብርታት ካብ ወግዓዊ መርበብ ሓበሬታኹም ዝተወስዱ ግምት እምበር ካብ መጽሓፍ ንግዲ ምልክትኩም ኣይኮኑን። ጌጋ እንተኾይኑ ኣብዚ ይእረም።</t>
         </is>
       </c>
       <c r="G158" s="13" t="inlineStr">
         <is>
-          <t>Keydi astaanta</t>
+          <t>Midabbada la soo bandhigay waa akhrinteenna degelkaaga guud, ma aha buuggaaga astaanta. Haddii ay khalad tahay, halkan ayaa lagu saxaa.</t>
         </is>
       </c>
       <c r="H158" s="13" t="inlineStr">
         <is>
-          <t>Hifadhi Alama</t>
+          <t>Rangi zilizowekwa awali ni uelewa wetu wa tovuti yako ya umma, si kitabu chako cha alama ya biashara. Ikiwa si sahihi, hapa ndipo pa kurekebisha.</t>
         </is>
       </c>
       <c r="I158" s="14" t="inlineStr"/>
@@ -13039,7 +13039,7 @@
     <row r="159" ht="44" customHeight="1">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>branding_saved</t>
+          <t>save_branding</t>
         </is>
       </c>
       <c r="B159" s="11" t="inlineStr">
@@ -13049,32 +13049,32 @@
       </c>
       <c r="C159" s="11" t="inlineStr">
         <is>
-          <t>Branding saved</t>
+          <t>Save branding</t>
         </is>
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>የምርት ስም ተቀምጧል</t>
+          <t>የምርት ስም አስቀምጥ</t>
         </is>
       </c>
       <c r="E159" s="13" t="inlineStr">
         <is>
-          <t>Mallattoon olkaa'ame</t>
+          <t>Mallattoo olkaa'i</t>
         </is>
       </c>
       <c r="F159" s="12" t="inlineStr">
         <is>
-          <t>ንግዲ ምልክት ተቐሚጡ</t>
+          <t>ንግዲ ምልክት ኣቐምጥ</t>
         </is>
       </c>
       <c r="G159" s="13" t="inlineStr">
         <is>
-          <t>Astaanta waa la keydiyay</t>
+          <t>Keydi astaanta</t>
         </is>
       </c>
       <c r="H159" s="13" t="inlineStr">
         <is>
-          <t>Alama Imehifadhiwa</t>
+          <t>Hifadhi Alama</t>
         </is>
       </c>
       <c r="I159" s="14" t="inlineStr"/>
@@ -13082,7 +13082,7 @@
     <row r="160" ht="44" customHeight="1">
       <c r="A160" s="11" t="inlineStr">
         <is>
-          <t>escalation_webhook</t>
+          <t>branding_saved</t>
         </is>
       </c>
       <c r="B160" s="11" t="inlineStr">
@@ -13092,32 +13092,32 @@
       </c>
       <c r="C160" s="11" t="inlineStr">
         <is>
-          <t>Escalation webhook</t>
+          <t>Branding saved</t>
         </is>
       </c>
       <c r="D160" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ዌብሁክ</t>
+          <t>የምርት ስም ተቀምጧል</t>
         </is>
       </c>
       <c r="E160" s="13" t="inlineStr">
         <is>
-          <t>Webhook dabarsaa</t>
+          <t>Mallattoon olkaa'ame</t>
         </is>
       </c>
       <c r="F160" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ምትሕልላፍ</t>
+          <t>ንግዲ ምልክት ተቐሚጡ</t>
         </is>
       </c>
       <c r="G160" s="13" t="inlineStr">
         <is>
-          <t>Webhook-ga gudbinta</t>
+          <t>Astaanta waa la keydiyay</t>
         </is>
       </c>
       <c r="H160" s="13" t="inlineStr">
         <is>
-          <t>Wavuti ya Masuala Yaliyoelekezwa</t>
+          <t>Alama Imehifadhiwa</t>
         </is>
       </c>
       <c r="I160" s="14" t="inlineStr"/>
@@ -13125,7 +13125,7 @@
     <row r="161" ht="44" customHeight="1">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>webhook_help</t>
+          <t>escalation_webhook</t>
         </is>
       </c>
       <c r="B161" s="11" t="inlineStr">
@@ -13135,32 +13135,32 @@
       </c>
       <c r="C161" s="11" t="inlineStr">
         <is>
-          <t>Where escalations are delivered in your contact-centre tool. Requests are signed, so the receiving system can verify they came from us. Clear the field to disconnect.</t>
+          <t>Escalation webhook</t>
         </is>
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>ጉዳዮች በእርስዎ የደንበኞች መገልገያ መሣሪያ ውስጥ የሚደርሱበት ቦታ። ጥያቄዎቹ የተፈረሙ ናቸው፤ ስለዚህ ተቀባዩ ሥርዓት ከእኛ መምጣታቸውን ማረጋገጥ ይችላል። ለማቋረጥ መስኩን ባዶ ያድርጉ።</t>
+          <t>የማሸጋገሪያ ዌብሁክ</t>
         </is>
       </c>
       <c r="E161" s="13" t="inlineStr">
         <is>
-          <t>Iddoo dhimmoonni meeshaa wiirtuu quunnamtii keessan keessatti geessifaman. Gaaffiiwwan mallatteeffamaniiru, kanaafuu sirni fudhatu nurraa dhufuu isaanii mirkaneessuu danda'a. Addaan kutuuf dirree duwwaa godhaa.</t>
+          <t>Webhook dabarsaa</t>
         </is>
       </c>
       <c r="F161" s="12" t="inlineStr">
         <is>
-          <t>ጉዳያት ኣብ መሳርሒ ማእከል ርክብኩም ዝበጽሑሉ ቦታ። እቶም ሕቶታት ዝተፈረሙ ስለዝኾኑ እቲ ተቐባሊ ስርዓት ካባና ምምጻኦም ከረጋግጽ ይኽእል። ንምቁራጽ እቲ ሜዳ ባዶ ግበሩ።</t>
+          <t>ዌብሁክ ምትሕልላፍ</t>
         </is>
       </c>
       <c r="G161" s="13" t="inlineStr">
         <is>
-          <t>Halka arrimaha lagu gudbiyo qalabkaaga xarunta macaamiisha. Codsiyada waa la saxeexay, sidaas darteed nidaamka qaataa wuu xaqiijin karaa inay naga yimaadeen. Si aad u gooyso, banaani meesha.</t>
+          <t>Webhook-ga gudbinta</t>
         </is>
       </c>
       <c r="H161" s="13" t="inlineStr">
         <is>
-          <t>Mahali masuala yanapopelekwa kwenye zana yako ya kituo cha huduma kwa wateja. Maombi yamesainiwa, ili mfumo unaopokea uweze kuthibitisha yametoka kwetu. Futa sehemu hii ili kukatisha muunganisho.</t>
+          <t>Wavuti ya Masuala Yaliyoelekezwa</t>
         </is>
       </c>
       <c r="I161" s="14" t="inlineStr"/>
@@ -13168,7 +13168,7 @@
     <row r="162" ht="44" customHeight="1">
       <c r="A162" s="11" t="inlineStr">
         <is>
-          <t>signing_secret_set</t>
+          <t>webhook_help</t>
         </is>
       </c>
       <c r="B162" s="11" t="inlineStr">
@@ -13178,32 +13178,32 @@
       </c>
       <c r="C162" s="11" t="inlineStr">
         <is>
-          <t>A signing secret is set. It cannot be shown again — saving a URL here issues a new one and the old one stops working.</t>
+          <t>Where escalations are delivered in your contact-centre tool. Requests are signed, so the receiving system can verify they came from us. Clear the field to disconnect.</t>
         </is>
       </c>
       <c r="D162" s="12" t="inlineStr">
         <is>
-          <t>የፊርማ ሚስጥር ተዘጋጅቷል። እንደገና ማሳየት አይቻልም — እዚህ አድራሻ ማስቀመጥ አዲስ ያወጣል፤ አሮጌው መስራት ያቆማል።</t>
+          <t>ጉዳዮች በእርስዎ የደንበኞች መገልገያ መሣሪያ ውስጥ የሚደርሱበት ቦታ። ጥያቄዎቹ የተፈረሙ ናቸው፤ ስለዚህ ተቀባዩ ሥርዓት ከእኛ መምጣታቸውን ማረጋገጥ ይችላል። ለማቋረጥ መስኩን ባዶ ያድርጉ።</t>
         </is>
       </c>
       <c r="E162" s="13" t="inlineStr">
         <is>
-          <t>Iccitiin mallattoo qophaa'eera. Irra deebi'anii agarsiisuun hin danda'amu — asitti URL olkaa'uun haaraa baasa, kan duraa immoo hojii dhaaba.</t>
+          <t>Iddoo dhimmoonni meeshaa wiirtuu quunnamtii keessan keessatti geessifaman. Gaaffiiwwan mallatteeffamaniiru, kanaafuu sirni fudhatu nurraa dhufuu isaanii mirkaneessuu danda'a. Addaan kutuuf dirree duwwaa godhaa.</t>
         </is>
       </c>
       <c r="F162" s="12" t="inlineStr">
         <is>
-          <t>ምስጢር ፌርማ ተቐሚጡ። መሊስካ ክርአ ኣይክእልን — ኣብዚ ኣድራሻ ምቕማጥ ሓድሽ የውጽእ፣ እቲ ናይ ቀደም ይቋረጽ።</t>
+          <t>ጉዳያት ኣብ መሳርሒ ማእከል ርክብኩም ዝበጽሑሉ ቦታ። እቶም ሕቶታት ዝተፈረሙ ስለዝኾኑ እቲ ተቐባሊ ስርዓት ካባና ምምጻኦም ከረጋግጽ ይኽእል። ንምቁራጽ እቲ ሜዳ ባዶ ግበሩ።</t>
         </is>
       </c>
       <c r="G162" s="13" t="inlineStr">
         <is>
-          <t>Sir saxeex ayaa la dejiyay. Mar kale lama tusi karo — URL halkan lagu keydiyo wuxuu soo saarayaa mid cusub, kii hore wuu shaqo joojiyaa.</t>
+          <t>Halka arrimaha lagu gudbiyo qalabkaaga xarunta macaamiisha. Codsiyada waa la saxeexay, sidaas darteed nidaamka qaataa wuu xaqiijin karaa inay naga yimaadeen. Si aad u gooyso, banaani meesha.</t>
         </is>
       </c>
       <c r="H162" s="13" t="inlineStr">
         <is>
-          <t>Siri ya kusaini imewekwa. Haiwezi kuonyeshwa tena — kuhifadhi kiungo hapa kunatoa siri mpya na ile ya zamani inaacha kufanya kazi.</t>
+          <t>Mahali masuala yanapopelekwa kwenye zana yako ya kituo cha huduma kwa wateja. Maombi yamesainiwa, ili mfumo unaopokea uweze kuthibitisha yametoka kwetu. Futa sehemu hii ili kukatisha muunganisho.</t>
         </is>
       </c>
       <c r="I162" s="14" t="inlineStr"/>
@@ -13211,7 +13211,7 @@
     <row r="163" ht="44" customHeight="1">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>webhook_connected</t>
+          <t>signing_secret_set</t>
         </is>
       </c>
       <c r="B163" s="11" t="inlineStr">
@@ -13221,32 +13221,32 @@
       </c>
       <c r="C163" s="11" t="inlineStr">
         <is>
-          <t>Webhook connected</t>
+          <t>A signing secret is set. It cannot be shown again — saving a URL here issues a new one and the old one stops working.</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ተገናኝቷል</t>
+          <t>የፊርማ ሚስጥር ተዘጋጅቷል። እንደገና ማሳየት አይቻልም — እዚህ አድራሻ ማስቀመጥ አዲስ ያወጣል፤ አሮጌው መስራት ያቆማል።</t>
         </is>
       </c>
       <c r="E163" s="13" t="inlineStr">
         <is>
-          <t>Webhook walqunnamsiifame</t>
+          <t>Iccitiin mallattoo qophaa'eera. Irra deebi'anii agarsiisuun hin danda'amu — asitti URL olkaa'uun haaraa baasa, kan duraa immoo hojii dhaaba.</t>
         </is>
       </c>
       <c r="F163" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ተራኺቡ</t>
+          <t>ምስጢር ፌርማ ተቐሚጡ። መሊስካ ክርአ ኣይክእልን — ኣብዚ ኣድራሻ ምቕማጥ ሓድሽ የውጽእ፣ እቲ ናይ ቀደም ይቋረጽ።</t>
         </is>
       </c>
       <c r="G163" s="13" t="inlineStr">
         <is>
-          <t>Webhook waa la xiray</t>
+          <t>Sir saxeex ayaa la dejiyay. Mar kale lama tusi karo — URL halkan lagu keydiyo wuxuu soo saarayaa mid cusub, kii hore wuu shaqo joojiyaa.</t>
         </is>
       </c>
       <c r="H163" s="13" t="inlineStr">
         <is>
-          <t>Wavuti Imeunganishwa</t>
+          <t>Siri ya kusaini imewekwa. Haiwezi kuonyeshwa tena — kuhifadhi kiungo hapa kunatoa siri mpya na ile ya zamani inaacha kufanya kazi.</t>
         </is>
       </c>
       <c r="I163" s="14" t="inlineStr"/>
@@ -13254,7 +13254,7 @@
     <row r="164" ht="44" customHeight="1">
       <c r="A164" s="11" t="inlineStr">
         <is>
-          <t>webhook_disconnected</t>
+          <t>webhook_connected</t>
         </is>
       </c>
       <c r="B164" s="11" t="inlineStr">
@@ -13264,32 +13264,32 @@
       </c>
       <c r="C164" s="11" t="inlineStr">
         <is>
-          <t>Webhook disconnected</t>
+          <t>Webhook connected</t>
         </is>
       </c>
       <c r="D164" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ተቋርጧል</t>
+          <t>ዌብሁክ ተገናኝቷል</t>
         </is>
       </c>
       <c r="E164" s="13" t="inlineStr">
         <is>
-          <t>Webhook addaan kutame</t>
+          <t>Webhook walqunnamsiifame</t>
         </is>
       </c>
       <c r="F164" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ተቛሪጹ</t>
+          <t>ዌብሁክ ተራኺቡ</t>
         </is>
       </c>
       <c r="G164" s="13" t="inlineStr">
         <is>
-          <t>Webhook waa la goynay</t>
+          <t>Webhook waa la xiray</t>
         </is>
       </c>
       <c r="H164" s="13" t="inlineStr">
         <is>
-          <t>Wavuti Imekatishwa</t>
+          <t>Wavuti Imeunganishwa</t>
         </is>
       </c>
       <c r="I164" s="14" t="inlineStr"/>
@@ -13297,7 +13297,7 @@
     <row r="165" ht="44" customHeight="1">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>your_password</t>
+          <t>webhook_disconnected</t>
         </is>
       </c>
       <c r="B165" s="11" t="inlineStr">
@@ -13307,32 +13307,32 @@
       </c>
       <c r="C165" s="11" t="inlineStr">
         <is>
-          <t>Your password</t>
+          <t>Webhook disconnected</t>
         </is>
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>የይለፍ ቃልዎ</t>
+          <t>ዌብሁክ ተቋርጧል</t>
         </is>
       </c>
       <c r="E165" s="13" t="inlineStr">
         <is>
-          <t>Jecha darbii keessan</t>
+          <t>Webhook addaan kutame</t>
         </is>
       </c>
       <c r="F165" s="12" t="inlineStr">
         <is>
-          <t>መሕለፊ ቃልኩም</t>
+          <t>ዌብሁክ ተቛሪጹ</t>
         </is>
       </c>
       <c r="G165" s="13" t="inlineStr">
         <is>
-          <t>Furahaaga sirta ah</t>
+          <t>Webhook waa la goynay</t>
         </is>
       </c>
       <c r="H165" s="13" t="inlineStr">
         <is>
-          <t>Nenosiri Lako</t>
+          <t>Wavuti Imekatishwa</t>
         </is>
       </c>
       <c r="I165" s="14" t="inlineStr"/>
@@ -13340,7 +13340,7 @@
     <row r="166" ht="44" customHeight="1">
       <c r="A166" s="11" t="inlineStr">
         <is>
-          <t>current_password</t>
+          <t>your_password</t>
         </is>
       </c>
       <c r="B166" s="11" t="inlineStr">
@@ -13350,32 +13350,32 @@
       </c>
       <c r="C166" s="11" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Your password</t>
         </is>
       </c>
       <c r="D166" s="12" t="inlineStr">
         <is>
-          <t>አሁን ያለው</t>
+          <t>የይለፍ ቃልዎ</t>
         </is>
       </c>
       <c r="E166" s="13" t="inlineStr">
         <is>
-          <t>Kan ammaa</t>
+          <t>Jecha darbii keessan</t>
         </is>
       </c>
       <c r="F166" s="12" t="inlineStr">
         <is>
-          <t>ናይ ሕጂ</t>
+          <t>መሕለፊ ቃልኩም</t>
         </is>
       </c>
       <c r="G166" s="13" t="inlineStr">
         <is>
-          <t>Kan hadda</t>
+          <t>Furahaaga sirta ah</t>
         </is>
       </c>
       <c r="H166" s="13" t="inlineStr">
         <is>
-          <t>La Sasa</t>
+          <t>Nenosiri Lako</t>
         </is>
       </c>
       <c r="I166" s="14" t="inlineStr"/>
@@ -13383,7 +13383,7 @@
     <row r="167" ht="44" customHeight="1">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>new_password_12</t>
+          <t>current_password</t>
         </is>
       </c>
       <c r="B167" s="11" t="inlineStr">
@@ -13393,32 +13393,32 @@
       </c>
       <c r="C167" s="11" t="inlineStr">
         <is>
-          <t>New (12+ characters)</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>አዲስ (12+ ቁምፊዎች)</t>
+          <t>አሁን ያለው</t>
         </is>
       </c>
       <c r="E167" s="13" t="inlineStr">
         <is>
-          <t>Haaraa (arfiilee 12+)</t>
+          <t>Kan ammaa</t>
         </is>
       </c>
       <c r="F167" s="12" t="inlineStr">
         <is>
-          <t>ሓድሽ (12+ ፊደላት)</t>
+          <t>ናይ ሕጂ</t>
         </is>
       </c>
       <c r="G167" s="13" t="inlineStr">
         <is>
-          <t>Cusub (12+ xaraf)</t>
+          <t>Kan hadda</t>
         </is>
       </c>
       <c r="H167" s="13" t="inlineStr">
         <is>
-          <t>Jipya (herufi 12+)</t>
+          <t>La Sasa</t>
         </is>
       </c>
       <c r="I167" s="14" t="inlineStr"/>
@@ -13426,7 +13426,7 @@
     <row r="168" ht="44" customHeight="1">
       <c r="A168" s="11" t="inlineStr">
         <is>
-          <t>password_change_help</t>
+          <t>new_password_12</t>
         </is>
       </c>
       <c r="B168" s="11" t="inlineStr">
@@ -13436,32 +13436,32 @@
       </c>
       <c r="C168" s="11" t="inlineStr">
         <is>
-          <t>Changing it signs out every other browser you are signed in on.</t>
+          <t>New (12+ characters)</t>
         </is>
       </c>
       <c r="D168" s="12" t="inlineStr">
         <is>
-          <t>መቀየር በገቡበት በሌላ በእያንዳንዱ አሳሽ ላይ ያስወጣዎታል።</t>
+          <t>አዲስ (12+ ቁምፊዎች)</t>
         </is>
       </c>
       <c r="E168" s="13" t="inlineStr">
         <is>
-          <t>Jijjiiruun biraawzarii biroo isin keessa seentan hunda irraa isin baasa.</t>
+          <t>Haaraa (arfiilee 12+)</t>
         </is>
       </c>
       <c r="F168" s="12" t="inlineStr">
         <is>
-          <t>ምቕያሩ ኣብ ካልእ ዝኣተኹምሉ ኩሉ መርበብ መንሸራተቲ የውጽኣኩም።</t>
+          <t>ሓድሽ (12+ ፊደላት)</t>
         </is>
       </c>
       <c r="G168" s="13" t="inlineStr">
         <is>
-          <t>Beddelkeedu wuxuu kaa saarayaa dhammaan browser-yada kale ee aad ku jirto.</t>
+          <t>Cusub (12+ xaraf)</t>
         </is>
       </c>
       <c r="H168" s="13" t="inlineStr">
         <is>
-          <t>Kulibadilisha kunamtoa kila kivinjari kingine ulichoingia.</t>
+          <t>Jipya (herufi 12+)</t>
         </is>
       </c>
       <c r="I168" s="14" t="inlineStr"/>
@@ -13469,7 +13469,7 @@
     <row r="169" ht="44" customHeight="1">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>change_password</t>
+          <t>password_change_help</t>
         </is>
       </c>
       <c r="B169" s="11" t="inlineStr">
@@ -13479,32 +13479,32 @@
       </c>
       <c r="C169" s="11" t="inlineStr">
         <is>
-          <t>Change password</t>
+          <t>Changing it signs out every other browser you are signed in on.</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>የይለፍ ቃል ቀይር</t>
+          <t>መቀየር በገቡበት በሌላ በእያንዳንዱ አሳሽ ላይ ያስወጣዎታል።</t>
         </is>
       </c>
       <c r="E169" s="13" t="inlineStr">
         <is>
-          <t>Jecha darbii jijjiiri</t>
+          <t>Jijjiiruun biraawzarii biroo isin keessa seentan hunda irraa isin baasa.</t>
         </is>
       </c>
       <c r="F169" s="12" t="inlineStr">
         <is>
-          <t>መሕለፊ ቃል ቀይር</t>
+          <t>ምቕያሩ ኣብ ካልእ ዝኣተኹምሉ ኩሉ መርበብ መንሸራተቲ የውጽኣኩም።</t>
         </is>
       </c>
       <c r="G169" s="13" t="inlineStr">
         <is>
-          <t>Bedel furaha sirta ah</t>
+          <t>Beddelkeedu wuxuu kaa saarayaa dhammaan browser-yada kale ee aad ku jirto.</t>
         </is>
       </c>
       <c r="H169" s="13" t="inlineStr">
         <is>
-          <t>Badilisha Nenosiri</t>
+          <t>Kulibadilisha kunamtoa kila kivinjari kingine ulichoingia.</t>
         </is>
       </c>
       <c r="I169" s="14" t="inlineStr"/>
@@ -13512,7 +13512,7 @@
     <row r="170" ht="44" customHeight="1">
       <c r="A170" s="11" t="inlineStr">
         <is>
-          <t>password_changed</t>
+          <t>change_password</t>
         </is>
       </c>
       <c r="B170" s="11" t="inlineStr">
@@ -13522,32 +13522,32 @@
       </c>
       <c r="C170" s="11" t="inlineStr">
         <is>
-          <t>Password changed. Other sessions were signed out.</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="D170" s="12" t="inlineStr">
         <is>
-          <t>የይለፍ ቃል ተቀይሯል። ሌሎች ክፍለ-ጊዜዎች ወጥተዋል።</t>
+          <t>የይለፍ ቃል ቀይር</t>
         </is>
       </c>
       <c r="E170" s="13" t="inlineStr">
         <is>
-          <t>Jechi darbii jijjiirameera. Sessionoonni biroo ba'aniiru.</t>
+          <t>Jecha darbii jijjiiri</t>
         </is>
       </c>
       <c r="F170" s="12" t="inlineStr">
         <is>
-          <t>መሕለፊ ቃል ተቐዪሩ። ካልኦት ክፍለ-ግዜታት ወጺኦም።</t>
+          <t>መሕለፊ ቃል ቀይር</t>
         </is>
       </c>
       <c r="G170" s="13" t="inlineStr">
         <is>
-          <t>Furaha sirta ah waa la beddelay. Kalfadhiyada kale waa laga saaray.</t>
+          <t>Bedel furaha sirta ah</t>
         </is>
       </c>
       <c r="H170" s="13" t="inlineStr">
         <is>
-          <t>Nenosiri Limebadilishwa. Vikao vingine vimetolewa.</t>
+          <t>Badilisha Nenosiri</t>
         </is>
       </c>
       <c r="I170" s="14" t="inlineStr"/>
@@ -13555,7 +13555,7 @@
     <row r="171" ht="44" customHeight="1">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>add_person</t>
+          <t>password_changed</t>
         </is>
       </c>
       <c r="B171" s="11" t="inlineStr">
@@ -13565,32 +13565,32 @@
       </c>
       <c r="C171" s="11" t="inlineStr">
         <is>
-          <t>Add person</t>
+          <t>Password changed. Other sessions were signed out.</t>
         </is>
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>ሰው ጨምር</t>
+          <t>የይለፍ ቃል ተቀይሯል። ሌሎች ክፍለ-ጊዜዎች ወጥተዋል።</t>
         </is>
       </c>
       <c r="E171" s="13" t="inlineStr">
         <is>
-          <t>Nama dabali</t>
+          <t>Jechi darbii jijjiirameera. Sessionoonni biroo ba'aniiru.</t>
         </is>
       </c>
       <c r="F171" s="12" t="inlineStr">
         <is>
-          <t>ሰብ ወስኽ</t>
+          <t>መሕለፊ ቃል ተቐዪሩ። ካልኦት ክፍለ-ግዜታት ወጺኦም።</t>
         </is>
       </c>
       <c r="G171" s="13" t="inlineStr">
         <is>
-          <t>Ku dar qof</t>
+          <t>Furaha sirta ah waa la beddelay. Kalfadhiyada kale waa laga saaray.</t>
         </is>
       </c>
       <c r="H171" s="13" t="inlineStr">
         <is>
-          <t>Ongeza Mtu</t>
+          <t>Nenosiri Limebadilishwa. Vikao vingine vimetolewa.</t>
         </is>
       </c>
       <c r="I171" s="14" t="inlineStr"/>
@@ -13598,7 +13598,7 @@
     <row r="172" ht="44" customHeight="1">
       <c r="A172" s="11" t="inlineStr">
         <is>
-          <t>n_accounts</t>
+          <t>add_person</t>
         </is>
       </c>
       <c r="B172" s="11" t="inlineStr">
@@ -13608,32 +13608,32 @@
       </c>
       <c r="C172" s="11" t="inlineStr">
         <is>
-          <t>{n} accounts</t>
+          <t>Add person</t>
         </is>
       </c>
       <c r="D172" s="12" t="inlineStr">
         <is>
-          <t>{n} መለያዎች</t>
+          <t>ሰው ጨምር</t>
         </is>
       </c>
       <c r="E172" s="13" t="inlineStr">
         <is>
-          <t>Herregoota {n}</t>
+          <t>Nama dabali</t>
         </is>
       </c>
       <c r="F172" s="12" t="inlineStr">
         <is>
-          <t>{n} ሕሳባት</t>
+          <t>ሰብ ወስኽ</t>
         </is>
       </c>
       <c r="G172" s="13" t="inlineStr">
         <is>
-          <t>{n} xisaabood</t>
+          <t>Ku dar qof</t>
         </is>
       </c>
       <c r="H172" s="13" t="inlineStr">
         <is>
-          <t>Akaunti {n}</t>
+          <t>Ongeza Mtu</t>
         </is>
       </c>
       <c r="I172" s="14" t="inlineStr"/>
@@ -13641,7 +13641,7 @@
     <row r="173" ht="44" customHeight="1">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>one_account</t>
+          <t>n_accounts</t>
         </is>
       </c>
       <c r="B173" s="11" t="inlineStr">
@@ -13651,27 +13651,27 @@
       </c>
       <c r="C173" s="11" t="inlineStr">
         <is>
-          <t>{n} account</t>
+          <t>{n} accounts</t>
         </is>
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>{n} መለያ</t>
+          <t>{n} መለያዎች</t>
         </is>
       </c>
       <c r="E173" s="13" t="inlineStr">
         <is>
-          <t>Herrega {n}</t>
+          <t>Herregoota {n}</t>
         </is>
       </c>
       <c r="F173" s="12" t="inlineStr">
         <is>
-          <t>{n} ሕሳብ</t>
+          <t>{n} ሕሳባት</t>
         </is>
       </c>
       <c r="G173" s="13" t="inlineStr">
         <is>
-          <t>{n} xisaab</t>
+          <t>{n} xisaabood</t>
         </is>
       </c>
       <c r="H173" s="13" t="inlineStr">
@@ -13684,7 +13684,7 @@
     <row r="174" ht="44" customHeight="1">
       <c r="A174" s="11" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>one_account</t>
         </is>
       </c>
       <c r="B174" s="11" t="inlineStr">
@@ -13694,32 +13694,32 @@
       </c>
       <c r="C174" s="11" t="inlineStr">
         <is>
-          <t>Person</t>
+          <t>{n} account</t>
         </is>
       </c>
       <c r="D174" s="12" t="inlineStr">
         <is>
-          <t>ሰው</t>
+          <t>{n} መለያ</t>
         </is>
       </c>
       <c r="E174" s="13" t="inlineStr">
         <is>
-          <t>Nama</t>
+          <t>Herrega {n}</t>
         </is>
       </c>
       <c r="F174" s="12" t="inlineStr">
         <is>
-          <t>ሰብ</t>
+          <t>{n} ሕሳብ</t>
         </is>
       </c>
       <c r="G174" s="13" t="inlineStr">
         <is>
-          <t>Qof</t>
+          <t>{n} xisaab</t>
         </is>
       </c>
       <c r="H174" s="13" t="inlineStr">
         <is>
-          <t>Mtu</t>
+          <t>Akaunti {n}</t>
         </is>
       </c>
       <c r="I174" s="14" t="inlineStr"/>
@@ -13727,7 +13727,7 @@
     <row r="175" ht="44" customHeight="1">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>person</t>
         </is>
       </c>
       <c r="B175" s="11" t="inlineStr">
@@ -13737,32 +13737,32 @@
       </c>
       <c r="C175" s="11" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Person</t>
         </is>
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>ሚና</t>
+          <t>ሰው</t>
         </is>
       </c>
       <c r="E175" s="13" t="inlineStr">
         <is>
-          <t>Gahee</t>
+          <t>Nama</t>
         </is>
       </c>
       <c r="F175" s="12" t="inlineStr">
         <is>
-          <t>ግደ</t>
+          <t>ሰብ</t>
         </is>
       </c>
       <c r="G175" s="13" t="inlineStr">
         <is>
-          <t>Doorka</t>
+          <t>Qof</t>
         </is>
       </c>
       <c r="H175" s="13" t="inlineStr">
         <is>
-          <t>Wadhifa</t>
+          <t>Mtu</t>
         </is>
       </c>
       <c r="I175" s="14" t="inlineStr"/>
@@ -13770,7 +13770,7 @@
     <row r="176" ht="44" customHeight="1">
       <c r="A176" s="11" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>role</t>
         </is>
       </c>
       <c r="B176" s="11" t="inlineStr">
@@ -13780,32 +13780,32 @@
       </c>
       <c r="C176" s="11" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="D176" s="12" t="inlineStr">
         <is>
-          <t>ሁኔታ</t>
+          <t>ሚና</t>
         </is>
       </c>
       <c r="E176" s="13" t="inlineStr">
         <is>
-          <t>Haala</t>
+          <t>Gahee</t>
         </is>
       </c>
       <c r="F176" s="12" t="inlineStr">
         <is>
-          <t>ኩነታት</t>
+          <t>ግደ</t>
         </is>
       </c>
       <c r="G176" s="13" t="inlineStr">
         <is>
-          <t>Xaalada</t>
+          <t>Doorka</t>
         </is>
       </c>
       <c r="H176" s="13" t="inlineStr">
         <is>
-          <t>Hali</t>
+          <t>Wadhifa</t>
         </is>
       </c>
       <c r="I176" s="14" t="inlineStr"/>
@@ -13813,7 +13813,7 @@
     <row r="177" ht="44" customHeight="1">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>last_signed_in</t>
+          <t>status</t>
         </is>
       </c>
       <c r="B177" s="11" t="inlineStr">
@@ -13823,32 +13823,32 @@
       </c>
       <c r="C177" s="11" t="inlineStr">
         <is>
-          <t>Last signed in</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>መጨረሻ የገቡበት</t>
+          <t>ሁኔታ</t>
         </is>
       </c>
       <c r="E177" s="13" t="inlineStr">
         <is>
-          <t>Yeroo dhumaa seenan</t>
+          <t>Haala</t>
         </is>
       </c>
       <c r="F177" s="12" t="inlineStr">
         <is>
-          <t>ናይ መወዳእታ ዝኣተዉሉ</t>
+          <t>ኩነታት</t>
         </is>
       </c>
       <c r="G177" s="13" t="inlineStr">
         <is>
-          <t>Markii ugu dambeysay ee la galay</t>
+          <t>Xaalada</t>
         </is>
       </c>
       <c r="H177" s="13" t="inlineStr">
         <is>
-          <t>Aliingia Mwisho</t>
+          <t>Hali</t>
         </is>
       </c>
       <c r="I177" s="14" t="inlineStr"/>
@@ -13856,7 +13856,7 @@
     <row r="178" ht="44" customHeight="1">
       <c r="A178" s="11" t="inlineStr">
         <is>
-          <t>actions</t>
+          <t>last_signed_in</t>
         </is>
       </c>
       <c r="B178" s="11" t="inlineStr">
@@ -13866,32 +13866,32 @@
       </c>
       <c r="C178" s="11" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Last signed in</t>
         </is>
       </c>
       <c r="D178" s="12" t="inlineStr">
         <is>
-          <t>ድርጊቶች</t>
+          <t>መጨረሻ የገቡበት</t>
         </is>
       </c>
       <c r="E178" s="13" t="inlineStr">
         <is>
-          <t>Gochaalee</t>
+          <t>Yeroo dhumaa seenan</t>
         </is>
       </c>
       <c r="F178" s="12" t="inlineStr">
         <is>
-          <t>ተግባራት</t>
+          <t>ናይ መወዳእታ ዝኣተዉሉ</t>
         </is>
       </c>
       <c r="G178" s="13" t="inlineStr">
         <is>
-          <t>Ficillo</t>
+          <t>Markii ugu dambeysay ee la galay</t>
         </is>
       </c>
       <c r="H178" s="13" t="inlineStr">
         <is>
-          <t>Vitendo</t>
+          <t>Aliingia Mwisho</t>
         </is>
       </c>
       <c r="I178" s="14" t="inlineStr"/>
@@ -13899,7 +13899,7 @@
     <row r="179" ht="44" customHeight="1">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>thats_you</t>
+          <t>actions</t>
         </is>
       </c>
       <c r="B179" s="11" t="inlineStr">
@@ -13909,32 +13909,32 @@
       </c>
       <c r="C179" s="11" t="inlineStr">
         <is>
-          <t>that’s you</t>
+          <t>Actions</t>
         </is>
       </c>
       <c r="D179" s="12" t="inlineStr">
         <is>
-          <t>ይህ እርስዎ ነዎት</t>
+          <t>ድርጊቶች</t>
         </is>
       </c>
       <c r="E179" s="13" t="inlineStr">
         <is>
-          <t>kun isinuma</t>
+          <t>Gochaalee</t>
         </is>
       </c>
       <c r="F179" s="12" t="inlineStr">
         <is>
-          <t>እዚ ንስኹም ኢኹም</t>
+          <t>ተግባራት</t>
         </is>
       </c>
       <c r="G179" s="13" t="inlineStr">
         <is>
-          <t>kaasi waa adiga</t>
+          <t>Ficillo</t>
         </is>
       </c>
       <c r="H179" s="13" t="inlineStr">
         <is>
-          <t>huyo ni wewe</t>
+          <t>Vitendo</t>
         </is>
       </c>
       <c r="I179" s="14" t="inlineStr"/>
@@ -13942,7 +13942,7 @@
     <row r="180" ht="44" customHeight="1">
       <c r="A180" s="11" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>thats_you</t>
         </is>
       </c>
       <c r="B180" s="11" t="inlineStr">
@@ -13952,32 +13952,32 @@
       </c>
       <c r="C180" s="11" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>that’s you</t>
         </is>
       </c>
       <c r="D180" s="12" t="inlineStr">
         <is>
-          <t>ንቁ</t>
+          <t>ይህ እርስዎ ነዎት</t>
         </is>
       </c>
       <c r="E180" s="13" t="inlineStr">
         <is>
-          <t>Ka'aa</t>
+          <t>kun isinuma</t>
         </is>
       </c>
       <c r="F180" s="12" t="inlineStr">
         <is>
-          <t>ንጡፍ</t>
+          <t>እዚ ንስኹም ኢኹም</t>
         </is>
       </c>
       <c r="G180" s="13" t="inlineStr">
         <is>
-          <t>Firfircoon</t>
+          <t>kaasi waa adiga</t>
         </is>
       </c>
       <c r="H180" s="13" t="inlineStr">
         <is>
-          <t>Hai</t>
+          <t>huyo ni wewe</t>
         </is>
       </c>
       <c r="I180" s="14" t="inlineStr"/>
@@ -13985,7 +13985,7 @@
     <row r="181" ht="44" customHeight="1">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t>disabled</t>
+          <t>active</t>
         </is>
       </c>
       <c r="B181" s="11" t="inlineStr">
@@ -13995,32 +13995,32 @@
       </c>
       <c r="C181" s="11" t="inlineStr">
         <is>
-          <t>Disabled</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>የተሰናከለ</t>
+          <t>ንቁ</t>
         </is>
       </c>
       <c r="E181" s="13" t="inlineStr">
         <is>
-          <t>Kan dhaabame</t>
+          <t>Ka'aa</t>
         </is>
       </c>
       <c r="F181" s="12" t="inlineStr">
         <is>
-          <t>ዝተዓገተ</t>
+          <t>ንጡፍ</t>
         </is>
       </c>
       <c r="G181" s="13" t="inlineStr">
         <is>
-          <t>La demiyay</t>
+          <t>Firfircoon</t>
         </is>
       </c>
       <c r="H181" s="13" t="inlineStr">
         <is>
-          <t>Imezimwa</t>
+          <t>Hai</t>
         </is>
       </c>
       <c r="I181" s="14" t="inlineStr"/>
@@ -14028,7 +14028,7 @@
     <row r="182" ht="44" customHeight="1">
       <c r="A182" s="11" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>disabled</t>
         </is>
       </c>
       <c r="B182" s="11" t="inlineStr">
@@ -14038,32 +14038,32 @@
       </c>
       <c r="C182" s="11" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>Disabled</t>
         </is>
       </c>
       <c r="D182" s="12" t="inlineStr">
         <is>
-          <t>በጭራሽ</t>
+          <t>የተሰናከለ</t>
         </is>
       </c>
       <c r="E182" s="13" t="inlineStr">
         <is>
-          <t>gonkumaa</t>
+          <t>Kan dhaabame</t>
         </is>
       </c>
       <c r="F182" s="12" t="inlineStr">
         <is>
-          <t>ፈጺሙ</t>
+          <t>ዝተዓገተ</t>
         </is>
       </c>
       <c r="G182" s="13" t="inlineStr">
         <is>
-          <t>waligeed</t>
+          <t>La demiyay</t>
         </is>
       </c>
       <c r="H182" s="13" t="inlineStr">
         <is>
-          <t>kamwe</t>
+          <t>Imezimwa</t>
         </is>
       </c>
       <c r="I182" s="14" t="inlineStr"/>
@@ -14071,7 +14071,7 @@
     <row r="183" ht="44" customHeight="1">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t>disable</t>
+          <t>never</t>
         </is>
       </c>
       <c r="B183" s="11" t="inlineStr">
@@ -14081,32 +14081,32 @@
       </c>
       <c r="C183" s="11" t="inlineStr">
         <is>
-          <t>Disable</t>
+          <t>never</t>
         </is>
       </c>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>አሰናክል</t>
+          <t>በጭራሽ</t>
         </is>
       </c>
       <c r="E183" s="13" t="inlineStr">
         <is>
-          <t>Dhaabi</t>
+          <t>gonkumaa</t>
         </is>
       </c>
       <c r="F183" s="12" t="inlineStr">
         <is>
-          <t>ዓግት</t>
+          <t>ፈጺሙ</t>
         </is>
       </c>
       <c r="G183" s="13" t="inlineStr">
         <is>
-          <t>Demi</t>
+          <t>waligeed</t>
         </is>
       </c>
       <c r="H183" s="13" t="inlineStr">
         <is>
-          <t>Zima</t>
+          <t>kamwe</t>
         </is>
       </c>
       <c r="I183" s="14" t="inlineStr"/>
@@ -14114,7 +14114,7 @@
     <row r="184" ht="44" customHeight="1">
       <c r="A184" s="11" t="inlineStr">
         <is>
-          <t>restore</t>
+          <t>disable</t>
         </is>
       </c>
       <c r="B184" s="11" t="inlineStr">
@@ -14124,32 +14124,32 @@
       </c>
       <c r="C184" s="11" t="inlineStr">
         <is>
-          <t>Restore</t>
+          <t>Disable</t>
         </is>
       </c>
       <c r="D184" s="12" t="inlineStr">
         <is>
-          <t>መልስ</t>
+          <t>አሰናክል</t>
         </is>
       </c>
       <c r="E184" s="13" t="inlineStr">
         <is>
-          <t>Deebisi</t>
+          <t>Dhaabi</t>
         </is>
       </c>
       <c r="F184" s="12" t="inlineStr">
         <is>
-          <t>መልስ</t>
+          <t>ዓግት</t>
         </is>
       </c>
       <c r="G184" s="13" t="inlineStr">
         <is>
-          <t>Soo celi</t>
+          <t>Demi</t>
         </is>
       </c>
       <c r="H184" s="13" t="inlineStr">
         <is>
-          <t>Rejesha</t>
+          <t>Zima</t>
         </is>
       </c>
       <c r="I184" s="14" t="inlineStr"/>
@@ -14157,7 +14157,7 @@
     <row r="185" ht="44" customHeight="1">
       <c r="A185" s="11" t="inlineStr">
         <is>
-          <t>what_each_role_can_do</t>
+          <t>restore</t>
         </is>
       </c>
       <c r="B185" s="11" t="inlineStr">
@@ -14167,32 +14167,32 @@
       </c>
       <c r="C185" s="11" t="inlineStr">
         <is>
-          <t>What each role can do</t>
+          <t>Restore</t>
         </is>
       </c>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>እያንዳንዱ ሚና ምን ማድረግ ይችላል</t>
+          <t>መልስ</t>
         </is>
       </c>
       <c r="E185" s="13" t="inlineStr">
         <is>
-          <t>Gaheen tokkoon tokkoon isaanii maal gochuu danda'a</t>
+          <t>Deebisi</t>
         </is>
       </c>
       <c r="F185" s="12" t="inlineStr">
         <is>
-          <t>ነፍስ ወከፍ ግደ እንታይ ክገብር ይኽእል</t>
+          <t>መልስ</t>
         </is>
       </c>
       <c r="G185" s="13" t="inlineStr">
         <is>
-          <t>Waxa doorkiiba uu samayn karo</t>
+          <t>Soo celi</t>
         </is>
       </c>
       <c r="H185" s="13" t="inlineStr">
         <is>
-          <t>Kila Wadhifa Unaweza Kufanya Nini</t>
+          <t>Rejesha</t>
         </is>
       </c>
       <c r="I185" s="14" t="inlineStr"/>
@@ -14200,7 +14200,7 @@
     <row r="186" ht="44" customHeight="1">
       <c r="A186" s="11" t="inlineStr">
         <is>
-          <t>calls_per_teller</t>
+          <t>what_each_role_can_do</t>
         </is>
       </c>
       <c r="B186" s="11" t="inlineStr">
@@ -14210,32 +14210,32 @@
       </c>
       <c r="C186" s="11" t="inlineStr">
         <is>
-          <t>Calls per teller</t>
+          <t>What each role can do</t>
         </is>
       </c>
       <c r="D186" s="12" t="inlineStr">
         <is>
-          <t>በተጠሪ የተያዙ ጥሪዎች</t>
+          <t>እያንዳንዱ ሚና ምን ማድረግ ይችላል</t>
         </is>
       </c>
       <c r="E186" s="13" t="inlineStr">
         <is>
-          <t>Bilbilawwan teellaraan</t>
+          <t>Gaheen tokkoon tokkoon isaanii maal gochuu danda'a</t>
         </is>
       </c>
       <c r="F186" s="12" t="inlineStr">
         <is>
-          <t>ጻውዒታት ብተለር</t>
+          <t>ነፍስ ወከፍ ግደ እንታይ ክገብር ይኽእል</t>
         </is>
       </c>
       <c r="G186" s="13" t="inlineStr">
         <is>
-          <t>Wicitaanka teller kasta</t>
+          <t>Waxa doorkiiba uu samayn karo</t>
         </is>
       </c>
       <c r="H186" s="13" t="inlineStr">
         <is>
-          <t>Simu kwa Kila Afisa</t>
+          <t>Kila Wadhifa Unaweza Kufanya Nini</t>
         </is>
       </c>
       <c r="I186" s="14" t="inlineStr"/>
@@ -14243,7 +14243,7 @@
     <row r="187" ht="44" customHeight="1">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t>unit_calls</t>
+          <t>calls_per_teller</t>
         </is>
       </c>
       <c r="B187" s="11" t="inlineStr">
@@ -14253,32 +14253,32 @@
       </c>
       <c r="C187" s="11" t="inlineStr">
         <is>
-          <t>calls</t>
+          <t>Calls per teller</t>
         </is>
       </c>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>ጥሪዎች</t>
+          <t>በተጠሪ የተያዙ ጥሪዎች</t>
         </is>
       </c>
       <c r="E187" s="13" t="inlineStr">
         <is>
-          <t>bilbilawwan</t>
+          <t>Bilbilawwan teellaraan</t>
         </is>
       </c>
       <c r="F187" s="12" t="inlineStr">
         <is>
-          <t>ጻውዒታት</t>
+          <t>ጻውዒታት ብተለር</t>
         </is>
       </c>
       <c r="G187" s="13" t="inlineStr">
         <is>
-          <t>wicitaanno</t>
+          <t>Wicitaanka teller kasta</t>
         </is>
       </c>
       <c r="H187" s="13" t="inlineStr">
         <is>
-          <t>simu</t>
+          <t>Simu kwa Kila Afisa</t>
         </is>
       </c>
       <c r="I187" s="14" t="inlineStr"/>
@@ -14286,7 +14286,7 @@
     <row r="188" ht="44" customHeight="1">
       <c r="A188" s="11" t="inlineStr">
         <is>
-          <t>unit_call</t>
+          <t>unit_calls</t>
         </is>
       </c>
       <c r="B188" s="11" t="inlineStr">
@@ -14296,27 +14296,27 @@
       </c>
       <c r="C188" s="11" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>calls</t>
         </is>
       </c>
       <c r="D188" s="12" t="inlineStr">
         <is>
-          <t>ጥሪ</t>
+          <t>ጥሪዎች</t>
         </is>
       </c>
       <c r="E188" s="13" t="inlineStr">
         <is>
-          <t>bilbila</t>
+          <t>bilbilawwan</t>
         </is>
       </c>
       <c r="F188" s="12" t="inlineStr">
         <is>
-          <t>ጻውዒት</t>
+          <t>ጻውዒታት</t>
         </is>
       </c>
       <c r="G188" s="13" t="inlineStr">
         <is>
-          <t>wicitaan</t>
+          <t>wicitaanno</t>
         </is>
       </c>
       <c r="H188" s="13" t="inlineStr">
@@ -14329,7 +14329,7 @@
     <row r="189" ht="44" customHeight="1">
       <c r="A189" s="11" t="inlineStr">
         <is>
-          <t>no_calls_taken_yet</t>
+          <t>unit_call</t>
         </is>
       </c>
       <c r="B189" s="11" t="inlineStr">
@@ -14339,32 +14339,32 @@
       </c>
       <c r="C189" s="11" t="inlineStr">
         <is>
-          <t>Nobody has taken a call yet in this window.</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>በዚህ ጊዜ ውስጥ ማንም ጥሪ አልያዘም።</t>
+          <t>ጥሪ</t>
         </is>
       </c>
       <c r="E189" s="13" t="inlineStr">
         <is>
-          <t>Yeroo kana keessatti namni bilbila fudhate hin jiru.</t>
+          <t>bilbila</t>
         </is>
       </c>
       <c r="F189" s="12" t="inlineStr">
         <is>
-          <t>ኣብዚ እዋን'ዚ ዝሓዘ ጻውዒት የለን።</t>
+          <t>ጻውዒት</t>
         </is>
       </c>
       <c r="G189" s="13" t="inlineStr">
         <is>
-          <t>Cidina ma qaadan wicitaan waqtigan.</t>
+          <t>wicitaan</t>
         </is>
       </c>
       <c r="H189" s="13" t="inlineStr">
         <is>
-          <t>Hakuna aliyepokea simu bado katika muda huu.</t>
+          <t>simu</t>
         </is>
       </c>
       <c r="I189" s="14" t="inlineStr"/>
@@ -14372,7 +14372,7 @@
     <row r="190" ht="44" customHeight="1">
       <c r="A190" s="11" t="inlineStr">
         <is>
-          <t>call_resolved</t>
+          <t>no_calls_taken_yet</t>
         </is>
       </c>
       <c r="B190" s="11" t="inlineStr">
@@ -14382,32 +14382,32 @@
       </c>
       <c r="C190" s="11" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Nobody has taken a call yet in this window.</t>
         </is>
       </c>
       <c r="D190" s="12" t="inlineStr">
         <is>
-          <t>ተፈትቷል</t>
+          <t>በዚህ ጊዜ ውስጥ ማንም ጥሪ አልያዘም።</t>
         </is>
       </c>
       <c r="E190" s="13" t="inlineStr">
         <is>
-          <t>Furameera</t>
+          <t>Yeroo kana keessatti namni bilbila fudhate hin jiru.</t>
         </is>
       </c>
       <c r="F190" s="12" t="inlineStr">
         <is>
-          <t>ተፈቲሑ</t>
+          <t>ኣብዚ እዋን'ዚ ዝሓዘ ጻውዒት የለን።</t>
         </is>
       </c>
       <c r="G190" s="13" t="inlineStr">
         <is>
-          <t>La xaliyay</t>
+          <t>Cidina ma qaadan wicitaan waqtigan.</t>
         </is>
       </c>
       <c r="H190" s="13" t="inlineStr">
         <is>
-          <t>Imetatuliwa</t>
+          <t>Hakuna aliyepokea simu bado katika muda huu.</t>
         </is>
       </c>
       <c r="I190" s="14" t="inlineStr"/>
@@ -14415,7 +14415,7 @@
     <row r="191" ht="44" customHeight="1">
       <c r="A191" s="11" t="inlineStr">
         <is>
-          <t>call_dropped</t>
+          <t>call_resolved</t>
         </is>
       </c>
       <c r="B191" s="11" t="inlineStr">
@@ -14425,32 +14425,32 @@
       </c>
       <c r="C191" s="11" t="inlineStr">
         <is>
-          <t>Dropped (technical issue)</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="D191" s="12" t="inlineStr">
         <is>
-          <t>ተቋርጧል (ቴክኒካዊ ችግር)</t>
+          <t>ተፈትቷል</t>
         </is>
       </c>
       <c r="E191" s="13" t="inlineStr">
         <is>
-          <t>Cite (rakkoo teekniikaa)</t>
+          <t>Furameera</t>
         </is>
       </c>
       <c r="F191" s="12" t="inlineStr">
         <is>
-          <t>ተቋሪጹ (ቴክኒካዊ ጸገም)</t>
+          <t>ተፈቲሑ</t>
         </is>
       </c>
       <c r="G191" s="13" t="inlineStr">
         <is>
-          <t>Wuu jabay (dhibaato farsamo)</t>
+          <t>La xaliyay</t>
         </is>
       </c>
       <c r="H191" s="13" t="inlineStr">
         <is>
-          <t>Imekatika (tatizo la kiufundi)</t>
+          <t>Imetatuliwa</t>
         </is>
       </c>
       <c r="I191" s="14" t="inlineStr"/>
@@ -14458,7 +14458,7 @@
     <row r="192" ht="44" customHeight="1">
       <c r="A192" s="11" t="inlineStr">
         <is>
-          <t>avg_wait_before_answering</t>
+          <t>call_dropped</t>
         </is>
       </c>
       <c r="B192" s="11" t="inlineStr">
@@ -14468,32 +14468,32 @@
       </c>
       <c r="C192" s="11" t="inlineStr">
         <is>
-          <t>Avg. wait before answering:</t>
+          <t>Dropped (technical issue)</t>
         </is>
       </c>
       <c r="D192" s="12" t="inlineStr">
         <is>
-          <t>ከመመለስ በፊት አማካይ የመጠበቅ ጊዜ፦</t>
+          <t>ተቋርጧል (ቴክኒካዊ ችግር)</t>
         </is>
       </c>
       <c r="E192" s="13" t="inlineStr">
         <is>
-          <t>Giddu-galeessa yeroo eegumsaa deebii dura:</t>
+          <t>Cite (rakkoo teekniikaa)</t>
         </is>
       </c>
       <c r="F192" s="12" t="inlineStr">
         <is>
-          <t>ማእከላይ ግዜ ምጽባይ ቅድሚ ምምላስ፦</t>
+          <t>ተቋሪጹ (ቴክኒካዊ ጸገም)</t>
         </is>
       </c>
       <c r="G192" s="13" t="inlineStr">
         <is>
-          <t>Celceliska sugitaanka ka hor jawaabta:</t>
+          <t>Wuu jabay (dhibaato farsamo)</t>
         </is>
       </c>
       <c r="H192" s="13" t="inlineStr">
         <is>
-          <t>Wastani wa kusubiri kabla ya kujibu:</t>
+          <t>Imekatika (tatizo la kiufundi)</t>
         </is>
       </c>
       <c r="I192" s="14" t="inlineStr"/>
@@ -14501,7 +14501,7 @@
     <row r="193" ht="44" customHeight="1">
       <c r="A193" s="11" t="inlineStr">
         <is>
-          <t>no_calls_yet_window</t>
+          <t>avg_wait_before_answering</t>
         </is>
       </c>
       <c r="B193" s="11" t="inlineStr">
@@ -14511,32 +14511,32 @@
       </c>
       <c r="C193" s="11" t="inlineStr">
         <is>
-          <t>No calls yet in this window.</t>
+          <t>Avg. wait before answering:</t>
         </is>
       </c>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>በዚህ ጊዜ ውስጥ ጥሪ የለም።</t>
+          <t>ከመመለስ በፊት አማካይ የመጠበቅ ጊዜ፦</t>
         </is>
       </c>
       <c r="E193" s="13" t="inlineStr">
         <is>
-          <t>Yeroo kana keessatti bilbilli hin jiru.</t>
+          <t>Giddu-galeessa yeroo eegumsaa deebii dura:</t>
         </is>
       </c>
       <c r="F193" s="12" t="inlineStr">
         <is>
-          <t>ኣብዚ እዋን'ዚ ጻውዒት የለን።</t>
+          <t>ማእከላይ ግዜ ምጽባይ ቅድሚ ምምላስ፦</t>
         </is>
       </c>
       <c r="G193" s="13" t="inlineStr">
         <is>
-          <t>Wicitaan lama helin waqtigan.</t>
+          <t>Celceliska sugitaanka ka hor jawaabta:</t>
         </is>
       </c>
       <c r="H193" s="13" t="inlineStr">
         <is>
-          <t>Hakuna simu bado katika muda huu.</t>
+          <t>Wastani wa kusubiri kabla ya kujibu:</t>
         </is>
       </c>
       <c r="I193" s="14" t="inlineStr"/>
@@ -14544,7 +14544,7 @@
     <row r="194" ht="44" customHeight="1">
       <c r="A194" s="11" t="inlineStr">
         <is>
-          <t>your_performance</t>
+          <t>no_calls_yet_window</t>
         </is>
       </c>
       <c r="B194" s="11" t="inlineStr">
@@ -14554,32 +14554,32 @@
       </c>
       <c r="C194" s="11" t="inlineStr">
         <is>
-          <t>Your performance</t>
+          <t>No calls yet in this window.</t>
         </is>
       </c>
       <c r="D194" s="12" t="inlineStr">
         <is>
-          <t>የእርስዎ አፈጻጸም</t>
+          <t>በዚህ ጊዜ ውስጥ ጥሪ የለም።</t>
         </is>
       </c>
       <c r="E194" s="13" t="inlineStr">
         <is>
-          <t>Hojii kee</t>
+          <t>Yeroo kana keessatti bilbilli hin jiru.</t>
         </is>
       </c>
       <c r="F194" s="12" t="inlineStr">
         <is>
-          <t>ኣፈጻጽማኻ</t>
+          <t>ኣብዚ እዋን'ዚ ጻውዒት የለን።</t>
         </is>
       </c>
       <c r="G194" s="13" t="inlineStr">
         <is>
-          <t>Waxqabadkaaga</t>
+          <t>Wicitaan lama helin waqtigan.</t>
         </is>
       </c>
       <c r="H194" s="13" t="inlineStr">
         <is>
-          <t>Utendaji Wako</t>
+          <t>Hakuna simu bado katika muda huu.</t>
         </is>
       </c>
       <c r="I194" s="14" t="inlineStr"/>
@@ -14587,7 +14587,7 @@
     <row r="195" ht="44" customHeight="1">
       <c r="A195" s="11" t="inlineStr">
         <is>
-          <t>n_other_tellers</t>
+          <t>your_performance</t>
         </is>
       </c>
       <c r="B195" s="11" t="inlineStr">
@@ -14597,32 +14597,32 @@
       </c>
       <c r="C195" s="11" t="inlineStr">
         <is>
-          <t>{n} other tellers</t>
+          <t>Your performance</t>
         </is>
       </c>
       <c r="D195" s="12" t="inlineStr">
         <is>
-          <t>{n} ሌሎች ተጠሪዎች</t>
+          <t>የእርስዎ አፈጻጸም</t>
         </is>
       </c>
       <c r="E195" s="13" t="inlineStr">
         <is>
-          <t>{n} teellaroota biroo</t>
+          <t>Hojii kee</t>
         </is>
       </c>
       <c r="F195" s="12" t="inlineStr">
         <is>
-          <t>{n} ካልኦት ተለራት</t>
+          <t>ኣፈጻጽማኻ</t>
         </is>
       </c>
       <c r="G195" s="13" t="inlineStr">
         <is>
-          <t>{n} teller oo kale</t>
+          <t>Waxqabadkaaga</t>
         </is>
       </c>
       <c r="H195" s="13" t="inlineStr">
         <is>
-          <t>Maafisa wengine {n}</t>
+          <t>Utendaji Wako</t>
         </is>
       </c>
       <c r="I195" s="14" t="inlineStr"/>
@@ -14630,7 +14630,7 @@
     <row r="196" ht="44" customHeight="1">
       <c r="A196" s="11" t="inlineStr">
         <is>
-          <t>built_in</t>
+          <t>n_other_tellers</t>
         </is>
       </c>
       <c r="B196" s="11" t="inlineStr">
@@ -14640,32 +14640,32 @@
       </c>
       <c r="C196" s="11" t="inlineStr">
         <is>
-          <t>built-in</t>
+          <t>{n} other tellers</t>
         </is>
       </c>
       <c r="D196" s="12" t="inlineStr">
         <is>
-          <t>አብሮ የተሰራ</t>
+          <t>{n} ሌሎች ተጠሪዎች</t>
         </is>
       </c>
       <c r="E196" s="13" t="inlineStr">
         <is>
-          <t>kan ijaarame</t>
+          <t>{n} teellaroota biroo</t>
         </is>
       </c>
       <c r="F196" s="12" t="inlineStr">
         <is>
-          <t>ውሁድ</t>
+          <t>{n} ካልኦት ተለራት</t>
         </is>
       </c>
       <c r="G196" s="13" t="inlineStr">
         <is>
-          <t>ku dhex jira</t>
+          <t>{n} teller oo kale</t>
         </is>
       </c>
       <c r="H196" s="13" t="inlineStr">
         <is>
-          <t>iliyojengwa ndani</t>
+          <t>Maafisa wengine {n}</t>
         </is>
       </c>
       <c r="I196" s="14" t="inlineStr"/>
@@ -14673,7 +14673,7 @@
     <row r="197" ht="44" customHeight="1">
       <c r="A197" s="11" t="inlineStr">
         <is>
-          <t>add_a_person</t>
+          <t>built_in</t>
         </is>
       </c>
       <c r="B197" s="11" t="inlineStr">
@@ -14683,32 +14683,32 @@
       </c>
       <c r="C197" s="11" t="inlineStr">
         <is>
-          <t>Add a person</t>
+          <t>built-in</t>
         </is>
       </c>
       <c r="D197" s="12" t="inlineStr">
         <is>
-          <t>ሰው ጨምር</t>
+          <t>አብሮ የተሰራ</t>
         </is>
       </c>
       <c r="E197" s="13" t="inlineStr">
         <is>
-          <t>Nama dabali</t>
+          <t>kan ijaarame</t>
         </is>
       </c>
       <c r="F197" s="12" t="inlineStr">
         <is>
-          <t>ሰብ ወስኽ</t>
+          <t>ውሁድ</t>
         </is>
       </c>
       <c r="G197" s="13" t="inlineStr">
         <is>
-          <t>Qof ku dar</t>
+          <t>ku dhex jira</t>
         </is>
       </c>
       <c r="H197" s="13" t="inlineStr">
         <is>
-          <t>Ongeza Mtu</t>
+          <t>iliyojengwa ndani</t>
         </is>
       </c>
       <c r="I197" s="14" t="inlineStr"/>
@@ -14716,7 +14716,7 @@
     <row r="198" ht="44" customHeight="1">
       <c r="A198" s="11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>add_a_person</t>
         </is>
       </c>
       <c r="B198" s="11" t="inlineStr">
@@ -14726,32 +14726,32 @@
       </c>
       <c r="C198" s="11" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Add a person</t>
         </is>
       </c>
       <c r="D198" s="12" t="inlineStr">
         <is>
-          <t>ኢሜይል</t>
+          <t>ሰው ጨምር</t>
         </is>
       </c>
       <c r="E198" s="13" t="inlineStr">
         <is>
-          <t>Imeelii</t>
+          <t>Nama dabali</t>
         </is>
       </c>
       <c r="F198" s="12" t="inlineStr">
         <is>
-          <t>ኢመይል</t>
+          <t>ሰብ ወስኽ</t>
         </is>
       </c>
       <c r="G198" s="13" t="inlineStr">
         <is>
-          <t>Iimayl</t>
+          <t>Qof ku dar</t>
         </is>
       </c>
       <c r="H198" s="13" t="inlineStr">
         <is>
-          <t>Barua Pepe</t>
+          <t>Ongeza Mtu</t>
         </is>
       </c>
       <c r="I198" s="14" t="inlineStr"/>
@@ -14759,7 +14759,7 @@
     <row r="199" ht="44" customHeight="1">
       <c r="A199" s="11" t="inlineStr">
         <is>
-          <t>name_optional</t>
+          <t>email</t>
         </is>
       </c>
       <c r="B199" s="11" t="inlineStr">
@@ -14769,32 +14769,32 @@
       </c>
       <c r="C199" s="11" t="inlineStr">
         <is>
-          <t>Name (optional)</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D199" s="12" t="inlineStr">
         <is>
-          <t>ስም (አማራጭ)</t>
+          <t>ኢሜይል</t>
         </is>
       </c>
       <c r="E199" s="13" t="inlineStr">
         <is>
-          <t>Maqaa (filannoo)</t>
+          <t>Imeelii</t>
         </is>
       </c>
       <c r="F199" s="12" t="inlineStr">
         <is>
-          <t>ስም (ኣማራጺ)</t>
+          <t>ኢመይል</t>
         </is>
       </c>
       <c r="G199" s="13" t="inlineStr">
         <is>
-          <t>Magac (ikhtiyaari)</t>
+          <t>Iimayl</t>
         </is>
       </c>
       <c r="H199" s="13" t="inlineStr">
         <is>
-          <t>Jina (si lazima)</t>
+          <t>Barua Pepe</t>
         </is>
       </c>
       <c r="I199" s="14" t="inlineStr"/>
@@ -14802,7 +14802,7 @@
     <row r="200" ht="44" customHeight="1">
       <c r="A200" s="11" t="inlineStr">
         <is>
-          <t>temporary_password</t>
+          <t>name_optional</t>
         </is>
       </c>
       <c r="B200" s="11" t="inlineStr">
@@ -14812,32 +14812,32 @@
       </c>
       <c r="C200" s="11" t="inlineStr">
         <is>
-          <t>Temporary password</t>
+          <t>Name (optional)</t>
         </is>
       </c>
       <c r="D200" s="12" t="inlineStr">
         <is>
-          <t>ጊዜያዊ የይለፍ ቃል</t>
+          <t>ስም (አማራጭ)</t>
         </is>
       </c>
       <c r="E200" s="13" t="inlineStr">
         <is>
-          <t>Jecha darbii yeroo</t>
+          <t>Maqaa (filannoo)</t>
         </is>
       </c>
       <c r="F200" s="12" t="inlineStr">
         <is>
-          <t>ግዝያዊ መሕለፊ ቃል</t>
+          <t>ስም (ኣማራጺ)</t>
         </is>
       </c>
       <c r="G200" s="13" t="inlineStr">
         <is>
-          <t>Fure ku meel gaar ah</t>
+          <t>Magac (ikhtiyaari)</t>
         </is>
       </c>
       <c r="H200" s="13" t="inlineStr">
         <is>
-          <t>Nenosiri la Muda</t>
+          <t>Jina (si lazima)</t>
         </is>
       </c>
       <c r="I200" s="14" t="inlineStr"/>
@@ -14845,7 +14845,7 @@
     <row r="201" ht="44" customHeight="1">
       <c r="A201" s="11" t="inlineStr">
         <is>
-          <t>temp_password_help</t>
+          <t>temporary_password</t>
         </is>
       </c>
       <c r="B201" s="11" t="inlineStr">
@@ -14855,32 +14855,32 @@
       </c>
       <c r="C201" s="11" t="inlineStr">
         <is>
-          <t>At least 12 characters. Until invitation emails are set up, this password has to be given to them directly — which is why it is shown here rather than hidden.</t>
+          <t>Temporary password</t>
         </is>
       </c>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>ቢያንስ 12 ቁምፊ። የግብዣ ኢሜይሎች እስኪዘጋጁ ድረስ ይህ የይለፍ ቃል በቀጥታ ሊሰጣቸው ይገባል — ስለዚህ ተደብቆ ሳይሆን እዚህ ይታያል።</t>
+          <t>ጊዜያዊ የይለፍ ቃል</t>
         </is>
       </c>
       <c r="E201" s="13" t="inlineStr">
         <is>
-          <t>Yoo xiqqaate arfiilee 12. Hanga imeeliin afeerraa qophaa'utti, jechi darbii kun kallattiin isaaniif kennamuu qaba — kanaafuu dhokfamuu mannaa asitti ni mul'ata.</t>
+          <t>Jecha darbii yeroo</t>
         </is>
       </c>
       <c r="F201" s="12" t="inlineStr">
         <is>
-          <t>ብውሑዱ 12 ፊደላት። መጸዋዕታ ኢመይል ክሳብ ዝዳሎ እዚ መሕለፊ ቃል ብቐጥታ ክወሃቦም ኣለዎ — ስለዚ ተሓቢኡ ዘይኮነ ኣብዚ ይረአ።</t>
+          <t>ግዝያዊ መሕለፊ ቃል</t>
         </is>
       </c>
       <c r="G201" s="13" t="inlineStr">
         <is>
-          <t>Ugu yaraan 12 xaraf. Ilaa iimaylada casumaadda la dejiyo, furahan si toos ah ayaa loo siin doonaa — sidaas darteed halkan ayuu ka muuqdaa halkii la qarin lahaa.</t>
+          <t>Fure ku meel gaar ah</t>
         </is>
       </c>
       <c r="H201" s="13" t="inlineStr">
         <is>
-          <t>Angalau herufi 12. Hadi barua pepe za mialiko zitakapowekwa, nenosiri hili linapaswa kupewa moja kwa moja — ndiyo maana linaonyeshwa hapa badala ya kufichwa.</t>
+          <t>Nenosiri la Muda</t>
         </is>
       </c>
       <c r="I201" s="14" t="inlineStr"/>
@@ -14888,7 +14888,7 @@
     <row r="202" ht="44" customHeight="1">
       <c r="A202" s="11" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>temp_password_help</t>
         </is>
       </c>
       <c r="B202" s="11" t="inlineStr">
@@ -14898,32 +14898,32 @@
       </c>
       <c r="C202" s="11" t="inlineStr">
         <is>
-          <t>Create</t>
+          <t>At least 12 characters. Until invitation emails are set up, this password has to be given to them directly — which is why it is shown here rather than hidden.</t>
         </is>
       </c>
       <c r="D202" s="12" t="inlineStr">
         <is>
-          <t>ፍጠር</t>
+          <t>ቢያንስ 12 ቁምፊ። የግብዣ ኢሜይሎች እስኪዘጋጁ ድረስ ይህ የይለፍ ቃል በቀጥታ ሊሰጣቸው ይገባል — ስለዚህ ተደብቆ ሳይሆን እዚህ ይታያል።</t>
         </is>
       </c>
       <c r="E202" s="13" t="inlineStr">
         <is>
-          <t>Uumi</t>
+          <t>Yoo xiqqaate arfiilee 12. Hanga imeeliin afeerraa qophaa'utti, jechi darbii kun kallattiin isaaniif kennamuu qaba — kanaafuu dhokfamuu mannaa asitti ni mul'ata.</t>
         </is>
       </c>
       <c r="F202" s="12" t="inlineStr">
         <is>
-          <t>ፍጠር</t>
+          <t>ብውሑዱ 12 ፊደላት። መጸዋዕታ ኢመይል ክሳብ ዝዳሎ እዚ መሕለፊ ቃል ብቐጥታ ክወሃቦም ኣለዎ — ስለዚ ተሓቢኡ ዘይኮነ ኣብዚ ይረአ።</t>
         </is>
       </c>
       <c r="G202" s="13" t="inlineStr">
         <is>
-          <t>Abuur</t>
+          <t>Ugu yaraan 12 xaraf. Ilaa iimaylada casumaadda la dejiyo, furahan si toos ah ayaa loo siin doonaa — sidaas darteed halkan ayuu ka muuqdaa halkii la qarin lahaa.</t>
         </is>
       </c>
       <c r="H202" s="13" t="inlineStr">
         <is>
-          <t>Unda</t>
+          <t>Angalau herufi 12. Hadi barua pepe za mialiko zitakapowekwa, nenosiri hili linapaswa kupewa moja kwa moja — ndiyo maana linaonyeshwa hapa badala ya kufichwa.</t>
         </is>
       </c>
       <c r="I202" s="14" t="inlineStr"/>
@@ -14931,7 +14931,7 @@
     <row r="203" ht="44" customHeight="1">
       <c r="A203" s="11" t="inlineStr">
         <is>
-          <t>account_created</t>
+          <t>create</t>
         </is>
       </c>
       <c r="B203" s="11" t="inlineStr">
@@ -14941,32 +14941,32 @@
       </c>
       <c r="C203" s="11" t="inlineStr">
         <is>
-          <t>Account created</t>
+          <t>Create</t>
         </is>
       </c>
       <c r="D203" s="12" t="inlineStr">
         <is>
-          <t>መለያ ተፈጥሯል</t>
+          <t>ፍጠር</t>
         </is>
       </c>
       <c r="E203" s="13" t="inlineStr">
         <is>
-          <t>Herregni uumame</t>
+          <t>Uumi</t>
         </is>
       </c>
       <c r="F203" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ ተፈጢሩ</t>
+          <t>ፍጠር</t>
         </is>
       </c>
       <c r="G203" s="13" t="inlineStr">
         <is>
-          <t>Xisaab waa la abuuray</t>
+          <t>Abuur</t>
         </is>
       </c>
       <c r="H203" s="13" t="inlineStr">
         <is>
-          <t>Akaunti Imeundwa</t>
+          <t>Unda</t>
         </is>
       </c>
       <c r="I203" s="14" t="inlineStr"/>
@@ -14974,7 +14974,7 @@
     <row r="204" ht="44" customHeight="1">
       <c r="A204" s="11" t="inlineStr">
         <is>
-          <t>account_restored</t>
+          <t>account_created</t>
         </is>
       </c>
       <c r="B204" s="11" t="inlineStr">
@@ -14984,32 +14984,32 @@
       </c>
       <c r="C204" s="11" t="inlineStr">
         <is>
-          <t>Account restored</t>
+          <t>Account created</t>
         </is>
       </c>
       <c r="D204" s="12" t="inlineStr">
         <is>
-          <t>መለያ ተመልሷል</t>
+          <t>መለያ ተፈጥሯል</t>
         </is>
       </c>
       <c r="E204" s="13" t="inlineStr">
         <is>
-          <t>Herregni deebi'e</t>
+          <t>Herregni uumame</t>
         </is>
       </c>
       <c r="F204" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ ተመሊሱ</t>
+          <t>ሕሳብ ተፈጢሩ</t>
         </is>
       </c>
       <c r="G204" s="13" t="inlineStr">
         <is>
-          <t>Xisaabta waa la soo celiyay</t>
+          <t>Xisaab waa la abuuray</t>
         </is>
       </c>
       <c r="H204" s="13" t="inlineStr">
         <is>
-          <t>Akaunti Imerejeshwa</t>
+          <t>Akaunti Imeundwa</t>
         </is>
       </c>
       <c r="I204" s="14" t="inlineStr"/>
@@ -15017,7 +15017,7 @@
     <row r="205" ht="44" customHeight="1">
       <c r="A205" s="11" t="inlineStr">
         <is>
-          <t>account_disabled_n</t>
+          <t>account_restored</t>
         </is>
       </c>
       <c r="B205" s="11" t="inlineStr">
@@ -15027,32 +15027,32 @@
       </c>
       <c r="C205" s="11" t="inlineStr">
         <is>
-          <t>Account disabled, {n} session(s) ended</t>
+          <t>Account restored</t>
         </is>
       </c>
       <c r="D205" s="12" t="inlineStr">
         <is>
-          <t>መለያ ተሰናክሏል፤ {n} ክፍለ-ጊዜ ተዘግቷል</t>
+          <t>መለያ ተመልሷል</t>
         </is>
       </c>
       <c r="E205" s="13" t="inlineStr">
         <is>
-          <t>Herregni dhaabame, session {n} xumurame</t>
+          <t>Herregni deebi'e</t>
         </is>
       </c>
       <c r="F205" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ ተዓጊቱ፣ {n} ክፍለ-ግዜ ተዛዚሙ</t>
+          <t>ሕሳብ ተመሊሱ</t>
         </is>
       </c>
       <c r="G205" s="13" t="inlineStr">
         <is>
-          <t>Xisaabta waa la demiyay, {n} kalfadhi ayaa dhammaaday</t>
+          <t>Xisaabta waa la soo celiyay</t>
         </is>
       </c>
       <c r="H205" s="13" t="inlineStr">
         <is>
-          <t>Akaunti imezimwa, vikao {n} vimemalizika</t>
+          <t>Akaunti Imerejeshwa</t>
         </is>
       </c>
       <c r="I205" s="14" t="inlineStr"/>
@@ -15060,7 +15060,7 @@
     <row r="206" ht="44" customHeight="1">
       <c r="A206" s="11" t="inlineStr">
         <is>
-          <t>confirm_disable_account</t>
+          <t>account_disabled_n</t>
         </is>
       </c>
       <c r="B206" s="11" t="inlineStr">
@@ -15070,32 +15070,32 @@
       </c>
       <c r="C206" s="11" t="inlineStr">
         <is>
-          <t>Disable this account? They will be signed out immediately.</t>
+          <t>Account disabled, {n} session(s) ended</t>
         </is>
       </c>
       <c r="D206" s="12" t="inlineStr">
         <is>
-          <t>ይህን መለያ ማሰናከል? ወዲያውኑ ይወጣሉ።</t>
+          <t>መለያ ተሰናክሏል፤ {n} ክፍለ-ጊዜ ተዘግቷል</t>
         </is>
       </c>
       <c r="E206" s="13" t="inlineStr">
         <is>
-          <t>Herrega kana dhaabuu? Battalumatti ni baafamu.</t>
+          <t>Herregni dhaabame, session {n} xumurame</t>
         </is>
       </c>
       <c r="F206" s="12" t="inlineStr">
         <is>
-          <t>ነዚ ሕሳብ ክዕገት? ብቕጽበት ይወጹ።</t>
+          <t>ሕሳብ ተዓጊቱ፣ {n} ክፍለ-ግዜ ተዛዚሙ</t>
         </is>
       </c>
       <c r="G206" s="13" t="inlineStr">
         <is>
-          <t>Xisaabtan ma demineysaa? Isla markiiba waa laga saarayaa.</t>
+          <t>Xisaabta waa la demiyay, {n} kalfadhi ayaa dhammaaday</t>
         </is>
       </c>
       <c r="H206" s="13" t="inlineStr">
         <is>
-          <t>Zima akaunti hii? Watatolewa mara moja.</t>
+          <t>Akaunti imezimwa, vikao {n} vimemalizika</t>
         </is>
       </c>
       <c r="I206" s="14" t="inlineStr"/>
@@ -15103,7 +15103,7 @@
     <row r="207" ht="44" customHeight="1">
       <c r="A207" s="11" t="inlineStr">
         <is>
-          <t>action_document_created</t>
+          <t>confirm_disable_account</t>
         </is>
       </c>
       <c r="B207" s="11" t="inlineStr">
@@ -15113,32 +15113,32 @@
       </c>
       <c r="C207" s="11" t="inlineStr">
         <is>
-          <t>added an article</t>
+          <t>Disable this account? They will be signed out immediately.</t>
         </is>
       </c>
       <c r="D207" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ጨምሯል</t>
+          <t>ይህን መለያ ማሰናከል? ወዲያውኑ ይወጣሉ።</t>
         </is>
       </c>
       <c r="E207" s="13" t="inlineStr">
         <is>
-          <t>barruu dabale</t>
+          <t>Herrega kana dhaabuu? Battalumatti ni baafamu.</t>
         </is>
       </c>
       <c r="F207" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ወሲኹ</t>
+          <t>ነዚ ሕሳብ ክዕገት? ብቕጽበት ይወጹ።</t>
         </is>
       </c>
       <c r="G207" s="13" t="inlineStr">
         <is>
-          <t>maqaal ku daray</t>
+          <t>Xisaabtan ma demineysaa? Isla markiiba waa laga saarayaa.</t>
         </is>
       </c>
       <c r="H207" s="13" t="inlineStr">
         <is>
-          <t>aliongeza makala</t>
+          <t>Zima akaunti hii? Watatolewa mara moja.</t>
         </is>
       </c>
       <c r="I207" s="14" t="inlineStr"/>
@@ -15146,7 +15146,7 @@
     <row r="208" ht="44" customHeight="1">
       <c r="A208" s="11" t="inlineStr">
         <is>
-          <t>action_document_updated</t>
+          <t>action_document_created</t>
         </is>
       </c>
       <c r="B208" s="11" t="inlineStr">
@@ -15156,32 +15156,32 @@
       </c>
       <c r="C208" s="11" t="inlineStr">
         <is>
-          <t>edited an article</t>
+          <t>added an article</t>
         </is>
       </c>
       <c r="D208" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ አርሟል</t>
+          <t>ጽሑፍ ጨምሯል</t>
         </is>
       </c>
       <c r="E208" s="13" t="inlineStr">
         <is>
-          <t>barruu gulaale</t>
+          <t>barruu dabale</t>
         </is>
       </c>
       <c r="F208" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ኣርሚዑ</t>
+          <t>ጽሑፍ ወሲኹ</t>
         </is>
       </c>
       <c r="G208" s="13" t="inlineStr">
         <is>
-          <t>maqaal wax ka beddelay</t>
+          <t>maqaal ku daray</t>
         </is>
       </c>
       <c r="H208" s="13" t="inlineStr">
         <is>
-          <t>alihariri makala</t>
+          <t>aliongeza makala</t>
         </is>
       </c>
       <c r="I208" s="14" t="inlineStr"/>
@@ -15189,7 +15189,7 @@
     <row r="209" ht="44" customHeight="1">
       <c r="A209" s="11" t="inlineStr">
         <is>
-          <t>action_document_deleted</t>
+          <t>action_document_updated</t>
         </is>
       </c>
       <c r="B209" s="11" t="inlineStr">
@@ -15199,32 +15199,32 @@
       </c>
       <c r="C209" s="11" t="inlineStr">
         <is>
-          <t>deleted an article</t>
+          <t>edited an article</t>
         </is>
       </c>
       <c r="D209" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ሰርዟል</t>
+          <t>ጽሑፍ አርሟል</t>
         </is>
       </c>
       <c r="E209" s="13" t="inlineStr">
         <is>
-          <t>barruu haqe</t>
+          <t>barruu gulaale</t>
         </is>
       </c>
       <c r="F209" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ደምሲሱ</t>
+          <t>ጽሑፍ ኣርሚዑ</t>
         </is>
       </c>
       <c r="G209" s="13" t="inlineStr">
         <is>
-          <t>maqaal tirtiray</t>
+          <t>maqaal wax ka beddelay</t>
         </is>
       </c>
       <c r="H209" s="13" t="inlineStr">
         <is>
-          <t>alifuta makala</t>
+          <t>alihariri makala</t>
         </is>
       </c>
       <c r="I209" s="14" t="inlineStr"/>
@@ -15232,7 +15232,7 @@
     <row r="210" ht="44" customHeight="1">
       <c r="A210" s="11" t="inlineStr">
         <is>
-          <t>action_documents_bulk_imported</t>
+          <t>action_document_deleted</t>
         </is>
       </c>
       <c r="B210" s="11" t="inlineStr">
@@ -15242,32 +15242,32 @@
       </c>
       <c r="C210" s="11" t="inlineStr">
         <is>
-          <t>imported articles</t>
+          <t>deleted an article</t>
         </is>
       </c>
       <c r="D210" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፎችን አስገብቷል</t>
+          <t>ጽሑፍ ሰርዟል</t>
         </is>
       </c>
       <c r="E210" s="13" t="inlineStr">
         <is>
-          <t>barruulee galche</t>
+          <t>barruu haqe</t>
         </is>
       </c>
       <c r="F210" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፋት ኣእትዩ</t>
+          <t>ጽሑፍ ደምሲሱ</t>
         </is>
       </c>
       <c r="G210" s="13" t="inlineStr">
         <is>
-          <t>maqaallo soo dhoofiyay</t>
+          <t>maqaal tirtiray</t>
         </is>
       </c>
       <c r="H210" s="13" t="inlineStr">
         <is>
-          <t>aliagiza makala</t>
+          <t>alifuta makala</t>
         </is>
       </c>
       <c r="I210" s="14" t="inlineStr"/>
@@ -15275,7 +15275,7 @@
     <row r="211" ht="44" customHeight="1">
       <c r="A211" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_closed</t>
+          <t>action_documents_bulk_imported</t>
         </is>
       </c>
       <c r="B211" s="11" t="inlineStr">
@@ -15285,32 +15285,32 @@
       </c>
       <c r="C211" s="11" t="inlineStr">
         <is>
-          <t>closed an escalation</t>
+          <t>imported articles</t>
         </is>
       </c>
       <c r="D211" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ ዘግቷል</t>
+          <t>ጽሑፎችን አስገብቷል</t>
         </is>
       </c>
       <c r="E211" s="13" t="inlineStr">
         <is>
-          <t>dhimma cufe</t>
+          <t>barruulee galche</t>
         </is>
       </c>
       <c r="F211" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ ዓጺዩ</t>
+          <t>ጽሑፋት ኣእትዩ</t>
         </is>
       </c>
       <c r="G211" s="13" t="inlineStr">
         <is>
-          <t>arrin xiray</t>
+          <t>maqaallo soo dhoofiyay</t>
         </is>
       </c>
       <c r="H211" s="13" t="inlineStr">
         <is>
-          <t>alifunga suala</t>
+          <t>aliagiza makala</t>
         </is>
       </c>
       <c r="I211" s="14" t="inlineStr"/>
@@ -15318,7 +15318,7 @@
     <row r="212" ht="44" customHeight="1">
       <c r="A212" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_reopened</t>
+          <t>action_handoff_closed</t>
         </is>
       </c>
       <c r="B212" s="11" t="inlineStr">
@@ -15328,32 +15328,32 @@
       </c>
       <c r="C212" s="11" t="inlineStr">
         <is>
-          <t>reopened an escalation</t>
+          <t>closed an escalation</t>
         </is>
       </c>
       <c r="D212" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ በድጋሚ ከፍቷል</t>
+          <t>ጉዳይ ዘግቷል</t>
         </is>
       </c>
       <c r="E212" s="13" t="inlineStr">
         <is>
-          <t>dhimma irra deebi'ee bane</t>
+          <t>dhimma cufe</t>
         </is>
       </c>
       <c r="F212" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ ደጊሙ ከፊቱ</t>
+          <t>ጉዳይ ዓጺዩ</t>
         </is>
       </c>
       <c r="G212" s="13" t="inlineStr">
         <is>
-          <t>arrin dib u furay</t>
+          <t>arrin xiray</t>
         </is>
       </c>
       <c r="H212" s="13" t="inlineStr">
         <is>
-          <t>alifungua tena suala</t>
+          <t>alifunga suala</t>
         </is>
       </c>
       <c r="I212" s="14" t="inlineStr"/>
@@ -15361,7 +15361,7 @@
     <row r="213" ht="44" customHeight="1">
       <c r="A213" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_webhook_connected</t>
+          <t>action_handoff_reopened</t>
         </is>
       </c>
       <c r="B213" s="11" t="inlineStr">
@@ -15371,32 +15371,32 @@
       </c>
       <c r="C213" s="11" t="inlineStr">
         <is>
-          <t>connected the escalation webhook</t>
+          <t>reopened an escalation</t>
         </is>
       </c>
       <c r="D213" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ዌብሁክ አገናኝቷል</t>
+          <t>ጉዳይ በድጋሚ ከፍቷል</t>
         </is>
       </c>
       <c r="E213" s="13" t="inlineStr">
         <is>
-          <t>webhook dabarsaa walqunnamsiise</t>
+          <t>dhimma irra deebi'ee bane</t>
         </is>
       </c>
       <c r="F213" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ምትሕልላፍ ኣራኺቡ</t>
+          <t>ጉዳይ ደጊሙ ከፊቱ</t>
         </is>
       </c>
       <c r="G213" s="13" t="inlineStr">
         <is>
-          <t>ku xiray webhook-ga gudbinta</t>
+          <t>arrin dib u furay</t>
         </is>
       </c>
       <c r="H213" s="13" t="inlineStr">
         <is>
-          <t>aliunganisha wavuti ya masuala</t>
+          <t>alifungua tena suala</t>
         </is>
       </c>
       <c r="I213" s="14" t="inlineStr"/>
@@ -15404,7 +15404,7 @@
     <row r="214" ht="44" customHeight="1">
       <c r="A214" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_webhook_disconnected</t>
+          <t>action_handoff_webhook_connected</t>
         </is>
       </c>
       <c r="B214" s="11" t="inlineStr">
@@ -15414,32 +15414,32 @@
       </c>
       <c r="C214" s="11" t="inlineStr">
         <is>
-          <t>disconnected the escalation webhook</t>
+          <t>connected the escalation webhook</t>
         </is>
       </c>
       <c r="D214" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ዌብሁክ አቋርጧል</t>
+          <t>የማሸጋገሪያ ዌብሁክ አገናኝቷል</t>
         </is>
       </c>
       <c r="E214" s="13" t="inlineStr">
         <is>
-          <t>webhook dabarsaa addaan kute</t>
+          <t>webhook dabarsaa walqunnamsiise</t>
         </is>
       </c>
       <c r="F214" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ምትሕልላፍ ቆሪጹ</t>
+          <t>ዌብሁክ ምትሕልላፍ ኣራኺቡ</t>
         </is>
       </c>
       <c r="G214" s="13" t="inlineStr">
         <is>
-          <t>goynay webhook-ga gudbinta</t>
+          <t>ku xiray webhook-ga gudbinta</t>
         </is>
       </c>
       <c r="H214" s="13" t="inlineStr">
         <is>
-          <t>alikatisha wavuti ya masuala</t>
+          <t>aliunganisha wavuti ya masuala</t>
         </is>
       </c>
       <c r="I214" s="14" t="inlineStr"/>
@@ -15447,7 +15447,7 @@
     <row r="215" ht="44" customHeight="1">
       <c r="A215" s="11" t="inlineStr">
         <is>
-          <t>action_telegram_connected</t>
+          <t>action_handoff_webhook_disconnected</t>
         </is>
       </c>
       <c r="B215" s="11" t="inlineStr">
@@ -15457,32 +15457,32 @@
       </c>
       <c r="C215" s="11" t="inlineStr">
         <is>
-          <t>connected Telegram</t>
+          <t>disconnected the escalation webhook</t>
         </is>
       </c>
       <c r="D215" s="12" t="inlineStr">
         <is>
-          <t>ቴሌግራም አገናኝቷል</t>
+          <t>የማሸጋገሪያ ዌብሁክ አቋርጧል</t>
         </is>
       </c>
       <c r="E215" s="13" t="inlineStr">
         <is>
-          <t>Telegram walqunnamsiise</t>
+          <t>webhook dabarsaa addaan kute</t>
         </is>
       </c>
       <c r="F215" s="12" t="inlineStr">
         <is>
-          <t>ቴሌግራም ኣራኺቡ</t>
+          <t>ዌብሁክ ምትሕልላፍ ቆሪጹ</t>
         </is>
       </c>
       <c r="G215" s="13" t="inlineStr">
         <is>
-          <t>Telegram ku xiray</t>
+          <t>goynay webhook-ga gudbinta</t>
         </is>
       </c>
       <c r="H215" s="13" t="inlineStr">
         <is>
-          <t>aliunganisha Telegram</t>
+          <t>alikatisha wavuti ya masuala</t>
         </is>
       </c>
       <c r="I215" s="14" t="inlineStr"/>
@@ -15490,7 +15490,7 @@
     <row r="216" ht="44" customHeight="1">
       <c r="A216" s="11" t="inlineStr">
         <is>
-          <t>action_user_created</t>
+          <t>action_telegram_connected</t>
         </is>
       </c>
       <c r="B216" s="11" t="inlineStr">
@@ -15500,32 +15500,32 @@
       </c>
       <c r="C216" s="11" t="inlineStr">
         <is>
-          <t>added a colleague</t>
+          <t>connected Telegram</t>
         </is>
       </c>
       <c r="D216" s="12" t="inlineStr">
         <is>
-          <t>ባልደረባ ጨምሯል</t>
+          <t>ቴሌግራም አገናኝቷል</t>
         </is>
       </c>
       <c r="E216" s="13" t="inlineStr">
         <is>
-          <t>hojjetaa dabale</t>
+          <t>Telegram walqunnamsiise</t>
         </is>
       </c>
       <c r="F216" s="12" t="inlineStr">
         <is>
-          <t>መሳርሕቲ ወሲኹ</t>
+          <t>ቴሌግራም ኣራኺቡ</t>
         </is>
       </c>
       <c r="G216" s="13" t="inlineStr">
         <is>
-          <t>shaqaale ku daray</t>
+          <t>Telegram ku xiray</t>
         </is>
       </c>
       <c r="H216" s="13" t="inlineStr">
         <is>
-          <t>aliongeza mwenzake</t>
+          <t>aliunganisha Telegram</t>
         </is>
       </c>
       <c r="I216" s="14" t="inlineStr"/>
@@ -15533,7 +15533,7 @@
     <row r="217" ht="44" customHeight="1">
       <c r="A217" s="11" t="inlineStr">
         <is>
-          <t>action_user_disabled</t>
+          <t>action_user_created</t>
         </is>
       </c>
       <c r="B217" s="11" t="inlineStr">
@@ -15543,32 +15543,32 @@
       </c>
       <c r="C217" s="11" t="inlineStr">
         <is>
-          <t>disabled an account</t>
+          <t>added a colleague</t>
         </is>
       </c>
       <c r="D217" s="12" t="inlineStr">
         <is>
-          <t>መለያ አሰናክሏል</t>
+          <t>ባልደረባ ጨምሯል</t>
         </is>
       </c>
       <c r="E217" s="13" t="inlineStr">
         <is>
-          <t>herrega dhaabe</t>
+          <t>hojjetaa dabale</t>
         </is>
       </c>
       <c r="F217" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ ዓጊቱ</t>
+          <t>መሳርሕቲ ወሲኹ</t>
         </is>
       </c>
       <c r="G217" s="13" t="inlineStr">
         <is>
-          <t>xisaab demiyay</t>
+          <t>shaqaale ku daray</t>
         </is>
       </c>
       <c r="H217" s="13" t="inlineStr">
         <is>
-          <t>alizima akaunti</t>
+          <t>aliongeza mwenzake</t>
         </is>
       </c>
       <c r="I217" s="14" t="inlineStr"/>
@@ -15576,7 +15576,7 @@
     <row r="218" ht="44" customHeight="1">
       <c r="A218" s="11" t="inlineStr">
         <is>
-          <t>action_user_enabled</t>
+          <t>action_user_disabled</t>
         </is>
       </c>
       <c r="B218" s="11" t="inlineStr">
@@ -15586,32 +15586,32 @@
       </c>
       <c r="C218" s="11" t="inlineStr">
         <is>
-          <t>restored an account</t>
+          <t>disabled an account</t>
         </is>
       </c>
       <c r="D218" s="12" t="inlineStr">
         <is>
-          <t>መለያ መልሷል</t>
+          <t>መለያ አሰናክሏል</t>
         </is>
       </c>
       <c r="E218" s="13" t="inlineStr">
         <is>
-          <t>herrega deebise</t>
+          <t>herrega dhaabe</t>
         </is>
       </c>
       <c r="F218" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ መሊሱ</t>
+          <t>ሕሳብ ዓጊቱ</t>
         </is>
       </c>
       <c r="G218" s="13" t="inlineStr">
         <is>
-          <t>xisaab soo celiyay</t>
+          <t>xisaab demiyay</t>
         </is>
       </c>
       <c r="H218" s="13" t="inlineStr">
         <is>
-          <t>alirejesha akaunti</t>
+          <t>alizima akaunti</t>
         </is>
       </c>
       <c r="I218" s="14" t="inlineStr"/>
@@ -15619,7 +15619,7 @@
     <row r="219" ht="44" customHeight="1">
       <c r="A219" s="11" t="inlineStr">
         <is>
-          <t>action_admin_login</t>
+          <t>action_user_enabled</t>
         </is>
       </c>
       <c r="B219" s="11" t="inlineStr">
@@ -15629,32 +15629,32 @@
       </c>
       <c r="C219" s="11" t="inlineStr">
         <is>
-          <t>signed in</t>
+          <t>restored an account</t>
         </is>
       </c>
       <c r="D219" s="12" t="inlineStr">
         <is>
-          <t>ገብቷል</t>
+          <t>መለያ መልሷል</t>
         </is>
       </c>
       <c r="E219" s="13" t="inlineStr">
         <is>
-          <t>seene</t>
+          <t>herrega deebise</t>
         </is>
       </c>
       <c r="F219" s="12" t="inlineStr">
         <is>
-          <t>ኣትዩ</t>
+          <t>ሕሳብ መሊሱ</t>
         </is>
       </c>
       <c r="G219" s="13" t="inlineStr">
         <is>
-          <t>gashay</t>
+          <t>xisaab soo celiyay</t>
         </is>
       </c>
       <c r="H219" s="13" t="inlineStr">
         <is>
-          <t>aliingia</t>
+          <t>alirejesha akaunti</t>
         </is>
       </c>
       <c r="I219" s="14" t="inlineStr"/>
@@ -15662,7 +15662,7 @@
     <row r="220" ht="44" customHeight="1">
       <c r="A220" s="11" t="inlineStr">
         <is>
-          <t>action_password_changed</t>
+          <t>action_admin_login</t>
         </is>
       </c>
       <c r="B220" s="11" t="inlineStr">
@@ -15672,32 +15672,32 @@
       </c>
       <c r="C220" s="11" t="inlineStr">
         <is>
-          <t>changed their password</t>
+          <t>signed in</t>
         </is>
       </c>
       <c r="D220" s="12" t="inlineStr">
         <is>
-          <t>የይለፍ ቃል ቀይሯል</t>
+          <t>ገብቷል</t>
         </is>
       </c>
       <c r="E220" s="13" t="inlineStr">
         <is>
-          <t>jecha darbii jijjiire</t>
+          <t>seene</t>
         </is>
       </c>
       <c r="F220" s="12" t="inlineStr">
         <is>
-          <t>መሕለፊ ቃል ቀዪሩ</t>
+          <t>ኣትዩ</t>
         </is>
       </c>
       <c r="G220" s="13" t="inlineStr">
         <is>
-          <t>beddelay furihiisa</t>
+          <t>gashay</t>
         </is>
       </c>
       <c r="H220" s="13" t="inlineStr">
         <is>
-          <t>alibadilisha nenosiri lake</t>
+          <t>aliingia</t>
         </is>
       </c>
       <c r="I220" s="14" t="inlineStr"/>
@@ -15705,7 +15705,7 @@
     <row r="221" ht="44" customHeight="1">
       <c r="A221" s="11" t="inlineStr">
         <is>
-          <t>nothing_yet</t>
+          <t>action_password_changed</t>
         </is>
       </c>
       <c r="B221" s="11" t="inlineStr">
@@ -15715,32 +15715,32 @@
       </c>
       <c r="C221" s="11" t="inlineStr">
         <is>
-          <t>Nothing yet.</t>
+          <t>changed their password</t>
         </is>
       </c>
       <c r="D221" s="12" t="inlineStr">
         <is>
-          <t>እስካሁን ምንም የለም።</t>
+          <t>የይለፍ ቃል ቀይሯል</t>
         </is>
       </c>
       <c r="E221" s="13" t="inlineStr">
         <is>
-          <t>Ammaaf homaa hin jiru.</t>
+          <t>jecha darbii jijjiire</t>
         </is>
       </c>
       <c r="F221" s="12" t="inlineStr">
         <is>
-          <t>ክሳብ ሕጂ ዋላ ሓደ የለን።</t>
+          <t>መሕለፊ ቃል ቀዪሩ</t>
         </is>
       </c>
       <c r="G221" s="13" t="inlineStr">
         <is>
-          <t>Weli waxba ma jiraan.</t>
+          <t>beddelay furihiisa</t>
         </is>
       </c>
       <c r="H221" s="13" t="inlineStr">
         <is>
-          <t>Bado hakuna.</t>
+          <t>alibadilisha nenosiri lake</t>
         </is>
       </c>
       <c r="I221" s="14" t="inlineStr"/>
@@ -15748,7 +15748,7 @@
     <row r="222" ht="44" customHeight="1">
       <c r="A222" s="11" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>nothing_yet</t>
         </is>
       </c>
       <c r="B222" s="11" t="inlineStr">
@@ -15758,32 +15758,32 @@
       </c>
       <c r="C222" s="11" t="inlineStr">
         <is>
-          <t>Unavailable.</t>
+          <t>Nothing yet.</t>
         </is>
       </c>
       <c r="D222" s="12" t="inlineStr">
         <is>
-          <t>አይገኝም።</t>
+          <t>እስካሁን ምንም የለም።</t>
         </is>
       </c>
       <c r="E222" s="13" t="inlineStr">
         <is>
-          <t>Hin argamu.</t>
+          <t>Ammaaf homaa hin jiru.</t>
         </is>
       </c>
       <c r="F222" s="12" t="inlineStr">
         <is>
-          <t>ኣይርከብን።</t>
+          <t>ክሳብ ሕጂ ዋላ ሓደ የለን።</t>
         </is>
       </c>
       <c r="G222" s="13" t="inlineStr">
         <is>
-          <t>Lama heli karo.</t>
+          <t>Weli waxba ma jiraan.</t>
         </is>
       </c>
       <c r="H222" s="13" t="inlineStr">
         <is>
-          <t>Haipatikani.</t>
+          <t>Bado hakuna.</t>
         </is>
       </c>
       <c r="I222" s="14" t="inlineStr"/>
@@ -15791,7 +15791,7 @@
     <row r="223" ht="44" customHeight="1">
       <c r="A223" s="11" t="inlineStr">
         <is>
-          <t>just_now</t>
+          <t>unavailable</t>
         </is>
       </c>
       <c r="B223" s="11" t="inlineStr">
@@ -15801,32 +15801,32 @@
       </c>
       <c r="C223" s="11" t="inlineStr">
         <is>
-          <t>just now</t>
+          <t>Unavailable.</t>
         </is>
       </c>
       <c r="D223" s="12" t="inlineStr">
         <is>
-          <t>አሁን</t>
+          <t>አይገኝም።</t>
         </is>
       </c>
       <c r="E223" s="13" t="inlineStr">
         <is>
-          <t>amma</t>
+          <t>Hin argamu.</t>
         </is>
       </c>
       <c r="F223" s="12" t="inlineStr">
         <is>
-          <t>ሕጂ</t>
+          <t>ኣይርከብን።</t>
         </is>
       </c>
       <c r="G223" s="13" t="inlineStr">
         <is>
-          <t>hadda</t>
+          <t>Lama heli karo.</t>
         </is>
       </c>
       <c r="H223" s="13" t="inlineStr">
         <is>
-          <t>sasa hivi</t>
+          <t>Haipatikani.</t>
         </is>
       </c>
       <c r="I223" s="14" t="inlineStr"/>
@@ -15834,7 +15834,7 @@
     <row r="224" ht="44" customHeight="1">
       <c r="A224" s="11" t="inlineStr">
         <is>
-          <t>n_min_ago</t>
+          <t>just_now</t>
         </is>
       </c>
       <c r="B224" s="11" t="inlineStr">
@@ -15844,32 +15844,32 @@
       </c>
       <c r="C224" s="11" t="inlineStr">
         <is>
-          <t>{n} min ago</t>
+          <t>just now</t>
         </is>
       </c>
       <c r="D224" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ደቂቃ በፊት</t>
+          <t>አሁን</t>
         </is>
       </c>
       <c r="E224" s="13" t="inlineStr">
         <is>
-          <t>daqiiqaa {n} dura</t>
+          <t>amma</t>
         </is>
       </c>
       <c r="F224" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ደቒቕ</t>
+          <t>ሕጂ</t>
         </is>
       </c>
       <c r="G224" s="13" t="inlineStr">
         <is>
-          <t>{n} daqiiqo ka hor</t>
+          <t>hadda</t>
         </is>
       </c>
       <c r="H224" s="13" t="inlineStr">
         <is>
-          <t>dakika {n} zilizopita</t>
+          <t>sasa hivi</t>
         </is>
       </c>
       <c r="I224" s="14" t="inlineStr"/>
@@ -15877,7 +15877,7 @@
     <row r="225" ht="44" customHeight="1">
       <c r="A225" s="11" t="inlineStr">
         <is>
-          <t>n_h_ago</t>
+          <t>n_min_ago</t>
         </is>
       </c>
       <c r="B225" s="11" t="inlineStr">
@@ -15887,32 +15887,32 @@
       </c>
       <c r="C225" s="11" t="inlineStr">
         <is>
-          <t>{n} h ago</t>
+          <t>{n} min ago</t>
         </is>
       </c>
       <c r="D225" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ሰዓት በፊት</t>
+          <t>ከ{n} ደቂቃ በፊት</t>
         </is>
       </c>
       <c r="E225" s="13" t="inlineStr">
         <is>
-          <t>sa'aatii {n} dura</t>
+          <t>daqiiqaa {n} dura</t>
         </is>
       </c>
       <c r="F225" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ሰዓት</t>
+          <t>ቅድሚ {n} ደቒቕ</t>
         </is>
       </c>
       <c r="G225" s="13" t="inlineStr">
         <is>
-          <t>{n} saac ka hor</t>
+          <t>{n} daqiiqo ka hor</t>
         </is>
       </c>
       <c r="H225" s="13" t="inlineStr">
         <is>
-          <t>saa {n} zilizopita</t>
+          <t>dakika {n} zilizopita</t>
         </is>
       </c>
       <c r="I225" s="14" t="inlineStr"/>
@@ -15920,7 +15920,7 @@
     <row r="226" ht="44" customHeight="1">
       <c r="A226" s="11" t="inlineStr">
         <is>
-          <t>n_d_ago</t>
+          <t>n_h_ago</t>
         </is>
       </c>
       <c r="B226" s="11" t="inlineStr">
@@ -15930,32 +15930,32 @@
       </c>
       <c r="C226" s="11" t="inlineStr">
         <is>
-          <t>{n} d ago</t>
+          <t>{n} h ago</t>
         </is>
       </c>
       <c r="D226" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ቀን በፊት</t>
+          <t>ከ{n} ሰዓት በፊት</t>
         </is>
       </c>
       <c r="E226" s="13" t="inlineStr">
         <is>
-          <t>guyyaa {n} dura</t>
+          <t>sa'aatii {n} dura</t>
         </is>
       </c>
       <c r="F226" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} መዓልቲ</t>
+          <t>ቅድሚ {n} ሰዓት</t>
         </is>
       </c>
       <c r="G226" s="13" t="inlineStr">
         <is>
-          <t>{n} maalmood ka hor</t>
+          <t>{n} saac ka hor</t>
         </is>
       </c>
       <c r="H226" s="13" t="inlineStr">
         <is>
-          <t>siku {n} zilizopita</t>
+          <t>saa {n} zilizopita</t>
         </is>
       </c>
       <c r="I226" s="14" t="inlineStr"/>
@@ -15963,7 +15963,7 @@
     <row r="227" ht="44" customHeight="1">
       <c r="A227" s="11" t="inlineStr">
         <is>
-          <t>channel_all_from</t>
+          <t>n_d_ago</t>
         </is>
       </c>
       <c r="B227" s="11" t="inlineStr">
@@ -15973,32 +15973,32 @@
       </c>
       <c r="C227" s="11" t="inlineStr">
         <is>
-          <t>All {n} conversations came from {label}.</t>
+          <t>{n} d ago</t>
         </is>
       </c>
       <c r="D227" s="12" t="inlineStr">
         <is>
-          <t>ሁሉም {n} ውይይቶች ከ{label} መጥተዋል።</t>
+          <t>ከ{n} ቀን በፊት</t>
         </is>
       </c>
       <c r="E227" s="13" t="inlineStr">
         <is>
-          <t>Mariin {n} hundi {label} irraa dhufe.</t>
+          <t>guyyaa {n} dura</t>
         </is>
       </c>
       <c r="F227" s="12" t="inlineStr">
         <is>
-          <t>ኩሎም {n} ዝርርባት ካብ {label} መጺኦም።</t>
+          <t>ቅድሚ {n} መዓልቲ</t>
         </is>
       </c>
       <c r="G227" s="13" t="inlineStr">
         <is>
-          <t>Dhammaan {n} wadahadal waxay ka yimaadeen {label}.</t>
+          <t>{n} maalmood ka hor</t>
         </is>
       </c>
       <c r="H227" s="13" t="inlineStr">
         <is>
-          <t>Mazungumzo yote {n} yalitoka {label}.</t>
+          <t>siku {n} zilizopita</t>
         </is>
       </c>
       <c r="I227" s="14" t="inlineStr"/>
@@ -16006,7 +16006,7 @@
     <row r="228" ht="44" customHeight="1">
       <c r="A228" s="11" t="inlineStr">
         <is>
-          <t>channel_live</t>
+          <t>channel_all_from</t>
         </is>
       </c>
       <c r="B228" s="11" t="inlineStr">
@@ -16016,32 +16016,32 @@
       </c>
       <c r="C228" s="11" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>All {n} conversations came from {label}.</t>
         </is>
       </c>
       <c r="D228" s="12" t="inlineStr">
         <is>
-          <t>በሥራ ላይ</t>
+          <t>ሁሉም {n} ውይይቶች ከ{label} መጥተዋል።</t>
         </is>
       </c>
       <c r="E228" s="13" t="inlineStr">
         <is>
-          <t>Hojiirra</t>
+          <t>Mariin {n} hundi {label} irraa dhufe.</t>
         </is>
       </c>
       <c r="F228" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ስራሕ</t>
+          <t>ኩሎም {n} ዝርርባት ካብ {label} መጺኦም።</t>
         </is>
       </c>
       <c r="G228" s="13" t="inlineStr">
         <is>
-          <t>Shaqeynaya</t>
+          <t>Dhammaan {n} wadahadal waxay ka yimaadeen {label}.</t>
         </is>
       </c>
       <c r="H228" s="13" t="inlineStr">
         <is>
-          <t>Moja kwa Moja</t>
+          <t>Mazungumzo yote {n} yalitoka {label}.</t>
         </is>
       </c>
       <c r="I228" s="14" t="inlineStr"/>
@@ -16049,7 +16049,7 @@
     <row r="229" ht="44" customHeight="1">
       <c r="A229" s="11" t="inlineStr">
         <is>
-          <t>channel_ready</t>
+          <t>channel_live</t>
         </is>
       </c>
       <c r="B229" s="11" t="inlineStr">
@@ -16059,32 +16059,32 @@
       </c>
       <c r="C229" s="11" t="inlineStr">
         <is>
-          <t>Ready to connect</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="D229" s="12" t="inlineStr">
         <is>
-          <t>ለመገናኘት ዝግጁ</t>
+          <t>በሥራ ላይ</t>
         </is>
       </c>
       <c r="E229" s="13" t="inlineStr">
         <is>
-          <t>Walqunnamuuf qophaa'aa</t>
+          <t>Hojiirra</t>
         </is>
       </c>
       <c r="F229" s="12" t="inlineStr">
         <is>
-          <t>ንምርኻብ ድሉው</t>
+          <t>ኣብ ስራሕ</t>
         </is>
       </c>
       <c r="G229" s="13" t="inlineStr">
         <is>
-          <t>Diyaar u ah xiriirka</t>
+          <t>Shaqeynaya</t>
         </is>
       </c>
       <c r="H229" s="13" t="inlineStr">
         <is>
-          <t>Tayari Kuunganishwa</t>
+          <t>Moja kwa Moja</t>
         </is>
       </c>
       <c r="I229" s="14" t="inlineStr"/>
@@ -16092,7 +16092,7 @@
     <row r="230" ht="44" customHeight="1">
       <c r="A230" s="11" t="inlineStr">
         <is>
-          <t>channel_needs_setup</t>
+          <t>channel_ready</t>
         </is>
       </c>
       <c r="B230" s="11" t="inlineStr">
@@ -16102,32 +16102,32 @@
       </c>
       <c r="C230" s="11" t="inlineStr">
         <is>
-          <t>Needs setup</t>
+          <t>Ready to connect</t>
         </is>
       </c>
       <c r="D230" s="12" t="inlineStr">
         <is>
-          <t>ማዋቀር ይፈልጋል</t>
+          <t>ለመገናኘት ዝግጁ</t>
         </is>
       </c>
       <c r="E230" s="13" t="inlineStr">
         <is>
-          <t>Qindeessuu barbaada</t>
+          <t>Walqunnamuuf qophaa'aa</t>
         </is>
       </c>
       <c r="F230" s="12" t="inlineStr">
         <is>
-          <t>ምድላው የድልዮ</t>
+          <t>ንምርኻብ ድሉው</t>
         </is>
       </c>
       <c r="G230" s="13" t="inlineStr">
         <is>
-          <t>Waxay u baahan tahay dejin</t>
+          <t>Diyaar u ah xiriirka</t>
         </is>
       </c>
       <c r="H230" s="13" t="inlineStr">
         <is>
-          <t>Inahitaji Kusanidiwa</t>
+          <t>Tayari Kuunganishwa</t>
         </is>
       </c>
       <c r="I230" s="14" t="inlineStr"/>
@@ -16135,7 +16135,7 @@
     <row r="231" ht="44" customHeight="1">
       <c r="A231" s="11" t="inlineStr">
         <is>
-          <t>share_by_channel</t>
+          <t>channel_needs_setup</t>
         </is>
       </c>
       <c r="B231" s="11" t="inlineStr">
@@ -16145,32 +16145,32 @@
       </c>
       <c r="C231" s="11" t="inlineStr">
         <is>
-          <t>Share of conversations by channel</t>
+          <t>Needs setup</t>
         </is>
       </c>
       <c r="D231" s="12" t="inlineStr">
         <is>
-          <t>በመስመር የተከፋፈሉ ውይይቶች ድርሻ</t>
+          <t>ማዋቀር ይፈልጋል</t>
         </is>
       </c>
       <c r="E231" s="13" t="inlineStr">
         <is>
-          <t>Qooda marii karaa tokkoon tokkoon isaanii</t>
+          <t>Qindeessuu barbaada</t>
         </is>
       </c>
       <c r="F231" s="12" t="inlineStr">
         <is>
-          <t>ብመስመር ዝተኸፋፈለ ግደ ዝርርባት</t>
+          <t>ምድላው የድልዮ</t>
         </is>
       </c>
       <c r="G231" s="13" t="inlineStr">
         <is>
-          <t>Qaybta wadahadallada kanaalka</t>
+          <t>Waxay u baahan tahay dejin</t>
         </is>
       </c>
       <c r="H231" s="13" t="inlineStr">
         <is>
-          <t>Mgawanyo wa Mazungumzo kwa Njia</t>
+          <t>Inahitaji Kusanidiwa</t>
         </is>
       </c>
       <c r="I231" s="14" t="inlineStr"/>
@@ -16178,7 +16178,7 @@
     <row r="232" ht="44" customHeight="1">
       <c r="A232" s="11" t="inlineStr">
         <is>
-          <t>up_to_date</t>
+          <t>share_by_channel</t>
         </is>
       </c>
       <c r="B232" s="11" t="inlineStr">
@@ -16188,32 +16188,32 @@
       </c>
       <c r="C232" s="11" t="inlineStr">
         <is>
-          <t>Up to date</t>
+          <t>Share of conversations by channel</t>
         </is>
       </c>
       <c r="D232" s="12" t="inlineStr">
         <is>
-          <t>የተዘመነ</t>
+          <t>በመስመር የተከፋፈሉ ውይይቶች ድርሻ</t>
         </is>
       </c>
       <c r="E232" s="13" t="inlineStr">
         <is>
-          <t>Haaraa</t>
+          <t>Qooda marii karaa tokkoon tokkoon isaanii</t>
         </is>
       </c>
       <c r="F232" s="12" t="inlineStr">
         <is>
-          <t>ዝተሓደሰ</t>
+          <t>ብመስመር ዝተኸፋፈለ ግደ ዝርርባት</t>
         </is>
       </c>
       <c r="G232" s="13" t="inlineStr">
         <is>
-          <t>La cusbooneysiiyay</t>
+          <t>Qaybta wadahadallada kanaalka</t>
         </is>
       </c>
       <c r="H232" s="13" t="inlineStr">
         <is>
-          <t>Ni ya Hivi Karibuni</t>
+          <t>Mgawanyo wa Mazungumzo kwa Njia</t>
         </is>
       </c>
       <c r="I232" s="14" t="inlineStr"/>
@@ -16221,7 +16221,7 @@
     <row r="233" ht="44" customHeight="1">
       <c r="A233" s="11" t="inlineStr">
         <is>
-          <t>updated_m_ago</t>
+          <t>up_to_date</t>
         </is>
       </c>
       <c r="B233" s="11" t="inlineStr">
@@ -16231,32 +16231,32 @@
       </c>
       <c r="C233" s="11" t="inlineStr">
         <is>
-          <t>Updated {n}m ago</t>
+          <t>Up to date</t>
         </is>
       </c>
       <c r="D233" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ደቂቃ በፊት ተዘምኗል</t>
+          <t>የተዘመነ</t>
         </is>
       </c>
       <c r="E233" s="13" t="inlineStr">
         <is>
-          <t>Daqiiqaa {n} dura haaromfame</t>
+          <t>Haaraa</t>
         </is>
       </c>
       <c r="F233" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ደቒቕ ተሓዲሱ</t>
+          <t>ዝተሓደሰ</t>
         </is>
       </c>
       <c r="G233" s="13" t="inlineStr">
         <is>
-          <t>La cusbooneysiiyay {n}daq ka hor</t>
+          <t>La cusbooneysiiyay</t>
         </is>
       </c>
       <c r="H233" s="13" t="inlineStr">
         <is>
-          <t>Imesasishwa dakika {n} zilizopita</t>
+          <t>Ni ya Hivi Karibuni</t>
         </is>
       </c>
       <c r="I233" s="14" t="inlineStr"/>
@@ -16264,7 +16264,7 @@
     <row r="234" ht="44" customHeight="1">
       <c r="A234" s="11" t="inlineStr">
         <is>
-          <t>updated_h_ago</t>
+          <t>updated_m_ago</t>
         </is>
       </c>
       <c r="B234" s="11" t="inlineStr">
@@ -16274,32 +16274,32 @@
       </c>
       <c r="C234" s="11" t="inlineStr">
         <is>
-          <t>Updated {n}h ago</t>
+          <t>Updated {n}m ago</t>
         </is>
       </c>
       <c r="D234" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ሰዓት በፊት ተዘምኗል</t>
+          <t>ከ{n} ደቂቃ በፊት ተዘምኗል</t>
         </is>
       </c>
       <c r="E234" s="13" t="inlineStr">
         <is>
-          <t>Sa'aatii {n} dura haaromfame</t>
+          <t>Daqiiqaa {n} dura haaromfame</t>
         </is>
       </c>
       <c r="F234" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ሰዓት ተሓዲሱ</t>
+          <t>ቅድሚ {n} ደቒቕ ተሓዲሱ</t>
         </is>
       </c>
       <c r="G234" s="13" t="inlineStr">
         <is>
-          <t>La cusbooneysiiyay {n}saac ka hor</t>
+          <t>La cusbooneysiiyay {n}daq ka hor</t>
         </is>
       </c>
       <c r="H234" s="13" t="inlineStr">
         <is>
-          <t>Imesasishwa saa {n} zilizopita</t>
+          <t>Imesasishwa dakika {n} zilizopita</t>
         </is>
       </c>
       <c r="I234" s="14" t="inlineStr"/>
@@ -16307,7 +16307,7 @@
     <row r="235" ht="44" customHeight="1">
       <c r="A235" s="11" t="inlineStr">
         <is>
-          <t>queue</t>
+          <t>updated_h_ago</t>
         </is>
       </c>
       <c r="B235" s="11" t="inlineStr">
@@ -16317,32 +16317,32 @@
       </c>
       <c r="C235" s="11" t="inlineStr">
         <is>
-          <t>Queue</t>
+          <t>Updated {n}h ago</t>
         </is>
       </c>
       <c r="D235" s="12" t="inlineStr">
         <is>
-          <t>ወረፋ</t>
+          <t>ከ{n} ሰዓት በፊት ተዘምኗል</t>
         </is>
       </c>
       <c r="E235" s="13" t="inlineStr">
         <is>
-          <t>Sararaa</t>
+          <t>Sa'aatii {n} dura haaromfame</t>
         </is>
       </c>
       <c r="F235" s="12" t="inlineStr">
         <is>
-          <t>ሪጋ</t>
+          <t>ቅድሚ {n} ሰዓት ተሓዲሱ</t>
         </is>
       </c>
       <c r="G235" s="13" t="inlineStr">
         <is>
-          <t>Safka</t>
+          <t>La cusbooneysiiyay {n}saac ka hor</t>
         </is>
       </c>
       <c r="H235" s="13" t="inlineStr">
         <is>
-          <t>Foleni</t>
+          <t>Imesasishwa saa {n} zilizopita</t>
         </is>
       </c>
       <c r="I235" s="14" t="inlineStr"/>
@@ -16350,7 +16350,7 @@
     <row r="236" ht="44" customHeight="1">
       <c r="A236" s="11" t="inlineStr">
         <is>
-          <t>collapse</t>
+          <t>queue</t>
         </is>
       </c>
       <c r="B236" s="11" t="inlineStr">
@@ -16360,32 +16360,32 @@
       </c>
       <c r="C236" s="11" t="inlineStr">
         <is>
-          <t>Collapse</t>
+          <t>Queue</t>
         </is>
       </c>
       <c r="D236" s="12" t="inlineStr">
         <is>
-          <t>አጥብብ</t>
+          <t>ወረፋ</t>
         </is>
       </c>
       <c r="E236" s="13" t="inlineStr">
         <is>
-          <t>Xiqqeessi</t>
+          <t>Sararaa</t>
         </is>
       </c>
       <c r="F236" s="12" t="inlineStr">
         <is>
-          <t>ኣጽብብ</t>
+          <t>ሪጋ</t>
         </is>
       </c>
       <c r="G236" s="13" t="inlineStr">
         <is>
-          <t>Yaree</t>
+          <t>Safka</t>
         </is>
       </c>
       <c r="H236" s="13" t="inlineStr">
         <is>
-          <t>Kunja</t>
+          <t>Foleni</t>
         </is>
       </c>
       <c r="I236" s="14" t="inlineStr"/>
@@ -16393,7 +16393,7 @@
     <row r="237" ht="44" customHeight="1">
       <c r="A237" s="11" t="inlineStr">
         <is>
-          <t>expand</t>
+          <t>collapse</t>
         </is>
       </c>
       <c r="B237" s="11" t="inlineStr">
@@ -16403,32 +16403,32 @@
       </c>
       <c r="C237" s="11" t="inlineStr">
         <is>
-          <t>Expand</t>
+          <t>Collapse</t>
         </is>
       </c>
       <c r="D237" s="12" t="inlineStr">
         <is>
-          <t>አስፋ</t>
+          <t>አጥብብ</t>
         </is>
       </c>
       <c r="E237" s="13" t="inlineStr">
         <is>
-          <t>Balleessi</t>
+          <t>Xiqqeessi</t>
         </is>
       </c>
       <c r="F237" s="12" t="inlineStr">
         <is>
-          <t>ኣስፍሕ</t>
+          <t>ኣጽብብ</t>
         </is>
       </c>
       <c r="G237" s="13" t="inlineStr">
         <is>
-          <t>Balaadhi</t>
+          <t>Yaree</t>
         </is>
       </c>
       <c r="H237" s="13" t="inlineStr">
         <is>
-          <t>Panua</t>
+          <t>Kunja</t>
         </is>
       </c>
       <c r="I237" s="14" t="inlineStr"/>
@@ -16436,7 +16436,7 @@
     <row r="238" ht="44" customHeight="1">
       <c r="A238" s="11" t="inlineStr">
         <is>
-          <t>collapse_or_expand</t>
+          <t>expand</t>
         </is>
       </c>
       <c r="B238" s="11" t="inlineStr">
@@ -16446,32 +16446,32 @@
       </c>
       <c r="C238" s="11" t="inlineStr">
         <is>
-          <t>Collapse or expand the sidebar</t>
+          <t>Expand</t>
         </is>
       </c>
       <c r="D238" s="12" t="inlineStr">
         <is>
-          <t>የጎን አሞሌውን አጥብብ ወይም አስፋ</t>
+          <t>አስፋ</t>
         </is>
       </c>
       <c r="E238" s="13" t="inlineStr">
         <is>
-          <t>Cinaacha xiqqeessi ykn balleessi</t>
+          <t>Balleessi</t>
         </is>
       </c>
       <c r="F238" s="12" t="inlineStr">
         <is>
-          <t>ናይ ጎኒ መስመር ኣጽብብ ወይ ኣስፍሕ</t>
+          <t>ኣስፍሕ</t>
         </is>
       </c>
       <c r="G238" s="13" t="inlineStr">
         <is>
-          <t>Yaree ama balaadhi dhinaca</t>
+          <t>Balaadhi</t>
         </is>
       </c>
       <c r="H238" s="13" t="inlineStr">
         <is>
-          <t>Kunja au panua upande wa kando</t>
+          <t>Panua</t>
         </is>
       </c>
       <c r="I238" s="14" t="inlineStr"/>
@@ -16479,7 +16479,7 @@
     <row r="239" ht="44" customHeight="1">
       <c r="A239" s="11" t="inlineStr">
         <is>
-          <t>show_hide_channels</t>
+          <t>collapse_or_expand</t>
         </is>
       </c>
       <c r="B239" s="11" t="inlineStr">
@@ -16489,32 +16489,32 @@
       </c>
       <c r="C239" s="11" t="inlineStr">
         <is>
-          <t>Show or hide the channel list</t>
+          <t>Collapse or expand the sidebar</t>
         </is>
       </c>
       <c r="D239" s="12" t="inlineStr">
         <is>
-          <t>የመስመሮችን ዝርዝር አሳይ ወይም ደብቅ</t>
+          <t>የጎን አሞሌውን አጥብብ ወይም አስፋ</t>
         </is>
       </c>
       <c r="E239" s="13" t="inlineStr">
         <is>
-          <t>Tarreeffama karaalee agarsiisi ykn dhoksi</t>
+          <t>Cinaacha xiqqeessi ykn balleessi</t>
         </is>
       </c>
       <c r="F239" s="12" t="inlineStr">
         <is>
-          <t>ዝርዝር መስመራት ኣርኢ ወይ ሕባእ</t>
+          <t>ናይ ጎኒ መስመር ኣጽብብ ወይ ኣስፍሕ</t>
         </is>
       </c>
       <c r="G239" s="13" t="inlineStr">
         <is>
-          <t>Muuji ama qari liiska kanaalada</t>
+          <t>Yaree ama balaadhi dhinaca</t>
         </is>
       </c>
       <c r="H239" s="13" t="inlineStr">
         <is>
-          <t>Onyesha au ficha orodha ya njia</t>
+          <t>Kunja au panua upande wa kando</t>
         </is>
       </c>
       <c r="I239" s="14" t="inlineStr"/>
@@ -16522,7 +16522,7 @@
     <row r="240" ht="44" customHeight="1">
       <c r="A240" s="11" t="inlineStr">
         <is>
-          <t>today</t>
+          <t>show_hide_channels</t>
         </is>
       </c>
       <c r="B240" s="11" t="inlineStr">
@@ -16532,32 +16532,32 @@
       </c>
       <c r="C240" s="11" t="inlineStr">
         <is>
-          <t>Today</t>
+          <t>Show or hide the channel list</t>
         </is>
       </c>
       <c r="D240" s="12" t="inlineStr">
         <is>
-          <t>ዛሬ</t>
+          <t>የመስመሮችን ዝርዝር አሳይ ወይም ደብቅ</t>
         </is>
       </c>
       <c r="E240" s="13" t="inlineStr">
         <is>
-          <t>Har'a</t>
+          <t>Tarreeffama karaalee agarsiisi ykn dhoksi</t>
         </is>
       </c>
       <c r="F240" s="12" t="inlineStr">
         <is>
-          <t>ሎሚ</t>
+          <t>ዝርዝር መስመራት ኣርኢ ወይ ሕባእ</t>
         </is>
       </c>
       <c r="G240" s="13" t="inlineStr">
         <is>
-          <t>Maanta</t>
+          <t>Muuji ama qari liiska kanaalada</t>
         </is>
       </c>
       <c r="H240" s="13" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Onyesha au ficha orodha ya njia</t>
         </is>
       </c>
       <c r="I240" s="14" t="inlineStr"/>
@@ -16565,7 +16565,7 @@
     <row r="241" ht="44" customHeight="1">
       <c r="A241" s="11" t="inlineStr">
         <is>
-          <t>yesterday</t>
+          <t>today</t>
         </is>
       </c>
       <c r="B241" s="11" t="inlineStr">
@@ -16575,32 +16575,32 @@
       </c>
       <c r="C241" s="11" t="inlineStr">
         <is>
-          <t>Yesterday</t>
+          <t>Today</t>
         </is>
       </c>
       <c r="D241" s="12" t="inlineStr">
         <is>
-          <t>ትናንት</t>
+          <t>ዛሬ</t>
         </is>
       </c>
       <c r="E241" s="13" t="inlineStr">
         <is>
-          <t>Kaleessa</t>
+          <t>Har'a</t>
         </is>
       </c>
       <c r="F241" s="12" t="inlineStr">
         <is>
-          <t>ትማሊ</t>
+          <t>ሎሚ</t>
         </is>
       </c>
       <c r="G241" s="13" t="inlineStr">
         <is>
-          <t>Shalay</t>
+          <t>Maanta</t>
         </is>
       </c>
       <c r="H241" s="13" t="inlineStr">
         <is>
-          <t>Jana</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="I241" s="14" t="inlineStr"/>
@@ -16608,7 +16608,7 @@
     <row r="242" ht="44" customHeight="1">
       <c r="A242" s="11" t="inlineStr">
         <is>
-          <t>call_started</t>
+          <t>yesterday</t>
         </is>
       </c>
       <c r="B242" s="11" t="inlineStr">
@@ -16618,32 +16618,32 @@
       </c>
       <c r="C242" s="11" t="inlineStr">
         <is>
-          <t>The customer asked for a person here</t>
+          <t>Yesterday</t>
         </is>
       </c>
       <c r="D242" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛው እዚህ ላይ ሰው ጠየቀ</t>
+          <t>ትናንት</t>
         </is>
       </c>
       <c r="E242" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan asitti nama gaafate</t>
+          <t>Kaleessa</t>
         </is>
       </c>
       <c r="F242" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዓሚል ኣብዚ ሰብ ሓቲቱ</t>
+          <t>ትማሊ</t>
         </is>
       </c>
       <c r="G242" s="13" t="inlineStr">
         <is>
-          <t>Macmiilku halkan ayuu qof weydiistay</t>
+          <t>Shalay</t>
         </is>
       </c>
       <c r="H242" s="13" t="inlineStr">
         <is>
-          <t>Mteja aliomba mtu hapa</t>
+          <t>Jana</t>
         </is>
       </c>
       <c r="I242" s="14" t="inlineStr"/>
@@ -16651,7 +16651,7 @@
     <row r="243" ht="44" customHeight="1">
       <c r="A243" s="11" t="inlineStr">
         <is>
-          <t>no_messages</t>
+          <t>call_started</t>
         </is>
       </c>
       <c r="B243" s="11" t="inlineStr">
@@ -16661,32 +16661,32 @@
       </c>
       <c r="C243" s="11" t="inlineStr">
         <is>
-          <t>No messages in this conversation.</t>
+          <t>The customer asked for a person here</t>
         </is>
       </c>
       <c r="D243" s="12" t="inlineStr">
         <is>
-          <t>በዚህ ውይይት ውስጥ መልእክት የለም።</t>
+          <t>ደንበኛው እዚህ ላይ ሰው ጠየቀ</t>
         </is>
       </c>
       <c r="E243" s="13" t="inlineStr">
         <is>
-          <t>Marii kana keessa ergaan hin jiru.</t>
+          <t>Maamilaan asitti nama gaafate</t>
         </is>
       </c>
       <c r="F243" s="12" t="inlineStr">
         <is>
-          <t>ኣብዚ ዝርርብ መልእኽቲ የለን።</t>
+          <t>እቲ ዓሚል ኣብዚ ሰብ ሓቲቱ</t>
         </is>
       </c>
       <c r="G243" s="13" t="inlineStr">
         <is>
-          <t>Wadahadalkan fariin kuma jirto.</t>
+          <t>Macmiilku halkan ayuu qof weydiistay</t>
         </is>
       </c>
       <c r="H243" s="13" t="inlineStr">
         <is>
-          <t>Hakuna ujumbe katika mazungumzo haya.</t>
+          <t>Mteja aliomba mtu hapa</t>
         </is>
       </c>
       <c r="I243" s="14" t="inlineStr"/>
@@ -16694,7 +16694,7 @@
     <row r="244" ht="44" customHeight="1">
       <c r="A244" s="11" t="inlineStr">
         <is>
-          <t>donut_all_in_one</t>
+          <t>no_messages</t>
         </is>
       </c>
       <c r="B244" s="11" t="inlineStr">
@@ -16704,32 +16704,32 @@
       </c>
       <c r="C244" s="11" t="inlineStr">
         <is>
-          <t>The single {unit} was in {label}.</t>
+          <t>No messages in this conversation.</t>
         </is>
       </c>
       <c r="D244" s="12" t="inlineStr">
         <is>
-          <t>ብቸኛው {unit} በ{label} ነበር።</t>
+          <t>በዚህ ውይይት ውስጥ መልእክት የለም።</t>
         </is>
       </c>
       <c r="E244" s="13" t="inlineStr">
         <is>
-          <t>{unit} tokkichi {label} keessa ture.</t>
+          <t>Marii kana keessa ergaan hin jiru.</t>
         </is>
       </c>
       <c r="F244" s="12" t="inlineStr">
         <is>
-          <t>እቲ ሓደ {unit} ብ{label} ነይሩ።</t>
+          <t>ኣብዚ ዝርርብ መልእኽቲ የለን።</t>
         </is>
       </c>
       <c r="G244" s="13" t="inlineStr">
         <is>
-          <t>{unit} kaliya wuxuu ku jiray {label}.</t>
+          <t>Wadahadalkan fariin kuma jirto.</t>
         </is>
       </c>
       <c r="H244" s="13" t="inlineStr">
         <is>
-          <t>{unit} pekee ilikuwa katika {label}.</t>
+          <t>Hakuna ujumbe katika mazungumzo haya.</t>
         </is>
       </c>
       <c r="I244" s="14" t="inlineStr"/>
@@ -16737,7 +16737,7 @@
     <row r="245" ht="44" customHeight="1">
       <c r="A245" s="11" t="inlineStr">
         <is>
-          <t>channel_all_from_one</t>
+          <t>donut_all_in_one</t>
         </is>
       </c>
       <c r="B245" s="11" t="inlineStr">
@@ -16747,32 +16747,32 @@
       </c>
       <c r="C245" s="11" t="inlineStr">
         <is>
-          <t>The single conversation came from {label}.</t>
+          <t>The single {unit} was in {label}.</t>
         </is>
       </c>
       <c r="D245" s="12" t="inlineStr">
         <is>
-          <t>ብቸኛው ውይይት ከ{label} መጥቷል።</t>
+          <t>ብቸኛው {unit} በ{label} ነበር።</t>
         </is>
       </c>
       <c r="E245" s="13" t="inlineStr">
         <is>
-          <t>Mariin tokkichi {label} irraa dhufe.</t>
+          <t>{unit} tokkichi {label} keessa ture.</t>
         </is>
       </c>
       <c r="F245" s="12" t="inlineStr">
         <is>
-          <t>እቲ ሓደ ዝርርብ ካብ {label} መጺኡ።</t>
+          <t>እቲ ሓደ {unit} ብ{label} ነይሩ።</t>
         </is>
       </c>
       <c r="G245" s="13" t="inlineStr">
         <is>
-          <t>Wadahadalka kaliya wuxuu ka yimid {label}.</t>
+          <t>{unit} kaliya wuxuu ku jiray {label}.</t>
         </is>
       </c>
       <c r="H245" s="13" t="inlineStr">
         <is>
-          <t>Mazungumzo pekee yalitoka {label}.</t>
+          <t>{unit} pekee ilikuwa katika {label}.</t>
         </is>
       </c>
       <c r="I245" s="14" t="inlineStr"/>
@@ -16780,7 +16780,7 @@
     <row r="246" ht="44" customHeight="1">
       <c r="A246" s="11" t="inlineStr">
         <is>
-          <t>unit_conversation</t>
+          <t>channel_all_from_one</t>
         </is>
       </c>
       <c r="B246" s="11" t="inlineStr">
@@ -16790,32 +16790,32 @@
       </c>
       <c r="C246" s="11" t="inlineStr">
         <is>
-          <t>conversation</t>
+          <t>The single conversation came from {label}.</t>
         </is>
       </c>
       <c r="D246" s="12" t="inlineStr">
         <is>
-          <t>ውይይት</t>
+          <t>ብቸኛው ውይይት ከ{label} መጥቷል።</t>
         </is>
       </c>
       <c r="E246" s="13" t="inlineStr">
         <is>
-          <t>marii</t>
+          <t>Mariin tokkichi {label} irraa dhufe.</t>
         </is>
       </c>
       <c r="F246" s="12" t="inlineStr">
         <is>
-          <t>ዝርርብ</t>
+          <t>እቲ ሓደ ዝርርብ ካብ {label} መጺኡ።</t>
         </is>
       </c>
       <c r="G246" s="13" t="inlineStr">
         <is>
-          <t>wadahadal</t>
+          <t>Wadahadalka kaliya wuxuu ka yimid {label}.</t>
         </is>
       </c>
       <c r="H246" s="13" t="inlineStr">
         <is>
-          <t>mazungumzo</t>
+          <t>Mazungumzo pekee yalitoka {label}.</t>
         </is>
       </c>
       <c r="I246" s="14" t="inlineStr"/>
@@ -16823,7 +16823,7 @@
     <row r="247" ht="44" customHeight="1">
       <c r="A247" s="11" t="inlineStr">
         <is>
-          <t>live_sessions</t>
+          <t>unit_conversation</t>
         </is>
       </c>
       <c r="B247" s="11" t="inlineStr">
@@ -16833,32 +16833,32 @@
       </c>
       <c r="C247" s="11" t="inlineStr">
         <is>
-          <t>Live sessions</t>
+          <t>conversation</t>
         </is>
       </c>
       <c r="D247" s="12" t="inlineStr">
         <is>
-          <t>የቀጥታ ክፍለ-ጊዜዎች</t>
+          <t>ውይይት</t>
         </is>
       </c>
       <c r="E247" s="13" t="inlineStr">
         <is>
-          <t>Marii kallattii</t>
+          <t>marii</t>
         </is>
       </c>
       <c r="F247" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታ ክፍለ-ግዜታት</t>
+          <t>ዝርርብ</t>
         </is>
       </c>
       <c r="G247" s="13" t="inlineStr">
         <is>
-          <t>Kalfadhiyada tooska ah</t>
+          <t>wadahadal</t>
         </is>
       </c>
       <c r="H247" s="13" t="inlineStr">
         <is>
-          <t>Vikao vya Moja kwa Moja</t>
+          <t>mazungumzo</t>
         </is>
       </c>
       <c r="I247" s="14" t="inlineStr"/>
@@ -16866,7 +16866,7 @@
     <row r="248" ht="44" customHeight="1">
       <c r="A248" s="11" t="inlineStr">
         <is>
-          <t>switched_off_for_bank</t>
+          <t>live_sessions</t>
         </is>
       </c>
       <c r="B248" s="11" t="inlineStr">
@@ -16876,32 +16876,32 @@
       </c>
       <c r="C248" s="11" t="inlineStr">
         <is>
-          <t>Switched off for this bank</t>
+          <t>Live sessions</t>
         </is>
       </c>
       <c r="D248" s="12" t="inlineStr">
         <is>
-          <t>ለዚህ ባንክ ጠፍቷል</t>
+          <t>የቀጥታ ክፍለ-ጊዜዎች</t>
         </is>
       </c>
       <c r="E248" s="13" t="inlineStr">
         <is>
-          <t>Baankii kanaaf dhaamsameera</t>
+          <t>Marii kallattii</t>
         </is>
       </c>
       <c r="F248" s="12" t="inlineStr">
         <is>
-          <t>ነዚ ባንኪ ጠፊኡ</t>
+          <t>ቀጥታ ክፍለ-ግዜታት</t>
         </is>
       </c>
       <c r="G248" s="13" t="inlineStr">
         <is>
-          <t>Bangigan waa la damiyay</t>
+          <t>Kalfadhiyada tooska ah</t>
         </is>
       </c>
       <c r="H248" s="13" t="inlineStr">
         <is>
-          <t>Vimezimwa kwa Benki Hii</t>
+          <t>Vikao vya Moja kwa Moja</t>
         </is>
       </c>
       <c r="I248" s="14" t="inlineStr"/>
@@ -16909,7 +16909,7 @@
     <row r="249" ht="44" customHeight="1">
       <c r="A249" s="11" t="inlineStr">
         <is>
-          <t>switched_on_nobody_on_duty</t>
+          <t>switched_off_for_bank</t>
         </is>
       </c>
       <c r="B249" s="11" t="inlineStr">
@@ -16919,32 +16919,32 @@
       </c>
       <c r="C249" s="11" t="inlineStr">
         <is>
-          <t>Switched on — but nobody is on duty</t>
+          <t>Switched off for this bank</t>
         </is>
       </c>
       <c r="D249" s="12" t="inlineStr">
         <is>
-          <t>በርቷል — ግን ማንም በሥራ ላይ የለም</t>
+          <t>ለዚህ ባንክ ጠፍቷል</t>
         </is>
       </c>
       <c r="E249" s="13" t="inlineStr">
         <is>
-          <t>Banameera — garuu namni hojii irra hin jiru</t>
+          <t>Baankii kanaaf dhaamsameera</t>
         </is>
       </c>
       <c r="F249" s="12" t="inlineStr">
         <is>
-          <t>በሪሁ — ግና ዋላ ሓደ ኣብ ስራሕ የለን</t>
+          <t>ነዚ ባንኪ ጠፊኡ</t>
         </is>
       </c>
       <c r="G249" s="13" t="inlineStr">
         <is>
-          <t>Waa la shiday — laakiin qofna shaqada ma joogo</t>
+          <t>Bangigan waa la damiyay</t>
         </is>
       </c>
       <c r="H249" s="13" t="inlineStr">
         <is>
-          <t>Vimewashwa — lakini hakuna aliye kazini</t>
+          <t>Vimezimwa kwa Benki Hii</t>
         </is>
       </c>
       <c r="I249" s="14" t="inlineStr"/>
@@ -16952,7 +16952,7 @@
     <row r="250" ht="44" customHeight="1">
       <c r="A250" s="11" t="inlineStr">
         <is>
-          <t>no_teller_button</t>
+          <t>switched_on_nobody_on_duty</t>
         </is>
       </c>
       <c r="B250" s="11" t="inlineStr">
@@ -16962,32 +16962,32 @@
       </c>
       <c r="C250" s="11" t="inlineStr">
         <is>
-          <t>No “Speak to a teller” button appears in your widget.</t>
+          <t>Switched on — but nobody is on duty</t>
         </is>
       </c>
       <c r="D250" s="12" t="inlineStr">
         <is>
-          <t>በመግብርዎ ውስጥ “ከገንዘብ ተቀባይ ጋር ይነጋገሩ” የሚል አዝራር አይታይም።</t>
+          <t>በርቷል — ግን ማንም በሥራ ላይ የለም</t>
         </is>
       </c>
       <c r="E250" s="13" t="inlineStr">
         <is>
-          <t>Widjetii keessan keessatti qabduun “Namaa waliin haasa'aa” hin mul'atu.</t>
+          <t>Banameera — garuu namni hojii irra hin jiru</t>
         </is>
       </c>
       <c r="F250" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መግበሪኹም “ምስ ተቐባሊ ገንዘብ ተዛረቡ” ዝብል መጠወቒ ኣይረአን።</t>
+          <t>በሪሁ — ግና ዋላ ሓደ ኣብ ስራሕ የለን</t>
         </is>
       </c>
       <c r="G250" s="13" t="inlineStr">
         <is>
-          <t>Badhanka “La hadal shaqaale” kama muuqan widget-kaaga.</t>
+          <t>Waa la shiday — laakiin qofna shaqada ma joogo</t>
         </is>
       </c>
       <c r="H250" s="13" t="inlineStr">
         <is>
-          <t>Hakuna kitufe cha "Zungumza na Afisa" kinachoonekana kwenye kidirisha chako.</t>
+          <t>Vimewashwa — lakini hakuna aliye kazini</t>
         </is>
       </c>
       <c r="I250" s="14" t="inlineStr"/>
@@ -16995,7 +16995,7 @@
     <row r="251" ht="44" customHeight="1">
       <c r="A251" s="11" t="inlineStr">
         <is>
-          <t>on_duty_explainer</t>
+          <t>no_teller_button</t>
         </is>
       </c>
       <c r="B251" s="11" t="inlineStr">
@@ -17005,32 +17005,32 @@
       </c>
       <c r="C251" s="11" t="inlineStr">
         <is>
-          <t>You are on duty, so waiting customers can be routed to you. Go off duty from the sidebar when you step away — you stay on the air anywhere in the console until you do.</t>
+          <t>No “Speak to a teller” button appears in your widget.</t>
         </is>
       </c>
       <c r="D251" s="12" t="inlineStr">
         <is>
-          <t>በሥራ ላይ ነዎት፤ ስለዚህ የሚጠብቁ ደንበኞች ወደ እርስዎ ሊመሩ ይችላሉ። ሲርቁ ከጎን አሞሌው ከሥራ ውጡ — እስከዚያ ድረስ በየትኛውም ገጽ ላይ በሥራ ላይ ይቆያሉ።</t>
+          <t>በመግብርዎ ውስጥ “ከገንዘብ ተቀባይ ጋር ይነጋገሩ” የሚል አዝራር አይታይም።</t>
         </is>
       </c>
       <c r="E251" s="13" t="inlineStr">
         <is>
-          <t>Hojii irra jirtu, kanaafuu maamiltoonni eegaa jiran gara keessan qajeelfamuu danda'u. Yeroo achii deemtan cinaacha irraa hojii keessaa ba'aa — hanga sanatti fuula kamiyyuu irratti hojii irra turtu.</t>
+          <t>Widjetii keessan keessatti qabduun “Namaa waliin haasa'aa” hin mul'atu.</t>
         </is>
       </c>
       <c r="F251" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ስራሕ ኢኹም፣ ስለዚ ዝጽበዩ ዓማዊል ናባኹም ክምርሑ ይኽእሉ። ክትርሕቁ ከለኹም ካብ ናይ ጎኒ መስመር ካብ ስራሕ ውጹ — ክሳብ ሽዑ ኣብ ዝኾነ ገጽ ኣብ ስራሕ ትጸንሑ።</t>
+          <t>ኣብ መግበሪኹም “ምስ ተቐባሊ ገንዘብ ተዛረቡ” ዝብል መጠወቒ ኣይረአን።</t>
         </is>
       </c>
       <c r="G251" s="13" t="inlineStr">
         <is>
-          <t>Shaqada ayaad joogtaa, sidaas darteed macaamiisha sugaya waa lagu soo dhiibi karaa. Marka aad tagto shaqada ka bax dhinaca — ilaa markaas bog kasta ayaad ku sii shaqeynaysaa.</t>
+          <t>Badhanka “La hadal shaqaale” kama muuqan widget-kaaga.</t>
         </is>
       </c>
       <c r="H251" s="13" t="inlineStr">
         <is>
-          <t>Upo kazini, kwa hivyo wateja wanaosubiri wanaweza kuelekezwa kwako. Toka kazini kutoka upande wa kando unapoondoka — unabaki kwenye mtandao popote kwenye paneli mpaka utakapofanya hivyo.</t>
+          <t>Hakuna kitufe cha "Zungumza na Afisa" kinachoonekana kwenye kidirisha chako.</t>
         </is>
       </c>
       <c r="I251" s="14" t="inlineStr"/>
@@ -17038,7 +17038,7 @@
     <row r="252" ht="44" customHeight="1">
       <c r="A252" s="11" t="inlineStr">
         <is>
-          <t>off_duty_explainer</t>
+          <t>on_duty_explainer</t>
         </is>
       </c>
       <c r="B252" s="11" t="inlineStr">
@@ -17048,32 +17048,32 @@
       </c>
       <c r="C252" s="11" t="inlineStr">
         <is>
-          <t>Switch On duty in the sidebar to start taking calls. It follows you across every page, so you no longer have to keep this one open.</t>
+          <t>You are on duty, so waiting customers can be routed to you. Go off duty from the sidebar when you step away — you stay on the air anywhere in the console until you do.</t>
         </is>
       </c>
       <c r="D252" s="12" t="inlineStr">
         <is>
-          <t>ጥሪዎችን መቀበል ለመጀመር ከጎን አሞሌው “በሥራ ላይ” ያብሩ። በሁሉም ገጽ ላይ ይከተልዎታል፤ ስለዚህ ይህን ገጽ ክፍት ማድረግ አያስፈልግም።</t>
+          <t>በሥራ ላይ ነዎት፤ ስለዚህ የሚጠብቁ ደንበኞች ወደ እርስዎ ሊመሩ ይችላሉ። ሲርቁ ከጎን አሞሌው ከሥራ ውጡ — እስከዚያ ድረስ በየትኛውም ገጽ ላይ በሥራ ላይ ይቆያሉ።</t>
         </is>
       </c>
       <c r="E252" s="13" t="inlineStr">
         <is>
-          <t>Bilbila fudhachuu jalqabuuf cinaacha irraa “Hojii irra” banaa. Fuula hunda irratti isin hordofa, kanaafuu fuula kana banaa gochuun hin barbaachisu.</t>
+          <t>Hojii irra jirtu, kanaafuu maamiltoonni eegaa jiran gara keessan qajeelfamuu danda'u. Yeroo achii deemtan cinaacha irraa hojii keessaa ba'aa — hanga sanatti fuula kamiyyuu irratti hojii irra turtu.</t>
         </is>
       </c>
       <c r="F252" s="12" t="inlineStr">
         <is>
-          <t>ጻውዒታት ክትቅበሉ ንምጅማር ካብ ናይ ጎኒ መስመር “ኣብ ስራሕ” ኣብርሁ። ኣብ ኩሉ ገጽ ይስዕበኩም፣ ስለዚ ነዚ ገጽ ክፉት ምግባር ኣየድልን።</t>
+          <t>ኣብ ስራሕ ኢኹም፣ ስለዚ ዝጽበዩ ዓማዊል ናባኹም ክምርሑ ይኽእሉ። ክትርሕቁ ከለኹም ካብ ናይ ጎኒ መስመር ካብ ስራሕ ውጹ — ክሳብ ሽዑ ኣብ ዝኾነ ገጽ ኣብ ስራሕ ትጸንሑ።</t>
         </is>
       </c>
       <c r="G252" s="13" t="inlineStr">
         <is>
-          <t>Si aad u bilowdo qaadista wicitaannada, dhinaca ka shid “Shaqada”. Bog kasta ayuu kula socdaa, sidaas darteed uma baahnid inaad tan furan ka tagto.</t>
+          <t>Shaqada ayaad joogtaa, sidaas darteed macaamiisha sugaya waa lagu soo dhiibi karaa. Marka aad tagto shaqada ka bax dhinaca — ilaa markaas bog kasta ayaad ku sii shaqeynaysaa.</t>
         </is>
       </c>
       <c r="H252" s="13" t="inlineStr">
         <is>
-          <t>Washa Kazini kwenye upande wa kando ili kuanza kupokea simu. Inakufuata kwenye kila ukurasa, hivyo huhitaji tena kuweka huu wazi.</t>
+          <t>Upo kazini, kwa hivyo wateja wanaosubiri wanaweza kuelekezwa kwako. Toka kazini kutoka upande wa kando unapoondoka — unabaki kwenye mtandao popote kwenye paneli mpaka utakapofanya hivyo.</t>
         </is>
       </c>
       <c r="I252" s="14" t="inlineStr"/>
@@ -17081,7 +17081,7 @@
     <row r="253" ht="44" customHeight="1">
       <c r="A253" s="11" t="inlineStr">
         <is>
-          <t>colleague_must_be_on_duty</t>
+          <t>off_duty_explainer</t>
         </is>
       </c>
       <c r="B253" s="11" t="inlineStr">
@@ -17091,32 +17091,32 @@
       </c>
       <c r="C253" s="11" t="inlineStr">
         <is>
-          <t>A colleague with permission to take calls has to be on duty before customers are offered one.</t>
+          <t>Switch On duty in the sidebar to start taking calls. It follows you across every page, so you no longer have to keep this one open.</t>
         </is>
       </c>
       <c r="D253" s="12" t="inlineStr">
         <is>
-          <t>ጥሪ የመቀበል ፈቃድ ያለው ባልደረባ በሥራ ላይ መሆን አለበት፤ ከዚያ በፊት ለደንበኞች አይቀርብም።</t>
+          <t>ጥሪዎችን መቀበል ለመጀመር ከጎን አሞሌው “በሥራ ላይ” ያብሩ። በሁሉም ገጽ ላይ ይከተልዎታል፤ ስለዚህ ይህን ገጽ ክፍት ማድረግ አያስፈልግም።</t>
         </is>
       </c>
       <c r="E253" s="13" t="inlineStr">
         <is>
-          <t>Hojjetaan hayyama bilbila fudhachuu qabu hojii irra jiraachuu qaba, sana dura maamiltootaaf hin dhiyaatu.</t>
+          <t>Bilbila fudhachuu jalqabuuf cinaacha irraa “Hojii irra” banaa. Fuula hunda irratti isin hordofa, kanaafuu fuula kana banaa gochuun hin barbaachisu.</t>
         </is>
       </c>
       <c r="F253" s="12" t="inlineStr">
         <is>
-          <t>ጻውዒት ናይ ምቕባል ፍቓድ ዘለዎ መሳርሕቲ ኣብ ስራሕ ክህሉ ኣለዎ፣ ቅድሚኡ ንዓማዊል ኣይቀርብን።</t>
+          <t>ጻውዒታት ክትቅበሉ ንምጅማር ካብ ናይ ጎኒ መስመር “ኣብ ስራሕ” ኣብርሁ። ኣብ ኩሉ ገጽ ይስዕበኩም፣ ስለዚ ነዚ ገጽ ክፉት ምግባር ኣየድልን።</t>
         </is>
       </c>
       <c r="G253" s="13" t="inlineStr">
         <is>
-          <t>Shaqaale haysta ogolaanshaha qaadista wicitaannada waa inuu shaqada joogaa ka hor inta aan macaamiisha la siin.</t>
+          <t>Si aad u bilowdo qaadista wicitaannada, dhinaca ka shid “Shaqada”. Bog kasta ayuu kula socdaa, sidaas darteed uma baahnid inaad tan furan ka tagto.</t>
         </is>
       </c>
       <c r="H253" s="13" t="inlineStr">
         <is>
-          <t>Mwenzako mwenye ruhusa ya kupokea simu lazima awe kazini kabla wateja hawajapewa fursa hiyo.</t>
+          <t>Washa Kazini kwenye upande wa kando ili kuanza kupokea simu. Inakufuata kwenye kila ukurasa, hivyo huhitaji tena kuweka huu wazi.</t>
         </is>
       </c>
       <c r="I253" s="14" t="inlineStr"/>
@@ -17124,7 +17124,7 @@
     <row r="254" ht="44" customHeight="1">
       <c r="A254" s="11" t="inlineStr">
         <is>
-          <t>i_can_converse_in</t>
+          <t>colleague_must_be_on_duty</t>
         </is>
       </c>
       <c r="B254" s="11" t="inlineStr">
@@ -17134,32 +17134,32 @@
       </c>
       <c r="C254" s="11" t="inlineStr">
         <is>
-          <t>I can hold a conversation in:</t>
+          <t>A colleague with permission to take calls has to be on duty before customers are offered one.</t>
         </is>
       </c>
       <c r="D254" s="12" t="inlineStr">
         <is>
-          <t>በእነዚህ ቋንቋዎች መነጋገር እችላለሁ፦</t>
+          <t>ጥሪ የመቀበል ፈቃድ ያለው ባልደረባ በሥራ ላይ መሆን አለበት፤ ከዚያ በፊት ለደንበኞች አይቀርብም።</t>
         </is>
       </c>
       <c r="E254" s="13" t="inlineStr">
         <is>
-          <t>Afaanota kanneeniin haasa'uu nan danda'a:</t>
+          <t>Hojjetaan hayyama bilbila fudhachuu qabu hojii irra jiraachuu qaba, sana dura maamiltootaaf hin dhiyaatu.</t>
         </is>
       </c>
       <c r="F254" s="12" t="inlineStr">
         <is>
-          <t>በዞም ቋንቋታት ክዛረብ እኽእል፦</t>
+          <t>ጻውዒት ናይ ምቕባል ፍቓድ ዘለዎ መሳርሕቲ ኣብ ስራሕ ክህሉ ኣለዎ፣ ቅድሚኡ ንዓማዊል ኣይቀርብን።</t>
         </is>
       </c>
       <c r="G254" s="13" t="inlineStr">
         <is>
-          <t>Waxaan ku hadli karaa:</t>
+          <t>Shaqaale haysta ogolaanshaha qaadista wicitaannada waa inuu shaqada joogaa ka hor inta aan macaamiisha la siin.</t>
         </is>
       </c>
       <c r="H254" s="13" t="inlineStr">
         <is>
-          <t>Ninaweza kufanya mazungumzo kwa:</t>
+          <t>Mwenzako mwenye ruhusa ya kupokea simu lazima awe kazini kabla wateja hawajapewa fursa hiyo.</t>
         </is>
       </c>
       <c r="I254" s="14" t="inlineStr"/>
@@ -17167,7 +17167,7 @@
     <row r="255" ht="44" customHeight="1">
       <c r="A255" s="11" t="inlineStr">
         <is>
-          <t>languages_picked_note</t>
+          <t>i_can_converse_in</t>
         </is>
       </c>
       <c r="B255" s="11" t="inlineStr">
@@ -17177,32 +17177,32 @@
       </c>
       <c r="C255" s="11" t="inlineStr">
         <is>
-          <t>Customers writing in these reach you first. Everyone else still reaches you — after a short wait, so nobody is stranded.</t>
+          <t>I can hold a conversation in:</t>
         </is>
       </c>
       <c r="D255" s="12" t="inlineStr">
         <is>
-          <t>በእነዚህ ቋንቋዎች የሚጽፉ ደንበኞች መጀመሪያ ወደ እርስዎ ይደርሳሉ። ሌሎችም ይደርሳሉ — ከአጭር ጥበቃ በኋላ፤ ማንም አይቀርም።</t>
+          <t>በእነዚህ ቋንቋዎች መነጋገር እችላለሁ፦</t>
         </is>
       </c>
       <c r="E255" s="13" t="inlineStr">
         <is>
-          <t>Maamiltoonni afaanota kanaan barreessan jalqaba isin bira ga'u. Kaan hundinuu ammas isin bira ga'u — eegumsa gabaabaa booda, namni hafu hin jiru.</t>
+          <t>Afaanota kanneeniin haasa'uu nan danda'a:</t>
         </is>
       </c>
       <c r="F255" s="12" t="inlineStr">
         <is>
-          <t>በዞም ቋንቋታት ዝጽሕፉ ዓማዊል ቅድም ናባኹም ይበጽሑ። እቶም ካልኦት እውን ይበጽሑ — ድሕሪ ሓጺር ጽበት፣ ዋላ ሓደ ኣይተርፍን።</t>
+          <t>በዞም ቋንቋታት ክዛረብ እኽእል፦</t>
         </is>
       </c>
       <c r="G255" s="13" t="inlineStr">
         <is>
-          <t>Macaamiisha ku qora kuwan ayaa marka hore kugu soo gaara. Qof kastana wuu ku soo gaari doonaa — sug gaaban ka dib, sidaas qofna ma harayo.</t>
+          <t>Waxaan ku hadli karaa:</t>
         </is>
       </c>
       <c r="H255" s="13" t="inlineStr">
         <is>
-          <t>Wateja wanaoandika kwa lugha hizi wanakufikia kwanza. Kila mtu mwingine bado anakufikia — baada ya kusubiri kidogo, ili asibaki bila msaada.</t>
+          <t>Ninaweza kufanya mazungumzo kwa:</t>
         </is>
       </c>
       <c r="I255" s="14" t="inlineStr"/>
@@ -17210,7 +17210,7 @@
     <row r="256" ht="44" customHeight="1">
       <c r="A256" s="11" t="inlineStr">
         <is>
-          <t>languages_none_note</t>
+          <t>languages_picked_note</t>
         </is>
       </c>
       <c r="B256" s="11" t="inlineStr">
@@ -17220,32 +17220,32 @@
       </c>
       <c r="C256" s="11" t="inlineStr">
         <is>
-          <t>Nothing selected, so every waiting customer is offered to you in plain oldest-first order.</t>
+          <t>Customers writing in these reach you first. Everyone else still reaches you — after a short wait, so nobody is stranded.</t>
         </is>
       </c>
       <c r="D256" s="12" t="inlineStr">
         <is>
-          <t>ምንም አልተመረጠም፤ ስለዚህ እያንዳንዱ የሚጠብቅ ደንበኛ በቀላል ቀዳሚ-መጀመሪያ ቅደም ተከተል ይቀርብልዎታል።</t>
+          <t>በእነዚህ ቋንቋዎች የሚጽፉ ደንበኞች መጀመሪያ ወደ እርስዎ ይደርሳሉ። ሌሎችም ይደርሳሉ — ከአጭር ጥበቃ በኋላ፤ ማንም አይቀርም።</t>
         </is>
       </c>
       <c r="E256" s="13" t="inlineStr">
         <is>
-          <t>Wanti filatame hin jiru, kanaafuu maamilli eegaa jiru hundi tartiiba dursaa-jalqabaatiin isinii dhiyaata.</t>
+          <t>Maamiltoonni afaanota kanaan barreessan jalqaba isin bira ga'u. Kaan hundinuu ammas isin bira ga'u — eegumsa gabaabaa booda, namni hafu hin jiru.</t>
         </is>
       </c>
       <c r="F256" s="12" t="inlineStr">
         <is>
-          <t>ዋላ ሓደ ኣይተመርጸን፣ ስለዚ ነፍስ ወከፍ ዝጽበ ዓሚል ብቐሊል ናይ ቀዳምነት ስርዓት ይቐርበልኩም።</t>
+          <t>በዞም ቋንቋታት ዝጽሕፉ ዓማዊል ቅድም ናባኹም ይበጽሑ። እቶም ካልኦት እውን ይበጽሑ — ድሕሪ ሓጺር ጽበት፣ ዋላ ሓደ ኣይተርፍን።</t>
         </is>
       </c>
       <c r="G256" s="13" t="inlineStr">
         <is>
-          <t>Waxba lama dooran, sidaas darteed macmiil kasta oo sugaya waxaa laguu soo bandhigayaa sida caadiga ah ee ugu horreeya.</t>
+          <t>Macaamiisha ku qora kuwan ayaa marka hore kugu soo gaara. Qof kastana wuu ku soo gaari doonaa — sug gaaban ka dib, sidaas qofna ma harayo.</t>
         </is>
       </c>
       <c r="H256" s="13" t="inlineStr">
         <is>
-          <t>Hakuna kilichochaguliwa, kwa hivyo kila mteja anayesubiri anapewa kwako kwa mpangilio wa zamani zaidi kwanza.</t>
+          <t>Wateja wanaoandika kwa lugha hizi wanakufikia kwanza. Kila mtu mwingine bado anakufikia — baada ya kusubiri kidogo, ili asibaki bila msaada.</t>
         </is>
       </c>
       <c r="I256" s="14" t="inlineStr"/>
@@ -17253,7 +17253,7 @@
     <row r="257" ht="44" customHeight="1">
       <c r="A257" s="11" t="inlineStr">
         <is>
-          <t>languages_updated</t>
+          <t>languages_none_note</t>
         </is>
       </c>
       <c r="B257" s="11" t="inlineStr">
@@ -17263,32 +17263,32 @@
       </c>
       <c r="C257" s="11" t="inlineStr">
         <is>
-          <t>Languages updated</t>
+          <t>Nothing selected, so every waiting customer is offered to you in plain oldest-first order.</t>
         </is>
       </c>
       <c r="D257" s="12" t="inlineStr">
         <is>
-          <t>ቋንቋዎች ተዘምነዋል</t>
+          <t>ምንም አልተመረጠም፤ ስለዚህ እያንዳንዱ የሚጠብቅ ደንበኛ በቀላል ቀዳሚ-መጀመሪያ ቅደም ተከተል ይቀርብልዎታል።</t>
         </is>
       </c>
       <c r="E257" s="13" t="inlineStr">
         <is>
-          <t>Afaanonni haaromfaman</t>
+          <t>Wanti filatame hin jiru, kanaafuu maamilli eegaa jiru hundi tartiiba dursaa-jalqabaatiin isinii dhiyaata.</t>
         </is>
       </c>
       <c r="F257" s="12" t="inlineStr">
         <is>
-          <t>ቋንቋታት ተሓዲሶም</t>
+          <t>ዋላ ሓደ ኣይተመርጸን፣ ስለዚ ነፍስ ወከፍ ዝጽበ ዓሚል ብቐሊል ናይ ቀዳምነት ስርዓት ይቐርበልኩም።</t>
         </is>
       </c>
       <c r="G257" s="13" t="inlineStr">
         <is>
-          <t>Luqadaha waa la cusbooneysiiyay</t>
+          <t>Waxba lama dooran, sidaas darteed macmiil kasta oo sugaya waxaa laguu soo bandhigayaa sida caadiga ah ee ugu horreeya.</t>
         </is>
       </c>
       <c r="H257" s="13" t="inlineStr">
         <is>
-          <t>Lugha Zimesasishwa</t>
+          <t>Hakuna kilichochaguliwa, kwa hivyo kila mteja anayesubiri anapewa kwako kwa mpangilio wa zamani zaidi kwanza.</t>
         </is>
       </c>
       <c r="I257" s="14" t="inlineStr"/>
@@ -17296,7 +17296,7 @@
     <row r="258" ht="44" customHeight="1">
       <c r="A258" s="11" t="inlineStr">
         <is>
-          <t>media_video</t>
+          <t>languages_updated</t>
         </is>
       </c>
       <c r="B258" s="11" t="inlineStr">
@@ -17306,32 +17306,32 @@
       </c>
       <c r="C258" s="11" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Languages updated</t>
         </is>
       </c>
       <c r="D258" s="12" t="inlineStr">
         <is>
-          <t>ቪዲዮ</t>
+          <t>ቋንቋዎች ተዘምነዋል</t>
         </is>
       </c>
       <c r="E258" s="13" t="inlineStr">
         <is>
-          <t>Viidiyoo</t>
+          <t>Afaanonni haaromfaman</t>
         </is>
       </c>
       <c r="F258" s="12" t="inlineStr">
         <is>
-          <t>ቪድዮ</t>
+          <t>ቋንቋታት ተሓዲሶም</t>
         </is>
       </c>
       <c r="G258" s="13" t="inlineStr">
         <is>
-          <t>Fiidyow</t>
+          <t>Luqadaha waa la cusbooneysiiyay</t>
         </is>
       </c>
       <c r="H258" s="13" t="inlineStr">
         <is>
-          <t>Vidio</t>
+          <t>Lugha Zimesasishwa</t>
         </is>
       </c>
       <c r="I258" s="14" t="inlineStr"/>
@@ -17339,7 +17339,7 @@
     <row r="259" ht="44" customHeight="1">
       <c r="A259" s="11" t="inlineStr">
         <is>
-          <t>media_audio</t>
+          <t>media_video</t>
         </is>
       </c>
       <c r="B259" s="11" t="inlineStr">
@@ -17349,32 +17349,32 @@
       </c>
       <c r="C259" s="11" t="inlineStr">
         <is>
-          <t>Audio</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="D259" s="12" t="inlineStr">
         <is>
-          <t>ድምፅ</t>
+          <t>ቪዲዮ</t>
         </is>
       </c>
       <c r="E259" s="13" t="inlineStr">
         <is>
-          <t>Sagalee</t>
+          <t>Viidiyoo</t>
         </is>
       </c>
       <c r="F259" s="12" t="inlineStr">
         <is>
-          <t>ድምጺ</t>
+          <t>ቪድዮ</t>
         </is>
       </c>
       <c r="G259" s="13" t="inlineStr">
         <is>
-          <t>Cod</t>
+          <t>Fiidyow</t>
         </is>
       </c>
       <c r="H259" s="13" t="inlineStr">
         <is>
-          <t>Sauti</t>
+          <t>Vidio</t>
         </is>
       </c>
       <c r="I259" s="14" t="inlineStr"/>
@@ -17382,7 +17382,7 @@
     <row r="260" ht="44" customHeight="1">
       <c r="A260" s="11" t="inlineStr">
         <is>
-          <t>not_your_language</t>
+          <t>media_audio</t>
         </is>
       </c>
       <c r="B260" s="11" t="inlineStr">
@@ -17392,32 +17392,32 @@
       </c>
       <c r="C260" s="11" t="inlineStr">
         <is>
-          <t>not your language</t>
+          <t>Audio</t>
         </is>
       </c>
       <c r="D260" s="12" t="inlineStr">
         <is>
-          <t>የእርስዎ ቋንቋ አይደለም</t>
+          <t>ድምፅ</t>
         </is>
       </c>
       <c r="E260" s="13" t="inlineStr">
         <is>
-          <t>afaan keessanii miti</t>
+          <t>Sagalee</t>
         </is>
       </c>
       <c r="F260" s="12" t="inlineStr">
         <is>
-          <t>ናትኩም ቋንቋ ኣይኮነን</t>
+          <t>ድምጺ</t>
         </is>
       </c>
       <c r="G260" s="13" t="inlineStr">
         <is>
-          <t>ma aha luqaddaada</t>
+          <t>Cod</t>
         </is>
       </c>
       <c r="H260" s="13" t="inlineStr">
         <is>
-          <t>si lugha yako</t>
+          <t>Sauti</t>
         </is>
       </c>
       <c r="I260" s="14" t="inlineStr"/>
@@ -17425,7 +17425,7 @@
     <row r="261" ht="44" customHeight="1">
       <c r="A261" s="11" t="inlineStr">
         <is>
-          <t>languages_first_note</t>
+          <t>not_your_language</t>
         </is>
       </c>
       <c r="B261" s="11" t="inlineStr">
@@ -17435,32 +17435,32 @@
       </c>
       <c r="C261" s="11" t="inlineStr">
         <is>
-          <t>Your languages first, longest wait within each. Anyone waiting too long moves to the top whatever they speak.</t>
+          <t>not your language</t>
         </is>
       </c>
       <c r="D261" s="12" t="inlineStr">
         <is>
-          <t>የእርስዎ ቋንቋዎች መጀመሪያ፤ በእያንዳንዱ ውስጥ ረጅም የጠበቀው ይቀድማል። ከልክ በላይ የጠበቀ ማንኛውም ሰው የሚናገረው ምንም ይሁን ወደ ላይ ይወጣል።</t>
+          <t>የእርስዎ ቋንቋ አይደለም</t>
         </is>
       </c>
       <c r="E261" s="13" t="inlineStr">
         <is>
-          <t>Afaanonni keessan jalqaba, tokkoon tokkoon isaanii keessatti kan yeroo dheeraa eege dursa. Namni baay'ee eege afaan kamiyyuu haa dubbatu gara oliitti deema.</t>
+          <t>afaan keessanii miti</t>
         </is>
       </c>
       <c r="F261" s="12" t="inlineStr">
         <is>
-          <t>ቋንቋታትኩም ቅድም፣ ኣብ ነፍስ ወከፍ እቲ ነዊሕ ዝጸንሐ ይቐድም። ካብ ንቡር ንላዕሊ ዝጸንሐ ዝኾነ ሰብ ዝዛረቦ ብዘየገድስ ናብ ላዕሊ ይመጽእ።</t>
+          <t>ናትኩም ቋንቋ ኣይኮነን</t>
         </is>
       </c>
       <c r="G261" s="13" t="inlineStr">
         <is>
-          <t>Luqadahaaga marka hore, kii ugu sugay dheeraa mid kasta gudahood. Qof kasta oo aad u sugay ayaa kor u kaca luqad kastoo uu ku hadloba.</t>
+          <t>ma aha luqaddaada</t>
         </is>
       </c>
       <c r="H261" s="13" t="inlineStr">
         <is>
-          <t>Lugha zako kwanza, aliyesubiri kwa muda mrefu zaidi ndani ya kila moja. Yeyote anayesubiri kwa muda mrefu sana anapanda juu bila kujali anazungumza lugha gani.</t>
+          <t>si lugha yako</t>
         </is>
       </c>
       <c r="I261" s="14" t="inlineStr"/>
@@ -17468,7 +17468,7 @@
     <row r="262" ht="44" customHeight="1">
       <c r="A262" s="11" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>languages_first_note</t>
         </is>
       </c>
       <c r="B262" s="11" t="inlineStr">
@@ -17478,32 +17478,32 @@
       </c>
       <c r="C262" s="11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Your languages first, longest wait within each. Anyone waiting too long moves to the top whatever they speak.</t>
         </is>
       </c>
       <c r="D262" s="12" t="inlineStr">
         <is>
-          <t>በሂደት ላይ</t>
+          <t>የእርስዎ ቋንቋዎች መጀመሪያ፤ በእያንዳንዱ ውስጥ ረጅም የጠበቀው ይቀድማል። ከልክ በላይ የጠበቀ ማንኛውም ሰው የሚናገረው ምንም ይሁን ወደ ላይ ይወጣል።</t>
         </is>
       </c>
       <c r="E262" s="13" t="inlineStr">
         <is>
-          <t>Adeemsa irra</t>
+          <t>Afaanonni keessan jalqaba, tokkoon tokkoon isaanii keessatti kan yeroo dheeraa eege dursa. Namni baay'ee eege afaan kamiyyuu haa dubbatu gara oliitti deema.</t>
         </is>
       </c>
       <c r="F262" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መስርሕ</t>
+          <t>ቋንቋታትኩም ቅድም፣ ኣብ ነፍስ ወከፍ እቲ ነዊሕ ዝጸንሐ ይቐድም። ካብ ንቡር ንላዕሊ ዝጸንሐ ዝኾነ ሰብ ዝዛረቦ ብዘየገድስ ናብ ላዕሊ ይመጽእ።</t>
         </is>
       </c>
       <c r="G262" s="13" t="inlineStr">
         <is>
-          <t>Socda</t>
+          <t>Luqadahaaga marka hore, kii ugu sugay dheeraa mid kasta gudahood. Qof kasta oo aad u sugay ayaa kor u kaca luqad kastoo uu ku hadloba.</t>
         </is>
       </c>
       <c r="H262" s="13" t="inlineStr">
         <is>
-          <t>Inaendelea</t>
+          <t>Lugha zako kwanza, aliyesubiri kwa muda mrefu zaidi ndani ya kila moja. Yeyote anayesubiri kwa muda mrefu sana anapanda juu bila kujali anazungumza lugha gani.</t>
         </is>
       </c>
       <c r="I262" s="14" t="inlineStr"/>
@@ -17511,7 +17511,7 @@
     <row r="263" ht="44" customHeight="1">
       <c r="A263" s="11" t="inlineStr">
         <is>
-          <t>no_session_in_progress</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="B263" s="11" t="inlineStr">
@@ -17521,32 +17521,32 @@
       </c>
       <c r="C263" s="11" t="inlineStr">
         <is>
-          <t>No session in progress.</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="D263" s="12" t="inlineStr">
         <is>
-          <t>በሂደት ላይ ያለ ክፍለ-ጊዜ የለም።</t>
+          <t>በሂደት ላይ</t>
         </is>
       </c>
       <c r="E263" s="13" t="inlineStr">
         <is>
-          <t>Sessionii adeemsa irra jiru hin jiru.</t>
+          <t>Adeemsa irra</t>
         </is>
       </c>
       <c r="F263" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መስርሕ ዘሎ ክፍለ-ግዜ የለን።</t>
+          <t>ኣብ መስርሕ</t>
         </is>
       </c>
       <c r="G263" s="13" t="inlineStr">
         <is>
-          <t>Ma jiro kalfadhi socda.</t>
+          <t>Socda</t>
         </is>
       </c>
       <c r="H263" s="13" t="inlineStr">
         <is>
-          <t>Hakuna kikao kinachoendelea.</t>
+          <t>Inaendelea</t>
         </is>
       </c>
       <c r="I263" s="14" t="inlineStr"/>
@@ -17554,7 +17554,7 @@
     <row r="264" ht="44" customHeight="1">
       <c r="A264" s="11" t="inlineStr">
         <is>
-          <t>wait_suffix</t>
+          <t>no_session_in_progress</t>
         </is>
       </c>
       <c r="B264" s="11" t="inlineStr">
@@ -17564,32 +17564,32 @@
       </c>
       <c r="C264" s="11" t="inlineStr">
         <is>
-          <t>wait</t>
+          <t>No session in progress.</t>
         </is>
       </c>
       <c r="D264" s="12" t="inlineStr">
         <is>
-          <t>ጥበቃ</t>
+          <t>በሂደት ላይ ያለ ክፍለ-ጊዜ የለም።</t>
         </is>
       </c>
       <c r="E264" s="13" t="inlineStr">
         <is>
-          <t>eegumsa</t>
+          <t>Sessionii adeemsa irra jiru hin jiru.</t>
         </is>
       </c>
       <c r="F264" s="12" t="inlineStr">
         <is>
-          <t>ጽበት</t>
+          <t>ኣብ መስርሕ ዘሎ ክፍለ-ግዜ የለን።</t>
         </is>
       </c>
       <c r="G264" s="13" t="inlineStr">
         <is>
-          <t>sug</t>
+          <t>Ma jiro kalfadhi socda.</t>
         </is>
       </c>
       <c r="H264" s="13" t="inlineStr">
         <is>
-          <t>kusubiri</t>
+          <t>Hakuna kikao kinachoendelea.</t>
         </is>
       </c>
       <c r="I264" s="14" t="inlineStr"/>
@@ -17597,7 +17597,7 @@
     <row r="265" ht="44" customHeight="1">
       <c r="A265" s="11" t="inlineStr">
         <is>
-          <t>what_session_covers</t>
+          <t>wait_suffix</t>
         </is>
       </c>
       <c r="B265" s="11" t="inlineStr">
@@ -17607,32 +17607,32 @@
       </c>
       <c r="C265" s="11" t="inlineStr">
         <is>
-          <t>What a session covers</t>
+          <t>wait</t>
         </is>
       </c>
       <c r="D265" s="12" t="inlineStr">
         <is>
-          <t>አንድ ክፍለ-ጊዜ ምን ይሸፍናል</t>
+          <t>ጥበቃ</t>
         </is>
       </c>
       <c r="E265" s="13" t="inlineStr">
         <is>
-          <t>Sessioniin maal haguuga</t>
+          <t>eegumsa</t>
         </is>
       </c>
       <c r="F265" s="12" t="inlineStr">
         <is>
-          <t>ሓደ ክፍለ-ግዜ እንታይ ይሽፍን</t>
+          <t>ጽበት</t>
         </is>
       </c>
       <c r="G265" s="13" t="inlineStr">
         <is>
-          <t>Waxa kalfadhigu daboolo</t>
+          <t>sug</t>
         </is>
       </c>
       <c r="H265" s="13" t="inlineStr">
         <is>
-          <t>Kikao Kinajumuisha Nini</t>
+          <t>kusubiri</t>
         </is>
       </c>
       <c r="I265" s="14" t="inlineStr"/>
@@ -17640,7 +17640,7 @@
     <row r="266" ht="44" customHeight="1">
       <c r="A266" s="11" t="inlineStr">
         <is>
-          <t>session_scope_body</t>
+          <t>what_session_covers</t>
         </is>
       </c>
       <c r="B266" s="11" t="inlineStr">
@@ -17650,32 +17650,32 @@
       </c>
       <c r="C266" s="11" t="inlineStr">
         <is>
-          <t>Before someone is identified: general questions about products, eligibility and how to apply. Once you have checked their Fayda ID against the account and asked something only the account holder could answer: their own application, documents and disputes.</t>
+          <t>What a session covers</t>
         </is>
       </c>
       <c r="D266" s="12" t="inlineStr">
         <is>
-          <t>አንድ ሰው ከመለየቱ በፊት፦ ስለ ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል አጠቃላይ ጥያቄዎች። የፋይዳ መታወቂያቸውን ከሂሳቡ ጋር አመሳክረው የሂሳቡ ባለቤት ብቻ ሊመልሰው የሚችለውን ከጠየቁ በኋላ፦ የራሳቸው ማመልከቻ፣ ሰነዶችና ቅሬታዎች።</t>
+          <t>አንድ ክፍለ-ጊዜ ምን ይሸፍናል</t>
         </is>
       </c>
       <c r="E266" s="13" t="inlineStr">
         <is>
-          <t>Namni tokko utuu hin beekamin dura: gaaffii waliigalaa waa'ee oomishaalee, ulaagaa fi akkaataa itti iyyatan. Erga waraqaa eenyummaa Fayda isaanii herrega waliin madaalchiftanii waan abbaan herregaa qofti deebisuu danda'u gaafattanii booda: iyyannoo, sanadoota fi komii isaanii.</t>
+          <t>Sessioniin maal haguuga</t>
         </is>
       </c>
       <c r="F266" s="12" t="inlineStr">
         <is>
-          <t>ሓደ ሰብ ቅድሚ ምልላዩ፦ ብዛዕባ ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን ሓፈሻዊ ሕቶታት። መንነት ፋይዳኦም ምስ ሕሳብ ኣረጋጊጽኩም እቲ ወናኒ ሕሳብ ጥራይ ክምልሶ ዝኽእል ምስ ሓተትኩም፦ ናቶም ምልክታ፣ ሰነዳትን ጥርዓናትን።</t>
+          <t>ሓደ ክፍለ-ግዜ እንታይ ይሽፍን</t>
         </is>
       </c>
       <c r="G266" s="13" t="inlineStr">
         <is>
-          <t>Ka hor inta aan qofka la aqoonsan: su'aalo guud oo ku saabsan alaabta, u-qalmitaanka iyo sida loo codsado. Marka aad hubiso aqoonsigooda Fayda ee xisaabta oo aad weydiiso wax uu kaliya milkiilaha xisaabtu ka jawaabi karo: codsigooda, dukumiintiyada iyo cabashooyinka.</t>
+          <t>Waxa kalfadhigu daboolo</t>
         </is>
       </c>
       <c r="H266" s="13" t="inlineStr">
         <is>
-          <t>Kabla mtu hajatambuliwa: maswali ya jumla kuhusu bidhaa, sifa za kustahiki na jinsi ya kuomba. Baada ya kukagua Kitambulisho chao cha Fayda dhidi ya akaunti na kuuliza kitu ambacho mmiliki wa akaunti pekee angeweza kujibu: maombi yao wenyewe, nyaraka na migogoro.</t>
+          <t>Kikao Kinajumuisha Nini</t>
         </is>
       </c>
       <c r="I266" s="14" t="inlineStr"/>
@@ -17683,7 +17683,7 @@
     <row r="267" ht="44" customHeight="1">
       <c r="A267" s="11" t="inlineStr">
         <is>
-          <t>never_money_movement</t>
+          <t>session_scope_body</t>
         </is>
       </c>
       <c r="B267" s="11" t="inlineStr">
@@ -17693,32 +17693,32 @@
       </c>
       <c r="C267" s="11" t="inlineStr">
         <is>
-          <t>Never, at any point and for anyone: deposits, withdrawals or transfers. Those do not happen on a call.</t>
+          <t>Before someone is identified: general questions about products, eligibility and how to apply. Once you have checked their Fayda ID against the account and asked something only the account holder could answer: their own application, documents and disputes.</t>
         </is>
       </c>
       <c r="D267" s="12" t="inlineStr">
         <is>
-          <t>በፍጹም፣ በማንኛውም ጊዜና ለማንም፦ ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም። እነዚያ በጥሪ ላይ አይፈጸሙም።</t>
+          <t>አንድ ሰው ከመለየቱ በፊት፦ ስለ ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል አጠቃላይ ጥያቄዎች። የፋይዳ መታወቂያቸውን ከሂሳቡ ጋር አመሳክረው የሂሳቡ ባለቤት ብቻ ሊመልሰው የሚችለውን ከጠየቁ በኋላ፦ የራሳቸው ማመልከቻ፣ ሰነዶችና ቅሬታዎች።</t>
         </is>
       </c>
       <c r="E267" s="13" t="inlineStr">
         <is>
-          <t>Gonkumaa, yeroo kamiyyuu fi eenyuufiyyuu: kuusaa, baasii yookiin dabarsa hin jiru. Isaan sun bilbila irratti hin raawwataman.</t>
+          <t>Namni tokko utuu hin beekamin dura: gaaffii waliigalaa waa'ee oomishaalee, ulaagaa fi akkaataa itti iyyatan. Erga waraqaa eenyummaa Fayda isaanii herrega waliin madaalchiftanii waan abbaan herregaa qofti deebisuu danda'u gaafattanii booda: iyyannoo, sanadoota fi komii isaanii.</t>
         </is>
       </c>
       <c r="F267" s="12" t="inlineStr">
         <is>
-          <t>ፈጺሙ፣ ኣብ ዝኾነ እዋንን ንዝኾነ ሰብን፦ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን። እዚኣቶም ኣብ ጻውዒት ኣይፍጸሙን።</t>
+          <t>ሓደ ሰብ ቅድሚ ምልላዩ፦ ብዛዕባ ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን ሓፈሻዊ ሕቶታት። መንነት ፋይዳኦም ምስ ሕሳብ ኣረጋጊጽኩም እቲ ወናኒ ሕሳብ ጥራይ ክምልሶ ዝኽእል ምስ ሓተትኩም፦ ናቶም ምልክታ፣ ሰነዳትን ጥርዓናትን።</t>
         </is>
       </c>
       <c r="G267" s="13" t="inlineStr">
         <is>
-          <t>Weligaa, wakhti kasta iyo qof kasta: dhigasho, qaadis ama wareejin ma jirto. Kuwaas wicitaan laguma sameeyo.</t>
+          <t>Ka hor inta aan qofka la aqoonsan: su'aalo guud oo ku saabsan alaabta, u-qalmitaanka iyo sida loo codsado. Marka aad hubiso aqoonsigooda Fayda ee xisaabta oo aad weydiiso wax uu kaliya milkiilaha xisaabtu ka jawaabi karo: codsigooda, dukumiintiyada iyo cabashooyinka.</t>
         </is>
       </c>
       <c r="H267" s="13" t="inlineStr">
         <is>
-          <t>Kamwe, wakati wowote na kwa yeyote: amana, uondoaji au uhamishaji. Hizo hazifanyiki kwenye simu.</t>
+          <t>Kabla mtu hajatambuliwa: maswali ya jumla kuhusu bidhaa, sifa za kustahiki na jinsi ya kuomba. Baada ya kukagua Kitambulisho chao cha Fayda dhidi ya akaunti na kuuliza kitu ambacho mmiliki wa akaunti pekee angeweza kujibu: maombi yao wenyewe, nyaraka na migogoro.</t>
         </is>
       </c>
       <c r="I267" s="14" t="inlineStr"/>
@@ -17726,7 +17726,7 @@
     <row r="268" ht="44" customHeight="1">
       <c r="A268" s="11" t="inlineStr">
         <is>
-          <t>open_escalation_queue</t>
+          <t>never_money_movement</t>
         </is>
       </c>
       <c r="B268" s="11" t="inlineStr">
@@ -17736,32 +17736,32 @@
       </c>
       <c r="C268" s="11" t="inlineStr">
         <is>
-          <t>Open the escalation queue</t>
+          <t>Never, at any point and for anyone: deposits, withdrawals or transfers. Those do not happen on a call.</t>
         </is>
       </c>
       <c r="D268" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ወረፋውን ክፈት</t>
+          <t>በፍጹም፣ በማንኛውም ጊዜና ለማንም፦ ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም። እነዚያ በጥሪ ላይ አይፈጸሙም።</t>
         </is>
       </c>
       <c r="E268" s="13" t="inlineStr">
         <is>
-          <t>Sararaa dabarsaa banaa</t>
+          <t>Gonkumaa, yeroo kamiyyuu fi eenyuufiyyuu: kuusaa, baasii yookiin dabarsa hin jiru. Isaan sun bilbila irratti hin raawwataman.</t>
         </is>
       </c>
       <c r="F268" s="12" t="inlineStr">
         <is>
-          <t>ሪጋ ምትሕልላፍ ክፈት</t>
+          <t>ፈጺሙ፣ ኣብ ዝኾነ እዋንን ንዝኾነ ሰብን፦ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን። እዚኣቶም ኣብ ጻውዒት ኣይፍጸሙን።</t>
         </is>
       </c>
       <c r="G268" s="13" t="inlineStr">
         <is>
-          <t>Fur safka gudbinta</t>
+          <t>Weligaa, wakhti kasta iyo qof kasta: dhigasho, qaadis ama wareejin ma jirto. Kuwaas wicitaan laguma sameeyo.</t>
         </is>
       </c>
       <c r="H268" s="13" t="inlineStr">
         <is>
-          <t>Fungua Foleni ya Masuala Yaliyoelekezwa</t>
+          <t>Kamwe, wakati wowote na kwa yeyote: amana, uondoaji au uhamishaji. Hizo hazifanyiki kwenye simu.</t>
         </is>
       </c>
       <c r="I268" s="14" t="inlineStr"/>
@@ -17769,7 +17769,7 @@
     <row r="269" ht="44" customHeight="1">
       <c r="A269" s="11" t="inlineStr">
         <is>
-          <t>open_live_queue</t>
+          <t>open_escalation_queue</t>
         </is>
       </c>
       <c r="B269" s="11" t="inlineStr">
@@ -17779,32 +17779,32 @@
       </c>
       <c r="C269" s="11" t="inlineStr">
         <is>
-          <t>Open the live call queue</t>
+          <t>Open the escalation queue</t>
         </is>
       </c>
       <c r="D269" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታ የጥሪ ወረፋውን ክፈት</t>
+          <t>የማሸጋገሪያ ወረፋውን ክፈት</t>
         </is>
       </c>
       <c r="E269" s="13" t="inlineStr">
         <is>
-          <t>Sarara bilbilaa kallattii banaa</t>
+          <t>Sararaa dabarsaa banaa</t>
         </is>
       </c>
       <c r="F269" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታዊ ናይ ጻውዒት ሰልፊ ክፈት</t>
+          <t>ሪጋ ምትሕልላፍ ክፈት</t>
         </is>
       </c>
       <c r="G269" s="13" t="inlineStr">
         <is>
-          <t>Fur safka wicitaanka tooska ah</t>
+          <t>Fur safka gudbinta</t>
         </is>
       </c>
       <c r="H269" s="13" t="inlineStr">
         <is>
-          <t>Fungua foleni ya simu za moja kwa moja</t>
+          <t>Fungua Foleni ya Masuala Yaliyoelekezwa</t>
         </is>
       </c>
       <c r="I269" s="14" t="inlineStr"/>
@@ -17812,7 +17812,7 @@
     <row r="270" ht="44" customHeight="1">
       <c r="A270" s="11" t="inlineStr">
         <is>
-          <t>live_waiting_one</t>
+          <t>open_live_queue</t>
         </is>
       </c>
       <c r="B270" s="11" t="inlineStr">
@@ -17822,32 +17822,32 @@
       </c>
       <c r="C270" s="11" t="inlineStr">
         <is>
-          <t>{n} customer waiting for a live call</t>
+          <t>Open the live call queue</t>
         </is>
       </c>
       <c r="D270" s="12" t="inlineStr">
         <is>
-          <t>{n} ደንበኛ ቀጥታ ጥሪ በመጠበቅ ላይ ነው</t>
+          <t>ቀጥታ የጥሪ ወረፋውን ክፈት</t>
         </is>
       </c>
       <c r="E270" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan {n} bilbila kallattii eegaa jira</t>
+          <t>Sarara bilbilaa kallattii banaa</t>
         </is>
       </c>
       <c r="F270" s="12" t="inlineStr">
         <is>
-          <t>{n} ዓሚል ቀጥታዊ ጻውዒት ይጽበ ኣሎ</t>
+          <t>ቀጥታዊ ናይ ጻውዒት ሰልፊ ክፈት</t>
         </is>
       </c>
       <c r="G270" s="13" t="inlineStr">
         <is>
-          <t>{n} macmiil ayaa sugaya wicitaan toos ah</t>
+          <t>Fur safka wicitaanka tooska ah</t>
         </is>
       </c>
       <c r="H270" s="13" t="inlineStr">
         <is>
-          <t>Mteja {n} anasubiri simu ya moja kwa moja</t>
+          <t>Fungua foleni ya simu za moja kwa moja</t>
         </is>
       </c>
       <c r="I270" s="14" t="inlineStr"/>
@@ -17855,7 +17855,7 @@
     <row r="271" ht="44" customHeight="1">
       <c r="A271" s="11" t="inlineStr">
         <is>
-          <t>live_waiting_many</t>
+          <t>live_waiting_one</t>
         </is>
       </c>
       <c r="B271" s="11" t="inlineStr">
@@ -17865,32 +17865,32 @@
       </c>
       <c r="C271" s="11" t="inlineStr">
         <is>
-          <t>{n} customers waiting for a live call</t>
+          <t>{n} customer waiting for a live call</t>
         </is>
       </c>
       <c r="D271" s="12" t="inlineStr">
         <is>
-          <t>{n} ደንበኞች ቀጥታ ጥሪ በመጠበቅ ላይ ናቸው</t>
+          <t>{n} ደንበኛ ቀጥታ ጥሪ በመጠበቅ ላይ ነው</t>
         </is>
       </c>
       <c r="E271" s="13" t="inlineStr">
         <is>
-          <t>Maamiltoonni {n} bilbila kallattii eegaa jiru</t>
+          <t>Maamilaan {n} bilbila kallattii eegaa jira</t>
         </is>
       </c>
       <c r="F271" s="12" t="inlineStr">
         <is>
-          <t>{n} ዓማዊል ቀጥታዊ ጻውዒት ይጽበዩ ኣለዉ</t>
+          <t>{n} ዓሚል ቀጥታዊ ጻውዒት ይጽበ ኣሎ</t>
         </is>
       </c>
       <c r="G271" s="13" t="inlineStr">
         <is>
-          <t>{n} macaamiil ayaa sugaya wicitaan toos ah</t>
+          <t>{n} macmiil ayaa sugaya wicitaan toos ah</t>
         </is>
       </c>
       <c r="H271" s="13" t="inlineStr">
         <is>
-          <t>Wateja {n} wanasubiri simu ya moja kwa moja</t>
+          <t>Mteja {n} anasubiri simu ya moja kwa moja</t>
         </is>
       </c>
       <c r="I271" s="14" t="inlineStr"/>
@@ -17898,7 +17898,7 @@
     <row r="272" ht="44" customHeight="1">
       <c r="A272" s="11" t="inlineStr">
         <is>
-          <t>switch_dark_light</t>
+          <t>live_waiting_many</t>
         </is>
       </c>
       <c r="B272" s="11" t="inlineStr">
@@ -17908,32 +17908,32 @@
       </c>
       <c r="C272" s="11" t="inlineStr">
         <is>
-          <t>Switch between dark and light</t>
+          <t>{n} customers waiting for a live call</t>
         </is>
       </c>
       <c r="D272" s="12" t="inlineStr">
         <is>
-          <t>በጨለማና በብርሃን መካከል ቀይር</t>
+          <t>{n} ደንበኞች ቀጥታ ጥሪ በመጠበቅ ላይ ናቸው</t>
         </is>
       </c>
       <c r="E272" s="13" t="inlineStr">
         <is>
-          <t>Dukkanaa fi ifa gidduu jijjiiri</t>
+          <t>Maamiltoonni {n} bilbila kallattii eegaa jiru</t>
         </is>
       </c>
       <c r="F272" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መንጎ ጸላምን ብርሃንን ቀይር</t>
+          <t>{n} ዓማዊል ቀጥታዊ ጻውዒት ይጽበዩ ኣለዉ</t>
         </is>
       </c>
       <c r="G272" s="13" t="inlineStr">
         <is>
-          <t>U beddel mugdiga iyo iftiinka</t>
+          <t>{n} macaamiil ayaa sugaya wicitaan toos ah</t>
         </is>
       </c>
       <c r="H272" s="13" t="inlineStr">
         <is>
-          <t>Badilisha Kati ya Giza na Mwanga</t>
+          <t>Wateja {n} wanasubiri simu ya moja kwa moja</t>
         </is>
       </c>
       <c r="I272" s="14" t="inlineStr"/>
@@ -17941,7 +17941,7 @@
     <row r="273" ht="44" customHeight="1">
       <c r="A273" s="11" t="inlineStr">
         <is>
-          <t>live_session</t>
+          <t>switch_dark_light</t>
         </is>
       </c>
       <c r="B273" s="11" t="inlineStr">
@@ -17951,32 +17951,32 @@
       </c>
       <c r="C273" s="11" t="inlineStr">
         <is>
-          <t>Live session</t>
+          <t>Switch between dark and light</t>
         </is>
       </c>
       <c r="D273" s="12" t="inlineStr">
         <is>
-          <t>የቀጥታ ክፍለ-ጊዜ</t>
+          <t>በጨለማና በብርሃን መካከል ቀይር</t>
         </is>
       </c>
       <c r="E273" s="13" t="inlineStr">
         <is>
-          <t>Session kallattii</t>
+          <t>Dukkanaa fi ifa gidduu jijjiiri</t>
         </is>
       </c>
       <c r="F273" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታ ክፍለ-ግዜ</t>
+          <t>ኣብ መንጎ ጸላምን ብርሃንን ቀይር</t>
         </is>
       </c>
       <c r="G273" s="13" t="inlineStr">
         <is>
-          <t>Kalfadhi toos ah</t>
+          <t>U beddel mugdiga iyo iftiinka</t>
         </is>
       </c>
       <c r="H273" s="13" t="inlineStr">
         <is>
-          <t>Kikao cha Moja kwa Moja</t>
+          <t>Badilisha Kati ya Giza na Mwanga</t>
         </is>
       </c>
       <c r="I273" s="14" t="inlineStr"/>
@@ -17984,7 +17984,7 @@
     <row r="274" ht="44" customHeight="1">
       <c r="A274" s="11" t="inlineStr">
         <is>
-          <t>customer_left_call</t>
+          <t>live_session</t>
         </is>
       </c>
       <c r="B274" s="11" t="inlineStr">
@@ -17994,32 +17994,32 @@
       </c>
       <c r="C274" s="11" t="inlineStr">
         <is>
-          <t>The customer has left the call.</t>
+          <t>Live session</t>
         </is>
       </c>
       <c r="D274" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛው ጥሪውን ለቅቋል።</t>
+          <t>የቀጥታ ክፍለ-ጊዜ</t>
         </is>
       </c>
       <c r="E274" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan bilbila irraa ba'eera.</t>
+          <t>Session kallattii</t>
         </is>
       </c>
       <c r="F274" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዓሚል ካብቲ ጻውዒት ወጺኡ።</t>
+          <t>ቀጥታ ክፍለ-ግዜ</t>
         </is>
       </c>
       <c r="G274" s="13" t="inlineStr">
         <is>
-          <t>Macmiilku wicitaanka wuu ka baxay.</t>
+          <t>Kalfadhi toos ah</t>
         </is>
       </c>
       <c r="H274" s="13" t="inlineStr">
         <is>
-          <t>Mteja ameondoka kwenye simu.</t>
+          <t>Kikao cha Moja kwa Moja</t>
         </is>
       </c>
       <c r="I274" s="14" t="inlineStr"/>
@@ -18027,7 +18027,7 @@
     <row r="275" ht="44" customHeight="1">
       <c r="A275" s="11" t="inlineStr">
         <is>
-          <t>waiting_for_customer</t>
+          <t>customer_left_call</t>
         </is>
       </c>
       <c r="B275" s="11" t="inlineStr">
@@ -18037,32 +18037,32 @@
       </c>
       <c r="C275" s="11" t="inlineStr">
         <is>
-          <t>Waiting for the customer…</t>
+          <t>The customer has left the call.</t>
         </is>
       </c>
       <c r="D275" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛውን በመጠበቅ ላይ…</t>
+          <t>ደንበኛው ጥሪውን ለቅቋል።</t>
         </is>
       </c>
       <c r="E275" s="13" t="inlineStr">
         <is>
-          <t>Maamilaa eegaa jirra…</t>
+          <t>Maamilaan bilbila irraa ba'eera.</t>
         </is>
       </c>
       <c r="F275" s="12" t="inlineStr">
         <is>
-          <t>ነቲ ዓሚል ንጽበ ኣለና…</t>
+          <t>እቲ ዓሚል ካብቲ ጻውዒት ወጺኡ።</t>
         </is>
       </c>
       <c r="G275" s="13" t="inlineStr">
         <is>
-          <t>Macmiilka la sugayo…</t>
+          <t>Macmiilku wicitaanka wuu ka baxay.</t>
         </is>
       </c>
       <c r="H275" s="13" t="inlineStr">
         <is>
-          <t>Inasubiri Mteja…</t>
+          <t>Mteja ameondoka kwenye simu.</t>
         </is>
       </c>
       <c r="I275" s="14" t="inlineStr"/>
@@ -18070,7 +18070,7 @@
     <row r="276" ht="44" customHeight="1">
       <c r="A276" s="11" t="inlineStr">
         <is>
-          <t>mic_blocked</t>
+          <t>waiting_for_customer</t>
         </is>
       </c>
       <c r="B276" s="11" t="inlineStr">
@@ -18080,32 +18080,32 @@
       </c>
       <c r="C276" s="11" t="inlineStr">
         <is>
-          <t>Microphone access is blocked. Allow it in your browser and take the session again.</t>
+          <t>Waiting for the customer…</t>
         </is>
       </c>
       <c r="D276" s="12" t="inlineStr">
         <is>
-          <t>የማይክሮፎን መዳረሻ ታግዷል። በአሳሽዎ ውስጥ ይፍቀዱና ክፍለ-ጊዜውን እንደገና ይውሰዱ።</t>
+          <t>ደንበኛውን በመጠበቅ ላይ…</t>
         </is>
       </c>
       <c r="E276" s="13" t="inlineStr">
         <is>
-          <t>Maayikiroofoonii dhorkameera. Biraawzarii keessan keessatti hayyamaatii session irra deebi'aa fudhadhaa.</t>
+          <t>Maamilaa eegaa jirra…</t>
         </is>
       </c>
       <c r="F276" s="12" t="inlineStr">
         <is>
-          <t>መእተዊ ማይክሮፎን ተዓጊቱ። ኣብ መርበብ መንሸራተቲኹም ፍቐዱ እሞ ነቲ ክፍለ-ግዜ ደጊምኩም ውሰዱ።</t>
+          <t>ነቲ ዓሚል ንጽበ ኣለና…</t>
         </is>
       </c>
       <c r="G276" s="13" t="inlineStr">
         <is>
-          <t>Makarafoonka waa la xannibay. Browser-kaaga ka ogolow oo kalfadhiga mar kale qaado.</t>
+          <t>Macmiilka la sugayo…</t>
         </is>
       </c>
       <c r="H276" s="13" t="inlineStr">
         <is>
-          <t>Ufikiaji wa maikrofoni umezuiwa. Ruhusu kwenye kivinjari chako na uanze kikao tena.</t>
+          <t>Inasubiri Mteja…</t>
         </is>
       </c>
       <c r="I276" s="14" t="inlineStr"/>
@@ -18113,7 +18113,7 @@
     <row r="277" ht="44" customHeight="1">
       <c r="A277" s="11" t="inlineStr">
         <is>
-          <t>unknown_error</t>
+          <t>mic_blocked</t>
         </is>
       </c>
       <c r="B277" s="11" t="inlineStr">
@@ -18123,32 +18123,32 @@
       </c>
       <c r="C277" s="11" t="inlineStr">
         <is>
-          <t>unknown error</t>
+          <t>Microphone access is blocked. Allow it in your browser and take the session again.</t>
         </is>
       </c>
       <c r="D277" s="12" t="inlineStr">
         <is>
-          <t>ያልታወቀ ስህተት</t>
+          <t>የማይክሮፎን መዳረሻ ታግዷል። በአሳሽዎ ውስጥ ይፍቀዱና ክፍለ-ጊዜውን እንደገና ይውሰዱ።</t>
         </is>
       </c>
       <c r="E277" s="13" t="inlineStr">
         <is>
-          <t>dogoggora hin beekamne</t>
+          <t>Maayikiroofoonii dhorkameera. Biraawzarii keessan keessatti hayyamaatii session irra deebi'aa fudhadhaa.</t>
         </is>
       </c>
       <c r="F277" s="12" t="inlineStr">
         <is>
-          <t>ዘይተፈልጠ ጌጋ</t>
+          <t>መእተዊ ማይክሮፎን ተዓጊቱ። ኣብ መርበብ መንሸራተቲኹም ፍቐዱ እሞ ነቲ ክፍለ-ግዜ ደጊምኩም ውሰዱ።</t>
         </is>
       </c>
       <c r="G277" s="13" t="inlineStr">
         <is>
-          <t>khalad aan la garanayn</t>
+          <t>Makarafoonka waa la xannibay. Browser-kaaga ka ogolow oo kalfadhiga mar kale qaado.</t>
         </is>
       </c>
       <c r="H277" s="13" t="inlineStr">
         <is>
-          <t>hitilafu isiyojulikana</t>
+          <t>Ufikiaji wa maikrofoni umezuiwa. Ruhusu kwenye kivinjari chako na uanze kikao tena.</t>
         </is>
       </c>
       <c r="I277" s="14" t="inlineStr"/>
@@ -18156,7 +18156,7 @@
     <row r="278" ht="44" customHeight="1">
       <c r="A278" s="11" t="inlineStr">
         <is>
-          <t>no_messages_yet</t>
+          <t>unknown_error</t>
         </is>
       </c>
       <c r="B278" s="11" t="inlineStr">
@@ -18166,32 +18166,32 @@
       </c>
       <c r="C278" s="11" t="inlineStr">
         <is>
-          <t>No messages yet.</t>
+          <t>unknown error</t>
         </is>
       </c>
       <c r="D278" s="12" t="inlineStr">
         <is>
-          <t>እስካሁን መልእክት የለም።</t>
+          <t>ያልታወቀ ስህተት</t>
         </is>
       </c>
       <c r="E278" s="13" t="inlineStr">
         <is>
-          <t>Ammaaf ergaan hin jiru.</t>
+          <t>dogoggora hin beekamne</t>
         </is>
       </c>
       <c r="F278" s="12" t="inlineStr">
         <is>
-          <t>ክሳብ ሕጂ መልእኽቲ የለን።</t>
+          <t>ዘይተፈልጠ ጌጋ</t>
         </is>
       </c>
       <c r="G278" s="13" t="inlineStr">
         <is>
-          <t>Weli fariimo ma jiraan.</t>
+          <t>khalad aan la garanayn</t>
         </is>
       </c>
       <c r="H278" s="13" t="inlineStr">
         <is>
-          <t>Hakuna ujumbe bado.</t>
+          <t>hitilafu isiyojulikana</t>
         </is>
       </c>
       <c r="I278" s="14" t="inlineStr"/>
@@ -18199,7 +18199,7 @@
     <row r="279" ht="44" customHeight="1">
       <c r="A279" s="11" t="inlineStr">
         <is>
-          <t>you_label</t>
+          <t>no_messages_yet</t>
         </is>
       </c>
       <c r="B279" s="11" t="inlineStr">
@@ -18209,32 +18209,32 @@
       </c>
       <c r="C279" s="11" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>No messages yet.</t>
         </is>
       </c>
       <c r="D279" s="12" t="inlineStr">
         <is>
-          <t>እርስዎ</t>
+          <t>እስካሁን መልእክት የለም።</t>
         </is>
       </c>
       <c r="E279" s="13" t="inlineStr">
         <is>
-          <t>Isin</t>
+          <t>Ammaaf ergaan hin jiru.</t>
         </is>
       </c>
       <c r="F279" s="12" t="inlineStr">
         <is>
-          <t>ንስኹም</t>
+          <t>ክሳብ ሕጂ መልእኽቲ የለን።</t>
         </is>
       </c>
       <c r="G279" s="13" t="inlineStr">
         <is>
-          <t>Adiga</t>
+          <t>Weli fariimo ma jiraan.</t>
         </is>
       </c>
       <c r="H279" s="13" t="inlineStr">
         <is>
-          <t>Wewe</t>
+          <t>Hakuna ujumbe bado.</t>
         </is>
       </c>
       <c r="I279" s="14" t="inlineStr"/>
@@ -18242,7 +18242,7 @@
     <row r="280" ht="44" customHeight="1">
       <c r="A280" s="11" t="inlineStr">
         <is>
-          <t>assistant_label</t>
+          <t>you_label</t>
         </is>
       </c>
       <c r="B280" s="11" t="inlineStr">
@@ -18252,32 +18252,32 @@
       </c>
       <c r="C280" s="11" t="inlineStr">
         <is>
-          <t>Assistant</t>
+          <t>You</t>
         </is>
       </c>
       <c r="D280" s="12" t="inlineStr">
         <is>
-          <t>ረዳት</t>
+          <t>እርስዎ</t>
         </is>
       </c>
       <c r="E280" s="13" t="inlineStr">
         <is>
-          <t>Gargaaraa</t>
+          <t>Isin</t>
         </is>
       </c>
       <c r="F280" s="12" t="inlineStr">
         <is>
-          <t>ሓጋዚ</t>
+          <t>ንስኹም</t>
         </is>
       </c>
       <c r="G280" s="13" t="inlineStr">
         <is>
-          <t>Kaaliye</t>
+          <t>Adiga</t>
         </is>
       </c>
       <c r="H280" s="13" t="inlineStr">
         <is>
-          <t>Msaidizi</t>
+          <t>Wewe</t>
         </is>
       </c>
       <c r="I280" s="14" t="inlineStr"/>
@@ -18285,7 +18285,7 @@
     <row r="281" ht="44" customHeight="1">
       <c r="A281" s="11" t="inlineStr">
         <is>
-          <t>conversation_unavailable</t>
+          <t>assistant_label</t>
         </is>
       </c>
       <c r="B281" s="11" t="inlineStr">
@@ -18295,32 +18295,32 @@
       </c>
       <c r="C281" s="11" t="inlineStr">
         <is>
-          <t>Conversation unavailable.</t>
+          <t>Assistant</t>
         </is>
       </c>
       <c r="D281" s="12" t="inlineStr">
         <is>
-          <t>ውይይቱ አይገኝም።</t>
+          <t>ረዳት</t>
         </is>
       </c>
       <c r="E281" s="13" t="inlineStr">
         <is>
-          <t>Mariin hin argamu.</t>
+          <t>Gargaaraa</t>
         </is>
       </c>
       <c r="F281" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዝርርብ ኣይርከብን።</t>
+          <t>ሓጋዚ</t>
         </is>
       </c>
       <c r="G281" s="13" t="inlineStr">
         <is>
-          <t>Wadahadalka lama heli karo.</t>
+          <t>Kaaliye</t>
         </is>
       </c>
       <c r="H281" s="13" t="inlineStr">
         <is>
-          <t>Mazungumzo hayapatikani.</t>
+          <t>Msaidizi</t>
         </is>
       </c>
       <c r="I281" s="14" t="inlineStr"/>
@@ -18328,7 +18328,7 @@
     <row r="282" ht="44" customHeight="1">
       <c r="A282" s="11" t="inlineStr">
         <is>
-          <t>unmute</t>
+          <t>conversation_unavailable</t>
         </is>
       </c>
       <c r="B282" s="11" t="inlineStr">
@@ -18338,32 +18338,32 @@
       </c>
       <c r="C282" s="11" t="inlineStr">
         <is>
-          <t>Unmute</t>
+          <t>Conversation unavailable.</t>
         </is>
       </c>
       <c r="D282" s="12" t="inlineStr">
         <is>
-          <t>ድምፅ አብራ</t>
+          <t>ውይይቱ አይገኝም።</t>
         </is>
       </c>
       <c r="E282" s="13" t="inlineStr">
         <is>
-          <t>Sagalee banaa</t>
+          <t>Mariin hin argamu.</t>
         </is>
       </c>
       <c r="F282" s="12" t="inlineStr">
         <is>
-          <t>ድምጺ ኣብርህ</t>
+          <t>እቲ ዝርርብ ኣይርከብን።</t>
         </is>
       </c>
       <c r="G282" s="13" t="inlineStr">
         <is>
-          <t>Codka fur</t>
+          <t>Wadahadalka lama heli karo.</t>
         </is>
       </c>
       <c r="H282" s="13" t="inlineStr">
         <is>
-          <t>Rudisha Sauti</t>
+          <t>Mazungumzo hayapatikani.</t>
         </is>
       </c>
       <c r="I282" s="14" t="inlineStr"/>
@@ -18371,7 +18371,7 @@
     <row r="283" ht="44" customHeight="1">
       <c r="A283" s="11" t="inlineStr">
         <is>
-          <t>session_summary_prompt</t>
+          <t>unmute</t>
         </is>
       </c>
       <c r="B283" s="11" t="inlineStr">
@@ -18381,32 +18381,32 @@
       </c>
       <c r="C283" s="11" t="inlineStr">
         <is>
-          <t>What did this session cover? (optional)</t>
+          <t>Unmute</t>
         </is>
       </c>
       <c r="D283" s="12" t="inlineStr">
         <is>
-          <t>ይህ ክፍለ-ጊዜ ምን ሸፈነ? (አማራጭ)</t>
+          <t>ድምፅ አብራ</t>
         </is>
       </c>
       <c r="E283" s="13" t="inlineStr">
         <is>
-          <t>Sessioniin kun maal haguuge? (filannoo)</t>
+          <t>Sagalee banaa</t>
         </is>
       </c>
       <c r="F283" s="12" t="inlineStr">
         <is>
-          <t>እዚ ክፍለ-ግዜ እንታይ ሸፈነ? (ኣማራጺ)</t>
+          <t>ድምጺ ኣብርህ</t>
         </is>
       </c>
       <c r="G283" s="13" t="inlineStr">
         <is>
-          <t>Kalfadhigan muxuu daboolay? (ikhtiyaari)</t>
+          <t>Codka fur</t>
         </is>
       </c>
       <c r="H283" s="13" t="inlineStr">
         <is>
-          <t>Kikao hiki kilihusu nini? (si lazima)</t>
+          <t>Rudisha Sauti</t>
         </is>
       </c>
       <c r="I283" s="14" t="inlineStr"/>
@@ -18414,7 +18414,7 @@
     <row r="284" ht="44" customHeight="1">
       <c r="A284" s="11" t="inlineStr">
         <is>
-          <t>customer_ended_call</t>
+          <t>session_summary_prompt</t>
         </is>
       </c>
       <c r="B284" s="11" t="inlineStr">
@@ -18424,32 +18424,32 @@
       </c>
       <c r="C284" s="11" t="inlineStr">
         <is>
-          <t>The customer ended the call</t>
+          <t>What did this session cover? (optional)</t>
         </is>
       </c>
       <c r="D284" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛው ጥሪውን አቋረጠ</t>
+          <t>ይህ ክፍለ-ጊዜ ምን ሸፈነ? (አማራጭ)</t>
         </is>
       </c>
       <c r="E284" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan bilbila xumure</t>
+          <t>Sessioniin kun maal haguuge? (filannoo)</t>
         </is>
       </c>
       <c r="F284" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዓሚል ነቲ ጻውዒት ወዲኡዎ</t>
+          <t>እዚ ክፍለ-ግዜ እንታይ ሸፈነ? (ኣማራጺ)</t>
         </is>
       </c>
       <c r="G284" s="13" t="inlineStr">
         <is>
-          <t>Macmiilku wicitaanka wuu joojiyay</t>
+          <t>Kalfadhigan muxuu daboolay? (ikhtiyaari)</t>
         </is>
       </c>
       <c r="H284" s="13" t="inlineStr">
         <is>
-          <t>Mteja alimaliza simu</t>
+          <t>Kikao hiki kilihusu nini? (si lazima)</t>
         </is>
       </c>
       <c r="I284" s="14" t="inlineStr"/>
@@ -18457,7 +18457,7 @@
     <row r="285" ht="44" customHeight="1">
       <c r="A285" s="11" t="inlineStr">
         <is>
-          <t>verified_scope</t>
+          <t>customer_ended_call</t>
         </is>
       </c>
       <c r="B285" s="11" t="inlineStr">
@@ -18467,32 +18467,32 @@
       </c>
       <c r="C285" s="11" t="inlineStr">
         <is>
-          <t>You can now discuss their own records, take documents and file a dispute. Never a deposit, withdrawal or transfer.</t>
+          <t>The customer ended the call</t>
         </is>
       </c>
       <c r="D285" s="12" t="inlineStr">
         <is>
-          <t>አሁን ስለ ራሳቸው መዝገቦች መወያየት፣ ሰነዶች መቀበልና ቅሬታ ማስመዝገብ ይችላሉ። በፍጹም ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም።</t>
+          <t>ደንበኛው ጥሪውን አቋረጠ</t>
         </is>
       </c>
       <c r="E285" s="13" t="inlineStr">
         <is>
-          <t>Amma waa'ee galmee isaanii mari'achuu, sanadoota fudhachuu fi komii galmeessuu dandeessu. Gonkumaa kuusaa, baasii yookiin dabarsa hin jiru.</t>
+          <t>Maamilaan bilbila xumure</t>
         </is>
       </c>
       <c r="F285" s="12" t="inlineStr">
         <is>
-          <t>ሕጂ ብዛዕባ ናቶም መዝገባት ክትዘራረቡ፣ ሰነዳት ክትቅበሉን ጥርዓን ከተመዝግቡን ትኽእሉ። ፈጺሙ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን።</t>
+          <t>እቲ ዓሚል ነቲ ጻውዒት ወዲኡዎ</t>
         </is>
       </c>
       <c r="G285" s="13" t="inlineStr">
         <is>
-          <t>Hadda waad kala hadli kartaa diiwaankooda, dukumiinti qaadan iyo cabasho diiwaangelin. Weligaa dhigasho, qaadis ama wareejin ma jirto.</t>
+          <t>Macmiilku wicitaanka wuu joojiyay</t>
         </is>
       </c>
       <c r="H285" s="13" t="inlineStr">
         <is>
-          <t>Sasa unaweza kuzungumzia rekodi zao wenyewe, kuchukua nyaraka na kuwasilisha mgogoro. Kamwe amana, uondoaji au uhamishaji.</t>
+          <t>Mteja alimaliza simu</t>
         </is>
       </c>
       <c r="I285" s="14" t="inlineStr"/>
@@ -18500,7 +18500,7 @@
     <row r="286" ht="44" customHeight="1">
       <c r="A286" s="11" t="inlineStr">
         <is>
-          <t>establish_who_they_are</t>
+          <t>verified_scope</t>
         </is>
       </c>
       <c r="B286" s="11" t="inlineStr">
@@ -18510,32 +18510,32 @@
       </c>
       <c r="C286" s="11" t="inlineStr">
         <is>
-          <t>Establish who they are — either one</t>
+          <t>You can now discuss their own records, take documents and file a dispute. Never a deposit, withdrawal or transfer.</t>
         </is>
       </c>
       <c r="D286" s="12" t="inlineStr">
         <is>
-          <t>ማንነታቸውን ያረጋግጡ — አንዱ ይበቃል</t>
+          <t>አሁን ስለ ራሳቸው መዝገቦች መወያየት፣ ሰነዶች መቀበልና ቅሬታ ማስመዝገብ ይችላሉ። በፍጹም ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም።</t>
         </is>
       </c>
       <c r="E286" s="13" t="inlineStr">
         <is>
-          <t>Eenyummaa isaanii mirkaneessaa — tokko ni ga'a</t>
+          <t>Amma waa'ee galmee isaanii mari'achuu, sanadoota fudhachuu fi komii galmeessuu dandeessu. Gonkumaa kuusaa, baasii yookiin dabarsa hin jiru.</t>
         </is>
       </c>
       <c r="F286" s="12" t="inlineStr">
         <is>
-          <t>መንነቶም ኣረጋግጹ — ሓደ እኹል እዩ</t>
+          <t>ሕጂ ብዛዕባ ናቶም መዝገባት ክትዘራረቡ፣ ሰነዳት ክትቅበሉን ጥርዓን ከተመዝግቡን ትኽእሉ። ፈጺሙ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን።</t>
         </is>
       </c>
       <c r="G286" s="13" t="inlineStr">
         <is>
-          <t>Ogow cidda ay yihiin — mid kasta</t>
+          <t>Hadda waad kala hadli kartaa diiwaankooda, dukumiinti qaadan iyo cabasho diiwaangelin. Weligaa dhigasho, qaadis ama wareejin ma jirto.</t>
         </is>
       </c>
       <c r="H286" s="13" t="inlineStr">
         <is>
-          <t>Thibitisha ni nani — mojawapo</t>
+          <t>Sasa unaweza kuzungumzia rekodi zao wenyewe, kuchukua nyaraka na kuwasilisha mgogoro. Kamwe amana, uondoaji au uhamishaji.</t>
         </is>
       </c>
       <c r="I286" s="14" t="inlineStr"/>
@@ -18543,7 +18543,7 @@
     <row r="287" ht="44" customHeight="1">
       <c r="A287" s="11" t="inlineStr">
         <is>
-          <t>chk_id_document</t>
+          <t>establish_who_they_are</t>
         </is>
       </c>
       <c r="B287" s="11" t="inlineStr">
@@ -18553,32 +18553,32 @@
       </c>
       <c r="C287" s="11" t="inlineStr">
         <is>
-          <t>Fayda ID shown and matches the account name</t>
+          <t>Establish who they are — either one</t>
         </is>
       </c>
       <c r="D287" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ መታወቂያ ታይቷል እና ከሂሳቡ ስም ጋር ይዛመዳል</t>
+          <t>ማንነታቸውን ያረጋግጡ — አንዱ ይበቃል</t>
         </is>
       </c>
       <c r="E287" s="13" t="inlineStr">
         <is>
-          <t>Waraqaan eenyummaa Fayda agarsiifame maqaa herregaa waliin walsimeera</t>
+          <t>Eenyummaa isaanii mirkaneessaa — tokko ni ga'a</t>
         </is>
       </c>
       <c r="F287" s="12" t="inlineStr">
         <is>
-          <t>መንነት ፋይዳ ተራእዩን ምስ ስም ሕሳብ ይሰማማዕን</t>
+          <t>መንነቶም ኣረጋግጹ — ሓደ እኹል እዩ</t>
         </is>
       </c>
       <c r="G287" s="13" t="inlineStr">
         <is>
-          <t>Aqoonsiga Fayda waa la tusay wuxuuna la mid yahay magaca xisaabta</t>
+          <t>Ogow cidda ay yihiin — mid kasta</t>
         </is>
       </c>
       <c r="H287" s="13" t="inlineStr">
         <is>
-          <t>Kitambulisho cha Fayda kimeonyeshwa na kinalingana na jina la akaunti</t>
+          <t>Thibitisha ni nani — mojawapo</t>
         </is>
       </c>
       <c r="I287" s="14" t="inlineStr"/>
@@ -18586,7 +18586,7 @@
     <row r="288" ht="44" customHeight="1">
       <c r="A288" s="11" t="inlineStr">
         <is>
-          <t>chk_fayda_matched</t>
+          <t>chk_id_document</t>
         </is>
       </c>
       <c r="B288" s="11" t="inlineStr">
@@ -18596,32 +18596,32 @@
       </c>
       <c r="C288" s="11" t="inlineStr">
         <is>
-          <t>Fayda number matches the account record</t>
+          <t>Fayda ID shown and matches the account name</t>
         </is>
       </c>
       <c r="D288" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ ቁጥር ከሂሳቡ መዝገብ ጋር ይዛመዳል</t>
+          <t>የፋይዳ መታወቂያ ታይቷል እና ከሂሳቡ ስም ጋር ይዛመዳል</t>
         </is>
       </c>
       <c r="E288" s="13" t="inlineStr">
         <is>
-          <t>Lakkoofsi Fayda galmee herregaa waliin walsimeera</t>
+          <t>Waraqaan eenyummaa Fayda agarsiifame maqaa herregaa waliin walsimeera</t>
         </is>
       </c>
       <c r="F288" s="12" t="inlineStr">
         <is>
-          <t>ቁጽሪ ፋይዳ ምስ መዝገብ ሕሳብ ይሰማማዕ</t>
+          <t>መንነት ፋይዳ ተራእዩን ምስ ስም ሕሳብ ይሰማማዕን</t>
         </is>
       </c>
       <c r="G288" s="13" t="inlineStr">
         <is>
-          <t>Lambarka Fayda wuxuu la mid yahay diiwaanka xisaabta</t>
+          <t>Aqoonsiga Fayda waa la tusay wuxuuna la mid yahay magaca xisaabta</t>
         </is>
       </c>
       <c r="H288" s="13" t="inlineStr">
         <is>
-          <t>Namba ya Fayda inalingana na rekodi ya akaunti</t>
+          <t>Kitambulisho cha Fayda kimeonyeshwa na kinalingana na jina la akaunti</t>
         </is>
       </c>
       <c r="I288" s="14" t="inlineStr"/>
@@ -18629,7 +18629,7 @@
     <row r="289" ht="44" customHeight="1">
       <c r="A289" s="11" t="inlineStr">
         <is>
-          <t>chk_fayda_matched_note</t>
+          <t>chk_fayda_matched</t>
         </is>
       </c>
       <c r="B289" s="11" t="inlineStr">
@@ -18639,32 +18639,32 @@
       </c>
       <c r="C289" s="11" t="inlineStr">
         <is>
-          <t>on your own screen — works on an audio call</t>
+          <t>Fayda number matches the account record</t>
         </is>
       </c>
       <c r="D289" s="12" t="inlineStr">
         <is>
-          <t>በራስዎ ስክሪን ላይ — በድምፅ ጥሪም ይሠራል</t>
+          <t>የፋይዳ ቁጥር ከሂሳቡ መዝገብ ጋር ይዛመዳል</t>
         </is>
       </c>
       <c r="E289" s="13" t="inlineStr">
         <is>
-          <t>iskiriinii keessan irratti — bilbila sagalee irrattis ni hojjeta</t>
+          <t>Lakkoofsi Fayda galmee herregaa waliin walsimeera</t>
         </is>
       </c>
       <c r="F289" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ናትኩም መርአዪ — ኣብ ናይ ድምጺ ጻውዒት እውን ይሰርሕ</t>
+          <t>ቁጽሪ ፋይዳ ምስ መዝገብ ሕሳብ ይሰማማዕ</t>
         </is>
       </c>
       <c r="G289" s="13" t="inlineStr">
         <is>
-          <t>shaashaddaada — wicitaan cod ahna wuu ka shaqeeyaa</t>
+          <t>Lambarka Fayda wuxuu la mid yahay diiwaanka xisaabta</t>
         </is>
       </c>
       <c r="H289" s="13" t="inlineStr">
         <is>
-          <t>kwenye skrini yako mwenyewe — inafanya kazi kwenye simu ya sauti</t>
+          <t>Namba ya Fayda inalingana na rekodi ya akaunti</t>
         </is>
       </c>
       <c r="I289" s="14" t="inlineStr"/>
@@ -18672,7 +18672,7 @@
     <row r="290" ht="44" customHeight="1">
       <c r="A290" s="11" t="inlineStr">
         <is>
-          <t>chk_id_photo</t>
+          <t>chk_fayda_matched_note</t>
         </is>
       </c>
       <c r="B290" s="11" t="inlineStr">
@@ -18682,32 +18682,32 @@
       </c>
       <c r="C290" s="11" t="inlineStr">
         <is>
-          <t>Photo on the ID matches the person on the call</t>
+          <t>on your own screen — works on an audio call</t>
         </is>
       </c>
       <c r="D290" s="12" t="inlineStr">
         <is>
-          <t>በመታወቂያው ላይ ያለው ፎቶ ከጥሪው ላይ ካለው ሰው ጋር ይዛመዳል</t>
+          <t>በራስዎ ስክሪን ላይ — በድምፅ ጥሪም ይሠራል</t>
         </is>
       </c>
       <c r="E290" s="13" t="inlineStr">
         <is>
-          <t>Suuraan waraqaa eenyummaa irra jiru nama bilbila irra jiru waliin walsimeera</t>
+          <t>iskiriinii keessan irratti — bilbila sagalee irrattis ni hojjeta</t>
         </is>
       </c>
       <c r="F290" s="12" t="inlineStr">
         <is>
-          <t>እቲ ኣብ መንነት ዘሎ ስእሊ ምስቲ ኣብ ጻውዒት ዘሎ ሰብ ይሰማማዕ</t>
+          <t>ኣብ ናትኩም መርአዪ — ኣብ ናይ ድምጺ ጻውዒት እውን ይሰርሕ</t>
         </is>
       </c>
       <c r="G290" s="13" t="inlineStr">
         <is>
-          <t>Sawirka aqoonsiga wuxuu la mid yahay qofka wicitaanka ku jira</t>
+          <t>shaashaddaada — wicitaan cod ahna wuu ka shaqeeyaa</t>
         </is>
       </c>
       <c r="H290" s="13" t="inlineStr">
         <is>
-          <t>Picha kwenye kitambulisho inalingana na mtu aliye kwenye simu</t>
+          <t>kwenye skrini yako mwenyewe — inafanya kazi kwenye simu ya sauti</t>
         </is>
       </c>
       <c r="I290" s="14" t="inlineStr"/>
@@ -18715,7 +18715,7 @@
     <row r="291" ht="44" customHeight="1">
       <c r="A291" s="11" t="inlineStr">
         <is>
-          <t>chk_video_only</t>
+          <t>chk_id_photo</t>
         </is>
       </c>
       <c r="B291" s="11" t="inlineStr">
@@ -18725,32 +18725,32 @@
       </c>
       <c r="C291" s="11" t="inlineStr">
         <is>
-          <t>video only</t>
+          <t>Photo on the ID matches the person on the call</t>
         </is>
       </c>
       <c r="D291" s="12" t="inlineStr">
         <is>
-          <t>ቪዲዮ ብቻ</t>
+          <t>በመታወቂያው ላይ ያለው ፎቶ ከጥሪው ላይ ካለው ሰው ጋር ይዛመዳል</t>
         </is>
       </c>
       <c r="E291" s="13" t="inlineStr">
         <is>
-          <t>viidiyoo qofa</t>
+          <t>Suuraan waraqaa eenyummaa irra jiru nama bilbila irra jiru waliin walsimeera</t>
         </is>
       </c>
       <c r="F291" s="12" t="inlineStr">
         <is>
-          <t>ቪድዮ ጥራይ</t>
+          <t>እቲ ኣብ መንነት ዘሎ ስእሊ ምስቲ ኣብ ጻውዒት ዘሎ ሰብ ይሰማማዕ</t>
         </is>
       </c>
       <c r="G291" s="13" t="inlineStr">
         <is>
-          <t>fiidyow oo kaliya</t>
+          <t>Sawirka aqoonsiga wuxuu la mid yahay qofka wicitaanka ku jira</t>
         </is>
       </c>
       <c r="H291" s="13" t="inlineStr">
         <is>
-          <t>video pekee</t>
+          <t>Picha kwenye kitambulisho inalingana na mtu aliye kwenye simu</t>
         </is>
       </c>
       <c r="I291" s="14" t="inlineStr"/>
@@ -18758,7 +18758,7 @@
     <row r="292" ht="44" customHeight="1">
       <c r="A292" s="11" t="inlineStr">
         <is>
-          <t>confirm_account_theirs</t>
+          <t>chk_video_only</t>
         </is>
       </c>
       <c r="B292" s="11" t="inlineStr">
@@ -18768,32 +18768,32 @@
       </c>
       <c r="C292" s="11" t="inlineStr">
         <is>
-          <t>And confirm the account is theirs</t>
+          <t>video only</t>
         </is>
       </c>
       <c r="D292" s="12" t="inlineStr">
         <is>
-          <t>እና ሂሳቡ የእነሱ መሆኑን ያረጋግጡ</t>
+          <t>ቪዲዮ ብቻ</t>
         </is>
       </c>
       <c r="E292" s="13" t="inlineStr">
         <is>
-          <t>Akkasumas herregni kan isaanii ta'uu mirkaneessaa</t>
+          <t>viidiyoo qofa</t>
         </is>
       </c>
       <c r="F292" s="12" t="inlineStr">
         <is>
-          <t>ከምኡ'ውን እቲ ሕሳብ ናቶም ምዃኑ ኣረጋግጹ</t>
+          <t>ቪድዮ ጥራይ</t>
         </is>
       </c>
       <c r="G292" s="13" t="inlineStr">
         <is>
-          <t>Xaqiiji in xisaabtu tahay tooda</t>
+          <t>fiidyow oo kaliya</t>
         </is>
       </c>
       <c r="H292" s="13" t="inlineStr">
         <is>
-          <t>Na thibitisha akaunti ni yao</t>
+          <t>video pekee</t>
         </is>
       </c>
       <c r="I292" s="14" t="inlineStr"/>
@@ -18801,7 +18801,7 @@
     <row r="293" ht="44" customHeight="1">
       <c r="A293" s="11" t="inlineStr">
         <is>
-          <t>confirm_identity</t>
+          <t>confirm_account_theirs</t>
         </is>
       </c>
       <c r="B293" s="11" t="inlineStr">
@@ -18811,32 +18811,32 @@
       </c>
       <c r="C293" s="11" t="inlineStr">
         <is>
-          <t>Confirm identity</t>
+          <t>And confirm the account is theirs</t>
         </is>
       </c>
       <c r="D293" s="12" t="inlineStr">
         <is>
-          <t>ማንነት አረጋግጥ</t>
+          <t>እና ሂሳቡ የእነሱ መሆኑን ያረጋግጡ</t>
         </is>
       </c>
       <c r="E293" s="13" t="inlineStr">
         <is>
-          <t>Eenyummaa mirkaneessi</t>
+          <t>Akkasumas herregni kan isaanii ta'uu mirkaneessaa</t>
         </is>
       </c>
       <c r="F293" s="12" t="inlineStr">
         <is>
-          <t>መንነት ኣረጋግጽ</t>
+          <t>ከምኡ'ውን እቲ ሕሳብ ናቶም ምዃኑ ኣረጋግጹ</t>
         </is>
       </c>
       <c r="G293" s="13" t="inlineStr">
         <is>
-          <t>Xaqiiji aqoonsiga</t>
+          <t>Xaqiiji in xisaabtu tahay tooda</t>
         </is>
       </c>
       <c r="H293" s="13" t="inlineStr">
         <is>
-          <t>Thibitisha Utambulisho</t>
+          <t>Na thibitisha akaunti ni yao</t>
         </is>
       </c>
       <c r="I293" s="14" t="inlineStr"/>
@@ -18844,7 +18844,7 @@
     <row r="294" ht="44" customHeight="1">
       <c r="A294" s="11" t="inlineStr">
         <is>
-          <t>unverified_scope</t>
+          <t>confirm_identity</t>
         </is>
       </c>
       <c r="B294" s="11" t="inlineStr">
@@ -18854,32 +18854,32 @@
       </c>
       <c r="C294" s="11" t="inlineStr">
         <is>
-          <t>Until this is done you can only give general guidance — products, eligibility and how to apply.</t>
+          <t>Confirm identity</t>
         </is>
       </c>
       <c r="D294" s="12" t="inlineStr">
         <is>
-          <t>ይህ እስኪከናወን ድረስ አጠቃላይ መመሪያ ብቻ መስጠት ይችላሉ — ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል።</t>
+          <t>ማንነት አረጋግጥ</t>
         </is>
       </c>
       <c r="E294" s="13" t="inlineStr">
         <is>
-          <t>Hanga kun raawwatutti qajeelfama waliigalaa qofa kennuu dandeessu — oomishaalee, ulaagaa fi akkaataa itti iyyatan.</t>
+          <t>Eenyummaa mirkaneessi</t>
         </is>
       </c>
       <c r="F294" s="12" t="inlineStr">
         <is>
-          <t>እዚ ክሳብ ዝፍጸም ሓፈሻዊ መምርሒ ጥራይ ክትህቡ ትኽእሉ — ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን።</t>
+          <t>መንነት ኣረጋግጽ</t>
         </is>
       </c>
       <c r="G294" s="13" t="inlineStr">
         <is>
-          <t>Ilaa tan la sameeyo waxaad kaliya bixin kartaa hagaajin guud — alaabta, u-qalmitaanka iyo sida loo codsado.</t>
+          <t>Xaqiiji aqoonsiga</t>
         </is>
       </c>
       <c r="H294" s="13" t="inlineStr">
         <is>
-          <t>Hadi hili litakapofanyika unaweza tu kutoa mwongozo wa jumla — bidhaa, sifa za kustahiki na jinsi ya kuomba.</t>
+          <t>Thibitisha Utambulisho</t>
         </is>
       </c>
       <c r="I294" s="14" t="inlineStr"/>
@@ -18887,7 +18887,7 @@
     <row r="295" ht="44" customHeight="1">
       <c r="A295" s="11" t="inlineStr">
         <is>
-          <t>fayda_number_required</t>
+          <t>unverified_scope</t>
         </is>
       </c>
       <c r="B295" s="11" t="inlineStr">
@@ -18897,32 +18897,32 @@
       </c>
       <c r="C295" s="11" t="inlineStr">
         <is>
-          <t>Fayda number (required — it is what the record keeps)</t>
+          <t>Until this is done you can only give general guidance — products, eligibility and how to apply.</t>
         </is>
       </c>
       <c r="D295" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ ቁጥር (ያስፈልጋል — መዝገቡ የሚይዘው ይህ ነው)</t>
+          <t>ይህ እስኪከናወን ድረስ አጠቃላይ መመሪያ ብቻ መስጠት ይችላሉ — ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል።</t>
         </is>
       </c>
       <c r="E295" s="13" t="inlineStr">
         <is>
-          <t>Lakkoofsa Fayda (barbaachisaa — kan galmeen qabatu isa kana)</t>
+          <t>Hanga kun raawwatutti qajeelfama waliigalaa qofa kennuu dandeessu — oomishaalee, ulaagaa fi akkaataa itti iyyatan.</t>
         </is>
       </c>
       <c r="F295" s="12" t="inlineStr">
         <is>
-          <t>ቁጽሪ ፋይዳ (የድሊ — እቲ መዝገብ ዝሕዞ እዚ እዩ)</t>
+          <t>እዚ ክሳብ ዝፍጸም ሓፈሻዊ መምርሒ ጥራይ ክትህቡ ትኽእሉ — ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን።</t>
         </is>
       </c>
       <c r="G295" s="13" t="inlineStr">
         <is>
-          <t>Lambarka Fayda (loo baahan yahay — waa waxa diiwaanku hayo)</t>
+          <t>Ilaa tan la sameeyo waxaad kaliya bixin kartaa hagaajin guud — alaabta, u-qalmitaanka iyo sida loo codsado.</t>
         </is>
       </c>
       <c r="H295" s="13" t="inlineStr">
         <is>
-          <t>Namba ya Fayda (inahitajika — ndiyo inayowekwa kwenye rekodi)</t>
+          <t>Hadi hili litakapofanyika unaweza tu kutoa mwongozo wa jumla — bidhaa, sifa za kustahiki na jinsi ya kuomba.</t>
         </is>
       </c>
       <c r="I295" s="14" t="inlineStr"/>
@@ -18930,7 +18930,7 @@
     <row r="296" ht="44" customHeight="1">
       <c r="A296" s="11" t="inlineStr">
         <is>
-          <t>download_for_translation</t>
+          <t>fayda_number_required</t>
         </is>
       </c>
       <c r="B296" s="11" t="inlineStr">
@@ -18940,32 +18940,32 @@
       </c>
       <c r="C296" s="11" t="inlineStr">
         <is>
-          <t>Download for translation</t>
+          <t>Fayda number (required — it is what the record keeps)</t>
         </is>
       </c>
       <c r="D296" s="12" t="inlineStr">
         <is>
-          <t>ለትርጉም አውርድ</t>
+          <t>የፋይዳ ቁጥር (ያስፈልጋል — መዝገቡ የሚይዘው ይህ ነው)</t>
         </is>
       </c>
       <c r="E296" s="13" t="inlineStr">
         <is>
-          <t>Hiikkaaf buufadhu</t>
+          <t>Lakkoofsa Fayda (barbaachisaa — kan galmeen qabatu isa kana)</t>
         </is>
       </c>
       <c r="F296" s="12" t="inlineStr">
         <is>
-          <t>ንትርጉም ኣውርድ</t>
+          <t>ቁጽሪ ፋይዳ (የድሊ — እቲ መዝገብ ዝሕዞ እዚ እዩ)</t>
         </is>
       </c>
       <c r="G296" s="13" t="inlineStr">
         <is>
-          <t>Soo dejiso turjumaadda</t>
+          <t>Lambarka Fayda (loo baahan yahay — waa waxa diiwaanku hayo)</t>
         </is>
       </c>
       <c r="H296" s="13" t="inlineStr">
         <is>
-          <t>Pakua kwa Tafsiri</t>
+          <t>Namba ya Fayda (inahitajika — ndiyo inayowekwa kwenye rekodi)</t>
         </is>
       </c>
       <c r="I296" s="14" t="inlineStr"/>
@@ -18973,48 +18973,91 @@
     <row r="297" ht="44" customHeight="1">
       <c r="A297" s="11" t="inlineStr">
         <is>
+          <t>download_for_translation</t>
+        </is>
+      </c>
+      <c r="B297" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C297" s="11" t="inlineStr">
+        <is>
+          <t>Download for translation</t>
+        </is>
+      </c>
+      <c r="D297" s="12" t="inlineStr">
+        <is>
+          <t>ለትርጉም አውርድ</t>
+        </is>
+      </c>
+      <c r="E297" s="13" t="inlineStr">
+        <is>
+          <t>Hiikkaaf buufadhu</t>
+        </is>
+      </c>
+      <c r="F297" s="12" t="inlineStr">
+        <is>
+          <t>ንትርጉም ኣውርድ</t>
+        </is>
+      </c>
+      <c r="G297" s="13" t="inlineStr">
+        <is>
+          <t>Soo dejiso turjumaadda</t>
+        </is>
+      </c>
+      <c r="H297" s="13" t="inlineStr">
+        <is>
+          <t>Pakua kwa Tafsiri</t>
+        </is>
+      </c>
+      <c r="I297" s="14" t="inlineStr"/>
+    </row>
+    <row r="298" ht="44" customHeight="1">
+      <c r="A298" s="11" t="inlineStr">
+        <is>
           <t>nothing_to_download</t>
         </is>
       </c>
-      <c r="B297" s="11" t="inlineStr">
-        <is>
-          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
-        </is>
-      </c>
-      <c r="C297" s="11" t="inlineStr">
+      <c r="B298" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C298" s="11" t="inlineStr">
         <is>
           <t>No approved answers to download yet.</t>
         </is>
       </c>
-      <c r="D297" s="12" t="inlineStr">
+      <c r="D298" s="12" t="inlineStr">
         <is>
           <t>እስካሁን የሚወርድ የተፈቀደ መልስ የለም።</t>
         </is>
       </c>
-      <c r="E297" s="13" t="inlineStr">
+      <c r="E298" s="13" t="inlineStr">
         <is>
           <t>Hanga ammaatti deebiin mirkanaa'e buufamu hin jiru.</t>
         </is>
       </c>
-      <c r="F297" s="12" t="inlineStr">
+      <c r="F298" s="12" t="inlineStr">
         <is>
           <t>ክሳብ ሕጂ ዝወርድ ዝጸደቐ መልሲ የለን።</t>
         </is>
       </c>
-      <c r="G297" s="13" t="inlineStr">
+      <c r="G298" s="13" t="inlineStr">
         <is>
           <t>Weli ma jiraan jawaabo la ansixiyay oo la soo dejiyo.</t>
         </is>
       </c>
-      <c r="H297" s="13" t="inlineStr">
+      <c r="H298" s="13" t="inlineStr">
         <is>
           <t>Hakuna majibu yaliyoidhinishwa ya kupakua bado.</t>
         </is>
       </c>
-      <c r="I297" s="14" t="inlineStr"/>
+      <c r="I298" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I297"/>
+  <autoFilter ref="A1:I298"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/review/Olink_Bank_Assist_language_review.xlsx
+++ b/review/Olink_Bank_Assist_language_review.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1. What the assistant says'!$A$1:$I$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2. What it understands'!$A$1:$E$91</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3. Buttons customers see'!$A$1:$I$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$I$297</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$I$306</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -752,7 +752,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>368 strings in 5 languages</t>
+          <t>377 strings in 5 languages</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I297"/>
+  <dimension ref="A1:I306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -17468,7 +17468,7 @@
     <row r="262" ht="44" customHeight="1">
       <c r="A262" s="11" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>my_desks</t>
         </is>
       </c>
       <c r="B262" s="11" t="inlineStr">
@@ -17478,32 +17478,32 @@
       </c>
       <c r="C262" s="11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>I can handle these desks:</t>
         </is>
       </c>
       <c r="D262" s="12" t="inlineStr">
         <is>
-          <t>በሂደት ላይ</t>
+          <t>እነዚህን ዴስኮች ማስተናገድ እችላለሁ፦</t>
         </is>
       </c>
       <c r="E262" s="13" t="inlineStr">
         <is>
-          <t>Adeemsa irra</t>
+          <t>Deeskiiwwan kanneen keessummeessuu nan danda'a:</t>
         </is>
       </c>
       <c r="F262" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መስርሕ</t>
+          <t>ነዞም ዴስክታት ከተኣናግድ እኽእል፦</t>
         </is>
       </c>
       <c r="G262" s="13" t="inlineStr">
         <is>
-          <t>Socda</t>
+          <t>Waxaan qaban karaa miisaskan:</t>
         </is>
       </c>
       <c r="H262" s="13" t="inlineStr">
         <is>
-          <t>Inaendelea</t>
+          <t>Ninaweza kushughulikia madawati haya:</t>
         </is>
       </c>
       <c r="I262" s="14" t="inlineStr"/>
@@ -17511,7 +17511,7 @@
     <row r="263" ht="44" customHeight="1">
       <c r="A263" s="11" t="inlineStr">
         <is>
-          <t>no_session_in_progress</t>
+          <t>desks_picked_note</t>
         </is>
       </c>
       <c r="B263" s="11" t="inlineStr">
@@ -17521,32 +17521,32 @@
       </c>
       <c r="C263" s="11" t="inlineStr">
         <is>
-          <t>No session in progress.</t>
+          <t>Questions about these desks reach you first. Everything else still reaches you — after a short wait, so nobody is stranded.</t>
         </is>
       </c>
       <c r="D263" s="12" t="inlineStr">
         <is>
-          <t>በሂደት ላይ ያለ ክፍለ-ጊዜ የለም።</t>
+          <t>ስለ እነዚህ ዴስኮች የሚነሱ ጥያቄዎች መጀመሪያ ወደ እርስዎ ይደርሳሉ። ሌላው ሁሉ አሁንም ይደርሳል — ከአጭር ጥበቃ በኋላ፤ ማንም አይቀርም።</t>
         </is>
       </c>
       <c r="E263" s="13" t="inlineStr">
         <is>
-          <t>Sessionii adeemsa irra jiru hin jiru.</t>
+          <t>Gaaffiiwwan waa'ee deeskiiwwan kanaa jalqaba isin bira ga'u. Kaan hundinuu ammas isin bira ga'a — eegumsa gabaabaa booda, namni hafu hin jiru.</t>
         </is>
       </c>
       <c r="F263" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መስርሕ ዘሎ ክፍለ-ግዜ የለን።</t>
+          <t>ብዛዕባ እዞም ዴስክታት ዝለዓሉ ሕቶታት ቅድም ናባኹም ይበጽሑ። ካልእ ኩሉ እውን ይበጽሕ — ድሕሪ ሓጺር ጽበት፣ ዋላ ሓደ ኣይተርፍን።</t>
         </is>
       </c>
       <c r="G263" s="13" t="inlineStr">
         <is>
-          <t>Ma jiro kalfadhi socda.</t>
+          <t>Su'aalaha ku saabsan miisaskan ayaa marka hore kugu soo gaara. Wax kastoo kalena wuu ku soo gaaraa — sug gaaban ka dib, sidaas qofna ma harayo.</t>
         </is>
       </c>
       <c r="H263" s="13" t="inlineStr">
         <is>
-          <t>Hakuna kikao kinachoendelea.</t>
+          <t>Maswali kuhusu madawati haya yanakufikia kwanza. Mengine yote bado yanakufikia — baada ya kusubiri kidogo, ili asibaki mtu bila msaada.</t>
         </is>
       </c>
       <c r="I263" s="14" t="inlineStr"/>
@@ -17554,7 +17554,7 @@
     <row r="264" ht="44" customHeight="1">
       <c r="A264" s="11" t="inlineStr">
         <is>
-          <t>wait_suffix</t>
+          <t>desks_none_note</t>
         </is>
       </c>
       <c r="B264" s="11" t="inlineStr">
@@ -17564,32 +17564,32 @@
       </c>
       <c r="C264" s="11" t="inlineStr">
         <is>
-          <t>wait</t>
+          <t>Nothing selected, so desk topics do not change your queue order.</t>
         </is>
       </c>
       <c r="D264" s="12" t="inlineStr">
         <is>
-          <t>ጥበቃ</t>
+          <t>ምንም አልተመረጠም፤ ስለዚህ የዴስክ ርዕሶች የወረፋዎን ቅደም ተከተል አይለውጡም።</t>
         </is>
       </c>
       <c r="E264" s="13" t="inlineStr">
         <is>
-          <t>eegumsa</t>
+          <t>Wanti filatame hin jiru, kanaafuu mata-dureewwan deeskii tartiiba sarara keessanii hin jijjiiran.</t>
         </is>
       </c>
       <c r="F264" s="12" t="inlineStr">
         <is>
-          <t>ጽበት</t>
+          <t>ዋላ ሓደ ኣይተመርጸን፣ ስለዚ ኣርእስታት ዴስክ ስርዓት ሰልፍኹም ኣይልውጡን።</t>
         </is>
       </c>
       <c r="G264" s="13" t="inlineStr">
         <is>
-          <t>sug</t>
+          <t>Waxba lama dooran, sidaas darteed mowduucyada miisasku ma beddelaan kala horreynta safkaaga.</t>
         </is>
       </c>
       <c r="H264" s="13" t="inlineStr">
         <is>
-          <t>kusubiri</t>
+          <t>Hakuna kilichochaguliwa, kwa hivyo mada za madawati hazibadilishi mpangilio wa foleni yako.</t>
         </is>
       </c>
       <c r="I264" s="14" t="inlineStr"/>
@@ -17597,7 +17597,7 @@
     <row r="265" ht="44" customHeight="1">
       <c r="A265" s="11" t="inlineStr">
         <is>
-          <t>what_session_covers</t>
+          <t>desks_first_note</t>
         </is>
       </c>
       <c r="B265" s="11" t="inlineStr">
@@ -17607,32 +17607,32 @@
       </c>
       <c r="C265" s="11" t="inlineStr">
         <is>
-          <t>What a session covers</t>
+          <t>Your desks first, longest wait within each. Anyone waiting too long moves to the top whatever they ask about.</t>
         </is>
       </c>
       <c r="D265" s="12" t="inlineStr">
         <is>
-          <t>አንድ ክፍለ-ጊዜ ምን ይሸፍናል</t>
+          <t>የእርስዎ ዴስኮች መጀመሪያ፤ በእያንዳንዱ ውስጥ ረጅም የጠበቀው ይቀድማል። ከልክ በላይ የጠበቀ ማንኛውም ሰው ስለ ምንም ይጠይቅ ወደ ላይ ይወጣል።</t>
         </is>
       </c>
       <c r="E265" s="13" t="inlineStr">
         <is>
-          <t>Sessioniin maal haguuga</t>
+          <t>Deeskiiwwan keessan jalqaba, tokkoon tokkoon isaanii keessatti kan yeroo dheeraa eege dursa. Namni baay'ee eege waan kamiyyuu haa gaafatu gara oliitti deema.</t>
         </is>
       </c>
       <c r="F265" s="12" t="inlineStr">
         <is>
-          <t>ሓደ ክፍለ-ግዜ እንታይ ይሽፍን</t>
+          <t>ዴስክታትኩም ቅድም፣ ኣብ ነፍስ ወከፍ እቲ ነዊሕ ዝጸንሐ ይቐድም። ካብ ንቡር ንላዕሊ ዝጸንሐ ዝኾነ ሰብ ብዛዕባ እንታይ ይሓትት ብዘየገድስ ናብ ላዕሊ ይመጽእ።</t>
         </is>
       </c>
       <c r="G265" s="13" t="inlineStr">
         <is>
-          <t>Waxa kalfadhigu daboolo</t>
+          <t>Miisaskaaga marka hore, kii ugu sugay dheeraa mid kasta gudahood. Qof kasta oo aad u sugay ayaa kor u kaca wax kastoo uu weydiinayoba.</t>
         </is>
       </c>
       <c r="H265" s="13" t="inlineStr">
         <is>
-          <t>Kikao Kinajumuisha Nini</t>
+          <t>Madawati yako kwanza, aliyesubiri kwa muda mrefu zaidi ndani ya kila moja. Yeyote anayesubiri kwa muda mrefu sana anapanda juu bila kujali anauliza nini.</t>
         </is>
       </c>
       <c r="I265" s="14" t="inlineStr"/>
@@ -17640,7 +17640,7 @@
     <row r="266" ht="44" customHeight="1">
       <c r="A266" s="11" t="inlineStr">
         <is>
-          <t>session_scope_body</t>
+          <t>routing_first_note</t>
         </is>
       </c>
       <c r="B266" s="11" t="inlineStr">
@@ -17650,32 +17650,32 @@
       </c>
       <c r="C266" s="11" t="inlineStr">
         <is>
-          <t>Before someone is identified: general questions about products, eligibility and how to apply. Once you have checked their Fayda ID against the account and asked something only the account holder could answer: their own application, documents and disputes.</t>
+          <t>Your languages first, your desks within them, longest wait within each. Anyone waiting too long moves to the top.</t>
         </is>
       </c>
       <c r="D266" s="12" t="inlineStr">
         <is>
-          <t>አንድ ሰው ከመለየቱ በፊት፦ ስለ ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል አጠቃላይ ጥያቄዎች። የፋይዳ መታወቂያቸውን ከሂሳቡ ጋር አመሳክረው የሂሳቡ ባለቤት ብቻ ሊመልሰው የሚችለውን ከጠየቁ በኋላ፦ የራሳቸው ማመልከቻ፣ ሰነዶችና ቅሬታዎች።</t>
+          <t>የእርስዎ ቋንቋዎች መጀመሪያ፣ በውስጣቸው የእርስዎ ዴስኮች፣ በእያንዳንዱ ውስጥ ረጅም የጠበቀው ይቀድማል። ከልክ በላይ የጠበቀ ወደ ላይ ይወጣል።</t>
         </is>
       </c>
       <c r="E266" s="13" t="inlineStr">
         <is>
-          <t>Namni tokko utuu hin beekamin dura: gaaffii waliigalaa waa'ee oomishaalee, ulaagaa fi akkaataa itti iyyatan. Erga waraqaa eenyummaa Fayda isaanii herrega waliin madaalchiftanii waan abbaan herregaa qofti deebisuu danda'u gaafattanii booda: iyyannoo, sanadoota fi komii isaanii.</t>
+          <t>Afaanonni keessan jalqaba, isaan keessatti deeskiiwwan keessan, tokkoon tokkoon keessatti kan yeroo dheeraa eege dursa. Namni baay'ee eege gara oliitti deema.</t>
         </is>
       </c>
       <c r="F266" s="12" t="inlineStr">
         <is>
-          <t>ሓደ ሰብ ቅድሚ ምልላዩ፦ ብዛዕባ ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን ሓፈሻዊ ሕቶታት። መንነት ፋይዳኦም ምስ ሕሳብ ኣረጋጊጽኩም እቲ ወናኒ ሕሳብ ጥራይ ክምልሶ ዝኽእል ምስ ሓተትኩም፦ ናቶም ምልክታ፣ ሰነዳትን ጥርዓናትን።</t>
+          <t>ቋንቋታትኩም ቅድም፣ ኣብ ውሽጦም ዴስክታትኩም፣ ኣብ ነፍስ ወከፍ እቲ ነዊሕ ዝጸንሐ ይቐድም። ካብ ንቡር ንላዕሊ ዝጸንሐ ናብ ላዕሊ ይመጽእ።</t>
         </is>
       </c>
       <c r="G266" s="13" t="inlineStr">
         <is>
-          <t>Ka hor inta aan qofka la aqoonsan: su'aalo guud oo ku saabsan alaabta, u-qalmitaanka iyo sida loo codsado. Marka aad hubiso aqoonsigooda Fayda ee xisaabta oo aad weydiiso wax uu kaliya milkiilaha xisaabtu ka jawaabi karo: codsigooda, dukumiintiyada iyo cabashooyinka.</t>
+          <t>Luqadahaaga marka hore, miisaskaaga gudahood, kii ugu sugay dheeraa mid kasta gudahood. Qof aad u sugay ayaa kor u kaca.</t>
         </is>
       </c>
       <c r="H266" s="13" t="inlineStr">
         <is>
-          <t>Kabla mtu hajatambuliwa: maswali ya jumla kuhusu bidhaa, sifa za kustahiki na jinsi ya kuomba. Baada ya kukagua Kitambulisho chao cha Fayda dhidi ya akaunti na kuuliza kitu ambacho mmiliki wa akaunti pekee angeweza kujibu: maombi yao wenyewe, nyaraka na migogoro.</t>
+          <t>Lugha zako kwanza, madawati yako ndani yake, aliyesubiri kwa muda mrefu zaidi ndani ya kila moja. Anayesubiri kwa muda mrefu sana anapanda juu.</t>
         </is>
       </c>
       <c r="I266" s="14" t="inlineStr"/>
@@ -17683,7 +17683,7 @@
     <row r="267" ht="44" customHeight="1">
       <c r="A267" s="11" t="inlineStr">
         <is>
-          <t>never_money_movement</t>
+          <t>not_your_desk</t>
         </is>
       </c>
       <c r="B267" s="11" t="inlineStr">
@@ -17693,32 +17693,32 @@
       </c>
       <c r="C267" s="11" t="inlineStr">
         <is>
-          <t>Never, at any point and for anyone: deposits, withdrawals or transfers. Those do not happen on a call.</t>
+          <t>outside your desks</t>
         </is>
       </c>
       <c r="D267" s="12" t="inlineStr">
         <is>
-          <t>በፍጹም፣ በማንኛውም ጊዜና ለማንም፦ ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም። እነዚያ በጥሪ ላይ አይፈጸሙም።</t>
+          <t>ከእርስዎ ዴስኮች ውጭ</t>
         </is>
       </c>
       <c r="E267" s="13" t="inlineStr">
         <is>
-          <t>Gonkumaa, yeroo kamiyyuu fi eenyuufiyyuu: kuusaa, baasii yookiin dabarsa hin jiru. Isaan sun bilbila irratti hin raawwataman.</t>
+          <t>deeskiiwwan keessanii ala</t>
         </is>
       </c>
       <c r="F267" s="12" t="inlineStr">
         <is>
-          <t>ፈጺሙ፣ ኣብ ዝኾነ እዋንን ንዝኾነ ሰብን፦ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን። እዚኣቶም ኣብ ጻውዒት ኣይፍጸሙን።</t>
+          <t>ካብ ዴስክታትኩም ወጻኢ</t>
         </is>
       </c>
       <c r="G267" s="13" t="inlineStr">
         <is>
-          <t>Weligaa, wakhti kasta iyo qof kasta: dhigasho, qaadis ama wareejin ma jirto. Kuwaas wicitaan laguma sameeyo.</t>
+          <t>ka baxsan miisaskaaga</t>
         </is>
       </c>
       <c r="H267" s="13" t="inlineStr">
         <is>
-          <t>Kamwe, wakati wowote na kwa yeyote: amana, uondoaji au uhamishaji. Hizo hazifanyiki kwenye simu.</t>
+          <t>nje ya madawati yako</t>
         </is>
       </c>
       <c r="I267" s="14" t="inlineStr"/>
@@ -17726,7 +17726,7 @@
     <row r="268" ht="44" customHeight="1">
       <c r="A268" s="11" t="inlineStr">
         <is>
-          <t>open_escalation_queue</t>
+          <t>desks_updated</t>
         </is>
       </c>
       <c r="B268" s="11" t="inlineStr">
@@ -17736,32 +17736,32 @@
       </c>
       <c r="C268" s="11" t="inlineStr">
         <is>
-          <t>Open the escalation queue</t>
+          <t>Desks updated</t>
         </is>
       </c>
       <c r="D268" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ወረፋውን ክፈት</t>
+          <t>ዴስኮች ተዘምነዋል</t>
         </is>
       </c>
       <c r="E268" s="13" t="inlineStr">
         <is>
-          <t>Sararaa dabarsaa banaa</t>
+          <t>Deeskiiwwan haaromfaman</t>
         </is>
       </c>
       <c r="F268" s="12" t="inlineStr">
         <is>
-          <t>ሪጋ ምትሕልላፍ ክፈት</t>
+          <t>ዴስክታት ተሓዲሶም</t>
         </is>
       </c>
       <c r="G268" s="13" t="inlineStr">
         <is>
-          <t>Fur safka gudbinta</t>
+          <t>Miisaska waa la cusbooneysiiyay</t>
         </is>
       </c>
       <c r="H268" s="13" t="inlineStr">
         <is>
-          <t>Fungua Foleni ya Masuala Yaliyoelekezwa</t>
+          <t>Madawati yamesasishwa</t>
         </is>
       </c>
       <c r="I268" s="14" t="inlineStr"/>
@@ -17769,7 +17769,7 @@
     <row r="269" ht="44" customHeight="1">
       <c r="A269" s="11" t="inlineStr">
         <is>
-          <t>open_live_queue</t>
+          <t>coverage</t>
         </is>
       </c>
       <c r="B269" s="11" t="inlineStr">
@@ -17779,32 +17779,32 @@
       </c>
       <c r="C269" s="11" t="inlineStr">
         <is>
-          <t>Open the live call queue</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="D269" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታ የጥሪ ወረፋውን ክፈት</t>
+          <t>ሽፋን</t>
         </is>
       </c>
       <c r="E269" s="13" t="inlineStr">
         <is>
-          <t>Sarara bilbilaa kallattii banaa</t>
+          <t>Haguuggii</t>
         </is>
       </c>
       <c r="F269" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታዊ ናይ ጻውዒት ሰልፊ ክፈት</t>
+          <t>ሽፋን</t>
         </is>
       </c>
       <c r="G269" s="13" t="inlineStr">
         <is>
-          <t>Fur safka wicitaanka tooska ah</t>
+          <t>Daboolid</t>
         </is>
       </c>
       <c r="H269" s="13" t="inlineStr">
         <is>
-          <t>Fungua foleni ya simu za moja kwa moja</t>
+          <t>Uwezo</t>
         </is>
       </c>
       <c r="I269" s="14" t="inlineStr"/>
@@ -17812,7 +17812,7 @@
     <row r="270" ht="44" customHeight="1">
       <c r="A270" s="11" t="inlineStr">
         <is>
-          <t>live_waiting_one</t>
+          <t>coverage_everything</t>
         </is>
       </c>
       <c r="B270" s="11" t="inlineStr">
@@ -17822,32 +17822,32 @@
       </c>
       <c r="C270" s="11" t="inlineStr">
         <is>
-          <t>{n} customer waiting for a live call</t>
+          <t>everything — nothing declared</t>
         </is>
       </c>
       <c r="D270" s="12" t="inlineStr">
         <is>
-          <t>{n} ደንበኛ ቀጥታ ጥሪ በመጠበቅ ላይ ነው</t>
+          <t>ሁሉም — ምንም አልተገለጸም</t>
         </is>
       </c>
       <c r="E270" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan {n} bilbila kallattii eegaa jira</t>
+          <t>hunda — wanti labsame hin jiru</t>
         </is>
       </c>
       <c r="F270" s="12" t="inlineStr">
         <is>
-          <t>{n} ዓሚል ቀጥታዊ ጻውዒት ይጽበ ኣሎ</t>
+          <t>ኩሉ — ዋላ ሓደ ኣይተገልጸን</t>
         </is>
       </c>
       <c r="G270" s="13" t="inlineStr">
         <is>
-          <t>{n} macmiil ayaa sugaya wicitaan toos ah</t>
+          <t>wax walba — waxba lama sheegin</t>
         </is>
       </c>
       <c r="H270" s="13" t="inlineStr">
         <is>
-          <t>Mteja {n} anasubiri simu ya moja kwa moja</t>
+          <t>yote — hakuna kilichotangazwa</t>
         </is>
       </c>
       <c r="I270" s="14" t="inlineStr"/>
@@ -17855,7 +17855,7 @@
     <row r="271" ht="44" customHeight="1">
       <c r="A271" s="11" t="inlineStr">
         <is>
-          <t>live_waiting_many</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="B271" s="11" t="inlineStr">
@@ -17865,32 +17865,32 @@
       </c>
       <c r="C271" s="11" t="inlineStr">
         <is>
-          <t>{n} customers waiting for a live call</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="D271" s="12" t="inlineStr">
         <is>
-          <t>{n} ደንበኞች ቀጥታ ጥሪ በመጠበቅ ላይ ናቸው</t>
+          <t>በሂደት ላይ</t>
         </is>
       </c>
       <c r="E271" s="13" t="inlineStr">
         <is>
-          <t>Maamiltoonni {n} bilbila kallattii eegaa jiru</t>
+          <t>Adeemsa irra</t>
         </is>
       </c>
       <c r="F271" s="12" t="inlineStr">
         <is>
-          <t>{n} ዓማዊል ቀጥታዊ ጻውዒት ይጽበዩ ኣለዉ</t>
+          <t>ኣብ መስርሕ</t>
         </is>
       </c>
       <c r="G271" s="13" t="inlineStr">
         <is>
-          <t>{n} macaamiil ayaa sugaya wicitaan toos ah</t>
+          <t>Socda</t>
         </is>
       </c>
       <c r="H271" s="13" t="inlineStr">
         <is>
-          <t>Wateja {n} wanasubiri simu ya moja kwa moja</t>
+          <t>Inaendelea</t>
         </is>
       </c>
       <c r="I271" s="14" t="inlineStr"/>
@@ -17898,7 +17898,7 @@
     <row r="272" ht="44" customHeight="1">
       <c r="A272" s="11" t="inlineStr">
         <is>
-          <t>switch_dark_light</t>
+          <t>no_session_in_progress</t>
         </is>
       </c>
       <c r="B272" s="11" t="inlineStr">
@@ -17908,32 +17908,32 @@
       </c>
       <c r="C272" s="11" t="inlineStr">
         <is>
-          <t>Switch between dark and light</t>
+          <t>No session in progress.</t>
         </is>
       </c>
       <c r="D272" s="12" t="inlineStr">
         <is>
-          <t>በጨለማና በብርሃን መካከል ቀይር</t>
+          <t>በሂደት ላይ ያለ ክፍለ-ጊዜ የለም።</t>
         </is>
       </c>
       <c r="E272" s="13" t="inlineStr">
         <is>
-          <t>Dukkanaa fi ifa gidduu jijjiiri</t>
+          <t>Sessionii adeemsa irra jiru hin jiru.</t>
         </is>
       </c>
       <c r="F272" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መንጎ ጸላምን ብርሃንን ቀይር</t>
+          <t>ኣብ መስርሕ ዘሎ ክፍለ-ግዜ የለን።</t>
         </is>
       </c>
       <c r="G272" s="13" t="inlineStr">
         <is>
-          <t>U beddel mugdiga iyo iftiinka</t>
+          <t>Ma jiro kalfadhi socda.</t>
         </is>
       </c>
       <c r="H272" s="13" t="inlineStr">
         <is>
-          <t>Badilisha Kati ya Giza na Mwanga</t>
+          <t>Hakuna kikao kinachoendelea.</t>
         </is>
       </c>
       <c r="I272" s="14" t="inlineStr"/>
@@ -17941,7 +17941,7 @@
     <row r="273" ht="44" customHeight="1">
       <c r="A273" s="11" t="inlineStr">
         <is>
-          <t>live_session</t>
+          <t>wait_suffix</t>
         </is>
       </c>
       <c r="B273" s="11" t="inlineStr">
@@ -17951,32 +17951,32 @@
       </c>
       <c r="C273" s="11" t="inlineStr">
         <is>
-          <t>Live session</t>
+          <t>wait</t>
         </is>
       </c>
       <c r="D273" s="12" t="inlineStr">
         <is>
-          <t>የቀጥታ ክፍለ-ጊዜ</t>
+          <t>ጥበቃ</t>
         </is>
       </c>
       <c r="E273" s="13" t="inlineStr">
         <is>
-          <t>Session kallattii</t>
+          <t>eegumsa</t>
         </is>
       </c>
       <c r="F273" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታ ክፍለ-ግዜ</t>
+          <t>ጽበት</t>
         </is>
       </c>
       <c r="G273" s="13" t="inlineStr">
         <is>
-          <t>Kalfadhi toos ah</t>
+          <t>sug</t>
         </is>
       </c>
       <c r="H273" s="13" t="inlineStr">
         <is>
-          <t>Kikao cha Moja kwa Moja</t>
+          <t>kusubiri</t>
         </is>
       </c>
       <c r="I273" s="14" t="inlineStr"/>
@@ -17984,7 +17984,7 @@
     <row r="274" ht="44" customHeight="1">
       <c r="A274" s="11" t="inlineStr">
         <is>
-          <t>customer_left_call</t>
+          <t>what_session_covers</t>
         </is>
       </c>
       <c r="B274" s="11" t="inlineStr">
@@ -17994,32 +17994,32 @@
       </c>
       <c r="C274" s="11" t="inlineStr">
         <is>
-          <t>The customer has left the call.</t>
+          <t>What a session covers</t>
         </is>
       </c>
       <c r="D274" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛው ጥሪውን ለቅቋል።</t>
+          <t>አንድ ክፍለ-ጊዜ ምን ይሸፍናል</t>
         </is>
       </c>
       <c r="E274" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan bilbila irraa ba'eera.</t>
+          <t>Sessioniin maal haguuga</t>
         </is>
       </c>
       <c r="F274" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዓሚል ካብቲ ጻውዒት ወጺኡ።</t>
+          <t>ሓደ ክፍለ-ግዜ እንታይ ይሽፍን</t>
         </is>
       </c>
       <c r="G274" s="13" t="inlineStr">
         <is>
-          <t>Macmiilku wicitaanka wuu ka baxay.</t>
+          <t>Waxa kalfadhigu daboolo</t>
         </is>
       </c>
       <c r="H274" s="13" t="inlineStr">
         <is>
-          <t>Mteja ameondoka kwenye simu.</t>
+          <t>Kikao Kinajumuisha Nini</t>
         </is>
       </c>
       <c r="I274" s="14" t="inlineStr"/>
@@ -18027,7 +18027,7 @@
     <row r="275" ht="44" customHeight="1">
       <c r="A275" s="11" t="inlineStr">
         <is>
-          <t>waiting_for_customer</t>
+          <t>session_scope_body</t>
         </is>
       </c>
       <c r="B275" s="11" t="inlineStr">
@@ -18037,32 +18037,32 @@
       </c>
       <c r="C275" s="11" t="inlineStr">
         <is>
-          <t>Waiting for the customer…</t>
+          <t>Before someone is identified: general questions about products, eligibility and how to apply. Once you have checked their Fayda ID against the account and asked something only the account holder could answer: their own application, documents and disputes.</t>
         </is>
       </c>
       <c r="D275" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛውን በመጠበቅ ላይ…</t>
+          <t>አንድ ሰው ከመለየቱ በፊት፦ ስለ ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል አጠቃላይ ጥያቄዎች። የፋይዳ መታወቂያቸውን ከሂሳቡ ጋር አመሳክረው የሂሳቡ ባለቤት ብቻ ሊመልሰው የሚችለውን ከጠየቁ በኋላ፦ የራሳቸው ማመልከቻ፣ ሰነዶችና ቅሬታዎች።</t>
         </is>
       </c>
       <c r="E275" s="13" t="inlineStr">
         <is>
-          <t>Maamilaa eegaa jirra…</t>
+          <t>Namni tokko utuu hin beekamin dura: gaaffii waliigalaa waa'ee oomishaalee, ulaagaa fi akkaataa itti iyyatan. Erga waraqaa eenyummaa Fayda isaanii herrega waliin madaalchiftanii waan abbaan herregaa qofti deebisuu danda'u gaafattanii booda: iyyannoo, sanadoota fi komii isaanii.</t>
         </is>
       </c>
       <c r="F275" s="12" t="inlineStr">
         <is>
-          <t>ነቲ ዓሚል ንጽበ ኣለና…</t>
+          <t>ሓደ ሰብ ቅድሚ ምልላዩ፦ ብዛዕባ ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን ሓፈሻዊ ሕቶታት። መንነት ፋይዳኦም ምስ ሕሳብ ኣረጋጊጽኩም እቲ ወናኒ ሕሳብ ጥራይ ክምልሶ ዝኽእል ምስ ሓተትኩም፦ ናቶም ምልክታ፣ ሰነዳትን ጥርዓናትን።</t>
         </is>
       </c>
       <c r="G275" s="13" t="inlineStr">
         <is>
-          <t>Macmiilka la sugayo…</t>
+          <t>Ka hor inta aan qofka la aqoonsan: su'aalo guud oo ku saabsan alaabta, u-qalmitaanka iyo sida loo codsado. Marka aad hubiso aqoonsigooda Fayda ee xisaabta oo aad weydiiso wax uu kaliya milkiilaha xisaabtu ka jawaabi karo: codsigooda, dukumiintiyada iyo cabashooyinka.</t>
         </is>
       </c>
       <c r="H275" s="13" t="inlineStr">
         <is>
-          <t>Inasubiri Mteja…</t>
+          <t>Kabla mtu hajatambuliwa: maswali ya jumla kuhusu bidhaa, sifa za kustahiki na jinsi ya kuomba. Baada ya kukagua Kitambulisho chao cha Fayda dhidi ya akaunti na kuuliza kitu ambacho mmiliki wa akaunti pekee angeweza kujibu: maombi yao wenyewe, nyaraka na migogoro.</t>
         </is>
       </c>
       <c r="I275" s="14" t="inlineStr"/>
@@ -18070,7 +18070,7 @@
     <row r="276" ht="44" customHeight="1">
       <c r="A276" s="11" t="inlineStr">
         <is>
-          <t>mic_blocked</t>
+          <t>never_money_movement</t>
         </is>
       </c>
       <c r="B276" s="11" t="inlineStr">
@@ -18080,32 +18080,32 @@
       </c>
       <c r="C276" s="11" t="inlineStr">
         <is>
-          <t>Microphone access is blocked. Allow it in your browser and take the session again.</t>
+          <t>Never, at any point and for anyone: deposits, withdrawals or transfers. Those do not happen on a call.</t>
         </is>
       </c>
       <c r="D276" s="12" t="inlineStr">
         <is>
-          <t>የማይክሮፎን መዳረሻ ታግዷል። በአሳሽዎ ውስጥ ይፍቀዱና ክፍለ-ጊዜውን እንደገና ይውሰዱ።</t>
+          <t>በፍጹም፣ በማንኛውም ጊዜና ለማንም፦ ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም። እነዚያ በጥሪ ላይ አይፈጸሙም።</t>
         </is>
       </c>
       <c r="E276" s="13" t="inlineStr">
         <is>
-          <t>Maayikiroofoonii dhorkameera. Biraawzarii keessan keessatti hayyamaatii session irra deebi'aa fudhadhaa.</t>
+          <t>Gonkumaa, yeroo kamiyyuu fi eenyuufiyyuu: kuusaa, baasii yookiin dabarsa hin jiru. Isaan sun bilbila irratti hin raawwataman.</t>
         </is>
       </c>
       <c r="F276" s="12" t="inlineStr">
         <is>
-          <t>መእተዊ ማይክሮፎን ተዓጊቱ። ኣብ መርበብ መንሸራተቲኹም ፍቐዱ እሞ ነቲ ክፍለ-ግዜ ደጊምኩም ውሰዱ።</t>
+          <t>ፈጺሙ፣ ኣብ ዝኾነ እዋንን ንዝኾነ ሰብን፦ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን። እዚኣቶም ኣብ ጻውዒት ኣይፍጸሙን።</t>
         </is>
       </c>
       <c r="G276" s="13" t="inlineStr">
         <is>
-          <t>Makarafoonka waa la xannibay. Browser-kaaga ka ogolow oo kalfadhiga mar kale qaado.</t>
+          <t>Weligaa, wakhti kasta iyo qof kasta: dhigasho, qaadis ama wareejin ma jirto. Kuwaas wicitaan laguma sameeyo.</t>
         </is>
       </c>
       <c r="H276" s="13" t="inlineStr">
         <is>
-          <t>Ufikiaji wa maikrofoni umezuiwa. Ruhusu kwenye kivinjari chako na uanze kikao tena.</t>
+          <t>Kamwe, wakati wowote na kwa yeyote: amana, uondoaji au uhamishaji. Hizo hazifanyiki kwenye simu.</t>
         </is>
       </c>
       <c r="I276" s="14" t="inlineStr"/>
@@ -18113,7 +18113,7 @@
     <row r="277" ht="44" customHeight="1">
       <c r="A277" s="11" t="inlineStr">
         <is>
-          <t>unknown_error</t>
+          <t>open_escalation_queue</t>
         </is>
       </c>
       <c r="B277" s="11" t="inlineStr">
@@ -18123,32 +18123,32 @@
       </c>
       <c r="C277" s="11" t="inlineStr">
         <is>
-          <t>unknown error</t>
+          <t>Open the escalation queue</t>
         </is>
       </c>
       <c r="D277" s="12" t="inlineStr">
         <is>
-          <t>ያልታወቀ ስህተት</t>
+          <t>የማሸጋገሪያ ወረፋውን ክፈት</t>
         </is>
       </c>
       <c r="E277" s="13" t="inlineStr">
         <is>
-          <t>dogoggora hin beekamne</t>
+          <t>Sararaa dabarsaa banaa</t>
         </is>
       </c>
       <c r="F277" s="12" t="inlineStr">
         <is>
-          <t>ዘይተፈልጠ ጌጋ</t>
+          <t>ሪጋ ምትሕልላፍ ክፈት</t>
         </is>
       </c>
       <c r="G277" s="13" t="inlineStr">
         <is>
-          <t>khalad aan la garanayn</t>
+          <t>Fur safka gudbinta</t>
         </is>
       </c>
       <c r="H277" s="13" t="inlineStr">
         <is>
-          <t>hitilafu isiyojulikana</t>
+          <t>Fungua Foleni ya Masuala Yaliyoelekezwa</t>
         </is>
       </c>
       <c r="I277" s="14" t="inlineStr"/>
@@ -18156,7 +18156,7 @@
     <row r="278" ht="44" customHeight="1">
       <c r="A278" s="11" t="inlineStr">
         <is>
-          <t>no_messages_yet</t>
+          <t>open_live_queue</t>
         </is>
       </c>
       <c r="B278" s="11" t="inlineStr">
@@ -18166,32 +18166,32 @@
       </c>
       <c r="C278" s="11" t="inlineStr">
         <is>
-          <t>No messages yet.</t>
+          <t>Open the live call queue</t>
         </is>
       </c>
       <c r="D278" s="12" t="inlineStr">
         <is>
-          <t>እስካሁን መልእክት የለም።</t>
+          <t>ቀጥታ የጥሪ ወረፋውን ክፈት</t>
         </is>
       </c>
       <c r="E278" s="13" t="inlineStr">
         <is>
-          <t>Ammaaf ergaan hin jiru.</t>
+          <t>Sarara bilbilaa kallattii banaa</t>
         </is>
       </c>
       <c r="F278" s="12" t="inlineStr">
         <is>
-          <t>ክሳብ ሕጂ መልእኽቲ የለን።</t>
+          <t>ቀጥታዊ ናይ ጻውዒት ሰልፊ ክፈት</t>
         </is>
       </c>
       <c r="G278" s="13" t="inlineStr">
         <is>
-          <t>Weli fariimo ma jiraan.</t>
+          <t>Fur safka wicitaanka tooska ah</t>
         </is>
       </c>
       <c r="H278" s="13" t="inlineStr">
         <is>
-          <t>Hakuna ujumbe bado.</t>
+          <t>Fungua foleni ya simu za moja kwa moja</t>
         </is>
       </c>
       <c r="I278" s="14" t="inlineStr"/>
@@ -18199,7 +18199,7 @@
     <row r="279" ht="44" customHeight="1">
       <c r="A279" s="11" t="inlineStr">
         <is>
-          <t>you_label</t>
+          <t>live_waiting_one</t>
         </is>
       </c>
       <c r="B279" s="11" t="inlineStr">
@@ -18209,32 +18209,32 @@
       </c>
       <c r="C279" s="11" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>{n} customer waiting for a live call</t>
         </is>
       </c>
       <c r="D279" s="12" t="inlineStr">
         <is>
-          <t>እርስዎ</t>
+          <t>{n} ደንበኛ ቀጥታ ጥሪ በመጠበቅ ላይ ነው</t>
         </is>
       </c>
       <c r="E279" s="13" t="inlineStr">
         <is>
-          <t>Isin</t>
+          <t>Maamilaan {n} bilbila kallattii eegaa jira</t>
         </is>
       </c>
       <c r="F279" s="12" t="inlineStr">
         <is>
-          <t>ንስኹም</t>
+          <t>{n} ዓሚል ቀጥታዊ ጻውዒት ይጽበ ኣሎ</t>
         </is>
       </c>
       <c r="G279" s="13" t="inlineStr">
         <is>
-          <t>Adiga</t>
+          <t>{n} macmiil ayaa sugaya wicitaan toos ah</t>
         </is>
       </c>
       <c r="H279" s="13" t="inlineStr">
         <is>
-          <t>Wewe</t>
+          <t>Mteja {n} anasubiri simu ya moja kwa moja</t>
         </is>
       </c>
       <c r="I279" s="14" t="inlineStr"/>
@@ -18242,7 +18242,7 @@
     <row r="280" ht="44" customHeight="1">
       <c r="A280" s="11" t="inlineStr">
         <is>
-          <t>assistant_label</t>
+          <t>live_waiting_many</t>
         </is>
       </c>
       <c r="B280" s="11" t="inlineStr">
@@ -18252,32 +18252,32 @@
       </c>
       <c r="C280" s="11" t="inlineStr">
         <is>
-          <t>Assistant</t>
+          <t>{n} customers waiting for a live call</t>
         </is>
       </c>
       <c r="D280" s="12" t="inlineStr">
         <is>
-          <t>ረዳት</t>
+          <t>{n} ደንበኞች ቀጥታ ጥሪ በመጠበቅ ላይ ናቸው</t>
         </is>
       </c>
       <c r="E280" s="13" t="inlineStr">
         <is>
-          <t>Gargaaraa</t>
+          <t>Maamiltoonni {n} bilbila kallattii eegaa jiru</t>
         </is>
       </c>
       <c r="F280" s="12" t="inlineStr">
         <is>
-          <t>ሓጋዚ</t>
+          <t>{n} ዓማዊል ቀጥታዊ ጻውዒት ይጽበዩ ኣለዉ</t>
         </is>
       </c>
       <c r="G280" s="13" t="inlineStr">
         <is>
-          <t>Kaaliye</t>
+          <t>{n} macaamiil ayaa sugaya wicitaan toos ah</t>
         </is>
       </c>
       <c r="H280" s="13" t="inlineStr">
         <is>
-          <t>Msaidizi</t>
+          <t>Wateja {n} wanasubiri simu ya moja kwa moja</t>
         </is>
       </c>
       <c r="I280" s="14" t="inlineStr"/>
@@ -18285,7 +18285,7 @@
     <row r="281" ht="44" customHeight="1">
       <c r="A281" s="11" t="inlineStr">
         <is>
-          <t>conversation_unavailable</t>
+          <t>switch_dark_light</t>
         </is>
       </c>
       <c r="B281" s="11" t="inlineStr">
@@ -18295,32 +18295,32 @@
       </c>
       <c r="C281" s="11" t="inlineStr">
         <is>
-          <t>Conversation unavailable.</t>
+          <t>Switch between dark and light</t>
         </is>
       </c>
       <c r="D281" s="12" t="inlineStr">
         <is>
-          <t>ውይይቱ አይገኝም።</t>
+          <t>በጨለማና በብርሃን መካከል ቀይር</t>
         </is>
       </c>
       <c r="E281" s="13" t="inlineStr">
         <is>
-          <t>Mariin hin argamu.</t>
+          <t>Dukkanaa fi ifa gidduu jijjiiri</t>
         </is>
       </c>
       <c r="F281" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዝርርብ ኣይርከብን።</t>
+          <t>ኣብ መንጎ ጸላምን ብርሃንን ቀይር</t>
         </is>
       </c>
       <c r="G281" s="13" t="inlineStr">
         <is>
-          <t>Wadahadalka lama heli karo.</t>
+          <t>U beddel mugdiga iyo iftiinka</t>
         </is>
       </c>
       <c r="H281" s="13" t="inlineStr">
         <is>
-          <t>Mazungumzo hayapatikani.</t>
+          <t>Badilisha Kati ya Giza na Mwanga</t>
         </is>
       </c>
       <c r="I281" s="14" t="inlineStr"/>
@@ -18328,7 +18328,7 @@
     <row r="282" ht="44" customHeight="1">
       <c r="A282" s="11" t="inlineStr">
         <is>
-          <t>unmute</t>
+          <t>live_session</t>
         </is>
       </c>
       <c r="B282" s="11" t="inlineStr">
@@ -18338,32 +18338,32 @@
       </c>
       <c r="C282" s="11" t="inlineStr">
         <is>
-          <t>Unmute</t>
+          <t>Live session</t>
         </is>
       </c>
       <c r="D282" s="12" t="inlineStr">
         <is>
-          <t>ድምፅ አብራ</t>
+          <t>የቀጥታ ክፍለ-ጊዜ</t>
         </is>
       </c>
       <c r="E282" s="13" t="inlineStr">
         <is>
-          <t>Sagalee banaa</t>
+          <t>Session kallattii</t>
         </is>
       </c>
       <c r="F282" s="12" t="inlineStr">
         <is>
-          <t>ድምጺ ኣብርህ</t>
+          <t>ቀጥታ ክፍለ-ግዜ</t>
         </is>
       </c>
       <c r="G282" s="13" t="inlineStr">
         <is>
-          <t>Codka fur</t>
+          <t>Kalfadhi toos ah</t>
         </is>
       </c>
       <c r="H282" s="13" t="inlineStr">
         <is>
-          <t>Rudisha Sauti</t>
+          <t>Kikao cha Moja kwa Moja</t>
         </is>
       </c>
       <c r="I282" s="14" t="inlineStr"/>
@@ -18371,7 +18371,7 @@
     <row r="283" ht="44" customHeight="1">
       <c r="A283" s="11" t="inlineStr">
         <is>
-          <t>session_summary_prompt</t>
+          <t>customer_left_call</t>
         </is>
       </c>
       <c r="B283" s="11" t="inlineStr">
@@ -18381,32 +18381,32 @@
       </c>
       <c r="C283" s="11" t="inlineStr">
         <is>
-          <t>What did this session cover? (optional)</t>
+          <t>The customer has left the call.</t>
         </is>
       </c>
       <c r="D283" s="12" t="inlineStr">
         <is>
-          <t>ይህ ክፍለ-ጊዜ ምን ሸፈነ? (አማራጭ)</t>
+          <t>ደንበኛው ጥሪውን ለቅቋል።</t>
         </is>
       </c>
       <c r="E283" s="13" t="inlineStr">
         <is>
-          <t>Sessioniin kun maal haguuge? (filannoo)</t>
+          <t>Maamilaan bilbila irraa ba'eera.</t>
         </is>
       </c>
       <c r="F283" s="12" t="inlineStr">
         <is>
-          <t>እዚ ክፍለ-ግዜ እንታይ ሸፈነ? (ኣማራጺ)</t>
+          <t>እቲ ዓሚል ካብቲ ጻውዒት ወጺኡ።</t>
         </is>
       </c>
       <c r="G283" s="13" t="inlineStr">
         <is>
-          <t>Kalfadhigan muxuu daboolay? (ikhtiyaari)</t>
+          <t>Macmiilku wicitaanka wuu ka baxay.</t>
         </is>
       </c>
       <c r="H283" s="13" t="inlineStr">
         <is>
-          <t>Kikao hiki kilihusu nini? (si lazima)</t>
+          <t>Mteja ameondoka kwenye simu.</t>
         </is>
       </c>
       <c r="I283" s="14" t="inlineStr"/>
@@ -18414,7 +18414,7 @@
     <row r="284" ht="44" customHeight="1">
       <c r="A284" s="11" t="inlineStr">
         <is>
-          <t>customer_ended_call</t>
+          <t>waiting_for_customer</t>
         </is>
       </c>
       <c r="B284" s="11" t="inlineStr">
@@ -18424,32 +18424,32 @@
       </c>
       <c r="C284" s="11" t="inlineStr">
         <is>
-          <t>The customer ended the call</t>
+          <t>Waiting for the customer…</t>
         </is>
       </c>
       <c r="D284" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛው ጥሪውን አቋረጠ</t>
+          <t>ደንበኛውን በመጠበቅ ላይ…</t>
         </is>
       </c>
       <c r="E284" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan bilbila xumure</t>
+          <t>Maamilaa eegaa jirra…</t>
         </is>
       </c>
       <c r="F284" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዓሚል ነቲ ጻውዒት ወዲኡዎ</t>
+          <t>ነቲ ዓሚል ንጽበ ኣለና…</t>
         </is>
       </c>
       <c r="G284" s="13" t="inlineStr">
         <is>
-          <t>Macmiilku wicitaanka wuu joojiyay</t>
+          <t>Macmiilka la sugayo…</t>
         </is>
       </c>
       <c r="H284" s="13" t="inlineStr">
         <is>
-          <t>Mteja alimaliza simu</t>
+          <t>Inasubiri Mteja…</t>
         </is>
       </c>
       <c r="I284" s="14" t="inlineStr"/>
@@ -18457,7 +18457,7 @@
     <row r="285" ht="44" customHeight="1">
       <c r="A285" s="11" t="inlineStr">
         <is>
-          <t>verified_scope</t>
+          <t>mic_blocked</t>
         </is>
       </c>
       <c r="B285" s="11" t="inlineStr">
@@ -18467,32 +18467,32 @@
       </c>
       <c r="C285" s="11" t="inlineStr">
         <is>
-          <t>You can now discuss their own records, take documents and file a dispute. Never a deposit, withdrawal or transfer.</t>
+          <t>Microphone access is blocked. Allow it in your browser and take the session again.</t>
         </is>
       </c>
       <c r="D285" s="12" t="inlineStr">
         <is>
-          <t>አሁን ስለ ራሳቸው መዝገቦች መወያየት፣ ሰነዶች መቀበልና ቅሬታ ማስመዝገብ ይችላሉ። በፍጹም ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም።</t>
+          <t>የማይክሮፎን መዳረሻ ታግዷል። በአሳሽዎ ውስጥ ይፍቀዱና ክፍለ-ጊዜውን እንደገና ይውሰዱ።</t>
         </is>
       </c>
       <c r="E285" s="13" t="inlineStr">
         <is>
-          <t>Amma waa'ee galmee isaanii mari'achuu, sanadoota fudhachuu fi komii galmeessuu dandeessu. Gonkumaa kuusaa, baasii yookiin dabarsa hin jiru.</t>
+          <t>Maayikiroofoonii dhorkameera. Biraawzarii keessan keessatti hayyamaatii session irra deebi'aa fudhadhaa.</t>
         </is>
       </c>
       <c r="F285" s="12" t="inlineStr">
         <is>
-          <t>ሕጂ ብዛዕባ ናቶም መዝገባት ክትዘራረቡ፣ ሰነዳት ክትቅበሉን ጥርዓን ከተመዝግቡን ትኽእሉ። ፈጺሙ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን።</t>
+          <t>መእተዊ ማይክሮፎን ተዓጊቱ። ኣብ መርበብ መንሸራተቲኹም ፍቐዱ እሞ ነቲ ክፍለ-ግዜ ደጊምኩም ውሰዱ።</t>
         </is>
       </c>
       <c r="G285" s="13" t="inlineStr">
         <is>
-          <t>Hadda waad kala hadli kartaa diiwaankooda, dukumiinti qaadan iyo cabasho diiwaangelin. Weligaa dhigasho, qaadis ama wareejin ma jirto.</t>
+          <t>Makarafoonka waa la xannibay. Browser-kaaga ka ogolow oo kalfadhiga mar kale qaado.</t>
         </is>
       </c>
       <c r="H285" s="13" t="inlineStr">
         <is>
-          <t>Sasa unaweza kuzungumzia rekodi zao wenyewe, kuchukua nyaraka na kuwasilisha mgogoro. Kamwe amana, uondoaji au uhamishaji.</t>
+          <t>Ufikiaji wa maikrofoni umezuiwa. Ruhusu kwenye kivinjari chako na uanze kikao tena.</t>
         </is>
       </c>
       <c r="I285" s="14" t="inlineStr"/>
@@ -18500,7 +18500,7 @@
     <row r="286" ht="44" customHeight="1">
       <c r="A286" s="11" t="inlineStr">
         <is>
-          <t>establish_who_they_are</t>
+          <t>unknown_error</t>
         </is>
       </c>
       <c r="B286" s="11" t="inlineStr">
@@ -18510,32 +18510,32 @@
       </c>
       <c r="C286" s="11" t="inlineStr">
         <is>
-          <t>Establish who they are — either one</t>
+          <t>unknown error</t>
         </is>
       </c>
       <c r="D286" s="12" t="inlineStr">
         <is>
-          <t>ማንነታቸውን ያረጋግጡ — አንዱ ይበቃል</t>
+          <t>ያልታወቀ ስህተት</t>
         </is>
       </c>
       <c r="E286" s="13" t="inlineStr">
         <is>
-          <t>Eenyummaa isaanii mirkaneessaa — tokko ni ga'a</t>
+          <t>dogoggora hin beekamne</t>
         </is>
       </c>
       <c r="F286" s="12" t="inlineStr">
         <is>
-          <t>መንነቶም ኣረጋግጹ — ሓደ እኹል እዩ</t>
+          <t>ዘይተፈልጠ ጌጋ</t>
         </is>
       </c>
       <c r="G286" s="13" t="inlineStr">
         <is>
-          <t>Ogow cidda ay yihiin — mid kasta</t>
+          <t>khalad aan la garanayn</t>
         </is>
       </c>
       <c r="H286" s="13" t="inlineStr">
         <is>
-          <t>Thibitisha ni nani — mojawapo</t>
+          <t>hitilafu isiyojulikana</t>
         </is>
       </c>
       <c r="I286" s="14" t="inlineStr"/>
@@ -18543,7 +18543,7 @@
     <row r="287" ht="44" customHeight="1">
       <c r="A287" s="11" t="inlineStr">
         <is>
-          <t>chk_id_document</t>
+          <t>no_messages_yet</t>
         </is>
       </c>
       <c r="B287" s="11" t="inlineStr">
@@ -18553,32 +18553,32 @@
       </c>
       <c r="C287" s="11" t="inlineStr">
         <is>
-          <t>Fayda ID shown and matches the account name</t>
+          <t>No messages yet.</t>
         </is>
       </c>
       <c r="D287" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ መታወቂያ ታይቷል እና ከሂሳቡ ስም ጋር ይዛመዳል</t>
+          <t>እስካሁን መልእክት የለም።</t>
         </is>
       </c>
       <c r="E287" s="13" t="inlineStr">
         <is>
-          <t>Waraqaan eenyummaa Fayda agarsiifame maqaa herregaa waliin walsimeera</t>
+          <t>Ammaaf ergaan hin jiru.</t>
         </is>
       </c>
       <c r="F287" s="12" t="inlineStr">
         <is>
-          <t>መንነት ፋይዳ ተራእዩን ምስ ስም ሕሳብ ይሰማማዕን</t>
+          <t>ክሳብ ሕጂ መልእኽቲ የለን።</t>
         </is>
       </c>
       <c r="G287" s="13" t="inlineStr">
         <is>
-          <t>Aqoonsiga Fayda waa la tusay wuxuuna la mid yahay magaca xisaabta</t>
+          <t>Weli fariimo ma jiraan.</t>
         </is>
       </c>
       <c r="H287" s="13" t="inlineStr">
         <is>
-          <t>Kitambulisho cha Fayda kimeonyeshwa na kinalingana na jina la akaunti</t>
+          <t>Hakuna ujumbe bado.</t>
         </is>
       </c>
       <c r="I287" s="14" t="inlineStr"/>
@@ -18586,7 +18586,7 @@
     <row r="288" ht="44" customHeight="1">
       <c r="A288" s="11" t="inlineStr">
         <is>
-          <t>chk_fayda_matched</t>
+          <t>you_label</t>
         </is>
       </c>
       <c r="B288" s="11" t="inlineStr">
@@ -18596,32 +18596,32 @@
       </c>
       <c r="C288" s="11" t="inlineStr">
         <is>
-          <t>Fayda number matches the account record</t>
+          <t>You</t>
         </is>
       </c>
       <c r="D288" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ ቁጥር ከሂሳቡ መዝገብ ጋር ይዛመዳል</t>
+          <t>እርስዎ</t>
         </is>
       </c>
       <c r="E288" s="13" t="inlineStr">
         <is>
-          <t>Lakkoofsi Fayda galmee herregaa waliin walsimeera</t>
+          <t>Isin</t>
         </is>
       </c>
       <c r="F288" s="12" t="inlineStr">
         <is>
-          <t>ቁጽሪ ፋይዳ ምስ መዝገብ ሕሳብ ይሰማማዕ</t>
+          <t>ንስኹም</t>
         </is>
       </c>
       <c r="G288" s="13" t="inlineStr">
         <is>
-          <t>Lambarka Fayda wuxuu la mid yahay diiwaanka xisaabta</t>
+          <t>Adiga</t>
         </is>
       </c>
       <c r="H288" s="13" t="inlineStr">
         <is>
-          <t>Namba ya Fayda inalingana na rekodi ya akaunti</t>
+          <t>Wewe</t>
         </is>
       </c>
       <c r="I288" s="14" t="inlineStr"/>
@@ -18629,7 +18629,7 @@
     <row r="289" ht="44" customHeight="1">
       <c r="A289" s="11" t="inlineStr">
         <is>
-          <t>chk_fayda_matched_note</t>
+          <t>assistant_label</t>
         </is>
       </c>
       <c r="B289" s="11" t="inlineStr">
@@ -18639,32 +18639,32 @@
       </c>
       <c r="C289" s="11" t="inlineStr">
         <is>
-          <t>on your own screen — works on an audio call</t>
+          <t>Assistant</t>
         </is>
       </c>
       <c r="D289" s="12" t="inlineStr">
         <is>
-          <t>በራስዎ ስክሪን ላይ — በድምፅ ጥሪም ይሠራል</t>
+          <t>ረዳት</t>
         </is>
       </c>
       <c r="E289" s="13" t="inlineStr">
         <is>
-          <t>iskiriinii keessan irratti — bilbila sagalee irrattis ni hojjeta</t>
+          <t>Gargaaraa</t>
         </is>
       </c>
       <c r="F289" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ናትኩም መርአዪ — ኣብ ናይ ድምጺ ጻውዒት እውን ይሰርሕ</t>
+          <t>ሓጋዚ</t>
         </is>
       </c>
       <c r="G289" s="13" t="inlineStr">
         <is>
-          <t>shaashaddaada — wicitaan cod ahna wuu ka shaqeeyaa</t>
+          <t>Kaaliye</t>
         </is>
       </c>
       <c r="H289" s="13" t="inlineStr">
         <is>
-          <t>kwenye skrini yako mwenyewe — inafanya kazi kwenye simu ya sauti</t>
+          <t>Msaidizi</t>
         </is>
       </c>
       <c r="I289" s="14" t="inlineStr"/>
@@ -18672,7 +18672,7 @@
     <row r="290" ht="44" customHeight="1">
       <c r="A290" s="11" t="inlineStr">
         <is>
-          <t>chk_id_photo</t>
+          <t>conversation_unavailable</t>
         </is>
       </c>
       <c r="B290" s="11" t="inlineStr">
@@ -18682,32 +18682,32 @@
       </c>
       <c r="C290" s="11" t="inlineStr">
         <is>
-          <t>Photo on the ID matches the person on the call</t>
+          <t>Conversation unavailable.</t>
         </is>
       </c>
       <c r="D290" s="12" t="inlineStr">
         <is>
-          <t>በመታወቂያው ላይ ያለው ፎቶ ከጥሪው ላይ ካለው ሰው ጋር ይዛመዳል</t>
+          <t>ውይይቱ አይገኝም።</t>
         </is>
       </c>
       <c r="E290" s="13" t="inlineStr">
         <is>
-          <t>Suuraan waraqaa eenyummaa irra jiru nama bilbila irra jiru waliin walsimeera</t>
+          <t>Mariin hin argamu.</t>
         </is>
       </c>
       <c r="F290" s="12" t="inlineStr">
         <is>
-          <t>እቲ ኣብ መንነት ዘሎ ስእሊ ምስቲ ኣብ ጻውዒት ዘሎ ሰብ ይሰማማዕ</t>
+          <t>እቲ ዝርርብ ኣይርከብን።</t>
         </is>
       </c>
       <c r="G290" s="13" t="inlineStr">
         <is>
-          <t>Sawirka aqoonsiga wuxuu la mid yahay qofka wicitaanka ku jira</t>
+          <t>Wadahadalka lama heli karo.</t>
         </is>
       </c>
       <c r="H290" s="13" t="inlineStr">
         <is>
-          <t>Picha kwenye kitambulisho inalingana na mtu aliye kwenye simu</t>
+          <t>Mazungumzo hayapatikani.</t>
         </is>
       </c>
       <c r="I290" s="14" t="inlineStr"/>
@@ -18715,7 +18715,7 @@
     <row r="291" ht="44" customHeight="1">
       <c r="A291" s="11" t="inlineStr">
         <is>
-          <t>chk_video_only</t>
+          <t>unmute</t>
         </is>
       </c>
       <c r="B291" s="11" t="inlineStr">
@@ -18725,32 +18725,32 @@
       </c>
       <c r="C291" s="11" t="inlineStr">
         <is>
-          <t>video only</t>
+          <t>Unmute</t>
         </is>
       </c>
       <c r="D291" s="12" t="inlineStr">
         <is>
-          <t>ቪዲዮ ብቻ</t>
+          <t>ድምፅ አብራ</t>
         </is>
       </c>
       <c r="E291" s="13" t="inlineStr">
         <is>
-          <t>viidiyoo qofa</t>
+          <t>Sagalee banaa</t>
         </is>
       </c>
       <c r="F291" s="12" t="inlineStr">
         <is>
-          <t>ቪድዮ ጥራይ</t>
+          <t>ድምጺ ኣብርህ</t>
         </is>
       </c>
       <c r="G291" s="13" t="inlineStr">
         <is>
-          <t>fiidyow oo kaliya</t>
+          <t>Codka fur</t>
         </is>
       </c>
       <c r="H291" s="13" t="inlineStr">
         <is>
-          <t>video pekee</t>
+          <t>Rudisha Sauti</t>
         </is>
       </c>
       <c r="I291" s="14" t="inlineStr"/>
@@ -18758,7 +18758,7 @@
     <row r="292" ht="44" customHeight="1">
       <c r="A292" s="11" t="inlineStr">
         <is>
-          <t>confirm_account_theirs</t>
+          <t>session_summary_prompt</t>
         </is>
       </c>
       <c r="B292" s="11" t="inlineStr">
@@ -18768,32 +18768,32 @@
       </c>
       <c r="C292" s="11" t="inlineStr">
         <is>
-          <t>And confirm the account is theirs</t>
+          <t>What did this session cover? (optional)</t>
         </is>
       </c>
       <c r="D292" s="12" t="inlineStr">
         <is>
-          <t>እና ሂሳቡ የእነሱ መሆኑን ያረጋግጡ</t>
+          <t>ይህ ክፍለ-ጊዜ ምን ሸፈነ? (አማራጭ)</t>
         </is>
       </c>
       <c r="E292" s="13" t="inlineStr">
         <is>
-          <t>Akkasumas herregni kan isaanii ta'uu mirkaneessaa</t>
+          <t>Sessioniin kun maal haguuge? (filannoo)</t>
         </is>
       </c>
       <c r="F292" s="12" t="inlineStr">
         <is>
-          <t>ከምኡ'ውን እቲ ሕሳብ ናቶም ምዃኑ ኣረጋግጹ</t>
+          <t>እዚ ክፍለ-ግዜ እንታይ ሸፈነ? (ኣማራጺ)</t>
         </is>
       </c>
       <c r="G292" s="13" t="inlineStr">
         <is>
-          <t>Xaqiiji in xisaabtu tahay tooda</t>
+          <t>Kalfadhigan muxuu daboolay? (ikhtiyaari)</t>
         </is>
       </c>
       <c r="H292" s="13" t="inlineStr">
         <is>
-          <t>Na thibitisha akaunti ni yao</t>
+          <t>Kikao hiki kilihusu nini? (si lazima)</t>
         </is>
       </c>
       <c r="I292" s="14" t="inlineStr"/>
@@ -18801,7 +18801,7 @@
     <row r="293" ht="44" customHeight="1">
       <c r="A293" s="11" t="inlineStr">
         <is>
-          <t>confirm_identity</t>
+          <t>customer_ended_call</t>
         </is>
       </c>
       <c r="B293" s="11" t="inlineStr">
@@ -18811,32 +18811,32 @@
       </c>
       <c r="C293" s="11" t="inlineStr">
         <is>
-          <t>Confirm identity</t>
+          <t>The customer ended the call</t>
         </is>
       </c>
       <c r="D293" s="12" t="inlineStr">
         <is>
-          <t>ማንነት አረጋግጥ</t>
+          <t>ደንበኛው ጥሪውን አቋረጠ</t>
         </is>
       </c>
       <c r="E293" s="13" t="inlineStr">
         <is>
-          <t>Eenyummaa mirkaneessi</t>
+          <t>Maamilaan bilbila xumure</t>
         </is>
       </c>
       <c r="F293" s="12" t="inlineStr">
         <is>
-          <t>መንነት ኣረጋግጽ</t>
+          <t>እቲ ዓሚል ነቲ ጻውዒት ወዲኡዎ</t>
         </is>
       </c>
       <c r="G293" s="13" t="inlineStr">
         <is>
-          <t>Xaqiiji aqoonsiga</t>
+          <t>Macmiilku wicitaanka wuu joojiyay</t>
         </is>
       </c>
       <c r="H293" s="13" t="inlineStr">
         <is>
-          <t>Thibitisha Utambulisho</t>
+          <t>Mteja alimaliza simu</t>
         </is>
       </c>
       <c r="I293" s="14" t="inlineStr"/>
@@ -18844,7 +18844,7 @@
     <row r="294" ht="44" customHeight="1">
       <c r="A294" s="11" t="inlineStr">
         <is>
-          <t>unverified_scope</t>
+          <t>verified_scope</t>
         </is>
       </c>
       <c r="B294" s="11" t="inlineStr">
@@ -18854,32 +18854,32 @@
       </c>
       <c r="C294" s="11" t="inlineStr">
         <is>
-          <t>Until this is done you can only give general guidance — products, eligibility and how to apply.</t>
+          <t>You can now discuss their own records, take documents and file a dispute. Never a deposit, withdrawal or transfer.</t>
         </is>
       </c>
       <c r="D294" s="12" t="inlineStr">
         <is>
-          <t>ይህ እስኪከናወን ድረስ አጠቃላይ መመሪያ ብቻ መስጠት ይችላሉ — ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል።</t>
+          <t>አሁን ስለ ራሳቸው መዝገቦች መወያየት፣ ሰነዶች መቀበልና ቅሬታ ማስመዝገብ ይችላሉ። በፍጹም ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም።</t>
         </is>
       </c>
       <c r="E294" s="13" t="inlineStr">
         <is>
-          <t>Hanga kun raawwatutti qajeelfama waliigalaa qofa kennuu dandeessu — oomishaalee, ulaagaa fi akkaataa itti iyyatan.</t>
+          <t>Amma waa'ee galmee isaanii mari'achuu, sanadoota fudhachuu fi komii galmeessuu dandeessu. Gonkumaa kuusaa, baasii yookiin dabarsa hin jiru.</t>
         </is>
       </c>
       <c r="F294" s="12" t="inlineStr">
         <is>
-          <t>እዚ ክሳብ ዝፍጸም ሓፈሻዊ መምርሒ ጥራይ ክትህቡ ትኽእሉ — ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን።</t>
+          <t>ሕጂ ብዛዕባ ናቶም መዝገባት ክትዘራረቡ፣ ሰነዳት ክትቅበሉን ጥርዓን ከተመዝግቡን ትኽእሉ። ፈጺሙ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን።</t>
         </is>
       </c>
       <c r="G294" s="13" t="inlineStr">
         <is>
-          <t>Ilaa tan la sameeyo waxaad kaliya bixin kartaa hagaajin guud — alaabta, u-qalmitaanka iyo sida loo codsado.</t>
+          <t>Hadda waad kala hadli kartaa diiwaankooda, dukumiinti qaadan iyo cabasho diiwaangelin. Weligaa dhigasho, qaadis ama wareejin ma jirto.</t>
         </is>
       </c>
       <c r="H294" s="13" t="inlineStr">
         <is>
-          <t>Hadi hili litakapofanyika unaweza tu kutoa mwongozo wa jumla — bidhaa, sifa za kustahiki na jinsi ya kuomba.</t>
+          <t>Sasa unaweza kuzungumzia rekodi zao wenyewe, kuchukua nyaraka na kuwasilisha mgogoro. Kamwe amana, uondoaji au uhamishaji.</t>
         </is>
       </c>
       <c r="I294" s="14" t="inlineStr"/>
@@ -18887,7 +18887,7 @@
     <row r="295" ht="44" customHeight="1">
       <c r="A295" s="11" t="inlineStr">
         <is>
-          <t>fayda_number_required</t>
+          <t>establish_who_they_are</t>
         </is>
       </c>
       <c r="B295" s="11" t="inlineStr">
@@ -18897,32 +18897,32 @@
       </c>
       <c r="C295" s="11" t="inlineStr">
         <is>
-          <t>Fayda number (required — it is what the record keeps)</t>
+          <t>Establish who they are — either one</t>
         </is>
       </c>
       <c r="D295" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ ቁጥር (ያስፈልጋል — መዝገቡ የሚይዘው ይህ ነው)</t>
+          <t>ማንነታቸውን ያረጋግጡ — አንዱ ይበቃል</t>
         </is>
       </c>
       <c r="E295" s="13" t="inlineStr">
         <is>
-          <t>Lakkoofsa Fayda (barbaachisaa — kan galmeen qabatu isa kana)</t>
+          <t>Eenyummaa isaanii mirkaneessaa — tokko ni ga'a</t>
         </is>
       </c>
       <c r="F295" s="12" t="inlineStr">
         <is>
-          <t>ቁጽሪ ፋይዳ (የድሊ — እቲ መዝገብ ዝሕዞ እዚ እዩ)</t>
+          <t>መንነቶም ኣረጋግጹ — ሓደ እኹል እዩ</t>
         </is>
       </c>
       <c r="G295" s="13" t="inlineStr">
         <is>
-          <t>Lambarka Fayda (loo baahan yahay — waa waxa diiwaanku hayo)</t>
+          <t>Ogow cidda ay yihiin — mid kasta</t>
         </is>
       </c>
       <c r="H295" s="13" t="inlineStr">
         <is>
-          <t>Namba ya Fayda (inahitajika — ndiyo inayowekwa kwenye rekodi)</t>
+          <t>Thibitisha ni nani — mojawapo</t>
         </is>
       </c>
       <c r="I295" s="14" t="inlineStr"/>
@@ -18930,7 +18930,7 @@
     <row r="296" ht="44" customHeight="1">
       <c r="A296" s="11" t="inlineStr">
         <is>
-          <t>download_for_translation</t>
+          <t>chk_id_document</t>
         </is>
       </c>
       <c r="B296" s="11" t="inlineStr">
@@ -18940,32 +18940,32 @@
       </c>
       <c r="C296" s="11" t="inlineStr">
         <is>
-          <t>Download for translation</t>
+          <t>Fayda ID shown and matches the account name</t>
         </is>
       </c>
       <c r="D296" s="12" t="inlineStr">
         <is>
-          <t>ለትርጉም አውርድ</t>
+          <t>የፋይዳ መታወቂያ ታይቷል እና ከሂሳቡ ስም ጋር ይዛመዳል</t>
         </is>
       </c>
       <c r="E296" s="13" t="inlineStr">
         <is>
-          <t>Hiikkaaf buufadhu</t>
+          <t>Waraqaan eenyummaa Fayda agarsiifame maqaa herregaa waliin walsimeera</t>
         </is>
       </c>
       <c r="F296" s="12" t="inlineStr">
         <is>
-          <t>ንትርጉም ኣውርድ</t>
+          <t>መንነት ፋይዳ ተራእዩን ምስ ስም ሕሳብ ይሰማማዕን</t>
         </is>
       </c>
       <c r="G296" s="13" t="inlineStr">
         <is>
-          <t>Soo dejiso turjumaadda</t>
+          <t>Aqoonsiga Fayda waa la tusay wuxuuna la mid yahay magaca xisaabta</t>
         </is>
       </c>
       <c r="H296" s="13" t="inlineStr">
         <is>
-          <t>Pakua kwa Tafsiri</t>
+          <t>Kitambulisho cha Fayda kimeonyeshwa na kinalingana na jina la akaunti</t>
         </is>
       </c>
       <c r="I296" s="14" t="inlineStr"/>
@@ -18973,48 +18973,435 @@
     <row r="297" ht="44" customHeight="1">
       <c r="A297" s="11" t="inlineStr">
         <is>
+          <t>chk_fayda_matched</t>
+        </is>
+      </c>
+      <c r="B297" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C297" s="11" t="inlineStr">
+        <is>
+          <t>Fayda number matches the account record</t>
+        </is>
+      </c>
+      <c r="D297" s="12" t="inlineStr">
+        <is>
+          <t>የፋይዳ ቁጥር ከሂሳቡ መዝገብ ጋር ይዛመዳል</t>
+        </is>
+      </c>
+      <c r="E297" s="13" t="inlineStr">
+        <is>
+          <t>Lakkoofsi Fayda galmee herregaa waliin walsimeera</t>
+        </is>
+      </c>
+      <c r="F297" s="12" t="inlineStr">
+        <is>
+          <t>ቁጽሪ ፋይዳ ምስ መዝገብ ሕሳብ ይሰማማዕ</t>
+        </is>
+      </c>
+      <c r="G297" s="13" t="inlineStr">
+        <is>
+          <t>Lambarka Fayda wuxuu la mid yahay diiwaanka xisaabta</t>
+        </is>
+      </c>
+      <c r="H297" s="13" t="inlineStr">
+        <is>
+          <t>Namba ya Fayda inalingana na rekodi ya akaunti</t>
+        </is>
+      </c>
+      <c r="I297" s="14" t="inlineStr"/>
+    </row>
+    <row r="298" ht="44" customHeight="1">
+      <c r="A298" s="11" t="inlineStr">
+        <is>
+          <t>chk_fayda_matched_note</t>
+        </is>
+      </c>
+      <c r="B298" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C298" s="11" t="inlineStr">
+        <is>
+          <t>on your own screen — works on an audio call</t>
+        </is>
+      </c>
+      <c r="D298" s="12" t="inlineStr">
+        <is>
+          <t>በራስዎ ስክሪን ላይ — በድምፅ ጥሪም ይሠራል</t>
+        </is>
+      </c>
+      <c r="E298" s="13" t="inlineStr">
+        <is>
+          <t>iskiriinii keessan irratti — bilbila sagalee irrattis ni hojjeta</t>
+        </is>
+      </c>
+      <c r="F298" s="12" t="inlineStr">
+        <is>
+          <t>ኣብ ናትኩም መርአዪ — ኣብ ናይ ድምጺ ጻውዒት እውን ይሰርሕ</t>
+        </is>
+      </c>
+      <c r="G298" s="13" t="inlineStr">
+        <is>
+          <t>shaashaddaada — wicitaan cod ahna wuu ka shaqeeyaa</t>
+        </is>
+      </c>
+      <c r="H298" s="13" t="inlineStr">
+        <is>
+          <t>kwenye skrini yako mwenyewe — inafanya kazi kwenye simu ya sauti</t>
+        </is>
+      </c>
+      <c r="I298" s="14" t="inlineStr"/>
+    </row>
+    <row r="299" ht="44" customHeight="1">
+      <c r="A299" s="11" t="inlineStr">
+        <is>
+          <t>chk_id_photo</t>
+        </is>
+      </c>
+      <c r="B299" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C299" s="11" t="inlineStr">
+        <is>
+          <t>Photo on the ID matches the person on the call</t>
+        </is>
+      </c>
+      <c r="D299" s="12" t="inlineStr">
+        <is>
+          <t>በመታወቂያው ላይ ያለው ፎቶ ከጥሪው ላይ ካለው ሰው ጋር ይዛመዳል</t>
+        </is>
+      </c>
+      <c r="E299" s="13" t="inlineStr">
+        <is>
+          <t>Suuraan waraqaa eenyummaa irra jiru nama bilbila irra jiru waliin walsimeera</t>
+        </is>
+      </c>
+      <c r="F299" s="12" t="inlineStr">
+        <is>
+          <t>እቲ ኣብ መንነት ዘሎ ስእሊ ምስቲ ኣብ ጻውዒት ዘሎ ሰብ ይሰማማዕ</t>
+        </is>
+      </c>
+      <c r="G299" s="13" t="inlineStr">
+        <is>
+          <t>Sawirka aqoonsiga wuxuu la mid yahay qofka wicitaanka ku jira</t>
+        </is>
+      </c>
+      <c r="H299" s="13" t="inlineStr">
+        <is>
+          <t>Picha kwenye kitambulisho inalingana na mtu aliye kwenye simu</t>
+        </is>
+      </c>
+      <c r="I299" s="14" t="inlineStr"/>
+    </row>
+    <row r="300" ht="44" customHeight="1">
+      <c r="A300" s="11" t="inlineStr">
+        <is>
+          <t>chk_video_only</t>
+        </is>
+      </c>
+      <c r="B300" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C300" s="11" t="inlineStr">
+        <is>
+          <t>video only</t>
+        </is>
+      </c>
+      <c r="D300" s="12" t="inlineStr">
+        <is>
+          <t>ቪዲዮ ብቻ</t>
+        </is>
+      </c>
+      <c r="E300" s="13" t="inlineStr">
+        <is>
+          <t>viidiyoo qofa</t>
+        </is>
+      </c>
+      <c r="F300" s="12" t="inlineStr">
+        <is>
+          <t>ቪድዮ ጥራይ</t>
+        </is>
+      </c>
+      <c r="G300" s="13" t="inlineStr">
+        <is>
+          <t>fiidyow oo kaliya</t>
+        </is>
+      </c>
+      <c r="H300" s="13" t="inlineStr">
+        <is>
+          <t>video pekee</t>
+        </is>
+      </c>
+      <c r="I300" s="14" t="inlineStr"/>
+    </row>
+    <row r="301" ht="44" customHeight="1">
+      <c r="A301" s="11" t="inlineStr">
+        <is>
+          <t>confirm_account_theirs</t>
+        </is>
+      </c>
+      <c r="B301" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C301" s="11" t="inlineStr">
+        <is>
+          <t>And confirm the account is theirs</t>
+        </is>
+      </c>
+      <c r="D301" s="12" t="inlineStr">
+        <is>
+          <t>እና ሂሳቡ የእነሱ መሆኑን ያረጋግጡ</t>
+        </is>
+      </c>
+      <c r="E301" s="13" t="inlineStr">
+        <is>
+          <t>Akkasumas herregni kan isaanii ta'uu mirkaneessaa</t>
+        </is>
+      </c>
+      <c r="F301" s="12" t="inlineStr">
+        <is>
+          <t>ከምኡ'ውን እቲ ሕሳብ ናቶም ምዃኑ ኣረጋግጹ</t>
+        </is>
+      </c>
+      <c r="G301" s="13" t="inlineStr">
+        <is>
+          <t>Xaqiiji in xisaabtu tahay tooda</t>
+        </is>
+      </c>
+      <c r="H301" s="13" t="inlineStr">
+        <is>
+          <t>Na thibitisha akaunti ni yao</t>
+        </is>
+      </c>
+      <c r="I301" s="14" t="inlineStr"/>
+    </row>
+    <row r="302" ht="44" customHeight="1">
+      <c r="A302" s="11" t="inlineStr">
+        <is>
+          <t>confirm_identity</t>
+        </is>
+      </c>
+      <c r="B302" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C302" s="11" t="inlineStr">
+        <is>
+          <t>Confirm identity</t>
+        </is>
+      </c>
+      <c r="D302" s="12" t="inlineStr">
+        <is>
+          <t>ማንነት አረጋግጥ</t>
+        </is>
+      </c>
+      <c r="E302" s="13" t="inlineStr">
+        <is>
+          <t>Eenyummaa mirkaneessi</t>
+        </is>
+      </c>
+      <c r="F302" s="12" t="inlineStr">
+        <is>
+          <t>መንነት ኣረጋግጽ</t>
+        </is>
+      </c>
+      <c r="G302" s="13" t="inlineStr">
+        <is>
+          <t>Xaqiiji aqoonsiga</t>
+        </is>
+      </c>
+      <c r="H302" s="13" t="inlineStr">
+        <is>
+          <t>Thibitisha Utambulisho</t>
+        </is>
+      </c>
+      <c r="I302" s="14" t="inlineStr"/>
+    </row>
+    <row r="303" ht="44" customHeight="1">
+      <c r="A303" s="11" t="inlineStr">
+        <is>
+          <t>unverified_scope</t>
+        </is>
+      </c>
+      <c r="B303" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C303" s="11" t="inlineStr">
+        <is>
+          <t>Until this is done you can only give general guidance — products, eligibility and how to apply.</t>
+        </is>
+      </c>
+      <c r="D303" s="12" t="inlineStr">
+        <is>
+          <t>ይህ እስኪከናወን ድረስ አጠቃላይ መመሪያ ብቻ መስጠት ይችላሉ — ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል።</t>
+        </is>
+      </c>
+      <c r="E303" s="13" t="inlineStr">
+        <is>
+          <t>Hanga kun raawwatutti qajeelfama waliigalaa qofa kennuu dandeessu — oomishaalee, ulaagaa fi akkaataa itti iyyatan.</t>
+        </is>
+      </c>
+      <c r="F303" s="12" t="inlineStr">
+        <is>
+          <t>እዚ ክሳብ ዝፍጸም ሓፈሻዊ መምርሒ ጥራይ ክትህቡ ትኽእሉ — ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን።</t>
+        </is>
+      </c>
+      <c r="G303" s="13" t="inlineStr">
+        <is>
+          <t>Ilaa tan la sameeyo waxaad kaliya bixin kartaa hagaajin guud — alaabta, u-qalmitaanka iyo sida loo codsado.</t>
+        </is>
+      </c>
+      <c r="H303" s="13" t="inlineStr">
+        <is>
+          <t>Hadi hili litakapofanyika unaweza tu kutoa mwongozo wa jumla — bidhaa, sifa za kustahiki na jinsi ya kuomba.</t>
+        </is>
+      </c>
+      <c r="I303" s="14" t="inlineStr"/>
+    </row>
+    <row r="304" ht="44" customHeight="1">
+      <c r="A304" s="11" t="inlineStr">
+        <is>
+          <t>fayda_number_required</t>
+        </is>
+      </c>
+      <c r="B304" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C304" s="11" t="inlineStr">
+        <is>
+          <t>Fayda number (required — it is what the record keeps)</t>
+        </is>
+      </c>
+      <c r="D304" s="12" t="inlineStr">
+        <is>
+          <t>የፋይዳ ቁጥር (ያስፈልጋል — መዝገቡ የሚይዘው ይህ ነው)</t>
+        </is>
+      </c>
+      <c r="E304" s="13" t="inlineStr">
+        <is>
+          <t>Lakkoofsa Fayda (barbaachisaa — kan galmeen qabatu isa kana)</t>
+        </is>
+      </c>
+      <c r="F304" s="12" t="inlineStr">
+        <is>
+          <t>ቁጽሪ ፋይዳ (የድሊ — እቲ መዝገብ ዝሕዞ እዚ እዩ)</t>
+        </is>
+      </c>
+      <c r="G304" s="13" t="inlineStr">
+        <is>
+          <t>Lambarka Fayda (loo baahan yahay — waa waxa diiwaanku hayo)</t>
+        </is>
+      </c>
+      <c r="H304" s="13" t="inlineStr">
+        <is>
+          <t>Namba ya Fayda (inahitajika — ndiyo inayowekwa kwenye rekodi)</t>
+        </is>
+      </c>
+      <c r="I304" s="14" t="inlineStr"/>
+    </row>
+    <row r="305" ht="44" customHeight="1">
+      <c r="A305" s="11" t="inlineStr">
+        <is>
+          <t>download_for_translation</t>
+        </is>
+      </c>
+      <c r="B305" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C305" s="11" t="inlineStr">
+        <is>
+          <t>Download for translation</t>
+        </is>
+      </c>
+      <c r="D305" s="12" t="inlineStr">
+        <is>
+          <t>ለትርጉም አውርድ</t>
+        </is>
+      </c>
+      <c r="E305" s="13" t="inlineStr">
+        <is>
+          <t>Hiikkaaf buufadhu</t>
+        </is>
+      </c>
+      <c r="F305" s="12" t="inlineStr">
+        <is>
+          <t>ንትርጉም ኣውርድ</t>
+        </is>
+      </c>
+      <c r="G305" s="13" t="inlineStr">
+        <is>
+          <t>Soo dejiso turjumaadda</t>
+        </is>
+      </c>
+      <c r="H305" s="13" t="inlineStr">
+        <is>
+          <t>Pakua kwa Tafsiri</t>
+        </is>
+      </c>
+      <c r="I305" s="14" t="inlineStr"/>
+    </row>
+    <row r="306" ht="44" customHeight="1">
+      <c r="A306" s="11" t="inlineStr">
+        <is>
           <t>nothing_to_download</t>
         </is>
       </c>
-      <c r="B297" s="11" t="inlineStr">
-        <is>
-          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
-        </is>
-      </c>
-      <c r="C297" s="11" t="inlineStr">
+      <c r="B306" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C306" s="11" t="inlineStr">
         <is>
           <t>No approved answers to download yet.</t>
         </is>
       </c>
-      <c r="D297" s="12" t="inlineStr">
+      <c r="D306" s="12" t="inlineStr">
         <is>
           <t>እስካሁን የሚወርድ የተፈቀደ መልስ የለም።</t>
         </is>
       </c>
-      <c r="E297" s="13" t="inlineStr">
+      <c r="E306" s="13" t="inlineStr">
         <is>
           <t>Hanga ammaatti deebiin mirkanaa'e buufamu hin jiru.</t>
         </is>
       </c>
-      <c r="F297" s="12" t="inlineStr">
+      <c r="F306" s="12" t="inlineStr">
         <is>
           <t>ክሳብ ሕጂ ዝወርድ ዝጸደቐ መልሲ የለን።</t>
         </is>
       </c>
-      <c r="G297" s="13" t="inlineStr">
+      <c r="G306" s="13" t="inlineStr">
         <is>
           <t>Weli ma jiraan jawaabo la ansixiyay oo la soo dejiyo.</t>
         </is>
       </c>
-      <c r="H297" s="13" t="inlineStr">
+      <c r="H306" s="13" t="inlineStr">
         <is>
           <t>Hakuna majibu yaliyoidhinishwa ya kupakua bado.</t>
         </is>
       </c>
-      <c r="I297" s="14" t="inlineStr"/>
+      <c r="I306" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I297"/>
+  <autoFilter ref="A1:I306"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/review/Olink_Bank_Assist_language_review.xlsx
+++ b/review/Olink_Bank_Assist_language_review.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1. What the assistant says'!$A$1:$I$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2. What it understands'!$A$1:$E$91</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3. Buttons customers see'!$A$1:$I$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$I$306</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$I$307</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -752,7 +752,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>377 strings in 5 languages</t>
+          <t>378 strings in 5 languages</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I306"/>
+  <dimension ref="A1:I307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -10975,7 +10975,7 @@
     <row r="111" ht="44" customHeight="1">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>escalation_queue</t>
+          <t>no_days_yet</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
@@ -10985,32 +10985,32 @@
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Escalation queue</t>
+          <t>Nothing in this window yet.</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ወረፋ</t>
+          <t>በዚህ ጊዜ ውስጥ እስካሁን ምንም የለም።</t>
         </is>
       </c>
       <c r="E111" s="13" t="inlineStr">
         <is>
-          <t>Sararaa dabarsaa</t>
+          <t>Yeroo kana keessa hanga ammaatti wanti jiru hin jiru.</t>
         </is>
       </c>
       <c r="F111" s="12" t="inlineStr">
         <is>
-          <t>ሪጋ ምትሕልላፍ</t>
+          <t>ኣብዚ ግዜ ክሳብ ሕጂ ዋላ ሓደ የለን።</t>
         </is>
       </c>
       <c r="G111" s="13" t="inlineStr">
         <is>
-          <t>Safka gudbinta</t>
+          <t>Muddadan weli waxba ma jiraan.</t>
         </is>
       </c>
       <c r="H111" s="13" t="inlineStr">
         <is>
-          <t>Foleni ya Masuala Yaliyoelekezwa</t>
+          <t>Hakuna kitu katika kipindi hiki bado.</t>
         </is>
       </c>
       <c r="I111" s="14" t="inlineStr"/>
@@ -11018,7 +11018,7 @@
     <row r="112" ht="44" customHeight="1">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>open_label</t>
+          <t>escalation_queue</t>
         </is>
       </c>
       <c r="B112" s="11" t="inlineStr">
@@ -11028,32 +11028,32 @@
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Escalation queue</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr">
         <is>
-          <t>ክፍት</t>
+          <t>የማሸጋገሪያ ወረፋ</t>
         </is>
       </c>
       <c r="E112" s="13" t="inlineStr">
         <is>
-          <t>Banaa</t>
+          <t>Sararaa dabarsaa</t>
         </is>
       </c>
       <c r="F112" s="12" t="inlineStr">
         <is>
-          <t>ክፉት</t>
+          <t>ሪጋ ምትሕልላፍ</t>
         </is>
       </c>
       <c r="G112" s="13" t="inlineStr">
         <is>
-          <t>Furan</t>
+          <t>Safka gudbinta</t>
         </is>
       </c>
       <c r="H112" s="13" t="inlineStr">
         <is>
-          <t>Wazi</t>
+          <t>Foleni ya Masuala Yaliyoelekezwa</t>
         </is>
       </c>
       <c r="I112" s="14" t="inlineStr"/>
@@ -11061,7 +11061,7 @@
     <row r="113" ht="44" customHeight="1">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>closed_label</t>
+          <t>open_label</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
@@ -11071,32 +11071,32 @@
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>የተዘጋ</t>
+          <t>ክፍት</t>
         </is>
       </c>
       <c r="E113" s="13" t="inlineStr">
         <is>
-          <t>Cufaa</t>
+          <t>Banaa</t>
         </is>
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
-          <t>ዕጹው</t>
+          <t>ክፉት</t>
         </is>
       </c>
       <c r="G113" s="13" t="inlineStr">
         <is>
-          <t>Xiran</t>
+          <t>Furan</t>
         </is>
       </c>
       <c r="H113" s="13" t="inlineStr">
         <is>
-          <t>Imefungwa</t>
+          <t>Wazi</t>
         </is>
       </c>
       <c r="I113" s="14" t="inlineStr"/>
@@ -11104,7 +11104,7 @@
     <row r="114" ht="44" customHeight="1">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>n_reachable</t>
+          <t>closed_label</t>
         </is>
       </c>
       <c r="B114" s="11" t="inlineStr">
@@ -11114,32 +11114,32 @@
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>{n} reachable</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="D114" s="12" t="inlineStr">
         <is>
-          <t>{n} ሊደረስባቸው የሚችሉ</t>
+          <t>የተዘጋ</t>
         </is>
       </c>
       <c r="E114" s="13" t="inlineStr">
         <is>
-          <t>{n} kan bira gahamu</t>
+          <t>Cufaa</t>
         </is>
       </c>
       <c r="F114" s="12" t="inlineStr">
         <is>
-          <t>{n} ክብጻሕዎም ዝኽእሉ</t>
+          <t>ዕጹው</t>
         </is>
       </c>
       <c r="G114" s="13" t="inlineStr">
         <is>
-          <t>{n} la gaari karo</t>
+          <t>Xiran</t>
         </is>
       </c>
       <c r="H114" s="13" t="inlineStr">
         <is>
-          <t>{n} wanapatikana</t>
+          <t>Imefungwa</t>
         </is>
       </c>
       <c r="I114" s="14" t="inlineStr"/>
@@ -11147,7 +11147,7 @@
     <row r="115" ht="44" customHeight="1">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>n_no_contact</t>
+          <t>n_reachable</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
@@ -11157,32 +11157,32 @@
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>{n} with no contact details</t>
+          <t>{n} reachable</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>{n} የመገናኛ መረጃ የሌላቸው</t>
+          <t>{n} ሊደረስባቸው የሚችሉ</t>
         </is>
       </c>
       <c r="E115" s="13" t="inlineStr">
         <is>
-          <t>{n} odeeffannoo quunnamtii hin qabne</t>
+          <t>{n} kan bira gahamu</t>
         </is>
       </c>
       <c r="F115" s="12" t="inlineStr">
         <is>
-          <t>{n} ሓበሬታ መራኸቢ ዘይብሎም</t>
+          <t>{n} ክብጻሕዎም ዝኽእሉ</t>
         </is>
       </c>
       <c r="G115" s="13" t="inlineStr">
         <is>
-          <t>{n} aan lahayn xogta xiriirka</t>
+          <t>{n} la gaari karo</t>
         </is>
       </c>
       <c r="H115" s="13" t="inlineStr">
         <is>
-          <t>{n} hawana taarifa za mawasiliano</t>
+          <t>{n} wanapatikana</t>
         </is>
       </c>
       <c r="I115" s="14" t="inlineStr"/>
@@ -11190,7 +11190,7 @@
     <row r="116" ht="44" customHeight="1">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>what_happened</t>
+          <t>n_no_contact</t>
         </is>
       </c>
       <c r="B116" s="11" t="inlineStr">
@@ -11200,32 +11200,32 @@
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>What happened to each question</t>
+          <t>{n} with no contact details</t>
         </is>
       </c>
       <c r="D116" s="12" t="inlineStr">
         <is>
-          <t>ለእያንዳንዱ ጥያቄ ምን ተፈጠረ</t>
+          <t>{n} የመገናኛ መረጃ የሌላቸው</t>
         </is>
       </c>
       <c r="E116" s="13" t="inlineStr">
         <is>
-          <t>Gaaffii tokkoon tokkoon isaanii maaltu isaan mudate</t>
+          <t>{n} odeeffannoo quunnamtii hin qabne</t>
         </is>
       </c>
       <c r="F116" s="12" t="inlineStr">
         <is>
-          <t>ንነፍስ ወከፍ ሕቶ እንታይ ኮነ</t>
+          <t>{n} ሓበሬታ መራኸቢ ዘይብሎም</t>
         </is>
       </c>
       <c r="G116" s="13" t="inlineStr">
         <is>
-          <t>Maxaa ku dhacay su'aal kasta</t>
+          <t>{n} aan lahayn xogta xiriirka</t>
         </is>
       </c>
       <c r="H116" s="13" t="inlineStr">
         <is>
-          <t>Kilichotokea kwa kila swali</t>
+          <t>{n} hawana taarifa za mawasiliano</t>
         </is>
       </c>
       <c r="I116" s="14" t="inlineStr"/>
@@ -11233,7 +11233,7 @@
     <row r="117" ht="44" customHeight="1">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>also_recorded</t>
+          <t>what_happened</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
@@ -11243,32 +11243,32 @@
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Also recorded: {items}</t>
+          <t>What happened to each question</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>እንዲሁም ተመዝግቧል፦ {items}</t>
+          <t>ለእያንዳንዱ ጥያቄ ምን ተፈጠረ</t>
         </is>
       </c>
       <c r="E117" s="13" t="inlineStr">
         <is>
-          <t>Akkasumas galmaa'e: {items}</t>
+          <t>Gaaffii tokkoon tokkoon isaanii maaltu isaan mudate</t>
         </is>
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
-          <t>ከምኡ'ውን ተመዝጊቡ፦ {items}</t>
+          <t>ንነፍስ ወከፍ ሕቶ እንታይ ኮነ</t>
         </is>
       </c>
       <c r="G117" s="13" t="inlineStr">
         <is>
-          <t>Sidoo kale waa la diiwaangeliyay: {items}</t>
+          <t>Maxaa ku dhacay su'aal kasta</t>
         </is>
       </c>
       <c r="H117" s="13" t="inlineStr">
         <is>
-          <t>Pia imerekodiwa: {items}</t>
+          <t>Kilichotokea kwa kila swali</t>
         </is>
       </c>
       <c r="I117" s="14" t="inlineStr"/>
@@ -11276,7 +11276,7 @@
     <row r="118" ht="44" customHeight="1">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>unclassified_note</t>
+          <t>also_recorded</t>
         </is>
       </c>
       <c r="B118" s="11" t="inlineStr">
@@ -11286,32 +11286,32 @@
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>{n} earlier replies carry no outcome and are not counted above.</t>
+          <t>Also recorded: {items}</t>
         </is>
       </c>
       <c r="D118" s="12" t="inlineStr">
         <is>
-          <t>{n} ቀደም ያሉ መልሶች ውጤት የላቸውም፤ ከላይ አልተቆጠሩም።</t>
+          <t>እንዲሁም ተመዝግቧል፦ {items}</t>
         </is>
       </c>
       <c r="E118" s="13" t="inlineStr">
         <is>
-          <t>Deebiiwwan {n} kanneen duraa bu'aa hin qaban, olitti hin lakkaa'amne.</t>
+          <t>Akkasumas galmaa'e: {items}</t>
         </is>
       </c>
       <c r="F118" s="12" t="inlineStr">
         <is>
-          <t>{n} ናይ ቅድሚ ሕጂ መልስታት ውጽኢት የብሎምን፣ ኣብ ላዕሊ ኣይተቖጽሩን።</t>
+          <t>ከምኡ'ውን ተመዝጊቡ፦ {items}</t>
         </is>
       </c>
       <c r="G118" s="13" t="inlineStr">
         <is>
-          <t>{n} jawaabihii hore natiijo ma laha, korna laguma tirin.</t>
+          <t>Sidoo kale waa la diiwaangeliyay: {items}</t>
         </is>
       </c>
       <c r="H118" s="13" t="inlineStr">
         <is>
-          <t>Majibu {n} ya awali hayana matokeo yaliyoainishwa na hayajahesabiwa hapo juu.</t>
+          <t>Pia imerekodiwa: {items}</t>
         </is>
       </c>
       <c r="I118" s="14" t="inlineStr"/>
@@ -11319,7 +11319,7 @@
     <row r="119" ht="44" customHeight="1">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>most_asked</t>
+          <t>unclassified_note</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
@@ -11329,32 +11329,32 @@
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Most asked</t>
+          <t>{n} earlier replies carry no outcome and are not counted above.</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>በብዛት የተጠየቁ</t>
+          <t>{n} ቀደም ያሉ መልሶች ውጤት የላቸውም፤ ከላይ አልተቆጠሩም።</t>
         </is>
       </c>
       <c r="E119" s="13" t="inlineStr">
         <is>
-          <t>Kan baay'inaan gaafataman</t>
+          <t>Deebiiwwan {n} kanneen duraa bu'aa hin qaban, olitti hin lakkaa'amne.</t>
         </is>
       </c>
       <c r="F119" s="12" t="inlineStr">
         <is>
-          <t>ብብዝሒ ዝተሓተቱ</t>
+          <t>{n} ናይ ቅድሚ ሕጂ መልስታት ውጽኢት የብሎምን፣ ኣብ ላዕሊ ኣይተቖጽሩን።</t>
         </is>
       </c>
       <c r="G119" s="13" t="inlineStr">
         <is>
-          <t>Kuwa ugu badan ee la weydiiyay</t>
+          <t>{n} jawaabihii hore natiijo ma laha, korna laguma tirin.</t>
         </is>
       </c>
       <c r="H119" s="13" t="inlineStr">
         <is>
-          <t>Yanayoulizwa Zaidi</t>
+          <t>Majibu {n} ya awali hayana matokeo yaliyoainishwa na hayajahesabiwa hapo juu.</t>
         </is>
       </c>
       <c r="I119" s="14" t="inlineStr"/>
@@ -11362,7 +11362,7 @@
     <row r="120" ht="44" customHeight="1">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>nothing_asked_yet</t>
+          <t>most_asked</t>
         </is>
       </c>
       <c r="B120" s="11" t="inlineStr">
@@ -11372,32 +11372,32 @@
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>Nothing asked yet in this window.</t>
+          <t>Most asked</t>
         </is>
       </c>
       <c r="D120" s="12" t="inlineStr">
         <is>
-          <t>በዚህ ጊዜ ውስጥ የተጠየቀ የለም።</t>
+          <t>በብዛት የተጠየቁ</t>
         </is>
       </c>
       <c r="E120" s="13" t="inlineStr">
         <is>
-          <t>Yeroo kana keessatti wanti gaafatame hin jiru.</t>
+          <t>Kan baay'inaan gaafataman</t>
         </is>
       </c>
       <c r="F120" s="12" t="inlineStr">
         <is>
-          <t>ኣብዚ እዋን'ዚ ዝተሓተተ የለን።</t>
+          <t>ብብዝሒ ዝተሓተቱ</t>
         </is>
       </c>
       <c r="G120" s="13" t="inlineStr">
         <is>
-          <t>Waqtigan waxba lama weydiin.</t>
+          <t>Kuwa ugu badan ee la weydiiyay</t>
         </is>
       </c>
       <c r="H120" s="13" t="inlineStr">
         <is>
-          <t>Hakuna kilichoulizwa katika muda huu.</t>
+          <t>Yanayoulizwa Zaidi</t>
         </is>
       </c>
       <c r="I120" s="14" t="inlineStr"/>
@@ -11405,7 +11405,7 @@
     <row r="121" ht="44" customHeight="1">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>grouped_by_wording</t>
+          <t>nothing_asked_yet</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Grouped by wording. Phone numbers and names are removed before grouping.</t>
+          <t>Nothing asked yet in this window.</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>በአገላለጽ የተመደበ። ስልክ ቁጥሮችና ስሞች ከመመደቡ በፊት ይወገዳሉ።</t>
+          <t>በዚህ ጊዜ ውስጥ የተጠየቀ የለም።</t>
         </is>
       </c>
       <c r="E121" s="13" t="inlineStr">
         <is>
-          <t>Jechaan kan ramadame. Lakkoofsi bilbilaa fi maqaan osoo hin ramadamin dura ni haqama.</t>
+          <t>Yeroo kana keessatti wanti gaafatame hin jiru.</t>
         </is>
       </c>
       <c r="F121" s="12" t="inlineStr">
         <is>
-          <t>ብኣዘራርባ ዝተጠርነፈ። ቁጽሪ ስልክን ስማትን ቅድሚ ምጥርናፍ ይእለዩ።</t>
+          <t>ኣብዚ እዋን'ዚ ዝተሓተተ የለን።</t>
         </is>
       </c>
       <c r="G121" s="13" t="inlineStr">
         <is>
-          <t>Waxaa loo kala saaray erayada. Lambarrada taleefanka iyo magacyada waa la saaraa ka hor.</t>
+          <t>Waqtigan waxba lama weydiin.</t>
         </is>
       </c>
       <c r="H121" s="13" t="inlineStr">
         <is>
-          <t>Yamepangwa kwa maneno. Namba za simu na majina yameondolewa kabla ya kupanga.</t>
+          <t>Hakuna kilichoulizwa katika muda huu.</t>
         </is>
       </c>
       <c r="I121" s="14" t="inlineStr"/>
@@ -11448,7 +11448,7 @@
     <row r="122" ht="44" customHeight="1">
       <c r="A122" s="11" t="inlineStr">
         <is>
-          <t>what_happened_when_asked</t>
+          <t>grouped_by_wording</t>
         </is>
       </c>
       <c r="B122" s="11" t="inlineStr">
@@ -11458,32 +11458,32 @@
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>What happened when this was asked</t>
+          <t>Grouped by wording. Phone numbers and names are removed before grouping.</t>
         </is>
       </c>
       <c r="D122" s="12" t="inlineStr">
         <is>
-          <t>ይህ ሲጠየቅ ምን ሆነ</t>
+          <t>በአገላለጽ የተመደበ። ስልክ ቁጥሮችና ስሞች ከመመደቡ በፊት ይወገዳሉ።</t>
         </is>
       </c>
       <c r="E122" s="13" t="inlineStr">
         <is>
-          <t>Yeroo kun gaafatametti maaltu ta'e</t>
+          <t>Jechaan kan ramadame. Lakkoofsi bilbilaa fi maqaan osoo hin ramadamin dura ni haqama.</t>
         </is>
       </c>
       <c r="F122" s="12" t="inlineStr">
         <is>
-          <t>እዚ ምስ ተሓተተ እንታይ ኮነ</t>
+          <t>ብኣዘራርባ ዝተጠርነፈ። ቁጽሪ ስልክን ስማትን ቅድሚ ምጥርናፍ ይእለዩ።</t>
         </is>
       </c>
       <c r="G122" s="13" t="inlineStr">
         <is>
-          <t>Maxaa dhacay markii tan la weydiiyay</t>
+          <t>Waxaa loo kala saaray erayada. Lambarrada taleefanka iyo magacyada waa la saaraa ka hor.</t>
         </is>
       </c>
       <c r="H122" s="13" t="inlineStr">
         <is>
-          <t>Kilichotokea liliposwali hili</t>
+          <t>Yamepangwa kwa maneno. Namba za simu na majina yameondolewa kabla ya kupanga.</t>
         </is>
       </c>
       <c r="I122" s="14" t="inlineStr"/>
@@ -11491,7 +11491,7 @@
     <row r="123" ht="44" customHeight="1">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>n_other_questions</t>
+          <t>what_happened_when_asked</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
@@ -11501,32 +11501,32 @@
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>{n} other questions</t>
+          <t>What happened when this was asked</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>{n} ሌሎች ጥያቄዎች</t>
+          <t>ይህ ሲጠየቅ ምን ሆነ</t>
         </is>
       </c>
       <c r="E123" s="13" t="inlineStr">
         <is>
-          <t>Gaaffii {n} biroo</t>
+          <t>Yeroo kun gaafatametti maaltu ta'e</t>
         </is>
       </c>
       <c r="F123" s="12" t="inlineStr">
         <is>
-          <t>{n} ካልኦት ሕቶታት</t>
+          <t>እዚ ምስ ተሓተተ እንታይ ኮነ</t>
         </is>
       </c>
       <c r="G123" s="13" t="inlineStr">
         <is>
-          <t>{n} su'aalood oo kale</t>
+          <t>Maxaa dhacay markii tan la weydiiyay</t>
         </is>
       </c>
       <c r="H123" s="13" t="inlineStr">
         <is>
-          <t>Maswali mengine {n}</t>
+          <t>Kilichotokea liliposwali hili</t>
         </is>
       </c>
       <c r="I123" s="14" t="inlineStr"/>
@@ -11534,7 +11534,7 @@
     <row r="124" ht="44" customHeight="1">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t>view_in_content_gaps</t>
+          <t>n_other_questions</t>
         </is>
       </c>
       <c r="B124" s="11" t="inlineStr">
@@ -11544,32 +11544,32 @@
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>View in Content Gaps</t>
+          <t>{n} other questions</t>
         </is>
       </c>
       <c r="D124" s="12" t="inlineStr">
         <is>
-          <t>በይዘት ክፍተቶች ይመልከቱ</t>
+          <t>{n} ሌሎች ጥያቄዎች</t>
         </is>
       </c>
       <c r="E124" s="13" t="inlineStr">
         <is>
-          <t>Hanqina Qabiyyee keessatti ilaali</t>
+          <t>Gaaffii {n} biroo</t>
         </is>
       </c>
       <c r="F124" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ናይ ትሕዝቶ ክፍተታት ርአ</t>
+          <t>{n} ካልኦት ሕቶታት</t>
         </is>
       </c>
       <c r="G124" s="13" t="inlineStr">
         <is>
-          <t>Ka eeg Farqiyada Nuxurka</t>
+          <t>{n} su'aalood oo kale</t>
         </is>
       </c>
       <c r="H124" s="13" t="inlineStr">
         <is>
-          <t>Angalia katika Mapungufu ya Maudhui</t>
+          <t>Maswali mengine {n}</t>
         </is>
       </c>
       <c r="I124" s="14" t="inlineStr"/>
@@ -11577,7 +11577,7 @@
     <row r="125" ht="44" customHeight="1">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>view_conversations</t>
+          <t>view_in_content_gaps</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
@@ -11587,32 +11587,32 @@
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>View Conversations</t>
+          <t>View in Content Gaps</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>ውይይቶችን ይመልከቱ</t>
+          <t>በይዘት ክፍተቶች ይመልከቱ</t>
         </is>
       </c>
       <c r="E125" s="13" t="inlineStr">
         <is>
-          <t>Haasawaa Ilaali</t>
+          <t>Hanqina Qabiyyee keessatti ilaali</t>
         </is>
       </c>
       <c r="F125" s="12" t="inlineStr">
         <is>
-          <t>ዝርርባት ርአ</t>
+          <t>ኣብ ናይ ትሕዝቶ ክፍተታት ርአ</t>
         </is>
       </c>
       <c r="G125" s="13" t="inlineStr">
         <is>
-          <t>Fiiri Wadahadalada</t>
+          <t>Ka eeg Farqiyada Nuxurka</t>
         </is>
       </c>
       <c r="H125" s="13" t="inlineStr">
         <is>
-          <t>Angalia Mazungumzo</t>
+          <t>Angalia katika Mapungufu ya Maudhui</t>
         </is>
       </c>
       <c r="I125" s="14" t="inlineStr"/>
@@ -11620,7 +11620,7 @@
     <row r="126" ht="44" customHeight="1">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>languages</t>
+          <t>view_conversations</t>
         </is>
       </c>
       <c r="B126" s="11" t="inlineStr">
@@ -11630,32 +11630,32 @@
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>Languages</t>
+          <t>View Conversations</t>
         </is>
       </c>
       <c r="D126" s="12" t="inlineStr">
         <is>
-          <t>ቋንቋዎች</t>
+          <t>ውይይቶችን ይመልከቱ</t>
         </is>
       </c>
       <c r="E126" s="13" t="inlineStr">
         <is>
-          <t>Afaanota</t>
+          <t>Haasawaa Ilaali</t>
         </is>
       </c>
       <c r="F126" s="12" t="inlineStr">
         <is>
-          <t>ቋንቋታት</t>
+          <t>ዝርርባት ርአ</t>
         </is>
       </c>
       <c r="G126" s="13" t="inlineStr">
         <is>
-          <t>Luqadaha</t>
+          <t>Fiiri Wadahadalada</t>
         </is>
       </c>
       <c r="H126" s="13" t="inlineStr">
         <is>
-          <t>Lugha</t>
+          <t>Angalia Mazungumzo</t>
         </is>
       </c>
       <c r="I126" s="14" t="inlineStr"/>
@@ -11663,7 +11663,7 @@
     <row r="127" ht="44" customHeight="1">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>unit_conversations</t>
+          <t>languages</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
@@ -11673,32 +11673,32 @@
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>conversations</t>
+          <t>Languages</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>ውይይቶች</t>
+          <t>ቋንቋዎች</t>
         </is>
       </c>
       <c r="E127" s="13" t="inlineStr">
         <is>
-          <t>marii</t>
+          <t>Afaanota</t>
         </is>
       </c>
       <c r="F127" s="12" t="inlineStr">
         <is>
-          <t>ዝርርባት</t>
+          <t>ቋንቋታት</t>
         </is>
       </c>
       <c r="G127" s="13" t="inlineStr">
         <is>
-          <t>wadahadallo</t>
+          <t>Luqadaha</t>
         </is>
       </c>
       <c r="H127" s="13" t="inlineStr">
         <is>
-          <t>mazungumzo</t>
+          <t>Lugha</t>
         </is>
       </c>
       <c r="I127" s="14" t="inlineStr"/>
@@ -11706,7 +11706,7 @@
     <row r="128" ht="44" customHeight="1">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t>unit_questions</t>
+          <t>unit_conversations</t>
         </is>
       </c>
       <c r="B128" s="11" t="inlineStr">
@@ -11716,32 +11716,32 @@
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>conversations</t>
         </is>
       </c>
       <c r="D128" s="12" t="inlineStr">
         <is>
-          <t>ጥያቄዎች</t>
+          <t>ውይይቶች</t>
         </is>
       </c>
       <c r="E128" s="13" t="inlineStr">
         <is>
-          <t>gaaffiiwwan</t>
+          <t>marii</t>
         </is>
       </c>
       <c r="F128" s="12" t="inlineStr">
         <is>
-          <t>ሕቶታት</t>
+          <t>ዝርርባት</t>
         </is>
       </c>
       <c r="G128" s="13" t="inlineStr">
         <is>
-          <t>su'aalaha</t>
+          <t>wadahadallo</t>
         </is>
       </c>
       <c r="H128" s="13" t="inlineStr">
         <is>
-          <t>maswali</t>
+          <t>mazungumzo</t>
         </is>
       </c>
       <c r="I128" s="14" t="inlineStr"/>
@@ -11749,7 +11749,7 @@
     <row r="129" ht="44" customHeight="1">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>donut_all_in</t>
+          <t>unit_questions</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
@@ -11759,32 +11759,32 @@
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>All {n} {unit} were in {label}.</t>
+          <t>questions</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>ሁሉም {n} {unit} በ{label} ነበሩ።</t>
+          <t>ጥያቄዎች</t>
         </is>
       </c>
       <c r="E129" s="13" t="inlineStr">
         <is>
-          <t>{unit} {n} hundi {label} keessa turan.</t>
+          <t>gaaffiiwwan</t>
         </is>
       </c>
       <c r="F129" s="12" t="inlineStr">
         <is>
-          <t>ኩሎም {n} {unit} ብ{label} ነይሮም።</t>
+          <t>ሕቶታት</t>
         </is>
       </c>
       <c r="G129" s="13" t="inlineStr">
         <is>
-          <t>Dhammaan {n} {unit} waxay ku jireen {label}.</t>
+          <t>su'aalaha</t>
         </is>
       </c>
       <c r="H129" s="13" t="inlineStr">
         <is>
-          <t>{unit} zote {n} zilikuwa katika {label}.</t>
+          <t>maswali</t>
         </is>
       </c>
       <c r="I129" s="14" t="inlineStr"/>
@@ -11792,7 +11792,7 @@
     <row r="130" ht="44" customHeight="1">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t>conversations_by_language</t>
+          <t>donut_all_in</t>
         </is>
       </c>
       <c r="B130" s="11" t="inlineStr">
@@ -11802,32 +11802,32 @@
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>Conversations by language</t>
+          <t>All {n} {unit} were in {label}.</t>
         </is>
       </c>
       <c r="D130" s="12" t="inlineStr">
         <is>
-          <t>በቋንቋ የተከፋፈሉ ውይይቶች</t>
+          <t>ሁሉም {n} {unit} በ{label} ነበሩ።</t>
         </is>
       </c>
       <c r="E130" s="13" t="inlineStr">
         <is>
-          <t>Marii afaaniin</t>
+          <t>{unit} {n} hundi {label} keessa turan.</t>
         </is>
       </c>
       <c r="F130" s="12" t="inlineStr">
         <is>
-          <t>ዝርርባት ብቋንቋ</t>
+          <t>ኩሎም {n} {unit} ብ{label} ነይሮም።</t>
         </is>
       </c>
       <c r="G130" s="13" t="inlineStr">
         <is>
-          <t>Wadahadallada luqadda</t>
+          <t>Dhammaan {n} {unit} waxay ku jireen {label}.</t>
         </is>
       </c>
       <c r="H130" s="13" t="inlineStr">
         <is>
-          <t>Mazungumzo kwa Lugha</t>
+          <t>{unit} zote {n} zilikuwa katika {label}.</t>
         </is>
       </c>
       <c r="I130" s="14" t="inlineStr"/>
@@ -11835,7 +11835,7 @@
     <row r="131" ht="44" customHeight="1">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>no_conversations_window</t>
+          <t>conversations_by_language</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
@@ -11845,32 +11845,32 @@
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>No conversations yet in this window.</t>
+          <t>Conversations by language</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>በዚህ ጊዜ ውስጥ ውይይት የለም።</t>
+          <t>በቋንቋ የተከፋፈሉ ውይይቶች</t>
         </is>
       </c>
       <c r="E131" s="13" t="inlineStr">
         <is>
-          <t>Yeroo kana keessatti mariin hin jiru.</t>
+          <t>Marii afaaniin</t>
         </is>
       </c>
       <c r="F131" s="12" t="inlineStr">
         <is>
-          <t>ኣብዚ እዋን'ዚ ዝርርብ የለን።</t>
+          <t>ዝርርባት ብቋንቋ</t>
         </is>
       </c>
       <c r="G131" s="13" t="inlineStr">
         <is>
-          <t>Waqtigan wadahadal ma jiro.</t>
+          <t>Wadahadallada luqadda</t>
         </is>
       </c>
       <c r="H131" s="13" t="inlineStr">
         <is>
-          <t>Hakuna mazungumzo bado katika muda huu.</t>
+          <t>Mazungumzo kwa Lugha</t>
         </is>
       </c>
       <c r="I131" s="14" t="inlineStr"/>
@@ -11878,7 +11878,7 @@
     <row r="132" ht="44" customHeight="1">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t>recent_activity</t>
+          <t>no_conversations_window</t>
         </is>
       </c>
       <c r="B132" s="11" t="inlineStr">
@@ -11888,32 +11888,32 @@
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>Recent activity</t>
+          <t>No conversations yet in this window.</t>
         </is>
       </c>
       <c r="D132" s="12" t="inlineStr">
         <is>
-          <t>የቅርብ ጊዜ እንቅስቃሴ</t>
+          <t>በዚህ ጊዜ ውስጥ ውይይት የለም።</t>
         </is>
       </c>
       <c r="E132" s="13" t="inlineStr">
         <is>
-          <t>Sochii dhiyoo</t>
+          <t>Yeroo kana keessatti mariin hin jiru.</t>
         </is>
       </c>
       <c r="F132" s="12" t="inlineStr">
         <is>
-          <t>ናይ ቀረባ እዋን ንጥፈት</t>
+          <t>ኣብዚ እዋን'ዚ ዝርርብ የለን።</t>
         </is>
       </c>
       <c r="G132" s="13" t="inlineStr">
         <is>
-          <t>Dhaqdhaqaaqa dhawaan</t>
+          <t>Waqtigan wadahadal ma jiro.</t>
         </is>
       </c>
       <c r="H132" s="13" t="inlineStr">
         <is>
-          <t>Shughuli za Hivi Karibuni</t>
+          <t>Hakuna mazungumzo bado katika muda huu.</t>
         </is>
       </c>
       <c r="I132" s="14" t="inlineStr"/>
@@ -11921,7 +11921,7 @@
     <row r="133" ht="44" customHeight="1">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>live_preview</t>
+          <t>recent_activity</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
@@ -11931,32 +11931,32 @@
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>Live preview</t>
+          <t>Recent activity</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>የቀጥታ ዕይታ</t>
+          <t>የቅርብ ጊዜ እንቅስቃሴ</t>
         </is>
       </c>
       <c r="E133" s="13" t="inlineStr">
         <is>
-          <t>Mul'ata kallattii</t>
+          <t>Sochii dhiyoo</t>
         </is>
       </c>
       <c r="F133" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታ ትርኢት</t>
+          <t>ናይ ቀረባ እዋን ንጥፈት</t>
         </is>
       </c>
       <c r="G133" s="13" t="inlineStr">
         <is>
-          <t>Muuqaal toos ah</t>
+          <t>Dhaqdhaqaaqa dhawaan</t>
         </is>
       </c>
       <c r="H133" s="13" t="inlineStr">
         <is>
-          <t>Muhtasari wa Moja kwa Moja</t>
+          <t>Shughuli za Hivi Karibuni</t>
         </is>
       </c>
       <c r="I133" s="14" t="inlineStr"/>
@@ -11964,7 +11964,7 @@
     <row r="134" ht="44" customHeight="1">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>assistant_preview</t>
+          <t>live_preview</t>
         </is>
       </c>
       <c r="B134" s="11" t="inlineStr">
@@ -11974,32 +11974,32 @@
       </c>
       <c r="C134" s="11" t="inlineStr">
         <is>
-          <t>Assistant preview</t>
+          <t>Live preview</t>
         </is>
       </c>
       <c r="D134" s="12" t="inlineStr">
         <is>
-          <t>የረዳት ዕይታ</t>
+          <t>የቀጥታ ዕይታ</t>
         </is>
       </c>
       <c r="E134" s="13" t="inlineStr">
         <is>
-          <t>Mul'ata gargaaraa</t>
+          <t>Mul'ata kallattii</t>
         </is>
       </c>
       <c r="F134" s="12" t="inlineStr">
         <is>
-          <t>ትርኢት ሓጋዚ</t>
+          <t>ቀጥታ ትርኢት</t>
         </is>
       </c>
       <c r="G134" s="13" t="inlineStr">
         <is>
-          <t>Muuqaalka kaaliyaha</t>
+          <t>Muuqaal toos ah</t>
         </is>
       </c>
       <c r="H134" s="13" t="inlineStr">
         <is>
-          <t>Muhtasari wa Msaidizi</t>
+          <t>Muhtasari wa Moja kwa Moja</t>
         </is>
       </c>
       <c r="I134" s="14" t="inlineStr"/>
@@ -12007,7 +12007,7 @@
     <row r="135" ht="44" customHeight="1">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>preview_caption</t>
+          <t>assistant_preview</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
@@ -12017,32 +12017,32 @@
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>Exactly what a customer sees on your website. Messages sent here are real and appear in Conversations.</t>
+          <t>Assistant preview</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛ በድረ-ገጽዎ ላይ የሚያየው በትክክል ይህ ነው። እዚህ የሚላኩ መልእክቶች እውነተኛ ናቸው እና በውይይቶች ውስጥ ይታያሉ።</t>
+          <t>የረዳት ዕይታ</t>
         </is>
       </c>
       <c r="E135" s="13" t="inlineStr">
         <is>
-          <t>Waanuma maamiltoonni marsariitii keessan irratti argan. Ergaan asitti ergamu dhugaadha, Marii keessattis ni mul'ata.</t>
+          <t>Mul'ata gargaaraa</t>
         </is>
       </c>
       <c r="F135" s="12" t="inlineStr">
         <is>
-          <t>ልክዕ ከምቲ ዓሚል ኣብ መርበብ ሓበሬታኹም ዝርእዮ። ኣብዚ ዝለኣኹ መልእኽትታት ናይ ሓቂ ኮይኖም ኣብ ዝርርባት ይረኣዩ።</t>
+          <t>ትርኢት ሓጋዚ</t>
         </is>
       </c>
       <c r="G135" s="13" t="inlineStr">
         <is>
-          <t>Waa waxa uu macmiilku ku arko degelkaaga. Fariimaha halkan laga diro waa dhab, waxayna ka muuqdaan Wadahadallada.</t>
+          <t>Muuqaalka kaaliyaha</t>
         </is>
       </c>
       <c r="H135" s="13" t="inlineStr">
         <is>
-          <t>Hasa kile mteja anachokiona kwenye tovuti yako. Ujumbe uliotumwa hapa ni halisi na unaonekana katika Mazungumzo.</t>
+          <t>Muhtasari wa Msaidizi</t>
         </is>
       </c>
       <c r="I135" s="14" t="inlineStr"/>
@@ -12050,7 +12050,7 @@
     <row r="136" ht="44" customHeight="1">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t>n_conversations</t>
+          <t>preview_caption</t>
         </is>
       </c>
       <c r="B136" s="11" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>{n} conversations</t>
+          <t>Exactly what a customer sees on your website. Messages sent here are real and appear in Conversations.</t>
         </is>
       </c>
       <c r="D136" s="12" t="inlineStr">
         <is>
-          <t>{n} ውይይቶች</t>
+          <t>ደንበኛ በድረ-ገጽዎ ላይ የሚያየው በትክክል ይህ ነው። እዚህ የሚላኩ መልእክቶች እውነተኛ ናቸው እና በውይይቶች ውስጥ ይታያሉ።</t>
         </is>
       </c>
       <c r="E136" s="13" t="inlineStr">
         <is>
-          <t>Marii {n}</t>
+          <t>Waanuma maamiltoonni marsariitii keessan irratti argan. Ergaan asitti ergamu dhugaadha, Marii keessattis ni mul'ata.</t>
         </is>
       </c>
       <c r="F136" s="12" t="inlineStr">
         <is>
-          <t>{n} ዝርርባት</t>
+          <t>ልክዕ ከምቲ ዓሚል ኣብ መርበብ ሓበሬታኹም ዝርእዮ። ኣብዚ ዝለኣኹ መልእኽትታት ናይ ሓቂ ኮይኖም ኣብ ዝርርባት ይረኣዩ።</t>
         </is>
       </c>
       <c r="G136" s="13" t="inlineStr">
         <is>
-          <t>{n} wadahadal</t>
+          <t>Waa waxa uu macmiilku ku arko degelkaaga. Fariimaha halkan laga diro waa dhab, waxayna ka muuqdaan Wadahadallada.</t>
         </is>
       </c>
       <c r="H136" s="13" t="inlineStr">
         <is>
-          <t>Mazungumzo {n}</t>
+          <t>Hasa kile mteja anachokiona kwenye tovuti yako. Ujumbe uliotumwa hapa ni halisi na unaonekana katika Mazungumzo.</t>
         </is>
       </c>
       <c r="I136" s="14" t="inlineStr"/>
@@ -12093,7 +12093,7 @@
     <row r="137" ht="44" customHeight="1">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>one_conversation</t>
+          <t>n_conversations</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
@@ -12103,12 +12103,12 @@
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>{n} conversation</t>
+          <t>{n} conversations</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>{n} ውይይት</t>
+          <t>{n} ውይይቶች</t>
         </is>
       </c>
       <c r="E137" s="13" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="F137" s="12" t="inlineStr">
         <is>
-          <t>{n} ዝርርብ</t>
+          <t>{n} ዝርርባት</t>
         </is>
       </c>
       <c r="G137" s="13" t="inlineStr">
@@ -12136,7 +12136,7 @@
     <row r="138" ht="44" customHeight="1">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t>outcome_answered</t>
+          <t>one_conversation</t>
         </is>
       </c>
       <c r="B138" s="11" t="inlineStr">
@@ -12146,32 +12146,32 @@
       </c>
       <c r="C138" s="11" t="inlineStr">
         <is>
-          <t>Answered from your content</t>
+          <t>{n} conversation</t>
         </is>
       </c>
       <c r="D138" s="12" t="inlineStr">
         <is>
-          <t>ከይዘትዎ የተመለሰ</t>
+          <t>{n} ውይይት</t>
         </is>
       </c>
       <c r="E138" s="13" t="inlineStr">
         <is>
-          <t>Qabiyyee keessan irraa deebi'e</t>
+          <t>Marii {n}</t>
         </is>
       </c>
       <c r="F138" s="12" t="inlineStr">
         <is>
-          <t>ካብ ትሕዝቶኹም ዝተመለሰ</t>
+          <t>{n} ዝርርብ</t>
         </is>
       </c>
       <c r="G138" s="13" t="inlineStr">
         <is>
-          <t>Laga jawaabay macluumaadkaaga</t>
+          <t>{n} wadahadal</t>
         </is>
       </c>
       <c r="H138" s="13" t="inlineStr">
         <is>
-          <t>Imejibiwa Kutoka kwa Maudhui Yako</t>
+          <t>Mazungumzo {n}</t>
         </is>
       </c>
       <c r="I138" s="14" t="inlineStr"/>
@@ -12179,7 +12179,7 @@
     <row r="139" ht="44" customHeight="1">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>outcome_general_guidance</t>
+          <t>outcome_answered</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
@@ -12189,32 +12189,32 @@
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>Answered from general banking knowledge</t>
+          <t>Answered from your content</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>ከአጠቃላይ የባንክ እውቀት የተመለሰ</t>
+          <t>ከይዘትዎ የተመለሰ</t>
         </is>
       </c>
       <c r="E139" s="13" t="inlineStr">
         <is>
-          <t>Beekumsa baankii waliigalaa irraa deebi'e</t>
+          <t>Qabiyyee keessan irraa deebi'e</t>
         </is>
       </c>
       <c r="F139" s="12" t="inlineStr">
         <is>
-          <t>ካብ ሓፈሻዊ ፍልጠት ባንክ ዝተመለሰ</t>
+          <t>ካብ ትሕዝቶኹም ዝተመለሰ</t>
         </is>
       </c>
       <c r="G139" s="13" t="inlineStr">
         <is>
-          <t>Laga jawaabay aqoonta guud ee bangiga</t>
+          <t>Laga jawaabay macluumaadkaaga</t>
         </is>
       </c>
       <c r="H139" s="13" t="inlineStr">
         <is>
-          <t>Imejibiwa Kutoka kwa Maarifa ya Jumla ya Kibenki</t>
+          <t>Imejibiwa Kutoka kwa Maudhui Yako</t>
         </is>
       </c>
       <c r="I139" s="14" t="inlineStr"/>
@@ -12222,7 +12222,7 @@
     <row r="140" ht="44" customHeight="1">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t>outcome_unanswered</t>
+          <t>outcome_general_guidance</t>
         </is>
       </c>
       <c r="B140" s="11" t="inlineStr">
@@ -12232,32 +12232,32 @@
       </c>
       <c r="C140" s="11" t="inlineStr">
         <is>
-          <t>Could not answer</t>
+          <t>Answered from general banking knowledge</t>
         </is>
       </c>
       <c r="D140" s="12" t="inlineStr">
         <is>
-          <t>መልስ ማግኘት አልተቻለም</t>
+          <t>ከአጠቃላይ የባንክ እውቀት የተመለሰ</t>
         </is>
       </c>
       <c r="E140" s="13" t="inlineStr">
         <is>
-          <t>Deebisuu hin dandeenye</t>
+          <t>Beekumsa baankii waliigalaa irraa deebi'e</t>
         </is>
       </c>
       <c r="F140" s="12" t="inlineStr">
         <is>
-          <t>መልሲ ክርከብ ኣይተኻእለን</t>
+          <t>ካብ ሓፈሻዊ ፍልጠት ባንክ ዝተመለሰ</t>
         </is>
       </c>
       <c r="G140" s="13" t="inlineStr">
         <is>
-          <t>Lama jawaabi karin</t>
+          <t>Laga jawaabay aqoonta guud ee bangiga</t>
         </is>
       </c>
       <c r="H140" s="13" t="inlineStr">
         <is>
-          <t>Haikuweza Kujibiwa</t>
+          <t>Imejibiwa Kutoka kwa Maarifa ya Jumla ya Kibenki</t>
         </is>
       </c>
       <c r="I140" s="14" t="inlineStr"/>
@@ -12265,7 +12265,7 @@
     <row r="141" ht="44" customHeight="1">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>outcome_complaint</t>
+          <t>outcome_unanswered</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
@@ -12275,32 +12275,32 @@
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Could not answer</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>ቅሬታ</t>
+          <t>መልስ ማግኘት አልተቻለም</t>
         </is>
       </c>
       <c r="E141" s="13" t="inlineStr">
         <is>
-          <t>Komii</t>
+          <t>Deebisuu hin dandeenye</t>
         </is>
       </c>
       <c r="F141" s="12" t="inlineStr">
         <is>
-          <t>ጥርዓን</t>
+          <t>መልሲ ክርከብ ኣይተኻእለን</t>
         </is>
       </c>
       <c r="G141" s="13" t="inlineStr">
         <is>
-          <t>Cabasho</t>
+          <t>Lama jawaabi karin</t>
         </is>
       </c>
       <c r="H141" s="13" t="inlineStr">
         <is>
-          <t>Malalamiko</t>
+          <t>Haikuweza Kujibiwa</t>
         </is>
       </c>
       <c r="I141" s="14" t="inlineStr"/>
@@ -12308,7 +12308,7 @@
     <row r="142" ht="44" customHeight="1">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t>outcome_account_blocked</t>
+          <t>outcome_complaint</t>
         </is>
       </c>
       <c r="B142" s="11" t="inlineStr">
@@ -12318,32 +12318,32 @@
       </c>
       <c r="C142" s="11" t="inlineStr">
         <is>
-          <t>Account access problem</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="D142" s="12" t="inlineStr">
         <is>
-          <t>የመለያ መግቢያ ችግር</t>
+          <t>ቅሬታ</t>
         </is>
       </c>
       <c r="E142" s="13" t="inlineStr">
         <is>
-          <t>Rakkoo herrega seenuu</t>
+          <t>Komii</t>
         </is>
       </c>
       <c r="F142" s="12" t="inlineStr">
         <is>
-          <t>ጸገም ኣታውነት ሕሳብ</t>
+          <t>ጥርዓን</t>
         </is>
       </c>
       <c r="G142" s="13" t="inlineStr">
         <is>
-          <t>Dhibaato gelitaanka xisaabta</t>
+          <t>Cabasho</t>
         </is>
       </c>
       <c r="H142" s="13" t="inlineStr">
         <is>
-          <t>Tatizo la Ufikiaji wa Akaunti</t>
+          <t>Malalamiko</t>
         </is>
       </c>
       <c r="I142" s="14" t="inlineStr"/>
@@ -12351,7 +12351,7 @@
     <row r="143" ht="44" customHeight="1">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>outcome_comparison</t>
+          <t>outcome_account_blocked</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
@@ -12361,32 +12361,32 @@
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>Compared with another bank</t>
+          <t>Account access problem</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>ከሌላ ባንክ ጋር ተነጻጽሯል</t>
+          <t>የመለያ መግቢያ ችግር</t>
         </is>
       </c>
       <c r="E143" s="13" t="inlineStr">
         <is>
-          <t>Baankii biraa waliin walbira qabame</t>
+          <t>Rakkoo herrega seenuu</t>
         </is>
       </c>
       <c r="F143" s="12" t="inlineStr">
         <is>
-          <t>ምስ ካልእ ባንክ ተነጻጺሩ</t>
+          <t>ጸገም ኣታውነት ሕሳብ</t>
         </is>
       </c>
       <c r="G143" s="13" t="inlineStr">
         <is>
-          <t>Lala barbardhigay bangi kale</t>
+          <t>Dhibaato gelitaanka xisaabta</t>
         </is>
       </c>
       <c r="H143" s="13" t="inlineStr">
         <is>
-          <t>Ililinganishwa na Benki Nyingine</t>
+          <t>Tatizo la Ufikiaji wa Akaunti</t>
         </is>
       </c>
       <c r="I143" s="14" t="inlineStr"/>
@@ -12394,7 +12394,7 @@
     <row r="144" ht="44" customHeight="1">
       <c r="A144" s="11" t="inlineStr">
         <is>
-          <t>outcome_greeting</t>
+          <t>outcome_comparison</t>
         </is>
       </c>
       <c r="B144" s="11" t="inlineStr">
@@ -12404,32 +12404,32 @@
       </c>
       <c r="C144" s="11" t="inlineStr">
         <is>
-          <t>Greeting</t>
+          <t>Compared with another bank</t>
         </is>
       </c>
       <c r="D144" s="12" t="inlineStr">
         <is>
-          <t>ሰላምታ</t>
+          <t>ከሌላ ባንክ ጋር ተነጻጽሯል</t>
         </is>
       </c>
       <c r="E144" s="13" t="inlineStr">
         <is>
-          <t>Nagaa</t>
+          <t>Baankii biraa waliin walbira qabame</t>
         </is>
       </c>
       <c r="F144" s="12" t="inlineStr">
         <is>
-          <t>ሰላምታ</t>
+          <t>ምስ ካልእ ባንክ ተነጻጺሩ</t>
         </is>
       </c>
       <c r="G144" s="13" t="inlineStr">
         <is>
-          <t>Salaan</t>
+          <t>Lala barbardhigay bangi kale</t>
         </is>
       </c>
       <c r="H144" s="13" t="inlineStr">
         <is>
-          <t>Salamu</t>
+          <t>Ililinganishwa na Benki Nyingine</t>
         </is>
       </c>
       <c r="I144" s="14" t="inlineStr"/>
@@ -12437,7 +12437,7 @@
     <row r="145" ht="44" customHeight="1">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>outcome_contact_captured</t>
+          <t>outcome_greeting</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>Contact details captured</t>
+          <t>Greeting</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>የመገናኛ መረጃ ተመዝግቧል</t>
+          <t>ሰላምታ</t>
         </is>
       </c>
       <c r="E145" s="13" t="inlineStr">
         <is>
-          <t>Odeeffannoon quunnamtii galmaa'e</t>
+          <t>Nagaa</t>
         </is>
       </c>
       <c r="F145" s="12" t="inlineStr">
         <is>
-          <t>ሓበሬታ መራኸቢ ተመዝጊቡ</t>
+          <t>ሰላምታ</t>
         </is>
       </c>
       <c r="G145" s="13" t="inlineStr">
         <is>
-          <t>Xogta xiriirka waa la diiwaangeliyay</t>
+          <t>Salaan</t>
         </is>
       </c>
       <c r="H145" s="13" t="inlineStr">
         <is>
-          <t>Taarifa za Mawasiliano Zimehifadhiwa</t>
+          <t>Salamu</t>
         </is>
       </c>
       <c r="I145" s="14" t="inlineStr"/>
@@ -12480,7 +12480,7 @@
     <row r="146" ht="44" customHeight="1">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t>outcome_human_request</t>
+          <t>outcome_contact_captured</t>
         </is>
       </c>
       <c r="B146" s="11" t="inlineStr">
@@ -12490,32 +12490,32 @@
       </c>
       <c r="C146" s="11" t="inlineStr">
         <is>
-          <t>Asked for a person</t>
+          <t>Contact details captured</t>
         </is>
       </c>
       <c r="D146" s="12" t="inlineStr">
         <is>
-          <t>ሰው ተጠይቋል</t>
+          <t>የመገናኛ መረጃ ተመዝግቧል</t>
         </is>
       </c>
       <c r="E146" s="13" t="inlineStr">
         <is>
-          <t>Nama gaafate</t>
+          <t>Odeeffannoon quunnamtii galmaa'e</t>
         </is>
       </c>
       <c r="F146" s="12" t="inlineStr">
         <is>
-          <t>ሰብ ተሓቲቱ</t>
+          <t>ሓበሬታ መራኸቢ ተመዝጊቡ</t>
         </is>
       </c>
       <c r="G146" s="13" t="inlineStr">
         <is>
-          <t>Qof ayaa la codsaday</t>
+          <t>Xogta xiriirka waa la diiwaangeliyay</t>
         </is>
       </c>
       <c r="H146" s="13" t="inlineStr">
         <is>
-          <t>Aliomba Mtu</t>
+          <t>Taarifa za Mawasiliano Zimehifadhiwa</t>
         </is>
       </c>
       <c r="I146" s="14" t="inlineStr"/>
@@ -12523,7 +12523,7 @@
     <row r="147" ht="44" customHeight="1">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>reason_complaint</t>
+          <t>outcome_human_request</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
@@ -12533,32 +12533,32 @@
       </c>
       <c r="C147" s="11" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Asked for a person</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>ቅሬታ</t>
+          <t>ሰው ተጠይቋል</t>
         </is>
       </c>
       <c r="E147" s="13" t="inlineStr">
         <is>
-          <t>Komii</t>
+          <t>Nama gaafate</t>
         </is>
       </c>
       <c r="F147" s="12" t="inlineStr">
         <is>
-          <t>ጥርዓን</t>
+          <t>ሰብ ተሓቲቱ</t>
         </is>
       </c>
       <c r="G147" s="13" t="inlineStr">
         <is>
-          <t>Cabasho</t>
+          <t>Qof ayaa la codsaday</t>
         </is>
       </c>
       <c r="H147" s="13" t="inlineStr">
         <is>
-          <t>Malalamiko</t>
+          <t>Aliomba Mtu</t>
         </is>
       </c>
       <c r="I147" s="14" t="inlineStr"/>
@@ -12566,7 +12566,7 @@
     <row r="148" ht="44" customHeight="1">
       <c r="A148" s="11" t="inlineStr">
         <is>
-          <t>reason_human_requested</t>
+          <t>reason_complaint</t>
         </is>
       </c>
       <c r="B148" s="11" t="inlineStr">
@@ -12576,32 +12576,32 @@
       </c>
       <c r="C148" s="11" t="inlineStr">
         <is>
-          <t>Asked for a person</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="D148" s="12" t="inlineStr">
         <is>
-          <t>ሰው ተጠይቋል</t>
+          <t>ቅሬታ</t>
         </is>
       </c>
       <c r="E148" s="13" t="inlineStr">
         <is>
-          <t>Nama gaafate</t>
+          <t>Komii</t>
         </is>
       </c>
       <c r="F148" s="12" t="inlineStr">
         <is>
-          <t>ሰብ ተሓቲቱ</t>
+          <t>ጥርዓን</t>
         </is>
       </c>
       <c r="G148" s="13" t="inlineStr">
         <is>
-          <t>Qof ayaa la codsaday</t>
+          <t>Cabasho</t>
         </is>
       </c>
       <c r="H148" s="13" t="inlineStr">
         <is>
-          <t>Aliomba Mtu</t>
+          <t>Malalamiko</t>
         </is>
       </c>
       <c r="I148" s="14" t="inlineStr"/>
@@ -12609,7 +12609,7 @@
     <row r="149" ht="44" customHeight="1">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>reason_unanswered_question</t>
+          <t>reason_human_requested</t>
         </is>
       </c>
       <c r="B149" s="11" t="inlineStr">
@@ -12619,32 +12619,32 @@
       </c>
       <c r="C149" s="11" t="inlineStr">
         <is>
-          <t>No answer in your content</t>
+          <t>Asked for a person</t>
         </is>
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>በይዘትዎ ውስጥ መልስ የለም</t>
+          <t>ሰው ተጠይቋል</t>
         </is>
       </c>
       <c r="E149" s="13" t="inlineStr">
         <is>
-          <t>Qabiyyee keessan keessa deebiin hin jiru</t>
+          <t>Nama gaafate</t>
         </is>
       </c>
       <c r="F149" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ትሕዝቶኹም መልሲ የለን</t>
+          <t>ሰብ ተሓቲቱ</t>
         </is>
       </c>
       <c r="G149" s="13" t="inlineStr">
         <is>
-          <t>Macluumaadkaaga jawaab kuma jirto</t>
+          <t>Qof ayaa la codsaday</t>
         </is>
       </c>
       <c r="H149" s="13" t="inlineStr">
         <is>
-          <t>Hakuna Jibu Katika Maudhui Yako</t>
+          <t>Aliomba Mtu</t>
         </is>
       </c>
       <c r="I149" s="14" t="inlineStr"/>
@@ -12652,7 +12652,7 @@
     <row r="150" ht="44" customHeight="1">
       <c r="A150" s="11" t="inlineStr">
         <is>
-          <t>reason_answered_from_general_knowledge</t>
+          <t>reason_unanswered_question</t>
         </is>
       </c>
       <c r="B150" s="11" t="inlineStr">
@@ -12662,32 +12662,32 @@
       </c>
       <c r="C150" s="11" t="inlineStr">
         <is>
-          <t>Answered from general knowledge</t>
+          <t>No answer in your content</t>
         </is>
       </c>
       <c r="D150" s="12" t="inlineStr">
         <is>
-          <t>ከአጠቃላይ እውቀት የተመለሰ</t>
+          <t>በይዘትዎ ውስጥ መልስ የለም</t>
         </is>
       </c>
       <c r="E150" s="13" t="inlineStr">
         <is>
-          <t>Beekumsa waliigalaa irraa deebi'e</t>
+          <t>Qabiyyee keessan keessa deebiin hin jiru</t>
         </is>
       </c>
       <c r="F150" s="12" t="inlineStr">
         <is>
-          <t>ካብ ሓፈሻዊ ፍልጠት ዝተመለሰ</t>
+          <t>ኣብ ትሕዝቶኹም መልሲ የለን</t>
         </is>
       </c>
       <c r="G150" s="13" t="inlineStr">
         <is>
-          <t>Laga jawaabay aqoon guud</t>
+          <t>Macluumaadkaaga jawaab kuma jirto</t>
         </is>
       </c>
       <c r="H150" s="13" t="inlineStr">
         <is>
-          <t>Imejibiwa Kutoka kwa Maarifa ya Jumla</t>
+          <t>Hakuna Jibu Katika Maudhui Yako</t>
         </is>
       </c>
       <c r="I150" s="14" t="inlineStr"/>
@@ -12695,7 +12695,7 @@
     <row r="151" ht="44" customHeight="1">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>branding</t>
+          <t>reason_answered_from_general_knowledge</t>
         </is>
       </c>
       <c r="B151" s="11" t="inlineStr">
@@ -12705,32 +12705,32 @@
       </c>
       <c r="C151" s="11" t="inlineStr">
         <is>
-          <t>Branding</t>
+          <t>Answered from general knowledge</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>የምርት ስም</t>
+          <t>ከአጠቃላይ እውቀት የተመለሰ</t>
         </is>
       </c>
       <c r="E151" s="13" t="inlineStr">
         <is>
-          <t>Mallattoo dhaabbataa</t>
+          <t>Beekumsa waliigalaa irraa deebi'e</t>
         </is>
       </c>
       <c r="F151" s="12" t="inlineStr">
         <is>
-          <t>ንግዲ ምልክት</t>
+          <t>ካብ ሓፈሻዊ ፍልጠት ዝተመለሰ</t>
         </is>
       </c>
       <c r="G151" s="13" t="inlineStr">
         <is>
-          <t>Astaanta</t>
+          <t>Laga jawaabay aqoon guud</t>
         </is>
       </c>
       <c r="H151" s="13" t="inlineStr">
         <is>
-          <t>Alama ya Biashara</t>
+          <t>Imejibiwa Kutoka kwa Maarifa ya Jumla</t>
         </is>
       </c>
       <c r="I151" s="14" t="inlineStr"/>
@@ -12738,7 +12738,7 @@
     <row r="152" ht="44" customHeight="1">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>branding_help</t>
+          <t>branding</t>
         </is>
       </c>
       <c r="B152" s="11" t="inlineStr">
@@ -12748,32 +12748,32 @@
       </c>
       <c r="C152" s="11" t="inlineStr">
         <is>
-          <t>Your colour and logo, used in this panel and in the chat widget on your website. Saved values apply immediately — no deploy.</t>
+          <t>Branding</t>
         </is>
       </c>
       <c r="D152" s="12" t="inlineStr">
         <is>
-          <t>በዚህ ፓነልና በድረ-ገጽዎ ላይ ባለው የውይይት መስኮት የሚያገለግሉ ቀለምዎና አርማዎ። የተቀመጡ እሴቶች ወዲያውኑ ተግባራዊ ይሆናሉ — ማሰማራት አያስፈልግም።</t>
+          <t>የምርት ስም</t>
         </is>
       </c>
       <c r="E152" s="13" t="inlineStr">
         <is>
-          <t>Halluu fi mallattoo keessan, panaalii kana keessattii fi widjetii chat marsariitii keessan irratti kan hojiirra oolu. Gatiin olkaa'ame battalumatti hojiirra oola — bobbaasuun hin barbaachisu.</t>
+          <t>Mallattoo dhaabbataa</t>
         </is>
       </c>
       <c r="F152" s="12" t="inlineStr">
         <is>
-          <t>ኣብዚ ፓነልን ኣብ መርበብ ሓበሬታኹም ዘሎ መስኮት ዝርርብን ዝጠቅም ሕብርኹምን ኣርማኹምን። ዝተዓቀቡ ዋጋታት ብቕጽበት ይሰርሑ — ምዝርጋሕ ኣየድልን።</t>
+          <t>ንግዲ ምልክት</t>
         </is>
       </c>
       <c r="G152" s="13" t="inlineStr">
         <is>
-          <t>Midabkaaga iyo astaantaada, oo laga isticmaalo daaqadan iyo widget-ka sheekada degelkaaga. Qiyamka la keydiyay isla markiiba way shaqeeyaan — geyn looma baahna.</t>
+          <t>Astaanta</t>
         </is>
       </c>
       <c r="H152" s="13" t="inlineStr">
         <is>
-          <t>Rangi na nembo yako, inayotumika kwenye paneli hii na kwenye kidirisha cha mazungumzo kwenye tovuti yako. Thamani zilizohifadhiwa zinatumika mara moja — bila kupeleka toleo jipya.</t>
+          <t>Alama ya Biashara</t>
         </is>
       </c>
       <c r="I152" s="14" t="inlineStr"/>
@@ -12781,7 +12781,7 @@
     <row r="153" ht="44" customHeight="1">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>brand_name</t>
+          <t>branding_help</t>
         </is>
       </c>
       <c r="B153" s="11" t="inlineStr">
@@ -12791,32 +12791,32 @@
       </c>
       <c r="C153" s="11" t="inlineStr">
         <is>
-          <t>Brand name</t>
+          <t>Your colour and logo, used in this panel and in the chat widget on your website. Saved values apply immediately — no deploy.</t>
         </is>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>የምርት ስም</t>
+          <t>በዚህ ፓነልና በድረ-ገጽዎ ላይ ባለው የውይይት መስኮት የሚያገለግሉ ቀለምዎና አርማዎ። የተቀመጡ እሴቶች ወዲያውኑ ተግባራዊ ይሆናሉ — ማሰማራት አያስፈልግም።</t>
         </is>
       </c>
       <c r="E153" s="13" t="inlineStr">
         <is>
-          <t>Maqaa mallattoo</t>
+          <t>Halluu fi mallattoo keessan, panaalii kana keessattii fi widjetii chat marsariitii keessan irratti kan hojiirra oolu. Gatiin olkaa'ame battalumatti hojiirra oola — bobbaasuun hin barbaachisu.</t>
         </is>
       </c>
       <c r="F153" s="12" t="inlineStr">
         <is>
-          <t>ስም ንግዲ ምልክት</t>
+          <t>ኣብዚ ፓነልን ኣብ መርበብ ሓበሬታኹም ዘሎ መስኮት ዝርርብን ዝጠቅም ሕብርኹምን ኣርማኹምን። ዝተዓቀቡ ዋጋታት ብቕጽበት ይሰርሑ — ምዝርጋሕ ኣየድልን።</t>
         </is>
       </c>
       <c r="G153" s="13" t="inlineStr">
         <is>
-          <t>Magaca astaanta</t>
+          <t>Midabkaaga iyo astaantaada, oo laga isticmaalo daaqadan iyo widget-ka sheekada degelkaaga. Qiyamka la keydiyay isla markiiba way shaqeeyaan — geyn looma baahna.</t>
         </is>
       </c>
       <c r="H153" s="13" t="inlineStr">
         <is>
-          <t>Jina la Alama</t>
+          <t>Rangi na nembo yako, inayotumika kwenye paneli hii na kwenye kidirisha cha mazungumzo kwenye tovuti yako. Thamani zilizohifadhiwa zinatumika mara moja — bila kupeleka toleo jipya.</t>
         </is>
       </c>
       <c r="I153" s="14" t="inlineStr"/>
@@ -12824,7 +12824,7 @@
     <row r="154" ht="44" customHeight="1">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t>brand_name_help</t>
+          <t>brand_name</t>
         </is>
       </c>
       <c r="B154" s="11" t="inlineStr">
@@ -12834,32 +12834,32 @@
       </c>
       <c r="C154" s="11" t="inlineStr">
         <is>
-          <t>What people call you — for example "CBE". Shown in the chat header, this panel and greetings to customers. Leave blank to use your registered name, {legal}, which is kept either way for printed reports.</t>
+          <t>Brand name</t>
         </is>
       </c>
       <c r="D154" s="12" t="inlineStr">
         <is>
-          <t>ሰዎች የሚጠሩዎት ስም — ለምሳሌ "CBE"። በውይይቱ ራስጌ፣ በዚህ ፓነልና ለደንበኞች በሚቀርብ ሰላምታ ላይ ይታያል። ባዶ ከተውት የተመዘገበው ስምዎ {legal} ይሆናል፤ ለሚታተሙ ሪፖርቶች በሁለቱም መንገድ ይቀመጣል።</t>
+          <t>የምርት ስም</t>
         </is>
       </c>
       <c r="E154" s="13" t="inlineStr">
         <is>
-          <t>Maqaa namoonni ittiin isin waaman — fakkeenyaaf "CBE". Mataduree chat, panaalii kanaa fi nagaa maamiltootaaf dhiyaatu irratti ni mul'ata. Duwwaa yoo dhiiftan maqaan galmaa'aa keessan {legal} fayyadama; gabaasa maxxanfamuuf karaa lamaanuu ni qabama.</t>
+          <t>Maqaa mallattoo</t>
         </is>
       </c>
       <c r="F154" s="12" t="inlineStr">
         <is>
-          <t>ሰባት ዝጽውዑኹም ስም — ንኣብነት "CBE"። ኣብ ርእሲ ዝርርብ፣ ኣብዚ ፓነልን ንዓማዊል ኣብ ዝቐርብ ሰላምታን ይረአ። ባዶ እንተ ገዲፍኩምዎ እቲ ዝተመዝገበ ስምኩም {legal} ይኸውን፤ ንዝሕተሙ ጸብጻባት ብኽልቲኡ መገዲ ይዕቀብ።</t>
+          <t>ስም ንግዲ ምልክት</t>
         </is>
       </c>
       <c r="G154" s="13" t="inlineStr">
         <is>
-          <t>Waxa dadku kugu yeeraan — tusaale "CBE". Waxay ka muuqataa madaxa sheekada, daaqadan iyo salaanta macaamiisha. Haddii aad banaan ka tagto waxaa la isticmaalayaa magacaaga diiwaangashan, {legal}, oo si kastaba lagu hayo warbixinnada la daabaco.</t>
+          <t>Magaca astaanta</t>
         </is>
       </c>
       <c r="H154" s="13" t="inlineStr">
         <is>
-          <t>Jina ambalo watu wanakuita — kwa mfano "CBE". Linaonyeshwa kwenye kichwa cha mazungumzo, paneli hii na salamu kwa wateja. Acha wazi ili kutumia jina lako lililosajiliwa, {legal}, ambalo linabaki kutumika kwa ripoti zilizochapishwa.</t>
+          <t>Jina la Alama</t>
         </is>
       </c>
       <c r="I154" s="14" t="inlineStr"/>
@@ -12867,7 +12867,7 @@
     <row r="155" ht="44" customHeight="1">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>brand_colour</t>
+          <t>brand_name_help</t>
         </is>
       </c>
       <c r="B155" s="11" t="inlineStr">
@@ -12877,32 +12877,32 @@
       </c>
       <c r="C155" s="11" t="inlineStr">
         <is>
-          <t>Brand colour</t>
+          <t>What people call you — for example "CBE". Shown in the chat header, this panel and greetings to customers. Leave blank to use your registered name, {legal}, which is kept either way for printed reports.</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>የምርት ቀለም</t>
+          <t>ሰዎች የሚጠሩዎት ስም — ለምሳሌ "CBE"። በውይይቱ ራስጌ፣ በዚህ ፓነልና ለደንበኞች በሚቀርብ ሰላምታ ላይ ይታያል። ባዶ ከተውት የተመዘገበው ስምዎ {legal} ይሆናል፤ ለሚታተሙ ሪፖርቶች በሁለቱም መንገድ ይቀመጣል።</t>
         </is>
       </c>
       <c r="E155" s="13" t="inlineStr">
         <is>
-          <t>Halluu mallattoo</t>
+          <t>Maqaa namoonni ittiin isin waaman — fakkeenyaaf "CBE". Mataduree chat, panaalii kanaa fi nagaa maamiltootaaf dhiyaatu irratti ni mul'ata. Duwwaa yoo dhiiftan maqaan galmaa'aa keessan {legal} fayyadama; gabaasa maxxanfamuuf karaa lamaanuu ni qabama.</t>
         </is>
       </c>
       <c r="F155" s="12" t="inlineStr">
         <is>
-          <t>ሕብሪ ንግዲ ምልክት</t>
+          <t>ሰባት ዝጽውዑኹም ስም — ንኣብነት "CBE"። ኣብ ርእሲ ዝርርብ፣ ኣብዚ ፓነልን ንዓማዊል ኣብ ዝቐርብ ሰላምታን ይረአ። ባዶ እንተ ገዲፍኩምዎ እቲ ዝተመዝገበ ስምኩም {legal} ይኸውን፤ ንዝሕተሙ ጸብጻባት ብኽልቲኡ መገዲ ይዕቀብ።</t>
         </is>
       </c>
       <c r="G155" s="13" t="inlineStr">
         <is>
-          <t>Midabka astaanta</t>
+          <t>Waxa dadku kugu yeeraan — tusaale "CBE". Waxay ka muuqataa madaxa sheekada, daaqadan iyo salaanta macaamiisha. Haddii aad banaan ka tagto waxaa la isticmaalayaa magacaaga diiwaangashan, {legal}, oo si kastaba lagu hayo warbixinnada la daabaco.</t>
         </is>
       </c>
       <c r="H155" s="13" t="inlineStr">
         <is>
-          <t>Rangi ya Alama</t>
+          <t>Jina ambalo watu wanakuita — kwa mfano "CBE". Linaonyeshwa kwenye kichwa cha mazungumzo, paneli hii na salamu kwa wateja. Acha wazi ili kutumia jina lako lililosajiliwa, {legal}, ambalo linabaki kutumika kwa ripoti zilizochapishwa.</t>
         </is>
       </c>
       <c r="I155" s="14" t="inlineStr"/>
@@ -12910,7 +12910,7 @@
     <row r="156" ht="44" customHeight="1">
       <c r="A156" s="11" t="inlineStr">
         <is>
-          <t>logo_url</t>
+          <t>brand_colour</t>
         </is>
       </c>
       <c r="B156" s="11" t="inlineStr">
@@ -12920,32 +12920,32 @@
       </c>
       <c r="C156" s="11" t="inlineStr">
         <is>
-          <t>Logo URL (https)</t>
+          <t>Brand colour</t>
         </is>
       </c>
       <c r="D156" s="12" t="inlineStr">
         <is>
-          <t>የአርማ አድራሻ (https)</t>
+          <t>የምርት ቀለም</t>
         </is>
       </c>
       <c r="E156" s="13" t="inlineStr">
         <is>
-          <t>Teessoo mallattoo (https)</t>
+          <t>Halluu mallattoo</t>
         </is>
       </c>
       <c r="F156" s="12" t="inlineStr">
         <is>
-          <t>ኣድራሻ ኣርማ (https)</t>
+          <t>ሕብሪ ንግዲ ምልክት</t>
         </is>
       </c>
       <c r="G156" s="13" t="inlineStr">
         <is>
-          <t>Ciwaanka astaanta (https)</t>
+          <t>Midabka astaanta</t>
         </is>
       </c>
       <c r="H156" s="13" t="inlineStr">
         <is>
-          <t>Kiungo cha Nembo (https)</t>
+          <t>Rangi ya Alama</t>
         </is>
       </c>
       <c r="I156" s="14" t="inlineStr"/>
@@ -12953,7 +12953,7 @@
     <row r="157" ht="44" customHeight="1">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>seeded_colours_help</t>
+          <t>logo_url</t>
         </is>
       </c>
       <c r="B157" s="11" t="inlineStr">
@@ -12963,32 +12963,32 @@
       </c>
       <c r="C157" s="11" t="inlineStr">
         <is>
-          <t>Seeded colours are our reading of your public site, not your brand book. If it is wrong, this is where to fix it.</t>
+          <t>Logo URL (https)</t>
         </is>
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>የቀረቡት ቀለሞች ከይፋዊ ድረ-ገጽዎ የተወሰዱ ግምቶች እንጂ ከምርት መመሪያ መጽሐፍዎ አይደሉም። ስህተት ከሆነ የሚታረመው እዚህ ነው።</t>
+          <t>የአርማ አድራሻ (https)</t>
         </is>
       </c>
       <c r="E157" s="13" t="inlineStr">
         <is>
-          <t>Halluuwwan durfaman marsariitii keessan ifaa irraa kan dubbifame malee kitaaba mallattoo keessanii irraa miti. Yoo dogoggora ta'e, asitti sirreessaa.</t>
+          <t>Teessoo mallattoo (https)</t>
         </is>
       </c>
       <c r="F157" s="12" t="inlineStr">
         <is>
-          <t>እቶም ዝቐረቡ ሕብርታት ካብ ወግዓዊ መርበብ ሓበሬታኹም ዝተወስዱ ግምት እምበር ካብ መጽሓፍ ንግዲ ምልክትኩም ኣይኮኑን። ጌጋ እንተኾይኑ ኣብዚ ይእረም።</t>
+          <t>ኣድራሻ ኣርማ (https)</t>
         </is>
       </c>
       <c r="G157" s="13" t="inlineStr">
         <is>
-          <t>Midabbada la soo bandhigay waa akhrinteenna degelkaaga guud, ma aha buuggaaga astaanta. Haddii ay khalad tahay, halkan ayaa lagu saxaa.</t>
+          <t>Ciwaanka astaanta (https)</t>
         </is>
       </c>
       <c r="H157" s="13" t="inlineStr">
         <is>
-          <t>Rangi zilizowekwa awali ni uelewa wetu wa tovuti yako ya umma, si kitabu chako cha alama ya biashara. Ikiwa si sahihi, hapa ndipo pa kurekebisha.</t>
+          <t>Kiungo cha Nembo (https)</t>
         </is>
       </c>
       <c r="I157" s="14" t="inlineStr"/>
@@ -12996,7 +12996,7 @@
     <row r="158" ht="44" customHeight="1">
       <c r="A158" s="11" t="inlineStr">
         <is>
-          <t>save_branding</t>
+          <t>seeded_colours_help</t>
         </is>
       </c>
       <c r="B158" s="11" t="inlineStr">
@@ -13006,32 +13006,32 @@
       </c>
       <c r="C158" s="11" t="inlineStr">
         <is>
-          <t>Save branding</t>
+          <t>Seeded colours are our reading of your public site, not your brand book. If it is wrong, this is where to fix it.</t>
         </is>
       </c>
       <c r="D158" s="12" t="inlineStr">
         <is>
-          <t>የምርት ስም አስቀምጥ</t>
+          <t>የቀረቡት ቀለሞች ከይፋዊ ድረ-ገጽዎ የተወሰዱ ግምቶች እንጂ ከምርት መመሪያ መጽሐፍዎ አይደሉም። ስህተት ከሆነ የሚታረመው እዚህ ነው።</t>
         </is>
       </c>
       <c r="E158" s="13" t="inlineStr">
         <is>
-          <t>Mallattoo olkaa'i</t>
+          <t>Halluuwwan durfaman marsariitii keessan ifaa irraa kan dubbifame malee kitaaba mallattoo keessanii irraa miti. Yoo dogoggora ta'e, asitti sirreessaa.</t>
         </is>
       </c>
       <c r="F158" s="12" t="inlineStr">
         <is>
-          <t>ንግዲ ምልክት ኣቐምጥ</t>
+          <t>እቶም ዝቐረቡ ሕብርታት ካብ ወግዓዊ መርበብ ሓበሬታኹም ዝተወስዱ ግምት እምበር ካብ መጽሓፍ ንግዲ ምልክትኩም ኣይኮኑን። ጌጋ እንተኾይኑ ኣብዚ ይእረም።</t>
         </is>
       </c>
       <c r="G158" s="13" t="inlineStr">
         <is>
-          <t>Keydi astaanta</t>
+          <t>Midabbada la soo bandhigay waa akhrinteenna degelkaaga guud, ma aha buuggaaga astaanta. Haddii ay khalad tahay, halkan ayaa lagu saxaa.</t>
         </is>
       </c>
       <c r="H158" s="13" t="inlineStr">
         <is>
-          <t>Hifadhi Alama</t>
+          <t>Rangi zilizowekwa awali ni uelewa wetu wa tovuti yako ya umma, si kitabu chako cha alama ya biashara. Ikiwa si sahihi, hapa ndipo pa kurekebisha.</t>
         </is>
       </c>
       <c r="I158" s="14" t="inlineStr"/>
@@ -13039,7 +13039,7 @@
     <row r="159" ht="44" customHeight="1">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>branding_saved</t>
+          <t>save_branding</t>
         </is>
       </c>
       <c r="B159" s="11" t="inlineStr">
@@ -13049,32 +13049,32 @@
       </c>
       <c r="C159" s="11" t="inlineStr">
         <is>
-          <t>Branding saved</t>
+          <t>Save branding</t>
         </is>
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>የምርት ስም ተቀምጧል</t>
+          <t>የምርት ስም አስቀምጥ</t>
         </is>
       </c>
       <c r="E159" s="13" t="inlineStr">
         <is>
-          <t>Mallattoon olkaa'ame</t>
+          <t>Mallattoo olkaa'i</t>
         </is>
       </c>
       <c r="F159" s="12" t="inlineStr">
         <is>
-          <t>ንግዲ ምልክት ተቐሚጡ</t>
+          <t>ንግዲ ምልክት ኣቐምጥ</t>
         </is>
       </c>
       <c r="G159" s="13" t="inlineStr">
         <is>
-          <t>Astaanta waa la keydiyay</t>
+          <t>Keydi astaanta</t>
         </is>
       </c>
       <c r="H159" s="13" t="inlineStr">
         <is>
-          <t>Alama Imehifadhiwa</t>
+          <t>Hifadhi Alama</t>
         </is>
       </c>
       <c r="I159" s="14" t="inlineStr"/>
@@ -13082,7 +13082,7 @@
     <row r="160" ht="44" customHeight="1">
       <c r="A160" s="11" t="inlineStr">
         <is>
-          <t>escalation_webhook</t>
+          <t>branding_saved</t>
         </is>
       </c>
       <c r="B160" s="11" t="inlineStr">
@@ -13092,32 +13092,32 @@
       </c>
       <c r="C160" s="11" t="inlineStr">
         <is>
-          <t>Escalation webhook</t>
+          <t>Branding saved</t>
         </is>
       </c>
       <c r="D160" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ዌብሁክ</t>
+          <t>የምርት ስም ተቀምጧል</t>
         </is>
       </c>
       <c r="E160" s="13" t="inlineStr">
         <is>
-          <t>Webhook dabarsaa</t>
+          <t>Mallattoon olkaa'ame</t>
         </is>
       </c>
       <c r="F160" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ምትሕልላፍ</t>
+          <t>ንግዲ ምልክት ተቐሚጡ</t>
         </is>
       </c>
       <c r="G160" s="13" t="inlineStr">
         <is>
-          <t>Webhook-ga gudbinta</t>
+          <t>Astaanta waa la keydiyay</t>
         </is>
       </c>
       <c r="H160" s="13" t="inlineStr">
         <is>
-          <t>Wavuti ya Masuala Yaliyoelekezwa</t>
+          <t>Alama Imehifadhiwa</t>
         </is>
       </c>
       <c r="I160" s="14" t="inlineStr"/>
@@ -13125,7 +13125,7 @@
     <row r="161" ht="44" customHeight="1">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>webhook_help</t>
+          <t>escalation_webhook</t>
         </is>
       </c>
       <c r="B161" s="11" t="inlineStr">
@@ -13135,32 +13135,32 @@
       </c>
       <c r="C161" s="11" t="inlineStr">
         <is>
-          <t>Where escalations are delivered in your contact-centre tool. Requests are signed, so the receiving system can verify they came from us. Clear the field to disconnect.</t>
+          <t>Escalation webhook</t>
         </is>
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>ጉዳዮች በእርስዎ የደንበኞች መገልገያ መሣሪያ ውስጥ የሚደርሱበት ቦታ። ጥያቄዎቹ የተፈረሙ ናቸው፤ ስለዚህ ተቀባዩ ሥርዓት ከእኛ መምጣታቸውን ማረጋገጥ ይችላል። ለማቋረጥ መስኩን ባዶ ያድርጉ።</t>
+          <t>የማሸጋገሪያ ዌብሁክ</t>
         </is>
       </c>
       <c r="E161" s="13" t="inlineStr">
         <is>
-          <t>Iddoo dhimmoonni meeshaa wiirtuu quunnamtii keessan keessatti geessifaman. Gaaffiiwwan mallatteeffamaniiru, kanaafuu sirni fudhatu nurraa dhufuu isaanii mirkaneessuu danda'a. Addaan kutuuf dirree duwwaa godhaa.</t>
+          <t>Webhook dabarsaa</t>
         </is>
       </c>
       <c r="F161" s="12" t="inlineStr">
         <is>
-          <t>ጉዳያት ኣብ መሳርሒ ማእከል ርክብኩም ዝበጽሑሉ ቦታ። እቶም ሕቶታት ዝተፈረሙ ስለዝኾኑ እቲ ተቐባሊ ስርዓት ካባና ምምጻኦም ከረጋግጽ ይኽእል። ንምቁራጽ እቲ ሜዳ ባዶ ግበሩ።</t>
+          <t>ዌብሁክ ምትሕልላፍ</t>
         </is>
       </c>
       <c r="G161" s="13" t="inlineStr">
         <is>
-          <t>Halka arrimaha lagu gudbiyo qalabkaaga xarunta macaamiisha. Codsiyada waa la saxeexay, sidaas darteed nidaamka qaataa wuu xaqiijin karaa inay naga yimaadeen. Si aad u gooyso, banaani meesha.</t>
+          <t>Webhook-ga gudbinta</t>
         </is>
       </c>
       <c r="H161" s="13" t="inlineStr">
         <is>
-          <t>Mahali masuala yanapopelekwa kwenye zana yako ya kituo cha huduma kwa wateja. Maombi yamesainiwa, ili mfumo unaopokea uweze kuthibitisha yametoka kwetu. Futa sehemu hii ili kukatisha muunganisho.</t>
+          <t>Wavuti ya Masuala Yaliyoelekezwa</t>
         </is>
       </c>
       <c r="I161" s="14" t="inlineStr"/>
@@ -13168,7 +13168,7 @@
     <row r="162" ht="44" customHeight="1">
       <c r="A162" s="11" t="inlineStr">
         <is>
-          <t>signing_secret_set</t>
+          <t>webhook_help</t>
         </is>
       </c>
       <c r="B162" s="11" t="inlineStr">
@@ -13178,32 +13178,32 @@
       </c>
       <c r="C162" s="11" t="inlineStr">
         <is>
-          <t>A signing secret is set. It cannot be shown again — saving a URL here issues a new one and the old one stops working.</t>
+          <t>Where escalations are delivered in your contact-centre tool. Requests are signed, so the receiving system can verify they came from us. Clear the field to disconnect.</t>
         </is>
       </c>
       <c r="D162" s="12" t="inlineStr">
         <is>
-          <t>የፊርማ ሚስጥር ተዘጋጅቷል። እንደገና ማሳየት አይቻልም — እዚህ አድራሻ ማስቀመጥ አዲስ ያወጣል፤ አሮጌው መስራት ያቆማል።</t>
+          <t>ጉዳዮች በእርስዎ የደንበኞች መገልገያ መሣሪያ ውስጥ የሚደርሱበት ቦታ። ጥያቄዎቹ የተፈረሙ ናቸው፤ ስለዚህ ተቀባዩ ሥርዓት ከእኛ መምጣታቸውን ማረጋገጥ ይችላል። ለማቋረጥ መስኩን ባዶ ያድርጉ።</t>
         </is>
       </c>
       <c r="E162" s="13" t="inlineStr">
         <is>
-          <t>Iccitiin mallattoo qophaa'eera. Irra deebi'anii agarsiisuun hin danda'amu — asitti URL olkaa'uun haaraa baasa, kan duraa immoo hojii dhaaba.</t>
+          <t>Iddoo dhimmoonni meeshaa wiirtuu quunnamtii keessan keessatti geessifaman. Gaaffiiwwan mallatteeffamaniiru, kanaafuu sirni fudhatu nurraa dhufuu isaanii mirkaneessuu danda'a. Addaan kutuuf dirree duwwaa godhaa.</t>
         </is>
       </c>
       <c r="F162" s="12" t="inlineStr">
         <is>
-          <t>ምስጢር ፌርማ ተቐሚጡ። መሊስካ ክርአ ኣይክእልን — ኣብዚ ኣድራሻ ምቕማጥ ሓድሽ የውጽእ፣ እቲ ናይ ቀደም ይቋረጽ።</t>
+          <t>ጉዳያት ኣብ መሳርሒ ማእከል ርክብኩም ዝበጽሑሉ ቦታ። እቶም ሕቶታት ዝተፈረሙ ስለዝኾኑ እቲ ተቐባሊ ስርዓት ካባና ምምጻኦም ከረጋግጽ ይኽእል። ንምቁራጽ እቲ ሜዳ ባዶ ግበሩ።</t>
         </is>
       </c>
       <c r="G162" s="13" t="inlineStr">
         <is>
-          <t>Sir saxeex ayaa la dejiyay. Mar kale lama tusi karo — URL halkan lagu keydiyo wuxuu soo saarayaa mid cusub, kii hore wuu shaqo joojiyaa.</t>
+          <t>Halka arrimaha lagu gudbiyo qalabkaaga xarunta macaamiisha. Codsiyada waa la saxeexay, sidaas darteed nidaamka qaataa wuu xaqiijin karaa inay naga yimaadeen. Si aad u gooyso, banaani meesha.</t>
         </is>
       </c>
       <c r="H162" s="13" t="inlineStr">
         <is>
-          <t>Siri ya kusaini imewekwa. Haiwezi kuonyeshwa tena — kuhifadhi kiungo hapa kunatoa siri mpya na ile ya zamani inaacha kufanya kazi.</t>
+          <t>Mahali masuala yanapopelekwa kwenye zana yako ya kituo cha huduma kwa wateja. Maombi yamesainiwa, ili mfumo unaopokea uweze kuthibitisha yametoka kwetu. Futa sehemu hii ili kukatisha muunganisho.</t>
         </is>
       </c>
       <c r="I162" s="14" t="inlineStr"/>
@@ -13211,7 +13211,7 @@
     <row r="163" ht="44" customHeight="1">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>webhook_connected</t>
+          <t>signing_secret_set</t>
         </is>
       </c>
       <c r="B163" s="11" t="inlineStr">
@@ -13221,32 +13221,32 @@
       </c>
       <c r="C163" s="11" t="inlineStr">
         <is>
-          <t>Webhook connected</t>
+          <t>A signing secret is set. It cannot be shown again — saving a URL here issues a new one and the old one stops working.</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ተገናኝቷል</t>
+          <t>የፊርማ ሚስጥር ተዘጋጅቷል። እንደገና ማሳየት አይቻልም — እዚህ አድራሻ ማስቀመጥ አዲስ ያወጣል፤ አሮጌው መስራት ያቆማል።</t>
         </is>
       </c>
       <c r="E163" s="13" t="inlineStr">
         <is>
-          <t>Webhook walqunnamsiifame</t>
+          <t>Iccitiin mallattoo qophaa'eera. Irra deebi'anii agarsiisuun hin danda'amu — asitti URL olkaa'uun haaraa baasa, kan duraa immoo hojii dhaaba.</t>
         </is>
       </c>
       <c r="F163" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ተራኺቡ</t>
+          <t>ምስጢር ፌርማ ተቐሚጡ። መሊስካ ክርአ ኣይክእልን — ኣብዚ ኣድራሻ ምቕማጥ ሓድሽ የውጽእ፣ እቲ ናይ ቀደም ይቋረጽ።</t>
         </is>
       </c>
       <c r="G163" s="13" t="inlineStr">
         <is>
-          <t>Webhook waa la xiray</t>
+          <t>Sir saxeex ayaa la dejiyay. Mar kale lama tusi karo — URL halkan lagu keydiyo wuxuu soo saarayaa mid cusub, kii hore wuu shaqo joojiyaa.</t>
         </is>
       </c>
       <c r="H163" s="13" t="inlineStr">
         <is>
-          <t>Wavuti Imeunganishwa</t>
+          <t>Siri ya kusaini imewekwa. Haiwezi kuonyeshwa tena — kuhifadhi kiungo hapa kunatoa siri mpya na ile ya zamani inaacha kufanya kazi.</t>
         </is>
       </c>
       <c r="I163" s="14" t="inlineStr"/>
@@ -13254,7 +13254,7 @@
     <row r="164" ht="44" customHeight="1">
       <c r="A164" s="11" t="inlineStr">
         <is>
-          <t>webhook_disconnected</t>
+          <t>webhook_connected</t>
         </is>
       </c>
       <c r="B164" s="11" t="inlineStr">
@@ -13264,32 +13264,32 @@
       </c>
       <c r="C164" s="11" t="inlineStr">
         <is>
-          <t>Webhook disconnected</t>
+          <t>Webhook connected</t>
         </is>
       </c>
       <c r="D164" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ተቋርጧል</t>
+          <t>ዌብሁክ ተገናኝቷል</t>
         </is>
       </c>
       <c r="E164" s="13" t="inlineStr">
         <is>
-          <t>Webhook addaan kutame</t>
+          <t>Webhook walqunnamsiifame</t>
         </is>
       </c>
       <c r="F164" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ተቛሪጹ</t>
+          <t>ዌብሁክ ተራኺቡ</t>
         </is>
       </c>
       <c r="G164" s="13" t="inlineStr">
         <is>
-          <t>Webhook waa la goynay</t>
+          <t>Webhook waa la xiray</t>
         </is>
       </c>
       <c r="H164" s="13" t="inlineStr">
         <is>
-          <t>Wavuti Imekatishwa</t>
+          <t>Wavuti Imeunganishwa</t>
         </is>
       </c>
       <c r="I164" s="14" t="inlineStr"/>
@@ -13297,7 +13297,7 @@
     <row r="165" ht="44" customHeight="1">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>your_password</t>
+          <t>webhook_disconnected</t>
         </is>
       </c>
       <c r="B165" s="11" t="inlineStr">
@@ -13307,32 +13307,32 @@
       </c>
       <c r="C165" s="11" t="inlineStr">
         <is>
-          <t>Your password</t>
+          <t>Webhook disconnected</t>
         </is>
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>የይለፍ ቃልዎ</t>
+          <t>ዌብሁክ ተቋርጧል</t>
         </is>
       </c>
       <c r="E165" s="13" t="inlineStr">
         <is>
-          <t>Jecha darbii keessan</t>
+          <t>Webhook addaan kutame</t>
         </is>
       </c>
       <c r="F165" s="12" t="inlineStr">
         <is>
-          <t>መሕለፊ ቃልኩም</t>
+          <t>ዌብሁክ ተቛሪጹ</t>
         </is>
       </c>
       <c r="G165" s="13" t="inlineStr">
         <is>
-          <t>Furahaaga sirta ah</t>
+          <t>Webhook waa la goynay</t>
         </is>
       </c>
       <c r="H165" s="13" t="inlineStr">
         <is>
-          <t>Nenosiri Lako</t>
+          <t>Wavuti Imekatishwa</t>
         </is>
       </c>
       <c r="I165" s="14" t="inlineStr"/>
@@ -13340,7 +13340,7 @@
     <row r="166" ht="44" customHeight="1">
       <c r="A166" s="11" t="inlineStr">
         <is>
-          <t>current_password</t>
+          <t>your_password</t>
         </is>
       </c>
       <c r="B166" s="11" t="inlineStr">
@@ -13350,32 +13350,32 @@
       </c>
       <c r="C166" s="11" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Your password</t>
         </is>
       </c>
       <c r="D166" s="12" t="inlineStr">
         <is>
-          <t>አሁን ያለው</t>
+          <t>የይለፍ ቃልዎ</t>
         </is>
       </c>
       <c r="E166" s="13" t="inlineStr">
         <is>
-          <t>Kan ammaa</t>
+          <t>Jecha darbii keessan</t>
         </is>
       </c>
       <c r="F166" s="12" t="inlineStr">
         <is>
-          <t>ናይ ሕጂ</t>
+          <t>መሕለፊ ቃልኩም</t>
         </is>
       </c>
       <c r="G166" s="13" t="inlineStr">
         <is>
-          <t>Kan hadda</t>
+          <t>Furahaaga sirta ah</t>
         </is>
       </c>
       <c r="H166" s="13" t="inlineStr">
         <is>
-          <t>La Sasa</t>
+          <t>Nenosiri Lako</t>
         </is>
       </c>
       <c r="I166" s="14" t="inlineStr"/>
@@ -13383,7 +13383,7 @@
     <row r="167" ht="44" customHeight="1">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>new_password_12</t>
+          <t>current_password</t>
         </is>
       </c>
       <c r="B167" s="11" t="inlineStr">
@@ -13393,32 +13393,32 @@
       </c>
       <c r="C167" s="11" t="inlineStr">
         <is>
-          <t>New (12+ characters)</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>አዲስ (12+ ቁምፊዎች)</t>
+          <t>አሁን ያለው</t>
         </is>
       </c>
       <c r="E167" s="13" t="inlineStr">
         <is>
-          <t>Haaraa (arfiilee 12+)</t>
+          <t>Kan ammaa</t>
         </is>
       </c>
       <c r="F167" s="12" t="inlineStr">
         <is>
-          <t>ሓድሽ (12+ ፊደላት)</t>
+          <t>ናይ ሕጂ</t>
         </is>
       </c>
       <c r="G167" s="13" t="inlineStr">
         <is>
-          <t>Cusub (12+ xaraf)</t>
+          <t>Kan hadda</t>
         </is>
       </c>
       <c r="H167" s="13" t="inlineStr">
         <is>
-          <t>Jipya (herufi 12+)</t>
+          <t>La Sasa</t>
         </is>
       </c>
       <c r="I167" s="14" t="inlineStr"/>
@@ -13426,7 +13426,7 @@
     <row r="168" ht="44" customHeight="1">
       <c r="A168" s="11" t="inlineStr">
         <is>
-          <t>password_change_help</t>
+          <t>new_password_12</t>
         </is>
       </c>
       <c r="B168" s="11" t="inlineStr">
@@ -13436,32 +13436,32 @@
       </c>
       <c r="C168" s="11" t="inlineStr">
         <is>
-          <t>Changing it signs out every other browser you are signed in on.</t>
+          <t>New (12+ characters)</t>
         </is>
       </c>
       <c r="D168" s="12" t="inlineStr">
         <is>
-          <t>መቀየር በገቡበት በሌላ በእያንዳንዱ አሳሽ ላይ ያስወጣዎታል።</t>
+          <t>አዲስ (12+ ቁምፊዎች)</t>
         </is>
       </c>
       <c r="E168" s="13" t="inlineStr">
         <is>
-          <t>Jijjiiruun biraawzarii biroo isin keessa seentan hunda irraa isin baasa.</t>
+          <t>Haaraa (arfiilee 12+)</t>
         </is>
       </c>
       <c r="F168" s="12" t="inlineStr">
         <is>
-          <t>ምቕያሩ ኣብ ካልእ ዝኣተኹምሉ ኩሉ መርበብ መንሸራተቲ የውጽኣኩም።</t>
+          <t>ሓድሽ (12+ ፊደላት)</t>
         </is>
       </c>
       <c r="G168" s="13" t="inlineStr">
         <is>
-          <t>Beddelkeedu wuxuu kaa saarayaa dhammaan browser-yada kale ee aad ku jirto.</t>
+          <t>Cusub (12+ xaraf)</t>
         </is>
       </c>
       <c r="H168" s="13" t="inlineStr">
         <is>
-          <t>Kulibadilisha kunamtoa kila kivinjari kingine ulichoingia.</t>
+          <t>Jipya (herufi 12+)</t>
         </is>
       </c>
       <c r="I168" s="14" t="inlineStr"/>
@@ -13469,7 +13469,7 @@
     <row r="169" ht="44" customHeight="1">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>change_password</t>
+          <t>password_change_help</t>
         </is>
       </c>
       <c r="B169" s="11" t="inlineStr">
@@ -13479,32 +13479,32 @@
       </c>
       <c r="C169" s="11" t="inlineStr">
         <is>
-          <t>Change password</t>
+          <t>Changing it signs out every other browser you are signed in on.</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>የይለፍ ቃል ቀይር</t>
+          <t>መቀየር በገቡበት በሌላ በእያንዳንዱ አሳሽ ላይ ያስወጣዎታል።</t>
         </is>
       </c>
       <c r="E169" s="13" t="inlineStr">
         <is>
-          <t>Jecha darbii jijjiiri</t>
+          <t>Jijjiiruun biraawzarii biroo isin keessa seentan hunda irraa isin baasa.</t>
         </is>
       </c>
       <c r="F169" s="12" t="inlineStr">
         <is>
-          <t>መሕለፊ ቃል ቀይር</t>
+          <t>ምቕያሩ ኣብ ካልእ ዝኣተኹምሉ ኩሉ መርበብ መንሸራተቲ የውጽኣኩም።</t>
         </is>
       </c>
       <c r="G169" s="13" t="inlineStr">
         <is>
-          <t>Bedel furaha sirta ah</t>
+          <t>Beddelkeedu wuxuu kaa saarayaa dhammaan browser-yada kale ee aad ku jirto.</t>
         </is>
       </c>
       <c r="H169" s="13" t="inlineStr">
         <is>
-          <t>Badilisha Nenosiri</t>
+          <t>Kulibadilisha kunamtoa kila kivinjari kingine ulichoingia.</t>
         </is>
       </c>
       <c r="I169" s="14" t="inlineStr"/>
@@ -13512,7 +13512,7 @@
     <row r="170" ht="44" customHeight="1">
       <c r="A170" s="11" t="inlineStr">
         <is>
-          <t>password_changed</t>
+          <t>change_password</t>
         </is>
       </c>
       <c r="B170" s="11" t="inlineStr">
@@ -13522,32 +13522,32 @@
       </c>
       <c r="C170" s="11" t="inlineStr">
         <is>
-          <t>Password changed. Other sessions were signed out.</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="D170" s="12" t="inlineStr">
         <is>
-          <t>የይለፍ ቃል ተቀይሯል። ሌሎች ክፍለ-ጊዜዎች ወጥተዋል።</t>
+          <t>የይለፍ ቃል ቀይር</t>
         </is>
       </c>
       <c r="E170" s="13" t="inlineStr">
         <is>
-          <t>Jechi darbii jijjiirameera. Sessionoonni biroo ba'aniiru.</t>
+          <t>Jecha darbii jijjiiri</t>
         </is>
       </c>
       <c r="F170" s="12" t="inlineStr">
         <is>
-          <t>መሕለፊ ቃል ተቐዪሩ። ካልኦት ክፍለ-ግዜታት ወጺኦም።</t>
+          <t>መሕለፊ ቃል ቀይር</t>
         </is>
       </c>
       <c r="G170" s="13" t="inlineStr">
         <is>
-          <t>Furaha sirta ah waa la beddelay. Kalfadhiyada kale waa laga saaray.</t>
+          <t>Bedel furaha sirta ah</t>
         </is>
       </c>
       <c r="H170" s="13" t="inlineStr">
         <is>
-          <t>Nenosiri Limebadilishwa. Vikao vingine vimetolewa.</t>
+          <t>Badilisha Nenosiri</t>
         </is>
       </c>
       <c r="I170" s="14" t="inlineStr"/>
@@ -13555,7 +13555,7 @@
     <row r="171" ht="44" customHeight="1">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>add_person</t>
+          <t>password_changed</t>
         </is>
       </c>
       <c r="B171" s="11" t="inlineStr">
@@ -13565,32 +13565,32 @@
       </c>
       <c r="C171" s="11" t="inlineStr">
         <is>
-          <t>Add person</t>
+          <t>Password changed. Other sessions were signed out.</t>
         </is>
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>ሰው ጨምር</t>
+          <t>የይለፍ ቃል ተቀይሯል። ሌሎች ክፍለ-ጊዜዎች ወጥተዋል።</t>
         </is>
       </c>
       <c r="E171" s="13" t="inlineStr">
         <is>
-          <t>Nama dabali</t>
+          <t>Jechi darbii jijjiirameera. Sessionoonni biroo ba'aniiru.</t>
         </is>
       </c>
       <c r="F171" s="12" t="inlineStr">
         <is>
-          <t>ሰብ ወስኽ</t>
+          <t>መሕለፊ ቃል ተቐዪሩ። ካልኦት ክፍለ-ግዜታት ወጺኦም።</t>
         </is>
       </c>
       <c r="G171" s="13" t="inlineStr">
         <is>
-          <t>Ku dar qof</t>
+          <t>Furaha sirta ah waa la beddelay. Kalfadhiyada kale waa laga saaray.</t>
         </is>
       </c>
       <c r="H171" s="13" t="inlineStr">
         <is>
-          <t>Ongeza Mtu</t>
+          <t>Nenosiri Limebadilishwa. Vikao vingine vimetolewa.</t>
         </is>
       </c>
       <c r="I171" s="14" t="inlineStr"/>
@@ -13598,7 +13598,7 @@
     <row r="172" ht="44" customHeight="1">
       <c r="A172" s="11" t="inlineStr">
         <is>
-          <t>n_accounts</t>
+          <t>add_person</t>
         </is>
       </c>
       <c r="B172" s="11" t="inlineStr">
@@ -13608,32 +13608,32 @@
       </c>
       <c r="C172" s="11" t="inlineStr">
         <is>
-          <t>{n} accounts</t>
+          <t>Add person</t>
         </is>
       </c>
       <c r="D172" s="12" t="inlineStr">
         <is>
-          <t>{n} መለያዎች</t>
+          <t>ሰው ጨምር</t>
         </is>
       </c>
       <c r="E172" s="13" t="inlineStr">
         <is>
-          <t>Herregoota {n}</t>
+          <t>Nama dabali</t>
         </is>
       </c>
       <c r="F172" s="12" t="inlineStr">
         <is>
-          <t>{n} ሕሳባት</t>
+          <t>ሰብ ወስኽ</t>
         </is>
       </c>
       <c r="G172" s="13" t="inlineStr">
         <is>
-          <t>{n} xisaabood</t>
+          <t>Ku dar qof</t>
         </is>
       </c>
       <c r="H172" s="13" t="inlineStr">
         <is>
-          <t>Akaunti {n}</t>
+          <t>Ongeza Mtu</t>
         </is>
       </c>
       <c r="I172" s="14" t="inlineStr"/>
@@ -13641,7 +13641,7 @@
     <row r="173" ht="44" customHeight="1">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>one_account</t>
+          <t>n_accounts</t>
         </is>
       </c>
       <c r="B173" s="11" t="inlineStr">
@@ -13651,27 +13651,27 @@
       </c>
       <c r="C173" s="11" t="inlineStr">
         <is>
-          <t>{n} account</t>
+          <t>{n} accounts</t>
         </is>
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>{n} መለያ</t>
+          <t>{n} መለያዎች</t>
         </is>
       </c>
       <c r="E173" s="13" t="inlineStr">
         <is>
-          <t>Herrega {n}</t>
+          <t>Herregoota {n}</t>
         </is>
       </c>
       <c r="F173" s="12" t="inlineStr">
         <is>
-          <t>{n} ሕሳብ</t>
+          <t>{n} ሕሳባት</t>
         </is>
       </c>
       <c r="G173" s="13" t="inlineStr">
         <is>
-          <t>{n} xisaab</t>
+          <t>{n} xisaabood</t>
         </is>
       </c>
       <c r="H173" s="13" t="inlineStr">
@@ -13684,7 +13684,7 @@
     <row r="174" ht="44" customHeight="1">
       <c r="A174" s="11" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>one_account</t>
         </is>
       </c>
       <c r="B174" s="11" t="inlineStr">
@@ -13694,32 +13694,32 @@
       </c>
       <c r="C174" s="11" t="inlineStr">
         <is>
-          <t>Person</t>
+          <t>{n} account</t>
         </is>
       </c>
       <c r="D174" s="12" t="inlineStr">
         <is>
-          <t>ሰው</t>
+          <t>{n} መለያ</t>
         </is>
       </c>
       <c r="E174" s="13" t="inlineStr">
         <is>
-          <t>Nama</t>
+          <t>Herrega {n}</t>
         </is>
       </c>
       <c r="F174" s="12" t="inlineStr">
         <is>
-          <t>ሰብ</t>
+          <t>{n} ሕሳብ</t>
         </is>
       </c>
       <c r="G174" s="13" t="inlineStr">
         <is>
-          <t>Qof</t>
+          <t>{n} xisaab</t>
         </is>
       </c>
       <c r="H174" s="13" t="inlineStr">
         <is>
-          <t>Mtu</t>
+          <t>Akaunti {n}</t>
         </is>
       </c>
       <c r="I174" s="14" t="inlineStr"/>
@@ -13727,7 +13727,7 @@
     <row r="175" ht="44" customHeight="1">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>person</t>
         </is>
       </c>
       <c r="B175" s="11" t="inlineStr">
@@ -13737,32 +13737,32 @@
       </c>
       <c r="C175" s="11" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Person</t>
         </is>
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>ሚና</t>
+          <t>ሰው</t>
         </is>
       </c>
       <c r="E175" s="13" t="inlineStr">
         <is>
-          <t>Gahee</t>
+          <t>Nama</t>
         </is>
       </c>
       <c r="F175" s="12" t="inlineStr">
         <is>
-          <t>ግደ</t>
+          <t>ሰብ</t>
         </is>
       </c>
       <c r="G175" s="13" t="inlineStr">
         <is>
-          <t>Doorka</t>
+          <t>Qof</t>
         </is>
       </c>
       <c r="H175" s="13" t="inlineStr">
         <is>
-          <t>Wadhifa</t>
+          <t>Mtu</t>
         </is>
       </c>
       <c r="I175" s="14" t="inlineStr"/>
@@ -13770,7 +13770,7 @@
     <row r="176" ht="44" customHeight="1">
       <c r="A176" s="11" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>role</t>
         </is>
       </c>
       <c r="B176" s="11" t="inlineStr">
@@ -13780,32 +13780,32 @@
       </c>
       <c r="C176" s="11" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="D176" s="12" t="inlineStr">
         <is>
-          <t>ሁኔታ</t>
+          <t>ሚና</t>
         </is>
       </c>
       <c r="E176" s="13" t="inlineStr">
         <is>
-          <t>Haala</t>
+          <t>Gahee</t>
         </is>
       </c>
       <c r="F176" s="12" t="inlineStr">
         <is>
-          <t>ኩነታት</t>
+          <t>ግደ</t>
         </is>
       </c>
       <c r="G176" s="13" t="inlineStr">
         <is>
-          <t>Xaalada</t>
+          <t>Doorka</t>
         </is>
       </c>
       <c r="H176" s="13" t="inlineStr">
         <is>
-          <t>Hali</t>
+          <t>Wadhifa</t>
         </is>
       </c>
       <c r="I176" s="14" t="inlineStr"/>
@@ -13813,7 +13813,7 @@
     <row r="177" ht="44" customHeight="1">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>last_signed_in</t>
+          <t>status</t>
         </is>
       </c>
       <c r="B177" s="11" t="inlineStr">
@@ -13823,32 +13823,32 @@
       </c>
       <c r="C177" s="11" t="inlineStr">
         <is>
-          <t>Last signed in</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>መጨረሻ የገቡበት</t>
+          <t>ሁኔታ</t>
         </is>
       </c>
       <c r="E177" s="13" t="inlineStr">
         <is>
-          <t>Yeroo dhumaa seenan</t>
+          <t>Haala</t>
         </is>
       </c>
       <c r="F177" s="12" t="inlineStr">
         <is>
-          <t>ናይ መወዳእታ ዝኣተዉሉ</t>
+          <t>ኩነታት</t>
         </is>
       </c>
       <c r="G177" s="13" t="inlineStr">
         <is>
-          <t>Markii ugu dambeysay ee la galay</t>
+          <t>Xaalada</t>
         </is>
       </c>
       <c r="H177" s="13" t="inlineStr">
         <is>
-          <t>Aliingia Mwisho</t>
+          <t>Hali</t>
         </is>
       </c>
       <c r="I177" s="14" t="inlineStr"/>
@@ -13856,7 +13856,7 @@
     <row r="178" ht="44" customHeight="1">
       <c r="A178" s="11" t="inlineStr">
         <is>
-          <t>actions</t>
+          <t>last_signed_in</t>
         </is>
       </c>
       <c r="B178" s="11" t="inlineStr">
@@ -13866,32 +13866,32 @@
       </c>
       <c r="C178" s="11" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Last signed in</t>
         </is>
       </c>
       <c r="D178" s="12" t="inlineStr">
         <is>
-          <t>ድርጊቶች</t>
+          <t>መጨረሻ የገቡበት</t>
         </is>
       </c>
       <c r="E178" s="13" t="inlineStr">
         <is>
-          <t>Gochaalee</t>
+          <t>Yeroo dhumaa seenan</t>
         </is>
       </c>
       <c r="F178" s="12" t="inlineStr">
         <is>
-          <t>ተግባራት</t>
+          <t>ናይ መወዳእታ ዝኣተዉሉ</t>
         </is>
       </c>
       <c r="G178" s="13" t="inlineStr">
         <is>
-          <t>Ficillo</t>
+          <t>Markii ugu dambeysay ee la galay</t>
         </is>
       </c>
       <c r="H178" s="13" t="inlineStr">
         <is>
-          <t>Vitendo</t>
+          <t>Aliingia Mwisho</t>
         </is>
       </c>
       <c r="I178" s="14" t="inlineStr"/>
@@ -13899,7 +13899,7 @@
     <row r="179" ht="44" customHeight="1">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>thats_you</t>
+          <t>actions</t>
         </is>
       </c>
       <c r="B179" s="11" t="inlineStr">
@@ -13909,32 +13909,32 @@
       </c>
       <c r="C179" s="11" t="inlineStr">
         <is>
-          <t>that’s you</t>
+          <t>Actions</t>
         </is>
       </c>
       <c r="D179" s="12" t="inlineStr">
         <is>
-          <t>ይህ እርስዎ ነዎት</t>
+          <t>ድርጊቶች</t>
         </is>
       </c>
       <c r="E179" s="13" t="inlineStr">
         <is>
-          <t>kun isinuma</t>
+          <t>Gochaalee</t>
         </is>
       </c>
       <c r="F179" s="12" t="inlineStr">
         <is>
-          <t>እዚ ንስኹም ኢኹም</t>
+          <t>ተግባራት</t>
         </is>
       </c>
       <c r="G179" s="13" t="inlineStr">
         <is>
-          <t>kaasi waa adiga</t>
+          <t>Ficillo</t>
         </is>
       </c>
       <c r="H179" s="13" t="inlineStr">
         <is>
-          <t>huyo ni wewe</t>
+          <t>Vitendo</t>
         </is>
       </c>
       <c r="I179" s="14" t="inlineStr"/>
@@ -13942,7 +13942,7 @@
     <row r="180" ht="44" customHeight="1">
       <c r="A180" s="11" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>thats_you</t>
         </is>
       </c>
       <c r="B180" s="11" t="inlineStr">
@@ -13952,32 +13952,32 @@
       </c>
       <c r="C180" s="11" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>that’s you</t>
         </is>
       </c>
       <c r="D180" s="12" t="inlineStr">
         <is>
-          <t>ንቁ</t>
+          <t>ይህ እርስዎ ነዎት</t>
         </is>
       </c>
       <c r="E180" s="13" t="inlineStr">
         <is>
-          <t>Ka'aa</t>
+          <t>kun isinuma</t>
         </is>
       </c>
       <c r="F180" s="12" t="inlineStr">
         <is>
-          <t>ንጡፍ</t>
+          <t>እዚ ንስኹም ኢኹም</t>
         </is>
       </c>
       <c r="G180" s="13" t="inlineStr">
         <is>
-          <t>Firfircoon</t>
+          <t>kaasi waa adiga</t>
         </is>
       </c>
       <c r="H180" s="13" t="inlineStr">
         <is>
-          <t>Hai</t>
+          <t>huyo ni wewe</t>
         </is>
       </c>
       <c r="I180" s="14" t="inlineStr"/>
@@ -13985,7 +13985,7 @@
     <row r="181" ht="44" customHeight="1">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t>disabled</t>
+          <t>active</t>
         </is>
       </c>
       <c r="B181" s="11" t="inlineStr">
@@ -13995,32 +13995,32 @@
       </c>
       <c r="C181" s="11" t="inlineStr">
         <is>
-          <t>Disabled</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>የተሰናከለ</t>
+          <t>ንቁ</t>
         </is>
       </c>
       <c r="E181" s="13" t="inlineStr">
         <is>
-          <t>Kan dhaabame</t>
+          <t>Ka'aa</t>
         </is>
       </c>
       <c r="F181" s="12" t="inlineStr">
         <is>
-          <t>ዝተዓገተ</t>
+          <t>ንጡፍ</t>
         </is>
       </c>
       <c r="G181" s="13" t="inlineStr">
         <is>
-          <t>La demiyay</t>
+          <t>Firfircoon</t>
         </is>
       </c>
       <c r="H181" s="13" t="inlineStr">
         <is>
-          <t>Imezimwa</t>
+          <t>Hai</t>
         </is>
       </c>
       <c r="I181" s="14" t="inlineStr"/>
@@ -14028,7 +14028,7 @@
     <row r="182" ht="44" customHeight="1">
       <c r="A182" s="11" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>disabled</t>
         </is>
       </c>
       <c r="B182" s="11" t="inlineStr">
@@ -14038,32 +14038,32 @@
       </c>
       <c r="C182" s="11" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>Disabled</t>
         </is>
       </c>
       <c r="D182" s="12" t="inlineStr">
         <is>
-          <t>በጭራሽ</t>
+          <t>የተሰናከለ</t>
         </is>
       </c>
       <c r="E182" s="13" t="inlineStr">
         <is>
-          <t>gonkumaa</t>
+          <t>Kan dhaabame</t>
         </is>
       </c>
       <c r="F182" s="12" t="inlineStr">
         <is>
-          <t>ፈጺሙ</t>
+          <t>ዝተዓገተ</t>
         </is>
       </c>
       <c r="G182" s="13" t="inlineStr">
         <is>
-          <t>waligeed</t>
+          <t>La demiyay</t>
         </is>
       </c>
       <c r="H182" s="13" t="inlineStr">
         <is>
-          <t>kamwe</t>
+          <t>Imezimwa</t>
         </is>
       </c>
       <c r="I182" s="14" t="inlineStr"/>
@@ -14071,7 +14071,7 @@
     <row r="183" ht="44" customHeight="1">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t>disable</t>
+          <t>never</t>
         </is>
       </c>
       <c r="B183" s="11" t="inlineStr">
@@ -14081,32 +14081,32 @@
       </c>
       <c r="C183" s="11" t="inlineStr">
         <is>
-          <t>Disable</t>
+          <t>never</t>
         </is>
       </c>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>አሰናክል</t>
+          <t>በጭራሽ</t>
         </is>
       </c>
       <c r="E183" s="13" t="inlineStr">
         <is>
-          <t>Dhaabi</t>
+          <t>gonkumaa</t>
         </is>
       </c>
       <c r="F183" s="12" t="inlineStr">
         <is>
-          <t>ዓግት</t>
+          <t>ፈጺሙ</t>
         </is>
       </c>
       <c r="G183" s="13" t="inlineStr">
         <is>
-          <t>Demi</t>
+          <t>waligeed</t>
         </is>
       </c>
       <c r="H183" s="13" t="inlineStr">
         <is>
-          <t>Zima</t>
+          <t>kamwe</t>
         </is>
       </c>
       <c r="I183" s="14" t="inlineStr"/>
@@ -14114,7 +14114,7 @@
     <row r="184" ht="44" customHeight="1">
       <c r="A184" s="11" t="inlineStr">
         <is>
-          <t>restore</t>
+          <t>disable</t>
         </is>
       </c>
       <c r="B184" s="11" t="inlineStr">
@@ -14124,32 +14124,32 @@
       </c>
       <c r="C184" s="11" t="inlineStr">
         <is>
-          <t>Restore</t>
+          <t>Disable</t>
         </is>
       </c>
       <c r="D184" s="12" t="inlineStr">
         <is>
-          <t>መልስ</t>
+          <t>አሰናክል</t>
         </is>
       </c>
       <c r="E184" s="13" t="inlineStr">
         <is>
-          <t>Deebisi</t>
+          <t>Dhaabi</t>
         </is>
       </c>
       <c r="F184" s="12" t="inlineStr">
         <is>
-          <t>መልስ</t>
+          <t>ዓግት</t>
         </is>
       </c>
       <c r="G184" s="13" t="inlineStr">
         <is>
-          <t>Soo celi</t>
+          <t>Demi</t>
         </is>
       </c>
       <c r="H184" s="13" t="inlineStr">
         <is>
-          <t>Rejesha</t>
+          <t>Zima</t>
         </is>
       </c>
       <c r="I184" s="14" t="inlineStr"/>
@@ -14157,7 +14157,7 @@
     <row r="185" ht="44" customHeight="1">
       <c r="A185" s="11" t="inlineStr">
         <is>
-          <t>what_each_role_can_do</t>
+          <t>restore</t>
         </is>
       </c>
       <c r="B185" s="11" t="inlineStr">
@@ -14167,32 +14167,32 @@
       </c>
       <c r="C185" s="11" t="inlineStr">
         <is>
-          <t>What each role can do</t>
+          <t>Restore</t>
         </is>
       </c>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>እያንዳንዱ ሚና ምን ማድረግ ይችላል</t>
+          <t>መልስ</t>
         </is>
       </c>
       <c r="E185" s="13" t="inlineStr">
         <is>
-          <t>Gaheen tokkoon tokkoon isaanii maal gochuu danda'a</t>
+          <t>Deebisi</t>
         </is>
       </c>
       <c r="F185" s="12" t="inlineStr">
         <is>
-          <t>ነፍስ ወከፍ ግደ እንታይ ክገብር ይኽእል</t>
+          <t>መልስ</t>
         </is>
       </c>
       <c r="G185" s="13" t="inlineStr">
         <is>
-          <t>Waxa doorkiiba uu samayn karo</t>
+          <t>Soo celi</t>
         </is>
       </c>
       <c r="H185" s="13" t="inlineStr">
         <is>
-          <t>Kila Wadhifa Unaweza Kufanya Nini</t>
+          <t>Rejesha</t>
         </is>
       </c>
       <c r="I185" s="14" t="inlineStr"/>
@@ -14200,7 +14200,7 @@
     <row r="186" ht="44" customHeight="1">
       <c r="A186" s="11" t="inlineStr">
         <is>
-          <t>calls_per_teller</t>
+          <t>what_each_role_can_do</t>
         </is>
       </c>
       <c r="B186" s="11" t="inlineStr">
@@ -14210,32 +14210,32 @@
       </c>
       <c r="C186" s="11" t="inlineStr">
         <is>
-          <t>Calls per teller</t>
+          <t>What each role can do</t>
         </is>
       </c>
       <c r="D186" s="12" t="inlineStr">
         <is>
-          <t>በተጠሪ የተያዙ ጥሪዎች</t>
+          <t>እያንዳንዱ ሚና ምን ማድረግ ይችላል</t>
         </is>
       </c>
       <c r="E186" s="13" t="inlineStr">
         <is>
-          <t>Bilbilawwan teellaraan</t>
+          <t>Gaheen tokkoon tokkoon isaanii maal gochuu danda'a</t>
         </is>
       </c>
       <c r="F186" s="12" t="inlineStr">
         <is>
-          <t>ጻውዒታት ብተለር</t>
+          <t>ነፍስ ወከፍ ግደ እንታይ ክገብር ይኽእል</t>
         </is>
       </c>
       <c r="G186" s="13" t="inlineStr">
         <is>
-          <t>Wicitaanka teller kasta</t>
+          <t>Waxa doorkiiba uu samayn karo</t>
         </is>
       </c>
       <c r="H186" s="13" t="inlineStr">
         <is>
-          <t>Simu kwa Kila Afisa</t>
+          <t>Kila Wadhifa Unaweza Kufanya Nini</t>
         </is>
       </c>
       <c r="I186" s="14" t="inlineStr"/>
@@ -14243,7 +14243,7 @@
     <row r="187" ht="44" customHeight="1">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t>unit_calls</t>
+          <t>calls_per_teller</t>
         </is>
       </c>
       <c r="B187" s="11" t="inlineStr">
@@ -14253,32 +14253,32 @@
       </c>
       <c r="C187" s="11" t="inlineStr">
         <is>
-          <t>calls</t>
+          <t>Calls per teller</t>
         </is>
       </c>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>ጥሪዎች</t>
+          <t>በተጠሪ የተያዙ ጥሪዎች</t>
         </is>
       </c>
       <c r="E187" s="13" t="inlineStr">
         <is>
-          <t>bilbilawwan</t>
+          <t>Bilbilawwan teellaraan</t>
         </is>
       </c>
       <c r="F187" s="12" t="inlineStr">
         <is>
-          <t>ጻውዒታት</t>
+          <t>ጻውዒታት ብተለር</t>
         </is>
       </c>
       <c r="G187" s="13" t="inlineStr">
         <is>
-          <t>wicitaanno</t>
+          <t>Wicitaanka teller kasta</t>
         </is>
       </c>
       <c r="H187" s="13" t="inlineStr">
         <is>
-          <t>simu</t>
+          <t>Simu kwa Kila Afisa</t>
         </is>
       </c>
       <c r="I187" s="14" t="inlineStr"/>
@@ -14286,7 +14286,7 @@
     <row r="188" ht="44" customHeight="1">
       <c r="A188" s="11" t="inlineStr">
         <is>
-          <t>unit_call</t>
+          <t>unit_calls</t>
         </is>
       </c>
       <c r="B188" s="11" t="inlineStr">
@@ -14296,27 +14296,27 @@
       </c>
       <c r="C188" s="11" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>calls</t>
         </is>
       </c>
       <c r="D188" s="12" t="inlineStr">
         <is>
-          <t>ጥሪ</t>
+          <t>ጥሪዎች</t>
         </is>
       </c>
       <c r="E188" s="13" t="inlineStr">
         <is>
-          <t>bilbila</t>
+          <t>bilbilawwan</t>
         </is>
       </c>
       <c r="F188" s="12" t="inlineStr">
         <is>
-          <t>ጻውዒት</t>
+          <t>ጻውዒታት</t>
         </is>
       </c>
       <c r="G188" s="13" t="inlineStr">
         <is>
-          <t>wicitaan</t>
+          <t>wicitaanno</t>
         </is>
       </c>
       <c r="H188" s="13" t="inlineStr">
@@ -14329,7 +14329,7 @@
     <row r="189" ht="44" customHeight="1">
       <c r="A189" s="11" t="inlineStr">
         <is>
-          <t>no_calls_taken_yet</t>
+          <t>unit_call</t>
         </is>
       </c>
       <c r="B189" s="11" t="inlineStr">
@@ -14339,32 +14339,32 @@
       </c>
       <c r="C189" s="11" t="inlineStr">
         <is>
-          <t>Nobody has taken a call yet in this window.</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>በዚህ ጊዜ ውስጥ ማንም ጥሪ አልያዘም።</t>
+          <t>ጥሪ</t>
         </is>
       </c>
       <c r="E189" s="13" t="inlineStr">
         <is>
-          <t>Yeroo kana keessatti namni bilbila fudhate hin jiru.</t>
+          <t>bilbila</t>
         </is>
       </c>
       <c r="F189" s="12" t="inlineStr">
         <is>
-          <t>ኣብዚ እዋን'ዚ ዝሓዘ ጻውዒት የለን።</t>
+          <t>ጻውዒት</t>
         </is>
       </c>
       <c r="G189" s="13" t="inlineStr">
         <is>
-          <t>Cidina ma qaadan wicitaan waqtigan.</t>
+          <t>wicitaan</t>
         </is>
       </c>
       <c r="H189" s="13" t="inlineStr">
         <is>
-          <t>Hakuna aliyepokea simu bado katika muda huu.</t>
+          <t>simu</t>
         </is>
       </c>
       <c r="I189" s="14" t="inlineStr"/>
@@ -14372,7 +14372,7 @@
     <row r="190" ht="44" customHeight="1">
       <c r="A190" s="11" t="inlineStr">
         <is>
-          <t>call_resolved</t>
+          <t>no_calls_taken_yet</t>
         </is>
       </c>
       <c r="B190" s="11" t="inlineStr">
@@ -14382,32 +14382,32 @@
       </c>
       <c r="C190" s="11" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Nobody has taken a call yet in this window.</t>
         </is>
       </c>
       <c r="D190" s="12" t="inlineStr">
         <is>
-          <t>ተፈትቷል</t>
+          <t>በዚህ ጊዜ ውስጥ ማንም ጥሪ አልያዘም።</t>
         </is>
       </c>
       <c r="E190" s="13" t="inlineStr">
         <is>
-          <t>Furameera</t>
+          <t>Yeroo kana keessatti namni bilbila fudhate hin jiru.</t>
         </is>
       </c>
       <c r="F190" s="12" t="inlineStr">
         <is>
-          <t>ተፈቲሑ</t>
+          <t>ኣብዚ እዋን'ዚ ዝሓዘ ጻውዒት የለን።</t>
         </is>
       </c>
       <c r="G190" s="13" t="inlineStr">
         <is>
-          <t>La xaliyay</t>
+          <t>Cidina ma qaadan wicitaan waqtigan.</t>
         </is>
       </c>
       <c r="H190" s="13" t="inlineStr">
         <is>
-          <t>Imetatuliwa</t>
+          <t>Hakuna aliyepokea simu bado katika muda huu.</t>
         </is>
       </c>
       <c r="I190" s="14" t="inlineStr"/>
@@ -14415,7 +14415,7 @@
     <row r="191" ht="44" customHeight="1">
       <c r="A191" s="11" t="inlineStr">
         <is>
-          <t>call_dropped</t>
+          <t>call_resolved</t>
         </is>
       </c>
       <c r="B191" s="11" t="inlineStr">
@@ -14425,32 +14425,32 @@
       </c>
       <c r="C191" s="11" t="inlineStr">
         <is>
-          <t>Dropped (technical issue)</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="D191" s="12" t="inlineStr">
         <is>
-          <t>ተቋርጧል (ቴክኒካዊ ችግር)</t>
+          <t>ተፈትቷል</t>
         </is>
       </c>
       <c r="E191" s="13" t="inlineStr">
         <is>
-          <t>Cite (rakkoo teekniikaa)</t>
+          <t>Furameera</t>
         </is>
       </c>
       <c r="F191" s="12" t="inlineStr">
         <is>
-          <t>ተቋሪጹ (ቴክኒካዊ ጸገም)</t>
+          <t>ተፈቲሑ</t>
         </is>
       </c>
       <c r="G191" s="13" t="inlineStr">
         <is>
-          <t>Wuu jabay (dhibaato farsamo)</t>
+          <t>La xaliyay</t>
         </is>
       </c>
       <c r="H191" s="13" t="inlineStr">
         <is>
-          <t>Imekatika (tatizo la kiufundi)</t>
+          <t>Imetatuliwa</t>
         </is>
       </c>
       <c r="I191" s="14" t="inlineStr"/>
@@ -14458,7 +14458,7 @@
     <row r="192" ht="44" customHeight="1">
       <c r="A192" s="11" t="inlineStr">
         <is>
-          <t>avg_wait_before_answering</t>
+          <t>call_dropped</t>
         </is>
       </c>
       <c r="B192" s="11" t="inlineStr">
@@ -14468,32 +14468,32 @@
       </c>
       <c r="C192" s="11" t="inlineStr">
         <is>
-          <t>Avg. wait before answering:</t>
+          <t>Dropped (technical issue)</t>
         </is>
       </c>
       <c r="D192" s="12" t="inlineStr">
         <is>
-          <t>ከመመለስ በፊት አማካይ የመጠበቅ ጊዜ፦</t>
+          <t>ተቋርጧል (ቴክኒካዊ ችግር)</t>
         </is>
       </c>
       <c r="E192" s="13" t="inlineStr">
         <is>
-          <t>Giddu-galeessa yeroo eegumsaa deebii dura:</t>
+          <t>Cite (rakkoo teekniikaa)</t>
         </is>
       </c>
       <c r="F192" s="12" t="inlineStr">
         <is>
-          <t>ማእከላይ ግዜ ምጽባይ ቅድሚ ምምላስ፦</t>
+          <t>ተቋሪጹ (ቴክኒካዊ ጸገም)</t>
         </is>
       </c>
       <c r="G192" s="13" t="inlineStr">
         <is>
-          <t>Celceliska sugitaanka ka hor jawaabta:</t>
+          <t>Wuu jabay (dhibaato farsamo)</t>
         </is>
       </c>
       <c r="H192" s="13" t="inlineStr">
         <is>
-          <t>Wastani wa kusubiri kabla ya kujibu:</t>
+          <t>Imekatika (tatizo la kiufundi)</t>
         </is>
       </c>
       <c r="I192" s="14" t="inlineStr"/>
@@ -14501,7 +14501,7 @@
     <row r="193" ht="44" customHeight="1">
       <c r="A193" s="11" t="inlineStr">
         <is>
-          <t>no_calls_yet_window</t>
+          <t>avg_wait_before_answering</t>
         </is>
       </c>
       <c r="B193" s="11" t="inlineStr">
@@ -14511,32 +14511,32 @@
       </c>
       <c r="C193" s="11" t="inlineStr">
         <is>
-          <t>No calls yet in this window.</t>
+          <t>Avg. wait before answering:</t>
         </is>
       </c>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>በዚህ ጊዜ ውስጥ ጥሪ የለም።</t>
+          <t>ከመመለስ በፊት አማካይ የመጠበቅ ጊዜ፦</t>
         </is>
       </c>
       <c r="E193" s="13" t="inlineStr">
         <is>
-          <t>Yeroo kana keessatti bilbilli hin jiru.</t>
+          <t>Giddu-galeessa yeroo eegumsaa deebii dura:</t>
         </is>
       </c>
       <c r="F193" s="12" t="inlineStr">
         <is>
-          <t>ኣብዚ እዋን'ዚ ጻውዒት የለን።</t>
+          <t>ማእከላይ ግዜ ምጽባይ ቅድሚ ምምላስ፦</t>
         </is>
       </c>
       <c r="G193" s="13" t="inlineStr">
         <is>
-          <t>Wicitaan lama helin waqtigan.</t>
+          <t>Celceliska sugitaanka ka hor jawaabta:</t>
         </is>
       </c>
       <c r="H193" s="13" t="inlineStr">
         <is>
-          <t>Hakuna simu bado katika muda huu.</t>
+          <t>Wastani wa kusubiri kabla ya kujibu:</t>
         </is>
       </c>
       <c r="I193" s="14" t="inlineStr"/>
@@ -14544,7 +14544,7 @@
     <row r="194" ht="44" customHeight="1">
       <c r="A194" s="11" t="inlineStr">
         <is>
-          <t>your_performance</t>
+          <t>no_calls_yet_window</t>
         </is>
       </c>
       <c r="B194" s="11" t="inlineStr">
@@ -14554,32 +14554,32 @@
       </c>
       <c r="C194" s="11" t="inlineStr">
         <is>
-          <t>Your performance</t>
+          <t>No calls yet in this window.</t>
         </is>
       </c>
       <c r="D194" s="12" t="inlineStr">
         <is>
-          <t>የእርስዎ አፈጻጸም</t>
+          <t>በዚህ ጊዜ ውስጥ ጥሪ የለም።</t>
         </is>
       </c>
       <c r="E194" s="13" t="inlineStr">
         <is>
-          <t>Hojii kee</t>
+          <t>Yeroo kana keessatti bilbilli hin jiru.</t>
         </is>
       </c>
       <c r="F194" s="12" t="inlineStr">
         <is>
-          <t>ኣፈጻጽማኻ</t>
+          <t>ኣብዚ እዋን'ዚ ጻውዒት የለን።</t>
         </is>
       </c>
       <c r="G194" s="13" t="inlineStr">
         <is>
-          <t>Waxqabadkaaga</t>
+          <t>Wicitaan lama helin waqtigan.</t>
         </is>
       </c>
       <c r="H194" s="13" t="inlineStr">
         <is>
-          <t>Utendaji Wako</t>
+          <t>Hakuna simu bado katika muda huu.</t>
         </is>
       </c>
       <c r="I194" s="14" t="inlineStr"/>
@@ -14587,7 +14587,7 @@
     <row r="195" ht="44" customHeight="1">
       <c r="A195" s="11" t="inlineStr">
         <is>
-          <t>n_other_tellers</t>
+          <t>your_performance</t>
         </is>
       </c>
       <c r="B195" s="11" t="inlineStr">
@@ -14597,32 +14597,32 @@
       </c>
       <c r="C195" s="11" t="inlineStr">
         <is>
-          <t>{n} other tellers</t>
+          <t>Your performance</t>
         </is>
       </c>
       <c r="D195" s="12" t="inlineStr">
         <is>
-          <t>{n} ሌሎች ተጠሪዎች</t>
+          <t>የእርስዎ አፈጻጸም</t>
         </is>
       </c>
       <c r="E195" s="13" t="inlineStr">
         <is>
-          <t>{n} teellaroota biroo</t>
+          <t>Hojii kee</t>
         </is>
       </c>
       <c r="F195" s="12" t="inlineStr">
         <is>
-          <t>{n} ካልኦት ተለራት</t>
+          <t>ኣፈጻጽማኻ</t>
         </is>
       </c>
       <c r="G195" s="13" t="inlineStr">
         <is>
-          <t>{n} teller oo kale</t>
+          <t>Waxqabadkaaga</t>
         </is>
       </c>
       <c r="H195" s="13" t="inlineStr">
         <is>
-          <t>Maafisa wengine {n}</t>
+          <t>Utendaji Wako</t>
         </is>
       </c>
       <c r="I195" s="14" t="inlineStr"/>
@@ -14630,7 +14630,7 @@
     <row r="196" ht="44" customHeight="1">
       <c r="A196" s="11" t="inlineStr">
         <is>
-          <t>built_in</t>
+          <t>n_other_tellers</t>
         </is>
       </c>
       <c r="B196" s="11" t="inlineStr">
@@ -14640,32 +14640,32 @@
       </c>
       <c r="C196" s="11" t="inlineStr">
         <is>
-          <t>built-in</t>
+          <t>{n} other tellers</t>
         </is>
       </c>
       <c r="D196" s="12" t="inlineStr">
         <is>
-          <t>አብሮ የተሰራ</t>
+          <t>{n} ሌሎች ተጠሪዎች</t>
         </is>
       </c>
       <c r="E196" s="13" t="inlineStr">
         <is>
-          <t>kan ijaarame</t>
+          <t>{n} teellaroota biroo</t>
         </is>
       </c>
       <c r="F196" s="12" t="inlineStr">
         <is>
-          <t>ውሁድ</t>
+          <t>{n} ካልኦት ተለራት</t>
         </is>
       </c>
       <c r="G196" s="13" t="inlineStr">
         <is>
-          <t>ku dhex jira</t>
+          <t>{n} teller oo kale</t>
         </is>
       </c>
       <c r="H196" s="13" t="inlineStr">
         <is>
-          <t>iliyojengwa ndani</t>
+          <t>Maafisa wengine {n}</t>
         </is>
       </c>
       <c r="I196" s="14" t="inlineStr"/>
@@ -14673,7 +14673,7 @@
     <row r="197" ht="44" customHeight="1">
       <c r="A197" s="11" t="inlineStr">
         <is>
-          <t>add_a_person</t>
+          <t>built_in</t>
         </is>
       </c>
       <c r="B197" s="11" t="inlineStr">
@@ -14683,32 +14683,32 @@
       </c>
       <c r="C197" s="11" t="inlineStr">
         <is>
-          <t>Add a person</t>
+          <t>built-in</t>
         </is>
       </c>
       <c r="D197" s="12" t="inlineStr">
         <is>
-          <t>ሰው ጨምር</t>
+          <t>አብሮ የተሰራ</t>
         </is>
       </c>
       <c r="E197" s="13" t="inlineStr">
         <is>
-          <t>Nama dabali</t>
+          <t>kan ijaarame</t>
         </is>
       </c>
       <c r="F197" s="12" t="inlineStr">
         <is>
-          <t>ሰብ ወስኽ</t>
+          <t>ውሁድ</t>
         </is>
       </c>
       <c r="G197" s="13" t="inlineStr">
         <is>
-          <t>Qof ku dar</t>
+          <t>ku dhex jira</t>
         </is>
       </c>
       <c r="H197" s="13" t="inlineStr">
         <is>
-          <t>Ongeza Mtu</t>
+          <t>iliyojengwa ndani</t>
         </is>
       </c>
       <c r="I197" s="14" t="inlineStr"/>
@@ -14716,7 +14716,7 @@
     <row r="198" ht="44" customHeight="1">
       <c r="A198" s="11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>add_a_person</t>
         </is>
       </c>
       <c r="B198" s="11" t="inlineStr">
@@ -14726,32 +14726,32 @@
       </c>
       <c r="C198" s="11" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Add a person</t>
         </is>
       </c>
       <c r="D198" s="12" t="inlineStr">
         <is>
-          <t>ኢሜይል</t>
+          <t>ሰው ጨምር</t>
         </is>
       </c>
       <c r="E198" s="13" t="inlineStr">
         <is>
-          <t>Imeelii</t>
+          <t>Nama dabali</t>
         </is>
       </c>
       <c r="F198" s="12" t="inlineStr">
         <is>
-          <t>ኢመይል</t>
+          <t>ሰብ ወስኽ</t>
         </is>
       </c>
       <c r="G198" s="13" t="inlineStr">
         <is>
-          <t>Iimayl</t>
+          <t>Qof ku dar</t>
         </is>
       </c>
       <c r="H198" s="13" t="inlineStr">
         <is>
-          <t>Barua Pepe</t>
+          <t>Ongeza Mtu</t>
         </is>
       </c>
       <c r="I198" s="14" t="inlineStr"/>
@@ -14759,7 +14759,7 @@
     <row r="199" ht="44" customHeight="1">
       <c r="A199" s="11" t="inlineStr">
         <is>
-          <t>name_optional</t>
+          <t>email</t>
         </is>
       </c>
       <c r="B199" s="11" t="inlineStr">
@@ -14769,32 +14769,32 @@
       </c>
       <c r="C199" s="11" t="inlineStr">
         <is>
-          <t>Name (optional)</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D199" s="12" t="inlineStr">
         <is>
-          <t>ስም (አማራጭ)</t>
+          <t>ኢሜይል</t>
         </is>
       </c>
       <c r="E199" s="13" t="inlineStr">
         <is>
-          <t>Maqaa (filannoo)</t>
+          <t>Imeelii</t>
         </is>
       </c>
       <c r="F199" s="12" t="inlineStr">
         <is>
-          <t>ስም (ኣማራጺ)</t>
+          <t>ኢመይል</t>
         </is>
       </c>
       <c r="G199" s="13" t="inlineStr">
         <is>
-          <t>Magac (ikhtiyaari)</t>
+          <t>Iimayl</t>
         </is>
       </c>
       <c r="H199" s="13" t="inlineStr">
         <is>
-          <t>Jina (si lazima)</t>
+          <t>Barua Pepe</t>
         </is>
       </c>
       <c r="I199" s="14" t="inlineStr"/>
@@ -14802,7 +14802,7 @@
     <row r="200" ht="44" customHeight="1">
       <c r="A200" s="11" t="inlineStr">
         <is>
-          <t>temporary_password</t>
+          <t>name_optional</t>
         </is>
       </c>
       <c r="B200" s="11" t="inlineStr">
@@ -14812,32 +14812,32 @@
       </c>
       <c r="C200" s="11" t="inlineStr">
         <is>
-          <t>Temporary password</t>
+          <t>Name (optional)</t>
         </is>
       </c>
       <c r="D200" s="12" t="inlineStr">
         <is>
-          <t>ጊዜያዊ የይለፍ ቃል</t>
+          <t>ስም (አማራጭ)</t>
         </is>
       </c>
       <c r="E200" s="13" t="inlineStr">
         <is>
-          <t>Jecha darbii yeroo</t>
+          <t>Maqaa (filannoo)</t>
         </is>
       </c>
       <c r="F200" s="12" t="inlineStr">
         <is>
-          <t>ግዝያዊ መሕለፊ ቃል</t>
+          <t>ስም (ኣማራጺ)</t>
         </is>
       </c>
       <c r="G200" s="13" t="inlineStr">
         <is>
-          <t>Fure ku meel gaar ah</t>
+          <t>Magac (ikhtiyaari)</t>
         </is>
       </c>
       <c r="H200" s="13" t="inlineStr">
         <is>
-          <t>Nenosiri la Muda</t>
+          <t>Jina (si lazima)</t>
         </is>
       </c>
       <c r="I200" s="14" t="inlineStr"/>
@@ -14845,7 +14845,7 @@
     <row r="201" ht="44" customHeight="1">
       <c r="A201" s="11" t="inlineStr">
         <is>
-          <t>temp_password_help</t>
+          <t>temporary_password</t>
         </is>
       </c>
       <c r="B201" s="11" t="inlineStr">
@@ -14855,32 +14855,32 @@
       </c>
       <c r="C201" s="11" t="inlineStr">
         <is>
-          <t>At least 12 characters. Until invitation emails are set up, this password has to be given to them directly — which is why it is shown here rather than hidden.</t>
+          <t>Temporary password</t>
         </is>
       </c>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>ቢያንስ 12 ቁምፊ። የግብዣ ኢሜይሎች እስኪዘጋጁ ድረስ ይህ የይለፍ ቃል በቀጥታ ሊሰጣቸው ይገባል — ስለዚህ ተደብቆ ሳይሆን እዚህ ይታያል።</t>
+          <t>ጊዜያዊ የይለፍ ቃል</t>
         </is>
       </c>
       <c r="E201" s="13" t="inlineStr">
         <is>
-          <t>Yoo xiqqaate arfiilee 12. Hanga imeeliin afeerraa qophaa'utti, jechi darbii kun kallattiin isaaniif kennamuu qaba — kanaafuu dhokfamuu mannaa asitti ni mul'ata.</t>
+          <t>Jecha darbii yeroo</t>
         </is>
       </c>
       <c r="F201" s="12" t="inlineStr">
         <is>
-          <t>ብውሑዱ 12 ፊደላት። መጸዋዕታ ኢመይል ክሳብ ዝዳሎ እዚ መሕለፊ ቃል ብቐጥታ ክወሃቦም ኣለዎ — ስለዚ ተሓቢኡ ዘይኮነ ኣብዚ ይረአ።</t>
+          <t>ግዝያዊ መሕለፊ ቃል</t>
         </is>
       </c>
       <c r="G201" s="13" t="inlineStr">
         <is>
-          <t>Ugu yaraan 12 xaraf. Ilaa iimaylada casumaadda la dejiyo, furahan si toos ah ayaa loo siin doonaa — sidaas darteed halkan ayuu ka muuqdaa halkii la qarin lahaa.</t>
+          <t>Fure ku meel gaar ah</t>
         </is>
       </c>
       <c r="H201" s="13" t="inlineStr">
         <is>
-          <t>Angalau herufi 12. Hadi barua pepe za mialiko zitakapowekwa, nenosiri hili linapaswa kupewa moja kwa moja — ndiyo maana linaonyeshwa hapa badala ya kufichwa.</t>
+          <t>Nenosiri la Muda</t>
         </is>
       </c>
       <c r="I201" s="14" t="inlineStr"/>
@@ -14888,7 +14888,7 @@
     <row r="202" ht="44" customHeight="1">
       <c r="A202" s="11" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>temp_password_help</t>
         </is>
       </c>
       <c r="B202" s="11" t="inlineStr">
@@ -14898,32 +14898,32 @@
       </c>
       <c r="C202" s="11" t="inlineStr">
         <is>
-          <t>Create</t>
+          <t>At least 12 characters. Until invitation emails are set up, this password has to be given to them directly — which is why it is shown here rather than hidden.</t>
         </is>
       </c>
       <c r="D202" s="12" t="inlineStr">
         <is>
-          <t>ፍጠር</t>
+          <t>ቢያንስ 12 ቁምፊ። የግብዣ ኢሜይሎች እስኪዘጋጁ ድረስ ይህ የይለፍ ቃል በቀጥታ ሊሰጣቸው ይገባል — ስለዚህ ተደብቆ ሳይሆን እዚህ ይታያል።</t>
         </is>
       </c>
       <c r="E202" s="13" t="inlineStr">
         <is>
-          <t>Uumi</t>
+          <t>Yoo xiqqaate arfiilee 12. Hanga imeeliin afeerraa qophaa'utti, jechi darbii kun kallattiin isaaniif kennamuu qaba — kanaafuu dhokfamuu mannaa asitti ni mul'ata.</t>
         </is>
       </c>
       <c r="F202" s="12" t="inlineStr">
         <is>
-          <t>ፍጠር</t>
+          <t>ብውሑዱ 12 ፊደላት። መጸዋዕታ ኢመይል ክሳብ ዝዳሎ እዚ መሕለፊ ቃል ብቐጥታ ክወሃቦም ኣለዎ — ስለዚ ተሓቢኡ ዘይኮነ ኣብዚ ይረአ።</t>
         </is>
       </c>
       <c r="G202" s="13" t="inlineStr">
         <is>
-          <t>Abuur</t>
+          <t>Ugu yaraan 12 xaraf. Ilaa iimaylada casumaadda la dejiyo, furahan si toos ah ayaa loo siin doonaa — sidaas darteed halkan ayuu ka muuqdaa halkii la qarin lahaa.</t>
         </is>
       </c>
       <c r="H202" s="13" t="inlineStr">
         <is>
-          <t>Unda</t>
+          <t>Angalau herufi 12. Hadi barua pepe za mialiko zitakapowekwa, nenosiri hili linapaswa kupewa moja kwa moja — ndiyo maana linaonyeshwa hapa badala ya kufichwa.</t>
         </is>
       </c>
       <c r="I202" s="14" t="inlineStr"/>
@@ -14931,7 +14931,7 @@
     <row r="203" ht="44" customHeight="1">
       <c r="A203" s="11" t="inlineStr">
         <is>
-          <t>account_created</t>
+          <t>create</t>
         </is>
       </c>
       <c r="B203" s="11" t="inlineStr">
@@ -14941,32 +14941,32 @@
       </c>
       <c r="C203" s="11" t="inlineStr">
         <is>
-          <t>Account created</t>
+          <t>Create</t>
         </is>
       </c>
       <c r="D203" s="12" t="inlineStr">
         <is>
-          <t>መለያ ተፈጥሯል</t>
+          <t>ፍጠር</t>
         </is>
       </c>
       <c r="E203" s="13" t="inlineStr">
         <is>
-          <t>Herregni uumame</t>
+          <t>Uumi</t>
         </is>
       </c>
       <c r="F203" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ ተፈጢሩ</t>
+          <t>ፍጠር</t>
         </is>
       </c>
       <c r="G203" s="13" t="inlineStr">
         <is>
-          <t>Xisaab waa la abuuray</t>
+          <t>Abuur</t>
         </is>
       </c>
       <c r="H203" s="13" t="inlineStr">
         <is>
-          <t>Akaunti Imeundwa</t>
+          <t>Unda</t>
         </is>
       </c>
       <c r="I203" s="14" t="inlineStr"/>
@@ -14974,7 +14974,7 @@
     <row r="204" ht="44" customHeight="1">
       <c r="A204" s="11" t="inlineStr">
         <is>
-          <t>account_restored</t>
+          <t>account_created</t>
         </is>
       </c>
       <c r="B204" s="11" t="inlineStr">
@@ -14984,32 +14984,32 @@
       </c>
       <c r="C204" s="11" t="inlineStr">
         <is>
-          <t>Account restored</t>
+          <t>Account created</t>
         </is>
       </c>
       <c r="D204" s="12" t="inlineStr">
         <is>
-          <t>መለያ ተመልሷል</t>
+          <t>መለያ ተፈጥሯል</t>
         </is>
       </c>
       <c r="E204" s="13" t="inlineStr">
         <is>
-          <t>Herregni deebi'e</t>
+          <t>Herregni uumame</t>
         </is>
       </c>
       <c r="F204" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ ተመሊሱ</t>
+          <t>ሕሳብ ተፈጢሩ</t>
         </is>
       </c>
       <c r="G204" s="13" t="inlineStr">
         <is>
-          <t>Xisaabta waa la soo celiyay</t>
+          <t>Xisaab waa la abuuray</t>
         </is>
       </c>
       <c r="H204" s="13" t="inlineStr">
         <is>
-          <t>Akaunti Imerejeshwa</t>
+          <t>Akaunti Imeundwa</t>
         </is>
       </c>
       <c r="I204" s="14" t="inlineStr"/>
@@ -15017,7 +15017,7 @@
     <row r="205" ht="44" customHeight="1">
       <c r="A205" s="11" t="inlineStr">
         <is>
-          <t>account_disabled_n</t>
+          <t>account_restored</t>
         </is>
       </c>
       <c r="B205" s="11" t="inlineStr">
@@ -15027,32 +15027,32 @@
       </c>
       <c r="C205" s="11" t="inlineStr">
         <is>
-          <t>Account disabled, {n} session(s) ended</t>
+          <t>Account restored</t>
         </is>
       </c>
       <c r="D205" s="12" t="inlineStr">
         <is>
-          <t>መለያ ተሰናክሏል፤ {n} ክፍለ-ጊዜ ተዘግቷል</t>
+          <t>መለያ ተመልሷል</t>
         </is>
       </c>
       <c r="E205" s="13" t="inlineStr">
         <is>
-          <t>Herregni dhaabame, session {n} xumurame</t>
+          <t>Herregni deebi'e</t>
         </is>
       </c>
       <c r="F205" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ ተዓጊቱ፣ {n} ክፍለ-ግዜ ተዛዚሙ</t>
+          <t>ሕሳብ ተመሊሱ</t>
         </is>
       </c>
       <c r="G205" s="13" t="inlineStr">
         <is>
-          <t>Xisaabta waa la demiyay, {n} kalfadhi ayaa dhammaaday</t>
+          <t>Xisaabta waa la soo celiyay</t>
         </is>
       </c>
       <c r="H205" s="13" t="inlineStr">
         <is>
-          <t>Akaunti imezimwa, vikao {n} vimemalizika</t>
+          <t>Akaunti Imerejeshwa</t>
         </is>
       </c>
       <c r="I205" s="14" t="inlineStr"/>
@@ -15060,7 +15060,7 @@
     <row r="206" ht="44" customHeight="1">
       <c r="A206" s="11" t="inlineStr">
         <is>
-          <t>confirm_disable_account</t>
+          <t>account_disabled_n</t>
         </is>
       </c>
       <c r="B206" s="11" t="inlineStr">
@@ -15070,32 +15070,32 @@
       </c>
       <c r="C206" s="11" t="inlineStr">
         <is>
-          <t>Disable this account? They will be signed out immediately.</t>
+          <t>Account disabled, {n} session(s) ended</t>
         </is>
       </c>
       <c r="D206" s="12" t="inlineStr">
         <is>
-          <t>ይህን መለያ ማሰናከል? ወዲያውኑ ይወጣሉ።</t>
+          <t>መለያ ተሰናክሏል፤ {n} ክፍለ-ጊዜ ተዘግቷል</t>
         </is>
       </c>
       <c r="E206" s="13" t="inlineStr">
         <is>
-          <t>Herrega kana dhaabuu? Battalumatti ni baafamu.</t>
+          <t>Herregni dhaabame, session {n} xumurame</t>
         </is>
       </c>
       <c r="F206" s="12" t="inlineStr">
         <is>
-          <t>ነዚ ሕሳብ ክዕገት? ብቕጽበት ይወጹ።</t>
+          <t>ሕሳብ ተዓጊቱ፣ {n} ክፍለ-ግዜ ተዛዚሙ</t>
         </is>
       </c>
       <c r="G206" s="13" t="inlineStr">
         <is>
-          <t>Xisaabtan ma demineysaa? Isla markiiba waa laga saarayaa.</t>
+          <t>Xisaabta waa la demiyay, {n} kalfadhi ayaa dhammaaday</t>
         </is>
       </c>
       <c r="H206" s="13" t="inlineStr">
         <is>
-          <t>Zima akaunti hii? Watatolewa mara moja.</t>
+          <t>Akaunti imezimwa, vikao {n} vimemalizika</t>
         </is>
       </c>
       <c r="I206" s="14" t="inlineStr"/>
@@ -15103,7 +15103,7 @@
     <row r="207" ht="44" customHeight="1">
       <c r="A207" s="11" t="inlineStr">
         <is>
-          <t>action_document_created</t>
+          <t>confirm_disable_account</t>
         </is>
       </c>
       <c r="B207" s="11" t="inlineStr">
@@ -15113,32 +15113,32 @@
       </c>
       <c r="C207" s="11" t="inlineStr">
         <is>
-          <t>added an article</t>
+          <t>Disable this account? They will be signed out immediately.</t>
         </is>
       </c>
       <c r="D207" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ጨምሯል</t>
+          <t>ይህን መለያ ማሰናከል? ወዲያውኑ ይወጣሉ።</t>
         </is>
       </c>
       <c r="E207" s="13" t="inlineStr">
         <is>
-          <t>barruu dabale</t>
+          <t>Herrega kana dhaabuu? Battalumatti ni baafamu.</t>
         </is>
       </c>
       <c r="F207" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ወሲኹ</t>
+          <t>ነዚ ሕሳብ ክዕገት? ብቕጽበት ይወጹ።</t>
         </is>
       </c>
       <c r="G207" s="13" t="inlineStr">
         <is>
-          <t>maqaal ku daray</t>
+          <t>Xisaabtan ma demineysaa? Isla markiiba waa laga saarayaa.</t>
         </is>
       </c>
       <c r="H207" s="13" t="inlineStr">
         <is>
-          <t>aliongeza makala</t>
+          <t>Zima akaunti hii? Watatolewa mara moja.</t>
         </is>
       </c>
       <c r="I207" s="14" t="inlineStr"/>
@@ -15146,7 +15146,7 @@
     <row r="208" ht="44" customHeight="1">
       <c r="A208" s="11" t="inlineStr">
         <is>
-          <t>action_document_updated</t>
+          <t>action_document_created</t>
         </is>
       </c>
       <c r="B208" s="11" t="inlineStr">
@@ -15156,32 +15156,32 @@
       </c>
       <c r="C208" s="11" t="inlineStr">
         <is>
-          <t>edited an article</t>
+          <t>added an article</t>
         </is>
       </c>
       <c r="D208" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ አርሟል</t>
+          <t>ጽሑፍ ጨምሯል</t>
         </is>
       </c>
       <c r="E208" s="13" t="inlineStr">
         <is>
-          <t>barruu gulaale</t>
+          <t>barruu dabale</t>
         </is>
       </c>
       <c r="F208" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ኣርሚዑ</t>
+          <t>ጽሑፍ ወሲኹ</t>
         </is>
       </c>
       <c r="G208" s="13" t="inlineStr">
         <is>
-          <t>maqaal wax ka beddelay</t>
+          <t>maqaal ku daray</t>
         </is>
       </c>
       <c r="H208" s="13" t="inlineStr">
         <is>
-          <t>alihariri makala</t>
+          <t>aliongeza makala</t>
         </is>
       </c>
       <c r="I208" s="14" t="inlineStr"/>
@@ -15189,7 +15189,7 @@
     <row r="209" ht="44" customHeight="1">
       <c r="A209" s="11" t="inlineStr">
         <is>
-          <t>action_document_deleted</t>
+          <t>action_document_updated</t>
         </is>
       </c>
       <c r="B209" s="11" t="inlineStr">
@@ -15199,32 +15199,32 @@
       </c>
       <c r="C209" s="11" t="inlineStr">
         <is>
-          <t>deleted an article</t>
+          <t>edited an article</t>
         </is>
       </c>
       <c r="D209" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ሰርዟል</t>
+          <t>ጽሑፍ አርሟል</t>
         </is>
       </c>
       <c r="E209" s="13" t="inlineStr">
         <is>
-          <t>barruu haqe</t>
+          <t>barruu gulaale</t>
         </is>
       </c>
       <c r="F209" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ደምሲሱ</t>
+          <t>ጽሑፍ ኣርሚዑ</t>
         </is>
       </c>
       <c r="G209" s="13" t="inlineStr">
         <is>
-          <t>maqaal tirtiray</t>
+          <t>maqaal wax ka beddelay</t>
         </is>
       </c>
       <c r="H209" s="13" t="inlineStr">
         <is>
-          <t>alifuta makala</t>
+          <t>alihariri makala</t>
         </is>
       </c>
       <c r="I209" s="14" t="inlineStr"/>
@@ -15232,7 +15232,7 @@
     <row r="210" ht="44" customHeight="1">
       <c r="A210" s="11" t="inlineStr">
         <is>
-          <t>action_documents_bulk_imported</t>
+          <t>action_document_deleted</t>
         </is>
       </c>
       <c r="B210" s="11" t="inlineStr">
@@ -15242,32 +15242,32 @@
       </c>
       <c r="C210" s="11" t="inlineStr">
         <is>
-          <t>imported articles</t>
+          <t>deleted an article</t>
         </is>
       </c>
       <c r="D210" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፎችን አስገብቷል</t>
+          <t>ጽሑፍ ሰርዟል</t>
         </is>
       </c>
       <c r="E210" s="13" t="inlineStr">
         <is>
-          <t>barruulee galche</t>
+          <t>barruu haqe</t>
         </is>
       </c>
       <c r="F210" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፋት ኣእትዩ</t>
+          <t>ጽሑፍ ደምሲሱ</t>
         </is>
       </c>
       <c r="G210" s="13" t="inlineStr">
         <is>
-          <t>maqaallo soo dhoofiyay</t>
+          <t>maqaal tirtiray</t>
         </is>
       </c>
       <c r="H210" s="13" t="inlineStr">
         <is>
-          <t>aliagiza makala</t>
+          <t>alifuta makala</t>
         </is>
       </c>
       <c r="I210" s="14" t="inlineStr"/>
@@ -15275,7 +15275,7 @@
     <row r="211" ht="44" customHeight="1">
       <c r="A211" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_closed</t>
+          <t>action_documents_bulk_imported</t>
         </is>
       </c>
       <c r="B211" s="11" t="inlineStr">
@@ -15285,32 +15285,32 @@
       </c>
       <c r="C211" s="11" t="inlineStr">
         <is>
-          <t>closed an escalation</t>
+          <t>imported articles</t>
         </is>
       </c>
       <c r="D211" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ ዘግቷል</t>
+          <t>ጽሑፎችን አስገብቷል</t>
         </is>
       </c>
       <c r="E211" s="13" t="inlineStr">
         <is>
-          <t>dhimma cufe</t>
+          <t>barruulee galche</t>
         </is>
       </c>
       <c r="F211" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ ዓጺዩ</t>
+          <t>ጽሑፋት ኣእትዩ</t>
         </is>
       </c>
       <c r="G211" s="13" t="inlineStr">
         <is>
-          <t>arrin xiray</t>
+          <t>maqaallo soo dhoofiyay</t>
         </is>
       </c>
       <c r="H211" s="13" t="inlineStr">
         <is>
-          <t>alifunga suala</t>
+          <t>aliagiza makala</t>
         </is>
       </c>
       <c r="I211" s="14" t="inlineStr"/>
@@ -15318,7 +15318,7 @@
     <row r="212" ht="44" customHeight="1">
       <c r="A212" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_reopened</t>
+          <t>action_handoff_closed</t>
         </is>
       </c>
       <c r="B212" s="11" t="inlineStr">
@@ -15328,32 +15328,32 @@
       </c>
       <c r="C212" s="11" t="inlineStr">
         <is>
-          <t>reopened an escalation</t>
+          <t>closed an escalation</t>
         </is>
       </c>
       <c r="D212" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ በድጋሚ ከፍቷል</t>
+          <t>ጉዳይ ዘግቷል</t>
         </is>
       </c>
       <c r="E212" s="13" t="inlineStr">
         <is>
-          <t>dhimma irra deebi'ee bane</t>
+          <t>dhimma cufe</t>
         </is>
       </c>
       <c r="F212" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ ደጊሙ ከፊቱ</t>
+          <t>ጉዳይ ዓጺዩ</t>
         </is>
       </c>
       <c r="G212" s="13" t="inlineStr">
         <is>
-          <t>arrin dib u furay</t>
+          <t>arrin xiray</t>
         </is>
       </c>
       <c r="H212" s="13" t="inlineStr">
         <is>
-          <t>alifungua tena suala</t>
+          <t>alifunga suala</t>
         </is>
       </c>
       <c r="I212" s="14" t="inlineStr"/>
@@ -15361,7 +15361,7 @@
     <row r="213" ht="44" customHeight="1">
       <c r="A213" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_webhook_connected</t>
+          <t>action_handoff_reopened</t>
         </is>
       </c>
       <c r="B213" s="11" t="inlineStr">
@@ -15371,32 +15371,32 @@
       </c>
       <c r="C213" s="11" t="inlineStr">
         <is>
-          <t>connected the escalation webhook</t>
+          <t>reopened an escalation</t>
         </is>
       </c>
       <c r="D213" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ዌብሁክ አገናኝቷል</t>
+          <t>ጉዳይ በድጋሚ ከፍቷል</t>
         </is>
       </c>
       <c r="E213" s="13" t="inlineStr">
         <is>
-          <t>webhook dabarsaa walqunnamsiise</t>
+          <t>dhimma irra deebi'ee bane</t>
         </is>
       </c>
       <c r="F213" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ምትሕልላፍ ኣራኺቡ</t>
+          <t>ጉዳይ ደጊሙ ከፊቱ</t>
         </is>
       </c>
       <c r="G213" s="13" t="inlineStr">
         <is>
-          <t>ku xiray webhook-ga gudbinta</t>
+          <t>arrin dib u furay</t>
         </is>
       </c>
       <c r="H213" s="13" t="inlineStr">
         <is>
-          <t>aliunganisha wavuti ya masuala</t>
+          <t>alifungua tena suala</t>
         </is>
       </c>
       <c r="I213" s="14" t="inlineStr"/>
@@ -15404,7 +15404,7 @@
     <row r="214" ht="44" customHeight="1">
       <c r="A214" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_webhook_disconnected</t>
+          <t>action_handoff_webhook_connected</t>
         </is>
       </c>
       <c r="B214" s="11" t="inlineStr">
@@ -15414,32 +15414,32 @@
       </c>
       <c r="C214" s="11" t="inlineStr">
         <is>
-          <t>disconnected the escalation webhook</t>
+          <t>connected the escalation webhook</t>
         </is>
       </c>
       <c r="D214" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ዌብሁክ አቋርጧል</t>
+          <t>የማሸጋገሪያ ዌብሁክ አገናኝቷል</t>
         </is>
       </c>
       <c r="E214" s="13" t="inlineStr">
         <is>
-          <t>webhook dabarsaa addaan kute</t>
+          <t>webhook dabarsaa walqunnamsiise</t>
         </is>
       </c>
       <c r="F214" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ምትሕልላፍ ቆሪጹ</t>
+          <t>ዌብሁክ ምትሕልላፍ ኣራኺቡ</t>
         </is>
       </c>
       <c r="G214" s="13" t="inlineStr">
         <is>
-          <t>goynay webhook-ga gudbinta</t>
+          <t>ku xiray webhook-ga gudbinta</t>
         </is>
       </c>
       <c r="H214" s="13" t="inlineStr">
         <is>
-          <t>alikatisha wavuti ya masuala</t>
+          <t>aliunganisha wavuti ya masuala</t>
         </is>
       </c>
       <c r="I214" s="14" t="inlineStr"/>
@@ -15447,7 +15447,7 @@
     <row r="215" ht="44" customHeight="1">
       <c r="A215" s="11" t="inlineStr">
         <is>
-          <t>action_telegram_connected</t>
+          <t>action_handoff_webhook_disconnected</t>
         </is>
       </c>
       <c r="B215" s="11" t="inlineStr">
@@ -15457,32 +15457,32 @@
       </c>
       <c r="C215" s="11" t="inlineStr">
         <is>
-          <t>connected Telegram</t>
+          <t>disconnected the escalation webhook</t>
         </is>
       </c>
       <c r="D215" s="12" t="inlineStr">
         <is>
-          <t>ቴሌግራም አገናኝቷል</t>
+          <t>የማሸጋገሪያ ዌብሁክ አቋርጧል</t>
         </is>
       </c>
       <c r="E215" s="13" t="inlineStr">
         <is>
-          <t>Telegram walqunnamsiise</t>
+          <t>webhook dabarsaa addaan kute</t>
         </is>
       </c>
       <c r="F215" s="12" t="inlineStr">
         <is>
-          <t>ቴሌግራም ኣራኺቡ</t>
+          <t>ዌብሁክ ምትሕልላፍ ቆሪጹ</t>
         </is>
       </c>
       <c r="G215" s="13" t="inlineStr">
         <is>
-          <t>Telegram ku xiray</t>
+          <t>goynay webhook-ga gudbinta</t>
         </is>
       </c>
       <c r="H215" s="13" t="inlineStr">
         <is>
-          <t>aliunganisha Telegram</t>
+          <t>alikatisha wavuti ya masuala</t>
         </is>
       </c>
       <c r="I215" s="14" t="inlineStr"/>
@@ -15490,7 +15490,7 @@
     <row r="216" ht="44" customHeight="1">
       <c r="A216" s="11" t="inlineStr">
         <is>
-          <t>action_user_created</t>
+          <t>action_telegram_connected</t>
         </is>
       </c>
       <c r="B216" s="11" t="inlineStr">
@@ -15500,32 +15500,32 @@
       </c>
       <c r="C216" s="11" t="inlineStr">
         <is>
-          <t>added a colleague</t>
+          <t>connected Telegram</t>
         </is>
       </c>
       <c r="D216" s="12" t="inlineStr">
         <is>
-          <t>ባልደረባ ጨምሯል</t>
+          <t>ቴሌግራም አገናኝቷል</t>
         </is>
       </c>
       <c r="E216" s="13" t="inlineStr">
         <is>
-          <t>hojjetaa dabale</t>
+          <t>Telegram walqunnamsiise</t>
         </is>
       </c>
       <c r="F216" s="12" t="inlineStr">
         <is>
-          <t>መሳርሕቲ ወሲኹ</t>
+          <t>ቴሌግራም ኣራኺቡ</t>
         </is>
       </c>
       <c r="G216" s="13" t="inlineStr">
         <is>
-          <t>shaqaale ku daray</t>
+          <t>Telegram ku xiray</t>
         </is>
       </c>
       <c r="H216" s="13" t="inlineStr">
         <is>
-          <t>aliongeza mwenzake</t>
+          <t>aliunganisha Telegram</t>
         </is>
       </c>
       <c r="I216" s="14" t="inlineStr"/>
@@ -15533,7 +15533,7 @@
     <row r="217" ht="44" customHeight="1">
       <c r="A217" s="11" t="inlineStr">
         <is>
-          <t>action_user_disabled</t>
+          <t>action_user_created</t>
         </is>
       </c>
       <c r="B217" s="11" t="inlineStr">
@@ -15543,32 +15543,32 @@
       </c>
       <c r="C217" s="11" t="inlineStr">
         <is>
-          <t>disabled an account</t>
+          <t>added a colleague</t>
         </is>
       </c>
       <c r="D217" s="12" t="inlineStr">
         <is>
-          <t>መለያ አሰናክሏል</t>
+          <t>ባልደረባ ጨምሯል</t>
         </is>
       </c>
       <c r="E217" s="13" t="inlineStr">
         <is>
-          <t>herrega dhaabe</t>
+          <t>hojjetaa dabale</t>
         </is>
       </c>
       <c r="F217" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ ዓጊቱ</t>
+          <t>መሳርሕቲ ወሲኹ</t>
         </is>
       </c>
       <c r="G217" s="13" t="inlineStr">
         <is>
-          <t>xisaab demiyay</t>
+          <t>shaqaale ku daray</t>
         </is>
       </c>
       <c r="H217" s="13" t="inlineStr">
         <is>
-          <t>alizima akaunti</t>
+          <t>aliongeza mwenzake</t>
         </is>
       </c>
       <c r="I217" s="14" t="inlineStr"/>
@@ -15576,7 +15576,7 @@
     <row r="218" ht="44" customHeight="1">
       <c r="A218" s="11" t="inlineStr">
         <is>
-          <t>action_user_enabled</t>
+          <t>action_user_disabled</t>
         </is>
       </c>
       <c r="B218" s="11" t="inlineStr">
@@ -15586,32 +15586,32 @@
       </c>
       <c r="C218" s="11" t="inlineStr">
         <is>
-          <t>restored an account</t>
+          <t>disabled an account</t>
         </is>
       </c>
       <c r="D218" s="12" t="inlineStr">
         <is>
-          <t>መለያ መልሷል</t>
+          <t>መለያ አሰናክሏል</t>
         </is>
       </c>
       <c r="E218" s="13" t="inlineStr">
         <is>
-          <t>herrega deebise</t>
+          <t>herrega dhaabe</t>
         </is>
       </c>
       <c r="F218" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ መሊሱ</t>
+          <t>ሕሳብ ዓጊቱ</t>
         </is>
       </c>
       <c r="G218" s="13" t="inlineStr">
         <is>
-          <t>xisaab soo celiyay</t>
+          <t>xisaab demiyay</t>
         </is>
       </c>
       <c r="H218" s="13" t="inlineStr">
         <is>
-          <t>alirejesha akaunti</t>
+          <t>alizima akaunti</t>
         </is>
       </c>
       <c r="I218" s="14" t="inlineStr"/>
@@ -15619,7 +15619,7 @@
     <row r="219" ht="44" customHeight="1">
       <c r="A219" s="11" t="inlineStr">
         <is>
-          <t>action_admin_login</t>
+          <t>action_user_enabled</t>
         </is>
       </c>
       <c r="B219" s="11" t="inlineStr">
@@ -15629,32 +15629,32 @@
       </c>
       <c r="C219" s="11" t="inlineStr">
         <is>
-          <t>signed in</t>
+          <t>restored an account</t>
         </is>
       </c>
       <c r="D219" s="12" t="inlineStr">
         <is>
-          <t>ገብቷል</t>
+          <t>መለያ መልሷል</t>
         </is>
       </c>
       <c r="E219" s="13" t="inlineStr">
         <is>
-          <t>seene</t>
+          <t>herrega deebise</t>
         </is>
       </c>
       <c r="F219" s="12" t="inlineStr">
         <is>
-          <t>ኣትዩ</t>
+          <t>ሕሳብ መሊሱ</t>
         </is>
       </c>
       <c r="G219" s="13" t="inlineStr">
         <is>
-          <t>gashay</t>
+          <t>xisaab soo celiyay</t>
         </is>
       </c>
       <c r="H219" s="13" t="inlineStr">
         <is>
-          <t>aliingia</t>
+          <t>alirejesha akaunti</t>
         </is>
       </c>
       <c r="I219" s="14" t="inlineStr"/>
@@ -15662,7 +15662,7 @@
     <row r="220" ht="44" customHeight="1">
       <c r="A220" s="11" t="inlineStr">
         <is>
-          <t>action_password_changed</t>
+          <t>action_admin_login</t>
         </is>
       </c>
       <c r="B220" s="11" t="inlineStr">
@@ -15672,32 +15672,32 @@
       </c>
       <c r="C220" s="11" t="inlineStr">
         <is>
-          <t>changed their password</t>
+          <t>signed in</t>
         </is>
       </c>
       <c r="D220" s="12" t="inlineStr">
         <is>
-          <t>የይለፍ ቃል ቀይሯል</t>
+          <t>ገብቷል</t>
         </is>
       </c>
       <c r="E220" s="13" t="inlineStr">
         <is>
-          <t>jecha darbii jijjiire</t>
+          <t>seene</t>
         </is>
       </c>
       <c r="F220" s="12" t="inlineStr">
         <is>
-          <t>መሕለፊ ቃል ቀዪሩ</t>
+          <t>ኣትዩ</t>
         </is>
       </c>
       <c r="G220" s="13" t="inlineStr">
         <is>
-          <t>beddelay furihiisa</t>
+          <t>gashay</t>
         </is>
       </c>
       <c r="H220" s="13" t="inlineStr">
         <is>
-          <t>alibadilisha nenosiri lake</t>
+          <t>aliingia</t>
         </is>
       </c>
       <c r="I220" s="14" t="inlineStr"/>
@@ -15705,7 +15705,7 @@
     <row r="221" ht="44" customHeight="1">
       <c r="A221" s="11" t="inlineStr">
         <is>
-          <t>nothing_yet</t>
+          <t>action_password_changed</t>
         </is>
       </c>
       <c r="B221" s="11" t="inlineStr">
@@ -15715,32 +15715,32 @@
       </c>
       <c r="C221" s="11" t="inlineStr">
         <is>
-          <t>Nothing yet.</t>
+          <t>changed their password</t>
         </is>
       </c>
       <c r="D221" s="12" t="inlineStr">
         <is>
-          <t>እስካሁን ምንም የለም።</t>
+          <t>የይለፍ ቃል ቀይሯል</t>
         </is>
       </c>
       <c r="E221" s="13" t="inlineStr">
         <is>
-          <t>Ammaaf homaa hin jiru.</t>
+          <t>jecha darbii jijjiire</t>
         </is>
       </c>
       <c r="F221" s="12" t="inlineStr">
         <is>
-          <t>ክሳብ ሕጂ ዋላ ሓደ የለን።</t>
+          <t>መሕለፊ ቃል ቀዪሩ</t>
         </is>
       </c>
       <c r="G221" s="13" t="inlineStr">
         <is>
-          <t>Weli waxba ma jiraan.</t>
+          <t>beddelay furihiisa</t>
         </is>
       </c>
       <c r="H221" s="13" t="inlineStr">
         <is>
-          <t>Bado hakuna.</t>
+          <t>alibadilisha nenosiri lake</t>
         </is>
       </c>
       <c r="I221" s="14" t="inlineStr"/>
@@ -15748,7 +15748,7 @@
     <row r="222" ht="44" customHeight="1">
       <c r="A222" s="11" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>nothing_yet</t>
         </is>
       </c>
       <c r="B222" s="11" t="inlineStr">
@@ -15758,32 +15758,32 @@
       </c>
       <c r="C222" s="11" t="inlineStr">
         <is>
-          <t>Unavailable.</t>
+          <t>Nothing yet.</t>
         </is>
       </c>
       <c r="D222" s="12" t="inlineStr">
         <is>
-          <t>አይገኝም።</t>
+          <t>እስካሁን ምንም የለም።</t>
         </is>
       </c>
       <c r="E222" s="13" t="inlineStr">
         <is>
-          <t>Hin argamu.</t>
+          <t>Ammaaf homaa hin jiru.</t>
         </is>
       </c>
       <c r="F222" s="12" t="inlineStr">
         <is>
-          <t>ኣይርከብን።</t>
+          <t>ክሳብ ሕጂ ዋላ ሓደ የለን።</t>
         </is>
       </c>
       <c r="G222" s="13" t="inlineStr">
         <is>
-          <t>Lama heli karo.</t>
+          <t>Weli waxba ma jiraan.</t>
         </is>
       </c>
       <c r="H222" s="13" t="inlineStr">
         <is>
-          <t>Haipatikani.</t>
+          <t>Bado hakuna.</t>
         </is>
       </c>
       <c r="I222" s="14" t="inlineStr"/>
@@ -15791,7 +15791,7 @@
     <row r="223" ht="44" customHeight="1">
       <c r="A223" s="11" t="inlineStr">
         <is>
-          <t>just_now</t>
+          <t>unavailable</t>
         </is>
       </c>
       <c r="B223" s="11" t="inlineStr">
@@ -15801,32 +15801,32 @@
       </c>
       <c r="C223" s="11" t="inlineStr">
         <is>
-          <t>just now</t>
+          <t>Unavailable.</t>
         </is>
       </c>
       <c r="D223" s="12" t="inlineStr">
         <is>
-          <t>አሁን</t>
+          <t>አይገኝም።</t>
         </is>
       </c>
       <c r="E223" s="13" t="inlineStr">
         <is>
-          <t>amma</t>
+          <t>Hin argamu.</t>
         </is>
       </c>
       <c r="F223" s="12" t="inlineStr">
         <is>
-          <t>ሕጂ</t>
+          <t>ኣይርከብን።</t>
         </is>
       </c>
       <c r="G223" s="13" t="inlineStr">
         <is>
-          <t>hadda</t>
+          <t>Lama heli karo.</t>
         </is>
       </c>
       <c r="H223" s="13" t="inlineStr">
         <is>
-          <t>sasa hivi</t>
+          <t>Haipatikani.</t>
         </is>
       </c>
       <c r="I223" s="14" t="inlineStr"/>
@@ -15834,7 +15834,7 @@
     <row r="224" ht="44" customHeight="1">
       <c r="A224" s="11" t="inlineStr">
         <is>
-          <t>n_min_ago</t>
+          <t>just_now</t>
         </is>
       </c>
       <c r="B224" s="11" t="inlineStr">
@@ -15844,32 +15844,32 @@
       </c>
       <c r="C224" s="11" t="inlineStr">
         <is>
-          <t>{n} min ago</t>
+          <t>just now</t>
         </is>
       </c>
       <c r="D224" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ደቂቃ በፊት</t>
+          <t>አሁን</t>
         </is>
       </c>
       <c r="E224" s="13" t="inlineStr">
         <is>
-          <t>daqiiqaa {n} dura</t>
+          <t>amma</t>
         </is>
       </c>
       <c r="F224" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ደቒቕ</t>
+          <t>ሕጂ</t>
         </is>
       </c>
       <c r="G224" s="13" t="inlineStr">
         <is>
-          <t>{n} daqiiqo ka hor</t>
+          <t>hadda</t>
         </is>
       </c>
       <c r="H224" s="13" t="inlineStr">
         <is>
-          <t>dakika {n} zilizopita</t>
+          <t>sasa hivi</t>
         </is>
       </c>
       <c r="I224" s="14" t="inlineStr"/>
@@ -15877,7 +15877,7 @@
     <row r="225" ht="44" customHeight="1">
       <c r="A225" s="11" t="inlineStr">
         <is>
-          <t>n_h_ago</t>
+          <t>n_min_ago</t>
         </is>
       </c>
       <c r="B225" s="11" t="inlineStr">
@@ -15887,32 +15887,32 @@
       </c>
       <c r="C225" s="11" t="inlineStr">
         <is>
-          <t>{n} h ago</t>
+          <t>{n} min ago</t>
         </is>
       </c>
       <c r="D225" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ሰዓት በፊት</t>
+          <t>ከ{n} ደቂቃ በፊት</t>
         </is>
       </c>
       <c r="E225" s="13" t="inlineStr">
         <is>
-          <t>sa'aatii {n} dura</t>
+          <t>daqiiqaa {n} dura</t>
         </is>
       </c>
       <c r="F225" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ሰዓት</t>
+          <t>ቅድሚ {n} ደቒቕ</t>
         </is>
       </c>
       <c r="G225" s="13" t="inlineStr">
         <is>
-          <t>{n} saac ka hor</t>
+          <t>{n} daqiiqo ka hor</t>
         </is>
       </c>
       <c r="H225" s="13" t="inlineStr">
         <is>
-          <t>saa {n} zilizopita</t>
+          <t>dakika {n} zilizopita</t>
         </is>
       </c>
       <c r="I225" s="14" t="inlineStr"/>
@@ -15920,7 +15920,7 @@
     <row r="226" ht="44" customHeight="1">
       <c r="A226" s="11" t="inlineStr">
         <is>
-          <t>n_d_ago</t>
+          <t>n_h_ago</t>
         </is>
       </c>
       <c r="B226" s="11" t="inlineStr">
@@ -15930,32 +15930,32 @@
       </c>
       <c r="C226" s="11" t="inlineStr">
         <is>
-          <t>{n} d ago</t>
+          <t>{n} h ago</t>
         </is>
       </c>
       <c r="D226" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ቀን በፊት</t>
+          <t>ከ{n} ሰዓት በፊት</t>
         </is>
       </c>
       <c r="E226" s="13" t="inlineStr">
         <is>
-          <t>guyyaa {n} dura</t>
+          <t>sa'aatii {n} dura</t>
         </is>
       </c>
       <c r="F226" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} መዓልቲ</t>
+          <t>ቅድሚ {n} ሰዓት</t>
         </is>
       </c>
       <c r="G226" s="13" t="inlineStr">
         <is>
-          <t>{n} maalmood ka hor</t>
+          <t>{n} saac ka hor</t>
         </is>
       </c>
       <c r="H226" s="13" t="inlineStr">
         <is>
-          <t>siku {n} zilizopita</t>
+          <t>saa {n} zilizopita</t>
         </is>
       </c>
       <c r="I226" s="14" t="inlineStr"/>
@@ -15963,7 +15963,7 @@
     <row r="227" ht="44" customHeight="1">
       <c r="A227" s="11" t="inlineStr">
         <is>
-          <t>channel_all_from</t>
+          <t>n_d_ago</t>
         </is>
       </c>
       <c r="B227" s="11" t="inlineStr">
@@ -15973,32 +15973,32 @@
       </c>
       <c r="C227" s="11" t="inlineStr">
         <is>
-          <t>All {n} conversations came from {label}.</t>
+          <t>{n} d ago</t>
         </is>
       </c>
       <c r="D227" s="12" t="inlineStr">
         <is>
-          <t>ሁሉም {n} ውይይቶች ከ{label} መጥተዋል።</t>
+          <t>ከ{n} ቀን በፊት</t>
         </is>
       </c>
       <c r="E227" s="13" t="inlineStr">
         <is>
-          <t>Mariin {n} hundi {label} irraa dhufe.</t>
+          <t>guyyaa {n} dura</t>
         </is>
       </c>
       <c r="F227" s="12" t="inlineStr">
         <is>
-          <t>ኩሎም {n} ዝርርባት ካብ {label} መጺኦም።</t>
+          <t>ቅድሚ {n} መዓልቲ</t>
         </is>
       </c>
       <c r="G227" s="13" t="inlineStr">
         <is>
-          <t>Dhammaan {n} wadahadal waxay ka yimaadeen {label}.</t>
+          <t>{n} maalmood ka hor</t>
         </is>
       </c>
       <c r="H227" s="13" t="inlineStr">
         <is>
-          <t>Mazungumzo yote {n} yalitoka {label}.</t>
+          <t>siku {n} zilizopita</t>
         </is>
       </c>
       <c r="I227" s="14" t="inlineStr"/>
@@ -16006,7 +16006,7 @@
     <row r="228" ht="44" customHeight="1">
       <c r="A228" s="11" t="inlineStr">
         <is>
-          <t>channel_live</t>
+          <t>channel_all_from</t>
         </is>
       </c>
       <c r="B228" s="11" t="inlineStr">
@@ -16016,32 +16016,32 @@
       </c>
       <c r="C228" s="11" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>All {n} conversations came from {label}.</t>
         </is>
       </c>
       <c r="D228" s="12" t="inlineStr">
         <is>
-          <t>በሥራ ላይ</t>
+          <t>ሁሉም {n} ውይይቶች ከ{label} መጥተዋል።</t>
         </is>
       </c>
       <c r="E228" s="13" t="inlineStr">
         <is>
-          <t>Hojiirra</t>
+          <t>Mariin {n} hundi {label} irraa dhufe.</t>
         </is>
       </c>
       <c r="F228" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ስራሕ</t>
+          <t>ኩሎም {n} ዝርርባት ካብ {label} መጺኦም።</t>
         </is>
       </c>
       <c r="G228" s="13" t="inlineStr">
         <is>
-          <t>Shaqeynaya</t>
+          <t>Dhammaan {n} wadahadal waxay ka yimaadeen {label}.</t>
         </is>
       </c>
       <c r="H228" s="13" t="inlineStr">
         <is>
-          <t>Moja kwa Moja</t>
+          <t>Mazungumzo yote {n} yalitoka {label}.</t>
         </is>
       </c>
       <c r="I228" s="14" t="inlineStr"/>
@@ -16049,7 +16049,7 @@
     <row r="229" ht="44" customHeight="1">
       <c r="A229" s="11" t="inlineStr">
         <is>
-          <t>channel_ready</t>
+          <t>channel_live</t>
         </is>
       </c>
       <c r="B229" s="11" t="inlineStr">
@@ -16059,32 +16059,32 @@
       </c>
       <c r="C229" s="11" t="inlineStr">
         <is>
-          <t>Ready to connect</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="D229" s="12" t="inlineStr">
         <is>
-          <t>ለመገናኘት ዝግጁ</t>
+          <t>በሥራ ላይ</t>
         </is>
       </c>
       <c r="E229" s="13" t="inlineStr">
         <is>
-          <t>Walqunnamuuf qophaa'aa</t>
+          <t>Hojiirra</t>
         </is>
       </c>
       <c r="F229" s="12" t="inlineStr">
         <is>
-          <t>ንምርኻብ ድሉው</t>
+          <t>ኣብ ስራሕ</t>
         </is>
       </c>
       <c r="G229" s="13" t="inlineStr">
         <is>
-          <t>Diyaar u ah xiriirka</t>
+          <t>Shaqeynaya</t>
         </is>
       </c>
       <c r="H229" s="13" t="inlineStr">
         <is>
-          <t>Tayari Kuunganishwa</t>
+          <t>Moja kwa Moja</t>
         </is>
       </c>
       <c r="I229" s="14" t="inlineStr"/>
@@ -16092,7 +16092,7 @@
     <row r="230" ht="44" customHeight="1">
       <c r="A230" s="11" t="inlineStr">
         <is>
-          <t>channel_needs_setup</t>
+          <t>channel_ready</t>
         </is>
       </c>
       <c r="B230" s="11" t="inlineStr">
@@ -16102,32 +16102,32 @@
       </c>
       <c r="C230" s="11" t="inlineStr">
         <is>
-          <t>Needs setup</t>
+          <t>Ready to connect</t>
         </is>
       </c>
       <c r="D230" s="12" t="inlineStr">
         <is>
-          <t>ማዋቀር ይፈልጋል</t>
+          <t>ለመገናኘት ዝግጁ</t>
         </is>
       </c>
       <c r="E230" s="13" t="inlineStr">
         <is>
-          <t>Qindeessuu barbaada</t>
+          <t>Walqunnamuuf qophaa'aa</t>
         </is>
       </c>
       <c r="F230" s="12" t="inlineStr">
         <is>
-          <t>ምድላው የድልዮ</t>
+          <t>ንምርኻብ ድሉው</t>
         </is>
       </c>
       <c r="G230" s="13" t="inlineStr">
         <is>
-          <t>Waxay u baahan tahay dejin</t>
+          <t>Diyaar u ah xiriirka</t>
         </is>
       </c>
       <c r="H230" s="13" t="inlineStr">
         <is>
-          <t>Inahitaji Kusanidiwa</t>
+          <t>Tayari Kuunganishwa</t>
         </is>
       </c>
       <c r="I230" s="14" t="inlineStr"/>
@@ -16135,7 +16135,7 @@
     <row r="231" ht="44" customHeight="1">
       <c r="A231" s="11" t="inlineStr">
         <is>
-          <t>share_by_channel</t>
+          <t>channel_needs_setup</t>
         </is>
       </c>
       <c r="B231" s="11" t="inlineStr">
@@ -16145,32 +16145,32 @@
       </c>
       <c r="C231" s="11" t="inlineStr">
         <is>
-          <t>Share of conversations by channel</t>
+          <t>Needs setup</t>
         </is>
       </c>
       <c r="D231" s="12" t="inlineStr">
         <is>
-          <t>በመስመር የተከፋፈሉ ውይይቶች ድርሻ</t>
+          <t>ማዋቀር ይፈልጋል</t>
         </is>
       </c>
       <c r="E231" s="13" t="inlineStr">
         <is>
-          <t>Qooda marii karaa tokkoon tokkoon isaanii</t>
+          <t>Qindeessuu barbaada</t>
         </is>
       </c>
       <c r="F231" s="12" t="inlineStr">
         <is>
-          <t>ብመስመር ዝተኸፋፈለ ግደ ዝርርባት</t>
+          <t>ምድላው የድልዮ</t>
         </is>
       </c>
       <c r="G231" s="13" t="inlineStr">
         <is>
-          <t>Qaybta wadahadallada kanaalka</t>
+          <t>Waxay u baahan tahay dejin</t>
         </is>
       </c>
       <c r="H231" s="13" t="inlineStr">
         <is>
-          <t>Mgawanyo wa Mazungumzo kwa Njia</t>
+          <t>Inahitaji Kusanidiwa</t>
         </is>
       </c>
       <c r="I231" s="14" t="inlineStr"/>
@@ -16178,7 +16178,7 @@
     <row r="232" ht="44" customHeight="1">
       <c r="A232" s="11" t="inlineStr">
         <is>
-          <t>up_to_date</t>
+          <t>share_by_channel</t>
         </is>
       </c>
       <c r="B232" s="11" t="inlineStr">
@@ -16188,32 +16188,32 @@
       </c>
       <c r="C232" s="11" t="inlineStr">
         <is>
-          <t>Up to date</t>
+          <t>Share of conversations by channel</t>
         </is>
       </c>
       <c r="D232" s="12" t="inlineStr">
         <is>
-          <t>የተዘመነ</t>
+          <t>በመስመር የተከፋፈሉ ውይይቶች ድርሻ</t>
         </is>
       </c>
       <c r="E232" s="13" t="inlineStr">
         <is>
-          <t>Haaraa</t>
+          <t>Qooda marii karaa tokkoon tokkoon isaanii</t>
         </is>
       </c>
       <c r="F232" s="12" t="inlineStr">
         <is>
-          <t>ዝተሓደሰ</t>
+          <t>ብመስመር ዝተኸፋፈለ ግደ ዝርርባት</t>
         </is>
       </c>
       <c r="G232" s="13" t="inlineStr">
         <is>
-          <t>La cusbooneysiiyay</t>
+          <t>Qaybta wadahadallada kanaalka</t>
         </is>
       </c>
       <c r="H232" s="13" t="inlineStr">
         <is>
-          <t>Ni ya Hivi Karibuni</t>
+          <t>Mgawanyo wa Mazungumzo kwa Njia</t>
         </is>
       </c>
       <c r="I232" s="14" t="inlineStr"/>
@@ -16221,7 +16221,7 @@
     <row r="233" ht="44" customHeight="1">
       <c r="A233" s="11" t="inlineStr">
         <is>
-          <t>updated_m_ago</t>
+          <t>up_to_date</t>
         </is>
       </c>
       <c r="B233" s="11" t="inlineStr">
@@ -16231,32 +16231,32 @@
       </c>
       <c r="C233" s="11" t="inlineStr">
         <is>
-          <t>Updated {n}m ago</t>
+          <t>Up to date</t>
         </is>
       </c>
       <c r="D233" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ደቂቃ በፊት ተዘምኗል</t>
+          <t>የተዘመነ</t>
         </is>
       </c>
       <c r="E233" s="13" t="inlineStr">
         <is>
-          <t>Daqiiqaa {n} dura haaromfame</t>
+          <t>Haaraa</t>
         </is>
       </c>
       <c r="F233" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ደቒቕ ተሓዲሱ</t>
+          <t>ዝተሓደሰ</t>
         </is>
       </c>
       <c r="G233" s="13" t="inlineStr">
         <is>
-          <t>La cusbooneysiiyay {n}daq ka hor</t>
+          <t>La cusbooneysiiyay</t>
         </is>
       </c>
       <c r="H233" s="13" t="inlineStr">
         <is>
-          <t>Imesasishwa dakika {n} zilizopita</t>
+          <t>Ni ya Hivi Karibuni</t>
         </is>
       </c>
       <c r="I233" s="14" t="inlineStr"/>
@@ -16264,7 +16264,7 @@
     <row r="234" ht="44" customHeight="1">
       <c r="A234" s="11" t="inlineStr">
         <is>
-          <t>updated_h_ago</t>
+          <t>updated_m_ago</t>
         </is>
       </c>
       <c r="B234" s="11" t="inlineStr">
@@ -16274,32 +16274,32 @@
       </c>
       <c r="C234" s="11" t="inlineStr">
         <is>
-          <t>Updated {n}h ago</t>
+          <t>Updated {n}m ago</t>
         </is>
       </c>
       <c r="D234" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ሰዓት በፊት ተዘምኗል</t>
+          <t>ከ{n} ደቂቃ በፊት ተዘምኗል</t>
         </is>
       </c>
       <c r="E234" s="13" t="inlineStr">
         <is>
-          <t>Sa'aatii {n} dura haaromfame</t>
+          <t>Daqiiqaa {n} dura haaromfame</t>
         </is>
       </c>
       <c r="F234" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ሰዓት ተሓዲሱ</t>
+          <t>ቅድሚ {n} ደቒቕ ተሓዲሱ</t>
         </is>
       </c>
       <c r="G234" s="13" t="inlineStr">
         <is>
-          <t>La cusbooneysiiyay {n}saac ka hor</t>
+          <t>La cusbooneysiiyay {n}daq ka hor</t>
         </is>
       </c>
       <c r="H234" s="13" t="inlineStr">
         <is>
-          <t>Imesasishwa saa {n} zilizopita</t>
+          <t>Imesasishwa dakika {n} zilizopita</t>
         </is>
       </c>
       <c r="I234" s="14" t="inlineStr"/>
@@ -16307,7 +16307,7 @@
     <row r="235" ht="44" customHeight="1">
       <c r="A235" s="11" t="inlineStr">
         <is>
-          <t>queue</t>
+          <t>updated_h_ago</t>
         </is>
       </c>
       <c r="B235" s="11" t="inlineStr">
@@ -16317,32 +16317,32 @@
       </c>
       <c r="C235" s="11" t="inlineStr">
         <is>
-          <t>Queue</t>
+          <t>Updated {n}h ago</t>
         </is>
       </c>
       <c r="D235" s="12" t="inlineStr">
         <is>
-          <t>ወረፋ</t>
+          <t>ከ{n} ሰዓት በፊት ተዘምኗል</t>
         </is>
       </c>
       <c r="E235" s="13" t="inlineStr">
         <is>
-          <t>Sararaa</t>
+          <t>Sa'aatii {n} dura haaromfame</t>
         </is>
       </c>
       <c r="F235" s="12" t="inlineStr">
         <is>
-          <t>ሪጋ</t>
+          <t>ቅድሚ {n} ሰዓት ተሓዲሱ</t>
         </is>
       </c>
       <c r="G235" s="13" t="inlineStr">
         <is>
-          <t>Safka</t>
+          <t>La cusbooneysiiyay {n}saac ka hor</t>
         </is>
       </c>
       <c r="H235" s="13" t="inlineStr">
         <is>
-          <t>Foleni</t>
+          <t>Imesasishwa saa {n} zilizopita</t>
         </is>
       </c>
       <c r="I235" s="14" t="inlineStr"/>
@@ -16350,7 +16350,7 @@
     <row r="236" ht="44" customHeight="1">
       <c r="A236" s="11" t="inlineStr">
         <is>
-          <t>collapse</t>
+          <t>queue</t>
         </is>
       </c>
       <c r="B236" s="11" t="inlineStr">
@@ -16360,32 +16360,32 @@
       </c>
       <c r="C236" s="11" t="inlineStr">
         <is>
-          <t>Collapse</t>
+          <t>Queue</t>
         </is>
       </c>
       <c r="D236" s="12" t="inlineStr">
         <is>
-          <t>አጥብብ</t>
+          <t>ወረፋ</t>
         </is>
       </c>
       <c r="E236" s="13" t="inlineStr">
         <is>
-          <t>Xiqqeessi</t>
+          <t>Sararaa</t>
         </is>
       </c>
       <c r="F236" s="12" t="inlineStr">
         <is>
-          <t>ኣጽብብ</t>
+          <t>ሪጋ</t>
         </is>
       </c>
       <c r="G236" s="13" t="inlineStr">
         <is>
-          <t>Yaree</t>
+          <t>Safka</t>
         </is>
       </c>
       <c r="H236" s="13" t="inlineStr">
         <is>
-          <t>Kunja</t>
+          <t>Foleni</t>
         </is>
       </c>
       <c r="I236" s="14" t="inlineStr"/>
@@ -16393,7 +16393,7 @@
     <row r="237" ht="44" customHeight="1">
       <c r="A237" s="11" t="inlineStr">
         <is>
-          <t>expand</t>
+          <t>collapse</t>
         </is>
       </c>
       <c r="B237" s="11" t="inlineStr">
@@ -16403,32 +16403,32 @@
       </c>
       <c r="C237" s="11" t="inlineStr">
         <is>
-          <t>Expand</t>
+          <t>Collapse</t>
         </is>
       </c>
       <c r="D237" s="12" t="inlineStr">
         <is>
-          <t>አስፋ</t>
+          <t>አጥብብ</t>
         </is>
       </c>
       <c r="E237" s="13" t="inlineStr">
         <is>
-          <t>Balleessi</t>
+          <t>Xiqqeessi</t>
         </is>
       </c>
       <c r="F237" s="12" t="inlineStr">
         <is>
-          <t>ኣስፍሕ</t>
+          <t>ኣጽብብ</t>
         </is>
       </c>
       <c r="G237" s="13" t="inlineStr">
         <is>
-          <t>Balaadhi</t>
+          <t>Yaree</t>
         </is>
       </c>
       <c r="H237" s="13" t="inlineStr">
         <is>
-          <t>Panua</t>
+          <t>Kunja</t>
         </is>
       </c>
       <c r="I237" s="14" t="inlineStr"/>
@@ -16436,7 +16436,7 @@
     <row r="238" ht="44" customHeight="1">
       <c r="A238" s="11" t="inlineStr">
         <is>
-          <t>collapse_or_expand</t>
+          <t>expand</t>
         </is>
       </c>
       <c r="B238" s="11" t="inlineStr">
@@ -16446,32 +16446,32 @@
       </c>
       <c r="C238" s="11" t="inlineStr">
         <is>
-          <t>Collapse or expand the sidebar</t>
+          <t>Expand</t>
         </is>
       </c>
       <c r="D238" s="12" t="inlineStr">
         <is>
-          <t>የጎን አሞሌውን አጥብብ ወይም አስፋ</t>
+          <t>አስፋ</t>
         </is>
       </c>
       <c r="E238" s="13" t="inlineStr">
         <is>
-          <t>Cinaacha xiqqeessi ykn balleessi</t>
+          <t>Balleessi</t>
         </is>
       </c>
       <c r="F238" s="12" t="inlineStr">
         <is>
-          <t>ናይ ጎኒ መስመር ኣጽብብ ወይ ኣስፍሕ</t>
+          <t>ኣስፍሕ</t>
         </is>
       </c>
       <c r="G238" s="13" t="inlineStr">
         <is>
-          <t>Yaree ama balaadhi dhinaca</t>
+          <t>Balaadhi</t>
         </is>
       </c>
       <c r="H238" s="13" t="inlineStr">
         <is>
-          <t>Kunja au panua upande wa kando</t>
+          <t>Panua</t>
         </is>
       </c>
       <c r="I238" s="14" t="inlineStr"/>
@@ -16479,7 +16479,7 @@
     <row r="239" ht="44" customHeight="1">
       <c r="A239" s="11" t="inlineStr">
         <is>
-          <t>show_hide_channels</t>
+          <t>collapse_or_expand</t>
         </is>
       </c>
       <c r="B239" s="11" t="inlineStr">
@@ -16489,32 +16489,32 @@
       </c>
       <c r="C239" s="11" t="inlineStr">
         <is>
-          <t>Show or hide the channel list</t>
+          <t>Collapse or expand the sidebar</t>
         </is>
       </c>
       <c r="D239" s="12" t="inlineStr">
         <is>
-          <t>የመስመሮችን ዝርዝር አሳይ ወይም ደብቅ</t>
+          <t>የጎን አሞሌውን አጥብብ ወይም አስፋ</t>
         </is>
       </c>
       <c r="E239" s="13" t="inlineStr">
         <is>
-          <t>Tarreeffama karaalee agarsiisi ykn dhoksi</t>
+          <t>Cinaacha xiqqeessi ykn balleessi</t>
         </is>
       </c>
       <c r="F239" s="12" t="inlineStr">
         <is>
-          <t>ዝርዝር መስመራት ኣርኢ ወይ ሕባእ</t>
+          <t>ናይ ጎኒ መስመር ኣጽብብ ወይ ኣስፍሕ</t>
         </is>
       </c>
       <c r="G239" s="13" t="inlineStr">
         <is>
-          <t>Muuji ama qari liiska kanaalada</t>
+          <t>Yaree ama balaadhi dhinaca</t>
         </is>
       </c>
       <c r="H239" s="13" t="inlineStr">
         <is>
-          <t>Onyesha au ficha orodha ya njia</t>
+          <t>Kunja au panua upande wa kando</t>
         </is>
       </c>
       <c r="I239" s="14" t="inlineStr"/>
@@ -16522,7 +16522,7 @@
     <row r="240" ht="44" customHeight="1">
       <c r="A240" s="11" t="inlineStr">
         <is>
-          <t>today</t>
+          <t>show_hide_channels</t>
         </is>
       </c>
       <c r="B240" s="11" t="inlineStr">
@@ -16532,32 +16532,32 @@
       </c>
       <c r="C240" s="11" t="inlineStr">
         <is>
-          <t>Today</t>
+          <t>Show or hide the channel list</t>
         </is>
       </c>
       <c r="D240" s="12" t="inlineStr">
         <is>
-          <t>ዛሬ</t>
+          <t>የመስመሮችን ዝርዝር አሳይ ወይም ደብቅ</t>
         </is>
       </c>
       <c r="E240" s="13" t="inlineStr">
         <is>
-          <t>Har'a</t>
+          <t>Tarreeffama karaalee agarsiisi ykn dhoksi</t>
         </is>
       </c>
       <c r="F240" s="12" t="inlineStr">
         <is>
-          <t>ሎሚ</t>
+          <t>ዝርዝር መስመራት ኣርኢ ወይ ሕባእ</t>
         </is>
       </c>
       <c r="G240" s="13" t="inlineStr">
         <is>
-          <t>Maanta</t>
+          <t>Muuji ama qari liiska kanaalada</t>
         </is>
       </c>
       <c r="H240" s="13" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Onyesha au ficha orodha ya njia</t>
         </is>
       </c>
       <c r="I240" s="14" t="inlineStr"/>
@@ -16565,7 +16565,7 @@
     <row r="241" ht="44" customHeight="1">
       <c r="A241" s="11" t="inlineStr">
         <is>
-          <t>yesterday</t>
+          <t>today</t>
         </is>
       </c>
       <c r="B241" s="11" t="inlineStr">
@@ -16575,32 +16575,32 @@
       </c>
       <c r="C241" s="11" t="inlineStr">
         <is>
-          <t>Yesterday</t>
+          <t>Today</t>
         </is>
       </c>
       <c r="D241" s="12" t="inlineStr">
         <is>
-          <t>ትናንት</t>
+          <t>ዛሬ</t>
         </is>
       </c>
       <c r="E241" s="13" t="inlineStr">
         <is>
-          <t>Kaleessa</t>
+          <t>Har'a</t>
         </is>
       </c>
       <c r="F241" s="12" t="inlineStr">
         <is>
-          <t>ትማሊ</t>
+          <t>ሎሚ</t>
         </is>
       </c>
       <c r="G241" s="13" t="inlineStr">
         <is>
-          <t>Shalay</t>
+          <t>Maanta</t>
         </is>
       </c>
       <c r="H241" s="13" t="inlineStr">
         <is>
-          <t>Jana</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="I241" s="14" t="inlineStr"/>
@@ -16608,7 +16608,7 @@
     <row r="242" ht="44" customHeight="1">
       <c r="A242" s="11" t="inlineStr">
         <is>
-          <t>call_started</t>
+          <t>yesterday</t>
         </is>
       </c>
       <c r="B242" s="11" t="inlineStr">
@@ -16618,32 +16618,32 @@
       </c>
       <c r="C242" s="11" t="inlineStr">
         <is>
-          <t>The customer asked for a person here</t>
+          <t>Yesterday</t>
         </is>
       </c>
       <c r="D242" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛው እዚህ ላይ ሰው ጠየቀ</t>
+          <t>ትናንት</t>
         </is>
       </c>
       <c r="E242" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan asitti nama gaafate</t>
+          <t>Kaleessa</t>
         </is>
       </c>
       <c r="F242" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዓሚል ኣብዚ ሰብ ሓቲቱ</t>
+          <t>ትማሊ</t>
         </is>
       </c>
       <c r="G242" s="13" t="inlineStr">
         <is>
-          <t>Macmiilku halkan ayuu qof weydiistay</t>
+          <t>Shalay</t>
         </is>
       </c>
       <c r="H242" s="13" t="inlineStr">
         <is>
-          <t>Mteja aliomba mtu hapa</t>
+          <t>Jana</t>
         </is>
       </c>
       <c r="I242" s="14" t="inlineStr"/>
@@ -16651,7 +16651,7 @@
     <row r="243" ht="44" customHeight="1">
       <c r="A243" s="11" t="inlineStr">
         <is>
-          <t>no_messages</t>
+          <t>call_started</t>
         </is>
       </c>
       <c r="B243" s="11" t="inlineStr">
@@ -16661,32 +16661,32 @@
       </c>
       <c r="C243" s="11" t="inlineStr">
         <is>
-          <t>No messages in this conversation.</t>
+          <t>The customer asked for a person here</t>
         </is>
       </c>
       <c r="D243" s="12" t="inlineStr">
         <is>
-          <t>በዚህ ውይይት ውስጥ መልእክት የለም።</t>
+          <t>ደንበኛው እዚህ ላይ ሰው ጠየቀ</t>
         </is>
       </c>
       <c r="E243" s="13" t="inlineStr">
         <is>
-          <t>Marii kana keessa ergaan hin jiru.</t>
+          <t>Maamilaan asitti nama gaafate</t>
         </is>
       </c>
       <c r="F243" s="12" t="inlineStr">
         <is>
-          <t>ኣብዚ ዝርርብ መልእኽቲ የለን።</t>
+          <t>እቲ ዓሚል ኣብዚ ሰብ ሓቲቱ</t>
         </is>
       </c>
       <c r="G243" s="13" t="inlineStr">
         <is>
-          <t>Wadahadalkan fariin kuma jirto.</t>
+          <t>Macmiilku halkan ayuu qof weydiistay</t>
         </is>
       </c>
       <c r="H243" s="13" t="inlineStr">
         <is>
-          <t>Hakuna ujumbe katika mazungumzo haya.</t>
+          <t>Mteja aliomba mtu hapa</t>
         </is>
       </c>
       <c r="I243" s="14" t="inlineStr"/>
@@ -16694,7 +16694,7 @@
     <row r="244" ht="44" customHeight="1">
       <c r="A244" s="11" t="inlineStr">
         <is>
-          <t>donut_all_in_one</t>
+          <t>no_messages</t>
         </is>
       </c>
       <c r="B244" s="11" t="inlineStr">
@@ -16704,32 +16704,32 @@
       </c>
       <c r="C244" s="11" t="inlineStr">
         <is>
-          <t>The single {unit} was in {label}.</t>
+          <t>No messages in this conversation.</t>
         </is>
       </c>
       <c r="D244" s="12" t="inlineStr">
         <is>
-          <t>ብቸኛው {unit} በ{label} ነበር።</t>
+          <t>በዚህ ውይይት ውስጥ መልእክት የለም።</t>
         </is>
       </c>
       <c r="E244" s="13" t="inlineStr">
         <is>
-          <t>{unit} tokkichi {label} keessa ture.</t>
+          <t>Marii kana keessa ergaan hin jiru.</t>
         </is>
       </c>
       <c r="F244" s="12" t="inlineStr">
         <is>
-          <t>እቲ ሓደ {unit} ብ{label} ነይሩ።</t>
+          <t>ኣብዚ ዝርርብ መልእኽቲ የለን።</t>
         </is>
       </c>
       <c r="G244" s="13" t="inlineStr">
         <is>
-          <t>{unit} kaliya wuxuu ku jiray {label}.</t>
+          <t>Wadahadalkan fariin kuma jirto.</t>
         </is>
       </c>
       <c r="H244" s="13" t="inlineStr">
         <is>
-          <t>{unit} pekee ilikuwa katika {label}.</t>
+          <t>Hakuna ujumbe katika mazungumzo haya.</t>
         </is>
       </c>
       <c r="I244" s="14" t="inlineStr"/>
@@ -16737,7 +16737,7 @@
     <row r="245" ht="44" customHeight="1">
       <c r="A245" s="11" t="inlineStr">
         <is>
-          <t>channel_all_from_one</t>
+          <t>donut_all_in_one</t>
         </is>
       </c>
       <c r="B245" s="11" t="inlineStr">
@@ -16747,32 +16747,32 @@
       </c>
       <c r="C245" s="11" t="inlineStr">
         <is>
-          <t>The single conversation came from {label}.</t>
+          <t>The single {unit} was in {label}.</t>
         </is>
       </c>
       <c r="D245" s="12" t="inlineStr">
         <is>
-          <t>ብቸኛው ውይይት ከ{label} መጥቷል።</t>
+          <t>ብቸኛው {unit} በ{label} ነበር።</t>
         </is>
       </c>
       <c r="E245" s="13" t="inlineStr">
         <is>
-          <t>Mariin tokkichi {label} irraa dhufe.</t>
+          <t>{unit} tokkichi {label} keessa ture.</t>
         </is>
       </c>
       <c r="F245" s="12" t="inlineStr">
         <is>
-          <t>እቲ ሓደ ዝርርብ ካብ {label} መጺኡ።</t>
+          <t>እቲ ሓደ {unit} ብ{label} ነይሩ።</t>
         </is>
       </c>
       <c r="G245" s="13" t="inlineStr">
         <is>
-          <t>Wadahadalka kaliya wuxuu ka yimid {label}.</t>
+          <t>{unit} kaliya wuxuu ku jiray {label}.</t>
         </is>
       </c>
       <c r="H245" s="13" t="inlineStr">
         <is>
-          <t>Mazungumzo pekee yalitoka {label}.</t>
+          <t>{unit} pekee ilikuwa katika {label}.</t>
         </is>
       </c>
       <c r="I245" s="14" t="inlineStr"/>
@@ -16780,7 +16780,7 @@
     <row r="246" ht="44" customHeight="1">
       <c r="A246" s="11" t="inlineStr">
         <is>
-          <t>unit_conversation</t>
+          <t>channel_all_from_one</t>
         </is>
       </c>
       <c r="B246" s="11" t="inlineStr">
@@ -16790,32 +16790,32 @@
       </c>
       <c r="C246" s="11" t="inlineStr">
         <is>
-          <t>conversation</t>
+          <t>The single conversation came from {label}.</t>
         </is>
       </c>
       <c r="D246" s="12" t="inlineStr">
         <is>
-          <t>ውይይት</t>
+          <t>ብቸኛው ውይይት ከ{label} መጥቷል።</t>
         </is>
       </c>
       <c r="E246" s="13" t="inlineStr">
         <is>
-          <t>marii</t>
+          <t>Mariin tokkichi {label} irraa dhufe.</t>
         </is>
       </c>
       <c r="F246" s="12" t="inlineStr">
         <is>
-          <t>ዝርርብ</t>
+          <t>እቲ ሓደ ዝርርብ ካብ {label} መጺኡ።</t>
         </is>
       </c>
       <c r="G246" s="13" t="inlineStr">
         <is>
-          <t>wadahadal</t>
+          <t>Wadahadalka kaliya wuxuu ka yimid {label}.</t>
         </is>
       </c>
       <c r="H246" s="13" t="inlineStr">
         <is>
-          <t>mazungumzo</t>
+          <t>Mazungumzo pekee yalitoka {label}.</t>
         </is>
       </c>
       <c r="I246" s="14" t="inlineStr"/>
@@ -16823,7 +16823,7 @@
     <row r="247" ht="44" customHeight="1">
       <c r="A247" s="11" t="inlineStr">
         <is>
-          <t>live_sessions</t>
+          <t>unit_conversation</t>
         </is>
       </c>
       <c r="B247" s="11" t="inlineStr">
@@ -16833,32 +16833,32 @@
       </c>
       <c r="C247" s="11" t="inlineStr">
         <is>
-          <t>Live sessions</t>
+          <t>conversation</t>
         </is>
       </c>
       <c r="D247" s="12" t="inlineStr">
         <is>
-          <t>የቀጥታ ክፍለ-ጊዜዎች</t>
+          <t>ውይይት</t>
         </is>
       </c>
       <c r="E247" s="13" t="inlineStr">
         <is>
-          <t>Marii kallattii</t>
+          <t>marii</t>
         </is>
       </c>
       <c r="F247" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታ ክፍለ-ግዜታት</t>
+          <t>ዝርርብ</t>
         </is>
       </c>
       <c r="G247" s="13" t="inlineStr">
         <is>
-          <t>Kalfadhiyada tooska ah</t>
+          <t>wadahadal</t>
         </is>
       </c>
       <c r="H247" s="13" t="inlineStr">
         <is>
-          <t>Vikao vya Moja kwa Moja</t>
+          <t>mazungumzo</t>
         </is>
       </c>
       <c r="I247" s="14" t="inlineStr"/>
@@ -16866,7 +16866,7 @@
     <row r="248" ht="44" customHeight="1">
       <c r="A248" s="11" t="inlineStr">
         <is>
-          <t>switched_off_for_bank</t>
+          <t>live_sessions</t>
         </is>
       </c>
       <c r="B248" s="11" t="inlineStr">
@@ -16876,32 +16876,32 @@
       </c>
       <c r="C248" s="11" t="inlineStr">
         <is>
-          <t>Switched off for this bank</t>
+          <t>Live sessions</t>
         </is>
       </c>
       <c r="D248" s="12" t="inlineStr">
         <is>
-          <t>ለዚህ ባንክ ጠፍቷል</t>
+          <t>የቀጥታ ክፍለ-ጊዜዎች</t>
         </is>
       </c>
       <c r="E248" s="13" t="inlineStr">
         <is>
-          <t>Baankii kanaaf dhaamsameera</t>
+          <t>Marii kallattii</t>
         </is>
       </c>
       <c r="F248" s="12" t="inlineStr">
         <is>
-          <t>ነዚ ባንኪ ጠፊኡ</t>
+          <t>ቀጥታ ክፍለ-ግዜታት</t>
         </is>
       </c>
       <c r="G248" s="13" t="inlineStr">
         <is>
-          <t>Bangigan waa la damiyay</t>
+          <t>Kalfadhiyada tooska ah</t>
         </is>
       </c>
       <c r="H248" s="13" t="inlineStr">
         <is>
-          <t>Vimezimwa kwa Benki Hii</t>
+          <t>Vikao vya Moja kwa Moja</t>
         </is>
       </c>
       <c r="I248" s="14" t="inlineStr"/>
@@ -16909,7 +16909,7 @@
     <row r="249" ht="44" customHeight="1">
       <c r="A249" s="11" t="inlineStr">
         <is>
-          <t>switched_on_nobody_on_duty</t>
+          <t>switched_off_for_bank</t>
         </is>
       </c>
       <c r="B249" s="11" t="inlineStr">
@@ -16919,32 +16919,32 @@
       </c>
       <c r="C249" s="11" t="inlineStr">
         <is>
-          <t>Switched on — but nobody is on duty</t>
+          <t>Switched off for this bank</t>
         </is>
       </c>
       <c r="D249" s="12" t="inlineStr">
         <is>
-          <t>በርቷል — ግን ማንም በሥራ ላይ የለም</t>
+          <t>ለዚህ ባንክ ጠፍቷል</t>
         </is>
       </c>
       <c r="E249" s="13" t="inlineStr">
         <is>
-          <t>Banameera — garuu namni hojii irra hin jiru</t>
+          <t>Baankii kanaaf dhaamsameera</t>
         </is>
       </c>
       <c r="F249" s="12" t="inlineStr">
         <is>
-          <t>በሪሁ — ግና ዋላ ሓደ ኣብ ስራሕ የለን</t>
+          <t>ነዚ ባንኪ ጠፊኡ</t>
         </is>
       </c>
       <c r="G249" s="13" t="inlineStr">
         <is>
-          <t>Waa la shiday — laakiin qofna shaqada ma joogo</t>
+          <t>Bangigan waa la damiyay</t>
         </is>
       </c>
       <c r="H249" s="13" t="inlineStr">
         <is>
-          <t>Vimewashwa — lakini hakuna aliye kazini</t>
+          <t>Vimezimwa kwa Benki Hii</t>
         </is>
       </c>
       <c r="I249" s="14" t="inlineStr"/>
@@ -16952,7 +16952,7 @@
     <row r="250" ht="44" customHeight="1">
       <c r="A250" s="11" t="inlineStr">
         <is>
-          <t>no_teller_button</t>
+          <t>switched_on_nobody_on_duty</t>
         </is>
       </c>
       <c r="B250" s="11" t="inlineStr">
@@ -16962,32 +16962,32 @@
       </c>
       <c r="C250" s="11" t="inlineStr">
         <is>
-          <t>No “Speak to a teller” button appears in your widget.</t>
+          <t>Switched on — but nobody is on duty</t>
         </is>
       </c>
       <c r="D250" s="12" t="inlineStr">
         <is>
-          <t>በመግብርዎ ውስጥ “ከገንዘብ ተቀባይ ጋር ይነጋገሩ” የሚል አዝራር አይታይም።</t>
+          <t>በርቷል — ግን ማንም በሥራ ላይ የለም</t>
         </is>
       </c>
       <c r="E250" s="13" t="inlineStr">
         <is>
-          <t>Widjetii keessan keessatti qabduun “Namaa waliin haasa'aa” hin mul'atu.</t>
+          <t>Banameera — garuu namni hojii irra hin jiru</t>
         </is>
       </c>
       <c r="F250" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መግበሪኹም “ምስ ተቐባሊ ገንዘብ ተዛረቡ” ዝብል መጠወቒ ኣይረአን።</t>
+          <t>በሪሁ — ግና ዋላ ሓደ ኣብ ስራሕ የለን</t>
         </is>
       </c>
       <c r="G250" s="13" t="inlineStr">
         <is>
-          <t>Badhanka “La hadal shaqaale” kama muuqan widget-kaaga.</t>
+          <t>Waa la shiday — laakiin qofna shaqada ma joogo</t>
         </is>
       </c>
       <c r="H250" s="13" t="inlineStr">
         <is>
-          <t>Hakuna kitufe cha "Zungumza na Afisa" kinachoonekana kwenye kidirisha chako.</t>
+          <t>Vimewashwa — lakini hakuna aliye kazini</t>
         </is>
       </c>
       <c r="I250" s="14" t="inlineStr"/>
@@ -16995,7 +16995,7 @@
     <row r="251" ht="44" customHeight="1">
       <c r="A251" s="11" t="inlineStr">
         <is>
-          <t>on_duty_explainer</t>
+          <t>no_teller_button</t>
         </is>
       </c>
       <c r="B251" s="11" t="inlineStr">
@@ -17005,32 +17005,32 @@
       </c>
       <c r="C251" s="11" t="inlineStr">
         <is>
-          <t>You are on duty, so waiting customers can be routed to you. Go off duty from the sidebar when you step away — you stay on the air anywhere in the console until you do.</t>
+          <t>No “Speak to a teller” button appears in your widget.</t>
         </is>
       </c>
       <c r="D251" s="12" t="inlineStr">
         <is>
-          <t>በሥራ ላይ ነዎት፤ ስለዚህ የሚጠብቁ ደንበኞች ወደ እርስዎ ሊመሩ ይችላሉ። ሲርቁ ከጎን አሞሌው ከሥራ ውጡ — እስከዚያ ድረስ በየትኛውም ገጽ ላይ በሥራ ላይ ይቆያሉ።</t>
+          <t>በመግብርዎ ውስጥ “ከገንዘብ ተቀባይ ጋር ይነጋገሩ” የሚል አዝራር አይታይም።</t>
         </is>
       </c>
       <c r="E251" s="13" t="inlineStr">
         <is>
-          <t>Hojii irra jirtu, kanaafuu maamiltoonni eegaa jiran gara keessan qajeelfamuu danda'u. Yeroo achii deemtan cinaacha irraa hojii keessaa ba'aa — hanga sanatti fuula kamiyyuu irratti hojii irra turtu.</t>
+          <t>Widjetii keessan keessatti qabduun “Namaa waliin haasa'aa” hin mul'atu.</t>
         </is>
       </c>
       <c r="F251" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ስራሕ ኢኹም፣ ስለዚ ዝጽበዩ ዓማዊል ናባኹም ክምርሑ ይኽእሉ። ክትርሕቁ ከለኹም ካብ ናይ ጎኒ መስመር ካብ ስራሕ ውጹ — ክሳብ ሽዑ ኣብ ዝኾነ ገጽ ኣብ ስራሕ ትጸንሑ።</t>
+          <t>ኣብ መግበሪኹም “ምስ ተቐባሊ ገንዘብ ተዛረቡ” ዝብል መጠወቒ ኣይረአን።</t>
         </is>
       </c>
       <c r="G251" s="13" t="inlineStr">
         <is>
-          <t>Shaqada ayaad joogtaa, sidaas darteed macaamiisha sugaya waa lagu soo dhiibi karaa. Marka aad tagto shaqada ka bax dhinaca — ilaa markaas bog kasta ayaad ku sii shaqeynaysaa.</t>
+          <t>Badhanka “La hadal shaqaale” kama muuqan widget-kaaga.</t>
         </is>
       </c>
       <c r="H251" s="13" t="inlineStr">
         <is>
-          <t>Upo kazini, kwa hivyo wateja wanaosubiri wanaweza kuelekezwa kwako. Toka kazini kutoka upande wa kando unapoondoka — unabaki kwenye mtandao popote kwenye paneli mpaka utakapofanya hivyo.</t>
+          <t>Hakuna kitufe cha "Zungumza na Afisa" kinachoonekana kwenye kidirisha chako.</t>
         </is>
       </c>
       <c r="I251" s="14" t="inlineStr"/>
@@ -17038,7 +17038,7 @@
     <row r="252" ht="44" customHeight="1">
       <c r="A252" s="11" t="inlineStr">
         <is>
-          <t>off_duty_explainer</t>
+          <t>on_duty_explainer</t>
         </is>
       </c>
       <c r="B252" s="11" t="inlineStr">
@@ -17048,32 +17048,32 @@
       </c>
       <c r="C252" s="11" t="inlineStr">
         <is>
-          <t>Switch On duty in the sidebar to start taking calls. It follows you across every page, so you no longer have to keep this one open.</t>
+          <t>You are on duty, so waiting customers can be routed to you. Go off duty from the sidebar when you step away — you stay on the air anywhere in the console until you do.</t>
         </is>
       </c>
       <c r="D252" s="12" t="inlineStr">
         <is>
-          <t>ጥሪዎችን መቀበል ለመጀመር ከጎን አሞሌው “በሥራ ላይ” ያብሩ። በሁሉም ገጽ ላይ ይከተልዎታል፤ ስለዚህ ይህን ገጽ ክፍት ማድረግ አያስፈልግም።</t>
+          <t>በሥራ ላይ ነዎት፤ ስለዚህ የሚጠብቁ ደንበኞች ወደ እርስዎ ሊመሩ ይችላሉ። ሲርቁ ከጎን አሞሌው ከሥራ ውጡ — እስከዚያ ድረስ በየትኛውም ገጽ ላይ በሥራ ላይ ይቆያሉ።</t>
         </is>
       </c>
       <c r="E252" s="13" t="inlineStr">
         <is>
-          <t>Bilbila fudhachuu jalqabuuf cinaacha irraa “Hojii irra” banaa. Fuula hunda irratti isin hordofa, kanaafuu fuula kana banaa gochuun hin barbaachisu.</t>
+          <t>Hojii irra jirtu, kanaafuu maamiltoonni eegaa jiran gara keessan qajeelfamuu danda'u. Yeroo achii deemtan cinaacha irraa hojii keessaa ba'aa — hanga sanatti fuula kamiyyuu irratti hojii irra turtu.</t>
         </is>
       </c>
       <c r="F252" s="12" t="inlineStr">
         <is>
-          <t>ጻውዒታት ክትቅበሉ ንምጅማር ካብ ናይ ጎኒ መስመር “ኣብ ስራሕ” ኣብርሁ። ኣብ ኩሉ ገጽ ይስዕበኩም፣ ስለዚ ነዚ ገጽ ክፉት ምግባር ኣየድልን።</t>
+          <t>ኣብ ስራሕ ኢኹም፣ ስለዚ ዝጽበዩ ዓማዊል ናባኹም ክምርሑ ይኽእሉ። ክትርሕቁ ከለኹም ካብ ናይ ጎኒ መስመር ካብ ስራሕ ውጹ — ክሳብ ሽዑ ኣብ ዝኾነ ገጽ ኣብ ስራሕ ትጸንሑ።</t>
         </is>
       </c>
       <c r="G252" s="13" t="inlineStr">
         <is>
-          <t>Si aad u bilowdo qaadista wicitaannada, dhinaca ka shid “Shaqada”. Bog kasta ayuu kula socdaa, sidaas darteed uma baahnid inaad tan furan ka tagto.</t>
+          <t>Shaqada ayaad joogtaa, sidaas darteed macaamiisha sugaya waa lagu soo dhiibi karaa. Marka aad tagto shaqada ka bax dhinaca — ilaa markaas bog kasta ayaad ku sii shaqeynaysaa.</t>
         </is>
       </c>
       <c r="H252" s="13" t="inlineStr">
         <is>
-          <t>Washa Kazini kwenye upande wa kando ili kuanza kupokea simu. Inakufuata kwenye kila ukurasa, hivyo huhitaji tena kuweka huu wazi.</t>
+          <t>Upo kazini, kwa hivyo wateja wanaosubiri wanaweza kuelekezwa kwako. Toka kazini kutoka upande wa kando unapoondoka — unabaki kwenye mtandao popote kwenye paneli mpaka utakapofanya hivyo.</t>
         </is>
       </c>
       <c r="I252" s="14" t="inlineStr"/>
@@ -17081,7 +17081,7 @@
     <row r="253" ht="44" customHeight="1">
       <c r="A253" s="11" t="inlineStr">
         <is>
-          <t>colleague_must_be_on_duty</t>
+          <t>off_duty_explainer</t>
         </is>
       </c>
       <c r="B253" s="11" t="inlineStr">
@@ -17091,32 +17091,32 @@
       </c>
       <c r="C253" s="11" t="inlineStr">
         <is>
-          <t>A colleague with permission to take calls has to be on duty before customers are offered one.</t>
+          <t>Switch On duty in the sidebar to start taking calls. It follows you across every page, so you no longer have to keep this one open.</t>
         </is>
       </c>
       <c r="D253" s="12" t="inlineStr">
         <is>
-          <t>ጥሪ የመቀበል ፈቃድ ያለው ባልደረባ በሥራ ላይ መሆን አለበት፤ ከዚያ በፊት ለደንበኞች አይቀርብም።</t>
+          <t>ጥሪዎችን መቀበል ለመጀመር ከጎን አሞሌው “በሥራ ላይ” ያብሩ። በሁሉም ገጽ ላይ ይከተልዎታል፤ ስለዚህ ይህን ገጽ ክፍት ማድረግ አያስፈልግም።</t>
         </is>
       </c>
       <c r="E253" s="13" t="inlineStr">
         <is>
-          <t>Hojjetaan hayyama bilbila fudhachuu qabu hojii irra jiraachuu qaba, sana dura maamiltootaaf hin dhiyaatu.</t>
+          <t>Bilbila fudhachuu jalqabuuf cinaacha irraa “Hojii irra” banaa. Fuula hunda irratti isin hordofa, kanaafuu fuula kana banaa gochuun hin barbaachisu.</t>
         </is>
       </c>
       <c r="F253" s="12" t="inlineStr">
         <is>
-          <t>ጻውዒት ናይ ምቕባል ፍቓድ ዘለዎ መሳርሕቲ ኣብ ስራሕ ክህሉ ኣለዎ፣ ቅድሚኡ ንዓማዊል ኣይቀርብን።</t>
+          <t>ጻውዒታት ክትቅበሉ ንምጅማር ካብ ናይ ጎኒ መስመር “ኣብ ስራሕ” ኣብርሁ። ኣብ ኩሉ ገጽ ይስዕበኩም፣ ስለዚ ነዚ ገጽ ክፉት ምግባር ኣየድልን።</t>
         </is>
       </c>
       <c r="G253" s="13" t="inlineStr">
         <is>
-          <t>Shaqaale haysta ogolaanshaha qaadista wicitaannada waa inuu shaqada joogaa ka hor inta aan macaamiisha la siin.</t>
+          <t>Si aad u bilowdo qaadista wicitaannada, dhinaca ka shid “Shaqada”. Bog kasta ayuu kula socdaa, sidaas darteed uma baahnid inaad tan furan ka tagto.</t>
         </is>
       </c>
       <c r="H253" s="13" t="inlineStr">
         <is>
-          <t>Mwenzako mwenye ruhusa ya kupokea simu lazima awe kazini kabla wateja hawajapewa fursa hiyo.</t>
+          <t>Washa Kazini kwenye upande wa kando ili kuanza kupokea simu. Inakufuata kwenye kila ukurasa, hivyo huhitaji tena kuweka huu wazi.</t>
         </is>
       </c>
       <c r="I253" s="14" t="inlineStr"/>
@@ -17124,7 +17124,7 @@
     <row r="254" ht="44" customHeight="1">
       <c r="A254" s="11" t="inlineStr">
         <is>
-          <t>i_can_converse_in</t>
+          <t>colleague_must_be_on_duty</t>
         </is>
       </c>
       <c r="B254" s="11" t="inlineStr">
@@ -17134,32 +17134,32 @@
       </c>
       <c r="C254" s="11" t="inlineStr">
         <is>
-          <t>I can hold a conversation in:</t>
+          <t>A colleague with permission to take calls has to be on duty before customers are offered one.</t>
         </is>
       </c>
       <c r="D254" s="12" t="inlineStr">
         <is>
-          <t>በእነዚህ ቋንቋዎች መነጋገር እችላለሁ፦</t>
+          <t>ጥሪ የመቀበል ፈቃድ ያለው ባልደረባ በሥራ ላይ መሆን አለበት፤ ከዚያ በፊት ለደንበኞች አይቀርብም።</t>
         </is>
       </c>
       <c r="E254" s="13" t="inlineStr">
         <is>
-          <t>Afaanota kanneeniin haasa'uu nan danda'a:</t>
+          <t>Hojjetaan hayyama bilbila fudhachuu qabu hojii irra jiraachuu qaba, sana dura maamiltootaaf hin dhiyaatu.</t>
         </is>
       </c>
       <c r="F254" s="12" t="inlineStr">
         <is>
-          <t>በዞም ቋንቋታት ክዛረብ እኽእል፦</t>
+          <t>ጻውዒት ናይ ምቕባል ፍቓድ ዘለዎ መሳርሕቲ ኣብ ስራሕ ክህሉ ኣለዎ፣ ቅድሚኡ ንዓማዊል ኣይቀርብን።</t>
         </is>
       </c>
       <c r="G254" s="13" t="inlineStr">
         <is>
-          <t>Waxaan ku hadli karaa:</t>
+          <t>Shaqaale haysta ogolaanshaha qaadista wicitaannada waa inuu shaqada joogaa ka hor inta aan macaamiisha la siin.</t>
         </is>
       </c>
       <c r="H254" s="13" t="inlineStr">
         <is>
-          <t>Ninaweza kufanya mazungumzo kwa:</t>
+          <t>Mwenzako mwenye ruhusa ya kupokea simu lazima awe kazini kabla wateja hawajapewa fursa hiyo.</t>
         </is>
       </c>
       <c r="I254" s="14" t="inlineStr"/>
@@ -17167,7 +17167,7 @@
     <row r="255" ht="44" customHeight="1">
       <c r="A255" s="11" t="inlineStr">
         <is>
-          <t>languages_picked_note</t>
+          <t>i_can_converse_in</t>
         </is>
       </c>
       <c r="B255" s="11" t="inlineStr">
@@ -17177,32 +17177,32 @@
       </c>
       <c r="C255" s="11" t="inlineStr">
         <is>
-          <t>Customers writing in these reach you first. Everyone else still reaches you — after a short wait, so nobody is stranded.</t>
+          <t>I can hold a conversation in:</t>
         </is>
       </c>
       <c r="D255" s="12" t="inlineStr">
         <is>
-          <t>በእነዚህ ቋንቋዎች የሚጽፉ ደንበኞች መጀመሪያ ወደ እርስዎ ይደርሳሉ። ሌሎችም ይደርሳሉ — ከአጭር ጥበቃ በኋላ፤ ማንም አይቀርም።</t>
+          <t>በእነዚህ ቋንቋዎች መነጋገር እችላለሁ፦</t>
         </is>
       </c>
       <c r="E255" s="13" t="inlineStr">
         <is>
-          <t>Maamiltoonni afaanota kanaan barreessan jalqaba isin bira ga'u. Kaan hundinuu ammas isin bira ga'u — eegumsa gabaabaa booda, namni hafu hin jiru.</t>
+          <t>Afaanota kanneeniin haasa'uu nan danda'a:</t>
         </is>
       </c>
       <c r="F255" s="12" t="inlineStr">
         <is>
-          <t>በዞም ቋንቋታት ዝጽሕፉ ዓማዊል ቅድም ናባኹም ይበጽሑ። እቶም ካልኦት እውን ይበጽሑ — ድሕሪ ሓጺር ጽበት፣ ዋላ ሓደ ኣይተርፍን።</t>
+          <t>በዞም ቋንቋታት ክዛረብ እኽእል፦</t>
         </is>
       </c>
       <c r="G255" s="13" t="inlineStr">
         <is>
-          <t>Macaamiisha ku qora kuwan ayaa marka hore kugu soo gaara. Qof kastana wuu ku soo gaari doonaa — sug gaaban ka dib, sidaas qofna ma harayo.</t>
+          <t>Waxaan ku hadli karaa:</t>
         </is>
       </c>
       <c r="H255" s="13" t="inlineStr">
         <is>
-          <t>Wateja wanaoandika kwa lugha hizi wanakufikia kwanza. Kila mtu mwingine bado anakufikia — baada ya kusubiri kidogo, ili asibaki bila msaada.</t>
+          <t>Ninaweza kufanya mazungumzo kwa:</t>
         </is>
       </c>
       <c r="I255" s="14" t="inlineStr"/>
@@ -17210,7 +17210,7 @@
     <row r="256" ht="44" customHeight="1">
       <c r="A256" s="11" t="inlineStr">
         <is>
-          <t>languages_none_note</t>
+          <t>languages_picked_note</t>
         </is>
       </c>
       <c r="B256" s="11" t="inlineStr">
@@ -17220,32 +17220,32 @@
       </c>
       <c r="C256" s="11" t="inlineStr">
         <is>
-          <t>Nothing selected, so every waiting customer is offered to you in plain oldest-first order.</t>
+          <t>Customers writing in these reach you first. Everyone else still reaches you — after a short wait, so nobody is stranded.</t>
         </is>
       </c>
       <c r="D256" s="12" t="inlineStr">
         <is>
-          <t>ምንም አልተመረጠም፤ ስለዚህ እያንዳንዱ የሚጠብቅ ደንበኛ በቀላል ቀዳሚ-መጀመሪያ ቅደም ተከተል ይቀርብልዎታል።</t>
+          <t>በእነዚህ ቋንቋዎች የሚጽፉ ደንበኞች መጀመሪያ ወደ እርስዎ ይደርሳሉ። ሌሎችም ይደርሳሉ — ከአጭር ጥበቃ በኋላ፤ ማንም አይቀርም።</t>
         </is>
       </c>
       <c r="E256" s="13" t="inlineStr">
         <is>
-          <t>Wanti filatame hin jiru, kanaafuu maamilli eegaa jiru hundi tartiiba dursaa-jalqabaatiin isinii dhiyaata.</t>
+          <t>Maamiltoonni afaanota kanaan barreessan jalqaba isin bira ga'u. Kaan hundinuu ammas isin bira ga'u — eegumsa gabaabaa booda, namni hafu hin jiru.</t>
         </is>
       </c>
       <c r="F256" s="12" t="inlineStr">
         <is>
-          <t>ዋላ ሓደ ኣይተመርጸን፣ ስለዚ ነፍስ ወከፍ ዝጽበ ዓሚል ብቐሊል ናይ ቀዳምነት ስርዓት ይቐርበልኩም።</t>
+          <t>በዞም ቋንቋታት ዝጽሕፉ ዓማዊል ቅድም ናባኹም ይበጽሑ። እቶም ካልኦት እውን ይበጽሑ — ድሕሪ ሓጺር ጽበት፣ ዋላ ሓደ ኣይተርፍን።</t>
         </is>
       </c>
       <c r="G256" s="13" t="inlineStr">
         <is>
-          <t>Waxba lama dooran, sidaas darteed macmiil kasta oo sugaya waxaa laguu soo bandhigayaa sida caadiga ah ee ugu horreeya.</t>
+          <t>Macaamiisha ku qora kuwan ayaa marka hore kugu soo gaara. Qof kastana wuu ku soo gaari doonaa — sug gaaban ka dib, sidaas qofna ma harayo.</t>
         </is>
       </c>
       <c r="H256" s="13" t="inlineStr">
         <is>
-          <t>Hakuna kilichochaguliwa, kwa hivyo kila mteja anayesubiri anapewa kwako kwa mpangilio wa zamani zaidi kwanza.</t>
+          <t>Wateja wanaoandika kwa lugha hizi wanakufikia kwanza. Kila mtu mwingine bado anakufikia — baada ya kusubiri kidogo, ili asibaki bila msaada.</t>
         </is>
       </c>
       <c r="I256" s="14" t="inlineStr"/>
@@ -17253,7 +17253,7 @@
     <row r="257" ht="44" customHeight="1">
       <c r="A257" s="11" t="inlineStr">
         <is>
-          <t>languages_updated</t>
+          <t>languages_none_note</t>
         </is>
       </c>
       <c r="B257" s="11" t="inlineStr">
@@ -17263,32 +17263,32 @@
       </c>
       <c r="C257" s="11" t="inlineStr">
         <is>
-          <t>Languages updated</t>
+          <t>Nothing selected, so every waiting customer is offered to you in plain oldest-first order.</t>
         </is>
       </c>
       <c r="D257" s="12" t="inlineStr">
         <is>
-          <t>ቋንቋዎች ተዘምነዋል</t>
+          <t>ምንም አልተመረጠም፤ ስለዚህ እያንዳንዱ የሚጠብቅ ደንበኛ በቀላል ቀዳሚ-መጀመሪያ ቅደም ተከተል ይቀርብልዎታል።</t>
         </is>
       </c>
       <c r="E257" s="13" t="inlineStr">
         <is>
-          <t>Afaanonni haaromfaman</t>
+          <t>Wanti filatame hin jiru, kanaafuu maamilli eegaa jiru hundi tartiiba dursaa-jalqabaatiin isinii dhiyaata.</t>
         </is>
       </c>
       <c r="F257" s="12" t="inlineStr">
         <is>
-          <t>ቋንቋታት ተሓዲሶም</t>
+          <t>ዋላ ሓደ ኣይተመርጸን፣ ስለዚ ነፍስ ወከፍ ዝጽበ ዓሚል ብቐሊል ናይ ቀዳምነት ስርዓት ይቐርበልኩም።</t>
         </is>
       </c>
       <c r="G257" s="13" t="inlineStr">
         <is>
-          <t>Luqadaha waa la cusbooneysiiyay</t>
+          <t>Waxba lama dooran, sidaas darteed macmiil kasta oo sugaya waxaa laguu soo bandhigayaa sida caadiga ah ee ugu horreeya.</t>
         </is>
       </c>
       <c r="H257" s="13" t="inlineStr">
         <is>
-          <t>Lugha Zimesasishwa</t>
+          <t>Hakuna kilichochaguliwa, kwa hivyo kila mteja anayesubiri anapewa kwako kwa mpangilio wa zamani zaidi kwanza.</t>
         </is>
       </c>
       <c r="I257" s="14" t="inlineStr"/>
@@ -17296,7 +17296,7 @@
     <row r="258" ht="44" customHeight="1">
       <c r="A258" s="11" t="inlineStr">
         <is>
-          <t>media_video</t>
+          <t>languages_updated</t>
         </is>
       </c>
       <c r="B258" s="11" t="inlineStr">
@@ -17306,32 +17306,32 @@
       </c>
       <c r="C258" s="11" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Languages updated</t>
         </is>
       </c>
       <c r="D258" s="12" t="inlineStr">
         <is>
-          <t>ቪዲዮ</t>
+          <t>ቋንቋዎች ተዘምነዋል</t>
         </is>
       </c>
       <c r="E258" s="13" t="inlineStr">
         <is>
-          <t>Viidiyoo</t>
+          <t>Afaanonni haaromfaman</t>
         </is>
       </c>
       <c r="F258" s="12" t="inlineStr">
         <is>
-          <t>ቪድዮ</t>
+          <t>ቋንቋታት ተሓዲሶም</t>
         </is>
       </c>
       <c r="G258" s="13" t="inlineStr">
         <is>
-          <t>Fiidyow</t>
+          <t>Luqadaha waa la cusbooneysiiyay</t>
         </is>
       </c>
       <c r="H258" s="13" t="inlineStr">
         <is>
-          <t>Vidio</t>
+          <t>Lugha Zimesasishwa</t>
         </is>
       </c>
       <c r="I258" s="14" t="inlineStr"/>
@@ -17339,7 +17339,7 @@
     <row r="259" ht="44" customHeight="1">
       <c r="A259" s="11" t="inlineStr">
         <is>
-          <t>media_audio</t>
+          <t>media_video</t>
         </is>
       </c>
       <c r="B259" s="11" t="inlineStr">
@@ -17349,32 +17349,32 @@
       </c>
       <c r="C259" s="11" t="inlineStr">
         <is>
-          <t>Audio</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="D259" s="12" t="inlineStr">
         <is>
-          <t>ድምፅ</t>
+          <t>ቪዲዮ</t>
         </is>
       </c>
       <c r="E259" s="13" t="inlineStr">
         <is>
-          <t>Sagalee</t>
+          <t>Viidiyoo</t>
         </is>
       </c>
       <c r="F259" s="12" t="inlineStr">
         <is>
-          <t>ድምጺ</t>
+          <t>ቪድዮ</t>
         </is>
       </c>
       <c r="G259" s="13" t="inlineStr">
         <is>
-          <t>Cod</t>
+          <t>Fiidyow</t>
         </is>
       </c>
       <c r="H259" s="13" t="inlineStr">
         <is>
-          <t>Sauti</t>
+          <t>Vidio</t>
         </is>
       </c>
       <c r="I259" s="14" t="inlineStr"/>
@@ -17382,7 +17382,7 @@
     <row r="260" ht="44" customHeight="1">
       <c r="A260" s="11" t="inlineStr">
         <is>
-          <t>not_your_language</t>
+          <t>media_audio</t>
         </is>
       </c>
       <c r="B260" s="11" t="inlineStr">
@@ -17392,32 +17392,32 @@
       </c>
       <c r="C260" s="11" t="inlineStr">
         <is>
-          <t>not your language</t>
+          <t>Audio</t>
         </is>
       </c>
       <c r="D260" s="12" t="inlineStr">
         <is>
-          <t>የእርስዎ ቋንቋ አይደለም</t>
+          <t>ድምፅ</t>
         </is>
       </c>
       <c r="E260" s="13" t="inlineStr">
         <is>
-          <t>afaan keessanii miti</t>
+          <t>Sagalee</t>
         </is>
       </c>
       <c r="F260" s="12" t="inlineStr">
         <is>
-          <t>ናትኩም ቋንቋ ኣይኮነን</t>
+          <t>ድምጺ</t>
         </is>
       </c>
       <c r="G260" s="13" t="inlineStr">
         <is>
-          <t>ma aha luqaddaada</t>
+          <t>Cod</t>
         </is>
       </c>
       <c r="H260" s="13" t="inlineStr">
         <is>
-          <t>si lugha yako</t>
+          <t>Sauti</t>
         </is>
       </c>
       <c r="I260" s="14" t="inlineStr"/>
@@ -17425,7 +17425,7 @@
     <row r="261" ht="44" customHeight="1">
       <c r="A261" s="11" t="inlineStr">
         <is>
-          <t>languages_first_note</t>
+          <t>not_your_language</t>
         </is>
       </c>
       <c r="B261" s="11" t="inlineStr">
@@ -17435,32 +17435,32 @@
       </c>
       <c r="C261" s="11" t="inlineStr">
         <is>
-          <t>Your languages first, longest wait within each. Anyone waiting too long moves to the top whatever they speak.</t>
+          <t>not your language</t>
         </is>
       </c>
       <c r="D261" s="12" t="inlineStr">
         <is>
-          <t>የእርስዎ ቋንቋዎች መጀመሪያ፤ በእያንዳንዱ ውስጥ ረጅም የጠበቀው ይቀድማል። ከልክ በላይ የጠበቀ ማንኛውም ሰው የሚናገረው ምንም ይሁን ወደ ላይ ይወጣል።</t>
+          <t>የእርስዎ ቋንቋ አይደለም</t>
         </is>
       </c>
       <c r="E261" s="13" t="inlineStr">
         <is>
-          <t>Afaanonni keessan jalqaba, tokkoon tokkoon isaanii keessatti kan yeroo dheeraa eege dursa. Namni baay'ee eege afaan kamiyyuu haa dubbatu gara oliitti deema.</t>
+          <t>afaan keessanii miti</t>
         </is>
       </c>
       <c r="F261" s="12" t="inlineStr">
         <is>
-          <t>ቋንቋታትኩም ቅድም፣ ኣብ ነፍስ ወከፍ እቲ ነዊሕ ዝጸንሐ ይቐድም። ካብ ንቡር ንላዕሊ ዝጸንሐ ዝኾነ ሰብ ዝዛረቦ ብዘየገድስ ናብ ላዕሊ ይመጽእ።</t>
+          <t>ናትኩም ቋንቋ ኣይኮነን</t>
         </is>
       </c>
       <c r="G261" s="13" t="inlineStr">
         <is>
-          <t>Luqadahaaga marka hore, kii ugu sugay dheeraa mid kasta gudahood. Qof kasta oo aad u sugay ayaa kor u kaca luqad kastoo uu ku hadloba.</t>
+          <t>ma aha luqaddaada</t>
         </is>
       </c>
       <c r="H261" s="13" t="inlineStr">
         <is>
-          <t>Lugha zako kwanza, aliyesubiri kwa muda mrefu zaidi ndani ya kila moja. Yeyote anayesubiri kwa muda mrefu sana anapanda juu bila kujali anazungumza lugha gani.</t>
+          <t>si lugha yako</t>
         </is>
       </c>
       <c r="I261" s="14" t="inlineStr"/>
@@ -17468,7 +17468,7 @@
     <row r="262" ht="44" customHeight="1">
       <c r="A262" s="11" t="inlineStr">
         <is>
-          <t>my_desks</t>
+          <t>languages_first_note</t>
         </is>
       </c>
       <c r="B262" s="11" t="inlineStr">
@@ -17478,32 +17478,32 @@
       </c>
       <c r="C262" s="11" t="inlineStr">
         <is>
-          <t>I can handle these desks:</t>
+          <t>Your languages first, longest wait within each. Anyone waiting too long moves to the top whatever they speak.</t>
         </is>
       </c>
       <c r="D262" s="12" t="inlineStr">
         <is>
-          <t>እነዚህን ዴስኮች ማስተናገድ እችላለሁ፦</t>
+          <t>የእርስዎ ቋንቋዎች መጀመሪያ፤ በእያንዳንዱ ውስጥ ረጅም የጠበቀው ይቀድማል። ከልክ በላይ የጠበቀ ማንኛውም ሰው የሚናገረው ምንም ይሁን ወደ ላይ ይወጣል።</t>
         </is>
       </c>
       <c r="E262" s="13" t="inlineStr">
         <is>
-          <t>Deeskiiwwan kanneen keessummeessuu nan danda'a:</t>
+          <t>Afaanonni keessan jalqaba, tokkoon tokkoon isaanii keessatti kan yeroo dheeraa eege dursa. Namni baay'ee eege afaan kamiyyuu haa dubbatu gara oliitti deema.</t>
         </is>
       </c>
       <c r="F262" s="12" t="inlineStr">
         <is>
-          <t>ነዞም ዴስክታት ከተኣናግድ እኽእል፦</t>
+          <t>ቋንቋታትኩም ቅድም፣ ኣብ ነፍስ ወከፍ እቲ ነዊሕ ዝጸንሐ ይቐድም። ካብ ንቡር ንላዕሊ ዝጸንሐ ዝኾነ ሰብ ዝዛረቦ ብዘየገድስ ናብ ላዕሊ ይመጽእ።</t>
         </is>
       </c>
       <c r="G262" s="13" t="inlineStr">
         <is>
-          <t>Waxaan qaban karaa miisaskan:</t>
+          <t>Luqadahaaga marka hore, kii ugu sugay dheeraa mid kasta gudahood. Qof kasta oo aad u sugay ayaa kor u kaca luqad kastoo uu ku hadloba.</t>
         </is>
       </c>
       <c r="H262" s="13" t="inlineStr">
         <is>
-          <t>Ninaweza kushughulikia madawati haya:</t>
+          <t>Lugha zako kwanza, aliyesubiri kwa muda mrefu zaidi ndani ya kila moja. Yeyote anayesubiri kwa muda mrefu sana anapanda juu bila kujali anazungumza lugha gani.</t>
         </is>
       </c>
       <c r="I262" s="14" t="inlineStr"/>
@@ -17511,7 +17511,7 @@
     <row r="263" ht="44" customHeight="1">
       <c r="A263" s="11" t="inlineStr">
         <is>
-          <t>desks_picked_note</t>
+          <t>my_desks</t>
         </is>
       </c>
       <c r="B263" s="11" t="inlineStr">
@@ -17521,32 +17521,32 @@
       </c>
       <c r="C263" s="11" t="inlineStr">
         <is>
-          <t>Questions about these desks reach you first. Everything else still reaches you — after a short wait, so nobody is stranded.</t>
+          <t>I can handle these desks:</t>
         </is>
       </c>
       <c r="D263" s="12" t="inlineStr">
         <is>
-          <t>ስለ እነዚህ ዴስኮች የሚነሱ ጥያቄዎች መጀመሪያ ወደ እርስዎ ይደርሳሉ። ሌላው ሁሉ አሁንም ይደርሳል — ከአጭር ጥበቃ በኋላ፤ ማንም አይቀርም።</t>
+          <t>እነዚህን ዴስኮች ማስተናገድ እችላለሁ፦</t>
         </is>
       </c>
       <c r="E263" s="13" t="inlineStr">
         <is>
-          <t>Gaaffiiwwan waa'ee deeskiiwwan kanaa jalqaba isin bira ga'u. Kaan hundinuu ammas isin bira ga'a — eegumsa gabaabaa booda, namni hafu hin jiru.</t>
+          <t>Deeskiiwwan kanneen keessummeessuu nan danda'a:</t>
         </is>
       </c>
       <c r="F263" s="12" t="inlineStr">
         <is>
-          <t>ብዛዕባ እዞም ዴስክታት ዝለዓሉ ሕቶታት ቅድም ናባኹም ይበጽሑ። ካልእ ኩሉ እውን ይበጽሕ — ድሕሪ ሓጺር ጽበት፣ ዋላ ሓደ ኣይተርፍን።</t>
+          <t>ነዞም ዴስክታት ከተኣናግድ እኽእል፦</t>
         </is>
       </c>
       <c r="G263" s="13" t="inlineStr">
         <is>
-          <t>Su'aalaha ku saabsan miisaskan ayaa marka hore kugu soo gaara. Wax kastoo kalena wuu ku soo gaaraa — sug gaaban ka dib, sidaas qofna ma harayo.</t>
+          <t>Waxaan qaban karaa miisaskan:</t>
         </is>
       </c>
       <c r="H263" s="13" t="inlineStr">
         <is>
-          <t>Maswali kuhusu madawati haya yanakufikia kwanza. Mengine yote bado yanakufikia — baada ya kusubiri kidogo, ili asibaki mtu bila msaada.</t>
+          <t>Ninaweza kushughulikia madawati haya:</t>
         </is>
       </c>
       <c r="I263" s="14" t="inlineStr"/>
@@ -17554,7 +17554,7 @@
     <row r="264" ht="44" customHeight="1">
       <c r="A264" s="11" t="inlineStr">
         <is>
-          <t>desks_none_note</t>
+          <t>desks_picked_note</t>
         </is>
       </c>
       <c r="B264" s="11" t="inlineStr">
@@ -17564,32 +17564,32 @@
       </c>
       <c r="C264" s="11" t="inlineStr">
         <is>
-          <t>Nothing selected, so desk topics do not change your queue order.</t>
+          <t>Questions about these desks reach you first. Everything else still reaches you — after a short wait, so nobody is stranded.</t>
         </is>
       </c>
       <c r="D264" s="12" t="inlineStr">
         <is>
-          <t>ምንም አልተመረጠም፤ ስለዚህ የዴስክ ርዕሶች የወረፋዎን ቅደም ተከተል አይለውጡም።</t>
+          <t>ስለ እነዚህ ዴስኮች የሚነሱ ጥያቄዎች መጀመሪያ ወደ እርስዎ ይደርሳሉ። ሌላው ሁሉ አሁንም ይደርሳል — ከአጭር ጥበቃ በኋላ፤ ማንም አይቀርም።</t>
         </is>
       </c>
       <c r="E264" s="13" t="inlineStr">
         <is>
-          <t>Wanti filatame hin jiru, kanaafuu mata-dureewwan deeskii tartiiba sarara keessanii hin jijjiiran.</t>
+          <t>Gaaffiiwwan waa'ee deeskiiwwan kanaa jalqaba isin bira ga'u. Kaan hundinuu ammas isin bira ga'a — eegumsa gabaabaa booda, namni hafu hin jiru.</t>
         </is>
       </c>
       <c r="F264" s="12" t="inlineStr">
         <is>
-          <t>ዋላ ሓደ ኣይተመርጸን፣ ስለዚ ኣርእስታት ዴስክ ስርዓት ሰልፍኹም ኣይልውጡን።</t>
+          <t>ብዛዕባ እዞም ዴስክታት ዝለዓሉ ሕቶታት ቅድም ናባኹም ይበጽሑ። ካልእ ኩሉ እውን ይበጽሕ — ድሕሪ ሓጺር ጽበት፣ ዋላ ሓደ ኣይተርፍን።</t>
         </is>
       </c>
       <c r="G264" s="13" t="inlineStr">
         <is>
-          <t>Waxba lama dooran, sidaas darteed mowduucyada miisasku ma beddelaan kala horreynta safkaaga.</t>
+          <t>Su'aalaha ku saabsan miisaskan ayaa marka hore kugu soo gaara. Wax kastoo kalena wuu ku soo gaaraa — sug gaaban ka dib, sidaas qofna ma harayo.</t>
         </is>
       </c>
       <c r="H264" s="13" t="inlineStr">
         <is>
-          <t>Hakuna kilichochaguliwa, kwa hivyo mada za madawati hazibadilishi mpangilio wa foleni yako.</t>
+          <t>Maswali kuhusu madawati haya yanakufikia kwanza. Mengine yote bado yanakufikia — baada ya kusubiri kidogo, ili asibaki mtu bila msaada.</t>
         </is>
       </c>
       <c r="I264" s="14" t="inlineStr"/>
@@ -17597,7 +17597,7 @@
     <row r="265" ht="44" customHeight="1">
       <c r="A265" s="11" t="inlineStr">
         <is>
-          <t>desks_first_note</t>
+          <t>desks_none_note</t>
         </is>
       </c>
       <c r="B265" s="11" t="inlineStr">
@@ -17607,32 +17607,32 @@
       </c>
       <c r="C265" s="11" t="inlineStr">
         <is>
-          <t>Your desks first, longest wait within each. Anyone waiting too long moves to the top whatever they ask about.</t>
+          <t>Nothing selected, so desk topics do not change your queue order.</t>
         </is>
       </c>
       <c r="D265" s="12" t="inlineStr">
         <is>
-          <t>የእርስዎ ዴስኮች መጀመሪያ፤ በእያንዳንዱ ውስጥ ረጅም የጠበቀው ይቀድማል። ከልክ በላይ የጠበቀ ማንኛውም ሰው ስለ ምንም ይጠይቅ ወደ ላይ ይወጣል።</t>
+          <t>ምንም አልተመረጠም፤ ስለዚህ የዴስክ ርዕሶች የወረፋዎን ቅደም ተከተል አይለውጡም።</t>
         </is>
       </c>
       <c r="E265" s="13" t="inlineStr">
         <is>
-          <t>Deeskiiwwan keessan jalqaba, tokkoon tokkoon isaanii keessatti kan yeroo dheeraa eege dursa. Namni baay'ee eege waan kamiyyuu haa gaafatu gara oliitti deema.</t>
+          <t>Wanti filatame hin jiru, kanaafuu mata-dureewwan deeskii tartiiba sarara keessanii hin jijjiiran.</t>
         </is>
       </c>
       <c r="F265" s="12" t="inlineStr">
         <is>
-          <t>ዴስክታትኩም ቅድም፣ ኣብ ነፍስ ወከፍ እቲ ነዊሕ ዝጸንሐ ይቐድም። ካብ ንቡር ንላዕሊ ዝጸንሐ ዝኾነ ሰብ ብዛዕባ እንታይ ይሓትት ብዘየገድስ ናብ ላዕሊ ይመጽእ።</t>
+          <t>ዋላ ሓደ ኣይተመርጸን፣ ስለዚ ኣርእስታት ዴስክ ስርዓት ሰልፍኹም ኣይልውጡን።</t>
         </is>
       </c>
       <c r="G265" s="13" t="inlineStr">
         <is>
-          <t>Miisaskaaga marka hore, kii ugu sugay dheeraa mid kasta gudahood. Qof kasta oo aad u sugay ayaa kor u kaca wax kastoo uu weydiinayoba.</t>
+          <t>Waxba lama dooran, sidaas darteed mowduucyada miisasku ma beddelaan kala horreynta safkaaga.</t>
         </is>
       </c>
       <c r="H265" s="13" t="inlineStr">
         <is>
-          <t>Madawati yako kwanza, aliyesubiri kwa muda mrefu zaidi ndani ya kila moja. Yeyote anayesubiri kwa muda mrefu sana anapanda juu bila kujali anauliza nini.</t>
+          <t>Hakuna kilichochaguliwa, kwa hivyo mada za madawati hazibadilishi mpangilio wa foleni yako.</t>
         </is>
       </c>
       <c r="I265" s="14" t="inlineStr"/>
@@ -17640,7 +17640,7 @@
     <row r="266" ht="44" customHeight="1">
       <c r="A266" s="11" t="inlineStr">
         <is>
-          <t>routing_first_note</t>
+          <t>desks_first_note</t>
         </is>
       </c>
       <c r="B266" s="11" t="inlineStr">
@@ -17650,32 +17650,32 @@
       </c>
       <c r="C266" s="11" t="inlineStr">
         <is>
-          <t>Your languages first, your desks within them, longest wait within each. Anyone waiting too long moves to the top.</t>
+          <t>Your desks first, longest wait within each. Anyone waiting too long moves to the top whatever they ask about.</t>
         </is>
       </c>
       <c r="D266" s="12" t="inlineStr">
         <is>
-          <t>የእርስዎ ቋንቋዎች መጀመሪያ፣ በውስጣቸው የእርስዎ ዴስኮች፣ በእያንዳንዱ ውስጥ ረጅም የጠበቀው ይቀድማል። ከልክ በላይ የጠበቀ ወደ ላይ ይወጣል።</t>
+          <t>የእርስዎ ዴስኮች መጀመሪያ፤ በእያንዳንዱ ውስጥ ረጅም የጠበቀው ይቀድማል። ከልክ በላይ የጠበቀ ማንኛውም ሰው ስለ ምንም ይጠይቅ ወደ ላይ ይወጣል።</t>
         </is>
       </c>
       <c r="E266" s="13" t="inlineStr">
         <is>
-          <t>Afaanonni keessan jalqaba, isaan keessatti deeskiiwwan keessan, tokkoon tokkoon keessatti kan yeroo dheeraa eege dursa. Namni baay'ee eege gara oliitti deema.</t>
+          <t>Deeskiiwwan keessan jalqaba, tokkoon tokkoon isaanii keessatti kan yeroo dheeraa eege dursa. Namni baay'ee eege waan kamiyyuu haa gaafatu gara oliitti deema.</t>
         </is>
       </c>
       <c r="F266" s="12" t="inlineStr">
         <is>
-          <t>ቋንቋታትኩም ቅድም፣ ኣብ ውሽጦም ዴስክታትኩም፣ ኣብ ነፍስ ወከፍ እቲ ነዊሕ ዝጸንሐ ይቐድም። ካብ ንቡር ንላዕሊ ዝጸንሐ ናብ ላዕሊ ይመጽእ።</t>
+          <t>ዴስክታትኩም ቅድም፣ ኣብ ነፍስ ወከፍ እቲ ነዊሕ ዝጸንሐ ይቐድም። ካብ ንቡር ንላዕሊ ዝጸንሐ ዝኾነ ሰብ ብዛዕባ እንታይ ይሓትት ብዘየገድስ ናብ ላዕሊ ይመጽእ።</t>
         </is>
       </c>
       <c r="G266" s="13" t="inlineStr">
         <is>
-          <t>Luqadahaaga marka hore, miisaskaaga gudahood, kii ugu sugay dheeraa mid kasta gudahood. Qof aad u sugay ayaa kor u kaca.</t>
+          <t>Miisaskaaga marka hore, kii ugu sugay dheeraa mid kasta gudahood. Qof kasta oo aad u sugay ayaa kor u kaca wax kastoo uu weydiinayoba.</t>
         </is>
       </c>
       <c r="H266" s="13" t="inlineStr">
         <is>
-          <t>Lugha zako kwanza, madawati yako ndani yake, aliyesubiri kwa muda mrefu zaidi ndani ya kila moja. Anayesubiri kwa muda mrefu sana anapanda juu.</t>
+          <t>Madawati yako kwanza, aliyesubiri kwa muda mrefu zaidi ndani ya kila moja. Yeyote anayesubiri kwa muda mrefu sana anapanda juu bila kujali anauliza nini.</t>
         </is>
       </c>
       <c r="I266" s="14" t="inlineStr"/>
@@ -17683,7 +17683,7 @@
     <row r="267" ht="44" customHeight="1">
       <c r="A267" s="11" t="inlineStr">
         <is>
-          <t>not_your_desk</t>
+          <t>routing_first_note</t>
         </is>
       </c>
       <c r="B267" s="11" t="inlineStr">
@@ -17693,32 +17693,32 @@
       </c>
       <c r="C267" s="11" t="inlineStr">
         <is>
-          <t>outside your desks</t>
+          <t>Your languages first, your desks within them, longest wait within each. Anyone waiting too long moves to the top.</t>
         </is>
       </c>
       <c r="D267" s="12" t="inlineStr">
         <is>
-          <t>ከእርስዎ ዴስኮች ውጭ</t>
+          <t>የእርስዎ ቋንቋዎች መጀመሪያ፣ በውስጣቸው የእርስዎ ዴስኮች፣ በእያንዳንዱ ውስጥ ረጅም የጠበቀው ይቀድማል። ከልክ በላይ የጠበቀ ወደ ላይ ይወጣል።</t>
         </is>
       </c>
       <c r="E267" s="13" t="inlineStr">
         <is>
-          <t>deeskiiwwan keessanii ala</t>
+          <t>Afaanonni keessan jalqaba, isaan keessatti deeskiiwwan keessan, tokkoon tokkoon keessatti kan yeroo dheeraa eege dursa. Namni baay'ee eege gara oliitti deema.</t>
         </is>
       </c>
       <c r="F267" s="12" t="inlineStr">
         <is>
-          <t>ካብ ዴስክታትኩም ወጻኢ</t>
+          <t>ቋንቋታትኩም ቅድም፣ ኣብ ውሽጦም ዴስክታትኩም፣ ኣብ ነፍስ ወከፍ እቲ ነዊሕ ዝጸንሐ ይቐድም። ካብ ንቡር ንላዕሊ ዝጸንሐ ናብ ላዕሊ ይመጽእ።</t>
         </is>
       </c>
       <c r="G267" s="13" t="inlineStr">
         <is>
-          <t>ka baxsan miisaskaaga</t>
+          <t>Luqadahaaga marka hore, miisaskaaga gudahood, kii ugu sugay dheeraa mid kasta gudahood. Qof aad u sugay ayaa kor u kaca.</t>
         </is>
       </c>
       <c r="H267" s="13" t="inlineStr">
         <is>
-          <t>nje ya madawati yako</t>
+          <t>Lugha zako kwanza, madawati yako ndani yake, aliyesubiri kwa muda mrefu zaidi ndani ya kila moja. Anayesubiri kwa muda mrefu sana anapanda juu.</t>
         </is>
       </c>
       <c r="I267" s="14" t="inlineStr"/>
@@ -17726,7 +17726,7 @@
     <row r="268" ht="44" customHeight="1">
       <c r="A268" s="11" t="inlineStr">
         <is>
-          <t>desks_updated</t>
+          <t>not_your_desk</t>
         </is>
       </c>
       <c r="B268" s="11" t="inlineStr">
@@ -17736,32 +17736,32 @@
       </c>
       <c r="C268" s="11" t="inlineStr">
         <is>
-          <t>Desks updated</t>
+          <t>outside your desks</t>
         </is>
       </c>
       <c r="D268" s="12" t="inlineStr">
         <is>
-          <t>ዴስኮች ተዘምነዋል</t>
+          <t>ከእርስዎ ዴስኮች ውጭ</t>
         </is>
       </c>
       <c r="E268" s="13" t="inlineStr">
         <is>
-          <t>Deeskiiwwan haaromfaman</t>
+          <t>deeskiiwwan keessanii ala</t>
         </is>
       </c>
       <c r="F268" s="12" t="inlineStr">
         <is>
-          <t>ዴስክታት ተሓዲሶም</t>
+          <t>ካብ ዴስክታትኩም ወጻኢ</t>
         </is>
       </c>
       <c r="G268" s="13" t="inlineStr">
         <is>
-          <t>Miisaska waa la cusbooneysiiyay</t>
+          <t>ka baxsan miisaskaaga</t>
         </is>
       </c>
       <c r="H268" s="13" t="inlineStr">
         <is>
-          <t>Madawati yamesasishwa</t>
+          <t>nje ya madawati yako</t>
         </is>
       </c>
       <c r="I268" s="14" t="inlineStr"/>
@@ -17769,7 +17769,7 @@
     <row r="269" ht="44" customHeight="1">
       <c r="A269" s="11" t="inlineStr">
         <is>
-          <t>coverage</t>
+          <t>desks_updated</t>
         </is>
       </c>
       <c r="B269" s="11" t="inlineStr">
@@ -17779,32 +17779,32 @@
       </c>
       <c r="C269" s="11" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>Desks updated</t>
         </is>
       </c>
       <c r="D269" s="12" t="inlineStr">
         <is>
-          <t>ሽፋን</t>
+          <t>ዴስኮች ተዘምነዋል</t>
         </is>
       </c>
       <c r="E269" s="13" t="inlineStr">
         <is>
-          <t>Haguuggii</t>
+          <t>Deeskiiwwan haaromfaman</t>
         </is>
       </c>
       <c r="F269" s="12" t="inlineStr">
         <is>
-          <t>ሽፋን</t>
+          <t>ዴስክታት ተሓዲሶም</t>
         </is>
       </c>
       <c r="G269" s="13" t="inlineStr">
         <is>
-          <t>Daboolid</t>
+          <t>Miisaska waa la cusbooneysiiyay</t>
         </is>
       </c>
       <c r="H269" s="13" t="inlineStr">
         <is>
-          <t>Uwezo</t>
+          <t>Madawati yamesasishwa</t>
         </is>
       </c>
       <c r="I269" s="14" t="inlineStr"/>
@@ -17812,7 +17812,7 @@
     <row r="270" ht="44" customHeight="1">
       <c r="A270" s="11" t="inlineStr">
         <is>
-          <t>coverage_everything</t>
+          <t>coverage</t>
         </is>
       </c>
       <c r="B270" s="11" t="inlineStr">
@@ -17822,32 +17822,32 @@
       </c>
       <c r="C270" s="11" t="inlineStr">
         <is>
-          <t>everything — nothing declared</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="D270" s="12" t="inlineStr">
         <is>
-          <t>ሁሉም — ምንም አልተገለጸም</t>
+          <t>ሽፋን</t>
         </is>
       </c>
       <c r="E270" s="13" t="inlineStr">
         <is>
-          <t>hunda — wanti labsame hin jiru</t>
+          <t>Haguuggii</t>
         </is>
       </c>
       <c r="F270" s="12" t="inlineStr">
         <is>
-          <t>ኩሉ — ዋላ ሓደ ኣይተገልጸን</t>
+          <t>ሽፋን</t>
         </is>
       </c>
       <c r="G270" s="13" t="inlineStr">
         <is>
-          <t>wax walba — waxba lama sheegin</t>
+          <t>Daboolid</t>
         </is>
       </c>
       <c r="H270" s="13" t="inlineStr">
         <is>
-          <t>yote — hakuna kilichotangazwa</t>
+          <t>Uwezo</t>
         </is>
       </c>
       <c r="I270" s="14" t="inlineStr"/>
@@ -17855,7 +17855,7 @@
     <row r="271" ht="44" customHeight="1">
       <c r="A271" s="11" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>coverage_everything</t>
         </is>
       </c>
       <c r="B271" s="11" t="inlineStr">
@@ -17865,32 +17865,32 @@
       </c>
       <c r="C271" s="11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>everything — nothing declared</t>
         </is>
       </c>
       <c r="D271" s="12" t="inlineStr">
         <is>
-          <t>በሂደት ላይ</t>
+          <t>ሁሉም — ምንም አልተገለጸም</t>
         </is>
       </c>
       <c r="E271" s="13" t="inlineStr">
         <is>
-          <t>Adeemsa irra</t>
+          <t>hunda — wanti labsame hin jiru</t>
         </is>
       </c>
       <c r="F271" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መስርሕ</t>
+          <t>ኩሉ — ዋላ ሓደ ኣይተገልጸን</t>
         </is>
       </c>
       <c r="G271" s="13" t="inlineStr">
         <is>
-          <t>Socda</t>
+          <t>wax walba — waxba lama sheegin</t>
         </is>
       </c>
       <c r="H271" s="13" t="inlineStr">
         <is>
-          <t>Inaendelea</t>
+          <t>yote — hakuna kilichotangazwa</t>
         </is>
       </c>
       <c r="I271" s="14" t="inlineStr"/>
@@ -17898,7 +17898,7 @@
     <row r="272" ht="44" customHeight="1">
       <c r="A272" s="11" t="inlineStr">
         <is>
-          <t>no_session_in_progress</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="B272" s="11" t="inlineStr">
@@ -17908,32 +17908,32 @@
       </c>
       <c r="C272" s="11" t="inlineStr">
         <is>
-          <t>No session in progress.</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="D272" s="12" t="inlineStr">
         <is>
-          <t>በሂደት ላይ ያለ ክፍለ-ጊዜ የለም።</t>
+          <t>በሂደት ላይ</t>
         </is>
       </c>
       <c r="E272" s="13" t="inlineStr">
         <is>
-          <t>Sessionii adeemsa irra jiru hin jiru.</t>
+          <t>Adeemsa irra</t>
         </is>
       </c>
       <c r="F272" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መስርሕ ዘሎ ክፍለ-ግዜ የለን።</t>
+          <t>ኣብ መስርሕ</t>
         </is>
       </c>
       <c r="G272" s="13" t="inlineStr">
         <is>
-          <t>Ma jiro kalfadhi socda.</t>
+          <t>Socda</t>
         </is>
       </c>
       <c r="H272" s="13" t="inlineStr">
         <is>
-          <t>Hakuna kikao kinachoendelea.</t>
+          <t>Inaendelea</t>
         </is>
       </c>
       <c r="I272" s="14" t="inlineStr"/>
@@ -17941,7 +17941,7 @@
     <row r="273" ht="44" customHeight="1">
       <c r="A273" s="11" t="inlineStr">
         <is>
-          <t>wait_suffix</t>
+          <t>no_session_in_progress</t>
         </is>
       </c>
       <c r="B273" s="11" t="inlineStr">
@@ -17951,32 +17951,32 @@
       </c>
       <c r="C273" s="11" t="inlineStr">
         <is>
-          <t>wait</t>
+          <t>No session in progress.</t>
         </is>
       </c>
       <c r="D273" s="12" t="inlineStr">
         <is>
-          <t>ጥበቃ</t>
+          <t>በሂደት ላይ ያለ ክፍለ-ጊዜ የለም።</t>
         </is>
       </c>
       <c r="E273" s="13" t="inlineStr">
         <is>
-          <t>eegumsa</t>
+          <t>Sessionii adeemsa irra jiru hin jiru.</t>
         </is>
       </c>
       <c r="F273" s="12" t="inlineStr">
         <is>
-          <t>ጽበት</t>
+          <t>ኣብ መስርሕ ዘሎ ክፍለ-ግዜ የለን።</t>
         </is>
       </c>
       <c r="G273" s="13" t="inlineStr">
         <is>
-          <t>sug</t>
+          <t>Ma jiro kalfadhi socda.</t>
         </is>
       </c>
       <c r="H273" s="13" t="inlineStr">
         <is>
-          <t>kusubiri</t>
+          <t>Hakuna kikao kinachoendelea.</t>
         </is>
       </c>
       <c r="I273" s="14" t="inlineStr"/>
@@ -17984,7 +17984,7 @@
     <row r="274" ht="44" customHeight="1">
       <c r="A274" s="11" t="inlineStr">
         <is>
-          <t>what_session_covers</t>
+          <t>wait_suffix</t>
         </is>
       </c>
       <c r="B274" s="11" t="inlineStr">
@@ -17994,32 +17994,32 @@
       </c>
       <c r="C274" s="11" t="inlineStr">
         <is>
-          <t>What a session covers</t>
+          <t>wait</t>
         </is>
       </c>
       <c r="D274" s="12" t="inlineStr">
         <is>
-          <t>አንድ ክፍለ-ጊዜ ምን ይሸፍናል</t>
+          <t>ጥበቃ</t>
         </is>
       </c>
       <c r="E274" s="13" t="inlineStr">
         <is>
-          <t>Sessioniin maal haguuga</t>
+          <t>eegumsa</t>
         </is>
       </c>
       <c r="F274" s="12" t="inlineStr">
         <is>
-          <t>ሓደ ክፍለ-ግዜ እንታይ ይሽፍን</t>
+          <t>ጽበት</t>
         </is>
       </c>
       <c r="G274" s="13" t="inlineStr">
         <is>
-          <t>Waxa kalfadhigu daboolo</t>
+          <t>sug</t>
         </is>
       </c>
       <c r="H274" s="13" t="inlineStr">
         <is>
-          <t>Kikao Kinajumuisha Nini</t>
+          <t>kusubiri</t>
         </is>
       </c>
       <c r="I274" s="14" t="inlineStr"/>
@@ -18027,7 +18027,7 @@
     <row r="275" ht="44" customHeight="1">
       <c r="A275" s="11" t="inlineStr">
         <is>
-          <t>session_scope_body</t>
+          <t>what_session_covers</t>
         </is>
       </c>
       <c r="B275" s="11" t="inlineStr">
@@ -18037,32 +18037,32 @@
       </c>
       <c r="C275" s="11" t="inlineStr">
         <is>
-          <t>Before someone is identified: general questions about products, eligibility and how to apply. Once you have checked their Fayda ID against the account and asked something only the account holder could answer: their own application, documents and disputes.</t>
+          <t>What a session covers</t>
         </is>
       </c>
       <c r="D275" s="12" t="inlineStr">
         <is>
-          <t>አንድ ሰው ከመለየቱ በፊት፦ ስለ ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል አጠቃላይ ጥያቄዎች። የፋይዳ መታወቂያቸውን ከሂሳቡ ጋር አመሳክረው የሂሳቡ ባለቤት ብቻ ሊመልሰው የሚችለውን ከጠየቁ በኋላ፦ የራሳቸው ማመልከቻ፣ ሰነዶችና ቅሬታዎች።</t>
+          <t>አንድ ክፍለ-ጊዜ ምን ይሸፍናል</t>
         </is>
       </c>
       <c r="E275" s="13" t="inlineStr">
         <is>
-          <t>Namni tokko utuu hin beekamin dura: gaaffii waliigalaa waa'ee oomishaalee, ulaagaa fi akkaataa itti iyyatan. Erga waraqaa eenyummaa Fayda isaanii herrega waliin madaalchiftanii waan abbaan herregaa qofti deebisuu danda'u gaafattanii booda: iyyannoo, sanadoota fi komii isaanii.</t>
+          <t>Sessioniin maal haguuga</t>
         </is>
       </c>
       <c r="F275" s="12" t="inlineStr">
         <is>
-          <t>ሓደ ሰብ ቅድሚ ምልላዩ፦ ብዛዕባ ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን ሓፈሻዊ ሕቶታት። መንነት ፋይዳኦም ምስ ሕሳብ ኣረጋጊጽኩም እቲ ወናኒ ሕሳብ ጥራይ ክምልሶ ዝኽእል ምስ ሓተትኩም፦ ናቶም ምልክታ፣ ሰነዳትን ጥርዓናትን።</t>
+          <t>ሓደ ክፍለ-ግዜ እንታይ ይሽፍን</t>
         </is>
       </c>
       <c r="G275" s="13" t="inlineStr">
         <is>
-          <t>Ka hor inta aan qofka la aqoonsan: su'aalo guud oo ku saabsan alaabta, u-qalmitaanka iyo sida loo codsado. Marka aad hubiso aqoonsigooda Fayda ee xisaabta oo aad weydiiso wax uu kaliya milkiilaha xisaabtu ka jawaabi karo: codsigooda, dukumiintiyada iyo cabashooyinka.</t>
+          <t>Waxa kalfadhigu daboolo</t>
         </is>
       </c>
       <c r="H275" s="13" t="inlineStr">
         <is>
-          <t>Kabla mtu hajatambuliwa: maswali ya jumla kuhusu bidhaa, sifa za kustahiki na jinsi ya kuomba. Baada ya kukagua Kitambulisho chao cha Fayda dhidi ya akaunti na kuuliza kitu ambacho mmiliki wa akaunti pekee angeweza kujibu: maombi yao wenyewe, nyaraka na migogoro.</t>
+          <t>Kikao Kinajumuisha Nini</t>
         </is>
       </c>
       <c r="I275" s="14" t="inlineStr"/>
@@ -18070,7 +18070,7 @@
     <row r="276" ht="44" customHeight="1">
       <c r="A276" s="11" t="inlineStr">
         <is>
-          <t>never_money_movement</t>
+          <t>session_scope_body</t>
         </is>
       </c>
       <c r="B276" s="11" t="inlineStr">
@@ -18080,32 +18080,32 @@
       </c>
       <c r="C276" s="11" t="inlineStr">
         <is>
-          <t>Never, at any point and for anyone: deposits, withdrawals or transfers. Those do not happen on a call.</t>
+          <t>Before someone is identified: general questions about products, eligibility and how to apply. Once you have checked their Fayda ID against the account and asked something only the account holder could answer: their own application, documents and disputes.</t>
         </is>
       </c>
       <c r="D276" s="12" t="inlineStr">
         <is>
-          <t>በፍጹም፣ በማንኛውም ጊዜና ለማንም፦ ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም። እነዚያ በጥሪ ላይ አይፈጸሙም።</t>
+          <t>አንድ ሰው ከመለየቱ በፊት፦ ስለ ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል አጠቃላይ ጥያቄዎች። የፋይዳ መታወቂያቸውን ከሂሳቡ ጋር አመሳክረው የሂሳቡ ባለቤት ብቻ ሊመልሰው የሚችለውን ከጠየቁ በኋላ፦ የራሳቸው ማመልከቻ፣ ሰነዶችና ቅሬታዎች።</t>
         </is>
       </c>
       <c r="E276" s="13" t="inlineStr">
         <is>
-          <t>Gonkumaa, yeroo kamiyyuu fi eenyuufiyyuu: kuusaa, baasii yookiin dabarsa hin jiru. Isaan sun bilbila irratti hin raawwataman.</t>
+          <t>Namni tokko utuu hin beekamin dura: gaaffii waliigalaa waa'ee oomishaalee, ulaagaa fi akkaataa itti iyyatan. Erga waraqaa eenyummaa Fayda isaanii herrega waliin madaalchiftanii waan abbaan herregaa qofti deebisuu danda'u gaafattanii booda: iyyannoo, sanadoota fi komii isaanii.</t>
         </is>
       </c>
       <c r="F276" s="12" t="inlineStr">
         <is>
-          <t>ፈጺሙ፣ ኣብ ዝኾነ እዋንን ንዝኾነ ሰብን፦ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን። እዚኣቶም ኣብ ጻውዒት ኣይፍጸሙን።</t>
+          <t>ሓደ ሰብ ቅድሚ ምልላዩ፦ ብዛዕባ ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን ሓፈሻዊ ሕቶታት። መንነት ፋይዳኦም ምስ ሕሳብ ኣረጋጊጽኩም እቲ ወናኒ ሕሳብ ጥራይ ክምልሶ ዝኽእል ምስ ሓተትኩም፦ ናቶም ምልክታ፣ ሰነዳትን ጥርዓናትን።</t>
         </is>
       </c>
       <c r="G276" s="13" t="inlineStr">
         <is>
-          <t>Weligaa, wakhti kasta iyo qof kasta: dhigasho, qaadis ama wareejin ma jirto. Kuwaas wicitaan laguma sameeyo.</t>
+          <t>Ka hor inta aan qofka la aqoonsan: su'aalo guud oo ku saabsan alaabta, u-qalmitaanka iyo sida loo codsado. Marka aad hubiso aqoonsigooda Fayda ee xisaabta oo aad weydiiso wax uu kaliya milkiilaha xisaabtu ka jawaabi karo: codsigooda, dukumiintiyada iyo cabashooyinka.</t>
         </is>
       </c>
       <c r="H276" s="13" t="inlineStr">
         <is>
-          <t>Kamwe, wakati wowote na kwa yeyote: amana, uondoaji au uhamishaji. Hizo hazifanyiki kwenye simu.</t>
+          <t>Kabla mtu hajatambuliwa: maswali ya jumla kuhusu bidhaa, sifa za kustahiki na jinsi ya kuomba. Baada ya kukagua Kitambulisho chao cha Fayda dhidi ya akaunti na kuuliza kitu ambacho mmiliki wa akaunti pekee angeweza kujibu: maombi yao wenyewe, nyaraka na migogoro.</t>
         </is>
       </c>
       <c r="I276" s="14" t="inlineStr"/>
@@ -18113,7 +18113,7 @@
     <row r="277" ht="44" customHeight="1">
       <c r="A277" s="11" t="inlineStr">
         <is>
-          <t>open_escalation_queue</t>
+          <t>never_money_movement</t>
         </is>
       </c>
       <c r="B277" s="11" t="inlineStr">
@@ -18123,32 +18123,32 @@
       </c>
       <c r="C277" s="11" t="inlineStr">
         <is>
-          <t>Open the escalation queue</t>
+          <t>Never, at any point and for anyone: deposits, withdrawals or transfers. Those do not happen on a call.</t>
         </is>
       </c>
       <c r="D277" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ወረፋውን ክፈት</t>
+          <t>በፍጹም፣ በማንኛውም ጊዜና ለማንም፦ ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም። እነዚያ በጥሪ ላይ አይፈጸሙም።</t>
         </is>
       </c>
       <c r="E277" s="13" t="inlineStr">
         <is>
-          <t>Sararaa dabarsaa banaa</t>
+          <t>Gonkumaa, yeroo kamiyyuu fi eenyuufiyyuu: kuusaa, baasii yookiin dabarsa hin jiru. Isaan sun bilbila irratti hin raawwataman.</t>
         </is>
       </c>
       <c r="F277" s="12" t="inlineStr">
         <is>
-          <t>ሪጋ ምትሕልላፍ ክፈት</t>
+          <t>ፈጺሙ፣ ኣብ ዝኾነ እዋንን ንዝኾነ ሰብን፦ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን። እዚኣቶም ኣብ ጻውዒት ኣይፍጸሙን።</t>
         </is>
       </c>
       <c r="G277" s="13" t="inlineStr">
         <is>
-          <t>Fur safka gudbinta</t>
+          <t>Weligaa, wakhti kasta iyo qof kasta: dhigasho, qaadis ama wareejin ma jirto. Kuwaas wicitaan laguma sameeyo.</t>
         </is>
       </c>
       <c r="H277" s="13" t="inlineStr">
         <is>
-          <t>Fungua Foleni ya Masuala Yaliyoelekezwa</t>
+          <t>Kamwe, wakati wowote na kwa yeyote: amana, uondoaji au uhamishaji. Hizo hazifanyiki kwenye simu.</t>
         </is>
       </c>
       <c r="I277" s="14" t="inlineStr"/>
@@ -18156,7 +18156,7 @@
     <row r="278" ht="44" customHeight="1">
       <c r="A278" s="11" t="inlineStr">
         <is>
-          <t>open_live_queue</t>
+          <t>open_escalation_queue</t>
         </is>
       </c>
       <c r="B278" s="11" t="inlineStr">
@@ -18166,32 +18166,32 @@
       </c>
       <c r="C278" s="11" t="inlineStr">
         <is>
-          <t>Open the live call queue</t>
+          <t>Open the escalation queue</t>
         </is>
       </c>
       <c r="D278" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታ የጥሪ ወረፋውን ክፈት</t>
+          <t>የማሸጋገሪያ ወረፋውን ክፈት</t>
         </is>
       </c>
       <c r="E278" s="13" t="inlineStr">
         <is>
-          <t>Sarara bilbilaa kallattii banaa</t>
+          <t>Sararaa dabarsaa banaa</t>
         </is>
       </c>
       <c r="F278" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታዊ ናይ ጻውዒት ሰልፊ ክፈት</t>
+          <t>ሪጋ ምትሕልላፍ ክፈት</t>
         </is>
       </c>
       <c r="G278" s="13" t="inlineStr">
         <is>
-          <t>Fur safka wicitaanka tooska ah</t>
+          <t>Fur safka gudbinta</t>
         </is>
       </c>
       <c r="H278" s="13" t="inlineStr">
         <is>
-          <t>Fungua foleni ya simu za moja kwa moja</t>
+          <t>Fungua Foleni ya Masuala Yaliyoelekezwa</t>
         </is>
       </c>
       <c r="I278" s="14" t="inlineStr"/>
@@ -18199,7 +18199,7 @@
     <row r="279" ht="44" customHeight="1">
       <c r="A279" s="11" t="inlineStr">
         <is>
-          <t>live_waiting_one</t>
+          <t>open_live_queue</t>
         </is>
       </c>
       <c r="B279" s="11" t="inlineStr">
@@ -18209,32 +18209,32 @@
       </c>
       <c r="C279" s="11" t="inlineStr">
         <is>
-          <t>{n} customer waiting for a live call</t>
+          <t>Open the live call queue</t>
         </is>
       </c>
       <c r="D279" s="12" t="inlineStr">
         <is>
-          <t>{n} ደንበኛ ቀጥታ ጥሪ በመጠበቅ ላይ ነው</t>
+          <t>ቀጥታ የጥሪ ወረፋውን ክፈት</t>
         </is>
       </c>
       <c r="E279" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan {n} bilbila kallattii eegaa jira</t>
+          <t>Sarara bilbilaa kallattii banaa</t>
         </is>
       </c>
       <c r="F279" s="12" t="inlineStr">
         <is>
-          <t>{n} ዓሚል ቀጥታዊ ጻውዒት ይጽበ ኣሎ</t>
+          <t>ቀጥታዊ ናይ ጻውዒት ሰልፊ ክፈት</t>
         </is>
       </c>
       <c r="G279" s="13" t="inlineStr">
         <is>
-          <t>{n} macmiil ayaa sugaya wicitaan toos ah</t>
+          <t>Fur safka wicitaanka tooska ah</t>
         </is>
       </c>
       <c r="H279" s="13" t="inlineStr">
         <is>
-          <t>Mteja {n} anasubiri simu ya moja kwa moja</t>
+          <t>Fungua foleni ya simu za moja kwa moja</t>
         </is>
       </c>
       <c r="I279" s="14" t="inlineStr"/>
@@ -18242,7 +18242,7 @@
     <row r="280" ht="44" customHeight="1">
       <c r="A280" s="11" t="inlineStr">
         <is>
-          <t>live_waiting_many</t>
+          <t>live_waiting_one</t>
         </is>
       </c>
       <c r="B280" s="11" t="inlineStr">
@@ -18252,32 +18252,32 @@
       </c>
       <c r="C280" s="11" t="inlineStr">
         <is>
-          <t>{n} customers waiting for a live call</t>
+          <t>{n} customer waiting for a live call</t>
         </is>
       </c>
       <c r="D280" s="12" t="inlineStr">
         <is>
-          <t>{n} ደንበኞች ቀጥታ ጥሪ በመጠበቅ ላይ ናቸው</t>
+          <t>{n} ደንበኛ ቀጥታ ጥሪ በመጠበቅ ላይ ነው</t>
         </is>
       </c>
       <c r="E280" s="13" t="inlineStr">
         <is>
-          <t>Maamiltoonni {n} bilbila kallattii eegaa jiru</t>
+          <t>Maamilaan {n} bilbila kallattii eegaa jira</t>
         </is>
       </c>
       <c r="F280" s="12" t="inlineStr">
         <is>
-          <t>{n} ዓማዊል ቀጥታዊ ጻውዒት ይጽበዩ ኣለዉ</t>
+          <t>{n} ዓሚል ቀጥታዊ ጻውዒት ይጽበ ኣሎ</t>
         </is>
       </c>
       <c r="G280" s="13" t="inlineStr">
         <is>
-          <t>{n} macaamiil ayaa sugaya wicitaan toos ah</t>
+          <t>{n} macmiil ayaa sugaya wicitaan toos ah</t>
         </is>
       </c>
       <c r="H280" s="13" t="inlineStr">
         <is>
-          <t>Wateja {n} wanasubiri simu ya moja kwa moja</t>
+          <t>Mteja {n} anasubiri simu ya moja kwa moja</t>
         </is>
       </c>
       <c r="I280" s="14" t="inlineStr"/>
@@ -18285,7 +18285,7 @@
     <row r="281" ht="44" customHeight="1">
       <c r="A281" s="11" t="inlineStr">
         <is>
-          <t>switch_dark_light</t>
+          <t>live_waiting_many</t>
         </is>
       </c>
       <c r="B281" s="11" t="inlineStr">
@@ -18295,32 +18295,32 @@
       </c>
       <c r="C281" s="11" t="inlineStr">
         <is>
-          <t>Switch between dark and light</t>
+          <t>{n} customers waiting for a live call</t>
         </is>
       </c>
       <c r="D281" s="12" t="inlineStr">
         <is>
-          <t>በጨለማና በብርሃን መካከል ቀይር</t>
+          <t>{n} ደንበኞች ቀጥታ ጥሪ በመጠበቅ ላይ ናቸው</t>
         </is>
       </c>
       <c r="E281" s="13" t="inlineStr">
         <is>
-          <t>Dukkanaa fi ifa gidduu jijjiiri</t>
+          <t>Maamiltoonni {n} bilbila kallattii eegaa jiru</t>
         </is>
       </c>
       <c r="F281" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መንጎ ጸላምን ብርሃንን ቀይር</t>
+          <t>{n} ዓማዊል ቀጥታዊ ጻውዒት ይጽበዩ ኣለዉ</t>
         </is>
       </c>
       <c r="G281" s="13" t="inlineStr">
         <is>
-          <t>U beddel mugdiga iyo iftiinka</t>
+          <t>{n} macaamiil ayaa sugaya wicitaan toos ah</t>
         </is>
       </c>
       <c r="H281" s="13" t="inlineStr">
         <is>
-          <t>Badilisha Kati ya Giza na Mwanga</t>
+          <t>Wateja {n} wanasubiri simu ya moja kwa moja</t>
         </is>
       </c>
       <c r="I281" s="14" t="inlineStr"/>
@@ -18328,7 +18328,7 @@
     <row r="282" ht="44" customHeight="1">
       <c r="A282" s="11" t="inlineStr">
         <is>
-          <t>live_session</t>
+          <t>switch_dark_light</t>
         </is>
       </c>
       <c r="B282" s="11" t="inlineStr">
@@ -18338,32 +18338,32 @@
       </c>
       <c r="C282" s="11" t="inlineStr">
         <is>
-          <t>Live session</t>
+          <t>Switch between dark and light</t>
         </is>
       </c>
       <c r="D282" s="12" t="inlineStr">
         <is>
-          <t>የቀጥታ ክፍለ-ጊዜ</t>
+          <t>በጨለማና በብርሃን መካከል ቀይር</t>
         </is>
       </c>
       <c r="E282" s="13" t="inlineStr">
         <is>
-          <t>Session kallattii</t>
+          <t>Dukkanaa fi ifa gidduu jijjiiri</t>
         </is>
       </c>
       <c r="F282" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታ ክፍለ-ግዜ</t>
+          <t>ኣብ መንጎ ጸላምን ብርሃንን ቀይር</t>
         </is>
       </c>
       <c r="G282" s="13" t="inlineStr">
         <is>
-          <t>Kalfadhi toos ah</t>
+          <t>U beddel mugdiga iyo iftiinka</t>
         </is>
       </c>
       <c r="H282" s="13" t="inlineStr">
         <is>
-          <t>Kikao cha Moja kwa Moja</t>
+          <t>Badilisha Kati ya Giza na Mwanga</t>
         </is>
       </c>
       <c r="I282" s="14" t="inlineStr"/>
@@ -18371,7 +18371,7 @@
     <row r="283" ht="44" customHeight="1">
       <c r="A283" s="11" t="inlineStr">
         <is>
-          <t>customer_left_call</t>
+          <t>live_session</t>
         </is>
       </c>
       <c r="B283" s="11" t="inlineStr">
@@ -18381,32 +18381,32 @@
       </c>
       <c r="C283" s="11" t="inlineStr">
         <is>
-          <t>The customer has left the call.</t>
+          <t>Live session</t>
         </is>
       </c>
       <c r="D283" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛው ጥሪውን ለቅቋል።</t>
+          <t>የቀጥታ ክፍለ-ጊዜ</t>
         </is>
       </c>
       <c r="E283" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan bilbila irraa ba'eera.</t>
+          <t>Session kallattii</t>
         </is>
       </c>
       <c r="F283" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዓሚል ካብቲ ጻውዒት ወጺኡ።</t>
+          <t>ቀጥታ ክፍለ-ግዜ</t>
         </is>
       </c>
       <c r="G283" s="13" t="inlineStr">
         <is>
-          <t>Macmiilku wicitaanka wuu ka baxay.</t>
+          <t>Kalfadhi toos ah</t>
         </is>
       </c>
       <c r="H283" s="13" t="inlineStr">
         <is>
-          <t>Mteja ameondoka kwenye simu.</t>
+          <t>Kikao cha Moja kwa Moja</t>
         </is>
       </c>
       <c r="I283" s="14" t="inlineStr"/>
@@ -18414,7 +18414,7 @@
     <row r="284" ht="44" customHeight="1">
       <c r="A284" s="11" t="inlineStr">
         <is>
-          <t>waiting_for_customer</t>
+          <t>customer_left_call</t>
         </is>
       </c>
       <c r="B284" s="11" t="inlineStr">
@@ -18424,32 +18424,32 @@
       </c>
       <c r="C284" s="11" t="inlineStr">
         <is>
-          <t>Waiting for the customer…</t>
+          <t>The customer has left the call.</t>
         </is>
       </c>
       <c r="D284" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛውን በመጠበቅ ላይ…</t>
+          <t>ደንበኛው ጥሪውን ለቅቋል።</t>
         </is>
       </c>
       <c r="E284" s="13" t="inlineStr">
         <is>
-          <t>Maamilaa eegaa jirra…</t>
+          <t>Maamilaan bilbila irraa ba'eera.</t>
         </is>
       </c>
       <c r="F284" s="12" t="inlineStr">
         <is>
-          <t>ነቲ ዓሚል ንጽበ ኣለና…</t>
+          <t>እቲ ዓሚል ካብቲ ጻውዒት ወጺኡ።</t>
         </is>
       </c>
       <c r="G284" s="13" t="inlineStr">
         <is>
-          <t>Macmiilka la sugayo…</t>
+          <t>Macmiilku wicitaanka wuu ka baxay.</t>
         </is>
       </c>
       <c r="H284" s="13" t="inlineStr">
         <is>
-          <t>Inasubiri Mteja…</t>
+          <t>Mteja ameondoka kwenye simu.</t>
         </is>
       </c>
       <c r="I284" s="14" t="inlineStr"/>
@@ -18457,7 +18457,7 @@
     <row r="285" ht="44" customHeight="1">
       <c r="A285" s="11" t="inlineStr">
         <is>
-          <t>mic_blocked</t>
+          <t>waiting_for_customer</t>
         </is>
       </c>
       <c r="B285" s="11" t="inlineStr">
@@ -18467,32 +18467,32 @@
       </c>
       <c r="C285" s="11" t="inlineStr">
         <is>
-          <t>Microphone access is blocked. Allow it in your browser and take the session again.</t>
+          <t>Waiting for the customer…</t>
         </is>
       </c>
       <c r="D285" s="12" t="inlineStr">
         <is>
-          <t>የማይክሮፎን መዳረሻ ታግዷል። በአሳሽዎ ውስጥ ይፍቀዱና ክፍለ-ጊዜውን እንደገና ይውሰዱ።</t>
+          <t>ደንበኛውን በመጠበቅ ላይ…</t>
         </is>
       </c>
       <c r="E285" s="13" t="inlineStr">
         <is>
-          <t>Maayikiroofoonii dhorkameera. Biraawzarii keessan keessatti hayyamaatii session irra deebi'aa fudhadhaa.</t>
+          <t>Maamilaa eegaa jirra…</t>
         </is>
       </c>
       <c r="F285" s="12" t="inlineStr">
         <is>
-          <t>መእተዊ ማይክሮፎን ተዓጊቱ። ኣብ መርበብ መንሸራተቲኹም ፍቐዱ እሞ ነቲ ክፍለ-ግዜ ደጊምኩም ውሰዱ።</t>
+          <t>ነቲ ዓሚል ንጽበ ኣለና…</t>
         </is>
       </c>
       <c r="G285" s="13" t="inlineStr">
         <is>
-          <t>Makarafoonka waa la xannibay. Browser-kaaga ka ogolow oo kalfadhiga mar kale qaado.</t>
+          <t>Macmiilka la sugayo…</t>
         </is>
       </c>
       <c r="H285" s="13" t="inlineStr">
         <is>
-          <t>Ufikiaji wa maikrofoni umezuiwa. Ruhusu kwenye kivinjari chako na uanze kikao tena.</t>
+          <t>Inasubiri Mteja…</t>
         </is>
       </c>
       <c r="I285" s="14" t="inlineStr"/>
@@ -18500,7 +18500,7 @@
     <row r="286" ht="44" customHeight="1">
       <c r="A286" s="11" t="inlineStr">
         <is>
-          <t>unknown_error</t>
+          <t>mic_blocked</t>
         </is>
       </c>
       <c r="B286" s="11" t="inlineStr">
@@ -18510,32 +18510,32 @@
       </c>
       <c r="C286" s="11" t="inlineStr">
         <is>
-          <t>unknown error</t>
+          <t>Microphone access is blocked. Allow it in your browser and take the session again.</t>
         </is>
       </c>
       <c r="D286" s="12" t="inlineStr">
         <is>
-          <t>ያልታወቀ ስህተት</t>
+          <t>የማይክሮፎን መዳረሻ ታግዷል። በአሳሽዎ ውስጥ ይፍቀዱና ክፍለ-ጊዜውን እንደገና ይውሰዱ።</t>
         </is>
       </c>
       <c r="E286" s="13" t="inlineStr">
         <is>
-          <t>dogoggora hin beekamne</t>
+          <t>Maayikiroofoonii dhorkameera. Biraawzarii keessan keessatti hayyamaatii session irra deebi'aa fudhadhaa.</t>
         </is>
       </c>
       <c r="F286" s="12" t="inlineStr">
         <is>
-          <t>ዘይተፈልጠ ጌጋ</t>
+          <t>መእተዊ ማይክሮፎን ተዓጊቱ። ኣብ መርበብ መንሸራተቲኹም ፍቐዱ እሞ ነቲ ክፍለ-ግዜ ደጊምኩም ውሰዱ።</t>
         </is>
       </c>
       <c r="G286" s="13" t="inlineStr">
         <is>
-          <t>khalad aan la garanayn</t>
+          <t>Makarafoonka waa la xannibay. Browser-kaaga ka ogolow oo kalfadhiga mar kale qaado.</t>
         </is>
       </c>
       <c r="H286" s="13" t="inlineStr">
         <is>
-          <t>hitilafu isiyojulikana</t>
+          <t>Ufikiaji wa maikrofoni umezuiwa. Ruhusu kwenye kivinjari chako na uanze kikao tena.</t>
         </is>
       </c>
       <c r="I286" s="14" t="inlineStr"/>
@@ -18543,7 +18543,7 @@
     <row r="287" ht="44" customHeight="1">
       <c r="A287" s="11" t="inlineStr">
         <is>
-          <t>no_messages_yet</t>
+          <t>unknown_error</t>
         </is>
       </c>
       <c r="B287" s="11" t="inlineStr">
@@ -18553,32 +18553,32 @@
       </c>
       <c r="C287" s="11" t="inlineStr">
         <is>
-          <t>No messages yet.</t>
+          <t>unknown error</t>
         </is>
       </c>
       <c r="D287" s="12" t="inlineStr">
         <is>
-          <t>እስካሁን መልእክት የለም።</t>
+          <t>ያልታወቀ ስህተት</t>
         </is>
       </c>
       <c r="E287" s="13" t="inlineStr">
         <is>
-          <t>Ammaaf ergaan hin jiru.</t>
+          <t>dogoggora hin beekamne</t>
         </is>
       </c>
       <c r="F287" s="12" t="inlineStr">
         <is>
-          <t>ክሳብ ሕጂ መልእኽቲ የለን።</t>
+          <t>ዘይተፈልጠ ጌጋ</t>
         </is>
       </c>
       <c r="G287" s="13" t="inlineStr">
         <is>
-          <t>Weli fariimo ma jiraan.</t>
+          <t>khalad aan la garanayn</t>
         </is>
       </c>
       <c r="H287" s="13" t="inlineStr">
         <is>
-          <t>Hakuna ujumbe bado.</t>
+          <t>hitilafu isiyojulikana</t>
         </is>
       </c>
       <c r="I287" s="14" t="inlineStr"/>
@@ -18586,7 +18586,7 @@
     <row r="288" ht="44" customHeight="1">
       <c r="A288" s="11" t="inlineStr">
         <is>
-          <t>you_label</t>
+          <t>no_messages_yet</t>
         </is>
       </c>
       <c r="B288" s="11" t="inlineStr">
@@ -18596,32 +18596,32 @@
       </c>
       <c r="C288" s="11" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>No messages yet.</t>
         </is>
       </c>
       <c r="D288" s="12" t="inlineStr">
         <is>
-          <t>እርስዎ</t>
+          <t>እስካሁን መልእክት የለም።</t>
         </is>
       </c>
       <c r="E288" s="13" t="inlineStr">
         <is>
-          <t>Isin</t>
+          <t>Ammaaf ergaan hin jiru.</t>
         </is>
       </c>
       <c r="F288" s="12" t="inlineStr">
         <is>
-          <t>ንስኹም</t>
+          <t>ክሳብ ሕጂ መልእኽቲ የለን።</t>
         </is>
       </c>
       <c r="G288" s="13" t="inlineStr">
         <is>
-          <t>Adiga</t>
+          <t>Weli fariimo ma jiraan.</t>
         </is>
       </c>
       <c r="H288" s="13" t="inlineStr">
         <is>
-          <t>Wewe</t>
+          <t>Hakuna ujumbe bado.</t>
         </is>
       </c>
       <c r="I288" s="14" t="inlineStr"/>
@@ -18629,7 +18629,7 @@
     <row r="289" ht="44" customHeight="1">
       <c r="A289" s="11" t="inlineStr">
         <is>
-          <t>assistant_label</t>
+          <t>you_label</t>
         </is>
       </c>
       <c r="B289" s="11" t="inlineStr">
@@ -18639,32 +18639,32 @@
       </c>
       <c r="C289" s="11" t="inlineStr">
         <is>
-          <t>Assistant</t>
+          <t>You</t>
         </is>
       </c>
       <c r="D289" s="12" t="inlineStr">
         <is>
-          <t>ረዳት</t>
+          <t>እርስዎ</t>
         </is>
       </c>
       <c r="E289" s="13" t="inlineStr">
         <is>
-          <t>Gargaaraa</t>
+          <t>Isin</t>
         </is>
       </c>
       <c r="F289" s="12" t="inlineStr">
         <is>
-          <t>ሓጋዚ</t>
+          <t>ንስኹም</t>
         </is>
       </c>
       <c r="G289" s="13" t="inlineStr">
         <is>
-          <t>Kaaliye</t>
+          <t>Adiga</t>
         </is>
       </c>
       <c r="H289" s="13" t="inlineStr">
         <is>
-          <t>Msaidizi</t>
+          <t>Wewe</t>
         </is>
       </c>
       <c r="I289" s="14" t="inlineStr"/>
@@ -18672,7 +18672,7 @@
     <row r="290" ht="44" customHeight="1">
       <c r="A290" s="11" t="inlineStr">
         <is>
-          <t>conversation_unavailable</t>
+          <t>assistant_label</t>
         </is>
       </c>
       <c r="B290" s="11" t="inlineStr">
@@ -18682,32 +18682,32 @@
       </c>
       <c r="C290" s="11" t="inlineStr">
         <is>
-          <t>Conversation unavailable.</t>
+          <t>Assistant</t>
         </is>
       </c>
       <c r="D290" s="12" t="inlineStr">
         <is>
-          <t>ውይይቱ አይገኝም።</t>
+          <t>ረዳት</t>
         </is>
       </c>
       <c r="E290" s="13" t="inlineStr">
         <is>
-          <t>Mariin hin argamu.</t>
+          <t>Gargaaraa</t>
         </is>
       </c>
       <c r="F290" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዝርርብ ኣይርከብን።</t>
+          <t>ሓጋዚ</t>
         </is>
       </c>
       <c r="G290" s="13" t="inlineStr">
         <is>
-          <t>Wadahadalka lama heli karo.</t>
+          <t>Kaaliye</t>
         </is>
       </c>
       <c r="H290" s="13" t="inlineStr">
         <is>
-          <t>Mazungumzo hayapatikani.</t>
+          <t>Msaidizi</t>
         </is>
       </c>
       <c r="I290" s="14" t="inlineStr"/>
@@ -18715,7 +18715,7 @@
     <row r="291" ht="44" customHeight="1">
       <c r="A291" s="11" t="inlineStr">
         <is>
-          <t>unmute</t>
+          <t>conversation_unavailable</t>
         </is>
       </c>
       <c r="B291" s="11" t="inlineStr">
@@ -18725,32 +18725,32 @@
       </c>
       <c r="C291" s="11" t="inlineStr">
         <is>
-          <t>Unmute</t>
+          <t>Conversation unavailable.</t>
         </is>
       </c>
       <c r="D291" s="12" t="inlineStr">
         <is>
-          <t>ድምፅ አብራ</t>
+          <t>ውይይቱ አይገኝም።</t>
         </is>
       </c>
       <c r="E291" s="13" t="inlineStr">
         <is>
-          <t>Sagalee banaa</t>
+          <t>Mariin hin argamu.</t>
         </is>
       </c>
       <c r="F291" s="12" t="inlineStr">
         <is>
-          <t>ድምጺ ኣብርህ</t>
+          <t>እቲ ዝርርብ ኣይርከብን።</t>
         </is>
       </c>
       <c r="G291" s="13" t="inlineStr">
         <is>
-          <t>Codka fur</t>
+          <t>Wadahadalka lama heli karo.</t>
         </is>
       </c>
       <c r="H291" s="13" t="inlineStr">
         <is>
-          <t>Rudisha Sauti</t>
+          <t>Mazungumzo hayapatikani.</t>
         </is>
       </c>
       <c r="I291" s="14" t="inlineStr"/>
@@ -18758,7 +18758,7 @@
     <row r="292" ht="44" customHeight="1">
       <c r="A292" s="11" t="inlineStr">
         <is>
-          <t>session_summary_prompt</t>
+          <t>unmute</t>
         </is>
       </c>
       <c r="B292" s="11" t="inlineStr">
@@ -18768,32 +18768,32 @@
       </c>
       <c r="C292" s="11" t="inlineStr">
         <is>
-          <t>What did this session cover? (optional)</t>
+          <t>Unmute</t>
         </is>
       </c>
       <c r="D292" s="12" t="inlineStr">
         <is>
-          <t>ይህ ክፍለ-ጊዜ ምን ሸፈነ? (አማራጭ)</t>
+          <t>ድምፅ አብራ</t>
         </is>
       </c>
       <c r="E292" s="13" t="inlineStr">
         <is>
-          <t>Sessioniin kun maal haguuge? (filannoo)</t>
+          <t>Sagalee banaa</t>
         </is>
       </c>
       <c r="F292" s="12" t="inlineStr">
         <is>
-          <t>እዚ ክፍለ-ግዜ እንታይ ሸፈነ? (ኣማራጺ)</t>
+          <t>ድምጺ ኣብርህ</t>
         </is>
       </c>
       <c r="G292" s="13" t="inlineStr">
         <is>
-          <t>Kalfadhigan muxuu daboolay? (ikhtiyaari)</t>
+          <t>Codka fur</t>
         </is>
       </c>
       <c r="H292" s="13" t="inlineStr">
         <is>
-          <t>Kikao hiki kilihusu nini? (si lazima)</t>
+          <t>Rudisha Sauti</t>
         </is>
       </c>
       <c r="I292" s="14" t="inlineStr"/>
@@ -18801,7 +18801,7 @@
     <row r="293" ht="44" customHeight="1">
       <c r="A293" s="11" t="inlineStr">
         <is>
-          <t>customer_ended_call</t>
+          <t>session_summary_prompt</t>
         </is>
       </c>
       <c r="B293" s="11" t="inlineStr">
@@ -18811,32 +18811,32 @@
       </c>
       <c r="C293" s="11" t="inlineStr">
         <is>
-          <t>The customer ended the call</t>
+          <t>What did this session cover? (optional)</t>
         </is>
       </c>
       <c r="D293" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛው ጥሪውን አቋረጠ</t>
+          <t>ይህ ክፍለ-ጊዜ ምን ሸፈነ? (አማራጭ)</t>
         </is>
       </c>
       <c r="E293" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan bilbila xumure</t>
+          <t>Sessioniin kun maal haguuge? (filannoo)</t>
         </is>
       </c>
       <c r="F293" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዓሚል ነቲ ጻውዒት ወዲኡዎ</t>
+          <t>እዚ ክፍለ-ግዜ እንታይ ሸፈነ? (ኣማራጺ)</t>
         </is>
       </c>
       <c r="G293" s="13" t="inlineStr">
         <is>
-          <t>Macmiilku wicitaanka wuu joojiyay</t>
+          <t>Kalfadhigan muxuu daboolay? (ikhtiyaari)</t>
         </is>
       </c>
       <c r="H293" s="13" t="inlineStr">
         <is>
-          <t>Mteja alimaliza simu</t>
+          <t>Kikao hiki kilihusu nini? (si lazima)</t>
         </is>
       </c>
       <c r="I293" s="14" t="inlineStr"/>
@@ -18844,7 +18844,7 @@
     <row r="294" ht="44" customHeight="1">
       <c r="A294" s="11" t="inlineStr">
         <is>
-          <t>verified_scope</t>
+          <t>customer_ended_call</t>
         </is>
       </c>
       <c r="B294" s="11" t="inlineStr">
@@ -18854,32 +18854,32 @@
       </c>
       <c r="C294" s="11" t="inlineStr">
         <is>
-          <t>You can now discuss their own records, take documents and file a dispute. Never a deposit, withdrawal or transfer.</t>
+          <t>The customer ended the call</t>
         </is>
       </c>
       <c r="D294" s="12" t="inlineStr">
         <is>
-          <t>አሁን ስለ ራሳቸው መዝገቦች መወያየት፣ ሰነዶች መቀበልና ቅሬታ ማስመዝገብ ይችላሉ። በፍጹም ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም።</t>
+          <t>ደንበኛው ጥሪውን አቋረጠ</t>
         </is>
       </c>
       <c r="E294" s="13" t="inlineStr">
         <is>
-          <t>Amma waa'ee galmee isaanii mari'achuu, sanadoota fudhachuu fi komii galmeessuu dandeessu. Gonkumaa kuusaa, baasii yookiin dabarsa hin jiru.</t>
+          <t>Maamilaan bilbila xumure</t>
         </is>
       </c>
       <c r="F294" s="12" t="inlineStr">
         <is>
-          <t>ሕጂ ብዛዕባ ናቶም መዝገባት ክትዘራረቡ፣ ሰነዳት ክትቅበሉን ጥርዓን ከተመዝግቡን ትኽእሉ። ፈጺሙ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን።</t>
+          <t>እቲ ዓሚል ነቲ ጻውዒት ወዲኡዎ</t>
         </is>
       </c>
       <c r="G294" s="13" t="inlineStr">
         <is>
-          <t>Hadda waad kala hadli kartaa diiwaankooda, dukumiinti qaadan iyo cabasho diiwaangelin. Weligaa dhigasho, qaadis ama wareejin ma jirto.</t>
+          <t>Macmiilku wicitaanka wuu joojiyay</t>
         </is>
       </c>
       <c r="H294" s="13" t="inlineStr">
         <is>
-          <t>Sasa unaweza kuzungumzia rekodi zao wenyewe, kuchukua nyaraka na kuwasilisha mgogoro. Kamwe amana, uondoaji au uhamishaji.</t>
+          <t>Mteja alimaliza simu</t>
         </is>
       </c>
       <c r="I294" s="14" t="inlineStr"/>
@@ -18887,7 +18887,7 @@
     <row r="295" ht="44" customHeight="1">
       <c r="A295" s="11" t="inlineStr">
         <is>
-          <t>establish_who_they_are</t>
+          <t>verified_scope</t>
         </is>
       </c>
       <c r="B295" s="11" t="inlineStr">
@@ -18897,32 +18897,32 @@
       </c>
       <c r="C295" s="11" t="inlineStr">
         <is>
-          <t>Establish who they are — either one</t>
+          <t>You can now discuss their own records, take documents and file a dispute. Never a deposit, withdrawal or transfer.</t>
         </is>
       </c>
       <c r="D295" s="12" t="inlineStr">
         <is>
-          <t>ማንነታቸውን ያረጋግጡ — አንዱ ይበቃል</t>
+          <t>አሁን ስለ ራሳቸው መዝገቦች መወያየት፣ ሰነዶች መቀበልና ቅሬታ ማስመዝገብ ይችላሉ። በፍጹም ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም።</t>
         </is>
       </c>
       <c r="E295" s="13" t="inlineStr">
         <is>
-          <t>Eenyummaa isaanii mirkaneessaa — tokko ni ga'a</t>
+          <t>Amma waa'ee galmee isaanii mari'achuu, sanadoota fudhachuu fi komii galmeessuu dandeessu. Gonkumaa kuusaa, baasii yookiin dabarsa hin jiru.</t>
         </is>
       </c>
       <c r="F295" s="12" t="inlineStr">
         <is>
-          <t>መንነቶም ኣረጋግጹ — ሓደ እኹል እዩ</t>
+          <t>ሕጂ ብዛዕባ ናቶም መዝገባት ክትዘራረቡ፣ ሰነዳት ክትቅበሉን ጥርዓን ከተመዝግቡን ትኽእሉ። ፈጺሙ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን።</t>
         </is>
       </c>
       <c r="G295" s="13" t="inlineStr">
         <is>
-          <t>Ogow cidda ay yihiin — mid kasta</t>
+          <t>Hadda waad kala hadli kartaa diiwaankooda, dukumiinti qaadan iyo cabasho diiwaangelin. Weligaa dhigasho, qaadis ama wareejin ma jirto.</t>
         </is>
       </c>
       <c r="H295" s="13" t="inlineStr">
         <is>
-          <t>Thibitisha ni nani — mojawapo</t>
+          <t>Sasa unaweza kuzungumzia rekodi zao wenyewe, kuchukua nyaraka na kuwasilisha mgogoro. Kamwe amana, uondoaji au uhamishaji.</t>
         </is>
       </c>
       <c r="I295" s="14" t="inlineStr"/>
@@ -18930,7 +18930,7 @@
     <row r="296" ht="44" customHeight="1">
       <c r="A296" s="11" t="inlineStr">
         <is>
-          <t>chk_id_document</t>
+          <t>establish_who_they_are</t>
         </is>
       </c>
       <c r="B296" s="11" t="inlineStr">
@@ -18940,32 +18940,32 @@
       </c>
       <c r="C296" s="11" t="inlineStr">
         <is>
-          <t>Fayda ID shown and matches the account name</t>
+          <t>Establish who they are — either one</t>
         </is>
       </c>
       <c r="D296" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ መታወቂያ ታይቷል እና ከሂሳቡ ስም ጋር ይዛመዳል</t>
+          <t>ማንነታቸውን ያረጋግጡ — አንዱ ይበቃል</t>
         </is>
       </c>
       <c r="E296" s="13" t="inlineStr">
         <is>
-          <t>Waraqaan eenyummaa Fayda agarsiifame maqaa herregaa waliin walsimeera</t>
+          <t>Eenyummaa isaanii mirkaneessaa — tokko ni ga'a</t>
         </is>
       </c>
       <c r="F296" s="12" t="inlineStr">
         <is>
-          <t>መንነት ፋይዳ ተራእዩን ምስ ስም ሕሳብ ይሰማማዕን</t>
+          <t>መንነቶም ኣረጋግጹ — ሓደ እኹል እዩ</t>
         </is>
       </c>
       <c r="G296" s="13" t="inlineStr">
         <is>
-          <t>Aqoonsiga Fayda waa la tusay wuxuuna la mid yahay magaca xisaabta</t>
+          <t>Ogow cidda ay yihiin — mid kasta</t>
         </is>
       </c>
       <c r="H296" s="13" t="inlineStr">
         <is>
-          <t>Kitambulisho cha Fayda kimeonyeshwa na kinalingana na jina la akaunti</t>
+          <t>Thibitisha ni nani — mojawapo</t>
         </is>
       </c>
       <c r="I296" s="14" t="inlineStr"/>
@@ -18973,7 +18973,7 @@
     <row r="297" ht="44" customHeight="1">
       <c r="A297" s="11" t="inlineStr">
         <is>
-          <t>chk_fayda_matched</t>
+          <t>chk_id_document</t>
         </is>
       </c>
       <c r="B297" s="11" t="inlineStr">
@@ -18983,32 +18983,32 @@
       </c>
       <c r="C297" s="11" t="inlineStr">
         <is>
-          <t>Fayda number matches the account record</t>
+          <t>Fayda ID shown and matches the account name</t>
         </is>
       </c>
       <c r="D297" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ ቁጥር ከሂሳቡ መዝገብ ጋር ይዛመዳል</t>
+          <t>የፋይዳ መታወቂያ ታይቷል እና ከሂሳቡ ስም ጋር ይዛመዳል</t>
         </is>
       </c>
       <c r="E297" s="13" t="inlineStr">
         <is>
-          <t>Lakkoofsi Fayda galmee herregaa waliin walsimeera</t>
+          <t>Waraqaan eenyummaa Fayda agarsiifame maqaa herregaa waliin walsimeera</t>
         </is>
       </c>
       <c r="F297" s="12" t="inlineStr">
         <is>
-          <t>ቁጽሪ ፋይዳ ምስ መዝገብ ሕሳብ ይሰማማዕ</t>
+          <t>መንነት ፋይዳ ተራእዩን ምስ ስም ሕሳብ ይሰማማዕን</t>
         </is>
       </c>
       <c r="G297" s="13" t="inlineStr">
         <is>
-          <t>Lambarka Fayda wuxuu la mid yahay diiwaanka xisaabta</t>
+          <t>Aqoonsiga Fayda waa la tusay wuxuuna la mid yahay magaca xisaabta</t>
         </is>
       </c>
       <c r="H297" s="13" t="inlineStr">
         <is>
-          <t>Namba ya Fayda inalingana na rekodi ya akaunti</t>
+          <t>Kitambulisho cha Fayda kimeonyeshwa na kinalingana na jina la akaunti</t>
         </is>
       </c>
       <c r="I297" s="14" t="inlineStr"/>
@@ -19016,7 +19016,7 @@
     <row r="298" ht="44" customHeight="1">
       <c r="A298" s="11" t="inlineStr">
         <is>
-          <t>chk_fayda_matched_note</t>
+          <t>chk_fayda_matched</t>
         </is>
       </c>
       <c r="B298" s="11" t="inlineStr">
@@ -19026,32 +19026,32 @@
       </c>
       <c r="C298" s="11" t="inlineStr">
         <is>
-          <t>on your own screen — works on an audio call</t>
+          <t>Fayda number matches the account record</t>
         </is>
       </c>
       <c r="D298" s="12" t="inlineStr">
         <is>
-          <t>በራስዎ ስክሪን ላይ — በድምፅ ጥሪም ይሠራል</t>
+          <t>የፋይዳ ቁጥር ከሂሳቡ መዝገብ ጋር ይዛመዳል</t>
         </is>
       </c>
       <c r="E298" s="13" t="inlineStr">
         <is>
-          <t>iskiriinii keessan irratti — bilbila sagalee irrattis ni hojjeta</t>
+          <t>Lakkoofsi Fayda galmee herregaa waliin walsimeera</t>
         </is>
       </c>
       <c r="F298" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ናትኩም መርአዪ — ኣብ ናይ ድምጺ ጻውዒት እውን ይሰርሕ</t>
+          <t>ቁጽሪ ፋይዳ ምስ መዝገብ ሕሳብ ይሰማማዕ</t>
         </is>
       </c>
       <c r="G298" s="13" t="inlineStr">
         <is>
-          <t>shaashaddaada — wicitaan cod ahna wuu ka shaqeeyaa</t>
+          <t>Lambarka Fayda wuxuu la mid yahay diiwaanka xisaabta</t>
         </is>
       </c>
       <c r="H298" s="13" t="inlineStr">
         <is>
-          <t>kwenye skrini yako mwenyewe — inafanya kazi kwenye simu ya sauti</t>
+          <t>Namba ya Fayda inalingana na rekodi ya akaunti</t>
         </is>
       </c>
       <c r="I298" s="14" t="inlineStr"/>
@@ -19059,7 +19059,7 @@
     <row r="299" ht="44" customHeight="1">
       <c r="A299" s="11" t="inlineStr">
         <is>
-          <t>chk_id_photo</t>
+          <t>chk_fayda_matched_note</t>
         </is>
       </c>
       <c r="B299" s="11" t="inlineStr">
@@ -19069,32 +19069,32 @@
       </c>
       <c r="C299" s="11" t="inlineStr">
         <is>
-          <t>Photo on the ID matches the person on the call</t>
+          <t>on your own screen — works on an audio call</t>
         </is>
       </c>
       <c r="D299" s="12" t="inlineStr">
         <is>
-          <t>በመታወቂያው ላይ ያለው ፎቶ ከጥሪው ላይ ካለው ሰው ጋር ይዛመዳል</t>
+          <t>በራስዎ ስክሪን ላይ — በድምፅ ጥሪም ይሠራል</t>
         </is>
       </c>
       <c r="E299" s="13" t="inlineStr">
         <is>
-          <t>Suuraan waraqaa eenyummaa irra jiru nama bilbila irra jiru waliin walsimeera</t>
+          <t>iskiriinii keessan irratti — bilbila sagalee irrattis ni hojjeta</t>
         </is>
       </c>
       <c r="F299" s="12" t="inlineStr">
         <is>
-          <t>እቲ ኣብ መንነት ዘሎ ስእሊ ምስቲ ኣብ ጻውዒት ዘሎ ሰብ ይሰማማዕ</t>
+          <t>ኣብ ናትኩም መርአዪ — ኣብ ናይ ድምጺ ጻውዒት እውን ይሰርሕ</t>
         </is>
       </c>
       <c r="G299" s="13" t="inlineStr">
         <is>
-          <t>Sawirka aqoonsiga wuxuu la mid yahay qofka wicitaanka ku jira</t>
+          <t>shaashaddaada — wicitaan cod ahna wuu ka shaqeeyaa</t>
         </is>
       </c>
       <c r="H299" s="13" t="inlineStr">
         <is>
-          <t>Picha kwenye kitambulisho inalingana na mtu aliye kwenye simu</t>
+          <t>kwenye skrini yako mwenyewe — inafanya kazi kwenye simu ya sauti</t>
         </is>
       </c>
       <c r="I299" s="14" t="inlineStr"/>
@@ -19102,7 +19102,7 @@
     <row r="300" ht="44" customHeight="1">
       <c r="A300" s="11" t="inlineStr">
         <is>
-          <t>chk_video_only</t>
+          <t>chk_id_photo</t>
         </is>
       </c>
       <c r="B300" s="11" t="inlineStr">
@@ -19112,32 +19112,32 @@
       </c>
       <c r="C300" s="11" t="inlineStr">
         <is>
-          <t>video only</t>
+          <t>Photo on the ID matches the person on the call</t>
         </is>
       </c>
       <c r="D300" s="12" t="inlineStr">
         <is>
-          <t>ቪዲዮ ብቻ</t>
+          <t>በመታወቂያው ላይ ያለው ፎቶ ከጥሪው ላይ ካለው ሰው ጋር ይዛመዳል</t>
         </is>
       </c>
       <c r="E300" s="13" t="inlineStr">
         <is>
-          <t>viidiyoo qofa</t>
+          <t>Suuraan waraqaa eenyummaa irra jiru nama bilbila irra jiru waliin walsimeera</t>
         </is>
       </c>
       <c r="F300" s="12" t="inlineStr">
         <is>
-          <t>ቪድዮ ጥራይ</t>
+          <t>እቲ ኣብ መንነት ዘሎ ስእሊ ምስቲ ኣብ ጻውዒት ዘሎ ሰብ ይሰማማዕ</t>
         </is>
       </c>
       <c r="G300" s="13" t="inlineStr">
         <is>
-          <t>fiidyow oo kaliya</t>
+          <t>Sawirka aqoonsiga wuxuu la mid yahay qofka wicitaanka ku jira</t>
         </is>
       </c>
       <c r="H300" s="13" t="inlineStr">
         <is>
-          <t>video pekee</t>
+          <t>Picha kwenye kitambulisho inalingana na mtu aliye kwenye simu</t>
         </is>
       </c>
       <c r="I300" s="14" t="inlineStr"/>
@@ -19145,7 +19145,7 @@
     <row r="301" ht="44" customHeight="1">
       <c r="A301" s="11" t="inlineStr">
         <is>
-          <t>confirm_account_theirs</t>
+          <t>chk_video_only</t>
         </is>
       </c>
       <c r="B301" s="11" t="inlineStr">
@@ -19155,32 +19155,32 @@
       </c>
       <c r="C301" s="11" t="inlineStr">
         <is>
-          <t>And confirm the account is theirs</t>
+          <t>video only</t>
         </is>
       </c>
       <c r="D301" s="12" t="inlineStr">
         <is>
-          <t>እና ሂሳቡ የእነሱ መሆኑን ያረጋግጡ</t>
+          <t>ቪዲዮ ብቻ</t>
         </is>
       </c>
       <c r="E301" s="13" t="inlineStr">
         <is>
-          <t>Akkasumas herregni kan isaanii ta'uu mirkaneessaa</t>
+          <t>viidiyoo qofa</t>
         </is>
       </c>
       <c r="F301" s="12" t="inlineStr">
         <is>
-          <t>ከምኡ'ውን እቲ ሕሳብ ናቶም ምዃኑ ኣረጋግጹ</t>
+          <t>ቪድዮ ጥራይ</t>
         </is>
       </c>
       <c r="G301" s="13" t="inlineStr">
         <is>
-          <t>Xaqiiji in xisaabtu tahay tooda</t>
+          <t>fiidyow oo kaliya</t>
         </is>
       </c>
       <c r="H301" s="13" t="inlineStr">
         <is>
-          <t>Na thibitisha akaunti ni yao</t>
+          <t>video pekee</t>
         </is>
       </c>
       <c r="I301" s="14" t="inlineStr"/>
@@ -19188,7 +19188,7 @@
     <row r="302" ht="44" customHeight="1">
       <c r="A302" s="11" t="inlineStr">
         <is>
-          <t>confirm_identity</t>
+          <t>confirm_account_theirs</t>
         </is>
       </c>
       <c r="B302" s="11" t="inlineStr">
@@ -19198,32 +19198,32 @@
       </c>
       <c r="C302" s="11" t="inlineStr">
         <is>
-          <t>Confirm identity</t>
+          <t>And confirm the account is theirs</t>
         </is>
       </c>
       <c r="D302" s="12" t="inlineStr">
         <is>
-          <t>ማንነት አረጋግጥ</t>
+          <t>እና ሂሳቡ የእነሱ መሆኑን ያረጋግጡ</t>
         </is>
       </c>
       <c r="E302" s="13" t="inlineStr">
         <is>
-          <t>Eenyummaa mirkaneessi</t>
+          <t>Akkasumas herregni kan isaanii ta'uu mirkaneessaa</t>
         </is>
       </c>
       <c r="F302" s="12" t="inlineStr">
         <is>
-          <t>መንነት ኣረጋግጽ</t>
+          <t>ከምኡ'ውን እቲ ሕሳብ ናቶም ምዃኑ ኣረጋግጹ</t>
         </is>
       </c>
       <c r="G302" s="13" t="inlineStr">
         <is>
-          <t>Xaqiiji aqoonsiga</t>
+          <t>Xaqiiji in xisaabtu tahay tooda</t>
         </is>
       </c>
       <c r="H302" s="13" t="inlineStr">
         <is>
-          <t>Thibitisha Utambulisho</t>
+          <t>Na thibitisha akaunti ni yao</t>
         </is>
       </c>
       <c r="I302" s="14" t="inlineStr"/>
@@ -19231,7 +19231,7 @@
     <row r="303" ht="44" customHeight="1">
       <c r="A303" s="11" t="inlineStr">
         <is>
-          <t>unverified_scope</t>
+          <t>confirm_identity</t>
         </is>
       </c>
       <c r="B303" s="11" t="inlineStr">
@@ -19241,32 +19241,32 @@
       </c>
       <c r="C303" s="11" t="inlineStr">
         <is>
-          <t>Until this is done you can only give general guidance — products, eligibility and how to apply.</t>
+          <t>Confirm identity</t>
         </is>
       </c>
       <c r="D303" s="12" t="inlineStr">
         <is>
-          <t>ይህ እስኪከናወን ድረስ አጠቃላይ መመሪያ ብቻ መስጠት ይችላሉ — ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል።</t>
+          <t>ማንነት አረጋግጥ</t>
         </is>
       </c>
       <c r="E303" s="13" t="inlineStr">
         <is>
-          <t>Hanga kun raawwatutti qajeelfama waliigalaa qofa kennuu dandeessu — oomishaalee, ulaagaa fi akkaataa itti iyyatan.</t>
+          <t>Eenyummaa mirkaneessi</t>
         </is>
       </c>
       <c r="F303" s="12" t="inlineStr">
         <is>
-          <t>እዚ ክሳብ ዝፍጸም ሓፈሻዊ መምርሒ ጥራይ ክትህቡ ትኽእሉ — ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን።</t>
+          <t>መንነት ኣረጋግጽ</t>
         </is>
       </c>
       <c r="G303" s="13" t="inlineStr">
         <is>
-          <t>Ilaa tan la sameeyo waxaad kaliya bixin kartaa hagaajin guud — alaabta, u-qalmitaanka iyo sida loo codsado.</t>
+          <t>Xaqiiji aqoonsiga</t>
         </is>
       </c>
       <c r="H303" s="13" t="inlineStr">
         <is>
-          <t>Hadi hili litakapofanyika unaweza tu kutoa mwongozo wa jumla — bidhaa, sifa za kustahiki na jinsi ya kuomba.</t>
+          <t>Thibitisha Utambulisho</t>
         </is>
       </c>
       <c r="I303" s="14" t="inlineStr"/>
@@ -19274,7 +19274,7 @@
     <row r="304" ht="44" customHeight="1">
       <c r="A304" s="11" t="inlineStr">
         <is>
-          <t>fayda_number_required</t>
+          <t>unverified_scope</t>
         </is>
       </c>
       <c r="B304" s="11" t="inlineStr">
@@ -19284,32 +19284,32 @@
       </c>
       <c r="C304" s="11" t="inlineStr">
         <is>
-          <t>Fayda number (required — it is what the record keeps)</t>
+          <t>Until this is done you can only give general guidance — products, eligibility and how to apply.</t>
         </is>
       </c>
       <c r="D304" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ ቁጥር (ያስፈልጋል — መዝገቡ የሚይዘው ይህ ነው)</t>
+          <t>ይህ እስኪከናወን ድረስ አጠቃላይ መመሪያ ብቻ መስጠት ይችላሉ — ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል።</t>
         </is>
       </c>
       <c r="E304" s="13" t="inlineStr">
         <is>
-          <t>Lakkoofsa Fayda (barbaachisaa — kan galmeen qabatu isa kana)</t>
+          <t>Hanga kun raawwatutti qajeelfama waliigalaa qofa kennuu dandeessu — oomishaalee, ulaagaa fi akkaataa itti iyyatan.</t>
         </is>
       </c>
       <c r="F304" s="12" t="inlineStr">
         <is>
-          <t>ቁጽሪ ፋይዳ (የድሊ — እቲ መዝገብ ዝሕዞ እዚ እዩ)</t>
+          <t>እዚ ክሳብ ዝፍጸም ሓፈሻዊ መምርሒ ጥራይ ክትህቡ ትኽእሉ — ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን።</t>
         </is>
       </c>
       <c r="G304" s="13" t="inlineStr">
         <is>
-          <t>Lambarka Fayda (loo baahan yahay — waa waxa diiwaanku hayo)</t>
+          <t>Ilaa tan la sameeyo waxaad kaliya bixin kartaa hagaajin guud — alaabta, u-qalmitaanka iyo sida loo codsado.</t>
         </is>
       </c>
       <c r="H304" s="13" t="inlineStr">
         <is>
-          <t>Namba ya Fayda (inahitajika — ndiyo inayowekwa kwenye rekodi)</t>
+          <t>Hadi hili litakapofanyika unaweza tu kutoa mwongozo wa jumla — bidhaa, sifa za kustahiki na jinsi ya kuomba.</t>
         </is>
       </c>
       <c r="I304" s="14" t="inlineStr"/>
@@ -19317,7 +19317,7 @@
     <row r="305" ht="44" customHeight="1">
       <c r="A305" s="11" t="inlineStr">
         <is>
-          <t>download_for_translation</t>
+          <t>fayda_number_required</t>
         </is>
       </c>
       <c r="B305" s="11" t="inlineStr">
@@ -19327,32 +19327,32 @@
       </c>
       <c r="C305" s="11" t="inlineStr">
         <is>
-          <t>Download for translation</t>
+          <t>Fayda number (required — it is what the record keeps)</t>
         </is>
       </c>
       <c r="D305" s="12" t="inlineStr">
         <is>
-          <t>ለትርጉም አውርድ</t>
+          <t>የፋይዳ ቁጥር (ያስፈልጋል — መዝገቡ የሚይዘው ይህ ነው)</t>
         </is>
       </c>
       <c r="E305" s="13" t="inlineStr">
         <is>
-          <t>Hiikkaaf buufadhu</t>
+          <t>Lakkoofsa Fayda (barbaachisaa — kan galmeen qabatu isa kana)</t>
         </is>
       </c>
       <c r="F305" s="12" t="inlineStr">
         <is>
-          <t>ንትርጉም ኣውርድ</t>
+          <t>ቁጽሪ ፋይዳ (የድሊ — እቲ መዝገብ ዝሕዞ እዚ እዩ)</t>
         </is>
       </c>
       <c r="G305" s="13" t="inlineStr">
         <is>
-          <t>Soo dejiso turjumaadda</t>
+          <t>Lambarka Fayda (loo baahan yahay — waa waxa diiwaanku hayo)</t>
         </is>
       </c>
       <c r="H305" s="13" t="inlineStr">
         <is>
-          <t>Pakua kwa Tafsiri</t>
+          <t>Namba ya Fayda (inahitajika — ndiyo inayowekwa kwenye rekodi)</t>
         </is>
       </c>
       <c r="I305" s="14" t="inlineStr"/>
@@ -19360,48 +19360,91 @@
     <row r="306" ht="44" customHeight="1">
       <c r="A306" s="11" t="inlineStr">
         <is>
+          <t>download_for_translation</t>
+        </is>
+      </c>
+      <c r="B306" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C306" s="11" t="inlineStr">
+        <is>
+          <t>Download for translation</t>
+        </is>
+      </c>
+      <c r="D306" s="12" t="inlineStr">
+        <is>
+          <t>ለትርጉም አውርድ</t>
+        </is>
+      </c>
+      <c r="E306" s="13" t="inlineStr">
+        <is>
+          <t>Hiikkaaf buufadhu</t>
+        </is>
+      </c>
+      <c r="F306" s="12" t="inlineStr">
+        <is>
+          <t>ንትርጉም ኣውርድ</t>
+        </is>
+      </c>
+      <c r="G306" s="13" t="inlineStr">
+        <is>
+          <t>Soo dejiso turjumaadda</t>
+        </is>
+      </c>
+      <c r="H306" s="13" t="inlineStr">
+        <is>
+          <t>Pakua kwa Tafsiri</t>
+        </is>
+      </c>
+      <c r="I306" s="14" t="inlineStr"/>
+    </row>
+    <row r="307" ht="44" customHeight="1">
+      <c r="A307" s="11" t="inlineStr">
+        <is>
           <t>nothing_to_download</t>
         </is>
       </c>
-      <c r="B306" s="11" t="inlineStr">
-        <is>
-          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
-        </is>
-      </c>
-      <c r="C306" s="11" t="inlineStr">
+      <c r="B307" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C307" s="11" t="inlineStr">
         <is>
           <t>No approved answers to download yet.</t>
         </is>
       </c>
-      <c r="D306" s="12" t="inlineStr">
+      <c r="D307" s="12" t="inlineStr">
         <is>
           <t>እስካሁን የሚወርድ የተፈቀደ መልስ የለም።</t>
         </is>
       </c>
-      <c r="E306" s="13" t="inlineStr">
+      <c r="E307" s="13" t="inlineStr">
         <is>
           <t>Hanga ammaatti deebiin mirkanaa'e buufamu hin jiru.</t>
         </is>
       </c>
-      <c r="F306" s="12" t="inlineStr">
+      <c r="F307" s="12" t="inlineStr">
         <is>
           <t>ክሳብ ሕጂ ዝወርድ ዝጸደቐ መልሲ የለን።</t>
         </is>
       </c>
-      <c r="G306" s="13" t="inlineStr">
+      <c r="G307" s="13" t="inlineStr">
         <is>
           <t>Weli ma jiraan jawaabo la ansixiyay oo la soo dejiyo.</t>
         </is>
       </c>
-      <c r="H306" s="13" t="inlineStr">
+      <c r="H307" s="13" t="inlineStr">
         <is>
           <t>Hakuna majibu yaliyoidhinishwa ya kupakua bado.</t>
         </is>
       </c>
-      <c r="I306" s="14" t="inlineStr"/>
+      <c r="I307" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I306"/>
+  <autoFilter ref="A1:I307"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/review/Olink_Bank_Assist_language_review.xlsx
+++ b/review/Olink_Bank_Assist_language_review.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1. What the assistant says'!$A$1:$I$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2. What it understands'!$A$1:$E$91</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3. Buttons customers see'!$A$1:$I$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$I$307</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$I$312</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -752,7 +752,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>378 strings in 5 languages</t>
+          <t>383 strings in 5 languages</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I307"/>
+  <dimension ref="A1:I312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -17898,7 +17898,7 @@
     <row r="272" ht="44" customHeight="1">
       <c r="A272" s="11" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>desk_teams</t>
         </is>
       </c>
       <c r="B272" s="11" t="inlineStr">
@@ -17908,32 +17908,32 @@
       </c>
       <c r="C272" s="11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Desk teams</t>
         </is>
       </c>
       <c r="D272" s="12" t="inlineStr">
         <is>
-          <t>በሂደት ላይ</t>
+          <t>የዴስክ ቡድኖች</t>
         </is>
       </c>
       <c r="E272" s="13" t="inlineStr">
         <is>
-          <t>Adeemsa irra</t>
+          <t>Gareewwan deeskii</t>
         </is>
       </c>
       <c r="F272" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መስርሕ</t>
+          <t>ጉጅለታት ዴስክ</t>
         </is>
       </c>
       <c r="G272" s="13" t="inlineStr">
         <is>
-          <t>Socda</t>
+          <t>Kooxaha miisaska</t>
         </is>
       </c>
       <c r="H272" s="13" t="inlineStr">
         <is>
-          <t>Inaendelea</t>
+          <t>Timu za madawati</t>
         </is>
       </c>
       <c r="I272" s="14" t="inlineStr"/>
@@ -17941,7 +17941,7 @@
     <row r="273" ht="44" customHeight="1">
       <c r="A273" s="11" t="inlineStr">
         <is>
-          <t>no_session_in_progress</t>
+          <t>desk_no_members</t>
         </is>
       </c>
       <c r="B273" s="11" t="inlineStr">
@@ -17951,32 +17951,32 @@
       </c>
       <c r="C273" s="11" t="inlineStr">
         <is>
-          <t>No session in progress.</t>
+          <t>Nobody has declared this desk</t>
         </is>
       </c>
       <c r="D273" s="12" t="inlineStr">
         <is>
-          <t>በሂደት ላይ ያለ ክፍለ-ጊዜ የለም።</t>
+          <t>ይህን ዴስክ ማንም አላወጀም</t>
         </is>
       </c>
       <c r="E273" s="13" t="inlineStr">
         <is>
-          <t>Sessionii adeemsa irra jiru hin jiru.</t>
+          <t>Deeskii kana namni labse hin jiru</t>
         </is>
       </c>
       <c r="F273" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መስርሕ ዘሎ ክፍለ-ግዜ የለን።</t>
+          <t>ነዚ ዴስክ ዝኣወጀ የለን</t>
         </is>
       </c>
       <c r="G273" s="13" t="inlineStr">
         <is>
-          <t>Ma jiro kalfadhi socda.</t>
+          <t>Cidna miiskan ma sheegan</t>
         </is>
       </c>
       <c r="H273" s="13" t="inlineStr">
         <is>
-          <t>Hakuna kikao kinachoendelea.</t>
+          <t>Hakuna aliyetangaza dawati hili</t>
         </is>
       </c>
       <c r="I273" s="14" t="inlineStr"/>
@@ -17984,7 +17984,7 @@
     <row r="274" ht="44" customHeight="1">
       <c r="A274" s="11" t="inlineStr">
         <is>
-          <t>wait_suffix</t>
+          <t>one_takes_everything</t>
         </is>
       </c>
       <c r="B274" s="11" t="inlineStr">
@@ -17994,32 +17994,32 @@
       </c>
       <c r="C274" s="11" t="inlineStr">
         <is>
-          <t>wait</t>
+          <t>{n} person has declared no desks, so they take every desk's calls</t>
         </is>
       </c>
       <c r="D274" s="12" t="inlineStr">
         <is>
-          <t>ጥበቃ</t>
+          <t>{n} ሰው ምንም ዴስክ አላወጀም፤ ስለዚህ የሁሉንም ዴስክ ጥሪዎች ይቀበላል</t>
         </is>
       </c>
       <c r="E274" s="13" t="inlineStr">
         <is>
-          <t>eegumsa</t>
+          <t>Namni {n} deeskii tokkollee hin labsine, kanaafuu bilbilawwan deeskii hundaa fudhata</t>
         </is>
       </c>
       <c r="F274" s="12" t="inlineStr">
         <is>
-          <t>ጽበት</t>
+          <t>{n} ሰብ ዋላ ሓደ ዴስክ ኣይኣወጀን፣ ስለዚ ጻውዒታት ኩሉ ዴስክ ይቕበል</t>
         </is>
       </c>
       <c r="G274" s="13" t="inlineStr">
         <is>
-          <t>sug</t>
+          <t>{n} qof miis ma sheegan, sidaas darteed wuxuu qaataa wicitaannada miis kasta</t>
         </is>
       </c>
       <c r="H274" s="13" t="inlineStr">
         <is>
-          <t>kusubiri</t>
+          <t>Mtu {n} hajatangaza dawati lolote, kwa hivyo anapokea simu za kila dawati</t>
         </is>
       </c>
       <c r="I274" s="14" t="inlineStr"/>
@@ -18027,7 +18027,7 @@
     <row r="275" ht="44" customHeight="1">
       <c r="A275" s="11" t="inlineStr">
         <is>
-          <t>what_session_covers</t>
+          <t>n_take_everything</t>
         </is>
       </c>
       <c r="B275" s="11" t="inlineStr">
@@ -18037,32 +18037,32 @@
       </c>
       <c r="C275" s="11" t="inlineStr">
         <is>
-          <t>What a session covers</t>
+          <t>{n} people have declared no desks, so they take every desk's calls</t>
         </is>
       </c>
       <c r="D275" s="12" t="inlineStr">
         <is>
-          <t>አንድ ክፍለ-ጊዜ ምን ይሸፍናል</t>
+          <t>{n} ሰዎች ምንም ዴስክ አላወጁም፤ ስለዚህ የሁሉንም ዴስክ ጥሪዎች ይቀበላሉ</t>
         </is>
       </c>
       <c r="E275" s="13" t="inlineStr">
         <is>
-          <t>Sessioniin maal haguuga</t>
+          <t>Namoonni {n} deeskii tokkollee hin labsine, kanaafuu bilbilawwan deeskii hundaa fudhatu</t>
         </is>
       </c>
       <c r="F275" s="12" t="inlineStr">
         <is>
-          <t>ሓደ ክፍለ-ግዜ እንታይ ይሽፍን</t>
+          <t>{n} ሰባት ዋላ ሓደ ዴስክ ኣይኣወጁን፣ ስለዚ ጻውዒታት ኩሉ ዴስክ ይቕበሉ</t>
         </is>
       </c>
       <c r="G275" s="13" t="inlineStr">
         <is>
-          <t>Waxa kalfadhigu daboolo</t>
+          <t>{n} qof miis ma sheegan, sidaas darteed waxay qaataan wicitaannada miis kasta</t>
         </is>
       </c>
       <c r="H275" s="13" t="inlineStr">
         <is>
-          <t>Kikao Kinajumuisha Nini</t>
+          <t>Watu {n} hawajatangaza dawati lolote, kwa hivyo wanapokea simu za kila dawati</t>
         </is>
       </c>
       <c r="I275" s="14" t="inlineStr"/>
@@ -18070,7 +18070,7 @@
     <row r="276" ht="44" customHeight="1">
       <c r="A276" s="11" t="inlineStr">
         <is>
-          <t>session_scope_body</t>
+          <t>desk_teams_note</t>
         </is>
       </c>
       <c r="B276" s="11" t="inlineStr">
@@ -18080,32 +18080,32 @@
       </c>
       <c r="C276" s="11" t="inlineStr">
         <is>
-          <t>Before someone is identified: general questions about products, eligibility and how to apply. Once you have checked their Fayda ID against the account and asked something only the account holder could answer: their own application, documents and disputes.</t>
+          <t>Grouped by each person's own declared expertise. An empty desk is a coverage gap worth a conversation — its calls still get answered, just not by a specialist first.</t>
         </is>
       </c>
       <c r="D276" s="12" t="inlineStr">
         <is>
-          <t>አንድ ሰው ከመለየቱ በፊት፦ ስለ ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል አጠቃላይ ጥያቄዎች። የፋይዳ መታወቂያቸውን ከሂሳቡ ጋር አመሳክረው የሂሳቡ ባለቤት ብቻ ሊመልሰው የሚችለውን ከጠየቁ በኋላ፦ የራሳቸው ማመልከቻ፣ ሰነዶችና ቅሬታዎች።</t>
+          <t>በእያንዳንዱ ሰው በራሱ ባወጀው ልምድ የተመደቡ። ባዶ ዴስክ ውይይት የሚገባው የሽፋን ክፍተት ነው — ጥሪዎቹ አሁንም ይመለሳሉ፣ ግን መጀመሪያ በባለሙያ አይደለም።</t>
         </is>
       </c>
       <c r="E276" s="13" t="inlineStr">
         <is>
-          <t>Namni tokko utuu hin beekamin dura: gaaffii waliigalaa waa'ee oomishaalee, ulaagaa fi akkaataa itti iyyatan. Erga waraqaa eenyummaa Fayda isaanii herrega waliin madaalchiftanii waan abbaan herregaa qofti deebisuu danda'u gaafattanii booda: iyyannoo, sanadoota fi komii isaanii.</t>
+          <t>Ogummaa tokkoon tokkoon namaa ofii labseen gurmaa'an. Deeskiin duwwaan hanqina haguuggii mari'achuu barbaachisu dha — bilbilawwan isaa ammas deebii argatu, garuu jalqaba ogeessaan miti.</t>
         </is>
       </c>
       <c r="F276" s="12" t="inlineStr">
         <is>
-          <t>ሓደ ሰብ ቅድሚ ምልላዩ፦ ብዛዕባ ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን ሓፈሻዊ ሕቶታት። መንነት ፋይዳኦም ምስ ሕሳብ ኣረጋጊጽኩም እቲ ወናኒ ሕሳብ ጥራይ ክምልሶ ዝኽእል ምስ ሓተትኩም፦ ናቶም ምልክታ፣ ሰነዳትን ጥርዓናትን።</t>
+          <t>በብናይ ነፍስ ወከፍ ሰብ ባዕሉ ዝኣወጆ ክእለት ዝተጠርነፉ። ባዶ ዴስክ ዝርርብ ዝግብኦ ክፍተት ሽፋን እዩ — ጻውዒታቱ ሕጂ እውን ይምለሱ፣ ግን ቅድም ብኽኢላ ኣይኮነን።</t>
         </is>
       </c>
       <c r="G276" s="13" t="inlineStr">
         <is>
-          <t>Ka hor inta aan qofka la aqoonsan: su'aalo guud oo ku saabsan alaabta, u-qalmitaanka iyo sida loo codsado. Marka aad hubiso aqoonsigooda Fayda ee xisaabta oo aad weydiiso wax uu kaliya milkiilaha xisaabtu ka jawaabi karo: codsigooda, dukumiintiyada iyo cabashooyinka.</t>
+          <t>Waxay ku kala qaybsan yihiin khibradda uu qof kastaa isagu sheegtay. Miis maran waa daldaloolo daboolid oo u qalanta wada hadal — wicitaannadiisa weli waa laga jawaabaa, laakiin marka hore khabiir maaha.</t>
         </is>
       </c>
       <c r="H276" s="13" t="inlineStr">
         <is>
-          <t>Kabla mtu hajatambuliwa: maswali ya jumla kuhusu bidhaa, sifa za kustahiki na jinsi ya kuomba. Baada ya kukagua Kitambulisho chao cha Fayda dhidi ya akaunti na kuuliza kitu ambacho mmiliki wa akaunti pekee angeweza kujibu: maombi yao wenyewe, nyaraka na migogoro.</t>
+          <t>Wamepangwa kwa utaalamu ambao kila mtu amejitangazia. Dawati tupu ni pengo la uwezo linalostahili mazungumzo — simu zake bado zinajibiwa, ila si na mtaalamu kwanza.</t>
         </is>
       </c>
       <c r="I276" s="14" t="inlineStr"/>
@@ -18113,7 +18113,7 @@
     <row r="277" ht="44" customHeight="1">
       <c r="A277" s="11" t="inlineStr">
         <is>
-          <t>never_money_movement</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="B277" s="11" t="inlineStr">
@@ -18123,32 +18123,32 @@
       </c>
       <c r="C277" s="11" t="inlineStr">
         <is>
-          <t>Never, at any point and for anyone: deposits, withdrawals or transfers. Those do not happen on a call.</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="D277" s="12" t="inlineStr">
         <is>
-          <t>በፍጹም፣ በማንኛውም ጊዜና ለማንም፦ ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም። እነዚያ በጥሪ ላይ አይፈጸሙም።</t>
+          <t>በሂደት ላይ</t>
         </is>
       </c>
       <c r="E277" s="13" t="inlineStr">
         <is>
-          <t>Gonkumaa, yeroo kamiyyuu fi eenyuufiyyuu: kuusaa, baasii yookiin dabarsa hin jiru. Isaan sun bilbila irratti hin raawwataman.</t>
+          <t>Adeemsa irra</t>
         </is>
       </c>
       <c r="F277" s="12" t="inlineStr">
         <is>
-          <t>ፈጺሙ፣ ኣብ ዝኾነ እዋንን ንዝኾነ ሰብን፦ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን። እዚኣቶም ኣብ ጻውዒት ኣይፍጸሙን።</t>
+          <t>ኣብ መስርሕ</t>
         </is>
       </c>
       <c r="G277" s="13" t="inlineStr">
         <is>
-          <t>Weligaa, wakhti kasta iyo qof kasta: dhigasho, qaadis ama wareejin ma jirto. Kuwaas wicitaan laguma sameeyo.</t>
+          <t>Socda</t>
         </is>
       </c>
       <c r="H277" s="13" t="inlineStr">
         <is>
-          <t>Kamwe, wakati wowote na kwa yeyote: amana, uondoaji au uhamishaji. Hizo hazifanyiki kwenye simu.</t>
+          <t>Inaendelea</t>
         </is>
       </c>
       <c r="I277" s="14" t="inlineStr"/>
@@ -18156,7 +18156,7 @@
     <row r="278" ht="44" customHeight="1">
       <c r="A278" s="11" t="inlineStr">
         <is>
-          <t>open_escalation_queue</t>
+          <t>no_session_in_progress</t>
         </is>
       </c>
       <c r="B278" s="11" t="inlineStr">
@@ -18166,32 +18166,32 @@
       </c>
       <c r="C278" s="11" t="inlineStr">
         <is>
-          <t>Open the escalation queue</t>
+          <t>No session in progress.</t>
         </is>
       </c>
       <c r="D278" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ወረፋውን ክፈት</t>
+          <t>በሂደት ላይ ያለ ክፍለ-ጊዜ የለም።</t>
         </is>
       </c>
       <c r="E278" s="13" t="inlineStr">
         <is>
-          <t>Sararaa dabarsaa banaa</t>
+          <t>Sessionii adeemsa irra jiru hin jiru.</t>
         </is>
       </c>
       <c r="F278" s="12" t="inlineStr">
         <is>
-          <t>ሪጋ ምትሕልላፍ ክፈት</t>
+          <t>ኣብ መስርሕ ዘሎ ክፍለ-ግዜ የለን።</t>
         </is>
       </c>
       <c r="G278" s="13" t="inlineStr">
         <is>
-          <t>Fur safka gudbinta</t>
+          <t>Ma jiro kalfadhi socda.</t>
         </is>
       </c>
       <c r="H278" s="13" t="inlineStr">
         <is>
-          <t>Fungua Foleni ya Masuala Yaliyoelekezwa</t>
+          <t>Hakuna kikao kinachoendelea.</t>
         </is>
       </c>
       <c r="I278" s="14" t="inlineStr"/>
@@ -18199,7 +18199,7 @@
     <row r="279" ht="44" customHeight="1">
       <c r="A279" s="11" t="inlineStr">
         <is>
-          <t>open_live_queue</t>
+          <t>wait_suffix</t>
         </is>
       </c>
       <c r="B279" s="11" t="inlineStr">
@@ -18209,32 +18209,32 @@
       </c>
       <c r="C279" s="11" t="inlineStr">
         <is>
-          <t>Open the live call queue</t>
+          <t>wait</t>
         </is>
       </c>
       <c r="D279" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታ የጥሪ ወረፋውን ክፈት</t>
+          <t>ጥበቃ</t>
         </is>
       </c>
       <c r="E279" s="13" t="inlineStr">
         <is>
-          <t>Sarara bilbilaa kallattii banaa</t>
+          <t>eegumsa</t>
         </is>
       </c>
       <c r="F279" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታዊ ናይ ጻውዒት ሰልፊ ክፈት</t>
+          <t>ጽበት</t>
         </is>
       </c>
       <c r="G279" s="13" t="inlineStr">
         <is>
-          <t>Fur safka wicitaanka tooska ah</t>
+          <t>sug</t>
         </is>
       </c>
       <c r="H279" s="13" t="inlineStr">
         <is>
-          <t>Fungua foleni ya simu za moja kwa moja</t>
+          <t>kusubiri</t>
         </is>
       </c>
       <c r="I279" s="14" t="inlineStr"/>
@@ -18242,7 +18242,7 @@
     <row r="280" ht="44" customHeight="1">
       <c r="A280" s="11" t="inlineStr">
         <is>
-          <t>live_waiting_one</t>
+          <t>what_session_covers</t>
         </is>
       </c>
       <c r="B280" s="11" t="inlineStr">
@@ -18252,32 +18252,32 @@
       </c>
       <c r="C280" s="11" t="inlineStr">
         <is>
-          <t>{n} customer waiting for a live call</t>
+          <t>What a session covers</t>
         </is>
       </c>
       <c r="D280" s="12" t="inlineStr">
         <is>
-          <t>{n} ደንበኛ ቀጥታ ጥሪ በመጠበቅ ላይ ነው</t>
+          <t>አንድ ክፍለ-ጊዜ ምን ይሸፍናል</t>
         </is>
       </c>
       <c r="E280" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan {n} bilbila kallattii eegaa jira</t>
+          <t>Sessioniin maal haguuga</t>
         </is>
       </c>
       <c r="F280" s="12" t="inlineStr">
         <is>
-          <t>{n} ዓሚል ቀጥታዊ ጻውዒት ይጽበ ኣሎ</t>
+          <t>ሓደ ክፍለ-ግዜ እንታይ ይሽፍን</t>
         </is>
       </c>
       <c r="G280" s="13" t="inlineStr">
         <is>
-          <t>{n} macmiil ayaa sugaya wicitaan toos ah</t>
+          <t>Waxa kalfadhigu daboolo</t>
         </is>
       </c>
       <c r="H280" s="13" t="inlineStr">
         <is>
-          <t>Mteja {n} anasubiri simu ya moja kwa moja</t>
+          <t>Kikao Kinajumuisha Nini</t>
         </is>
       </c>
       <c r="I280" s="14" t="inlineStr"/>
@@ -18285,7 +18285,7 @@
     <row r="281" ht="44" customHeight="1">
       <c r="A281" s="11" t="inlineStr">
         <is>
-          <t>live_waiting_many</t>
+          <t>session_scope_body</t>
         </is>
       </c>
       <c r="B281" s="11" t="inlineStr">
@@ -18295,32 +18295,32 @@
       </c>
       <c r="C281" s="11" t="inlineStr">
         <is>
-          <t>{n} customers waiting for a live call</t>
+          <t>Before someone is identified: general questions about products, eligibility and how to apply. Once you have checked their Fayda ID against the account and asked something only the account holder could answer: their own application, documents and disputes.</t>
         </is>
       </c>
       <c r="D281" s="12" t="inlineStr">
         <is>
-          <t>{n} ደንበኞች ቀጥታ ጥሪ በመጠበቅ ላይ ናቸው</t>
+          <t>አንድ ሰው ከመለየቱ በፊት፦ ስለ ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል አጠቃላይ ጥያቄዎች። የፋይዳ መታወቂያቸውን ከሂሳቡ ጋር አመሳክረው የሂሳቡ ባለቤት ብቻ ሊመልሰው የሚችለውን ከጠየቁ በኋላ፦ የራሳቸው ማመልከቻ፣ ሰነዶችና ቅሬታዎች።</t>
         </is>
       </c>
       <c r="E281" s="13" t="inlineStr">
         <is>
-          <t>Maamiltoonni {n} bilbila kallattii eegaa jiru</t>
+          <t>Namni tokko utuu hin beekamin dura: gaaffii waliigalaa waa'ee oomishaalee, ulaagaa fi akkaataa itti iyyatan. Erga waraqaa eenyummaa Fayda isaanii herrega waliin madaalchiftanii waan abbaan herregaa qofti deebisuu danda'u gaafattanii booda: iyyannoo, sanadoota fi komii isaanii.</t>
         </is>
       </c>
       <c r="F281" s="12" t="inlineStr">
         <is>
-          <t>{n} ዓማዊል ቀጥታዊ ጻውዒት ይጽበዩ ኣለዉ</t>
+          <t>ሓደ ሰብ ቅድሚ ምልላዩ፦ ብዛዕባ ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን ሓፈሻዊ ሕቶታት። መንነት ፋይዳኦም ምስ ሕሳብ ኣረጋጊጽኩም እቲ ወናኒ ሕሳብ ጥራይ ክምልሶ ዝኽእል ምስ ሓተትኩም፦ ናቶም ምልክታ፣ ሰነዳትን ጥርዓናትን።</t>
         </is>
       </c>
       <c r="G281" s="13" t="inlineStr">
         <is>
-          <t>{n} macaamiil ayaa sugaya wicitaan toos ah</t>
+          <t>Ka hor inta aan qofka la aqoonsan: su'aalo guud oo ku saabsan alaabta, u-qalmitaanka iyo sida loo codsado. Marka aad hubiso aqoonsigooda Fayda ee xisaabta oo aad weydiiso wax uu kaliya milkiilaha xisaabtu ka jawaabi karo: codsigooda, dukumiintiyada iyo cabashooyinka.</t>
         </is>
       </c>
       <c r="H281" s="13" t="inlineStr">
         <is>
-          <t>Wateja {n} wanasubiri simu ya moja kwa moja</t>
+          <t>Kabla mtu hajatambuliwa: maswali ya jumla kuhusu bidhaa, sifa za kustahiki na jinsi ya kuomba. Baada ya kukagua Kitambulisho chao cha Fayda dhidi ya akaunti na kuuliza kitu ambacho mmiliki wa akaunti pekee angeweza kujibu: maombi yao wenyewe, nyaraka na migogoro.</t>
         </is>
       </c>
       <c r="I281" s="14" t="inlineStr"/>
@@ -18328,7 +18328,7 @@
     <row r="282" ht="44" customHeight="1">
       <c r="A282" s="11" t="inlineStr">
         <is>
-          <t>switch_dark_light</t>
+          <t>never_money_movement</t>
         </is>
       </c>
       <c r="B282" s="11" t="inlineStr">
@@ -18338,32 +18338,32 @@
       </c>
       <c r="C282" s="11" t="inlineStr">
         <is>
-          <t>Switch between dark and light</t>
+          <t>Never, at any point and for anyone: deposits, withdrawals or transfers. Those do not happen on a call.</t>
         </is>
       </c>
       <c r="D282" s="12" t="inlineStr">
         <is>
-          <t>በጨለማና በብርሃን መካከል ቀይር</t>
+          <t>በፍጹም፣ በማንኛውም ጊዜና ለማንም፦ ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም። እነዚያ በጥሪ ላይ አይፈጸሙም።</t>
         </is>
       </c>
       <c r="E282" s="13" t="inlineStr">
         <is>
-          <t>Dukkanaa fi ifa gidduu jijjiiri</t>
+          <t>Gonkumaa, yeroo kamiyyuu fi eenyuufiyyuu: kuusaa, baasii yookiin dabarsa hin jiru. Isaan sun bilbila irratti hin raawwataman.</t>
         </is>
       </c>
       <c r="F282" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መንጎ ጸላምን ብርሃንን ቀይር</t>
+          <t>ፈጺሙ፣ ኣብ ዝኾነ እዋንን ንዝኾነ ሰብን፦ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን። እዚኣቶም ኣብ ጻውዒት ኣይፍጸሙን።</t>
         </is>
       </c>
       <c r="G282" s="13" t="inlineStr">
         <is>
-          <t>U beddel mugdiga iyo iftiinka</t>
+          <t>Weligaa, wakhti kasta iyo qof kasta: dhigasho, qaadis ama wareejin ma jirto. Kuwaas wicitaan laguma sameeyo.</t>
         </is>
       </c>
       <c r="H282" s="13" t="inlineStr">
         <is>
-          <t>Badilisha Kati ya Giza na Mwanga</t>
+          <t>Kamwe, wakati wowote na kwa yeyote: amana, uondoaji au uhamishaji. Hizo hazifanyiki kwenye simu.</t>
         </is>
       </c>
       <c r="I282" s="14" t="inlineStr"/>
@@ -18371,7 +18371,7 @@
     <row r="283" ht="44" customHeight="1">
       <c r="A283" s="11" t="inlineStr">
         <is>
-          <t>live_session</t>
+          <t>open_escalation_queue</t>
         </is>
       </c>
       <c r="B283" s="11" t="inlineStr">
@@ -18381,32 +18381,32 @@
       </c>
       <c r="C283" s="11" t="inlineStr">
         <is>
-          <t>Live session</t>
+          <t>Open the escalation queue</t>
         </is>
       </c>
       <c r="D283" s="12" t="inlineStr">
         <is>
-          <t>የቀጥታ ክፍለ-ጊዜ</t>
+          <t>የማሸጋገሪያ ወረፋውን ክፈት</t>
         </is>
       </c>
       <c r="E283" s="13" t="inlineStr">
         <is>
-          <t>Session kallattii</t>
+          <t>Sararaa dabarsaa banaa</t>
         </is>
       </c>
       <c r="F283" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታ ክፍለ-ግዜ</t>
+          <t>ሪጋ ምትሕልላፍ ክፈት</t>
         </is>
       </c>
       <c r="G283" s="13" t="inlineStr">
         <is>
-          <t>Kalfadhi toos ah</t>
+          <t>Fur safka gudbinta</t>
         </is>
       </c>
       <c r="H283" s="13" t="inlineStr">
         <is>
-          <t>Kikao cha Moja kwa Moja</t>
+          <t>Fungua Foleni ya Masuala Yaliyoelekezwa</t>
         </is>
       </c>
       <c r="I283" s="14" t="inlineStr"/>
@@ -18414,7 +18414,7 @@
     <row r="284" ht="44" customHeight="1">
       <c r="A284" s="11" t="inlineStr">
         <is>
-          <t>customer_left_call</t>
+          <t>open_live_queue</t>
         </is>
       </c>
       <c r="B284" s="11" t="inlineStr">
@@ -18424,32 +18424,32 @@
       </c>
       <c r="C284" s="11" t="inlineStr">
         <is>
-          <t>The customer has left the call.</t>
+          <t>Open the live call queue</t>
         </is>
       </c>
       <c r="D284" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛው ጥሪውን ለቅቋል።</t>
+          <t>ቀጥታ የጥሪ ወረፋውን ክፈት</t>
         </is>
       </c>
       <c r="E284" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan bilbila irraa ba'eera.</t>
+          <t>Sarara bilbilaa kallattii banaa</t>
         </is>
       </c>
       <c r="F284" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዓሚል ካብቲ ጻውዒት ወጺኡ።</t>
+          <t>ቀጥታዊ ናይ ጻውዒት ሰልፊ ክፈት</t>
         </is>
       </c>
       <c r="G284" s="13" t="inlineStr">
         <is>
-          <t>Macmiilku wicitaanka wuu ka baxay.</t>
+          <t>Fur safka wicitaanka tooska ah</t>
         </is>
       </c>
       <c r="H284" s="13" t="inlineStr">
         <is>
-          <t>Mteja ameondoka kwenye simu.</t>
+          <t>Fungua foleni ya simu za moja kwa moja</t>
         </is>
       </c>
       <c r="I284" s="14" t="inlineStr"/>
@@ -18457,7 +18457,7 @@
     <row r="285" ht="44" customHeight="1">
       <c r="A285" s="11" t="inlineStr">
         <is>
-          <t>waiting_for_customer</t>
+          <t>live_waiting_one</t>
         </is>
       </c>
       <c r="B285" s="11" t="inlineStr">
@@ -18467,32 +18467,32 @@
       </c>
       <c r="C285" s="11" t="inlineStr">
         <is>
-          <t>Waiting for the customer…</t>
+          <t>{n} customer waiting for a live call</t>
         </is>
       </c>
       <c r="D285" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛውን በመጠበቅ ላይ…</t>
+          <t>{n} ደንበኛ ቀጥታ ጥሪ በመጠበቅ ላይ ነው</t>
         </is>
       </c>
       <c r="E285" s="13" t="inlineStr">
         <is>
-          <t>Maamilaa eegaa jirra…</t>
+          <t>Maamilaan {n} bilbila kallattii eegaa jira</t>
         </is>
       </c>
       <c r="F285" s="12" t="inlineStr">
         <is>
-          <t>ነቲ ዓሚል ንጽበ ኣለና…</t>
+          <t>{n} ዓሚል ቀጥታዊ ጻውዒት ይጽበ ኣሎ</t>
         </is>
       </c>
       <c r="G285" s="13" t="inlineStr">
         <is>
-          <t>Macmiilka la sugayo…</t>
+          <t>{n} macmiil ayaa sugaya wicitaan toos ah</t>
         </is>
       </c>
       <c r="H285" s="13" t="inlineStr">
         <is>
-          <t>Inasubiri Mteja…</t>
+          <t>Mteja {n} anasubiri simu ya moja kwa moja</t>
         </is>
       </c>
       <c r="I285" s="14" t="inlineStr"/>
@@ -18500,7 +18500,7 @@
     <row r="286" ht="44" customHeight="1">
       <c r="A286" s="11" t="inlineStr">
         <is>
-          <t>mic_blocked</t>
+          <t>live_waiting_many</t>
         </is>
       </c>
       <c r="B286" s="11" t="inlineStr">
@@ -18510,32 +18510,32 @@
       </c>
       <c r="C286" s="11" t="inlineStr">
         <is>
-          <t>Microphone access is blocked. Allow it in your browser and take the session again.</t>
+          <t>{n} customers waiting for a live call</t>
         </is>
       </c>
       <c r="D286" s="12" t="inlineStr">
         <is>
-          <t>የማይክሮፎን መዳረሻ ታግዷል። በአሳሽዎ ውስጥ ይፍቀዱና ክፍለ-ጊዜውን እንደገና ይውሰዱ።</t>
+          <t>{n} ደንበኞች ቀጥታ ጥሪ በመጠበቅ ላይ ናቸው</t>
         </is>
       </c>
       <c r="E286" s="13" t="inlineStr">
         <is>
-          <t>Maayikiroofoonii dhorkameera. Biraawzarii keessan keessatti hayyamaatii session irra deebi'aa fudhadhaa.</t>
+          <t>Maamiltoonni {n} bilbila kallattii eegaa jiru</t>
         </is>
       </c>
       <c r="F286" s="12" t="inlineStr">
         <is>
-          <t>መእተዊ ማይክሮፎን ተዓጊቱ። ኣብ መርበብ መንሸራተቲኹም ፍቐዱ እሞ ነቲ ክፍለ-ግዜ ደጊምኩም ውሰዱ።</t>
+          <t>{n} ዓማዊል ቀጥታዊ ጻውዒት ይጽበዩ ኣለዉ</t>
         </is>
       </c>
       <c r="G286" s="13" t="inlineStr">
         <is>
-          <t>Makarafoonka waa la xannibay. Browser-kaaga ka ogolow oo kalfadhiga mar kale qaado.</t>
+          <t>{n} macaamiil ayaa sugaya wicitaan toos ah</t>
         </is>
       </c>
       <c r="H286" s="13" t="inlineStr">
         <is>
-          <t>Ufikiaji wa maikrofoni umezuiwa. Ruhusu kwenye kivinjari chako na uanze kikao tena.</t>
+          <t>Wateja {n} wanasubiri simu ya moja kwa moja</t>
         </is>
       </c>
       <c r="I286" s="14" t="inlineStr"/>
@@ -18543,7 +18543,7 @@
     <row r="287" ht="44" customHeight="1">
       <c r="A287" s="11" t="inlineStr">
         <is>
-          <t>unknown_error</t>
+          <t>switch_dark_light</t>
         </is>
       </c>
       <c r="B287" s="11" t="inlineStr">
@@ -18553,32 +18553,32 @@
       </c>
       <c r="C287" s="11" t="inlineStr">
         <is>
-          <t>unknown error</t>
+          <t>Switch between dark and light</t>
         </is>
       </c>
       <c r="D287" s="12" t="inlineStr">
         <is>
-          <t>ያልታወቀ ስህተት</t>
+          <t>በጨለማና በብርሃን መካከል ቀይር</t>
         </is>
       </c>
       <c r="E287" s="13" t="inlineStr">
         <is>
-          <t>dogoggora hin beekamne</t>
+          <t>Dukkanaa fi ifa gidduu jijjiiri</t>
         </is>
       </c>
       <c r="F287" s="12" t="inlineStr">
         <is>
-          <t>ዘይተፈልጠ ጌጋ</t>
+          <t>ኣብ መንጎ ጸላምን ብርሃንን ቀይር</t>
         </is>
       </c>
       <c r="G287" s="13" t="inlineStr">
         <is>
-          <t>khalad aan la garanayn</t>
+          <t>U beddel mugdiga iyo iftiinka</t>
         </is>
       </c>
       <c r="H287" s="13" t="inlineStr">
         <is>
-          <t>hitilafu isiyojulikana</t>
+          <t>Badilisha Kati ya Giza na Mwanga</t>
         </is>
       </c>
       <c r="I287" s="14" t="inlineStr"/>
@@ -18586,7 +18586,7 @@
     <row r="288" ht="44" customHeight="1">
       <c r="A288" s="11" t="inlineStr">
         <is>
-          <t>no_messages_yet</t>
+          <t>live_session</t>
         </is>
       </c>
       <c r="B288" s="11" t="inlineStr">
@@ -18596,32 +18596,32 @@
       </c>
       <c r="C288" s="11" t="inlineStr">
         <is>
-          <t>No messages yet.</t>
+          <t>Live session</t>
         </is>
       </c>
       <c r="D288" s="12" t="inlineStr">
         <is>
-          <t>እስካሁን መልእክት የለም።</t>
+          <t>የቀጥታ ክፍለ-ጊዜ</t>
         </is>
       </c>
       <c r="E288" s="13" t="inlineStr">
         <is>
-          <t>Ammaaf ergaan hin jiru.</t>
+          <t>Session kallattii</t>
         </is>
       </c>
       <c r="F288" s="12" t="inlineStr">
         <is>
-          <t>ክሳብ ሕጂ መልእኽቲ የለን።</t>
+          <t>ቀጥታ ክፍለ-ግዜ</t>
         </is>
       </c>
       <c r="G288" s="13" t="inlineStr">
         <is>
-          <t>Weli fariimo ma jiraan.</t>
+          <t>Kalfadhi toos ah</t>
         </is>
       </c>
       <c r="H288" s="13" t="inlineStr">
         <is>
-          <t>Hakuna ujumbe bado.</t>
+          <t>Kikao cha Moja kwa Moja</t>
         </is>
       </c>
       <c r="I288" s="14" t="inlineStr"/>
@@ -18629,7 +18629,7 @@
     <row r="289" ht="44" customHeight="1">
       <c r="A289" s="11" t="inlineStr">
         <is>
-          <t>you_label</t>
+          <t>customer_left_call</t>
         </is>
       </c>
       <c r="B289" s="11" t="inlineStr">
@@ -18639,32 +18639,32 @@
       </c>
       <c r="C289" s="11" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>The customer has left the call.</t>
         </is>
       </c>
       <c r="D289" s="12" t="inlineStr">
         <is>
-          <t>እርስዎ</t>
+          <t>ደንበኛው ጥሪውን ለቅቋል።</t>
         </is>
       </c>
       <c r="E289" s="13" t="inlineStr">
         <is>
-          <t>Isin</t>
+          <t>Maamilaan bilbila irraa ba'eera.</t>
         </is>
       </c>
       <c r="F289" s="12" t="inlineStr">
         <is>
-          <t>ንስኹም</t>
+          <t>እቲ ዓሚል ካብቲ ጻውዒት ወጺኡ።</t>
         </is>
       </c>
       <c r="G289" s="13" t="inlineStr">
         <is>
-          <t>Adiga</t>
+          <t>Macmiilku wicitaanka wuu ka baxay.</t>
         </is>
       </c>
       <c r="H289" s="13" t="inlineStr">
         <is>
-          <t>Wewe</t>
+          <t>Mteja ameondoka kwenye simu.</t>
         </is>
       </c>
       <c r="I289" s="14" t="inlineStr"/>
@@ -18672,7 +18672,7 @@
     <row r="290" ht="44" customHeight="1">
       <c r="A290" s="11" t="inlineStr">
         <is>
-          <t>assistant_label</t>
+          <t>waiting_for_customer</t>
         </is>
       </c>
       <c r="B290" s="11" t="inlineStr">
@@ -18682,32 +18682,32 @@
       </c>
       <c r="C290" s="11" t="inlineStr">
         <is>
-          <t>Assistant</t>
+          <t>Waiting for the customer…</t>
         </is>
       </c>
       <c r="D290" s="12" t="inlineStr">
         <is>
-          <t>ረዳት</t>
+          <t>ደንበኛውን በመጠበቅ ላይ…</t>
         </is>
       </c>
       <c r="E290" s="13" t="inlineStr">
         <is>
-          <t>Gargaaraa</t>
+          <t>Maamilaa eegaa jirra…</t>
         </is>
       </c>
       <c r="F290" s="12" t="inlineStr">
         <is>
-          <t>ሓጋዚ</t>
+          <t>ነቲ ዓሚል ንጽበ ኣለና…</t>
         </is>
       </c>
       <c r="G290" s="13" t="inlineStr">
         <is>
-          <t>Kaaliye</t>
+          <t>Macmiilka la sugayo…</t>
         </is>
       </c>
       <c r="H290" s="13" t="inlineStr">
         <is>
-          <t>Msaidizi</t>
+          <t>Inasubiri Mteja…</t>
         </is>
       </c>
       <c r="I290" s="14" t="inlineStr"/>
@@ -18715,7 +18715,7 @@
     <row r="291" ht="44" customHeight="1">
       <c r="A291" s="11" t="inlineStr">
         <is>
-          <t>conversation_unavailable</t>
+          <t>mic_blocked</t>
         </is>
       </c>
       <c r="B291" s="11" t="inlineStr">
@@ -18725,32 +18725,32 @@
       </c>
       <c r="C291" s="11" t="inlineStr">
         <is>
-          <t>Conversation unavailable.</t>
+          <t>Microphone access is blocked. Allow it in your browser and take the session again.</t>
         </is>
       </c>
       <c r="D291" s="12" t="inlineStr">
         <is>
-          <t>ውይይቱ አይገኝም።</t>
+          <t>የማይክሮፎን መዳረሻ ታግዷል። በአሳሽዎ ውስጥ ይፍቀዱና ክፍለ-ጊዜውን እንደገና ይውሰዱ።</t>
         </is>
       </c>
       <c r="E291" s="13" t="inlineStr">
         <is>
-          <t>Mariin hin argamu.</t>
+          <t>Maayikiroofoonii dhorkameera. Biraawzarii keessan keessatti hayyamaatii session irra deebi'aa fudhadhaa.</t>
         </is>
       </c>
       <c r="F291" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዝርርብ ኣይርከብን።</t>
+          <t>መእተዊ ማይክሮፎን ተዓጊቱ። ኣብ መርበብ መንሸራተቲኹም ፍቐዱ እሞ ነቲ ክፍለ-ግዜ ደጊምኩም ውሰዱ።</t>
         </is>
       </c>
       <c r="G291" s="13" t="inlineStr">
         <is>
-          <t>Wadahadalka lama heli karo.</t>
+          <t>Makarafoonka waa la xannibay. Browser-kaaga ka ogolow oo kalfadhiga mar kale qaado.</t>
         </is>
       </c>
       <c r="H291" s="13" t="inlineStr">
         <is>
-          <t>Mazungumzo hayapatikani.</t>
+          <t>Ufikiaji wa maikrofoni umezuiwa. Ruhusu kwenye kivinjari chako na uanze kikao tena.</t>
         </is>
       </c>
       <c r="I291" s="14" t="inlineStr"/>
@@ -18758,7 +18758,7 @@
     <row r="292" ht="44" customHeight="1">
       <c r="A292" s="11" t="inlineStr">
         <is>
-          <t>unmute</t>
+          <t>unknown_error</t>
         </is>
       </c>
       <c r="B292" s="11" t="inlineStr">
@@ -18768,32 +18768,32 @@
       </c>
       <c r="C292" s="11" t="inlineStr">
         <is>
-          <t>Unmute</t>
+          <t>unknown error</t>
         </is>
       </c>
       <c r="D292" s="12" t="inlineStr">
         <is>
-          <t>ድምፅ አብራ</t>
+          <t>ያልታወቀ ስህተት</t>
         </is>
       </c>
       <c r="E292" s="13" t="inlineStr">
         <is>
-          <t>Sagalee banaa</t>
+          <t>dogoggora hin beekamne</t>
         </is>
       </c>
       <c r="F292" s="12" t="inlineStr">
         <is>
-          <t>ድምጺ ኣብርህ</t>
+          <t>ዘይተፈልጠ ጌጋ</t>
         </is>
       </c>
       <c r="G292" s="13" t="inlineStr">
         <is>
-          <t>Codka fur</t>
+          <t>khalad aan la garanayn</t>
         </is>
       </c>
       <c r="H292" s="13" t="inlineStr">
         <is>
-          <t>Rudisha Sauti</t>
+          <t>hitilafu isiyojulikana</t>
         </is>
       </c>
       <c r="I292" s="14" t="inlineStr"/>
@@ -18801,7 +18801,7 @@
     <row r="293" ht="44" customHeight="1">
       <c r="A293" s="11" t="inlineStr">
         <is>
-          <t>session_summary_prompt</t>
+          <t>no_messages_yet</t>
         </is>
       </c>
       <c r="B293" s="11" t="inlineStr">
@@ -18811,32 +18811,32 @@
       </c>
       <c r="C293" s="11" t="inlineStr">
         <is>
-          <t>What did this session cover? (optional)</t>
+          <t>No messages yet.</t>
         </is>
       </c>
       <c r="D293" s="12" t="inlineStr">
         <is>
-          <t>ይህ ክፍለ-ጊዜ ምን ሸፈነ? (አማራጭ)</t>
+          <t>እስካሁን መልእክት የለም።</t>
         </is>
       </c>
       <c r="E293" s="13" t="inlineStr">
         <is>
-          <t>Sessioniin kun maal haguuge? (filannoo)</t>
+          <t>Ammaaf ergaan hin jiru.</t>
         </is>
       </c>
       <c r="F293" s="12" t="inlineStr">
         <is>
-          <t>እዚ ክፍለ-ግዜ እንታይ ሸፈነ? (ኣማራጺ)</t>
+          <t>ክሳብ ሕጂ መልእኽቲ የለን።</t>
         </is>
       </c>
       <c r="G293" s="13" t="inlineStr">
         <is>
-          <t>Kalfadhigan muxuu daboolay? (ikhtiyaari)</t>
+          <t>Weli fariimo ma jiraan.</t>
         </is>
       </c>
       <c r="H293" s="13" t="inlineStr">
         <is>
-          <t>Kikao hiki kilihusu nini? (si lazima)</t>
+          <t>Hakuna ujumbe bado.</t>
         </is>
       </c>
       <c r="I293" s="14" t="inlineStr"/>
@@ -18844,7 +18844,7 @@
     <row r="294" ht="44" customHeight="1">
       <c r="A294" s="11" t="inlineStr">
         <is>
-          <t>customer_ended_call</t>
+          <t>you_label</t>
         </is>
       </c>
       <c r="B294" s="11" t="inlineStr">
@@ -18854,32 +18854,32 @@
       </c>
       <c r="C294" s="11" t="inlineStr">
         <is>
-          <t>The customer ended the call</t>
+          <t>You</t>
         </is>
       </c>
       <c r="D294" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛው ጥሪውን አቋረጠ</t>
+          <t>እርስዎ</t>
         </is>
       </c>
       <c r="E294" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan bilbila xumure</t>
+          <t>Isin</t>
         </is>
       </c>
       <c r="F294" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዓሚል ነቲ ጻውዒት ወዲኡዎ</t>
+          <t>ንስኹም</t>
         </is>
       </c>
       <c r="G294" s="13" t="inlineStr">
         <is>
-          <t>Macmiilku wicitaanka wuu joojiyay</t>
+          <t>Adiga</t>
         </is>
       </c>
       <c r="H294" s="13" t="inlineStr">
         <is>
-          <t>Mteja alimaliza simu</t>
+          <t>Wewe</t>
         </is>
       </c>
       <c r="I294" s="14" t="inlineStr"/>
@@ -18887,7 +18887,7 @@
     <row r="295" ht="44" customHeight="1">
       <c r="A295" s="11" t="inlineStr">
         <is>
-          <t>verified_scope</t>
+          <t>assistant_label</t>
         </is>
       </c>
       <c r="B295" s="11" t="inlineStr">
@@ -18897,32 +18897,32 @@
       </c>
       <c r="C295" s="11" t="inlineStr">
         <is>
-          <t>You can now discuss their own records, take documents and file a dispute. Never a deposit, withdrawal or transfer.</t>
+          <t>Assistant</t>
         </is>
       </c>
       <c r="D295" s="12" t="inlineStr">
         <is>
-          <t>አሁን ስለ ራሳቸው መዝገቦች መወያየት፣ ሰነዶች መቀበልና ቅሬታ ማስመዝገብ ይችላሉ። በፍጹም ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም።</t>
+          <t>ረዳት</t>
         </is>
       </c>
       <c r="E295" s="13" t="inlineStr">
         <is>
-          <t>Amma waa'ee galmee isaanii mari'achuu, sanadoota fudhachuu fi komii galmeessuu dandeessu. Gonkumaa kuusaa, baasii yookiin dabarsa hin jiru.</t>
+          <t>Gargaaraa</t>
         </is>
       </c>
       <c r="F295" s="12" t="inlineStr">
         <is>
-          <t>ሕጂ ብዛዕባ ናቶም መዝገባት ክትዘራረቡ፣ ሰነዳት ክትቅበሉን ጥርዓን ከተመዝግቡን ትኽእሉ። ፈጺሙ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን።</t>
+          <t>ሓጋዚ</t>
         </is>
       </c>
       <c r="G295" s="13" t="inlineStr">
         <is>
-          <t>Hadda waad kala hadli kartaa diiwaankooda, dukumiinti qaadan iyo cabasho diiwaangelin. Weligaa dhigasho, qaadis ama wareejin ma jirto.</t>
+          <t>Kaaliye</t>
         </is>
       </c>
       <c r="H295" s="13" t="inlineStr">
         <is>
-          <t>Sasa unaweza kuzungumzia rekodi zao wenyewe, kuchukua nyaraka na kuwasilisha mgogoro. Kamwe amana, uondoaji au uhamishaji.</t>
+          <t>Msaidizi</t>
         </is>
       </c>
       <c r="I295" s="14" t="inlineStr"/>
@@ -18930,7 +18930,7 @@
     <row r="296" ht="44" customHeight="1">
       <c r="A296" s="11" t="inlineStr">
         <is>
-          <t>establish_who_they_are</t>
+          <t>conversation_unavailable</t>
         </is>
       </c>
       <c r="B296" s="11" t="inlineStr">
@@ -18940,32 +18940,32 @@
       </c>
       <c r="C296" s="11" t="inlineStr">
         <is>
-          <t>Establish who they are — either one</t>
+          <t>Conversation unavailable.</t>
         </is>
       </c>
       <c r="D296" s="12" t="inlineStr">
         <is>
-          <t>ማንነታቸውን ያረጋግጡ — አንዱ ይበቃል</t>
+          <t>ውይይቱ አይገኝም።</t>
         </is>
       </c>
       <c r="E296" s="13" t="inlineStr">
         <is>
-          <t>Eenyummaa isaanii mirkaneessaa — tokko ni ga'a</t>
+          <t>Mariin hin argamu.</t>
         </is>
       </c>
       <c r="F296" s="12" t="inlineStr">
         <is>
-          <t>መንነቶም ኣረጋግጹ — ሓደ እኹል እዩ</t>
+          <t>እቲ ዝርርብ ኣይርከብን።</t>
         </is>
       </c>
       <c r="G296" s="13" t="inlineStr">
         <is>
-          <t>Ogow cidda ay yihiin — mid kasta</t>
+          <t>Wadahadalka lama heli karo.</t>
         </is>
       </c>
       <c r="H296" s="13" t="inlineStr">
         <is>
-          <t>Thibitisha ni nani — mojawapo</t>
+          <t>Mazungumzo hayapatikani.</t>
         </is>
       </c>
       <c r="I296" s="14" t="inlineStr"/>
@@ -18973,7 +18973,7 @@
     <row r="297" ht="44" customHeight="1">
       <c r="A297" s="11" t="inlineStr">
         <is>
-          <t>chk_id_document</t>
+          <t>unmute</t>
         </is>
       </c>
       <c r="B297" s="11" t="inlineStr">
@@ -18983,32 +18983,32 @@
       </c>
       <c r="C297" s="11" t="inlineStr">
         <is>
-          <t>Fayda ID shown and matches the account name</t>
+          <t>Unmute</t>
         </is>
       </c>
       <c r="D297" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ መታወቂያ ታይቷል እና ከሂሳቡ ስም ጋር ይዛመዳል</t>
+          <t>ድምፅ አብራ</t>
         </is>
       </c>
       <c r="E297" s="13" t="inlineStr">
         <is>
-          <t>Waraqaan eenyummaa Fayda agarsiifame maqaa herregaa waliin walsimeera</t>
+          <t>Sagalee banaa</t>
         </is>
       </c>
       <c r="F297" s="12" t="inlineStr">
         <is>
-          <t>መንነት ፋይዳ ተራእዩን ምስ ስም ሕሳብ ይሰማማዕን</t>
+          <t>ድምጺ ኣብርህ</t>
         </is>
       </c>
       <c r="G297" s="13" t="inlineStr">
         <is>
-          <t>Aqoonsiga Fayda waa la tusay wuxuuna la mid yahay magaca xisaabta</t>
+          <t>Codka fur</t>
         </is>
       </c>
       <c r="H297" s="13" t="inlineStr">
         <is>
-          <t>Kitambulisho cha Fayda kimeonyeshwa na kinalingana na jina la akaunti</t>
+          <t>Rudisha Sauti</t>
         </is>
       </c>
       <c r="I297" s="14" t="inlineStr"/>
@@ -19016,7 +19016,7 @@
     <row r="298" ht="44" customHeight="1">
       <c r="A298" s="11" t="inlineStr">
         <is>
-          <t>chk_fayda_matched</t>
+          <t>session_summary_prompt</t>
         </is>
       </c>
       <c r="B298" s="11" t="inlineStr">
@@ -19026,32 +19026,32 @@
       </c>
       <c r="C298" s="11" t="inlineStr">
         <is>
-          <t>Fayda number matches the account record</t>
+          <t>What did this session cover? (optional)</t>
         </is>
       </c>
       <c r="D298" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ ቁጥር ከሂሳቡ መዝገብ ጋር ይዛመዳል</t>
+          <t>ይህ ክፍለ-ጊዜ ምን ሸፈነ? (አማራጭ)</t>
         </is>
       </c>
       <c r="E298" s="13" t="inlineStr">
         <is>
-          <t>Lakkoofsi Fayda galmee herregaa waliin walsimeera</t>
+          <t>Sessioniin kun maal haguuge? (filannoo)</t>
         </is>
       </c>
       <c r="F298" s="12" t="inlineStr">
         <is>
-          <t>ቁጽሪ ፋይዳ ምስ መዝገብ ሕሳብ ይሰማማዕ</t>
+          <t>እዚ ክፍለ-ግዜ እንታይ ሸፈነ? (ኣማራጺ)</t>
         </is>
       </c>
       <c r="G298" s="13" t="inlineStr">
         <is>
-          <t>Lambarka Fayda wuxuu la mid yahay diiwaanka xisaabta</t>
+          <t>Kalfadhigan muxuu daboolay? (ikhtiyaari)</t>
         </is>
       </c>
       <c r="H298" s="13" t="inlineStr">
         <is>
-          <t>Namba ya Fayda inalingana na rekodi ya akaunti</t>
+          <t>Kikao hiki kilihusu nini? (si lazima)</t>
         </is>
       </c>
       <c r="I298" s="14" t="inlineStr"/>
@@ -19059,7 +19059,7 @@
     <row r="299" ht="44" customHeight="1">
       <c r="A299" s="11" t="inlineStr">
         <is>
-          <t>chk_fayda_matched_note</t>
+          <t>customer_ended_call</t>
         </is>
       </c>
       <c r="B299" s="11" t="inlineStr">
@@ -19069,32 +19069,32 @@
       </c>
       <c r="C299" s="11" t="inlineStr">
         <is>
-          <t>on your own screen — works on an audio call</t>
+          <t>The customer ended the call</t>
         </is>
       </c>
       <c r="D299" s="12" t="inlineStr">
         <is>
-          <t>በራስዎ ስክሪን ላይ — በድምፅ ጥሪም ይሠራል</t>
+          <t>ደንበኛው ጥሪውን አቋረጠ</t>
         </is>
       </c>
       <c r="E299" s="13" t="inlineStr">
         <is>
-          <t>iskiriinii keessan irratti — bilbila sagalee irrattis ni hojjeta</t>
+          <t>Maamilaan bilbila xumure</t>
         </is>
       </c>
       <c r="F299" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ናትኩም መርአዪ — ኣብ ናይ ድምጺ ጻውዒት እውን ይሰርሕ</t>
+          <t>እቲ ዓሚል ነቲ ጻውዒት ወዲኡዎ</t>
         </is>
       </c>
       <c r="G299" s="13" t="inlineStr">
         <is>
-          <t>shaashaddaada — wicitaan cod ahna wuu ka shaqeeyaa</t>
+          <t>Macmiilku wicitaanka wuu joojiyay</t>
         </is>
       </c>
       <c r="H299" s="13" t="inlineStr">
         <is>
-          <t>kwenye skrini yako mwenyewe — inafanya kazi kwenye simu ya sauti</t>
+          <t>Mteja alimaliza simu</t>
         </is>
       </c>
       <c r="I299" s="14" t="inlineStr"/>
@@ -19102,7 +19102,7 @@
     <row r="300" ht="44" customHeight="1">
       <c r="A300" s="11" t="inlineStr">
         <is>
-          <t>chk_id_photo</t>
+          <t>verified_scope</t>
         </is>
       </c>
       <c r="B300" s="11" t="inlineStr">
@@ -19112,32 +19112,32 @@
       </c>
       <c r="C300" s="11" t="inlineStr">
         <is>
-          <t>Photo on the ID matches the person on the call</t>
+          <t>You can now discuss their own records, take documents and file a dispute. Never a deposit, withdrawal or transfer.</t>
         </is>
       </c>
       <c r="D300" s="12" t="inlineStr">
         <is>
-          <t>በመታወቂያው ላይ ያለው ፎቶ ከጥሪው ላይ ካለው ሰው ጋር ይዛመዳል</t>
+          <t>አሁን ስለ ራሳቸው መዝገቦች መወያየት፣ ሰነዶች መቀበልና ቅሬታ ማስመዝገብ ይችላሉ። በፍጹም ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም።</t>
         </is>
       </c>
       <c r="E300" s="13" t="inlineStr">
         <is>
-          <t>Suuraan waraqaa eenyummaa irra jiru nama bilbila irra jiru waliin walsimeera</t>
+          <t>Amma waa'ee galmee isaanii mari'achuu, sanadoota fudhachuu fi komii galmeessuu dandeessu. Gonkumaa kuusaa, baasii yookiin dabarsa hin jiru.</t>
         </is>
       </c>
       <c r="F300" s="12" t="inlineStr">
         <is>
-          <t>እቲ ኣብ መንነት ዘሎ ስእሊ ምስቲ ኣብ ጻውዒት ዘሎ ሰብ ይሰማማዕ</t>
+          <t>ሕጂ ብዛዕባ ናቶም መዝገባት ክትዘራረቡ፣ ሰነዳት ክትቅበሉን ጥርዓን ከተመዝግቡን ትኽእሉ። ፈጺሙ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን።</t>
         </is>
       </c>
       <c r="G300" s="13" t="inlineStr">
         <is>
-          <t>Sawirka aqoonsiga wuxuu la mid yahay qofka wicitaanka ku jira</t>
+          <t>Hadda waad kala hadli kartaa diiwaankooda, dukumiinti qaadan iyo cabasho diiwaangelin. Weligaa dhigasho, qaadis ama wareejin ma jirto.</t>
         </is>
       </c>
       <c r="H300" s="13" t="inlineStr">
         <is>
-          <t>Picha kwenye kitambulisho inalingana na mtu aliye kwenye simu</t>
+          <t>Sasa unaweza kuzungumzia rekodi zao wenyewe, kuchukua nyaraka na kuwasilisha mgogoro. Kamwe amana, uondoaji au uhamishaji.</t>
         </is>
       </c>
       <c r="I300" s="14" t="inlineStr"/>
@@ -19145,7 +19145,7 @@
     <row r="301" ht="44" customHeight="1">
       <c r="A301" s="11" t="inlineStr">
         <is>
-          <t>chk_video_only</t>
+          <t>establish_who_they_are</t>
         </is>
       </c>
       <c r="B301" s="11" t="inlineStr">
@@ -19155,32 +19155,32 @@
       </c>
       <c r="C301" s="11" t="inlineStr">
         <is>
-          <t>video only</t>
+          <t>Establish who they are — either one</t>
         </is>
       </c>
       <c r="D301" s="12" t="inlineStr">
         <is>
-          <t>ቪዲዮ ብቻ</t>
+          <t>ማንነታቸውን ያረጋግጡ — አንዱ ይበቃል</t>
         </is>
       </c>
       <c r="E301" s="13" t="inlineStr">
         <is>
-          <t>viidiyoo qofa</t>
+          <t>Eenyummaa isaanii mirkaneessaa — tokko ni ga'a</t>
         </is>
       </c>
       <c r="F301" s="12" t="inlineStr">
         <is>
-          <t>ቪድዮ ጥራይ</t>
+          <t>መንነቶም ኣረጋግጹ — ሓደ እኹል እዩ</t>
         </is>
       </c>
       <c r="G301" s="13" t="inlineStr">
         <is>
-          <t>fiidyow oo kaliya</t>
+          <t>Ogow cidda ay yihiin — mid kasta</t>
         </is>
       </c>
       <c r="H301" s="13" t="inlineStr">
         <is>
-          <t>video pekee</t>
+          <t>Thibitisha ni nani — mojawapo</t>
         </is>
       </c>
       <c r="I301" s="14" t="inlineStr"/>
@@ -19188,7 +19188,7 @@
     <row r="302" ht="44" customHeight="1">
       <c r="A302" s="11" t="inlineStr">
         <is>
-          <t>confirm_account_theirs</t>
+          <t>chk_id_document</t>
         </is>
       </c>
       <c r="B302" s="11" t="inlineStr">
@@ -19198,32 +19198,32 @@
       </c>
       <c r="C302" s="11" t="inlineStr">
         <is>
-          <t>And confirm the account is theirs</t>
+          <t>Fayda ID shown and matches the account name</t>
         </is>
       </c>
       <c r="D302" s="12" t="inlineStr">
         <is>
-          <t>እና ሂሳቡ የእነሱ መሆኑን ያረጋግጡ</t>
+          <t>የፋይዳ መታወቂያ ታይቷል እና ከሂሳቡ ስም ጋር ይዛመዳል</t>
         </is>
       </c>
       <c r="E302" s="13" t="inlineStr">
         <is>
-          <t>Akkasumas herregni kan isaanii ta'uu mirkaneessaa</t>
+          <t>Waraqaan eenyummaa Fayda agarsiifame maqaa herregaa waliin walsimeera</t>
         </is>
       </c>
       <c r="F302" s="12" t="inlineStr">
         <is>
-          <t>ከምኡ'ውን እቲ ሕሳብ ናቶም ምዃኑ ኣረጋግጹ</t>
+          <t>መንነት ፋይዳ ተራእዩን ምስ ስም ሕሳብ ይሰማማዕን</t>
         </is>
       </c>
       <c r="G302" s="13" t="inlineStr">
         <is>
-          <t>Xaqiiji in xisaabtu tahay tooda</t>
+          <t>Aqoonsiga Fayda waa la tusay wuxuuna la mid yahay magaca xisaabta</t>
         </is>
       </c>
       <c r="H302" s="13" t="inlineStr">
         <is>
-          <t>Na thibitisha akaunti ni yao</t>
+          <t>Kitambulisho cha Fayda kimeonyeshwa na kinalingana na jina la akaunti</t>
         </is>
       </c>
       <c r="I302" s="14" t="inlineStr"/>
@@ -19231,7 +19231,7 @@
     <row r="303" ht="44" customHeight="1">
       <c r="A303" s="11" t="inlineStr">
         <is>
-          <t>confirm_identity</t>
+          <t>chk_fayda_matched</t>
         </is>
       </c>
       <c r="B303" s="11" t="inlineStr">
@@ -19241,32 +19241,32 @@
       </c>
       <c r="C303" s="11" t="inlineStr">
         <is>
-          <t>Confirm identity</t>
+          <t>Fayda number matches the account record</t>
         </is>
       </c>
       <c r="D303" s="12" t="inlineStr">
         <is>
-          <t>ማንነት አረጋግጥ</t>
+          <t>የፋይዳ ቁጥር ከሂሳቡ መዝገብ ጋር ይዛመዳል</t>
         </is>
       </c>
       <c r="E303" s="13" t="inlineStr">
         <is>
-          <t>Eenyummaa mirkaneessi</t>
+          <t>Lakkoofsi Fayda galmee herregaa waliin walsimeera</t>
         </is>
       </c>
       <c r="F303" s="12" t="inlineStr">
         <is>
-          <t>መንነት ኣረጋግጽ</t>
+          <t>ቁጽሪ ፋይዳ ምስ መዝገብ ሕሳብ ይሰማማዕ</t>
         </is>
       </c>
       <c r="G303" s="13" t="inlineStr">
         <is>
-          <t>Xaqiiji aqoonsiga</t>
+          <t>Lambarka Fayda wuxuu la mid yahay diiwaanka xisaabta</t>
         </is>
       </c>
       <c r="H303" s="13" t="inlineStr">
         <is>
-          <t>Thibitisha Utambulisho</t>
+          <t>Namba ya Fayda inalingana na rekodi ya akaunti</t>
         </is>
       </c>
       <c r="I303" s="14" t="inlineStr"/>
@@ -19274,7 +19274,7 @@
     <row r="304" ht="44" customHeight="1">
       <c r="A304" s="11" t="inlineStr">
         <is>
-          <t>unverified_scope</t>
+          <t>chk_fayda_matched_note</t>
         </is>
       </c>
       <c r="B304" s="11" t="inlineStr">
@@ -19284,32 +19284,32 @@
       </c>
       <c r="C304" s="11" t="inlineStr">
         <is>
-          <t>Until this is done you can only give general guidance — products, eligibility and how to apply.</t>
+          <t>on your own screen — works on an audio call</t>
         </is>
       </c>
       <c r="D304" s="12" t="inlineStr">
         <is>
-          <t>ይህ እስኪከናወን ድረስ አጠቃላይ መመሪያ ብቻ መስጠት ይችላሉ — ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል።</t>
+          <t>በራስዎ ስክሪን ላይ — በድምፅ ጥሪም ይሠራል</t>
         </is>
       </c>
       <c r="E304" s="13" t="inlineStr">
         <is>
-          <t>Hanga kun raawwatutti qajeelfama waliigalaa qofa kennuu dandeessu — oomishaalee, ulaagaa fi akkaataa itti iyyatan.</t>
+          <t>iskiriinii keessan irratti — bilbila sagalee irrattis ni hojjeta</t>
         </is>
       </c>
       <c r="F304" s="12" t="inlineStr">
         <is>
-          <t>እዚ ክሳብ ዝፍጸም ሓፈሻዊ መምርሒ ጥራይ ክትህቡ ትኽእሉ — ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን።</t>
+          <t>ኣብ ናትኩም መርአዪ — ኣብ ናይ ድምጺ ጻውዒት እውን ይሰርሕ</t>
         </is>
       </c>
       <c r="G304" s="13" t="inlineStr">
         <is>
-          <t>Ilaa tan la sameeyo waxaad kaliya bixin kartaa hagaajin guud — alaabta, u-qalmitaanka iyo sida loo codsado.</t>
+          <t>shaashaddaada — wicitaan cod ahna wuu ka shaqeeyaa</t>
         </is>
       </c>
       <c r="H304" s="13" t="inlineStr">
         <is>
-          <t>Hadi hili litakapofanyika unaweza tu kutoa mwongozo wa jumla — bidhaa, sifa za kustahiki na jinsi ya kuomba.</t>
+          <t>kwenye skrini yako mwenyewe — inafanya kazi kwenye simu ya sauti</t>
         </is>
       </c>
       <c r="I304" s="14" t="inlineStr"/>
@@ -19317,7 +19317,7 @@
     <row r="305" ht="44" customHeight="1">
       <c r="A305" s="11" t="inlineStr">
         <is>
-          <t>fayda_number_required</t>
+          <t>chk_id_photo</t>
         </is>
       </c>
       <c r="B305" s="11" t="inlineStr">
@@ -19327,32 +19327,32 @@
       </c>
       <c r="C305" s="11" t="inlineStr">
         <is>
-          <t>Fayda number (required — it is what the record keeps)</t>
+          <t>Photo on the ID matches the person on the call</t>
         </is>
       </c>
       <c r="D305" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ ቁጥር (ያስፈልጋል — መዝገቡ የሚይዘው ይህ ነው)</t>
+          <t>በመታወቂያው ላይ ያለው ፎቶ ከጥሪው ላይ ካለው ሰው ጋር ይዛመዳል</t>
         </is>
       </c>
       <c r="E305" s="13" t="inlineStr">
         <is>
-          <t>Lakkoofsa Fayda (barbaachisaa — kan galmeen qabatu isa kana)</t>
+          <t>Suuraan waraqaa eenyummaa irra jiru nama bilbila irra jiru waliin walsimeera</t>
         </is>
       </c>
       <c r="F305" s="12" t="inlineStr">
         <is>
-          <t>ቁጽሪ ፋይዳ (የድሊ — እቲ መዝገብ ዝሕዞ እዚ እዩ)</t>
+          <t>እቲ ኣብ መንነት ዘሎ ስእሊ ምስቲ ኣብ ጻውዒት ዘሎ ሰብ ይሰማማዕ</t>
         </is>
       </c>
       <c r="G305" s="13" t="inlineStr">
         <is>
-          <t>Lambarka Fayda (loo baahan yahay — waa waxa diiwaanku hayo)</t>
+          <t>Sawirka aqoonsiga wuxuu la mid yahay qofka wicitaanka ku jira</t>
         </is>
       </c>
       <c r="H305" s="13" t="inlineStr">
         <is>
-          <t>Namba ya Fayda (inahitajika — ndiyo inayowekwa kwenye rekodi)</t>
+          <t>Picha kwenye kitambulisho inalingana na mtu aliye kwenye simu</t>
         </is>
       </c>
       <c r="I305" s="14" t="inlineStr"/>
@@ -19360,7 +19360,7 @@
     <row r="306" ht="44" customHeight="1">
       <c r="A306" s="11" t="inlineStr">
         <is>
-          <t>download_for_translation</t>
+          <t>chk_video_only</t>
         </is>
       </c>
       <c r="B306" s="11" t="inlineStr">
@@ -19370,32 +19370,32 @@
       </c>
       <c r="C306" s="11" t="inlineStr">
         <is>
-          <t>Download for translation</t>
+          <t>video only</t>
         </is>
       </c>
       <c r="D306" s="12" t="inlineStr">
         <is>
-          <t>ለትርጉም አውርድ</t>
+          <t>ቪዲዮ ብቻ</t>
         </is>
       </c>
       <c r="E306" s="13" t="inlineStr">
         <is>
-          <t>Hiikkaaf buufadhu</t>
+          <t>viidiyoo qofa</t>
         </is>
       </c>
       <c r="F306" s="12" t="inlineStr">
         <is>
-          <t>ንትርጉም ኣውርድ</t>
+          <t>ቪድዮ ጥራይ</t>
         </is>
       </c>
       <c r="G306" s="13" t="inlineStr">
         <is>
-          <t>Soo dejiso turjumaadda</t>
+          <t>fiidyow oo kaliya</t>
         </is>
       </c>
       <c r="H306" s="13" t="inlineStr">
         <is>
-          <t>Pakua kwa Tafsiri</t>
+          <t>video pekee</t>
         </is>
       </c>
       <c r="I306" s="14" t="inlineStr"/>
@@ -19403,48 +19403,263 @@
     <row r="307" ht="44" customHeight="1">
       <c r="A307" s="11" t="inlineStr">
         <is>
+          <t>confirm_account_theirs</t>
+        </is>
+      </c>
+      <c r="B307" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C307" s="11" t="inlineStr">
+        <is>
+          <t>And confirm the account is theirs</t>
+        </is>
+      </c>
+      <c r="D307" s="12" t="inlineStr">
+        <is>
+          <t>እና ሂሳቡ የእነሱ መሆኑን ያረጋግጡ</t>
+        </is>
+      </c>
+      <c r="E307" s="13" t="inlineStr">
+        <is>
+          <t>Akkasumas herregni kan isaanii ta'uu mirkaneessaa</t>
+        </is>
+      </c>
+      <c r="F307" s="12" t="inlineStr">
+        <is>
+          <t>ከምኡ'ውን እቲ ሕሳብ ናቶም ምዃኑ ኣረጋግጹ</t>
+        </is>
+      </c>
+      <c r="G307" s="13" t="inlineStr">
+        <is>
+          <t>Xaqiiji in xisaabtu tahay tooda</t>
+        </is>
+      </c>
+      <c r="H307" s="13" t="inlineStr">
+        <is>
+          <t>Na thibitisha akaunti ni yao</t>
+        </is>
+      </c>
+      <c r="I307" s="14" t="inlineStr"/>
+    </row>
+    <row r="308" ht="44" customHeight="1">
+      <c r="A308" s="11" t="inlineStr">
+        <is>
+          <t>confirm_identity</t>
+        </is>
+      </c>
+      <c r="B308" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C308" s="11" t="inlineStr">
+        <is>
+          <t>Confirm identity</t>
+        </is>
+      </c>
+      <c r="D308" s="12" t="inlineStr">
+        <is>
+          <t>ማንነት አረጋግጥ</t>
+        </is>
+      </c>
+      <c r="E308" s="13" t="inlineStr">
+        <is>
+          <t>Eenyummaa mirkaneessi</t>
+        </is>
+      </c>
+      <c r="F308" s="12" t="inlineStr">
+        <is>
+          <t>መንነት ኣረጋግጽ</t>
+        </is>
+      </c>
+      <c r="G308" s="13" t="inlineStr">
+        <is>
+          <t>Xaqiiji aqoonsiga</t>
+        </is>
+      </c>
+      <c r="H308" s="13" t="inlineStr">
+        <is>
+          <t>Thibitisha Utambulisho</t>
+        </is>
+      </c>
+      <c r="I308" s="14" t="inlineStr"/>
+    </row>
+    <row r="309" ht="44" customHeight="1">
+      <c r="A309" s="11" t="inlineStr">
+        <is>
+          <t>unverified_scope</t>
+        </is>
+      </c>
+      <c r="B309" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C309" s="11" t="inlineStr">
+        <is>
+          <t>Until this is done you can only give general guidance — products, eligibility and how to apply.</t>
+        </is>
+      </c>
+      <c r="D309" s="12" t="inlineStr">
+        <is>
+          <t>ይህ እስኪከናወን ድረስ አጠቃላይ መመሪያ ብቻ መስጠት ይችላሉ — ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል።</t>
+        </is>
+      </c>
+      <c r="E309" s="13" t="inlineStr">
+        <is>
+          <t>Hanga kun raawwatutti qajeelfama waliigalaa qofa kennuu dandeessu — oomishaalee, ulaagaa fi akkaataa itti iyyatan.</t>
+        </is>
+      </c>
+      <c r="F309" s="12" t="inlineStr">
+        <is>
+          <t>እዚ ክሳብ ዝፍጸም ሓፈሻዊ መምርሒ ጥራይ ክትህቡ ትኽእሉ — ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን።</t>
+        </is>
+      </c>
+      <c r="G309" s="13" t="inlineStr">
+        <is>
+          <t>Ilaa tan la sameeyo waxaad kaliya bixin kartaa hagaajin guud — alaabta, u-qalmitaanka iyo sida loo codsado.</t>
+        </is>
+      </c>
+      <c r="H309" s="13" t="inlineStr">
+        <is>
+          <t>Hadi hili litakapofanyika unaweza tu kutoa mwongozo wa jumla — bidhaa, sifa za kustahiki na jinsi ya kuomba.</t>
+        </is>
+      </c>
+      <c r="I309" s="14" t="inlineStr"/>
+    </row>
+    <row r="310" ht="44" customHeight="1">
+      <c r="A310" s="11" t="inlineStr">
+        <is>
+          <t>fayda_number_required</t>
+        </is>
+      </c>
+      <c r="B310" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C310" s="11" t="inlineStr">
+        <is>
+          <t>Fayda number (required — it is what the record keeps)</t>
+        </is>
+      </c>
+      <c r="D310" s="12" t="inlineStr">
+        <is>
+          <t>የፋይዳ ቁጥር (ያስፈልጋል — መዝገቡ የሚይዘው ይህ ነው)</t>
+        </is>
+      </c>
+      <c r="E310" s="13" t="inlineStr">
+        <is>
+          <t>Lakkoofsa Fayda (barbaachisaa — kan galmeen qabatu isa kana)</t>
+        </is>
+      </c>
+      <c r="F310" s="12" t="inlineStr">
+        <is>
+          <t>ቁጽሪ ፋይዳ (የድሊ — እቲ መዝገብ ዝሕዞ እዚ እዩ)</t>
+        </is>
+      </c>
+      <c r="G310" s="13" t="inlineStr">
+        <is>
+          <t>Lambarka Fayda (loo baahan yahay — waa waxa diiwaanku hayo)</t>
+        </is>
+      </c>
+      <c r="H310" s="13" t="inlineStr">
+        <is>
+          <t>Namba ya Fayda (inahitajika — ndiyo inayowekwa kwenye rekodi)</t>
+        </is>
+      </c>
+      <c r="I310" s="14" t="inlineStr"/>
+    </row>
+    <row r="311" ht="44" customHeight="1">
+      <c r="A311" s="11" t="inlineStr">
+        <is>
+          <t>download_for_translation</t>
+        </is>
+      </c>
+      <c r="B311" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C311" s="11" t="inlineStr">
+        <is>
+          <t>Download for translation</t>
+        </is>
+      </c>
+      <c r="D311" s="12" t="inlineStr">
+        <is>
+          <t>ለትርጉም አውርድ</t>
+        </is>
+      </c>
+      <c r="E311" s="13" t="inlineStr">
+        <is>
+          <t>Hiikkaaf buufadhu</t>
+        </is>
+      </c>
+      <c r="F311" s="12" t="inlineStr">
+        <is>
+          <t>ንትርጉም ኣውርድ</t>
+        </is>
+      </c>
+      <c r="G311" s="13" t="inlineStr">
+        <is>
+          <t>Soo dejiso turjumaadda</t>
+        </is>
+      </c>
+      <c r="H311" s="13" t="inlineStr">
+        <is>
+          <t>Pakua kwa Tafsiri</t>
+        </is>
+      </c>
+      <c r="I311" s="14" t="inlineStr"/>
+    </row>
+    <row r="312" ht="44" customHeight="1">
+      <c r="A312" s="11" t="inlineStr">
+        <is>
           <t>nothing_to_download</t>
         </is>
       </c>
-      <c r="B307" s="11" t="inlineStr">
-        <is>
-          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
-        </is>
-      </c>
-      <c r="C307" s="11" t="inlineStr">
+      <c r="B312" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C312" s="11" t="inlineStr">
         <is>
           <t>No approved answers to download yet.</t>
         </is>
       </c>
-      <c r="D307" s="12" t="inlineStr">
+      <c r="D312" s="12" t="inlineStr">
         <is>
           <t>እስካሁን የሚወርድ የተፈቀደ መልስ የለም።</t>
         </is>
       </c>
-      <c r="E307" s="13" t="inlineStr">
+      <c r="E312" s="13" t="inlineStr">
         <is>
           <t>Hanga ammaatti deebiin mirkanaa'e buufamu hin jiru.</t>
         </is>
       </c>
-      <c r="F307" s="12" t="inlineStr">
+      <c r="F312" s="12" t="inlineStr">
         <is>
           <t>ክሳብ ሕጂ ዝወርድ ዝጸደቐ መልሲ የለን።</t>
         </is>
       </c>
-      <c r="G307" s="13" t="inlineStr">
+      <c r="G312" s="13" t="inlineStr">
         <is>
           <t>Weli ma jiraan jawaabo la ansixiyay oo la soo dejiyo.</t>
         </is>
       </c>
-      <c r="H307" s="13" t="inlineStr">
+      <c r="H312" s="13" t="inlineStr">
         <is>
           <t>Hakuna majibu yaliyoidhinishwa ya kupakua bado.</t>
         </is>
       </c>
-      <c r="I307" s="14" t="inlineStr"/>
+      <c r="I312" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I307"/>
+  <autoFilter ref="A1:I312"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/review/Olink_Bank_Assist_language_review.xlsx
+++ b/review/Olink_Bank_Assist_language_review.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1. What the assistant says'!$A$1:$I$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2. What it understands'!$A$1:$E$91</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3. Buttons customers see'!$A$1:$I$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$I$336</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$I$342</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -752,7 +752,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>407 strings in 5 languages</t>
+          <t>413 strings in 5 languages</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I336"/>
+  <dimension ref="A1:I342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -19145,7 +19145,7 @@
     <row r="301" ht="44" customHeight="1">
       <c r="A301" s="11" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>manage_desk_members</t>
         </is>
       </c>
       <c r="B301" s="11" t="inlineStr">
@@ -19155,32 +19155,32 @@
       </c>
       <c r="C301" s="11" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Manage who handles this desk</t>
         </is>
       </c>
       <c r="D301" s="12" t="inlineStr">
         <is>
-          <t>በሂደት ላይ</t>
+          <t>ይህን ዴስክ ማን እንደሚይዝ ያስተዳድሩ</t>
         </is>
       </c>
       <c r="E301" s="13" t="inlineStr">
         <is>
-          <t>Adeemsa irra</t>
+          <t>Deeskii kana eenyu akka qabatu bulchi</t>
         </is>
       </c>
       <c r="F301" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መስርሕ</t>
+          <t>ነዚ ዴስክ መን ከም ዝሕዞ ኣመሓድር</t>
         </is>
       </c>
       <c r="G301" s="13" t="inlineStr">
         <is>
-          <t>Socda</t>
+          <t>Maamul cidda miiskan qabata</t>
         </is>
       </c>
       <c r="H301" s="13" t="inlineStr">
         <is>
-          <t>Inaendelea</t>
+          <t>Simamia nani anayeshughulikia dawati hili</t>
         </is>
       </c>
       <c r="I301" s="14" t="inlineStr"/>
@@ -19188,7 +19188,7 @@
     <row r="302" ht="44" customHeight="1">
       <c r="A302" s="11" t="inlineStr">
         <is>
-          <t>no_session_in_progress</t>
+          <t>assign_for_desk</t>
         </is>
       </c>
       <c r="B302" s="11" t="inlineStr">
@@ -19198,32 +19198,32 @@
       </c>
       <c r="C302" s="11" t="inlineStr">
         <is>
-          <t>No session in progress.</t>
+          <t>Who handles {desk}?</t>
         </is>
       </c>
       <c r="D302" s="12" t="inlineStr">
         <is>
-          <t>በሂደት ላይ ያለ ክፍለ-ጊዜ የለም።</t>
+          <t>{desk}ን ማን ይይዛል?</t>
         </is>
       </c>
       <c r="E302" s="13" t="inlineStr">
         <is>
-          <t>Sessionii adeemsa irra jiru hin jiru.</t>
+          <t>{desk} eenyutu qabata?</t>
         </is>
       </c>
       <c r="F302" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መስርሕ ዘሎ ክፍለ-ግዜ የለን።</t>
+          <t>{desk} መን ይሕዞ?</t>
         </is>
       </c>
       <c r="G302" s="13" t="inlineStr">
         <is>
-          <t>Ma jiro kalfadhi socda.</t>
+          <t>Yaa qabta {desk}?</t>
         </is>
       </c>
       <c r="H302" s="13" t="inlineStr">
         <is>
-          <t>Hakuna kikao kinachoendelea.</t>
+          <t>Nani anashughulikia {desk}?</t>
         </is>
       </c>
       <c r="I302" s="14" t="inlineStr"/>
@@ -19231,7 +19231,7 @@
     <row r="303" ht="44" customHeight="1">
       <c r="A303" s="11" t="inlineStr">
         <is>
-          <t>wait_suffix</t>
+          <t>assign_for_person</t>
         </is>
       </c>
       <c r="B303" s="11" t="inlineStr">
@@ -19241,32 +19241,32 @@
       </c>
       <c r="C303" s="11" t="inlineStr">
         <is>
-          <t>wait</t>
+          <t>Desks for {name}</t>
         </is>
       </c>
       <c r="D303" s="12" t="inlineStr">
         <is>
-          <t>ጥበቃ</t>
+          <t>የ{name} ዴስኮች</t>
         </is>
       </c>
       <c r="E303" s="13" t="inlineStr">
         <is>
-          <t>eegumsa</t>
+          <t>Deeskiiwwan {name}</t>
         </is>
       </c>
       <c r="F303" s="12" t="inlineStr">
         <is>
-          <t>ጽበት</t>
+          <t>ዴስክታት {name}</t>
         </is>
       </c>
       <c r="G303" s="13" t="inlineStr">
         <is>
-          <t>sug</t>
+          <t>Miisaska {name}</t>
         </is>
       </c>
       <c r="H303" s="13" t="inlineStr">
         <is>
-          <t>kusubiri</t>
+          <t>Madawati ya {name}</t>
         </is>
       </c>
       <c r="I303" s="14" t="inlineStr"/>
@@ -19274,7 +19274,7 @@
     <row r="304" ht="44" customHeight="1">
       <c r="A304" s="11" t="inlineStr">
         <is>
-          <t>what_session_covers</t>
+          <t>assign_hint</t>
         </is>
       </c>
       <c r="B304" s="11" t="inlineStr">
@@ -19284,32 +19284,32 @@
       </c>
       <c r="C304" s="11" t="inlineStr">
         <is>
-          <t>What a session covers</t>
+          <t>Changes save immediately. People can still adjust their own desks from the Live queue, and every change is in the audit log.</t>
         </is>
       </c>
       <c r="D304" s="12" t="inlineStr">
         <is>
-          <t>አንድ ክፍለ-ጊዜ ምን ይሸፍናል</t>
+          <t>ለውጦች ወዲያውኑ ይቀመጣሉ። ሰዎች አሁንም ከቀጥታ ወረፋው የራሳቸውን ዴስኮች ማስተካከል ይችላሉ፤ እያንዳንዱ ለውጥ በኦዲት መዝገብ ውስጥ አለ።</t>
         </is>
       </c>
       <c r="E304" s="13" t="inlineStr">
         <is>
-          <t>Sessioniin maal haguuga</t>
+          <t>Jijjiiramoonni battalumatti ni kuufamu. Namoonni ammas sarara kallattii irraa deeskiiwwan ofii sirreessuu danda'u; jijjiiramni hundi galmee odiitii keessa jira.</t>
         </is>
       </c>
       <c r="F304" s="12" t="inlineStr">
         <is>
-          <t>ሓደ ክፍለ-ግዜ እንታይ ይሽፍን</t>
+          <t>ለውጥታት ብቕጽበት ይቕመጡ። ሰባት ሕጂ እውን ካብ ቀጥታዊ ሰልፊ ናቶም ዴስክታት ከስተኻኽሉ ይኽእሉ፤ ነፍስ ወከፍ ለውጢ ኣብ መዝገብ ኦዲት ኣሎ።</t>
         </is>
       </c>
       <c r="G304" s="13" t="inlineStr">
         <is>
-          <t>Waxa kalfadhigu daboolo</t>
+          <t>Isbeddelladu isla markiiba way kaydsamaan. Dadku weli waxay ka hagaajin karaan miisaskooda safka tooska ah; isbeddel kastaa wuxuu ku jiraa diiwaanka hubinta.</t>
         </is>
       </c>
       <c r="H304" s="13" t="inlineStr">
         <is>
-          <t>Kikao Kinajumuisha Nini</t>
+          <t>Mabadiliko yanahifadhiwa mara moja. Watu bado wanaweza kurekebisha madawati yao kutoka foleni ya moja kwa moja; kila badiliko liko katika kumbukumbu ya ukaguzi.</t>
         </is>
       </c>
       <c r="I304" s="14" t="inlineStr"/>
@@ -19317,7 +19317,7 @@
     <row r="305" ht="44" customHeight="1">
       <c r="A305" s="11" t="inlineStr">
         <is>
-          <t>session_scope_body</t>
+          <t>edit_desks</t>
         </is>
       </c>
       <c r="B305" s="11" t="inlineStr">
@@ -19327,32 +19327,32 @@
       </c>
       <c r="C305" s="11" t="inlineStr">
         <is>
-          <t>Before someone is identified: general questions about products, eligibility and how to apply. Once you have checked their Fayda ID against the account and asked something only the account holder could answer: their own application, documents and disputes.</t>
+          <t>Desks</t>
         </is>
       </c>
       <c r="D305" s="12" t="inlineStr">
         <is>
-          <t>አንድ ሰው ከመለየቱ በፊት፦ ስለ ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል አጠቃላይ ጥያቄዎች። የፋይዳ መታወቂያቸውን ከሂሳቡ ጋር አመሳክረው የሂሳቡ ባለቤት ብቻ ሊመልሰው የሚችለውን ከጠየቁ በኋላ፦ የራሳቸው ማመልከቻ፣ ሰነዶችና ቅሬታዎች።</t>
+          <t>ዴስኮች</t>
         </is>
       </c>
       <c r="E305" s="13" t="inlineStr">
         <is>
-          <t>Namni tokko utuu hin beekamin dura: gaaffii waliigalaa waa'ee oomishaalee, ulaagaa fi akkaataa itti iyyatan. Erga waraqaa eenyummaa Fayda isaanii herrega waliin madaalchiftanii waan abbaan herregaa qofti deebisuu danda'u gaafattanii booda: iyyannoo, sanadoota fi komii isaanii.</t>
+          <t>Deeskiiwwan</t>
         </is>
       </c>
       <c r="F305" s="12" t="inlineStr">
         <is>
-          <t>ሓደ ሰብ ቅድሚ ምልላዩ፦ ብዛዕባ ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን ሓፈሻዊ ሕቶታት። መንነት ፋይዳኦም ምስ ሕሳብ ኣረጋጊጽኩም እቲ ወናኒ ሕሳብ ጥራይ ክምልሶ ዝኽእል ምስ ሓተትኩም፦ ናቶም ምልክታ፣ ሰነዳትን ጥርዓናትን።</t>
+          <t>ዴስክታት</t>
         </is>
       </c>
       <c r="G305" s="13" t="inlineStr">
         <is>
-          <t>Ka hor inta aan qofka la aqoonsan: su'aalo guud oo ku saabsan alaabta, u-qalmitaanka iyo sida loo codsado. Marka aad hubiso aqoonsigooda Fayda ee xisaabta oo aad weydiiso wax uu kaliya milkiilaha xisaabtu ka jawaabi karo: codsigooda, dukumiintiyada iyo cabashooyinka.</t>
+          <t>Miisaska</t>
         </is>
       </c>
       <c r="H305" s="13" t="inlineStr">
         <is>
-          <t>Kabla mtu hajatambuliwa: maswali ya jumla kuhusu bidhaa, sifa za kustahiki na jinsi ya kuomba. Baada ya kukagua Kitambulisho chao cha Fayda dhidi ya akaunti na kuuliza kitu ambacho mmiliki wa akaunti pekee angeweza kujibu: maombi yao wenyewe, nyaraka na migogoro.</t>
+          <t>Madawati</t>
         </is>
       </c>
       <c r="I305" s="14" t="inlineStr"/>
@@ -19360,7 +19360,7 @@
     <row r="306" ht="44" customHeight="1">
       <c r="A306" s="11" t="inlineStr">
         <is>
-          <t>never_money_movement</t>
+          <t>no_eligible_people</t>
         </is>
       </c>
       <c r="B306" s="11" t="inlineStr">
@@ -19370,32 +19370,32 @@
       </c>
       <c r="C306" s="11" t="inlineStr">
         <is>
-          <t>Never, at any point and for anyone: deposits, withdrawals or transfers. Those do not happen on a call.</t>
+          <t>Nobody on this team can take live calls yet.</t>
         </is>
       </c>
       <c r="D306" s="12" t="inlineStr">
         <is>
-          <t>በፍጹም፣ በማንኛውም ጊዜና ለማንም፦ ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም። እነዚያ በጥሪ ላይ አይፈጸሙም።</t>
+          <t>በዚህ ቡድን ውስጥ ቀጥታ ጥሪ መቀበል የሚችል እስካሁን የለም።</t>
         </is>
       </c>
       <c r="E306" s="13" t="inlineStr">
         <is>
-          <t>Gonkumaa, yeroo kamiyyuu fi eenyuufiyyuu: kuusaa, baasii yookiin dabarsa hin jiru. Isaan sun bilbila irratti hin raawwataman.</t>
+          <t>Garee kana keessa namni bilbila kallattii fudhachuu danda'u hanga ammaatti hin jiru.</t>
         </is>
       </c>
       <c r="F306" s="12" t="inlineStr">
         <is>
-          <t>ፈጺሙ፣ ኣብ ዝኾነ እዋንን ንዝኾነ ሰብን፦ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን። እዚኣቶም ኣብ ጻውዒት ኣይፍጸሙን።</t>
+          <t>ኣብዚ ጉጅለ ቀጥታዊ ጻውዒት ክቕበል ዝኽእል ክሳብ ሕጂ የለን።</t>
         </is>
       </c>
       <c r="G306" s="13" t="inlineStr">
         <is>
-          <t>Weligaa, wakhti kasta iyo qof kasta: dhigasho, qaadis ama wareejin ma jirto. Kuwaas wicitaan laguma sameeyo.</t>
+          <t>Kooxdan qofna weli ma qaadan karo wicitaanno toos ah.</t>
         </is>
       </c>
       <c r="H306" s="13" t="inlineStr">
         <is>
-          <t>Kamwe, wakati wowote na kwa yeyote: amana, uondoaji au uhamishaji. Hizo hazifanyiki kwenye simu.</t>
+          <t>Hakuna mtu katika timu hii anayeweza kupokea simu za moja kwa moja bado.</t>
         </is>
       </c>
       <c r="I306" s="14" t="inlineStr"/>
@@ -19403,7 +19403,7 @@
     <row r="307" ht="44" customHeight="1">
       <c r="A307" s="11" t="inlineStr">
         <is>
-          <t>open_escalation_queue</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="B307" s="11" t="inlineStr">
@@ -19413,32 +19413,32 @@
       </c>
       <c r="C307" s="11" t="inlineStr">
         <is>
-          <t>Open the escalation queue</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="D307" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ወረፋውን ክፈት</t>
+          <t>በሂደት ላይ</t>
         </is>
       </c>
       <c r="E307" s="13" t="inlineStr">
         <is>
-          <t>Sararaa dabarsaa banaa</t>
+          <t>Adeemsa irra</t>
         </is>
       </c>
       <c r="F307" s="12" t="inlineStr">
         <is>
-          <t>ሪጋ ምትሕልላፍ ክፈት</t>
+          <t>ኣብ መስርሕ</t>
         </is>
       </c>
       <c r="G307" s="13" t="inlineStr">
         <is>
-          <t>Fur safka gudbinta</t>
+          <t>Socda</t>
         </is>
       </c>
       <c r="H307" s="13" t="inlineStr">
         <is>
-          <t>Fungua Foleni ya Masuala Yaliyoelekezwa</t>
+          <t>Inaendelea</t>
         </is>
       </c>
       <c r="I307" s="14" t="inlineStr"/>
@@ -19446,7 +19446,7 @@
     <row r="308" ht="44" customHeight="1">
       <c r="A308" s="11" t="inlineStr">
         <is>
-          <t>open_live_queue</t>
+          <t>no_session_in_progress</t>
         </is>
       </c>
       <c r="B308" s="11" t="inlineStr">
@@ -19456,32 +19456,32 @@
       </c>
       <c r="C308" s="11" t="inlineStr">
         <is>
-          <t>Open the live call queue</t>
+          <t>No session in progress.</t>
         </is>
       </c>
       <c r="D308" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታ የጥሪ ወረፋውን ክፈት</t>
+          <t>በሂደት ላይ ያለ ክፍለ-ጊዜ የለም።</t>
         </is>
       </c>
       <c r="E308" s="13" t="inlineStr">
         <is>
-          <t>Sarara bilbilaa kallattii banaa</t>
+          <t>Sessionii adeemsa irra jiru hin jiru.</t>
         </is>
       </c>
       <c r="F308" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታዊ ናይ ጻውዒት ሰልፊ ክፈት</t>
+          <t>ኣብ መስርሕ ዘሎ ክፍለ-ግዜ የለን።</t>
         </is>
       </c>
       <c r="G308" s="13" t="inlineStr">
         <is>
-          <t>Fur safka wicitaanka tooska ah</t>
+          <t>Ma jiro kalfadhi socda.</t>
         </is>
       </c>
       <c r="H308" s="13" t="inlineStr">
         <is>
-          <t>Fungua foleni ya simu za moja kwa moja</t>
+          <t>Hakuna kikao kinachoendelea.</t>
         </is>
       </c>
       <c r="I308" s="14" t="inlineStr"/>
@@ -19489,7 +19489,7 @@
     <row r="309" ht="44" customHeight="1">
       <c r="A309" s="11" t="inlineStr">
         <is>
-          <t>live_waiting_one</t>
+          <t>wait_suffix</t>
         </is>
       </c>
       <c r="B309" s="11" t="inlineStr">
@@ -19499,32 +19499,32 @@
       </c>
       <c r="C309" s="11" t="inlineStr">
         <is>
-          <t>{n} customer waiting for a live call</t>
+          <t>wait</t>
         </is>
       </c>
       <c r="D309" s="12" t="inlineStr">
         <is>
-          <t>{n} ደንበኛ ቀጥታ ጥሪ በመጠበቅ ላይ ነው</t>
+          <t>ጥበቃ</t>
         </is>
       </c>
       <c r="E309" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan {n} bilbila kallattii eegaa jira</t>
+          <t>eegumsa</t>
         </is>
       </c>
       <c r="F309" s="12" t="inlineStr">
         <is>
-          <t>{n} ዓሚል ቀጥታዊ ጻውዒት ይጽበ ኣሎ</t>
+          <t>ጽበት</t>
         </is>
       </c>
       <c r="G309" s="13" t="inlineStr">
         <is>
-          <t>{n} macmiil ayaa sugaya wicitaan toos ah</t>
+          <t>sug</t>
         </is>
       </c>
       <c r="H309" s="13" t="inlineStr">
         <is>
-          <t>Mteja {n} anasubiri simu ya moja kwa moja</t>
+          <t>kusubiri</t>
         </is>
       </c>
       <c r="I309" s="14" t="inlineStr"/>
@@ -19532,7 +19532,7 @@
     <row r="310" ht="44" customHeight="1">
       <c r="A310" s="11" t="inlineStr">
         <is>
-          <t>live_waiting_many</t>
+          <t>what_session_covers</t>
         </is>
       </c>
       <c r="B310" s="11" t="inlineStr">
@@ -19542,32 +19542,32 @@
       </c>
       <c r="C310" s="11" t="inlineStr">
         <is>
-          <t>{n} customers waiting for a live call</t>
+          <t>What a session covers</t>
         </is>
       </c>
       <c r="D310" s="12" t="inlineStr">
         <is>
-          <t>{n} ደንበኞች ቀጥታ ጥሪ በመጠበቅ ላይ ናቸው</t>
+          <t>አንድ ክፍለ-ጊዜ ምን ይሸፍናል</t>
         </is>
       </c>
       <c r="E310" s="13" t="inlineStr">
         <is>
-          <t>Maamiltoonni {n} bilbila kallattii eegaa jiru</t>
+          <t>Sessioniin maal haguuga</t>
         </is>
       </c>
       <c r="F310" s="12" t="inlineStr">
         <is>
-          <t>{n} ዓማዊል ቀጥታዊ ጻውዒት ይጽበዩ ኣለዉ</t>
+          <t>ሓደ ክፍለ-ግዜ እንታይ ይሽፍን</t>
         </is>
       </c>
       <c r="G310" s="13" t="inlineStr">
         <is>
-          <t>{n} macaamiil ayaa sugaya wicitaan toos ah</t>
+          <t>Waxa kalfadhigu daboolo</t>
         </is>
       </c>
       <c r="H310" s="13" t="inlineStr">
         <is>
-          <t>Wateja {n} wanasubiri simu ya moja kwa moja</t>
+          <t>Kikao Kinajumuisha Nini</t>
         </is>
       </c>
       <c r="I310" s="14" t="inlineStr"/>
@@ -19575,7 +19575,7 @@
     <row r="311" ht="44" customHeight="1">
       <c r="A311" s="11" t="inlineStr">
         <is>
-          <t>switch_dark_light</t>
+          <t>session_scope_body</t>
         </is>
       </c>
       <c r="B311" s="11" t="inlineStr">
@@ -19585,32 +19585,32 @@
       </c>
       <c r="C311" s="11" t="inlineStr">
         <is>
-          <t>Switch between dark and light</t>
+          <t>Before someone is identified: general questions about products, eligibility and how to apply. Once you have checked their Fayda ID against the account and asked something only the account holder could answer: their own application, documents and disputes.</t>
         </is>
       </c>
       <c r="D311" s="12" t="inlineStr">
         <is>
-          <t>በጨለማና በብርሃን መካከል ቀይር</t>
+          <t>አንድ ሰው ከመለየቱ በፊት፦ ስለ ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል አጠቃላይ ጥያቄዎች። የፋይዳ መታወቂያቸውን ከሂሳቡ ጋር አመሳክረው የሂሳቡ ባለቤት ብቻ ሊመልሰው የሚችለውን ከጠየቁ በኋላ፦ የራሳቸው ማመልከቻ፣ ሰነዶችና ቅሬታዎች።</t>
         </is>
       </c>
       <c r="E311" s="13" t="inlineStr">
         <is>
-          <t>Dukkanaa fi ifa gidduu jijjiiri</t>
+          <t>Namni tokko utuu hin beekamin dura: gaaffii waliigalaa waa'ee oomishaalee, ulaagaa fi akkaataa itti iyyatan. Erga waraqaa eenyummaa Fayda isaanii herrega waliin madaalchiftanii waan abbaan herregaa qofti deebisuu danda'u gaafattanii booda: iyyannoo, sanadoota fi komii isaanii.</t>
         </is>
       </c>
       <c r="F311" s="12" t="inlineStr">
         <is>
-          <t>ኣብ መንጎ ጸላምን ብርሃንን ቀይር</t>
+          <t>ሓደ ሰብ ቅድሚ ምልላዩ፦ ብዛዕባ ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን ሓፈሻዊ ሕቶታት። መንነት ፋይዳኦም ምስ ሕሳብ ኣረጋጊጽኩም እቲ ወናኒ ሕሳብ ጥራይ ክምልሶ ዝኽእል ምስ ሓተትኩም፦ ናቶም ምልክታ፣ ሰነዳትን ጥርዓናትን።</t>
         </is>
       </c>
       <c r="G311" s="13" t="inlineStr">
         <is>
-          <t>U beddel mugdiga iyo iftiinka</t>
+          <t>Ka hor inta aan qofka la aqoonsan: su'aalo guud oo ku saabsan alaabta, u-qalmitaanka iyo sida loo codsado. Marka aad hubiso aqoonsigooda Fayda ee xisaabta oo aad weydiiso wax uu kaliya milkiilaha xisaabtu ka jawaabi karo: codsigooda, dukumiintiyada iyo cabashooyinka.</t>
         </is>
       </c>
       <c r="H311" s="13" t="inlineStr">
         <is>
-          <t>Badilisha Kati ya Giza na Mwanga</t>
+          <t>Kabla mtu hajatambuliwa: maswali ya jumla kuhusu bidhaa, sifa za kustahiki na jinsi ya kuomba. Baada ya kukagua Kitambulisho chao cha Fayda dhidi ya akaunti na kuuliza kitu ambacho mmiliki wa akaunti pekee angeweza kujibu: maombi yao wenyewe, nyaraka na migogoro.</t>
         </is>
       </c>
       <c r="I311" s="14" t="inlineStr"/>
@@ -19618,7 +19618,7 @@
     <row r="312" ht="44" customHeight="1">
       <c r="A312" s="11" t="inlineStr">
         <is>
-          <t>live_session</t>
+          <t>never_money_movement</t>
         </is>
       </c>
       <c r="B312" s="11" t="inlineStr">
@@ -19628,32 +19628,32 @@
       </c>
       <c r="C312" s="11" t="inlineStr">
         <is>
-          <t>Live session</t>
+          <t>Never, at any point and for anyone: deposits, withdrawals or transfers. Those do not happen on a call.</t>
         </is>
       </c>
       <c r="D312" s="12" t="inlineStr">
         <is>
-          <t>የቀጥታ ክፍለ-ጊዜ</t>
+          <t>በፍጹም፣ በማንኛውም ጊዜና ለማንም፦ ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም። እነዚያ በጥሪ ላይ አይፈጸሙም።</t>
         </is>
       </c>
       <c r="E312" s="13" t="inlineStr">
         <is>
-          <t>Session kallattii</t>
+          <t>Gonkumaa, yeroo kamiyyuu fi eenyuufiyyuu: kuusaa, baasii yookiin dabarsa hin jiru. Isaan sun bilbila irratti hin raawwataman.</t>
         </is>
       </c>
       <c r="F312" s="12" t="inlineStr">
         <is>
-          <t>ቀጥታ ክፍለ-ግዜ</t>
+          <t>ፈጺሙ፣ ኣብ ዝኾነ እዋንን ንዝኾነ ሰብን፦ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን። እዚኣቶም ኣብ ጻውዒት ኣይፍጸሙን።</t>
         </is>
       </c>
       <c r="G312" s="13" t="inlineStr">
         <is>
-          <t>Kalfadhi toos ah</t>
+          <t>Weligaa, wakhti kasta iyo qof kasta: dhigasho, qaadis ama wareejin ma jirto. Kuwaas wicitaan laguma sameeyo.</t>
         </is>
       </c>
       <c r="H312" s="13" t="inlineStr">
         <is>
-          <t>Kikao cha Moja kwa Moja</t>
+          <t>Kamwe, wakati wowote na kwa yeyote: amana, uondoaji au uhamishaji. Hizo hazifanyiki kwenye simu.</t>
         </is>
       </c>
       <c r="I312" s="14" t="inlineStr"/>
@@ -19661,7 +19661,7 @@
     <row r="313" ht="44" customHeight="1">
       <c r="A313" s="11" t="inlineStr">
         <is>
-          <t>customer_left_call</t>
+          <t>open_escalation_queue</t>
         </is>
       </c>
       <c r="B313" s="11" t="inlineStr">
@@ -19671,32 +19671,32 @@
       </c>
       <c r="C313" s="11" t="inlineStr">
         <is>
-          <t>The customer has left the call.</t>
+          <t>Open the escalation queue</t>
         </is>
       </c>
       <c r="D313" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛው ጥሪውን ለቅቋል።</t>
+          <t>የማሸጋገሪያ ወረፋውን ክፈት</t>
         </is>
       </c>
       <c r="E313" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan bilbila irraa ba'eera.</t>
+          <t>Sararaa dabarsaa banaa</t>
         </is>
       </c>
       <c r="F313" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዓሚል ካብቲ ጻውዒት ወጺኡ።</t>
+          <t>ሪጋ ምትሕልላፍ ክፈት</t>
         </is>
       </c>
       <c r="G313" s="13" t="inlineStr">
         <is>
-          <t>Macmiilku wicitaanka wuu ka baxay.</t>
+          <t>Fur safka gudbinta</t>
         </is>
       </c>
       <c r="H313" s="13" t="inlineStr">
         <is>
-          <t>Mteja ameondoka kwenye simu.</t>
+          <t>Fungua Foleni ya Masuala Yaliyoelekezwa</t>
         </is>
       </c>
       <c r="I313" s="14" t="inlineStr"/>
@@ -19704,7 +19704,7 @@
     <row r="314" ht="44" customHeight="1">
       <c r="A314" s="11" t="inlineStr">
         <is>
-          <t>waiting_for_customer</t>
+          <t>open_live_queue</t>
         </is>
       </c>
       <c r="B314" s="11" t="inlineStr">
@@ -19714,32 +19714,32 @@
       </c>
       <c r="C314" s="11" t="inlineStr">
         <is>
-          <t>Waiting for the customer…</t>
+          <t>Open the live call queue</t>
         </is>
       </c>
       <c r="D314" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛውን በመጠበቅ ላይ…</t>
+          <t>ቀጥታ የጥሪ ወረፋውን ክፈት</t>
         </is>
       </c>
       <c r="E314" s="13" t="inlineStr">
         <is>
-          <t>Maamilaa eegaa jirra…</t>
+          <t>Sarara bilbilaa kallattii banaa</t>
         </is>
       </c>
       <c r="F314" s="12" t="inlineStr">
         <is>
-          <t>ነቲ ዓሚል ንጽበ ኣለና…</t>
+          <t>ቀጥታዊ ናይ ጻውዒት ሰልፊ ክፈት</t>
         </is>
       </c>
       <c r="G314" s="13" t="inlineStr">
         <is>
-          <t>Macmiilka la sugayo…</t>
+          <t>Fur safka wicitaanka tooska ah</t>
         </is>
       </c>
       <c r="H314" s="13" t="inlineStr">
         <is>
-          <t>Inasubiri Mteja…</t>
+          <t>Fungua foleni ya simu za moja kwa moja</t>
         </is>
       </c>
       <c r="I314" s="14" t="inlineStr"/>
@@ -19747,7 +19747,7 @@
     <row r="315" ht="44" customHeight="1">
       <c r="A315" s="11" t="inlineStr">
         <is>
-          <t>mic_blocked</t>
+          <t>live_waiting_one</t>
         </is>
       </c>
       <c r="B315" s="11" t="inlineStr">
@@ -19757,32 +19757,32 @@
       </c>
       <c r="C315" s="11" t="inlineStr">
         <is>
-          <t>Microphone access is blocked. Allow it in your browser and take the session again.</t>
+          <t>{n} customer waiting for a live call</t>
         </is>
       </c>
       <c r="D315" s="12" t="inlineStr">
         <is>
-          <t>የማይክሮፎን መዳረሻ ታግዷል። በአሳሽዎ ውስጥ ይፍቀዱና ክፍለ-ጊዜውን እንደገና ይውሰዱ።</t>
+          <t>{n} ደንበኛ ቀጥታ ጥሪ በመጠበቅ ላይ ነው</t>
         </is>
       </c>
       <c r="E315" s="13" t="inlineStr">
         <is>
-          <t>Maayikiroofoonii dhorkameera. Biraawzarii keessan keessatti hayyamaatii session irra deebi'aa fudhadhaa.</t>
+          <t>Maamilaan {n} bilbila kallattii eegaa jira</t>
         </is>
       </c>
       <c r="F315" s="12" t="inlineStr">
         <is>
-          <t>መእተዊ ማይክሮፎን ተዓጊቱ። ኣብ መርበብ መንሸራተቲኹም ፍቐዱ እሞ ነቲ ክፍለ-ግዜ ደጊምኩም ውሰዱ።</t>
+          <t>{n} ዓሚል ቀጥታዊ ጻውዒት ይጽበ ኣሎ</t>
         </is>
       </c>
       <c r="G315" s="13" t="inlineStr">
         <is>
-          <t>Makarafoonka waa la xannibay. Browser-kaaga ka ogolow oo kalfadhiga mar kale qaado.</t>
+          <t>{n} macmiil ayaa sugaya wicitaan toos ah</t>
         </is>
       </c>
       <c r="H315" s="13" t="inlineStr">
         <is>
-          <t>Ufikiaji wa maikrofoni umezuiwa. Ruhusu kwenye kivinjari chako na uanze kikao tena.</t>
+          <t>Mteja {n} anasubiri simu ya moja kwa moja</t>
         </is>
       </c>
       <c r="I315" s="14" t="inlineStr"/>
@@ -19790,7 +19790,7 @@
     <row r="316" ht="44" customHeight="1">
       <c r="A316" s="11" t="inlineStr">
         <is>
-          <t>unknown_error</t>
+          <t>live_waiting_many</t>
         </is>
       </c>
       <c r="B316" s="11" t="inlineStr">
@@ -19800,32 +19800,32 @@
       </c>
       <c r="C316" s="11" t="inlineStr">
         <is>
-          <t>unknown error</t>
+          <t>{n} customers waiting for a live call</t>
         </is>
       </c>
       <c r="D316" s="12" t="inlineStr">
         <is>
-          <t>ያልታወቀ ስህተት</t>
+          <t>{n} ደንበኞች ቀጥታ ጥሪ በመጠበቅ ላይ ናቸው</t>
         </is>
       </c>
       <c r="E316" s="13" t="inlineStr">
         <is>
-          <t>dogoggora hin beekamne</t>
+          <t>Maamiltoonni {n} bilbila kallattii eegaa jiru</t>
         </is>
       </c>
       <c r="F316" s="12" t="inlineStr">
         <is>
-          <t>ዘይተፈልጠ ጌጋ</t>
+          <t>{n} ዓማዊል ቀጥታዊ ጻውዒት ይጽበዩ ኣለዉ</t>
         </is>
       </c>
       <c r="G316" s="13" t="inlineStr">
         <is>
-          <t>khalad aan la garanayn</t>
+          <t>{n} macaamiil ayaa sugaya wicitaan toos ah</t>
         </is>
       </c>
       <c r="H316" s="13" t="inlineStr">
         <is>
-          <t>hitilafu isiyojulikana</t>
+          <t>Wateja {n} wanasubiri simu ya moja kwa moja</t>
         </is>
       </c>
       <c r="I316" s="14" t="inlineStr"/>
@@ -19833,7 +19833,7 @@
     <row r="317" ht="44" customHeight="1">
       <c r="A317" s="11" t="inlineStr">
         <is>
-          <t>no_messages_yet</t>
+          <t>switch_dark_light</t>
         </is>
       </c>
       <c r="B317" s="11" t="inlineStr">
@@ -19843,32 +19843,32 @@
       </c>
       <c r="C317" s="11" t="inlineStr">
         <is>
-          <t>No messages yet.</t>
+          <t>Switch between dark and light</t>
         </is>
       </c>
       <c r="D317" s="12" t="inlineStr">
         <is>
-          <t>እስካሁን መልእክት የለም።</t>
+          <t>በጨለማና በብርሃን መካከል ቀይር</t>
         </is>
       </c>
       <c r="E317" s="13" t="inlineStr">
         <is>
-          <t>Ammaaf ergaan hin jiru.</t>
+          <t>Dukkanaa fi ifa gidduu jijjiiri</t>
         </is>
       </c>
       <c r="F317" s="12" t="inlineStr">
         <is>
-          <t>ክሳብ ሕጂ መልእኽቲ የለን።</t>
+          <t>ኣብ መንጎ ጸላምን ብርሃንን ቀይር</t>
         </is>
       </c>
       <c r="G317" s="13" t="inlineStr">
         <is>
-          <t>Weli fariimo ma jiraan.</t>
+          <t>U beddel mugdiga iyo iftiinka</t>
         </is>
       </c>
       <c r="H317" s="13" t="inlineStr">
         <is>
-          <t>Hakuna ujumbe bado.</t>
+          <t>Badilisha Kati ya Giza na Mwanga</t>
         </is>
       </c>
       <c r="I317" s="14" t="inlineStr"/>
@@ -19876,7 +19876,7 @@
     <row r="318" ht="44" customHeight="1">
       <c r="A318" s="11" t="inlineStr">
         <is>
-          <t>you_label</t>
+          <t>live_session</t>
         </is>
       </c>
       <c r="B318" s="11" t="inlineStr">
@@ -19886,32 +19886,32 @@
       </c>
       <c r="C318" s="11" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>Live session</t>
         </is>
       </c>
       <c r="D318" s="12" t="inlineStr">
         <is>
-          <t>እርስዎ</t>
+          <t>የቀጥታ ክፍለ-ጊዜ</t>
         </is>
       </c>
       <c r="E318" s="13" t="inlineStr">
         <is>
-          <t>Isin</t>
+          <t>Session kallattii</t>
         </is>
       </c>
       <c r="F318" s="12" t="inlineStr">
         <is>
-          <t>ንስኹም</t>
+          <t>ቀጥታ ክፍለ-ግዜ</t>
         </is>
       </c>
       <c r="G318" s="13" t="inlineStr">
         <is>
-          <t>Adiga</t>
+          <t>Kalfadhi toos ah</t>
         </is>
       </c>
       <c r="H318" s="13" t="inlineStr">
         <is>
-          <t>Wewe</t>
+          <t>Kikao cha Moja kwa Moja</t>
         </is>
       </c>
       <c r="I318" s="14" t="inlineStr"/>
@@ -19919,7 +19919,7 @@
     <row r="319" ht="44" customHeight="1">
       <c r="A319" s="11" t="inlineStr">
         <is>
-          <t>assistant_label</t>
+          <t>customer_left_call</t>
         </is>
       </c>
       <c r="B319" s="11" t="inlineStr">
@@ -19929,32 +19929,32 @@
       </c>
       <c r="C319" s="11" t="inlineStr">
         <is>
-          <t>Assistant</t>
+          <t>The customer has left the call.</t>
         </is>
       </c>
       <c r="D319" s="12" t="inlineStr">
         <is>
-          <t>ረዳት</t>
+          <t>ደንበኛው ጥሪውን ለቅቋል።</t>
         </is>
       </c>
       <c r="E319" s="13" t="inlineStr">
         <is>
-          <t>Gargaaraa</t>
+          <t>Maamilaan bilbila irraa ba'eera.</t>
         </is>
       </c>
       <c r="F319" s="12" t="inlineStr">
         <is>
-          <t>ሓጋዚ</t>
+          <t>እቲ ዓሚል ካብቲ ጻውዒት ወጺኡ።</t>
         </is>
       </c>
       <c r="G319" s="13" t="inlineStr">
         <is>
-          <t>Kaaliye</t>
+          <t>Macmiilku wicitaanka wuu ka baxay.</t>
         </is>
       </c>
       <c r="H319" s="13" t="inlineStr">
         <is>
-          <t>Msaidizi</t>
+          <t>Mteja ameondoka kwenye simu.</t>
         </is>
       </c>
       <c r="I319" s="14" t="inlineStr"/>
@@ -19962,7 +19962,7 @@
     <row r="320" ht="44" customHeight="1">
       <c r="A320" s="11" t="inlineStr">
         <is>
-          <t>conversation_unavailable</t>
+          <t>waiting_for_customer</t>
         </is>
       </c>
       <c r="B320" s="11" t="inlineStr">
@@ -19972,32 +19972,32 @@
       </c>
       <c r="C320" s="11" t="inlineStr">
         <is>
-          <t>Conversation unavailable.</t>
+          <t>Waiting for the customer…</t>
         </is>
       </c>
       <c r="D320" s="12" t="inlineStr">
         <is>
-          <t>ውይይቱ አይገኝም።</t>
+          <t>ደንበኛውን በመጠበቅ ላይ…</t>
         </is>
       </c>
       <c r="E320" s="13" t="inlineStr">
         <is>
-          <t>Mariin hin argamu.</t>
+          <t>Maamilaa eegaa jirra…</t>
         </is>
       </c>
       <c r="F320" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዝርርብ ኣይርከብን።</t>
+          <t>ነቲ ዓሚል ንጽበ ኣለና…</t>
         </is>
       </c>
       <c r="G320" s="13" t="inlineStr">
         <is>
-          <t>Wadahadalka lama heli karo.</t>
+          <t>Macmiilka la sugayo…</t>
         </is>
       </c>
       <c r="H320" s="13" t="inlineStr">
         <is>
-          <t>Mazungumzo hayapatikani.</t>
+          <t>Inasubiri Mteja…</t>
         </is>
       </c>
       <c r="I320" s="14" t="inlineStr"/>
@@ -20005,7 +20005,7 @@
     <row r="321" ht="44" customHeight="1">
       <c r="A321" s="11" t="inlineStr">
         <is>
-          <t>unmute</t>
+          <t>mic_blocked</t>
         </is>
       </c>
       <c r="B321" s="11" t="inlineStr">
@@ -20015,32 +20015,32 @@
       </c>
       <c r="C321" s="11" t="inlineStr">
         <is>
-          <t>Unmute</t>
+          <t>Microphone access is blocked. Allow it in your browser and take the session again.</t>
         </is>
       </c>
       <c r="D321" s="12" t="inlineStr">
         <is>
-          <t>ድምፅ አብራ</t>
+          <t>የማይክሮፎን መዳረሻ ታግዷል። በአሳሽዎ ውስጥ ይፍቀዱና ክፍለ-ጊዜውን እንደገና ይውሰዱ።</t>
         </is>
       </c>
       <c r="E321" s="13" t="inlineStr">
         <is>
-          <t>Sagalee banaa</t>
+          <t>Maayikiroofoonii dhorkameera. Biraawzarii keessan keessatti hayyamaatii session irra deebi'aa fudhadhaa.</t>
         </is>
       </c>
       <c r="F321" s="12" t="inlineStr">
         <is>
-          <t>ድምጺ ኣብርህ</t>
+          <t>መእተዊ ማይክሮፎን ተዓጊቱ። ኣብ መርበብ መንሸራተቲኹም ፍቐዱ እሞ ነቲ ክፍለ-ግዜ ደጊምኩም ውሰዱ።</t>
         </is>
       </c>
       <c r="G321" s="13" t="inlineStr">
         <is>
-          <t>Codka fur</t>
+          <t>Makarafoonka waa la xannibay. Browser-kaaga ka ogolow oo kalfadhiga mar kale qaado.</t>
         </is>
       </c>
       <c r="H321" s="13" t="inlineStr">
         <is>
-          <t>Rudisha Sauti</t>
+          <t>Ufikiaji wa maikrofoni umezuiwa. Ruhusu kwenye kivinjari chako na uanze kikao tena.</t>
         </is>
       </c>
       <c r="I321" s="14" t="inlineStr"/>
@@ -20048,7 +20048,7 @@
     <row r="322" ht="44" customHeight="1">
       <c r="A322" s="11" t="inlineStr">
         <is>
-          <t>session_summary_prompt</t>
+          <t>unknown_error</t>
         </is>
       </c>
       <c r="B322" s="11" t="inlineStr">
@@ -20058,32 +20058,32 @@
       </c>
       <c r="C322" s="11" t="inlineStr">
         <is>
-          <t>What did this session cover? (optional)</t>
+          <t>unknown error</t>
         </is>
       </c>
       <c r="D322" s="12" t="inlineStr">
         <is>
-          <t>ይህ ክፍለ-ጊዜ ምን ሸፈነ? (አማራጭ)</t>
+          <t>ያልታወቀ ስህተት</t>
         </is>
       </c>
       <c r="E322" s="13" t="inlineStr">
         <is>
-          <t>Sessioniin kun maal haguuge? (filannoo)</t>
+          <t>dogoggora hin beekamne</t>
         </is>
       </c>
       <c r="F322" s="12" t="inlineStr">
         <is>
-          <t>እዚ ክፍለ-ግዜ እንታይ ሸፈነ? (ኣማራጺ)</t>
+          <t>ዘይተፈልጠ ጌጋ</t>
         </is>
       </c>
       <c r="G322" s="13" t="inlineStr">
         <is>
-          <t>Kalfadhigan muxuu daboolay? (ikhtiyaari)</t>
+          <t>khalad aan la garanayn</t>
         </is>
       </c>
       <c r="H322" s="13" t="inlineStr">
         <is>
-          <t>Kikao hiki kilihusu nini? (si lazima)</t>
+          <t>hitilafu isiyojulikana</t>
         </is>
       </c>
       <c r="I322" s="14" t="inlineStr"/>
@@ -20091,7 +20091,7 @@
     <row r="323" ht="44" customHeight="1">
       <c r="A323" s="11" t="inlineStr">
         <is>
-          <t>customer_ended_call</t>
+          <t>no_messages_yet</t>
         </is>
       </c>
       <c r="B323" s="11" t="inlineStr">
@@ -20101,32 +20101,32 @@
       </c>
       <c r="C323" s="11" t="inlineStr">
         <is>
-          <t>The customer ended the call</t>
+          <t>No messages yet.</t>
         </is>
       </c>
       <c r="D323" s="12" t="inlineStr">
         <is>
-          <t>ደንበኛው ጥሪውን አቋረጠ</t>
+          <t>እስካሁን መልእክት የለም።</t>
         </is>
       </c>
       <c r="E323" s="13" t="inlineStr">
         <is>
-          <t>Maamilaan bilbila xumure</t>
+          <t>Ammaaf ergaan hin jiru.</t>
         </is>
       </c>
       <c r="F323" s="12" t="inlineStr">
         <is>
-          <t>እቲ ዓሚል ነቲ ጻውዒት ወዲኡዎ</t>
+          <t>ክሳብ ሕጂ መልእኽቲ የለን።</t>
         </is>
       </c>
       <c r="G323" s="13" t="inlineStr">
         <is>
-          <t>Macmiilku wicitaanka wuu joojiyay</t>
+          <t>Weli fariimo ma jiraan.</t>
         </is>
       </c>
       <c r="H323" s="13" t="inlineStr">
         <is>
-          <t>Mteja alimaliza simu</t>
+          <t>Hakuna ujumbe bado.</t>
         </is>
       </c>
       <c r="I323" s="14" t="inlineStr"/>
@@ -20134,7 +20134,7 @@
     <row r="324" ht="44" customHeight="1">
       <c r="A324" s="11" t="inlineStr">
         <is>
-          <t>verified_scope</t>
+          <t>you_label</t>
         </is>
       </c>
       <c r="B324" s="11" t="inlineStr">
@@ -20144,32 +20144,32 @@
       </c>
       <c r="C324" s="11" t="inlineStr">
         <is>
-          <t>You can now discuss their own records, take documents and file a dispute. Never a deposit, withdrawal or transfer.</t>
+          <t>You</t>
         </is>
       </c>
       <c r="D324" s="12" t="inlineStr">
         <is>
-          <t>አሁን ስለ ራሳቸው መዝገቦች መወያየት፣ ሰነዶች መቀበልና ቅሬታ ማስመዝገብ ይችላሉ። በፍጹም ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም።</t>
+          <t>እርስዎ</t>
         </is>
       </c>
       <c r="E324" s="13" t="inlineStr">
         <is>
-          <t>Amma waa'ee galmee isaanii mari'achuu, sanadoota fudhachuu fi komii galmeessuu dandeessu. Gonkumaa kuusaa, baasii yookiin dabarsa hin jiru.</t>
+          <t>Isin</t>
         </is>
       </c>
       <c r="F324" s="12" t="inlineStr">
         <is>
-          <t>ሕጂ ብዛዕባ ናቶም መዝገባት ክትዘራረቡ፣ ሰነዳት ክትቅበሉን ጥርዓን ከተመዝግቡን ትኽእሉ። ፈጺሙ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን።</t>
+          <t>ንስኹም</t>
         </is>
       </c>
       <c r="G324" s="13" t="inlineStr">
         <is>
-          <t>Hadda waad kala hadli kartaa diiwaankooda, dukumiinti qaadan iyo cabasho diiwaangelin. Weligaa dhigasho, qaadis ama wareejin ma jirto.</t>
+          <t>Adiga</t>
         </is>
       </c>
       <c r="H324" s="13" t="inlineStr">
         <is>
-          <t>Sasa unaweza kuzungumzia rekodi zao wenyewe, kuchukua nyaraka na kuwasilisha mgogoro. Kamwe amana, uondoaji au uhamishaji.</t>
+          <t>Wewe</t>
         </is>
       </c>
       <c r="I324" s="14" t="inlineStr"/>
@@ -20177,7 +20177,7 @@
     <row r="325" ht="44" customHeight="1">
       <c r="A325" s="11" t="inlineStr">
         <is>
-          <t>establish_who_they_are</t>
+          <t>assistant_label</t>
         </is>
       </c>
       <c r="B325" s="11" t="inlineStr">
@@ -20187,32 +20187,32 @@
       </c>
       <c r="C325" s="11" t="inlineStr">
         <is>
-          <t>Establish who they are — either one</t>
+          <t>Assistant</t>
         </is>
       </c>
       <c r="D325" s="12" t="inlineStr">
         <is>
-          <t>ማንነታቸውን ያረጋግጡ — አንዱ ይበቃል</t>
+          <t>ረዳት</t>
         </is>
       </c>
       <c r="E325" s="13" t="inlineStr">
         <is>
-          <t>Eenyummaa isaanii mirkaneessaa — tokko ni ga'a</t>
+          <t>Gargaaraa</t>
         </is>
       </c>
       <c r="F325" s="12" t="inlineStr">
         <is>
-          <t>መንነቶም ኣረጋግጹ — ሓደ እኹል እዩ</t>
+          <t>ሓጋዚ</t>
         </is>
       </c>
       <c r="G325" s="13" t="inlineStr">
         <is>
-          <t>Ogow cidda ay yihiin — mid kasta</t>
+          <t>Kaaliye</t>
         </is>
       </c>
       <c r="H325" s="13" t="inlineStr">
         <is>
-          <t>Thibitisha ni nani — mojawapo</t>
+          <t>Msaidizi</t>
         </is>
       </c>
       <c r="I325" s="14" t="inlineStr"/>
@@ -20220,7 +20220,7 @@
     <row r="326" ht="44" customHeight="1">
       <c r="A326" s="11" t="inlineStr">
         <is>
-          <t>chk_id_document</t>
+          <t>conversation_unavailable</t>
         </is>
       </c>
       <c r="B326" s="11" t="inlineStr">
@@ -20230,32 +20230,32 @@
       </c>
       <c r="C326" s="11" t="inlineStr">
         <is>
-          <t>Fayda ID shown and matches the account name</t>
+          <t>Conversation unavailable.</t>
         </is>
       </c>
       <c r="D326" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ መታወቂያ ታይቷል እና ከሂሳቡ ስም ጋር ይዛመዳል</t>
+          <t>ውይይቱ አይገኝም።</t>
         </is>
       </c>
       <c r="E326" s="13" t="inlineStr">
         <is>
-          <t>Waraqaan eenyummaa Fayda agarsiifame maqaa herregaa waliin walsimeera</t>
+          <t>Mariin hin argamu.</t>
         </is>
       </c>
       <c r="F326" s="12" t="inlineStr">
         <is>
-          <t>መንነት ፋይዳ ተራእዩን ምስ ስም ሕሳብ ይሰማማዕን</t>
+          <t>እቲ ዝርርብ ኣይርከብን።</t>
         </is>
       </c>
       <c r="G326" s="13" t="inlineStr">
         <is>
-          <t>Aqoonsiga Fayda waa la tusay wuxuuna la mid yahay magaca xisaabta</t>
+          <t>Wadahadalka lama heli karo.</t>
         </is>
       </c>
       <c r="H326" s="13" t="inlineStr">
         <is>
-          <t>Kitambulisho cha Fayda kimeonyeshwa na kinalingana na jina la akaunti</t>
+          <t>Mazungumzo hayapatikani.</t>
         </is>
       </c>
       <c r="I326" s="14" t="inlineStr"/>
@@ -20263,7 +20263,7 @@
     <row r="327" ht="44" customHeight="1">
       <c r="A327" s="11" t="inlineStr">
         <is>
-          <t>chk_fayda_matched</t>
+          <t>unmute</t>
         </is>
       </c>
       <c r="B327" s="11" t="inlineStr">
@@ -20273,32 +20273,32 @@
       </c>
       <c r="C327" s="11" t="inlineStr">
         <is>
-          <t>Fayda number matches the account record</t>
+          <t>Unmute</t>
         </is>
       </c>
       <c r="D327" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ ቁጥር ከሂሳቡ መዝገብ ጋር ይዛመዳል</t>
+          <t>ድምፅ አብራ</t>
         </is>
       </c>
       <c r="E327" s="13" t="inlineStr">
         <is>
-          <t>Lakkoofsi Fayda galmee herregaa waliin walsimeera</t>
+          <t>Sagalee banaa</t>
         </is>
       </c>
       <c r="F327" s="12" t="inlineStr">
         <is>
-          <t>ቁጽሪ ፋይዳ ምስ መዝገብ ሕሳብ ይሰማማዕ</t>
+          <t>ድምጺ ኣብርህ</t>
         </is>
       </c>
       <c r="G327" s="13" t="inlineStr">
         <is>
-          <t>Lambarka Fayda wuxuu la mid yahay diiwaanka xisaabta</t>
+          <t>Codka fur</t>
         </is>
       </c>
       <c r="H327" s="13" t="inlineStr">
         <is>
-          <t>Namba ya Fayda inalingana na rekodi ya akaunti</t>
+          <t>Rudisha Sauti</t>
         </is>
       </c>
       <c r="I327" s="14" t="inlineStr"/>
@@ -20306,7 +20306,7 @@
     <row r="328" ht="44" customHeight="1">
       <c r="A328" s="11" t="inlineStr">
         <is>
-          <t>chk_fayda_matched_note</t>
+          <t>session_summary_prompt</t>
         </is>
       </c>
       <c r="B328" s="11" t="inlineStr">
@@ -20316,32 +20316,32 @@
       </c>
       <c r="C328" s="11" t="inlineStr">
         <is>
-          <t>on your own screen — works on an audio call</t>
+          <t>What did this session cover? (optional)</t>
         </is>
       </c>
       <c r="D328" s="12" t="inlineStr">
         <is>
-          <t>በራስዎ ስክሪን ላይ — በድምፅ ጥሪም ይሠራል</t>
+          <t>ይህ ክፍለ-ጊዜ ምን ሸፈነ? (አማራጭ)</t>
         </is>
       </c>
       <c r="E328" s="13" t="inlineStr">
         <is>
-          <t>iskiriinii keessan irratti — bilbila sagalee irrattis ni hojjeta</t>
+          <t>Sessioniin kun maal haguuge? (filannoo)</t>
         </is>
       </c>
       <c r="F328" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ናትኩም መርአዪ — ኣብ ናይ ድምጺ ጻውዒት እውን ይሰርሕ</t>
+          <t>እዚ ክፍለ-ግዜ እንታይ ሸፈነ? (ኣማራጺ)</t>
         </is>
       </c>
       <c r="G328" s="13" t="inlineStr">
         <is>
-          <t>shaashaddaada — wicitaan cod ahna wuu ka shaqeeyaa</t>
+          <t>Kalfadhigan muxuu daboolay? (ikhtiyaari)</t>
         </is>
       </c>
       <c r="H328" s="13" t="inlineStr">
         <is>
-          <t>kwenye skrini yako mwenyewe — inafanya kazi kwenye simu ya sauti</t>
+          <t>Kikao hiki kilihusu nini? (si lazima)</t>
         </is>
       </c>
       <c r="I328" s="14" t="inlineStr"/>
@@ -20349,7 +20349,7 @@
     <row r="329" ht="44" customHeight="1">
       <c r="A329" s="11" t="inlineStr">
         <is>
-          <t>chk_id_photo</t>
+          <t>customer_ended_call</t>
         </is>
       </c>
       <c r="B329" s="11" t="inlineStr">
@@ -20359,32 +20359,32 @@
       </c>
       <c r="C329" s="11" t="inlineStr">
         <is>
-          <t>Photo on the ID matches the person on the call</t>
+          <t>The customer ended the call</t>
         </is>
       </c>
       <c r="D329" s="12" t="inlineStr">
         <is>
-          <t>በመታወቂያው ላይ ያለው ፎቶ ከጥሪው ላይ ካለው ሰው ጋር ይዛመዳል</t>
+          <t>ደንበኛው ጥሪውን አቋረጠ</t>
         </is>
       </c>
       <c r="E329" s="13" t="inlineStr">
         <is>
-          <t>Suuraan waraqaa eenyummaa irra jiru nama bilbila irra jiru waliin walsimeera</t>
+          <t>Maamilaan bilbila xumure</t>
         </is>
       </c>
       <c r="F329" s="12" t="inlineStr">
         <is>
-          <t>እቲ ኣብ መንነት ዘሎ ስእሊ ምስቲ ኣብ ጻውዒት ዘሎ ሰብ ይሰማማዕ</t>
+          <t>እቲ ዓሚል ነቲ ጻውዒት ወዲኡዎ</t>
         </is>
       </c>
       <c r="G329" s="13" t="inlineStr">
         <is>
-          <t>Sawirka aqoonsiga wuxuu la mid yahay qofka wicitaanka ku jira</t>
+          <t>Macmiilku wicitaanka wuu joojiyay</t>
         </is>
       </c>
       <c r="H329" s="13" t="inlineStr">
         <is>
-          <t>Picha kwenye kitambulisho inalingana na mtu aliye kwenye simu</t>
+          <t>Mteja alimaliza simu</t>
         </is>
       </c>
       <c r="I329" s="14" t="inlineStr"/>
@@ -20392,7 +20392,7 @@
     <row r="330" ht="44" customHeight="1">
       <c r="A330" s="11" t="inlineStr">
         <is>
-          <t>chk_video_only</t>
+          <t>verified_scope</t>
         </is>
       </c>
       <c r="B330" s="11" t="inlineStr">
@@ -20402,32 +20402,32 @@
       </c>
       <c r="C330" s="11" t="inlineStr">
         <is>
-          <t>video only</t>
+          <t>You can now discuss their own records, take documents and file a dispute. Never a deposit, withdrawal or transfer.</t>
         </is>
       </c>
       <c r="D330" s="12" t="inlineStr">
         <is>
-          <t>ቪዲዮ ብቻ</t>
+          <t>አሁን ስለ ራሳቸው መዝገቦች መወያየት፣ ሰነዶች መቀበልና ቅሬታ ማስመዝገብ ይችላሉ። በፍጹም ተቀማጭ፣ ወጪ ወይም ማስተላለፍ የለም።</t>
         </is>
       </c>
       <c r="E330" s="13" t="inlineStr">
         <is>
-          <t>viidiyoo qofa</t>
+          <t>Amma waa'ee galmee isaanii mari'achuu, sanadoota fudhachuu fi komii galmeessuu dandeessu. Gonkumaa kuusaa, baasii yookiin dabarsa hin jiru.</t>
         </is>
       </c>
       <c r="F330" s="12" t="inlineStr">
         <is>
-          <t>ቪድዮ ጥራይ</t>
+          <t>ሕጂ ብዛዕባ ናቶም መዝገባት ክትዘራረቡ፣ ሰነዳት ክትቅበሉን ጥርዓን ከተመዝግቡን ትኽእሉ። ፈጺሙ መቐመጢ፣ ወጻኢ ወይ ምትሕልላፍ የለን።</t>
         </is>
       </c>
       <c r="G330" s="13" t="inlineStr">
         <is>
-          <t>fiidyow oo kaliya</t>
+          <t>Hadda waad kala hadli kartaa diiwaankooda, dukumiinti qaadan iyo cabasho diiwaangelin. Weligaa dhigasho, qaadis ama wareejin ma jirto.</t>
         </is>
       </c>
       <c r="H330" s="13" t="inlineStr">
         <is>
-          <t>video pekee</t>
+          <t>Sasa unaweza kuzungumzia rekodi zao wenyewe, kuchukua nyaraka na kuwasilisha mgogoro. Kamwe amana, uondoaji au uhamishaji.</t>
         </is>
       </c>
       <c r="I330" s="14" t="inlineStr"/>
@@ -20435,7 +20435,7 @@
     <row r="331" ht="44" customHeight="1">
       <c r="A331" s="11" t="inlineStr">
         <is>
-          <t>confirm_account_theirs</t>
+          <t>establish_who_they_are</t>
         </is>
       </c>
       <c r="B331" s="11" t="inlineStr">
@@ -20445,32 +20445,32 @@
       </c>
       <c r="C331" s="11" t="inlineStr">
         <is>
-          <t>And confirm the account is theirs</t>
+          <t>Establish who they are — either one</t>
         </is>
       </c>
       <c r="D331" s="12" t="inlineStr">
         <is>
-          <t>እና ሂሳቡ የእነሱ መሆኑን ያረጋግጡ</t>
+          <t>ማንነታቸውን ያረጋግጡ — አንዱ ይበቃል</t>
         </is>
       </c>
       <c r="E331" s="13" t="inlineStr">
         <is>
-          <t>Akkasumas herregni kan isaanii ta'uu mirkaneessaa</t>
+          <t>Eenyummaa isaanii mirkaneessaa — tokko ni ga'a</t>
         </is>
       </c>
       <c r="F331" s="12" t="inlineStr">
         <is>
-          <t>ከምኡ'ውን እቲ ሕሳብ ናቶም ምዃኑ ኣረጋግጹ</t>
+          <t>መንነቶም ኣረጋግጹ — ሓደ እኹል እዩ</t>
         </is>
       </c>
       <c r="G331" s="13" t="inlineStr">
         <is>
-          <t>Xaqiiji in xisaabtu tahay tooda</t>
+          <t>Ogow cidda ay yihiin — mid kasta</t>
         </is>
       </c>
       <c r="H331" s="13" t="inlineStr">
         <is>
-          <t>Na thibitisha akaunti ni yao</t>
+          <t>Thibitisha ni nani — mojawapo</t>
         </is>
       </c>
       <c r="I331" s="14" t="inlineStr"/>
@@ -20478,7 +20478,7 @@
     <row r="332" ht="44" customHeight="1">
       <c r="A332" s="11" t="inlineStr">
         <is>
-          <t>confirm_identity</t>
+          <t>chk_id_document</t>
         </is>
       </c>
       <c r="B332" s="11" t="inlineStr">
@@ -20488,32 +20488,32 @@
       </c>
       <c r="C332" s="11" t="inlineStr">
         <is>
-          <t>Confirm identity</t>
+          <t>Fayda ID shown and matches the account name</t>
         </is>
       </c>
       <c r="D332" s="12" t="inlineStr">
         <is>
-          <t>ማንነት አረጋግጥ</t>
+          <t>የፋይዳ መታወቂያ ታይቷል እና ከሂሳቡ ስም ጋር ይዛመዳል</t>
         </is>
       </c>
       <c r="E332" s="13" t="inlineStr">
         <is>
-          <t>Eenyummaa mirkaneessi</t>
+          <t>Waraqaan eenyummaa Fayda agarsiifame maqaa herregaa waliin walsimeera</t>
         </is>
       </c>
       <c r="F332" s="12" t="inlineStr">
         <is>
-          <t>መንነት ኣረጋግጽ</t>
+          <t>መንነት ፋይዳ ተራእዩን ምስ ስም ሕሳብ ይሰማማዕን</t>
         </is>
       </c>
       <c r="G332" s="13" t="inlineStr">
         <is>
-          <t>Xaqiiji aqoonsiga</t>
+          <t>Aqoonsiga Fayda waa la tusay wuxuuna la mid yahay magaca xisaabta</t>
         </is>
       </c>
       <c r="H332" s="13" t="inlineStr">
         <is>
-          <t>Thibitisha Utambulisho</t>
+          <t>Kitambulisho cha Fayda kimeonyeshwa na kinalingana na jina la akaunti</t>
         </is>
       </c>
       <c r="I332" s="14" t="inlineStr"/>
@@ -20521,7 +20521,7 @@
     <row r="333" ht="44" customHeight="1">
       <c r="A333" s="11" t="inlineStr">
         <is>
-          <t>unverified_scope</t>
+          <t>chk_fayda_matched</t>
         </is>
       </c>
       <c r="B333" s="11" t="inlineStr">
@@ -20531,32 +20531,32 @@
       </c>
       <c r="C333" s="11" t="inlineStr">
         <is>
-          <t>Until this is done you can only give general guidance — products, eligibility and how to apply.</t>
+          <t>Fayda number matches the account record</t>
         </is>
       </c>
       <c r="D333" s="12" t="inlineStr">
         <is>
-          <t>ይህ እስኪከናወን ድረስ አጠቃላይ መመሪያ ብቻ መስጠት ይችላሉ — ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል።</t>
+          <t>የፋይዳ ቁጥር ከሂሳቡ መዝገብ ጋር ይዛመዳል</t>
         </is>
       </c>
       <c r="E333" s="13" t="inlineStr">
         <is>
-          <t>Hanga kun raawwatutti qajeelfama waliigalaa qofa kennuu dandeessu — oomishaalee, ulaagaa fi akkaataa itti iyyatan.</t>
+          <t>Lakkoofsi Fayda galmee herregaa waliin walsimeera</t>
         </is>
       </c>
       <c r="F333" s="12" t="inlineStr">
         <is>
-          <t>እዚ ክሳብ ዝፍጸም ሓፈሻዊ መምርሒ ጥራይ ክትህቡ ትኽእሉ — ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን።</t>
+          <t>ቁጽሪ ፋይዳ ምስ መዝገብ ሕሳብ ይሰማማዕ</t>
         </is>
       </c>
       <c r="G333" s="13" t="inlineStr">
         <is>
-          <t>Ilaa tan la sameeyo waxaad kaliya bixin kartaa hagaajin guud — alaabta, u-qalmitaanka iyo sida loo codsado.</t>
+          <t>Lambarka Fayda wuxuu la mid yahay diiwaanka xisaabta</t>
         </is>
       </c>
       <c r="H333" s="13" t="inlineStr">
         <is>
-          <t>Hadi hili litakapofanyika unaweza tu kutoa mwongozo wa jumla — bidhaa, sifa za kustahiki na jinsi ya kuomba.</t>
+          <t>Namba ya Fayda inalingana na rekodi ya akaunti</t>
         </is>
       </c>
       <c r="I333" s="14" t="inlineStr"/>
@@ -20564,7 +20564,7 @@
     <row r="334" ht="44" customHeight="1">
       <c r="A334" s="11" t="inlineStr">
         <is>
-          <t>fayda_number_required</t>
+          <t>chk_fayda_matched_note</t>
         </is>
       </c>
       <c r="B334" s="11" t="inlineStr">
@@ -20574,32 +20574,32 @@
       </c>
       <c r="C334" s="11" t="inlineStr">
         <is>
-          <t>Fayda number (required — it is what the record keeps)</t>
+          <t>on your own screen — works on an audio call</t>
         </is>
       </c>
       <c r="D334" s="12" t="inlineStr">
         <is>
-          <t>የፋይዳ ቁጥር (ያስፈልጋል — መዝገቡ የሚይዘው ይህ ነው)</t>
+          <t>በራስዎ ስክሪን ላይ — በድምፅ ጥሪም ይሠራል</t>
         </is>
       </c>
       <c r="E334" s="13" t="inlineStr">
         <is>
-          <t>Lakkoofsa Fayda (barbaachisaa — kan galmeen qabatu isa kana)</t>
+          <t>iskiriinii keessan irratti — bilbila sagalee irrattis ni hojjeta</t>
         </is>
       </c>
       <c r="F334" s="12" t="inlineStr">
         <is>
-          <t>ቁጽሪ ፋይዳ (የድሊ — እቲ መዝገብ ዝሕዞ እዚ እዩ)</t>
+          <t>ኣብ ናትኩም መርአዪ — ኣብ ናይ ድምጺ ጻውዒት እውን ይሰርሕ</t>
         </is>
       </c>
       <c r="G334" s="13" t="inlineStr">
         <is>
-          <t>Lambarka Fayda (loo baahan yahay — waa waxa diiwaanku hayo)</t>
+          <t>shaashaddaada — wicitaan cod ahna wuu ka shaqeeyaa</t>
         </is>
       </c>
       <c r="H334" s="13" t="inlineStr">
         <is>
-          <t>Namba ya Fayda (inahitajika — ndiyo inayowekwa kwenye rekodi)</t>
+          <t>kwenye skrini yako mwenyewe — inafanya kazi kwenye simu ya sauti</t>
         </is>
       </c>
       <c r="I334" s="14" t="inlineStr"/>
@@ -20607,7 +20607,7 @@
     <row r="335" ht="44" customHeight="1">
       <c r="A335" s="11" t="inlineStr">
         <is>
-          <t>download_for_translation</t>
+          <t>chk_id_photo</t>
         </is>
       </c>
       <c r="B335" s="11" t="inlineStr">
@@ -20617,32 +20617,32 @@
       </c>
       <c r="C335" s="11" t="inlineStr">
         <is>
-          <t>Download for translation</t>
+          <t>Photo on the ID matches the person on the call</t>
         </is>
       </c>
       <c r="D335" s="12" t="inlineStr">
         <is>
-          <t>ለትርጉም አውርድ</t>
+          <t>በመታወቂያው ላይ ያለው ፎቶ ከጥሪው ላይ ካለው ሰው ጋር ይዛመዳል</t>
         </is>
       </c>
       <c r="E335" s="13" t="inlineStr">
         <is>
-          <t>Hiikkaaf buufadhu</t>
+          <t>Suuraan waraqaa eenyummaa irra jiru nama bilbila irra jiru waliin walsimeera</t>
         </is>
       </c>
       <c r="F335" s="12" t="inlineStr">
         <is>
-          <t>ንትርጉም ኣውርድ</t>
+          <t>እቲ ኣብ መንነት ዘሎ ስእሊ ምስቲ ኣብ ጻውዒት ዘሎ ሰብ ይሰማማዕ</t>
         </is>
       </c>
       <c r="G335" s="13" t="inlineStr">
         <is>
-          <t>Soo dejiso turjumaadda</t>
+          <t>Sawirka aqoonsiga wuxuu la mid yahay qofka wicitaanka ku jira</t>
         </is>
       </c>
       <c r="H335" s="13" t="inlineStr">
         <is>
-          <t>Pakua kwa Tafsiri</t>
+          <t>Picha kwenye kitambulisho inalingana na mtu aliye kwenye simu</t>
         </is>
       </c>
       <c r="I335" s="14" t="inlineStr"/>
@@ -20650,48 +20650,306 @@
     <row r="336" ht="44" customHeight="1">
       <c r="A336" s="11" t="inlineStr">
         <is>
+          <t>chk_video_only</t>
+        </is>
+      </c>
+      <c r="B336" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C336" s="11" t="inlineStr">
+        <is>
+          <t>video only</t>
+        </is>
+      </c>
+      <c r="D336" s="12" t="inlineStr">
+        <is>
+          <t>ቪዲዮ ብቻ</t>
+        </is>
+      </c>
+      <c r="E336" s="13" t="inlineStr">
+        <is>
+          <t>viidiyoo qofa</t>
+        </is>
+      </c>
+      <c r="F336" s="12" t="inlineStr">
+        <is>
+          <t>ቪድዮ ጥራይ</t>
+        </is>
+      </c>
+      <c r="G336" s="13" t="inlineStr">
+        <is>
+          <t>fiidyow oo kaliya</t>
+        </is>
+      </c>
+      <c r="H336" s="13" t="inlineStr">
+        <is>
+          <t>video pekee</t>
+        </is>
+      </c>
+      <c r="I336" s="14" t="inlineStr"/>
+    </row>
+    <row r="337" ht="44" customHeight="1">
+      <c r="A337" s="11" t="inlineStr">
+        <is>
+          <t>confirm_account_theirs</t>
+        </is>
+      </c>
+      <c r="B337" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C337" s="11" t="inlineStr">
+        <is>
+          <t>And confirm the account is theirs</t>
+        </is>
+      </c>
+      <c r="D337" s="12" t="inlineStr">
+        <is>
+          <t>እና ሂሳቡ የእነሱ መሆኑን ያረጋግጡ</t>
+        </is>
+      </c>
+      <c r="E337" s="13" t="inlineStr">
+        <is>
+          <t>Akkasumas herregni kan isaanii ta'uu mirkaneessaa</t>
+        </is>
+      </c>
+      <c r="F337" s="12" t="inlineStr">
+        <is>
+          <t>ከምኡ'ውን እቲ ሕሳብ ናቶም ምዃኑ ኣረጋግጹ</t>
+        </is>
+      </c>
+      <c r="G337" s="13" t="inlineStr">
+        <is>
+          <t>Xaqiiji in xisaabtu tahay tooda</t>
+        </is>
+      </c>
+      <c r="H337" s="13" t="inlineStr">
+        <is>
+          <t>Na thibitisha akaunti ni yao</t>
+        </is>
+      </c>
+      <c r="I337" s="14" t="inlineStr"/>
+    </row>
+    <row r="338" ht="44" customHeight="1">
+      <c r="A338" s="11" t="inlineStr">
+        <is>
+          <t>confirm_identity</t>
+        </is>
+      </c>
+      <c r="B338" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C338" s="11" t="inlineStr">
+        <is>
+          <t>Confirm identity</t>
+        </is>
+      </c>
+      <c r="D338" s="12" t="inlineStr">
+        <is>
+          <t>ማንነት አረጋግጥ</t>
+        </is>
+      </c>
+      <c r="E338" s="13" t="inlineStr">
+        <is>
+          <t>Eenyummaa mirkaneessi</t>
+        </is>
+      </c>
+      <c r="F338" s="12" t="inlineStr">
+        <is>
+          <t>መንነት ኣረጋግጽ</t>
+        </is>
+      </c>
+      <c r="G338" s="13" t="inlineStr">
+        <is>
+          <t>Xaqiiji aqoonsiga</t>
+        </is>
+      </c>
+      <c r="H338" s="13" t="inlineStr">
+        <is>
+          <t>Thibitisha Utambulisho</t>
+        </is>
+      </c>
+      <c r="I338" s="14" t="inlineStr"/>
+    </row>
+    <row r="339" ht="44" customHeight="1">
+      <c r="A339" s="11" t="inlineStr">
+        <is>
+          <t>unverified_scope</t>
+        </is>
+      </c>
+      <c r="B339" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C339" s="11" t="inlineStr">
+        <is>
+          <t>Until this is done you can only give general guidance — products, eligibility and how to apply.</t>
+        </is>
+      </c>
+      <c r="D339" s="12" t="inlineStr">
+        <is>
+          <t>ይህ እስኪከናወን ድረስ አጠቃላይ መመሪያ ብቻ መስጠት ይችላሉ — ምርቶች፣ ብቁነትና እንዴት ማመልከት እንደሚቻል።</t>
+        </is>
+      </c>
+      <c r="E339" s="13" t="inlineStr">
+        <is>
+          <t>Hanga kun raawwatutti qajeelfama waliigalaa qofa kennuu dandeessu — oomishaalee, ulaagaa fi akkaataa itti iyyatan.</t>
+        </is>
+      </c>
+      <c r="F339" s="12" t="inlineStr">
+        <is>
+          <t>እዚ ክሳብ ዝፍጸም ሓፈሻዊ መምርሒ ጥራይ ክትህቡ ትኽእሉ — ኣቕሑ፣ ብቕዓትን ከመይ ጌርካ ከም እትሓትትን።</t>
+        </is>
+      </c>
+      <c r="G339" s="13" t="inlineStr">
+        <is>
+          <t>Ilaa tan la sameeyo waxaad kaliya bixin kartaa hagaajin guud — alaabta, u-qalmitaanka iyo sida loo codsado.</t>
+        </is>
+      </c>
+      <c r="H339" s="13" t="inlineStr">
+        <is>
+          <t>Hadi hili litakapofanyika unaweza tu kutoa mwongozo wa jumla — bidhaa, sifa za kustahiki na jinsi ya kuomba.</t>
+        </is>
+      </c>
+      <c r="I339" s="14" t="inlineStr"/>
+    </row>
+    <row r="340" ht="44" customHeight="1">
+      <c r="A340" s="11" t="inlineStr">
+        <is>
+          <t>fayda_number_required</t>
+        </is>
+      </c>
+      <c r="B340" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C340" s="11" t="inlineStr">
+        <is>
+          <t>Fayda number (required — it is what the record keeps)</t>
+        </is>
+      </c>
+      <c r="D340" s="12" t="inlineStr">
+        <is>
+          <t>የፋይዳ ቁጥር (ያስፈልጋል — መዝገቡ የሚይዘው ይህ ነው)</t>
+        </is>
+      </c>
+      <c r="E340" s="13" t="inlineStr">
+        <is>
+          <t>Lakkoofsa Fayda (barbaachisaa — kan galmeen qabatu isa kana)</t>
+        </is>
+      </c>
+      <c r="F340" s="12" t="inlineStr">
+        <is>
+          <t>ቁጽሪ ፋይዳ (የድሊ — እቲ መዝገብ ዝሕዞ እዚ እዩ)</t>
+        </is>
+      </c>
+      <c r="G340" s="13" t="inlineStr">
+        <is>
+          <t>Lambarka Fayda (loo baahan yahay — waa waxa diiwaanku hayo)</t>
+        </is>
+      </c>
+      <c r="H340" s="13" t="inlineStr">
+        <is>
+          <t>Namba ya Fayda (inahitajika — ndiyo inayowekwa kwenye rekodi)</t>
+        </is>
+      </c>
+      <c r="I340" s="14" t="inlineStr"/>
+    </row>
+    <row r="341" ht="44" customHeight="1">
+      <c r="A341" s="11" t="inlineStr">
+        <is>
+          <t>download_for_translation</t>
+        </is>
+      </c>
+      <c r="B341" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C341" s="11" t="inlineStr">
+        <is>
+          <t>Download for translation</t>
+        </is>
+      </c>
+      <c r="D341" s="12" t="inlineStr">
+        <is>
+          <t>ለትርጉም አውርድ</t>
+        </is>
+      </c>
+      <c r="E341" s="13" t="inlineStr">
+        <is>
+          <t>Hiikkaaf buufadhu</t>
+        </is>
+      </c>
+      <c r="F341" s="12" t="inlineStr">
+        <is>
+          <t>ንትርጉም ኣውርድ</t>
+        </is>
+      </c>
+      <c r="G341" s="13" t="inlineStr">
+        <is>
+          <t>Soo dejiso turjumaadda</t>
+        </is>
+      </c>
+      <c r="H341" s="13" t="inlineStr">
+        <is>
+          <t>Pakua kwa Tafsiri</t>
+        </is>
+      </c>
+      <c r="I341" s="14" t="inlineStr"/>
+    </row>
+    <row r="342" ht="44" customHeight="1">
+      <c r="A342" s="11" t="inlineStr">
+        <is>
           <t>nothing_to_download</t>
         </is>
       </c>
-      <c r="B336" s="11" t="inlineStr">
-        <is>
-          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
-        </is>
-      </c>
-      <c r="C336" s="11" t="inlineStr">
+      <c r="B342" s="11" t="inlineStr">
+        <is>
+          <t>Read by bank staff, not customers. Keep it short — it has to fit the same space as the English. Use the words your branch staff already use.</t>
+        </is>
+      </c>
+      <c r="C342" s="11" t="inlineStr">
         <is>
           <t>No approved answers to download yet.</t>
         </is>
       </c>
-      <c r="D336" s="12" t="inlineStr">
+      <c r="D342" s="12" t="inlineStr">
         <is>
           <t>እስካሁን የሚወርድ የተፈቀደ መልስ የለም።</t>
         </is>
       </c>
-      <c r="E336" s="13" t="inlineStr">
+      <c r="E342" s="13" t="inlineStr">
         <is>
           <t>Hanga ammaatti deebiin mirkanaa'e buufamu hin jiru.</t>
         </is>
       </c>
-      <c r="F336" s="12" t="inlineStr">
+      <c r="F342" s="12" t="inlineStr">
         <is>
           <t>ክሳብ ሕጂ ዝወርድ ዝጸደቐ መልሲ የለን።</t>
         </is>
       </c>
-      <c r="G336" s="13" t="inlineStr">
+      <c r="G342" s="13" t="inlineStr">
         <is>
           <t>Weli ma jiraan jawaabo la ansixiyay oo la soo dejiyo.</t>
         </is>
       </c>
-      <c r="H336" s="13" t="inlineStr">
+      <c r="H342" s="13" t="inlineStr">
         <is>
           <t>Hakuna majibu yaliyoidhinishwa ya kupakua bado.</t>
         </is>
       </c>
-      <c r="I336" s="14" t="inlineStr"/>
+      <c r="I342" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I336"/>
+  <autoFilter ref="A1:I342"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/review/Olink_Bank_Assist_language_review.xlsx
+++ b/review/Olink_Bank_Assist_language_review.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1. What the assistant says'!$A$1:$I$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2. What it understands'!$A$1:$E$91</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3. Buttons customers see'!$A$1:$I$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$I$342</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. The staff panel'!$A$1:$I$358</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -752,7 +752,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>413 strings in 5 languages</t>
+          <t>429 strings in 5 languages</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I342"/>
+  <dimension ref="A1:I358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -16178,7 +16178,7 @@
     <row r="232" ht="44" customHeight="1">
       <c r="A232" s="11" t="inlineStr">
         <is>
-          <t>action_document_created</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="B232" s="11" t="inlineStr">
@@ -16188,32 +16188,32 @@
       </c>
       <c r="C232" s="11" t="inlineStr">
         <is>
-          <t>added an article</t>
+          <t>Delete</t>
         </is>
       </c>
       <c r="D232" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ጨምሯል</t>
+          <t>ሰርዝ</t>
         </is>
       </c>
       <c r="E232" s="13" t="inlineStr">
         <is>
-          <t>barruu dabale</t>
+          <t>Haqi</t>
         </is>
       </c>
       <c r="F232" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ወሲኹ</t>
+          <t>ሰርዝ</t>
         </is>
       </c>
       <c r="G232" s="13" t="inlineStr">
         <is>
-          <t>maqaal ku daray</t>
+          <t>Tirtir</t>
         </is>
       </c>
       <c r="H232" s="13" t="inlineStr">
         <is>
-          <t>aliongeza makala</t>
+          <t>Futa</t>
         </is>
       </c>
       <c r="I232" s="14" t="inlineStr"/>
@@ -16221,7 +16221,7 @@
     <row r="233" ht="44" customHeight="1">
       <c r="A233" s="11" t="inlineStr">
         <is>
-          <t>action_document_updated</t>
+          <t>confirm_delete_answer</t>
         </is>
       </c>
       <c r="B233" s="11" t="inlineStr">
@@ -16231,32 +16231,32 @@
       </c>
       <c r="C233" s="11" t="inlineStr">
         <is>
-          <t>edited an article</t>
+          <t>Delete this answer? The question goes back to the assistant.</t>
         </is>
       </c>
       <c r="D233" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ አርሟል</t>
+          <t>ይህን መልስ መሰረዝ ይፈልጋሉ? ጥያቄው ወደ ረዳቱ ይመለሳል።</t>
         </is>
       </c>
       <c r="E233" s="13" t="inlineStr">
         <is>
-          <t>barruu gulaale</t>
+          <t>Deebii kana haquu barbaadduu? Gaaffiin gara gargaaraatti deebi'a.</t>
         </is>
       </c>
       <c r="F233" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ኣርሚዑ</t>
+          <t>ነዚ መልሲ ክትሰርዞ ትደሊ ዲኻ? እቲ ሕቶ ናብቲ ሓጋዚ ይምለስ።</t>
         </is>
       </c>
       <c r="G233" s="13" t="inlineStr">
         <is>
-          <t>maqaal wax ka beddelay</t>
+          <t>Ma tirtirtaa jawaabtan? Su'aashu waxay ku noqonaysaa kaaliyaha.</t>
         </is>
       </c>
       <c r="H233" s="13" t="inlineStr">
         <is>
-          <t>alihariri makala</t>
+          <t>Ufute jibu hili? Swali linarudi kwa msaidizi.</t>
         </is>
       </c>
       <c r="I233" s="14" t="inlineStr"/>
@@ -16264,7 +16264,7 @@
     <row r="234" ht="44" customHeight="1">
       <c r="A234" s="11" t="inlineStr">
         <is>
-          <t>action_document_deleted</t>
+          <t>confirm_delete_article</t>
         </is>
       </c>
       <c r="B234" s="11" t="inlineStr">
@@ -16274,32 +16274,32 @@
       </c>
       <c r="C234" s="11" t="inlineStr">
         <is>
-          <t>deleted an article</t>
+          <t>Delete this article? The assistant will stop using it.</t>
         </is>
       </c>
       <c r="D234" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ሰርዟል</t>
+          <t>ይህን ጽሑፍ መሰረዝ ይፈልጋሉ? ረዳቱ መጠቀሙን ያቆማል።</t>
         </is>
       </c>
       <c r="E234" s="13" t="inlineStr">
         <is>
-          <t>barruu haqe</t>
+          <t>Barreeffama kana haquu barbaadduu? Gargaaraan itti fayyadamuu ni dhaaba.</t>
         </is>
       </c>
       <c r="F234" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፍ ደምሲሱ</t>
+          <t>ነዚ ጽሑፍ ክትሰርዞ ትደሊ ዲኻ? እቲ ሓጋዚ ምጥቃም የቋርጽ።</t>
         </is>
       </c>
       <c r="G234" s="13" t="inlineStr">
         <is>
-          <t>maqaal tirtiray</t>
+          <t>Ma tirtirtaa maqaalkan? Kaaliyuhu wuu joojin doonaa isticmaalkiisa.</t>
         </is>
       </c>
       <c r="H234" s="13" t="inlineStr">
         <is>
-          <t>alifuta makala</t>
+          <t>Ufute makala hii? Msaidizi ataacha kuitumia.</t>
         </is>
       </c>
       <c r="I234" s="14" t="inlineStr"/>
@@ -16307,7 +16307,7 @@
     <row r="235" ht="44" customHeight="1">
       <c r="A235" s="11" t="inlineStr">
         <is>
-          <t>action_documents_bulk_imported</t>
+          <t>deleted</t>
         </is>
       </c>
       <c r="B235" s="11" t="inlineStr">
@@ -16317,32 +16317,32 @@
       </c>
       <c r="C235" s="11" t="inlineStr">
         <is>
-          <t>imported articles</t>
+          <t>Deleted</t>
         </is>
       </c>
       <c r="D235" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፎችን አስገብቷል</t>
+          <t>ተሰርዟል</t>
         </is>
       </c>
       <c r="E235" s="13" t="inlineStr">
         <is>
-          <t>barruulee galche</t>
+          <t>Haqameera</t>
         </is>
       </c>
       <c r="F235" s="12" t="inlineStr">
         <is>
-          <t>ጽሑፋት ኣእትዩ</t>
+          <t>ተሰሪዙ</t>
         </is>
       </c>
       <c r="G235" s="13" t="inlineStr">
         <is>
-          <t>maqaallo soo dhoofiyay</t>
+          <t>Waa la tirtiray</t>
         </is>
       </c>
       <c r="H235" s="13" t="inlineStr">
         <is>
-          <t>aliagiza makala</t>
+          <t>Imefutwa</t>
         </is>
       </c>
       <c r="I235" s="14" t="inlineStr"/>
@@ -16350,7 +16350,7 @@
     <row r="236" ht="44" customHeight="1">
       <c r="A236" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_closed</t>
+          <t>saved</t>
         </is>
       </c>
       <c r="B236" s="11" t="inlineStr">
@@ -16360,32 +16360,32 @@
       </c>
       <c r="C236" s="11" t="inlineStr">
         <is>
-          <t>closed an escalation</t>
+          <t>Saved</t>
         </is>
       </c>
       <c r="D236" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ ዘግቷል</t>
+          <t>ተቀምጧል</t>
         </is>
       </c>
       <c r="E236" s="13" t="inlineStr">
         <is>
-          <t>dhimma cufe</t>
+          <t>Kuufameera</t>
         </is>
       </c>
       <c r="F236" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ ዓጺዩ</t>
+          <t>ተዓቂቡ</t>
         </is>
       </c>
       <c r="G236" s="13" t="inlineStr">
         <is>
-          <t>arrin xiray</t>
+          <t>Waa la kaydiyay</t>
         </is>
       </c>
       <c r="H236" s="13" t="inlineStr">
         <is>
-          <t>alifunga suala</t>
+          <t>Imehifadhiwa</t>
         </is>
       </c>
       <c r="I236" s="14" t="inlineStr"/>
@@ -16393,7 +16393,7 @@
     <row r="237" ht="44" customHeight="1">
       <c r="A237" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_reopened</t>
+          <t>escalation_closed</t>
         </is>
       </c>
       <c r="B237" s="11" t="inlineStr">
@@ -16403,32 +16403,32 @@
       </c>
       <c r="C237" s="11" t="inlineStr">
         <is>
-          <t>reopened an escalation</t>
+          <t>Escalation closed</t>
         </is>
       </c>
       <c r="D237" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ በድጋሚ ከፍቷል</t>
+          <t>የተላለፈው ጥያቄ ተዘግቷል</t>
         </is>
       </c>
       <c r="E237" s="13" t="inlineStr">
         <is>
-          <t>dhimma irra deebi'ee bane</t>
+          <t>Gaaffiin ol dabarfame cufameera</t>
         </is>
       </c>
       <c r="F237" s="12" t="inlineStr">
         <is>
-          <t>ጉዳይ ደጊሙ ከፊቱ</t>
+          <t>እቲ ዝተመሓላለፈ ሕቶ ተዓጽዩ</t>
         </is>
       </c>
       <c r="G237" s="13" t="inlineStr">
         <is>
-          <t>arrin dib u furay</t>
+          <t>Su'aashii la gudbiyay waa la xiray</t>
         </is>
       </c>
       <c r="H237" s="13" t="inlineStr">
         <is>
-          <t>alifungua tena suala</t>
+          <t>Suala lililoelekezwa limefungwa</t>
         </is>
       </c>
       <c r="I237" s="14" t="inlineStr"/>
@@ -16436,7 +16436,7 @@
     <row r="238" ht="44" customHeight="1">
       <c r="A238" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_webhook_connected</t>
+          <t>moved_to_desk</t>
         </is>
       </c>
       <c r="B238" s="11" t="inlineStr">
@@ -16446,32 +16446,32 @@
       </c>
       <c r="C238" s="11" t="inlineStr">
         <is>
-          <t>connected the escalation webhook</t>
+          <t>Moved to {desk}</t>
         </is>
       </c>
       <c r="D238" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ዌብሁክ አገናኝቷል</t>
+          <t>ወደ {desk} ተዛውሯል</t>
         </is>
       </c>
       <c r="E238" s="13" t="inlineStr">
         <is>
-          <t>webhook dabarsaa walqunnamsiise</t>
+          <t>Gara {desk} sochoofameera</t>
         </is>
       </c>
       <c r="F238" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ምትሕልላፍ ኣራኺቡ</t>
+          <t>ናብ {desk} ተሰጋጊሩ</t>
         </is>
       </c>
       <c r="G238" s="13" t="inlineStr">
         <is>
-          <t>ku xiray webhook-ga gudbinta</t>
+          <t>Waxaa loo raray {desk}</t>
         </is>
       </c>
       <c r="H238" s="13" t="inlineStr">
         <is>
-          <t>aliunganisha wavuti ya masuala</t>
+          <t>Imehamishiwa {desk}</t>
         </is>
       </c>
       <c r="I238" s="14" t="inlineStr"/>
@@ -16479,7 +16479,7 @@
     <row r="239" ht="44" customHeight="1">
       <c r="A239" s="11" t="inlineStr">
         <is>
-          <t>action_handoff_webhook_disconnected</t>
+          <t>nothing_ticked</t>
         </is>
       </c>
       <c r="B239" s="11" t="inlineStr">
@@ -16489,32 +16489,32 @@
       </c>
       <c r="C239" s="11" t="inlineStr">
         <is>
-          <t>disconnected the escalation webhook</t>
+          <t>Nothing ticked.</t>
         </is>
       </c>
       <c r="D239" s="12" t="inlineStr">
         <is>
-          <t>የማሸጋገሪያ ዌብሁክ አቋርጧል</t>
+          <t>ምንም አልተመረጠም።</t>
         </is>
       </c>
       <c r="E239" s="13" t="inlineStr">
         <is>
-          <t>webhook dabarsaa addaan kute</t>
+          <t>Wanti filatame hin jiru.</t>
         </is>
       </c>
       <c r="F239" s="12" t="inlineStr">
         <is>
-          <t>ዌብሁክ ምትሕልላፍ ቆሪጹ</t>
+          <t>ዋላ ሓደ ኣይተመርጸን።</t>
         </is>
       </c>
       <c r="G239" s="13" t="inlineStr">
         <is>
-          <t>goynay webhook-ga gudbinta</t>
+          <t>Waxba lama dooran.</t>
         </is>
       </c>
       <c r="H239" s="13" t="inlineStr">
         <is>
-          <t>alikatisha wavuti ya masuala</t>
+          <t>Hakuna kilichochaguliwa.</t>
         </is>
       </c>
       <c r="I239" s="14" t="inlineStr"/>
@@ -16522,7 +16522,7 @@
     <row r="240" ht="44" customHeight="1">
       <c r="A240" s="11" t="inlineStr">
         <is>
-          <t>action_telegram_connected</t>
+          <t>paste_page_first</t>
         </is>
       </c>
       <c r="B240" s="11" t="inlineStr">
@@ -16532,32 +16532,32 @@
       </c>
       <c r="C240" s="11" t="inlineStr">
         <is>
-          <t>connected Telegram</t>
+          <t>Paste the page first.</t>
         </is>
       </c>
       <c r="D240" s="12" t="inlineStr">
         <is>
-          <t>ቴሌግራም አገናኝቷል</t>
+          <t>መጀመሪያ ገጹን ይለጥፉ።</t>
         </is>
       </c>
       <c r="E240" s="13" t="inlineStr">
         <is>
-          <t>Telegram walqunnamsiise</t>
+          <t>Dursa fuula maxxansi.</t>
         </is>
       </c>
       <c r="F240" s="12" t="inlineStr">
         <is>
-          <t>ቴሌግራም ኣራኺቡ</t>
+          <t>ቅድም ነቲ ገጽ ለጥፍ።</t>
         </is>
       </c>
       <c r="G240" s="13" t="inlineStr">
         <is>
-          <t>Telegram ku xiray</t>
+          <t>Marka hore dhaji bogga.</t>
         </is>
       </c>
       <c r="H240" s="13" t="inlineStr">
         <is>
-          <t>aliunganisha Telegram</t>
+          <t>Bandika ukurasa kwanza.</t>
         </is>
       </c>
       <c r="I240" s="14" t="inlineStr"/>
@@ -16565,7 +16565,7 @@
     <row r="241" ht="44" customHeight="1">
       <c r="A241" s="11" t="inlineStr">
         <is>
-          <t>action_user_created</t>
+          <t>need_url_or_source</t>
         </is>
       </c>
       <c r="B241" s="11" t="inlineStr">
@@ -16575,32 +16575,32 @@
       </c>
       <c r="C241" s="11" t="inlineStr">
         <is>
-          <t>added a colleague</t>
+          <t>An address or some page source, please.</t>
         </is>
       </c>
       <c r="D241" s="12" t="inlineStr">
         <is>
-          <t>ባልደረባ ጨምሯል</t>
+          <t>አድራሻ ወይም የገጽ ምንጭ ያስፈልጋል።</t>
         </is>
       </c>
       <c r="E241" s="13" t="inlineStr">
         <is>
-          <t>hojjetaa dabale</t>
+          <t>Teessoo yookiin madda fuulaa barbaachisa.</t>
         </is>
       </c>
       <c r="F241" s="12" t="inlineStr">
         <is>
-          <t>መሳርሕቲ ወሲኹ</t>
+          <t>ኣድራሻ ወይ ምንጪ ገጽ የድሊ።</t>
         </is>
       </c>
       <c r="G241" s="13" t="inlineStr">
         <is>
-          <t>shaqaale ku daray</t>
+          <t>Cinwaan ama il bog ayaa loo baahan yahay.</t>
         </is>
       </c>
       <c r="H241" s="13" t="inlineStr">
         <is>
-          <t>aliongeza mwenzake</t>
+          <t>Anwani au chanzo cha ukurasa kinahitajika.</t>
         </is>
       </c>
       <c r="I241" s="14" t="inlineStr"/>
@@ -16608,7 +16608,7 @@
     <row r="242" ht="44" customHeight="1">
       <c r="A242" s="11" t="inlineStr">
         <is>
-          <t>action_user_disabled</t>
+          <t>need_question_answer</t>
         </is>
       </c>
       <c r="B242" s="11" t="inlineStr">
@@ -16618,32 +16618,32 @@
       </c>
       <c r="C242" s="11" t="inlineStr">
         <is>
-          <t>disabled an account</t>
+          <t>A question and an answer, please.</t>
         </is>
       </c>
       <c r="D242" s="12" t="inlineStr">
         <is>
-          <t>መለያ አሰናክሏል</t>
+          <t>ጥያቄ እና መልስ ያስፈልጋል።</t>
         </is>
       </c>
       <c r="E242" s="13" t="inlineStr">
         <is>
-          <t>herrega dhaabe</t>
+          <t>Gaaffii fi deebiin barbaachisa.</t>
         </is>
       </c>
       <c r="F242" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ ዓጊቱ</t>
+          <t>ሕቶን መልስን የድሊ።</t>
         </is>
       </c>
       <c r="G242" s="13" t="inlineStr">
         <is>
-          <t>xisaab demiyay</t>
+          <t>Su'aal iyo jawaab ayaa loo baahan yahay.</t>
         </is>
       </c>
       <c r="H242" s="13" t="inlineStr">
         <is>
-          <t>alizima akaunti</t>
+          <t>Swali na jibu vinahitajika.</t>
         </is>
       </c>
       <c r="I242" s="14" t="inlineStr"/>
@@ -16651,7 +16651,7 @@
     <row r="243" ht="44" customHeight="1">
       <c r="A243" s="11" t="inlineStr">
         <is>
-          <t>action_user_enabled</t>
+          <t>invalid_json</t>
         </is>
       </c>
       <c r="B243" s="11" t="inlineStr">
@@ -16661,32 +16661,32 @@
       </c>
       <c r="C243" s="11" t="inlineStr">
         <is>
-          <t>restored an account</t>
+          <t>That is not valid JSON: {error}</t>
         </is>
       </c>
       <c r="D243" s="12" t="inlineStr">
         <is>
-          <t>መለያ መልሷል</t>
+          <t>ትክክለኛ JSON አይደለም፦ {error}</t>
         </is>
       </c>
       <c r="E243" s="13" t="inlineStr">
         <is>
-          <t>herrega deebise</t>
+          <t>JSON sirrii miti: {error}</t>
         </is>
       </c>
       <c r="F243" s="12" t="inlineStr">
         <is>
-          <t>ሕሳብ መሊሱ</t>
+          <t>ቅኑዕ JSON ኣይኮነን፦ {error}</t>
         </is>
       </c>
       <c r="G243" s="13" t="inlineStr">
         <is>
-          <t>xisaab soo celiyay</t>
+          <t>JSON sax ah maaha: {error}</t>
         </is>
       </c>
       <c r="H243" s="13" t="inlineStr">
         <is>
-          <t>alirejesha akaunti</t>
+          <t>Si JSON sahihi: {error}</t>
         </is>
       </c>
       <c r="I243" s="14" t="inlineStr"/>
@@ -16694,7 +16694,7 @@
     <row r="244" ht="44" customHeight="1">
       <c r="A244" s="11" t="inlineStr">
         <is>
-          <t>action_admin_login</t>
+          <t>imported_n_articles</t>
         </is>
       </c>
       <c r="B244" s="11" t="inlineStr">
@@ -16704,32 +16704,32 @@
       </c>
       <c r="C244" s="11" t="inlineStr">
         <is>
-          <t>signed in</t>
+          <t>{n} articles imported</t>
         </is>
       </c>
       <c r="D244" s="12" t="inlineStr">
         <is>
-          <t>ገብቷል</t>
+          <t>{n} ጽሑፎች ገብተዋል</t>
         </is>
       </c>
       <c r="E244" s="13" t="inlineStr">
         <is>
-          <t>seene</t>
+          <t>Barreeffamoonni {n} galfamaniiru</t>
         </is>
       </c>
       <c r="F244" s="12" t="inlineStr">
         <is>
-          <t>ኣትዩ</t>
+          <t>{n} ጽሑፋት ኣትዮም</t>
         </is>
       </c>
       <c r="G244" s="13" t="inlineStr">
         <is>
-          <t>gashay</t>
+          <t>{n} maqaal ayaa la soo geliyay</t>
         </is>
       </c>
       <c r="H244" s="13" t="inlineStr">
         <is>
-          <t>aliingia</t>
+          <t>Makala {n} zimeingizwa</t>
         </is>
       </c>
       <c r="I244" s="14" t="inlineStr"/>
@@ -16737,7 +16737,7 @@
     <row r="245" ht="44" customHeight="1">
       <c r="A245" s="11" t="inlineStr">
         <is>
-          <t>action_password_changed</t>
+          <t>embed_copied</t>
         </is>
       </c>
       <c r="B245" s="11" t="inlineStr">
@@ -16747,32 +16747,32 @@
       </c>
       <c r="C245" s="11" t="inlineStr">
         <is>
-          <t>changed their password</t>
+          <t>Embed code copied</t>
         </is>
       </c>
       <c r="D245" s="12" t="inlineStr">
         <is>
-          <t>የይለፍ ቃል ቀይሯል</t>
+          <t>የመክተቻ ኮዱ ተቀድቷል</t>
         </is>
       </c>
       <c r="E245" s="13" t="inlineStr">
         <is>
-          <t>jecha darbii jijjiire</t>
+          <t>Koodiin maxxansaa garagalfameera</t>
         </is>
       </c>
       <c r="F245" s="12" t="inlineStr">
         <is>
-          <t>መሕለፊ ቃል ቀዪሩ</t>
+          <t>ናይ ምትእትታው ኮድ ተቐዲሑ</t>
         </is>
       </c>
       <c r="G245" s="13" t="inlineStr">
         <is>
-          <t>beddelay furihiisa</t>
+          <t>Koodhka gelinta waa la koobiyay</t>
         </is>
       </c>
       <c r="H245" s="13" t="inlineStr">
         <is>
-          <t>alibadilisha nenosiri lake</t>
+          <t>Msimbo wa kupachika umenakiliwa</t>
         </is>
       </c>
       <c r="I245" s="14" t="inlineStr"/>
@@ -16780,7 +16780,7 @@
     <row r="246" ht="44" customHeight="1">
       <c r="A246" s="11" t="inlineStr">
         <is>
-          <t>nothing_yet</t>
+          <t>copy_manually</t>
         </is>
       </c>
       <c r="B246" s="11" t="inlineStr">
@@ -16790,32 +16790,32 @@
       </c>
       <c r="C246" s="11" t="inlineStr">
         <is>
-          <t>Nothing yet.</t>
+          <t>Select the text and copy it manually.</t>
         </is>
       </c>
       <c r="D246" s="12" t="inlineStr">
         <is>
-          <t>እስካሁን ምንም የለም።</t>
+          <t>ጽሑፉን መርጠው በእጅ ይቅዱ።</t>
         </is>
       </c>
       <c r="E246" s="13" t="inlineStr">
         <is>
-          <t>Ammaaf homaa hin jiru.</t>
+          <t>Barreeffama filadhuutii harkaan garagalchi.</t>
         </is>
       </c>
       <c r="F246" s="12" t="inlineStr">
         <is>
-          <t>ክሳብ ሕጂ ዋላ ሓደ የለን።</t>
+          <t>ነቲ ጽሑፍ መሪጽካ ብኢድ ቅዳሕ።</t>
         </is>
       </c>
       <c r="G246" s="13" t="inlineStr">
         <is>
-          <t>Weli waxba ma jiraan.</t>
+          <t>Dooro qoraalka oo gacanta ku koobi.</t>
         </is>
       </c>
       <c r="H246" s="13" t="inlineStr">
         <is>
-          <t>Bado hakuna.</t>
+          <t>Chagua maandishi na unakili kwa mkono.</t>
         </is>
       </c>
       <c r="I246" s="14" t="inlineStr"/>
@@ -16823,7 +16823,7 @@
     <row r="247" ht="44" customHeight="1">
       <c r="A247" s="11" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>telegram_connected</t>
         </is>
       </c>
       <c r="B247" s="11" t="inlineStr">
@@ -16833,32 +16833,32 @@
       </c>
       <c r="C247" s="11" t="inlineStr">
         <is>
-          <t>Unavailable.</t>
+          <t>Telegram connected</t>
         </is>
       </c>
       <c r="D247" s="12" t="inlineStr">
         <is>
-          <t>አይገኝም።</t>
+          <t>Telegram ተገናኝቷል</t>
         </is>
       </c>
       <c r="E247" s="13" t="inlineStr">
         <is>
-          <t>Hin argamu.</t>
+          <t>Telegram walqabsiifameera</t>
         </is>
       </c>
       <c r="F247" s="12" t="inlineStr">
         <is>
-          <t>ኣይርከብን።</t>
+          <t>Telegram ተራኺቡ</t>
         </is>
       </c>
       <c r="G247" s="13" t="inlineStr">
         <is>
-          <t>Lama heli karo.</t>
+          <t>Telegram waa la xiriiriyay</t>
         </is>
       </c>
       <c r="H247" s="13" t="inlineStr">
         <is>
-          <t>Haipatikani.</t>
+          <t>Telegram imeunganishwa</t>
         </is>
       </c>
       <c r="I247" s="14" t="inlineStr"/>
@@ -16866,7 +16866,7 @@
     <row r="248" ht="44" customHeight="1">
       <c r="A248" s="11" t="inlineStr">
         <is>
-          <t>just_now</t>
+          <t>action_document_created</t>
         </is>
       </c>
       <c r="B248" s="11" t="inlineStr">
@@ -16876,32 +16876,32 @@
       </c>
       <c r="C248" s="11" t="inlineStr">
         <is>
-          <t>just now</t>
+          <t>added an article</t>
         </is>
       </c>
       <c r="D248" s="12" t="inlineStr">
         <is>
-          <t>አሁን</t>
+          <t>ጽሑፍ ጨምሯል</t>
         </is>
       </c>
       <c r="E248" s="13" t="inlineStr">
         <is>
-          <t>amma</t>
+          <t>barruu dabale</t>
         </is>
       </c>
       <c r="F248" s="12" t="inlineStr">
         <is>
-          <t>ሕጂ</t>
+          <t>ጽሑፍ ወሲኹ</t>
         </is>
       </c>
       <c r="G248" s="13" t="inlineStr">
         <is>
-          <t>hadda</t>
+          <t>maqaal ku daray</t>
         </is>
       </c>
       <c r="H248" s="13" t="inlineStr">
         <is>
-          <t>sasa hivi</t>
+          <t>aliongeza makala</t>
         </is>
       </c>
       <c r="I248" s="14" t="inlineStr"/>
@@ -16909,7 +16909,7 @@
     <row r="249" ht="44" customHeight="1">
       <c r="A249" s="11" t="inlineStr">
         <is>
-          <t>n_min_ago</t>
+          <t>action_document_updated</t>
         </is>
       </c>
       <c r="B249" s="11" t="inlineStr">
@@ -16919,32 +16919,32 @@
       </c>
       <c r="C249" s="11" t="inlineStr">
         <is>
-          <t>{n} min ago</t>
+          <t>edited an article</t>
         </is>
       </c>
       <c r="D249" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ደቂቃ በፊት</t>
+          <t>ጽሑፍ አርሟል</t>
         </is>
       </c>
       <c r="E249" s="13" t="inlineStr">
         <is>
-          <t>daqiiqaa {n} dura</t>
+          <t>barruu gulaale</t>
         </is>
       </c>
       <c r="F249" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ደቒቕ</t>
+          <t>ጽሑፍ ኣርሚዑ</t>
         </is>
       </c>
       <c r="G249" s="13" t="inlineStr">
         <is>
-          <t>{n} daqiiqo ka hor</t>
+          <t>maqaal wax ka beddelay</t>
         </is>
       </c>
       <c r="H249" s="13" t="inlineStr">
         <is>
-          <t>dakika {n} zilizopita</t>
+          <t>alihariri makala</t>
         </is>
       </c>
       <c r="I249" s="14" t="inlineStr"/>
@@ -16952,7 +16952,7 @@
     <row r="250" ht="44" customHeight="1">
       <c r="A250" s="11" t="inlineStr">
         <is>
-          <t>n_h_ago</t>
+          <t>action_document_deleted</t>
         </is>
       </c>
       <c r="B250" s="11" t="inlineStr">
@@ -16962,32 +16962,32 @@
       </c>
       <c r="C250" s="11" t="inlineStr">
         <is>
-          <t>{n} h ago</t>
+          <t>deleted an article</t>
         </is>
       </c>
       <c r="D250" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ሰዓት በፊት</t>
+          <t>ጽሑፍ ሰርዟል</t>
         </is>
       </c>
       <c r="E250" s="13" t="inlineStr">
         <is>
-          <t>sa'aatii {n} dura</t>
+          <t>barruu haqe</t>
         </is>
       </c>
       <c r="F250" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ሰዓት</t>
+          <t>ጽሑፍ ደምሲሱ</t>
         </is>
       </c>
       <c r="G250" s="13" t="inlineStr">
         <is>
-          <t>{n} saac ka hor</t>
+          <t>maqaal tirtiray</t>
         </is>
       </c>
       <c r="H250" s="13" t="inlineStr">
         <is>
-          <t>saa {n} zilizopita</t>
+          <t>alifuta makala</t>
         </is>
       </c>
       <c r="I250" s="14" t="inlineStr"/>
@@ -16995,7 +16995,7 @@
     <row r="251" ht="44" customHeight="1">
       <c r="A251" s="11" t="inlineStr">
         <is>
-          <t>n_d_ago</t>
+          <t>action_documents_bulk_imported</t>
         </is>
       </c>
       <c r="B251" s="11" t="inlineStr">
@@ -17005,32 +17005,32 @@
       </c>
       <c r="C251" s="11" t="inlineStr">
         <is>
-          <t>{n} d ago</t>
+          <t>imported articles</t>
         </is>
       </c>
       <c r="D251" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ቀን በፊት</t>
+          <t>ጽሑፎችን አስገብቷል</t>
         </is>
       </c>
       <c r="E251" s="13" t="inlineStr">
         <is>
-          <t>guyyaa {n} dura</t>
+          <t>barruulee galche</t>
         </is>
       </c>
       <c r="F251" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} መዓልቲ</t>
+          <t>ጽሑፋት ኣእትዩ</t>
         </is>
       </c>
       <c r="G251" s="13" t="inlineStr">
         <is>
-          <t>{n} maalmood ka hor</t>
+          <t>maqaallo soo dhoofiyay</t>
         </is>
       </c>
       <c r="H251" s="13" t="inlineStr">
         <is>
-          <t>siku {n} zilizopita</t>
+          <t>aliagiza makala</t>
         </is>
       </c>
       <c r="I251" s="14" t="inlineStr"/>
@@ -17038,7 +17038,7 @@
     <row r="252" ht="44" customHeight="1">
       <c r="A252" s="11" t="inlineStr">
         <is>
-          <t>channel_all_from</t>
+          <t>action_handoff_closed</t>
         </is>
       </c>
       <c r="B252" s="11" t="inlineStr">
@@ -17048,32 +17048,32 @@
       </c>
       <c r="C252" s="11" t="inlineStr">
         <is>
-          <t>All {n} conversations came from {label}.</t>
+          <t>closed an escalation</t>
         </is>
       </c>
       <c r="D252" s="12" t="inlineStr">
         <is>
-          <t>ሁሉም {n} ውይይቶች ከ{label} መጥተዋል።</t>
+          <t>ጉዳይ ዘግቷል</t>
         </is>
       </c>
       <c r="E252" s="13" t="inlineStr">
         <is>
-          <t>Mariin {n} hundi {label} irraa dhufe.</t>
+          <t>dhimma cufe</t>
         </is>
       </c>
       <c r="F252" s="12" t="inlineStr">
         <is>
-          <t>ኩሎም {n} ዝርርባት ካብ {label} መጺኦም።</t>
+          <t>ጉዳይ ዓጺዩ</t>
         </is>
       </c>
       <c r="G252" s="13" t="inlineStr">
         <is>
-          <t>Dhammaan {n} wadahadal waxay ka yimaadeen {label}.</t>
+          <t>arrin xiray</t>
         </is>
       </c>
       <c r="H252" s="13" t="inlineStr">
         <is>
-          <t>Mazungumzo yote {n} yalitoka {label}.</t>
+          <t>alifunga suala</t>
         </is>
       </c>
       <c r="I252" s="14" t="inlineStr"/>
@@ -17081,7 +17081,7 @@
     <row r="253" ht="44" customHeight="1">
       <c r="A253" s="11" t="inlineStr">
         <is>
-          <t>channel_live</t>
+          <t>action_handoff_reopened</t>
         </is>
       </c>
       <c r="B253" s="11" t="inlineStr">
@@ -17091,32 +17091,32 @@
       </c>
       <c r="C253" s="11" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>reopened an escalation</t>
         </is>
       </c>
       <c r="D253" s="12" t="inlineStr">
         <is>
-          <t>በሥራ ላይ</t>
+          <t>ጉዳይ በድጋሚ ከፍቷል</t>
         </is>
       </c>
       <c r="E253" s="13" t="inlineStr">
         <is>
-          <t>Hojiirra</t>
+          <t>dhimma irra deebi'ee bane</t>
         </is>
       </c>
       <c r="F253" s="12" t="inlineStr">
         <is>
-          <t>ኣብ ስራሕ</t>
+          <t>ጉዳይ ደጊሙ ከፊቱ</t>
         </is>
       </c>
       <c r="G253" s="13" t="inlineStr">
         <is>
-          <t>Shaqeynaya</t>
+          <t>arrin dib u furay</t>
         </is>
       </c>
       <c r="H253" s="13" t="inlineStr">
         <is>
-          <t>Moja kwa Moja</t>
+          <t>alifungua tena suala</t>
         </is>
       </c>
       <c r="I253" s="14" t="inlineStr"/>
@@ -17124,7 +17124,7 @@
     <row r="254" ht="44" customHeight="1">
       <c r="A254" s="11" t="inlineStr">
         <is>
-          <t>channel_ready</t>
+          <t>action_handoff_webhook_connected</t>
         </is>
       </c>
       <c r="B254" s="11" t="inlineStr">
@@ -17134,32 +17134,32 @@
       </c>
       <c r="C254" s="11" t="inlineStr">
         <is>
-          <t>Ready to connect</t>
+          <t>connected the escalation webhook</t>
         </is>
       </c>
       <c r="D254" s="12" t="inlineStr">
         <is>
-          <t>ለመገናኘት ዝግጁ</t>
+          <t>የማሸጋገሪያ ዌብሁክ አገናኝቷል</t>
         </is>
       </c>
       <c r="E254" s="13" t="inlineStr">
         <is>
-          <t>Walqunnamuuf qophaa'aa</t>
+          <t>webhook dabarsaa walqunnamsiise</t>
         </is>
       </c>
       <c r="F254" s="12" t="inlineStr">
         <is>
-          <t>ንምርኻብ ድሉው</t>
+          <t>ዌብሁክ ምትሕልላፍ ኣራኺቡ</t>
         </is>
       </c>
       <c r="G254" s="13" t="inlineStr">
         <is>
-          <t>Diyaar u ah xiriirka</t>
+          <t>ku xiray webhook-ga gudbinta</t>
         </is>
       </c>
       <c r="H254" s="13" t="inlineStr">
         <is>
-          <t>Tayari Kuunganishwa</t>
+          <t>aliunganisha wavuti ya masuala</t>
         </is>
       </c>
       <c r="I254" s="14" t="inlineStr"/>
@@ -17167,7 +17167,7 @@
     <row r="255" ht="44" customHeight="1">
       <c r="A255" s="11" t="inlineStr">
         <is>
-          <t>channel_needs_setup</t>
+          <t>action_handoff_webhook_disconnected</t>
         </is>
       </c>
       <c r="B255" s="11" t="inlineStr">
@@ -17177,32 +17177,32 @@
       </c>
       <c r="C255" s="11" t="inlineStr">
         <is>
-          <t>Needs setup</t>
+          <t>disconnected the escalation webhook</t>
         </is>
       </c>
       <c r="D255" s="12" t="inlineStr">
         <is>
-          <t>ማዋቀር ይፈልጋል</t>
+          <t>የማሸጋገሪያ ዌብሁክ አቋርጧል</t>
         </is>
       </c>
       <c r="E255" s="13" t="inlineStr">
         <is>
-          <t>Qindeessuu barbaada</t>
+          <t>webhook dabarsaa addaan kute</t>
         </is>
       </c>
       <c r="F255" s="12" t="inlineStr">
         <is>
-          <t>ምድላው የድልዮ</t>
+          <t>ዌብሁክ ምትሕልላፍ ቆሪጹ</t>
         </is>
       </c>
       <c r="G255" s="13" t="inlineStr">
         <is>
-          <t>Waxay u baahan tahay dejin</t>
+          <t>goynay webhook-ga gudbinta</t>
         </is>
       </c>
       <c r="H255" s="13" t="inlineStr">
         <is>
-          <t>Inahitaji Kusanidiwa</t>
+          <t>alikatisha wavuti ya masuala</t>
         </is>
       </c>
       <c r="I255" s="14" t="inlineStr"/>
@@ -17210,7 +17210,7 @@
     <row r="256" ht="44" customHeight="1">
       <c r="A256" s="11" t="inlineStr">
         <is>
-          <t>share_by_channel</t>
+          <t>action_telegram_connected</t>
         </is>
       </c>
       <c r="B256" s="11" t="inlineStr">
@@ -17220,32 +17220,32 @@
       </c>
       <c r="C256" s="11" t="inlineStr">
         <is>
-          <t>Share of conversations by channel</t>
+          <t>connected Telegram</t>
         </is>
       </c>
       <c r="D256" s="12" t="inlineStr">
         <is>
-          <t>በመስመር የተከፋፈሉ ውይይቶች ድርሻ</t>
+          <t>ቴሌግራም አገናኝቷል</t>
         </is>
       </c>
       <c r="E256" s="13" t="inlineStr">
         <is>
-          <t>Qooda marii karaa tokkoon tokkoon isaanii</t>
+          <t>Telegram walqunnamsiise</t>
         </is>
       </c>
       <c r="F256" s="12" t="inlineStr">
         <is>
-          <t>ብመስመር ዝተኸፋፈለ ግደ ዝርርባት</t>
+          <t>ቴሌግራም ኣራኺቡ</t>
         </is>
       </c>
       <c r="G256" s="13" t="inlineStr">
         <is>
-          <t>Qaybta wadahadallada kanaalka</t>
+          <t>Telegram ku xiray</t>
         </is>
       </c>
       <c r="H256" s="13" t="inlineStr">
         <is>
-          <t>Mgawanyo wa Mazungumzo kwa Njia</t>
+          <t>aliunganisha Telegram</t>
         </is>
       </c>
       <c r="I256" s="14" t="inlineStr"/>
@@ -17253,7 +17253,7 @@
     <row r="257" ht="44" customHeight="1">
       <c r="A257" s="11" t="inlineStr">
         <is>
-          <t>up_to_date</t>
+          <t>action_user_created</t>
         </is>
       </c>
       <c r="B257" s="11" t="inlineStr">
@@ -17263,32 +17263,32 @@
       </c>
       <c r="C257" s="11" t="inlineStr">
         <is>
-          <t>Up to date</t>
+          <t>added a colleague</t>
         </is>
       </c>
       <c r="D257" s="12" t="inlineStr">
         <is>
-          <t>የተዘመነ</t>
+          <t>ባልደረባ ጨምሯል</t>
         </is>
       </c>
       <c r="E257" s="13" t="inlineStr">
         <is>
-          <t>Haaraa</t>
+          <t>hojjetaa dabale</t>
         </is>
       </c>
       <c r="F257" s="12" t="inlineStr">
         <is>
-          <t>ዝተሓደሰ</t>
+          <t>መሳርሕቲ ወሲኹ</t>
         </is>
       </c>
       <c r="G257" s="13" t="inlineStr">
         <is>
-          <t>La cusbooneysiiyay</t>
+          <t>shaqaale ku daray</t>
         </is>
       </c>
       <c r="H257" s="13" t="inlineStr">
         <is>
-          <t>Ni ya Hivi Karibuni</t>
+          <t>aliongeza mwenzake</t>
         </is>
       </c>
       <c r="I257" s="14" t="inlineStr"/>
@@ -17296,7 +17296,7 @@
     <row r="258" ht="44" customHeight="1">
       <c r="A258" s="11" t="inlineStr">
         <is>
-          <t>updated_m_ago</t>
+          <t>action_user_disabled</t>
         </is>
       </c>
       <c r="B258" s="11" t="inlineStr">
@@ -17306,32 +17306,32 @@
       </c>
       <c r="C258" s="11" t="inlineStr">
         <is>
-          <t>Updated {n}m ago</t>
+          <t>disabled an account</t>
         </is>
       </c>
       <c r="D258" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ደቂቃ በፊት ተዘምኗል</t>
+          <t>መለያ አሰናክሏል</t>
         </is>
       </c>
       <c r="E258" s="13" t="inlineStr">
         <is>
-          <t>Daqiiqaa {n} dura haaromfame</t>
+          <t>herrega dhaabe</t>
         </is>
       </c>
       <c r="F258" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ደቒቕ ተሓዲሱ</t>
+          <t>ሕሳብ ዓጊቱ</t>
         </is>
       </c>
       <c r="G258" s="13" t="inlineStr">
         <is>
-          <t>La cusbooneysiiyay {n}daq ka hor</t>
+          <t>xisaab demiyay</t>
         </is>
       </c>
       <c r="H258" s="13" t="inlineStr">
         <is>
-          <t>Imesasishwa dakika {n} zilizopita</t>
+          <t>alizima akaunti</t>
         </is>
       </c>
       <c r="I258" s="14" t="inlineStr"/>
@@ -17339,7 +17339,7 @@
     <row r="259" ht="44" customHeight="1">
       <c r="A259" s="11" t="inlineStr">
         <is>
-          <t>updated_h_ago</t>
+          <t>action_user_enabled</t>
         </is>
       </c>
       <c r="B259" s="11" t="inlineStr">
@@ -17349,32 +17349,32 @@
       </c>
       <c r="C259" s="11" t="inlineStr">
         <is>
-          <t>Updated {n}h ago</t>
+          <t>restored an account</t>
         </is>
       </c>
       <c r="D259" s="12" t="inlineStr">
         <is>
-          <t>ከ{n} ሰዓት በፊት ተዘምኗል</t>
+          <t>መለያ መልሷል</t>
         </is>
       </c>
       <c r="E259" s="13" t="inlineStr">
         <is>
-          <t>Sa'aatii {n} dura haaromfame</t>
+          <t>herrega deebise</t>
         </is>
       </c>
       <c r="F259" s="12" t="inlineStr">
         <is>
-          <t>ቅድሚ {n} ሰዓት ተሓዲሱ</t>
+          <t>ሕሳብ መሊሱ</t>
         </is>
       </c>
       <c r="G259" s="13" t="inlineStr">
         <is>
-          <t>La cusbooneysiiyay {n}saac ka hor</t>
+          <t>xisaab soo celiyay</t>
         </is>
       </c>
       <c r="H259" s="13" t="inlineStr">
         <is>
-          <t>Imesasishwa saa {n} zilizopita</t>
+          <t>alirejesha akaunti</t>
         </is>
       </c>
       <c r="I259" s="14" t="inlineStr"/>
@@ -17382,7 +17382,7 @@
     <row r="260" ht="44" customHeight="1">
       <c r="A260" s="11" t="inlineStr">
         <is>
-          <t>queue</t>
+          <t>action_admin_login</t>
         </is>
       </c>
       <c r="B260" s="11" t="inlineStr">
@@ -17392,32 +17392,32 @@
       </c>
       <c r="C260" s="11" t="inlineStr">
         <is>
-          <t>Queue</t>
+          <t>signed in</t>
         </is>
       </c>
       <c r="D260" s="12" t="inlineStr">
         <is>
-          <t>ወረፋ</t>
+          <t>ገብቷል</t>
         </is>
       </c>
       <c r="E260" s="13" t="inlineStr">
         <is>
-          <t>Sararaa</t>
+          <t>seene</t>
         </is>
       </c>
       <c r="F260" s="12" t="inlineStr">
         <is>
-          <t>ሪጋ</t>
+          <t>ኣትዩ</t>
         </is>
       </c>
       <c r="G260" s="13" t="inlineStr">
         <is>
-          <t>Safka</t>
+          <t>gashay</t>
         </is>
       </c>
       <c r="H260" s="13" t="inlineStr">
         <is>
-          <t>Foleni</t>
+          <t>aliingia</t>
         </is>
       </c>
       <c r="I260" s="14" t="inlineStr"/>
@@ -17425,7 +17425,7 @@
     <row r="261" ht="44" customHeight="1">
       <c r="A261" s="11" t="inlineStr">
         <is>
-          <t>collapse</t>
+          <t>action_password_changed</t>
         </is>
       </c>
       <c r="B261" s="11" t="inlineStr">
@@ -17435,32 +17435,32 @@
       </c>
       <c r="C261" s="11" t="inlineStr">
         <is>
-          <t>Collapse</t>
+          <t>changed their password</t>
         </is>
       </c>
       <c r="D261" s="12" t="inlineStr">
         <is>
-          <t>አጥብብ</t>
+          <t>የይለፍ ቃል ቀይሯል</t>
         </is>
       </c>
       <c r="E261" s="13" t="inlineStr">
         <is>
-          <t>Xiqqeessi</t>
+          <t>jecha darbii jijjiire</t>
         </is>
       </c>
       <c r="F261" s="12" t="inlineStr">
         <is>
-          <t>ኣጽብብ</t>
+          <t>መሕለፊ ቃል ቀዪሩ</t>
         </is>
       </c>
       <c r="G261" s="13" t="inlineStr">
         <is>
-          <t>Yaree</t>
+          <t>beddelay furihiisa</t>
         </is>
       </c>
       <c r="H261" s="13" t="inlineStr">
         <is>
-          <t>Kunja</t>
+          <t>alibadilisha nenosiri lake</t>
         </is>
       </c>
       <c r="I261" s="14" t="inlineStr"/>
@@ -17468,7 +17468,7 @@
     <row r="262" ht="44" customHeight="1">
       <c r="A262" s="11" t="inlineStr">
         <is>
-          <t>expand</t>
+          <t>nothing_yet</t>
         </is>
       </c>
       <c r="B262" s="11" t="inlineStr">
@@ -17478,32 +17478,32 @@
       </c>
       <c r="C262" s="11" t="inlineStr">
         <is>
-          <t>Expand</t>
+          <t>Nothing yet.</t>
         </is>
       </c>
       <c r="D262" s="12" t="inlineStr">
         <is>
-          <t>አስፋ</t>
+          <t>እስካሁን ምንም የለም።</t>
         </is>
       </c>
       <c r="E262" s="13" t="inlineStr">
         <is>
-          <t>Balleessi</t>
+          <t>Ammaaf homaa hin jiru.</t>
         </is>
       </c>
       <c r="F262" s="12" t="inlineStr">
         <is>
-          <t>ኣስፍሕ</t>
+          <t>ክሳብ ሕጂ ዋላ ሓደ የለን።</t>
         </is>
       </c>
       <c r="G262" s="13" t="inlineStr">
         <is>
-          <t>Balaadhi</t>
+          <t>Weli waxba ma jiraan.</t>
         </is>
       </c>
       <c r="H262" s="13" t="inlineStr">
         <is>
-          <t>Panua</t>
+          <t>Bado hakuna.</t>
         </is>
       </c>
       <c r="I262" s="14" t="inlineStr"/>
@@ -17511,7 +17511,7 @@
     <row r="263" ht="44" customHeight="1">
       <c r="A263" s="11" t="inlineStr">
         <is>
-          <t>collapse_or_expand</t>
+          <t>unavailable</t>
         </is>
       </c>
       <c r="B263" s="11" t="inlineStr">
@@ -17521,32 +17521,32 @@
       </c>
       <c r="C263" s="11" t="inlineStr">
         <is>
-          <t>Collapse or expand the sidebar</t>
+          <t>Unavailable.</t>
         </is>
       </c>
       <c r="D263" s="12" t="inlineStr">
         <is>
-          <t>የጎን አሞሌውን አጥብብ ወይም አስፋ</t>
+          <t>አይገኝም።</t>
         </is>
       </c>
       <c r="E263" s="13" t="inlineStr">
         <is>
-          <t>Cinaacha xiqqeessi ykn balleessi</t>
+          <t>Hin argamu.</t>
         </is>
       </c>
       <c r="F263" s="12" t="inlineStr">
         <is>
-          <t>ናይ ጎኒ መስመር ኣጽብብ ወይ ኣስፍሕ</t>
+          <t>ኣይርከብን።</t>
         </is>
       </c>
       <c r="G263" s="13" t="inlineStr">
         <is>
-          <t>Yaree ama balaadhi dhinaca</t>
+          <t>Lama heli karo.</t>
         </is>
       </c>
       <c r="H263" s="13" t="inlineStr">
         <is>
-          <t>Kunja au panua upande wa kando</t>
+          <t>Haipatikani.</t>
         </is>
       </c>
       <c r="I263" s="14" t="inlineStr"/>
@@ -17554,7 +17554,7 @@
     <row r="264" ht="44" customHeight="1">
       <c r="A264" s="11" t="inlineStr">
         <is>
-          <t>show_hide_channels</t>
+          <t>just_now</t>
         </is>
       </c>
       <c r="B264" s="11" t="inlineStr">
@@ -17564,32 +17564,32 @@
       </c>
       <c r="C264" s="11" t="inlineStr">
         <is>
-          <t>Show or hide the channel list</t>
+          <t>just now</t>
         </is>
       </c>
       <c r="D264" s="12" t="inlineStr">
         <is>
-          <t>የመስመሮችን ዝርዝር አሳይ ወይም ደብቅ</t>
+          <t>አሁን</t>
         </is>
       </c>
       <c r="E264" s="13" t="inlineStr">
         <is>
-          <t>Tarreeffama karaalee agarsiisi ykn dhoksi</t>
+          <t>amma</t>
         </is>
       </c>
       <c r="F264" s="12" t="inlineStr">
         <is>
-          <t>ዝርዝር መስመራት ኣርኢ ወይ ሕባእ</t>
+          <t>ሕጂ</t>
         </is>
       </c>
       <c r="G264" s="13" t="inlineStr">
         <is>
-          <t>Muuji ama qari liiska kanaalada</t>
+          <t>hadda</t>
         </is>
       </c>
       <c r="H264" s="13" t="inlineStr">
         <is>
-          <t>Onyesha au ficha orodha ya njia</t>
+          <t>sasa hivi</t>
         </is>
       </c>
       <c r="I264" s="14" t="inlineStr"/>
@@ -17597,7 +17597,7 @@
     <row r="265" ht="44" customHeight="1">
       <c r="A265" s="11" t="inlineStr">
         <is>
-          <t>today</t>
+          <t>n_min_ago</t>
         </is>
       </c>
       <c r="B265" s="11" t="inlineStr">
@@ -17607,32 +17607,32 @@
       </c>
       <c r="C265" s="11" t="inlineStr">
         <is>
-          <t>Today</t>
+          <t>{n} min ago</t>
         </is>
       </c>
       <c r="D265" s="12" t="inlineStr">
         <is>
-          <t>ዛሬ</t>
+          <t>ከ{n} ደቂቃ በፊት</t>
         </is>
       </c>
       <c r="E265" s="13" t="inlineStr">
         <is>
-          <t>Har'a</t>
+          <t>daqiiqaa {n} dura</t>
         </is>
       </c>
       <c r="F265" s="12" t="inlineStr">
         <is>
-          <t>ሎሚ</t>
+          <t>ቅድሚ {n} ደቒቕ</t>
         </is>
       </c>
       <c r="G265" s="13" t="inlineStr">
         <is>
-          <t>Maanta</t>
+          <t>{n} daqiiqo ka hor</t>
         </is>
       </c>
       <c r="H265" s="13" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>dakika {n} zilizopita</t>
         </is>
       </c>
       <c r="I265" s="14" t="inlineStr"/>
@@ -17640,7 +17640,7 @@
     <row r="266" ht="44" customHeight="1">
       <c r="A266" s="11" t="inlineStr">
         <is>
-          <t>yesterday</t>
+          <t>n_h_ago</t>
         </is>
       </c>
       <c r="B266" s="11" t="inlineStr">
@@ -17650,32 +17650,32 @@
       </c>
       <c r="C266" s="11" t="inlineStr">
         <is>
-          <t>Yesterday</t>
+          <t>{n} h ago</t>
         </is>
       </c>
       <c r="D266" s="12" t="inlineStr">
         <is>
-          <t>ትናንት</t>
+          <t>ከ{n} ሰዓት በፊት</t>
         </is>
       </c>
       <c r="E266" s="13" t="inlineStr">
         <is>
-          <t>Kaleessa</t>
+          <t>sa'aatii {n} dura</t>
         </is>
       </c>
       <c r="F266" s="12